--- a/BIRLA_GROUP_Technical_Metrics.xlsx
+++ b/BIRLA_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="287" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="293" uniqueCount="77">
   <si>
     <t>Symbol</t>
   </si>
@@ -166,12 +166,12 @@
     <t>Yes</t>
   </si>
   <si>
+    <t>DOWN</t>
+  </si>
+  <si>
     <t>UP</t>
   </si>
   <si>
-    <t>DOWN</t>
-  </si>
-  <si>
     <t>▶  SIGNAL EVENTS (vs Previous Run)</t>
   </si>
   <si>
@@ -190,19 +190,28 @@
     <t>Curr Value</t>
   </si>
   <si>
-    <t>Left 52W High Zone</t>
-  </si>
-  <si>
-    <t>-1.8% → -2.9%</t>
-  </si>
-  <si>
-    <t>⚪ NEUTRAL</t>
-  </si>
-  <si>
-    <t>-1.8%</t>
-  </si>
-  <si>
-    <t>-2.9%</t>
+    <t>RSI Momentum</t>
+  </si>
+  <si>
+    <t>50.5 → 38.5</t>
+  </si>
+  <si>
+    <t>🔴 BEARISH</t>
+  </si>
+  <si>
+    <t>50.5</t>
+  </si>
+  <si>
+    <t>38.5</t>
+  </si>
+  <si>
+    <t>56.9 → 49.8</t>
+  </si>
+  <si>
+    <t>56.9</t>
+  </si>
+  <si>
+    <t>49.8</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -254,7 +263,7 @@
     <numFmt numFmtId="166" formatCode="0.0"/>
     <numFmt numFmtId="167" formatCode="0.00%"/>
   </numFmts>
-  <fonts count="7">
+  <fonts count="6">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -288,13 +297,6 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF1F4E79"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <color rgb="FF9C0006"/>
       <name val="Calibri"/>
       <family val="2"/>
@@ -308,7 +310,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="10">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -330,12 +332,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF4A6FA5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDDEBF7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -427,12 +423,12 @@
     <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="6" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
@@ -441,7 +437,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="167" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
@@ -940,10 +936,10 @@
         <v>45</v>
       </c>
       <c r="C2">
-        <v>395</v>
+        <v>378.8</v>
       </c>
       <c r="D2">
-        <v>-1.25</v>
+        <v>-4.1</v>
       </c>
       <c r="E2">
         <v>424.7</v>
@@ -952,46 +948,46 @@
         <v>278.9</v>
       </c>
       <c r="G2">
-        <v>-6.99</v>
+        <v>-10.81</v>
       </c>
       <c r="H2">
-        <v>41.63</v>
+        <v>35.82</v>
       </c>
       <c r="I2">
-        <v>-2.45</v>
+        <v>-6.06</v>
       </c>
       <c r="J2">
-        <v>-3.12</v>
+        <v>-5.54</v>
       </c>
       <c r="K2">
-        <v>7.28</v>
+        <v>1.34</v>
       </c>
       <c r="L2">
-        <v>36.35</v>
+        <v>31.69</v>
       </c>
       <c r="M2">
-        <v>28.45</v>
+        <v>27.01</v>
       </c>
       <c r="N2">
         <v>74</v>
       </c>
       <c r="O2">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="P2">
-        <v>399.04</v>
+        <v>394.15</v>
       </c>
       <c r="Q2">
-        <v>403.55</v>
+        <v>402.55</v>
       </c>
       <c r="R2">
-        <v>404.15</v>
+        <v>403.53</v>
       </c>
       <c r="S2">
-        <v>362.39</v>
+        <v>362.54</v>
       </c>
       <c r="T2">
-        <v>9</v>
+        <v>4.49</v>
       </c>
       <c r="U2" t="s">
         <v>46</v>
@@ -1006,43 +1002,43 @@
         <v>2</v>
       </c>
       <c r="Y2">
-        <v>43.4</v>
+        <v>33.83</v>
       </c>
       <c r="Z2">
-        <v>-1.49</v>
+        <v>-3.16</v>
       </c>
       <c r="AA2">
-        <v>-0.22</v>
+        <v>-0.8100000000000001</v>
       </c>
       <c r="AB2">
-        <v>-1.27</v>
+        <v>-2.35</v>
       </c>
       <c r="AC2">
-        <v>26.21</v>
+        <v>14.49</v>
       </c>
       <c r="AD2">
-        <v>29.68</v>
+        <v>23.22</v>
       </c>
       <c r="AE2">
-        <v>8.960000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AF2">
-        <v>-44</v>
+        <v>-12.04</v>
       </c>
       <c r="AG2">
-        <v>415.99</v>
+        <v>419.13</v>
       </c>
       <c r="AH2">
-        <v>391.11</v>
+        <v>385.98</v>
       </c>
       <c r="AI2">
-        <v>389.09</v>
+        <v>416.61</v>
       </c>
       <c r="AJ2" t="s">
         <v>48</v>
       </c>
       <c r="AK2">
-        <v>24.53</v>
+        <v>29.09</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1053,58 +1049,58 @@
         <v>45</v>
       </c>
       <c r="C3">
-        <v>50.44</v>
+        <v>49.02</v>
       </c>
       <c r="D3">
-        <v>-0.88</v>
+        <v>-2.82</v>
       </c>
       <c r="E3">
         <v>93.48</v>
       </c>
       <c r="F3">
-        <v>50.41</v>
+        <v>49.02</v>
       </c>
       <c r="G3">
-        <v>-46.04</v>
+        <v>-47.56</v>
       </c>
       <c r="H3">
-        <v>0.06</v>
+        <v>0</v>
       </c>
       <c r="I3">
-        <v>-4.78</v>
+        <v>-7.87</v>
       </c>
       <c r="J3">
-        <v>-11.09</v>
+        <v>-12.43</v>
       </c>
       <c r="K3">
-        <v>-17.37</v>
+        <v>-19.6</v>
       </c>
       <c r="L3">
-        <v>-44.62</v>
+        <v>-44.81</v>
       </c>
       <c r="M3">
-        <v>-25.26</v>
+        <v>-25.92</v>
       </c>
       <c r="N3">
         <v>13</v>
       </c>
       <c r="O3">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="P3">
-        <v>51.62</v>
+        <v>50.78</v>
       </c>
       <c r="Q3">
-        <v>52.94</v>
+        <v>52.59</v>
       </c>
       <c r="R3">
-        <v>56.59</v>
+        <v>56.32</v>
       </c>
       <c r="S3">
-        <v>64.09999999999999</v>
+        <v>63.96</v>
       </c>
       <c r="T3">
-        <v>-21.31</v>
+        <v>-23.35</v>
       </c>
       <c r="U3" t="s">
         <v>46</v>
@@ -1119,43 +1115,43 @@
         <v>0</v>
       </c>
       <c r="Y3">
-        <v>32.79</v>
+        <v>28.76</v>
       </c>
       <c r="Z3">
-        <v>-1.74</v>
+        <v>-1.86</v>
       </c>
       <c r="AA3">
-        <v>-1.72</v>
+        <v>-1.75</v>
       </c>
       <c r="AB3">
-        <v>-0.02</v>
+        <v>-0.11</v>
       </c>
       <c r="AC3">
-        <v>53.84</v>
+        <v>40.59</v>
       </c>
       <c r="AD3">
-        <v>66.47</v>
+        <v>53.18</v>
       </c>
       <c r="AE3">
-        <v>1.69</v>
+        <v>1.71</v>
       </c>
       <c r="AF3">
-        <v>0.36</v>
+        <v>120.5</v>
       </c>
       <c r="AG3">
-        <v>56.42</v>
+        <v>56.19</v>
       </c>
       <c r="AH3">
-        <v>49.45</v>
+        <v>48.99</v>
       </c>
       <c r="AI3">
-        <v>55.1</v>
+        <v>54.83</v>
       </c>
       <c r="AJ3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="AK3">
-        <v>32.55</v>
+        <v>33.2</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1166,10 +1162,10 @@
         <v>45</v>
       </c>
       <c r="C4">
-        <v>3281.9</v>
+        <v>3171</v>
       </c>
       <c r="D4">
-        <v>-1.12</v>
+        <v>-3.38</v>
       </c>
       <c r="E4">
         <v>3380.5</v>
@@ -1178,46 +1174,46 @@
         <v>2531.1</v>
       </c>
       <c r="G4">
-        <v>-2.92</v>
+        <v>-6.2</v>
       </c>
       <c r="H4">
-        <v>29.66</v>
+        <v>25.28</v>
       </c>
       <c r="I4">
-        <v>-1.21</v>
+        <v>-3.98</v>
       </c>
       <c r="J4">
-        <v>0.76</v>
+        <v>-2.39</v>
       </c>
       <c r="K4">
-        <v>3.71</v>
+        <v>0.98</v>
       </c>
       <c r="L4">
-        <v>17.38</v>
+        <v>13.83</v>
       </c>
       <c r="M4">
-        <v>15.92</v>
+        <v>15.1</v>
       </c>
       <c r="N4">
         <v>50</v>
       </c>
       <c r="O4">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="P4">
-        <v>3302.02</v>
+        <v>3275.74</v>
       </c>
       <c r="Q4">
-        <v>3297.28</v>
+        <v>3293.31</v>
       </c>
       <c r="R4">
-        <v>3226.74</v>
+        <v>3225.9</v>
       </c>
       <c r="S4">
-        <v>2951.36</v>
+        <v>2953.49</v>
       </c>
       <c r="T4">
-        <v>11.2</v>
+        <v>7.36</v>
       </c>
       <c r="U4" t="s">
         <v>47</v>
@@ -1232,43 +1228,43 @@
         <v>3</v>
       </c>
       <c r="Y4">
-        <v>50.53</v>
+        <v>38.51</v>
       </c>
       <c r="Z4">
-        <v>20.77</v>
+        <v>8.880000000000001</v>
       </c>
       <c r="AA4">
-        <v>27.25</v>
+        <v>23.58</v>
       </c>
       <c r="AB4">
-        <v>-6.48</v>
+        <v>-14.69</v>
       </c>
       <c r="AC4">
-        <v>15.45</v>
+        <v>11.26</v>
       </c>
       <c r="AD4">
-        <v>18.3</v>
+        <v>16.43</v>
       </c>
       <c r="AE4">
-        <v>62.44</v>
+        <v>65.90000000000001</v>
       </c>
       <c r="AF4">
-        <v>-54.75</v>
+        <v>19.52</v>
       </c>
       <c r="AG4">
-        <v>3348.08</v>
+        <v>3366.86</v>
       </c>
       <c r="AH4">
-        <v>3246.49</v>
+        <v>3219.76</v>
       </c>
       <c r="AI4">
         <v>3120.02</v>
       </c>
       <c r="AJ4" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="AK4">
-        <v>13.18</v>
+        <v>17.81</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1279,10 +1275,10 @@
         <v>45</v>
       </c>
       <c r="C5">
-        <v>981.5</v>
+        <v>958.7</v>
       </c>
       <c r="D5">
-        <v>-3.21</v>
+        <v>-2.32</v>
       </c>
       <c r="E5">
         <v>1149.7</v>
@@ -1291,46 +1287,46 @@
         <v>741.05</v>
       </c>
       <c r="G5">
-        <v>-14.63</v>
+        <v>-16.61</v>
       </c>
       <c r="H5">
-        <v>32.45</v>
+        <v>29.37</v>
       </c>
       <c r="I5">
-        <v>-2.92</v>
+        <v>-4.7</v>
       </c>
       <c r="J5">
-        <v>-6.19</v>
+        <v>-6.88</v>
       </c>
       <c r="K5">
-        <v>-3.2</v>
+        <v>-2.41</v>
       </c>
       <c r="L5">
-        <v>32.12</v>
+        <v>29</v>
       </c>
       <c r="M5">
-        <v>16.14</v>
+        <v>15.18</v>
       </c>
       <c r="N5">
         <v>62</v>
       </c>
       <c r="O5">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="P5">
-        <v>1007.48</v>
+        <v>998.02</v>
       </c>
       <c r="Q5">
-        <v>1025.81</v>
+        <v>1021.25</v>
       </c>
       <c r="R5">
-        <v>1002.09</v>
+        <v>1001.66</v>
       </c>
       <c r="S5">
-        <v>971.1799999999999</v>
+        <v>971.97</v>
       </c>
       <c r="T5">
-        <v>1.06</v>
+        <v>-1.37</v>
       </c>
       <c r="U5" t="s">
         <v>47</v>
@@ -1342,46 +1338,46 @@
         <v>47</v>
       </c>
       <c r="X5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Y5">
-        <v>39.07</v>
+        <v>34.23</v>
       </c>
       <c r="Z5">
-        <v>-3.43</v>
+        <v>-7.54</v>
       </c>
       <c r="AA5">
-        <v>1.83</v>
+        <v>-0.04</v>
       </c>
       <c r="AB5">
-        <v>-5.27</v>
+        <v>-7.5</v>
       </c>
       <c r="AC5">
-        <v>22.87</v>
+        <v>6.69</v>
       </c>
       <c r="AD5">
-        <v>22.28</v>
+        <v>18.3</v>
       </c>
       <c r="AE5">
-        <v>23.63</v>
+        <v>23.57</v>
       </c>
       <c r="AF5">
-        <v>55.57</v>
+        <v>-26.29</v>
       </c>
       <c r="AG5">
-        <v>1065.32</v>
+        <v>1069.2</v>
       </c>
       <c r="AH5">
-        <v>986.3</v>
+        <v>973.3</v>
       </c>
       <c r="AI5">
-        <v>1053.85</v>
+        <v>1040.57</v>
       </c>
       <c r="AJ5" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="AK5">
-        <v>20.01</v>
+        <v>23.87</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1392,37 +1388,37 @@
         <v>45</v>
       </c>
       <c r="C6">
-        <v>14.97</v>
+        <v>14.45</v>
       </c>
       <c r="D6">
-        <v>0.47</v>
+        <v>-3.47</v>
       </c>
       <c r="E6">
         <v>15.6</v>
       </c>
       <c r="F6">
-        <v>7.32</v>
+        <v>7.41</v>
       </c>
       <c r="G6">
-        <v>-4.04</v>
+        <v>-7.37</v>
       </c>
       <c r="H6">
-        <v>104.51</v>
+        <v>95.01000000000001</v>
       </c>
       <c r="I6">
-        <v>-0.33</v>
+        <v>-7.37</v>
       </c>
       <c r="J6">
-        <v>10.81</v>
+        <v>2.41</v>
       </c>
       <c r="K6">
-        <v>0.13</v>
+        <v>-1.16</v>
       </c>
       <c r="L6">
-        <v>105.91</v>
+        <v>97.40000000000001</v>
       </c>
       <c r="M6">
-        <v>13.51</v>
+        <v>10.06</v>
       </c>
       <c r="N6">
         <v>87</v>
@@ -1431,19 +1427,19 @@
         <v>92</v>
       </c>
       <c r="P6">
-        <v>15.28</v>
+        <v>15.05</v>
       </c>
       <c r="Q6">
-        <v>14.63</v>
+        <v>14.67</v>
       </c>
       <c r="R6">
-        <v>13.89</v>
+        <v>13.9</v>
       </c>
       <c r="S6">
-        <v>12.02</v>
+        <v>12.05</v>
       </c>
       <c r="T6">
-        <v>24.49</v>
+        <v>19.95</v>
       </c>
       <c r="U6" t="s">
         <v>47</v>
@@ -1458,43 +1454,43 @@
         <v>3</v>
       </c>
       <c r="Y6">
-        <v>56.93</v>
+        <v>49.78</v>
       </c>
       <c r="Z6">
-        <v>0.4</v>
+        <v>0.33</v>
       </c>
       <c r="AA6">
-        <v>0.37</v>
+        <v>0.36</v>
       </c>
       <c r="AB6">
-        <v>0.03</v>
+        <v>-0.03</v>
       </c>
       <c r="AC6">
-        <v>39.08</v>
+        <v>16.12</v>
       </c>
       <c r="AD6">
-        <v>53.94</v>
+        <v>35.71</v>
       </c>
       <c r="AE6">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="AF6">
-        <v>6.72</v>
+        <v>-28.15</v>
       </c>
       <c r="AG6">
-        <v>15.79</v>
+        <v>15.75</v>
       </c>
       <c r="AH6">
-        <v>13.48</v>
+        <v>13.6</v>
       </c>
       <c r="AI6">
         <v>14.01</v>
       </c>
       <c r="AJ6" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="AK6">
-        <v>35.27</v>
+        <v>31.45</v>
       </c>
     </row>
     <row r="7" spans="1:37">
@@ -1505,10 +1501,10 @@
         <v>45</v>
       </c>
       <c r="C7">
-        <v>12.01</v>
+        <v>12.6</v>
       </c>
       <c r="D7">
-        <v>1.95</v>
+        <v>4.91</v>
       </c>
       <c r="E7">
         <v>13.92</v>
@@ -1517,46 +1513,46 @@
         <v>4.69</v>
       </c>
       <c r="G7">
-        <v>-13.72</v>
+        <v>-9.48</v>
       </c>
       <c r="H7">
-        <v>156.08</v>
+        <v>168.66</v>
       </c>
       <c r="I7">
-        <v>10.18</v>
+        <v>13.41</v>
       </c>
       <c r="J7">
-        <v>1.18</v>
+        <v>7.69</v>
       </c>
       <c r="K7">
-        <v>4.25</v>
+        <v>4.22</v>
       </c>
       <c r="L7">
-        <v>128.33</v>
+        <v>139.09</v>
       </c>
       <c r="M7">
-        <v>-30.46</v>
+        <v>-30.32</v>
       </c>
       <c r="N7">
         <v>99</v>
       </c>
       <c r="O7">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="P7">
-        <v>11.56</v>
+        <v>11.85</v>
       </c>
       <c r="Q7">
-        <v>11.4</v>
+        <v>11.44</v>
       </c>
       <c r="R7">
-        <v>11.58</v>
+        <v>11.62</v>
       </c>
       <c r="S7">
-        <v>10.48</v>
+        <v>10.52</v>
       </c>
       <c r="T7">
-        <v>14.57</v>
+        <v>19.77</v>
       </c>
       <c r="U7" t="s">
         <v>46</v>
@@ -1571,43 +1567,43 @@
         <v>2</v>
       </c>
       <c r="Y7">
-        <v>59.33</v>
+        <v>66.98</v>
       </c>
       <c r="Z7">
-        <v>-0.06</v>
+        <v>0.04</v>
       </c>
       <c r="AA7">
-        <v>-0.14</v>
+        <v>-0.11</v>
       </c>
       <c r="AB7">
-        <v>0.09</v>
+        <v>0.14</v>
       </c>
       <c r="AC7">
         <v>100</v>
       </c>
       <c r="AD7">
-        <v>95.09999999999999</v>
+        <v>100</v>
       </c>
       <c r="AE7">
-        <v>0.25</v>
+        <v>0.27</v>
       </c>
       <c r="AF7">
-        <v>336.55</v>
+        <v>493.26</v>
       </c>
       <c r="AG7">
-        <v>12.04</v>
+        <v>12.27</v>
       </c>
       <c r="AH7">
-        <v>10.75</v>
+        <v>10.61</v>
       </c>
       <c r="AI7">
-        <v>11.26</v>
+        <v>11.49</v>
       </c>
       <c r="AJ7" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="AK7">
-        <v>30.71</v>
+        <v>35.32</v>
       </c>
     </row>
     <row r="8" spans="1:37">
@@ -1618,58 +1614,58 @@
         <v>45</v>
       </c>
       <c r="C8">
-        <v>4191.6</v>
+        <v>4081.8</v>
       </c>
       <c r="D8">
-        <v>-1.04</v>
+        <v>-2.62</v>
       </c>
       <c r="E8">
         <v>5809.5</v>
       </c>
       <c r="F8">
-        <v>4109.8</v>
+        <v>4081.8</v>
       </c>
       <c r="G8">
-        <v>-27.85</v>
+        <v>-29.74</v>
       </c>
       <c r="H8">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="I8">
-        <v>-3.06</v>
+        <v>-5.05</v>
       </c>
       <c r="J8">
-        <v>-7.54</v>
+        <v>-10.23</v>
       </c>
       <c r="K8">
-        <v>-4.31</v>
+        <v>-7.53</v>
       </c>
       <c r="L8">
-        <v>-19.34</v>
+        <v>-21.58</v>
       </c>
       <c r="M8">
-        <v>17.76</v>
+        <v>17.37</v>
       </c>
       <c r="N8">
         <v>26</v>
       </c>
       <c r="O8">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="P8">
-        <v>4219.52</v>
+        <v>4176.14</v>
       </c>
       <c r="Q8">
-        <v>4331.62</v>
+        <v>4308.36</v>
       </c>
       <c r="R8">
-        <v>4354.54</v>
+        <v>4348.19</v>
       </c>
       <c r="S8">
-        <v>4603.73</v>
+        <v>4598.44</v>
       </c>
       <c r="T8">
-        <v>-8.949999999999999</v>
+        <v>-11.24</v>
       </c>
       <c r="U8" t="s">
         <v>46</v>
@@ -1684,43 +1680,43 @@
         <v>0</v>
       </c>
       <c r="Y8">
-        <v>40.04</v>
+        <v>34.28</v>
       </c>
       <c r="Z8">
-        <v>-43.8</v>
+        <v>-56.06</v>
       </c>
       <c r="AA8">
-        <v>-23.36</v>
+        <v>-29.9</v>
       </c>
       <c r="AB8">
-        <v>-20.44</v>
+        <v>-26.16</v>
       </c>
       <c r="AC8">
-        <v>31.41</v>
+        <v>36.99</v>
       </c>
       <c r="AD8">
-        <v>16.65</v>
+        <v>28.67</v>
       </c>
       <c r="AE8">
-        <v>108.81</v>
+        <v>113.54</v>
       </c>
       <c r="AF8">
-        <v>-50.6</v>
+        <v>4.1</v>
       </c>
       <c r="AG8">
-        <v>4512.52</v>
+        <v>4492.26</v>
       </c>
       <c r="AH8">
-        <v>4150.72</v>
+        <v>4124.46</v>
       </c>
       <c r="AI8">
         <v>4473.44</v>
       </c>
       <c r="AJ8" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="AK8">
-        <v>37.3</v>
+        <v>42.63</v>
       </c>
     </row>
     <row r="9" spans="1:37">
@@ -1731,10 +1727,10 @@
         <v>45</v>
       </c>
       <c r="C9">
-        <v>11000</v>
+        <v>10697</v>
       </c>
       <c r="D9">
-        <v>0.19</v>
+        <v>-2.75</v>
       </c>
       <c r="E9">
         <v>13052</v>
@@ -1743,46 +1739,46 @@
         <v>10362</v>
       </c>
       <c r="G9">
-        <v>-15.72</v>
+        <v>-18.04</v>
       </c>
       <c r="H9">
-        <v>6.16</v>
+        <v>3.23</v>
       </c>
       <c r="I9">
-        <v>-3.58</v>
+        <v>-4.28</v>
       </c>
       <c r="J9">
-        <v>-6.03</v>
+        <v>-7.94</v>
       </c>
       <c r="K9">
-        <v>-4.06</v>
+        <v>-6.09</v>
       </c>
       <c r="L9">
-        <v>-12.5</v>
+        <v>-14.27</v>
       </c>
       <c r="M9">
-        <v>7.22</v>
+        <v>6.95</v>
       </c>
       <c r="N9">
         <v>38</v>
       </c>
       <c r="O9">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="P9">
-        <v>11012.6</v>
+        <v>10917</v>
       </c>
       <c r="Q9">
-        <v>11388.45</v>
+        <v>11342.35</v>
       </c>
       <c r="R9">
-        <v>11655.62</v>
+        <v>11636.34</v>
       </c>
       <c r="S9">
-        <v>11750.17</v>
+        <v>11744.86</v>
       </c>
       <c r="T9">
-        <v>-6.38</v>
+        <v>-8.92</v>
       </c>
       <c r="U9" t="s">
         <v>46</v>
@@ -1797,43 +1793,43 @@
         <v>0</v>
       </c>
       <c r="Y9">
-        <v>33.71</v>
+        <v>27.28</v>
       </c>
       <c r="Z9">
-        <v>-193.78</v>
+        <v>-220.86</v>
       </c>
       <c r="AA9">
-        <v>-139.56</v>
+        <v>-155.82</v>
       </c>
       <c r="AB9">
-        <v>-54.22</v>
+        <v>-65.04000000000001</v>
       </c>
       <c r="AC9">
         <v>13.51</v>
       </c>
       <c r="AD9">
-        <v>6.49</v>
+        <v>11</v>
       </c>
       <c r="AE9">
-        <v>190.1</v>
+        <v>201.38</v>
       </c>
       <c r="AF9">
-        <v>-10.72</v>
+        <v>36.28</v>
       </c>
       <c r="AG9">
-        <v>11889.65</v>
+        <v>11918.3</v>
       </c>
       <c r="AH9">
-        <v>10887.25</v>
+        <v>10766.4</v>
       </c>
       <c r="AI9">
         <v>11470.36</v>
       </c>
       <c r="AJ9" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="AK9">
-        <v>43.78</v>
+        <v>45.17</v>
       </c>
     </row>
   </sheetData>
@@ -1974,7 +1970,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F70"/>
+  <dimension ref="A1:F71"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -2032,1124 +2028,1144 @@
         <v>60</v>
       </c>
     </row>
-    <row r="5" spans="1:6">
-      <c r="A5" s="2" t="s">
+    <row r="4" spans="1:6">
+      <c r="A4" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="C4" s="4" t="s">
         <v>61</v>
       </c>
-      <c r="B5" s="2"/>
-      <c r="C5" s="2"/>
-      <c r="D5" s="2"/>
-      <c r="E5" s="2"/>
+      <c r="D4" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="6" spans="1:6">
-      <c r="A6" s="3" t="s">
+      <c r="A6" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="B6" s="2"/>
+      <c r="C6" s="2"/>
+      <c r="D6" s="2"/>
+      <c r="E6" s="2"/>
+    </row>
+    <row r="7" spans="1:6">
+      <c r="A7" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B6" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="E6" s="3" t="s">
+      <c r="B7" s="3" t="s">
         <v>65</v>
       </c>
-    </row>
-    <row r="7" spans="1:6">
-      <c r="A7" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B7" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C7" s="6">
-        <v>-2.66</v>
-      </c>
-      <c r="D7" s="6">
-        <v>-3.12</v>
-      </c>
-      <c r="E7" s="7">
-        <v>-0.46</v>
+      <c r="C7" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>68</v>
       </c>
     </row>
     <row r="8" spans="1:6">
       <c r="A8" s="5" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B8" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C8" s="6">
-        <v>-10.97</v>
+        <v>-3.12</v>
       </c>
       <c r="D8" s="6">
-        <v>-11.09</v>
+        <v>-5.54</v>
       </c>
       <c r="E8" s="7">
-        <v>-0.12</v>
+        <v>-2.42</v>
       </c>
     </row>
     <row r="9" spans="1:6">
       <c r="A9" s="5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B9" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C9" s="6">
-        <v>0.34</v>
+        <v>-11.09</v>
       </c>
       <c r="D9" s="6">
-        <v>0.76</v>
-      </c>
-      <c r="E9" s="8">
-        <v>0.42</v>
+        <v>-12.43</v>
+      </c>
+      <c r="E9" s="7">
+        <v>-1.34</v>
       </c>
     </row>
     <row r="10" spans="1:6">
       <c r="A10" s="5" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B10" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C10" s="6">
-        <v>-5.98</v>
+        <v>0.76</v>
       </c>
       <c r="D10" s="6">
-        <v>-6.19</v>
+        <v>-2.39</v>
       </c>
       <c r="E10" s="7">
-        <v>-0.21</v>
+        <v>-3.15</v>
       </c>
     </row>
     <row r="11" spans="1:6">
       <c r="A11" s="5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B11" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C11" s="6">
-        <v>10.37</v>
+        <v>-6.19</v>
       </c>
       <c r="D11" s="6">
-        <v>10.81</v>
-      </c>
-      <c r="E11" s="8">
-        <v>0.44</v>
+        <v>-6.88</v>
+      </c>
+      <c r="E11" s="7">
+        <v>-0.6899999999999999</v>
       </c>
     </row>
     <row r="12" spans="1:6">
       <c r="A12" s="5" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B12" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C12" s="6">
-        <v>-2.73</v>
+        <v>10.81</v>
       </c>
       <c r="D12" s="6">
-        <v>1.18</v>
-      </c>
-      <c r="E12" s="8">
-        <v>3.91</v>
+        <v>2.41</v>
+      </c>
+      <c r="E12" s="7">
+        <v>-8.4</v>
       </c>
     </row>
     <row r="13" spans="1:6">
       <c r="A13" s="5" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B13" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C13" s="6">
-        <v>-2.96</v>
+        <v>1.18</v>
       </c>
       <c r="D13" s="6">
-        <v>-7.54</v>
-      </c>
-      <c r="E13" s="7">
-        <v>-4.58</v>
+        <v>7.69</v>
+      </c>
+      <c r="E13" s="8">
+        <v>6.51</v>
       </c>
     </row>
     <row r="14" spans="1:6">
       <c r="A14" s="5" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B14" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C14" s="6">
-        <v>-7.67</v>
+        <v>-7.54</v>
       </c>
       <c r="D14" s="6">
-        <v>-6.03</v>
-      </c>
-      <c r="E14" s="8">
-        <v>1.64</v>
+        <v>-10.23</v>
+      </c>
+      <c r="E14" s="7">
+        <v>-2.69</v>
       </c>
     </row>
     <row r="15" spans="1:6">
       <c r="A15" s="5" t="s">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C15" s="6">
-        <v>-0.5</v>
+        <v>-6.03</v>
       </c>
       <c r="D15" s="6">
-        <v>-2.45</v>
+        <v>-7.94</v>
       </c>
       <c r="E15" s="7">
-        <v>-1.95</v>
+        <v>-1.91</v>
       </c>
     </row>
     <row r="16" spans="1:6">
       <c r="A16" s="5" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B16" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C16" s="6">
-        <v>0.95</v>
+        <v>-2.45</v>
       </c>
       <c r="D16" s="6">
-        <v>-4.78</v>
+        <v>-6.06</v>
       </c>
       <c r="E16" s="7">
-        <v>-5.73</v>
+        <v>-3.61</v>
       </c>
     </row>
     <row r="17" spans="1:5">
       <c r="A17" s="5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B17" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C17" s="6">
-        <v>0.27</v>
+        <v>-4.78</v>
       </c>
       <c r="D17" s="6">
-        <v>-1.21</v>
+        <v>-7.87</v>
       </c>
       <c r="E17" s="7">
-        <v>-1.48</v>
+        <v>-3.09</v>
       </c>
     </row>
     <row r="18" spans="1:5">
       <c r="A18" s="5" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B18" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C18" s="6">
-        <v>0.4</v>
+        <v>-1.21</v>
       </c>
       <c r="D18" s="6">
-        <v>-2.92</v>
+        <v>-3.98</v>
       </c>
       <c r="E18" s="7">
-        <v>-3.32</v>
+        <v>-2.77</v>
       </c>
     </row>
     <row r="19" spans="1:5">
       <c r="A19" s="5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B19" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C19" s="6">
-        <v>2.9</v>
+        <v>-2.92</v>
       </c>
       <c r="D19" s="6">
-        <v>-0.33</v>
+        <v>-4.7</v>
       </c>
       <c r="E19" s="7">
-        <v>-3.23</v>
+        <v>-1.78</v>
       </c>
     </row>
     <row r="20" spans="1:5">
       <c r="A20" s="5" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B20" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C20" s="6">
-        <v>6.61</v>
+        <v>-0.33</v>
       </c>
       <c r="D20" s="6">
-        <v>10.18</v>
-      </c>
-      <c r="E20" s="8">
-        <v>3.57</v>
+        <v>-7.37</v>
+      </c>
+      <c r="E20" s="7">
+        <v>-7.04</v>
       </c>
     </row>
     <row r="21" spans="1:5">
       <c r="A21" s="5" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B21" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C21" s="6">
-        <v>-2.73</v>
+        <v>10.18</v>
       </c>
       <c r="D21" s="6">
-        <v>-3.06</v>
-      </c>
-      <c r="E21" s="7">
-        <v>-0.33</v>
+        <v>13.41</v>
+      </c>
+      <c r="E21" s="8">
+        <v>3.23</v>
       </c>
     </row>
     <row r="22" spans="1:5">
       <c r="A22" s="5" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B22" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C22" s="6">
-        <v>-2.63</v>
+        <v>-3.06</v>
       </c>
       <c r="D22" s="6">
-        <v>-3.58</v>
+        <v>-5.05</v>
       </c>
       <c r="E22" s="7">
-        <v>-0.95</v>
+        <v>-1.99</v>
       </c>
     </row>
     <row r="23" spans="1:5">
       <c r="A23" s="5" t="s">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="C23" s="6">
-        <v>38.46</v>
+        <v>-3.58</v>
       </c>
       <c r="D23" s="6">
-        <v>36.35</v>
+        <v>-4.28</v>
       </c>
       <c r="E23" s="7">
-        <v>-2.11</v>
+        <v>-0.7</v>
       </c>
     </row>
     <row r="24" spans="1:5">
       <c r="A24" s="5" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B24" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C24" s="6">
-        <v>-42.73</v>
+        <v>36.35</v>
       </c>
       <c r="D24" s="6">
-        <v>-44.62</v>
+        <v>31.69</v>
       </c>
       <c r="E24" s="7">
-        <v>-1.89</v>
+        <v>-4.66</v>
       </c>
     </row>
     <row r="25" spans="1:5">
       <c r="A25" s="5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B25" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C25" s="6">
-        <v>18.36</v>
+        <v>-44.62</v>
       </c>
       <c r="D25" s="6">
-        <v>17.38</v>
+        <v>-44.81</v>
       </c>
       <c r="E25" s="7">
-        <v>-0.98</v>
+        <v>-0.19</v>
       </c>
     </row>
     <row r="26" spans="1:5">
       <c r="A26" s="5" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B26" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C26" s="6">
-        <v>37.26</v>
+        <v>17.38</v>
       </c>
       <c r="D26" s="6">
-        <v>32.12</v>
+        <v>13.83</v>
       </c>
       <c r="E26" s="7">
-        <v>-5.14</v>
+        <v>-3.55</v>
       </c>
     </row>
     <row r="27" spans="1:5">
       <c r="A27" s="5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B27" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C27" s="6">
-        <v>104.39</v>
+        <v>32.12</v>
       </c>
       <c r="D27" s="6">
-        <v>105.91</v>
-      </c>
-      <c r="E27" s="8">
-        <v>1.52</v>
+        <v>29</v>
+      </c>
+      <c r="E27" s="7">
+        <v>-3.12</v>
       </c>
     </row>
     <row r="28" spans="1:5">
       <c r="A28" s="5" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B28" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C28" s="6">
-        <v>118.55</v>
+        <v>105.91</v>
       </c>
       <c r="D28" s="6">
-        <v>128.33</v>
-      </c>
-      <c r="E28" s="8">
-        <v>9.779999999999999</v>
+        <v>97.40000000000001</v>
+      </c>
+      <c r="E28" s="7">
+        <v>-8.51</v>
       </c>
     </row>
     <row r="29" spans="1:5">
       <c r="A29" s="5" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B29" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C29" s="6">
-        <v>-17.73</v>
+        <v>128.33</v>
       </c>
       <c r="D29" s="6">
-        <v>-19.34</v>
-      </c>
-      <c r="E29" s="7">
-        <v>-1.61</v>
+        <v>139.09</v>
+      </c>
+      <c r="E29" s="8">
+        <v>10.76</v>
       </c>
     </row>
     <row r="30" spans="1:5">
       <c r="A30" s="5" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B30" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C30" s="6">
-        <v>-13.31</v>
+        <v>-19.34</v>
       </c>
       <c r="D30" s="6">
-        <v>-12.5</v>
-      </c>
-      <c r="E30" s="8">
-        <v>0.8100000000000001</v>
+        <v>-21.58</v>
+      </c>
+      <c r="E30" s="7">
+        <v>-2.24</v>
       </c>
     </row>
     <row r="31" spans="1:5">
       <c r="A31" s="5" t="s">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="B31" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C31" s="6">
-        <v>11.7</v>
+        <v>-12.5</v>
       </c>
       <c r="D31" s="6">
-        <v>7.28</v>
+        <v>-14.27</v>
       </c>
       <c r="E31" s="7">
-        <v>-4.42</v>
+        <v>-1.77</v>
       </c>
     </row>
     <row r="32" spans="1:5">
       <c r="A32" s="5" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B32" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C32" s="6">
-        <v>-15.04</v>
+        <v>7.28</v>
       </c>
       <c r="D32" s="6">
-        <v>-17.37</v>
+        <v>1.34</v>
       </c>
       <c r="E32" s="7">
-        <v>-2.33</v>
+        <v>-5.94</v>
       </c>
     </row>
     <row r="33" spans="1:5">
       <c r="A33" s="5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B33" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C33" s="6">
-        <v>6.87</v>
+        <v>-17.37</v>
       </c>
       <c r="D33" s="6">
-        <v>3.71</v>
+        <v>-19.6</v>
       </c>
       <c r="E33" s="7">
-        <v>-3.16</v>
+        <v>-2.23</v>
       </c>
     </row>
     <row r="34" spans="1:5">
       <c r="A34" s="5" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B34" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C34" s="6">
-        <v>-0.74</v>
+        <v>3.71</v>
       </c>
       <c r="D34" s="6">
-        <v>-3.2</v>
+        <v>0.98</v>
       </c>
       <c r="E34" s="7">
-        <v>-2.46</v>
+        <v>-2.73</v>
       </c>
     </row>
     <row r="35" spans="1:5">
       <c r="A35" s="5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B35" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C35" s="6">
-        <v>-0</v>
+        <v>-3.2</v>
       </c>
       <c r="D35" s="6">
-        <v>0.13</v>
+        <v>-2.41</v>
       </c>
       <c r="E35" s="8">
-        <v>0.13</v>
+        <v>0.79</v>
       </c>
     </row>
     <row r="36" spans="1:5">
       <c r="A36" s="5" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B36" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C36" s="6">
-        <v>7.29</v>
+        <v>0.13</v>
       </c>
       <c r="D36" s="6">
-        <v>4.25</v>
+        <v>-1.16</v>
       </c>
       <c r="E36" s="7">
-        <v>-3.04</v>
+        <v>-1.29</v>
       </c>
     </row>
     <row r="37" spans="1:5">
       <c r="A37" s="5" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B37" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C37" s="6">
-        <v>-1.22</v>
+        <v>4.25</v>
       </c>
       <c r="D37" s="6">
-        <v>-4.31</v>
+        <v>4.22</v>
       </c>
       <c r="E37" s="7">
-        <v>-3.09</v>
+        <v>-0.03</v>
       </c>
     </row>
     <row r="38" spans="1:5">
       <c r="A38" s="5" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B38" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C38" s="6">
-        <v>-1.24</v>
+        <v>-4.31</v>
       </c>
       <c r="D38" s="6">
-        <v>-4.06</v>
+        <v>-7.53</v>
       </c>
       <c r="E38" s="7">
-        <v>-2.82</v>
+        <v>-3.22</v>
       </c>
     </row>
     <row r="39" spans="1:5">
       <c r="A39" s="5" t="s">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="B39" s="5" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C39" s="6">
-        <v>-5.82</v>
+        <v>-4.06</v>
       </c>
       <c r="D39" s="6">
-        <v>-6.99</v>
+        <v>-6.09</v>
       </c>
       <c r="E39" s="7">
-        <v>-1.17</v>
+        <v>-2.03</v>
       </c>
     </row>
     <row r="40" spans="1:5">
       <c r="A40" s="5" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B40" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C40" s="6">
-        <v>-45.56</v>
+        <v>-6.99</v>
       </c>
       <c r="D40" s="6">
-        <v>-46.04</v>
+        <v>-10.81</v>
       </c>
       <c r="E40" s="7">
-        <v>-0.48</v>
+        <v>-3.82</v>
       </c>
     </row>
     <row r="41" spans="1:5">
       <c r="A41" s="5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B41" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C41" s="6">
-        <v>-1.82</v>
+        <v>-46.04</v>
       </c>
       <c r="D41" s="6">
-        <v>-2.92</v>
+        <v>-47.56</v>
       </c>
       <c r="E41" s="7">
-        <v>-1.1</v>
+        <v>-1.52</v>
       </c>
     </row>
     <row r="42" spans="1:5">
       <c r="A42" s="5" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B42" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C42" s="6">
-        <v>-11.8</v>
+        <v>-2.92</v>
       </c>
       <c r="D42" s="6">
-        <v>-14.63</v>
+        <v>-6.2</v>
       </c>
       <c r="E42" s="7">
-        <v>-2.83</v>
+        <v>-3.28</v>
       </c>
     </row>
     <row r="43" spans="1:5">
       <c r="A43" s="5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B43" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C43" s="6">
-        <v>-4.49</v>
+        <v>-14.63</v>
       </c>
       <c r="D43" s="6">
-        <v>-4.04</v>
-      </c>
-      <c r="E43" s="8">
-        <v>0.45</v>
+        <v>-16.61</v>
+      </c>
+      <c r="E43" s="7">
+        <v>-1.98</v>
       </c>
     </row>
     <row r="44" spans="1:5">
       <c r="A44" s="5" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B44" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C44" s="6">
-        <v>-15.37</v>
+        <v>-4.04</v>
       </c>
       <c r="D44" s="6">
-        <v>-13.72</v>
-      </c>
-      <c r="E44" s="8">
-        <v>1.65</v>
+        <v>-7.37</v>
+      </c>
+      <c r="E44" s="7">
+        <v>-3.33</v>
       </c>
     </row>
     <row r="45" spans="1:5">
       <c r="A45" s="5" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B45" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C45" s="6">
-        <v>-27.09</v>
+        <v>-13.72</v>
       </c>
       <c r="D45" s="6">
-        <v>-27.85</v>
-      </c>
-      <c r="E45" s="7">
-        <v>-0.76</v>
+        <v>-9.48</v>
+      </c>
+      <c r="E45" s="8">
+        <v>4.24</v>
       </c>
     </row>
     <row r="46" spans="1:5">
       <c r="A46" s="5" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B46" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C46" s="6">
-        <v>-15.88</v>
+        <v>-27.85</v>
       </c>
       <c r="D46" s="6">
-        <v>-15.72</v>
-      </c>
-      <c r="E46" s="8">
-        <v>0.16</v>
+        <v>-29.74</v>
+      </c>
+      <c r="E46" s="7">
+        <v>-1.89</v>
       </c>
     </row>
     <row r="47" spans="1:5">
       <c r="A47" s="5" t="s">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="B47" s="5" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C47" s="6">
-        <v>400</v>
+        <v>-15.72</v>
       </c>
       <c r="D47" s="6">
-        <v>395</v>
+        <v>-18.04</v>
       </c>
       <c r="E47" s="7">
-        <v>-5</v>
+        <v>-2.32</v>
       </c>
     </row>
     <row r="48" spans="1:5">
       <c r="A48" s="5" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B48" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C48" s="6">
-        <v>50.89</v>
+        <v>395</v>
       </c>
       <c r="D48" s="6">
-        <v>50.44</v>
+        <v>378.8</v>
       </c>
       <c r="E48" s="7">
-        <v>-0.45</v>
+        <v>-16.2</v>
       </c>
     </row>
     <row r="49" spans="1:5">
       <c r="A49" s="5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B49" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C49" s="6">
-        <v>3319</v>
+        <v>50.44</v>
       </c>
       <c r="D49" s="6">
-        <v>3281.9</v>
+        <v>49.02</v>
       </c>
       <c r="E49" s="7">
-        <v>-37.1</v>
+        <v>-1.42</v>
       </c>
     </row>
     <row r="50" spans="1:5">
       <c r="A50" s="5" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B50" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C50" s="6">
-        <v>1014</v>
+        <v>3281.9</v>
       </c>
       <c r="D50" s="6">
-        <v>981.5</v>
+        <v>3171</v>
       </c>
       <c r="E50" s="7">
-        <v>-32.5</v>
+        <v>-110.9</v>
       </c>
     </row>
     <row r="51" spans="1:5">
       <c r="A51" s="5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B51" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C51" s="6">
-        <v>14.9</v>
+        <v>981.5</v>
       </c>
       <c r="D51" s="6">
-        <v>14.97</v>
-      </c>
-      <c r="E51" s="8">
-        <v>0.07000000000000001</v>
+        <v>958.7</v>
+      </c>
+      <c r="E51" s="7">
+        <v>-22.8</v>
       </c>
     </row>
     <row r="52" spans="1:5">
       <c r="A52" s="5" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B52" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C52" s="6">
-        <v>11.78</v>
+        <v>14.97</v>
       </c>
       <c r="D52" s="6">
-        <v>12.01</v>
-      </c>
-      <c r="E52" s="8">
-        <v>0.23</v>
+        <v>14.45</v>
+      </c>
+      <c r="E52" s="7">
+        <v>-0.52</v>
       </c>
     </row>
     <row r="53" spans="1:5">
       <c r="A53" s="5" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B53" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C53" s="6">
-        <v>4235.8</v>
+        <v>12.01</v>
       </c>
       <c r="D53" s="6">
-        <v>4191.6</v>
-      </c>
-      <c r="E53" s="7">
-        <v>-44.2</v>
+        <v>12.6</v>
+      </c>
+      <c r="E53" s="8">
+        <v>0.59</v>
       </c>
     </row>
     <row r="54" spans="1:5">
       <c r="A54" s="5" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B54" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C54" s="6">
-        <v>10979</v>
+        <v>4191.6</v>
       </c>
       <c r="D54" s="6">
-        <v>11000</v>
-      </c>
-      <c r="E54" s="8">
-        <v>21</v>
+        <v>4081.8</v>
+      </c>
+      <c r="E54" s="7">
+        <v>-109.8</v>
       </c>
     </row>
     <row r="55" spans="1:5">
       <c r="A55" s="5" t="s">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="B55" s="5" t="s">
-        <v>24</v>
+        <v>2</v>
       </c>
       <c r="C55" s="6">
-        <v>47.23</v>
+        <v>11000</v>
       </c>
       <c r="D55" s="6">
-        <v>43.4</v>
+        <v>10697</v>
       </c>
       <c r="E55" s="7">
-        <v>-3.83</v>
+        <v>-303</v>
       </c>
     </row>
     <row r="56" spans="1:5">
       <c r="A56" s="5" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B56" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C56" s="6">
-        <v>34.19</v>
+        <v>43.4</v>
       </c>
       <c r="D56" s="6">
-        <v>32.79</v>
+        <v>33.83</v>
       </c>
       <c r="E56" s="7">
-        <v>-1.4</v>
+        <v>-9.57</v>
       </c>
     </row>
     <row r="57" spans="1:5">
       <c r="A57" s="5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B57" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C57" s="6">
-        <v>55.96</v>
+        <v>32.79</v>
       </c>
       <c r="D57" s="6">
-        <v>50.53</v>
+        <v>28.76</v>
       </c>
       <c r="E57" s="7">
-        <v>-5.43</v>
+        <v>-4.03</v>
       </c>
     </row>
     <row r="58" spans="1:5">
       <c r="A58" s="5" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B58" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C58" s="6">
-        <v>48.07</v>
+        <v>50.53</v>
       </c>
       <c r="D58" s="6">
-        <v>39.07</v>
+        <v>38.51</v>
       </c>
       <c r="E58" s="7">
-        <v>-9</v>
+        <v>-12.02</v>
       </c>
     </row>
     <row r="59" spans="1:5">
       <c r="A59" s="5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B59" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C59" s="6">
-        <v>56.14</v>
+        <v>39.07</v>
       </c>
       <c r="D59" s="6">
-        <v>56.93</v>
-      </c>
-      <c r="E59" s="8">
-        <v>0.79</v>
+        <v>34.23</v>
+      </c>
+      <c r="E59" s="7">
+        <v>-4.84</v>
       </c>
     </row>
     <row r="60" spans="1:5">
       <c r="A60" s="5" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B60" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C60" s="6">
-        <v>55.61</v>
+        <v>56.93</v>
       </c>
       <c r="D60" s="6">
-        <v>59.33</v>
-      </c>
-      <c r="E60" s="8">
-        <v>3.72</v>
+        <v>49.78</v>
+      </c>
+      <c r="E60" s="7">
+        <v>-7.15</v>
       </c>
     </row>
     <row r="61" spans="1:5">
       <c r="A61" s="5" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B61" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C61" s="6">
-        <v>42.72</v>
+        <v>59.33</v>
       </c>
       <c r="D61" s="6">
-        <v>40.04</v>
-      </c>
-      <c r="E61" s="7">
-        <v>-2.68</v>
+        <v>66.98</v>
+      </c>
+      <c r="E61" s="8">
+        <v>7.65</v>
       </c>
     </row>
     <row r="62" spans="1:5">
       <c r="A62" s="5" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B62" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C62" s="6">
-        <v>32.69</v>
+        <v>40.04</v>
       </c>
       <c r="D62" s="6">
-        <v>33.71</v>
-      </c>
-      <c r="E62" s="8">
-        <v>1.02</v>
+        <v>34.28</v>
+      </c>
+      <c r="E62" s="7">
+        <v>-5.76</v>
       </c>
     </row>
     <row r="63" spans="1:5">
       <c r="A63" s="5" t="s">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="B63" s="5" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="C63" s="6">
-        <v>-52.8</v>
+        <v>33.71</v>
       </c>
       <c r="D63" s="6">
-        <v>-44</v>
-      </c>
-      <c r="E63" s="8">
-        <v>8.800000000000001</v>
+        <v>27.28</v>
+      </c>
+      <c r="E63" s="7">
+        <v>-6.43</v>
       </c>
     </row>
     <row r="64" spans="1:5">
       <c r="A64" s="5" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B64" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C64" s="6">
-        <v>-40.2</v>
+        <v>-44</v>
       </c>
       <c r="D64" s="6">
-        <v>0.36</v>
+        <v>-12.04</v>
       </c>
       <c r="E64" s="8">
-        <v>40.56</v>
+        <v>31.96</v>
       </c>
     </row>
     <row r="65" spans="1:5">
       <c r="A65" s="5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B65" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C65" s="6">
-        <v>-11.97</v>
+        <v>0.36</v>
       </c>
       <c r="D65" s="6">
-        <v>-54.75</v>
-      </c>
-      <c r="E65" s="7">
-        <v>-42.78</v>
+        <v>120.5</v>
+      </c>
+      <c r="E65" s="8">
+        <v>120.14</v>
       </c>
     </row>
     <row r="66" spans="1:5">
       <c r="A66" s="5" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B66" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C66" s="6">
-        <v>-35.54</v>
+        <v>-54.75</v>
       </c>
       <c r="D66" s="6">
-        <v>55.57</v>
+        <v>19.52</v>
       </c>
       <c r="E66" s="8">
-        <v>91.11</v>
+        <v>74.27</v>
       </c>
     </row>
     <row r="67" spans="1:5">
       <c r="A67" s="5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B67" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C67" s="6">
-        <v>74.97</v>
+        <v>55.57</v>
       </c>
       <c r="D67" s="6">
-        <v>6.72</v>
+        <v>-26.29</v>
       </c>
       <c r="E67" s="7">
-        <v>-68.25</v>
+        <v>-81.86</v>
       </c>
     </row>
     <row r="68" spans="1:5">
       <c r="A68" s="5" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B68" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C68" s="6">
-        <v>54.9</v>
+        <v>6.72</v>
       </c>
       <c r="D68" s="6">
-        <v>336.55</v>
-      </c>
-      <c r="E68" s="8">
-        <v>281.65</v>
+        <v>-28.15</v>
+      </c>
+      <c r="E68" s="7">
+        <v>-34.87</v>
       </c>
     </row>
     <row r="69" spans="1:5">
       <c r="A69" s="5" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B69" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C69" s="6">
-        <v>-10.49</v>
+        <v>336.55</v>
       </c>
       <c r="D69" s="6">
-        <v>-50.6</v>
-      </c>
-      <c r="E69" s="7">
-        <v>-40.11</v>
+        <v>493.26</v>
+      </c>
+      <c r="E69" s="8">
+        <v>156.71</v>
       </c>
     </row>
     <row r="70" spans="1:5">
       <c r="A70" s="5" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B70" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C70" s="6">
-        <v>7.15</v>
+        <v>-50.6</v>
       </c>
       <c r="D70" s="6">
+        <v>4.1</v>
+      </c>
+      <c r="E70" s="8">
+        <v>54.7</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5">
+      <c r="A71" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="B71" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C71" s="6">
         <v>-10.72</v>
       </c>
-      <c r="E70" s="7">
-        <v>-17.87</v>
+      <c r="D71" s="6">
+        <v>36.28</v>
+      </c>
+      <c r="E71" s="8">
+        <v>47</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A5:E5"/>
+    <mergeCell ref="A6:E6"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3173,28 +3189,28 @@
         <v>1</v>
       </c>
       <c r="B1" s="9" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="C1" s="9" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="D1" s="9" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="E1" s="9" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="F1" s="9" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="G1" s="9" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="H1" s="9" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="I1" s="9" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -3202,22 +3218,22 @@
         <v>45</v>
       </c>
       <c r="B2" s="11">
-        <v>56.44</v>
+        <v>52.44</v>
       </c>
       <c r="C2" s="12">
         <v>8</v>
       </c>
       <c r="D2" s="11">
-        <v>44.5</v>
+        <v>39.2</v>
       </c>
       <c r="E2" s="11">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="F2" s="11">
-        <v>-2.7</v>
+        <v>-4.4</v>
       </c>
       <c r="G2" s="11">
-        <v>-1.7</v>
+        <v>-3.8</v>
       </c>
       <c r="H2" s="11">
         <v>56.1</v>
@@ -3351,28 +3367,28 @@
     </row>
     <row r="2" spans="1:8">
       <c r="A2" s="14">
-        <v>0.2845</v>
+        <v>0.2701</v>
       </c>
       <c r="B2" s="14">
-        <v>0.1776</v>
+        <v>0.1737</v>
       </c>
       <c r="C2" s="14">
-        <v>0.1614</v>
+        <v>0.1518</v>
       </c>
       <c r="D2" s="14">
-        <v>0.1592</v>
+        <v>0.151</v>
       </c>
       <c r="E2" s="14">
-        <v>0.1351</v>
+        <v>0.1006</v>
       </c>
       <c r="F2" s="14">
-        <v>0.0722</v>
+        <v>0.06950000000000001</v>
       </c>
       <c r="G2" s="14">
-        <v>-0.2526</v>
+        <v>-0.2592</v>
       </c>
       <c r="H2" s="14">
-        <v>-0.3046</v>
+        <v>-0.3032</v>
       </c>
     </row>
   </sheetData>

--- a/BIRLA_GROUP_Technical_Metrics.xlsx
+++ b/BIRLA_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="293" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="287" uniqueCount="74">
   <si>
     <t>Symbol</t>
   </si>
@@ -190,28 +190,19 @@
     <t>Curr Value</t>
   </si>
   <si>
-    <t>RSI Momentum</t>
-  </si>
-  <si>
-    <t>50.5 → 38.5</t>
-  </si>
-  <si>
-    <t>🔴 BEARISH</t>
-  </si>
-  <si>
-    <t>50.5</t>
-  </si>
-  <si>
-    <t>38.5</t>
-  </si>
-  <si>
-    <t>56.9 → 49.8</t>
-  </si>
-  <si>
-    <t>56.9</t>
-  </si>
-  <si>
-    <t>49.8</t>
+    <t>RSI Oversold Recovery</t>
+  </si>
+  <si>
+    <t>28.8 → 33.2</t>
+  </si>
+  <si>
+    <t>🟢 BULLISH</t>
+  </si>
+  <si>
+    <t>28.8</t>
+  </si>
+  <si>
+    <t>33.2</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -297,14 +288,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF006100"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF9C0006"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -337,13 +328,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -795,8 +786,8 @@
     <col min="13" max="13" width="10.7109375" customWidth="1"/>
     <col min="14" max="14" width="11.7109375" customWidth="1"/>
     <col min="15" max="15" width="10.7109375" customWidth="1"/>
-    <col min="16" max="16" width="9.7109375" customWidth="1"/>
-    <col min="17" max="19" width="10.7109375" customWidth="1"/>
+    <col min="16" max="17" width="9.7109375" customWidth="1"/>
+    <col min="18" max="19" width="10.7109375" customWidth="1"/>
     <col min="20" max="20" width="22.7109375" customWidth="1"/>
     <col min="21" max="21" width="9.7109375" customWidth="1"/>
     <col min="22" max="22" width="10.7109375" customWidth="1"/>
@@ -936,10 +927,10 @@
         <v>45</v>
       </c>
       <c r="C2">
-        <v>378.8</v>
+        <v>381.3</v>
       </c>
       <c r="D2">
-        <v>-4.1</v>
+        <v>0.66</v>
       </c>
       <c r="E2">
         <v>424.7</v>
@@ -948,46 +939,46 @@
         <v>278.9</v>
       </c>
       <c r="G2">
-        <v>-10.81</v>
+        <v>-10.22</v>
       </c>
       <c r="H2">
-        <v>35.82</v>
+        <v>36.72</v>
       </c>
       <c r="I2">
-        <v>-6.06</v>
+        <v>-3.94</v>
       </c>
       <c r="J2">
-        <v>-5.54</v>
+        <v>-4.36</v>
       </c>
       <c r="K2">
-        <v>1.34</v>
+        <v>2.38</v>
       </c>
       <c r="L2">
-        <v>31.69</v>
+        <v>31.48</v>
       </c>
       <c r="M2">
-        <v>27.01</v>
+        <v>27.12</v>
       </c>
       <c r="N2">
         <v>74</v>
       </c>
       <c r="O2">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="P2">
-        <v>394.15</v>
+        <v>391.02</v>
       </c>
       <c r="Q2">
-        <v>402.55</v>
+        <v>401.52</v>
       </c>
       <c r="R2">
-        <v>403.53</v>
+        <v>403.05</v>
       </c>
       <c r="S2">
-        <v>362.54</v>
+        <v>362.68</v>
       </c>
       <c r="T2">
-        <v>4.49</v>
+        <v>5.13</v>
       </c>
       <c r="U2" t="s">
         <v>46</v>
@@ -1002,43 +993,43 @@
         <v>2</v>
       </c>
       <c r="Y2">
-        <v>33.83</v>
+        <v>36.17</v>
       </c>
       <c r="Z2">
-        <v>-3.16</v>
+        <v>-4.23</v>
       </c>
       <c r="AA2">
-        <v>-0.8100000000000001</v>
+        <v>-1.5</v>
       </c>
       <c r="AB2">
-        <v>-2.35</v>
+        <v>-2.74</v>
       </c>
       <c r="AC2">
-        <v>14.49</v>
+        <v>6.61</v>
       </c>
       <c r="AD2">
-        <v>23.22</v>
+        <v>15.77</v>
       </c>
       <c r="AE2">
-        <v>9.6</v>
+        <v>9.35</v>
       </c>
       <c r="AF2">
-        <v>-12.04</v>
+        <v>-56.17</v>
       </c>
       <c r="AG2">
-        <v>419.13</v>
+        <v>420.63</v>
       </c>
       <c r="AH2">
-        <v>385.98</v>
+        <v>382.41</v>
       </c>
       <c r="AI2">
-        <v>416.61</v>
+        <v>409.07</v>
       </c>
       <c r="AJ2" t="s">
         <v>48</v>
       </c>
       <c r="AK2">
-        <v>29.09</v>
+        <v>33.18</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1049,10 +1040,10 @@
         <v>45</v>
       </c>
       <c r="C3">
-        <v>49.02</v>
+        <v>49.74</v>
       </c>
       <c r="D3">
-        <v>-2.82</v>
+        <v>1.47</v>
       </c>
       <c r="E3">
         <v>93.48</v>
@@ -1061,25 +1052,25 @@
         <v>49.02</v>
       </c>
       <c r="G3">
-        <v>-47.56</v>
+        <v>-46.79</v>
       </c>
       <c r="H3">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="I3">
-        <v>-7.87</v>
+        <v>-4.79</v>
       </c>
       <c r="J3">
-        <v>-12.43</v>
+        <v>-11.15</v>
       </c>
       <c r="K3">
-        <v>-19.6</v>
+        <v>-19.41</v>
       </c>
       <c r="L3">
-        <v>-44.81</v>
+        <v>-44.21</v>
       </c>
       <c r="M3">
-        <v>-25.92</v>
+        <v>-25.57</v>
       </c>
       <c r="N3">
         <v>13</v>
@@ -1088,19 +1079,19 @@
         <v>7</v>
       </c>
       <c r="P3">
-        <v>50.78</v>
+        <v>50.28</v>
       </c>
       <c r="Q3">
-        <v>52.59</v>
+        <v>52.33</v>
       </c>
       <c r="R3">
-        <v>56.32</v>
+        <v>56.13</v>
       </c>
       <c r="S3">
-        <v>63.96</v>
+        <v>63.82</v>
       </c>
       <c r="T3">
-        <v>-23.35</v>
+        <v>-22.06</v>
       </c>
       <c r="U3" t="s">
         <v>46</v>
@@ -1115,43 +1106,43 @@
         <v>0</v>
       </c>
       <c r="Y3">
-        <v>28.76</v>
+        <v>33.24</v>
       </c>
       <c r="Z3">
-        <v>-1.86</v>
+        <v>-1.87</v>
       </c>
       <c r="AA3">
-        <v>-1.75</v>
+        <v>-1.77</v>
       </c>
       <c r="AB3">
-        <v>-0.11</v>
+        <v>-0.1</v>
       </c>
       <c r="AC3">
-        <v>40.59</v>
+        <v>38.73</v>
       </c>
       <c r="AD3">
-        <v>53.18</v>
+        <v>44.39</v>
       </c>
       <c r="AE3">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="AF3">
-        <v>120.5</v>
+        <v>87.08</v>
       </c>
       <c r="AG3">
-        <v>56.19</v>
+        <v>55.96</v>
       </c>
       <c r="AH3">
-        <v>48.99</v>
+        <v>48.7</v>
       </c>
       <c r="AI3">
-        <v>54.83</v>
+        <v>54.78</v>
       </c>
       <c r="AJ3" t="s">
         <v>48</v>
       </c>
       <c r="AK3">
-        <v>33.2</v>
+        <v>33.75</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1162,10 +1153,10 @@
         <v>45</v>
       </c>
       <c r="C4">
-        <v>3171</v>
+        <v>3187</v>
       </c>
       <c r="D4">
-        <v>-3.38</v>
+        <v>0.5</v>
       </c>
       <c r="E4">
         <v>3380.5</v>
@@ -1174,46 +1165,46 @@
         <v>2531.1</v>
       </c>
       <c r="G4">
-        <v>-6.2</v>
+        <v>-5.72</v>
       </c>
       <c r="H4">
-        <v>25.28</v>
+        <v>25.91</v>
       </c>
       <c r="I4">
-        <v>-3.98</v>
+        <v>-3.62</v>
       </c>
       <c r="J4">
-        <v>-2.39</v>
+        <v>-1.95</v>
       </c>
       <c r="K4">
-        <v>0.98</v>
+        <v>1.16</v>
       </c>
       <c r="L4">
-        <v>13.83</v>
+        <v>13.86</v>
       </c>
       <c r="M4">
-        <v>15.1</v>
+        <v>15.62</v>
       </c>
       <c r="N4">
         <v>50</v>
       </c>
       <c r="O4">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="P4">
-        <v>3275.74</v>
+        <v>3251.78</v>
       </c>
       <c r="Q4">
-        <v>3293.31</v>
+        <v>3288.72</v>
       </c>
       <c r="R4">
-        <v>3225.9</v>
+        <v>3225.82</v>
       </c>
       <c r="S4">
-        <v>2953.49</v>
+        <v>2955.73</v>
       </c>
       <c r="T4">
-        <v>7.36</v>
+        <v>7.82</v>
       </c>
       <c r="U4" t="s">
         <v>47</v>
@@ -1228,34 +1219,34 @@
         <v>3</v>
       </c>
       <c r="Y4">
-        <v>38.51</v>
+        <v>40.7</v>
       </c>
       <c r="Z4">
-        <v>8.880000000000001</v>
+        <v>0.74</v>
       </c>
       <c r="AA4">
-        <v>23.58</v>
+        <v>19.01</v>
       </c>
       <c r="AB4">
-        <v>-14.69</v>
+        <v>-18.27</v>
       </c>
       <c r="AC4">
-        <v>11.26</v>
+        <v>2.94</v>
       </c>
       <c r="AD4">
-        <v>16.43</v>
+        <v>9.890000000000001</v>
       </c>
       <c r="AE4">
-        <v>65.90000000000001</v>
+        <v>64.23999999999999</v>
       </c>
       <c r="AF4">
-        <v>19.52</v>
+        <v>-25.62</v>
       </c>
       <c r="AG4">
-        <v>3366.86</v>
+        <v>3376.22</v>
       </c>
       <c r="AH4">
-        <v>3219.76</v>
+        <v>3201.23</v>
       </c>
       <c r="AI4">
         <v>3120.02</v>
@@ -1264,7 +1255,7 @@
         <v>49</v>
       </c>
       <c r="AK4">
-        <v>17.81</v>
+        <v>22.26</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1275,10 +1266,10 @@
         <v>45</v>
       </c>
       <c r="C5">
-        <v>958.7</v>
+        <v>972.7</v>
       </c>
       <c r="D5">
-        <v>-2.32</v>
+        <v>1.46</v>
       </c>
       <c r="E5">
         <v>1149.7</v>
@@ -1287,46 +1278,46 @@
         <v>741.05</v>
       </c>
       <c r="G5">
-        <v>-16.61</v>
+        <v>-15.4</v>
       </c>
       <c r="H5">
-        <v>29.37</v>
+        <v>31.26</v>
       </c>
       <c r="I5">
-        <v>-4.7</v>
+        <v>-3.6</v>
       </c>
       <c r="J5">
-        <v>-6.88</v>
+        <v>-7.35</v>
       </c>
       <c r="K5">
-        <v>-2.41</v>
+        <v>-3.49</v>
       </c>
       <c r="L5">
-        <v>29</v>
+        <v>30.98</v>
       </c>
       <c r="M5">
-        <v>15.18</v>
+        <v>15.68</v>
       </c>
       <c r="N5">
         <v>62</v>
       </c>
       <c r="O5">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="P5">
-        <v>998.02</v>
+        <v>990.76</v>
       </c>
       <c r="Q5">
-        <v>1021.25</v>
+        <v>1017.81</v>
       </c>
       <c r="R5">
-        <v>1001.66</v>
+        <v>1001.72</v>
       </c>
       <c r="S5">
-        <v>971.97</v>
+        <v>972.8</v>
       </c>
       <c r="T5">
-        <v>-1.37</v>
+        <v>-0.01</v>
       </c>
       <c r="U5" t="s">
         <v>47</v>
@@ -1341,43 +1332,43 @@
         <v>2</v>
       </c>
       <c r="Y5">
-        <v>34.23</v>
+        <v>39.21</v>
       </c>
       <c r="Z5">
-        <v>-7.54</v>
+        <v>-9.56</v>
       </c>
       <c r="AA5">
-        <v>-0.04</v>
+        <v>-1.94</v>
       </c>
       <c r="AB5">
-        <v>-7.5</v>
+        <v>-7.61</v>
       </c>
       <c r="AC5">
-        <v>6.69</v>
+        <v>8.68</v>
       </c>
       <c r="AD5">
-        <v>18.3</v>
+        <v>12.75</v>
       </c>
       <c r="AE5">
-        <v>23.57</v>
+        <v>23.47</v>
       </c>
       <c r="AF5">
-        <v>-26.29</v>
+        <v>15.06</v>
       </c>
       <c r="AG5">
-        <v>1069.2</v>
+        <v>1069.36</v>
       </c>
       <c r="AH5">
-        <v>973.3</v>
+        <v>966.25</v>
       </c>
       <c r="AI5">
-        <v>1040.57</v>
+        <v>1037.86</v>
       </c>
       <c r="AJ5" t="s">
         <v>48</v>
       </c>
       <c r="AK5">
-        <v>23.87</v>
+        <v>27.41</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1388,58 +1379,58 @@
         <v>45</v>
       </c>
       <c r="C6">
-        <v>14.45</v>
+        <v>14.26</v>
       </c>
       <c r="D6">
-        <v>-3.47</v>
+        <v>-1.31</v>
       </c>
       <c r="E6">
         <v>15.6</v>
       </c>
       <c r="F6">
-        <v>7.41</v>
+        <v>7.66</v>
       </c>
       <c r="G6">
-        <v>-7.37</v>
+        <v>-8.59</v>
       </c>
       <c r="H6">
-        <v>95.01000000000001</v>
+        <v>86.16</v>
       </c>
       <c r="I6">
-        <v>-7.37</v>
+        <v>-7.52</v>
       </c>
       <c r="J6">
-        <v>2.41</v>
+        <v>4.01</v>
       </c>
       <c r="K6">
-        <v>-1.16</v>
+        <v>-4.42</v>
       </c>
       <c r="L6">
-        <v>97.40000000000001</v>
+        <v>92.44</v>
       </c>
       <c r="M6">
-        <v>10.06</v>
+        <v>4.86</v>
       </c>
       <c r="N6">
         <v>87</v>
       </c>
       <c r="O6">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="P6">
-        <v>15.05</v>
+        <v>14.82</v>
       </c>
       <c r="Q6">
-        <v>14.67</v>
+        <v>14.68</v>
       </c>
       <c r="R6">
-        <v>13.9</v>
+        <v>13.91</v>
       </c>
       <c r="S6">
-        <v>12.05</v>
+        <v>12.07</v>
       </c>
       <c r="T6">
-        <v>19.95</v>
+        <v>18.17</v>
       </c>
       <c r="U6" t="s">
         <v>47</v>
@@ -1454,34 +1445,34 @@
         <v>3</v>
       </c>
       <c r="Y6">
-        <v>49.78</v>
+        <v>47.44</v>
       </c>
       <c r="Z6">
-        <v>0.33</v>
+        <v>0.26</v>
       </c>
       <c r="AA6">
-        <v>0.36</v>
+        <v>0.34</v>
       </c>
       <c r="AB6">
-        <v>-0.03</v>
+        <v>-0.08</v>
       </c>
       <c r="AC6">
-        <v>16.12</v>
+        <v>8.68</v>
       </c>
       <c r="AD6">
-        <v>35.71</v>
+        <v>21.29</v>
       </c>
       <c r="AE6">
-        <v>0.52</v>
+        <v>0.51</v>
       </c>
       <c r="AF6">
-        <v>-28.15</v>
+        <v>-37.62</v>
       </c>
       <c r="AG6">
-        <v>15.75</v>
+        <v>15.74</v>
       </c>
       <c r="AH6">
-        <v>13.6</v>
+        <v>13.62</v>
       </c>
       <c r="AI6">
         <v>14.01</v>
@@ -1490,7 +1481,7 @@
         <v>49</v>
       </c>
       <c r="AK6">
-        <v>31.45</v>
+        <v>30.14</v>
       </c>
     </row>
     <row r="7" spans="1:37">
@@ -1501,10 +1492,10 @@
         <v>45</v>
       </c>
       <c r="C7">
-        <v>12.6</v>
+        <v>12.36</v>
       </c>
       <c r="D7">
-        <v>4.91</v>
+        <v>-1.9</v>
       </c>
       <c r="E7">
         <v>13.92</v>
@@ -1513,25 +1504,25 @@
         <v>4.69</v>
       </c>
       <c r="G7">
-        <v>-9.48</v>
+        <v>-11.21</v>
       </c>
       <c r="H7">
-        <v>168.66</v>
+        <v>163.54</v>
       </c>
       <c r="I7">
-        <v>13.41</v>
+        <v>9.09</v>
       </c>
       <c r="J7">
-        <v>7.69</v>
+        <v>5.64</v>
       </c>
       <c r="K7">
-        <v>4.22</v>
+        <v>0.24</v>
       </c>
       <c r="L7">
-        <v>139.09</v>
+        <v>137.69</v>
       </c>
       <c r="M7">
-        <v>-30.32</v>
+        <v>-30.77</v>
       </c>
       <c r="N7">
         <v>99</v>
@@ -1540,19 +1531,19 @@
         <v>96</v>
       </c>
       <c r="P7">
-        <v>11.85</v>
+        <v>12.06</v>
       </c>
       <c r="Q7">
-        <v>11.44</v>
+        <v>11.46</v>
       </c>
       <c r="R7">
-        <v>11.62</v>
+        <v>11.65</v>
       </c>
       <c r="S7">
-        <v>10.52</v>
+        <v>10.56</v>
       </c>
       <c r="T7">
-        <v>19.77</v>
+        <v>17.1</v>
       </c>
       <c r="U7" t="s">
         <v>46</v>
@@ -1567,43 +1558,43 @@
         <v>2</v>
       </c>
       <c r="Y7">
-        <v>66.98</v>
+        <v>61.88</v>
       </c>
       <c r="Z7">
-        <v>0.04</v>
+        <v>0.09</v>
       </c>
       <c r="AA7">
-        <v>-0.11</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="AB7">
-        <v>0.14</v>
+        <v>0.16</v>
       </c>
       <c r="AC7">
-        <v>100</v>
+        <v>94.28</v>
       </c>
       <c r="AD7">
-        <v>100</v>
+        <v>98.09</v>
       </c>
       <c r="AE7">
-        <v>0.27</v>
+        <v>0.33</v>
       </c>
       <c r="AF7">
-        <v>493.26</v>
+        <v>210.43</v>
       </c>
       <c r="AG7">
-        <v>12.27</v>
+        <v>12.36</v>
       </c>
       <c r="AH7">
-        <v>10.61</v>
+        <v>10.56</v>
       </c>
       <c r="AI7">
-        <v>11.49</v>
+        <v>11.5</v>
       </c>
       <c r="AJ7" t="s">
         <v>49</v>
       </c>
       <c r="AK7">
-        <v>35.32</v>
+        <v>40.28</v>
       </c>
     </row>
     <row r="8" spans="1:37">
@@ -1614,37 +1605,37 @@
         <v>45</v>
       </c>
       <c r="C8">
-        <v>4081.8</v>
+        <v>4052.2</v>
       </c>
       <c r="D8">
-        <v>-2.62</v>
+        <v>-0.73</v>
       </c>
       <c r="E8">
         <v>5809.5</v>
       </c>
       <c r="F8">
-        <v>4081.8</v>
+        <v>4052.2</v>
       </c>
       <c r="G8">
-        <v>-29.74</v>
+        <v>-30.25</v>
       </c>
       <c r="H8">
         <v>0</v>
       </c>
       <c r="I8">
-        <v>-5.05</v>
+        <v>-4.92</v>
       </c>
       <c r="J8">
-        <v>-10.23</v>
+        <v>-10.88</v>
       </c>
       <c r="K8">
-        <v>-7.53</v>
+        <v>-8.550000000000001</v>
       </c>
       <c r="L8">
-        <v>-21.58</v>
+        <v>-23.35</v>
       </c>
       <c r="M8">
-        <v>17.37</v>
+        <v>17.01</v>
       </c>
       <c r="N8">
         <v>26</v>
@@ -1653,19 +1644,19 @@
         <v>30</v>
       </c>
       <c r="P8">
-        <v>4176.14</v>
+        <v>4134.24</v>
       </c>
       <c r="Q8">
-        <v>4308.36</v>
+        <v>4291.68</v>
       </c>
       <c r="R8">
-        <v>4348.19</v>
+        <v>4341.52</v>
       </c>
       <c r="S8">
-        <v>4598.44</v>
+        <v>4593.42</v>
       </c>
       <c r="T8">
-        <v>-11.24</v>
+        <v>-11.78</v>
       </c>
       <c r="U8" t="s">
         <v>46</v>
@@ -1680,43 +1671,43 @@
         <v>0</v>
       </c>
       <c r="Y8">
-        <v>34.28</v>
+        <v>32.91</v>
       </c>
       <c r="Z8">
-        <v>-56.06</v>
+        <v>-67.39</v>
       </c>
       <c r="AA8">
-        <v>-29.9</v>
+        <v>-37.4</v>
       </c>
       <c r="AB8">
-        <v>-26.16</v>
+        <v>-29.99</v>
       </c>
       <c r="AC8">
-        <v>36.99</v>
+        <v>23.55</v>
       </c>
       <c r="AD8">
-        <v>28.67</v>
+        <v>30.65</v>
       </c>
       <c r="AE8">
-        <v>113.54</v>
+        <v>110.65</v>
       </c>
       <c r="AF8">
-        <v>4.1</v>
+        <v>65.79000000000001</v>
       </c>
       <c r="AG8">
-        <v>4492.26</v>
+        <v>4504.3</v>
       </c>
       <c r="AH8">
-        <v>4124.46</v>
+        <v>4079.07</v>
       </c>
       <c r="AI8">
-        <v>4473.44</v>
+        <v>4395.41</v>
       </c>
       <c r="AJ8" t="s">
         <v>48</v>
       </c>
       <c r="AK8">
-        <v>42.63</v>
+        <v>47.51</v>
       </c>
     </row>
     <row r="9" spans="1:37">
@@ -1727,10 +1718,10 @@
         <v>45</v>
       </c>
       <c r="C9">
-        <v>10697</v>
+        <v>10700</v>
       </c>
       <c r="D9">
-        <v>-2.75</v>
+        <v>0.03</v>
       </c>
       <c r="E9">
         <v>13052</v>
@@ -1739,46 +1730,46 @@
         <v>10362</v>
       </c>
       <c r="G9">
-        <v>-18.04</v>
+        <v>-18.02</v>
       </c>
       <c r="H9">
-        <v>3.23</v>
+        <v>3.26</v>
       </c>
       <c r="I9">
-        <v>-4.28</v>
+        <v>-2.81</v>
       </c>
       <c r="J9">
-        <v>-7.94</v>
+        <v>-7.91</v>
       </c>
       <c r="K9">
-        <v>-6.09</v>
+        <v>-5.92</v>
       </c>
       <c r="L9">
-        <v>-14.27</v>
+        <v>-13.65</v>
       </c>
       <c r="M9">
-        <v>6.95</v>
+        <v>7.1</v>
       </c>
       <c r="N9">
         <v>38</v>
       </c>
       <c r="O9">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="P9">
-        <v>10917</v>
+        <v>10855.2</v>
       </c>
       <c r="Q9">
-        <v>11342.35</v>
+        <v>11302.4</v>
       </c>
       <c r="R9">
-        <v>11636.34</v>
+        <v>11617.36</v>
       </c>
       <c r="S9">
-        <v>11744.86</v>
+        <v>11740.28</v>
       </c>
       <c r="T9">
-        <v>-8.92</v>
+        <v>-8.859999999999999</v>
       </c>
       <c r="U9" t="s">
         <v>46</v>
@@ -1793,43 +1784,43 @@
         <v>0</v>
       </c>
       <c r="Y9">
-        <v>27.28</v>
+        <v>27.43</v>
       </c>
       <c r="Z9">
-        <v>-220.86</v>
+        <v>-239.31</v>
       </c>
       <c r="AA9">
-        <v>-155.82</v>
+        <v>-172.52</v>
       </c>
       <c r="AB9">
-        <v>-65.04000000000001</v>
+        <v>-66.79000000000001</v>
       </c>
       <c r="AC9">
-        <v>13.51</v>
+        <v>7.77</v>
       </c>
       <c r="AD9">
-        <v>11</v>
+        <v>11.6</v>
       </c>
       <c r="AE9">
-        <v>201.38</v>
+        <v>204.21</v>
       </c>
       <c r="AF9">
-        <v>36.28</v>
+        <v>-6.19</v>
       </c>
       <c r="AG9">
-        <v>11918.3</v>
+        <v>11940.13</v>
       </c>
       <c r="AH9">
-        <v>10766.4</v>
+        <v>10664.67</v>
       </c>
       <c r="AI9">
-        <v>11470.36</v>
+        <v>11372.12</v>
       </c>
       <c r="AJ9" t="s">
         <v>48</v>
       </c>
       <c r="AK9">
-        <v>45.17</v>
+        <v>46.93</v>
       </c>
     </row>
   </sheetData>
@@ -1970,7 +1961,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F71"/>
+  <dimension ref="A1:F70"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -2010,7 +2001,7 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B3" s="4" t="s">
         <v>56</v>
@@ -2028,1144 +2019,1124 @@
         <v>60</v>
       </c>
     </row>
-    <row r="4" spans="1:6">
-      <c r="A4" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="B4" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="C4" s="4" t="s">
+    <row r="5" spans="1:6">
+      <c r="A5" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="D4" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="E4" s="4" t="s">
+      <c r="B5" s="2"/>
+      <c r="C5" s="2"/>
+      <c r="D5" s="2"/>
+      <c r="E5" s="2"/>
+    </row>
+    <row r="6" spans="1:6">
+      <c r="A6" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B6" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="F4" s="4" t="s">
+      <c r="C6" s="3" t="s">
         <v>63</v>
       </c>
-    </row>
-    <row r="6" spans="1:6">
-      <c r="A6" s="2" t="s">
+      <c r="D6" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="B6" s="2"/>
-      <c r="C6" s="2"/>
-      <c r="D6" s="2"/>
-      <c r="E6" s="2"/>
+      <c r="E6" s="3" t="s">
+        <v>65</v>
+      </c>
     </row>
     <row r="7" spans="1:6">
-      <c r="A7" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="E7" s="3" t="s">
-        <v>68</v>
+      <c r="A7" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C7" s="6">
+        <v>-5.54</v>
+      </c>
+      <c r="D7" s="6">
+        <v>-4.36</v>
+      </c>
+      <c r="E7" s="7">
+        <v>1.18</v>
       </c>
     </row>
     <row r="8" spans="1:6">
       <c r="A8" s="5" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B8" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C8" s="6">
-        <v>-3.12</v>
+        <v>-12.43</v>
       </c>
       <c r="D8" s="6">
-        <v>-5.54</v>
+        <v>-11.15</v>
       </c>
       <c r="E8" s="7">
-        <v>-2.42</v>
+        <v>1.28</v>
       </c>
     </row>
     <row r="9" spans="1:6">
       <c r="A9" s="5" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B9" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C9" s="6">
-        <v>-11.09</v>
+        <v>-2.39</v>
       </c>
       <c r="D9" s="6">
-        <v>-12.43</v>
+        <v>-1.95</v>
       </c>
       <c r="E9" s="7">
-        <v>-1.34</v>
+        <v>0.44</v>
       </c>
     </row>
     <row r="10" spans="1:6">
       <c r="A10" s="5" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B10" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C10" s="6">
-        <v>0.76</v>
+        <v>-6.88</v>
       </c>
       <c r="D10" s="6">
-        <v>-2.39</v>
-      </c>
-      <c r="E10" s="7">
-        <v>-3.15</v>
+        <v>-7.35</v>
+      </c>
+      <c r="E10" s="8">
+        <v>-0.47</v>
       </c>
     </row>
     <row r="11" spans="1:6">
       <c r="A11" s="5" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B11" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C11" s="6">
-        <v>-6.19</v>
+        <v>2.41</v>
       </c>
       <c r="D11" s="6">
-        <v>-6.88</v>
+        <v>4.01</v>
       </c>
       <c r="E11" s="7">
-        <v>-0.6899999999999999</v>
+        <v>1.6</v>
       </c>
     </row>
     <row r="12" spans="1:6">
       <c r="A12" s="5" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B12" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C12" s="6">
-        <v>10.81</v>
+        <v>7.69</v>
       </c>
       <c r="D12" s="6">
-        <v>2.41</v>
-      </c>
-      <c r="E12" s="7">
-        <v>-8.4</v>
+        <v>5.64</v>
+      </c>
+      <c r="E12" s="8">
+        <v>-2.05</v>
       </c>
     </row>
     <row r="13" spans="1:6">
       <c r="A13" s="5" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B13" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C13" s="6">
-        <v>1.18</v>
+        <v>-10.23</v>
       </c>
       <c r="D13" s="6">
-        <v>7.69</v>
+        <v>-10.88</v>
       </c>
       <c r="E13" s="8">
-        <v>6.51</v>
+        <v>-0.65</v>
       </c>
     </row>
     <row r="14" spans="1:6">
       <c r="A14" s="5" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B14" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C14" s="6">
-        <v>-7.54</v>
+        <v>-7.94</v>
       </c>
       <c r="D14" s="6">
-        <v>-10.23</v>
+        <v>-7.91</v>
       </c>
       <c r="E14" s="7">
-        <v>-2.69</v>
+        <v>0.03</v>
       </c>
     </row>
     <row r="15" spans="1:6">
       <c r="A15" s="5" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C15" s="6">
-        <v>-6.03</v>
+        <v>-6.06</v>
       </c>
       <c r="D15" s="6">
-        <v>-7.94</v>
+        <v>-3.94</v>
       </c>
       <c r="E15" s="7">
-        <v>-1.91</v>
+        <v>2.12</v>
       </c>
     </row>
     <row r="16" spans="1:6">
       <c r="A16" s="5" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B16" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C16" s="6">
-        <v>-2.45</v>
+        <v>-7.87</v>
       </c>
       <c r="D16" s="6">
-        <v>-6.06</v>
+        <v>-4.79</v>
       </c>
       <c r="E16" s="7">
-        <v>-3.61</v>
+        <v>3.08</v>
       </c>
     </row>
     <row r="17" spans="1:5">
       <c r="A17" s="5" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B17" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C17" s="6">
-        <v>-4.78</v>
+        <v>-3.98</v>
       </c>
       <c r="D17" s="6">
-        <v>-7.87</v>
+        <v>-3.62</v>
       </c>
       <c r="E17" s="7">
-        <v>-3.09</v>
+        <v>0.36</v>
       </c>
     </row>
     <row r="18" spans="1:5">
       <c r="A18" s="5" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B18" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C18" s="6">
-        <v>-1.21</v>
+        <v>-4.7</v>
       </c>
       <c r="D18" s="6">
-        <v>-3.98</v>
+        <v>-3.6</v>
       </c>
       <c r="E18" s="7">
-        <v>-2.77</v>
+        <v>1.1</v>
       </c>
     </row>
     <row r="19" spans="1:5">
       <c r="A19" s="5" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B19" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C19" s="6">
-        <v>-2.92</v>
+        <v>-7.37</v>
       </c>
       <c r="D19" s="6">
-        <v>-4.7</v>
-      </c>
-      <c r="E19" s="7">
-        <v>-1.78</v>
+        <v>-7.52</v>
+      </c>
+      <c r="E19" s="8">
+        <v>-0.15</v>
       </c>
     </row>
     <row r="20" spans="1:5">
       <c r="A20" s="5" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B20" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C20" s="6">
-        <v>-0.33</v>
+        <v>13.41</v>
       </c>
       <c r="D20" s="6">
-        <v>-7.37</v>
-      </c>
-      <c r="E20" s="7">
-        <v>-7.04</v>
+        <v>9.09</v>
+      </c>
+      <c r="E20" s="8">
+        <v>-4.32</v>
       </c>
     </row>
     <row r="21" spans="1:5">
       <c r="A21" s="5" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B21" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C21" s="6">
-        <v>10.18</v>
+        <v>-5.05</v>
       </c>
       <c r="D21" s="6">
-        <v>13.41</v>
-      </c>
-      <c r="E21" s="8">
-        <v>3.23</v>
+        <v>-4.92</v>
+      </c>
+      <c r="E21" s="7">
+        <v>0.13</v>
       </c>
     </row>
     <row r="22" spans="1:5">
       <c r="A22" s="5" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B22" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C22" s="6">
-        <v>-3.06</v>
+        <v>-4.28</v>
       </c>
       <c r="D22" s="6">
-        <v>-5.05</v>
+        <v>-2.81</v>
       </c>
       <c r="E22" s="7">
-        <v>-1.99</v>
+        <v>1.47</v>
       </c>
     </row>
     <row r="23" spans="1:5">
       <c r="A23" s="5" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="C23" s="6">
-        <v>-3.58</v>
+        <v>31.69</v>
       </c>
       <c r="D23" s="6">
-        <v>-4.28</v>
-      </c>
-      <c r="E23" s="7">
-        <v>-0.7</v>
+        <v>31.48</v>
+      </c>
+      <c r="E23" s="8">
+        <v>-0.21</v>
       </c>
     </row>
     <row r="24" spans="1:5">
       <c r="A24" s="5" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B24" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C24" s="6">
-        <v>36.35</v>
+        <v>-44.81</v>
       </c>
       <c r="D24" s="6">
-        <v>31.69</v>
+        <v>-44.21</v>
       </c>
       <c r="E24" s="7">
-        <v>-4.66</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="25" spans="1:5">
       <c r="A25" s="5" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B25" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C25" s="6">
-        <v>-44.62</v>
+        <v>13.83</v>
       </c>
       <c r="D25" s="6">
-        <v>-44.81</v>
+        <v>13.86</v>
       </c>
       <c r="E25" s="7">
-        <v>-0.19</v>
+        <v>0.03</v>
       </c>
     </row>
     <row r="26" spans="1:5">
       <c r="A26" s="5" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B26" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C26" s="6">
-        <v>17.38</v>
+        <v>29</v>
       </c>
       <c r="D26" s="6">
-        <v>13.83</v>
+        <v>30.98</v>
       </c>
       <c r="E26" s="7">
-        <v>-3.55</v>
+        <v>1.98</v>
       </c>
     </row>
     <row r="27" spans="1:5">
       <c r="A27" s="5" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B27" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C27" s="6">
-        <v>32.12</v>
+        <v>97.40000000000001</v>
       </c>
       <c r="D27" s="6">
-        <v>29</v>
-      </c>
-      <c r="E27" s="7">
-        <v>-3.12</v>
+        <v>92.44</v>
+      </c>
+      <c r="E27" s="8">
+        <v>-4.96</v>
       </c>
     </row>
     <row r="28" spans="1:5">
       <c r="A28" s="5" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B28" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C28" s="6">
-        <v>105.91</v>
+        <v>139.09</v>
       </c>
       <c r="D28" s="6">
-        <v>97.40000000000001</v>
-      </c>
-      <c r="E28" s="7">
-        <v>-8.51</v>
+        <v>137.69</v>
+      </c>
+      <c r="E28" s="8">
+        <v>-1.4</v>
       </c>
     </row>
     <row r="29" spans="1:5">
       <c r="A29" s="5" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B29" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C29" s="6">
-        <v>128.33</v>
+        <v>-21.58</v>
       </c>
       <c r="D29" s="6">
-        <v>139.09</v>
+        <v>-23.35</v>
       </c>
       <c r="E29" s="8">
-        <v>10.76</v>
+        <v>-1.77</v>
       </c>
     </row>
     <row r="30" spans="1:5">
       <c r="A30" s="5" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B30" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C30" s="6">
-        <v>-19.34</v>
+        <v>-14.27</v>
       </c>
       <c r="D30" s="6">
-        <v>-21.58</v>
+        <v>-13.65</v>
       </c>
       <c r="E30" s="7">
-        <v>-2.24</v>
+        <v>0.62</v>
       </c>
     </row>
     <row r="31" spans="1:5">
       <c r="A31" s="5" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="B31" s="5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C31" s="6">
-        <v>-12.5</v>
+        <v>1.34</v>
       </c>
       <c r="D31" s="6">
-        <v>-14.27</v>
+        <v>2.38</v>
       </c>
       <c r="E31" s="7">
-        <v>-1.77</v>
+        <v>1.04</v>
       </c>
     </row>
     <row r="32" spans="1:5">
       <c r="A32" s="5" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B32" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C32" s="6">
-        <v>7.28</v>
+        <v>-19.6</v>
       </c>
       <c r="D32" s="6">
-        <v>1.34</v>
+        <v>-19.41</v>
       </c>
       <c r="E32" s="7">
-        <v>-5.94</v>
+        <v>0.19</v>
       </c>
     </row>
     <row r="33" spans="1:5">
       <c r="A33" s="5" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B33" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C33" s="6">
-        <v>-17.37</v>
+        <v>0.98</v>
       </c>
       <c r="D33" s="6">
-        <v>-19.6</v>
+        <v>1.16</v>
       </c>
       <c r="E33" s="7">
-        <v>-2.23</v>
+        <v>0.18</v>
       </c>
     </row>
     <row r="34" spans="1:5">
       <c r="A34" s="5" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B34" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C34" s="6">
-        <v>3.71</v>
+        <v>-2.41</v>
       </c>
       <c r="D34" s="6">
-        <v>0.98</v>
-      </c>
-      <c r="E34" s="7">
-        <v>-2.73</v>
+        <v>-3.49</v>
+      </c>
+      <c r="E34" s="8">
+        <v>-1.08</v>
       </c>
     </row>
     <row r="35" spans="1:5">
       <c r="A35" s="5" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B35" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C35" s="6">
-        <v>-3.2</v>
+        <v>-1.16</v>
       </c>
       <c r="D35" s="6">
-        <v>-2.41</v>
+        <v>-4.42</v>
       </c>
       <c r="E35" s="8">
-        <v>0.79</v>
+        <v>-3.26</v>
       </c>
     </row>
     <row r="36" spans="1:5">
       <c r="A36" s="5" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B36" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C36" s="6">
-        <v>0.13</v>
+        <v>4.22</v>
       </c>
       <c r="D36" s="6">
-        <v>-1.16</v>
-      </c>
-      <c r="E36" s="7">
-        <v>-1.29</v>
+        <v>0.24</v>
+      </c>
+      <c r="E36" s="8">
+        <v>-3.98</v>
       </c>
     </row>
     <row r="37" spans="1:5">
       <c r="A37" s="5" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B37" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C37" s="6">
-        <v>4.25</v>
+        <v>-7.53</v>
       </c>
       <c r="D37" s="6">
-        <v>4.22</v>
-      </c>
-      <c r="E37" s="7">
-        <v>-0.03</v>
+        <v>-8.550000000000001</v>
+      </c>
+      <c r="E37" s="8">
+        <v>-1.02</v>
       </c>
     </row>
     <row r="38" spans="1:5">
       <c r="A38" s="5" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B38" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C38" s="6">
-        <v>-4.31</v>
+        <v>-6.09</v>
       </c>
       <c r="D38" s="6">
-        <v>-7.53</v>
+        <v>-5.92</v>
       </c>
       <c r="E38" s="7">
-        <v>-3.22</v>
+        <v>0.17</v>
       </c>
     </row>
     <row r="39" spans="1:5">
       <c r="A39" s="5" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="B39" s="5" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C39" s="6">
-        <v>-4.06</v>
+        <v>-10.81</v>
       </c>
       <c r="D39" s="6">
-        <v>-6.09</v>
+        <v>-10.22</v>
       </c>
       <c r="E39" s="7">
-        <v>-2.03</v>
+        <v>0.59</v>
       </c>
     </row>
     <row r="40" spans="1:5">
       <c r="A40" s="5" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B40" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C40" s="6">
-        <v>-6.99</v>
+        <v>-47.56</v>
       </c>
       <c r="D40" s="6">
-        <v>-10.81</v>
+        <v>-46.79</v>
       </c>
       <c r="E40" s="7">
-        <v>-3.82</v>
+        <v>0.77</v>
       </c>
     </row>
     <row r="41" spans="1:5">
       <c r="A41" s="5" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B41" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C41" s="6">
-        <v>-46.04</v>
+        <v>-6.2</v>
       </c>
       <c r="D41" s="6">
-        <v>-47.56</v>
+        <v>-5.72</v>
       </c>
       <c r="E41" s="7">
-        <v>-1.52</v>
+        <v>0.48</v>
       </c>
     </row>
     <row r="42" spans="1:5">
       <c r="A42" s="5" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B42" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C42" s="6">
-        <v>-2.92</v>
+        <v>-16.61</v>
       </c>
       <c r="D42" s="6">
-        <v>-6.2</v>
+        <v>-15.4</v>
       </c>
       <c r="E42" s="7">
-        <v>-3.28</v>
+        <v>1.21</v>
       </c>
     </row>
     <row r="43" spans="1:5">
       <c r="A43" s="5" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B43" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C43" s="6">
-        <v>-14.63</v>
+        <v>-7.37</v>
       </c>
       <c r="D43" s="6">
-        <v>-16.61</v>
-      </c>
-      <c r="E43" s="7">
-        <v>-1.98</v>
+        <v>-8.59</v>
+      </c>
+      <c r="E43" s="8">
+        <v>-1.22</v>
       </c>
     </row>
     <row r="44" spans="1:5">
       <c r="A44" s="5" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B44" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C44" s="6">
-        <v>-4.04</v>
+        <v>-9.48</v>
       </c>
       <c r="D44" s="6">
-        <v>-7.37</v>
-      </c>
-      <c r="E44" s="7">
-        <v>-3.33</v>
+        <v>-11.21</v>
+      </c>
+      <c r="E44" s="8">
+        <v>-1.73</v>
       </c>
     </row>
     <row r="45" spans="1:5">
       <c r="A45" s="5" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B45" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C45" s="6">
-        <v>-13.72</v>
+        <v>-29.74</v>
       </c>
       <c r="D45" s="6">
-        <v>-9.48</v>
+        <v>-30.25</v>
       </c>
       <c r="E45" s="8">
-        <v>4.24</v>
+        <v>-0.51</v>
       </c>
     </row>
     <row r="46" spans="1:5">
       <c r="A46" s="5" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B46" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C46" s="6">
-        <v>-27.85</v>
+        <v>-18.04</v>
       </c>
       <c r="D46" s="6">
-        <v>-29.74</v>
+        <v>-18.02</v>
       </c>
       <c r="E46" s="7">
-        <v>-1.89</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="47" spans="1:5">
       <c r="A47" s="5" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="B47" s="5" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="C47" s="6">
-        <v>-15.72</v>
+        <v>378.8</v>
       </c>
       <c r="D47" s="6">
-        <v>-18.04</v>
+        <v>381.3</v>
       </c>
       <c r="E47" s="7">
-        <v>-2.32</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="48" spans="1:5">
       <c r="A48" s="5" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B48" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C48" s="6">
-        <v>395</v>
+        <v>49.02</v>
       </c>
       <c r="D48" s="6">
-        <v>378.8</v>
+        <v>49.74</v>
       </c>
       <c r="E48" s="7">
-        <v>-16.2</v>
+        <v>0.72</v>
       </c>
     </row>
     <row r="49" spans="1:5">
       <c r="A49" s="5" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B49" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C49" s="6">
-        <v>50.44</v>
+        <v>3171</v>
       </c>
       <c r="D49" s="6">
-        <v>49.02</v>
+        <v>3187</v>
       </c>
       <c r="E49" s="7">
-        <v>-1.42</v>
+        <v>16</v>
       </c>
     </row>
     <row r="50" spans="1:5">
       <c r="A50" s="5" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B50" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C50" s="6">
-        <v>3281.9</v>
+        <v>958.7</v>
       </c>
       <c r="D50" s="6">
-        <v>3171</v>
+        <v>972.7</v>
       </c>
       <c r="E50" s="7">
-        <v>-110.9</v>
+        <v>14</v>
       </c>
     </row>
     <row r="51" spans="1:5">
       <c r="A51" s="5" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B51" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C51" s="6">
-        <v>981.5</v>
+        <v>14.45</v>
       </c>
       <c r="D51" s="6">
-        <v>958.7</v>
-      </c>
-      <c r="E51" s="7">
-        <v>-22.8</v>
+        <v>14.26</v>
+      </c>
+      <c r="E51" s="8">
+        <v>-0.19</v>
       </c>
     </row>
     <row r="52" spans="1:5">
       <c r="A52" s="5" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B52" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C52" s="6">
-        <v>14.97</v>
+        <v>12.6</v>
       </c>
       <c r="D52" s="6">
-        <v>14.45</v>
-      </c>
-      <c r="E52" s="7">
-        <v>-0.52</v>
+        <v>12.36</v>
+      </c>
+      <c r="E52" s="8">
+        <v>-0.24</v>
       </c>
     </row>
     <row r="53" spans="1:5">
       <c r="A53" s="5" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B53" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C53" s="6">
-        <v>12.01</v>
+        <v>4081.8</v>
       </c>
       <c r="D53" s="6">
-        <v>12.6</v>
+        <v>4052.2</v>
       </c>
       <c r="E53" s="8">
-        <v>0.59</v>
+        <v>-29.6</v>
       </c>
     </row>
     <row r="54" spans="1:5">
       <c r="A54" s="5" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B54" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C54" s="6">
-        <v>4191.6</v>
+        <v>10697</v>
       </c>
       <c r="D54" s="6">
-        <v>4081.8</v>
+        <v>10700</v>
       </c>
       <c r="E54" s="7">
-        <v>-109.8</v>
+        <v>3</v>
       </c>
     </row>
     <row r="55" spans="1:5">
       <c r="A55" s="5" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="B55" s="5" t="s">
-        <v>2</v>
+        <v>24</v>
       </c>
       <c r="C55" s="6">
-        <v>11000</v>
+        <v>33.83</v>
       </c>
       <c r="D55" s="6">
-        <v>10697</v>
+        <v>36.17</v>
       </c>
       <c r="E55" s="7">
-        <v>-303</v>
+        <v>2.34</v>
       </c>
     </row>
     <row r="56" spans="1:5">
       <c r="A56" s="5" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B56" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C56" s="6">
-        <v>43.4</v>
+        <v>28.76</v>
       </c>
       <c r="D56" s="6">
-        <v>33.83</v>
+        <v>33.24</v>
       </c>
       <c r="E56" s="7">
-        <v>-9.57</v>
+        <v>4.48</v>
       </c>
     </row>
     <row r="57" spans="1:5">
       <c r="A57" s="5" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B57" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C57" s="6">
-        <v>32.79</v>
+        <v>38.51</v>
       </c>
       <c r="D57" s="6">
-        <v>28.76</v>
+        <v>40.7</v>
       </c>
       <c r="E57" s="7">
-        <v>-4.03</v>
+        <v>2.19</v>
       </c>
     </row>
     <row r="58" spans="1:5">
       <c r="A58" s="5" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B58" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C58" s="6">
-        <v>50.53</v>
+        <v>34.23</v>
       </c>
       <c r="D58" s="6">
-        <v>38.51</v>
+        <v>39.21</v>
       </c>
       <c r="E58" s="7">
-        <v>-12.02</v>
+        <v>4.98</v>
       </c>
     </row>
     <row r="59" spans="1:5">
       <c r="A59" s="5" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B59" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C59" s="6">
-        <v>39.07</v>
+        <v>49.78</v>
       </c>
       <c r="D59" s="6">
-        <v>34.23</v>
-      </c>
-      <c r="E59" s="7">
-        <v>-4.84</v>
+        <v>47.44</v>
+      </c>
+      <c r="E59" s="8">
+        <v>-2.34</v>
       </c>
     </row>
     <row r="60" spans="1:5">
       <c r="A60" s="5" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B60" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C60" s="6">
-        <v>56.93</v>
+        <v>66.98</v>
       </c>
       <c r="D60" s="6">
-        <v>49.78</v>
-      </c>
-      <c r="E60" s="7">
-        <v>-7.15</v>
+        <v>61.88</v>
+      </c>
+      <c r="E60" s="8">
+        <v>-5.1</v>
       </c>
     </row>
     <row r="61" spans="1:5">
       <c r="A61" s="5" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B61" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C61" s="6">
-        <v>59.33</v>
+        <v>34.28</v>
       </c>
       <c r="D61" s="6">
-        <v>66.98</v>
+        <v>32.91</v>
       </c>
       <c r="E61" s="8">
-        <v>7.65</v>
+        <v>-1.37</v>
       </c>
     </row>
     <row r="62" spans="1:5">
       <c r="A62" s="5" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B62" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C62" s="6">
-        <v>40.04</v>
+        <v>27.28</v>
       </c>
       <c r="D62" s="6">
-        <v>34.28</v>
+        <v>27.43</v>
       </c>
       <c r="E62" s="7">
-        <v>-5.76</v>
+        <v>0.15</v>
       </c>
     </row>
     <row r="63" spans="1:5">
       <c r="A63" s="5" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="B63" s="5" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="C63" s="6">
-        <v>33.71</v>
+        <v>-12.04</v>
       </c>
       <c r="D63" s="6">
-        <v>27.28</v>
-      </c>
-      <c r="E63" s="7">
-        <v>-6.43</v>
+        <v>-56.17</v>
+      </c>
+      <c r="E63" s="8">
+        <v>-44.13</v>
       </c>
     </row>
     <row r="64" spans="1:5">
       <c r="A64" s="5" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B64" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C64" s="6">
-        <v>-44</v>
+        <v>120.5</v>
       </c>
       <c r="D64" s="6">
-        <v>-12.04</v>
+        <v>87.08</v>
       </c>
       <c r="E64" s="8">
-        <v>31.96</v>
+        <v>-33.42</v>
       </c>
     </row>
     <row r="65" spans="1:5">
       <c r="A65" s="5" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B65" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C65" s="6">
-        <v>0.36</v>
+        <v>19.52</v>
       </c>
       <c r="D65" s="6">
-        <v>120.5</v>
+        <v>-25.62</v>
       </c>
       <c r="E65" s="8">
-        <v>120.14</v>
+        <v>-45.14</v>
       </c>
     </row>
     <row r="66" spans="1:5">
       <c r="A66" s="5" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B66" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C66" s="6">
-        <v>-54.75</v>
+        <v>-26.29</v>
       </c>
       <c r="D66" s="6">
-        <v>19.52</v>
-      </c>
-      <c r="E66" s="8">
-        <v>74.27</v>
+        <v>15.06</v>
+      </c>
+      <c r="E66" s="7">
+        <v>41.35</v>
       </c>
     </row>
     <row r="67" spans="1:5">
       <c r="A67" s="5" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B67" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C67" s="6">
-        <v>55.57</v>
+        <v>-28.15</v>
       </c>
       <c r="D67" s="6">
-        <v>-26.29</v>
-      </c>
-      <c r="E67" s="7">
-        <v>-81.86</v>
+        <v>-37.62</v>
+      </c>
+      <c r="E67" s="8">
+        <v>-9.470000000000001</v>
       </c>
     </row>
     <row r="68" spans="1:5">
       <c r="A68" s="5" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B68" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C68" s="6">
-        <v>6.72</v>
+        <v>493.26</v>
       </c>
       <c r="D68" s="6">
-        <v>-28.15</v>
-      </c>
-      <c r="E68" s="7">
-        <v>-34.87</v>
+        <v>210.43</v>
+      </c>
+      <c r="E68" s="8">
+        <v>-282.83</v>
       </c>
     </row>
     <row r="69" spans="1:5">
       <c r="A69" s="5" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B69" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C69" s="6">
-        <v>336.55</v>
+        <v>4.1</v>
       </c>
       <c r="D69" s="6">
-        <v>493.26</v>
-      </c>
-      <c r="E69" s="8">
-        <v>156.71</v>
+        <v>65.79000000000001</v>
+      </c>
+      <c r="E69" s="7">
+        <v>61.69</v>
       </c>
     </row>
     <row r="70" spans="1:5">
       <c r="A70" s="5" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B70" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C70" s="6">
-        <v>-50.6</v>
+        <v>36.28</v>
       </c>
       <c r="D70" s="6">
-        <v>4.1</v>
+        <v>-6.19</v>
       </c>
       <c r="E70" s="8">
-        <v>54.7</v>
-      </c>
-    </row>
-    <row r="71" spans="1:5">
-      <c r="A71" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="B71" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C71" s="6">
-        <v>-10.72</v>
-      </c>
-      <c r="D71" s="6">
-        <v>36.28</v>
-      </c>
-      <c r="E71" s="8">
-        <v>47</v>
+        <v>-42.47</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A6:E6"/>
+    <mergeCell ref="A5:E5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3189,28 +3160,28 @@
         <v>1</v>
       </c>
       <c r="B1" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="C1" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="D1" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="E1" s="9" t="s">
         <v>69</v>
       </c>
-      <c r="C1" s="9" t="s">
+      <c r="F1" s="9" t="s">
         <v>70</v>
       </c>
-      <c r="D1" s="9" t="s">
+      <c r="G1" s="9" t="s">
         <v>71</v>
       </c>
-      <c r="E1" s="9" t="s">
+      <c r="H1" s="9" t="s">
         <v>72</v>
       </c>
-      <c r="F1" s="9" t="s">
+      <c r="I1" s="9" t="s">
         <v>73</v>
-      </c>
-      <c r="G1" s="9" t="s">
-        <v>74</v>
-      </c>
-      <c r="H1" s="9" t="s">
-        <v>75</v>
-      </c>
-      <c r="I1" s="9" t="s">
-        <v>76</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -3224,16 +3195,16 @@
         <v>8</v>
       </c>
       <c r="D2" s="11">
-        <v>39.2</v>
+        <v>39.9</v>
       </c>
       <c r="E2" s="11">
         <v>50</v>
       </c>
       <c r="F2" s="11">
-        <v>-4.4</v>
+        <v>-4.2</v>
       </c>
       <c r="G2" s="11">
-        <v>-3.8</v>
+        <v>-4.8</v>
       </c>
       <c r="H2" s="11">
         <v>56.1</v>
@@ -3353,10 +3324,10 @@
         <v>39</v>
       </c>
       <c r="E1" s="13" t="s">
+        <v>44</v>
+      </c>
+      <c r="F1" s="13" t="s">
         <v>41</v>
-      </c>
-      <c r="F1" s="13" t="s">
-        <v>44</v>
       </c>
       <c r="G1" s="13" t="s">
         <v>38</v>
@@ -3367,28 +3338,28 @@
     </row>
     <row r="2" spans="1:8">
       <c r="A2" s="14">
-        <v>0.2701</v>
+        <v>0.2712</v>
       </c>
       <c r="B2" s="14">
-        <v>0.1737</v>
+        <v>0.1701</v>
       </c>
       <c r="C2" s="14">
-        <v>0.1518</v>
+        <v>0.1568</v>
       </c>
       <c r="D2" s="14">
-        <v>0.151</v>
+        <v>0.1562</v>
       </c>
       <c r="E2" s="14">
-        <v>0.1006</v>
+        <v>0.07099999999999999</v>
       </c>
       <c r="F2" s="14">
-        <v>0.06950000000000001</v>
+        <v>0.0486</v>
       </c>
       <c r="G2" s="14">
-        <v>-0.2592</v>
+        <v>-0.2557</v>
       </c>
       <c r="H2" s="14">
-        <v>-0.3032</v>
+        <v>-0.3077</v>
       </c>
     </row>
   </sheetData>

--- a/BIRLA_GROUP_Technical_Metrics.xlsx
+++ b/BIRLA_GROUP_Technical_Metrics.xlsx
@@ -193,16 +193,16 @@
     <t>RSI Oversold Recovery</t>
   </si>
   <si>
-    <t>28.8 → 33.2</t>
+    <t>27.4 → 30.7</t>
   </si>
   <si>
     <t>🟢 BULLISH</t>
   </si>
   <si>
-    <t>28.8</t>
-  </si>
-  <si>
-    <t>33.2</t>
+    <t>27.4</t>
+  </si>
+  <si>
+    <t>30.7</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -787,7 +787,8 @@
     <col min="14" max="14" width="11.7109375" customWidth="1"/>
     <col min="15" max="15" width="10.7109375" customWidth="1"/>
     <col min="16" max="17" width="9.7109375" customWidth="1"/>
-    <col min="18" max="19" width="10.7109375" customWidth="1"/>
+    <col min="18" max="18" width="10.7109375" customWidth="1"/>
+    <col min="19" max="19" width="9.7109375" customWidth="1"/>
     <col min="20" max="20" width="22.7109375" customWidth="1"/>
     <col min="21" max="21" width="9.7109375" customWidth="1"/>
     <col min="22" max="22" width="10.7109375" customWidth="1"/>
@@ -927,10 +928,10 @@
         <v>45</v>
       </c>
       <c r="C2">
-        <v>381.3</v>
+        <v>390</v>
       </c>
       <c r="D2">
-        <v>0.66</v>
+        <v>2.28</v>
       </c>
       <c r="E2">
         <v>424.7</v>
@@ -939,46 +940,46 @@
         <v>278.9</v>
       </c>
       <c r="G2">
-        <v>-10.22</v>
+        <v>-8.17</v>
       </c>
       <c r="H2">
-        <v>36.72</v>
+        <v>39.84</v>
       </c>
       <c r="I2">
-        <v>-3.94</v>
+        <v>-2.5</v>
       </c>
       <c r="J2">
-        <v>-4.36</v>
+        <v>-2.99</v>
       </c>
       <c r="K2">
-        <v>2.38</v>
+        <v>5.23</v>
       </c>
       <c r="L2">
-        <v>31.48</v>
+        <v>33.79</v>
       </c>
       <c r="M2">
-        <v>27.12</v>
+        <v>28.95</v>
       </c>
       <c r="N2">
         <v>74</v>
       </c>
       <c r="O2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="P2">
-        <v>391.02</v>
+        <v>389.02</v>
       </c>
       <c r="Q2">
-        <v>401.52</v>
+        <v>401.22</v>
       </c>
       <c r="R2">
-        <v>403.05</v>
+        <v>403.14</v>
       </c>
       <c r="S2">
-        <v>362.68</v>
+        <v>362.84</v>
       </c>
       <c r="T2">
-        <v>5.13</v>
+        <v>7.48</v>
       </c>
       <c r="U2" t="s">
         <v>46</v>
@@ -993,34 +994,34 @@
         <v>2</v>
       </c>
       <c r="Y2">
-        <v>36.17</v>
+        <v>43.64</v>
       </c>
       <c r="Z2">
-        <v>-4.23</v>
+        <v>-4.33</v>
       </c>
       <c r="AA2">
-        <v>-1.5</v>
+        <v>-2.06</v>
       </c>
       <c r="AB2">
-        <v>-2.74</v>
+        <v>-2.27</v>
       </c>
       <c r="AC2">
-        <v>6.61</v>
+        <v>20.85</v>
       </c>
       <c r="AD2">
-        <v>15.77</v>
+        <v>13.99</v>
       </c>
       <c r="AE2">
-        <v>9.35</v>
+        <v>9.41</v>
       </c>
       <c r="AF2">
-        <v>-56.17</v>
+        <v>-4.15</v>
       </c>
       <c r="AG2">
-        <v>420.63</v>
+        <v>420.88</v>
       </c>
       <c r="AH2">
-        <v>382.41</v>
+        <v>381.56</v>
       </c>
       <c r="AI2">
         <v>409.07</v>
@@ -1029,7 +1030,7 @@
         <v>48</v>
       </c>
       <c r="AK2">
-        <v>33.18</v>
+        <v>32.04</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1040,10 +1041,10 @@
         <v>45</v>
       </c>
       <c r="C3">
-        <v>49.74</v>
+        <v>50.45</v>
       </c>
       <c r="D3">
-        <v>1.47</v>
+        <v>1.43</v>
       </c>
       <c r="E3">
         <v>93.48</v>
@@ -1052,46 +1053,46 @@
         <v>49.02</v>
       </c>
       <c r="G3">
-        <v>-46.79</v>
+        <v>-46.03</v>
       </c>
       <c r="H3">
-        <v>1.47</v>
+        <v>2.92</v>
       </c>
       <c r="I3">
-        <v>-4.79</v>
+        <v>-1.71</v>
       </c>
       <c r="J3">
-        <v>-11.15</v>
+        <v>-8.220000000000001</v>
       </c>
       <c r="K3">
-        <v>-19.41</v>
+        <v>-18.02</v>
       </c>
       <c r="L3">
-        <v>-44.21</v>
+        <v>-42.92</v>
       </c>
       <c r="M3">
-        <v>-25.57</v>
+        <v>-24.97</v>
       </c>
       <c r="N3">
         <v>13</v>
       </c>
       <c r="O3">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="P3">
-        <v>50.28</v>
+        <v>50.11</v>
       </c>
       <c r="Q3">
-        <v>52.33</v>
+        <v>52.13</v>
       </c>
       <c r="R3">
-        <v>56.13</v>
+        <v>55.97</v>
       </c>
       <c r="S3">
-        <v>63.82</v>
+        <v>63.68</v>
       </c>
       <c r="T3">
-        <v>-22.06</v>
+        <v>-20.78</v>
       </c>
       <c r="U3" t="s">
         <v>46</v>
@@ -1106,34 +1107,34 @@
         <v>0</v>
       </c>
       <c r="Y3">
-        <v>33.24</v>
+        <v>37.41</v>
       </c>
       <c r="Z3">
-        <v>-1.87</v>
+        <v>-1.8</v>
       </c>
       <c r="AA3">
-        <v>-1.77</v>
+        <v>-1.78</v>
       </c>
       <c r="AB3">
-        <v>-0.1</v>
+        <v>-0.02</v>
       </c>
       <c r="AC3">
-        <v>38.73</v>
+        <v>47.71</v>
       </c>
       <c r="AD3">
-        <v>44.39</v>
+        <v>42.35</v>
       </c>
       <c r="AE3">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="AF3">
-        <v>87.08</v>
+        <v>-45.19</v>
       </c>
       <c r="AG3">
-        <v>55.96</v>
+        <v>55.7</v>
       </c>
       <c r="AH3">
-        <v>48.7</v>
+        <v>48.55</v>
       </c>
       <c r="AI3">
         <v>54.78</v>
@@ -1142,7 +1143,7 @@
         <v>48</v>
       </c>
       <c r="AK3">
-        <v>33.75</v>
+        <v>33.54</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1153,10 +1154,10 @@
         <v>45</v>
       </c>
       <c r="C4">
-        <v>3187</v>
+        <v>3173.1</v>
       </c>
       <c r="D4">
-        <v>0.5</v>
+        <v>-0.44</v>
       </c>
       <c r="E4">
         <v>3380.5</v>
@@ -1165,46 +1166,46 @@
         <v>2531.1</v>
       </c>
       <c r="G4">
-        <v>-5.72</v>
+        <v>-6.14</v>
       </c>
       <c r="H4">
-        <v>25.91</v>
+        <v>25.36</v>
       </c>
       <c r="I4">
-        <v>-3.62</v>
+        <v>-3.85</v>
       </c>
       <c r="J4">
-        <v>-1.95</v>
+        <v>-3.22</v>
       </c>
       <c r="K4">
-        <v>1.16</v>
+        <v>0.89</v>
       </c>
       <c r="L4">
-        <v>13.86</v>
+        <v>13.24</v>
       </c>
       <c r="M4">
-        <v>15.62</v>
+        <v>15.67</v>
       </c>
       <c r="N4">
         <v>50</v>
       </c>
       <c r="O4">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="P4">
-        <v>3251.78</v>
+        <v>3226.4</v>
       </c>
       <c r="Q4">
-        <v>3288.72</v>
+        <v>3283.88</v>
       </c>
       <c r="R4">
-        <v>3225.82</v>
+        <v>3226.59</v>
       </c>
       <c r="S4">
-        <v>2955.73</v>
+        <v>2957.9</v>
       </c>
       <c r="T4">
-        <v>7.82</v>
+        <v>7.28</v>
       </c>
       <c r="U4" t="s">
         <v>47</v>
@@ -1219,34 +1220,34 @@
         <v>3</v>
       </c>
       <c r="Y4">
-        <v>40.7</v>
+        <v>39.39</v>
       </c>
       <c r="Z4">
-        <v>0.74</v>
+        <v>-6.75</v>
       </c>
       <c r="AA4">
-        <v>19.01</v>
+        <v>13.86</v>
       </c>
       <c r="AB4">
-        <v>-18.27</v>
+        <v>-20.61</v>
       </c>
       <c r="AC4">
-        <v>2.94</v>
+        <v>4.12</v>
       </c>
       <c r="AD4">
-        <v>9.890000000000001</v>
+        <v>6.11</v>
       </c>
       <c r="AE4">
-        <v>64.23999999999999</v>
+        <v>62.94</v>
       </c>
       <c r="AF4">
-        <v>-25.62</v>
+        <v>-34.89</v>
       </c>
       <c r="AG4">
-        <v>3376.22</v>
+        <v>3385.36</v>
       </c>
       <c r="AH4">
-        <v>3201.23</v>
+        <v>3182.4</v>
       </c>
       <c r="AI4">
         <v>3120.02</v>
@@ -1255,7 +1256,7 @@
         <v>49</v>
       </c>
       <c r="AK4">
-        <v>22.26</v>
+        <v>25.73</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1266,10 +1267,10 @@
         <v>45</v>
       </c>
       <c r="C5">
-        <v>972.7</v>
+        <v>980.5</v>
       </c>
       <c r="D5">
-        <v>1.46</v>
+        <v>0.8</v>
       </c>
       <c r="E5">
         <v>1149.7</v>
@@ -1278,46 +1279,46 @@
         <v>741.05</v>
       </c>
       <c r="G5">
-        <v>-15.4</v>
+        <v>-14.72</v>
       </c>
       <c r="H5">
-        <v>31.26</v>
+        <v>32.31</v>
       </c>
       <c r="I5">
-        <v>-3.6</v>
+        <v>-4.52</v>
       </c>
       <c r="J5">
-        <v>-7.35</v>
+        <v>-5.87</v>
       </c>
       <c r="K5">
-        <v>-3.49</v>
+        <v>-2.78</v>
       </c>
       <c r="L5">
-        <v>30.98</v>
+        <v>29.35</v>
       </c>
       <c r="M5">
-        <v>15.68</v>
+        <v>16.36</v>
       </c>
       <c r="N5">
         <v>62</v>
       </c>
       <c r="O5">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="P5">
-        <v>990.76</v>
+        <v>981.48</v>
       </c>
       <c r="Q5">
-        <v>1017.81</v>
+        <v>1014.88</v>
       </c>
       <c r="R5">
-        <v>1001.72</v>
+        <v>1001.9</v>
       </c>
       <c r="S5">
-        <v>972.8</v>
+        <v>973.66</v>
       </c>
       <c r="T5">
-        <v>-0.01</v>
+        <v>0.7</v>
       </c>
       <c r="U5" t="s">
         <v>47</v>
@@ -1329,37 +1330,37 @@
         <v>47</v>
       </c>
       <c r="X5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Y5">
-        <v>39.21</v>
+        <v>41.85</v>
       </c>
       <c r="Z5">
-        <v>-9.56</v>
+        <v>-10.41</v>
       </c>
       <c r="AA5">
-        <v>-1.94</v>
+        <v>-3.64</v>
       </c>
       <c r="AB5">
-        <v>-7.61</v>
+        <v>-6.77</v>
       </c>
       <c r="AC5">
-        <v>8.68</v>
+        <v>21.97</v>
       </c>
       <c r="AD5">
-        <v>12.75</v>
+        <v>12.45</v>
       </c>
       <c r="AE5">
-        <v>23.47</v>
+        <v>22.99</v>
       </c>
       <c r="AF5">
-        <v>15.06</v>
+        <v>-9.41</v>
       </c>
       <c r="AG5">
-        <v>1069.36</v>
+        <v>1068</v>
       </c>
       <c r="AH5">
-        <v>966.25</v>
+        <v>961.77</v>
       </c>
       <c r="AI5">
         <v>1037.86</v>
@@ -1368,7 +1369,7 @@
         <v>48</v>
       </c>
       <c r="AK5">
-        <v>27.41</v>
+        <v>28.21</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1379,58 +1380,58 @@
         <v>45</v>
       </c>
       <c r="C6">
-        <v>14.26</v>
+        <v>14.22</v>
       </c>
       <c r="D6">
-        <v>-1.31</v>
+        <v>-0.28</v>
       </c>
       <c r="E6">
         <v>15.6</v>
       </c>
       <c r="F6">
-        <v>7.66</v>
+        <v>7.77</v>
       </c>
       <c r="G6">
-        <v>-8.59</v>
+        <v>-8.85</v>
       </c>
       <c r="H6">
-        <v>86.16</v>
+        <v>83.01000000000001</v>
       </c>
       <c r="I6">
-        <v>-7.52</v>
+        <v>-8.380000000000001</v>
       </c>
       <c r="J6">
-        <v>4.01</v>
+        <v>0.71</v>
       </c>
       <c r="K6">
-        <v>-4.42</v>
+        <v>-5.26</v>
       </c>
       <c r="L6">
-        <v>92.44</v>
+        <v>85.64</v>
       </c>
       <c r="M6">
-        <v>4.86</v>
+        <v>4.99</v>
       </c>
       <c r="N6">
         <v>87</v>
       </c>
       <c r="O6">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="P6">
-        <v>14.82</v>
+        <v>14.56</v>
       </c>
       <c r="Q6">
-        <v>14.68</v>
+        <v>14.69</v>
       </c>
       <c r="R6">
         <v>13.91</v>
       </c>
       <c r="S6">
-        <v>12.07</v>
+        <v>12.09</v>
       </c>
       <c r="T6">
-        <v>18.17</v>
+        <v>17.63</v>
       </c>
       <c r="U6" t="s">
         <v>47</v>
@@ -1445,34 +1446,34 @@
         <v>3</v>
       </c>
       <c r="Y6">
-        <v>47.44</v>
+        <v>46.94</v>
       </c>
       <c r="Z6">
-        <v>0.26</v>
+        <v>0.2</v>
       </c>
       <c r="AA6">
-        <v>0.34</v>
+        <v>0.32</v>
       </c>
       <c r="AB6">
-        <v>-0.08</v>
+        <v>-0.11</v>
       </c>
       <c r="AC6">
-        <v>8.68</v>
+        <v>0</v>
       </c>
       <c r="AD6">
-        <v>21.29</v>
+        <v>8.27</v>
       </c>
       <c r="AE6">
-        <v>0.51</v>
+        <v>0.49</v>
       </c>
       <c r="AF6">
-        <v>-37.62</v>
+        <v>-62.23</v>
       </c>
       <c r="AG6">
-        <v>15.74</v>
+        <v>15.73</v>
       </c>
       <c r="AH6">
-        <v>13.62</v>
+        <v>13.64</v>
       </c>
       <c r="AI6">
         <v>14.01</v>
@@ -1481,7 +1482,7 @@
         <v>49</v>
       </c>
       <c r="AK6">
-        <v>30.14</v>
+        <v>29.01</v>
       </c>
     </row>
     <row r="7" spans="1:37">
@@ -1492,10 +1493,10 @@
         <v>45</v>
       </c>
       <c r="C7">
-        <v>12.36</v>
+        <v>12.34</v>
       </c>
       <c r="D7">
-        <v>-1.9</v>
+        <v>-0.16</v>
       </c>
       <c r="E7">
         <v>13.92</v>
@@ -1504,46 +1505,46 @@
         <v>4.69</v>
       </c>
       <c r="G7">
-        <v>-11.21</v>
+        <v>-11.35</v>
       </c>
       <c r="H7">
-        <v>163.54</v>
+        <v>163.11</v>
       </c>
       <c r="I7">
-        <v>9.09</v>
+        <v>6.84</v>
       </c>
       <c r="J7">
-        <v>5.64</v>
+        <v>3.26</v>
       </c>
       <c r="K7">
-        <v>0.24</v>
+        <v>0.41</v>
       </c>
       <c r="L7">
-        <v>137.69</v>
+        <v>147.29</v>
       </c>
       <c r="M7">
-        <v>-30.77</v>
+        <v>-30.66</v>
       </c>
       <c r="N7">
         <v>99</v>
       </c>
       <c r="O7">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="P7">
-        <v>12.06</v>
+        <v>12.22</v>
       </c>
       <c r="Q7">
-        <v>11.46</v>
+        <v>11.49</v>
       </c>
       <c r="R7">
-        <v>11.65</v>
+        <v>11.69</v>
       </c>
       <c r="S7">
-        <v>10.56</v>
+        <v>10.59</v>
       </c>
       <c r="T7">
-        <v>17.1</v>
+        <v>16.53</v>
       </c>
       <c r="U7" t="s">
         <v>46</v>
@@ -1558,34 +1559,34 @@
         <v>2</v>
       </c>
       <c r="Y7">
-        <v>61.88</v>
+        <v>61.46</v>
       </c>
       <c r="Z7">
-        <v>0.09</v>
+        <v>0.13</v>
       </c>
       <c r="AA7">
-        <v>-0.07000000000000001</v>
+        <v>-0.03</v>
       </c>
       <c r="AB7">
         <v>0.16</v>
       </c>
       <c r="AC7">
-        <v>94.28</v>
+        <v>88.09</v>
       </c>
       <c r="AD7">
-        <v>98.09</v>
+        <v>94.13</v>
       </c>
       <c r="AE7">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="AF7">
-        <v>210.43</v>
+        <v>7.02</v>
       </c>
       <c r="AG7">
-        <v>12.36</v>
+        <v>12.47</v>
       </c>
       <c r="AH7">
-        <v>10.56</v>
+        <v>10.52</v>
       </c>
       <c r="AI7">
         <v>11.5</v>
@@ -1594,7 +1595,7 @@
         <v>49</v>
       </c>
       <c r="AK7">
-        <v>40.28</v>
+        <v>44.57</v>
       </c>
     </row>
     <row r="8" spans="1:37">
@@ -1605,10 +1606,10 @@
         <v>45</v>
       </c>
       <c r="C8">
-        <v>4052.2</v>
+        <v>4082.2</v>
       </c>
       <c r="D8">
-        <v>-0.73</v>
+        <v>0.74</v>
       </c>
       <c r="E8">
         <v>5809.5</v>
@@ -1617,46 +1618,46 @@
         <v>4052.2</v>
       </c>
       <c r="G8">
-        <v>-30.25</v>
+        <v>-29.73</v>
       </c>
       <c r="H8">
-        <v>0</v>
+        <v>0.74</v>
       </c>
       <c r="I8">
-        <v>-4.92</v>
+        <v>-0.67</v>
       </c>
       <c r="J8">
-        <v>-10.88</v>
+        <v>-6.92</v>
       </c>
       <c r="K8">
-        <v>-8.550000000000001</v>
+        <v>-8.07</v>
       </c>
       <c r="L8">
-        <v>-23.35</v>
+        <v>-21.64</v>
       </c>
       <c r="M8">
-        <v>17.01</v>
+        <v>17.14</v>
       </c>
       <c r="N8">
         <v>26</v>
       </c>
       <c r="O8">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="P8">
-        <v>4134.24</v>
+        <v>4128.72</v>
       </c>
       <c r="Q8">
-        <v>4291.68</v>
+        <v>4281.2</v>
       </c>
       <c r="R8">
-        <v>4341.52</v>
+        <v>4337.01</v>
       </c>
       <c r="S8">
-        <v>4593.42</v>
+        <v>4588.27</v>
       </c>
       <c r="T8">
-        <v>-11.78</v>
+        <v>-11.03</v>
       </c>
       <c r="U8" t="s">
         <v>46</v>
@@ -1671,43 +1672,43 @@
         <v>0</v>
       </c>
       <c r="Y8">
-        <v>32.91</v>
+        <v>35.72</v>
       </c>
       <c r="Z8">
-        <v>-67.39</v>
+        <v>-73.11</v>
       </c>
       <c r="AA8">
-        <v>-37.4</v>
+        <v>-44.54</v>
       </c>
       <c r="AB8">
-        <v>-29.99</v>
+        <v>-28.57</v>
       </c>
       <c r="AC8">
-        <v>23.55</v>
+        <v>18.59</v>
       </c>
       <c r="AD8">
-        <v>30.65</v>
+        <v>26.38</v>
       </c>
       <c r="AE8">
-        <v>110.65</v>
+        <v>106.02</v>
       </c>
       <c r="AF8">
-        <v>65.79000000000001</v>
+        <v>-30.36</v>
       </c>
       <c r="AG8">
-        <v>4504.3</v>
+        <v>4513.54</v>
       </c>
       <c r="AH8">
-        <v>4079.07</v>
+        <v>4048.87</v>
       </c>
       <c r="AI8">
-        <v>4395.41</v>
+        <v>4394.81</v>
       </c>
       <c r="AJ8" t="s">
         <v>48</v>
       </c>
       <c r="AK8">
-        <v>47.51</v>
+        <v>51.74</v>
       </c>
     </row>
     <row r="9" spans="1:37">
@@ -1718,10 +1719,10 @@
         <v>45</v>
       </c>
       <c r="C9">
-        <v>10700</v>
+        <v>10764</v>
       </c>
       <c r="D9">
-        <v>0.03</v>
+        <v>0.6</v>
       </c>
       <c r="E9">
         <v>13052</v>
@@ -1730,25 +1731,25 @@
         <v>10362</v>
       </c>
       <c r="G9">
-        <v>-18.02</v>
+        <v>-17.53</v>
       </c>
       <c r="H9">
-        <v>3.26</v>
+        <v>3.88</v>
       </c>
       <c r="I9">
-        <v>-2.81</v>
+        <v>-1.25</v>
       </c>
       <c r="J9">
-        <v>-7.91</v>
+        <v>-6.39</v>
       </c>
       <c r="K9">
-        <v>-5.92</v>
+        <v>-5.83</v>
       </c>
       <c r="L9">
-        <v>-13.65</v>
+        <v>-12.98</v>
       </c>
       <c r="M9">
-        <v>7.1</v>
+        <v>7.38</v>
       </c>
       <c r="N9">
         <v>38</v>
@@ -1757,19 +1758,19 @@
         <v>43</v>
       </c>
       <c r="P9">
-        <v>10855.2</v>
+        <v>10828</v>
       </c>
       <c r="Q9">
-        <v>11302.4</v>
+        <v>11268.1</v>
       </c>
       <c r="R9">
-        <v>11617.36</v>
+        <v>11605.58</v>
       </c>
       <c r="S9">
-        <v>11740.28</v>
+        <v>11736.1</v>
       </c>
       <c r="T9">
-        <v>-8.859999999999999</v>
+        <v>-8.279999999999999</v>
       </c>
       <c r="U9" t="s">
         <v>46</v>
@@ -1784,43 +1785,43 @@
         <v>0</v>
       </c>
       <c r="Y9">
-        <v>27.43</v>
+        <v>30.66</v>
       </c>
       <c r="Z9">
-        <v>-239.31</v>
+        <v>-245.94</v>
       </c>
       <c r="AA9">
-        <v>-172.52</v>
+        <v>-187.2</v>
       </c>
       <c r="AB9">
-        <v>-66.79000000000001</v>
+        <v>-58.74</v>
       </c>
       <c r="AC9">
-        <v>7.77</v>
+        <v>6.47</v>
       </c>
       <c r="AD9">
-        <v>11.6</v>
+        <v>9.25</v>
       </c>
       <c r="AE9">
-        <v>204.21</v>
+        <v>199.69</v>
       </c>
       <c r="AF9">
-        <v>-6.19</v>
+        <v>-28.96</v>
       </c>
       <c r="AG9">
-        <v>11940.13</v>
+        <v>11944.99</v>
       </c>
       <c r="AH9">
-        <v>10664.67</v>
+        <v>10591.21</v>
       </c>
       <c r="AI9">
-        <v>11372.12</v>
+        <v>11371.08</v>
       </c>
       <c r="AJ9" t="s">
         <v>48</v>
       </c>
       <c r="AK9">
-        <v>46.93</v>
+        <v>48.46</v>
       </c>
     </row>
   </sheetData>
@@ -2001,7 +2002,7 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="4" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="B3" s="4" t="s">
         <v>56</v>
@@ -2053,13 +2054,13 @@
         <v>9</v>
       </c>
       <c r="C7" s="6">
-        <v>-5.54</v>
+        <v>-4.36</v>
       </c>
       <c r="D7" s="6">
-        <v>-4.36</v>
+        <v>-2.99</v>
       </c>
       <c r="E7" s="7">
-        <v>1.18</v>
+        <v>1.37</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -2070,13 +2071,13 @@
         <v>9</v>
       </c>
       <c r="C8" s="6">
-        <v>-12.43</v>
+        <v>-11.15</v>
       </c>
       <c r="D8" s="6">
-        <v>-11.15</v>
+        <v>-8.220000000000001</v>
       </c>
       <c r="E8" s="7">
-        <v>1.28</v>
+        <v>2.93</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -2087,13 +2088,13 @@
         <v>9</v>
       </c>
       <c r="C9" s="6">
-        <v>-2.39</v>
+        <v>-1.95</v>
       </c>
       <c r="D9" s="6">
-        <v>-1.95</v>
-      </c>
-      <c r="E9" s="7">
-        <v>0.44</v>
+        <v>-3.22</v>
+      </c>
+      <c r="E9" s="8">
+        <v>-1.27</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -2104,13 +2105,13 @@
         <v>9</v>
       </c>
       <c r="C10" s="6">
-        <v>-6.88</v>
+        <v>-7.35</v>
       </c>
       <c r="D10" s="6">
-        <v>-7.35</v>
-      </c>
-      <c r="E10" s="8">
-        <v>-0.47</v>
+        <v>-5.87</v>
+      </c>
+      <c r="E10" s="7">
+        <v>1.48</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -2121,13 +2122,13 @@
         <v>9</v>
       </c>
       <c r="C11" s="6">
-        <v>2.41</v>
+        <v>4.01</v>
       </c>
       <c r="D11" s="6">
-        <v>4.01</v>
-      </c>
-      <c r="E11" s="7">
-        <v>1.6</v>
+        <v>0.71</v>
+      </c>
+      <c r="E11" s="8">
+        <v>-3.3</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -2138,13 +2139,13 @@
         <v>9</v>
       </c>
       <c r="C12" s="6">
-        <v>7.69</v>
+        <v>5.64</v>
       </c>
       <c r="D12" s="6">
-        <v>5.64</v>
+        <v>3.26</v>
       </c>
       <c r="E12" s="8">
-        <v>-2.05</v>
+        <v>-2.38</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -2155,13 +2156,13 @@
         <v>9</v>
       </c>
       <c r="C13" s="6">
-        <v>-10.23</v>
+        <v>-10.88</v>
       </c>
       <c r="D13" s="6">
-        <v>-10.88</v>
-      </c>
-      <c r="E13" s="8">
-        <v>-0.65</v>
+        <v>-6.92</v>
+      </c>
+      <c r="E13" s="7">
+        <v>3.96</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -2172,13 +2173,13 @@
         <v>9</v>
       </c>
       <c r="C14" s="6">
-        <v>-7.94</v>
+        <v>-7.91</v>
       </c>
       <c r="D14" s="6">
-        <v>-7.91</v>
+        <v>-6.39</v>
       </c>
       <c r="E14" s="7">
-        <v>0.03</v>
+        <v>1.52</v>
       </c>
     </row>
     <row r="15" spans="1:6">
@@ -2189,13 +2190,13 @@
         <v>8</v>
       </c>
       <c r="C15" s="6">
-        <v>-6.06</v>
+        <v>-3.94</v>
       </c>
       <c r="D15" s="6">
-        <v>-3.94</v>
+        <v>-2.5</v>
       </c>
       <c r="E15" s="7">
-        <v>2.12</v>
+        <v>1.44</v>
       </c>
     </row>
     <row r="16" spans="1:6">
@@ -2206,10 +2207,10 @@
         <v>8</v>
       </c>
       <c r="C16" s="6">
-        <v>-7.87</v>
+        <v>-4.79</v>
       </c>
       <c r="D16" s="6">
-        <v>-4.79</v>
+        <v>-1.71</v>
       </c>
       <c r="E16" s="7">
         <v>3.08</v>
@@ -2223,13 +2224,13 @@
         <v>8</v>
       </c>
       <c r="C17" s="6">
-        <v>-3.98</v>
+        <v>-3.62</v>
       </c>
       <c r="D17" s="6">
-        <v>-3.62</v>
-      </c>
-      <c r="E17" s="7">
-        <v>0.36</v>
+        <v>-3.85</v>
+      </c>
+      <c r="E17" s="8">
+        <v>-0.23</v>
       </c>
     </row>
     <row r="18" spans="1:5">
@@ -2240,13 +2241,13 @@
         <v>8</v>
       </c>
       <c r="C18" s="6">
-        <v>-4.7</v>
+        <v>-3.6</v>
       </c>
       <c r="D18" s="6">
-        <v>-3.6</v>
-      </c>
-      <c r="E18" s="7">
-        <v>1.1</v>
+        <v>-4.52</v>
+      </c>
+      <c r="E18" s="8">
+        <v>-0.92</v>
       </c>
     </row>
     <row r="19" spans="1:5">
@@ -2257,13 +2258,13 @@
         <v>8</v>
       </c>
       <c r="C19" s="6">
-        <v>-7.37</v>
+        <v>-7.52</v>
       </c>
       <c r="D19" s="6">
-        <v>-7.52</v>
+        <v>-8.380000000000001</v>
       </c>
       <c r="E19" s="8">
-        <v>-0.15</v>
+        <v>-0.86</v>
       </c>
     </row>
     <row r="20" spans="1:5">
@@ -2274,13 +2275,13 @@
         <v>8</v>
       </c>
       <c r="C20" s="6">
-        <v>13.41</v>
+        <v>9.09</v>
       </c>
       <c r="D20" s="6">
-        <v>9.09</v>
+        <v>6.84</v>
       </c>
       <c r="E20" s="8">
-        <v>-4.32</v>
+        <v>-2.25</v>
       </c>
     </row>
     <row r="21" spans="1:5">
@@ -2291,13 +2292,13 @@
         <v>8</v>
       </c>
       <c r="C21" s="6">
-        <v>-5.05</v>
+        <v>-4.92</v>
       </c>
       <c r="D21" s="6">
-        <v>-4.92</v>
+        <v>-0.67</v>
       </c>
       <c r="E21" s="7">
-        <v>0.13</v>
+        <v>4.25</v>
       </c>
     </row>
     <row r="22" spans="1:5">
@@ -2308,13 +2309,13 @@
         <v>8</v>
       </c>
       <c r="C22" s="6">
-        <v>-4.28</v>
+        <v>-2.81</v>
       </c>
       <c r="D22" s="6">
-        <v>-2.81</v>
+        <v>-1.25</v>
       </c>
       <c r="E22" s="7">
-        <v>1.47</v>
+        <v>1.56</v>
       </c>
     </row>
     <row r="23" spans="1:5">
@@ -2325,13 +2326,13 @@
         <v>11</v>
       </c>
       <c r="C23" s="6">
-        <v>31.69</v>
+        <v>31.48</v>
       </c>
       <c r="D23" s="6">
-        <v>31.48</v>
-      </c>
-      <c r="E23" s="8">
-        <v>-0.21</v>
+        <v>33.79</v>
+      </c>
+      <c r="E23" s="7">
+        <v>2.31</v>
       </c>
     </row>
     <row r="24" spans="1:5">
@@ -2342,13 +2343,13 @@
         <v>11</v>
       </c>
       <c r="C24" s="6">
-        <v>-44.81</v>
+        <v>-44.21</v>
       </c>
       <c r="D24" s="6">
-        <v>-44.21</v>
+        <v>-42.92</v>
       </c>
       <c r="E24" s="7">
-        <v>0.6</v>
+        <v>1.29</v>
       </c>
     </row>
     <row r="25" spans="1:5">
@@ -2359,13 +2360,13 @@
         <v>11</v>
       </c>
       <c r="C25" s="6">
-        <v>13.83</v>
+        <v>13.86</v>
       </c>
       <c r="D25" s="6">
-        <v>13.86</v>
-      </c>
-      <c r="E25" s="7">
-        <v>0.03</v>
+        <v>13.24</v>
+      </c>
+      <c r="E25" s="8">
+        <v>-0.62</v>
       </c>
     </row>
     <row r="26" spans="1:5">
@@ -2376,13 +2377,13 @@
         <v>11</v>
       </c>
       <c r="C26" s="6">
-        <v>29</v>
+        <v>30.98</v>
       </c>
       <c r="D26" s="6">
-        <v>30.98</v>
-      </c>
-      <c r="E26" s="7">
-        <v>1.98</v>
+        <v>29.35</v>
+      </c>
+      <c r="E26" s="8">
+        <v>-1.63</v>
       </c>
     </row>
     <row r="27" spans="1:5">
@@ -2393,13 +2394,13 @@
         <v>11</v>
       </c>
       <c r="C27" s="6">
-        <v>97.40000000000001</v>
+        <v>92.44</v>
       </c>
       <c r="D27" s="6">
-        <v>92.44</v>
+        <v>85.64</v>
       </c>
       <c r="E27" s="8">
-        <v>-4.96</v>
+        <v>-6.8</v>
       </c>
     </row>
     <row r="28" spans="1:5">
@@ -2410,13 +2411,13 @@
         <v>11</v>
       </c>
       <c r="C28" s="6">
-        <v>139.09</v>
+        <v>137.69</v>
       </c>
       <c r="D28" s="6">
-        <v>137.69</v>
-      </c>
-      <c r="E28" s="8">
-        <v>-1.4</v>
+        <v>147.29</v>
+      </c>
+      <c r="E28" s="7">
+        <v>9.6</v>
       </c>
     </row>
     <row r="29" spans="1:5">
@@ -2427,13 +2428,13 @@
         <v>11</v>
       </c>
       <c r="C29" s="6">
-        <v>-21.58</v>
+        <v>-23.35</v>
       </c>
       <c r="D29" s="6">
-        <v>-23.35</v>
-      </c>
-      <c r="E29" s="8">
-        <v>-1.77</v>
+        <v>-21.64</v>
+      </c>
+      <c r="E29" s="7">
+        <v>1.71</v>
       </c>
     </row>
     <row r="30" spans="1:5">
@@ -2444,13 +2445,13 @@
         <v>11</v>
       </c>
       <c r="C30" s="6">
-        <v>-14.27</v>
+        <v>-13.65</v>
       </c>
       <c r="D30" s="6">
-        <v>-13.65</v>
+        <v>-12.98</v>
       </c>
       <c r="E30" s="7">
-        <v>0.62</v>
+        <v>0.67</v>
       </c>
     </row>
     <row r="31" spans="1:5">
@@ -2461,13 +2462,13 @@
         <v>10</v>
       </c>
       <c r="C31" s="6">
-        <v>1.34</v>
+        <v>2.38</v>
       </c>
       <c r="D31" s="6">
-        <v>2.38</v>
+        <v>5.23</v>
       </c>
       <c r="E31" s="7">
-        <v>1.04</v>
+        <v>2.85</v>
       </c>
     </row>
     <row r="32" spans="1:5">
@@ -2478,13 +2479,13 @@
         <v>10</v>
       </c>
       <c r="C32" s="6">
-        <v>-19.6</v>
+        <v>-19.41</v>
       </c>
       <c r="D32" s="6">
-        <v>-19.41</v>
+        <v>-18.02</v>
       </c>
       <c r="E32" s="7">
-        <v>0.19</v>
+        <v>1.39</v>
       </c>
     </row>
     <row r="33" spans="1:5">
@@ -2495,13 +2496,13 @@
         <v>10</v>
       </c>
       <c r="C33" s="6">
-        <v>0.98</v>
+        <v>1.16</v>
       </c>
       <c r="D33" s="6">
-        <v>1.16</v>
-      </c>
-      <c r="E33" s="7">
-        <v>0.18</v>
+        <v>0.89</v>
+      </c>
+      <c r="E33" s="8">
+        <v>-0.27</v>
       </c>
     </row>
     <row r="34" spans="1:5">
@@ -2512,13 +2513,13 @@
         <v>10</v>
       </c>
       <c r="C34" s="6">
-        <v>-2.41</v>
+        <v>-3.49</v>
       </c>
       <c r="D34" s="6">
-        <v>-3.49</v>
-      </c>
-      <c r="E34" s="8">
-        <v>-1.08</v>
+        <v>-2.78</v>
+      </c>
+      <c r="E34" s="7">
+        <v>0.71</v>
       </c>
     </row>
     <row r="35" spans="1:5">
@@ -2529,13 +2530,13 @@
         <v>10</v>
       </c>
       <c r="C35" s="6">
-        <v>-1.16</v>
+        <v>-4.42</v>
       </c>
       <c r="D35" s="6">
-        <v>-4.42</v>
+        <v>-5.26</v>
       </c>
       <c r="E35" s="8">
-        <v>-3.26</v>
+        <v>-0.84</v>
       </c>
     </row>
     <row r="36" spans="1:5">
@@ -2546,13 +2547,13 @@
         <v>10</v>
       </c>
       <c r="C36" s="6">
-        <v>4.22</v>
+        <v>0.24</v>
       </c>
       <c r="D36" s="6">
-        <v>0.24</v>
-      </c>
-      <c r="E36" s="8">
-        <v>-3.98</v>
+        <v>0.41</v>
+      </c>
+      <c r="E36" s="7">
+        <v>0.17</v>
       </c>
     </row>
     <row r="37" spans="1:5">
@@ -2563,13 +2564,13 @@
         <v>10</v>
       </c>
       <c r="C37" s="6">
-        <v>-7.53</v>
+        <v>-8.550000000000001</v>
       </c>
       <c r="D37" s="6">
-        <v>-8.550000000000001</v>
-      </c>
-      <c r="E37" s="8">
-        <v>-1.02</v>
+        <v>-8.07</v>
+      </c>
+      <c r="E37" s="7">
+        <v>0.48</v>
       </c>
     </row>
     <row r="38" spans="1:5">
@@ -2580,13 +2581,13 @@
         <v>10</v>
       </c>
       <c r="C38" s="6">
-        <v>-6.09</v>
+        <v>-5.92</v>
       </c>
       <c r="D38" s="6">
-        <v>-5.92</v>
+        <v>-5.83</v>
       </c>
       <c r="E38" s="7">
-        <v>0.17</v>
+        <v>0.09</v>
       </c>
     </row>
     <row r="39" spans="1:5">
@@ -2597,13 +2598,13 @@
         <v>6</v>
       </c>
       <c r="C39" s="6">
-        <v>-10.81</v>
+        <v>-10.22</v>
       </c>
       <c r="D39" s="6">
-        <v>-10.22</v>
+        <v>-8.17</v>
       </c>
       <c r="E39" s="7">
-        <v>0.59</v>
+        <v>2.05</v>
       </c>
     </row>
     <row r="40" spans="1:5">
@@ -2614,13 +2615,13 @@
         <v>6</v>
       </c>
       <c r="C40" s="6">
-        <v>-47.56</v>
+        <v>-46.79</v>
       </c>
       <c r="D40" s="6">
-        <v>-46.79</v>
+        <v>-46.03</v>
       </c>
       <c r="E40" s="7">
-        <v>0.77</v>
+        <v>0.76</v>
       </c>
     </row>
     <row r="41" spans="1:5">
@@ -2631,13 +2632,13 @@
         <v>6</v>
       </c>
       <c r="C41" s="6">
-        <v>-6.2</v>
+        <v>-5.72</v>
       </c>
       <c r="D41" s="6">
-        <v>-5.72</v>
-      </c>
-      <c r="E41" s="7">
-        <v>0.48</v>
+        <v>-6.14</v>
+      </c>
+      <c r="E41" s="8">
+        <v>-0.42</v>
       </c>
     </row>
     <row r="42" spans="1:5">
@@ -2648,13 +2649,13 @@
         <v>6</v>
       </c>
       <c r="C42" s="6">
-        <v>-16.61</v>
+        <v>-15.4</v>
       </c>
       <c r="D42" s="6">
-        <v>-15.4</v>
+        <v>-14.72</v>
       </c>
       <c r="E42" s="7">
-        <v>1.21</v>
+        <v>0.68</v>
       </c>
     </row>
     <row r="43" spans="1:5">
@@ -2665,13 +2666,13 @@
         <v>6</v>
       </c>
       <c r="C43" s="6">
-        <v>-7.37</v>
+        <v>-8.59</v>
       </c>
       <c r="D43" s="6">
-        <v>-8.59</v>
+        <v>-8.85</v>
       </c>
       <c r="E43" s="8">
-        <v>-1.22</v>
+        <v>-0.26</v>
       </c>
     </row>
     <row r="44" spans="1:5">
@@ -2682,13 +2683,13 @@
         <v>6</v>
       </c>
       <c r="C44" s="6">
-        <v>-9.48</v>
+        <v>-11.21</v>
       </c>
       <c r="D44" s="6">
-        <v>-11.21</v>
+        <v>-11.35</v>
       </c>
       <c r="E44" s="8">
-        <v>-1.73</v>
+        <v>-0.14</v>
       </c>
     </row>
     <row r="45" spans="1:5">
@@ -2699,13 +2700,13 @@
         <v>6</v>
       </c>
       <c r="C45" s="6">
-        <v>-29.74</v>
+        <v>-30.25</v>
       </c>
       <c r="D45" s="6">
-        <v>-30.25</v>
-      </c>
-      <c r="E45" s="8">
-        <v>-0.51</v>
+        <v>-29.73</v>
+      </c>
+      <c r="E45" s="7">
+        <v>0.52</v>
       </c>
     </row>
     <row r="46" spans="1:5">
@@ -2716,13 +2717,13 @@
         <v>6</v>
       </c>
       <c r="C46" s="6">
-        <v>-18.04</v>
+        <v>-18.02</v>
       </c>
       <c r="D46" s="6">
-        <v>-18.02</v>
+        <v>-17.53</v>
       </c>
       <c r="E46" s="7">
-        <v>0.02</v>
+        <v>0.49</v>
       </c>
     </row>
     <row r="47" spans="1:5">
@@ -2733,13 +2734,13 @@
         <v>2</v>
       </c>
       <c r="C47" s="6">
-        <v>378.8</v>
+        <v>381.3</v>
       </c>
       <c r="D47" s="6">
-        <v>381.3</v>
+        <v>390</v>
       </c>
       <c r="E47" s="7">
-        <v>2.5</v>
+        <v>8.699999999999999</v>
       </c>
     </row>
     <row r="48" spans="1:5">
@@ -2750,13 +2751,13 @@
         <v>2</v>
       </c>
       <c r="C48" s="6">
-        <v>49.02</v>
+        <v>49.74</v>
       </c>
       <c r="D48" s="6">
-        <v>49.74</v>
+        <v>50.45</v>
       </c>
       <c r="E48" s="7">
-        <v>0.72</v>
+        <v>0.71</v>
       </c>
     </row>
     <row r="49" spans="1:5">
@@ -2767,13 +2768,13 @@
         <v>2</v>
       </c>
       <c r="C49" s="6">
-        <v>3171</v>
+        <v>3187</v>
       </c>
       <c r="D49" s="6">
-        <v>3187</v>
-      </c>
-      <c r="E49" s="7">
-        <v>16</v>
+        <v>3173.1</v>
+      </c>
+      <c r="E49" s="8">
+        <v>-13.9</v>
       </c>
     </row>
     <row r="50" spans="1:5">
@@ -2784,13 +2785,13 @@
         <v>2</v>
       </c>
       <c r="C50" s="6">
-        <v>958.7</v>
+        <v>972.7</v>
       </c>
       <c r="D50" s="6">
-        <v>972.7</v>
+        <v>980.5</v>
       </c>
       <c r="E50" s="7">
-        <v>14</v>
+        <v>7.8</v>
       </c>
     </row>
     <row r="51" spans="1:5">
@@ -2801,13 +2802,13 @@
         <v>2</v>
       </c>
       <c r="C51" s="6">
-        <v>14.45</v>
+        <v>14.26</v>
       </c>
       <c r="D51" s="6">
-        <v>14.26</v>
+        <v>14.22</v>
       </c>
       <c r="E51" s="8">
-        <v>-0.19</v>
+        <v>-0.04</v>
       </c>
     </row>
     <row r="52" spans="1:5">
@@ -2818,13 +2819,13 @@
         <v>2</v>
       </c>
       <c r="C52" s="6">
-        <v>12.6</v>
+        <v>12.36</v>
       </c>
       <c r="D52" s="6">
-        <v>12.36</v>
+        <v>12.34</v>
       </c>
       <c r="E52" s="8">
-        <v>-0.24</v>
+        <v>-0.02</v>
       </c>
     </row>
     <row r="53" spans="1:5">
@@ -2835,13 +2836,13 @@
         <v>2</v>
       </c>
       <c r="C53" s="6">
-        <v>4081.8</v>
+        <v>4052.2</v>
       </c>
       <c r="D53" s="6">
-        <v>4052.2</v>
-      </c>
-      <c r="E53" s="8">
-        <v>-29.6</v>
+        <v>4082.2</v>
+      </c>
+      <c r="E53" s="7">
+        <v>30</v>
       </c>
     </row>
     <row r="54" spans="1:5">
@@ -2852,13 +2853,13 @@
         <v>2</v>
       </c>
       <c r="C54" s="6">
-        <v>10697</v>
+        <v>10700</v>
       </c>
       <c r="D54" s="6">
-        <v>10700</v>
+        <v>10764</v>
       </c>
       <c r="E54" s="7">
-        <v>3</v>
+        <v>64</v>
       </c>
     </row>
     <row r="55" spans="1:5">
@@ -2869,13 +2870,13 @@
         <v>24</v>
       </c>
       <c r="C55" s="6">
-        <v>33.83</v>
+        <v>36.17</v>
       </c>
       <c r="D55" s="6">
-        <v>36.17</v>
+        <v>43.64</v>
       </c>
       <c r="E55" s="7">
-        <v>2.34</v>
+        <v>7.47</v>
       </c>
     </row>
     <row r="56" spans="1:5">
@@ -2886,13 +2887,13 @@
         <v>24</v>
       </c>
       <c r="C56" s="6">
-        <v>28.76</v>
+        <v>33.24</v>
       </c>
       <c r="D56" s="6">
-        <v>33.24</v>
+        <v>37.41</v>
       </c>
       <c r="E56" s="7">
-        <v>4.48</v>
+        <v>4.17</v>
       </c>
     </row>
     <row r="57" spans="1:5">
@@ -2903,13 +2904,13 @@
         <v>24</v>
       </c>
       <c r="C57" s="6">
-        <v>38.51</v>
+        <v>40.7</v>
       </c>
       <c r="D57" s="6">
-        <v>40.7</v>
-      </c>
-      <c r="E57" s="7">
-        <v>2.19</v>
+        <v>39.39</v>
+      </c>
+      <c r="E57" s="8">
+        <v>-1.31</v>
       </c>
     </row>
     <row r="58" spans="1:5">
@@ -2920,13 +2921,13 @@
         <v>24</v>
       </c>
       <c r="C58" s="6">
-        <v>34.23</v>
+        <v>39.21</v>
       </c>
       <c r="D58" s="6">
-        <v>39.21</v>
+        <v>41.85</v>
       </c>
       <c r="E58" s="7">
-        <v>4.98</v>
+        <v>2.64</v>
       </c>
     </row>
     <row r="59" spans="1:5">
@@ -2937,13 +2938,13 @@
         <v>24</v>
       </c>
       <c r="C59" s="6">
-        <v>49.78</v>
+        <v>47.44</v>
       </c>
       <c r="D59" s="6">
-        <v>47.44</v>
+        <v>46.94</v>
       </c>
       <c r="E59" s="8">
-        <v>-2.34</v>
+        <v>-0.5</v>
       </c>
     </row>
     <row r="60" spans="1:5">
@@ -2954,13 +2955,13 @@
         <v>24</v>
       </c>
       <c r="C60" s="6">
-        <v>66.98</v>
+        <v>61.88</v>
       </c>
       <c r="D60" s="6">
-        <v>61.88</v>
+        <v>61.46</v>
       </c>
       <c r="E60" s="8">
-        <v>-5.1</v>
+        <v>-0.42</v>
       </c>
     </row>
     <row r="61" spans="1:5">
@@ -2971,13 +2972,13 @@
         <v>24</v>
       </c>
       <c r="C61" s="6">
-        <v>34.28</v>
+        <v>32.91</v>
       </c>
       <c r="D61" s="6">
-        <v>32.91</v>
-      </c>
-      <c r="E61" s="8">
-        <v>-1.37</v>
+        <v>35.72</v>
+      </c>
+      <c r="E61" s="7">
+        <v>2.81</v>
       </c>
     </row>
     <row r="62" spans="1:5">
@@ -2988,13 +2989,13 @@
         <v>24</v>
       </c>
       <c r="C62" s="6">
-        <v>27.28</v>
+        <v>27.43</v>
       </c>
       <c r="D62" s="6">
-        <v>27.43</v>
+        <v>30.66</v>
       </c>
       <c r="E62" s="7">
-        <v>0.15</v>
+        <v>3.23</v>
       </c>
     </row>
     <row r="63" spans="1:5">
@@ -3005,13 +3006,13 @@
         <v>31</v>
       </c>
       <c r="C63" s="6">
-        <v>-12.04</v>
+        <v>-56.17</v>
       </c>
       <c r="D63" s="6">
-        <v>-56.17</v>
-      </c>
-      <c r="E63" s="8">
-        <v>-44.13</v>
+        <v>-4.15</v>
+      </c>
+      <c r="E63" s="7">
+        <v>52.02</v>
       </c>
     </row>
     <row r="64" spans="1:5">
@@ -3022,13 +3023,13 @@
         <v>31</v>
       </c>
       <c r="C64" s="6">
-        <v>120.5</v>
+        <v>87.08</v>
       </c>
       <c r="D64" s="6">
-        <v>87.08</v>
+        <v>-45.19</v>
       </c>
       <c r="E64" s="8">
-        <v>-33.42</v>
+        <v>-132.27</v>
       </c>
     </row>
     <row r="65" spans="1:5">
@@ -3039,13 +3040,13 @@
         <v>31</v>
       </c>
       <c r="C65" s="6">
-        <v>19.52</v>
+        <v>-25.62</v>
       </c>
       <c r="D65" s="6">
-        <v>-25.62</v>
+        <v>-34.89</v>
       </c>
       <c r="E65" s="8">
-        <v>-45.14</v>
+        <v>-9.27</v>
       </c>
     </row>
     <row r="66" spans="1:5">
@@ -3056,13 +3057,13 @@
         <v>31</v>
       </c>
       <c r="C66" s="6">
-        <v>-26.29</v>
+        <v>15.06</v>
       </c>
       <c r="D66" s="6">
-        <v>15.06</v>
-      </c>
-      <c r="E66" s="7">
-        <v>41.35</v>
+        <v>-9.41</v>
+      </c>
+      <c r="E66" s="8">
+        <v>-24.47</v>
       </c>
     </row>
     <row r="67" spans="1:5">
@@ -3073,13 +3074,13 @@
         <v>31</v>
       </c>
       <c r="C67" s="6">
-        <v>-28.15</v>
+        <v>-37.62</v>
       </c>
       <c r="D67" s="6">
-        <v>-37.62</v>
+        <v>-62.23</v>
       </c>
       <c r="E67" s="8">
-        <v>-9.470000000000001</v>
+        <v>-24.61</v>
       </c>
     </row>
     <row r="68" spans="1:5">
@@ -3090,13 +3091,13 @@
         <v>31</v>
       </c>
       <c r="C68" s="6">
-        <v>493.26</v>
+        <v>210.43</v>
       </c>
       <c r="D68" s="6">
-        <v>210.43</v>
+        <v>7.02</v>
       </c>
       <c r="E68" s="8">
-        <v>-282.83</v>
+        <v>-203.41</v>
       </c>
     </row>
     <row r="69" spans="1:5">
@@ -3107,13 +3108,13 @@
         <v>31</v>
       </c>
       <c r="C69" s="6">
-        <v>4.1</v>
+        <v>65.79000000000001</v>
       </c>
       <c r="D69" s="6">
-        <v>65.79000000000001</v>
-      </c>
-      <c r="E69" s="7">
-        <v>61.69</v>
+        <v>-30.36</v>
+      </c>
+      <c r="E69" s="8">
+        <v>-96.15000000000001</v>
       </c>
     </row>
     <row r="70" spans="1:5">
@@ -3124,13 +3125,13 @@
         <v>31</v>
       </c>
       <c r="C70" s="6">
-        <v>36.28</v>
+        <v>-6.19</v>
       </c>
       <c r="D70" s="6">
-        <v>-6.19</v>
+        <v>-28.96</v>
       </c>
       <c r="E70" s="8">
-        <v>-42.47</v>
+        <v>-22.77</v>
       </c>
     </row>
   </sheetData>
@@ -3189,22 +3190,22 @@
         <v>45</v>
       </c>
       <c r="B2" s="11">
-        <v>52.44</v>
+        <v>56.44</v>
       </c>
       <c r="C2" s="12">
         <v>8</v>
       </c>
       <c r="D2" s="11">
-        <v>39.9</v>
+        <v>42.1</v>
       </c>
       <c r="E2" s="11">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="F2" s="11">
+        <v>-3.7</v>
+      </c>
+      <c r="G2" s="11">
         <v>-4.2</v>
-      </c>
-      <c r="G2" s="11">
-        <v>-4.8</v>
       </c>
       <c r="H2" s="11">
         <v>56.1</v>
@@ -3338,28 +3339,28 @@
     </row>
     <row r="2" spans="1:8">
       <c r="A2" s="14">
-        <v>0.2712</v>
+        <v>0.2895</v>
       </c>
       <c r="B2" s="14">
-        <v>0.1701</v>
+        <v>0.1714</v>
       </c>
       <c r="C2" s="14">
-        <v>0.1568</v>
+        <v>0.1636</v>
       </c>
       <c r="D2" s="14">
-        <v>0.1562</v>
+        <v>0.1567</v>
       </c>
       <c r="E2" s="14">
-        <v>0.07099999999999999</v>
+        <v>0.0738</v>
       </c>
       <c r="F2" s="14">
-        <v>0.0486</v>
+        <v>0.0499</v>
       </c>
       <c r="G2" s="14">
-        <v>-0.2557</v>
+        <v>-0.2497</v>
       </c>
       <c r="H2" s="14">
-        <v>-0.3077</v>
+        <v>-0.3066</v>
       </c>
     </row>
   </sheetData>

--- a/BIRLA_GROUP_Technical_Metrics.xlsx
+++ b/BIRLA_GROUP_Technical_Metrics.xlsx
@@ -166,12 +166,12 @@
     <t>Yes</t>
   </si>
   <si>
+    <t>UP</t>
+  </si>
+  <si>
     <t>DOWN</t>
   </si>
   <si>
-    <t>UP</t>
-  </si>
-  <si>
     <t>▶  SIGNAL EVENTS (vs Previous Run)</t>
   </si>
   <si>
@@ -190,19 +190,19 @@
     <t>Curr Value</t>
   </si>
   <si>
-    <t>RSI Oversold Recovery</t>
-  </si>
-  <si>
-    <t>27.4 → 30.7</t>
+    <t>RSI Momentum</t>
+  </si>
+  <si>
+    <t>43.6 → 56.3</t>
   </si>
   <si>
     <t>🟢 BULLISH</t>
   </si>
   <si>
-    <t>27.4</t>
-  </si>
-  <si>
-    <t>30.7</t>
+    <t>43.6</t>
+  </si>
+  <si>
+    <t>56.3</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -786,9 +786,8 @@
     <col min="13" max="13" width="10.7109375" customWidth="1"/>
     <col min="14" max="14" width="11.7109375" customWidth="1"/>
     <col min="15" max="15" width="10.7109375" customWidth="1"/>
-    <col min="16" max="17" width="9.7109375" customWidth="1"/>
-    <col min="18" max="18" width="10.7109375" customWidth="1"/>
-    <col min="19" max="19" width="9.7109375" customWidth="1"/>
+    <col min="16" max="16" width="9.7109375" customWidth="1"/>
+    <col min="17" max="19" width="10.7109375" customWidth="1"/>
     <col min="20" max="20" width="22.7109375" customWidth="1"/>
     <col min="21" max="21" width="9.7109375" customWidth="1"/>
     <col min="22" max="22" width="10.7109375" customWidth="1"/>
@@ -928,10 +927,10 @@
         <v>45</v>
       </c>
       <c r="C2">
-        <v>390</v>
+        <v>410.05</v>
       </c>
       <c r="D2">
-        <v>2.28</v>
+        <v>5.14</v>
       </c>
       <c r="E2">
         <v>424.7</v>
@@ -940,46 +939,46 @@
         <v>278.9</v>
       </c>
       <c r="G2">
-        <v>-8.17</v>
+        <v>-3.45</v>
       </c>
       <c r="H2">
-        <v>39.84</v>
+        <v>47.02</v>
       </c>
       <c r="I2">
-        <v>-2.5</v>
+        <v>2.51</v>
       </c>
       <c r="J2">
-        <v>-2.99</v>
+        <v>3.55</v>
       </c>
       <c r="K2">
-        <v>5.23</v>
+        <v>9.08</v>
       </c>
       <c r="L2">
-        <v>33.79</v>
+        <v>41.06</v>
       </c>
       <c r="M2">
-        <v>28.95</v>
+        <v>30.78</v>
       </c>
       <c r="N2">
         <v>74</v>
       </c>
       <c r="O2">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="P2">
-        <v>389.02</v>
+        <v>391.03</v>
       </c>
       <c r="Q2">
-        <v>401.22</v>
+        <v>401.27</v>
       </c>
       <c r="R2">
-        <v>403.14</v>
+        <v>403.39</v>
       </c>
       <c r="S2">
-        <v>362.84</v>
+        <v>363.11</v>
       </c>
       <c r="T2">
-        <v>7.48</v>
+        <v>12.93</v>
       </c>
       <c r="U2" t="s">
         <v>46</v>
@@ -994,43 +993,43 @@
         <v>2</v>
       </c>
       <c r="Y2">
-        <v>43.64</v>
+        <v>56.32</v>
       </c>
       <c r="Z2">
-        <v>-4.33</v>
+        <v>-2.76</v>
       </c>
       <c r="AA2">
-        <v>-2.06</v>
+        <v>-2.2</v>
       </c>
       <c r="AB2">
-        <v>-2.27</v>
+        <v>-0.5600000000000001</v>
       </c>
       <c r="AC2">
-        <v>20.85</v>
+        <v>54.19</v>
       </c>
       <c r="AD2">
-        <v>13.99</v>
+        <v>27.22</v>
       </c>
       <c r="AE2">
-        <v>9.41</v>
+        <v>10.17</v>
       </c>
       <c r="AF2">
-        <v>-4.15</v>
+        <v>72.67</v>
       </c>
       <c r="AG2">
-        <v>420.88</v>
+        <v>421.02</v>
       </c>
       <c r="AH2">
-        <v>381.56</v>
+        <v>381.52</v>
       </c>
       <c r="AI2">
-        <v>409.07</v>
+        <v>369.75</v>
       </c>
       <c r="AJ2" t="s">
         <v>48</v>
       </c>
       <c r="AK2">
-        <v>32.04</v>
+        <v>30.88</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1041,10 +1040,10 @@
         <v>45</v>
       </c>
       <c r="C3">
-        <v>50.45</v>
+        <v>50.16</v>
       </c>
       <c r="D3">
-        <v>1.43</v>
+        <v>-0.57</v>
       </c>
       <c r="E3">
         <v>93.48</v>
@@ -1053,46 +1052,46 @@
         <v>49.02</v>
       </c>
       <c r="G3">
-        <v>-46.03</v>
+        <v>-46.34</v>
       </c>
       <c r="H3">
-        <v>2.92</v>
+        <v>2.33</v>
       </c>
       <c r="I3">
-        <v>-1.71</v>
+        <v>-1.43</v>
       </c>
       <c r="J3">
-        <v>-8.220000000000001</v>
+        <v>-7.91</v>
       </c>
       <c r="K3">
-        <v>-18.02</v>
+        <v>-17.28</v>
       </c>
       <c r="L3">
-        <v>-42.92</v>
+        <v>-42.57</v>
       </c>
       <c r="M3">
-        <v>-24.97</v>
+        <v>-24.3</v>
       </c>
       <c r="N3">
         <v>13</v>
       </c>
       <c r="O3">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="P3">
-        <v>50.11</v>
+        <v>49.96</v>
       </c>
       <c r="Q3">
-        <v>52.13</v>
+        <v>51.9</v>
       </c>
       <c r="R3">
-        <v>55.97</v>
+        <v>55.8</v>
       </c>
       <c r="S3">
-        <v>63.68</v>
+        <v>63.55</v>
       </c>
       <c r="T3">
-        <v>-20.78</v>
+        <v>-21.07</v>
       </c>
       <c r="U3" t="s">
         <v>46</v>
@@ -1107,43 +1106,43 @@
         <v>0</v>
       </c>
       <c r="Y3">
-        <v>37.41</v>
+        <v>36.41</v>
       </c>
       <c r="Z3">
-        <v>-1.8</v>
+        <v>-1.75</v>
       </c>
       <c r="AA3">
-        <v>-1.78</v>
+        <v>-1.77</v>
       </c>
       <c r="AB3">
-        <v>-0.02</v>
+        <v>0.02</v>
       </c>
       <c r="AC3">
-        <v>47.71</v>
+        <v>62.57</v>
       </c>
       <c r="AD3">
-        <v>42.35</v>
+        <v>49.67</v>
       </c>
       <c r="AE3">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="AF3">
-        <v>-45.19</v>
+        <v>-26.41</v>
       </c>
       <c r="AG3">
-        <v>55.7</v>
+        <v>55.35</v>
       </c>
       <c r="AH3">
-        <v>48.55</v>
+        <v>48.45</v>
       </c>
       <c r="AI3">
         <v>54.78</v>
       </c>
       <c r="AJ3" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="AK3">
-        <v>33.54</v>
+        <v>32.77</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1154,10 +1153,10 @@
         <v>45</v>
       </c>
       <c r="C4">
-        <v>3173.1</v>
+        <v>3209.2</v>
       </c>
       <c r="D4">
-        <v>-0.44</v>
+        <v>1.14</v>
       </c>
       <c r="E4">
         <v>3380.5</v>
@@ -1166,25 +1165,25 @@
         <v>2531.1</v>
       </c>
       <c r="G4">
-        <v>-6.14</v>
+        <v>-5.07</v>
       </c>
       <c r="H4">
-        <v>25.36</v>
+        <v>26.79</v>
       </c>
       <c r="I4">
-        <v>-3.85</v>
+        <v>-3.31</v>
       </c>
       <c r="J4">
-        <v>-3.22</v>
+        <v>-1.86</v>
       </c>
       <c r="K4">
-        <v>0.89</v>
+        <v>1.9</v>
       </c>
       <c r="L4">
-        <v>13.24</v>
+        <v>14.52</v>
       </c>
       <c r="M4">
-        <v>15.67</v>
+        <v>16.44</v>
       </c>
       <c r="N4">
         <v>50</v>
@@ -1193,19 +1192,19 @@
         <v>68</v>
       </c>
       <c r="P4">
-        <v>3226.4</v>
+        <v>3204.44</v>
       </c>
       <c r="Q4">
-        <v>3283.88</v>
+        <v>3279.34</v>
       </c>
       <c r="R4">
-        <v>3226.59</v>
+        <v>3226.93</v>
       </c>
       <c r="S4">
-        <v>2957.9</v>
+        <v>2960.28</v>
       </c>
       <c r="T4">
-        <v>7.28</v>
+        <v>8.41</v>
       </c>
       <c r="U4" t="s">
         <v>47</v>
@@ -1220,43 +1219,43 @@
         <v>3</v>
       </c>
       <c r="Y4">
-        <v>39.39</v>
+        <v>44.41</v>
       </c>
       <c r="Z4">
-        <v>-6.75</v>
+        <v>-9.66</v>
       </c>
       <c r="AA4">
-        <v>13.86</v>
+        <v>9.15</v>
       </c>
       <c r="AB4">
-        <v>-20.61</v>
+        <v>-18.82</v>
       </c>
       <c r="AC4">
-        <v>4.12</v>
+        <v>12.03</v>
       </c>
       <c r="AD4">
-        <v>6.11</v>
+        <v>6.36</v>
       </c>
       <c r="AE4">
-        <v>62.94</v>
+        <v>61.02</v>
       </c>
       <c r="AF4">
-        <v>-34.89</v>
+        <v>-37.8</v>
       </c>
       <c r="AG4">
-        <v>3385.36</v>
+        <v>3385.78</v>
       </c>
       <c r="AH4">
-        <v>3182.4</v>
+        <v>3172.9</v>
       </c>
       <c r="AI4">
         <v>3120.02</v>
       </c>
       <c r="AJ4" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="AK4">
-        <v>25.73</v>
+        <v>28.19</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1267,10 +1266,10 @@
         <v>45</v>
       </c>
       <c r="C5">
-        <v>980.5</v>
+        <v>986.5</v>
       </c>
       <c r="D5">
-        <v>0.8</v>
+        <v>0.61</v>
       </c>
       <c r="E5">
         <v>1149.7</v>
@@ -1279,25 +1278,25 @@
         <v>741.05</v>
       </c>
       <c r="G5">
-        <v>-14.72</v>
+        <v>-14.2</v>
       </c>
       <c r="H5">
-        <v>32.31</v>
+        <v>33.12</v>
       </c>
       <c r="I5">
-        <v>-4.52</v>
+        <v>-2.71</v>
       </c>
       <c r="J5">
-        <v>-5.87</v>
+        <v>-5.05</v>
       </c>
       <c r="K5">
-        <v>-2.78</v>
+        <v>-2.33</v>
       </c>
       <c r="L5">
-        <v>29.35</v>
+        <v>30.9</v>
       </c>
       <c r="M5">
-        <v>16.36</v>
+        <v>17.99</v>
       </c>
       <c r="N5">
         <v>62</v>
@@ -1306,19 +1305,19 @@
         <v>74</v>
       </c>
       <c r="P5">
-        <v>981.48</v>
+        <v>975.98</v>
       </c>
       <c r="Q5">
-        <v>1014.88</v>
+        <v>1012.72</v>
       </c>
       <c r="R5">
-        <v>1001.9</v>
+        <v>1002.36</v>
       </c>
       <c r="S5">
-        <v>973.66</v>
+        <v>974.54</v>
       </c>
       <c r="T5">
-        <v>0.7</v>
+        <v>1.23</v>
       </c>
       <c r="U5" t="s">
         <v>47</v>
@@ -1333,43 +1332,43 @@
         <v>3</v>
       </c>
       <c r="Y5">
-        <v>41.85</v>
+        <v>43.87</v>
       </c>
       <c r="Z5">
-        <v>-10.41</v>
+        <v>-10.47</v>
       </c>
       <c r="AA5">
-        <v>-3.64</v>
+        <v>-5</v>
       </c>
       <c r="AB5">
-        <v>-6.77</v>
+        <v>-5.47</v>
       </c>
       <c r="AC5">
-        <v>21.97</v>
+        <v>39.53</v>
       </c>
       <c r="AD5">
-        <v>12.45</v>
+        <v>23.39</v>
       </c>
       <c r="AE5">
-        <v>22.99</v>
+        <v>22.76</v>
       </c>
       <c r="AF5">
-        <v>-9.41</v>
+        <v>175.47</v>
       </c>
       <c r="AG5">
-        <v>1068</v>
+        <v>1066.79</v>
       </c>
       <c r="AH5">
-        <v>961.77</v>
+        <v>958.64</v>
       </c>
       <c r="AI5">
         <v>1037.86</v>
       </c>
       <c r="AJ5" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="AK5">
-        <v>28.21</v>
+        <v>26.17</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1380,10 +1379,10 @@
         <v>45</v>
       </c>
       <c r="C6">
-        <v>14.22</v>
+        <v>13.92</v>
       </c>
       <c r="D6">
-        <v>-0.28</v>
+        <v>-2.11</v>
       </c>
       <c r="E6">
         <v>15.6</v>
@@ -1392,46 +1391,46 @@
         <v>7.77</v>
       </c>
       <c r="G6">
-        <v>-8.85</v>
+        <v>-10.77</v>
       </c>
       <c r="H6">
-        <v>83.01000000000001</v>
+        <v>79.15000000000001</v>
       </c>
       <c r="I6">
-        <v>-8.380000000000001</v>
+        <v>-6.58</v>
       </c>
       <c r="J6">
-        <v>0.71</v>
+        <v>-1.07</v>
       </c>
       <c r="K6">
-        <v>-5.26</v>
+        <v>-6.7</v>
       </c>
       <c r="L6">
-        <v>85.64</v>
+        <v>71.01000000000001</v>
       </c>
       <c r="M6">
-        <v>4.99</v>
+        <v>5.31</v>
       </c>
       <c r="N6">
         <v>87</v>
       </c>
       <c r="O6">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="P6">
-        <v>14.56</v>
+        <v>14.36</v>
       </c>
       <c r="Q6">
-        <v>14.69</v>
+        <v>14.68</v>
       </c>
       <c r="R6">
         <v>13.91</v>
       </c>
       <c r="S6">
-        <v>12.09</v>
+        <v>12.11</v>
       </c>
       <c r="T6">
-        <v>17.63</v>
+        <v>14.96</v>
       </c>
       <c r="U6" t="s">
         <v>47</v>
@@ -1446,43 +1445,43 @@
         <v>3</v>
       </c>
       <c r="Y6">
-        <v>46.94</v>
+        <v>43.25</v>
       </c>
       <c r="Z6">
-        <v>0.2</v>
+        <v>0.13</v>
       </c>
       <c r="AA6">
-        <v>0.32</v>
+        <v>0.28</v>
       </c>
       <c r="AB6">
-        <v>-0.11</v>
+        <v>-0.15</v>
       </c>
       <c r="AC6">
         <v>0</v>
       </c>
       <c r="AD6">
-        <v>8.27</v>
+        <v>2.89</v>
       </c>
       <c r="AE6">
         <v>0.49</v>
       </c>
       <c r="AF6">
-        <v>-62.23</v>
+        <v>-24.86</v>
       </c>
       <c r="AG6">
-        <v>15.73</v>
+        <v>15.74</v>
       </c>
       <c r="AH6">
-        <v>13.64</v>
+        <v>13.62</v>
       </c>
       <c r="AI6">
-        <v>14.01</v>
+        <v>15.61</v>
       </c>
       <c r="AJ6" t="s">
         <v>49</v>
       </c>
       <c r="AK6">
-        <v>29.01</v>
+        <v>29.61</v>
       </c>
     </row>
     <row r="7" spans="1:37">
@@ -1493,10 +1492,10 @@
         <v>45</v>
       </c>
       <c r="C7">
-        <v>12.34</v>
+        <v>11.94</v>
       </c>
       <c r="D7">
-        <v>-0.16</v>
+        <v>-3.24</v>
       </c>
       <c r="E7">
         <v>13.92</v>
@@ -1505,46 +1504,46 @@
         <v>4.69</v>
       </c>
       <c r="G7">
-        <v>-11.35</v>
+        <v>-14.22</v>
       </c>
       <c r="H7">
-        <v>163.11</v>
+        <v>154.58</v>
       </c>
       <c r="I7">
-        <v>6.84</v>
+        <v>1.36</v>
       </c>
       <c r="J7">
-        <v>3.26</v>
+        <v>1.88</v>
       </c>
       <c r="K7">
-        <v>0.41</v>
+        <v>-0.91</v>
       </c>
       <c r="L7">
-        <v>147.29</v>
+        <v>129.62</v>
       </c>
       <c r="M7">
-        <v>-30.66</v>
+        <v>-30.18</v>
       </c>
       <c r="N7">
         <v>99</v>
       </c>
       <c r="O7">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="P7">
-        <v>12.22</v>
+        <v>12.25</v>
       </c>
       <c r="Q7">
-        <v>11.49</v>
+        <v>11.51</v>
       </c>
       <c r="R7">
-        <v>11.69</v>
+        <v>11.73</v>
       </c>
       <c r="S7">
-        <v>10.59</v>
+        <v>10.62</v>
       </c>
       <c r="T7">
-        <v>16.53</v>
+        <v>12.41</v>
       </c>
       <c r="U7" t="s">
         <v>46</v>
@@ -1559,43 +1558,43 @@
         <v>2</v>
       </c>
       <c r="Y7">
-        <v>61.46</v>
+        <v>53.63</v>
       </c>
       <c r="Z7">
         <v>0.13</v>
       </c>
       <c r="AA7">
-        <v>-0.03</v>
+        <v>0</v>
       </c>
       <c r="AB7">
-        <v>0.16</v>
+        <v>0.13</v>
       </c>
       <c r="AC7">
-        <v>88.09</v>
+        <v>73.12</v>
       </c>
       <c r="AD7">
-        <v>94.13</v>
+        <v>85.16</v>
       </c>
       <c r="AE7">
-        <v>0.34</v>
+        <v>0.36</v>
       </c>
       <c r="AF7">
-        <v>7.02</v>
+        <v>16.47</v>
       </c>
       <c r="AG7">
-        <v>12.47</v>
+        <v>12.5</v>
       </c>
       <c r="AH7">
-        <v>10.52</v>
+        <v>10.51</v>
       </c>
       <c r="AI7">
         <v>11.5</v>
       </c>
       <c r="AJ7" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="AK7">
-        <v>44.57</v>
+        <v>45.32</v>
       </c>
     </row>
     <row r="8" spans="1:37">
@@ -1606,10 +1605,10 @@
         <v>45</v>
       </c>
       <c r="C8">
-        <v>4082.2</v>
+        <v>4067</v>
       </c>
       <c r="D8">
-        <v>0.74</v>
+        <v>-0.37</v>
       </c>
       <c r="E8">
         <v>5809.5</v>
@@ -1618,46 +1617,46 @@
         <v>4052.2</v>
       </c>
       <c r="G8">
-        <v>-29.73</v>
+        <v>-29.99</v>
       </c>
       <c r="H8">
-        <v>0.74</v>
+        <v>0.37</v>
       </c>
       <c r="I8">
-        <v>-0.67</v>
+        <v>-3.99</v>
       </c>
       <c r="J8">
-        <v>-6.92</v>
+        <v>-5.24</v>
       </c>
       <c r="K8">
-        <v>-8.07</v>
+        <v>-8.08</v>
       </c>
       <c r="L8">
-        <v>-21.64</v>
+        <v>-22.43</v>
       </c>
       <c r="M8">
-        <v>17.14</v>
+        <v>17.6</v>
       </c>
       <c r="N8">
         <v>26</v>
       </c>
       <c r="O8">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="P8">
-        <v>4128.72</v>
+        <v>4094.96</v>
       </c>
       <c r="Q8">
-        <v>4281.2</v>
+        <v>4269.08</v>
       </c>
       <c r="R8">
-        <v>4337.01</v>
+        <v>4330.67</v>
       </c>
       <c r="S8">
-        <v>4588.27</v>
+        <v>4582.71</v>
       </c>
       <c r="T8">
-        <v>-11.03</v>
+        <v>-11.25</v>
       </c>
       <c r="U8" t="s">
         <v>46</v>
@@ -1672,43 +1671,43 @@
         <v>0</v>
       </c>
       <c r="Y8">
-        <v>35.72</v>
+        <v>34.92</v>
       </c>
       <c r="Z8">
-        <v>-73.11</v>
+        <v>-77.95999999999999</v>
       </c>
       <c r="AA8">
-        <v>-44.54</v>
+        <v>-51.22</v>
       </c>
       <c r="AB8">
-        <v>-28.57</v>
+        <v>-26.74</v>
       </c>
       <c r="AC8">
-        <v>18.59</v>
+        <v>21.53</v>
       </c>
       <c r="AD8">
-        <v>26.38</v>
+        <v>21.23</v>
       </c>
       <c r="AE8">
-        <v>106.02</v>
+        <v>103.44</v>
       </c>
       <c r="AF8">
-        <v>-30.36</v>
+        <v>-42.23</v>
       </c>
       <c r="AG8">
-        <v>4513.54</v>
+        <v>4519.79</v>
       </c>
       <c r="AH8">
-        <v>4048.87</v>
+        <v>4018.37</v>
       </c>
       <c r="AI8">
         <v>4394.81</v>
       </c>
       <c r="AJ8" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="AK8">
-        <v>51.74</v>
+        <v>53.7</v>
       </c>
     </row>
     <row r="9" spans="1:37">
@@ -1719,10 +1718,10 @@
         <v>45</v>
       </c>
       <c r="C9">
-        <v>10764</v>
+        <v>11014</v>
       </c>
       <c r="D9">
-        <v>0.6</v>
+        <v>2.32</v>
       </c>
       <c r="E9">
         <v>13052</v>
@@ -1731,46 +1730,46 @@
         <v>10362</v>
       </c>
       <c r="G9">
-        <v>-17.53</v>
+        <v>-15.61</v>
       </c>
       <c r="H9">
-        <v>3.88</v>
+        <v>6.29</v>
       </c>
       <c r="I9">
-        <v>-1.25</v>
+        <v>0.32</v>
       </c>
       <c r="J9">
-        <v>-6.39</v>
+        <v>-3.81</v>
       </c>
       <c r="K9">
-        <v>-5.83</v>
+        <v>-3.11</v>
       </c>
       <c r="L9">
-        <v>-12.98</v>
+        <v>-11.43</v>
       </c>
       <c r="M9">
-        <v>7.38</v>
+        <v>8.27</v>
       </c>
       <c r="N9">
         <v>38</v>
       </c>
       <c r="O9">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="P9">
-        <v>10828</v>
+        <v>10835</v>
       </c>
       <c r="Q9">
-        <v>11268.1</v>
+        <v>11240.05</v>
       </c>
       <c r="R9">
-        <v>11605.58</v>
+        <v>11595.38</v>
       </c>
       <c r="S9">
-        <v>11736.1</v>
+        <v>11732.86</v>
       </c>
       <c r="T9">
-        <v>-8.279999999999999</v>
+        <v>-6.13</v>
       </c>
       <c r="U9" t="s">
         <v>46</v>
@@ -1785,43 +1784,43 @@
         <v>0</v>
       </c>
       <c r="Y9">
-        <v>30.66</v>
+        <v>41.61</v>
       </c>
       <c r="Z9">
-        <v>-245.94</v>
+        <v>-228.39</v>
       </c>
       <c r="AA9">
-        <v>-187.2</v>
+        <v>-195.44</v>
       </c>
       <c r="AB9">
-        <v>-58.74</v>
+        <v>-32.95</v>
       </c>
       <c r="AC9">
-        <v>6.47</v>
+        <v>39.25</v>
       </c>
       <c r="AD9">
-        <v>9.25</v>
+        <v>17.83</v>
       </c>
       <c r="AE9">
-        <v>199.69</v>
+        <v>206.57</v>
       </c>
       <c r="AF9">
-        <v>-28.96</v>
+        <v>81.31</v>
       </c>
       <c r="AG9">
-        <v>11944.99</v>
+        <v>11909.85</v>
       </c>
       <c r="AH9">
-        <v>10591.21</v>
+        <v>10570.25</v>
       </c>
       <c r="AI9">
         <v>11371.08</v>
       </c>
       <c r="AJ9" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="AK9">
-        <v>48.46</v>
+        <v>43.16</v>
       </c>
     </row>
   </sheetData>
@@ -2002,7 +2001,7 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="4" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="B3" s="4" t="s">
         <v>56</v>
@@ -2054,13 +2053,13 @@
         <v>9</v>
       </c>
       <c r="C7" s="6">
-        <v>-4.36</v>
+        <v>-2.99</v>
       </c>
       <c r="D7" s="6">
-        <v>-2.99</v>
+        <v>3.55</v>
       </c>
       <c r="E7" s="7">
-        <v>1.37</v>
+        <v>6.54</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -2071,13 +2070,13 @@
         <v>9</v>
       </c>
       <c r="C8" s="6">
-        <v>-11.15</v>
+        <v>-8.220000000000001</v>
       </c>
       <c r="D8" s="6">
-        <v>-8.220000000000001</v>
+        <v>-7.91</v>
       </c>
       <c r="E8" s="7">
-        <v>2.93</v>
+        <v>0.31</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -2088,13 +2087,13 @@
         <v>9</v>
       </c>
       <c r="C9" s="6">
-        <v>-1.95</v>
+        <v>-3.22</v>
       </c>
       <c r="D9" s="6">
-        <v>-3.22</v>
-      </c>
-      <c r="E9" s="8">
-        <v>-1.27</v>
+        <v>-1.86</v>
+      </c>
+      <c r="E9" s="7">
+        <v>1.36</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -2105,13 +2104,13 @@
         <v>9</v>
       </c>
       <c r="C10" s="6">
-        <v>-7.35</v>
+        <v>-5.87</v>
       </c>
       <c r="D10" s="6">
-        <v>-5.87</v>
+        <v>-5.05</v>
       </c>
       <c r="E10" s="7">
-        <v>1.48</v>
+        <v>0.82</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -2122,13 +2121,13 @@
         <v>9</v>
       </c>
       <c r="C11" s="6">
-        <v>4.01</v>
+        <v>0.71</v>
       </c>
       <c r="D11" s="6">
-        <v>0.71</v>
+        <v>-1.07</v>
       </c>
       <c r="E11" s="8">
-        <v>-3.3</v>
+        <v>-1.78</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -2139,13 +2138,13 @@
         <v>9</v>
       </c>
       <c r="C12" s="6">
-        <v>5.64</v>
+        <v>3.26</v>
       </c>
       <c r="D12" s="6">
-        <v>3.26</v>
+        <v>1.88</v>
       </c>
       <c r="E12" s="8">
-        <v>-2.38</v>
+        <v>-1.38</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -2156,13 +2155,13 @@
         <v>9</v>
       </c>
       <c r="C13" s="6">
-        <v>-10.88</v>
+        <v>-6.92</v>
       </c>
       <c r="D13" s="6">
-        <v>-6.92</v>
+        <v>-5.24</v>
       </c>
       <c r="E13" s="7">
-        <v>3.96</v>
+        <v>1.68</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -2173,13 +2172,13 @@
         <v>9</v>
       </c>
       <c r="C14" s="6">
-        <v>-7.91</v>
+        <v>-6.39</v>
       </c>
       <c r="D14" s="6">
-        <v>-6.39</v>
+        <v>-3.81</v>
       </c>
       <c r="E14" s="7">
-        <v>1.52</v>
+        <v>2.58</v>
       </c>
     </row>
     <row r="15" spans="1:6">
@@ -2190,13 +2189,13 @@
         <v>8</v>
       </c>
       <c r="C15" s="6">
-        <v>-3.94</v>
+        <v>-2.5</v>
       </c>
       <c r="D15" s="6">
-        <v>-2.5</v>
+        <v>2.51</v>
       </c>
       <c r="E15" s="7">
-        <v>1.44</v>
+        <v>5.01</v>
       </c>
     </row>
     <row r="16" spans="1:6">
@@ -2207,13 +2206,13 @@
         <v>8</v>
       </c>
       <c r="C16" s="6">
-        <v>-4.79</v>
+        <v>-1.71</v>
       </c>
       <c r="D16" s="6">
-        <v>-1.71</v>
+        <v>-1.43</v>
       </c>
       <c r="E16" s="7">
-        <v>3.08</v>
+        <v>0.28</v>
       </c>
     </row>
     <row r="17" spans="1:5">
@@ -2224,13 +2223,13 @@
         <v>8</v>
       </c>
       <c r="C17" s="6">
-        <v>-3.62</v>
+        <v>-3.85</v>
       </c>
       <c r="D17" s="6">
-        <v>-3.85</v>
-      </c>
-      <c r="E17" s="8">
-        <v>-0.23</v>
+        <v>-3.31</v>
+      </c>
+      <c r="E17" s="7">
+        <v>0.54</v>
       </c>
     </row>
     <row r="18" spans="1:5">
@@ -2241,13 +2240,13 @@
         <v>8</v>
       </c>
       <c r="C18" s="6">
-        <v>-3.6</v>
+        <v>-4.52</v>
       </c>
       <c r="D18" s="6">
-        <v>-4.52</v>
-      </c>
-      <c r="E18" s="8">
-        <v>-0.92</v>
+        <v>-2.71</v>
+      </c>
+      <c r="E18" s="7">
+        <v>1.81</v>
       </c>
     </row>
     <row r="19" spans="1:5">
@@ -2258,13 +2257,13 @@
         <v>8</v>
       </c>
       <c r="C19" s="6">
-        <v>-7.52</v>
+        <v>-8.380000000000001</v>
       </c>
       <c r="D19" s="6">
-        <v>-8.380000000000001</v>
-      </c>
-      <c r="E19" s="8">
-        <v>-0.86</v>
+        <v>-6.58</v>
+      </c>
+      <c r="E19" s="7">
+        <v>1.8</v>
       </c>
     </row>
     <row r="20" spans="1:5">
@@ -2275,13 +2274,13 @@
         <v>8</v>
       </c>
       <c r="C20" s="6">
-        <v>9.09</v>
+        <v>6.84</v>
       </c>
       <c r="D20" s="6">
-        <v>6.84</v>
+        <v>1.36</v>
       </c>
       <c r="E20" s="8">
-        <v>-2.25</v>
+        <v>-5.48</v>
       </c>
     </row>
     <row r="21" spans="1:5">
@@ -2292,13 +2291,13 @@
         <v>8</v>
       </c>
       <c r="C21" s="6">
-        <v>-4.92</v>
+        <v>-0.67</v>
       </c>
       <c r="D21" s="6">
-        <v>-0.67</v>
-      </c>
-      <c r="E21" s="7">
-        <v>4.25</v>
+        <v>-3.99</v>
+      </c>
+      <c r="E21" s="8">
+        <v>-3.32</v>
       </c>
     </row>
     <row r="22" spans="1:5">
@@ -2309,13 +2308,13 @@
         <v>8</v>
       </c>
       <c r="C22" s="6">
-        <v>-2.81</v>
+        <v>-1.25</v>
       </c>
       <c r="D22" s="6">
-        <v>-1.25</v>
+        <v>0.32</v>
       </c>
       <c r="E22" s="7">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
     </row>
     <row r="23" spans="1:5">
@@ -2326,13 +2325,13 @@
         <v>11</v>
       </c>
       <c r="C23" s="6">
-        <v>31.48</v>
+        <v>33.79</v>
       </c>
       <c r="D23" s="6">
-        <v>33.79</v>
+        <v>41.06</v>
       </c>
       <c r="E23" s="7">
-        <v>2.31</v>
+        <v>7.27</v>
       </c>
     </row>
     <row r="24" spans="1:5">
@@ -2343,13 +2342,13 @@
         <v>11</v>
       </c>
       <c r="C24" s="6">
-        <v>-44.21</v>
+        <v>-42.92</v>
       </c>
       <c r="D24" s="6">
-        <v>-42.92</v>
+        <v>-42.57</v>
       </c>
       <c r="E24" s="7">
-        <v>1.29</v>
+        <v>0.35</v>
       </c>
     </row>
     <row r="25" spans="1:5">
@@ -2360,13 +2359,13 @@
         <v>11</v>
       </c>
       <c r="C25" s="6">
-        <v>13.86</v>
+        <v>13.24</v>
       </c>
       <c r="D25" s="6">
-        <v>13.24</v>
-      </c>
-      <c r="E25" s="8">
-        <v>-0.62</v>
+        <v>14.52</v>
+      </c>
+      <c r="E25" s="7">
+        <v>1.28</v>
       </c>
     </row>
     <row r="26" spans="1:5">
@@ -2377,13 +2376,13 @@
         <v>11</v>
       </c>
       <c r="C26" s="6">
-        <v>30.98</v>
+        <v>29.35</v>
       </c>
       <c r="D26" s="6">
-        <v>29.35</v>
-      </c>
-      <c r="E26" s="8">
-        <v>-1.63</v>
+        <v>30.9</v>
+      </c>
+      <c r="E26" s="7">
+        <v>1.55</v>
       </c>
     </row>
     <row r="27" spans="1:5">
@@ -2394,13 +2393,13 @@
         <v>11</v>
       </c>
       <c r="C27" s="6">
-        <v>92.44</v>
+        <v>85.64</v>
       </c>
       <c r="D27" s="6">
-        <v>85.64</v>
+        <v>71.01000000000001</v>
       </c>
       <c r="E27" s="8">
-        <v>-6.8</v>
+        <v>-14.63</v>
       </c>
     </row>
     <row r="28" spans="1:5">
@@ -2411,13 +2410,13 @@
         <v>11</v>
       </c>
       <c r="C28" s="6">
-        <v>137.69</v>
+        <v>147.29</v>
       </c>
       <c r="D28" s="6">
-        <v>147.29</v>
-      </c>
-      <c r="E28" s="7">
-        <v>9.6</v>
+        <v>129.62</v>
+      </c>
+      <c r="E28" s="8">
+        <v>-17.67</v>
       </c>
     </row>
     <row r="29" spans="1:5">
@@ -2428,13 +2427,13 @@
         <v>11</v>
       </c>
       <c r="C29" s="6">
-        <v>-23.35</v>
+        <v>-21.64</v>
       </c>
       <c r="D29" s="6">
-        <v>-21.64</v>
-      </c>
-      <c r="E29" s="7">
-        <v>1.71</v>
+        <v>-22.43</v>
+      </c>
+      <c r="E29" s="8">
+        <v>-0.79</v>
       </c>
     </row>
     <row r="30" spans="1:5">
@@ -2445,13 +2444,13 @@
         <v>11</v>
       </c>
       <c r="C30" s="6">
-        <v>-13.65</v>
+        <v>-12.98</v>
       </c>
       <c r="D30" s="6">
-        <v>-12.98</v>
+        <v>-11.43</v>
       </c>
       <c r="E30" s="7">
-        <v>0.67</v>
+        <v>1.55</v>
       </c>
     </row>
     <row r="31" spans="1:5">
@@ -2462,13 +2461,13 @@
         <v>10</v>
       </c>
       <c r="C31" s="6">
-        <v>2.38</v>
+        <v>5.23</v>
       </c>
       <c r="D31" s="6">
-        <v>5.23</v>
+        <v>9.08</v>
       </c>
       <c r="E31" s="7">
-        <v>2.85</v>
+        <v>3.85</v>
       </c>
     </row>
     <row r="32" spans="1:5">
@@ -2479,13 +2478,13 @@
         <v>10</v>
       </c>
       <c r="C32" s="6">
-        <v>-19.41</v>
+        <v>-18.02</v>
       </c>
       <c r="D32" s="6">
-        <v>-18.02</v>
+        <v>-17.28</v>
       </c>
       <c r="E32" s="7">
-        <v>1.39</v>
+        <v>0.74</v>
       </c>
     </row>
     <row r="33" spans="1:5">
@@ -2496,13 +2495,13 @@
         <v>10</v>
       </c>
       <c r="C33" s="6">
-        <v>1.16</v>
+        <v>0.89</v>
       </c>
       <c r="D33" s="6">
-        <v>0.89</v>
-      </c>
-      <c r="E33" s="8">
-        <v>-0.27</v>
+        <v>1.9</v>
+      </c>
+      <c r="E33" s="7">
+        <v>1.01</v>
       </c>
     </row>
     <row r="34" spans="1:5">
@@ -2513,13 +2512,13 @@
         <v>10</v>
       </c>
       <c r="C34" s="6">
-        <v>-3.49</v>
+        <v>-2.78</v>
       </c>
       <c r="D34" s="6">
-        <v>-2.78</v>
+        <v>-2.33</v>
       </c>
       <c r="E34" s="7">
-        <v>0.71</v>
+        <v>0.45</v>
       </c>
     </row>
     <row r="35" spans="1:5">
@@ -2530,13 +2529,13 @@
         <v>10</v>
       </c>
       <c r="C35" s="6">
-        <v>-4.42</v>
+        <v>-5.26</v>
       </c>
       <c r="D35" s="6">
-        <v>-5.26</v>
+        <v>-6.7</v>
       </c>
       <c r="E35" s="8">
-        <v>-0.84</v>
+        <v>-1.44</v>
       </c>
     </row>
     <row r="36" spans="1:5">
@@ -2547,13 +2546,13 @@
         <v>10</v>
       </c>
       <c r="C36" s="6">
-        <v>0.24</v>
+        <v>0.41</v>
       </c>
       <c r="D36" s="6">
-        <v>0.41</v>
-      </c>
-      <c r="E36" s="7">
-        <v>0.17</v>
+        <v>-0.91</v>
+      </c>
+      <c r="E36" s="8">
+        <v>-1.32</v>
       </c>
     </row>
     <row r="37" spans="1:5">
@@ -2564,13 +2563,13 @@
         <v>10</v>
       </c>
       <c r="C37" s="6">
-        <v>-8.550000000000001</v>
+        <v>-8.07</v>
       </c>
       <c r="D37" s="6">
-        <v>-8.07</v>
-      </c>
-      <c r="E37" s="7">
-        <v>0.48</v>
+        <v>-8.08</v>
+      </c>
+      <c r="E37" s="8">
+        <v>-0.01</v>
       </c>
     </row>
     <row r="38" spans="1:5">
@@ -2581,13 +2580,13 @@
         <v>10</v>
       </c>
       <c r="C38" s="6">
-        <v>-5.92</v>
+        <v>-5.83</v>
       </c>
       <c r="D38" s="6">
-        <v>-5.83</v>
+        <v>-3.11</v>
       </c>
       <c r="E38" s="7">
-        <v>0.09</v>
+        <v>2.72</v>
       </c>
     </row>
     <row r="39" spans="1:5">
@@ -2598,13 +2597,13 @@
         <v>6</v>
       </c>
       <c r="C39" s="6">
-        <v>-10.22</v>
+        <v>-8.17</v>
       </c>
       <c r="D39" s="6">
-        <v>-8.17</v>
+        <v>-3.45</v>
       </c>
       <c r="E39" s="7">
-        <v>2.05</v>
+        <v>4.72</v>
       </c>
     </row>
     <row r="40" spans="1:5">
@@ -2615,13 +2614,13 @@
         <v>6</v>
       </c>
       <c r="C40" s="6">
-        <v>-46.79</v>
+        <v>-46.03</v>
       </c>
       <c r="D40" s="6">
-        <v>-46.03</v>
-      </c>
-      <c r="E40" s="7">
-        <v>0.76</v>
+        <v>-46.34</v>
+      </c>
+      <c r="E40" s="8">
+        <v>-0.31</v>
       </c>
     </row>
     <row r="41" spans="1:5">
@@ -2632,13 +2631,13 @@
         <v>6</v>
       </c>
       <c r="C41" s="6">
-        <v>-5.72</v>
+        <v>-6.14</v>
       </c>
       <c r="D41" s="6">
-        <v>-6.14</v>
-      </c>
-      <c r="E41" s="8">
-        <v>-0.42</v>
+        <v>-5.07</v>
+      </c>
+      <c r="E41" s="7">
+        <v>1.07</v>
       </c>
     </row>
     <row r="42" spans="1:5">
@@ -2649,13 +2648,13 @@
         <v>6</v>
       </c>
       <c r="C42" s="6">
-        <v>-15.4</v>
+        <v>-14.72</v>
       </c>
       <c r="D42" s="6">
-        <v>-14.72</v>
+        <v>-14.2</v>
       </c>
       <c r="E42" s="7">
-        <v>0.68</v>
+        <v>0.52</v>
       </c>
     </row>
     <row r="43" spans="1:5">
@@ -2666,13 +2665,13 @@
         <v>6</v>
       </c>
       <c r="C43" s="6">
-        <v>-8.59</v>
+        <v>-8.85</v>
       </c>
       <c r="D43" s="6">
-        <v>-8.85</v>
+        <v>-10.77</v>
       </c>
       <c r="E43" s="8">
-        <v>-0.26</v>
+        <v>-1.92</v>
       </c>
     </row>
     <row r="44" spans="1:5">
@@ -2683,13 +2682,13 @@
         <v>6</v>
       </c>
       <c r="C44" s="6">
-        <v>-11.21</v>
+        <v>-11.35</v>
       </c>
       <c r="D44" s="6">
-        <v>-11.35</v>
+        <v>-14.22</v>
       </c>
       <c r="E44" s="8">
-        <v>-0.14</v>
+        <v>-2.87</v>
       </c>
     </row>
     <row r="45" spans="1:5">
@@ -2700,13 +2699,13 @@
         <v>6</v>
       </c>
       <c r="C45" s="6">
-        <v>-30.25</v>
+        <v>-29.73</v>
       </c>
       <c r="D45" s="6">
-        <v>-29.73</v>
-      </c>
-      <c r="E45" s="7">
-        <v>0.52</v>
+        <v>-29.99</v>
+      </c>
+      <c r="E45" s="8">
+        <v>-0.26</v>
       </c>
     </row>
     <row r="46" spans="1:5">
@@ -2717,13 +2716,13 @@
         <v>6</v>
       </c>
       <c r="C46" s="6">
-        <v>-18.02</v>
+        <v>-17.53</v>
       </c>
       <c r="D46" s="6">
-        <v>-17.53</v>
+        <v>-15.61</v>
       </c>
       <c r="E46" s="7">
-        <v>0.49</v>
+        <v>1.92</v>
       </c>
     </row>
     <row r="47" spans="1:5">
@@ -2734,13 +2733,13 @@
         <v>2</v>
       </c>
       <c r="C47" s="6">
-        <v>381.3</v>
+        <v>390</v>
       </c>
       <c r="D47" s="6">
-        <v>390</v>
+        <v>410.05</v>
       </c>
       <c r="E47" s="7">
-        <v>8.699999999999999</v>
+        <v>20.05</v>
       </c>
     </row>
     <row r="48" spans="1:5">
@@ -2751,13 +2750,13 @@
         <v>2</v>
       </c>
       <c r="C48" s="6">
-        <v>49.74</v>
+        <v>50.45</v>
       </c>
       <c r="D48" s="6">
-        <v>50.45</v>
-      </c>
-      <c r="E48" s="7">
-        <v>0.71</v>
+        <v>50.16</v>
+      </c>
+      <c r="E48" s="8">
+        <v>-0.29</v>
       </c>
     </row>
     <row r="49" spans="1:5">
@@ -2768,13 +2767,13 @@
         <v>2</v>
       </c>
       <c r="C49" s="6">
-        <v>3187</v>
+        <v>3173.1</v>
       </c>
       <c r="D49" s="6">
-        <v>3173.1</v>
-      </c>
-      <c r="E49" s="8">
-        <v>-13.9</v>
+        <v>3209.2</v>
+      </c>
+      <c r="E49" s="7">
+        <v>36.1</v>
       </c>
     </row>
     <row r="50" spans="1:5">
@@ -2785,13 +2784,13 @@
         <v>2</v>
       </c>
       <c r="C50" s="6">
-        <v>972.7</v>
+        <v>980.5</v>
       </c>
       <c r="D50" s="6">
-        <v>980.5</v>
+        <v>986.5</v>
       </c>
       <c r="E50" s="7">
-        <v>7.8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="51" spans="1:5">
@@ -2802,13 +2801,13 @@
         <v>2</v>
       </c>
       <c r="C51" s="6">
-        <v>14.26</v>
+        <v>14.22</v>
       </c>
       <c r="D51" s="6">
-        <v>14.22</v>
+        <v>13.92</v>
       </c>
       <c r="E51" s="8">
-        <v>-0.04</v>
+        <v>-0.3</v>
       </c>
     </row>
     <row r="52" spans="1:5">
@@ -2819,13 +2818,13 @@
         <v>2</v>
       </c>
       <c r="C52" s="6">
-        <v>12.36</v>
+        <v>12.34</v>
       </c>
       <c r="D52" s="6">
-        <v>12.34</v>
+        <v>11.94</v>
       </c>
       <c r="E52" s="8">
-        <v>-0.02</v>
+        <v>-0.4</v>
       </c>
     </row>
     <row r="53" spans="1:5">
@@ -2836,13 +2835,13 @@
         <v>2</v>
       </c>
       <c r="C53" s="6">
-        <v>4052.2</v>
+        <v>4082.2</v>
       </c>
       <c r="D53" s="6">
-        <v>4082.2</v>
-      </c>
-      <c r="E53" s="7">
-        <v>30</v>
+        <v>4067</v>
+      </c>
+      <c r="E53" s="8">
+        <v>-15.2</v>
       </c>
     </row>
     <row r="54" spans="1:5">
@@ -2853,13 +2852,13 @@
         <v>2</v>
       </c>
       <c r="C54" s="6">
-        <v>10700</v>
+        <v>10764</v>
       </c>
       <c r="D54" s="6">
-        <v>10764</v>
+        <v>11014</v>
       </c>
       <c r="E54" s="7">
-        <v>64</v>
+        <v>250</v>
       </c>
     </row>
     <row r="55" spans="1:5">
@@ -2870,13 +2869,13 @@
         <v>24</v>
       </c>
       <c r="C55" s="6">
-        <v>36.17</v>
+        <v>43.64</v>
       </c>
       <c r="D55" s="6">
-        <v>43.64</v>
+        <v>56.32</v>
       </c>
       <c r="E55" s="7">
-        <v>7.47</v>
+        <v>12.68</v>
       </c>
     </row>
     <row r="56" spans="1:5">
@@ -2887,13 +2886,13 @@
         <v>24</v>
       </c>
       <c r="C56" s="6">
-        <v>33.24</v>
+        <v>37.41</v>
       </c>
       <c r="D56" s="6">
-        <v>37.41</v>
-      </c>
-      <c r="E56" s="7">
-        <v>4.17</v>
+        <v>36.41</v>
+      </c>
+      <c r="E56" s="8">
+        <v>-1</v>
       </c>
     </row>
     <row r="57" spans="1:5">
@@ -2904,13 +2903,13 @@
         <v>24</v>
       </c>
       <c r="C57" s="6">
-        <v>40.7</v>
+        <v>39.39</v>
       </c>
       <c r="D57" s="6">
-        <v>39.39</v>
-      </c>
-      <c r="E57" s="8">
-        <v>-1.31</v>
+        <v>44.41</v>
+      </c>
+      <c r="E57" s="7">
+        <v>5.02</v>
       </c>
     </row>
     <row r="58" spans="1:5">
@@ -2921,13 +2920,13 @@
         <v>24</v>
       </c>
       <c r="C58" s="6">
-        <v>39.21</v>
+        <v>41.85</v>
       </c>
       <c r="D58" s="6">
-        <v>41.85</v>
+        <v>43.87</v>
       </c>
       <c r="E58" s="7">
-        <v>2.64</v>
+        <v>2.02</v>
       </c>
     </row>
     <row r="59" spans="1:5">
@@ -2938,13 +2937,13 @@
         <v>24</v>
       </c>
       <c r="C59" s="6">
-        <v>47.44</v>
+        <v>46.94</v>
       </c>
       <c r="D59" s="6">
-        <v>46.94</v>
+        <v>43.25</v>
       </c>
       <c r="E59" s="8">
-        <v>-0.5</v>
+        <v>-3.69</v>
       </c>
     </row>
     <row r="60" spans="1:5">
@@ -2955,13 +2954,13 @@
         <v>24</v>
       </c>
       <c r="C60" s="6">
-        <v>61.88</v>
+        <v>61.46</v>
       </c>
       <c r="D60" s="6">
-        <v>61.46</v>
+        <v>53.63</v>
       </c>
       <c r="E60" s="8">
-        <v>-0.42</v>
+        <v>-7.83</v>
       </c>
     </row>
     <row r="61" spans="1:5">
@@ -2972,13 +2971,13 @@
         <v>24</v>
       </c>
       <c r="C61" s="6">
-        <v>32.91</v>
+        <v>35.72</v>
       </c>
       <c r="D61" s="6">
-        <v>35.72</v>
-      </c>
-      <c r="E61" s="7">
-        <v>2.81</v>
+        <v>34.92</v>
+      </c>
+      <c r="E61" s="8">
+        <v>-0.8</v>
       </c>
     </row>
     <row r="62" spans="1:5">
@@ -2989,13 +2988,13 @@
         <v>24</v>
       </c>
       <c r="C62" s="6">
-        <v>27.43</v>
+        <v>30.66</v>
       </c>
       <c r="D62" s="6">
-        <v>30.66</v>
+        <v>41.61</v>
       </c>
       <c r="E62" s="7">
-        <v>3.23</v>
+        <v>10.95</v>
       </c>
     </row>
     <row r="63" spans="1:5">
@@ -3006,13 +3005,13 @@
         <v>31</v>
       </c>
       <c r="C63" s="6">
-        <v>-56.17</v>
+        <v>-4.15</v>
       </c>
       <c r="D63" s="6">
-        <v>-4.15</v>
+        <v>72.67</v>
       </c>
       <c r="E63" s="7">
-        <v>52.02</v>
+        <v>76.81999999999999</v>
       </c>
     </row>
     <row r="64" spans="1:5">
@@ -3023,13 +3022,13 @@
         <v>31</v>
       </c>
       <c r="C64" s="6">
-        <v>87.08</v>
+        <v>-45.19</v>
       </c>
       <c r="D64" s="6">
-        <v>-45.19</v>
-      </c>
-      <c r="E64" s="8">
-        <v>-132.27</v>
+        <v>-26.41</v>
+      </c>
+      <c r="E64" s="7">
+        <v>18.78</v>
       </c>
     </row>
     <row r="65" spans="1:5">
@@ -3040,13 +3039,13 @@
         <v>31</v>
       </c>
       <c r="C65" s="6">
-        <v>-25.62</v>
+        <v>-34.89</v>
       </c>
       <c r="D65" s="6">
-        <v>-34.89</v>
+        <v>-37.8</v>
       </c>
       <c r="E65" s="8">
-        <v>-9.27</v>
+        <v>-2.91</v>
       </c>
     </row>
     <row r="66" spans="1:5">
@@ -3057,13 +3056,13 @@
         <v>31</v>
       </c>
       <c r="C66" s="6">
-        <v>15.06</v>
+        <v>-9.41</v>
       </c>
       <c r="D66" s="6">
-        <v>-9.41</v>
-      </c>
-      <c r="E66" s="8">
-        <v>-24.47</v>
+        <v>175.47</v>
+      </c>
+      <c r="E66" s="7">
+        <v>184.88</v>
       </c>
     </row>
     <row r="67" spans="1:5">
@@ -3074,13 +3073,13 @@
         <v>31</v>
       </c>
       <c r="C67" s="6">
-        <v>-37.62</v>
+        <v>-62.23</v>
       </c>
       <c r="D67" s="6">
-        <v>-62.23</v>
-      </c>
-      <c r="E67" s="8">
-        <v>-24.61</v>
+        <v>-24.86</v>
+      </c>
+      <c r="E67" s="7">
+        <v>37.37</v>
       </c>
     </row>
     <row r="68" spans="1:5">
@@ -3091,13 +3090,13 @@
         <v>31</v>
       </c>
       <c r="C68" s="6">
-        <v>210.43</v>
+        <v>7.02</v>
       </c>
       <c r="D68" s="6">
-        <v>7.02</v>
-      </c>
-      <c r="E68" s="8">
-        <v>-203.41</v>
+        <v>16.47</v>
+      </c>
+      <c r="E68" s="7">
+        <v>9.449999999999999</v>
       </c>
     </row>
     <row r="69" spans="1:5">
@@ -3108,13 +3107,13 @@
         <v>31</v>
       </c>
       <c r="C69" s="6">
-        <v>65.79000000000001</v>
+        <v>-30.36</v>
       </c>
       <c r="D69" s="6">
-        <v>-30.36</v>
+        <v>-42.23</v>
       </c>
       <c r="E69" s="8">
-        <v>-96.15000000000001</v>
+        <v>-11.87</v>
       </c>
     </row>
     <row r="70" spans="1:5">
@@ -3125,13 +3124,13 @@
         <v>31</v>
       </c>
       <c r="C70" s="6">
-        <v>-6.19</v>
+        <v>-28.96</v>
       </c>
       <c r="D70" s="6">
-        <v>-28.96</v>
-      </c>
-      <c r="E70" s="8">
-        <v>-22.77</v>
+        <v>81.31</v>
+      </c>
+      <c r="E70" s="7">
+        <v>110.27</v>
       </c>
     </row>
   </sheetData>
@@ -3196,16 +3195,16 @@
         <v>8</v>
       </c>
       <c r="D2" s="11">
-        <v>42.1</v>
+        <v>44.3</v>
       </c>
       <c r="E2" s="11">
         <v>60</v>
       </c>
       <c r="F2" s="11">
-        <v>-3.7</v>
+        <v>-2.4</v>
       </c>
       <c r="G2" s="11">
-        <v>-4.2</v>
+        <v>-3.4</v>
       </c>
       <c r="H2" s="11">
         <v>56.1</v>
@@ -3316,10 +3315,10 @@
         <v>37</v>
       </c>
       <c r="B1" s="13" t="s">
+        <v>40</v>
+      </c>
+      <c r="C1" s="13" t="s">
         <v>43</v>
-      </c>
-      <c r="C1" s="13" t="s">
-        <v>40</v>
       </c>
       <c r="D1" s="13" t="s">
         <v>39</v>
@@ -3339,28 +3338,28 @@
     </row>
     <row r="2" spans="1:8">
       <c r="A2" s="14">
-        <v>0.2895</v>
+        <v>0.3078</v>
       </c>
       <c r="B2" s="14">
-        <v>0.1714</v>
+        <v>0.1799</v>
       </c>
       <c r="C2" s="14">
-        <v>0.1636</v>
+        <v>0.176</v>
       </c>
       <c r="D2" s="14">
-        <v>0.1567</v>
+        <v>0.1644</v>
       </c>
       <c r="E2" s="14">
-        <v>0.0738</v>
+        <v>0.0827</v>
       </c>
       <c r="F2" s="14">
-        <v>0.0499</v>
+        <v>0.05309999999999999</v>
       </c>
       <c r="G2" s="14">
-        <v>-0.2497</v>
+        <v>-0.243</v>
       </c>
       <c r="H2" s="14">
-        <v>-0.3066</v>
+        <v>-0.3018</v>
       </c>
     </row>
   </sheetData>

--- a/BIRLA_GROUP_Technical_Metrics.xlsx
+++ b/BIRLA_GROUP_Technical_Metrics.xlsx
@@ -193,16 +193,16 @@
     <t>RSI Momentum</t>
   </si>
   <si>
-    <t>43.6 → 56.3</t>
-  </si>
-  <si>
-    <t>🟢 BULLISH</t>
-  </si>
-  <si>
-    <t>43.6</t>
-  </si>
-  <si>
-    <t>56.3</t>
+    <t>53.6 → 48.9</t>
+  </si>
+  <si>
+    <t>🔴 BEARISH</t>
+  </si>
+  <si>
+    <t>53.6</t>
+  </si>
+  <si>
+    <t>48.9</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -288,14 +288,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF9C0006"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF006100"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -328,13 +328,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -927,10 +927,10 @@
         <v>45</v>
       </c>
       <c r="C2">
-        <v>410.05</v>
+        <v>403.4</v>
       </c>
       <c r="D2">
-        <v>5.14</v>
+        <v>-1.62</v>
       </c>
       <c r="E2">
         <v>424.7</v>
@@ -939,46 +939,46 @@
         <v>278.9</v>
       </c>
       <c r="G2">
-        <v>-3.45</v>
+        <v>-5.02</v>
       </c>
       <c r="H2">
-        <v>47.02</v>
+        <v>44.64</v>
       </c>
       <c r="I2">
-        <v>2.51</v>
+        <v>2.13</v>
       </c>
       <c r="J2">
-        <v>3.55</v>
+        <v>-1.37</v>
       </c>
       <c r="K2">
-        <v>9.08</v>
+        <v>2.92</v>
       </c>
       <c r="L2">
-        <v>41.06</v>
+        <v>39.13</v>
       </c>
       <c r="M2">
-        <v>30.78</v>
+        <v>30.1</v>
       </c>
       <c r="N2">
         <v>74</v>
       </c>
       <c r="O2">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="P2">
-        <v>391.03</v>
+        <v>392.71</v>
       </c>
       <c r="Q2">
-        <v>401.27</v>
+        <v>400.79</v>
       </c>
       <c r="R2">
-        <v>403.39</v>
+        <v>403.29</v>
       </c>
       <c r="S2">
-        <v>363.11</v>
+        <v>363.35</v>
       </c>
       <c r="T2">
-        <v>12.93</v>
+        <v>11.02</v>
       </c>
       <c r="U2" t="s">
         <v>46</v>
@@ -993,43 +993,43 @@
         <v>2</v>
       </c>
       <c r="Y2">
-        <v>56.32</v>
+        <v>52.13</v>
       </c>
       <c r="Z2">
-        <v>-2.76</v>
+        <v>-2.03</v>
       </c>
       <c r="AA2">
-        <v>-2.2</v>
+        <v>-2.17</v>
       </c>
       <c r="AB2">
-        <v>-0.5600000000000001</v>
+        <v>0.14</v>
       </c>
       <c r="AC2">
-        <v>54.19</v>
+        <v>77.41</v>
       </c>
       <c r="AD2">
-        <v>27.22</v>
+        <v>50.81</v>
       </c>
       <c r="AE2">
-        <v>10.17</v>
+        <v>10.1</v>
       </c>
       <c r="AF2">
-        <v>72.67</v>
+        <v>-44.44</v>
       </c>
       <c r="AG2">
-        <v>421.02</v>
+        <v>419.79</v>
       </c>
       <c r="AH2">
-        <v>381.52</v>
+        <v>381.79</v>
       </c>
       <c r="AI2">
-        <v>369.75</v>
+        <v>372.91</v>
       </c>
       <c r="AJ2" t="s">
         <v>48</v>
       </c>
       <c r="AK2">
-        <v>30.88</v>
+        <v>29.87</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1040,10 +1040,10 @@
         <v>45</v>
       </c>
       <c r="C3">
-        <v>50.16</v>
+        <v>49.85</v>
       </c>
       <c r="D3">
-        <v>-0.57</v>
+        <v>-0.62</v>
       </c>
       <c r="E3">
         <v>93.48</v>
@@ -1052,46 +1052,46 @@
         <v>49.02</v>
       </c>
       <c r="G3">
-        <v>-46.34</v>
+        <v>-46.67</v>
       </c>
       <c r="H3">
-        <v>2.33</v>
+        <v>1.69</v>
       </c>
       <c r="I3">
-        <v>-1.43</v>
+        <v>-1.17</v>
       </c>
       <c r="J3">
-        <v>-7.91</v>
+        <v>-8.949999999999999</v>
       </c>
       <c r="K3">
-        <v>-17.28</v>
+        <v>-17.9</v>
       </c>
       <c r="L3">
-        <v>-42.57</v>
+        <v>-42.49</v>
       </c>
       <c r="M3">
-        <v>-24.3</v>
+        <v>-24.38</v>
       </c>
       <c r="N3">
         <v>13</v>
       </c>
       <c r="O3">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="P3">
-        <v>49.96</v>
+        <v>49.84</v>
       </c>
       <c r="Q3">
-        <v>51.9</v>
+        <v>51.67</v>
       </c>
       <c r="R3">
-        <v>55.8</v>
+        <v>55.6</v>
       </c>
       <c r="S3">
-        <v>63.55</v>
+        <v>63.41</v>
       </c>
       <c r="T3">
-        <v>-21.07</v>
+        <v>-21.39</v>
       </c>
       <c r="U3" t="s">
         <v>46</v>
@@ -1106,34 +1106,34 @@
         <v>0</v>
       </c>
       <c r="Y3">
-        <v>36.41</v>
+        <v>35.32</v>
       </c>
       <c r="Z3">
-        <v>-1.75</v>
+        <v>-1.72</v>
       </c>
       <c r="AA3">
-        <v>-1.77</v>
+        <v>-1.76</v>
       </c>
       <c r="AB3">
-        <v>0.02</v>
+        <v>0.05</v>
       </c>
       <c r="AC3">
-        <v>62.57</v>
+        <v>66.62</v>
       </c>
       <c r="AD3">
-        <v>49.67</v>
+        <v>58.97</v>
       </c>
       <c r="AE3">
-        <v>1.62</v>
+        <v>1.56</v>
       </c>
       <c r="AF3">
-        <v>-26.41</v>
+        <v>-46.79</v>
       </c>
       <c r="AG3">
-        <v>55.35</v>
+        <v>55.04</v>
       </c>
       <c r="AH3">
-        <v>48.45</v>
+        <v>48.31</v>
       </c>
       <c r="AI3">
         <v>54.78</v>
@@ -1142,7 +1142,7 @@
         <v>49</v>
       </c>
       <c r="AK3">
-        <v>32.77</v>
+        <v>32.36</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1153,10 +1153,10 @@
         <v>45</v>
       </c>
       <c r="C4">
-        <v>3209.2</v>
+        <v>3166</v>
       </c>
       <c r="D4">
-        <v>1.14</v>
+        <v>-1.35</v>
       </c>
       <c r="E4">
         <v>3380.5</v>
@@ -1165,46 +1165,46 @@
         <v>2531.1</v>
       </c>
       <c r="G4">
-        <v>-5.07</v>
+        <v>-6.35</v>
       </c>
       <c r="H4">
-        <v>26.79</v>
+        <v>25.08</v>
       </c>
       <c r="I4">
-        <v>-3.31</v>
+        <v>-3.53</v>
       </c>
       <c r="J4">
-        <v>-1.86</v>
+        <v>-4.06</v>
       </c>
       <c r="K4">
-        <v>1.9</v>
+        <v>-0.29</v>
       </c>
       <c r="L4">
-        <v>14.52</v>
+        <v>11.36</v>
       </c>
       <c r="M4">
-        <v>16.44</v>
+        <v>15.79</v>
       </c>
       <c r="N4">
         <v>50</v>
       </c>
       <c r="O4">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="P4">
-        <v>3204.44</v>
+        <v>3181.26</v>
       </c>
       <c r="Q4">
-        <v>3279.34</v>
+        <v>3272.24</v>
       </c>
       <c r="R4">
-        <v>3226.93</v>
+        <v>3225.98</v>
       </c>
       <c r="S4">
-        <v>2960.28</v>
+        <v>2962.44</v>
       </c>
       <c r="T4">
-        <v>8.41</v>
+        <v>6.87</v>
       </c>
       <c r="U4" t="s">
         <v>47</v>
@@ -1219,34 +1219,34 @@
         <v>3</v>
       </c>
       <c r="Y4">
-        <v>44.41</v>
+        <v>40.12</v>
       </c>
       <c r="Z4">
-        <v>-9.66</v>
+        <v>-15.28</v>
       </c>
       <c r="AA4">
-        <v>9.15</v>
+        <v>4.27</v>
       </c>
       <c r="AB4">
-        <v>-18.82</v>
+        <v>-19.55</v>
       </c>
       <c r="AC4">
-        <v>12.03</v>
+        <v>12.06</v>
       </c>
       <c r="AD4">
-        <v>6.36</v>
+        <v>9.4</v>
       </c>
       <c r="AE4">
-        <v>61.02</v>
+        <v>60.33</v>
       </c>
       <c r="AF4">
-        <v>-37.8</v>
+        <v>-82.73999999999999</v>
       </c>
       <c r="AG4">
-        <v>3385.78</v>
+        <v>3389.07</v>
       </c>
       <c r="AH4">
-        <v>3172.9</v>
+        <v>3155.41</v>
       </c>
       <c r="AI4">
         <v>3120.02</v>
@@ -1255,7 +1255,7 @@
         <v>48</v>
       </c>
       <c r="AK4">
-        <v>28.19</v>
+        <v>30.77</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1266,10 +1266,10 @@
         <v>45</v>
       </c>
       <c r="C5">
-        <v>986.5</v>
+        <v>981.2</v>
       </c>
       <c r="D5">
-        <v>0.61</v>
+        <v>-0.54</v>
       </c>
       <c r="E5">
         <v>1149.7</v>
@@ -1278,25 +1278,25 @@
         <v>741.05</v>
       </c>
       <c r="G5">
-        <v>-14.2</v>
+        <v>-14.66</v>
       </c>
       <c r="H5">
-        <v>33.12</v>
+        <v>32.41</v>
       </c>
       <c r="I5">
-        <v>-2.71</v>
+        <v>-0.03</v>
       </c>
       <c r="J5">
-        <v>-5.05</v>
+        <v>-4.72</v>
       </c>
       <c r="K5">
-        <v>-2.33</v>
+        <v>-3.25</v>
       </c>
       <c r="L5">
-        <v>30.9</v>
+        <v>29.8</v>
       </c>
       <c r="M5">
-        <v>17.99</v>
+        <v>17.49</v>
       </c>
       <c r="N5">
         <v>62</v>
@@ -1305,19 +1305,19 @@
         <v>74</v>
       </c>
       <c r="P5">
-        <v>975.98</v>
+        <v>975.92</v>
       </c>
       <c r="Q5">
-        <v>1012.72</v>
+        <v>1010.08</v>
       </c>
       <c r="R5">
-        <v>1002.36</v>
+        <v>1002.63</v>
       </c>
       <c r="S5">
-        <v>974.54</v>
+        <v>975.41</v>
       </c>
       <c r="T5">
-        <v>1.23</v>
+        <v>0.59</v>
       </c>
       <c r="U5" t="s">
         <v>47</v>
@@ -1332,34 +1332,34 @@
         <v>3</v>
       </c>
       <c r="Y5">
-        <v>43.87</v>
+        <v>42.47</v>
       </c>
       <c r="Z5">
-        <v>-10.47</v>
+        <v>-10.83</v>
       </c>
       <c r="AA5">
-        <v>-5</v>
+        <v>-6.17</v>
       </c>
       <c r="AB5">
-        <v>-5.47</v>
+        <v>-4.66</v>
       </c>
       <c r="AC5">
-        <v>39.53</v>
+        <v>45.86</v>
       </c>
       <c r="AD5">
-        <v>23.39</v>
+        <v>35.79</v>
       </c>
       <c r="AE5">
-        <v>22.76</v>
+        <v>22.39</v>
       </c>
       <c r="AF5">
-        <v>175.47</v>
+        <v>1.12</v>
       </c>
       <c r="AG5">
-        <v>1066.79</v>
+        <v>1064.92</v>
       </c>
       <c r="AH5">
-        <v>958.64</v>
+        <v>955.23</v>
       </c>
       <c r="AI5">
         <v>1037.86</v>
@@ -1368,7 +1368,7 @@
         <v>49</v>
       </c>
       <c r="AK5">
-        <v>26.17</v>
+        <v>24.95</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1379,10 +1379,10 @@
         <v>45</v>
       </c>
       <c r="C6">
-        <v>13.92</v>
+        <v>13.84</v>
       </c>
       <c r="D6">
-        <v>-2.11</v>
+        <v>-0.57</v>
       </c>
       <c r="E6">
         <v>15.6</v>
@@ -1391,46 +1391,46 @@
         <v>7.77</v>
       </c>
       <c r="G6">
-        <v>-10.77</v>
+        <v>-11.28</v>
       </c>
       <c r="H6">
-        <v>79.15000000000001</v>
+        <v>78.12</v>
       </c>
       <c r="I6">
-        <v>-6.58</v>
+        <v>-7.55</v>
       </c>
       <c r="J6">
-        <v>-1.07</v>
+        <v>-1.35</v>
       </c>
       <c r="K6">
-        <v>-6.7</v>
+        <v>-6.61</v>
       </c>
       <c r="L6">
-        <v>71.01000000000001</v>
+        <v>74.31</v>
       </c>
       <c r="M6">
-        <v>5.31</v>
+        <v>5.09</v>
       </c>
       <c r="N6">
         <v>87</v>
       </c>
       <c r="O6">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="P6">
-        <v>14.36</v>
+        <v>14.14</v>
       </c>
       <c r="Q6">
-        <v>14.68</v>
+        <v>14.67</v>
       </c>
       <c r="R6">
-        <v>13.91</v>
+        <v>13.9</v>
       </c>
       <c r="S6">
-        <v>12.11</v>
+        <v>12.13</v>
       </c>
       <c r="T6">
-        <v>14.96</v>
+        <v>14.12</v>
       </c>
       <c r="U6" t="s">
         <v>47</v>
@@ -1445,43 +1445,43 @@
         <v>3</v>
       </c>
       <c r="Y6">
-        <v>43.25</v>
+        <v>42.3</v>
       </c>
       <c r="Z6">
-        <v>0.13</v>
+        <v>0.06</v>
       </c>
       <c r="AA6">
-        <v>0.28</v>
+        <v>0.24</v>
       </c>
       <c r="AB6">
-        <v>-0.15</v>
+        <v>-0.17</v>
       </c>
       <c r="AC6">
         <v>0</v>
       </c>
       <c r="AD6">
-        <v>2.89</v>
+        <v>0</v>
       </c>
       <c r="AE6">
-        <v>0.49</v>
+        <v>0.48</v>
       </c>
       <c r="AF6">
-        <v>-24.86</v>
+        <v>-35.68</v>
       </c>
       <c r="AG6">
-        <v>15.74</v>
+        <v>15.75</v>
       </c>
       <c r="AH6">
-        <v>13.62</v>
+        <v>13.6</v>
       </c>
       <c r="AI6">
-        <v>15.61</v>
+        <v>15.41</v>
       </c>
       <c r="AJ6" t="s">
         <v>49</v>
       </c>
       <c r="AK6">
-        <v>29.61</v>
+        <v>30.7</v>
       </c>
     </row>
     <row r="7" spans="1:37">
@@ -1492,10 +1492,10 @@
         <v>45</v>
       </c>
       <c r="C7">
-        <v>11.94</v>
+        <v>11.66</v>
       </c>
       <c r="D7">
-        <v>-3.24</v>
+        <v>-2.35</v>
       </c>
       <c r="E7">
         <v>13.92</v>
@@ -1504,46 +1504,46 @@
         <v>4.69</v>
       </c>
       <c r="G7">
-        <v>-14.22</v>
+        <v>-16.24</v>
       </c>
       <c r="H7">
-        <v>154.58</v>
+        <v>148.61</v>
       </c>
       <c r="I7">
-        <v>1.36</v>
+        <v>-2.91</v>
       </c>
       <c r="J7">
-        <v>1.88</v>
+        <v>-0.17</v>
       </c>
       <c r="K7">
-        <v>-0.91</v>
+        <v>-1.27</v>
       </c>
       <c r="L7">
-        <v>129.62</v>
+        <v>113.55</v>
       </c>
       <c r="M7">
-        <v>-30.18</v>
+        <v>-30.8</v>
       </c>
       <c r="N7">
         <v>99</v>
       </c>
       <c r="O7">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="P7">
-        <v>12.25</v>
+        <v>12.18</v>
       </c>
       <c r="Q7">
-        <v>11.51</v>
+        <v>11.52</v>
       </c>
       <c r="R7">
-        <v>11.73</v>
+        <v>11.75</v>
       </c>
       <c r="S7">
-        <v>10.62</v>
+        <v>10.65</v>
       </c>
       <c r="T7">
-        <v>12.41</v>
+        <v>9.449999999999999</v>
       </c>
       <c r="U7" t="s">
         <v>46</v>
@@ -1558,34 +1558,34 @@
         <v>2</v>
       </c>
       <c r="Y7">
-        <v>53.63</v>
+        <v>48.93</v>
       </c>
       <c r="Z7">
-        <v>0.13</v>
+        <v>0.1</v>
       </c>
       <c r="AA7">
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="AB7">
-        <v>0.13</v>
+        <v>0.08</v>
       </c>
       <c r="AC7">
-        <v>73.12</v>
+        <v>58.58</v>
       </c>
       <c r="AD7">
-        <v>85.16</v>
+        <v>73.26000000000001</v>
       </c>
       <c r="AE7">
-        <v>0.36</v>
+        <v>0.38</v>
       </c>
       <c r="AF7">
-        <v>16.47</v>
+        <v>6.56</v>
       </c>
       <c r="AG7">
-        <v>12.5</v>
+        <v>12.51</v>
       </c>
       <c r="AH7">
-        <v>10.51</v>
+        <v>10.52</v>
       </c>
       <c r="AI7">
         <v>11.5</v>
@@ -1594,7 +1594,7 @@
         <v>48</v>
       </c>
       <c r="AK7">
-        <v>45.32</v>
+        <v>41.12</v>
       </c>
     </row>
     <row r="8" spans="1:37">
@@ -1605,37 +1605,37 @@
         <v>45</v>
       </c>
       <c r="C8">
-        <v>4067</v>
+        <v>4027.1</v>
       </c>
       <c r="D8">
-        <v>-0.37</v>
+        <v>-0.98</v>
       </c>
       <c r="E8">
         <v>5809.5</v>
       </c>
       <c r="F8">
-        <v>4052.2</v>
+        <v>4027.1</v>
       </c>
       <c r="G8">
-        <v>-29.99</v>
+        <v>-30.68</v>
       </c>
       <c r="H8">
-        <v>0.37</v>
+        <v>0</v>
       </c>
       <c r="I8">
-        <v>-3.99</v>
+        <v>-3.92</v>
       </c>
       <c r="J8">
-        <v>-5.24</v>
+        <v>-6.55</v>
       </c>
       <c r="K8">
-        <v>-8.08</v>
+        <v>-9.17</v>
       </c>
       <c r="L8">
-        <v>-22.43</v>
+        <v>-23.54</v>
       </c>
       <c r="M8">
-        <v>17.6</v>
+        <v>17.01</v>
       </c>
       <c r="N8">
         <v>26</v>
@@ -1644,19 +1644,19 @@
         <v>31</v>
       </c>
       <c r="P8">
-        <v>4094.96</v>
+        <v>4062.06</v>
       </c>
       <c r="Q8">
-        <v>4269.08</v>
+        <v>4252.59</v>
       </c>
       <c r="R8">
-        <v>4330.67</v>
+        <v>4322.52</v>
       </c>
       <c r="S8">
-        <v>4582.71</v>
+        <v>4576.62</v>
       </c>
       <c r="T8">
-        <v>-11.25</v>
+        <v>-12.01</v>
       </c>
       <c r="U8" t="s">
         <v>46</v>
@@ -1671,43 +1671,43 @@
         <v>0</v>
       </c>
       <c r="Y8">
-        <v>34.92</v>
+        <v>32.85</v>
       </c>
       <c r="Z8">
-        <v>-77.95999999999999</v>
+        <v>-84.06</v>
       </c>
       <c r="AA8">
-        <v>-51.22</v>
+        <v>-57.79</v>
       </c>
       <c r="AB8">
-        <v>-26.74</v>
+        <v>-26.27</v>
       </c>
       <c r="AC8">
-        <v>21.53</v>
+        <v>21.98</v>
       </c>
       <c r="AD8">
-        <v>21.23</v>
+        <v>20.7</v>
       </c>
       <c r="AE8">
-        <v>103.44</v>
+        <v>104.92</v>
       </c>
       <c r="AF8">
-        <v>-42.23</v>
+        <v>89.36</v>
       </c>
       <c r="AG8">
-        <v>4519.79</v>
+        <v>4521.69</v>
       </c>
       <c r="AH8">
-        <v>4018.37</v>
+        <v>3983.49</v>
       </c>
       <c r="AI8">
-        <v>4394.81</v>
+        <v>4318.07</v>
       </c>
       <c r="AJ8" t="s">
         <v>49</v>
       </c>
       <c r="AK8">
-        <v>53.7</v>
+        <v>56.69</v>
       </c>
     </row>
     <row r="9" spans="1:37">
@@ -1718,10 +1718,10 @@
         <v>45</v>
       </c>
       <c r="C9">
-        <v>11014</v>
+        <v>11100</v>
       </c>
       <c r="D9">
-        <v>2.32</v>
+        <v>0.78</v>
       </c>
       <c r="E9">
         <v>13052</v>
@@ -1730,46 +1730,46 @@
         <v>10362</v>
       </c>
       <c r="G9">
-        <v>-15.61</v>
+        <v>-14.96</v>
       </c>
       <c r="H9">
-        <v>6.29</v>
+        <v>7.12</v>
       </c>
       <c r="I9">
-        <v>0.32</v>
+        <v>0.91</v>
       </c>
       <c r="J9">
-        <v>-3.81</v>
+        <v>-4.1</v>
       </c>
       <c r="K9">
-        <v>-3.11</v>
+        <v>-2.65</v>
       </c>
       <c r="L9">
-        <v>-11.43</v>
+        <v>-11.75</v>
       </c>
       <c r="M9">
-        <v>8.27</v>
+        <v>8.380000000000001</v>
       </c>
       <c r="N9">
         <v>38</v>
       </c>
       <c r="O9">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="P9">
-        <v>10835</v>
+        <v>10855</v>
       </c>
       <c r="Q9">
-        <v>11240.05</v>
+        <v>11216.55</v>
       </c>
       <c r="R9">
-        <v>11595.38</v>
+        <v>11583.16</v>
       </c>
       <c r="S9">
-        <v>11732.86</v>
+        <v>11730.02</v>
       </c>
       <c r="T9">
-        <v>-6.13</v>
+        <v>-5.37</v>
       </c>
       <c r="U9" t="s">
         <v>46</v>
@@ -1784,34 +1784,34 @@
         <v>0</v>
       </c>
       <c r="Y9">
-        <v>41.61</v>
+        <v>44.84</v>
       </c>
       <c r="Z9">
-        <v>-228.39</v>
+        <v>-205.17</v>
       </c>
       <c r="AA9">
-        <v>-195.44</v>
+        <v>-197.39</v>
       </c>
       <c r="AB9">
-        <v>-32.95</v>
+        <v>-7.78</v>
       </c>
       <c r="AC9">
-        <v>39.25</v>
+        <v>72.37</v>
       </c>
       <c r="AD9">
-        <v>17.83</v>
+        <v>39.36</v>
       </c>
       <c r="AE9">
-        <v>206.57</v>
+        <v>203.46</v>
       </c>
       <c r="AF9">
-        <v>81.31</v>
+        <v>-42.09</v>
       </c>
       <c r="AG9">
-        <v>11909.85</v>
+        <v>11870.4</v>
       </c>
       <c r="AH9">
-        <v>10570.25</v>
+        <v>10562.7</v>
       </c>
       <c r="AI9">
         <v>11371.08</v>
@@ -1820,7 +1820,7 @@
         <v>49</v>
       </c>
       <c r="AK9">
-        <v>43.16</v>
+        <v>38.05</v>
       </c>
     </row>
   </sheetData>
@@ -2001,7 +2001,7 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="4" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="B3" s="4" t="s">
         <v>56</v>
@@ -2053,13 +2053,13 @@
         <v>9</v>
       </c>
       <c r="C7" s="6">
-        <v>-2.99</v>
+        <v>3.55</v>
       </c>
       <c r="D7" s="6">
-        <v>3.55</v>
+        <v>-1.37</v>
       </c>
       <c r="E7" s="7">
-        <v>6.54</v>
+        <v>-4.92</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -2070,13 +2070,13 @@
         <v>9</v>
       </c>
       <c r="C8" s="6">
-        <v>-8.220000000000001</v>
+        <v>-7.91</v>
       </c>
       <c r="D8" s="6">
-        <v>-7.91</v>
+        <v>-8.949999999999999</v>
       </c>
       <c r="E8" s="7">
-        <v>0.31</v>
+        <v>-1.04</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -2087,13 +2087,13 @@
         <v>9</v>
       </c>
       <c r="C9" s="6">
-        <v>-3.22</v>
+        <v>-1.86</v>
       </c>
       <c r="D9" s="6">
-        <v>-1.86</v>
+        <v>-4.06</v>
       </c>
       <c r="E9" s="7">
-        <v>1.36</v>
+        <v>-2.2</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -2104,13 +2104,13 @@
         <v>9</v>
       </c>
       <c r="C10" s="6">
-        <v>-5.87</v>
+        <v>-5.05</v>
       </c>
       <c r="D10" s="6">
-        <v>-5.05</v>
-      </c>
-      <c r="E10" s="7">
-        <v>0.82</v>
+        <v>-4.72</v>
+      </c>
+      <c r="E10" s="8">
+        <v>0.33</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -2121,13 +2121,13 @@
         <v>9</v>
       </c>
       <c r="C11" s="6">
-        <v>0.71</v>
+        <v>-1.07</v>
       </c>
       <c r="D11" s="6">
-        <v>-1.07</v>
-      </c>
-      <c r="E11" s="8">
-        <v>-1.78</v>
+        <v>-1.35</v>
+      </c>
+      <c r="E11" s="7">
+        <v>-0.28</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -2138,13 +2138,13 @@
         <v>9</v>
       </c>
       <c r="C12" s="6">
-        <v>3.26</v>
+        <v>1.88</v>
       </c>
       <c r="D12" s="6">
-        <v>1.88</v>
-      </c>
-      <c r="E12" s="8">
-        <v>-1.38</v>
+        <v>-0.17</v>
+      </c>
+      <c r="E12" s="7">
+        <v>-2.05</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -2155,13 +2155,13 @@
         <v>9</v>
       </c>
       <c r="C13" s="6">
-        <v>-6.92</v>
+        <v>-5.24</v>
       </c>
       <c r="D13" s="6">
-        <v>-5.24</v>
+        <v>-6.55</v>
       </c>
       <c r="E13" s="7">
-        <v>1.68</v>
+        <v>-1.31</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -2172,13 +2172,13 @@
         <v>9</v>
       </c>
       <c r="C14" s="6">
-        <v>-6.39</v>
+        <v>-3.81</v>
       </c>
       <c r="D14" s="6">
-        <v>-3.81</v>
+        <v>-4.1</v>
       </c>
       <c r="E14" s="7">
-        <v>2.58</v>
+        <v>-0.29</v>
       </c>
     </row>
     <row r="15" spans="1:6">
@@ -2189,13 +2189,13 @@
         <v>8</v>
       </c>
       <c r="C15" s="6">
-        <v>-2.5</v>
+        <v>2.51</v>
       </c>
       <c r="D15" s="6">
-        <v>2.51</v>
+        <v>2.13</v>
       </c>
       <c r="E15" s="7">
-        <v>5.01</v>
+        <v>-0.38</v>
       </c>
     </row>
     <row r="16" spans="1:6">
@@ -2206,13 +2206,13 @@
         <v>8</v>
       </c>
       <c r="C16" s="6">
-        <v>-1.71</v>
+        <v>-1.43</v>
       </c>
       <c r="D16" s="6">
-        <v>-1.43</v>
-      </c>
-      <c r="E16" s="7">
-        <v>0.28</v>
+        <v>-1.17</v>
+      </c>
+      <c r="E16" s="8">
+        <v>0.26</v>
       </c>
     </row>
     <row r="17" spans="1:5">
@@ -2223,13 +2223,13 @@
         <v>8</v>
       </c>
       <c r="C17" s="6">
-        <v>-3.85</v>
+        <v>-3.31</v>
       </c>
       <c r="D17" s="6">
-        <v>-3.31</v>
+        <v>-3.53</v>
       </c>
       <c r="E17" s="7">
-        <v>0.54</v>
+        <v>-0.22</v>
       </c>
     </row>
     <row r="18" spans="1:5">
@@ -2240,13 +2240,13 @@
         <v>8</v>
       </c>
       <c r="C18" s="6">
-        <v>-4.52</v>
+        <v>-2.71</v>
       </c>
       <c r="D18" s="6">
-        <v>-2.71</v>
-      </c>
-      <c r="E18" s="7">
-        <v>1.81</v>
+        <v>-0.03</v>
+      </c>
+      <c r="E18" s="8">
+        <v>2.68</v>
       </c>
     </row>
     <row r="19" spans="1:5">
@@ -2257,13 +2257,13 @@
         <v>8</v>
       </c>
       <c r="C19" s="6">
-        <v>-8.380000000000001</v>
+        <v>-6.58</v>
       </c>
       <c r="D19" s="6">
-        <v>-6.58</v>
+        <v>-7.55</v>
       </c>
       <c r="E19" s="7">
-        <v>1.8</v>
+        <v>-0.97</v>
       </c>
     </row>
     <row r="20" spans="1:5">
@@ -2274,13 +2274,13 @@
         <v>8</v>
       </c>
       <c r="C20" s="6">
-        <v>6.84</v>
+        <v>1.36</v>
       </c>
       <c r="D20" s="6">
-        <v>1.36</v>
-      </c>
-      <c r="E20" s="8">
-        <v>-5.48</v>
+        <v>-2.91</v>
+      </c>
+      <c r="E20" s="7">
+        <v>-4.27</v>
       </c>
     </row>
     <row r="21" spans="1:5">
@@ -2291,13 +2291,13 @@
         <v>8</v>
       </c>
       <c r="C21" s="6">
-        <v>-0.67</v>
+        <v>-3.99</v>
       </c>
       <c r="D21" s="6">
-        <v>-3.99</v>
+        <v>-3.92</v>
       </c>
       <c r="E21" s="8">
-        <v>-3.32</v>
+        <v>0.07000000000000001</v>
       </c>
     </row>
     <row r="22" spans="1:5">
@@ -2308,13 +2308,13 @@
         <v>8</v>
       </c>
       <c r="C22" s="6">
-        <v>-1.25</v>
+        <v>0.32</v>
       </c>
       <c r="D22" s="6">
-        <v>0.32</v>
-      </c>
-      <c r="E22" s="7">
-        <v>1.57</v>
+        <v>0.91</v>
+      </c>
+      <c r="E22" s="8">
+        <v>0.59</v>
       </c>
     </row>
     <row r="23" spans="1:5">
@@ -2325,13 +2325,13 @@
         <v>11</v>
       </c>
       <c r="C23" s="6">
-        <v>33.79</v>
+        <v>41.06</v>
       </c>
       <c r="D23" s="6">
-        <v>41.06</v>
+        <v>39.13</v>
       </c>
       <c r="E23" s="7">
-        <v>7.27</v>
+        <v>-1.93</v>
       </c>
     </row>
     <row r="24" spans="1:5">
@@ -2342,13 +2342,13 @@
         <v>11</v>
       </c>
       <c r="C24" s="6">
-        <v>-42.92</v>
+        <v>-42.57</v>
       </c>
       <c r="D24" s="6">
-        <v>-42.57</v>
-      </c>
-      <c r="E24" s="7">
-        <v>0.35</v>
+        <v>-42.49</v>
+      </c>
+      <c r="E24" s="8">
+        <v>0.08</v>
       </c>
     </row>
     <row r="25" spans="1:5">
@@ -2359,13 +2359,13 @@
         <v>11</v>
       </c>
       <c r="C25" s="6">
-        <v>13.24</v>
+        <v>14.52</v>
       </c>
       <c r="D25" s="6">
-        <v>14.52</v>
+        <v>11.36</v>
       </c>
       <c r="E25" s="7">
-        <v>1.28</v>
+        <v>-3.16</v>
       </c>
     </row>
     <row r="26" spans="1:5">
@@ -2376,13 +2376,13 @@
         <v>11</v>
       </c>
       <c r="C26" s="6">
-        <v>29.35</v>
+        <v>30.9</v>
       </c>
       <c r="D26" s="6">
-        <v>30.9</v>
+        <v>29.8</v>
       </c>
       <c r="E26" s="7">
-        <v>1.55</v>
+        <v>-1.1</v>
       </c>
     </row>
     <row r="27" spans="1:5">
@@ -2393,13 +2393,13 @@
         <v>11</v>
       </c>
       <c r="C27" s="6">
-        <v>85.64</v>
+        <v>71.01000000000001</v>
       </c>
       <c r="D27" s="6">
-        <v>71.01000000000001</v>
+        <v>74.31</v>
       </c>
       <c r="E27" s="8">
-        <v>-14.63</v>
+        <v>3.3</v>
       </c>
     </row>
     <row r="28" spans="1:5">
@@ -2410,13 +2410,13 @@
         <v>11</v>
       </c>
       <c r="C28" s="6">
-        <v>147.29</v>
+        <v>129.62</v>
       </c>
       <c r="D28" s="6">
-        <v>129.62</v>
-      </c>
-      <c r="E28" s="8">
-        <v>-17.67</v>
+        <v>113.55</v>
+      </c>
+      <c r="E28" s="7">
+        <v>-16.07</v>
       </c>
     </row>
     <row r="29" spans="1:5">
@@ -2427,13 +2427,13 @@
         <v>11</v>
       </c>
       <c r="C29" s="6">
-        <v>-21.64</v>
+        <v>-22.43</v>
       </c>
       <c r="D29" s="6">
-        <v>-22.43</v>
-      </c>
-      <c r="E29" s="8">
-        <v>-0.79</v>
+        <v>-23.54</v>
+      </c>
+      <c r="E29" s="7">
+        <v>-1.11</v>
       </c>
     </row>
     <row r="30" spans="1:5">
@@ -2444,13 +2444,13 @@
         <v>11</v>
       </c>
       <c r="C30" s="6">
-        <v>-12.98</v>
+        <v>-11.43</v>
       </c>
       <c r="D30" s="6">
-        <v>-11.43</v>
+        <v>-11.75</v>
       </c>
       <c r="E30" s="7">
-        <v>1.55</v>
+        <v>-0.32</v>
       </c>
     </row>
     <row r="31" spans="1:5">
@@ -2461,13 +2461,13 @@
         <v>10</v>
       </c>
       <c r="C31" s="6">
-        <v>5.23</v>
+        <v>9.08</v>
       </c>
       <c r="D31" s="6">
-        <v>9.08</v>
+        <v>2.92</v>
       </c>
       <c r="E31" s="7">
-        <v>3.85</v>
+        <v>-6.16</v>
       </c>
     </row>
     <row r="32" spans="1:5">
@@ -2478,13 +2478,13 @@
         <v>10</v>
       </c>
       <c r="C32" s="6">
-        <v>-18.02</v>
+        <v>-17.28</v>
       </c>
       <c r="D32" s="6">
-        <v>-17.28</v>
+        <v>-17.9</v>
       </c>
       <c r="E32" s="7">
-        <v>0.74</v>
+        <v>-0.62</v>
       </c>
     </row>
     <row r="33" spans="1:5">
@@ -2495,13 +2495,13 @@
         <v>10</v>
       </c>
       <c r="C33" s="6">
-        <v>0.89</v>
+        <v>1.9</v>
       </c>
       <c r="D33" s="6">
-        <v>1.9</v>
+        <v>-0.29</v>
       </c>
       <c r="E33" s="7">
-        <v>1.01</v>
+        <v>-2.19</v>
       </c>
     </row>
     <row r="34" spans="1:5">
@@ -2512,13 +2512,13 @@
         <v>10</v>
       </c>
       <c r="C34" s="6">
-        <v>-2.78</v>
+        <v>-2.33</v>
       </c>
       <c r="D34" s="6">
-        <v>-2.33</v>
+        <v>-3.25</v>
       </c>
       <c r="E34" s="7">
-        <v>0.45</v>
+        <v>-0.92</v>
       </c>
     </row>
     <row r="35" spans="1:5">
@@ -2529,13 +2529,13 @@
         <v>10</v>
       </c>
       <c r="C35" s="6">
-        <v>-5.26</v>
+        <v>-6.7</v>
       </c>
       <c r="D35" s="6">
-        <v>-6.7</v>
+        <v>-6.61</v>
       </c>
       <c r="E35" s="8">
-        <v>-1.44</v>
+        <v>0.09</v>
       </c>
     </row>
     <row r="36" spans="1:5">
@@ -2546,13 +2546,13 @@
         <v>10</v>
       </c>
       <c r="C36" s="6">
-        <v>0.41</v>
+        <v>-0.91</v>
       </c>
       <c r="D36" s="6">
-        <v>-0.91</v>
-      </c>
-      <c r="E36" s="8">
-        <v>-1.32</v>
+        <v>-1.27</v>
+      </c>
+      <c r="E36" s="7">
+        <v>-0.36</v>
       </c>
     </row>
     <row r="37" spans="1:5">
@@ -2563,13 +2563,13 @@
         <v>10</v>
       </c>
       <c r="C37" s="6">
-        <v>-8.07</v>
+        <v>-8.08</v>
       </c>
       <c r="D37" s="6">
-        <v>-8.08</v>
-      </c>
-      <c r="E37" s="8">
-        <v>-0.01</v>
+        <v>-9.17</v>
+      </c>
+      <c r="E37" s="7">
+        <v>-1.09</v>
       </c>
     </row>
     <row r="38" spans="1:5">
@@ -2580,13 +2580,13 @@
         <v>10</v>
       </c>
       <c r="C38" s="6">
-        <v>-5.83</v>
+        <v>-3.11</v>
       </c>
       <c r="D38" s="6">
-        <v>-3.11</v>
-      </c>
-      <c r="E38" s="7">
-        <v>2.72</v>
+        <v>-2.65</v>
+      </c>
+      <c r="E38" s="8">
+        <v>0.46</v>
       </c>
     </row>
     <row r="39" spans="1:5">
@@ -2597,13 +2597,13 @@
         <v>6</v>
       </c>
       <c r="C39" s="6">
-        <v>-8.17</v>
+        <v>-3.45</v>
       </c>
       <c r="D39" s="6">
-        <v>-3.45</v>
+        <v>-5.02</v>
       </c>
       <c r="E39" s="7">
-        <v>4.72</v>
+        <v>-1.57</v>
       </c>
     </row>
     <row r="40" spans="1:5">
@@ -2614,13 +2614,13 @@
         <v>6</v>
       </c>
       <c r="C40" s="6">
-        <v>-46.03</v>
+        <v>-46.34</v>
       </c>
       <c r="D40" s="6">
-        <v>-46.34</v>
-      </c>
-      <c r="E40" s="8">
-        <v>-0.31</v>
+        <v>-46.67</v>
+      </c>
+      <c r="E40" s="7">
+        <v>-0.33</v>
       </c>
     </row>
     <row r="41" spans="1:5">
@@ -2631,13 +2631,13 @@
         <v>6</v>
       </c>
       <c r="C41" s="6">
-        <v>-6.14</v>
+        <v>-5.07</v>
       </c>
       <c r="D41" s="6">
-        <v>-5.07</v>
+        <v>-6.35</v>
       </c>
       <c r="E41" s="7">
-        <v>1.07</v>
+        <v>-1.28</v>
       </c>
     </row>
     <row r="42" spans="1:5">
@@ -2648,13 +2648,13 @@
         <v>6</v>
       </c>
       <c r="C42" s="6">
-        <v>-14.72</v>
+        <v>-14.2</v>
       </c>
       <c r="D42" s="6">
-        <v>-14.2</v>
+        <v>-14.66</v>
       </c>
       <c r="E42" s="7">
-        <v>0.52</v>
+        <v>-0.46</v>
       </c>
     </row>
     <row r="43" spans="1:5">
@@ -2665,13 +2665,13 @@
         <v>6</v>
       </c>
       <c r="C43" s="6">
-        <v>-8.85</v>
+        <v>-10.77</v>
       </c>
       <c r="D43" s="6">
-        <v>-10.77</v>
-      </c>
-      <c r="E43" s="8">
-        <v>-1.92</v>
+        <v>-11.28</v>
+      </c>
+      <c r="E43" s="7">
+        <v>-0.51</v>
       </c>
     </row>
     <row r="44" spans="1:5">
@@ -2682,13 +2682,13 @@
         <v>6</v>
       </c>
       <c r="C44" s="6">
-        <v>-11.35</v>
+        <v>-14.22</v>
       </c>
       <c r="D44" s="6">
-        <v>-14.22</v>
-      </c>
-      <c r="E44" s="8">
-        <v>-2.87</v>
+        <v>-16.24</v>
+      </c>
+      <c r="E44" s="7">
+        <v>-2.02</v>
       </c>
     </row>
     <row r="45" spans="1:5">
@@ -2699,13 +2699,13 @@
         <v>6</v>
       </c>
       <c r="C45" s="6">
-        <v>-29.73</v>
+        <v>-29.99</v>
       </c>
       <c r="D45" s="6">
-        <v>-29.99</v>
-      </c>
-      <c r="E45" s="8">
-        <v>-0.26</v>
+        <v>-30.68</v>
+      </c>
+      <c r="E45" s="7">
+        <v>-0.6899999999999999</v>
       </c>
     </row>
     <row r="46" spans="1:5">
@@ -2716,13 +2716,13 @@
         <v>6</v>
       </c>
       <c r="C46" s="6">
-        <v>-17.53</v>
+        <v>-15.61</v>
       </c>
       <c r="D46" s="6">
-        <v>-15.61</v>
-      </c>
-      <c r="E46" s="7">
-        <v>1.92</v>
+        <v>-14.96</v>
+      </c>
+      <c r="E46" s="8">
+        <v>0.65</v>
       </c>
     </row>
     <row r="47" spans="1:5">
@@ -2733,13 +2733,13 @@
         <v>2</v>
       </c>
       <c r="C47" s="6">
-        <v>390</v>
+        <v>410.05</v>
       </c>
       <c r="D47" s="6">
-        <v>410.05</v>
+        <v>403.4</v>
       </c>
       <c r="E47" s="7">
-        <v>20.05</v>
+        <v>-6.65</v>
       </c>
     </row>
     <row r="48" spans="1:5">
@@ -2750,13 +2750,13 @@
         <v>2</v>
       </c>
       <c r="C48" s="6">
-        <v>50.45</v>
+        <v>50.16</v>
       </c>
       <c r="D48" s="6">
-        <v>50.16</v>
-      </c>
-      <c r="E48" s="8">
-        <v>-0.29</v>
+        <v>49.85</v>
+      </c>
+      <c r="E48" s="7">
+        <v>-0.31</v>
       </c>
     </row>
     <row r="49" spans="1:5">
@@ -2767,13 +2767,13 @@
         <v>2</v>
       </c>
       <c r="C49" s="6">
-        <v>3173.1</v>
+        <v>3209.2</v>
       </c>
       <c r="D49" s="6">
-        <v>3209.2</v>
+        <v>3166</v>
       </c>
       <c r="E49" s="7">
-        <v>36.1</v>
+        <v>-43.2</v>
       </c>
     </row>
     <row r="50" spans="1:5">
@@ -2784,13 +2784,13 @@
         <v>2</v>
       </c>
       <c r="C50" s="6">
-        <v>980.5</v>
+        <v>986.5</v>
       </c>
       <c r="D50" s="6">
-        <v>986.5</v>
+        <v>981.2</v>
       </c>
       <c r="E50" s="7">
-        <v>6</v>
+        <v>-5.3</v>
       </c>
     </row>
     <row r="51" spans="1:5">
@@ -2801,13 +2801,13 @@
         <v>2</v>
       </c>
       <c r="C51" s="6">
-        <v>14.22</v>
+        <v>13.92</v>
       </c>
       <c r="D51" s="6">
-        <v>13.92</v>
-      </c>
-      <c r="E51" s="8">
-        <v>-0.3</v>
+        <v>13.84</v>
+      </c>
+      <c r="E51" s="7">
+        <v>-0.08</v>
       </c>
     </row>
     <row r="52" spans="1:5">
@@ -2818,13 +2818,13 @@
         <v>2</v>
       </c>
       <c r="C52" s="6">
-        <v>12.34</v>
+        <v>11.94</v>
       </c>
       <c r="D52" s="6">
-        <v>11.94</v>
-      </c>
-      <c r="E52" s="8">
-        <v>-0.4</v>
+        <v>11.66</v>
+      </c>
+      <c r="E52" s="7">
+        <v>-0.28</v>
       </c>
     </row>
     <row r="53" spans="1:5">
@@ -2835,13 +2835,13 @@
         <v>2</v>
       </c>
       <c r="C53" s="6">
-        <v>4082.2</v>
+        <v>4067</v>
       </c>
       <c r="D53" s="6">
-        <v>4067</v>
-      </c>
-      <c r="E53" s="8">
-        <v>-15.2</v>
+        <v>4027.1</v>
+      </c>
+      <c r="E53" s="7">
+        <v>-39.9</v>
       </c>
     </row>
     <row r="54" spans="1:5">
@@ -2852,13 +2852,13 @@
         <v>2</v>
       </c>
       <c r="C54" s="6">
-        <v>10764</v>
+        <v>11014</v>
       </c>
       <c r="D54" s="6">
-        <v>11014</v>
-      </c>
-      <c r="E54" s="7">
-        <v>250</v>
+        <v>11100</v>
+      </c>
+      <c r="E54" s="8">
+        <v>86</v>
       </c>
     </row>
     <row r="55" spans="1:5">
@@ -2869,13 +2869,13 @@
         <v>24</v>
       </c>
       <c r="C55" s="6">
-        <v>43.64</v>
+        <v>56.32</v>
       </c>
       <c r="D55" s="6">
-        <v>56.32</v>
+        <v>52.13</v>
       </c>
       <c r="E55" s="7">
-        <v>12.68</v>
+        <v>-4.19</v>
       </c>
     </row>
     <row r="56" spans="1:5">
@@ -2886,13 +2886,13 @@
         <v>24</v>
       </c>
       <c r="C56" s="6">
-        <v>37.41</v>
+        <v>36.41</v>
       </c>
       <c r="D56" s="6">
-        <v>36.41</v>
-      </c>
-      <c r="E56" s="8">
-        <v>-1</v>
+        <v>35.32</v>
+      </c>
+      <c r="E56" s="7">
+        <v>-1.09</v>
       </c>
     </row>
     <row r="57" spans="1:5">
@@ -2903,13 +2903,13 @@
         <v>24</v>
       </c>
       <c r="C57" s="6">
-        <v>39.39</v>
+        <v>44.41</v>
       </c>
       <c r="D57" s="6">
-        <v>44.41</v>
+        <v>40.12</v>
       </c>
       <c r="E57" s="7">
-        <v>5.02</v>
+        <v>-4.29</v>
       </c>
     </row>
     <row r="58" spans="1:5">
@@ -2920,13 +2920,13 @@
         <v>24</v>
       </c>
       <c r="C58" s="6">
-        <v>41.85</v>
+        <v>43.87</v>
       </c>
       <c r="D58" s="6">
-        <v>43.87</v>
+        <v>42.47</v>
       </c>
       <c r="E58" s="7">
-        <v>2.02</v>
+        <v>-1.4</v>
       </c>
     </row>
     <row r="59" spans="1:5">
@@ -2937,13 +2937,13 @@
         <v>24</v>
       </c>
       <c r="C59" s="6">
-        <v>46.94</v>
+        <v>43.25</v>
       </c>
       <c r="D59" s="6">
-        <v>43.25</v>
-      </c>
-      <c r="E59" s="8">
-        <v>-3.69</v>
+        <v>42.3</v>
+      </c>
+      <c r="E59" s="7">
+        <v>-0.95</v>
       </c>
     </row>
     <row r="60" spans="1:5">
@@ -2954,13 +2954,13 @@
         <v>24</v>
       </c>
       <c r="C60" s="6">
-        <v>61.46</v>
+        <v>53.63</v>
       </c>
       <c r="D60" s="6">
-        <v>53.63</v>
-      </c>
-      <c r="E60" s="8">
-        <v>-7.83</v>
+        <v>48.93</v>
+      </c>
+      <c r="E60" s="7">
+        <v>-4.7</v>
       </c>
     </row>
     <row r="61" spans="1:5">
@@ -2971,13 +2971,13 @@
         <v>24</v>
       </c>
       <c r="C61" s="6">
-        <v>35.72</v>
+        <v>34.92</v>
       </c>
       <c r="D61" s="6">
-        <v>34.92</v>
-      </c>
-      <c r="E61" s="8">
-        <v>-0.8</v>
+        <v>32.85</v>
+      </c>
+      <c r="E61" s="7">
+        <v>-2.07</v>
       </c>
     </row>
     <row r="62" spans="1:5">
@@ -2988,13 +2988,13 @@
         <v>24</v>
       </c>
       <c r="C62" s="6">
-        <v>30.66</v>
+        <v>41.61</v>
       </c>
       <c r="D62" s="6">
-        <v>41.61</v>
-      </c>
-      <c r="E62" s="7">
-        <v>10.95</v>
+        <v>44.84</v>
+      </c>
+      <c r="E62" s="8">
+        <v>3.23</v>
       </c>
     </row>
     <row r="63" spans="1:5">
@@ -3005,13 +3005,13 @@
         <v>31</v>
       </c>
       <c r="C63" s="6">
-        <v>-4.15</v>
+        <v>72.67</v>
       </c>
       <c r="D63" s="6">
-        <v>72.67</v>
+        <v>-44.44</v>
       </c>
       <c r="E63" s="7">
-        <v>76.81999999999999</v>
+        <v>-117.11</v>
       </c>
     </row>
     <row r="64" spans="1:5">
@@ -3022,13 +3022,13 @@
         <v>31</v>
       </c>
       <c r="C64" s="6">
-        <v>-45.19</v>
+        <v>-26.41</v>
       </c>
       <c r="D64" s="6">
-        <v>-26.41</v>
+        <v>-46.79</v>
       </c>
       <c r="E64" s="7">
-        <v>18.78</v>
+        <v>-20.38</v>
       </c>
     </row>
     <row r="65" spans="1:5">
@@ -3039,13 +3039,13 @@
         <v>31</v>
       </c>
       <c r="C65" s="6">
-        <v>-34.89</v>
+        <v>-37.8</v>
       </c>
       <c r="D65" s="6">
-        <v>-37.8</v>
-      </c>
-      <c r="E65" s="8">
-        <v>-2.91</v>
+        <v>-82.73999999999999</v>
+      </c>
+      <c r="E65" s="7">
+        <v>-44.94</v>
       </c>
     </row>
     <row r="66" spans="1:5">
@@ -3056,13 +3056,13 @@
         <v>31</v>
       </c>
       <c r="C66" s="6">
-        <v>-9.41</v>
+        <v>175.47</v>
       </c>
       <c r="D66" s="6">
-        <v>175.47</v>
+        <v>1.12</v>
       </c>
       <c r="E66" s="7">
-        <v>184.88</v>
+        <v>-174.35</v>
       </c>
     </row>
     <row r="67" spans="1:5">
@@ -3073,13 +3073,13 @@
         <v>31</v>
       </c>
       <c r="C67" s="6">
-        <v>-62.23</v>
+        <v>-24.86</v>
       </c>
       <c r="D67" s="6">
-        <v>-24.86</v>
+        <v>-35.68</v>
       </c>
       <c r="E67" s="7">
-        <v>37.37</v>
+        <v>-10.82</v>
       </c>
     </row>
     <row r="68" spans="1:5">
@@ -3090,13 +3090,13 @@
         <v>31</v>
       </c>
       <c r="C68" s="6">
-        <v>7.02</v>
+        <v>16.47</v>
       </c>
       <c r="D68" s="6">
-        <v>16.47</v>
+        <v>6.56</v>
       </c>
       <c r="E68" s="7">
-        <v>9.449999999999999</v>
+        <v>-9.91</v>
       </c>
     </row>
     <row r="69" spans="1:5">
@@ -3107,13 +3107,13 @@
         <v>31</v>
       </c>
       <c r="C69" s="6">
-        <v>-30.36</v>
+        <v>-42.23</v>
       </c>
       <c r="D69" s="6">
-        <v>-42.23</v>
+        <v>89.36</v>
       </c>
       <c r="E69" s="8">
-        <v>-11.87</v>
+        <v>131.59</v>
       </c>
     </row>
     <row r="70" spans="1:5">
@@ -3124,13 +3124,13 @@
         <v>31</v>
       </c>
       <c r="C70" s="6">
-        <v>-28.96</v>
+        <v>81.31</v>
       </c>
       <c r="D70" s="6">
-        <v>81.31</v>
+        <v>-42.09</v>
       </c>
       <c r="E70" s="7">
-        <v>110.27</v>
+        <v>-123.4</v>
       </c>
     </row>
   </sheetData>
@@ -3195,16 +3195,16 @@
         <v>8</v>
       </c>
       <c r="D2" s="11">
-        <v>44.3</v>
+        <v>42.4</v>
       </c>
       <c r="E2" s="11">
         <v>60</v>
       </c>
       <c r="F2" s="11">
-        <v>-2.4</v>
+        <v>-3.9</v>
       </c>
       <c r="G2" s="11">
-        <v>-3.4</v>
+        <v>-4.8</v>
       </c>
       <c r="H2" s="11">
         <v>56.1</v>
@@ -3338,28 +3338,28 @@
     </row>
     <row r="2" spans="1:8">
       <c r="A2" s="14">
-        <v>0.3078</v>
+        <v>0.301</v>
       </c>
       <c r="B2" s="14">
-        <v>0.1799</v>
+        <v>0.1749</v>
       </c>
       <c r="C2" s="14">
-        <v>0.176</v>
+        <v>0.1701</v>
       </c>
       <c r="D2" s="14">
-        <v>0.1644</v>
+        <v>0.1579</v>
       </c>
       <c r="E2" s="14">
-        <v>0.0827</v>
+        <v>0.08380000000000001</v>
       </c>
       <c r="F2" s="14">
-        <v>0.05309999999999999</v>
+        <v>0.0509</v>
       </c>
       <c r="G2" s="14">
-        <v>-0.243</v>
+        <v>-0.2438</v>
       </c>
       <c r="H2" s="14">
-        <v>-0.3018</v>
+        <v>-0.308</v>
       </c>
     </row>
   </sheetData>

--- a/BIRLA_GROUP_Technical_Metrics.xlsx
+++ b/BIRLA_GROUP_Technical_Metrics.xlsx
@@ -193,16 +193,16 @@
     <t>RSI Momentum</t>
   </si>
   <si>
-    <t>53.6 → 48.9</t>
+    <t>52.1 → 48.4</t>
   </si>
   <si>
     <t>🔴 BEARISH</t>
   </si>
   <si>
-    <t>53.6</t>
-  </si>
-  <si>
-    <t>48.9</t>
+    <t>52.1</t>
+  </si>
+  <si>
+    <t>48.4</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -927,10 +927,10 @@
         <v>45</v>
       </c>
       <c r="C2">
-        <v>403.4</v>
+        <v>397</v>
       </c>
       <c r="D2">
-        <v>-1.62</v>
+        <v>-1.59</v>
       </c>
       <c r="E2">
         <v>424.7</v>
@@ -939,25 +939,25 @@
         <v>278.9</v>
       </c>
       <c r="G2">
-        <v>-5.02</v>
+        <v>-6.52</v>
       </c>
       <c r="H2">
-        <v>44.64</v>
+        <v>42.34</v>
       </c>
       <c r="I2">
-        <v>2.13</v>
+        <v>4.8</v>
       </c>
       <c r="J2">
-        <v>-1.37</v>
+        <v>-3.87</v>
       </c>
       <c r="K2">
-        <v>2.92</v>
+        <v>3.45</v>
       </c>
       <c r="L2">
-        <v>39.13</v>
+        <v>39.81</v>
       </c>
       <c r="M2">
-        <v>30.1</v>
+        <v>29.28</v>
       </c>
       <c r="N2">
         <v>74</v>
@@ -966,19 +966,19 @@
         <v>80</v>
       </c>
       <c r="P2">
-        <v>392.71</v>
+        <v>396.35</v>
       </c>
       <c r="Q2">
-        <v>400.79</v>
+        <v>400</v>
       </c>
       <c r="R2">
-        <v>403.29</v>
+        <v>403.08</v>
       </c>
       <c r="S2">
-        <v>363.35</v>
+        <v>363.59</v>
       </c>
       <c r="T2">
-        <v>11.02</v>
+        <v>9.19</v>
       </c>
       <c r="U2" t="s">
         <v>46</v>
@@ -993,34 +993,34 @@
         <v>2</v>
       </c>
       <c r="Y2">
-        <v>52.13</v>
+        <v>48.4</v>
       </c>
       <c r="Z2">
-        <v>-2.03</v>
+        <v>-1.94</v>
       </c>
       <c r="AA2">
-        <v>-2.17</v>
+        <v>-2.12</v>
       </c>
       <c r="AB2">
-        <v>0.14</v>
+        <v>0.18</v>
       </c>
       <c r="AC2">
-        <v>77.41</v>
+        <v>82.05</v>
       </c>
       <c r="AD2">
-        <v>50.81</v>
+        <v>71.20999999999999</v>
       </c>
       <c r="AE2">
-        <v>10.1</v>
+        <v>10.11</v>
       </c>
       <c r="AF2">
-        <v>-44.44</v>
+        <v>-11.32</v>
       </c>
       <c r="AG2">
-        <v>419.79</v>
+        <v>418.18</v>
       </c>
       <c r="AH2">
-        <v>381.79</v>
+        <v>381.82</v>
       </c>
       <c r="AI2">
         <v>372.91</v>
@@ -1029,7 +1029,7 @@
         <v>48</v>
       </c>
       <c r="AK2">
-        <v>29.87</v>
+        <v>26.56</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1040,10 +1040,10 @@
         <v>45</v>
       </c>
       <c r="C3">
-        <v>49.85</v>
+        <v>49.22</v>
       </c>
       <c r="D3">
-        <v>-0.62</v>
+        <v>-1.26</v>
       </c>
       <c r="E3">
         <v>93.48</v>
@@ -1052,46 +1052,46 @@
         <v>49.02</v>
       </c>
       <c r="G3">
-        <v>-46.67</v>
+        <v>-47.35</v>
       </c>
       <c r="H3">
-        <v>1.69</v>
+        <v>0.41</v>
       </c>
       <c r="I3">
-        <v>-1.17</v>
+        <v>0.41</v>
       </c>
       <c r="J3">
-        <v>-8.949999999999999</v>
+        <v>-9.44</v>
       </c>
       <c r="K3">
-        <v>-17.9</v>
+        <v>-17.32</v>
       </c>
       <c r="L3">
-        <v>-42.49</v>
+        <v>-45.41</v>
       </c>
       <c r="M3">
-        <v>-24.38</v>
+        <v>-25.51</v>
       </c>
       <c r="N3">
         <v>13</v>
       </c>
       <c r="O3">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="P3">
-        <v>49.84</v>
+        <v>49.88</v>
       </c>
       <c r="Q3">
-        <v>51.67</v>
+        <v>51.44</v>
       </c>
       <c r="R3">
-        <v>55.6</v>
+        <v>55.37</v>
       </c>
       <c r="S3">
-        <v>63.41</v>
+        <v>63.28</v>
       </c>
       <c r="T3">
-        <v>-21.39</v>
+        <v>-22.21</v>
       </c>
       <c r="U3" t="s">
         <v>46</v>
@@ -1106,43 +1106,43 @@
         <v>0</v>
       </c>
       <c r="Y3">
-        <v>35.32</v>
+        <v>33.15</v>
       </c>
       <c r="Z3">
         <v>-1.72</v>
       </c>
       <c r="AA3">
-        <v>-1.76</v>
+        <v>-1.75</v>
       </c>
       <c r="AB3">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="AC3">
-        <v>66.62</v>
+        <v>58.34</v>
       </c>
       <c r="AD3">
-        <v>58.97</v>
+        <v>62.51</v>
       </c>
       <c r="AE3">
-        <v>1.56</v>
+        <v>1.54</v>
       </c>
       <c r="AF3">
-        <v>-46.79</v>
+        <v>-38.35</v>
       </c>
       <c r="AG3">
-        <v>55.04</v>
+        <v>54.79</v>
       </c>
       <c r="AH3">
-        <v>48.31</v>
+        <v>48.08</v>
       </c>
       <c r="AI3">
-        <v>54.78</v>
+        <v>54.24</v>
       </c>
       <c r="AJ3" t="s">
         <v>49</v>
       </c>
       <c r="AK3">
-        <v>32.36</v>
+        <v>33.64</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1153,10 +1153,10 @@
         <v>45</v>
       </c>
       <c r="C4">
-        <v>3166</v>
+        <v>3128.2</v>
       </c>
       <c r="D4">
-        <v>-1.35</v>
+        <v>-1.19</v>
       </c>
       <c r="E4">
         <v>3380.5</v>
@@ -1165,46 +1165,46 @@
         <v>2531.1</v>
       </c>
       <c r="G4">
-        <v>-6.35</v>
+        <v>-7.46</v>
       </c>
       <c r="H4">
-        <v>25.08</v>
+        <v>23.59</v>
       </c>
       <c r="I4">
-        <v>-3.53</v>
+        <v>-1.35</v>
       </c>
       <c r="J4">
-        <v>-4.06</v>
+        <v>-5.44</v>
       </c>
       <c r="K4">
-        <v>-0.29</v>
+        <v>-0.51</v>
       </c>
       <c r="L4">
-        <v>11.36</v>
+        <v>9.17</v>
       </c>
       <c r="M4">
-        <v>15.79</v>
+        <v>15.25</v>
       </c>
       <c r="N4">
         <v>50</v>
       </c>
       <c r="O4">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="P4">
-        <v>3181.26</v>
+        <v>3172.7</v>
       </c>
       <c r="Q4">
-        <v>3272.24</v>
+        <v>3264.25</v>
       </c>
       <c r="R4">
-        <v>3225.98</v>
+        <v>3225.66</v>
       </c>
       <c r="S4">
-        <v>2962.44</v>
+        <v>2964.48</v>
       </c>
       <c r="T4">
-        <v>6.87</v>
+        <v>5.52</v>
       </c>
       <c r="U4" t="s">
         <v>47</v>
@@ -1219,34 +1219,34 @@
         <v>3</v>
       </c>
       <c r="Y4">
-        <v>40.12</v>
+        <v>36.78</v>
       </c>
       <c r="Z4">
-        <v>-15.28</v>
+        <v>-22.53</v>
       </c>
       <c r="AA4">
-        <v>4.27</v>
+        <v>-1.09</v>
       </c>
       <c r="AB4">
-        <v>-19.55</v>
+        <v>-21.43</v>
       </c>
       <c r="AC4">
-        <v>12.06</v>
+        <v>10.88</v>
       </c>
       <c r="AD4">
-        <v>9.4</v>
+        <v>11.66</v>
       </c>
       <c r="AE4">
-        <v>60.33</v>
+        <v>60</v>
       </c>
       <c r="AF4">
-        <v>-82.73999999999999</v>
+        <v>-33.13</v>
       </c>
       <c r="AG4">
-        <v>3389.07</v>
+        <v>3397.28</v>
       </c>
       <c r="AH4">
-        <v>3155.41</v>
+        <v>3131.22</v>
       </c>
       <c r="AI4">
         <v>3120.02</v>
@@ -1255,7 +1255,7 @@
         <v>48</v>
       </c>
       <c r="AK4">
-        <v>30.77</v>
+        <v>34.79</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1266,10 +1266,10 @@
         <v>45</v>
       </c>
       <c r="C5">
-        <v>981.2</v>
+        <v>973</v>
       </c>
       <c r="D5">
-        <v>-0.54</v>
+        <v>-0.84</v>
       </c>
       <c r="E5">
         <v>1149.7</v>
@@ -1278,46 +1278,46 @@
         <v>741.05</v>
       </c>
       <c r="G5">
-        <v>-14.66</v>
+        <v>-15.37</v>
       </c>
       <c r="H5">
-        <v>32.41</v>
+        <v>31.3</v>
       </c>
       <c r="I5">
-        <v>-0.03</v>
+        <v>1.49</v>
       </c>
       <c r="J5">
-        <v>-4.72</v>
+        <v>-5.9</v>
       </c>
       <c r="K5">
-        <v>-3.25</v>
+        <v>-1.4</v>
       </c>
       <c r="L5">
-        <v>29.8</v>
+        <v>29.72</v>
       </c>
       <c r="M5">
-        <v>17.49</v>
+        <v>16.68</v>
       </c>
       <c r="N5">
         <v>62</v>
       </c>
       <c r="O5">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="P5">
-        <v>975.92</v>
+        <v>978.78</v>
       </c>
       <c r="Q5">
-        <v>1010.08</v>
+        <v>1005.8</v>
       </c>
       <c r="R5">
-        <v>1002.63</v>
+        <v>1002.76</v>
       </c>
       <c r="S5">
-        <v>975.41</v>
+        <v>976.1900000000001</v>
       </c>
       <c r="T5">
-        <v>0.59</v>
+        <v>-0.33</v>
       </c>
       <c r="U5" t="s">
         <v>47</v>
@@ -1329,37 +1329,37 @@
         <v>47</v>
       </c>
       <c r="X5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Y5">
-        <v>42.47</v>
+        <v>40.32</v>
       </c>
       <c r="Z5">
-        <v>-10.83</v>
+        <v>-11.64</v>
       </c>
       <c r="AA5">
-        <v>-6.17</v>
+        <v>-7.26</v>
       </c>
       <c r="AB5">
-        <v>-4.66</v>
+        <v>-4.38</v>
       </c>
       <c r="AC5">
-        <v>45.86</v>
+        <v>43.67</v>
       </c>
       <c r="AD5">
-        <v>35.79</v>
+        <v>43.02</v>
       </c>
       <c r="AE5">
-        <v>22.39</v>
+        <v>22.25</v>
       </c>
       <c r="AF5">
-        <v>1.12</v>
+        <v>2.18</v>
       </c>
       <c r="AG5">
-        <v>1064.92</v>
+        <v>1058.02</v>
       </c>
       <c r="AH5">
-        <v>955.23</v>
+        <v>953.58</v>
       </c>
       <c r="AI5">
         <v>1037.86</v>
@@ -1368,7 +1368,7 @@
         <v>49</v>
       </c>
       <c r="AK5">
-        <v>24.95</v>
+        <v>25.28</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1379,58 +1379,58 @@
         <v>45</v>
       </c>
       <c r="C6">
-        <v>13.84</v>
+        <v>14.27</v>
       </c>
       <c r="D6">
-        <v>-0.57</v>
+        <v>3.11</v>
       </c>
       <c r="E6">
         <v>15.6</v>
       </c>
       <c r="F6">
-        <v>7.77</v>
+        <v>7.84</v>
       </c>
       <c r="G6">
-        <v>-11.28</v>
+        <v>-8.529999999999999</v>
       </c>
       <c r="H6">
-        <v>78.12</v>
+        <v>82.02</v>
       </c>
       <c r="I6">
-        <v>-7.55</v>
+        <v>-1.25</v>
       </c>
       <c r="J6">
-        <v>-1.35</v>
+        <v>2.37</v>
       </c>
       <c r="K6">
-        <v>-6.61</v>
+        <v>-1.25</v>
       </c>
       <c r="L6">
-        <v>74.31</v>
+        <v>83.66</v>
       </c>
       <c r="M6">
-        <v>5.09</v>
+        <v>6.53</v>
       </c>
       <c r="N6">
         <v>87</v>
       </c>
       <c r="O6">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="P6">
-        <v>14.14</v>
+        <v>14.1</v>
       </c>
       <c r="Q6">
-        <v>14.67</v>
+        <v>14.68</v>
       </c>
       <c r="R6">
-        <v>13.9</v>
+        <v>13.91</v>
       </c>
       <c r="S6">
-        <v>12.13</v>
+        <v>12.15</v>
       </c>
       <c r="T6">
-        <v>14.12</v>
+        <v>17.49</v>
       </c>
       <c r="U6" t="s">
         <v>47</v>
@@ -1445,34 +1445,34 @@
         <v>3</v>
       </c>
       <c r="Y6">
-        <v>42.3</v>
+        <v>48.83</v>
       </c>
       <c r="Z6">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="AA6">
-        <v>0.24</v>
+        <v>0.2</v>
       </c>
       <c r="AB6">
-        <v>-0.17</v>
+        <v>-0.15</v>
       </c>
       <c r="AC6">
-        <v>0</v>
+        <v>8.390000000000001</v>
       </c>
       <c r="AD6">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AE6">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="AF6">
-        <v>-35.68</v>
+        <v>12.88</v>
       </c>
       <c r="AG6">
-        <v>15.75</v>
+        <v>15.74</v>
       </c>
       <c r="AH6">
-        <v>13.6</v>
+        <v>13.63</v>
       </c>
       <c r="AI6">
         <v>15.41</v>
@@ -1481,7 +1481,7 @@
         <v>49</v>
       </c>
       <c r="AK6">
-        <v>30.7</v>
+        <v>29.04</v>
       </c>
     </row>
     <row r="7" spans="1:37">
@@ -1492,10 +1492,10 @@
         <v>45</v>
       </c>
       <c r="C7">
-        <v>11.66</v>
+        <v>11.35</v>
       </c>
       <c r="D7">
-        <v>-2.35</v>
+        <v>-2.66</v>
       </c>
       <c r="E7">
         <v>13.92</v>
@@ -1504,46 +1504,46 @@
         <v>4.69</v>
       </c>
       <c r="G7">
-        <v>-16.24</v>
+        <v>-18.46</v>
       </c>
       <c r="H7">
-        <v>148.61</v>
+        <v>142</v>
       </c>
       <c r="I7">
-        <v>-2.91</v>
+        <v>-9.92</v>
       </c>
       <c r="J7">
-        <v>-0.17</v>
+        <v>-1.3</v>
       </c>
       <c r="K7">
-        <v>-1.27</v>
+        <v>-1.99</v>
       </c>
       <c r="L7">
-        <v>113.55</v>
+        <v>98.08</v>
       </c>
       <c r="M7">
-        <v>-30.8</v>
+        <v>-31.02</v>
       </c>
       <c r="N7">
         <v>99</v>
       </c>
       <c r="O7">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="P7">
-        <v>12.18</v>
+        <v>11.93</v>
       </c>
       <c r="Q7">
         <v>11.52</v>
       </c>
       <c r="R7">
-        <v>11.75</v>
+        <v>11.77</v>
       </c>
       <c r="S7">
-        <v>10.65</v>
+        <v>10.68</v>
       </c>
       <c r="T7">
-        <v>9.449999999999999</v>
+        <v>6.24</v>
       </c>
       <c r="U7" t="s">
         <v>46</v>
@@ -1558,28 +1558,28 @@
         <v>2</v>
       </c>
       <c r="Y7">
-        <v>48.93</v>
+        <v>44.3</v>
       </c>
       <c r="Z7">
-        <v>0.1</v>
+        <v>0.06</v>
       </c>
       <c r="AA7">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="AB7">
-        <v>0.08</v>
+        <v>0.03</v>
       </c>
       <c r="AC7">
-        <v>58.58</v>
+        <v>39.32</v>
       </c>
       <c r="AD7">
-        <v>73.26000000000001</v>
+        <v>57.01</v>
       </c>
       <c r="AE7">
         <v>0.38</v>
       </c>
       <c r="AF7">
-        <v>6.56</v>
+        <v>-4.79</v>
       </c>
       <c r="AG7">
         <v>12.51</v>
@@ -1588,13 +1588,13 @@
         <v>10.52</v>
       </c>
       <c r="AI7">
-        <v>11.5</v>
+        <v>12.59</v>
       </c>
       <c r="AJ7" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="AK7">
-        <v>41.12</v>
+        <v>35.96</v>
       </c>
     </row>
     <row r="8" spans="1:37">
@@ -1605,58 +1605,58 @@
         <v>45</v>
       </c>
       <c r="C8">
-        <v>4027.1</v>
+        <v>4008.3</v>
       </c>
       <c r="D8">
-        <v>-0.98</v>
+        <v>-0.47</v>
       </c>
       <c r="E8">
         <v>5809.5</v>
       </c>
       <c r="F8">
-        <v>4027.1</v>
+        <v>4008.3</v>
       </c>
       <c r="G8">
-        <v>-30.68</v>
+        <v>-31</v>
       </c>
       <c r="H8">
         <v>0</v>
       </c>
       <c r="I8">
-        <v>-3.92</v>
+        <v>-1.8</v>
       </c>
       <c r="J8">
-        <v>-6.55</v>
+        <v>-8</v>
       </c>
       <c r="K8">
-        <v>-9.17</v>
+        <v>-7.56</v>
       </c>
       <c r="L8">
-        <v>-23.54</v>
+        <v>-23.96</v>
       </c>
       <c r="M8">
-        <v>17.01</v>
+        <v>16.96</v>
       </c>
       <c r="N8">
         <v>26</v>
       </c>
       <c r="O8">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="P8">
-        <v>4062.06</v>
+        <v>4047.36</v>
       </c>
       <c r="Q8">
-        <v>4252.59</v>
+        <v>4234.9</v>
       </c>
       <c r="R8">
-        <v>4322.52</v>
+        <v>4313.5</v>
       </c>
       <c r="S8">
-        <v>4576.62</v>
+        <v>4570.74</v>
       </c>
       <c r="T8">
-        <v>-12.01</v>
+        <v>-12.31</v>
       </c>
       <c r="U8" t="s">
         <v>46</v>
@@ -1671,34 +1671,34 @@
         <v>0</v>
       </c>
       <c r="Y8">
-        <v>32.85</v>
+        <v>31.88</v>
       </c>
       <c r="Z8">
-        <v>-84.06</v>
+        <v>-89.38</v>
       </c>
       <c r="AA8">
-        <v>-57.79</v>
+        <v>-64.11</v>
       </c>
       <c r="AB8">
-        <v>-26.27</v>
+        <v>-25.27</v>
       </c>
       <c r="AC8">
-        <v>21.98</v>
+        <v>15.97</v>
       </c>
       <c r="AD8">
-        <v>20.7</v>
+        <v>19.83</v>
       </c>
       <c r="AE8">
-        <v>104.92</v>
+        <v>102.2</v>
       </c>
       <c r="AF8">
-        <v>89.36</v>
+        <v>-37.81</v>
       </c>
       <c r="AG8">
-        <v>4521.69</v>
+        <v>4519.74</v>
       </c>
       <c r="AH8">
-        <v>3983.49</v>
+        <v>3950.06</v>
       </c>
       <c r="AI8">
         <v>4318.07</v>
@@ -1707,7 +1707,7 @@
         <v>49</v>
       </c>
       <c r="AK8">
-        <v>56.69</v>
+        <v>58.64</v>
       </c>
     </row>
     <row r="9" spans="1:37">
@@ -1718,10 +1718,10 @@
         <v>45</v>
       </c>
       <c r="C9">
-        <v>11100</v>
+        <v>11000</v>
       </c>
       <c r="D9">
-        <v>0.78</v>
+        <v>-0.9</v>
       </c>
       <c r="E9">
         <v>13052</v>
@@ -1730,46 +1730,46 @@
         <v>10362</v>
       </c>
       <c r="G9">
-        <v>-14.96</v>
+        <v>-15.72</v>
       </c>
       <c r="H9">
-        <v>7.12</v>
+        <v>6.16</v>
       </c>
       <c r="I9">
-        <v>0.91</v>
+        <v>2.83</v>
       </c>
       <c r="J9">
-        <v>-4.1</v>
+        <v>-4.93</v>
       </c>
       <c r="K9">
-        <v>-2.65</v>
+        <v>-2.72</v>
       </c>
       <c r="L9">
-        <v>-11.75</v>
+        <v>-13.53</v>
       </c>
       <c r="M9">
-        <v>8.380000000000001</v>
+        <v>8.09</v>
       </c>
       <c r="N9">
         <v>38</v>
       </c>
       <c r="O9">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="P9">
-        <v>10855</v>
+        <v>10915.6</v>
       </c>
       <c r="Q9">
-        <v>11216.55</v>
+        <v>11191.35</v>
       </c>
       <c r="R9">
-        <v>11583.16</v>
+        <v>11571.74</v>
       </c>
       <c r="S9">
-        <v>11730.02</v>
+        <v>11727.07</v>
       </c>
       <c r="T9">
-        <v>-5.37</v>
+        <v>-6.2</v>
       </c>
       <c r="U9" t="s">
         <v>46</v>
@@ -1784,34 +1784,34 @@
         <v>0</v>
       </c>
       <c r="Y9">
-        <v>44.84</v>
+        <v>41.94</v>
       </c>
       <c r="Z9">
-        <v>-205.17</v>
+        <v>-192.62</v>
       </c>
       <c r="AA9">
-        <v>-197.39</v>
+        <v>-196.43</v>
       </c>
       <c r="AB9">
-        <v>-7.78</v>
+        <v>3.81</v>
       </c>
       <c r="AC9">
-        <v>72.37</v>
+        <v>93.94</v>
       </c>
       <c r="AD9">
-        <v>39.36</v>
+        <v>68.52</v>
       </c>
       <c r="AE9">
-        <v>203.46</v>
+        <v>199.07</v>
       </c>
       <c r="AF9">
-        <v>-42.09</v>
+        <v>23.29</v>
       </c>
       <c r="AG9">
-        <v>11870.4</v>
+        <v>11837.36</v>
       </c>
       <c r="AH9">
-        <v>10562.7</v>
+        <v>10545.34</v>
       </c>
       <c r="AI9">
         <v>11371.08</v>
@@ -1820,7 +1820,7 @@
         <v>49</v>
       </c>
       <c r="AK9">
-        <v>38.05</v>
+        <v>33.63</v>
       </c>
     </row>
   </sheetData>
@@ -2001,7 +2001,7 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="4" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="B3" s="4" t="s">
         <v>56</v>
@@ -2053,13 +2053,13 @@
         <v>9</v>
       </c>
       <c r="C7" s="6">
-        <v>3.55</v>
+        <v>-1.37</v>
       </c>
       <c r="D7" s="6">
-        <v>-1.37</v>
+        <v>-3.87</v>
       </c>
       <c r="E7" s="7">
-        <v>-4.92</v>
+        <v>-2.5</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -2070,13 +2070,13 @@
         <v>9</v>
       </c>
       <c r="C8" s="6">
-        <v>-7.91</v>
+        <v>-8.949999999999999</v>
       </c>
       <c r="D8" s="6">
-        <v>-8.949999999999999</v>
+        <v>-9.44</v>
       </c>
       <c r="E8" s="7">
-        <v>-1.04</v>
+        <v>-0.49</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -2087,13 +2087,13 @@
         <v>9</v>
       </c>
       <c r="C9" s="6">
-        <v>-1.86</v>
+        <v>-4.06</v>
       </c>
       <c r="D9" s="6">
-        <v>-4.06</v>
+        <v>-5.44</v>
       </c>
       <c r="E9" s="7">
-        <v>-2.2</v>
+        <v>-1.38</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -2104,13 +2104,13 @@
         <v>9</v>
       </c>
       <c r="C10" s="6">
-        <v>-5.05</v>
+        <v>-4.72</v>
       </c>
       <c r="D10" s="6">
-        <v>-4.72</v>
-      </c>
-      <c r="E10" s="8">
-        <v>0.33</v>
+        <v>-5.9</v>
+      </c>
+      <c r="E10" s="7">
+        <v>-1.18</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -2121,13 +2121,13 @@
         <v>9</v>
       </c>
       <c r="C11" s="6">
-        <v>-1.07</v>
+        <v>-1.35</v>
       </c>
       <c r="D11" s="6">
-        <v>-1.35</v>
-      </c>
-      <c r="E11" s="7">
-        <v>-0.28</v>
+        <v>2.37</v>
+      </c>
+      <c r="E11" s="8">
+        <v>3.72</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -2138,13 +2138,13 @@
         <v>9</v>
       </c>
       <c r="C12" s="6">
-        <v>1.88</v>
+        <v>-0.17</v>
       </c>
       <c r="D12" s="6">
-        <v>-0.17</v>
+        <v>-1.3</v>
       </c>
       <c r="E12" s="7">
-        <v>-2.05</v>
+        <v>-1.13</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -2155,13 +2155,13 @@
         <v>9</v>
       </c>
       <c r="C13" s="6">
-        <v>-5.24</v>
+        <v>-6.55</v>
       </c>
       <c r="D13" s="6">
-        <v>-6.55</v>
+        <v>-8</v>
       </c>
       <c r="E13" s="7">
-        <v>-1.31</v>
+        <v>-1.45</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -2172,13 +2172,13 @@
         <v>9</v>
       </c>
       <c r="C14" s="6">
-        <v>-3.81</v>
+        <v>-4.1</v>
       </c>
       <c r="D14" s="6">
-        <v>-4.1</v>
+        <v>-4.93</v>
       </c>
       <c r="E14" s="7">
-        <v>-0.29</v>
+        <v>-0.83</v>
       </c>
     </row>
     <row r="15" spans="1:6">
@@ -2189,13 +2189,13 @@
         <v>8</v>
       </c>
       <c r="C15" s="6">
-        <v>2.51</v>
+        <v>2.13</v>
       </c>
       <c r="D15" s="6">
-        <v>2.13</v>
-      </c>
-      <c r="E15" s="7">
-        <v>-0.38</v>
+        <v>4.8</v>
+      </c>
+      <c r="E15" s="8">
+        <v>2.67</v>
       </c>
     </row>
     <row r="16" spans="1:6">
@@ -2206,13 +2206,13 @@
         <v>8</v>
       </c>
       <c r="C16" s="6">
-        <v>-1.43</v>
+        <v>-1.17</v>
       </c>
       <c r="D16" s="6">
-        <v>-1.17</v>
+        <v>0.41</v>
       </c>
       <c r="E16" s="8">
-        <v>0.26</v>
+        <v>1.58</v>
       </c>
     </row>
     <row r="17" spans="1:5">
@@ -2223,13 +2223,13 @@
         <v>8</v>
       </c>
       <c r="C17" s="6">
-        <v>-3.31</v>
+        <v>-3.53</v>
       </c>
       <c r="D17" s="6">
-        <v>-3.53</v>
-      </c>
-      <c r="E17" s="7">
-        <v>-0.22</v>
+        <v>-1.35</v>
+      </c>
+      <c r="E17" s="8">
+        <v>2.18</v>
       </c>
     </row>
     <row r="18" spans="1:5">
@@ -2240,13 +2240,13 @@
         <v>8</v>
       </c>
       <c r="C18" s="6">
-        <v>-2.71</v>
+        <v>-0.03</v>
       </c>
       <c r="D18" s="6">
-        <v>-0.03</v>
+        <v>1.49</v>
       </c>
       <c r="E18" s="8">
-        <v>2.68</v>
+        <v>1.52</v>
       </c>
     </row>
     <row r="19" spans="1:5">
@@ -2257,13 +2257,13 @@
         <v>8</v>
       </c>
       <c r="C19" s="6">
-        <v>-6.58</v>
+        <v>-7.55</v>
       </c>
       <c r="D19" s="6">
-        <v>-7.55</v>
-      </c>
-      <c r="E19" s="7">
-        <v>-0.97</v>
+        <v>-1.25</v>
+      </c>
+      <c r="E19" s="8">
+        <v>6.3</v>
       </c>
     </row>
     <row r="20" spans="1:5">
@@ -2274,13 +2274,13 @@
         <v>8</v>
       </c>
       <c r="C20" s="6">
-        <v>1.36</v>
+        <v>-2.91</v>
       </c>
       <c r="D20" s="6">
-        <v>-2.91</v>
+        <v>-9.92</v>
       </c>
       <c r="E20" s="7">
-        <v>-4.27</v>
+        <v>-7.01</v>
       </c>
     </row>
     <row r="21" spans="1:5">
@@ -2291,13 +2291,13 @@
         <v>8</v>
       </c>
       <c r="C21" s="6">
-        <v>-3.99</v>
+        <v>-3.92</v>
       </c>
       <c r="D21" s="6">
-        <v>-3.92</v>
+        <v>-1.8</v>
       </c>
       <c r="E21" s="8">
-        <v>0.07000000000000001</v>
+        <v>2.12</v>
       </c>
     </row>
     <row r="22" spans="1:5">
@@ -2308,13 +2308,13 @@
         <v>8</v>
       </c>
       <c r="C22" s="6">
-        <v>0.32</v>
+        <v>0.91</v>
       </c>
       <c r="D22" s="6">
-        <v>0.91</v>
+        <v>2.83</v>
       </c>
       <c r="E22" s="8">
-        <v>0.59</v>
+        <v>1.92</v>
       </c>
     </row>
     <row r="23" spans="1:5">
@@ -2325,13 +2325,13 @@
         <v>11</v>
       </c>
       <c r="C23" s="6">
-        <v>41.06</v>
+        <v>39.13</v>
       </c>
       <c r="D23" s="6">
-        <v>39.13</v>
-      </c>
-      <c r="E23" s="7">
-        <v>-1.93</v>
+        <v>39.81</v>
+      </c>
+      <c r="E23" s="8">
+        <v>0.68</v>
       </c>
     </row>
     <row r="24" spans="1:5">
@@ -2342,13 +2342,13 @@
         <v>11</v>
       </c>
       <c r="C24" s="6">
-        <v>-42.57</v>
+        <v>-42.49</v>
       </c>
       <c r="D24" s="6">
-        <v>-42.49</v>
-      </c>
-      <c r="E24" s="8">
-        <v>0.08</v>
+        <v>-45.41</v>
+      </c>
+      <c r="E24" s="7">
+        <v>-2.92</v>
       </c>
     </row>
     <row r="25" spans="1:5">
@@ -2359,13 +2359,13 @@
         <v>11</v>
       </c>
       <c r="C25" s="6">
-        <v>14.52</v>
+        <v>11.36</v>
       </c>
       <c r="D25" s="6">
-        <v>11.36</v>
+        <v>9.17</v>
       </c>
       <c r="E25" s="7">
-        <v>-3.16</v>
+        <v>-2.19</v>
       </c>
     </row>
     <row r="26" spans="1:5">
@@ -2376,13 +2376,13 @@
         <v>11</v>
       </c>
       <c r="C26" s="6">
-        <v>30.9</v>
+        <v>29.8</v>
       </c>
       <c r="D26" s="6">
-        <v>29.8</v>
+        <v>29.72</v>
       </c>
       <c r="E26" s="7">
-        <v>-1.1</v>
+        <v>-0.08</v>
       </c>
     </row>
     <row r="27" spans="1:5">
@@ -2393,13 +2393,13 @@
         <v>11</v>
       </c>
       <c r="C27" s="6">
-        <v>71.01000000000001</v>
+        <v>74.31</v>
       </c>
       <c r="D27" s="6">
-        <v>74.31</v>
+        <v>83.66</v>
       </c>
       <c r="E27" s="8">
-        <v>3.3</v>
+        <v>9.35</v>
       </c>
     </row>
     <row r="28" spans="1:5">
@@ -2410,13 +2410,13 @@
         <v>11</v>
       </c>
       <c r="C28" s="6">
-        <v>129.62</v>
+        <v>113.55</v>
       </c>
       <c r="D28" s="6">
-        <v>113.55</v>
+        <v>98.08</v>
       </c>
       <c r="E28" s="7">
-        <v>-16.07</v>
+        <v>-15.47</v>
       </c>
     </row>
     <row r="29" spans="1:5">
@@ -2427,13 +2427,13 @@
         <v>11</v>
       </c>
       <c r="C29" s="6">
-        <v>-22.43</v>
+        <v>-23.54</v>
       </c>
       <c r="D29" s="6">
-        <v>-23.54</v>
+        <v>-23.96</v>
       </c>
       <c r="E29" s="7">
-        <v>-1.11</v>
+        <v>-0.42</v>
       </c>
     </row>
     <row r="30" spans="1:5">
@@ -2444,13 +2444,13 @@
         <v>11</v>
       </c>
       <c r="C30" s="6">
-        <v>-11.43</v>
+        <v>-11.75</v>
       </c>
       <c r="D30" s="6">
-        <v>-11.75</v>
+        <v>-13.53</v>
       </c>
       <c r="E30" s="7">
-        <v>-0.32</v>
+        <v>-1.78</v>
       </c>
     </row>
     <row r="31" spans="1:5">
@@ -2461,13 +2461,13 @@
         <v>10</v>
       </c>
       <c r="C31" s="6">
-        <v>9.08</v>
+        <v>2.92</v>
       </c>
       <c r="D31" s="6">
-        <v>2.92</v>
-      </c>
-      <c r="E31" s="7">
-        <v>-6.16</v>
+        <v>3.45</v>
+      </c>
+      <c r="E31" s="8">
+        <v>0.53</v>
       </c>
     </row>
     <row r="32" spans="1:5">
@@ -2478,13 +2478,13 @@
         <v>10</v>
       </c>
       <c r="C32" s="6">
-        <v>-17.28</v>
+        <v>-17.9</v>
       </c>
       <c r="D32" s="6">
-        <v>-17.9</v>
-      </c>
-      <c r="E32" s="7">
-        <v>-0.62</v>
+        <v>-17.32</v>
+      </c>
+      <c r="E32" s="8">
+        <v>0.58</v>
       </c>
     </row>
     <row r="33" spans="1:5">
@@ -2495,13 +2495,13 @@
         <v>10</v>
       </c>
       <c r="C33" s="6">
-        <v>1.9</v>
+        <v>-0.29</v>
       </c>
       <c r="D33" s="6">
-        <v>-0.29</v>
+        <v>-0.51</v>
       </c>
       <c r="E33" s="7">
-        <v>-2.19</v>
+        <v>-0.22</v>
       </c>
     </row>
     <row r="34" spans="1:5">
@@ -2512,13 +2512,13 @@
         <v>10</v>
       </c>
       <c r="C34" s="6">
-        <v>-2.33</v>
+        <v>-3.25</v>
       </c>
       <c r="D34" s="6">
-        <v>-3.25</v>
-      </c>
-      <c r="E34" s="7">
-        <v>-0.92</v>
+        <v>-1.4</v>
+      </c>
+      <c r="E34" s="8">
+        <v>1.85</v>
       </c>
     </row>
     <row r="35" spans="1:5">
@@ -2529,13 +2529,13 @@
         <v>10</v>
       </c>
       <c r="C35" s="6">
-        <v>-6.7</v>
+        <v>-6.61</v>
       </c>
       <c r="D35" s="6">
-        <v>-6.61</v>
+        <v>-1.25</v>
       </c>
       <c r="E35" s="8">
-        <v>0.09</v>
+        <v>5.36</v>
       </c>
     </row>
     <row r="36" spans="1:5">
@@ -2546,13 +2546,13 @@
         <v>10</v>
       </c>
       <c r="C36" s="6">
-        <v>-0.91</v>
+        <v>-1.27</v>
       </c>
       <c r="D36" s="6">
-        <v>-1.27</v>
+        <v>-1.99</v>
       </c>
       <c r="E36" s="7">
-        <v>-0.36</v>
+        <v>-0.72</v>
       </c>
     </row>
     <row r="37" spans="1:5">
@@ -2563,13 +2563,13 @@
         <v>10</v>
       </c>
       <c r="C37" s="6">
-        <v>-8.08</v>
+        <v>-9.17</v>
       </c>
       <c r="D37" s="6">
-        <v>-9.17</v>
-      </c>
-      <c r="E37" s="7">
-        <v>-1.09</v>
+        <v>-7.56</v>
+      </c>
+      <c r="E37" s="8">
+        <v>1.61</v>
       </c>
     </row>
     <row r="38" spans="1:5">
@@ -2580,13 +2580,13 @@
         <v>10</v>
       </c>
       <c r="C38" s="6">
-        <v>-3.11</v>
+        <v>-2.65</v>
       </c>
       <c r="D38" s="6">
-        <v>-2.65</v>
-      </c>
-      <c r="E38" s="8">
-        <v>0.46</v>
+        <v>-2.72</v>
+      </c>
+      <c r="E38" s="7">
+        <v>-0.07000000000000001</v>
       </c>
     </row>
     <row r="39" spans="1:5">
@@ -2597,13 +2597,13 @@
         <v>6</v>
       </c>
       <c r="C39" s="6">
-        <v>-3.45</v>
+        <v>-5.02</v>
       </c>
       <c r="D39" s="6">
-        <v>-5.02</v>
+        <v>-6.52</v>
       </c>
       <c r="E39" s="7">
-        <v>-1.57</v>
+        <v>-1.5</v>
       </c>
     </row>
     <row r="40" spans="1:5">
@@ -2614,13 +2614,13 @@
         <v>6</v>
       </c>
       <c r="C40" s="6">
-        <v>-46.34</v>
+        <v>-46.67</v>
       </c>
       <c r="D40" s="6">
-        <v>-46.67</v>
+        <v>-47.35</v>
       </c>
       <c r="E40" s="7">
-        <v>-0.33</v>
+        <v>-0.68</v>
       </c>
     </row>
     <row r="41" spans="1:5">
@@ -2631,13 +2631,13 @@
         <v>6</v>
       </c>
       <c r="C41" s="6">
-        <v>-5.07</v>
+        <v>-6.35</v>
       </c>
       <c r="D41" s="6">
-        <v>-6.35</v>
+        <v>-7.46</v>
       </c>
       <c r="E41" s="7">
-        <v>-1.28</v>
+        <v>-1.11</v>
       </c>
     </row>
     <row r="42" spans="1:5">
@@ -2648,13 +2648,13 @@
         <v>6</v>
       </c>
       <c r="C42" s="6">
-        <v>-14.2</v>
+        <v>-14.66</v>
       </c>
       <c r="D42" s="6">
-        <v>-14.66</v>
+        <v>-15.37</v>
       </c>
       <c r="E42" s="7">
-        <v>-0.46</v>
+        <v>-0.71</v>
       </c>
     </row>
     <row r="43" spans="1:5">
@@ -2665,13 +2665,13 @@
         <v>6</v>
       </c>
       <c r="C43" s="6">
-        <v>-10.77</v>
+        <v>-11.28</v>
       </c>
       <c r="D43" s="6">
-        <v>-11.28</v>
-      </c>
-      <c r="E43" s="7">
-        <v>-0.51</v>
+        <v>-8.529999999999999</v>
+      </c>
+      <c r="E43" s="8">
+        <v>2.75</v>
       </c>
     </row>
     <row r="44" spans="1:5">
@@ -2682,13 +2682,13 @@
         <v>6</v>
       </c>
       <c r="C44" s="6">
-        <v>-14.22</v>
+        <v>-16.24</v>
       </c>
       <c r="D44" s="6">
-        <v>-16.24</v>
+        <v>-18.46</v>
       </c>
       <c r="E44" s="7">
-        <v>-2.02</v>
+        <v>-2.22</v>
       </c>
     </row>
     <row r="45" spans="1:5">
@@ -2699,13 +2699,13 @@
         <v>6</v>
       </c>
       <c r="C45" s="6">
-        <v>-29.99</v>
+        <v>-30.68</v>
       </c>
       <c r="D45" s="6">
-        <v>-30.68</v>
+        <v>-31</v>
       </c>
       <c r="E45" s="7">
-        <v>-0.6899999999999999</v>
+        <v>-0.32</v>
       </c>
     </row>
     <row r="46" spans="1:5">
@@ -2716,13 +2716,13 @@
         <v>6</v>
       </c>
       <c r="C46" s="6">
-        <v>-15.61</v>
+        <v>-14.96</v>
       </c>
       <c r="D46" s="6">
-        <v>-14.96</v>
-      </c>
-      <c r="E46" s="8">
-        <v>0.65</v>
+        <v>-15.72</v>
+      </c>
+      <c r="E46" s="7">
+        <v>-0.76</v>
       </c>
     </row>
     <row r="47" spans="1:5">
@@ -2733,13 +2733,13 @@
         <v>2</v>
       </c>
       <c r="C47" s="6">
-        <v>410.05</v>
+        <v>403.4</v>
       </c>
       <c r="D47" s="6">
-        <v>403.4</v>
+        <v>397</v>
       </c>
       <c r="E47" s="7">
-        <v>-6.65</v>
+        <v>-6.4</v>
       </c>
     </row>
     <row r="48" spans="1:5">
@@ -2750,13 +2750,13 @@
         <v>2</v>
       </c>
       <c r="C48" s="6">
-        <v>50.16</v>
+        <v>49.85</v>
       </c>
       <c r="D48" s="6">
-        <v>49.85</v>
+        <v>49.22</v>
       </c>
       <c r="E48" s="7">
-        <v>-0.31</v>
+        <v>-0.63</v>
       </c>
     </row>
     <row r="49" spans="1:5">
@@ -2767,13 +2767,13 @@
         <v>2</v>
       </c>
       <c r="C49" s="6">
-        <v>3209.2</v>
+        <v>3166</v>
       </c>
       <c r="D49" s="6">
-        <v>3166</v>
+        <v>3128.2</v>
       </c>
       <c r="E49" s="7">
-        <v>-43.2</v>
+        <v>-37.8</v>
       </c>
     </row>
     <row r="50" spans="1:5">
@@ -2784,13 +2784,13 @@
         <v>2</v>
       </c>
       <c r="C50" s="6">
-        <v>986.5</v>
+        <v>981.2</v>
       </c>
       <c r="D50" s="6">
-        <v>981.2</v>
+        <v>973</v>
       </c>
       <c r="E50" s="7">
-        <v>-5.3</v>
+        <v>-8.199999999999999</v>
       </c>
     </row>
     <row r="51" spans="1:5">
@@ -2801,13 +2801,13 @@
         <v>2</v>
       </c>
       <c r="C51" s="6">
-        <v>13.92</v>
+        <v>13.84</v>
       </c>
       <c r="D51" s="6">
-        <v>13.84</v>
-      </c>
-      <c r="E51" s="7">
-        <v>-0.08</v>
+        <v>14.27</v>
+      </c>
+      <c r="E51" s="8">
+        <v>0.43</v>
       </c>
     </row>
     <row r="52" spans="1:5">
@@ -2818,13 +2818,13 @@
         <v>2</v>
       </c>
       <c r="C52" s="6">
-        <v>11.94</v>
+        <v>11.66</v>
       </c>
       <c r="D52" s="6">
-        <v>11.66</v>
+        <v>11.35</v>
       </c>
       <c r="E52" s="7">
-        <v>-0.28</v>
+        <v>-0.31</v>
       </c>
     </row>
     <row r="53" spans="1:5">
@@ -2835,13 +2835,13 @@
         <v>2</v>
       </c>
       <c r="C53" s="6">
-        <v>4067</v>
+        <v>4027.1</v>
       </c>
       <c r="D53" s="6">
-        <v>4027.1</v>
+        <v>4008.3</v>
       </c>
       <c r="E53" s="7">
-        <v>-39.9</v>
+        <v>-18.8</v>
       </c>
     </row>
     <row r="54" spans="1:5">
@@ -2852,13 +2852,13 @@
         <v>2</v>
       </c>
       <c r="C54" s="6">
-        <v>11014</v>
+        <v>11100</v>
       </c>
       <c r="D54" s="6">
-        <v>11100</v>
-      </c>
-      <c r="E54" s="8">
-        <v>86</v>
+        <v>11000</v>
+      </c>
+      <c r="E54" s="7">
+        <v>-100</v>
       </c>
     </row>
     <row r="55" spans="1:5">
@@ -2869,13 +2869,13 @@
         <v>24</v>
       </c>
       <c r="C55" s="6">
-        <v>56.32</v>
+        <v>52.13</v>
       </c>
       <c r="D55" s="6">
-        <v>52.13</v>
+        <v>48.4</v>
       </c>
       <c r="E55" s="7">
-        <v>-4.19</v>
+        <v>-3.73</v>
       </c>
     </row>
     <row r="56" spans="1:5">
@@ -2886,13 +2886,13 @@
         <v>24</v>
       </c>
       <c r="C56" s="6">
-        <v>36.41</v>
+        <v>35.32</v>
       </c>
       <c r="D56" s="6">
-        <v>35.32</v>
+        <v>33.15</v>
       </c>
       <c r="E56" s="7">
-        <v>-1.09</v>
+        <v>-2.17</v>
       </c>
     </row>
     <row r="57" spans="1:5">
@@ -2903,13 +2903,13 @@
         <v>24</v>
       </c>
       <c r="C57" s="6">
-        <v>44.41</v>
+        <v>40.12</v>
       </c>
       <c r="D57" s="6">
-        <v>40.12</v>
+        <v>36.78</v>
       </c>
       <c r="E57" s="7">
-        <v>-4.29</v>
+        <v>-3.34</v>
       </c>
     </row>
     <row r="58" spans="1:5">
@@ -2920,13 +2920,13 @@
         <v>24</v>
       </c>
       <c r="C58" s="6">
-        <v>43.87</v>
+        <v>42.47</v>
       </c>
       <c r="D58" s="6">
-        <v>42.47</v>
+        <v>40.32</v>
       </c>
       <c r="E58" s="7">
-        <v>-1.4</v>
+        <v>-2.15</v>
       </c>
     </row>
     <row r="59" spans="1:5">
@@ -2937,13 +2937,13 @@
         <v>24</v>
       </c>
       <c r="C59" s="6">
-        <v>43.25</v>
+        <v>42.3</v>
       </c>
       <c r="D59" s="6">
-        <v>42.3</v>
-      </c>
-      <c r="E59" s="7">
-        <v>-0.95</v>
+        <v>48.83</v>
+      </c>
+      <c r="E59" s="8">
+        <v>6.53</v>
       </c>
     </row>
     <row r="60" spans="1:5">
@@ -2954,13 +2954,13 @@
         <v>24</v>
       </c>
       <c r="C60" s="6">
-        <v>53.63</v>
+        <v>48.93</v>
       </c>
       <c r="D60" s="6">
-        <v>48.93</v>
+        <v>44.3</v>
       </c>
       <c r="E60" s="7">
-        <v>-4.7</v>
+        <v>-4.63</v>
       </c>
     </row>
     <row r="61" spans="1:5">
@@ -2971,13 +2971,13 @@
         <v>24</v>
       </c>
       <c r="C61" s="6">
-        <v>34.92</v>
+        <v>32.85</v>
       </c>
       <c r="D61" s="6">
-        <v>32.85</v>
+        <v>31.88</v>
       </c>
       <c r="E61" s="7">
-        <v>-2.07</v>
+        <v>-0.97</v>
       </c>
     </row>
     <row r="62" spans="1:5">
@@ -2988,13 +2988,13 @@
         <v>24</v>
       </c>
       <c r="C62" s="6">
-        <v>41.61</v>
+        <v>44.84</v>
       </c>
       <c r="D62" s="6">
-        <v>44.84</v>
-      </c>
-      <c r="E62" s="8">
-        <v>3.23</v>
+        <v>41.94</v>
+      </c>
+      <c r="E62" s="7">
+        <v>-2.9</v>
       </c>
     </row>
     <row r="63" spans="1:5">
@@ -3005,13 +3005,13 @@
         <v>31</v>
       </c>
       <c r="C63" s="6">
-        <v>72.67</v>
+        <v>-44.44</v>
       </c>
       <c r="D63" s="6">
-        <v>-44.44</v>
-      </c>
-      <c r="E63" s="7">
-        <v>-117.11</v>
+        <v>-11.32</v>
+      </c>
+      <c r="E63" s="8">
+        <v>33.12</v>
       </c>
     </row>
     <row r="64" spans="1:5">
@@ -3022,13 +3022,13 @@
         <v>31</v>
       </c>
       <c r="C64" s="6">
-        <v>-26.41</v>
+        <v>-46.79</v>
       </c>
       <c r="D64" s="6">
-        <v>-46.79</v>
-      </c>
-      <c r="E64" s="7">
-        <v>-20.38</v>
+        <v>-38.35</v>
+      </c>
+      <c r="E64" s="8">
+        <v>8.44</v>
       </c>
     </row>
     <row r="65" spans="1:5">
@@ -3039,13 +3039,13 @@
         <v>31</v>
       </c>
       <c r="C65" s="6">
-        <v>-37.8</v>
+        <v>-82.73999999999999</v>
       </c>
       <c r="D65" s="6">
-        <v>-82.73999999999999</v>
-      </c>
-      <c r="E65" s="7">
-        <v>-44.94</v>
+        <v>-33.13</v>
+      </c>
+      <c r="E65" s="8">
+        <v>49.61</v>
       </c>
     </row>
     <row r="66" spans="1:5">
@@ -3056,13 +3056,13 @@
         <v>31</v>
       </c>
       <c r="C66" s="6">
-        <v>175.47</v>
+        <v>1.12</v>
       </c>
       <c r="D66" s="6">
-        <v>1.12</v>
-      </c>
-      <c r="E66" s="7">
-        <v>-174.35</v>
+        <v>2.18</v>
+      </c>
+      <c r="E66" s="8">
+        <v>1.06</v>
       </c>
     </row>
     <row r="67" spans="1:5">
@@ -3073,13 +3073,13 @@
         <v>31</v>
       </c>
       <c r="C67" s="6">
-        <v>-24.86</v>
+        <v>-35.68</v>
       </c>
       <c r="D67" s="6">
-        <v>-35.68</v>
-      </c>
-      <c r="E67" s="7">
-        <v>-10.82</v>
+        <v>12.88</v>
+      </c>
+      <c r="E67" s="8">
+        <v>48.56</v>
       </c>
     </row>
     <row r="68" spans="1:5">
@@ -3090,13 +3090,13 @@
         <v>31</v>
       </c>
       <c r="C68" s="6">
-        <v>16.47</v>
+        <v>6.56</v>
       </c>
       <c r="D68" s="6">
-        <v>6.56</v>
+        <v>-4.79</v>
       </c>
       <c r="E68" s="7">
-        <v>-9.91</v>
+        <v>-11.35</v>
       </c>
     </row>
     <row r="69" spans="1:5">
@@ -3107,13 +3107,13 @@
         <v>31</v>
       </c>
       <c r="C69" s="6">
-        <v>-42.23</v>
+        <v>89.36</v>
       </c>
       <c r="D69" s="6">
-        <v>89.36</v>
-      </c>
-      <c r="E69" s="8">
-        <v>131.59</v>
+        <v>-37.81</v>
+      </c>
+      <c r="E69" s="7">
+        <v>-127.17</v>
       </c>
     </row>
     <row r="70" spans="1:5">
@@ -3124,13 +3124,13 @@
         <v>31</v>
       </c>
       <c r="C70" s="6">
-        <v>81.31</v>
+        <v>-42.09</v>
       </c>
       <c r="D70" s="6">
-        <v>-42.09</v>
-      </c>
-      <c r="E70" s="7">
-        <v>-123.4</v>
+        <v>23.29</v>
+      </c>
+      <c r="E70" s="8">
+        <v>65.38</v>
       </c>
     </row>
   </sheetData>
@@ -3189,22 +3189,22 @@
         <v>45</v>
       </c>
       <c r="B2" s="11">
-        <v>56.44</v>
+        <v>52.44</v>
       </c>
       <c r="C2" s="12">
         <v>8</v>
       </c>
       <c r="D2" s="11">
-        <v>42.4</v>
+        <v>40.7</v>
       </c>
       <c r="E2" s="11">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="F2" s="11">
-        <v>-3.9</v>
+        <v>-4.6</v>
       </c>
       <c r="G2" s="11">
-        <v>-4.8</v>
+        <v>-3.7</v>
       </c>
       <c r="H2" s="11">
         <v>56.1</v>
@@ -3315,10 +3315,10 @@
         <v>37</v>
       </c>
       <c r="B1" s="13" t="s">
+        <v>43</v>
+      </c>
+      <c r="C1" s="13" t="s">
         <v>40</v>
-      </c>
-      <c r="C1" s="13" t="s">
-        <v>43</v>
       </c>
       <c r="D1" s="13" t="s">
         <v>39</v>
@@ -3338,28 +3338,28 @@
     </row>
     <row r="2" spans="1:8">
       <c r="A2" s="14">
-        <v>0.301</v>
+        <v>0.2928</v>
       </c>
       <c r="B2" s="14">
-        <v>0.1749</v>
+        <v>0.1696</v>
       </c>
       <c r="C2" s="14">
-        <v>0.1701</v>
+        <v>0.1668</v>
       </c>
       <c r="D2" s="14">
-        <v>0.1579</v>
+        <v>0.1525</v>
       </c>
       <c r="E2" s="14">
-        <v>0.08380000000000001</v>
+        <v>0.0809</v>
       </c>
       <c r="F2" s="14">
-        <v>0.0509</v>
+        <v>0.0653</v>
       </c>
       <c r="G2" s="14">
-        <v>-0.2438</v>
+        <v>-0.2551</v>
       </c>
       <c r="H2" s="14">
-        <v>-0.308</v>
+        <v>-0.3102</v>
       </c>
     </row>
   </sheetData>

--- a/BIRLA_GROUP_Technical_Metrics.xlsx
+++ b/BIRLA_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="287" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="299" uniqueCount="80">
   <si>
     <t>Symbol</t>
   </si>
@@ -193,16 +193,34 @@
     <t>RSI Momentum</t>
   </si>
   <si>
-    <t>52.1 → 48.4</t>
-  </si>
-  <si>
-    <t>🔴 BEARISH</t>
-  </si>
-  <si>
-    <t>52.1</t>
+    <t>48.4 → 51.6</t>
+  </si>
+  <si>
+    <t>🟢 BULLISH</t>
   </si>
   <si>
     <t>48.4</t>
+  </si>
+  <si>
+    <t>51.6</t>
+  </si>
+  <si>
+    <t>40.3 → 50.5</t>
+  </si>
+  <si>
+    <t>40.3</t>
+  </si>
+  <si>
+    <t>50.5</t>
+  </si>
+  <si>
+    <t>48.8 → 52.2</t>
+  </si>
+  <si>
+    <t>48.8</t>
+  </si>
+  <si>
+    <t>52.2</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -288,14 +306,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF006100"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF9C0006"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -328,13 +346,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -786,8 +804,9 @@
     <col min="13" max="13" width="10.7109375" customWidth="1"/>
     <col min="14" max="14" width="11.7109375" customWidth="1"/>
     <col min="15" max="15" width="10.7109375" customWidth="1"/>
-    <col min="16" max="16" width="9.7109375" customWidth="1"/>
-    <col min="17" max="19" width="10.7109375" customWidth="1"/>
+    <col min="16" max="17" width="9.7109375" customWidth="1"/>
+    <col min="18" max="18" width="10.7109375" customWidth="1"/>
+    <col min="19" max="19" width="9.7109375" customWidth="1"/>
     <col min="20" max="20" width="22.7109375" customWidth="1"/>
     <col min="21" max="21" width="9.7109375" customWidth="1"/>
     <col min="22" max="22" width="10.7109375" customWidth="1"/>
@@ -927,10 +946,10 @@
         <v>45</v>
       </c>
       <c r="C2">
-        <v>397</v>
+        <v>402.45</v>
       </c>
       <c r="D2">
-        <v>-1.59</v>
+        <v>1.37</v>
       </c>
       <c r="E2">
         <v>424.7</v>
@@ -939,46 +958,46 @@
         <v>278.9</v>
       </c>
       <c r="G2">
-        <v>-6.52</v>
+        <v>-5.24</v>
       </c>
       <c r="H2">
-        <v>42.34</v>
+        <v>44.3</v>
       </c>
       <c r="I2">
-        <v>4.8</v>
+        <v>5.55</v>
       </c>
       <c r="J2">
-        <v>-3.87</v>
+        <v>-2.53</v>
       </c>
       <c r="K2">
-        <v>3.45</v>
+        <v>1.94</v>
       </c>
       <c r="L2">
-        <v>39.81</v>
+        <v>38.35</v>
       </c>
       <c r="M2">
-        <v>29.28</v>
+        <v>28.9</v>
       </c>
       <c r="N2">
         <v>74</v>
       </c>
       <c r="O2">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="P2">
-        <v>396.35</v>
+        <v>400.58</v>
       </c>
       <c r="Q2">
-        <v>400</v>
+        <v>399.58</v>
       </c>
       <c r="R2">
-        <v>403.08</v>
+        <v>403.15</v>
       </c>
       <c r="S2">
-        <v>363.59</v>
+        <v>363.85</v>
       </c>
       <c r="T2">
-        <v>9.19</v>
+        <v>10.61</v>
       </c>
       <c r="U2" t="s">
         <v>46</v>
@@ -993,34 +1012,34 @@
         <v>2</v>
       </c>
       <c r="Y2">
-        <v>48.4</v>
+        <v>51.58</v>
       </c>
       <c r="Z2">
-        <v>-1.94</v>
+        <v>-1.41</v>
       </c>
       <c r="AA2">
-        <v>-2.12</v>
+        <v>-1.98</v>
       </c>
       <c r="AB2">
-        <v>0.18</v>
+        <v>0.57</v>
       </c>
       <c r="AC2">
-        <v>82.05</v>
+        <v>75.02</v>
       </c>
       <c r="AD2">
-        <v>71.20999999999999</v>
+        <v>78.16</v>
       </c>
       <c r="AE2">
-        <v>10.11</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AF2">
-        <v>-11.32</v>
+        <v>-25.14</v>
       </c>
       <c r="AG2">
-        <v>418.18</v>
+        <v>417.08</v>
       </c>
       <c r="AH2">
-        <v>381.82</v>
+        <v>382.08</v>
       </c>
       <c r="AI2">
         <v>372.91</v>
@@ -1029,7 +1048,7 @@
         <v>48</v>
       </c>
       <c r="AK2">
-        <v>26.56</v>
+        <v>23.68</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1040,10 +1059,10 @@
         <v>45</v>
       </c>
       <c r="C3">
-        <v>49.22</v>
+        <v>49.09</v>
       </c>
       <c r="D3">
-        <v>-1.26</v>
+        <v>-0.26</v>
       </c>
       <c r="E3">
         <v>93.48</v>
@@ -1052,46 +1071,46 @@
         <v>49.02</v>
       </c>
       <c r="G3">
-        <v>-47.35</v>
+        <v>-47.49</v>
       </c>
       <c r="H3">
-        <v>0.41</v>
+        <v>0.14</v>
       </c>
       <c r="I3">
-        <v>0.41</v>
+        <v>-1.31</v>
       </c>
       <c r="J3">
-        <v>-9.44</v>
+        <v>-9.01</v>
       </c>
       <c r="K3">
-        <v>-17.32</v>
+        <v>-20.31</v>
       </c>
       <c r="L3">
-        <v>-45.41</v>
+        <v>-45.38</v>
       </c>
       <c r="M3">
-        <v>-25.51</v>
+        <v>-25.83</v>
       </c>
       <c r="N3">
         <v>13</v>
       </c>
       <c r="O3">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="P3">
-        <v>49.88</v>
+        <v>49.75</v>
       </c>
       <c r="Q3">
-        <v>51.44</v>
+        <v>51.17</v>
       </c>
       <c r="R3">
-        <v>55.37</v>
+        <v>55.17</v>
       </c>
       <c r="S3">
-        <v>63.28</v>
+        <v>63.14</v>
       </c>
       <c r="T3">
-        <v>-22.21</v>
+        <v>-22.25</v>
       </c>
       <c r="U3" t="s">
         <v>46</v>
@@ -1106,43 +1125,43 @@
         <v>0</v>
       </c>
       <c r="Y3">
-        <v>33.15</v>
+        <v>32.71</v>
       </c>
       <c r="Z3">
-        <v>-1.72</v>
+        <v>-1.71</v>
       </c>
       <c r="AA3">
-        <v>-1.75</v>
+        <v>-1.74</v>
       </c>
       <c r="AB3">
-        <v>0.04</v>
+        <v>0.03</v>
       </c>
       <c r="AC3">
-        <v>58.34</v>
+        <v>51.15</v>
       </c>
       <c r="AD3">
-        <v>62.51</v>
+        <v>58.7</v>
       </c>
       <c r="AE3">
-        <v>1.54</v>
+        <v>1.48</v>
       </c>
       <c r="AF3">
-        <v>-38.35</v>
+        <v>-38.57</v>
       </c>
       <c r="AG3">
-        <v>54.79</v>
+        <v>54.35</v>
       </c>
       <c r="AH3">
-        <v>48.08</v>
+        <v>47.98</v>
       </c>
       <c r="AI3">
-        <v>54.24</v>
+        <v>53.68</v>
       </c>
       <c r="AJ3" t="s">
         <v>49</v>
       </c>
       <c r="AK3">
-        <v>33.64</v>
+        <v>34.99</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1153,10 +1172,10 @@
         <v>45</v>
       </c>
       <c r="C4">
-        <v>3128.2</v>
+        <v>3188.5</v>
       </c>
       <c r="D4">
-        <v>-1.19</v>
+        <v>1.93</v>
       </c>
       <c r="E4">
         <v>3380.5</v>
@@ -1165,46 +1184,46 @@
         <v>2531.1</v>
       </c>
       <c r="G4">
-        <v>-7.46</v>
+        <v>-5.68</v>
       </c>
       <c r="H4">
-        <v>23.59</v>
+        <v>25.97</v>
       </c>
       <c r="I4">
-        <v>-1.35</v>
+        <v>0.05</v>
       </c>
       <c r="J4">
-        <v>-5.44</v>
+        <v>-3.03</v>
       </c>
       <c r="K4">
-        <v>-0.51</v>
+        <v>1.94</v>
       </c>
       <c r="L4">
-        <v>9.17</v>
+        <v>10.76</v>
       </c>
       <c r="M4">
-        <v>15.25</v>
+        <v>15.22</v>
       </c>
       <c r="N4">
         <v>50</v>
       </c>
       <c r="O4">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="P4">
-        <v>3172.7</v>
+        <v>3173</v>
       </c>
       <c r="Q4">
-        <v>3264.25</v>
+        <v>3259.19</v>
       </c>
       <c r="R4">
-        <v>3225.66</v>
+        <v>3227.16</v>
       </c>
       <c r="S4">
-        <v>2964.48</v>
+        <v>2966.77</v>
       </c>
       <c r="T4">
-        <v>5.52</v>
+        <v>7.47</v>
       </c>
       <c r="U4" t="s">
         <v>47</v>
@@ -1219,34 +1238,34 @@
         <v>3</v>
       </c>
       <c r="Y4">
-        <v>36.78</v>
+        <v>44.7</v>
       </c>
       <c r="Z4">
-        <v>-22.53</v>
+        <v>-23.13</v>
       </c>
       <c r="AA4">
-        <v>-1.09</v>
+        <v>-5.5</v>
       </c>
       <c r="AB4">
-        <v>-21.43</v>
+        <v>-17.63</v>
       </c>
       <c r="AC4">
-        <v>10.88</v>
+        <v>16.24</v>
       </c>
       <c r="AD4">
-        <v>11.66</v>
+        <v>13.06</v>
       </c>
       <c r="AE4">
-        <v>60</v>
+        <v>60.21</v>
       </c>
       <c r="AF4">
-        <v>-33.13</v>
+        <v>-58.83</v>
       </c>
       <c r="AG4">
-        <v>3397.28</v>
+        <v>3395.8</v>
       </c>
       <c r="AH4">
-        <v>3131.22</v>
+        <v>3122.59</v>
       </c>
       <c r="AI4">
         <v>3120.02</v>
@@ -1255,7 +1274,7 @@
         <v>48</v>
       </c>
       <c r="AK4">
-        <v>34.79</v>
+        <v>36.95</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1266,10 +1285,10 @@
         <v>45</v>
       </c>
       <c r="C5">
-        <v>973</v>
+        <v>1003.8</v>
       </c>
       <c r="D5">
-        <v>-0.84</v>
+        <v>3.17</v>
       </c>
       <c r="E5">
         <v>1149.7</v>
@@ -1278,46 +1297,46 @@
         <v>741.05</v>
       </c>
       <c r="G5">
-        <v>-15.37</v>
+        <v>-12.69</v>
       </c>
       <c r="H5">
-        <v>31.3</v>
+        <v>35.46</v>
       </c>
       <c r="I5">
-        <v>1.49</v>
+        <v>3.2</v>
       </c>
       <c r="J5">
-        <v>-5.9</v>
+        <v>-5.17</v>
       </c>
       <c r="K5">
-        <v>-1.4</v>
+        <v>2.79</v>
       </c>
       <c r="L5">
-        <v>29.72</v>
+        <v>33.81</v>
       </c>
       <c r="M5">
-        <v>16.68</v>
+        <v>16.41</v>
       </c>
       <c r="N5">
         <v>62</v>
       </c>
       <c r="O5">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="P5">
-        <v>978.78</v>
+        <v>985</v>
       </c>
       <c r="Q5">
-        <v>1005.8</v>
+        <v>1003.44</v>
       </c>
       <c r="R5">
-        <v>1002.76</v>
+        <v>1003.35</v>
       </c>
       <c r="S5">
-        <v>976.1900000000001</v>
+        <v>977.16</v>
       </c>
       <c r="T5">
-        <v>-0.33</v>
+        <v>2.73</v>
       </c>
       <c r="U5" t="s">
         <v>47</v>
@@ -1329,37 +1348,37 @@
         <v>47</v>
       </c>
       <c r="X5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Y5">
-        <v>40.32</v>
+        <v>50.46</v>
       </c>
       <c r="Z5">
-        <v>-11.64</v>
+        <v>-9.68</v>
       </c>
       <c r="AA5">
-        <v>-7.26</v>
+        <v>-7.75</v>
       </c>
       <c r="AB5">
-        <v>-4.38</v>
+        <v>-1.94</v>
       </c>
       <c r="AC5">
-        <v>43.67</v>
+        <v>55.67</v>
       </c>
       <c r="AD5">
-        <v>43.02</v>
+        <v>48.4</v>
       </c>
       <c r="AE5">
-        <v>22.25</v>
+        <v>22.86</v>
       </c>
       <c r="AF5">
-        <v>2.18</v>
+        <v>56.4</v>
       </c>
       <c r="AG5">
-        <v>1058.02</v>
+        <v>1051.12</v>
       </c>
       <c r="AH5">
-        <v>953.58</v>
+        <v>955.76</v>
       </c>
       <c r="AI5">
         <v>1037.86</v>
@@ -1368,7 +1387,7 @@
         <v>49</v>
       </c>
       <c r="AK5">
-        <v>25.28</v>
+        <v>22.01</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1379,37 +1398,37 @@
         <v>45</v>
       </c>
       <c r="C6">
-        <v>14.27</v>
+        <v>14.52</v>
       </c>
       <c r="D6">
-        <v>3.11</v>
+        <v>1.75</v>
       </c>
       <c r="E6">
         <v>15.6</v>
       </c>
       <c r="F6">
-        <v>7.84</v>
+        <v>8.02</v>
       </c>
       <c r="G6">
-        <v>-8.529999999999999</v>
+        <v>-6.92</v>
       </c>
       <c r="H6">
-        <v>82.02</v>
+        <v>81.05</v>
       </c>
       <c r="I6">
-        <v>-1.25</v>
+        <v>1.82</v>
       </c>
       <c r="J6">
-        <v>2.37</v>
+        <v>3.2</v>
       </c>
       <c r="K6">
-        <v>-1.25</v>
+        <v>1.47</v>
       </c>
       <c r="L6">
-        <v>83.66</v>
+        <v>85.2</v>
       </c>
       <c r="M6">
-        <v>6.53</v>
+        <v>6.6</v>
       </c>
       <c r="N6">
         <v>87</v>
@@ -1418,19 +1437,19 @@
         <v>90</v>
       </c>
       <c r="P6">
-        <v>14.1</v>
+        <v>14.15</v>
       </c>
       <c r="Q6">
-        <v>14.68</v>
+        <v>14.65</v>
       </c>
       <c r="R6">
-        <v>13.91</v>
+        <v>13.92</v>
       </c>
       <c r="S6">
-        <v>12.15</v>
+        <v>12.17</v>
       </c>
       <c r="T6">
-        <v>17.49</v>
+        <v>19.36</v>
       </c>
       <c r="U6" t="s">
         <v>47</v>
@@ -1445,34 +1464,34 @@
         <v>3</v>
       </c>
       <c r="Y6">
-        <v>48.83</v>
+        <v>52.22</v>
       </c>
       <c r="Z6">
         <v>0.05</v>
       </c>
       <c r="AA6">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="AB6">
-        <v>-0.15</v>
+        <v>-0.12</v>
       </c>
       <c r="AC6">
-        <v>8.390000000000001</v>
+        <v>21.14</v>
       </c>
       <c r="AD6">
-        <v>2.8</v>
+        <v>9.85</v>
       </c>
       <c r="AE6">
-        <v>0.49</v>
+        <v>0.48</v>
       </c>
       <c r="AF6">
-        <v>12.88</v>
+        <v>-43.76</v>
       </c>
       <c r="AG6">
-        <v>15.74</v>
+        <v>15.68</v>
       </c>
       <c r="AH6">
-        <v>13.63</v>
+        <v>13.62</v>
       </c>
       <c r="AI6">
         <v>15.41</v>
@@ -1481,7 +1500,7 @@
         <v>49</v>
       </c>
       <c r="AK6">
-        <v>29.04</v>
+        <v>25.64</v>
       </c>
     </row>
     <row r="7" spans="1:37">
@@ -1492,10 +1511,10 @@
         <v>45</v>
       </c>
       <c r="C7">
-        <v>11.35</v>
+        <v>11.57</v>
       </c>
       <c r="D7">
-        <v>-2.66</v>
+        <v>1.94</v>
       </c>
       <c r="E7">
         <v>13.92</v>
@@ -1504,25 +1523,25 @@
         <v>4.69</v>
       </c>
       <c r="G7">
-        <v>-18.46</v>
+        <v>-16.88</v>
       </c>
       <c r="H7">
-        <v>142</v>
+        <v>146.7</v>
       </c>
       <c r="I7">
-        <v>-9.92</v>
+        <v>-6.39</v>
       </c>
       <c r="J7">
-        <v>-1.3</v>
+        <v>1.94</v>
       </c>
       <c r="K7">
-        <v>-1.99</v>
+        <v>1.94</v>
       </c>
       <c r="L7">
-        <v>98.08</v>
+        <v>92.51000000000001</v>
       </c>
       <c r="M7">
-        <v>-31.02</v>
+        <v>-30.79</v>
       </c>
       <c r="N7">
         <v>99</v>
@@ -1531,19 +1550,19 @@
         <v>90</v>
       </c>
       <c r="P7">
-        <v>11.93</v>
+        <v>11.77</v>
       </c>
       <c r="Q7">
-        <v>11.52</v>
+        <v>11.53</v>
       </c>
       <c r="R7">
-        <v>11.77</v>
+        <v>11.78</v>
       </c>
       <c r="S7">
-        <v>10.68</v>
+        <v>10.71</v>
       </c>
       <c r="T7">
-        <v>6.24</v>
+        <v>7.99</v>
       </c>
       <c r="U7" t="s">
         <v>46</v>
@@ -1558,34 +1577,34 @@
         <v>2</v>
       </c>
       <c r="Y7">
-        <v>44.3</v>
+        <v>48.06</v>
       </c>
       <c r="Z7">
-        <v>0.06</v>
+        <v>0.04</v>
       </c>
       <c r="AA7">
         <v>0.03</v>
       </c>
       <c r="AB7">
-        <v>0.03</v>
+        <v>0.01</v>
       </c>
       <c r="AC7">
-        <v>39.32</v>
+        <v>33.07</v>
       </c>
       <c r="AD7">
-        <v>57.01</v>
+        <v>43.66</v>
       </c>
       <c r="AE7">
-        <v>0.38</v>
+        <v>0.41</v>
       </c>
       <c r="AF7">
-        <v>-4.79</v>
+        <v>-1.54</v>
       </c>
       <c r="AG7">
-        <v>12.51</v>
+        <v>12.52</v>
       </c>
       <c r="AH7">
-        <v>10.52</v>
+        <v>10.53</v>
       </c>
       <c r="AI7">
         <v>12.59</v>
@@ -1594,7 +1613,7 @@
         <v>49</v>
       </c>
       <c r="AK7">
-        <v>35.96</v>
+        <v>32.74</v>
       </c>
     </row>
     <row r="8" spans="1:37">
@@ -1605,10 +1624,10 @@
         <v>45</v>
       </c>
       <c r="C8">
-        <v>4008.3</v>
+        <v>4041.8</v>
       </c>
       <c r="D8">
-        <v>-0.47</v>
+        <v>0.84</v>
       </c>
       <c r="E8">
         <v>5809.5</v>
@@ -1617,46 +1636,46 @@
         <v>4008.3</v>
       </c>
       <c r="G8">
-        <v>-31</v>
+        <v>-30.43</v>
       </c>
       <c r="H8">
-        <v>0</v>
+        <v>0.84</v>
       </c>
       <c r="I8">
-        <v>-1.8</v>
+        <v>-0.26</v>
       </c>
       <c r="J8">
-        <v>-8</v>
+        <v>-7.34</v>
       </c>
       <c r="K8">
-        <v>-7.56</v>
+        <v>-7.83</v>
       </c>
       <c r="L8">
-        <v>-23.96</v>
+        <v>-25.3</v>
       </c>
       <c r="M8">
-        <v>16.96</v>
+        <v>16.28</v>
       </c>
       <c r="N8">
         <v>26</v>
       </c>
       <c r="O8">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="P8">
-        <v>4047.36</v>
+        <v>4045.28</v>
       </c>
       <c r="Q8">
-        <v>4234.9</v>
+        <v>4217.22</v>
       </c>
       <c r="R8">
-        <v>4313.5</v>
+        <v>4307.09</v>
       </c>
       <c r="S8">
-        <v>4570.74</v>
+        <v>4565.15</v>
       </c>
       <c r="T8">
-        <v>-12.31</v>
+        <v>-11.46</v>
       </c>
       <c r="U8" t="s">
         <v>46</v>
@@ -1671,34 +1690,34 @@
         <v>0</v>
       </c>
       <c r="Y8">
-        <v>31.88</v>
+        <v>35.51</v>
       </c>
       <c r="Z8">
-        <v>-89.38</v>
+        <v>-89.86</v>
       </c>
       <c r="AA8">
-        <v>-64.11</v>
+        <v>-69.26000000000001</v>
       </c>
       <c r="AB8">
-        <v>-25.27</v>
+        <v>-20.6</v>
       </c>
       <c r="AC8">
-        <v>15.97</v>
+        <v>17.07</v>
       </c>
       <c r="AD8">
-        <v>19.83</v>
+        <v>18.34</v>
       </c>
       <c r="AE8">
-        <v>102.2</v>
+        <v>99.90000000000001</v>
       </c>
       <c r="AF8">
-        <v>-37.81</v>
+        <v>-68.31999999999999</v>
       </c>
       <c r="AG8">
-        <v>4519.74</v>
+        <v>4504.02</v>
       </c>
       <c r="AH8">
-        <v>3950.06</v>
+        <v>3930.43</v>
       </c>
       <c r="AI8">
         <v>4318.07</v>
@@ -1707,7 +1726,7 @@
         <v>49</v>
       </c>
       <c r="AK8">
-        <v>58.64</v>
+        <v>60.4</v>
       </c>
     </row>
     <row r="9" spans="1:37">
@@ -1718,10 +1737,10 @@
         <v>45</v>
       </c>
       <c r="C9">
-        <v>11000</v>
+        <v>11155</v>
       </c>
       <c r="D9">
-        <v>-0.9</v>
+        <v>1.41</v>
       </c>
       <c r="E9">
         <v>13052</v>
@@ -1730,46 +1749,46 @@
         <v>10362</v>
       </c>
       <c r="G9">
-        <v>-15.72</v>
+        <v>-14.53</v>
       </c>
       <c r="H9">
-        <v>6.16</v>
+        <v>7.65</v>
       </c>
       <c r="I9">
-        <v>2.83</v>
+        <v>4.25</v>
       </c>
       <c r="J9">
-        <v>-4.93</v>
+        <v>-3.03</v>
       </c>
       <c r="K9">
-        <v>-2.72</v>
+        <v>-2.41</v>
       </c>
       <c r="L9">
-        <v>-13.53</v>
+        <v>-11.65</v>
       </c>
       <c r="M9">
-        <v>8.09</v>
+        <v>8.41</v>
       </c>
       <c r="N9">
         <v>38</v>
       </c>
       <c r="O9">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="P9">
-        <v>10915.6</v>
+        <v>11006.6</v>
       </c>
       <c r="Q9">
-        <v>11191.35</v>
+        <v>11172.1</v>
       </c>
       <c r="R9">
-        <v>11571.74</v>
+        <v>11564.92</v>
       </c>
       <c r="S9">
-        <v>11727.07</v>
+        <v>11724.8</v>
       </c>
       <c r="T9">
-        <v>-6.2</v>
+        <v>-4.86</v>
       </c>
       <c r="U9" t="s">
         <v>46</v>
@@ -1784,34 +1803,34 @@
         <v>0</v>
       </c>
       <c r="Y9">
-        <v>41.94</v>
+        <v>47.6</v>
       </c>
       <c r="Z9">
-        <v>-192.62</v>
+        <v>-168.23</v>
       </c>
       <c r="AA9">
-        <v>-196.43</v>
+        <v>-190.79</v>
       </c>
       <c r="AB9">
-        <v>3.81</v>
+        <v>22.56</v>
       </c>
       <c r="AC9">
-        <v>93.94</v>
+        <v>94.48999999999999</v>
       </c>
       <c r="AD9">
-        <v>68.52</v>
+        <v>86.93000000000001</v>
       </c>
       <c r="AE9">
-        <v>199.07</v>
+        <v>198.99</v>
       </c>
       <c r="AF9">
-        <v>23.29</v>
+        <v>-18.97</v>
       </c>
       <c r="AG9">
-        <v>11837.36</v>
+        <v>11796.96</v>
       </c>
       <c r="AH9">
-        <v>10545.34</v>
+        <v>10547.24</v>
       </c>
       <c r="AI9">
         <v>11371.08</v>
@@ -1820,7 +1839,7 @@
         <v>49</v>
       </c>
       <c r="AK9">
-        <v>33.63</v>
+        <v>31.02</v>
       </c>
     </row>
   </sheetData>
@@ -1961,7 +1980,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F70"/>
+  <dimension ref="A1:F72"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -2019,1124 +2038,1164 @@
         <v>60</v>
       </c>
     </row>
+    <row r="4" spans="1:6">
+      <c r="A4" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>63</v>
+      </c>
+    </row>
     <row r="5" spans="1:6">
-      <c r="A5" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="B5" s="2"/>
-      <c r="C5" s="2"/>
-      <c r="D5" s="2"/>
-      <c r="E5" s="2"/>
-    </row>
-    <row r="6" spans="1:6">
-      <c r="A6" s="3" t="s">
+      <c r="A5" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="E5" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="F5" s="4" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6">
+      <c r="A7" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="B7" s="2"/>
+      <c r="C7" s="2"/>
+      <c r="D7" s="2"/>
+      <c r="E7" s="2"/>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B6" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6">
-      <c r="A7" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B7" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C7" s="6">
-        <v>-1.37</v>
-      </c>
-      <c r="D7" s="6">
-        <v>-3.87</v>
-      </c>
-      <c r="E7" s="7">
-        <v>-2.5</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
-      <c r="A8" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B8" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C8" s="6">
-        <v>-8.949999999999999</v>
-      </c>
-      <c r="D8" s="6">
-        <v>-9.44</v>
-      </c>
-      <c r="E8" s="7">
-        <v>-0.49</v>
+      <c r="B8" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>71</v>
       </c>
     </row>
     <row r="9" spans="1:6">
       <c r="A9" s="5" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B9" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C9" s="6">
-        <v>-4.06</v>
+        <v>-3.87</v>
       </c>
       <c r="D9" s="6">
-        <v>-5.44</v>
+        <v>-2.53</v>
       </c>
       <c r="E9" s="7">
-        <v>-1.38</v>
+        <v>1.34</v>
       </c>
     </row>
     <row r="10" spans="1:6">
       <c r="A10" s="5" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B10" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C10" s="6">
-        <v>-4.72</v>
+        <v>-9.44</v>
       </c>
       <c r="D10" s="6">
-        <v>-5.9</v>
+        <v>-9.01</v>
       </c>
       <c r="E10" s="7">
-        <v>-1.18</v>
+        <v>0.43</v>
       </c>
     </row>
     <row r="11" spans="1:6">
       <c r="A11" s="5" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B11" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C11" s="6">
-        <v>-1.35</v>
+        <v>-5.44</v>
       </c>
       <c r="D11" s="6">
-        <v>2.37</v>
-      </c>
-      <c r="E11" s="8">
-        <v>3.72</v>
+        <v>-3.03</v>
+      </c>
+      <c r="E11" s="7">
+        <v>2.41</v>
       </c>
     </row>
     <row r="12" spans="1:6">
       <c r="A12" s="5" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B12" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C12" s="6">
-        <v>-0.17</v>
+        <v>-5.9</v>
       </c>
       <c r="D12" s="6">
-        <v>-1.3</v>
+        <v>-5.17</v>
       </c>
       <c r="E12" s="7">
-        <v>-1.13</v>
+        <v>0.73</v>
       </c>
     </row>
     <row r="13" spans="1:6">
       <c r="A13" s="5" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B13" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C13" s="6">
-        <v>-6.55</v>
+        <v>2.37</v>
       </c>
       <c r="D13" s="6">
-        <v>-8</v>
+        <v>3.2</v>
       </c>
       <c r="E13" s="7">
-        <v>-1.45</v>
+        <v>0.83</v>
       </c>
     </row>
     <row r="14" spans="1:6">
       <c r="A14" s="5" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B14" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C14" s="6">
-        <v>-4.1</v>
+        <v>-1.3</v>
       </c>
       <c r="D14" s="6">
-        <v>-4.93</v>
+        <v>1.94</v>
       </c>
       <c r="E14" s="7">
-        <v>-0.83</v>
+        <v>3.24</v>
       </c>
     </row>
     <row r="15" spans="1:6">
       <c r="A15" s="5" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C15" s="6">
-        <v>2.13</v>
+        <v>-8</v>
       </c>
       <c r="D15" s="6">
-        <v>4.8</v>
-      </c>
-      <c r="E15" s="8">
-        <v>2.67</v>
+        <v>-7.34</v>
+      </c>
+      <c r="E15" s="7">
+        <v>0.66</v>
       </c>
     </row>
     <row r="16" spans="1:6">
       <c r="A16" s="5" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C16" s="6">
-        <v>-1.17</v>
+        <v>-4.93</v>
       </c>
       <c r="D16" s="6">
-        <v>0.41</v>
-      </c>
-      <c r="E16" s="8">
-        <v>1.58</v>
+        <v>-3.03</v>
+      </c>
+      <c r="E16" s="7">
+        <v>1.9</v>
       </c>
     </row>
     <row r="17" spans="1:5">
       <c r="A17" s="5" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B17" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C17" s="6">
-        <v>-3.53</v>
+        <v>4.8</v>
       </c>
       <c r="D17" s="6">
-        <v>-1.35</v>
-      </c>
-      <c r="E17" s="8">
-        <v>2.18</v>
+        <v>5.55</v>
+      </c>
+      <c r="E17" s="7">
+        <v>0.75</v>
       </c>
     </row>
     <row r="18" spans="1:5">
       <c r="A18" s="5" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B18" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C18" s="6">
-        <v>-0.03</v>
+        <v>0.41</v>
       </c>
       <c r="D18" s="6">
-        <v>1.49</v>
+        <v>-1.31</v>
       </c>
       <c r="E18" s="8">
-        <v>1.52</v>
+        <v>-1.72</v>
       </c>
     </row>
     <row r="19" spans="1:5">
       <c r="A19" s="5" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B19" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C19" s="6">
-        <v>-7.55</v>
+        <v>-1.35</v>
       </c>
       <c r="D19" s="6">
-        <v>-1.25</v>
-      </c>
-      <c r="E19" s="8">
-        <v>6.3</v>
+        <v>0.05</v>
+      </c>
+      <c r="E19" s="7">
+        <v>1.4</v>
       </c>
     </row>
     <row r="20" spans="1:5">
       <c r="A20" s="5" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B20" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C20" s="6">
-        <v>-2.91</v>
+        <v>1.49</v>
       </c>
       <c r="D20" s="6">
-        <v>-9.92</v>
+        <v>3.2</v>
       </c>
       <c r="E20" s="7">
-        <v>-7.01</v>
+        <v>1.71</v>
       </c>
     </row>
     <row r="21" spans="1:5">
       <c r="A21" s="5" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B21" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C21" s="6">
-        <v>-3.92</v>
+        <v>-1.25</v>
       </c>
       <c r="D21" s="6">
-        <v>-1.8</v>
-      </c>
-      <c r="E21" s="8">
-        <v>2.12</v>
+        <v>1.82</v>
+      </c>
+      <c r="E21" s="7">
+        <v>3.07</v>
       </c>
     </row>
     <row r="22" spans="1:5">
       <c r="A22" s="5" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B22" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C22" s="6">
-        <v>0.91</v>
+        <v>-9.92</v>
       </c>
       <c r="D22" s="6">
-        <v>2.83</v>
-      </c>
-      <c r="E22" s="8">
-        <v>1.92</v>
+        <v>-6.39</v>
+      </c>
+      <c r="E22" s="7">
+        <v>3.53</v>
       </c>
     </row>
     <row r="23" spans="1:5">
       <c r="A23" s="5" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="C23" s="6">
-        <v>39.13</v>
+        <v>-1.8</v>
       </c>
       <c r="D23" s="6">
-        <v>39.81</v>
-      </c>
-      <c r="E23" s="8">
-        <v>0.68</v>
+        <v>-0.26</v>
+      </c>
+      <c r="E23" s="7">
+        <v>1.54</v>
       </c>
     </row>
     <row r="24" spans="1:5">
       <c r="A24" s="5" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="C24" s="6">
-        <v>-42.49</v>
+        <v>2.83</v>
       </c>
       <c r="D24" s="6">
-        <v>-45.41</v>
+        <v>4.25</v>
       </c>
       <c r="E24" s="7">
-        <v>-2.92</v>
+        <v>1.42</v>
       </c>
     </row>
     <row r="25" spans="1:5">
       <c r="A25" s="5" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B25" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C25" s="6">
-        <v>11.36</v>
+        <v>39.81</v>
       </c>
       <c r="D25" s="6">
-        <v>9.17</v>
-      </c>
-      <c r="E25" s="7">
-        <v>-2.19</v>
+        <v>38.35</v>
+      </c>
+      <c r="E25" s="8">
+        <v>-1.46</v>
       </c>
     </row>
     <row r="26" spans="1:5">
       <c r="A26" s="5" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B26" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C26" s="6">
-        <v>29.8</v>
+        <v>-45.41</v>
       </c>
       <c r="D26" s="6">
-        <v>29.72</v>
+        <v>-45.38</v>
       </c>
       <c r="E26" s="7">
-        <v>-0.08</v>
+        <v>0.03</v>
       </c>
     </row>
     <row r="27" spans="1:5">
       <c r="A27" s="5" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B27" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C27" s="6">
-        <v>74.31</v>
+        <v>9.17</v>
       </c>
       <c r="D27" s="6">
-        <v>83.66</v>
-      </c>
-      <c r="E27" s="8">
-        <v>9.35</v>
+        <v>10.76</v>
+      </c>
+      <c r="E27" s="7">
+        <v>1.59</v>
       </c>
     </row>
     <row r="28" spans="1:5">
       <c r="A28" s="5" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B28" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C28" s="6">
-        <v>113.55</v>
+        <v>29.72</v>
       </c>
       <c r="D28" s="6">
-        <v>98.08</v>
+        <v>33.81</v>
       </c>
       <c r="E28" s="7">
-        <v>-15.47</v>
+        <v>4.09</v>
       </c>
     </row>
     <row r="29" spans="1:5">
       <c r="A29" s="5" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B29" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C29" s="6">
-        <v>-23.54</v>
+        <v>83.66</v>
       </c>
       <c r="D29" s="6">
-        <v>-23.96</v>
+        <v>85.2</v>
       </c>
       <c r="E29" s="7">
-        <v>-0.42</v>
+        <v>1.54</v>
       </c>
     </row>
     <row r="30" spans="1:5">
       <c r="A30" s="5" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B30" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C30" s="6">
-        <v>-11.75</v>
+        <v>98.08</v>
       </c>
       <c r="D30" s="6">
-        <v>-13.53</v>
-      </c>
-      <c r="E30" s="7">
-        <v>-1.78</v>
+        <v>92.51000000000001</v>
+      </c>
+      <c r="E30" s="8">
+        <v>-5.57</v>
       </c>
     </row>
     <row r="31" spans="1:5">
       <c r="A31" s="5" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="B31" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C31" s="6">
-        <v>2.92</v>
+        <v>-23.96</v>
       </c>
       <c r="D31" s="6">
-        <v>3.45</v>
+        <v>-25.3</v>
       </c>
       <c r="E31" s="8">
-        <v>0.53</v>
+        <v>-1.34</v>
       </c>
     </row>
     <row r="32" spans="1:5">
       <c r="A32" s="5" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="B32" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C32" s="6">
-        <v>-17.9</v>
+        <v>-13.53</v>
       </c>
       <c r="D32" s="6">
-        <v>-17.32</v>
-      </c>
-      <c r="E32" s="8">
-        <v>0.58</v>
+        <v>-11.65</v>
+      </c>
+      <c r="E32" s="7">
+        <v>1.88</v>
       </c>
     </row>
     <row r="33" spans="1:5">
       <c r="A33" s="5" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B33" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C33" s="6">
-        <v>-0.29</v>
+        <v>3.45</v>
       </c>
       <c r="D33" s="6">
-        <v>-0.51</v>
-      </c>
-      <c r="E33" s="7">
-        <v>-0.22</v>
+        <v>1.94</v>
+      </c>
+      <c r="E33" s="8">
+        <v>-1.51</v>
       </c>
     </row>
     <row r="34" spans="1:5">
       <c r="A34" s="5" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B34" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C34" s="6">
-        <v>-3.25</v>
+        <v>-17.32</v>
       </c>
       <c r="D34" s="6">
-        <v>-1.4</v>
+        <v>-20.31</v>
       </c>
       <c r="E34" s="8">
-        <v>1.85</v>
+        <v>-2.99</v>
       </c>
     </row>
     <row r="35" spans="1:5">
       <c r="A35" s="5" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B35" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C35" s="6">
-        <v>-6.61</v>
+        <v>-0.51</v>
       </c>
       <c r="D35" s="6">
-        <v>-1.25</v>
-      </c>
-      <c r="E35" s="8">
-        <v>5.36</v>
+        <v>1.94</v>
+      </c>
+      <c r="E35" s="7">
+        <v>2.45</v>
       </c>
     </row>
     <row r="36" spans="1:5">
       <c r="A36" s="5" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B36" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C36" s="6">
-        <v>-1.27</v>
+        <v>-1.4</v>
       </c>
       <c r="D36" s="6">
-        <v>-1.99</v>
+        <v>2.79</v>
       </c>
       <c r="E36" s="7">
-        <v>-0.72</v>
+        <v>4.19</v>
       </c>
     </row>
     <row r="37" spans="1:5">
       <c r="A37" s="5" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B37" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C37" s="6">
-        <v>-9.17</v>
+        <v>-1.25</v>
       </c>
       <c r="D37" s="6">
-        <v>-7.56</v>
-      </c>
-      <c r="E37" s="8">
-        <v>1.61</v>
+        <v>1.47</v>
+      </c>
+      <c r="E37" s="7">
+        <v>2.72</v>
       </c>
     </row>
     <row r="38" spans="1:5">
       <c r="A38" s="5" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B38" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C38" s="6">
-        <v>-2.65</v>
+        <v>-1.99</v>
       </c>
       <c r="D38" s="6">
-        <v>-2.72</v>
+        <v>1.94</v>
       </c>
       <c r="E38" s="7">
-        <v>-0.07000000000000001</v>
+        <v>3.93</v>
       </c>
     </row>
     <row r="39" spans="1:5">
       <c r="A39" s="5" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="B39" s="5" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C39" s="6">
-        <v>-5.02</v>
+        <v>-7.56</v>
       </c>
       <c r="D39" s="6">
-        <v>-6.52</v>
-      </c>
-      <c r="E39" s="7">
-        <v>-1.5</v>
+        <v>-7.83</v>
+      </c>
+      <c r="E39" s="8">
+        <v>-0.27</v>
       </c>
     </row>
     <row r="40" spans="1:5">
       <c r="A40" s="5" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="B40" s="5" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C40" s="6">
-        <v>-46.67</v>
+        <v>-2.72</v>
       </c>
       <c r="D40" s="6">
-        <v>-47.35</v>
+        <v>-2.41</v>
       </c>
       <c r="E40" s="7">
-        <v>-0.68</v>
+        <v>0.31</v>
       </c>
     </row>
     <row r="41" spans="1:5">
       <c r="A41" s="5" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B41" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C41" s="6">
-        <v>-6.35</v>
+        <v>-6.52</v>
       </c>
       <c r="D41" s="6">
-        <v>-7.46</v>
+        <v>-5.24</v>
       </c>
       <c r="E41" s="7">
-        <v>-1.11</v>
+        <v>1.28</v>
       </c>
     </row>
     <row r="42" spans="1:5">
       <c r="A42" s="5" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B42" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C42" s="6">
-        <v>-14.66</v>
+        <v>-47.35</v>
       </c>
       <c r="D42" s="6">
-        <v>-15.37</v>
-      </c>
-      <c r="E42" s="7">
-        <v>-0.71</v>
+        <v>-47.49</v>
+      </c>
+      <c r="E42" s="8">
+        <v>-0.14</v>
       </c>
     </row>
     <row r="43" spans="1:5">
       <c r="A43" s="5" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B43" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C43" s="6">
-        <v>-11.28</v>
+        <v>-7.46</v>
       </c>
       <c r="D43" s="6">
-        <v>-8.529999999999999</v>
-      </c>
-      <c r="E43" s="8">
-        <v>2.75</v>
+        <v>-5.68</v>
+      </c>
+      <c r="E43" s="7">
+        <v>1.78</v>
       </c>
     </row>
     <row r="44" spans="1:5">
       <c r="A44" s="5" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B44" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C44" s="6">
-        <v>-16.24</v>
+        <v>-15.37</v>
       </c>
       <c r="D44" s="6">
-        <v>-18.46</v>
+        <v>-12.69</v>
       </c>
       <c r="E44" s="7">
-        <v>-2.22</v>
+        <v>2.68</v>
       </c>
     </row>
     <row r="45" spans="1:5">
       <c r="A45" s="5" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B45" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C45" s="6">
-        <v>-30.68</v>
+        <v>-8.529999999999999</v>
       </c>
       <c r="D45" s="6">
-        <v>-31</v>
+        <v>-6.92</v>
       </c>
       <c r="E45" s="7">
-        <v>-0.32</v>
+        <v>1.61</v>
       </c>
     </row>
     <row r="46" spans="1:5">
       <c r="A46" s="5" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B46" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C46" s="6">
-        <v>-14.96</v>
+        <v>-18.46</v>
       </c>
       <c r="D46" s="6">
-        <v>-15.72</v>
+        <v>-16.88</v>
       </c>
       <c r="E46" s="7">
-        <v>-0.76</v>
+        <v>1.58</v>
       </c>
     </row>
     <row r="47" spans="1:5">
       <c r="A47" s="5" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="B47" s="5" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C47" s="6">
-        <v>403.4</v>
+        <v>-31</v>
       </c>
       <c r="D47" s="6">
-        <v>397</v>
+        <v>-30.43</v>
       </c>
       <c r="E47" s="7">
-        <v>-6.4</v>
+        <v>0.57</v>
       </c>
     </row>
     <row r="48" spans="1:5">
       <c r="A48" s="5" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="B48" s="5" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C48" s="6">
-        <v>49.85</v>
+        <v>-15.72</v>
       </c>
       <c r="D48" s="6">
-        <v>49.22</v>
+        <v>-14.53</v>
       </c>
       <c r="E48" s="7">
-        <v>-0.63</v>
+        <v>1.19</v>
       </c>
     </row>
     <row r="49" spans="1:5">
       <c r="A49" s="5" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B49" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C49" s="6">
-        <v>3166</v>
+        <v>397</v>
       </c>
       <c r="D49" s="6">
-        <v>3128.2</v>
+        <v>402.45</v>
       </c>
       <c r="E49" s="7">
-        <v>-37.8</v>
+        <v>5.45</v>
       </c>
     </row>
     <row r="50" spans="1:5">
       <c r="A50" s="5" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B50" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C50" s="6">
-        <v>981.2</v>
+        <v>49.22</v>
       </c>
       <c r="D50" s="6">
-        <v>973</v>
-      </c>
-      <c r="E50" s="7">
-        <v>-8.199999999999999</v>
+        <v>49.09</v>
+      </c>
+      <c r="E50" s="8">
+        <v>-0.13</v>
       </c>
     </row>
     <row r="51" spans="1:5">
       <c r="A51" s="5" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B51" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C51" s="6">
-        <v>13.84</v>
+        <v>3128.2</v>
       </c>
       <c r="D51" s="6">
-        <v>14.27</v>
-      </c>
-      <c r="E51" s="8">
-        <v>0.43</v>
+        <v>3188.5</v>
+      </c>
+      <c r="E51" s="7">
+        <v>60.3</v>
       </c>
     </row>
     <row r="52" spans="1:5">
       <c r="A52" s="5" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B52" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C52" s="6">
-        <v>11.66</v>
+        <v>973</v>
       </c>
       <c r="D52" s="6">
-        <v>11.35</v>
+        <v>1003.8</v>
       </c>
       <c r="E52" s="7">
-        <v>-0.31</v>
+        <v>30.8</v>
       </c>
     </row>
     <row r="53" spans="1:5">
       <c r="A53" s="5" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B53" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C53" s="6">
-        <v>4027.1</v>
+        <v>14.27</v>
       </c>
       <c r="D53" s="6">
-        <v>4008.3</v>
+        <v>14.52</v>
       </c>
       <c r="E53" s="7">
-        <v>-18.8</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="54" spans="1:5">
       <c r="A54" s="5" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B54" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C54" s="6">
-        <v>11100</v>
+        <v>11.35</v>
       </c>
       <c r="D54" s="6">
-        <v>11000</v>
+        <v>11.57</v>
       </c>
       <c r="E54" s="7">
-        <v>-100</v>
+        <v>0.22</v>
       </c>
     </row>
     <row r="55" spans="1:5">
       <c r="A55" s="5" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="B55" s="5" t="s">
-        <v>24</v>
+        <v>2</v>
       </c>
       <c r="C55" s="6">
-        <v>52.13</v>
+        <v>4008.3</v>
       </c>
       <c r="D55" s="6">
-        <v>48.4</v>
+        <v>4041.8</v>
       </c>
       <c r="E55" s="7">
-        <v>-3.73</v>
+        <v>33.5</v>
       </c>
     </row>
     <row r="56" spans="1:5">
       <c r="A56" s="5" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="B56" s="5" t="s">
-        <v>24</v>
+        <v>2</v>
       </c>
       <c r="C56" s="6">
-        <v>35.32</v>
+        <v>11000</v>
       </c>
       <c r="D56" s="6">
-        <v>33.15</v>
+        <v>11155</v>
       </c>
       <c r="E56" s="7">
-        <v>-2.17</v>
+        <v>155</v>
       </c>
     </row>
     <row r="57" spans="1:5">
       <c r="A57" s="5" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B57" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C57" s="6">
-        <v>40.12</v>
+        <v>48.4</v>
       </c>
       <c r="D57" s="6">
-        <v>36.78</v>
+        <v>51.58</v>
       </c>
       <c r="E57" s="7">
-        <v>-3.34</v>
+        <v>3.18</v>
       </c>
     </row>
     <row r="58" spans="1:5">
       <c r="A58" s="5" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B58" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C58" s="6">
-        <v>42.47</v>
+        <v>33.15</v>
       </c>
       <c r="D58" s="6">
-        <v>40.32</v>
-      </c>
-      <c r="E58" s="7">
-        <v>-2.15</v>
+        <v>32.71</v>
+      </c>
+      <c r="E58" s="8">
+        <v>-0.44</v>
       </c>
     </row>
     <row r="59" spans="1:5">
       <c r="A59" s="5" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B59" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C59" s="6">
-        <v>42.3</v>
+        <v>36.78</v>
       </c>
       <c r="D59" s="6">
-        <v>48.83</v>
-      </c>
-      <c r="E59" s="8">
-        <v>6.53</v>
+        <v>44.7</v>
+      </c>
+      <c r="E59" s="7">
+        <v>7.92</v>
       </c>
     </row>
     <row r="60" spans="1:5">
       <c r="A60" s="5" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B60" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C60" s="6">
-        <v>48.93</v>
+        <v>40.32</v>
       </c>
       <c r="D60" s="6">
-        <v>44.3</v>
+        <v>50.46</v>
       </c>
       <c r="E60" s="7">
-        <v>-4.63</v>
+        <v>10.14</v>
       </c>
     </row>
     <row r="61" spans="1:5">
       <c r="A61" s="5" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B61" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C61" s="6">
-        <v>32.85</v>
+        <v>48.83</v>
       </c>
       <c r="D61" s="6">
-        <v>31.88</v>
+        <v>52.22</v>
       </c>
       <c r="E61" s="7">
-        <v>-0.97</v>
+        <v>3.39</v>
       </c>
     </row>
     <row r="62" spans="1:5">
       <c r="A62" s="5" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B62" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C62" s="6">
-        <v>44.84</v>
+        <v>44.3</v>
       </c>
       <c r="D62" s="6">
-        <v>41.94</v>
+        <v>48.06</v>
       </c>
       <c r="E62" s="7">
-        <v>-2.9</v>
+        <v>3.76</v>
       </c>
     </row>
     <row r="63" spans="1:5">
       <c r="A63" s="5" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="B63" s="5" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="C63" s="6">
-        <v>-44.44</v>
+        <v>31.88</v>
       </c>
       <c r="D63" s="6">
-        <v>-11.32</v>
-      </c>
-      <c r="E63" s="8">
-        <v>33.12</v>
+        <v>35.51</v>
+      </c>
+      <c r="E63" s="7">
+        <v>3.63</v>
       </c>
     </row>
     <row r="64" spans="1:5">
       <c r="A64" s="5" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="B64" s="5" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="C64" s="6">
-        <v>-46.79</v>
+        <v>41.94</v>
       </c>
       <c r="D64" s="6">
-        <v>-38.35</v>
-      </c>
-      <c r="E64" s="8">
-        <v>8.44</v>
+        <v>47.6</v>
+      </c>
+      <c r="E64" s="7">
+        <v>5.66</v>
       </c>
     </row>
     <row r="65" spans="1:5">
       <c r="A65" s="5" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B65" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C65" s="6">
-        <v>-82.73999999999999</v>
+        <v>-11.32</v>
       </c>
       <c r="D65" s="6">
-        <v>-33.13</v>
+        <v>-25.14</v>
       </c>
       <c r="E65" s="8">
-        <v>49.61</v>
+        <v>-13.82</v>
       </c>
     </row>
     <row r="66" spans="1:5">
       <c r="A66" s="5" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B66" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C66" s="6">
-        <v>1.12</v>
+        <v>-38.35</v>
       </c>
       <c r="D66" s="6">
-        <v>2.18</v>
+        <v>-38.57</v>
       </c>
       <c r="E66" s="8">
-        <v>1.06</v>
+        <v>-0.22</v>
       </c>
     </row>
     <row r="67" spans="1:5">
       <c r="A67" s="5" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B67" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C67" s="6">
-        <v>-35.68</v>
+        <v>-33.13</v>
       </c>
       <c r="D67" s="6">
-        <v>12.88</v>
+        <v>-58.83</v>
       </c>
       <c r="E67" s="8">
-        <v>48.56</v>
+        <v>-25.7</v>
       </c>
     </row>
     <row r="68" spans="1:5">
       <c r="A68" s="5" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B68" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C68" s="6">
-        <v>6.56</v>
+        <v>2.18</v>
       </c>
       <c r="D68" s="6">
-        <v>-4.79</v>
+        <v>56.4</v>
       </c>
       <c r="E68" s="7">
-        <v>-11.35</v>
+        <v>54.22</v>
       </c>
     </row>
     <row r="69" spans="1:5">
       <c r="A69" s="5" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B69" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C69" s="6">
-        <v>89.36</v>
+        <v>12.88</v>
       </c>
       <c r="D69" s="6">
-        <v>-37.81</v>
-      </c>
-      <c r="E69" s="7">
-        <v>-127.17</v>
+        <v>-43.76</v>
+      </c>
+      <c r="E69" s="8">
+        <v>-56.64</v>
       </c>
     </row>
     <row r="70" spans="1:5">
       <c r="A70" s="5" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B70" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C70" s="6">
-        <v>-42.09</v>
+        <v>-4.79</v>
       </c>
       <c r="D70" s="6">
+        <v>-1.54</v>
+      </c>
+      <c r="E70" s="7">
+        <v>3.25</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5">
+      <c r="A71" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B71" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C71" s="6">
+        <v>-37.81</v>
+      </c>
+      <c r="D71" s="6">
+        <v>-68.31999999999999</v>
+      </c>
+      <c r="E71" s="8">
+        <v>-30.51</v>
+      </c>
+    </row>
+    <row r="72" spans="1:5">
+      <c r="A72" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="B72" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C72" s="6">
         <v>23.29</v>
       </c>
-      <c r="E70" s="8">
-        <v>65.38</v>
+      <c r="D72" s="6">
+        <v>-18.97</v>
+      </c>
+      <c r="E72" s="8">
+        <v>-42.26</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A5:E5"/>
+    <mergeCell ref="A7:E7"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3160,28 +3219,28 @@
         <v>1</v>
       </c>
       <c r="B1" s="9" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="C1" s="9" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="D1" s="9" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="E1" s="9" t="s">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="F1" s="9" t="s">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="G1" s="9" t="s">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="H1" s="9" t="s">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="I1" s="9" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -3189,22 +3248,22 @@
         <v>45</v>
       </c>
       <c r="B2" s="11">
-        <v>52.44</v>
+        <v>56.44</v>
       </c>
       <c r="C2" s="12">
         <v>8</v>
       </c>
       <c r="D2" s="11">
-        <v>40.7</v>
+        <v>45.4</v>
       </c>
       <c r="E2" s="11">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="F2" s="11">
-        <v>-4.6</v>
+        <v>-3.1</v>
       </c>
       <c r="G2" s="11">
-        <v>-3.7</v>
+        <v>-2.6</v>
       </c>
       <c r="H2" s="11">
         <v>56.1</v>
@@ -3315,10 +3374,10 @@
         <v>37</v>
       </c>
       <c r="B1" s="13" t="s">
+        <v>40</v>
+      </c>
+      <c r="C1" s="13" t="s">
         <v>43</v>
-      </c>
-      <c r="C1" s="13" t="s">
-        <v>40</v>
       </c>
       <c r="D1" s="13" t="s">
         <v>39</v>
@@ -3338,28 +3397,28 @@
     </row>
     <row r="2" spans="1:8">
       <c r="A2" s="14">
-        <v>0.2928</v>
+        <v>0.289</v>
       </c>
       <c r="B2" s="14">
-        <v>0.1696</v>
+        <v>0.1641</v>
       </c>
       <c r="C2" s="14">
-        <v>0.1668</v>
+        <v>0.1628</v>
       </c>
       <c r="D2" s="14">
-        <v>0.1525</v>
+        <v>0.1522</v>
       </c>
       <c r="E2" s="14">
-        <v>0.0809</v>
+        <v>0.08410000000000001</v>
       </c>
       <c r="F2" s="14">
-        <v>0.0653</v>
+        <v>0.066</v>
       </c>
       <c r="G2" s="14">
-        <v>-0.2551</v>
+        <v>-0.2583</v>
       </c>
       <c r="H2" s="14">
-        <v>-0.3102</v>
+        <v>-0.3079</v>
       </c>
     </row>
   </sheetData>

--- a/BIRLA_GROUP_Technical_Metrics.xlsx
+++ b/BIRLA_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="299" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="311" uniqueCount="82">
   <si>
     <t>Symbol</t>
   </si>
@@ -193,34 +193,40 @@
     <t>RSI Momentum</t>
   </si>
   <si>
-    <t>48.4 → 51.6</t>
-  </si>
-  <si>
-    <t>🟢 BULLISH</t>
-  </si>
-  <si>
-    <t>48.4</t>
+    <t>51.6 → 44.8</t>
+  </si>
+  <si>
+    <t>🔴 BEARISH</t>
   </si>
   <si>
     <t>51.6</t>
   </si>
   <si>
-    <t>40.3 → 50.5</t>
-  </si>
-  <si>
-    <t>40.3</t>
+    <t>44.8</t>
+  </si>
+  <si>
+    <t>Yes → No</t>
+  </si>
+  <si>
+    <t>20 DMA &gt; 50 DMA</t>
+  </si>
+  <si>
+    <t>50.5 → 44.7</t>
   </si>
   <si>
     <t>50.5</t>
   </si>
   <si>
-    <t>48.8 → 52.2</t>
-  </si>
-  <si>
-    <t>48.8</t>
+    <t>44.7</t>
+  </si>
+  <si>
+    <t>52.2 → 46.9</t>
   </si>
   <si>
     <t>52.2</t>
+  </si>
+  <si>
+    <t>46.9</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -306,14 +312,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF9C0006"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF006100"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -346,13 +352,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -804,16 +810,16 @@
     <col min="13" max="13" width="10.7109375" customWidth="1"/>
     <col min="14" max="14" width="11.7109375" customWidth="1"/>
     <col min="15" max="15" width="10.7109375" customWidth="1"/>
-    <col min="16" max="17" width="9.7109375" customWidth="1"/>
-    <col min="18" max="18" width="10.7109375" customWidth="1"/>
-    <col min="19" max="19" width="9.7109375" customWidth="1"/>
+    <col min="16" max="16" width="9.7109375" customWidth="1"/>
+    <col min="17" max="17" width="10.7109375" customWidth="1"/>
+    <col min="18" max="19" width="9.7109375" customWidth="1"/>
     <col min="20" max="20" width="22.7109375" customWidth="1"/>
     <col min="21" max="21" width="9.7109375" customWidth="1"/>
     <col min="22" max="22" width="10.7109375" customWidth="1"/>
     <col min="23" max="23" width="16.7109375" customWidth="1"/>
     <col min="24" max="24" width="13.7109375" customWidth="1"/>
     <col min="25" max="25" width="7.7109375" customWidth="1"/>
-    <col min="26" max="26" width="9.7109375" customWidth="1"/>
+    <col min="26" max="26" width="8.7109375" customWidth="1"/>
     <col min="27" max="27" width="13.7109375" customWidth="1"/>
     <col min="28" max="28" width="11.7109375" customWidth="1"/>
     <col min="29" max="30" width="13.7109375" customWidth="1"/>
@@ -946,10 +952,10 @@
         <v>45</v>
       </c>
       <c r="C2">
-        <v>402.45</v>
+        <v>390.1</v>
       </c>
       <c r="D2">
-        <v>1.37</v>
+        <v>-3.07</v>
       </c>
       <c r="E2">
         <v>424.7</v>
@@ -958,46 +964,46 @@
         <v>278.9</v>
       </c>
       <c r="G2">
-        <v>-5.24</v>
+        <v>-8.15</v>
       </c>
       <c r="H2">
-        <v>44.3</v>
+        <v>39.87</v>
       </c>
       <c r="I2">
-        <v>5.55</v>
+        <v>0.03</v>
       </c>
       <c r="J2">
-        <v>-2.53</v>
+        <v>-5.05</v>
       </c>
       <c r="K2">
-        <v>1.94</v>
+        <v>-0.18</v>
       </c>
       <c r="L2">
-        <v>38.35</v>
+        <v>34.91</v>
       </c>
       <c r="M2">
-        <v>28.9</v>
+        <v>27.58</v>
       </c>
       <c r="N2">
         <v>74</v>
       </c>
       <c r="O2">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="P2">
-        <v>400.58</v>
+        <v>400.6</v>
       </c>
       <c r="Q2">
-        <v>399.58</v>
+        <v>398.58</v>
       </c>
       <c r="R2">
-        <v>403.15</v>
+        <v>402.86</v>
       </c>
       <c r="S2">
-        <v>363.85</v>
+        <v>364.01</v>
       </c>
       <c r="T2">
-        <v>10.61</v>
+        <v>7.17</v>
       </c>
       <c r="U2" t="s">
         <v>46</v>
@@ -1012,34 +1018,34 @@
         <v>2</v>
       </c>
       <c r="Y2">
-        <v>51.58</v>
+        <v>44.84</v>
       </c>
       <c r="Z2">
-        <v>-1.41</v>
+        <v>-1.97</v>
       </c>
       <c r="AA2">
         <v>-1.98</v>
       </c>
       <c r="AB2">
-        <v>0.57</v>
+        <v>0.01</v>
       </c>
       <c r="AC2">
-        <v>75.02</v>
+        <v>64.20999999999999</v>
       </c>
       <c r="AD2">
-        <v>78.16</v>
+        <v>73.76000000000001</v>
       </c>
       <c r="AE2">
-        <v>9.800000000000001</v>
+        <v>10.1</v>
       </c>
       <c r="AF2">
-        <v>-25.14</v>
+        <v>55.16</v>
       </c>
       <c r="AG2">
-        <v>417.08</v>
+        <v>415.85</v>
       </c>
       <c r="AH2">
-        <v>382.08</v>
+        <v>381.32</v>
       </c>
       <c r="AI2">
         <v>372.91</v>
@@ -1048,7 +1054,7 @@
         <v>48</v>
       </c>
       <c r="AK2">
-        <v>23.68</v>
+        <v>22.97</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1059,58 +1065,58 @@
         <v>45</v>
       </c>
       <c r="C3">
-        <v>49.09</v>
+        <v>48.06</v>
       </c>
       <c r="D3">
-        <v>-0.26</v>
+        <v>-2.1</v>
       </c>
       <c r="E3">
         <v>93.48</v>
       </c>
       <c r="F3">
-        <v>49.02</v>
+        <v>48.06</v>
       </c>
       <c r="G3">
-        <v>-47.49</v>
+        <v>-48.59</v>
       </c>
       <c r="H3">
-        <v>0.14</v>
+        <v>0</v>
       </c>
       <c r="I3">
-        <v>-1.31</v>
+        <v>-4.74</v>
       </c>
       <c r="J3">
-        <v>-9.01</v>
+        <v>-11.78</v>
       </c>
       <c r="K3">
-        <v>-20.31</v>
+        <v>-20.06</v>
       </c>
       <c r="L3">
-        <v>-45.38</v>
+        <v>-47.82</v>
       </c>
       <c r="M3">
-        <v>-25.83</v>
+        <v>-26.49</v>
       </c>
       <c r="N3">
         <v>13</v>
       </c>
       <c r="O3">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="P3">
-        <v>49.75</v>
+        <v>49.28</v>
       </c>
       <c r="Q3">
-        <v>51.17</v>
+        <v>50.84</v>
       </c>
       <c r="R3">
-        <v>55.17</v>
+        <v>54.95</v>
       </c>
       <c r="S3">
-        <v>63.14</v>
+        <v>62.99</v>
       </c>
       <c r="T3">
-        <v>-22.25</v>
+        <v>-23.7</v>
       </c>
       <c r="U3" t="s">
         <v>46</v>
@@ -1125,43 +1131,43 @@
         <v>0</v>
       </c>
       <c r="Y3">
-        <v>32.71</v>
+        <v>29.34</v>
       </c>
       <c r="Z3">
-        <v>-1.71</v>
+        <v>-1.77</v>
       </c>
       <c r="AA3">
-        <v>-1.74</v>
+        <v>-1.75</v>
       </c>
       <c r="AB3">
-        <v>0.03</v>
+        <v>-0.02</v>
       </c>
       <c r="AC3">
-        <v>51.15</v>
+        <v>32.44</v>
       </c>
       <c r="AD3">
-        <v>58.7</v>
+        <v>47.31</v>
       </c>
       <c r="AE3">
-        <v>1.48</v>
+        <v>1.45</v>
       </c>
       <c r="AF3">
-        <v>-38.57</v>
+        <v>15.66</v>
       </c>
       <c r="AG3">
-        <v>54.35</v>
+        <v>53.91</v>
       </c>
       <c r="AH3">
-        <v>47.98</v>
+        <v>47.78</v>
       </c>
       <c r="AI3">
-        <v>53.68</v>
+        <v>52.83</v>
       </c>
       <c r="AJ3" t="s">
         <v>49</v>
       </c>
       <c r="AK3">
-        <v>34.99</v>
+        <v>37.94</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1172,10 +1178,10 @@
         <v>45</v>
       </c>
       <c r="C4">
-        <v>3188.5</v>
+        <v>3166.5</v>
       </c>
       <c r="D4">
-        <v>1.93</v>
+        <v>-0.6899999999999999</v>
       </c>
       <c r="E4">
         <v>3380.5</v>
@@ -1184,46 +1190,46 @@
         <v>2531.1</v>
       </c>
       <c r="G4">
-        <v>-5.68</v>
+        <v>-6.33</v>
       </c>
       <c r="H4">
-        <v>25.97</v>
+        <v>25.1</v>
       </c>
       <c r="I4">
-        <v>0.05</v>
+        <v>-0.21</v>
       </c>
       <c r="J4">
-        <v>-3.03</v>
+        <v>-3.74</v>
       </c>
       <c r="K4">
-        <v>1.94</v>
+        <v>1.28</v>
       </c>
       <c r="L4">
-        <v>10.76</v>
+        <v>10.03</v>
       </c>
       <c r="M4">
-        <v>15.22</v>
+        <v>14.74</v>
       </c>
       <c r="N4">
         <v>50</v>
       </c>
       <c r="O4">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="P4">
-        <v>3173</v>
+        <v>3171.68</v>
       </c>
       <c r="Q4">
-        <v>3259.19</v>
+        <v>3252.52</v>
       </c>
       <c r="R4">
-        <v>3227.16</v>
+        <v>3228.77</v>
       </c>
       <c r="S4">
-        <v>2966.77</v>
+        <v>2968.87</v>
       </c>
       <c r="T4">
-        <v>7.47</v>
+        <v>6.66</v>
       </c>
       <c r="U4" t="s">
         <v>47</v>
@@ -1238,34 +1244,34 @@
         <v>3</v>
       </c>
       <c r="Y4">
-        <v>44.7</v>
+        <v>42.6</v>
       </c>
       <c r="Z4">
-        <v>-23.13</v>
+        <v>-25.1</v>
       </c>
       <c r="AA4">
-        <v>-5.5</v>
+        <v>-9.42</v>
       </c>
       <c r="AB4">
-        <v>-17.63</v>
+        <v>-15.68</v>
       </c>
       <c r="AC4">
-        <v>16.24</v>
+        <v>23.03</v>
       </c>
       <c r="AD4">
-        <v>13.06</v>
+        <v>16.72</v>
       </c>
       <c r="AE4">
-        <v>60.21</v>
+        <v>59.7</v>
       </c>
       <c r="AF4">
-        <v>-58.83</v>
+        <v>-49.97</v>
       </c>
       <c r="AG4">
-        <v>3395.8</v>
+        <v>3393.71</v>
       </c>
       <c r="AH4">
-        <v>3122.59</v>
+        <v>3111.34</v>
       </c>
       <c r="AI4">
         <v>3120.02</v>
@@ -1274,7 +1280,7 @@
         <v>48</v>
       </c>
       <c r="AK4">
-        <v>36.95</v>
+        <v>36.88</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1285,10 +1291,10 @@
         <v>45</v>
       </c>
       <c r="C5">
-        <v>1003.8</v>
+        <v>982</v>
       </c>
       <c r="D5">
-        <v>3.17</v>
+        <v>-2.17</v>
       </c>
       <c r="E5">
         <v>1149.7</v>
@@ -1297,25 +1303,25 @@
         <v>741.05</v>
       </c>
       <c r="G5">
-        <v>-12.69</v>
+        <v>-14.59</v>
       </c>
       <c r="H5">
-        <v>35.46</v>
+        <v>32.51</v>
       </c>
       <c r="I5">
-        <v>3.2</v>
+        <v>0.15</v>
       </c>
       <c r="J5">
-        <v>-5.17</v>
+        <v>-6.57</v>
       </c>
       <c r="K5">
-        <v>2.79</v>
+        <v>3.02</v>
       </c>
       <c r="L5">
-        <v>33.81</v>
+        <v>32.11</v>
       </c>
       <c r="M5">
-        <v>16.41</v>
+        <v>16.12</v>
       </c>
       <c r="N5">
         <v>62</v>
@@ -1324,61 +1330,61 @@
         <v>76</v>
       </c>
       <c r="P5">
-        <v>985</v>
+        <v>985.3</v>
       </c>
       <c r="Q5">
-        <v>1003.44</v>
+        <v>999.89</v>
       </c>
       <c r="R5">
-        <v>1003.35</v>
+        <v>1003.87</v>
       </c>
       <c r="S5">
-        <v>977.16</v>
+        <v>977.95</v>
       </c>
       <c r="T5">
-        <v>2.73</v>
+        <v>0.41</v>
       </c>
       <c r="U5" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="V5" t="s">
         <v>47</v>
       </c>
       <c r="W5" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="X5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Y5">
-        <v>50.46</v>
+        <v>44.68</v>
       </c>
       <c r="Z5">
-        <v>-9.68</v>
+        <v>-9.779999999999999</v>
       </c>
       <c r="AA5">
-        <v>-7.75</v>
+        <v>-8.15</v>
       </c>
       <c r="AB5">
-        <v>-1.94</v>
+        <v>-1.63</v>
       </c>
       <c r="AC5">
-        <v>55.67</v>
+        <v>59.69</v>
       </c>
       <c r="AD5">
-        <v>48.4</v>
+        <v>53.01</v>
       </c>
       <c r="AE5">
-        <v>22.86</v>
+        <v>23.18</v>
       </c>
       <c r="AF5">
-        <v>56.4</v>
+        <v>29.25</v>
       </c>
       <c r="AG5">
-        <v>1051.12</v>
+        <v>1042.31</v>
       </c>
       <c r="AH5">
-        <v>955.76</v>
+        <v>957.46</v>
       </c>
       <c r="AI5">
         <v>1037.86</v>
@@ -1387,7 +1393,7 @@
         <v>49</v>
       </c>
       <c r="AK5">
-        <v>22.01</v>
+        <v>19.5</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1398,10 +1404,10 @@
         <v>45</v>
       </c>
       <c r="C6">
-        <v>14.52</v>
+        <v>14.12</v>
       </c>
       <c r="D6">
-        <v>1.75</v>
+        <v>-2.75</v>
       </c>
       <c r="E6">
         <v>15.6</v>
@@ -1410,46 +1416,46 @@
         <v>8.02</v>
       </c>
       <c r="G6">
-        <v>-6.92</v>
+        <v>-9.49</v>
       </c>
       <c r="H6">
-        <v>81.05</v>
+        <v>76.06</v>
       </c>
       <c r="I6">
-        <v>1.82</v>
+        <v>-0.7</v>
       </c>
       <c r="J6">
-        <v>3.2</v>
+        <v>-7.04</v>
       </c>
       <c r="K6">
-        <v>1.47</v>
+        <v>0.43</v>
       </c>
       <c r="L6">
-        <v>85.2</v>
+        <v>68.09999999999999</v>
       </c>
       <c r="M6">
-        <v>6.6</v>
+        <v>4.19</v>
       </c>
       <c r="N6">
         <v>87</v>
       </c>
       <c r="O6">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="P6">
-        <v>14.15</v>
+        <v>14.13</v>
       </c>
       <c r="Q6">
-        <v>14.65</v>
+        <v>14.6</v>
       </c>
       <c r="R6">
-        <v>13.92</v>
+        <v>13.93</v>
       </c>
       <c r="S6">
-        <v>12.17</v>
+        <v>12.18</v>
       </c>
       <c r="T6">
-        <v>19.36</v>
+        <v>15.91</v>
       </c>
       <c r="U6" t="s">
         <v>47</v>
@@ -1464,34 +1470,34 @@
         <v>3</v>
       </c>
       <c r="Y6">
-        <v>52.22</v>
+        <v>46.87</v>
       </c>
       <c r="Z6">
-        <v>0.05</v>
+        <v>0.02</v>
       </c>
       <c r="AA6">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="AB6">
         <v>-0.12</v>
       </c>
       <c r="AC6">
-        <v>21.14</v>
+        <v>27.02</v>
       </c>
       <c r="AD6">
-        <v>9.85</v>
+        <v>18.85</v>
       </c>
       <c r="AE6">
         <v>0.48</v>
       </c>
       <c r="AF6">
-        <v>-43.76</v>
+        <v>-25.07</v>
       </c>
       <c r="AG6">
-        <v>15.68</v>
+        <v>15.64</v>
       </c>
       <c r="AH6">
-        <v>13.62</v>
+        <v>13.57</v>
       </c>
       <c r="AI6">
         <v>15.41</v>
@@ -1500,7 +1506,7 @@
         <v>49</v>
       </c>
       <c r="AK6">
-        <v>25.64</v>
+        <v>23.85</v>
       </c>
     </row>
     <row r="7" spans="1:37">
@@ -1511,10 +1517,10 @@
         <v>45</v>
       </c>
       <c r="C7">
-        <v>11.57</v>
+        <v>11.39</v>
       </c>
       <c r="D7">
-        <v>1.94</v>
+        <v>-1.56</v>
       </c>
       <c r="E7">
         <v>13.92</v>
@@ -1523,46 +1529,46 @@
         <v>4.69</v>
       </c>
       <c r="G7">
-        <v>-16.88</v>
+        <v>-18.18</v>
       </c>
       <c r="H7">
-        <v>146.7</v>
+        <v>142.86</v>
       </c>
       <c r="I7">
-        <v>-6.39</v>
+        <v>-7.7</v>
       </c>
       <c r="J7">
-        <v>1.94</v>
+        <v>0.53</v>
       </c>
       <c r="K7">
-        <v>1.94</v>
+        <v>2.34</v>
       </c>
       <c r="L7">
-        <v>92.51000000000001</v>
+        <v>80.51000000000001</v>
       </c>
       <c r="M7">
-        <v>-30.79</v>
+        <v>-30.81</v>
       </c>
       <c r="N7">
         <v>99</v>
       </c>
       <c r="O7">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="P7">
-        <v>11.77</v>
+        <v>11.58</v>
       </c>
       <c r="Q7">
-        <v>11.53</v>
+        <v>11.54</v>
       </c>
       <c r="R7">
-        <v>11.78</v>
+        <v>11.79</v>
       </c>
       <c r="S7">
-        <v>10.71</v>
+        <v>10.74</v>
       </c>
       <c r="T7">
-        <v>7.99</v>
+        <v>6.07</v>
       </c>
       <c r="U7" t="s">
         <v>46</v>
@@ -1577,34 +1583,34 @@
         <v>2</v>
       </c>
       <c r="Y7">
-        <v>48.06</v>
+        <v>45.36</v>
       </c>
       <c r="Z7">
-        <v>0.04</v>
+        <v>0.01</v>
       </c>
       <c r="AA7">
         <v>0.03</v>
       </c>
       <c r="AB7">
-        <v>0.01</v>
+        <v>-0.02</v>
       </c>
       <c r="AC7">
-        <v>33.07</v>
+        <v>29.06</v>
       </c>
       <c r="AD7">
-        <v>43.66</v>
+        <v>33.82</v>
       </c>
       <c r="AE7">
-        <v>0.41</v>
+        <v>0.43</v>
       </c>
       <c r="AF7">
-        <v>-1.54</v>
+        <v>-38.81</v>
       </c>
       <c r="AG7">
         <v>12.52</v>
       </c>
       <c r="AH7">
-        <v>10.53</v>
+        <v>10.56</v>
       </c>
       <c r="AI7">
         <v>12.59</v>
@@ -1613,7 +1619,7 @@
         <v>49</v>
       </c>
       <c r="AK7">
-        <v>32.74</v>
+        <v>29.05</v>
       </c>
     </row>
     <row r="8" spans="1:37">
@@ -1624,58 +1630,58 @@
         <v>45</v>
       </c>
       <c r="C8">
-        <v>4041.8</v>
+        <v>4007.1</v>
       </c>
       <c r="D8">
-        <v>0.84</v>
+        <v>-0.86</v>
       </c>
       <c r="E8">
         <v>5809.5</v>
       </c>
       <c r="F8">
-        <v>4008.3</v>
+        <v>4007.1</v>
       </c>
       <c r="G8">
-        <v>-30.43</v>
+        <v>-31.03</v>
       </c>
       <c r="H8">
-        <v>0.84</v>
+        <v>0</v>
       </c>
       <c r="I8">
-        <v>-0.26</v>
+        <v>-1.84</v>
       </c>
       <c r="J8">
-        <v>-7.34</v>
+        <v>-8.83</v>
       </c>
       <c r="K8">
-        <v>-7.83</v>
+        <v>-8.880000000000001</v>
       </c>
       <c r="L8">
-        <v>-25.3</v>
+        <v>-27.08</v>
       </c>
       <c r="M8">
-        <v>16.28</v>
+        <v>16.45</v>
       </c>
       <c r="N8">
         <v>26</v>
       </c>
       <c r="O8">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="P8">
-        <v>4045.28</v>
+        <v>4030.26</v>
       </c>
       <c r="Q8">
-        <v>4217.22</v>
+        <v>4196.33</v>
       </c>
       <c r="R8">
-        <v>4307.09</v>
+        <v>4300</v>
       </c>
       <c r="S8">
-        <v>4565.15</v>
+        <v>4559.5</v>
       </c>
       <c r="T8">
-        <v>-11.46</v>
+        <v>-12.12</v>
       </c>
       <c r="U8" t="s">
         <v>46</v>
@@ -1690,34 +1696,34 @@
         <v>0</v>
       </c>
       <c r="Y8">
-        <v>35.51</v>
+        <v>33.52</v>
       </c>
       <c r="Z8">
-        <v>-89.86</v>
+        <v>-91.98</v>
       </c>
       <c r="AA8">
-        <v>-69.26000000000001</v>
+        <v>-73.8</v>
       </c>
       <c r="AB8">
-        <v>-20.6</v>
+        <v>-18.18</v>
       </c>
       <c r="AC8">
-        <v>17.07</v>
+        <v>19.43</v>
       </c>
       <c r="AD8">
-        <v>18.34</v>
+        <v>17.49</v>
       </c>
       <c r="AE8">
-        <v>99.90000000000001</v>
+        <v>97.97</v>
       </c>
       <c r="AF8">
-        <v>-68.31999999999999</v>
+        <v>-38.8</v>
       </c>
       <c r="AG8">
-        <v>4504.02</v>
+        <v>4480.29</v>
       </c>
       <c r="AH8">
-        <v>3930.43</v>
+        <v>3912.38</v>
       </c>
       <c r="AI8">
         <v>4318.07</v>
@@ -1726,7 +1732,7 @@
         <v>49</v>
       </c>
       <c r="AK8">
-        <v>60.4</v>
+        <v>62.05</v>
       </c>
     </row>
     <row r="9" spans="1:37">
@@ -1737,10 +1743,10 @@
         <v>45</v>
       </c>
       <c r="C9">
-        <v>11155</v>
+        <v>11056</v>
       </c>
       <c r="D9">
-        <v>1.41</v>
+        <v>-0.89</v>
       </c>
       <c r="E9">
         <v>13052</v>
@@ -1749,46 +1755,46 @@
         <v>10362</v>
       </c>
       <c r="G9">
-        <v>-14.53</v>
+        <v>-15.29</v>
       </c>
       <c r="H9">
-        <v>7.65</v>
+        <v>6.7</v>
       </c>
       <c r="I9">
-        <v>4.25</v>
+        <v>2.71</v>
       </c>
       <c r="J9">
-        <v>-3.03</v>
+        <v>-4.19</v>
       </c>
       <c r="K9">
-        <v>-2.41</v>
+        <v>-3.77</v>
       </c>
       <c r="L9">
-        <v>-11.65</v>
+        <v>-11.61</v>
       </c>
       <c r="M9">
-        <v>8.41</v>
+        <v>8.5</v>
       </c>
       <c r="N9">
         <v>38</v>
       </c>
       <c r="O9">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="P9">
-        <v>11006.6</v>
+        <v>11065</v>
       </c>
       <c r="Q9">
-        <v>11172.1</v>
+        <v>11139.05</v>
       </c>
       <c r="R9">
-        <v>11564.92</v>
+        <v>11549.8</v>
       </c>
       <c r="S9">
-        <v>11724.8</v>
+        <v>11722.1</v>
       </c>
       <c r="T9">
-        <v>-4.86</v>
+        <v>-5.68</v>
       </c>
       <c r="U9" t="s">
         <v>46</v>
@@ -1803,34 +1809,34 @@
         <v>0</v>
       </c>
       <c r="Y9">
-        <v>47.6</v>
+        <v>44.61</v>
       </c>
       <c r="Z9">
-        <v>-168.23</v>
+        <v>-155.1</v>
       </c>
       <c r="AA9">
-        <v>-190.79</v>
+        <v>-183.65</v>
       </c>
       <c r="AB9">
-        <v>22.56</v>
+        <v>28.56</v>
       </c>
       <c r="AC9">
-        <v>94.48999999999999</v>
+        <v>89.58</v>
       </c>
       <c r="AD9">
-        <v>86.93000000000001</v>
+        <v>92.67</v>
       </c>
       <c r="AE9">
-        <v>198.99</v>
+        <v>194.49</v>
       </c>
       <c r="AF9">
-        <v>-18.97</v>
+        <v>14.87</v>
       </c>
       <c r="AG9">
-        <v>11796.96</v>
+        <v>11710.17</v>
       </c>
       <c r="AH9">
-        <v>10547.24</v>
+        <v>10567.93</v>
       </c>
       <c r="AI9">
         <v>11371.08</v>
@@ -1839,7 +1845,7 @@
         <v>49</v>
       </c>
       <c r="AK9">
-        <v>31.02</v>
+        <v>28.77</v>
       </c>
     </row>
   </sheetData>
@@ -1980,7 +1986,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F72"/>
+  <dimension ref="A1:F74"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -2043,7 +2049,7 @@
         <v>40</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>56</v>
+        <v>22</v>
       </c>
       <c r="C4" s="4" t="s">
         <v>61</v>
@@ -2052,1150 +2058,1190 @@
         <v>58</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>62</v>
+        <v>47</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>63</v>
+        <v>46</v>
       </c>
     </row>
     <row r="5" spans="1:6">
       <c r="A5" s="4" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="D5" s="4" t="s">
         <v>58</v>
       </c>
       <c r="E5" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="F5" s="4" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6">
+      <c r="A6" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="F6" s="4" t="s">
         <v>65</v>
       </c>
-      <c r="F5" s="4" t="s">
+    </row>
+    <row r="7" spans="1:6">
+      <c r="A7" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="C7" s="4" t="s">
         <v>66</v>
       </c>
-    </row>
-    <row r="7" spans="1:6">
-      <c r="A7" s="2" t="s">
+      <c r="D7" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="E7" s="4" t="s">
         <v>67</v>
       </c>
-      <c r="B7" s="2"/>
-      <c r="C7" s="2"/>
-      <c r="D7" s="2"/>
-      <c r="E7" s="2"/>
-    </row>
-    <row r="8" spans="1:6">
-      <c r="A8" s="3" t="s">
+      <c r="F7" s="4" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="B9" s="2"/>
+      <c r="C9" s="2"/>
+      <c r="D9" s="2"/>
+      <c r="E9" s="2"/>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B8" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="D8" s="3" t="s">
+      <c r="B10" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="E8" s="3" t="s">
+      <c r="C10" s="3" t="s">
         <v>71</v>
       </c>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B9" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C9" s="6">
-        <v>-3.87</v>
-      </c>
-      <c r="D9" s="6">
-        <v>-2.53</v>
-      </c>
-      <c r="E9" s="7">
-        <v>1.34</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B10" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C10" s="6">
-        <v>-9.44</v>
-      </c>
-      <c r="D10" s="6">
-        <v>-9.01</v>
-      </c>
-      <c r="E10" s="7">
-        <v>0.43</v>
+      <c r="D10" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>73</v>
       </c>
     </row>
     <row r="11" spans="1:6">
       <c r="A11" s="5" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B11" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C11" s="6">
-        <v>-5.44</v>
+        <v>-2.53</v>
       </c>
       <c r="D11" s="6">
-        <v>-3.03</v>
+        <v>-5.05</v>
       </c>
       <c r="E11" s="7">
-        <v>2.41</v>
+        <v>-2.52</v>
       </c>
     </row>
     <row r="12" spans="1:6">
       <c r="A12" s="5" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B12" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C12" s="6">
-        <v>-5.9</v>
+        <v>-9.01</v>
       </c>
       <c r="D12" s="6">
-        <v>-5.17</v>
+        <v>-11.78</v>
       </c>
       <c r="E12" s="7">
-        <v>0.73</v>
+        <v>-2.77</v>
       </c>
     </row>
     <row r="13" spans="1:6">
       <c r="A13" s="5" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B13" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C13" s="6">
-        <v>2.37</v>
+        <v>-3.03</v>
       </c>
       <c r="D13" s="6">
-        <v>3.2</v>
+        <v>-3.74</v>
       </c>
       <c r="E13" s="7">
-        <v>0.83</v>
+        <v>-0.71</v>
       </c>
     </row>
     <row r="14" spans="1:6">
       <c r="A14" s="5" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B14" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C14" s="6">
-        <v>-1.3</v>
+        <v>-5.17</v>
       </c>
       <c r="D14" s="6">
-        <v>1.94</v>
+        <v>-6.57</v>
       </c>
       <c r="E14" s="7">
-        <v>3.24</v>
+        <v>-1.4</v>
       </c>
     </row>
     <row r="15" spans="1:6">
       <c r="A15" s="5" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B15" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C15" s="6">
-        <v>-8</v>
+        <v>3.2</v>
       </c>
       <c r="D15" s="6">
-        <v>-7.34</v>
+        <v>-7.04</v>
       </c>
       <c r="E15" s="7">
-        <v>0.66</v>
+        <v>-10.24</v>
       </c>
     </row>
     <row r="16" spans="1:6">
       <c r="A16" s="5" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B16" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C16" s="6">
-        <v>-4.93</v>
+        <v>1.94</v>
       </c>
       <c r="D16" s="6">
-        <v>-3.03</v>
+        <v>0.53</v>
       </c>
       <c r="E16" s="7">
-        <v>1.9</v>
+        <v>-1.41</v>
       </c>
     </row>
     <row r="17" spans="1:5">
       <c r="A17" s="5" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C17" s="6">
-        <v>4.8</v>
+        <v>-7.34</v>
       </c>
       <c r="D17" s="6">
-        <v>5.55</v>
+        <v>-8.83</v>
       </c>
       <c r="E17" s="7">
-        <v>0.75</v>
+        <v>-1.49</v>
       </c>
     </row>
     <row r="18" spans="1:5">
       <c r="A18" s="5" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C18" s="6">
-        <v>0.41</v>
+        <v>-3.03</v>
       </c>
       <c r="D18" s="6">
-        <v>-1.31</v>
-      </c>
-      <c r="E18" s="8">
-        <v>-1.72</v>
+        <v>-4.19</v>
+      </c>
+      <c r="E18" s="7">
+        <v>-1.16</v>
       </c>
     </row>
     <row r="19" spans="1:5">
       <c r="A19" s="5" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B19" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C19" s="6">
-        <v>-1.35</v>
+        <v>5.55</v>
       </c>
       <c r="D19" s="6">
-        <v>0.05</v>
+        <v>0.03</v>
       </c>
       <c r="E19" s="7">
-        <v>1.4</v>
+        <v>-5.52</v>
       </c>
     </row>
     <row r="20" spans="1:5">
       <c r="A20" s="5" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B20" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C20" s="6">
-        <v>1.49</v>
+        <v>-1.31</v>
       </c>
       <c r="D20" s="6">
-        <v>3.2</v>
+        <v>-4.74</v>
       </c>
       <c r="E20" s="7">
-        <v>1.71</v>
+        <v>-3.43</v>
       </c>
     </row>
     <row r="21" spans="1:5">
       <c r="A21" s="5" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B21" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C21" s="6">
-        <v>-1.25</v>
+        <v>0.05</v>
       </c>
       <c r="D21" s="6">
-        <v>1.82</v>
+        <v>-0.21</v>
       </c>
       <c r="E21" s="7">
-        <v>3.07</v>
+        <v>-0.26</v>
       </c>
     </row>
     <row r="22" spans="1:5">
       <c r="A22" s="5" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B22" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C22" s="6">
-        <v>-9.92</v>
+        <v>3.2</v>
       </c>
       <c r="D22" s="6">
-        <v>-6.39</v>
+        <v>0.15</v>
       </c>
       <c r="E22" s="7">
-        <v>3.53</v>
+        <v>-3.05</v>
       </c>
     </row>
     <row r="23" spans="1:5">
       <c r="A23" s="5" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B23" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C23" s="6">
-        <v>-1.8</v>
+        <v>1.82</v>
       </c>
       <c r="D23" s="6">
-        <v>-0.26</v>
+        <v>-0.7</v>
       </c>
       <c r="E23" s="7">
-        <v>1.54</v>
+        <v>-2.52</v>
       </c>
     </row>
     <row r="24" spans="1:5">
       <c r="A24" s="5" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B24" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C24" s="6">
-        <v>2.83</v>
+        <v>-6.39</v>
       </c>
       <c r="D24" s="6">
-        <v>4.25</v>
+        <v>-7.7</v>
       </c>
       <c r="E24" s="7">
-        <v>1.42</v>
+        <v>-1.31</v>
       </c>
     </row>
     <row r="25" spans="1:5">
       <c r="A25" s="5" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="C25" s="6">
-        <v>39.81</v>
+        <v>-0.26</v>
       </c>
       <c r="D25" s="6">
-        <v>38.35</v>
-      </c>
-      <c r="E25" s="8">
-        <v>-1.46</v>
+        <v>-1.84</v>
+      </c>
+      <c r="E25" s="7">
+        <v>-1.58</v>
       </c>
     </row>
     <row r="26" spans="1:5">
       <c r="A26" s="5" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="C26" s="6">
-        <v>-45.41</v>
+        <v>4.25</v>
       </c>
       <c r="D26" s="6">
-        <v>-45.38</v>
+        <v>2.71</v>
       </c>
       <c r="E26" s="7">
-        <v>0.03</v>
+        <v>-1.54</v>
       </c>
     </row>
     <row r="27" spans="1:5">
       <c r="A27" s="5" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B27" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C27" s="6">
-        <v>9.17</v>
+        <v>38.35</v>
       </c>
       <c r="D27" s="6">
-        <v>10.76</v>
+        <v>34.91</v>
       </c>
       <c r="E27" s="7">
-        <v>1.59</v>
+        <v>-3.44</v>
       </c>
     </row>
     <row r="28" spans="1:5">
       <c r="A28" s="5" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B28" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C28" s="6">
-        <v>29.72</v>
+        <v>-45.38</v>
       </c>
       <c r="D28" s="6">
-        <v>33.81</v>
+        <v>-47.82</v>
       </c>
       <c r="E28" s="7">
-        <v>4.09</v>
+        <v>-2.44</v>
       </c>
     </row>
     <row r="29" spans="1:5">
       <c r="A29" s="5" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B29" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C29" s="6">
-        <v>83.66</v>
+        <v>10.76</v>
       </c>
       <c r="D29" s="6">
-        <v>85.2</v>
+        <v>10.03</v>
       </c>
       <c r="E29" s="7">
-        <v>1.54</v>
+        <v>-0.73</v>
       </c>
     </row>
     <row r="30" spans="1:5">
       <c r="A30" s="5" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B30" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C30" s="6">
-        <v>98.08</v>
+        <v>33.81</v>
       </c>
       <c r="D30" s="6">
-        <v>92.51000000000001</v>
-      </c>
-      <c r="E30" s="8">
-        <v>-5.57</v>
+        <v>32.11</v>
+      </c>
+      <c r="E30" s="7">
+        <v>-1.7</v>
       </c>
     </row>
     <row r="31" spans="1:5">
       <c r="A31" s="5" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B31" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C31" s="6">
-        <v>-23.96</v>
+        <v>85.2</v>
       </c>
       <c r="D31" s="6">
-        <v>-25.3</v>
-      </c>
-      <c r="E31" s="8">
-        <v>-1.34</v>
+        <v>68.09999999999999</v>
+      </c>
+      <c r="E31" s="7">
+        <v>-17.1</v>
       </c>
     </row>
     <row r="32" spans="1:5">
       <c r="A32" s="5" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B32" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C32" s="6">
-        <v>-13.53</v>
+        <v>92.51000000000001</v>
       </c>
       <c r="D32" s="6">
-        <v>-11.65</v>
+        <v>80.51000000000001</v>
       </c>
       <c r="E32" s="7">
-        <v>1.88</v>
+        <v>-12</v>
       </c>
     </row>
     <row r="33" spans="1:5">
       <c r="A33" s="5" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="B33" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C33" s="6">
-        <v>3.45</v>
+        <v>-25.3</v>
       </c>
       <c r="D33" s="6">
-        <v>1.94</v>
-      </c>
-      <c r="E33" s="8">
-        <v>-1.51</v>
+        <v>-27.08</v>
+      </c>
+      <c r="E33" s="7">
+        <v>-1.78</v>
       </c>
     </row>
     <row r="34" spans="1:5">
       <c r="A34" s="5" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="B34" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C34" s="6">
-        <v>-17.32</v>
+        <v>-11.65</v>
       </c>
       <c r="D34" s="6">
-        <v>-20.31</v>
+        <v>-11.61</v>
       </c>
       <c r="E34" s="8">
-        <v>-2.99</v>
+        <v>0.04</v>
       </c>
     </row>
     <row r="35" spans="1:5">
       <c r="A35" s="5" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B35" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C35" s="6">
-        <v>-0.51</v>
+        <v>1.94</v>
       </c>
       <c r="D35" s="6">
-        <v>1.94</v>
+        <v>-0.18</v>
       </c>
       <c r="E35" s="7">
-        <v>2.45</v>
+        <v>-2.12</v>
       </c>
     </row>
     <row r="36" spans="1:5">
       <c r="A36" s="5" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B36" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C36" s="6">
-        <v>-1.4</v>
+        <v>-20.31</v>
       </c>
       <c r="D36" s="6">
-        <v>2.79</v>
-      </c>
-      <c r="E36" s="7">
-        <v>4.19</v>
+        <v>-20.06</v>
+      </c>
+      <c r="E36" s="8">
+        <v>0.25</v>
       </c>
     </row>
     <row r="37" spans="1:5">
       <c r="A37" s="5" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B37" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C37" s="6">
-        <v>-1.25</v>
+        <v>1.94</v>
       </c>
       <c r="D37" s="6">
-        <v>1.47</v>
+        <v>1.28</v>
       </c>
       <c r="E37" s="7">
-        <v>2.72</v>
+        <v>-0.66</v>
       </c>
     </row>
     <row r="38" spans="1:5">
       <c r="A38" s="5" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B38" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C38" s="6">
-        <v>-1.99</v>
+        <v>2.79</v>
       </c>
       <c r="D38" s="6">
-        <v>1.94</v>
-      </c>
-      <c r="E38" s="7">
-        <v>3.93</v>
+        <v>3.02</v>
+      </c>
+      <c r="E38" s="8">
+        <v>0.23</v>
       </c>
     </row>
     <row r="39" spans="1:5">
       <c r="A39" s="5" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B39" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C39" s="6">
-        <v>-7.56</v>
+        <v>1.47</v>
       </c>
       <c r="D39" s="6">
-        <v>-7.83</v>
-      </c>
-      <c r="E39" s="8">
-        <v>-0.27</v>
+        <v>0.43</v>
+      </c>
+      <c r="E39" s="7">
+        <v>-1.04</v>
       </c>
     </row>
     <row r="40" spans="1:5">
       <c r="A40" s="5" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B40" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C40" s="6">
-        <v>-2.72</v>
+        <v>1.94</v>
       </c>
       <c r="D40" s="6">
-        <v>-2.41</v>
-      </c>
-      <c r="E40" s="7">
-        <v>0.31</v>
+        <v>2.34</v>
+      </c>
+      <c r="E40" s="8">
+        <v>0.4</v>
       </c>
     </row>
     <row r="41" spans="1:5">
       <c r="A41" s="5" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="B41" s="5" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C41" s="6">
-        <v>-6.52</v>
+        <v>-7.83</v>
       </c>
       <c r="D41" s="6">
-        <v>-5.24</v>
+        <v>-8.880000000000001</v>
       </c>
       <c r="E41" s="7">
-        <v>1.28</v>
+        <v>-1.05</v>
       </c>
     </row>
     <row r="42" spans="1:5">
       <c r="A42" s="5" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="B42" s="5" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C42" s="6">
-        <v>-47.35</v>
+        <v>-2.41</v>
       </c>
       <c r="D42" s="6">
-        <v>-47.49</v>
-      </c>
-      <c r="E42" s="8">
-        <v>-0.14</v>
+        <v>-3.77</v>
+      </c>
+      <c r="E42" s="7">
+        <v>-1.36</v>
       </c>
     </row>
     <row r="43" spans="1:5">
       <c r="A43" s="5" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B43" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C43" s="6">
-        <v>-7.46</v>
+        <v>-5.24</v>
       </c>
       <c r="D43" s="6">
-        <v>-5.68</v>
+        <v>-8.15</v>
       </c>
       <c r="E43" s="7">
-        <v>1.78</v>
+        <v>-2.91</v>
       </c>
     </row>
     <row r="44" spans="1:5">
       <c r="A44" s="5" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B44" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C44" s="6">
-        <v>-15.37</v>
+        <v>-47.49</v>
       </c>
       <c r="D44" s="6">
-        <v>-12.69</v>
+        <v>-48.59</v>
       </c>
       <c r="E44" s="7">
-        <v>2.68</v>
+        <v>-1.1</v>
       </c>
     </row>
     <row r="45" spans="1:5">
       <c r="A45" s="5" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B45" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C45" s="6">
-        <v>-8.529999999999999</v>
+        <v>-5.68</v>
       </c>
       <c r="D45" s="6">
-        <v>-6.92</v>
+        <v>-6.33</v>
       </c>
       <c r="E45" s="7">
-        <v>1.61</v>
+        <v>-0.65</v>
       </c>
     </row>
     <row r="46" spans="1:5">
       <c r="A46" s="5" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B46" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C46" s="6">
-        <v>-18.46</v>
+        <v>-12.69</v>
       </c>
       <c r="D46" s="6">
-        <v>-16.88</v>
+        <v>-14.59</v>
       </c>
       <c r="E46" s="7">
-        <v>1.58</v>
+        <v>-1.9</v>
       </c>
     </row>
     <row r="47" spans="1:5">
       <c r="A47" s="5" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B47" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C47" s="6">
-        <v>-31</v>
+        <v>-6.92</v>
       </c>
       <c r="D47" s="6">
-        <v>-30.43</v>
+        <v>-9.49</v>
       </c>
       <c r="E47" s="7">
-        <v>0.57</v>
+        <v>-2.57</v>
       </c>
     </row>
     <row r="48" spans="1:5">
       <c r="A48" s="5" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B48" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C48" s="6">
-        <v>-15.72</v>
+        <v>-16.88</v>
       </c>
       <c r="D48" s="6">
-        <v>-14.53</v>
+        <v>-18.18</v>
       </c>
       <c r="E48" s="7">
-        <v>1.19</v>
+        <v>-1.3</v>
       </c>
     </row>
     <row r="49" spans="1:5">
       <c r="A49" s="5" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="B49" s="5" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C49" s="6">
-        <v>397</v>
+        <v>-30.43</v>
       </c>
       <c r="D49" s="6">
-        <v>402.45</v>
+        <v>-31.03</v>
       </c>
       <c r="E49" s="7">
-        <v>5.45</v>
+        <v>-0.6</v>
       </c>
     </row>
     <row r="50" spans="1:5">
       <c r="A50" s="5" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="B50" s="5" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C50" s="6">
-        <v>49.22</v>
+        <v>-14.53</v>
       </c>
       <c r="D50" s="6">
-        <v>49.09</v>
-      </c>
-      <c r="E50" s="8">
-        <v>-0.13</v>
+        <v>-15.29</v>
+      </c>
+      <c r="E50" s="7">
+        <v>-0.76</v>
       </c>
     </row>
     <row r="51" spans="1:5">
       <c r="A51" s="5" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B51" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C51" s="6">
-        <v>3128.2</v>
+        <v>402.45</v>
       </c>
       <c r="D51" s="6">
-        <v>3188.5</v>
+        <v>390.1</v>
       </c>
       <c r="E51" s="7">
-        <v>60.3</v>
+        <v>-12.35</v>
       </c>
     </row>
     <row r="52" spans="1:5">
       <c r="A52" s="5" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B52" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C52" s="6">
-        <v>973</v>
+        <v>49.09</v>
       </c>
       <c r="D52" s="6">
-        <v>1003.8</v>
+        <v>48.06</v>
       </c>
       <c r="E52" s="7">
-        <v>30.8</v>
+        <v>-1.03</v>
       </c>
     </row>
     <row r="53" spans="1:5">
       <c r="A53" s="5" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B53" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C53" s="6">
-        <v>14.27</v>
+        <v>3188.5</v>
       </c>
       <c r="D53" s="6">
-        <v>14.52</v>
+        <v>3166.5</v>
       </c>
       <c r="E53" s="7">
-        <v>0.25</v>
+        <v>-22</v>
       </c>
     </row>
     <row r="54" spans="1:5">
       <c r="A54" s="5" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B54" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C54" s="6">
-        <v>11.35</v>
+        <v>1003.8</v>
       </c>
       <c r="D54" s="6">
-        <v>11.57</v>
+        <v>982</v>
       </c>
       <c r="E54" s="7">
-        <v>0.22</v>
+        <v>-21.8</v>
       </c>
     </row>
     <row r="55" spans="1:5">
       <c r="A55" s="5" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B55" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C55" s="6">
-        <v>4008.3</v>
+        <v>14.52</v>
       </c>
       <c r="D55" s="6">
-        <v>4041.8</v>
+        <v>14.12</v>
       </c>
       <c r="E55" s="7">
-        <v>33.5</v>
+        <v>-0.4</v>
       </c>
     </row>
     <row r="56" spans="1:5">
       <c r="A56" s="5" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B56" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C56" s="6">
-        <v>11000</v>
+        <v>11.57</v>
       </c>
       <c r="D56" s="6">
-        <v>11155</v>
+        <v>11.39</v>
       </c>
       <c r="E56" s="7">
-        <v>155</v>
+        <v>-0.18</v>
       </c>
     </row>
     <row r="57" spans="1:5">
       <c r="A57" s="5" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="B57" s="5" t="s">
-        <v>24</v>
+        <v>2</v>
       </c>
       <c r="C57" s="6">
-        <v>48.4</v>
+        <v>4041.8</v>
       </c>
       <c r="D57" s="6">
-        <v>51.58</v>
+        <v>4007.1</v>
       </c>
       <c r="E57" s="7">
-        <v>3.18</v>
+        <v>-34.7</v>
       </c>
     </row>
     <row r="58" spans="1:5">
       <c r="A58" s="5" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="B58" s="5" t="s">
-        <v>24</v>
+        <v>2</v>
       </c>
       <c r="C58" s="6">
-        <v>33.15</v>
+        <v>11155</v>
       </c>
       <c r="D58" s="6">
-        <v>32.71</v>
-      </c>
-      <c r="E58" s="8">
-        <v>-0.44</v>
+        <v>11056</v>
+      </c>
+      <c r="E58" s="7">
+        <v>-99</v>
       </c>
     </row>
     <row r="59" spans="1:5">
       <c r="A59" s="5" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B59" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C59" s="6">
-        <v>36.78</v>
+        <v>51.58</v>
       </c>
       <c r="D59" s="6">
-        <v>44.7</v>
+        <v>44.84</v>
       </c>
       <c r="E59" s="7">
-        <v>7.92</v>
+        <v>-6.74</v>
       </c>
     </row>
     <row r="60" spans="1:5">
       <c r="A60" s="5" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B60" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C60" s="6">
-        <v>40.32</v>
+        <v>32.71</v>
       </c>
       <c r="D60" s="6">
-        <v>50.46</v>
+        <v>29.34</v>
       </c>
       <c r="E60" s="7">
-        <v>10.14</v>
+        <v>-3.37</v>
       </c>
     </row>
     <row r="61" spans="1:5">
       <c r="A61" s="5" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B61" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C61" s="6">
-        <v>48.83</v>
+        <v>44.7</v>
       </c>
       <c r="D61" s="6">
-        <v>52.22</v>
+        <v>42.6</v>
       </c>
       <c r="E61" s="7">
-        <v>3.39</v>
+        <v>-2.1</v>
       </c>
     </row>
     <row r="62" spans="1:5">
       <c r="A62" s="5" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B62" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C62" s="6">
-        <v>44.3</v>
+        <v>50.46</v>
       </c>
       <c r="D62" s="6">
-        <v>48.06</v>
+        <v>44.68</v>
       </c>
       <c r="E62" s="7">
-        <v>3.76</v>
+        <v>-5.78</v>
       </c>
     </row>
     <row r="63" spans="1:5">
       <c r="A63" s="5" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B63" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C63" s="6">
-        <v>31.88</v>
+        <v>52.22</v>
       </c>
       <c r="D63" s="6">
-        <v>35.51</v>
+        <v>46.87</v>
       </c>
       <c r="E63" s="7">
-        <v>3.63</v>
+        <v>-5.35</v>
       </c>
     </row>
     <row r="64" spans="1:5">
       <c r="A64" s="5" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B64" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C64" s="6">
-        <v>41.94</v>
+        <v>48.06</v>
       </c>
       <c r="D64" s="6">
-        <v>47.6</v>
+        <v>45.36</v>
       </c>
       <c r="E64" s="7">
-        <v>5.66</v>
+        <v>-2.7</v>
       </c>
     </row>
     <row r="65" spans="1:5">
       <c r="A65" s="5" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="B65" s="5" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="C65" s="6">
-        <v>-11.32</v>
+        <v>35.51</v>
       </c>
       <c r="D65" s="6">
-        <v>-25.14</v>
-      </c>
-      <c r="E65" s="8">
-        <v>-13.82</v>
+        <v>33.52</v>
+      </c>
+      <c r="E65" s="7">
+        <v>-1.99</v>
       </c>
     </row>
     <row r="66" spans="1:5">
       <c r="A66" s="5" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="B66" s="5" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="C66" s="6">
-        <v>-38.35</v>
+        <v>47.6</v>
       </c>
       <c r="D66" s="6">
-        <v>-38.57</v>
-      </c>
-      <c r="E66" s="8">
-        <v>-0.22</v>
+        <v>44.61</v>
+      </c>
+      <c r="E66" s="7">
+        <v>-2.99</v>
       </c>
     </row>
     <row r="67" spans="1:5">
       <c r="A67" s="5" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B67" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C67" s="6">
-        <v>-33.13</v>
+        <v>-25.14</v>
       </c>
       <c r="D67" s="6">
-        <v>-58.83</v>
+        <v>55.16</v>
       </c>
       <c r="E67" s="8">
-        <v>-25.7</v>
+        <v>80.3</v>
       </c>
     </row>
     <row r="68" spans="1:5">
       <c r="A68" s="5" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B68" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C68" s="6">
-        <v>2.18</v>
+        <v>-38.57</v>
       </c>
       <c r="D68" s="6">
-        <v>56.4</v>
-      </c>
-      <c r="E68" s="7">
-        <v>54.22</v>
+        <v>15.66</v>
+      </c>
+      <c r="E68" s="8">
+        <v>54.23</v>
       </c>
     </row>
     <row r="69" spans="1:5">
       <c r="A69" s="5" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B69" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C69" s="6">
-        <v>12.88</v>
+        <v>-58.83</v>
       </c>
       <c r="D69" s="6">
-        <v>-43.76</v>
+        <v>-49.97</v>
       </c>
       <c r="E69" s="8">
-        <v>-56.64</v>
+        <v>8.859999999999999</v>
       </c>
     </row>
     <row r="70" spans="1:5">
       <c r="A70" s="5" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B70" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C70" s="6">
-        <v>-4.79</v>
+        <v>56.4</v>
       </c>
       <c r="D70" s="6">
-        <v>-1.54</v>
+        <v>29.25</v>
       </c>
       <c r="E70" s="7">
-        <v>3.25</v>
+        <v>-27.15</v>
       </c>
     </row>
     <row r="71" spans="1:5">
       <c r="A71" s="5" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B71" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C71" s="6">
-        <v>-37.81</v>
+        <v>-43.76</v>
       </c>
       <c r="D71" s="6">
-        <v>-68.31999999999999</v>
+        <v>-25.07</v>
       </c>
       <c r="E71" s="8">
-        <v>-30.51</v>
+        <v>18.69</v>
       </c>
     </row>
     <row r="72" spans="1:5">
       <c r="A72" s="5" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B72" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C72" s="6">
-        <v>23.29</v>
+        <v>-1.54</v>
       </c>
       <c r="D72" s="6">
+        <v>-38.81</v>
+      </c>
+      <c r="E72" s="7">
+        <v>-37.27</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5">
+      <c r="A73" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B73" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C73" s="6">
+        <v>-68.31999999999999</v>
+      </c>
+      <c r="D73" s="6">
+        <v>-38.8</v>
+      </c>
+      <c r="E73" s="8">
+        <v>29.52</v>
+      </c>
+    </row>
+    <row r="74" spans="1:5">
+      <c r="A74" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="B74" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C74" s="6">
         <v>-18.97</v>
       </c>
-      <c r="E72" s="8">
-        <v>-42.26</v>
+      <c r="D74" s="6">
+        <v>14.87</v>
+      </c>
+      <c r="E74" s="8">
+        <v>33.84</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A7:E7"/>
+    <mergeCell ref="A9:E9"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3219,28 +3265,28 @@
         <v>1</v>
       </c>
       <c r="B1" s="9" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="C1" s="9" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="D1" s="9" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="E1" s="9" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="F1" s="9" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="G1" s="9" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="H1" s="9" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="I1" s="9" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -3254,22 +3300,22 @@
         <v>8</v>
       </c>
       <c r="D2" s="11">
-        <v>45.4</v>
+        <v>41.5</v>
       </c>
       <c r="E2" s="11">
         <v>60</v>
       </c>
       <c r="F2" s="11">
-        <v>-3.1</v>
+        <v>-5.8</v>
       </c>
       <c r="G2" s="11">
-        <v>-2.6</v>
+        <v>-3.2</v>
       </c>
       <c r="H2" s="11">
         <v>56.1</v>
       </c>
       <c r="I2" s="11">
-        <v>40</v>
+        <v>20</v>
       </c>
     </row>
   </sheetData>
@@ -3374,10 +3420,10 @@
         <v>37</v>
       </c>
       <c r="B1" s="13" t="s">
+        <v>43</v>
+      </c>
+      <c r="C1" s="13" t="s">
         <v>40</v>
-      </c>
-      <c r="C1" s="13" t="s">
-        <v>43</v>
       </c>
       <c r="D1" s="13" t="s">
         <v>39</v>
@@ -3397,28 +3443,28 @@
     </row>
     <row r="2" spans="1:8">
       <c r="A2" s="14">
-        <v>0.289</v>
+        <v>0.2758</v>
       </c>
       <c r="B2" s="14">
-        <v>0.1641</v>
+        <v>0.1645</v>
       </c>
       <c r="C2" s="14">
-        <v>0.1628</v>
+        <v>0.1612</v>
       </c>
       <c r="D2" s="14">
-        <v>0.1522</v>
+        <v>0.1474</v>
       </c>
       <c r="E2" s="14">
-        <v>0.08410000000000001</v>
+        <v>0.08500000000000001</v>
       </c>
       <c r="F2" s="14">
-        <v>0.066</v>
+        <v>0.04190000000000001</v>
       </c>
       <c r="G2" s="14">
-        <v>-0.2583</v>
+        <v>-0.2649</v>
       </c>
       <c r="H2" s="14">
-        <v>-0.3079</v>
+        <v>-0.3081</v>
       </c>
     </row>
   </sheetData>

--- a/BIRLA_GROUP_Technical_Metrics.xlsx
+++ b/BIRLA_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="311" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="287" uniqueCount="74">
   <si>
     <t>Symbol</t>
   </si>
@@ -190,43 +190,19 @@
     <t>Curr Value</t>
   </si>
   <si>
-    <t>RSI Momentum</t>
-  </si>
-  <si>
-    <t>51.6 → 44.8</t>
-  </si>
-  <si>
-    <t>🔴 BEARISH</t>
-  </si>
-  <si>
-    <t>51.6</t>
-  </si>
-  <si>
-    <t>44.8</t>
-  </si>
-  <si>
-    <t>Yes → No</t>
-  </si>
-  <si>
-    <t>20 DMA &gt; 50 DMA</t>
-  </si>
-  <si>
-    <t>50.5 → 44.7</t>
-  </si>
-  <si>
-    <t>50.5</t>
-  </si>
-  <si>
-    <t>44.7</t>
-  </si>
-  <si>
-    <t>52.2 → 46.9</t>
-  </si>
-  <si>
-    <t>52.2</t>
-  </si>
-  <si>
-    <t>46.9</t>
+    <t>RSI Oversold Recovery</t>
+  </si>
+  <si>
+    <t>29.3 → 36.7</t>
+  </si>
+  <si>
+    <t>🟢 BULLISH</t>
+  </si>
+  <si>
+    <t>29.3</t>
+  </si>
+  <si>
+    <t>36.7</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -312,14 +288,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF006100"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF9C0006"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -352,13 +328,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -811,15 +787,14 @@
     <col min="14" max="14" width="11.7109375" customWidth="1"/>
     <col min="15" max="15" width="10.7109375" customWidth="1"/>
     <col min="16" max="16" width="9.7109375" customWidth="1"/>
-    <col min="17" max="17" width="10.7109375" customWidth="1"/>
-    <col min="18" max="19" width="9.7109375" customWidth="1"/>
+    <col min="17" max="19" width="10.7109375" customWidth="1"/>
     <col min="20" max="20" width="22.7109375" customWidth="1"/>
     <col min="21" max="21" width="9.7109375" customWidth="1"/>
     <col min="22" max="22" width="10.7109375" customWidth="1"/>
     <col min="23" max="23" width="16.7109375" customWidth="1"/>
     <col min="24" max="24" width="13.7109375" customWidth="1"/>
     <col min="25" max="25" width="7.7109375" customWidth="1"/>
-    <col min="26" max="26" width="8.7109375" customWidth="1"/>
+    <col min="26" max="26" width="9.7109375" customWidth="1"/>
     <col min="27" max="27" width="13.7109375" customWidth="1"/>
     <col min="28" max="28" width="11.7109375" customWidth="1"/>
     <col min="29" max="30" width="13.7109375" customWidth="1"/>
@@ -952,10 +927,10 @@
         <v>45</v>
       </c>
       <c r="C2">
-        <v>390.1</v>
+        <v>390</v>
       </c>
       <c r="D2">
-        <v>-3.07</v>
+        <v>-0.03</v>
       </c>
       <c r="E2">
         <v>424.7</v>
@@ -964,46 +939,46 @@
         <v>278.9</v>
       </c>
       <c r="G2">
-        <v>-8.15</v>
+        <v>-8.17</v>
       </c>
       <c r="H2">
-        <v>39.87</v>
+        <v>39.84</v>
       </c>
       <c r="I2">
-        <v>0.03</v>
+        <v>-4.89</v>
       </c>
       <c r="J2">
-        <v>-5.05</v>
+        <v>-4.88</v>
       </c>
       <c r="K2">
-        <v>-0.18</v>
+        <v>1.22</v>
       </c>
       <c r="L2">
-        <v>34.91</v>
+        <v>35.35</v>
       </c>
       <c r="M2">
-        <v>27.58</v>
+        <v>27.26</v>
       </c>
       <c r="N2">
         <v>74</v>
       </c>
       <c r="O2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="P2">
-        <v>400.6</v>
+        <v>396.59</v>
       </c>
       <c r="Q2">
-        <v>398.58</v>
+        <v>397.58</v>
       </c>
       <c r="R2">
-        <v>402.86</v>
+        <v>402.67</v>
       </c>
       <c r="S2">
-        <v>364.01</v>
+        <v>364.17</v>
       </c>
       <c r="T2">
-        <v>7.17</v>
+        <v>7.09</v>
       </c>
       <c r="U2" t="s">
         <v>46</v>
@@ -1018,34 +993,34 @@
         <v>2</v>
       </c>
       <c r="Y2">
-        <v>44.84</v>
+        <v>44.79</v>
       </c>
       <c r="Z2">
-        <v>-1.97</v>
+        <v>-2.39</v>
       </c>
       <c r="AA2">
-        <v>-1.98</v>
+        <v>-2.06</v>
       </c>
       <c r="AB2">
-        <v>0.01</v>
+        <v>-0.33</v>
       </c>
       <c r="AC2">
-        <v>64.20999999999999</v>
+        <v>58.86</v>
       </c>
       <c r="AD2">
-        <v>73.76000000000001</v>
+        <v>66.03</v>
       </c>
       <c r="AE2">
-        <v>10.1</v>
+        <v>9.91</v>
       </c>
       <c r="AF2">
-        <v>55.16</v>
+        <v>5.17</v>
       </c>
       <c r="AG2">
-        <v>415.85</v>
+        <v>414.37</v>
       </c>
       <c r="AH2">
-        <v>381.32</v>
+        <v>380.79</v>
       </c>
       <c r="AI2">
         <v>372.91</v>
@@ -1054,7 +1029,7 @@
         <v>48</v>
       </c>
       <c r="AK2">
-        <v>22.97</v>
+        <v>23.38</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1065,58 +1040,58 @@
         <v>45</v>
       </c>
       <c r="C3">
-        <v>48.06</v>
+        <v>49.14</v>
       </c>
       <c r="D3">
-        <v>-2.1</v>
+        <v>2.25</v>
       </c>
       <c r="E3">
-        <v>93.48</v>
+        <v>92.03</v>
       </c>
       <c r="F3">
         <v>48.06</v>
       </c>
       <c r="G3">
-        <v>-48.59</v>
+        <v>-46.6</v>
       </c>
       <c r="H3">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="I3">
-        <v>-4.74</v>
+        <v>-2.03</v>
       </c>
       <c r="J3">
-        <v>-11.78</v>
+        <v>-9.869999999999999</v>
       </c>
       <c r="K3">
-        <v>-20.06</v>
+        <v>-16.43</v>
       </c>
       <c r="L3">
-        <v>-47.82</v>
+        <v>-47.43</v>
       </c>
       <c r="M3">
-        <v>-26.49</v>
+        <v>-26.32</v>
       </c>
       <c r="N3">
         <v>13</v>
       </c>
       <c r="O3">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="P3">
-        <v>49.28</v>
+        <v>49.07</v>
       </c>
       <c r="Q3">
-        <v>50.84</v>
+        <v>50.62</v>
       </c>
       <c r="R3">
-        <v>54.95</v>
+        <v>54.76</v>
       </c>
       <c r="S3">
-        <v>62.99</v>
+        <v>62.86</v>
       </c>
       <c r="T3">
-        <v>-23.7</v>
+        <v>-21.83</v>
       </c>
       <c r="U3" t="s">
         <v>46</v>
@@ -1131,34 +1106,34 @@
         <v>0</v>
       </c>
       <c r="Y3">
-        <v>29.34</v>
+        <v>36.7</v>
       </c>
       <c r="Z3">
-        <v>-1.77</v>
+        <v>-1.71</v>
       </c>
       <c r="AA3">
-        <v>-1.75</v>
+        <v>-1.74</v>
       </c>
       <c r="AB3">
-        <v>-0.02</v>
+        <v>0.03</v>
       </c>
       <c r="AC3">
-        <v>32.44</v>
+        <v>36.33</v>
       </c>
       <c r="AD3">
-        <v>47.31</v>
+        <v>39.97</v>
       </c>
       <c r="AE3">
         <v>1.45</v>
       </c>
       <c r="AF3">
-        <v>15.66</v>
+        <v>2.98</v>
       </c>
       <c r="AG3">
-        <v>53.91</v>
+        <v>53.47</v>
       </c>
       <c r="AH3">
-        <v>47.78</v>
+        <v>47.77</v>
       </c>
       <c r="AI3">
         <v>52.83</v>
@@ -1167,7 +1142,7 @@
         <v>49</v>
       </c>
       <c r="AK3">
-        <v>37.94</v>
+        <v>38.95</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1178,10 +1153,10 @@
         <v>45</v>
       </c>
       <c r="C4">
-        <v>3166.5</v>
+        <v>3191</v>
       </c>
       <c r="D4">
-        <v>-0.6899999999999999</v>
+        <v>0.77</v>
       </c>
       <c r="E4">
         <v>3380.5</v>
@@ -1190,46 +1165,46 @@
         <v>2531.1</v>
       </c>
       <c r="G4">
-        <v>-6.33</v>
+        <v>-5.61</v>
       </c>
       <c r="H4">
-        <v>25.1</v>
+        <v>26.07</v>
       </c>
       <c r="I4">
-        <v>-0.21</v>
+        <v>-0.57</v>
       </c>
       <c r="J4">
-        <v>-3.74</v>
+        <v>-3.3</v>
       </c>
       <c r="K4">
-        <v>1.28</v>
+        <v>3.6</v>
       </c>
       <c r="L4">
-        <v>10.03</v>
+        <v>11.8</v>
       </c>
       <c r="M4">
-        <v>14.74</v>
+        <v>14.67</v>
       </c>
       <c r="N4">
         <v>50</v>
       </c>
       <c r="O4">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="P4">
-        <v>3171.68</v>
+        <v>3168.04</v>
       </c>
       <c r="Q4">
-        <v>3252.52</v>
+        <v>3249.17</v>
       </c>
       <c r="R4">
-        <v>3228.77</v>
+        <v>3231.13</v>
       </c>
       <c r="S4">
-        <v>2968.87</v>
+        <v>2971.1</v>
       </c>
       <c r="T4">
-        <v>6.66</v>
+        <v>7.4</v>
       </c>
       <c r="U4" t="s">
         <v>47</v>
@@ -1244,34 +1219,34 @@
         <v>3</v>
       </c>
       <c r="Y4">
-        <v>42.6</v>
+        <v>45.66</v>
       </c>
       <c r="Z4">
-        <v>-25.1</v>
+        <v>-24.4</v>
       </c>
       <c r="AA4">
-        <v>-9.42</v>
+        <v>-12.42</v>
       </c>
       <c r="AB4">
-        <v>-15.68</v>
+        <v>-11.99</v>
       </c>
       <c r="AC4">
-        <v>23.03</v>
+        <v>38.45</v>
       </c>
       <c r="AD4">
-        <v>16.72</v>
+        <v>25.91</v>
       </c>
       <c r="AE4">
-        <v>59.7</v>
+        <v>59.12</v>
       </c>
       <c r="AF4">
-        <v>-49.97</v>
+        <v>-12.22</v>
       </c>
       <c r="AG4">
-        <v>3393.71</v>
+        <v>3392.97</v>
       </c>
       <c r="AH4">
-        <v>3111.34</v>
+        <v>3105.38</v>
       </c>
       <c r="AI4">
         <v>3120.02</v>
@@ -1280,7 +1255,7 @@
         <v>48</v>
       </c>
       <c r="AK4">
-        <v>36.88</v>
+        <v>35.62</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1291,10 +1266,10 @@
         <v>45</v>
       </c>
       <c r="C5">
-        <v>982</v>
+        <v>977</v>
       </c>
       <c r="D5">
-        <v>-2.17</v>
+        <v>-0.51</v>
       </c>
       <c r="E5">
         <v>1149.7</v>
@@ -1303,46 +1278,46 @@
         <v>741.05</v>
       </c>
       <c r="G5">
-        <v>-14.59</v>
+        <v>-15.02</v>
       </c>
       <c r="H5">
-        <v>32.51</v>
+        <v>31.84</v>
       </c>
       <c r="I5">
-        <v>0.15</v>
+        <v>-0.96</v>
       </c>
       <c r="J5">
-        <v>-6.57</v>
+        <v>-7.22</v>
       </c>
       <c r="K5">
-        <v>3.02</v>
+        <v>1.37</v>
       </c>
       <c r="L5">
-        <v>32.11</v>
+        <v>31.02</v>
       </c>
       <c r="M5">
-        <v>16.12</v>
+        <v>15.89</v>
       </c>
       <c r="N5">
         <v>62</v>
       </c>
       <c r="O5">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="P5">
-        <v>985.3</v>
+        <v>983.4</v>
       </c>
       <c r="Q5">
-        <v>999.89</v>
+        <v>997.54</v>
       </c>
       <c r="R5">
-        <v>1003.87</v>
+        <v>1004.23</v>
       </c>
       <c r="S5">
-        <v>977.95</v>
+        <v>978.74</v>
       </c>
       <c r="T5">
-        <v>0.41</v>
+        <v>-0.18</v>
       </c>
       <c r="U5" t="s">
         <v>46</v>
@@ -1354,37 +1329,37 @@
         <v>46</v>
       </c>
       <c r="X5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y5">
-        <v>44.68</v>
+        <v>43.44</v>
       </c>
       <c r="Z5">
-        <v>-9.779999999999999</v>
+        <v>-10.14</v>
       </c>
       <c r="AA5">
-        <v>-8.15</v>
+        <v>-8.550000000000001</v>
       </c>
       <c r="AB5">
-        <v>-1.63</v>
+        <v>-1.59</v>
       </c>
       <c r="AC5">
-        <v>59.69</v>
+        <v>65.38</v>
       </c>
       <c r="AD5">
-        <v>53.01</v>
+        <v>60.25</v>
       </c>
       <c r="AE5">
-        <v>23.18</v>
+        <v>22.39</v>
       </c>
       <c r="AF5">
-        <v>29.25</v>
+        <v>-27.17</v>
       </c>
       <c r="AG5">
-        <v>1042.31</v>
+        <v>1039.54</v>
       </c>
       <c r="AH5">
-        <v>957.46</v>
+        <v>955.53</v>
       </c>
       <c r="AI5">
         <v>1037.86</v>
@@ -1393,7 +1368,7 @@
         <v>49</v>
       </c>
       <c r="AK5">
-        <v>19.5</v>
+        <v>18.38</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1404,10 +1379,10 @@
         <v>45</v>
       </c>
       <c r="C6">
-        <v>14.12</v>
+        <v>14.26</v>
       </c>
       <c r="D6">
-        <v>-2.75</v>
+        <v>0.99</v>
       </c>
       <c r="E6">
         <v>15.6</v>
@@ -1416,25 +1391,25 @@
         <v>8.02</v>
       </c>
       <c r="G6">
-        <v>-9.49</v>
+        <v>-8.59</v>
       </c>
       <c r="H6">
-        <v>76.06</v>
+        <v>77.81</v>
       </c>
       <c r="I6">
-        <v>-0.7</v>
+        <v>2.44</v>
       </c>
       <c r="J6">
-        <v>-7.04</v>
+        <v>-5.31</v>
       </c>
       <c r="K6">
-        <v>0.43</v>
+        <v>-1.18</v>
       </c>
       <c r="L6">
-        <v>68.09999999999999</v>
+        <v>69.95999999999999</v>
       </c>
       <c r="M6">
-        <v>4.19</v>
+        <v>4.68</v>
       </c>
       <c r="N6">
         <v>87</v>
@@ -1443,19 +1418,19 @@
         <v>86</v>
       </c>
       <c r="P6">
-        <v>14.13</v>
+        <v>14.2</v>
       </c>
       <c r="Q6">
-        <v>14.6</v>
+        <v>14.57</v>
       </c>
       <c r="R6">
-        <v>13.93</v>
+        <v>13.94</v>
       </c>
       <c r="S6">
-        <v>12.18</v>
+        <v>12.2</v>
       </c>
       <c r="T6">
-        <v>15.91</v>
+        <v>16.87</v>
       </c>
       <c r="U6" t="s">
         <v>47</v>
@@ -1470,34 +1445,34 @@
         <v>3</v>
       </c>
       <c r="Y6">
-        <v>46.87</v>
+        <v>48.85</v>
       </c>
       <c r="Z6">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="AA6">
-        <v>0.14</v>
+        <v>0.11</v>
       </c>
       <c r="AB6">
-        <v>-0.12</v>
+        <v>-0.1</v>
       </c>
       <c r="AC6">
-        <v>27.02</v>
+        <v>27.04</v>
       </c>
       <c r="AD6">
-        <v>18.85</v>
+        <v>25.07</v>
       </c>
       <c r="AE6">
-        <v>0.48</v>
+        <v>0.47</v>
       </c>
       <c r="AF6">
-        <v>-25.07</v>
+        <v>-28.09</v>
       </c>
       <c r="AG6">
-        <v>15.64</v>
+        <v>15.6</v>
       </c>
       <c r="AH6">
-        <v>13.57</v>
+        <v>13.53</v>
       </c>
       <c r="AI6">
         <v>15.41</v>
@@ -1506,7 +1481,7 @@
         <v>49</v>
       </c>
       <c r="AK6">
-        <v>23.85</v>
+        <v>22.29</v>
       </c>
     </row>
     <row r="7" spans="1:37">
@@ -1517,10 +1492,10 @@
         <v>45</v>
       </c>
       <c r="C7">
-        <v>11.39</v>
+        <v>11.57</v>
       </c>
       <c r="D7">
-        <v>-1.56</v>
+        <v>1.58</v>
       </c>
       <c r="E7">
         <v>13.92</v>
@@ -1529,46 +1504,46 @@
         <v>4.69</v>
       </c>
       <c r="G7">
-        <v>-18.18</v>
+        <v>-16.88</v>
       </c>
       <c r="H7">
-        <v>142.86</v>
+        <v>146.7</v>
       </c>
       <c r="I7">
-        <v>-7.7</v>
+        <v>-3.1</v>
       </c>
       <c r="J7">
-        <v>0.53</v>
+        <v>4.14</v>
       </c>
       <c r="K7">
-        <v>2.34</v>
+        <v>1.94</v>
       </c>
       <c r="L7">
-        <v>80.51000000000001</v>
+        <v>91.87</v>
       </c>
       <c r="M7">
-        <v>-30.81</v>
+        <v>-29.87</v>
       </c>
       <c r="N7">
         <v>99</v>
       </c>
       <c r="O7">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="P7">
-        <v>11.58</v>
+        <v>11.51</v>
       </c>
       <c r="Q7">
-        <v>11.54</v>
+        <v>11.56</v>
       </c>
       <c r="R7">
-        <v>11.79</v>
+        <v>11.8</v>
       </c>
       <c r="S7">
-        <v>10.74</v>
+        <v>10.76</v>
       </c>
       <c r="T7">
-        <v>6.07</v>
+        <v>7.56</v>
       </c>
       <c r="U7" t="s">
         <v>46</v>
@@ -1583,34 +1558,34 @@
         <v>2</v>
       </c>
       <c r="Y7">
-        <v>45.36</v>
+        <v>48.47</v>
       </c>
       <c r="Z7">
-        <v>0.01</v>
+        <v>-0</v>
       </c>
       <c r="AA7">
-        <v>0.03</v>
+        <v>0.02</v>
       </c>
       <c r="AB7">
         <v>-0.02</v>
       </c>
       <c r="AC7">
-        <v>29.06</v>
+        <v>29.49</v>
       </c>
       <c r="AD7">
-        <v>33.82</v>
+        <v>30.54</v>
       </c>
       <c r="AE7">
-        <v>0.43</v>
+        <v>0.46</v>
       </c>
       <c r="AF7">
-        <v>-38.81</v>
+        <v>-8.359999999999999</v>
       </c>
       <c r="AG7">
         <v>12.52</v>
       </c>
       <c r="AH7">
-        <v>10.56</v>
+        <v>10.61</v>
       </c>
       <c r="AI7">
         <v>12.59</v>
@@ -1619,7 +1594,7 @@
         <v>49</v>
       </c>
       <c r="AK7">
-        <v>29.05</v>
+        <v>28.38</v>
       </c>
     </row>
     <row r="8" spans="1:37">
@@ -1630,10 +1605,10 @@
         <v>45</v>
       </c>
       <c r="C8">
-        <v>4007.1</v>
+        <v>4015</v>
       </c>
       <c r="D8">
-        <v>-0.86</v>
+        <v>0.2</v>
       </c>
       <c r="E8">
         <v>5809.5</v>
@@ -1642,46 +1617,46 @@
         <v>4007.1</v>
       </c>
       <c r="G8">
-        <v>-31.03</v>
+        <v>-30.89</v>
       </c>
       <c r="H8">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="I8">
-        <v>-1.84</v>
+        <v>-1.28</v>
       </c>
       <c r="J8">
-        <v>-8.83</v>
+        <v>-9.26</v>
       </c>
       <c r="K8">
-        <v>-8.880000000000001</v>
+        <v>-7.66</v>
       </c>
       <c r="L8">
-        <v>-27.08</v>
+        <v>-25.03</v>
       </c>
       <c r="M8">
-        <v>16.45</v>
+        <v>16.76</v>
       </c>
       <c r="N8">
         <v>26</v>
       </c>
       <c r="O8">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="P8">
-        <v>4030.26</v>
+        <v>4019.86</v>
       </c>
       <c r="Q8">
-        <v>4196.33</v>
+        <v>4178.9</v>
       </c>
       <c r="R8">
-        <v>4300</v>
+        <v>4292.07</v>
       </c>
       <c r="S8">
-        <v>4559.5</v>
+        <v>4553.89</v>
       </c>
       <c r="T8">
-        <v>-12.12</v>
+        <v>-11.83</v>
       </c>
       <c r="U8" t="s">
         <v>46</v>
@@ -1696,43 +1671,43 @@
         <v>0</v>
       </c>
       <c r="Y8">
-        <v>33.52</v>
+        <v>34.42</v>
       </c>
       <c r="Z8">
-        <v>-91.98</v>
+        <v>-91.95999999999999</v>
       </c>
       <c r="AA8">
-        <v>-73.8</v>
+        <v>-77.44</v>
       </c>
       <c r="AB8">
-        <v>-18.18</v>
+        <v>-14.53</v>
       </c>
       <c r="AC8">
-        <v>19.43</v>
+        <v>27.16</v>
       </c>
       <c r="AD8">
-        <v>17.49</v>
+        <v>21.22</v>
       </c>
       <c r="AE8">
-        <v>97.97</v>
+        <v>95.23</v>
       </c>
       <c r="AF8">
-        <v>-38.8</v>
+        <v>-55.64</v>
       </c>
       <c r="AG8">
-        <v>4480.29</v>
+        <v>4462.39</v>
       </c>
       <c r="AH8">
-        <v>3912.38</v>
+        <v>3895.4</v>
       </c>
       <c r="AI8">
-        <v>4318.07</v>
+        <v>4295.89</v>
       </c>
       <c r="AJ8" t="s">
         <v>49</v>
       </c>
       <c r="AK8">
-        <v>62.05</v>
+        <v>63.65</v>
       </c>
     </row>
     <row r="9" spans="1:37">
@@ -1743,10 +1718,10 @@
         <v>45</v>
       </c>
       <c r="C9">
-        <v>11056</v>
+        <v>11155</v>
       </c>
       <c r="D9">
-        <v>-0.89</v>
+        <v>0.9</v>
       </c>
       <c r="E9">
         <v>13052</v>
@@ -1755,25 +1730,25 @@
         <v>10362</v>
       </c>
       <c r="G9">
-        <v>-15.29</v>
+        <v>-14.53</v>
       </c>
       <c r="H9">
-        <v>6.7</v>
+        <v>7.65</v>
       </c>
       <c r="I9">
-        <v>2.71</v>
+        <v>1.28</v>
       </c>
       <c r="J9">
-        <v>-4.19</v>
+        <v>-4.8</v>
       </c>
       <c r="K9">
-        <v>-3.77</v>
+        <v>-1.6</v>
       </c>
       <c r="L9">
-        <v>-11.61</v>
+        <v>-11.82</v>
       </c>
       <c r="M9">
-        <v>8.5</v>
+        <v>8.41</v>
       </c>
       <c r="N9">
         <v>38</v>
@@ -1782,19 +1757,19 @@
         <v>47</v>
       </c>
       <c r="P9">
-        <v>11065</v>
+        <v>11093.2</v>
       </c>
       <c r="Q9">
-        <v>11139.05</v>
+        <v>11110.95</v>
       </c>
       <c r="R9">
-        <v>11549.8</v>
+        <v>11537.48</v>
       </c>
       <c r="S9">
-        <v>11722.1</v>
+        <v>11720.18</v>
       </c>
       <c r="T9">
-        <v>-5.68</v>
+        <v>-4.82</v>
       </c>
       <c r="U9" t="s">
         <v>46</v>
@@ -1809,34 +1784,34 @@
         <v>0</v>
       </c>
       <c r="Y9">
-        <v>44.61</v>
+        <v>48.12</v>
       </c>
       <c r="Z9">
-        <v>-155.1</v>
+        <v>-135.15</v>
       </c>
       <c r="AA9">
-        <v>-183.65</v>
+        <v>-173.95</v>
       </c>
       <c r="AB9">
-        <v>28.56</v>
+        <v>38.81</v>
       </c>
       <c r="AC9">
-        <v>89.58</v>
+        <v>95.09</v>
       </c>
       <c r="AD9">
-        <v>92.67</v>
+        <v>93.05</v>
       </c>
       <c r="AE9">
-        <v>194.49</v>
+        <v>191.82</v>
       </c>
       <c r="AF9">
-        <v>14.87</v>
+        <v>-28.95</v>
       </c>
       <c r="AG9">
-        <v>11710.17</v>
+        <v>11613.53</v>
       </c>
       <c r="AH9">
-        <v>10567.93</v>
+        <v>10608.37</v>
       </c>
       <c r="AI9">
         <v>11371.08</v>
@@ -1845,7 +1820,7 @@
         <v>49</v>
       </c>
       <c r="AK9">
-        <v>28.77</v>
+        <v>25.86</v>
       </c>
     </row>
   </sheetData>
@@ -1986,7 +1961,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F74"/>
+  <dimension ref="A1:F70"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -2026,7 +2001,7 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="4" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B3" s="4" t="s">
         <v>56</v>
@@ -2044,1204 +2019,1124 @@
         <v>60</v>
       </c>
     </row>
-    <row r="4" spans="1:6">
-      <c r="A4" s="4" t="s">
+    <row r="5" spans="1:6">
+      <c r="A5" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="B5" s="2"/>
+      <c r="C5" s="2"/>
+      <c r="D5" s="2"/>
+      <c r="E5" s="2"/>
+    </row>
+    <row r="6" spans="1:6">
+      <c r="A6" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6">
+      <c r="A7" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C7" s="6">
+        <v>-5.05</v>
+      </c>
+      <c r="D7" s="6">
+        <v>-4.88</v>
+      </c>
+      <c r="E7" s="7">
+        <v>0.17</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C8" s="6">
+        <v>-11.78</v>
+      </c>
+      <c r="D8" s="6">
+        <v>-9.869999999999999</v>
+      </c>
+      <c r="E8" s="7">
+        <v>1.91</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C9" s="6">
+        <v>-3.74</v>
+      </c>
+      <c r="D9" s="6">
+        <v>-3.3</v>
+      </c>
+      <c r="E9" s="7">
+        <v>0.44</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B4" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="C4" s="4" t="s">
-        <v>61</v>
-      </c>
-      <c r="D4" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="E4" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="F4" s="4" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6">
-      <c r="A5" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="B5" s="4" t="s">
-        <v>62</v>
-      </c>
-      <c r="C5" s="4" t="s">
-        <v>61</v>
-      </c>
-      <c r="D5" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="E5" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="F5" s="4" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6">
-      <c r="A6" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>63</v>
-      </c>
-      <c r="D6" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="E6" s="4" t="s">
-        <v>64</v>
-      </c>
-      <c r="F6" s="4" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6">
-      <c r="A7" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="B7" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="C7" s="4" t="s">
-        <v>66</v>
-      </c>
-      <c r="D7" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="E7" s="4" t="s">
-        <v>67</v>
-      </c>
-      <c r="F7" s="4" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="B9" s="2"/>
-      <c r="C9" s="2"/>
-      <c r="D9" s="2"/>
-      <c r="E9" s="2"/>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B10" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="C10" s="3" t="s">
-        <v>71</v>
-      </c>
-      <c r="D10" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="E10" s="3" t="s">
-        <v>73</v>
+      <c r="B10" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C10" s="6">
+        <v>-6.57</v>
+      </c>
+      <c r="D10" s="6">
+        <v>-7.22</v>
+      </c>
+      <c r="E10" s="8">
+        <v>-0.65</v>
       </c>
     </row>
     <row r="11" spans="1:6">
       <c r="A11" s="5" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="B11" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C11" s="6">
-        <v>-2.53</v>
+        <v>-7.04</v>
       </c>
       <c r="D11" s="6">
-        <v>-5.05</v>
+        <v>-5.31</v>
       </c>
       <c r="E11" s="7">
-        <v>-2.52</v>
+        <v>1.73</v>
       </c>
     </row>
     <row r="12" spans="1:6">
       <c r="A12" s="5" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="B12" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C12" s="6">
-        <v>-9.01</v>
+        <v>0.53</v>
       </c>
       <c r="D12" s="6">
-        <v>-11.78</v>
+        <v>4.14</v>
       </c>
       <c r="E12" s="7">
-        <v>-2.77</v>
+        <v>3.61</v>
       </c>
     </row>
     <row r="13" spans="1:6">
       <c r="A13" s="5" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="B13" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C13" s="6">
-        <v>-3.03</v>
+        <v>-8.83</v>
       </c>
       <c r="D13" s="6">
-        <v>-3.74</v>
-      </c>
-      <c r="E13" s="7">
-        <v>-0.71</v>
+        <v>-9.26</v>
+      </c>
+      <c r="E13" s="8">
+        <v>-0.43</v>
       </c>
     </row>
     <row r="14" spans="1:6">
       <c r="A14" s="5" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="B14" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C14" s="6">
-        <v>-5.17</v>
+        <v>-4.19</v>
       </c>
       <c r="D14" s="6">
-        <v>-6.57</v>
-      </c>
-      <c r="E14" s="7">
-        <v>-1.4</v>
+        <v>-4.8</v>
+      </c>
+      <c r="E14" s="8">
+        <v>-0.61</v>
       </c>
     </row>
     <row r="15" spans="1:6">
       <c r="A15" s="5" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C15" s="6">
-        <v>3.2</v>
+        <v>0.03</v>
       </c>
       <c r="D15" s="6">
-        <v>-7.04</v>
-      </c>
-      <c r="E15" s="7">
-        <v>-10.24</v>
+        <v>-4.89</v>
+      </c>
+      <c r="E15" s="8">
+        <v>-4.92</v>
       </c>
     </row>
     <row r="16" spans="1:6">
       <c r="A16" s="5" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C16" s="6">
-        <v>1.94</v>
+        <v>-4.74</v>
       </c>
       <c r="D16" s="6">
-        <v>0.53</v>
+        <v>-2.03</v>
       </c>
       <c r="E16" s="7">
-        <v>-1.41</v>
+        <v>2.71</v>
       </c>
     </row>
     <row r="17" spans="1:5">
       <c r="A17" s="5" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C17" s="6">
-        <v>-7.34</v>
+        <v>-0.21</v>
       </c>
       <c r="D17" s="6">
-        <v>-8.83</v>
-      </c>
-      <c r="E17" s="7">
-        <v>-1.49</v>
+        <v>-0.57</v>
+      </c>
+      <c r="E17" s="8">
+        <v>-0.36</v>
       </c>
     </row>
     <row r="18" spans="1:5">
       <c r="A18" s="5" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C18" s="6">
-        <v>-3.03</v>
+        <v>0.15</v>
       </c>
       <c r="D18" s="6">
-        <v>-4.19</v>
-      </c>
-      <c r="E18" s="7">
-        <v>-1.16</v>
+        <v>-0.96</v>
+      </c>
+      <c r="E18" s="8">
+        <v>-1.11</v>
       </c>
     </row>
     <row r="19" spans="1:5">
       <c r="A19" s="5" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="B19" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C19" s="6">
-        <v>5.55</v>
+        <v>-0.7</v>
       </c>
       <c r="D19" s="6">
-        <v>0.03</v>
+        <v>2.44</v>
       </c>
       <c r="E19" s="7">
-        <v>-5.52</v>
+        <v>3.14</v>
       </c>
     </row>
     <row r="20" spans="1:5">
       <c r="A20" s="5" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="B20" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C20" s="6">
-        <v>-1.31</v>
+        <v>-7.7</v>
       </c>
       <c r="D20" s="6">
-        <v>-4.74</v>
+        <v>-3.1</v>
       </c>
       <c r="E20" s="7">
-        <v>-3.43</v>
+        <v>4.6</v>
       </c>
     </row>
     <row r="21" spans="1:5">
       <c r="A21" s="5" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="B21" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C21" s="6">
-        <v>0.05</v>
+        <v>-1.84</v>
       </c>
       <c r="D21" s="6">
-        <v>-0.21</v>
+        <v>-1.28</v>
       </c>
       <c r="E21" s="7">
-        <v>-0.26</v>
+        <v>0.5600000000000001</v>
       </c>
     </row>
     <row r="22" spans="1:5">
       <c r="A22" s="5" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="B22" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C22" s="6">
-        <v>3.2</v>
+        <v>2.71</v>
       </c>
       <c r="D22" s="6">
-        <v>0.15</v>
-      </c>
-      <c r="E22" s="7">
-        <v>-3.05</v>
+        <v>1.28</v>
+      </c>
+      <c r="E22" s="8">
+        <v>-1.43</v>
       </c>
     </row>
     <row r="23" spans="1:5">
       <c r="A23" s="5" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="C23" s="6">
-        <v>1.82</v>
+        <v>34.91</v>
       </c>
       <c r="D23" s="6">
-        <v>-0.7</v>
+        <v>35.35</v>
       </c>
       <c r="E23" s="7">
-        <v>-2.52</v>
+        <v>0.44</v>
       </c>
     </row>
     <row r="24" spans="1:5">
       <c r="A24" s="5" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="C24" s="6">
-        <v>-6.39</v>
+        <v>-47.82</v>
       </c>
       <c r="D24" s="6">
-        <v>-7.7</v>
+        <v>-47.43</v>
       </c>
       <c r="E24" s="7">
-        <v>-1.31</v>
+        <v>0.39</v>
       </c>
     </row>
     <row r="25" spans="1:5">
       <c r="A25" s="5" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="C25" s="6">
-        <v>-0.26</v>
+        <v>10.03</v>
       </c>
       <c r="D25" s="6">
-        <v>-1.84</v>
+        <v>11.8</v>
       </c>
       <c r="E25" s="7">
-        <v>-1.58</v>
+        <v>1.77</v>
       </c>
     </row>
     <row r="26" spans="1:5">
       <c r="A26" s="5" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="C26" s="6">
-        <v>4.25</v>
+        <v>32.11</v>
       </c>
       <c r="D26" s="6">
-        <v>2.71</v>
-      </c>
-      <c r="E26" s="7">
-        <v>-1.54</v>
+        <v>31.02</v>
+      </c>
+      <c r="E26" s="8">
+        <v>-1.09</v>
       </c>
     </row>
     <row r="27" spans="1:5">
       <c r="A27" s="5" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="B27" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C27" s="6">
-        <v>38.35</v>
+        <v>68.09999999999999</v>
       </c>
       <c r="D27" s="6">
-        <v>34.91</v>
+        <v>69.95999999999999</v>
       </c>
       <c r="E27" s="7">
-        <v>-3.44</v>
+        <v>1.86</v>
       </c>
     </row>
     <row r="28" spans="1:5">
       <c r="A28" s="5" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="B28" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C28" s="6">
-        <v>-45.38</v>
+        <v>80.51000000000001</v>
       </c>
       <c r="D28" s="6">
-        <v>-47.82</v>
+        <v>91.87</v>
       </c>
       <c r="E28" s="7">
-        <v>-2.44</v>
+        <v>11.36</v>
       </c>
     </row>
     <row r="29" spans="1:5">
       <c r="A29" s="5" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="B29" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C29" s="6">
-        <v>10.76</v>
+        <v>-27.08</v>
       </c>
       <c r="D29" s="6">
-        <v>10.03</v>
+        <v>-25.03</v>
       </c>
       <c r="E29" s="7">
-        <v>-0.73</v>
+        <v>2.05</v>
       </c>
     </row>
     <row r="30" spans="1:5">
       <c r="A30" s="5" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="B30" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C30" s="6">
-        <v>33.81</v>
+        <v>-11.61</v>
       </c>
       <c r="D30" s="6">
-        <v>32.11</v>
-      </c>
-      <c r="E30" s="7">
-        <v>-1.7</v>
+        <v>-11.82</v>
+      </c>
+      <c r="E30" s="8">
+        <v>-0.21</v>
       </c>
     </row>
     <row r="31" spans="1:5">
       <c r="A31" s="5" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="B31" s="5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C31" s="6">
-        <v>85.2</v>
+        <v>-0.18</v>
       </c>
       <c r="D31" s="6">
-        <v>68.09999999999999</v>
+        <v>1.22</v>
       </c>
       <c r="E31" s="7">
-        <v>-17.1</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="32" spans="1:5">
       <c r="A32" s="5" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="B32" s="5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C32" s="6">
-        <v>92.51000000000001</v>
+        <v>-20.06</v>
       </c>
       <c r="D32" s="6">
-        <v>80.51000000000001</v>
+        <v>-16.43</v>
       </c>
       <c r="E32" s="7">
-        <v>-12</v>
+        <v>3.63</v>
       </c>
     </row>
     <row r="33" spans="1:5">
       <c r="A33" s="5" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="B33" s="5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C33" s="6">
-        <v>-25.3</v>
+        <v>1.28</v>
       </c>
       <c r="D33" s="6">
-        <v>-27.08</v>
+        <v>3.6</v>
       </c>
       <c r="E33" s="7">
-        <v>-1.78</v>
+        <v>2.32</v>
       </c>
     </row>
     <row r="34" spans="1:5">
       <c r="A34" s="5" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="B34" s="5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C34" s="6">
-        <v>-11.65</v>
+        <v>3.02</v>
       </c>
       <c r="D34" s="6">
-        <v>-11.61</v>
+        <v>1.37</v>
       </c>
       <c r="E34" s="8">
-        <v>0.04</v>
+        <v>-1.65</v>
       </c>
     </row>
     <row r="35" spans="1:5">
       <c r="A35" s="5" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="B35" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C35" s="6">
-        <v>1.94</v>
+        <v>0.43</v>
       </c>
       <c r="D35" s="6">
-        <v>-0.18</v>
-      </c>
-      <c r="E35" s="7">
-        <v>-2.12</v>
+        <v>-1.18</v>
+      </c>
+      <c r="E35" s="8">
+        <v>-1.61</v>
       </c>
     </row>
     <row r="36" spans="1:5">
       <c r="A36" s="5" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="B36" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C36" s="6">
-        <v>-20.31</v>
+        <v>2.34</v>
       </c>
       <c r="D36" s="6">
-        <v>-20.06</v>
+        <v>1.94</v>
       </c>
       <c r="E36" s="8">
-        <v>0.25</v>
+        <v>-0.4</v>
       </c>
     </row>
     <row r="37" spans="1:5">
       <c r="A37" s="5" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="B37" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C37" s="6">
-        <v>1.94</v>
+        <v>-8.880000000000001</v>
       </c>
       <c r="D37" s="6">
-        <v>1.28</v>
+        <v>-7.66</v>
       </c>
       <c r="E37" s="7">
-        <v>-0.66</v>
+        <v>1.22</v>
       </c>
     </row>
     <row r="38" spans="1:5">
       <c r="A38" s="5" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="B38" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C38" s="6">
-        <v>2.79</v>
+        <v>-3.77</v>
       </c>
       <c r="D38" s="6">
-        <v>3.02</v>
-      </c>
-      <c r="E38" s="8">
-        <v>0.23</v>
+        <v>-1.6</v>
+      </c>
+      <c r="E38" s="7">
+        <v>2.17</v>
       </c>
     </row>
     <row r="39" spans="1:5">
       <c r="A39" s="5" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="B39" s="5" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C39" s="6">
-        <v>1.47</v>
+        <v>-8.15</v>
       </c>
       <c r="D39" s="6">
-        <v>0.43</v>
-      </c>
-      <c r="E39" s="7">
-        <v>-1.04</v>
+        <v>-8.17</v>
+      </c>
+      <c r="E39" s="8">
+        <v>-0.02</v>
       </c>
     </row>
     <row r="40" spans="1:5">
       <c r="A40" s="5" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="B40" s="5" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C40" s="6">
-        <v>1.94</v>
+        <v>-48.59</v>
       </c>
       <c r="D40" s="6">
-        <v>2.34</v>
-      </c>
-      <c r="E40" s="8">
-        <v>0.4</v>
+        <v>-46.6</v>
+      </c>
+      <c r="E40" s="7">
+        <v>1.99</v>
       </c>
     </row>
     <row r="41" spans="1:5">
       <c r="A41" s="5" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="B41" s="5" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C41" s="6">
-        <v>-7.83</v>
+        <v>-6.33</v>
       </c>
       <c r="D41" s="6">
-        <v>-8.880000000000001</v>
+        <v>-5.61</v>
       </c>
       <c r="E41" s="7">
-        <v>-1.05</v>
+        <v>0.72</v>
       </c>
     </row>
     <row r="42" spans="1:5">
       <c r="A42" s="5" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="B42" s="5" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C42" s="6">
-        <v>-2.41</v>
+        <v>-14.59</v>
       </c>
       <c r="D42" s="6">
-        <v>-3.77</v>
-      </c>
-      <c r="E42" s="7">
-        <v>-1.36</v>
+        <v>-15.02</v>
+      </c>
+      <c r="E42" s="8">
+        <v>-0.43</v>
       </c>
     </row>
     <row r="43" spans="1:5">
       <c r="A43" s="5" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="B43" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C43" s="6">
-        <v>-5.24</v>
+        <v>-9.49</v>
       </c>
       <c r="D43" s="6">
-        <v>-8.15</v>
+        <v>-8.59</v>
       </c>
       <c r="E43" s="7">
-        <v>-2.91</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="44" spans="1:5">
       <c r="A44" s="5" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="B44" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C44" s="6">
-        <v>-47.49</v>
+        <v>-18.18</v>
       </c>
       <c r="D44" s="6">
-        <v>-48.59</v>
+        <v>-16.88</v>
       </c>
       <c r="E44" s="7">
-        <v>-1.1</v>
+        <v>1.3</v>
       </c>
     </row>
     <row r="45" spans="1:5">
       <c r="A45" s="5" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="B45" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C45" s="6">
-        <v>-5.68</v>
+        <v>-31.03</v>
       </c>
       <c r="D45" s="6">
-        <v>-6.33</v>
+        <v>-30.89</v>
       </c>
       <c r="E45" s="7">
-        <v>-0.65</v>
+        <v>0.14</v>
       </c>
     </row>
     <row r="46" spans="1:5">
       <c r="A46" s="5" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="B46" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C46" s="6">
-        <v>-12.69</v>
+        <v>-15.29</v>
       </c>
       <c r="D46" s="6">
-        <v>-14.59</v>
+        <v>-14.53</v>
       </c>
       <c r="E46" s="7">
-        <v>-1.9</v>
+        <v>0.76</v>
       </c>
     </row>
     <row r="47" spans="1:5">
       <c r="A47" s="5" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="B47" s="5" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="C47" s="6">
-        <v>-6.92</v>
+        <v>390.1</v>
       </c>
       <c r="D47" s="6">
-        <v>-9.49</v>
-      </c>
-      <c r="E47" s="7">
-        <v>-2.57</v>
+        <v>390</v>
+      </c>
+      <c r="E47" s="8">
+        <v>-0.1</v>
       </c>
     </row>
     <row r="48" spans="1:5">
       <c r="A48" s="5" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="B48" s="5" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="C48" s="6">
-        <v>-16.88</v>
+        <v>48.06</v>
       </c>
       <c r="D48" s="6">
-        <v>-18.18</v>
+        <v>49.14</v>
       </c>
       <c r="E48" s="7">
-        <v>-1.3</v>
+        <v>1.08</v>
       </c>
     </row>
     <row r="49" spans="1:5">
       <c r="A49" s="5" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="B49" s="5" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="C49" s="6">
-        <v>-30.43</v>
+        <v>3166.5</v>
       </c>
       <c r="D49" s="6">
-        <v>-31.03</v>
+        <v>3191</v>
       </c>
       <c r="E49" s="7">
-        <v>-0.6</v>
+        <v>24.5</v>
       </c>
     </row>
     <row r="50" spans="1:5">
       <c r="A50" s="5" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="B50" s="5" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="C50" s="6">
-        <v>-14.53</v>
+        <v>982</v>
       </c>
       <c r="D50" s="6">
-        <v>-15.29</v>
-      </c>
-      <c r="E50" s="7">
-        <v>-0.76</v>
+        <v>977</v>
+      </c>
+      <c r="E50" s="8">
+        <v>-5</v>
       </c>
     </row>
     <row r="51" spans="1:5">
       <c r="A51" s="5" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="B51" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C51" s="6">
-        <v>402.45</v>
+        <v>14.12</v>
       </c>
       <c r="D51" s="6">
-        <v>390.1</v>
+        <v>14.26</v>
       </c>
       <c r="E51" s="7">
-        <v>-12.35</v>
+        <v>0.14</v>
       </c>
     </row>
     <row r="52" spans="1:5">
       <c r="A52" s="5" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="B52" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C52" s="6">
-        <v>49.09</v>
+        <v>11.39</v>
       </c>
       <c r="D52" s="6">
-        <v>48.06</v>
+        <v>11.57</v>
       </c>
       <c r="E52" s="7">
-        <v>-1.03</v>
+        <v>0.18</v>
       </c>
     </row>
     <row r="53" spans="1:5">
       <c r="A53" s="5" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="B53" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C53" s="6">
-        <v>3188.5</v>
+        <v>4007.1</v>
       </c>
       <c r="D53" s="6">
-        <v>3166.5</v>
+        <v>4015</v>
       </c>
       <c r="E53" s="7">
-        <v>-22</v>
+        <v>7.9</v>
       </c>
     </row>
     <row r="54" spans="1:5">
       <c r="A54" s="5" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="B54" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C54" s="6">
-        <v>1003.8</v>
+        <v>11056</v>
       </c>
       <c r="D54" s="6">
-        <v>982</v>
+        <v>11155</v>
       </c>
       <c r="E54" s="7">
-        <v>-21.8</v>
+        <v>99</v>
       </c>
     </row>
     <row r="55" spans="1:5">
       <c r="A55" s="5" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="B55" s="5" t="s">
-        <v>2</v>
+        <v>24</v>
       </c>
       <c r="C55" s="6">
-        <v>14.52</v>
+        <v>44.84</v>
       </c>
       <c r="D55" s="6">
-        <v>14.12</v>
-      </c>
-      <c r="E55" s="7">
-        <v>-0.4</v>
+        <v>44.79</v>
+      </c>
+      <c r="E55" s="8">
+        <v>-0.05</v>
       </c>
     </row>
     <row r="56" spans="1:5">
       <c r="A56" s="5" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="B56" s="5" t="s">
-        <v>2</v>
+        <v>24</v>
       </c>
       <c r="C56" s="6">
-        <v>11.57</v>
+        <v>29.34</v>
       </c>
       <c r="D56" s="6">
-        <v>11.39</v>
+        <v>36.7</v>
       </c>
       <c r="E56" s="7">
-        <v>-0.18</v>
+        <v>7.36</v>
       </c>
     </row>
     <row r="57" spans="1:5">
       <c r="A57" s="5" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="B57" s="5" t="s">
-        <v>2</v>
+        <v>24</v>
       </c>
       <c r="C57" s="6">
-        <v>4041.8</v>
+        <v>42.6</v>
       </c>
       <c r="D57" s="6">
-        <v>4007.1</v>
+        <v>45.66</v>
       </c>
       <c r="E57" s="7">
-        <v>-34.7</v>
+        <v>3.06</v>
       </c>
     </row>
     <row r="58" spans="1:5">
       <c r="A58" s="5" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="B58" s="5" t="s">
-        <v>2</v>
+        <v>24</v>
       </c>
       <c r="C58" s="6">
-        <v>11155</v>
+        <v>44.68</v>
       </c>
       <c r="D58" s="6">
-        <v>11056</v>
-      </c>
-      <c r="E58" s="7">
-        <v>-99</v>
+        <v>43.44</v>
+      </c>
+      <c r="E58" s="8">
+        <v>-1.24</v>
       </c>
     </row>
     <row r="59" spans="1:5">
       <c r="A59" s="5" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="B59" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C59" s="6">
-        <v>51.58</v>
+        <v>46.87</v>
       </c>
       <c r="D59" s="6">
-        <v>44.84</v>
+        <v>48.85</v>
       </c>
       <c r="E59" s="7">
-        <v>-6.74</v>
+        <v>1.98</v>
       </c>
     </row>
     <row r="60" spans="1:5">
       <c r="A60" s="5" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="B60" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C60" s="6">
-        <v>32.71</v>
+        <v>45.36</v>
       </c>
       <c r="D60" s="6">
-        <v>29.34</v>
+        <v>48.47</v>
       </c>
       <c r="E60" s="7">
-        <v>-3.37</v>
+        <v>3.11</v>
       </c>
     </row>
     <row r="61" spans="1:5">
       <c r="A61" s="5" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="B61" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C61" s="6">
-        <v>44.7</v>
+        <v>33.52</v>
       </c>
       <c r="D61" s="6">
-        <v>42.6</v>
+        <v>34.42</v>
       </c>
       <c r="E61" s="7">
-        <v>-2.1</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="62" spans="1:5">
       <c r="A62" s="5" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="B62" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C62" s="6">
-        <v>50.46</v>
+        <v>44.61</v>
       </c>
       <c r="D62" s="6">
-        <v>44.68</v>
+        <v>48.12</v>
       </c>
       <c r="E62" s="7">
-        <v>-5.78</v>
+        <v>3.51</v>
       </c>
     </row>
     <row r="63" spans="1:5">
       <c r="A63" s="5" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="B63" s="5" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="C63" s="6">
-        <v>52.22</v>
+        <v>55.16</v>
       </c>
       <c r="D63" s="6">
-        <v>46.87</v>
-      </c>
-      <c r="E63" s="7">
-        <v>-5.35</v>
+        <v>5.17</v>
+      </c>
+      <c r="E63" s="8">
+        <v>-49.99</v>
       </c>
     </row>
     <row r="64" spans="1:5">
       <c r="A64" s="5" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="B64" s="5" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="C64" s="6">
-        <v>48.06</v>
+        <v>15.66</v>
       </c>
       <c r="D64" s="6">
-        <v>45.36</v>
-      </c>
-      <c r="E64" s="7">
-        <v>-2.7</v>
+        <v>2.98</v>
+      </c>
+      <c r="E64" s="8">
+        <v>-12.68</v>
       </c>
     </row>
     <row r="65" spans="1:5">
       <c r="A65" s="5" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="B65" s="5" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="C65" s="6">
-        <v>35.51</v>
+        <v>-49.97</v>
       </c>
       <c r="D65" s="6">
-        <v>33.52</v>
+        <v>-12.22</v>
       </c>
       <c r="E65" s="7">
-        <v>-1.99</v>
+        <v>37.75</v>
       </c>
     </row>
     <row r="66" spans="1:5">
       <c r="A66" s="5" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="B66" s="5" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="C66" s="6">
-        <v>47.6</v>
+        <v>29.25</v>
       </c>
       <c r="D66" s="6">
-        <v>44.61</v>
-      </c>
-      <c r="E66" s="7">
-        <v>-2.99</v>
+        <v>-27.17</v>
+      </c>
+      <c r="E66" s="8">
+        <v>-56.42</v>
       </c>
     </row>
     <row r="67" spans="1:5">
       <c r="A67" s="5" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="B67" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C67" s="6">
-        <v>-25.14</v>
+        <v>-25.07</v>
       </c>
       <c r="D67" s="6">
-        <v>55.16</v>
+        <v>-28.09</v>
       </c>
       <c r="E67" s="8">
-        <v>80.3</v>
+        <v>-3.02</v>
       </c>
     </row>
     <row r="68" spans="1:5">
       <c r="A68" s="5" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="B68" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C68" s="6">
-        <v>-38.57</v>
+        <v>-38.81</v>
       </c>
       <c r="D68" s="6">
-        <v>15.66</v>
-      </c>
-      <c r="E68" s="8">
-        <v>54.23</v>
+        <v>-8.359999999999999</v>
+      </c>
+      <c r="E68" s="7">
+        <v>30.45</v>
       </c>
     </row>
     <row r="69" spans="1:5">
       <c r="A69" s="5" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="B69" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C69" s="6">
-        <v>-58.83</v>
+        <v>-38.8</v>
       </c>
       <c r="D69" s="6">
-        <v>-49.97</v>
+        <v>-55.64</v>
       </c>
       <c r="E69" s="8">
-        <v>8.859999999999999</v>
+        <v>-16.84</v>
       </c>
     </row>
     <row r="70" spans="1:5">
       <c r="A70" s="5" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="B70" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C70" s="6">
-        <v>56.4</v>
+        <v>14.87</v>
       </c>
       <c r="D70" s="6">
-        <v>29.25</v>
-      </c>
-      <c r="E70" s="7">
-        <v>-27.15</v>
-      </c>
-    </row>
-    <row r="71" spans="1:5">
-      <c r="A71" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B71" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C71" s="6">
-        <v>-43.76</v>
-      </c>
-      <c r="D71" s="6">
-        <v>-25.07</v>
-      </c>
-      <c r="E71" s="8">
-        <v>18.69</v>
-      </c>
-    </row>
-    <row r="72" spans="1:5">
-      <c r="A72" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B72" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C72" s="6">
-        <v>-1.54</v>
-      </c>
-      <c r="D72" s="6">
-        <v>-38.81</v>
-      </c>
-      <c r="E72" s="7">
-        <v>-37.27</v>
-      </c>
-    </row>
-    <row r="73" spans="1:5">
-      <c r="A73" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B73" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C73" s="6">
-        <v>-68.31999999999999</v>
-      </c>
-      <c r="D73" s="6">
-        <v>-38.8</v>
-      </c>
-      <c r="E73" s="8">
-        <v>29.52</v>
-      </c>
-    </row>
-    <row r="74" spans="1:5">
-      <c r="A74" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="B74" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C74" s="6">
-        <v>-18.97</v>
-      </c>
-      <c r="D74" s="6">
-        <v>14.87</v>
-      </c>
-      <c r="E74" s="8">
-        <v>33.84</v>
+        <v>-28.95</v>
+      </c>
+      <c r="E70" s="8">
+        <v>-43.82</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A9:E9"/>
+    <mergeCell ref="A5:E5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3265,28 +3160,28 @@
         <v>1</v>
       </c>
       <c r="B1" s="9" t="s">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="C1" s="9" t="s">
-        <v>75</v>
+        <v>67</v>
       </c>
       <c r="D1" s="9" t="s">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="E1" s="9" t="s">
-        <v>77</v>
+        <v>69</v>
       </c>
       <c r="F1" s="9" t="s">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="G1" s="9" t="s">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="H1" s="9" t="s">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="I1" s="9" t="s">
-        <v>81</v>
+        <v>73</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -3294,22 +3189,22 @@
         <v>45</v>
       </c>
       <c r="B2" s="11">
-        <v>56.44</v>
+        <v>52.44</v>
       </c>
       <c r="C2" s="12">
         <v>8</v>
       </c>
       <c r="D2" s="11">
-        <v>41.5</v>
+        <v>43.8</v>
       </c>
       <c r="E2" s="11">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="F2" s="11">
-        <v>-5.8</v>
+        <v>-5.1</v>
       </c>
       <c r="G2" s="11">
-        <v>-3.2</v>
+        <v>-2.3</v>
       </c>
       <c r="H2" s="11">
         <v>56.1</v>
@@ -3443,28 +3338,28 @@
     </row>
     <row r="2" spans="1:8">
       <c r="A2" s="14">
-        <v>0.2758</v>
+        <v>0.2726</v>
       </c>
       <c r="B2" s="14">
-        <v>0.1645</v>
+        <v>0.1676</v>
       </c>
       <c r="C2" s="14">
-        <v>0.1612</v>
+        <v>0.1589</v>
       </c>
       <c r="D2" s="14">
-        <v>0.1474</v>
+        <v>0.1467</v>
       </c>
       <c r="E2" s="14">
-        <v>0.08500000000000001</v>
+        <v>0.08410000000000001</v>
       </c>
       <c r="F2" s="14">
-        <v>0.04190000000000001</v>
+        <v>0.04679999999999999</v>
       </c>
       <c r="G2" s="14">
-        <v>-0.2649</v>
+        <v>-0.2632</v>
       </c>
       <c r="H2" s="14">
-        <v>-0.3081</v>
+        <v>-0.2987</v>
       </c>
     </row>
   </sheetData>

--- a/BIRLA_GROUP_Technical_Metrics.xlsx
+++ b/BIRLA_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="287" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="276" uniqueCount="65">
   <si>
     <t>Symbol</t>
   </si>
@@ -175,34 +175,7 @@
     <t>▶  SIGNAL EVENTS (vs Previous Run)</t>
   </si>
   <si>
-    <t>Signal</t>
-  </si>
-  <si>
-    <t>Change</t>
-  </si>
-  <si>
-    <t>Direction</t>
-  </si>
-  <si>
-    <t>Prev Value</t>
-  </si>
-  <si>
-    <t>Curr Value</t>
-  </si>
-  <si>
-    <t>RSI Oversold Recovery</t>
-  </si>
-  <si>
-    <t>29.3 → 36.7</t>
-  </si>
-  <si>
-    <t>🟢 BULLISH</t>
-  </si>
-  <si>
-    <t>29.3</t>
-  </si>
-  <si>
-    <t>36.7</t>
+    <t>No signal events detected since last run.</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -288,14 +261,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF9C0006"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF006100"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -328,13 +301,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -404,15 +377,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -927,10 +899,10 @@
         <v>45</v>
       </c>
       <c r="C2">
-        <v>390</v>
+        <v>382.7</v>
       </c>
       <c r="D2">
-        <v>-0.03</v>
+        <v>-1.87</v>
       </c>
       <c r="E2">
         <v>424.7</v>
@@ -939,46 +911,46 @@
         <v>278.9</v>
       </c>
       <c r="G2">
-        <v>-8.17</v>
+        <v>-9.890000000000001</v>
       </c>
       <c r="H2">
-        <v>39.84</v>
+        <v>37.22</v>
       </c>
       <c r="I2">
-        <v>-4.89</v>
+        <v>-5.13</v>
       </c>
       <c r="J2">
-        <v>-4.88</v>
+        <v>-6.66</v>
       </c>
       <c r="K2">
-        <v>1.22</v>
+        <v>-2.36</v>
       </c>
       <c r="L2">
-        <v>35.35</v>
+        <v>31.31</v>
       </c>
       <c r="M2">
-        <v>27.26</v>
+        <v>27.46</v>
       </c>
       <c r="N2">
         <v>74</v>
       </c>
       <c r="O2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="P2">
-        <v>396.59</v>
+        <v>392.45</v>
       </c>
       <c r="Q2">
-        <v>397.58</v>
+        <v>396.44</v>
       </c>
       <c r="R2">
-        <v>402.67</v>
+        <v>402.29</v>
       </c>
       <c r="S2">
-        <v>364.17</v>
+        <v>364.27</v>
       </c>
       <c r="T2">
-        <v>7.09</v>
+        <v>5.06</v>
       </c>
       <c r="U2" t="s">
         <v>46</v>
@@ -993,34 +965,34 @@
         <v>2</v>
       </c>
       <c r="Y2">
-        <v>44.79</v>
+        <v>41.11</v>
       </c>
       <c r="Z2">
-        <v>-2.39</v>
+        <v>-3.28</v>
       </c>
       <c r="AA2">
-        <v>-2.06</v>
+        <v>-2.31</v>
       </c>
       <c r="AB2">
-        <v>-0.33</v>
+        <v>-0.98</v>
       </c>
       <c r="AC2">
-        <v>58.86</v>
+        <v>43.34</v>
       </c>
       <c r="AD2">
-        <v>66.03</v>
+        <v>55.47</v>
       </c>
       <c r="AE2">
-        <v>9.91</v>
+        <v>9.859999999999999</v>
       </c>
       <c r="AF2">
-        <v>5.17</v>
+        <v>-30.33</v>
       </c>
       <c r="AG2">
-        <v>414.37</v>
+        <v>414.04</v>
       </c>
       <c r="AH2">
-        <v>380.79</v>
+        <v>378.84</v>
       </c>
       <c r="AI2">
         <v>372.91</v>
@@ -1029,7 +1001,7 @@
         <v>48</v>
       </c>
       <c r="AK2">
-        <v>23.38</v>
+        <v>24.77</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1040,37 +1012,37 @@
         <v>45</v>
       </c>
       <c r="C3">
-        <v>49.14</v>
+        <v>47.59</v>
       </c>
       <c r="D3">
-        <v>2.25</v>
+        <v>-3.15</v>
       </c>
       <c r="E3">
-        <v>92.03</v>
+        <v>91.13</v>
       </c>
       <c r="F3">
-        <v>48.06</v>
+        <v>47.59</v>
       </c>
       <c r="G3">
-        <v>-46.6</v>
+        <v>-47.78</v>
       </c>
       <c r="H3">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="I3">
-        <v>-2.03</v>
+        <v>-4.53</v>
       </c>
       <c r="J3">
-        <v>-9.869999999999999</v>
+        <v>-11.28</v>
       </c>
       <c r="K3">
-        <v>-16.43</v>
+        <v>-18.03</v>
       </c>
       <c r="L3">
-        <v>-47.43</v>
+        <v>-48.29</v>
       </c>
       <c r="M3">
-        <v>-26.32</v>
+        <v>-26.61</v>
       </c>
       <c r="N3">
         <v>13</v>
@@ -1079,19 +1051,19 @@
         <v>6</v>
       </c>
       <c r="P3">
-        <v>49.07</v>
+        <v>48.62</v>
       </c>
       <c r="Q3">
-        <v>50.62</v>
+        <v>50.37</v>
       </c>
       <c r="R3">
-        <v>54.76</v>
+        <v>54.55</v>
       </c>
       <c r="S3">
-        <v>62.86</v>
+        <v>62.72</v>
       </c>
       <c r="T3">
-        <v>-21.83</v>
+        <v>-24.13</v>
       </c>
       <c r="U3" t="s">
         <v>46</v>
@@ -1106,34 +1078,34 @@
         <v>0</v>
       </c>
       <c r="Y3">
-        <v>36.7</v>
+        <v>31.61</v>
       </c>
       <c r="Z3">
-        <v>-1.71</v>
+        <v>-1.76</v>
       </c>
       <c r="AA3">
-        <v>-1.74</v>
+        <v>-1.75</v>
       </c>
       <c r="AB3">
-        <v>0.03</v>
+        <v>-0.02</v>
       </c>
       <c r="AC3">
-        <v>36.33</v>
+        <v>30.92</v>
       </c>
       <c r="AD3">
-        <v>39.97</v>
+        <v>33.23</v>
       </c>
       <c r="AE3">
-        <v>1.45</v>
+        <v>1.51</v>
       </c>
       <c r="AF3">
-        <v>2.98</v>
+        <v>-19.88</v>
       </c>
       <c r="AG3">
-        <v>53.47</v>
+        <v>53.39</v>
       </c>
       <c r="AH3">
-        <v>47.77</v>
+        <v>47.36</v>
       </c>
       <c r="AI3">
         <v>52.83</v>
@@ -1142,7 +1114,7 @@
         <v>49</v>
       </c>
       <c r="AK3">
-        <v>38.95</v>
+        <v>41</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1153,10 +1125,10 @@
         <v>45</v>
       </c>
       <c r="C4">
-        <v>3191</v>
+        <v>3150</v>
       </c>
       <c r="D4">
-        <v>0.77</v>
+        <v>-1.28</v>
       </c>
       <c r="E4">
         <v>3380.5</v>
@@ -1165,46 +1137,46 @@
         <v>2531.1</v>
       </c>
       <c r="G4">
-        <v>-5.61</v>
+        <v>-6.82</v>
       </c>
       <c r="H4">
-        <v>26.07</v>
+        <v>24.45</v>
       </c>
       <c r="I4">
-        <v>-0.57</v>
+        <v>-0.51</v>
       </c>
       <c r="J4">
-        <v>-3.3</v>
+        <v>-3.31</v>
       </c>
       <c r="K4">
-        <v>3.6</v>
+        <v>1.61</v>
       </c>
       <c r="L4">
-        <v>11.8</v>
+        <v>11.96</v>
       </c>
       <c r="M4">
-        <v>14.67</v>
+        <v>14.35</v>
       </c>
       <c r="N4">
         <v>50</v>
       </c>
       <c r="O4">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="P4">
-        <v>3168.04</v>
+        <v>3164.84</v>
       </c>
       <c r="Q4">
-        <v>3249.17</v>
+        <v>3242.17</v>
       </c>
       <c r="R4">
-        <v>3231.13</v>
+        <v>3231.94</v>
       </c>
       <c r="S4">
-        <v>2971.1</v>
+        <v>2973.12</v>
       </c>
       <c r="T4">
-        <v>7.4</v>
+        <v>5.95</v>
       </c>
       <c r="U4" t="s">
         <v>47</v>
@@ -1219,34 +1191,34 @@
         <v>3</v>
       </c>
       <c r="Y4">
-        <v>45.66</v>
+        <v>41.66</v>
       </c>
       <c r="Z4">
-        <v>-24.4</v>
+        <v>-26.85</v>
       </c>
       <c r="AA4">
-        <v>-12.42</v>
+        <v>-15.3</v>
       </c>
       <c r="AB4">
-        <v>-11.99</v>
+        <v>-11.55</v>
       </c>
       <c r="AC4">
-        <v>38.45</v>
+        <v>33.65</v>
       </c>
       <c r="AD4">
-        <v>25.91</v>
+        <v>31.71</v>
       </c>
       <c r="AE4">
-        <v>59.12</v>
+        <v>58.68</v>
       </c>
       <c r="AF4">
-        <v>-12.22</v>
+        <v>-13.65</v>
       </c>
       <c r="AG4">
-        <v>3392.97</v>
+        <v>3391.14</v>
       </c>
       <c r="AH4">
-        <v>3105.38</v>
+        <v>3093.21</v>
       </c>
       <c r="AI4">
         <v>3120.02</v>
@@ -1255,7 +1227,7 @@
         <v>48</v>
       </c>
       <c r="AK4">
-        <v>35.62</v>
+        <v>36.14</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1266,10 +1238,10 @@
         <v>45</v>
       </c>
       <c r="C5">
-        <v>977</v>
+        <v>955.9</v>
       </c>
       <c r="D5">
-        <v>-0.51</v>
+        <v>-2.16</v>
       </c>
       <c r="E5">
         <v>1149.7</v>
@@ -1278,25 +1250,25 @@
         <v>741.05</v>
       </c>
       <c r="G5">
-        <v>-15.02</v>
+        <v>-16.86</v>
       </c>
       <c r="H5">
-        <v>31.84</v>
+        <v>28.99</v>
       </c>
       <c r="I5">
-        <v>-0.96</v>
+        <v>-2.58</v>
       </c>
       <c r="J5">
-        <v>-7.22</v>
+        <v>-6.65</v>
       </c>
       <c r="K5">
-        <v>1.37</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="L5">
-        <v>31.02</v>
+        <v>28.15</v>
       </c>
       <c r="M5">
-        <v>15.89</v>
+        <v>15.52</v>
       </c>
       <c r="N5">
         <v>62</v>
@@ -1305,19 +1277,19 @@
         <v>75</v>
       </c>
       <c r="P5">
-        <v>983.4</v>
+        <v>978.34</v>
       </c>
       <c r="Q5">
-        <v>997.54</v>
+        <v>993.46</v>
       </c>
       <c r="R5">
-        <v>1004.23</v>
+        <v>1004.46</v>
       </c>
       <c r="S5">
-        <v>978.74</v>
+        <v>979.45</v>
       </c>
       <c r="T5">
-        <v>-0.18</v>
+        <v>-2.4</v>
       </c>
       <c r="U5" t="s">
         <v>46</v>
@@ -1332,43 +1304,43 @@
         <v>1</v>
       </c>
       <c r="Y5">
-        <v>43.44</v>
+        <v>38.61</v>
       </c>
       <c r="Z5">
-        <v>-10.14</v>
+        <v>-12</v>
       </c>
       <c r="AA5">
-        <v>-8.550000000000001</v>
+        <v>-9.24</v>
       </c>
       <c r="AB5">
-        <v>-1.59</v>
+        <v>-2.76</v>
       </c>
       <c r="AC5">
-        <v>65.38</v>
+        <v>43.79</v>
       </c>
       <c r="AD5">
-        <v>60.25</v>
+        <v>56.29</v>
       </c>
       <c r="AE5">
-        <v>22.39</v>
+        <v>22.64</v>
       </c>
       <c r="AF5">
-        <v>-27.17</v>
+        <v>-1.32</v>
       </c>
       <c r="AG5">
-        <v>1039.54</v>
+        <v>1034.99</v>
       </c>
       <c r="AH5">
-        <v>955.53</v>
+        <v>951.9299999999999</v>
       </c>
       <c r="AI5">
-        <v>1037.86</v>
+        <v>1029.93</v>
       </c>
       <c r="AJ5" t="s">
         <v>49</v>
       </c>
       <c r="AK5">
-        <v>18.38</v>
+        <v>20.51</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1379,10 +1351,10 @@
         <v>45</v>
       </c>
       <c r="C6">
-        <v>14.26</v>
+        <v>13.47</v>
       </c>
       <c r="D6">
-        <v>0.99</v>
+        <v>-5.54</v>
       </c>
       <c r="E6">
         <v>15.6</v>
@@ -1391,46 +1363,46 @@
         <v>8.02</v>
       </c>
       <c r="G6">
-        <v>-8.59</v>
+        <v>-13.65</v>
       </c>
       <c r="H6">
-        <v>77.81</v>
+        <v>67.95999999999999</v>
       </c>
       <c r="I6">
-        <v>2.44</v>
+        <v>-2.67</v>
       </c>
       <c r="J6">
-        <v>-5.31</v>
+        <v>-10.02</v>
       </c>
       <c r="K6">
-        <v>-1.18</v>
+        <v>-6.85</v>
       </c>
       <c r="L6">
-        <v>69.95999999999999</v>
+        <v>54.47</v>
       </c>
       <c r="M6">
-        <v>4.68</v>
+        <v>4.23</v>
       </c>
       <c r="N6">
         <v>87</v>
       </c>
       <c r="O6">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="P6">
-        <v>14.2</v>
+        <v>14.13</v>
       </c>
       <c r="Q6">
-        <v>14.57</v>
+        <v>14.51</v>
       </c>
       <c r="R6">
-        <v>13.94</v>
+        <v>13.93</v>
       </c>
       <c r="S6">
-        <v>12.2</v>
+        <v>12.22</v>
       </c>
       <c r="T6">
-        <v>16.87</v>
+        <v>10.27</v>
       </c>
       <c r="U6" t="s">
         <v>47</v>
@@ -1445,43 +1417,43 @@
         <v>3</v>
       </c>
       <c r="Y6">
-        <v>48.85</v>
+        <v>39.85</v>
       </c>
       <c r="Z6">
-        <v>0.01</v>
+        <v>-0.06</v>
       </c>
       <c r="AA6">
-        <v>0.11</v>
+        <v>0.08</v>
       </c>
       <c r="AB6">
-        <v>-0.1</v>
+        <v>-0.14</v>
       </c>
       <c r="AC6">
-        <v>27.04</v>
+        <v>14.29</v>
       </c>
       <c r="AD6">
-        <v>25.07</v>
+        <v>22.78</v>
       </c>
       <c r="AE6">
-        <v>0.47</v>
+        <v>0.49</v>
       </c>
       <c r="AF6">
-        <v>-28.09</v>
+        <v>18.57</v>
       </c>
       <c r="AG6">
-        <v>15.6</v>
+        <v>15.65</v>
       </c>
       <c r="AH6">
-        <v>13.53</v>
+        <v>13.37</v>
       </c>
       <c r="AI6">
-        <v>15.41</v>
+        <v>15.31</v>
       </c>
       <c r="AJ6" t="s">
         <v>49</v>
       </c>
       <c r="AK6">
-        <v>22.29</v>
+        <v>25.3</v>
       </c>
     </row>
     <row r="7" spans="1:37">
@@ -1492,10 +1464,10 @@
         <v>45</v>
       </c>
       <c r="C7">
-        <v>11.57</v>
+        <v>11.02</v>
       </c>
       <c r="D7">
-        <v>1.58</v>
+        <v>-4.75</v>
       </c>
       <c r="E7">
         <v>13.92</v>
@@ -1504,46 +1476,46 @@
         <v>4.69</v>
       </c>
       <c r="G7">
-        <v>-16.88</v>
+        <v>-20.83</v>
       </c>
       <c r="H7">
-        <v>146.7</v>
+        <v>134.97</v>
       </c>
       <c r="I7">
-        <v>-3.1</v>
+        <v>-5.49</v>
       </c>
       <c r="J7">
-        <v>4.14</v>
+        <v>-0.8100000000000001</v>
       </c>
       <c r="K7">
-        <v>1.94</v>
+        <v>-3.08</v>
       </c>
       <c r="L7">
-        <v>91.87</v>
+        <v>92.66</v>
       </c>
       <c r="M7">
-        <v>-29.87</v>
+        <v>-29.92</v>
       </c>
       <c r="N7">
         <v>99</v>
       </c>
       <c r="O7">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="P7">
-        <v>11.51</v>
+        <v>11.38</v>
       </c>
       <c r="Q7">
-        <v>11.56</v>
+        <v>11.55</v>
       </c>
       <c r="R7">
-        <v>11.8</v>
+        <v>11.79</v>
       </c>
       <c r="S7">
-        <v>10.76</v>
+        <v>10.77</v>
       </c>
       <c r="T7">
-        <v>7.56</v>
+        <v>2.3</v>
       </c>
       <c r="U7" t="s">
         <v>46</v>
@@ -1558,43 +1530,43 @@
         <v>2</v>
       </c>
       <c r="Y7">
-        <v>48.47</v>
+        <v>40.82</v>
       </c>
       <c r="Z7">
-        <v>-0</v>
+        <v>-0.05</v>
       </c>
       <c r="AA7">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="AB7">
-        <v>-0.02</v>
+        <v>-0.06</v>
       </c>
       <c r="AC7">
-        <v>29.49</v>
+        <v>17.38</v>
       </c>
       <c r="AD7">
-        <v>30.54</v>
+        <v>25.31</v>
       </c>
       <c r="AE7">
         <v>0.46</v>
       </c>
       <c r="AF7">
-        <v>-8.359999999999999</v>
+        <v>31.47</v>
       </c>
       <c r="AG7">
-        <v>12.52</v>
+        <v>12.53</v>
       </c>
       <c r="AH7">
-        <v>10.61</v>
+        <v>10.57</v>
       </c>
       <c r="AI7">
-        <v>12.59</v>
+        <v>12.58</v>
       </c>
       <c r="AJ7" t="s">
         <v>49</v>
       </c>
       <c r="AK7">
-        <v>28.38</v>
+        <v>27.8</v>
       </c>
     </row>
     <row r="8" spans="1:37">
@@ -1605,58 +1577,58 @@
         <v>45</v>
       </c>
       <c r="C8">
-        <v>4015</v>
+        <v>3997.5</v>
       </c>
       <c r="D8">
-        <v>0.2</v>
+        <v>-0.44</v>
       </c>
       <c r="E8">
         <v>5809.5</v>
       </c>
       <c r="F8">
-        <v>4007.1</v>
+        <v>3997.5</v>
       </c>
       <c r="G8">
-        <v>-30.89</v>
+        <v>-31.19</v>
       </c>
       <c r="H8">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="I8">
-        <v>-1.28</v>
+        <v>-0.74</v>
       </c>
       <c r="J8">
-        <v>-9.26</v>
+        <v>-8.390000000000001</v>
       </c>
       <c r="K8">
-        <v>-7.66</v>
+        <v>-8.08</v>
       </c>
       <c r="L8">
-        <v>-25.03</v>
+        <v>-24.71</v>
       </c>
       <c r="M8">
-        <v>16.76</v>
+        <v>16.7</v>
       </c>
       <c r="N8">
         <v>26</v>
       </c>
       <c r="O8">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="P8">
-        <v>4019.86</v>
+        <v>4013.94</v>
       </c>
       <c r="Q8">
-        <v>4178.9</v>
+        <v>4159.38</v>
       </c>
       <c r="R8">
-        <v>4292.07</v>
+        <v>4284.31</v>
       </c>
       <c r="S8">
-        <v>4553.89</v>
+        <v>4548.04</v>
       </c>
       <c r="T8">
-        <v>-11.83</v>
+        <v>-12.11</v>
       </c>
       <c r="U8" t="s">
         <v>46</v>
@@ -1671,43 +1643,43 @@
         <v>0</v>
       </c>
       <c r="Y8">
-        <v>34.42</v>
+        <v>33.34</v>
       </c>
       <c r="Z8">
-        <v>-91.95999999999999</v>
+        <v>-92.3</v>
       </c>
       <c r="AA8">
-        <v>-77.44</v>
+        <v>-80.41</v>
       </c>
       <c r="AB8">
-        <v>-14.53</v>
+        <v>-11.89</v>
       </c>
       <c r="AC8">
-        <v>27.16</v>
+        <v>25.55</v>
       </c>
       <c r="AD8">
-        <v>21.22</v>
+        <v>24.05</v>
       </c>
       <c r="AE8">
-        <v>95.23</v>
+        <v>95.70999999999999</v>
       </c>
       <c r="AF8">
-        <v>-55.64</v>
+        <v>-36.85</v>
       </c>
       <c r="AG8">
-        <v>4462.39</v>
+        <v>4435.95</v>
       </c>
       <c r="AH8">
-        <v>3895.4</v>
+        <v>3882.8</v>
       </c>
       <c r="AI8">
-        <v>4295.89</v>
+        <v>4288.14</v>
       </c>
       <c r="AJ8" t="s">
         <v>49</v>
       </c>
       <c r="AK8">
-        <v>63.65</v>
+        <v>65.48999999999999</v>
       </c>
     </row>
     <row r="9" spans="1:37">
@@ -1718,10 +1690,10 @@
         <v>45</v>
       </c>
       <c r="C9">
-        <v>11155</v>
+        <v>11025</v>
       </c>
       <c r="D9">
-        <v>0.9</v>
+        <v>-1.17</v>
       </c>
       <c r="E9">
         <v>13052</v>
@@ -1730,46 +1702,46 @@
         <v>10362</v>
       </c>
       <c r="G9">
-        <v>-14.53</v>
+        <v>-15.53</v>
       </c>
       <c r="H9">
-        <v>7.65</v>
+        <v>6.4</v>
       </c>
       <c r="I9">
-        <v>1.28</v>
+        <v>-0.68</v>
       </c>
       <c r="J9">
-        <v>-4.8</v>
+        <v>-5.91</v>
       </c>
       <c r="K9">
-        <v>-1.6</v>
+        <v>-2.03</v>
       </c>
       <c r="L9">
-        <v>-11.82</v>
+        <v>-11.1</v>
       </c>
       <c r="M9">
-        <v>8.41</v>
+        <v>8.24</v>
       </c>
       <c r="N9">
         <v>38</v>
       </c>
       <c r="O9">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="P9">
-        <v>11093.2</v>
+        <v>11078.2</v>
       </c>
       <c r="Q9">
-        <v>11110.95</v>
+        <v>11082.75</v>
       </c>
       <c r="R9">
-        <v>11537.48</v>
+        <v>11523.44</v>
       </c>
       <c r="S9">
-        <v>11720.18</v>
+        <v>11718.23</v>
       </c>
       <c r="T9">
-        <v>-4.82</v>
+        <v>-5.92</v>
       </c>
       <c r="U9" t="s">
         <v>46</v>
@@ -1784,34 +1756,34 @@
         <v>0</v>
       </c>
       <c r="Y9">
-        <v>48.12</v>
+        <v>44.16</v>
       </c>
       <c r="Z9">
-        <v>-135.15</v>
+        <v>-128.34</v>
       </c>
       <c r="AA9">
-        <v>-173.95</v>
+        <v>-164.83</v>
       </c>
       <c r="AB9">
-        <v>38.81</v>
+        <v>36.49</v>
       </c>
       <c r="AC9">
-        <v>95.09</v>
+        <v>88.76000000000001</v>
       </c>
       <c r="AD9">
-        <v>93.05</v>
+        <v>91.14</v>
       </c>
       <c r="AE9">
-        <v>191.82</v>
+        <v>190.76</v>
       </c>
       <c r="AF9">
-        <v>-28.95</v>
+        <v>23.7</v>
       </c>
       <c r="AG9">
-        <v>11613.53</v>
+        <v>11532.95</v>
       </c>
       <c r="AH9">
-        <v>10608.37</v>
+        <v>10632.55</v>
       </c>
       <c r="AI9">
         <v>11371.08</v>
@@ -1820,7 +1792,7 @@
         <v>49</v>
       </c>
       <c r="AK9">
-        <v>25.86</v>
+        <v>23.05</v>
       </c>
     </row>
   </sheetData>
@@ -1981,47 +1953,12 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="3" t="s">
         <v>51</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="D2" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="F2" s="3" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6">
-      <c r="A3" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="B3" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="C3" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="D3" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="E3" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="F3" s="4" t="s">
-        <v>60</v>
       </c>
     </row>
     <row r="5" spans="1:6">
       <c r="A5" s="2" t="s">
-        <v>61</v>
+        <v>52</v>
       </c>
       <c r="B5" s="2"/>
       <c r="C5" s="2"/>
@@ -2029,1108 +1966,1108 @@
       <c r="E5" s="2"/>
     </row>
     <row r="6" spans="1:6">
-      <c r="A6" s="3" t="s">
+      <c r="A6" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B6" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>65</v>
+      <c r="B6" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>56</v>
       </c>
     </row>
     <row r="7" spans="1:6">
-      <c r="A7" s="5" t="s">
+      <c r="A7" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B7" s="5" t="s">
+      <c r="B7" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C7" s="6">
-        <v>-5.05</v>
-      </c>
-      <c r="D7" s="6">
+      <c r="C7" s="5">
         <v>-4.88</v>
       </c>
-      <c r="E7" s="7">
-        <v>0.17</v>
+      <c r="D7" s="5">
+        <v>-6.66</v>
+      </c>
+      <c r="E7" s="6">
+        <v>-1.78</v>
       </c>
     </row>
     <row r="8" spans="1:6">
-      <c r="A8" s="5" t="s">
+      <c r="A8" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B8" s="5" t="s">
+      <c r="B8" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C8" s="6">
-        <v>-11.78</v>
-      </c>
-      <c r="D8" s="6">
+      <c r="C8" s="5">
         <v>-9.869999999999999</v>
       </c>
-      <c r="E8" s="7">
-        <v>1.91</v>
+      <c r="D8" s="5">
+        <v>-11.28</v>
+      </c>
+      <c r="E8" s="6">
+        <v>-1.41</v>
       </c>
     </row>
     <row r="9" spans="1:6">
-      <c r="A9" s="5" t="s">
+      <c r="A9" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B9" s="5" t="s">
+      <c r="B9" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C9" s="6">
-        <v>-3.74</v>
-      </c>
-      <c r="D9" s="6">
+      <c r="C9" s="5">
         <v>-3.3</v>
       </c>
-      <c r="E9" s="7">
-        <v>0.44</v>
+      <c r="D9" s="5">
+        <v>-3.31</v>
+      </c>
+      <c r="E9" s="6">
+        <v>-0.01</v>
       </c>
     </row>
     <row r="10" spans="1:6">
-      <c r="A10" s="5" t="s">
+      <c r="A10" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="B10" s="5" t="s">
+      <c r="B10" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C10" s="6">
-        <v>-6.57</v>
-      </c>
-      <c r="D10" s="6">
+      <c r="C10" s="5">
         <v>-7.22</v>
       </c>
-      <c r="E10" s="8">
-        <v>-0.65</v>
+      <c r="D10" s="5">
+        <v>-6.65</v>
+      </c>
+      <c r="E10" s="7">
+        <v>0.57</v>
       </c>
     </row>
     <row r="11" spans="1:6">
-      <c r="A11" s="5" t="s">
+      <c r="A11" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="B11" s="5" t="s">
+      <c r="B11" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C11" s="6">
-        <v>-7.04</v>
-      </c>
-      <c r="D11" s="6">
+      <c r="C11" s="5">
         <v>-5.31</v>
       </c>
-      <c r="E11" s="7">
-        <v>1.73</v>
+      <c r="D11" s="5">
+        <v>-10.02</v>
+      </c>
+      <c r="E11" s="6">
+        <v>-4.71</v>
       </c>
     </row>
     <row r="12" spans="1:6">
-      <c r="A12" s="5" t="s">
+      <c r="A12" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="B12" s="5" t="s">
+      <c r="B12" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C12" s="6">
-        <v>0.53</v>
-      </c>
-      <c r="D12" s="6">
+      <c r="C12" s="5">
         <v>4.14</v>
       </c>
-      <c r="E12" s="7">
-        <v>3.61</v>
+      <c r="D12" s="5">
+        <v>-0.8100000000000001</v>
+      </c>
+      <c r="E12" s="6">
+        <v>-4.95</v>
       </c>
     </row>
     <row r="13" spans="1:6">
-      <c r="A13" s="5" t="s">
+      <c r="A13" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="B13" s="5" t="s">
+      <c r="B13" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C13" s="6">
-        <v>-8.83</v>
-      </c>
-      <c r="D13" s="6">
+      <c r="C13" s="5">
         <v>-9.26</v>
       </c>
-      <c r="E13" s="8">
+      <c r="D13" s="5">
+        <v>-8.390000000000001</v>
+      </c>
+      <c r="E13" s="7">
+        <v>0.87</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C14" s="5">
+        <v>-4.8</v>
+      </c>
+      <c r="D14" s="5">
+        <v>-5.91</v>
+      </c>
+      <c r="E14" s="6">
+        <v>-1.11</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="A15" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C15" s="5">
+        <v>-4.89</v>
+      </c>
+      <c r="D15" s="5">
+        <v>-5.13</v>
+      </c>
+      <c r="E15" s="6">
+        <v>-0.24</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="A16" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C16" s="5">
+        <v>-2.03</v>
+      </c>
+      <c r="D16" s="5">
+        <v>-4.53</v>
+      </c>
+      <c r="E16" s="6">
+        <v>-2.5</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C17" s="5">
+        <v>-0.57</v>
+      </c>
+      <c r="D17" s="5">
+        <v>-0.51</v>
+      </c>
+      <c r="E17" s="7">
+        <v>0.06</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C18" s="5">
+        <v>-0.96</v>
+      </c>
+      <c r="D18" s="5">
+        <v>-2.58</v>
+      </c>
+      <c r="E18" s="6">
+        <v>-1.62</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C19" s="5">
+        <v>2.44</v>
+      </c>
+      <c r="D19" s="5">
+        <v>-2.67</v>
+      </c>
+      <c r="E19" s="6">
+        <v>-5.11</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C20" s="5">
+        <v>-3.1</v>
+      </c>
+      <c r="D20" s="5">
+        <v>-5.49</v>
+      </c>
+      <c r="E20" s="6">
+        <v>-2.39</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C21" s="5">
+        <v>-1.28</v>
+      </c>
+      <c r="D21" s="5">
+        <v>-0.74</v>
+      </c>
+      <c r="E21" s="7">
+        <v>0.54</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C22" s="5">
+        <v>1.28</v>
+      </c>
+      <c r="D22" s="5">
+        <v>-0.68</v>
+      </c>
+      <c r="E22" s="6">
+        <v>-1.96</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C23" s="5">
+        <v>35.35</v>
+      </c>
+      <c r="D23" s="5">
+        <v>31.31</v>
+      </c>
+      <c r="E23" s="6">
+        <v>-4.04</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C24" s="5">
+        <v>-47.43</v>
+      </c>
+      <c r="D24" s="5">
+        <v>-48.29</v>
+      </c>
+      <c r="E24" s="6">
+        <v>-0.86</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B25" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C25" s="5">
+        <v>11.8</v>
+      </c>
+      <c r="D25" s="5">
+        <v>11.96</v>
+      </c>
+      <c r="E25" s="7">
+        <v>0.16</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C26" s="5">
+        <v>31.02</v>
+      </c>
+      <c r="D26" s="5">
+        <v>28.15</v>
+      </c>
+      <c r="E26" s="6">
+        <v>-2.87</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B27" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C27" s="5">
+        <v>69.95999999999999</v>
+      </c>
+      <c r="D27" s="5">
+        <v>54.47</v>
+      </c>
+      <c r="E27" s="6">
+        <v>-15.49</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B28" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C28" s="5">
+        <v>91.87</v>
+      </c>
+      <c r="D28" s="5">
+        <v>92.66</v>
+      </c>
+      <c r="E28" s="7">
+        <v>0.79</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="B29" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C29" s="5">
+        <v>-25.03</v>
+      </c>
+      <c r="D29" s="5">
+        <v>-24.71</v>
+      </c>
+      <c r="E29" s="7">
+        <v>0.32</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="B30" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C30" s="5">
+        <v>-11.82</v>
+      </c>
+      <c r="D30" s="5">
+        <v>-11.1</v>
+      </c>
+      <c r="E30" s="7">
+        <v>0.72</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5">
+      <c r="A31" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B31" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C31" s="5">
+        <v>1.22</v>
+      </c>
+      <c r="D31" s="5">
+        <v>-2.36</v>
+      </c>
+      <c r="E31" s="6">
+        <v>-3.58</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5">
+      <c r="A32" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B32" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C32" s="5">
+        <v>-16.43</v>
+      </c>
+      <c r="D32" s="5">
+        <v>-18.03</v>
+      </c>
+      <c r="E32" s="6">
+        <v>-1.6</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5">
+      <c r="A33" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B33" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C33" s="5">
+        <v>3.6</v>
+      </c>
+      <c r="D33" s="5">
+        <v>1.61</v>
+      </c>
+      <c r="E33" s="6">
+        <v>-1.99</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5">
+      <c r="A34" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B34" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C34" s="5">
+        <v>1.37</v>
+      </c>
+      <c r="D34" s="5">
+        <v>-0.07000000000000001</v>
+      </c>
+      <c r="E34" s="6">
+        <v>-1.44</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5">
+      <c r="A35" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B35" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C35" s="5">
+        <v>-1.18</v>
+      </c>
+      <c r="D35" s="5">
+        <v>-6.85</v>
+      </c>
+      <c r="E35" s="6">
+        <v>-5.67</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5">
+      <c r="A36" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B36" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C36" s="5">
+        <v>1.94</v>
+      </c>
+      <c r="D36" s="5">
+        <v>-3.08</v>
+      </c>
+      <c r="E36" s="6">
+        <v>-5.02</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5">
+      <c r="A37" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="B37" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C37" s="5">
+        <v>-7.66</v>
+      </c>
+      <c r="D37" s="5">
+        <v>-8.08</v>
+      </c>
+      <c r="E37" s="6">
+        <v>-0.42</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5">
+      <c r="A38" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="B38" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C38" s="5">
+        <v>-1.6</v>
+      </c>
+      <c r="D38" s="5">
+        <v>-2.03</v>
+      </c>
+      <c r="E38" s="6">
         <v>-0.43</v>
       </c>
     </row>
-    <row r="14" spans="1:6">
-      <c r="A14" s="5" t="s">
+    <row r="39" spans="1:5">
+      <c r="A39" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B39" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C39" s="5">
+        <v>-8.17</v>
+      </c>
+      <c r="D39" s="5">
+        <v>-9.890000000000001</v>
+      </c>
+      <c r="E39" s="6">
+        <v>-1.72</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5">
+      <c r="A40" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B40" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C40" s="5">
+        <v>-46.6</v>
+      </c>
+      <c r="D40" s="5">
+        <v>-47.78</v>
+      </c>
+      <c r="E40" s="6">
+        <v>-1.18</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5">
+      <c r="A41" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B41" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C41" s="5">
+        <v>-5.61</v>
+      </c>
+      <c r="D41" s="5">
+        <v>-6.82</v>
+      </c>
+      <c r="E41" s="6">
+        <v>-1.21</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5">
+      <c r="A42" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B42" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C42" s="5">
+        <v>-15.02</v>
+      </c>
+      <c r="D42" s="5">
+        <v>-16.86</v>
+      </c>
+      <c r="E42" s="6">
+        <v>-1.84</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5">
+      <c r="A43" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B43" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C43" s="5">
+        <v>-8.59</v>
+      </c>
+      <c r="D43" s="5">
+        <v>-13.65</v>
+      </c>
+      <c r="E43" s="6">
+        <v>-5.06</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5">
+      <c r="A44" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B44" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C44" s="5">
+        <v>-16.88</v>
+      </c>
+      <c r="D44" s="5">
+        <v>-20.83</v>
+      </c>
+      <c r="E44" s="6">
+        <v>-3.95</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5">
+      <c r="A45" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="B45" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C45" s="5">
+        <v>-30.89</v>
+      </c>
+      <c r="D45" s="5">
+        <v>-31.19</v>
+      </c>
+      <c r="E45" s="6">
+        <v>-0.3</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5">
+      <c r="A46" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="B14" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C14" s="6">
-        <v>-4.19</v>
-      </c>
-      <c r="D14" s="6">
-        <v>-4.8</v>
-      </c>
-      <c r="E14" s="8">
-        <v>-0.61</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15" s="5" t="s">
+      <c r="B46" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C46" s="5">
+        <v>-14.53</v>
+      </c>
+      <c r="D46" s="5">
+        <v>-15.53</v>
+      </c>
+      <c r="E46" s="6">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5">
+      <c r="A47" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B15" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C15" s="6">
-        <v>0.03</v>
-      </c>
-      <c r="D15" s="6">
-        <v>-4.89</v>
-      </c>
-      <c r="E15" s="8">
-        <v>-4.92</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16" s="5" t="s">
+      <c r="B47" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C47" s="5">
+        <v>390</v>
+      </c>
+      <c r="D47" s="5">
+        <v>382.7</v>
+      </c>
+      <c r="E47" s="6">
+        <v>-7.3</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5">
+      <c r="A48" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B16" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C16" s="6">
-        <v>-4.74</v>
-      </c>
-      <c r="D16" s="6">
-        <v>-2.03</v>
-      </c>
-      <c r="E16" s="7">
-        <v>2.71</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5">
-      <c r="A17" s="5" t="s">
+      <c r="B48" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C48" s="5">
+        <v>49.14</v>
+      </c>
+      <c r="D48" s="5">
+        <v>47.59</v>
+      </c>
+      <c r="E48" s="6">
+        <v>-1.55</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5">
+      <c r="A49" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B17" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C17" s="6">
-        <v>-0.21</v>
-      </c>
-      <c r="D17" s="6">
-        <v>-0.57</v>
-      </c>
-      <c r="E17" s="8">
-        <v>-0.36</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5">
-      <c r="A18" s="5" t="s">
+      <c r="B49" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C49" s="5">
+        <v>3191</v>
+      </c>
+      <c r="D49" s="5">
+        <v>3150</v>
+      </c>
+      <c r="E49" s="6">
+        <v>-41</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5">
+      <c r="A50" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="B18" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C18" s="6">
-        <v>0.15</v>
-      </c>
-      <c r="D18" s="6">
-        <v>-0.96</v>
-      </c>
-      <c r="E18" s="8">
-        <v>-1.11</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5">
-      <c r="A19" s="5" t="s">
+      <c r="B50" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C50" s="5">
+        <v>977</v>
+      </c>
+      <c r="D50" s="5">
+        <v>955.9</v>
+      </c>
+      <c r="E50" s="6">
+        <v>-21.1</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5">
+      <c r="A51" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="B19" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C19" s="6">
-        <v>-0.7</v>
-      </c>
-      <c r="D19" s="6">
-        <v>2.44</v>
-      </c>
-      <c r="E19" s="7">
-        <v>3.14</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5">
-      <c r="A20" s="5" t="s">
+      <c r="B51" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C51" s="5">
+        <v>14.26</v>
+      </c>
+      <c r="D51" s="5">
+        <v>13.47</v>
+      </c>
+      <c r="E51" s="6">
+        <v>-0.79</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5">
+      <c r="A52" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="B20" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C20" s="6">
-        <v>-7.7</v>
-      </c>
-      <c r="D20" s="6">
-        <v>-3.1</v>
-      </c>
-      <c r="E20" s="7">
-        <v>4.6</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5">
-      <c r="A21" s="5" t="s">
+      <c r="B52" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C52" s="5">
+        <v>11.57</v>
+      </c>
+      <c r="D52" s="5">
+        <v>11.02</v>
+      </c>
+      <c r="E52" s="6">
+        <v>-0.55</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5">
+      <c r="A53" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="B21" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C21" s="6">
-        <v>-1.84</v>
-      </c>
-      <c r="D21" s="6">
-        <v>-1.28</v>
-      </c>
-      <c r="E21" s="7">
-        <v>0.5600000000000001</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5">
-      <c r="A22" s="5" t="s">
+      <c r="B53" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C53" s="5">
+        <v>4015</v>
+      </c>
+      <c r="D53" s="5">
+        <v>3997.5</v>
+      </c>
+      <c r="E53" s="6">
+        <v>-17.5</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5">
+      <c r="A54" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="B22" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C22" s="6">
-        <v>2.71</v>
-      </c>
-      <c r="D22" s="6">
-        <v>1.28</v>
-      </c>
-      <c r="E22" s="8">
+      <c r="B54" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C54" s="5">
+        <v>11155</v>
+      </c>
+      <c r="D54" s="5">
+        <v>11025</v>
+      </c>
+      <c r="E54" s="6">
+        <v>-130</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5">
+      <c r="A55" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B55" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C55" s="5">
+        <v>44.79</v>
+      </c>
+      <c r="D55" s="5">
+        <v>41.11</v>
+      </c>
+      <c r="E55" s="6">
+        <v>-3.68</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5">
+      <c r="A56" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B56" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C56" s="5">
+        <v>36.7</v>
+      </c>
+      <c r="D56" s="5">
+        <v>31.61</v>
+      </c>
+      <c r="E56" s="6">
+        <v>-5.09</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5">
+      <c r="A57" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B57" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C57" s="5">
+        <v>45.66</v>
+      </c>
+      <c r="D57" s="5">
+        <v>41.66</v>
+      </c>
+      <c r="E57" s="6">
+        <v>-4</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5">
+      <c r="A58" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B58" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C58" s="5">
+        <v>43.44</v>
+      </c>
+      <c r="D58" s="5">
+        <v>38.61</v>
+      </c>
+      <c r="E58" s="6">
+        <v>-4.83</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5">
+      <c r="A59" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B59" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C59" s="5">
+        <v>48.85</v>
+      </c>
+      <c r="D59" s="5">
+        <v>39.85</v>
+      </c>
+      <c r="E59" s="6">
+        <v>-9</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5">
+      <c r="A60" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B60" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C60" s="5">
+        <v>48.47</v>
+      </c>
+      <c r="D60" s="5">
+        <v>40.82</v>
+      </c>
+      <c r="E60" s="6">
+        <v>-7.65</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5">
+      <c r="A61" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="B61" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C61" s="5">
+        <v>34.42</v>
+      </c>
+      <c r="D61" s="5">
+        <v>33.34</v>
+      </c>
+      <c r="E61" s="6">
+        <v>-1.08</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5">
+      <c r="A62" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="B62" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C62" s="5">
+        <v>48.12</v>
+      </c>
+      <c r="D62" s="5">
+        <v>44.16</v>
+      </c>
+      <c r="E62" s="6">
+        <v>-3.96</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5">
+      <c r="A63" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B63" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C63" s="5">
+        <v>5.17</v>
+      </c>
+      <c r="D63" s="5">
+        <v>-30.33</v>
+      </c>
+      <c r="E63" s="6">
+        <v>-35.5</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5">
+      <c r="A64" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B64" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C64" s="5">
+        <v>2.98</v>
+      </c>
+      <c r="D64" s="5">
+        <v>-19.88</v>
+      </c>
+      <c r="E64" s="6">
+        <v>-22.86</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5">
+      <c r="A65" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B65" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C65" s="5">
+        <v>-12.22</v>
+      </c>
+      <c r="D65" s="5">
+        <v>-13.65</v>
+      </c>
+      <c r="E65" s="6">
         <v>-1.43</v>
       </c>
     </row>
-    <row r="23" spans="1:5">
-      <c r="A23" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B23" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C23" s="6">
-        <v>34.91</v>
-      </c>
-      <c r="D23" s="6">
-        <v>35.35</v>
-      </c>
-      <c r="E23" s="7">
-        <v>0.44</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5">
-      <c r="A24" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B24" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C24" s="6">
-        <v>-47.82</v>
-      </c>
-      <c r="D24" s="6">
-        <v>-47.43</v>
-      </c>
-      <c r="E24" s="7">
-        <v>0.39</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5">
-      <c r="A25" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B25" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C25" s="6">
-        <v>10.03</v>
-      </c>
-      <c r="D25" s="6">
-        <v>11.8</v>
-      </c>
-      <c r="E25" s="7">
-        <v>1.77</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5">
-      <c r="A26" s="5" t="s">
+    <row r="66" spans="1:5">
+      <c r="A66" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="B26" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C26" s="6">
-        <v>32.11</v>
-      </c>
-      <c r="D26" s="6">
-        <v>31.02</v>
-      </c>
-      <c r="E26" s="8">
-        <v>-1.09</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5">
-      <c r="A27" s="5" t="s">
+      <c r="B66" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C66" s="5">
+        <v>-27.17</v>
+      </c>
+      <c r="D66" s="5">
+        <v>-1.32</v>
+      </c>
+      <c r="E66" s="7">
+        <v>25.85</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5">
+      <c r="A67" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="B27" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C27" s="6">
-        <v>68.09999999999999</v>
-      </c>
-      <c r="D27" s="6">
-        <v>69.95999999999999</v>
-      </c>
-      <c r="E27" s="7">
-        <v>1.86</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5">
-      <c r="A28" s="5" t="s">
+      <c r="B67" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C67" s="5">
+        <v>-28.09</v>
+      </c>
+      <c r="D67" s="5">
+        <v>18.57</v>
+      </c>
+      <c r="E67" s="7">
+        <v>46.66</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5">
+      <c r="A68" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="B28" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C28" s="6">
-        <v>80.51000000000001</v>
-      </c>
-      <c r="D28" s="6">
-        <v>91.87</v>
-      </c>
-      <c r="E28" s="7">
-        <v>11.36</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5">
-      <c r="A29" s="5" t="s">
+      <c r="B68" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C68" s="5">
+        <v>-8.359999999999999</v>
+      </c>
+      <c r="D68" s="5">
+        <v>31.47</v>
+      </c>
+      <c r="E68" s="7">
+        <v>39.83</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5">
+      <c r="A69" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="B29" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C29" s="6">
-        <v>-27.08</v>
-      </c>
-      <c r="D29" s="6">
-        <v>-25.03</v>
-      </c>
-      <c r="E29" s="7">
-        <v>2.05</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5">
-      <c r="A30" s="5" t="s">
+      <c r="B69" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C69" s="5">
+        <v>-55.64</v>
+      </c>
+      <c r="D69" s="5">
+        <v>-36.85</v>
+      </c>
+      <c r="E69" s="7">
+        <v>18.79</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5">
+      <c r="A70" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="B30" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C30" s="6">
-        <v>-11.61</v>
-      </c>
-      <c r="D30" s="6">
-        <v>-11.82</v>
-      </c>
-      <c r="E30" s="8">
-        <v>-0.21</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5">
-      <c r="A31" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B31" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C31" s="6">
-        <v>-0.18</v>
-      </c>
-      <c r="D31" s="6">
-        <v>1.22</v>
-      </c>
-      <c r="E31" s="7">
-        <v>1.4</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5">
-      <c r="A32" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B32" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C32" s="6">
-        <v>-20.06</v>
-      </c>
-      <c r="D32" s="6">
-        <v>-16.43</v>
-      </c>
-      <c r="E32" s="7">
-        <v>3.63</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5">
-      <c r="A33" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B33" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C33" s="6">
-        <v>1.28</v>
-      </c>
-      <c r="D33" s="6">
-        <v>3.6</v>
-      </c>
-      <c r="E33" s="7">
-        <v>2.32</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5">
-      <c r="A34" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B34" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C34" s="6">
-        <v>3.02</v>
-      </c>
-      <c r="D34" s="6">
-        <v>1.37</v>
-      </c>
-      <c r="E34" s="8">
-        <v>-1.65</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5">
-      <c r="A35" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B35" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C35" s="6">
-        <v>0.43</v>
-      </c>
-      <c r="D35" s="6">
-        <v>-1.18</v>
-      </c>
-      <c r="E35" s="8">
-        <v>-1.61</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5">
-      <c r="A36" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B36" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C36" s="6">
-        <v>2.34</v>
-      </c>
-      <c r="D36" s="6">
-        <v>1.94</v>
-      </c>
-      <c r="E36" s="8">
-        <v>-0.4</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5">
-      <c r="A37" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B37" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C37" s="6">
-        <v>-8.880000000000001</v>
-      </c>
-      <c r="D37" s="6">
-        <v>-7.66</v>
-      </c>
-      <c r="E37" s="7">
-        <v>1.22</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5">
-      <c r="A38" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="B38" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C38" s="6">
-        <v>-3.77</v>
-      </c>
-      <c r="D38" s="6">
-        <v>-1.6</v>
-      </c>
-      <c r="E38" s="7">
-        <v>2.17</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5">
-      <c r="A39" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B39" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C39" s="6">
-        <v>-8.15</v>
-      </c>
-      <c r="D39" s="6">
-        <v>-8.17</v>
-      </c>
-      <c r="E39" s="8">
-        <v>-0.02</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5">
-      <c r="A40" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B40" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C40" s="6">
-        <v>-48.59</v>
-      </c>
-      <c r="D40" s="6">
-        <v>-46.6</v>
-      </c>
-      <c r="E40" s="7">
-        <v>1.99</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5">
-      <c r="A41" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B41" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C41" s="6">
-        <v>-6.33</v>
-      </c>
-      <c r="D41" s="6">
-        <v>-5.61</v>
-      </c>
-      <c r="E41" s="7">
-        <v>0.72</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5">
-      <c r="A42" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B42" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C42" s="6">
-        <v>-14.59</v>
-      </c>
-      <c r="D42" s="6">
-        <v>-15.02</v>
-      </c>
-      <c r="E42" s="8">
-        <v>-0.43</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5">
-      <c r="A43" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B43" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C43" s="6">
-        <v>-9.49</v>
-      </c>
-      <c r="D43" s="6">
-        <v>-8.59</v>
-      </c>
-      <c r="E43" s="7">
-        <v>0.9</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5">
-      <c r="A44" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B44" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C44" s="6">
-        <v>-18.18</v>
-      </c>
-      <c r="D44" s="6">
-        <v>-16.88</v>
-      </c>
-      <c r="E44" s="7">
-        <v>1.3</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5">
-      <c r="A45" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B45" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C45" s="6">
-        <v>-31.03</v>
-      </c>
-      <c r="D45" s="6">
-        <v>-30.89</v>
-      </c>
-      <c r="E45" s="7">
-        <v>0.14</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5">
-      <c r="A46" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="B46" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C46" s="6">
-        <v>-15.29</v>
-      </c>
-      <c r="D46" s="6">
-        <v>-14.53</v>
-      </c>
-      <c r="E46" s="7">
-        <v>0.76</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5">
-      <c r="A47" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B47" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C47" s="6">
-        <v>390.1</v>
-      </c>
-      <c r="D47" s="6">
-        <v>390</v>
-      </c>
-      <c r="E47" s="8">
-        <v>-0.1</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5">
-      <c r="A48" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B48" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C48" s="6">
-        <v>48.06</v>
-      </c>
-      <c r="D48" s="6">
-        <v>49.14</v>
-      </c>
-      <c r="E48" s="7">
-        <v>1.08</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5">
-      <c r="A49" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B49" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C49" s="6">
-        <v>3166.5</v>
-      </c>
-      <c r="D49" s="6">
-        <v>3191</v>
-      </c>
-      <c r="E49" s="7">
-        <v>24.5</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5">
-      <c r="A50" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B50" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C50" s="6">
-        <v>982</v>
-      </c>
-      <c r="D50" s="6">
-        <v>977</v>
-      </c>
-      <c r="E50" s="8">
-        <v>-5</v>
-      </c>
-    </row>
-    <row r="51" spans="1:5">
-      <c r="A51" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B51" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C51" s="6">
-        <v>14.12</v>
-      </c>
-      <c r="D51" s="6">
-        <v>14.26</v>
-      </c>
-      <c r="E51" s="7">
-        <v>0.14</v>
-      </c>
-    </row>
-    <row r="52" spans="1:5">
-      <c r="A52" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B52" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C52" s="6">
-        <v>11.39</v>
-      </c>
-      <c r="D52" s="6">
-        <v>11.57</v>
-      </c>
-      <c r="E52" s="7">
-        <v>0.18</v>
-      </c>
-    </row>
-    <row r="53" spans="1:5">
-      <c r="A53" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B53" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C53" s="6">
-        <v>4007.1</v>
-      </c>
-      <c r="D53" s="6">
-        <v>4015</v>
-      </c>
-      <c r="E53" s="7">
-        <v>7.9</v>
-      </c>
-    </row>
-    <row r="54" spans="1:5">
-      <c r="A54" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="B54" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C54" s="6">
-        <v>11056</v>
-      </c>
-      <c r="D54" s="6">
-        <v>11155</v>
-      </c>
-      <c r="E54" s="7">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="55" spans="1:5">
-      <c r="A55" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B55" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C55" s="6">
-        <v>44.84</v>
-      </c>
-      <c r="D55" s="6">
-        <v>44.79</v>
-      </c>
-      <c r="E55" s="8">
-        <v>-0.05</v>
-      </c>
-    </row>
-    <row r="56" spans="1:5">
-      <c r="A56" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B56" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C56" s="6">
-        <v>29.34</v>
-      </c>
-      <c r="D56" s="6">
-        <v>36.7</v>
-      </c>
-      <c r="E56" s="7">
-        <v>7.36</v>
-      </c>
-    </row>
-    <row r="57" spans="1:5">
-      <c r="A57" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B57" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C57" s="6">
-        <v>42.6</v>
-      </c>
-      <c r="D57" s="6">
-        <v>45.66</v>
-      </c>
-      <c r="E57" s="7">
-        <v>3.06</v>
-      </c>
-    </row>
-    <row r="58" spans="1:5">
-      <c r="A58" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B58" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C58" s="6">
-        <v>44.68</v>
-      </c>
-      <c r="D58" s="6">
-        <v>43.44</v>
-      </c>
-      <c r="E58" s="8">
-        <v>-1.24</v>
-      </c>
-    </row>
-    <row r="59" spans="1:5">
-      <c r="A59" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B59" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C59" s="6">
-        <v>46.87</v>
-      </c>
-      <c r="D59" s="6">
-        <v>48.85</v>
-      </c>
-      <c r="E59" s="7">
-        <v>1.98</v>
-      </c>
-    </row>
-    <row r="60" spans="1:5">
-      <c r="A60" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B60" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C60" s="6">
-        <v>45.36</v>
-      </c>
-      <c r="D60" s="6">
-        <v>48.47</v>
-      </c>
-      <c r="E60" s="7">
-        <v>3.11</v>
-      </c>
-    </row>
-    <row r="61" spans="1:5">
-      <c r="A61" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B61" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C61" s="6">
-        <v>33.52</v>
-      </c>
-      <c r="D61" s="6">
-        <v>34.42</v>
-      </c>
-      <c r="E61" s="7">
-        <v>0.9</v>
-      </c>
-    </row>
-    <row r="62" spans="1:5">
-      <c r="A62" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="B62" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C62" s="6">
-        <v>44.61</v>
-      </c>
-      <c r="D62" s="6">
-        <v>48.12</v>
-      </c>
-      <c r="E62" s="7">
-        <v>3.51</v>
-      </c>
-    </row>
-    <row r="63" spans="1:5">
-      <c r="A63" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B63" s="5" t="s">
+      <c r="B70" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="C63" s="6">
-        <v>55.16</v>
-      </c>
-      <c r="D63" s="6">
-        <v>5.17</v>
-      </c>
-      <c r="E63" s="8">
-        <v>-49.99</v>
-      </c>
-    </row>
-    <row r="64" spans="1:5">
-      <c r="A64" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B64" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C64" s="6">
-        <v>15.66</v>
-      </c>
-      <c r="D64" s="6">
-        <v>2.98</v>
-      </c>
-      <c r="E64" s="8">
-        <v>-12.68</v>
-      </c>
-    </row>
-    <row r="65" spans="1:5">
-      <c r="A65" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B65" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C65" s="6">
-        <v>-49.97</v>
-      </c>
-      <c r="D65" s="6">
-        <v>-12.22</v>
-      </c>
-      <c r="E65" s="7">
-        <v>37.75</v>
-      </c>
-    </row>
-    <row r="66" spans="1:5">
-      <c r="A66" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B66" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C66" s="6">
-        <v>29.25</v>
-      </c>
-      <c r="D66" s="6">
-        <v>-27.17</v>
-      </c>
-      <c r="E66" s="8">
-        <v>-56.42</v>
-      </c>
-    </row>
-    <row r="67" spans="1:5">
-      <c r="A67" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B67" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C67" s="6">
-        <v>-25.07</v>
-      </c>
-      <c r="D67" s="6">
-        <v>-28.09</v>
-      </c>
-      <c r="E67" s="8">
-        <v>-3.02</v>
-      </c>
-    </row>
-    <row r="68" spans="1:5">
-      <c r="A68" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B68" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C68" s="6">
-        <v>-38.81</v>
-      </c>
-      <c r="D68" s="6">
-        <v>-8.359999999999999</v>
-      </c>
-      <c r="E68" s="7">
-        <v>30.45</v>
-      </c>
-    </row>
-    <row r="69" spans="1:5">
-      <c r="A69" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B69" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C69" s="6">
-        <v>-38.8</v>
-      </c>
-      <c r="D69" s="6">
-        <v>-55.64</v>
-      </c>
-      <c r="E69" s="8">
-        <v>-16.84</v>
-      </c>
-    </row>
-    <row r="70" spans="1:5">
-      <c r="A70" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="B70" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C70" s="6">
-        <v>14.87</v>
-      </c>
-      <c r="D70" s="6">
+      <c r="C70" s="5">
         <v>-28.95</v>
       </c>
-      <c r="E70" s="8">
-        <v>-43.82</v>
+      <c r="D70" s="5">
+        <v>23.7</v>
+      </c>
+      <c r="E70" s="7">
+        <v>52.65</v>
       </c>
     </row>
   </sheetData>
@@ -3156,60 +3093,60 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="28" customHeight="1">
-      <c r="A1" s="9" t="s">
+      <c r="A1" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="C1" s="9" t="s">
-        <v>67</v>
-      </c>
-      <c r="D1" s="9" t="s">
-        <v>68</v>
-      </c>
-      <c r="E1" s="9" t="s">
-        <v>69</v>
-      </c>
-      <c r="F1" s="9" t="s">
-        <v>70</v>
-      </c>
-      <c r="G1" s="9" t="s">
-        <v>71</v>
-      </c>
-      <c r="H1" s="9" t="s">
-        <v>72</v>
-      </c>
-      <c r="I1" s="9" t="s">
-        <v>73</v>
+      <c r="B1" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="C1" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="D1" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="E1" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="F1" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="G1" s="8" t="s">
+        <v>62</v>
+      </c>
+      <c r="H1" s="8" t="s">
+        <v>63</v>
+      </c>
+      <c r="I1" s="8" t="s">
+        <v>64</v>
       </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="10" t="s">
+      <c r="A2" s="9" t="s">
         <v>45</v>
       </c>
-      <c r="B2" s="11">
+      <c r="B2" s="10">
         <v>52.44</v>
       </c>
-      <c r="C2" s="12">
+      <c r="C2" s="11">
         <v>8</v>
       </c>
-      <c r="D2" s="11">
-        <v>43.8</v>
-      </c>
-      <c r="E2" s="11">
+      <c r="D2" s="10">
+        <v>38.9</v>
+      </c>
+      <c r="E2" s="10">
         <v>50</v>
       </c>
-      <c r="F2" s="11">
-        <v>-5.1</v>
-      </c>
-      <c r="G2" s="11">
-        <v>-2.3</v>
-      </c>
-      <c r="H2" s="11">
+      <c r="F2" s="10">
+        <v>-6.6</v>
+      </c>
+      <c r="G2" s="10">
+        <v>-4.9</v>
+      </c>
+      <c r="H2" s="10">
         <v>56.1</v>
       </c>
-      <c r="I2" s="11">
+      <c r="I2" s="10">
         <v>20</v>
       </c>
     </row>
@@ -3311,55 +3248,55 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8">
-      <c r="A1" s="13" t="s">
+      <c r="A1" s="12" t="s">
         <v>37</v>
       </c>
-      <c r="B1" s="13" t="s">
+      <c r="B1" s="12" t="s">
         <v>43</v>
       </c>
-      <c r="C1" s="13" t="s">
+      <c r="C1" s="12" t="s">
         <v>40</v>
       </c>
-      <c r="D1" s="13" t="s">
+      <c r="D1" s="12" t="s">
         <v>39</v>
       </c>
-      <c r="E1" s="13" t="s">
+      <c r="E1" s="12" t="s">
         <v>44</v>
       </c>
-      <c r="F1" s="13" t="s">
+      <c r="F1" s="12" t="s">
         <v>41</v>
       </c>
-      <c r="G1" s="13" t="s">
+      <c r="G1" s="12" t="s">
         <v>38</v>
       </c>
-      <c r="H1" s="13" t="s">
+      <c r="H1" s="12" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="2" spans="1:8">
-      <c r="A2" s="14">
-        <v>0.2726</v>
-      </c>
-      <c r="B2" s="14">
-        <v>0.1676</v>
-      </c>
-      <c r="C2" s="14">
-        <v>0.1589</v>
-      </c>
-      <c r="D2" s="14">
-        <v>0.1467</v>
-      </c>
-      <c r="E2" s="14">
-        <v>0.08410000000000001</v>
-      </c>
-      <c r="F2" s="14">
-        <v>0.04679999999999999</v>
-      </c>
-      <c r="G2" s="14">
-        <v>-0.2632</v>
-      </c>
-      <c r="H2" s="14">
-        <v>-0.2987</v>
+      <c r="A2" s="13">
+        <v>0.2746</v>
+      </c>
+      <c r="B2" s="13">
+        <v>0.167</v>
+      </c>
+      <c r="C2" s="13">
+        <v>0.1552</v>
+      </c>
+      <c r="D2" s="13">
+        <v>0.1435</v>
+      </c>
+      <c r="E2" s="13">
+        <v>0.0824</v>
+      </c>
+      <c r="F2" s="13">
+        <v>0.0423</v>
+      </c>
+      <c r="G2" s="13">
+        <v>-0.2661</v>
+      </c>
+      <c r="H2" s="13">
+        <v>-0.2992</v>
       </c>
     </row>
   </sheetData>

--- a/BIRLA_GROUP_Technical_Metrics.xlsx
+++ b/BIRLA_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="276" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="297" uniqueCount="72">
   <si>
     <t>Symbol</t>
   </si>
@@ -175,7 +175,28 @@
     <t>▶  SIGNAL EVENTS (vs Previous Run)</t>
   </si>
   <si>
-    <t>No signal events detected since last run.</t>
+    <t>Signal</t>
+  </si>
+  <si>
+    <t>Change</t>
+  </si>
+  <si>
+    <t>Direction</t>
+  </si>
+  <si>
+    <t>Prev Value</t>
+  </si>
+  <si>
+    <t>Curr Value</t>
+  </si>
+  <si>
+    <t>Yes → No</t>
+  </si>
+  <si>
+    <t>🔴 BEARISH</t>
+  </si>
+  <si>
+    <t>20 DMA &gt; 50 DMA</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -377,14 +398,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -758,8 +780,8 @@
     <col min="13" max="13" width="10.7109375" customWidth="1"/>
     <col min="14" max="14" width="11.7109375" customWidth="1"/>
     <col min="15" max="15" width="10.7109375" customWidth="1"/>
-    <col min="16" max="16" width="9.7109375" customWidth="1"/>
-    <col min="17" max="19" width="10.7109375" customWidth="1"/>
+    <col min="16" max="17" width="9.7109375" customWidth="1"/>
+    <col min="18" max="19" width="10.7109375" customWidth="1"/>
     <col min="20" max="20" width="22.7109375" customWidth="1"/>
     <col min="21" max="21" width="9.7109375" customWidth="1"/>
     <col min="22" max="22" width="10.7109375" customWidth="1"/>
@@ -899,10 +921,10 @@
         <v>45</v>
       </c>
       <c r="C2">
-        <v>382.7</v>
+        <v>378</v>
       </c>
       <c r="D2">
-        <v>-1.87</v>
+        <v>-1.23</v>
       </c>
       <c r="E2">
         <v>424.7</v>
@@ -911,46 +933,46 @@
         <v>278.9</v>
       </c>
       <c r="G2">
-        <v>-9.890000000000001</v>
+        <v>-11</v>
       </c>
       <c r="H2">
-        <v>37.22</v>
+        <v>35.53</v>
       </c>
       <c r="I2">
-        <v>-5.13</v>
+        <v>-4.79</v>
       </c>
       <c r="J2">
-        <v>-6.66</v>
+        <v>-6.79</v>
       </c>
       <c r="K2">
-        <v>-2.36</v>
+        <v>-3.85</v>
       </c>
       <c r="L2">
-        <v>31.31</v>
+        <v>29.47</v>
       </c>
       <c r="M2">
-        <v>27.46</v>
+        <v>27.06</v>
       </c>
       <c r="N2">
+        <v>62</v>
+      </c>
+      <c r="O2">
         <v>74</v>
       </c>
-      <c r="O2">
-        <v>76</v>
-      </c>
       <c r="P2">
-        <v>392.45</v>
+        <v>388.65</v>
       </c>
       <c r="Q2">
-        <v>396.44</v>
+        <v>394.87</v>
       </c>
       <c r="R2">
-        <v>402.29</v>
+        <v>401.83</v>
       </c>
       <c r="S2">
-        <v>364.27</v>
+        <v>364.36</v>
       </c>
       <c r="T2">
-        <v>5.06</v>
+        <v>3.74</v>
       </c>
       <c r="U2" t="s">
         <v>46</v>
@@ -965,34 +987,34 @@
         <v>2</v>
       </c>
       <c r="Y2">
-        <v>41.11</v>
+        <v>38.89</v>
       </c>
       <c r="Z2">
-        <v>-3.28</v>
+        <v>-4.31</v>
       </c>
       <c r="AA2">
-        <v>-2.31</v>
+        <v>-2.71</v>
       </c>
       <c r="AB2">
-        <v>-0.98</v>
+        <v>-1.61</v>
       </c>
       <c r="AC2">
-        <v>43.34</v>
+        <v>34.53</v>
       </c>
       <c r="AD2">
-        <v>55.47</v>
+        <v>45.57</v>
       </c>
       <c r="AE2">
-        <v>9.859999999999999</v>
+        <v>9.65</v>
       </c>
       <c r="AF2">
-        <v>-30.33</v>
+        <v>69.65000000000001</v>
       </c>
       <c r="AG2">
-        <v>414.04</v>
+        <v>413.19</v>
       </c>
       <c r="AH2">
-        <v>378.84</v>
+        <v>376.55</v>
       </c>
       <c r="AI2">
         <v>372.91</v>
@@ -1001,7 +1023,7 @@
         <v>48</v>
       </c>
       <c r="AK2">
-        <v>24.77</v>
+        <v>27.09</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1012,58 +1034,58 @@
         <v>45</v>
       </c>
       <c r="C3">
-        <v>47.59</v>
+        <v>46.24</v>
       </c>
       <c r="D3">
-        <v>-3.15</v>
+        <v>-2.84</v>
       </c>
       <c r="E3">
-        <v>91.13</v>
+        <v>87.98999999999999</v>
       </c>
       <c r="F3">
-        <v>47.59</v>
+        <v>46.24</v>
       </c>
       <c r="G3">
-        <v>-47.78</v>
+        <v>-47.45</v>
       </c>
       <c r="H3">
         <v>0</v>
       </c>
       <c r="I3">
-        <v>-4.53</v>
+        <v>-6.05</v>
       </c>
       <c r="J3">
-        <v>-11.28</v>
+        <v>-11.91</v>
       </c>
       <c r="K3">
-        <v>-18.03</v>
+        <v>-21.19</v>
       </c>
       <c r="L3">
-        <v>-48.29</v>
+        <v>-49.26</v>
       </c>
       <c r="M3">
-        <v>-26.61</v>
+        <v>-27.55</v>
       </c>
       <c r="N3">
         <v>13</v>
       </c>
       <c r="O3">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="P3">
-        <v>48.62</v>
+        <v>48.02</v>
       </c>
       <c r="Q3">
-        <v>50.37</v>
+        <v>50.08</v>
       </c>
       <c r="R3">
-        <v>54.55</v>
+        <v>54.33</v>
       </c>
       <c r="S3">
-        <v>62.72</v>
+        <v>62.58</v>
       </c>
       <c r="T3">
-        <v>-24.13</v>
+        <v>-26.11</v>
       </c>
       <c r="U3" t="s">
         <v>46</v>
@@ -1078,43 +1100,43 @@
         <v>0</v>
       </c>
       <c r="Y3">
-        <v>31.61</v>
+        <v>27.97</v>
       </c>
       <c r="Z3">
-        <v>-1.76</v>
+        <v>-1.89</v>
       </c>
       <c r="AA3">
-        <v>-1.75</v>
+        <v>-1.78</v>
       </c>
       <c r="AB3">
-        <v>-0.02</v>
+        <v>-0.12</v>
       </c>
       <c r="AC3">
-        <v>30.92</v>
+        <v>29.48</v>
       </c>
       <c r="AD3">
-        <v>33.23</v>
+        <v>32.24</v>
       </c>
       <c r="AE3">
-        <v>1.51</v>
+        <v>1.53</v>
       </c>
       <c r="AF3">
-        <v>-19.88</v>
+        <v>184.13</v>
       </c>
       <c r="AG3">
-        <v>53.39</v>
+        <v>53.5</v>
       </c>
       <c r="AH3">
-        <v>47.36</v>
+        <v>46.66</v>
       </c>
       <c r="AI3">
-        <v>52.83</v>
+        <v>51.45</v>
       </c>
       <c r="AJ3" t="s">
         <v>49</v>
       </c>
       <c r="AK3">
-        <v>41</v>
+        <v>44.42</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1125,10 +1147,10 @@
         <v>45</v>
       </c>
       <c r="C4">
-        <v>3150</v>
+        <v>3100</v>
       </c>
       <c r="D4">
-        <v>-1.28</v>
+        <v>-1.59</v>
       </c>
       <c r="E4">
         <v>3380.5</v>
@@ -1137,97 +1159,97 @@
         <v>2531.1</v>
       </c>
       <c r="G4">
-        <v>-6.82</v>
+        <v>-8.300000000000001</v>
       </c>
       <c r="H4">
-        <v>24.45</v>
+        <v>22.48</v>
       </c>
       <c r="I4">
-        <v>-0.51</v>
+        <v>-0.9</v>
       </c>
       <c r="J4">
-        <v>-3.31</v>
+        <v>-5.78</v>
       </c>
       <c r="K4">
-        <v>1.61</v>
+        <v>-1.29</v>
       </c>
       <c r="L4">
-        <v>11.96</v>
+        <v>10.42</v>
       </c>
       <c r="M4">
-        <v>14.35</v>
+        <v>13.7</v>
       </c>
       <c r="N4">
         <v>50</v>
       </c>
       <c r="O4">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="P4">
-        <v>3164.84</v>
+        <v>3159.2</v>
       </c>
       <c r="Q4">
-        <v>3242.17</v>
+        <v>3228.62</v>
       </c>
       <c r="R4">
-        <v>3231.94</v>
+        <v>3231.06</v>
       </c>
       <c r="S4">
-        <v>2973.12</v>
+        <v>2974.89</v>
       </c>
       <c r="T4">
-        <v>5.95</v>
+        <v>4.21</v>
       </c>
       <c r="U4" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="V4" t="s">
         <v>47</v>
       </c>
       <c r="W4" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="X4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Y4">
-        <v>41.66</v>
+        <v>37.36</v>
       </c>
       <c r="Z4">
-        <v>-26.85</v>
+        <v>-32.45</v>
       </c>
       <c r="AA4">
-        <v>-15.3</v>
+        <v>-18.73</v>
       </c>
       <c r="AB4">
-        <v>-11.55</v>
+        <v>-13.71</v>
       </c>
       <c r="AC4">
-        <v>33.65</v>
+        <v>24.91</v>
       </c>
       <c r="AD4">
-        <v>31.71</v>
+        <v>32.34</v>
       </c>
       <c r="AE4">
-        <v>58.68</v>
+        <v>58.95</v>
       </c>
       <c r="AF4">
-        <v>-13.65</v>
+        <v>33.1</v>
       </c>
       <c r="AG4">
-        <v>3391.14</v>
+        <v>3377.55</v>
       </c>
       <c r="AH4">
-        <v>3093.21</v>
+        <v>3079.7</v>
       </c>
       <c r="AI4">
-        <v>3120.02</v>
+        <v>3297.11</v>
       </c>
       <c r="AJ4" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="AK4">
-        <v>36.14</v>
+        <v>38.93</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1238,58 +1260,58 @@
         <v>45</v>
       </c>
       <c r="C5">
-        <v>955.9</v>
+        <v>955.2</v>
       </c>
       <c r="D5">
-        <v>-2.16</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="E5">
         <v>1149.7</v>
       </c>
       <c r="F5">
-        <v>741.05</v>
+        <v>743.85</v>
       </c>
       <c r="G5">
-        <v>-16.86</v>
+        <v>-16.92</v>
       </c>
       <c r="H5">
-        <v>28.99</v>
+        <v>28.41</v>
       </c>
       <c r="I5">
-        <v>-2.58</v>
+        <v>-1.83</v>
       </c>
       <c r="J5">
-        <v>-6.65</v>
+        <v>-7.92</v>
       </c>
       <c r="K5">
-        <v>-0.07000000000000001</v>
+        <v>1.65</v>
       </c>
       <c r="L5">
-        <v>28.15</v>
+        <v>28.9</v>
       </c>
       <c r="M5">
-        <v>15.52</v>
+        <v>14.75</v>
       </c>
       <c r="N5">
-        <v>62</v>
+        <v>74</v>
       </c>
       <c r="O5">
         <v>75</v>
       </c>
       <c r="P5">
-        <v>978.34</v>
+        <v>974.78</v>
       </c>
       <c r="Q5">
-        <v>993.46</v>
+        <v>990.45</v>
       </c>
       <c r="R5">
-        <v>1004.46</v>
+        <v>1004.61</v>
       </c>
       <c r="S5">
-        <v>979.45</v>
+        <v>980.12</v>
       </c>
       <c r="T5">
-        <v>-2.4</v>
+        <v>-2.54</v>
       </c>
       <c r="U5" t="s">
         <v>46</v>
@@ -1304,43 +1326,43 @@
         <v>1</v>
       </c>
       <c r="Y5">
-        <v>38.61</v>
+        <v>38.46</v>
       </c>
       <c r="Z5">
-        <v>-12</v>
+        <v>-13.37</v>
       </c>
       <c r="AA5">
-        <v>-9.24</v>
+        <v>-10.07</v>
       </c>
       <c r="AB5">
-        <v>-2.76</v>
+        <v>-3.3</v>
       </c>
       <c r="AC5">
-        <v>43.79</v>
+        <v>32.47</v>
       </c>
       <c r="AD5">
-        <v>56.29</v>
+        <v>47.21</v>
       </c>
       <c r="AE5">
-        <v>22.64</v>
+        <v>22.2</v>
       </c>
       <c r="AF5">
-        <v>-1.32</v>
+        <v>50.43</v>
       </c>
       <c r="AG5">
-        <v>1034.99</v>
+        <v>1033.96</v>
       </c>
       <c r="AH5">
-        <v>951.9299999999999</v>
+        <v>946.9400000000001</v>
       </c>
       <c r="AI5">
-        <v>1029.93</v>
+        <v>1021.89</v>
       </c>
       <c r="AJ5" t="s">
         <v>49</v>
       </c>
       <c r="AK5">
-        <v>20.51</v>
+        <v>22.86</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1351,10 +1373,10 @@
         <v>45</v>
       </c>
       <c r="C6">
-        <v>13.47</v>
+        <v>13.56</v>
       </c>
       <c r="D6">
-        <v>-5.54</v>
+        <v>0.67</v>
       </c>
       <c r="E6">
         <v>15.6</v>
@@ -1363,46 +1385,46 @@
         <v>8.02</v>
       </c>
       <c r="G6">
-        <v>-13.65</v>
+        <v>-13.08</v>
       </c>
       <c r="H6">
-        <v>67.95999999999999</v>
+        <v>69.08</v>
       </c>
       <c r="I6">
-        <v>-2.67</v>
+        <v>-4.98</v>
       </c>
       <c r="J6">
-        <v>-10.02</v>
+        <v>-7.63</v>
       </c>
       <c r="K6">
-        <v>-6.85</v>
+        <v>-7.38</v>
       </c>
       <c r="L6">
-        <v>54.47</v>
+        <v>57.86</v>
       </c>
       <c r="M6">
-        <v>4.23</v>
+        <v>3.81</v>
       </c>
       <c r="N6">
         <v>87</v>
       </c>
       <c r="O6">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="P6">
-        <v>14.13</v>
+        <v>13.99</v>
       </c>
       <c r="Q6">
-        <v>14.51</v>
+        <v>14.47</v>
       </c>
       <c r="R6">
         <v>13.93</v>
       </c>
       <c r="S6">
-        <v>12.22</v>
+        <v>12.23</v>
       </c>
       <c r="T6">
-        <v>10.27</v>
+        <v>10.88</v>
       </c>
       <c r="U6" t="s">
         <v>47</v>
@@ -1417,43 +1439,43 @@
         <v>3</v>
       </c>
       <c r="Y6">
-        <v>39.85</v>
+        <v>41.18</v>
       </c>
       <c r="Z6">
-        <v>-0.06</v>
+        <v>-0.11</v>
       </c>
       <c r="AA6">
-        <v>0.08</v>
+        <v>0.04</v>
       </c>
       <c r="AB6">
-        <v>-0.14</v>
+        <v>-0.15</v>
       </c>
       <c r="AC6">
-        <v>14.29</v>
+        <v>10.1</v>
       </c>
       <c r="AD6">
-        <v>22.78</v>
+        <v>17.14</v>
       </c>
       <c r="AE6">
         <v>0.49</v>
       </c>
       <c r="AF6">
-        <v>18.57</v>
+        <v>170.27</v>
       </c>
       <c r="AG6">
-        <v>15.65</v>
+        <v>15.69</v>
       </c>
       <c r="AH6">
-        <v>13.37</v>
+        <v>13.25</v>
       </c>
       <c r="AI6">
-        <v>15.31</v>
+        <v>14.94</v>
       </c>
       <c r="AJ6" t="s">
         <v>49</v>
       </c>
       <c r="AK6">
-        <v>25.3</v>
+        <v>28.66</v>
       </c>
     </row>
     <row r="7" spans="1:37">
@@ -1464,10 +1486,10 @@
         <v>45</v>
       </c>
       <c r="C7">
-        <v>11.02</v>
+        <v>10.84</v>
       </c>
       <c r="D7">
-        <v>-4.75</v>
+        <v>-1.63</v>
       </c>
       <c r="E7">
         <v>13.92</v>
@@ -1476,46 +1498,46 @@
         <v>4.69</v>
       </c>
       <c r="G7">
-        <v>-20.83</v>
+        <v>-22.13</v>
       </c>
       <c r="H7">
-        <v>134.97</v>
+        <v>131.13</v>
       </c>
       <c r="I7">
-        <v>-5.49</v>
+        <v>-4.49</v>
       </c>
       <c r="J7">
-        <v>-0.8100000000000001</v>
+        <v>-4.07</v>
       </c>
       <c r="K7">
-        <v>-3.08</v>
+        <v>-2.78</v>
       </c>
       <c r="L7">
-        <v>92.66</v>
+        <v>80.67</v>
       </c>
       <c r="M7">
-        <v>-29.92</v>
+        <v>-29.77</v>
       </c>
       <c r="N7">
         <v>99</v>
       </c>
       <c r="O7">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="P7">
-        <v>11.38</v>
+        <v>11.28</v>
       </c>
       <c r="Q7">
-        <v>11.55</v>
+        <v>11.54</v>
       </c>
       <c r="R7">
-        <v>11.79</v>
+        <v>11.78</v>
       </c>
       <c r="S7">
-        <v>10.77</v>
+        <v>10.79</v>
       </c>
       <c r="T7">
-        <v>2.3</v>
+        <v>0.5</v>
       </c>
       <c r="U7" t="s">
         <v>46</v>
@@ -1530,43 +1552,43 @@
         <v>2</v>
       </c>
       <c r="Y7">
-        <v>40.82</v>
+        <v>38.67</v>
       </c>
       <c r="Z7">
-        <v>-0.05</v>
+        <v>-0.11</v>
       </c>
       <c r="AA7">
-        <v>0.01</v>
+        <v>-0.02</v>
       </c>
       <c r="AB7">
-        <v>-0.06</v>
+        <v>-0.09</v>
       </c>
       <c r="AC7">
-        <v>17.38</v>
+        <v>8.31</v>
       </c>
       <c r="AD7">
-        <v>25.31</v>
+        <v>18.39</v>
       </c>
       <c r="AE7">
-        <v>0.46</v>
+        <v>0.48</v>
       </c>
       <c r="AF7">
-        <v>31.47</v>
+        <v>146.62</v>
       </c>
       <c r="AG7">
-        <v>12.53</v>
+        <v>12.55</v>
       </c>
       <c r="AH7">
-        <v>10.57</v>
+        <v>10.53</v>
       </c>
       <c r="AI7">
-        <v>12.58</v>
+        <v>12.33</v>
       </c>
       <c r="AJ7" t="s">
         <v>49</v>
       </c>
       <c r="AK7">
-        <v>27.8</v>
+        <v>29.96</v>
       </c>
     </row>
     <row r="8" spans="1:37">
@@ -1577,10 +1599,10 @@
         <v>45</v>
       </c>
       <c r="C8">
-        <v>3997.5</v>
+        <v>4027.7</v>
       </c>
       <c r="D8">
-        <v>-0.44</v>
+        <v>0.76</v>
       </c>
       <c r="E8">
         <v>5809.5</v>
@@ -1589,46 +1611,46 @@
         <v>3997.5</v>
       </c>
       <c r="G8">
-        <v>-31.19</v>
+        <v>-30.67</v>
       </c>
       <c r="H8">
-        <v>0</v>
+        <v>0.76</v>
       </c>
       <c r="I8">
-        <v>-0.74</v>
+        <v>0.48</v>
       </c>
       <c r="J8">
-        <v>-8.390000000000001</v>
+        <v>-8.210000000000001</v>
       </c>
       <c r="K8">
-        <v>-8.08</v>
+        <v>-8.51</v>
       </c>
       <c r="L8">
-        <v>-24.71</v>
+        <v>-25.89</v>
       </c>
       <c r="M8">
-        <v>16.7</v>
+        <v>16.9</v>
       </c>
       <c r="N8">
         <v>26</v>
       </c>
       <c r="O8">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="P8">
-        <v>4013.94</v>
+        <v>4017.82</v>
       </c>
       <c r="Q8">
-        <v>4159.38</v>
+        <v>4143.09</v>
       </c>
       <c r="R8">
-        <v>4284.31</v>
+        <v>4277.5</v>
       </c>
       <c r="S8">
-        <v>4548.04</v>
+        <v>4542.5</v>
       </c>
       <c r="T8">
-        <v>-12.11</v>
+        <v>-11.33</v>
       </c>
       <c r="U8" t="s">
         <v>46</v>
@@ -1643,34 +1665,34 @@
         <v>0</v>
       </c>
       <c r="Y8">
-        <v>33.34</v>
+        <v>37.01</v>
       </c>
       <c r="Z8">
-        <v>-92.3</v>
+        <v>-89.09999999999999</v>
       </c>
       <c r="AA8">
-        <v>-80.41</v>
+        <v>-82.15000000000001</v>
       </c>
       <c r="AB8">
-        <v>-11.89</v>
+        <v>-6.95</v>
       </c>
       <c r="AC8">
-        <v>25.55</v>
+        <v>36.46</v>
       </c>
       <c r="AD8">
-        <v>24.05</v>
+        <v>29.73</v>
       </c>
       <c r="AE8">
-        <v>95.70999999999999</v>
+        <v>100.48</v>
       </c>
       <c r="AF8">
-        <v>-36.85</v>
+        <v>4.84</v>
       </c>
       <c r="AG8">
-        <v>4435.95</v>
+        <v>4409.74</v>
       </c>
       <c r="AH8">
-        <v>3882.8</v>
+        <v>3876.44</v>
       </c>
       <c r="AI8">
         <v>4288.14</v>
@@ -1679,7 +1701,7 @@
         <v>49</v>
       </c>
       <c r="AK8">
-        <v>65.48999999999999</v>
+        <v>60.73</v>
       </c>
     </row>
     <row r="9" spans="1:37">
@@ -1690,10 +1712,10 @@
         <v>45</v>
       </c>
       <c r="C9">
-        <v>11025</v>
+        <v>10829</v>
       </c>
       <c r="D9">
-        <v>-1.17</v>
+        <v>-1.78</v>
       </c>
       <c r="E9">
         <v>13052</v>
@@ -1702,46 +1724,46 @@
         <v>10362</v>
       </c>
       <c r="G9">
-        <v>-15.53</v>
+        <v>-17.03</v>
       </c>
       <c r="H9">
-        <v>6.4</v>
+        <v>4.51</v>
       </c>
       <c r="I9">
-        <v>-0.68</v>
+        <v>-1.55</v>
       </c>
       <c r="J9">
-        <v>-5.91</v>
+        <v>-6.56</v>
       </c>
       <c r="K9">
-        <v>-2.03</v>
+        <v>-5.47</v>
       </c>
       <c r="L9">
-        <v>-11.1</v>
+        <v>-11.34</v>
       </c>
       <c r="M9">
-        <v>8.24</v>
+        <v>8.210000000000001</v>
       </c>
       <c r="N9">
         <v>38</v>
       </c>
       <c r="O9">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="P9">
-        <v>11078.2</v>
+        <v>11044</v>
       </c>
       <c r="Q9">
-        <v>11082.75</v>
+        <v>11051.7</v>
       </c>
       <c r="R9">
-        <v>11523.44</v>
+        <v>11501.96</v>
       </c>
       <c r="S9">
-        <v>11718.23</v>
+        <v>11715.79</v>
       </c>
       <c r="T9">
-        <v>-5.92</v>
+        <v>-7.57</v>
       </c>
       <c r="U9" t="s">
         <v>46</v>
@@ -1756,34 +1778,34 @@
         <v>0</v>
       </c>
       <c r="Y9">
-        <v>44.16</v>
+        <v>38.95</v>
       </c>
       <c r="Z9">
-        <v>-128.34</v>
+        <v>-137.19</v>
       </c>
       <c r="AA9">
-        <v>-164.83</v>
+        <v>-159.3</v>
       </c>
       <c r="AB9">
-        <v>36.49</v>
+        <v>22.11</v>
       </c>
       <c r="AC9">
-        <v>88.76000000000001</v>
+        <v>79.01000000000001</v>
       </c>
       <c r="AD9">
-        <v>91.14</v>
+        <v>87.62</v>
       </c>
       <c r="AE9">
-        <v>190.76</v>
+        <v>191.49</v>
       </c>
       <c r="AF9">
-        <v>23.7</v>
+        <v>91.52</v>
       </c>
       <c r="AG9">
-        <v>11532.95</v>
+        <v>11480.4</v>
       </c>
       <c r="AH9">
-        <v>10632.55</v>
+        <v>10623</v>
       </c>
       <c r="AI9">
         <v>11371.08</v>
@@ -1792,7 +1814,7 @@
         <v>49</v>
       </c>
       <c r="AK9">
-        <v>23.05</v>
+        <v>24.18</v>
       </c>
     </row>
   </sheetData>
@@ -1933,7 +1955,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F70"/>
+  <dimension ref="A1:F73"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -1953,1127 +1975,1216 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="3" t="s">
         <v>51</v>
       </c>
-    </row>
-    <row r="5" spans="1:6">
-      <c r="A5" s="2" t="s">
+      <c r="C2" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="B5" s="2"/>
-      <c r="C5" s="2"/>
-      <c r="D5" s="2"/>
-      <c r="E5" s="2"/>
+      <c r="D2" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
+      <c r="A4" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>46</v>
+      </c>
     </row>
     <row r="6" spans="1:6">
-      <c r="A6" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="D6" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="E6" s="4" t="s">
-        <v>56</v>
-      </c>
+      <c r="A6" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="B6" s="2"/>
+      <c r="C6" s="2"/>
+      <c r="D6" s="2"/>
+      <c r="E6" s="2"/>
     </row>
     <row r="7" spans="1:6">
       <c r="A7" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B7" s="3" t="s">
+      <c r="B8" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C7" s="5">
-        <v>-4.88</v>
-      </c>
-      <c r="D7" s="5">
+      <c r="C8" s="6">
         <v>-6.66</v>
       </c>
-      <c r="E7" s="6">
-        <v>-1.78</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
-      <c r="A8" s="3" t="s">
+      <c r="D8" s="6">
+        <v>-6.79</v>
+      </c>
+      <c r="E8" s="7">
+        <v>-0.13</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B8" s="3" t="s">
+      <c r="B9" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C8" s="5">
-        <v>-9.869999999999999</v>
-      </c>
-      <c r="D8" s="5">
+      <c r="C9" s="6">
         <v>-11.28</v>
       </c>
-      <c r="E8" s="6">
-        <v>-1.41</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9" s="3" t="s">
+      <c r="D9" s="6">
+        <v>-11.91</v>
+      </c>
+      <c r="E9" s="7">
+        <v>-0.63</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B9" s="3" t="s">
+      <c r="B10" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C9" s="5">
-        <v>-3.3</v>
-      </c>
-      <c r="D9" s="5">
+      <c r="C10" s="6">
         <v>-3.31</v>
       </c>
-      <c r="E9" s="6">
-        <v>-0.01</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10" s="3" t="s">
+      <c r="D10" s="6">
+        <v>-5.78</v>
+      </c>
+      <c r="E10" s="7">
+        <v>-2.47</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B10" s="3" t="s">
+      <c r="B11" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C10" s="5">
-        <v>-7.22</v>
-      </c>
-      <c r="D10" s="5">
+      <c r="C11" s="6">
         <v>-6.65</v>
       </c>
-      <c r="E10" s="7">
+      <c r="D11" s="6">
+        <v>-7.92</v>
+      </c>
+      <c r="E11" s="7">
+        <v>-1.27</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B12" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C12" s="6">
+        <v>-10.02</v>
+      </c>
+      <c r="D12" s="6">
+        <v>-7.63</v>
+      </c>
+      <c r="E12" s="8">
+        <v>2.39</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="A13" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B13" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C13" s="6">
+        <v>-0.8100000000000001</v>
+      </c>
+      <c r="D13" s="6">
+        <v>-4.07</v>
+      </c>
+      <c r="E13" s="7">
+        <v>-3.26</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B14" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C14" s="6">
+        <v>-8.390000000000001</v>
+      </c>
+      <c r="D14" s="6">
+        <v>-8.210000000000001</v>
+      </c>
+      <c r="E14" s="8">
+        <v>0.18</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="A15" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="B15" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C15" s="6">
+        <v>-5.91</v>
+      </c>
+      <c r="D15" s="6">
+        <v>-6.56</v>
+      </c>
+      <c r="E15" s="7">
+        <v>-0.65</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="A16" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B16" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C16" s="6">
+        <v>-5.13</v>
+      </c>
+      <c r="D16" s="6">
+        <v>-4.79</v>
+      </c>
+      <c r="E16" s="8">
+        <v>0.34</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B17" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C17" s="6">
+        <v>-4.53</v>
+      </c>
+      <c r="D17" s="6">
+        <v>-6.05</v>
+      </c>
+      <c r="E17" s="7">
+        <v>-1.52</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B18" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C18" s="6">
+        <v>-0.51</v>
+      </c>
+      <c r="D18" s="6">
+        <v>-0.9</v>
+      </c>
+      <c r="E18" s="7">
+        <v>-0.39</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B19" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C19" s="6">
+        <v>-2.58</v>
+      </c>
+      <c r="D19" s="6">
+        <v>-1.83</v>
+      </c>
+      <c r="E19" s="8">
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B20" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C20" s="6">
+        <v>-2.67</v>
+      </c>
+      <c r="D20" s="6">
+        <v>-4.98</v>
+      </c>
+      <c r="E20" s="7">
+        <v>-2.31</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B21" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C21" s="6">
+        <v>-5.49</v>
+      </c>
+      <c r="D21" s="6">
+        <v>-4.49</v>
+      </c>
+      <c r="E21" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B22" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C22" s="6">
+        <v>-0.74</v>
+      </c>
+      <c r="D22" s="6">
+        <v>0.48</v>
+      </c>
+      <c r="E22" s="8">
+        <v>1.22</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="B23" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C23" s="6">
+        <v>-0.68</v>
+      </c>
+      <c r="D23" s="6">
+        <v>-1.55</v>
+      </c>
+      <c r="E23" s="7">
+        <v>-0.87</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B24" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C24" s="6">
+        <v>31.31</v>
+      </c>
+      <c r="D24" s="6">
+        <v>29.47</v>
+      </c>
+      <c r="E24" s="7">
+        <v>-1.84</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B25" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C25" s="6">
+        <v>-48.29</v>
+      </c>
+      <c r="D25" s="6">
+        <v>-49.26</v>
+      </c>
+      <c r="E25" s="7">
+        <v>-0.97</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B26" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C26" s="6">
+        <v>11.96</v>
+      </c>
+      <c r="D26" s="6">
+        <v>10.42</v>
+      </c>
+      <c r="E26" s="7">
+        <v>-1.54</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B27" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C27" s="6">
+        <v>28.15</v>
+      </c>
+      <c r="D27" s="6">
+        <v>28.9</v>
+      </c>
+      <c r="E27" s="8">
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B28" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C28" s="6">
+        <v>54.47</v>
+      </c>
+      <c r="D28" s="6">
+        <v>57.86</v>
+      </c>
+      <c r="E28" s="8">
+        <v>3.39</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B29" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C29" s="6">
+        <v>92.66</v>
+      </c>
+      <c r="D29" s="6">
+        <v>80.67</v>
+      </c>
+      <c r="E29" s="7">
+        <v>-11.99</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B30" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C30" s="6">
+        <v>-24.71</v>
+      </c>
+      <c r="D30" s="6">
+        <v>-25.89</v>
+      </c>
+      <c r="E30" s="7">
+        <v>-1.18</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5">
+      <c r="A31" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="B31" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C31" s="6">
+        <v>-11.1</v>
+      </c>
+      <c r="D31" s="6">
+        <v>-11.34</v>
+      </c>
+      <c r="E31" s="7">
+        <v>-0.24</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5">
+      <c r="A32" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B32" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C32" s="6">
+        <v>-2.36</v>
+      </c>
+      <c r="D32" s="6">
+        <v>-3.85</v>
+      </c>
+      <c r="E32" s="7">
+        <v>-1.49</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5">
+      <c r="A33" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B33" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C33" s="6">
+        <v>-18.03</v>
+      </c>
+      <c r="D33" s="6">
+        <v>-21.19</v>
+      </c>
+      <c r="E33" s="7">
+        <v>-3.16</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5">
+      <c r="A34" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B34" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C34" s="6">
+        <v>1.61</v>
+      </c>
+      <c r="D34" s="6">
+        <v>-1.29</v>
+      </c>
+      <c r="E34" s="7">
+        <v>-2.9</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5">
+      <c r="A35" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B35" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C35" s="6">
+        <v>-0.07000000000000001</v>
+      </c>
+      <c r="D35" s="6">
+        <v>1.65</v>
+      </c>
+      <c r="E35" s="8">
+        <v>1.72</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5">
+      <c r="A36" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B36" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C36" s="6">
+        <v>-6.85</v>
+      </c>
+      <c r="D36" s="6">
+        <v>-7.38</v>
+      </c>
+      <c r="E36" s="7">
+        <v>-0.53</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5">
+      <c r="A37" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B37" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C37" s="6">
+        <v>-3.08</v>
+      </c>
+      <c r="D37" s="6">
+        <v>-2.78</v>
+      </c>
+      <c r="E37" s="8">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5">
+      <c r="A38" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B38" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C38" s="6">
+        <v>-8.08</v>
+      </c>
+      <c r="D38" s="6">
+        <v>-8.51</v>
+      </c>
+      <c r="E38" s="7">
+        <v>-0.43</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5">
+      <c r="A39" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="B39" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C39" s="6">
+        <v>-2.03</v>
+      </c>
+      <c r="D39" s="6">
+        <v>-5.47</v>
+      </c>
+      <c r="E39" s="7">
+        <v>-3.44</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5">
+      <c r="A40" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B40" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C40" s="6">
+        <v>-9.890000000000001</v>
+      </c>
+      <c r="D40" s="6">
+        <v>-11</v>
+      </c>
+      <c r="E40" s="7">
+        <v>-1.11</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5">
+      <c r="A41" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B41" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C41" s="6">
+        <v>-47.78</v>
+      </c>
+      <c r="D41" s="6">
+        <v>-47.45</v>
+      </c>
+      <c r="E41" s="8">
+        <v>0.33</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5">
+      <c r="A42" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B42" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C42" s="6">
+        <v>-6.82</v>
+      </c>
+      <c r="D42" s="6">
+        <v>-8.300000000000001</v>
+      </c>
+      <c r="E42" s="7">
+        <v>-1.48</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5">
+      <c r="A43" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B43" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C43" s="6">
+        <v>-16.86</v>
+      </c>
+      <c r="D43" s="6">
+        <v>-16.92</v>
+      </c>
+      <c r="E43" s="7">
+        <v>-0.06</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5">
+      <c r="A44" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B44" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C44" s="6">
+        <v>-13.65</v>
+      </c>
+      <c r="D44" s="6">
+        <v>-13.08</v>
+      </c>
+      <c r="E44" s="8">
         <v>0.57</v>
       </c>
     </row>
-    <row r="11" spans="1:6">
-      <c r="A11" s="3" t="s">
+    <row r="45" spans="1:5">
+      <c r="A45" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B45" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C45" s="6">
+        <v>-20.83</v>
+      </c>
+      <c r="D45" s="6">
+        <v>-22.13</v>
+      </c>
+      <c r="E45" s="7">
+        <v>-1.3</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5">
+      <c r="A46" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B46" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C46" s="6">
+        <v>-31.19</v>
+      </c>
+      <c r="D46" s="6">
+        <v>-30.67</v>
+      </c>
+      <c r="E46" s="8">
+        <v>0.52</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5">
+      <c r="A47" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="B47" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C47" s="6">
+        <v>-15.53</v>
+      </c>
+      <c r="D47" s="6">
+        <v>-17.03</v>
+      </c>
+      <c r="E47" s="7">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5">
+      <c r="A48" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B48" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C48" s="6">
+        <v>382.7</v>
+      </c>
+      <c r="D48" s="6">
+        <v>378</v>
+      </c>
+      <c r="E48" s="7">
+        <v>-4.7</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5">
+      <c r="A49" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B49" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C49" s="6">
+        <v>47.59</v>
+      </c>
+      <c r="D49" s="6">
+        <v>46.24</v>
+      </c>
+      <c r="E49" s="7">
+        <v>-1.35</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5">
+      <c r="A50" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B50" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C50" s="6">
+        <v>3150</v>
+      </c>
+      <c r="D50" s="6">
+        <v>3100</v>
+      </c>
+      <c r="E50" s="7">
+        <v>-50</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5">
+      <c r="A51" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B51" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C51" s="6">
+        <v>955.9</v>
+      </c>
+      <c r="D51" s="6">
+        <v>955.2</v>
+      </c>
+      <c r="E51" s="7">
+        <v>-0.7</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5">
+      <c r="A52" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B11" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C11" s="5">
-        <v>-5.31</v>
-      </c>
-      <c r="D11" s="5">
-        <v>-10.02</v>
-      </c>
-      <c r="E11" s="6">
-        <v>-4.71</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12" s="3" t="s">
+      <c r="B52" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C52" s="6">
+        <v>13.47</v>
+      </c>
+      <c r="D52" s="6">
+        <v>13.56</v>
+      </c>
+      <c r="E52" s="8">
+        <v>0.09</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5">
+      <c r="A53" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="B12" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C12" s="5">
-        <v>4.14</v>
-      </c>
-      <c r="D12" s="5">
-        <v>-0.8100000000000001</v>
-      </c>
-      <c r="E12" s="6">
-        <v>-4.95</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13" s="3" t="s">
+      <c r="B53" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C53" s="6">
+        <v>11.02</v>
+      </c>
+      <c r="D53" s="6">
+        <v>10.84</v>
+      </c>
+      <c r="E53" s="7">
+        <v>-0.18</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5">
+      <c r="A54" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="B13" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C13" s="5">
-        <v>-9.26</v>
-      </c>
-      <c r="D13" s="5">
-        <v>-8.390000000000001</v>
-      </c>
-      <c r="E13" s="7">
-        <v>0.87</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14" s="3" t="s">
+      <c r="B54" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C54" s="6">
+        <v>3997.5</v>
+      </c>
+      <c r="D54" s="6">
+        <v>4027.7</v>
+      </c>
+      <c r="E54" s="8">
+        <v>30.2</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5">
+      <c r="A55" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="B14" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C14" s="5">
-        <v>-4.8</v>
-      </c>
-      <c r="D14" s="5">
-        <v>-5.91</v>
-      </c>
-      <c r="E14" s="6">
-        <v>-1.11</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15" s="3" t="s">
+      <c r="B55" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C55" s="6">
+        <v>11025</v>
+      </c>
+      <c r="D55" s="6">
+        <v>10829</v>
+      </c>
+      <c r="E55" s="7">
+        <v>-196</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5">
+      <c r="A56" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B15" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C15" s="5">
-        <v>-4.89</v>
-      </c>
-      <c r="D15" s="5">
-        <v>-5.13</v>
-      </c>
-      <c r="E15" s="6">
-        <v>-0.24</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16" s="3" t="s">
+      <c r="B56" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C56" s="6">
+        <v>74</v>
+      </c>
+      <c r="D56" s="6">
+        <v>62</v>
+      </c>
+      <c r="E56" s="7">
+        <v>-12</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5">
+      <c r="A57" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B57" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C57" s="6">
+        <v>62</v>
+      </c>
+      <c r="D57" s="6">
+        <v>74</v>
+      </c>
+      <c r="E57" s="8">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5">
+      <c r="A58" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B58" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C58" s="6">
+        <v>41.11</v>
+      </c>
+      <c r="D58" s="6">
+        <v>38.89</v>
+      </c>
+      <c r="E58" s="7">
+        <v>-2.22</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5">
+      <c r="A59" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B16" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C16" s="5">
-        <v>-2.03</v>
-      </c>
-      <c r="D16" s="5">
-        <v>-4.53</v>
-      </c>
-      <c r="E16" s="6">
-        <v>-2.5</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5">
-      <c r="A17" s="3" t="s">
+      <c r="B59" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C59" s="6">
+        <v>31.61</v>
+      </c>
+      <c r="D59" s="6">
+        <v>27.97</v>
+      </c>
+      <c r="E59" s="7">
+        <v>-3.64</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5">
+      <c r="A60" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B17" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C17" s="5">
-        <v>-0.57</v>
-      </c>
-      <c r="D17" s="5">
-        <v>-0.51</v>
-      </c>
-      <c r="E17" s="7">
-        <v>0.06</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5">
-      <c r="A18" s="3" t="s">
+      <c r="B60" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C60" s="6">
+        <v>41.66</v>
+      </c>
+      <c r="D60" s="6">
+        <v>37.36</v>
+      </c>
+      <c r="E60" s="7">
+        <v>-4.3</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5">
+      <c r="A61" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B18" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C18" s="5">
-        <v>-0.96</v>
-      </c>
-      <c r="D18" s="5">
-        <v>-2.58</v>
-      </c>
-      <c r="E18" s="6">
-        <v>-1.62</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5">
-      <c r="A19" s="3" t="s">
+      <c r="B61" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C61" s="6">
+        <v>38.61</v>
+      </c>
+      <c r="D61" s="6">
+        <v>38.46</v>
+      </c>
+      <c r="E61" s="7">
+        <v>-0.15</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5">
+      <c r="A62" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B19" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C19" s="5">
-        <v>2.44</v>
-      </c>
-      <c r="D19" s="5">
-        <v>-2.67</v>
-      </c>
-      <c r="E19" s="6">
-        <v>-5.11</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5">
-      <c r="A20" s="3" t="s">
+      <c r="B62" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C62" s="6">
+        <v>39.85</v>
+      </c>
+      <c r="D62" s="6">
+        <v>41.18</v>
+      </c>
+      <c r="E62" s="8">
+        <v>1.33</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5">
+      <c r="A63" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="B20" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C20" s="5">
-        <v>-3.1</v>
-      </c>
-      <c r="D20" s="5">
-        <v>-5.49</v>
-      </c>
-      <c r="E20" s="6">
-        <v>-2.39</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5">
-      <c r="A21" s="3" t="s">
+      <c r="B63" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C63" s="6">
+        <v>40.82</v>
+      </c>
+      <c r="D63" s="6">
+        <v>38.67</v>
+      </c>
+      <c r="E63" s="7">
+        <v>-2.15</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5">
+      <c r="A64" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="B21" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C21" s="5">
-        <v>-1.28</v>
-      </c>
-      <c r="D21" s="5">
-        <v>-0.74</v>
-      </c>
-      <c r="E21" s="7">
-        <v>0.54</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5">
-      <c r="A22" s="3" t="s">
+      <c r="B64" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C64" s="6">
+        <v>33.34</v>
+      </c>
+      <c r="D64" s="6">
+        <v>37.01</v>
+      </c>
+      <c r="E64" s="8">
+        <v>3.67</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5">
+      <c r="A65" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="B22" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C22" s="5">
-        <v>1.28</v>
-      </c>
-      <c r="D22" s="5">
-        <v>-0.68</v>
-      </c>
-      <c r="E22" s="6">
-        <v>-1.96</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5">
-      <c r="A23" s="3" t="s">
+      <c r="B65" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C65" s="6">
+        <v>44.16</v>
+      </c>
+      <c r="D65" s="6">
+        <v>38.95</v>
+      </c>
+      <c r="E65" s="7">
+        <v>-5.21</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5">
+      <c r="A66" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B23" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C23" s="5">
-        <v>35.35</v>
-      </c>
-      <c r="D23" s="5">
-        <v>31.31</v>
-      </c>
-      <c r="E23" s="6">
-        <v>-4.04</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5">
-      <c r="A24" s="3" t="s">
+      <c r="B66" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C66" s="6">
+        <v>-30.33</v>
+      </c>
+      <c r="D66" s="6">
+        <v>69.65000000000001</v>
+      </c>
+      <c r="E66" s="8">
+        <v>99.98</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5">
+      <c r="A67" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B24" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C24" s="5">
-        <v>-47.43</v>
-      </c>
-      <c r="D24" s="5">
-        <v>-48.29</v>
-      </c>
-      <c r="E24" s="6">
-        <v>-0.86</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5">
-      <c r="A25" s="3" t="s">
+      <c r="B67" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C67" s="6">
+        <v>-19.88</v>
+      </c>
+      <c r="D67" s="6">
+        <v>184.13</v>
+      </c>
+      <c r="E67" s="8">
+        <v>204.01</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5">
+      <c r="A68" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B25" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C25" s="5">
-        <v>11.8</v>
-      </c>
-      <c r="D25" s="5">
-        <v>11.96</v>
-      </c>
-      <c r="E25" s="7">
-        <v>0.16</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5">
-      <c r="A26" s="3" t="s">
+      <c r="B68" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C68" s="6">
+        <v>-13.65</v>
+      </c>
+      <c r="D68" s="6">
+        <v>33.1</v>
+      </c>
+      <c r="E68" s="8">
+        <v>46.75</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5">
+      <c r="A69" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B26" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C26" s="5">
-        <v>31.02</v>
-      </c>
-      <c r="D26" s="5">
-        <v>28.15</v>
-      </c>
-      <c r="E26" s="6">
-        <v>-2.87</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5">
-      <c r="A27" s="3" t="s">
+      <c r="B69" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C69" s="6">
+        <v>-1.32</v>
+      </c>
+      <c r="D69" s="6">
+        <v>50.43</v>
+      </c>
+      <c r="E69" s="8">
+        <v>51.75</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5">
+      <c r="A70" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B27" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C27" s="5">
-        <v>69.95999999999999</v>
-      </c>
-      <c r="D27" s="5">
-        <v>54.47</v>
-      </c>
-      <c r="E27" s="6">
-        <v>-15.49</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5">
-      <c r="A28" s="3" t="s">
+      <c r="B70" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C70" s="6">
+        <v>18.57</v>
+      </c>
+      <c r="D70" s="6">
+        <v>170.27</v>
+      </c>
+      <c r="E70" s="8">
+        <v>151.7</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5">
+      <c r="A71" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="B28" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C28" s="5">
-        <v>91.87</v>
-      </c>
-      <c r="D28" s="5">
-        <v>92.66</v>
-      </c>
-      <c r="E28" s="7">
-        <v>0.79</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5">
-      <c r="A29" s="3" t="s">
+      <c r="B71" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C71" s="6">
+        <v>31.47</v>
+      </c>
+      <c r="D71" s="6">
+        <v>146.62</v>
+      </c>
+      <c r="E71" s="8">
+        <v>115.15</v>
+      </c>
+    </row>
+    <row r="72" spans="1:5">
+      <c r="A72" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="B29" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C29" s="5">
-        <v>-25.03</v>
-      </c>
-      <c r="D29" s="5">
-        <v>-24.71</v>
-      </c>
-      <c r="E29" s="7">
-        <v>0.32</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5">
-      <c r="A30" s="3" t="s">
+      <c r="B72" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C72" s="6">
+        <v>-36.85</v>
+      </c>
+      <c r="D72" s="6">
+        <v>4.84</v>
+      </c>
+      <c r="E72" s="8">
+        <v>41.69</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5">
+      <c r="A73" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="B30" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C30" s="5">
-        <v>-11.82</v>
-      </c>
-      <c r="D30" s="5">
-        <v>-11.1</v>
-      </c>
-      <c r="E30" s="7">
-        <v>0.72</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5">
-      <c r="A31" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B31" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C31" s="5">
-        <v>1.22</v>
-      </c>
-      <c r="D31" s="5">
-        <v>-2.36</v>
-      </c>
-      <c r="E31" s="6">
-        <v>-3.58</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5">
-      <c r="A32" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B32" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C32" s="5">
-        <v>-16.43</v>
-      </c>
-      <c r="D32" s="5">
-        <v>-18.03</v>
-      </c>
-      <c r="E32" s="6">
-        <v>-1.6</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5">
-      <c r="A33" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B33" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C33" s="5">
-        <v>3.6</v>
-      </c>
-      <c r="D33" s="5">
-        <v>1.61</v>
-      </c>
-      <c r="E33" s="6">
-        <v>-1.99</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5">
-      <c r="A34" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="B34" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C34" s="5">
-        <v>1.37</v>
-      </c>
-      <c r="D34" s="5">
-        <v>-0.07000000000000001</v>
-      </c>
-      <c r="E34" s="6">
-        <v>-1.44</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5">
-      <c r="A35" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="B35" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C35" s="5">
-        <v>-1.18</v>
-      </c>
-      <c r="D35" s="5">
-        <v>-6.85</v>
-      </c>
-      <c r="E35" s="6">
-        <v>-5.67</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5">
-      <c r="A36" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="B36" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C36" s="5">
-        <v>1.94</v>
-      </c>
-      <c r="D36" s="5">
-        <v>-3.08</v>
-      </c>
-      <c r="E36" s="6">
-        <v>-5.02</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5">
-      <c r="A37" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="B37" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C37" s="5">
-        <v>-7.66</v>
-      </c>
-      <c r="D37" s="5">
-        <v>-8.08</v>
-      </c>
-      <c r="E37" s="6">
-        <v>-0.42</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5">
-      <c r="A38" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="B38" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C38" s="5">
-        <v>-1.6</v>
-      </c>
-      <c r="D38" s="5">
-        <v>-2.03</v>
-      </c>
-      <c r="E38" s="6">
-        <v>-0.43</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5">
-      <c r="A39" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B39" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C39" s="5">
-        <v>-8.17</v>
-      </c>
-      <c r="D39" s="5">
-        <v>-9.890000000000001</v>
-      </c>
-      <c r="E39" s="6">
-        <v>-1.72</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5">
-      <c r="A40" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B40" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C40" s="5">
-        <v>-46.6</v>
-      </c>
-      <c r="D40" s="5">
-        <v>-47.78</v>
-      </c>
-      <c r="E40" s="6">
-        <v>-1.18</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5">
-      <c r="A41" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B41" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C41" s="5">
-        <v>-5.61</v>
-      </c>
-      <c r="D41" s="5">
-        <v>-6.82</v>
-      </c>
-      <c r="E41" s="6">
-        <v>-1.21</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5">
-      <c r="A42" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="B42" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C42" s="5">
-        <v>-15.02</v>
-      </c>
-      <c r="D42" s="5">
-        <v>-16.86</v>
-      </c>
-      <c r="E42" s="6">
-        <v>-1.84</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5">
-      <c r="A43" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="B43" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C43" s="5">
-        <v>-8.59</v>
-      </c>
-      <c r="D43" s="5">
-        <v>-13.65</v>
-      </c>
-      <c r="E43" s="6">
-        <v>-5.06</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5">
-      <c r="A44" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="B44" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C44" s="5">
-        <v>-16.88</v>
-      </c>
-      <c r="D44" s="5">
-        <v>-20.83</v>
-      </c>
-      <c r="E44" s="6">
-        <v>-3.95</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5">
-      <c r="A45" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="B45" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C45" s="5">
-        <v>-30.89</v>
-      </c>
-      <c r="D45" s="5">
-        <v>-31.19</v>
-      </c>
-      <c r="E45" s="6">
-        <v>-0.3</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5">
-      <c r="A46" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="B46" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C46" s="5">
-        <v>-14.53</v>
-      </c>
-      <c r="D46" s="5">
-        <v>-15.53</v>
-      </c>
-      <c r="E46" s="6">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5">
-      <c r="A47" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B47" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C47" s="5">
-        <v>390</v>
-      </c>
-      <c r="D47" s="5">
-        <v>382.7</v>
-      </c>
-      <c r="E47" s="6">
-        <v>-7.3</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5">
-      <c r="A48" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B48" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C48" s="5">
-        <v>49.14</v>
-      </c>
-      <c r="D48" s="5">
-        <v>47.59</v>
-      </c>
-      <c r="E48" s="6">
-        <v>-1.55</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5">
-      <c r="A49" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B49" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C49" s="5">
-        <v>3191</v>
-      </c>
-      <c r="D49" s="5">
-        <v>3150</v>
-      </c>
-      <c r="E49" s="6">
-        <v>-41</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5">
-      <c r="A50" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="B50" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C50" s="5">
-        <v>977</v>
-      </c>
-      <c r="D50" s="5">
-        <v>955.9</v>
-      </c>
-      <c r="E50" s="6">
-        <v>-21.1</v>
-      </c>
-    </row>
-    <row r="51" spans="1:5">
-      <c r="A51" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="B51" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C51" s="5">
-        <v>14.26</v>
-      </c>
-      <c r="D51" s="5">
-        <v>13.47</v>
-      </c>
-      <c r="E51" s="6">
-        <v>-0.79</v>
-      </c>
-    </row>
-    <row r="52" spans="1:5">
-      <c r="A52" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="B52" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C52" s="5">
-        <v>11.57</v>
-      </c>
-      <c r="D52" s="5">
-        <v>11.02</v>
-      </c>
-      <c r="E52" s="6">
-        <v>-0.55</v>
-      </c>
-    </row>
-    <row r="53" spans="1:5">
-      <c r="A53" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="B53" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C53" s="5">
-        <v>4015</v>
-      </c>
-      <c r="D53" s="5">
-        <v>3997.5</v>
-      </c>
-      <c r="E53" s="6">
-        <v>-17.5</v>
-      </c>
-    </row>
-    <row r="54" spans="1:5">
-      <c r="A54" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="B54" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C54" s="5">
-        <v>11155</v>
-      </c>
-      <c r="D54" s="5">
-        <v>11025</v>
-      </c>
-      <c r="E54" s="6">
-        <v>-130</v>
-      </c>
-    </row>
-    <row r="55" spans="1:5">
-      <c r="A55" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B55" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C55" s="5">
-        <v>44.79</v>
-      </c>
-      <c r="D55" s="5">
-        <v>41.11</v>
-      </c>
-      <c r="E55" s="6">
-        <v>-3.68</v>
-      </c>
-    </row>
-    <row r="56" spans="1:5">
-      <c r="A56" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B56" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C56" s="5">
-        <v>36.7</v>
-      </c>
-      <c r="D56" s="5">
-        <v>31.61</v>
-      </c>
-      <c r="E56" s="6">
-        <v>-5.09</v>
-      </c>
-    </row>
-    <row r="57" spans="1:5">
-      <c r="A57" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B57" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C57" s="5">
-        <v>45.66</v>
-      </c>
-      <c r="D57" s="5">
-        <v>41.66</v>
-      </c>
-      <c r="E57" s="6">
-        <v>-4</v>
-      </c>
-    </row>
-    <row r="58" spans="1:5">
-      <c r="A58" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="B58" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C58" s="5">
-        <v>43.44</v>
-      </c>
-      <c r="D58" s="5">
-        <v>38.61</v>
-      </c>
-      <c r="E58" s="6">
-        <v>-4.83</v>
-      </c>
-    </row>
-    <row r="59" spans="1:5">
-      <c r="A59" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="B59" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C59" s="5">
-        <v>48.85</v>
-      </c>
-      <c r="D59" s="5">
-        <v>39.85</v>
-      </c>
-      <c r="E59" s="6">
-        <v>-9</v>
-      </c>
-    </row>
-    <row r="60" spans="1:5">
-      <c r="A60" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="B60" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C60" s="5">
-        <v>48.47</v>
-      </c>
-      <c r="D60" s="5">
-        <v>40.82</v>
-      </c>
-      <c r="E60" s="6">
-        <v>-7.65</v>
-      </c>
-    </row>
-    <row r="61" spans="1:5">
-      <c r="A61" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="B61" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C61" s="5">
-        <v>34.42</v>
-      </c>
-      <c r="D61" s="5">
-        <v>33.34</v>
-      </c>
-      <c r="E61" s="6">
-        <v>-1.08</v>
-      </c>
-    </row>
-    <row r="62" spans="1:5">
-      <c r="A62" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="B62" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C62" s="5">
-        <v>48.12</v>
-      </c>
-      <c r="D62" s="5">
-        <v>44.16</v>
-      </c>
-      <c r="E62" s="6">
-        <v>-3.96</v>
-      </c>
-    </row>
-    <row r="63" spans="1:5">
-      <c r="A63" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B63" s="3" t="s">
+      <c r="B73" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="C63" s="5">
-        <v>5.17</v>
-      </c>
-      <c r="D63" s="5">
-        <v>-30.33</v>
-      </c>
-      <c r="E63" s="6">
-        <v>-35.5</v>
-      </c>
-    </row>
-    <row r="64" spans="1:5">
-      <c r="A64" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B64" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C64" s="5">
-        <v>2.98</v>
-      </c>
-      <c r="D64" s="5">
-        <v>-19.88</v>
-      </c>
-      <c r="E64" s="6">
-        <v>-22.86</v>
-      </c>
-    </row>
-    <row r="65" spans="1:5">
-      <c r="A65" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B65" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C65" s="5">
-        <v>-12.22</v>
-      </c>
-      <c r="D65" s="5">
-        <v>-13.65</v>
-      </c>
-      <c r="E65" s="6">
-        <v>-1.43</v>
-      </c>
-    </row>
-    <row r="66" spans="1:5">
-      <c r="A66" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="B66" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C66" s="5">
-        <v>-27.17</v>
-      </c>
-      <c r="D66" s="5">
-        <v>-1.32</v>
-      </c>
-      <c r="E66" s="7">
-        <v>25.85</v>
-      </c>
-    </row>
-    <row r="67" spans="1:5">
-      <c r="A67" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="B67" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C67" s="5">
-        <v>-28.09</v>
-      </c>
-      <c r="D67" s="5">
-        <v>18.57</v>
-      </c>
-      <c r="E67" s="7">
-        <v>46.66</v>
-      </c>
-    </row>
-    <row r="68" spans="1:5">
-      <c r="A68" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="B68" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C68" s="5">
-        <v>-8.359999999999999</v>
-      </c>
-      <c r="D68" s="5">
-        <v>31.47</v>
-      </c>
-      <c r="E68" s="7">
-        <v>39.83</v>
-      </c>
-    </row>
-    <row r="69" spans="1:5">
-      <c r="A69" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="B69" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C69" s="5">
-        <v>-55.64</v>
-      </c>
-      <c r="D69" s="5">
-        <v>-36.85</v>
-      </c>
-      <c r="E69" s="7">
-        <v>18.79</v>
-      </c>
-    </row>
-    <row r="70" spans="1:5">
-      <c r="A70" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="B70" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C70" s="5">
-        <v>-28.95</v>
-      </c>
-      <c r="D70" s="5">
+      <c r="C73" s="6">
         <v>23.7</v>
       </c>
-      <c r="E70" s="7">
-        <v>52.65</v>
+      <c r="D73" s="6">
+        <v>91.52</v>
+      </c>
+      <c r="E73" s="8">
+        <v>67.81999999999999</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A5:E5"/>
+    <mergeCell ref="A6:E6"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3093,61 +3204,61 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="28" customHeight="1">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="8" t="s">
-        <v>57</v>
-      </c>
-      <c r="C1" s="8" t="s">
-        <v>58</v>
-      </c>
-      <c r="D1" s="8" t="s">
-        <v>59</v>
-      </c>
-      <c r="E1" s="8" t="s">
-        <v>60</v>
-      </c>
-      <c r="F1" s="8" t="s">
-        <v>61</v>
-      </c>
-      <c r="G1" s="8" t="s">
-        <v>62</v>
-      </c>
-      <c r="H1" s="8" t="s">
-        <v>63</v>
-      </c>
-      <c r="I1" s="8" t="s">
+      <c r="B1" s="9" t="s">
         <v>64</v>
       </c>
+      <c r="C1" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="D1" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="E1" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="F1" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="G1" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="H1" s="9" t="s">
+        <v>70</v>
+      </c>
+      <c r="I1" s="9" t="s">
+        <v>71</v>
+      </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="9" t="s">
+      <c r="A2" s="10" t="s">
         <v>45</v>
       </c>
-      <c r="B2" s="10">
+      <c r="B2" s="11">
         <v>52.44</v>
       </c>
-      <c r="C2" s="11">
+      <c r="C2" s="12">
         <v>8</v>
       </c>
-      <c r="D2" s="10">
-        <v>38.9</v>
-      </c>
-      <c r="E2" s="10">
+      <c r="D2" s="11">
+        <v>37.3</v>
+      </c>
+      <c r="E2" s="11">
         <v>50</v>
       </c>
-      <c r="F2" s="10">
-        <v>-6.6</v>
-      </c>
-      <c r="G2" s="10">
-        <v>-4.9</v>
-      </c>
-      <c r="H2" s="10">
+      <c r="F2" s="11">
+        <v>-7.4</v>
+      </c>
+      <c r="G2" s="11">
+        <v>-6.1</v>
+      </c>
+      <c r="H2" s="11">
         <v>56.1</v>
       </c>
-      <c r="I2" s="10">
-        <v>20</v>
+      <c r="I2" s="11">
+        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -3248,55 +3359,55 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8">
-      <c r="A1" s="12" t="s">
+      <c r="A1" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="B1" s="12" t="s">
+      <c r="B1" s="13" t="s">
         <v>43</v>
       </c>
-      <c r="C1" s="12" t="s">
+      <c r="C1" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="D1" s="12" t="s">
+      <c r="D1" s="13" t="s">
         <v>39</v>
       </c>
-      <c r="E1" s="12" t="s">
+      <c r="E1" s="13" t="s">
         <v>44</v>
       </c>
-      <c r="F1" s="12" t="s">
+      <c r="F1" s="13" t="s">
         <v>41</v>
       </c>
-      <c r="G1" s="12" t="s">
+      <c r="G1" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="H1" s="12" t="s">
+      <c r="H1" s="13" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="2" spans="1:8">
-      <c r="A2" s="13">
-        <v>0.2746</v>
-      </c>
-      <c r="B2" s="13">
-        <v>0.167</v>
-      </c>
-      <c r="C2" s="13">
-        <v>0.1552</v>
-      </c>
-      <c r="D2" s="13">
-        <v>0.1435</v>
-      </c>
-      <c r="E2" s="13">
-        <v>0.0824</v>
-      </c>
-      <c r="F2" s="13">
-        <v>0.0423</v>
-      </c>
-      <c r="G2" s="13">
-        <v>-0.2661</v>
-      </c>
-      <c r="H2" s="13">
-        <v>-0.2992</v>
+      <c r="A2" s="14">
+        <v>0.2706</v>
+      </c>
+      <c r="B2" s="14">
+        <v>0.169</v>
+      </c>
+      <c r="C2" s="14">
+        <v>0.1475</v>
+      </c>
+      <c r="D2" s="14">
+        <v>0.137</v>
+      </c>
+      <c r="E2" s="14">
+        <v>0.08210000000000001</v>
+      </c>
+      <c r="F2" s="14">
+        <v>0.0381</v>
+      </c>
+      <c r="G2" s="14">
+        <v>-0.2755</v>
+      </c>
+      <c r="H2" s="14">
+        <v>-0.2977</v>
       </c>
     </row>
   </sheetData>

--- a/BIRLA_GROUP_Technical_Metrics.xlsx
+++ b/BIRLA_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="297" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="280" uniqueCount="65">
   <si>
     <t>Symbol</t>
   </si>
@@ -175,28 +175,7 @@
     <t>▶  SIGNAL EVENTS (vs Previous Run)</t>
   </si>
   <si>
-    <t>Signal</t>
-  </si>
-  <si>
-    <t>Change</t>
-  </si>
-  <si>
-    <t>Direction</t>
-  </si>
-  <si>
-    <t>Prev Value</t>
-  </si>
-  <si>
-    <t>Curr Value</t>
-  </si>
-  <si>
-    <t>Yes → No</t>
-  </si>
-  <si>
-    <t>🔴 BEARISH</t>
-  </si>
-  <si>
-    <t>20 DMA &gt; 50 DMA</t>
+    <t>No signal events detected since last run.</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -398,15 +377,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -780,8 +758,8 @@
     <col min="13" max="13" width="10.7109375" customWidth="1"/>
     <col min="14" max="14" width="11.7109375" customWidth="1"/>
     <col min="15" max="15" width="10.7109375" customWidth="1"/>
-    <col min="16" max="17" width="9.7109375" customWidth="1"/>
-    <col min="18" max="19" width="10.7109375" customWidth="1"/>
+    <col min="16" max="18" width="9.7109375" customWidth="1"/>
+    <col min="19" max="19" width="10.7109375" customWidth="1"/>
     <col min="20" max="20" width="22.7109375" customWidth="1"/>
     <col min="21" max="21" width="9.7109375" customWidth="1"/>
     <col min="22" max="22" width="10.7109375" customWidth="1"/>
@@ -921,10 +899,10 @@
         <v>45</v>
       </c>
       <c r="C2">
-        <v>378</v>
+        <v>380.6</v>
       </c>
       <c r="D2">
-        <v>-1.23</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="E2">
         <v>424.7</v>
@@ -933,46 +911,46 @@
         <v>278.9</v>
       </c>
       <c r="G2">
-        <v>-11</v>
+        <v>-10.38</v>
       </c>
       <c r="H2">
-        <v>35.53</v>
+        <v>36.46</v>
       </c>
       <c r="I2">
-        <v>-4.79</v>
+        <v>-5.43</v>
       </c>
       <c r="J2">
-        <v>-6.79</v>
+        <v>-7.03</v>
       </c>
       <c r="K2">
-        <v>-3.85</v>
+        <v>-3.14</v>
       </c>
       <c r="L2">
-        <v>29.47</v>
+        <v>32.84</v>
       </c>
       <c r="M2">
-        <v>27.06</v>
+        <v>27.55</v>
       </c>
       <c r="N2">
-        <v>62</v>
+        <v>74</v>
       </c>
       <c r="O2">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="P2">
-        <v>388.65</v>
+        <v>384.28</v>
       </c>
       <c r="Q2">
-        <v>394.87</v>
+        <v>394.18</v>
       </c>
       <c r="R2">
-        <v>401.83</v>
+        <v>401.26</v>
       </c>
       <c r="S2">
-        <v>364.36</v>
+        <v>364.49</v>
       </c>
       <c r="T2">
-        <v>3.74</v>
+        <v>4.42</v>
       </c>
       <c r="U2" t="s">
         <v>46</v>
@@ -987,34 +965,34 @@
         <v>2</v>
       </c>
       <c r="Y2">
-        <v>38.89</v>
+        <v>40.79</v>
       </c>
       <c r="Z2">
-        <v>-4.31</v>
+        <v>-4.86</v>
       </c>
       <c r="AA2">
-        <v>-2.71</v>
+        <v>-3.14</v>
       </c>
       <c r="AB2">
-        <v>-1.61</v>
+        <v>-1.73</v>
       </c>
       <c r="AC2">
-        <v>34.53</v>
+        <v>28.61</v>
       </c>
       <c r="AD2">
-        <v>45.57</v>
+        <v>35.49</v>
       </c>
       <c r="AE2">
-        <v>9.65</v>
+        <v>9.5</v>
       </c>
       <c r="AF2">
-        <v>69.65000000000001</v>
+        <v>26.92</v>
       </c>
       <c r="AG2">
-        <v>413.19</v>
+        <v>413.58</v>
       </c>
       <c r="AH2">
-        <v>376.55</v>
+        <v>374.78</v>
       </c>
       <c r="AI2">
         <v>372.91</v>
@@ -1023,7 +1001,7 @@
         <v>48</v>
       </c>
       <c r="AK2">
-        <v>27.09</v>
+        <v>27.73</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1034,10 +1012,10 @@
         <v>45</v>
       </c>
       <c r="C3">
-        <v>46.24</v>
+        <v>46.32</v>
       </c>
       <c r="D3">
-        <v>-2.84</v>
+        <v>0.17</v>
       </c>
       <c r="E3">
         <v>87.98999999999999</v>
@@ -1046,25 +1024,25 @@
         <v>46.24</v>
       </c>
       <c r="G3">
-        <v>-47.45</v>
+        <v>-47.36</v>
       </c>
       <c r="H3">
-        <v>0</v>
+        <v>0.17</v>
       </c>
       <c r="I3">
-        <v>-6.05</v>
+        <v>-5.64</v>
       </c>
       <c r="J3">
-        <v>-11.91</v>
+        <v>-11.09</v>
       </c>
       <c r="K3">
-        <v>-21.19</v>
+        <v>-25.15</v>
       </c>
       <c r="L3">
-        <v>-49.26</v>
+        <v>-46.95</v>
       </c>
       <c r="M3">
-        <v>-27.55</v>
+        <v>-28.41</v>
       </c>
       <c r="N3">
         <v>13</v>
@@ -1073,19 +1051,19 @@
         <v>5</v>
       </c>
       <c r="P3">
-        <v>48.02</v>
+        <v>47.47</v>
       </c>
       <c r="Q3">
-        <v>50.08</v>
+        <v>49.84</v>
       </c>
       <c r="R3">
-        <v>54.33</v>
+        <v>54.11</v>
       </c>
       <c r="S3">
-        <v>62.58</v>
+        <v>62.43</v>
       </c>
       <c r="T3">
-        <v>-26.11</v>
+        <v>-25.81</v>
       </c>
       <c r="U3" t="s">
         <v>46</v>
@@ -1100,43 +1078,43 @@
         <v>0</v>
       </c>
       <c r="Y3">
-        <v>27.97</v>
+        <v>28.49</v>
       </c>
       <c r="Z3">
-        <v>-1.89</v>
+        <v>-1.97</v>
       </c>
       <c r="AA3">
-        <v>-1.78</v>
+        <v>-1.81</v>
       </c>
       <c r="AB3">
-        <v>-0.12</v>
+        <v>-0.16</v>
       </c>
       <c r="AC3">
-        <v>29.48</v>
+        <v>11.51</v>
       </c>
       <c r="AD3">
-        <v>32.24</v>
+        <v>23.97</v>
       </c>
       <c r="AE3">
-        <v>1.53</v>
+        <v>1.51</v>
       </c>
       <c r="AF3">
-        <v>184.13</v>
+        <v>-22.58</v>
       </c>
       <c r="AG3">
-        <v>53.5</v>
+        <v>53.61</v>
       </c>
       <c r="AH3">
-        <v>46.66</v>
+        <v>46.07</v>
       </c>
       <c r="AI3">
-        <v>51.45</v>
+        <v>51.17</v>
       </c>
       <c r="AJ3" t="s">
         <v>49</v>
       </c>
       <c r="AK3">
-        <v>44.42</v>
+        <v>47.41</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1147,10 +1125,10 @@
         <v>45</v>
       </c>
       <c r="C4">
-        <v>3100</v>
+        <v>3061.9</v>
       </c>
       <c r="D4">
-        <v>-1.59</v>
+        <v>-1.23</v>
       </c>
       <c r="E4">
         <v>3380.5</v>
@@ -1159,46 +1137,46 @@
         <v>2531.1</v>
       </c>
       <c r="G4">
-        <v>-8.300000000000001</v>
+        <v>-9.42</v>
       </c>
       <c r="H4">
-        <v>22.48</v>
+        <v>20.97</v>
       </c>
       <c r="I4">
-        <v>-0.9</v>
+        <v>-3.97</v>
       </c>
       <c r="J4">
-        <v>-5.78</v>
+        <v>-9.17</v>
       </c>
       <c r="K4">
-        <v>-1.29</v>
+        <v>-3.39</v>
       </c>
       <c r="L4">
-        <v>10.42</v>
+        <v>10.2</v>
       </c>
       <c r="M4">
-        <v>13.7</v>
+        <v>13.42</v>
       </c>
       <c r="N4">
         <v>50</v>
       </c>
       <c r="O4">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="P4">
-        <v>3159.2</v>
+        <v>3133.88</v>
       </c>
       <c r="Q4">
-        <v>3228.62</v>
+        <v>3216.47</v>
       </c>
       <c r="R4">
-        <v>3231.06</v>
+        <v>3228.7</v>
       </c>
       <c r="S4">
-        <v>2974.89</v>
+        <v>2976.21</v>
       </c>
       <c r="T4">
-        <v>4.21</v>
+        <v>2.88</v>
       </c>
       <c r="U4" t="s">
         <v>46</v>
@@ -1213,43 +1191,43 @@
         <v>2</v>
       </c>
       <c r="Y4">
-        <v>37.36</v>
+        <v>34.45</v>
       </c>
       <c r="Z4">
-        <v>-32.45</v>
+        <v>-39.5</v>
       </c>
       <c r="AA4">
-        <v>-18.73</v>
+        <v>-22.89</v>
       </c>
       <c r="AB4">
-        <v>-13.71</v>
+        <v>-16.62</v>
       </c>
       <c r="AC4">
-        <v>24.91</v>
+        <v>9.49</v>
       </c>
       <c r="AD4">
-        <v>32.34</v>
+        <v>22.68</v>
       </c>
       <c r="AE4">
-        <v>58.95</v>
+        <v>59.45</v>
       </c>
       <c r="AF4">
-        <v>33.1</v>
+        <v>-49.56</v>
       </c>
       <c r="AG4">
-        <v>3377.55</v>
+        <v>3378.28</v>
       </c>
       <c r="AH4">
-        <v>3079.7</v>
+        <v>3054.66</v>
       </c>
       <c r="AI4">
-        <v>3297.11</v>
+        <v>3257.7</v>
       </c>
       <c r="AJ4" t="s">
         <v>49</v>
       </c>
       <c r="AK4">
-        <v>38.93</v>
+        <v>42.65</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1260,10 +1238,10 @@
         <v>45</v>
       </c>
       <c r="C5">
-        <v>955.2</v>
+        <v>941.8</v>
       </c>
       <c r="D5">
-        <v>-0.07000000000000001</v>
+        <v>-1.4</v>
       </c>
       <c r="E5">
         <v>1149.7</v>
@@ -1272,46 +1250,46 @@
         <v>743.85</v>
       </c>
       <c r="G5">
-        <v>-16.92</v>
+        <v>-18.08</v>
       </c>
       <c r="H5">
-        <v>28.41</v>
+        <v>26.61</v>
       </c>
       <c r="I5">
-        <v>-1.83</v>
+        <v>-6.18</v>
       </c>
       <c r="J5">
-        <v>-7.92</v>
+        <v>-7.25</v>
       </c>
       <c r="K5">
-        <v>1.65</v>
+        <v>-0.78</v>
       </c>
       <c r="L5">
-        <v>28.9</v>
+        <v>26.31</v>
       </c>
       <c r="M5">
-        <v>14.75</v>
+        <v>14.71</v>
       </c>
       <c r="N5">
+        <v>62</v>
+      </c>
+      <c r="O5">
         <v>74</v>
       </c>
-      <c r="O5">
-        <v>75</v>
-      </c>
       <c r="P5">
-        <v>974.78</v>
+        <v>962.38</v>
       </c>
       <c r="Q5">
-        <v>990.45</v>
+        <v>986.8200000000001</v>
       </c>
       <c r="R5">
-        <v>1004.61</v>
+        <v>1004.42</v>
       </c>
       <c r="S5">
-        <v>980.12</v>
+        <v>980.71</v>
       </c>
       <c r="T5">
-        <v>-2.54</v>
+        <v>-3.97</v>
       </c>
       <c r="U5" t="s">
         <v>46</v>
@@ -1326,43 +1304,43 @@
         <v>1</v>
       </c>
       <c r="Y5">
-        <v>38.46</v>
+        <v>35.55</v>
       </c>
       <c r="Z5">
-        <v>-13.37</v>
+        <v>-15.36</v>
       </c>
       <c r="AA5">
-        <v>-10.07</v>
+        <v>-11.12</v>
       </c>
       <c r="AB5">
-        <v>-3.3</v>
+        <v>-4.23</v>
       </c>
       <c r="AC5">
-        <v>32.47</v>
+        <v>18.41</v>
       </c>
       <c r="AD5">
-        <v>47.21</v>
+        <v>31.56</v>
       </c>
       <c r="AE5">
-        <v>22.2</v>
+        <v>21.73</v>
       </c>
       <c r="AF5">
-        <v>50.43</v>
+        <v>24.58</v>
       </c>
       <c r="AG5">
-        <v>1033.96</v>
+        <v>1033.89</v>
       </c>
       <c r="AH5">
-        <v>946.9400000000001</v>
+        <v>939.75</v>
       </c>
       <c r="AI5">
-        <v>1021.89</v>
+        <v>1014.15</v>
       </c>
       <c r="AJ5" t="s">
         <v>49</v>
       </c>
       <c r="AK5">
-        <v>22.86</v>
+        <v>25.63</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1373,10 +1351,10 @@
         <v>45</v>
       </c>
       <c r="C6">
-        <v>13.56</v>
+        <v>12.95</v>
       </c>
       <c r="D6">
-        <v>0.67</v>
+        <v>-4.5</v>
       </c>
       <c r="E6">
         <v>15.6</v>
@@ -1385,46 +1363,46 @@
         <v>8.02</v>
       </c>
       <c r="G6">
-        <v>-13.08</v>
+        <v>-16.99</v>
       </c>
       <c r="H6">
-        <v>69.08</v>
+        <v>61.47</v>
       </c>
       <c r="I6">
-        <v>-4.98</v>
+        <v>-10.81</v>
       </c>
       <c r="J6">
-        <v>-7.63</v>
+        <v>-9.630000000000001</v>
       </c>
       <c r="K6">
-        <v>-7.38</v>
+        <v>-10.57</v>
       </c>
       <c r="L6">
-        <v>57.86</v>
+        <v>49.19</v>
       </c>
       <c r="M6">
-        <v>3.81</v>
+        <v>1.71</v>
       </c>
       <c r="N6">
         <v>87</v>
       </c>
       <c r="O6">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="P6">
-        <v>13.99</v>
+        <v>13.67</v>
       </c>
       <c r="Q6">
-        <v>14.47</v>
+        <v>14.41</v>
       </c>
       <c r="R6">
-        <v>13.93</v>
+        <v>13.92</v>
       </c>
       <c r="S6">
-        <v>12.23</v>
+        <v>12.24</v>
       </c>
       <c r="T6">
-        <v>10.88</v>
+        <v>5.82</v>
       </c>
       <c r="U6" t="s">
         <v>47</v>
@@ -1439,43 +1417,43 @@
         <v>3</v>
       </c>
       <c r="Y6">
-        <v>41.18</v>
+        <v>35.45</v>
       </c>
       <c r="Z6">
-        <v>-0.11</v>
+        <v>-0.19</v>
       </c>
       <c r="AA6">
-        <v>0.04</v>
+        <v>-0.01</v>
       </c>
       <c r="AB6">
-        <v>-0.15</v>
+        <v>-0.19</v>
       </c>
       <c r="AC6">
-        <v>10.1</v>
+        <v>1.69</v>
       </c>
       <c r="AD6">
-        <v>17.14</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="AE6">
-        <v>0.49</v>
+        <v>0.51</v>
       </c>
       <c r="AF6">
-        <v>170.27</v>
+        <v>38.55</v>
       </c>
       <c r="AG6">
-        <v>15.69</v>
+        <v>15.8</v>
       </c>
       <c r="AH6">
-        <v>13.25</v>
+        <v>13.03</v>
       </c>
       <c r="AI6">
-        <v>14.94</v>
+        <v>14.75</v>
       </c>
       <c r="AJ6" t="s">
         <v>49</v>
       </c>
       <c r="AK6">
-        <v>28.66</v>
+        <v>33.05</v>
       </c>
     </row>
     <row r="7" spans="1:37">
@@ -1486,10 +1464,10 @@
         <v>45</v>
       </c>
       <c r="C7">
-        <v>10.84</v>
+        <v>10.92</v>
       </c>
       <c r="D7">
-        <v>-1.63</v>
+        <v>0.74</v>
       </c>
       <c r="E7">
         <v>13.92</v>
@@ -1498,46 +1476,46 @@
         <v>4.69</v>
       </c>
       <c r="G7">
-        <v>-22.13</v>
+        <v>-21.55</v>
       </c>
       <c r="H7">
-        <v>131.13</v>
+        <v>132.84</v>
       </c>
       <c r="I7">
-        <v>-4.49</v>
+        <v>-5.62</v>
       </c>
       <c r="J7">
-        <v>-4.07</v>
+        <v>-1.62</v>
       </c>
       <c r="K7">
-        <v>-2.78</v>
+        <v>-0.27</v>
       </c>
       <c r="L7">
-        <v>80.67</v>
+        <v>82.91</v>
       </c>
       <c r="M7">
-        <v>-29.77</v>
+        <v>-29.65</v>
       </c>
       <c r="N7">
         <v>99</v>
       </c>
       <c r="O7">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="P7">
-        <v>11.28</v>
+        <v>11.15</v>
       </c>
       <c r="Q7">
-        <v>11.54</v>
+        <v>11.53</v>
       </c>
       <c r="R7">
-        <v>11.78</v>
+        <v>11.76</v>
       </c>
       <c r="S7">
-        <v>10.79</v>
+        <v>10.8</v>
       </c>
       <c r="T7">
-        <v>0.5</v>
+        <v>1.1</v>
       </c>
       <c r="U7" t="s">
         <v>46</v>
@@ -1552,43 +1530,43 @@
         <v>2</v>
       </c>
       <c r="Y7">
-        <v>38.67</v>
+        <v>40.18</v>
       </c>
       <c r="Z7">
-        <v>-0.11</v>
+        <v>-0.14</v>
       </c>
       <c r="AA7">
-        <v>-0.02</v>
+        <v>-0.04</v>
       </c>
       <c r="AB7">
-        <v>-0.09</v>
+        <v>-0.1</v>
       </c>
       <c r="AC7">
-        <v>8.31</v>
+        <v>1.78</v>
       </c>
       <c r="AD7">
-        <v>18.39</v>
+        <v>9.16</v>
       </c>
       <c r="AE7">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="AF7">
-        <v>146.62</v>
+        <v>24.38</v>
       </c>
       <c r="AG7">
-        <v>12.55</v>
+        <v>12.56</v>
       </c>
       <c r="AH7">
-        <v>10.53</v>
+        <v>10.5</v>
       </c>
       <c r="AI7">
-        <v>12.33</v>
+        <v>12.29</v>
       </c>
       <c r="AJ7" t="s">
         <v>49</v>
       </c>
       <c r="AK7">
-        <v>29.96</v>
+        <v>31.82</v>
       </c>
     </row>
     <row r="8" spans="1:37">
@@ -1599,58 +1577,58 @@
         <v>45</v>
       </c>
       <c r="C8">
-        <v>4027.7</v>
+        <v>3956.5</v>
       </c>
       <c r="D8">
-        <v>0.76</v>
+        <v>-1.77</v>
       </c>
       <c r="E8">
         <v>5809.5</v>
       </c>
       <c r="F8">
-        <v>3997.5</v>
+        <v>3956.5</v>
       </c>
       <c r="G8">
-        <v>-30.67</v>
+        <v>-31.9</v>
       </c>
       <c r="H8">
-        <v>0.76</v>
+        <v>0</v>
       </c>
       <c r="I8">
-        <v>0.48</v>
+        <v>-2.11</v>
       </c>
       <c r="J8">
-        <v>-8.210000000000001</v>
+        <v>-9.119999999999999</v>
       </c>
       <c r="K8">
-        <v>-8.51</v>
+        <v>-10.83</v>
       </c>
       <c r="L8">
-        <v>-25.89</v>
+        <v>-26.25</v>
       </c>
       <c r="M8">
-        <v>16.9</v>
+        <v>16.35</v>
       </c>
       <c r="N8">
         <v>26</v>
       </c>
       <c r="O8">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="P8">
-        <v>4017.82</v>
+        <v>4000.76</v>
       </c>
       <c r="Q8">
-        <v>4143.09</v>
+        <v>4123.26</v>
       </c>
       <c r="R8">
-        <v>4277.5</v>
+        <v>4267.88</v>
       </c>
       <c r="S8">
-        <v>4542.5</v>
+        <v>4536.48</v>
       </c>
       <c r="T8">
-        <v>-11.33</v>
+        <v>-12.78</v>
       </c>
       <c r="U8" t="s">
         <v>46</v>
@@ -1665,34 +1643,34 @@
         <v>0</v>
       </c>
       <c r="Y8">
-        <v>37.01</v>
+        <v>32.47</v>
       </c>
       <c r="Z8">
-        <v>-89.09999999999999</v>
+        <v>-91.25</v>
       </c>
       <c r="AA8">
-        <v>-82.15000000000001</v>
+        <v>-83.97</v>
       </c>
       <c r="AB8">
-        <v>-6.95</v>
+        <v>-7.29</v>
       </c>
       <c r="AC8">
-        <v>36.46</v>
+        <v>27.72</v>
       </c>
       <c r="AD8">
-        <v>29.73</v>
+        <v>29.91</v>
       </c>
       <c r="AE8">
-        <v>100.48</v>
+        <v>109.39</v>
       </c>
       <c r="AF8">
-        <v>4.84</v>
+        <v>141.95</v>
       </c>
       <c r="AG8">
-        <v>4409.74</v>
+        <v>4383.03</v>
       </c>
       <c r="AH8">
-        <v>3876.44</v>
+        <v>3863.48</v>
       </c>
       <c r="AI8">
         <v>4288.14</v>
@@ -1701,7 +1679,7 @@
         <v>49</v>
       </c>
       <c r="AK8">
-        <v>60.73</v>
+        <v>58.53</v>
       </c>
     </row>
     <row r="9" spans="1:37">
@@ -1712,10 +1690,10 @@
         <v>45</v>
       </c>
       <c r="C9">
-        <v>10829</v>
+        <v>10956</v>
       </c>
       <c r="D9">
-        <v>-1.78</v>
+        <v>1.17</v>
       </c>
       <c r="E9">
         <v>13052</v>
@@ -1724,46 +1702,46 @@
         <v>10362</v>
       </c>
       <c r="G9">
-        <v>-17.03</v>
+        <v>-16.06</v>
       </c>
       <c r="H9">
-        <v>4.51</v>
+        <v>5.73</v>
       </c>
       <c r="I9">
-        <v>-1.55</v>
+        <v>-1.78</v>
       </c>
       <c r="J9">
-        <v>-6.56</v>
+        <v>-4.31</v>
       </c>
       <c r="K9">
-        <v>-5.47</v>
+        <v>-5.03</v>
       </c>
       <c r="L9">
-        <v>-11.34</v>
+        <v>-9.76</v>
       </c>
       <c r="M9">
-        <v>8.210000000000001</v>
+        <v>8.67</v>
       </c>
       <c r="N9">
         <v>38</v>
       </c>
       <c r="O9">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="P9">
-        <v>11044</v>
+        <v>11004.2</v>
       </c>
       <c r="Q9">
-        <v>11051.7</v>
+        <v>11029.5</v>
       </c>
       <c r="R9">
-        <v>11501.96</v>
+        <v>11479.2</v>
       </c>
       <c r="S9">
-        <v>11715.79</v>
+        <v>11713.21</v>
       </c>
       <c r="T9">
-        <v>-7.57</v>
+        <v>-6.46</v>
       </c>
       <c r="U9" t="s">
         <v>46</v>
@@ -1778,34 +1756,34 @@
         <v>0</v>
       </c>
       <c r="Y9">
-        <v>38.95</v>
+        <v>43.59</v>
       </c>
       <c r="Z9">
-        <v>-137.19</v>
+        <v>-132.42</v>
       </c>
       <c r="AA9">
-        <v>-159.3</v>
+        <v>-153.93</v>
       </c>
       <c r="AB9">
-        <v>22.11</v>
+        <v>21.5</v>
       </c>
       <c r="AC9">
-        <v>79.01000000000001</v>
+        <v>71.77</v>
       </c>
       <c r="AD9">
-        <v>87.62</v>
+        <v>79.84999999999999</v>
       </c>
       <c r="AE9">
-        <v>191.49</v>
+        <v>190.03</v>
       </c>
       <c r="AF9">
-        <v>91.52</v>
+        <v>-8.699999999999999</v>
       </c>
       <c r="AG9">
-        <v>11480.4</v>
+        <v>11427.12</v>
       </c>
       <c r="AH9">
-        <v>10623</v>
+        <v>10631.88</v>
       </c>
       <c r="AI9">
         <v>11371.08</v>
@@ -1814,7 +1792,7 @@
         <v>49</v>
       </c>
       <c r="AK9">
-        <v>24.18</v>
+        <v>25.64</v>
       </c>
     </row>
   </sheetData>
@@ -1955,7 +1933,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F73"/>
+  <dimension ref="A1:F72"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -1975,1216 +1953,1161 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="3" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6">
+      <c r="A5" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="B5" s="2"/>
+      <c r="C5" s="2"/>
+      <c r="D5" s="2"/>
+      <c r="E5" s="2"/>
+    </row>
+    <row r="6" spans="1:6">
+      <c r="A6" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="D2" s="3" t="s">
+      <c r="B6" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="E2" s="3" t="s">
+      <c r="C6" s="4" t="s">
         <v>54</v>
       </c>
-      <c r="F2" s="3" t="s">
+      <c r="D6" s="4" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="3" spans="1:6">
-      <c r="A3" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="B3" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="C3" s="4" t="s">
+      <c r="E6" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="D3" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="E3" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="F3" s="4" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6">
-      <c r="A4" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="B4" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="C4" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="D4" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="E4" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="F4" s="4" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6">
-      <c r="A6" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="B6" s="2"/>
-      <c r="C6" s="2"/>
-      <c r="D6" s="2"/>
-      <c r="E6" s="2"/>
     </row>
     <row r="7" spans="1:6">
       <c r="A7" s="3" t="s">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="D7" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C7" s="5">
+        <v>-6.79</v>
+      </c>
+      <c r="D7" s="5">
+        <v>-7.03</v>
+      </c>
+      <c r="E7" s="6">
+        <v>-0.24</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C8" s="5">
+        <v>-11.91</v>
+      </c>
+      <c r="D8" s="5">
+        <v>-11.09</v>
+      </c>
+      <c r="E8" s="7">
+        <v>0.82</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C9" s="5">
+        <v>-5.78</v>
+      </c>
+      <c r="D9" s="5">
+        <v>-9.17</v>
+      </c>
+      <c r="E9" s="6">
+        <v>-3.39</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C10" s="5">
+        <v>-7.92</v>
+      </c>
+      <c r="D10" s="5">
+        <v>-7.25</v>
+      </c>
+      <c r="E10" s="7">
+        <v>0.67</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C11" s="5">
+        <v>-7.63</v>
+      </c>
+      <c r="D11" s="5">
+        <v>-9.630000000000001</v>
+      </c>
+      <c r="E11" s="6">
+        <v>-2</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C12" s="5">
+        <v>-4.07</v>
+      </c>
+      <c r="D12" s="5">
+        <v>-1.62</v>
+      </c>
+      <c r="E12" s="7">
+        <v>2.45</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="A13" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C13" s="5">
+        <v>-8.210000000000001</v>
+      </c>
+      <c r="D13" s="5">
+        <v>-9.119999999999999</v>
+      </c>
+      <c r="E13" s="6">
+        <v>-0.91</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C14" s="5">
+        <v>-6.56</v>
+      </c>
+      <c r="D14" s="5">
+        <v>-4.31</v>
+      </c>
+      <c r="E14" s="7">
+        <v>2.25</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="A15" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C15" s="5">
+        <v>-4.79</v>
+      </c>
+      <c r="D15" s="5">
+        <v>-5.43</v>
+      </c>
+      <c r="E15" s="6">
+        <v>-0.64</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="A16" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C16" s="5">
+        <v>-6.05</v>
+      </c>
+      <c r="D16" s="5">
+        <v>-5.64</v>
+      </c>
+      <c r="E16" s="7">
+        <v>0.41</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C17" s="5">
+        <v>-0.9</v>
+      </c>
+      <c r="D17" s="5">
+        <v>-3.97</v>
+      </c>
+      <c r="E17" s="6">
+        <v>-3.07</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C18" s="5">
+        <v>-1.83</v>
+      </c>
+      <c r="D18" s="5">
+        <v>-6.18</v>
+      </c>
+      <c r="E18" s="6">
+        <v>-4.35</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C19" s="5">
+        <v>-4.98</v>
+      </c>
+      <c r="D19" s="5">
+        <v>-10.81</v>
+      </c>
+      <c r="E19" s="6">
+        <v>-5.83</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C20" s="5">
+        <v>-4.49</v>
+      </c>
+      <c r="D20" s="5">
+        <v>-5.62</v>
+      </c>
+      <c r="E20" s="6">
+        <v>-1.13</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C21" s="5">
+        <v>0.48</v>
+      </c>
+      <c r="D21" s="5">
+        <v>-2.11</v>
+      </c>
+      <c r="E21" s="6">
+        <v>-2.59</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C22" s="5">
+        <v>-1.55</v>
+      </c>
+      <c r="D22" s="5">
+        <v>-1.78</v>
+      </c>
+      <c r="E22" s="6">
+        <v>-0.23</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C23" s="5">
+        <v>29.47</v>
+      </c>
+      <c r="D23" s="5">
+        <v>32.84</v>
+      </c>
+      <c r="E23" s="7">
+        <v>3.37</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C24" s="5">
+        <v>-49.26</v>
+      </c>
+      <c r="D24" s="5">
+        <v>-46.95</v>
+      </c>
+      <c r="E24" s="7">
+        <v>2.31</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B25" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C25" s="5">
+        <v>10.42</v>
+      </c>
+      <c r="D25" s="5">
+        <v>10.2</v>
+      </c>
+      <c r="E25" s="6">
+        <v>-0.22</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C26" s="5">
+        <v>28.9</v>
+      </c>
+      <c r="D26" s="5">
+        <v>26.31</v>
+      </c>
+      <c r="E26" s="6">
+        <v>-2.59</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B27" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C27" s="5">
+        <v>57.86</v>
+      </c>
+      <c r="D27" s="5">
+        <v>49.19</v>
+      </c>
+      <c r="E27" s="6">
+        <v>-8.67</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B28" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C28" s="5">
+        <v>80.67</v>
+      </c>
+      <c r="D28" s="5">
+        <v>82.91</v>
+      </c>
+      <c r="E28" s="7">
+        <v>2.24</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="B29" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C29" s="5">
+        <v>-25.89</v>
+      </c>
+      <c r="D29" s="5">
+        <v>-26.25</v>
+      </c>
+      <c r="E29" s="6">
+        <v>-0.36</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="B30" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C30" s="5">
+        <v>-11.34</v>
+      </c>
+      <c r="D30" s="5">
+        <v>-9.76</v>
+      </c>
+      <c r="E30" s="7">
+        <v>1.58</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5">
+      <c r="A31" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B31" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C31" s="5">
+        <v>-3.85</v>
+      </c>
+      <c r="D31" s="5">
+        <v>-3.14</v>
+      </c>
+      <c r="E31" s="7">
+        <v>0.71</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5">
+      <c r="A32" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B32" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C32" s="5">
+        <v>-21.19</v>
+      </c>
+      <c r="D32" s="5">
+        <v>-25.15</v>
+      </c>
+      <c r="E32" s="6">
+        <v>-3.96</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5">
+      <c r="A33" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B33" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C33" s="5">
+        <v>-1.29</v>
+      </c>
+      <c r="D33" s="5">
+        <v>-3.39</v>
+      </c>
+      <c r="E33" s="6">
+        <v>-2.1</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5">
+      <c r="A34" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B34" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C34" s="5">
+        <v>1.65</v>
+      </c>
+      <c r="D34" s="5">
+        <v>-0.78</v>
+      </c>
+      <c r="E34" s="6">
+        <v>-2.43</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5">
+      <c r="A35" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B35" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C35" s="5">
+        <v>-7.38</v>
+      </c>
+      <c r="D35" s="5">
+        <v>-10.57</v>
+      </c>
+      <c r="E35" s="6">
+        <v>-3.19</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5">
+      <c r="A36" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B36" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C36" s="5">
+        <v>-2.78</v>
+      </c>
+      <c r="D36" s="5">
+        <v>-0.27</v>
+      </c>
+      <c r="E36" s="7">
+        <v>2.51</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5">
+      <c r="A37" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="B37" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C37" s="5">
+        <v>-8.51</v>
+      </c>
+      <c r="D37" s="5">
+        <v>-10.83</v>
+      </c>
+      <c r="E37" s="6">
+        <v>-2.32</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5">
+      <c r="A38" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="B38" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C38" s="5">
+        <v>-5.47</v>
+      </c>
+      <c r="D38" s="5">
+        <v>-5.03</v>
+      </c>
+      <c r="E38" s="7">
+        <v>0.44</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5">
+      <c r="A39" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B39" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C39" s="5">
+        <v>-11</v>
+      </c>
+      <c r="D39" s="5">
+        <v>-10.38</v>
+      </c>
+      <c r="E39" s="7">
+        <v>0.62</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5">
+      <c r="A40" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B40" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C40" s="5">
+        <v>-47.45</v>
+      </c>
+      <c r="D40" s="5">
+        <v>-47.36</v>
+      </c>
+      <c r="E40" s="7">
+        <v>0.09</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5">
+      <c r="A41" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B41" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C41" s="5">
+        <v>-8.300000000000001</v>
+      </c>
+      <c r="D41" s="5">
+        <v>-9.42</v>
+      </c>
+      <c r="E41" s="6">
+        <v>-1.12</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5">
+      <c r="A42" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B42" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C42" s="5">
+        <v>-16.92</v>
+      </c>
+      <c r="D42" s="5">
+        <v>-18.08</v>
+      </c>
+      <c r="E42" s="6">
+        <v>-1.16</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5">
+      <c r="A43" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B43" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C43" s="5">
+        <v>-13.08</v>
+      </c>
+      <c r="D43" s="5">
+        <v>-16.99</v>
+      </c>
+      <c r="E43" s="6">
+        <v>-3.91</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5">
+      <c r="A44" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B44" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C44" s="5">
+        <v>-22.13</v>
+      </c>
+      <c r="D44" s="5">
+        <v>-21.55</v>
+      </c>
+      <c r="E44" s="7">
+        <v>0.58</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5">
+      <c r="A45" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="B45" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C45" s="5">
+        <v>-30.67</v>
+      </c>
+      <c r="D45" s="5">
+        <v>-31.9</v>
+      </c>
+      <c r="E45" s="6">
+        <v>-1.23</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5">
+      <c r="A46" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="B46" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C46" s="5">
+        <v>-17.03</v>
+      </c>
+      <c r="D46" s="5">
+        <v>-16.06</v>
+      </c>
+      <c r="E46" s="7">
+        <v>0.97</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5">
+      <c r="A47" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B47" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C47" s="5">
+        <v>378</v>
+      </c>
+      <c r="D47" s="5">
+        <v>380.6</v>
+      </c>
+      <c r="E47" s="7">
+        <v>2.6</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5">
+      <c r="A48" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B48" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C48" s="5">
+        <v>46.24</v>
+      </c>
+      <c r="D48" s="5">
+        <v>46.32</v>
+      </c>
+      <c r="E48" s="7">
+        <v>0.08</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5">
+      <c r="A49" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B49" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C49" s="5">
+        <v>3100</v>
+      </c>
+      <c r="D49" s="5">
+        <v>3061.9</v>
+      </c>
+      <c r="E49" s="6">
+        <v>-38.1</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5">
+      <c r="A50" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B50" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C50" s="5">
+        <v>955.2</v>
+      </c>
+      <c r="D50" s="5">
+        <v>941.8</v>
+      </c>
+      <c r="E50" s="6">
+        <v>-13.4</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5">
+      <c r="A51" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B51" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C51" s="5">
+        <v>13.56</v>
+      </c>
+      <c r="D51" s="5">
+        <v>12.95</v>
+      </c>
+      <c r="E51" s="6">
+        <v>-0.61</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5">
+      <c r="A52" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B52" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C52" s="5">
+        <v>10.84</v>
+      </c>
+      <c r="D52" s="5">
+        <v>10.92</v>
+      </c>
+      <c r="E52" s="7">
+        <v>0.08</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5">
+      <c r="A53" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="B53" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C53" s="5">
+        <v>4027.7</v>
+      </c>
+      <c r="D53" s="5">
+        <v>3956.5</v>
+      </c>
+      <c r="E53" s="6">
+        <v>-71.2</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5">
+      <c r="A54" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="B54" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C54" s="5">
+        <v>10829</v>
+      </c>
+      <c r="D54" s="5">
+        <v>10956</v>
+      </c>
+      <c r="E54" s="7">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5">
+      <c r="A55" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B55" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C55" s="5">
         <v>62</v>
       </c>
-      <c r="E7" s="3" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
-      <c r="A8" s="5" t="s">
+      <c r="D55" s="5">
+        <v>74</v>
+      </c>
+      <c r="E55" s="7">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5">
+      <c r="A56" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B56" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C56" s="5">
+        <v>74</v>
+      </c>
+      <c r="D56" s="5">
+        <v>62</v>
+      </c>
+      <c r="E56" s="6">
+        <v>-12</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5">
+      <c r="A57" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B8" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C8" s="6">
-        <v>-6.66</v>
-      </c>
-      <c r="D8" s="6">
-        <v>-6.79</v>
-      </c>
-      <c r="E8" s="7">
-        <v>-0.13</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9" s="5" t="s">
+      <c r="B57" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C57" s="5">
+        <v>38.89</v>
+      </c>
+      <c r="D57" s="5">
+        <v>40.79</v>
+      </c>
+      <c r="E57" s="7">
+        <v>1.9</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5">
+      <c r="A58" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B9" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C9" s="6">
-        <v>-11.28</v>
-      </c>
-      <c r="D9" s="6">
-        <v>-11.91</v>
-      </c>
-      <c r="E9" s="7">
-        <v>-0.63</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10" s="5" t="s">
+      <c r="B58" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C58" s="5">
+        <v>27.97</v>
+      </c>
+      <c r="D58" s="5">
+        <v>28.49</v>
+      </c>
+      <c r="E58" s="7">
+        <v>0.52</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5">
+      <c r="A59" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B10" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C10" s="6">
-        <v>-3.31</v>
-      </c>
-      <c r="D10" s="6">
-        <v>-5.78</v>
-      </c>
-      <c r="E10" s="7">
-        <v>-2.47</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11" s="5" t="s">
+      <c r="B59" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C59" s="5">
+        <v>37.36</v>
+      </c>
+      <c r="D59" s="5">
+        <v>34.45</v>
+      </c>
+      <c r="E59" s="6">
+        <v>-2.91</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5">
+      <c r="A60" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="B11" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C11" s="6">
-        <v>-6.65</v>
-      </c>
-      <c r="D11" s="6">
-        <v>-7.92</v>
-      </c>
-      <c r="E11" s="7">
-        <v>-1.27</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12" s="5" t="s">
+      <c r="B60" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C60" s="5">
+        <v>38.46</v>
+      </c>
+      <c r="D60" s="5">
+        <v>35.55</v>
+      </c>
+      <c r="E60" s="6">
+        <v>-2.91</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5">
+      <c r="A61" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="B12" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C12" s="6">
-        <v>-10.02</v>
-      </c>
-      <c r="D12" s="6">
-        <v>-7.63</v>
-      </c>
-      <c r="E12" s="8">
-        <v>2.39</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13" s="5" t="s">
+      <c r="B61" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C61" s="5">
+        <v>41.18</v>
+      </c>
+      <c r="D61" s="5">
+        <v>35.45</v>
+      </c>
+      <c r="E61" s="6">
+        <v>-5.73</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5">
+      <c r="A62" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="B13" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C13" s="6">
-        <v>-0.8100000000000001</v>
-      </c>
-      <c r="D13" s="6">
-        <v>-4.07</v>
-      </c>
-      <c r="E13" s="7">
-        <v>-3.26</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14" s="5" t="s">
+      <c r="B62" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C62" s="5">
+        <v>38.67</v>
+      </c>
+      <c r="D62" s="5">
+        <v>40.18</v>
+      </c>
+      <c r="E62" s="7">
+        <v>1.51</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5">
+      <c r="A63" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="B14" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C14" s="6">
-        <v>-8.390000000000001</v>
-      </c>
-      <c r="D14" s="6">
-        <v>-8.210000000000001</v>
-      </c>
-      <c r="E14" s="8">
-        <v>0.18</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15" s="5" t="s">
+      <c r="B63" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C63" s="5">
+        <v>37.01</v>
+      </c>
+      <c r="D63" s="5">
+        <v>32.47</v>
+      </c>
+      <c r="E63" s="6">
+        <v>-4.54</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5">
+      <c r="A64" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="B15" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C15" s="6">
-        <v>-5.91</v>
-      </c>
-      <c r="D15" s="6">
-        <v>-6.56</v>
-      </c>
-      <c r="E15" s="7">
-        <v>-0.65</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16" s="5" t="s">
+      <c r="B64" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C64" s="5">
+        <v>38.95</v>
+      </c>
+      <c r="D64" s="5">
+        <v>43.59</v>
+      </c>
+      <c r="E64" s="7">
+        <v>4.64</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5">
+      <c r="A65" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B16" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C16" s="6">
-        <v>-5.13</v>
-      </c>
-      <c r="D16" s="6">
-        <v>-4.79</v>
-      </c>
-      <c r="E16" s="8">
-        <v>0.34</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5">
-      <c r="A17" s="5" t="s">
+      <c r="B65" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C65" s="5">
+        <v>69.65000000000001</v>
+      </c>
+      <c r="D65" s="5">
+        <v>26.92</v>
+      </c>
+      <c r="E65" s="6">
+        <v>-42.73</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5">
+      <c r="A66" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B17" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C17" s="6">
-        <v>-4.53</v>
-      </c>
-      <c r="D17" s="6">
-        <v>-6.05</v>
-      </c>
-      <c r="E17" s="7">
-        <v>-1.52</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5">
-      <c r="A18" s="5" t="s">
+      <c r="B66" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C66" s="5">
+        <v>184.13</v>
+      </c>
+      <c r="D66" s="5">
+        <v>-22.58</v>
+      </c>
+      <c r="E66" s="6">
+        <v>-206.71</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5">
+      <c r="A67" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B18" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C18" s="6">
-        <v>-0.51</v>
-      </c>
-      <c r="D18" s="6">
-        <v>-0.9</v>
-      </c>
-      <c r="E18" s="7">
-        <v>-0.39</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5">
-      <c r="A19" s="5" t="s">
+      <c r="B67" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C67" s="5">
+        <v>33.1</v>
+      </c>
+      <c r="D67" s="5">
+        <v>-49.56</v>
+      </c>
+      <c r="E67" s="6">
+        <v>-82.66</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5">
+      <c r="A68" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="B19" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C19" s="6">
-        <v>-2.58</v>
-      </c>
-      <c r="D19" s="6">
-        <v>-1.83</v>
-      </c>
-      <c r="E19" s="8">
-        <v>0.75</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5">
-      <c r="A20" s="5" t="s">
+      <c r="B68" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C68" s="5">
+        <v>50.43</v>
+      </c>
+      <c r="D68" s="5">
+        <v>24.58</v>
+      </c>
+      <c r="E68" s="6">
+        <v>-25.85</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5">
+      <c r="A69" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="B20" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C20" s="6">
-        <v>-2.67</v>
-      </c>
-      <c r="D20" s="6">
-        <v>-4.98</v>
-      </c>
-      <c r="E20" s="7">
-        <v>-2.31</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5">
-      <c r="A21" s="5" t="s">
+      <c r="B69" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C69" s="5">
+        <v>170.27</v>
+      </c>
+      <c r="D69" s="5">
+        <v>38.55</v>
+      </c>
+      <c r="E69" s="6">
+        <v>-131.72</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5">
+      <c r="A70" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="B21" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C21" s="6">
-        <v>-5.49</v>
-      </c>
-      <c r="D21" s="6">
-        <v>-4.49</v>
-      </c>
-      <c r="E21" s="8">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5">
-      <c r="A22" s="5" t="s">
+      <c r="B70" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C70" s="5">
+        <v>146.62</v>
+      </c>
+      <c r="D70" s="5">
+        <v>24.38</v>
+      </c>
+      <c r="E70" s="6">
+        <v>-122.24</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5">
+      <c r="A71" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="B22" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C22" s="6">
-        <v>-0.74</v>
-      </c>
-      <c r="D22" s="6">
-        <v>0.48</v>
-      </c>
-      <c r="E22" s="8">
-        <v>1.22</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5">
-      <c r="A23" s="5" t="s">
+      <c r="B71" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C71" s="5">
+        <v>4.84</v>
+      </c>
+      <c r="D71" s="5">
+        <v>141.95</v>
+      </c>
+      <c r="E71" s="7">
+        <v>137.11</v>
+      </c>
+    </row>
+    <row r="72" spans="1:5">
+      <c r="A72" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="B23" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C23" s="6">
-        <v>-0.68</v>
-      </c>
-      <c r="D23" s="6">
-        <v>-1.55</v>
-      </c>
-      <c r="E23" s="7">
-        <v>-0.87</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5">
-      <c r="A24" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B24" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C24" s="6">
-        <v>31.31</v>
-      </c>
-      <c r="D24" s="6">
-        <v>29.47</v>
-      </c>
-      <c r="E24" s="7">
-        <v>-1.84</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5">
-      <c r="A25" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B25" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C25" s="6">
-        <v>-48.29</v>
-      </c>
-      <c r="D25" s="6">
-        <v>-49.26</v>
-      </c>
-      <c r="E25" s="7">
-        <v>-0.97</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5">
-      <c r="A26" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B26" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C26" s="6">
-        <v>11.96</v>
-      </c>
-      <c r="D26" s="6">
-        <v>10.42</v>
-      </c>
-      <c r="E26" s="7">
-        <v>-1.54</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5">
-      <c r="A27" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B27" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C27" s="6">
-        <v>28.15</v>
-      </c>
-      <c r="D27" s="6">
-        <v>28.9</v>
-      </c>
-      <c r="E27" s="8">
-        <v>0.75</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5">
-      <c r="A28" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B28" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C28" s="6">
-        <v>54.47</v>
-      </c>
-      <c r="D28" s="6">
-        <v>57.86</v>
-      </c>
-      <c r="E28" s="8">
-        <v>3.39</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5">
-      <c r="A29" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B29" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C29" s="6">
-        <v>92.66</v>
-      </c>
-      <c r="D29" s="6">
-        <v>80.67</v>
-      </c>
-      <c r="E29" s="7">
-        <v>-11.99</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5">
-      <c r="A30" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B30" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C30" s="6">
-        <v>-24.71</v>
-      </c>
-      <c r="D30" s="6">
-        <v>-25.89</v>
-      </c>
-      <c r="E30" s="7">
-        <v>-1.18</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5">
-      <c r="A31" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="B31" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C31" s="6">
-        <v>-11.1</v>
-      </c>
-      <c r="D31" s="6">
-        <v>-11.34</v>
-      </c>
-      <c r="E31" s="7">
-        <v>-0.24</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5">
-      <c r="A32" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B32" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C32" s="6">
-        <v>-2.36</v>
-      </c>
-      <c r="D32" s="6">
-        <v>-3.85</v>
-      </c>
-      <c r="E32" s="7">
-        <v>-1.49</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5">
-      <c r="A33" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B33" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C33" s="6">
-        <v>-18.03</v>
-      </c>
-      <c r="D33" s="6">
-        <v>-21.19</v>
-      </c>
-      <c r="E33" s="7">
-        <v>-3.16</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5">
-      <c r="A34" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B34" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C34" s="6">
-        <v>1.61</v>
-      </c>
-      <c r="D34" s="6">
-        <v>-1.29</v>
-      </c>
-      <c r="E34" s="7">
-        <v>-2.9</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5">
-      <c r="A35" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B35" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C35" s="6">
-        <v>-0.07000000000000001</v>
-      </c>
-      <c r="D35" s="6">
-        <v>1.65</v>
-      </c>
-      <c r="E35" s="8">
-        <v>1.72</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5">
-      <c r="A36" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B36" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C36" s="6">
-        <v>-6.85</v>
-      </c>
-      <c r="D36" s="6">
-        <v>-7.38</v>
-      </c>
-      <c r="E36" s="7">
-        <v>-0.53</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5">
-      <c r="A37" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B37" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C37" s="6">
-        <v>-3.08</v>
-      </c>
-      <c r="D37" s="6">
-        <v>-2.78</v>
-      </c>
-      <c r="E37" s="8">
-        <v>0.3</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5">
-      <c r="A38" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B38" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C38" s="6">
-        <v>-8.08</v>
-      </c>
-      <c r="D38" s="6">
-        <v>-8.51</v>
-      </c>
-      <c r="E38" s="7">
-        <v>-0.43</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5">
-      <c r="A39" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="B39" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C39" s="6">
-        <v>-2.03</v>
-      </c>
-      <c r="D39" s="6">
-        <v>-5.47</v>
-      </c>
-      <c r="E39" s="7">
-        <v>-3.44</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5">
-      <c r="A40" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B40" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C40" s="6">
-        <v>-9.890000000000001</v>
-      </c>
-      <c r="D40" s="6">
-        <v>-11</v>
-      </c>
-      <c r="E40" s="7">
-        <v>-1.11</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5">
-      <c r="A41" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B41" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C41" s="6">
-        <v>-47.78</v>
-      </c>
-      <c r="D41" s="6">
-        <v>-47.45</v>
-      </c>
-      <c r="E41" s="8">
-        <v>0.33</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5">
-      <c r="A42" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B42" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C42" s="6">
-        <v>-6.82</v>
-      </c>
-      <c r="D42" s="6">
-        <v>-8.300000000000001</v>
-      </c>
-      <c r="E42" s="7">
-        <v>-1.48</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5">
-      <c r="A43" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B43" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C43" s="6">
-        <v>-16.86</v>
-      </c>
-      <c r="D43" s="6">
-        <v>-16.92</v>
-      </c>
-      <c r="E43" s="7">
-        <v>-0.06</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5">
-      <c r="A44" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B44" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C44" s="6">
-        <v>-13.65</v>
-      </c>
-      <c r="D44" s="6">
-        <v>-13.08</v>
-      </c>
-      <c r="E44" s="8">
-        <v>0.57</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5">
-      <c r="A45" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B45" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C45" s="6">
-        <v>-20.83</v>
-      </c>
-      <c r="D45" s="6">
-        <v>-22.13</v>
-      </c>
-      <c r="E45" s="7">
-        <v>-1.3</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5">
-      <c r="A46" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B46" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C46" s="6">
-        <v>-31.19</v>
-      </c>
-      <c r="D46" s="6">
-        <v>-30.67</v>
-      </c>
-      <c r="E46" s="8">
-        <v>0.52</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5">
-      <c r="A47" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="B47" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C47" s="6">
-        <v>-15.53</v>
-      </c>
-      <c r="D47" s="6">
-        <v>-17.03</v>
-      </c>
-      <c r="E47" s="7">
-        <v>-1.5</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5">
-      <c r="A48" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B48" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C48" s="6">
-        <v>382.7</v>
-      </c>
-      <c r="D48" s="6">
-        <v>378</v>
-      </c>
-      <c r="E48" s="7">
-        <v>-4.7</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5">
-      <c r="A49" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B49" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C49" s="6">
-        <v>47.59</v>
-      </c>
-      <c r="D49" s="6">
-        <v>46.24</v>
-      </c>
-      <c r="E49" s="7">
-        <v>-1.35</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5">
-      <c r="A50" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B50" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C50" s="6">
-        <v>3150</v>
-      </c>
-      <c r="D50" s="6">
-        <v>3100</v>
-      </c>
-      <c r="E50" s="7">
-        <v>-50</v>
-      </c>
-    </row>
-    <row r="51" spans="1:5">
-      <c r="A51" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B51" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C51" s="6">
-        <v>955.9</v>
-      </c>
-      <c r="D51" s="6">
-        <v>955.2</v>
-      </c>
-      <c r="E51" s="7">
-        <v>-0.7</v>
-      </c>
-    </row>
-    <row r="52" spans="1:5">
-      <c r="A52" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B52" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C52" s="6">
-        <v>13.47</v>
-      </c>
-      <c r="D52" s="6">
-        <v>13.56</v>
-      </c>
-      <c r="E52" s="8">
-        <v>0.09</v>
-      </c>
-    </row>
-    <row r="53" spans="1:5">
-      <c r="A53" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B53" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C53" s="6">
-        <v>11.02</v>
-      </c>
-      <c r="D53" s="6">
-        <v>10.84</v>
-      </c>
-      <c r="E53" s="7">
-        <v>-0.18</v>
-      </c>
-    </row>
-    <row r="54" spans="1:5">
-      <c r="A54" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B54" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C54" s="6">
-        <v>3997.5</v>
-      </c>
-      <c r="D54" s="6">
-        <v>4027.7</v>
-      </c>
-      <c r="E54" s="8">
-        <v>30.2</v>
-      </c>
-    </row>
-    <row r="55" spans="1:5">
-      <c r="A55" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="B55" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C55" s="6">
-        <v>11025</v>
-      </c>
-      <c r="D55" s="6">
-        <v>10829</v>
-      </c>
-      <c r="E55" s="7">
-        <v>-196</v>
-      </c>
-    </row>
-    <row r="56" spans="1:5">
-      <c r="A56" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B56" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="C56" s="6">
-        <v>74</v>
-      </c>
-      <c r="D56" s="6">
-        <v>62</v>
-      </c>
-      <c r="E56" s="7">
-        <v>-12</v>
-      </c>
-    </row>
-    <row r="57" spans="1:5">
-      <c r="A57" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B57" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="C57" s="6">
-        <v>62</v>
-      </c>
-      <c r="D57" s="6">
-        <v>74</v>
-      </c>
-      <c r="E57" s="8">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="58" spans="1:5">
-      <c r="A58" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B58" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C58" s="6">
-        <v>41.11</v>
-      </c>
-      <c r="D58" s="6">
-        <v>38.89</v>
-      </c>
-      <c r="E58" s="7">
-        <v>-2.22</v>
-      </c>
-    </row>
-    <row r="59" spans="1:5">
-      <c r="A59" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B59" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C59" s="6">
-        <v>31.61</v>
-      </c>
-      <c r="D59" s="6">
-        <v>27.97</v>
-      </c>
-      <c r="E59" s="7">
-        <v>-3.64</v>
-      </c>
-    </row>
-    <row r="60" spans="1:5">
-      <c r="A60" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B60" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C60" s="6">
-        <v>41.66</v>
-      </c>
-      <c r="D60" s="6">
-        <v>37.36</v>
-      </c>
-      <c r="E60" s="7">
-        <v>-4.3</v>
-      </c>
-    </row>
-    <row r="61" spans="1:5">
-      <c r="A61" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B61" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C61" s="6">
-        <v>38.61</v>
-      </c>
-      <c r="D61" s="6">
-        <v>38.46</v>
-      </c>
-      <c r="E61" s="7">
-        <v>-0.15</v>
-      </c>
-    </row>
-    <row r="62" spans="1:5">
-      <c r="A62" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B62" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C62" s="6">
-        <v>39.85</v>
-      </c>
-      <c r="D62" s="6">
-        <v>41.18</v>
-      </c>
-      <c r="E62" s="8">
-        <v>1.33</v>
-      </c>
-    </row>
-    <row r="63" spans="1:5">
-      <c r="A63" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B63" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C63" s="6">
-        <v>40.82</v>
-      </c>
-      <c r="D63" s="6">
-        <v>38.67</v>
-      </c>
-      <c r="E63" s="7">
-        <v>-2.15</v>
-      </c>
-    </row>
-    <row r="64" spans="1:5">
-      <c r="A64" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B64" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C64" s="6">
-        <v>33.34</v>
-      </c>
-      <c r="D64" s="6">
-        <v>37.01</v>
-      </c>
-      <c r="E64" s="8">
-        <v>3.67</v>
-      </c>
-    </row>
-    <row r="65" spans="1:5">
-      <c r="A65" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="B65" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C65" s="6">
-        <v>44.16</v>
-      </c>
-      <c r="D65" s="6">
-        <v>38.95</v>
-      </c>
-      <c r="E65" s="7">
-        <v>-5.21</v>
-      </c>
-    </row>
-    <row r="66" spans="1:5">
-      <c r="A66" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B66" s="5" t="s">
+      <c r="B72" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="C66" s="6">
-        <v>-30.33</v>
-      </c>
-      <c r="D66" s="6">
-        <v>69.65000000000001</v>
-      </c>
-      <c r="E66" s="8">
-        <v>99.98</v>
-      </c>
-    </row>
-    <row r="67" spans="1:5">
-      <c r="A67" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B67" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C67" s="6">
-        <v>-19.88</v>
-      </c>
-      <c r="D67" s="6">
-        <v>184.13</v>
-      </c>
-      <c r="E67" s="8">
-        <v>204.01</v>
-      </c>
-    </row>
-    <row r="68" spans="1:5">
-      <c r="A68" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B68" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C68" s="6">
-        <v>-13.65</v>
-      </c>
-      <c r="D68" s="6">
-        <v>33.1</v>
-      </c>
-      <c r="E68" s="8">
-        <v>46.75</v>
-      </c>
-    </row>
-    <row r="69" spans="1:5">
-      <c r="A69" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B69" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C69" s="6">
-        <v>-1.32</v>
-      </c>
-      <c r="D69" s="6">
-        <v>50.43</v>
-      </c>
-      <c r="E69" s="8">
-        <v>51.75</v>
-      </c>
-    </row>
-    <row r="70" spans="1:5">
-      <c r="A70" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B70" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C70" s="6">
-        <v>18.57</v>
-      </c>
-      <c r="D70" s="6">
-        <v>170.27</v>
-      </c>
-      <c r="E70" s="8">
-        <v>151.7</v>
-      </c>
-    </row>
-    <row r="71" spans="1:5">
-      <c r="A71" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B71" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C71" s="6">
-        <v>31.47</v>
-      </c>
-      <c r="D71" s="6">
-        <v>146.62</v>
-      </c>
-      <c r="E71" s="8">
-        <v>115.15</v>
-      </c>
-    </row>
-    <row r="72" spans="1:5">
-      <c r="A72" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B72" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C72" s="6">
-        <v>-36.85</v>
-      </c>
-      <c r="D72" s="6">
-        <v>4.84</v>
-      </c>
-      <c r="E72" s="8">
-        <v>41.69</v>
-      </c>
-    </row>
-    <row r="73" spans="1:5">
-      <c r="A73" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="B73" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C73" s="6">
-        <v>23.7</v>
-      </c>
-      <c r="D73" s="6">
+      <c r="C72" s="5">
         <v>91.52</v>
       </c>
-      <c r="E73" s="8">
-        <v>67.81999999999999</v>
+      <c r="D72" s="5">
+        <v>-8.699999999999999</v>
+      </c>
+      <c r="E72" s="6">
+        <v>-100.22</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A6:E6"/>
+    <mergeCell ref="A5:E5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3204,60 +3127,60 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="28" customHeight="1">
-      <c r="A1" s="9" t="s">
+      <c r="A1" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="9" t="s">
+      <c r="B1" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="C1" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="D1" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="E1" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="F1" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="G1" s="8" t="s">
+        <v>62</v>
+      </c>
+      <c r="H1" s="8" t="s">
+        <v>63</v>
+      </c>
+      <c r="I1" s="8" t="s">
         <v>64</v>
       </c>
-      <c r="C1" s="9" t="s">
-        <v>65</v>
-      </c>
-      <c r="D1" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="E1" s="9" t="s">
-        <v>67</v>
-      </c>
-      <c r="F1" s="9" t="s">
-        <v>68</v>
-      </c>
-      <c r="G1" s="9" t="s">
-        <v>69</v>
-      </c>
-      <c r="H1" s="9" t="s">
-        <v>70</v>
-      </c>
-      <c r="I1" s="9" t="s">
-        <v>71</v>
-      </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="10" t="s">
+      <c r="A2" s="9" t="s">
         <v>45</v>
       </c>
-      <c r="B2" s="11">
+      <c r="B2" s="10">
         <v>52.44</v>
       </c>
-      <c r="C2" s="12">
+      <c r="C2" s="11">
         <v>8</v>
       </c>
-      <c r="D2" s="11">
-        <v>37.3</v>
-      </c>
-      <c r="E2" s="11">
+      <c r="D2" s="10">
+        <v>36.4</v>
+      </c>
+      <c r="E2" s="10">
         <v>50</v>
       </c>
-      <c r="F2" s="11">
+      <c r="F2" s="10">
         <v>-7.4</v>
       </c>
-      <c r="G2" s="11">
-        <v>-6.1</v>
-      </c>
-      <c r="H2" s="11">
+      <c r="G2" s="10">
+        <v>-7.4</v>
+      </c>
+      <c r="H2" s="10">
         <v>56.1</v>
       </c>
-      <c r="I2" s="11">
+      <c r="I2" s="10">
         <v>10</v>
       </c>
     </row>
@@ -3359,55 +3282,55 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8">
-      <c r="A1" s="13" t="s">
+      <c r="A1" s="12" t="s">
         <v>37</v>
       </c>
-      <c r="B1" s="13" t="s">
+      <c r="B1" s="12" t="s">
         <v>43</v>
       </c>
-      <c r="C1" s="13" t="s">
+      <c r="C1" s="12" t="s">
         <v>40</v>
       </c>
-      <c r="D1" s="13" t="s">
+      <c r="D1" s="12" t="s">
         <v>39</v>
       </c>
-      <c r="E1" s="13" t="s">
+      <c r="E1" s="12" t="s">
         <v>44</v>
       </c>
-      <c r="F1" s="13" t="s">
+      <c r="F1" s="12" t="s">
         <v>41</v>
       </c>
-      <c r="G1" s="13" t="s">
+      <c r="G1" s="12" t="s">
         <v>38</v>
       </c>
-      <c r="H1" s="13" t="s">
+      <c r="H1" s="12" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="2" spans="1:8">
-      <c r="A2" s="14">
-        <v>0.2706</v>
-      </c>
-      <c r="B2" s="14">
-        <v>0.169</v>
-      </c>
-      <c r="C2" s="14">
-        <v>0.1475</v>
-      </c>
-      <c r="D2" s="14">
-        <v>0.137</v>
-      </c>
-      <c r="E2" s="14">
-        <v>0.08210000000000001</v>
-      </c>
-      <c r="F2" s="14">
-        <v>0.0381</v>
-      </c>
-      <c r="G2" s="14">
-        <v>-0.2755</v>
-      </c>
-      <c r="H2" s="14">
-        <v>-0.2977</v>
+      <c r="A2" s="13">
+        <v>0.2755</v>
+      </c>
+      <c r="B2" s="13">
+        <v>0.1635</v>
+      </c>
+      <c r="C2" s="13">
+        <v>0.1471</v>
+      </c>
+      <c r="D2" s="13">
+        <v>0.1342</v>
+      </c>
+      <c r="E2" s="13">
+        <v>0.0867</v>
+      </c>
+      <c r="F2" s="13">
+        <v>0.0171</v>
+      </c>
+      <c r="G2" s="13">
+        <v>-0.2841</v>
+      </c>
+      <c r="H2" s="13">
+        <v>-0.2965</v>
       </c>
     </row>
   </sheetData>

--- a/BIRLA_GROUP_Technical_Metrics.xlsx
+++ b/BIRLA_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="280" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="274" uniqueCount="65">
   <si>
     <t>Symbol</t>
   </si>
@@ -261,14 +261,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF006100"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF9C0006"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -301,13 +301,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -758,15 +758,15 @@
     <col min="13" max="13" width="10.7109375" customWidth="1"/>
     <col min="14" max="14" width="11.7109375" customWidth="1"/>
     <col min="15" max="15" width="10.7109375" customWidth="1"/>
-    <col min="16" max="18" width="9.7109375" customWidth="1"/>
-    <col min="19" max="19" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="9.7109375" customWidth="1"/>
+    <col min="17" max="19" width="10.7109375" customWidth="1"/>
     <col min="20" max="20" width="22.7109375" customWidth="1"/>
     <col min="21" max="21" width="9.7109375" customWidth="1"/>
     <col min="22" max="22" width="10.7109375" customWidth="1"/>
     <col min="23" max="23" width="16.7109375" customWidth="1"/>
     <col min="24" max="24" width="13.7109375" customWidth="1"/>
     <col min="25" max="25" width="7.7109375" customWidth="1"/>
-    <col min="26" max="26" width="9.7109375" customWidth="1"/>
+    <col min="26" max="26" width="8.7109375" customWidth="1"/>
     <col min="27" max="27" width="13.7109375" customWidth="1"/>
     <col min="28" max="28" width="11.7109375" customWidth="1"/>
     <col min="29" max="30" width="13.7109375" customWidth="1"/>
@@ -899,58 +899,58 @@
         <v>45</v>
       </c>
       <c r="C2">
-        <v>380.6</v>
+        <v>375.05</v>
       </c>
       <c r="D2">
-        <v>0.6899999999999999</v>
+        <v>-1.46</v>
       </c>
       <c r="E2">
         <v>424.7</v>
       </c>
       <c r="F2">
-        <v>278.9</v>
+        <v>289.85</v>
       </c>
       <c r="G2">
-        <v>-10.38</v>
+        <v>-11.69</v>
       </c>
       <c r="H2">
-        <v>36.46</v>
+        <v>29.39</v>
       </c>
       <c r="I2">
-        <v>-5.43</v>
+        <v>-3.86</v>
       </c>
       <c r="J2">
-        <v>-7.03</v>
+        <v>-4.92</v>
       </c>
       <c r="K2">
-        <v>-3.14</v>
+        <v>-6.53</v>
       </c>
       <c r="L2">
-        <v>32.84</v>
+        <v>34.47</v>
       </c>
       <c r="M2">
-        <v>27.55</v>
+        <v>27.36</v>
       </c>
       <c r="N2">
         <v>74</v>
       </c>
       <c r="O2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="P2">
-        <v>384.28</v>
+        <v>381.27</v>
       </c>
       <c r="Q2">
-        <v>394.18</v>
+        <v>393.08</v>
       </c>
       <c r="R2">
-        <v>401.26</v>
+        <v>400.75</v>
       </c>
       <c r="S2">
-        <v>364.49</v>
+        <v>364.55</v>
       </c>
       <c r="T2">
-        <v>4.42</v>
+        <v>2.88</v>
       </c>
       <c r="U2" t="s">
         <v>46</v>
@@ -965,34 +965,34 @@
         <v>2</v>
       </c>
       <c r="Y2">
-        <v>40.79</v>
+        <v>38.07</v>
       </c>
       <c r="Z2">
-        <v>-4.86</v>
+        <v>-5.68</v>
       </c>
       <c r="AA2">
-        <v>-3.14</v>
+        <v>-3.65</v>
       </c>
       <c r="AB2">
-        <v>-1.73</v>
+        <v>-2.04</v>
       </c>
       <c r="AC2">
-        <v>28.61</v>
+        <v>24.11</v>
       </c>
       <c r="AD2">
-        <v>35.49</v>
+        <v>29.08</v>
       </c>
       <c r="AE2">
-        <v>9.5</v>
+        <v>9.56</v>
       </c>
       <c r="AF2">
-        <v>26.92</v>
+        <v>85</v>
       </c>
       <c r="AG2">
-        <v>413.58</v>
+        <v>414.21</v>
       </c>
       <c r="AH2">
-        <v>374.78</v>
+        <v>371.94</v>
       </c>
       <c r="AI2">
         <v>372.91</v>
@@ -1001,7 +1001,7 @@
         <v>48</v>
       </c>
       <c r="AK2">
-        <v>27.73</v>
+        <v>30.49</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1012,58 +1012,58 @@
         <v>45</v>
       </c>
       <c r="C3">
-        <v>46.32</v>
+        <v>44.53</v>
       </c>
       <c r="D3">
-        <v>0.17</v>
+        <v>-3.86</v>
       </c>
       <c r="E3">
         <v>87.98999999999999</v>
       </c>
       <c r="F3">
-        <v>46.24</v>
+        <v>44.53</v>
       </c>
       <c r="G3">
-        <v>-47.36</v>
+        <v>-49.39</v>
       </c>
       <c r="H3">
-        <v>0.17</v>
+        <v>0</v>
       </c>
       <c r="I3">
-        <v>-5.64</v>
+        <v>-7.34</v>
       </c>
       <c r="J3">
-        <v>-11.09</v>
+        <v>-12.86</v>
       </c>
       <c r="K3">
-        <v>-25.15</v>
+        <v>-28.72</v>
       </c>
       <c r="L3">
-        <v>-46.95</v>
+        <v>-47.55</v>
       </c>
       <c r="M3">
-        <v>-28.41</v>
+        <v>-28.86</v>
       </c>
       <c r="N3">
         <v>13</v>
       </c>
       <c r="O3">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="P3">
-        <v>47.47</v>
+        <v>46.76</v>
       </c>
       <c r="Q3">
-        <v>49.84</v>
+        <v>49.55</v>
       </c>
       <c r="R3">
-        <v>54.11</v>
+        <v>53.86</v>
       </c>
       <c r="S3">
-        <v>62.43</v>
+        <v>62.27</v>
       </c>
       <c r="T3">
-        <v>-25.81</v>
+        <v>-28.48</v>
       </c>
       <c r="U3" t="s">
         <v>46</v>
@@ -1078,43 +1078,43 @@
         <v>0</v>
       </c>
       <c r="Y3">
-        <v>28.49</v>
+        <v>24.23</v>
       </c>
       <c r="Z3">
-        <v>-1.97</v>
+        <v>-2.15</v>
       </c>
       <c r="AA3">
-        <v>-1.81</v>
+        <v>-1.88</v>
       </c>
       <c r="AB3">
-        <v>-0.16</v>
+        <v>-0.27</v>
       </c>
       <c r="AC3">
-        <v>11.51</v>
+        <v>1.85</v>
       </c>
       <c r="AD3">
-        <v>23.97</v>
+        <v>14.28</v>
       </c>
       <c r="AE3">
-        <v>1.51</v>
+        <v>1.58</v>
       </c>
       <c r="AF3">
-        <v>-22.58</v>
+        <v>13.7</v>
       </c>
       <c r="AG3">
-        <v>53.61</v>
+        <v>53.98</v>
       </c>
       <c r="AH3">
-        <v>46.07</v>
+        <v>45.11</v>
       </c>
       <c r="AI3">
-        <v>51.17</v>
+        <v>50.02</v>
       </c>
       <c r="AJ3" t="s">
         <v>49</v>
       </c>
       <c r="AK3">
-        <v>47.41</v>
+        <v>51.58</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1125,10 +1125,10 @@
         <v>45</v>
       </c>
       <c r="C4">
-        <v>3061.9</v>
+        <v>2962</v>
       </c>
       <c r="D4">
-        <v>-1.23</v>
+        <v>-3.26</v>
       </c>
       <c r="E4">
         <v>3380.5</v>
@@ -1137,46 +1137,46 @@
         <v>2531.1</v>
       </c>
       <c r="G4">
-        <v>-9.42</v>
+        <v>-12.38</v>
       </c>
       <c r="H4">
-        <v>20.97</v>
+        <v>17.02</v>
       </c>
       <c r="I4">
-        <v>-3.97</v>
+        <v>-6.46</v>
       </c>
       <c r="J4">
-        <v>-9.17</v>
+        <v>-10.38</v>
       </c>
       <c r="K4">
-        <v>-3.39</v>
+        <v>-6.88</v>
       </c>
       <c r="L4">
-        <v>10.2</v>
+        <v>7.83</v>
       </c>
       <c r="M4">
-        <v>13.42</v>
+        <v>12.57</v>
       </c>
       <c r="N4">
         <v>50</v>
       </c>
       <c r="O4">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="P4">
-        <v>3133.88</v>
+        <v>3092.98</v>
       </c>
       <c r="Q4">
-        <v>3216.47</v>
+        <v>3199.82</v>
       </c>
       <c r="R4">
-        <v>3228.7</v>
+        <v>3224.62</v>
       </c>
       <c r="S4">
-        <v>2976.21</v>
+        <v>2976.83</v>
       </c>
       <c r="T4">
-        <v>2.88</v>
+        <v>-0.5</v>
       </c>
       <c r="U4" t="s">
         <v>46</v>
@@ -1188,46 +1188,46 @@
         <v>46</v>
       </c>
       <c r="X4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y4">
-        <v>34.45</v>
+        <v>28.23</v>
       </c>
       <c r="Z4">
-        <v>-39.5</v>
+        <v>-52.55</v>
       </c>
       <c r="AA4">
-        <v>-22.89</v>
+        <v>-28.82</v>
       </c>
       <c r="AB4">
-        <v>-16.62</v>
+        <v>-23.73</v>
       </c>
       <c r="AC4">
-        <v>9.49</v>
+        <v>1.01</v>
       </c>
       <c r="AD4">
-        <v>22.68</v>
+        <v>11.8</v>
       </c>
       <c r="AE4">
-        <v>59.45</v>
+        <v>63.6</v>
       </c>
       <c r="AF4">
-        <v>-49.56</v>
+        <v>60.86</v>
       </c>
       <c r="AG4">
-        <v>3378.28</v>
+        <v>3393.09</v>
       </c>
       <c r="AH4">
-        <v>3054.66</v>
+        <v>3006.56</v>
       </c>
       <c r="AI4">
-        <v>3257.7</v>
+        <v>3185.49</v>
       </c>
       <c r="AJ4" t="s">
         <v>49</v>
       </c>
       <c r="AK4">
-        <v>42.65</v>
+        <v>47.57</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1238,37 +1238,37 @@
         <v>45</v>
       </c>
       <c r="C5">
-        <v>941.8</v>
+        <v>941.85</v>
       </c>
       <c r="D5">
-        <v>-1.4</v>
+        <v>0.01</v>
       </c>
       <c r="E5">
         <v>1149.7</v>
       </c>
       <c r="F5">
-        <v>743.85</v>
+        <v>753.8</v>
       </c>
       <c r="G5">
         <v>-18.08</v>
       </c>
       <c r="H5">
-        <v>26.61</v>
+        <v>24.95</v>
       </c>
       <c r="I5">
-        <v>-6.18</v>
+        <v>-4.09</v>
       </c>
       <c r="J5">
-        <v>-7.25</v>
+        <v>-7.15</v>
       </c>
       <c r="K5">
-        <v>-0.78</v>
+        <v>-1.19</v>
       </c>
       <c r="L5">
-        <v>26.31</v>
+        <v>26.62</v>
       </c>
       <c r="M5">
-        <v>14.71</v>
+        <v>14.88</v>
       </c>
       <c r="N5">
         <v>62</v>
@@ -1277,19 +1277,19 @@
         <v>74</v>
       </c>
       <c r="P5">
-        <v>962.38</v>
+        <v>954.35</v>
       </c>
       <c r="Q5">
-        <v>986.8200000000001</v>
+        <v>983.4299999999999</v>
       </c>
       <c r="R5">
-        <v>1004.42</v>
+        <v>1004.25</v>
       </c>
       <c r="S5">
-        <v>980.71</v>
+        <v>981.16</v>
       </c>
       <c r="T5">
-        <v>-3.97</v>
+        <v>-4.01</v>
       </c>
       <c r="U5" t="s">
         <v>46</v>
@@ -1304,43 +1304,43 @@
         <v>1</v>
       </c>
       <c r="Y5">
-        <v>35.55</v>
+        <v>35.57</v>
       </c>
       <c r="Z5">
-        <v>-15.36</v>
+        <v>-16.74</v>
       </c>
       <c r="AA5">
-        <v>-11.12</v>
+        <v>-12.25</v>
       </c>
       <c r="AB5">
-        <v>-4.23</v>
+        <v>-4.49</v>
       </c>
       <c r="AC5">
-        <v>18.41</v>
+        <v>13.19</v>
       </c>
       <c r="AD5">
-        <v>31.56</v>
+        <v>21.35</v>
       </c>
       <c r="AE5">
-        <v>21.73</v>
+        <v>21.83</v>
       </c>
       <c r="AF5">
-        <v>24.58</v>
+        <v>68.70999999999999</v>
       </c>
       <c r="AG5">
-        <v>1033.89</v>
+        <v>1033.25</v>
       </c>
       <c r="AH5">
-        <v>939.75</v>
+        <v>933.61</v>
       </c>
       <c r="AI5">
-        <v>1014.15</v>
+        <v>1000.57</v>
       </c>
       <c r="AJ5" t="s">
         <v>49</v>
       </c>
       <c r="AK5">
-        <v>25.63</v>
+        <v>29.78</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1351,58 +1351,58 @@
         <v>45</v>
       </c>
       <c r="C6">
-        <v>12.95</v>
+        <v>12.64</v>
       </c>
       <c r="D6">
-        <v>-4.5</v>
+        <v>-2.39</v>
       </c>
       <c r="E6">
         <v>15.6</v>
       </c>
       <c r="F6">
-        <v>8.02</v>
+        <v>8.130000000000001</v>
       </c>
       <c r="G6">
-        <v>-16.99</v>
+        <v>-18.97</v>
       </c>
       <c r="H6">
-        <v>61.47</v>
+        <v>55.47</v>
       </c>
       <c r="I6">
-        <v>-10.81</v>
+        <v>-10.48</v>
       </c>
       <c r="J6">
-        <v>-9.630000000000001</v>
+        <v>-10.1</v>
       </c>
       <c r="K6">
-        <v>-10.57</v>
+        <v>-11.3</v>
       </c>
       <c r="L6">
-        <v>49.19</v>
+        <v>57.61</v>
       </c>
       <c r="M6">
-        <v>1.71</v>
+        <v>2.09</v>
       </c>
       <c r="N6">
         <v>87</v>
       </c>
       <c r="O6">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="P6">
-        <v>13.67</v>
+        <v>13.38</v>
       </c>
       <c r="Q6">
-        <v>14.41</v>
+        <v>14.32</v>
       </c>
       <c r="R6">
-        <v>13.92</v>
+        <v>13.91</v>
       </c>
       <c r="S6">
         <v>12.24</v>
       </c>
       <c r="T6">
-        <v>5.82</v>
+        <v>3.24</v>
       </c>
       <c r="U6" t="s">
         <v>47</v>
@@ -1417,43 +1417,43 @@
         <v>3</v>
       </c>
       <c r="Y6">
-        <v>35.45</v>
+        <v>32.95</v>
       </c>
       <c r="Z6">
-        <v>-0.19</v>
+        <v>-0.28</v>
       </c>
       <c r="AA6">
-        <v>-0.01</v>
+        <v>-0.06</v>
       </c>
       <c r="AB6">
-        <v>-0.19</v>
+        <v>-0.22</v>
       </c>
       <c r="AC6">
         <v>1.69</v>
       </c>
       <c r="AD6">
-        <v>8.699999999999999</v>
+        <v>4.49</v>
       </c>
       <c r="AE6">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="AF6">
-        <v>38.55</v>
+        <v>29.55</v>
       </c>
       <c r="AG6">
-        <v>15.8</v>
+        <v>15.91</v>
       </c>
       <c r="AH6">
-        <v>13.03</v>
+        <v>12.73</v>
       </c>
       <c r="AI6">
-        <v>14.75</v>
+        <v>14.37</v>
       </c>
       <c r="AJ6" t="s">
         <v>49</v>
       </c>
       <c r="AK6">
-        <v>33.05</v>
+        <v>37.74</v>
       </c>
     </row>
     <row r="7" spans="1:37">
@@ -1464,10 +1464,10 @@
         <v>45</v>
       </c>
       <c r="C7">
-        <v>10.92</v>
+        <v>10.73</v>
       </c>
       <c r="D7">
-        <v>0.74</v>
+        <v>-1.74</v>
       </c>
       <c r="E7">
         <v>13.92</v>
@@ -1476,25 +1476,25 @@
         <v>4.69</v>
       </c>
       <c r="G7">
-        <v>-21.55</v>
+        <v>-22.92</v>
       </c>
       <c r="H7">
-        <v>132.84</v>
+        <v>128.78</v>
       </c>
       <c r="I7">
-        <v>-5.62</v>
+        <v>-5.79</v>
       </c>
       <c r="J7">
-        <v>-1.62</v>
+        <v>-3.33</v>
       </c>
       <c r="K7">
-        <v>-0.27</v>
+        <v>-2.45</v>
       </c>
       <c r="L7">
-        <v>82.91</v>
+        <v>86.28</v>
       </c>
       <c r="M7">
-        <v>-29.65</v>
+        <v>-29.84</v>
       </c>
       <c r="N7">
         <v>99</v>
@@ -1503,19 +1503,19 @@
         <v>90</v>
       </c>
       <c r="P7">
-        <v>11.15</v>
+        <v>11.02</v>
       </c>
       <c r="Q7">
-        <v>11.53</v>
+        <v>11.5</v>
       </c>
       <c r="R7">
-        <v>11.76</v>
+        <v>11.73</v>
       </c>
       <c r="S7">
-        <v>10.8</v>
+        <v>10.81</v>
       </c>
       <c r="T7">
-        <v>1.1</v>
+        <v>-0.78</v>
       </c>
       <c r="U7" t="s">
         <v>46</v>
@@ -1527,46 +1527,46 @@
         <v>46</v>
       </c>
       <c r="X7">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y7">
-        <v>40.18</v>
+        <v>37.8</v>
       </c>
       <c r="Z7">
-        <v>-0.14</v>
+        <v>-0.18</v>
       </c>
       <c r="AA7">
-        <v>-0.04</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="AB7">
-        <v>-0.1</v>
+        <v>-0.11</v>
       </c>
       <c r="AC7">
         <v>1.78</v>
       </c>
       <c r="AD7">
-        <v>9.16</v>
+        <v>3.95</v>
       </c>
       <c r="AE7">
         <v>0.49</v>
       </c>
       <c r="AF7">
-        <v>24.38</v>
+        <v>30.84</v>
       </c>
       <c r="AG7">
-        <v>12.56</v>
+        <v>12.59</v>
       </c>
       <c r="AH7">
-        <v>10.5</v>
+        <v>10.42</v>
       </c>
       <c r="AI7">
-        <v>12.29</v>
+        <v>12.13</v>
       </c>
       <c r="AJ7" t="s">
         <v>49</v>
       </c>
       <c r="AK7">
-        <v>31.82</v>
+        <v>34.13</v>
       </c>
     </row>
     <row r="8" spans="1:37">
@@ -1577,58 +1577,58 @@
         <v>45</v>
       </c>
       <c r="C8">
-        <v>3956.5</v>
+        <v>3892.3</v>
       </c>
       <c r="D8">
-        <v>-1.77</v>
+        <v>-1.62</v>
       </c>
       <c r="E8">
         <v>5809.5</v>
       </c>
       <c r="F8">
-        <v>3956.5</v>
+        <v>3892.3</v>
       </c>
       <c r="G8">
-        <v>-31.9</v>
+        <v>-33</v>
       </c>
       <c r="H8">
         <v>0</v>
       </c>
       <c r="I8">
-        <v>-2.11</v>
+        <v>-2.86</v>
       </c>
       <c r="J8">
-        <v>-9.119999999999999</v>
+        <v>-10.59</v>
       </c>
       <c r="K8">
-        <v>-10.83</v>
+        <v>-11.85</v>
       </c>
       <c r="L8">
-        <v>-26.25</v>
+        <v>-26.15</v>
       </c>
       <c r="M8">
-        <v>16.35</v>
+        <v>15.87</v>
       </c>
       <c r="N8">
         <v>26</v>
       </c>
       <c r="O8">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="P8">
-        <v>4000.76</v>
+        <v>3977.8</v>
       </c>
       <c r="Q8">
-        <v>4123.26</v>
+        <v>4101.62</v>
       </c>
       <c r="R8">
-        <v>4267.88</v>
+        <v>4258.68</v>
       </c>
       <c r="S8">
-        <v>4536.48</v>
+        <v>4529.8</v>
       </c>
       <c r="T8">
-        <v>-12.78</v>
+        <v>-14.07</v>
       </c>
       <c r="U8" t="s">
         <v>46</v>
@@ -1643,43 +1643,43 @@
         <v>0</v>
       </c>
       <c r="Y8">
-        <v>32.47</v>
+        <v>29.02</v>
       </c>
       <c r="Z8">
-        <v>-91.25</v>
+        <v>-97.02</v>
       </c>
       <c r="AA8">
-        <v>-83.97</v>
+        <v>-86.58</v>
       </c>
       <c r="AB8">
-        <v>-7.29</v>
+        <v>-10.45</v>
       </c>
       <c r="AC8">
-        <v>27.72</v>
+        <v>19.71</v>
       </c>
       <c r="AD8">
-        <v>29.91</v>
+        <v>27.96</v>
       </c>
       <c r="AE8">
-        <v>109.39</v>
+        <v>109.36</v>
       </c>
       <c r="AF8">
-        <v>141.95</v>
+        <v>-7.38</v>
       </c>
       <c r="AG8">
-        <v>4383.03</v>
+        <v>4362.72</v>
       </c>
       <c r="AH8">
-        <v>3863.48</v>
+        <v>3840.52</v>
       </c>
       <c r="AI8">
-        <v>4288.14</v>
+        <v>4247.59</v>
       </c>
       <c r="AJ8" t="s">
         <v>49</v>
       </c>
       <c r="AK8">
-        <v>58.53</v>
+        <v>57.53</v>
       </c>
     </row>
     <row r="9" spans="1:37">
@@ -1690,10 +1690,10 @@
         <v>45</v>
       </c>
       <c r="C9">
-        <v>10956</v>
+        <v>10710</v>
       </c>
       <c r="D9">
-        <v>1.17</v>
+        <v>-2.25</v>
       </c>
       <c r="E9">
         <v>13052</v>
@@ -1702,46 +1702,46 @@
         <v>10362</v>
       </c>
       <c r="G9">
-        <v>-16.06</v>
+        <v>-17.94</v>
       </c>
       <c r="H9">
-        <v>5.73</v>
+        <v>3.36</v>
       </c>
       <c r="I9">
-        <v>-1.78</v>
+        <v>-3.13</v>
       </c>
       <c r="J9">
-        <v>-4.31</v>
+        <v>-6.05</v>
       </c>
       <c r="K9">
-        <v>-5.03</v>
+        <v>-8.640000000000001</v>
       </c>
       <c r="L9">
-        <v>-9.76</v>
+        <v>-11.27</v>
       </c>
       <c r="M9">
-        <v>8.67</v>
+        <v>7.92</v>
       </c>
       <c r="N9">
         <v>38</v>
       </c>
       <c r="O9">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="P9">
-        <v>11004.2</v>
+        <v>10935</v>
       </c>
       <c r="Q9">
-        <v>11029.5</v>
+        <v>10995.35</v>
       </c>
       <c r="R9">
-        <v>11479.2</v>
+        <v>11455.54</v>
       </c>
       <c r="S9">
-        <v>11713.21</v>
+        <v>11708.14</v>
       </c>
       <c r="T9">
-        <v>-6.46</v>
+        <v>-8.529999999999999</v>
       </c>
       <c r="U9" t="s">
         <v>46</v>
@@ -1756,43 +1756,43 @@
         <v>0</v>
       </c>
       <c r="Y9">
-        <v>43.59</v>
+        <v>37.63</v>
       </c>
       <c r="Z9">
-        <v>-132.42</v>
+        <v>-146.8</v>
       </c>
       <c r="AA9">
-        <v>-153.93</v>
+        <v>-152.5</v>
       </c>
       <c r="AB9">
-        <v>21.5</v>
+        <v>5.7</v>
       </c>
       <c r="AC9">
-        <v>71.77</v>
+        <v>61.33</v>
       </c>
       <c r="AD9">
-        <v>79.84999999999999</v>
+        <v>70.7</v>
       </c>
       <c r="AE9">
-        <v>190.03</v>
+        <v>201.02</v>
       </c>
       <c r="AF9">
-        <v>-8.699999999999999</v>
+        <v>106.59</v>
       </c>
       <c r="AG9">
-        <v>11427.12</v>
+        <v>11378.58</v>
       </c>
       <c r="AH9">
-        <v>10631.88</v>
+        <v>10612.12</v>
       </c>
       <c r="AI9">
-        <v>11371.08</v>
+        <v>11348.57</v>
       </c>
       <c r="AJ9" t="s">
         <v>49</v>
       </c>
       <c r="AK9">
-        <v>25.64</v>
+        <v>29.54</v>
       </c>
     </row>
   </sheetData>
@@ -1933,7 +1933,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F72"/>
+  <dimension ref="A1:F69"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -1990,13 +1990,13 @@
         <v>9</v>
       </c>
       <c r="C7" s="5">
-        <v>-6.79</v>
+        <v>-7.03</v>
       </c>
       <c r="D7" s="5">
-        <v>-7.03</v>
+        <v>-4.92</v>
       </c>
       <c r="E7" s="6">
-        <v>-0.24</v>
+        <v>2.11</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -2007,13 +2007,13 @@
         <v>9</v>
       </c>
       <c r="C8" s="5">
-        <v>-11.91</v>
+        <v>-11.09</v>
       </c>
       <c r="D8" s="5">
-        <v>-11.09</v>
+        <v>-12.86</v>
       </c>
       <c r="E8" s="7">
-        <v>0.82</v>
+        <v>-1.77</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -2024,13 +2024,13 @@
         <v>9</v>
       </c>
       <c r="C9" s="5">
-        <v>-5.78</v>
+        <v>-9.17</v>
       </c>
       <c r="D9" s="5">
-        <v>-9.17</v>
-      </c>
-      <c r="E9" s="6">
-        <v>-3.39</v>
+        <v>-10.38</v>
+      </c>
+      <c r="E9" s="7">
+        <v>-1.21</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -2041,13 +2041,13 @@
         <v>9</v>
       </c>
       <c r="C10" s="5">
-        <v>-7.92</v>
+        <v>-7.25</v>
       </c>
       <c r="D10" s="5">
-        <v>-7.25</v>
-      </c>
-      <c r="E10" s="7">
-        <v>0.67</v>
+        <v>-7.15</v>
+      </c>
+      <c r="E10" s="6">
+        <v>0.1</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -2058,13 +2058,13 @@
         <v>9</v>
       </c>
       <c r="C11" s="5">
-        <v>-7.63</v>
+        <v>-9.630000000000001</v>
       </c>
       <c r="D11" s="5">
-        <v>-9.630000000000001</v>
-      </c>
-      <c r="E11" s="6">
-        <v>-2</v>
+        <v>-10.1</v>
+      </c>
+      <c r="E11" s="7">
+        <v>-0.47</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -2075,13 +2075,13 @@
         <v>9</v>
       </c>
       <c r="C12" s="5">
-        <v>-4.07</v>
+        <v>-1.62</v>
       </c>
       <c r="D12" s="5">
-        <v>-1.62</v>
+        <v>-3.33</v>
       </c>
       <c r="E12" s="7">
-        <v>2.45</v>
+        <v>-1.71</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -2092,13 +2092,13 @@
         <v>9</v>
       </c>
       <c r="C13" s="5">
-        <v>-8.210000000000001</v>
+        <v>-9.119999999999999</v>
       </c>
       <c r="D13" s="5">
-        <v>-9.119999999999999</v>
-      </c>
-      <c r="E13" s="6">
-        <v>-0.91</v>
+        <v>-10.59</v>
+      </c>
+      <c r="E13" s="7">
+        <v>-1.47</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -2109,13 +2109,13 @@
         <v>9</v>
       </c>
       <c r="C14" s="5">
-        <v>-6.56</v>
+        <v>-4.31</v>
       </c>
       <c r="D14" s="5">
-        <v>-4.31</v>
+        <v>-6.05</v>
       </c>
       <c r="E14" s="7">
-        <v>2.25</v>
+        <v>-1.74</v>
       </c>
     </row>
     <row r="15" spans="1:6">
@@ -2126,13 +2126,13 @@
         <v>8</v>
       </c>
       <c r="C15" s="5">
-        <v>-4.79</v>
+        <v>-5.43</v>
       </c>
       <c r="D15" s="5">
-        <v>-5.43</v>
+        <v>-3.86</v>
       </c>
       <c r="E15" s="6">
-        <v>-0.64</v>
+        <v>1.57</v>
       </c>
     </row>
     <row r="16" spans="1:6">
@@ -2143,13 +2143,13 @@
         <v>8</v>
       </c>
       <c r="C16" s="5">
-        <v>-6.05</v>
+        <v>-5.64</v>
       </c>
       <c r="D16" s="5">
-        <v>-5.64</v>
+        <v>-7.34</v>
       </c>
       <c r="E16" s="7">
-        <v>0.41</v>
+        <v>-1.7</v>
       </c>
     </row>
     <row r="17" spans="1:5">
@@ -2160,13 +2160,13 @@
         <v>8</v>
       </c>
       <c r="C17" s="5">
-        <v>-0.9</v>
+        <v>-3.97</v>
       </c>
       <c r="D17" s="5">
-        <v>-3.97</v>
-      </c>
-      <c r="E17" s="6">
-        <v>-3.07</v>
+        <v>-6.46</v>
+      </c>
+      <c r="E17" s="7">
+        <v>-2.49</v>
       </c>
     </row>
     <row r="18" spans="1:5">
@@ -2177,13 +2177,13 @@
         <v>8</v>
       </c>
       <c r="C18" s="5">
-        <v>-1.83</v>
+        <v>-6.18</v>
       </c>
       <c r="D18" s="5">
-        <v>-6.18</v>
+        <v>-4.09</v>
       </c>
       <c r="E18" s="6">
-        <v>-4.35</v>
+        <v>2.09</v>
       </c>
     </row>
     <row r="19" spans="1:5">
@@ -2194,13 +2194,13 @@
         <v>8</v>
       </c>
       <c r="C19" s="5">
-        <v>-4.98</v>
+        <v>-10.81</v>
       </c>
       <c r="D19" s="5">
-        <v>-10.81</v>
+        <v>-10.48</v>
       </c>
       <c r="E19" s="6">
-        <v>-5.83</v>
+        <v>0.33</v>
       </c>
     </row>
     <row r="20" spans="1:5">
@@ -2211,13 +2211,13 @@
         <v>8</v>
       </c>
       <c r="C20" s="5">
-        <v>-4.49</v>
+        <v>-5.62</v>
       </c>
       <c r="D20" s="5">
-        <v>-5.62</v>
-      </c>
-      <c r="E20" s="6">
-        <v>-1.13</v>
+        <v>-5.79</v>
+      </c>
+      <c r="E20" s="7">
+        <v>-0.17</v>
       </c>
     </row>
     <row r="21" spans="1:5">
@@ -2228,13 +2228,13 @@
         <v>8</v>
       </c>
       <c r="C21" s="5">
-        <v>0.48</v>
+        <v>-2.11</v>
       </c>
       <c r="D21" s="5">
-        <v>-2.11</v>
-      </c>
-      <c r="E21" s="6">
-        <v>-2.59</v>
+        <v>-2.86</v>
+      </c>
+      <c r="E21" s="7">
+        <v>-0.75</v>
       </c>
     </row>
     <row r="22" spans="1:5">
@@ -2245,13 +2245,13 @@
         <v>8</v>
       </c>
       <c r="C22" s="5">
-        <v>-1.55</v>
+        <v>-1.78</v>
       </c>
       <c r="D22" s="5">
-        <v>-1.78</v>
-      </c>
-      <c r="E22" s="6">
-        <v>-0.23</v>
+        <v>-3.13</v>
+      </c>
+      <c r="E22" s="7">
+        <v>-1.35</v>
       </c>
     </row>
     <row r="23" spans="1:5">
@@ -2262,13 +2262,13 @@
         <v>11</v>
       </c>
       <c r="C23" s="5">
-        <v>29.47</v>
+        <v>32.84</v>
       </c>
       <c r="D23" s="5">
-        <v>32.84</v>
-      </c>
-      <c r="E23" s="7">
-        <v>3.37</v>
+        <v>34.47</v>
+      </c>
+      <c r="E23" s="6">
+        <v>1.63</v>
       </c>
     </row>
     <row r="24" spans="1:5">
@@ -2279,13 +2279,13 @@
         <v>11</v>
       </c>
       <c r="C24" s="5">
-        <v>-49.26</v>
+        <v>-46.95</v>
       </c>
       <c r="D24" s="5">
-        <v>-46.95</v>
+        <v>-47.55</v>
       </c>
       <c r="E24" s="7">
-        <v>2.31</v>
+        <v>-0.6</v>
       </c>
     </row>
     <row r="25" spans="1:5">
@@ -2296,13 +2296,13 @@
         <v>11</v>
       </c>
       <c r="C25" s="5">
-        <v>10.42</v>
+        <v>10.2</v>
       </c>
       <c r="D25" s="5">
-        <v>10.2</v>
-      </c>
-      <c r="E25" s="6">
-        <v>-0.22</v>
+        <v>7.83</v>
+      </c>
+      <c r="E25" s="7">
+        <v>-2.37</v>
       </c>
     </row>
     <row r="26" spans="1:5">
@@ -2313,13 +2313,13 @@
         <v>11</v>
       </c>
       <c r="C26" s="5">
-        <v>28.9</v>
+        <v>26.31</v>
       </c>
       <c r="D26" s="5">
-        <v>26.31</v>
+        <v>26.62</v>
       </c>
       <c r="E26" s="6">
-        <v>-2.59</v>
+        <v>0.31</v>
       </c>
     </row>
     <row r="27" spans="1:5">
@@ -2330,13 +2330,13 @@
         <v>11</v>
       </c>
       <c r="C27" s="5">
-        <v>57.86</v>
+        <v>49.19</v>
       </c>
       <c r="D27" s="5">
-        <v>49.19</v>
+        <v>57.61</v>
       </c>
       <c r="E27" s="6">
-        <v>-8.67</v>
+        <v>8.42</v>
       </c>
     </row>
     <row r="28" spans="1:5">
@@ -2347,13 +2347,13 @@
         <v>11</v>
       </c>
       <c r="C28" s="5">
-        <v>80.67</v>
+        <v>82.91</v>
       </c>
       <c r="D28" s="5">
-        <v>82.91</v>
-      </c>
-      <c r="E28" s="7">
-        <v>2.24</v>
+        <v>86.28</v>
+      </c>
+      <c r="E28" s="6">
+        <v>3.37</v>
       </c>
     </row>
     <row r="29" spans="1:5">
@@ -2364,13 +2364,13 @@
         <v>11</v>
       </c>
       <c r="C29" s="5">
-        <v>-25.89</v>
+        <v>-26.25</v>
       </c>
       <c r="D29" s="5">
-        <v>-26.25</v>
+        <v>-26.15</v>
       </c>
       <c r="E29" s="6">
-        <v>-0.36</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="30" spans="1:5">
@@ -2381,13 +2381,13 @@
         <v>11</v>
       </c>
       <c r="C30" s="5">
-        <v>-11.34</v>
+        <v>-9.76</v>
       </c>
       <c r="D30" s="5">
-        <v>-9.76</v>
+        <v>-11.27</v>
       </c>
       <c r="E30" s="7">
-        <v>1.58</v>
+        <v>-1.51</v>
       </c>
     </row>
     <row r="31" spans="1:5">
@@ -2398,13 +2398,13 @@
         <v>10</v>
       </c>
       <c r="C31" s="5">
-        <v>-3.85</v>
+        <v>-3.14</v>
       </c>
       <c r="D31" s="5">
-        <v>-3.14</v>
+        <v>-6.53</v>
       </c>
       <c r="E31" s="7">
-        <v>0.71</v>
+        <v>-3.39</v>
       </c>
     </row>
     <row r="32" spans="1:5">
@@ -2415,13 +2415,13 @@
         <v>10</v>
       </c>
       <c r="C32" s="5">
-        <v>-21.19</v>
+        <v>-25.15</v>
       </c>
       <c r="D32" s="5">
-        <v>-25.15</v>
-      </c>
-      <c r="E32" s="6">
-        <v>-3.96</v>
+        <v>-28.72</v>
+      </c>
+      <c r="E32" s="7">
+        <v>-3.57</v>
       </c>
     </row>
     <row r="33" spans="1:5">
@@ -2432,13 +2432,13 @@
         <v>10</v>
       </c>
       <c r="C33" s="5">
-        <v>-1.29</v>
+        <v>-3.39</v>
       </c>
       <c r="D33" s="5">
-        <v>-3.39</v>
-      </c>
-      <c r="E33" s="6">
-        <v>-2.1</v>
+        <v>-6.88</v>
+      </c>
+      <c r="E33" s="7">
+        <v>-3.49</v>
       </c>
     </row>
     <row r="34" spans="1:5">
@@ -2449,13 +2449,13 @@
         <v>10</v>
       </c>
       <c r="C34" s="5">
-        <v>1.65</v>
+        <v>-0.78</v>
       </c>
       <c r="D34" s="5">
-        <v>-0.78</v>
-      </c>
-      <c r="E34" s="6">
-        <v>-2.43</v>
+        <v>-1.19</v>
+      </c>
+      <c r="E34" s="7">
+        <v>-0.41</v>
       </c>
     </row>
     <row r="35" spans="1:5">
@@ -2466,13 +2466,13 @@
         <v>10</v>
       </c>
       <c r="C35" s="5">
-        <v>-7.38</v>
+        <v>-10.57</v>
       </c>
       <c r="D35" s="5">
-        <v>-10.57</v>
-      </c>
-      <c r="E35" s="6">
-        <v>-3.19</v>
+        <v>-11.3</v>
+      </c>
+      <c r="E35" s="7">
+        <v>-0.73</v>
       </c>
     </row>
     <row r="36" spans="1:5">
@@ -2483,13 +2483,13 @@
         <v>10</v>
       </c>
       <c r="C36" s="5">
-        <v>-2.78</v>
+        <v>-0.27</v>
       </c>
       <c r="D36" s="5">
-        <v>-0.27</v>
+        <v>-2.45</v>
       </c>
       <c r="E36" s="7">
-        <v>2.51</v>
+        <v>-2.18</v>
       </c>
     </row>
     <row r="37" spans="1:5">
@@ -2500,13 +2500,13 @@
         <v>10</v>
       </c>
       <c r="C37" s="5">
-        <v>-8.51</v>
+        <v>-10.83</v>
       </c>
       <c r="D37" s="5">
-        <v>-10.83</v>
-      </c>
-      <c r="E37" s="6">
-        <v>-2.32</v>
+        <v>-11.85</v>
+      </c>
+      <c r="E37" s="7">
+        <v>-1.02</v>
       </c>
     </row>
     <row r="38" spans="1:5">
@@ -2517,13 +2517,13 @@
         <v>10</v>
       </c>
       <c r="C38" s="5">
-        <v>-5.47</v>
+        <v>-5.03</v>
       </c>
       <c r="D38" s="5">
-        <v>-5.03</v>
+        <v>-8.640000000000001</v>
       </c>
       <c r="E38" s="7">
-        <v>0.44</v>
+        <v>-3.61</v>
       </c>
     </row>
     <row r="39" spans="1:5">
@@ -2534,13 +2534,13 @@
         <v>6</v>
       </c>
       <c r="C39" s="5">
-        <v>-11</v>
+        <v>-10.38</v>
       </c>
       <c r="D39" s="5">
-        <v>-10.38</v>
+        <v>-11.69</v>
       </c>
       <c r="E39" s="7">
-        <v>0.62</v>
+        <v>-1.31</v>
       </c>
     </row>
     <row r="40" spans="1:5">
@@ -2551,13 +2551,13 @@
         <v>6</v>
       </c>
       <c r="C40" s="5">
-        <v>-47.45</v>
+        <v>-47.36</v>
       </c>
       <c r="D40" s="5">
-        <v>-47.36</v>
+        <v>-49.39</v>
       </c>
       <c r="E40" s="7">
-        <v>0.09</v>
+        <v>-2.03</v>
       </c>
     </row>
     <row r="41" spans="1:5">
@@ -2568,540 +2568,489 @@
         <v>6</v>
       </c>
       <c r="C41" s="5">
-        <v>-8.300000000000001</v>
+        <v>-9.42</v>
       </c>
       <c r="D41" s="5">
-        <v>-9.42</v>
-      </c>
-      <c r="E41" s="6">
-        <v>-1.12</v>
+        <v>-12.38</v>
+      </c>
+      <c r="E41" s="7">
+        <v>-2.96</v>
       </c>
     </row>
     <row r="42" spans="1:5">
       <c r="A42" s="3" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B42" s="3" t="s">
         <v>6</v>
       </c>
       <c r="C42" s="5">
-        <v>-16.92</v>
+        <v>-16.99</v>
       </c>
       <c r="D42" s="5">
-        <v>-18.08</v>
-      </c>
-      <c r="E42" s="6">
-        <v>-1.16</v>
+        <v>-18.97</v>
+      </c>
+      <c r="E42" s="7">
+        <v>-1.98</v>
       </c>
     </row>
     <row r="43" spans="1:5">
       <c r="A43" s="3" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B43" s="3" t="s">
         <v>6</v>
       </c>
       <c r="C43" s="5">
-        <v>-13.08</v>
+        <v>-21.55</v>
       </c>
       <c r="D43" s="5">
-        <v>-16.99</v>
-      </c>
-      <c r="E43" s="6">
-        <v>-3.91</v>
+        <v>-22.92</v>
+      </c>
+      <c r="E43" s="7">
+        <v>-1.37</v>
       </c>
     </row>
     <row r="44" spans="1:5">
       <c r="A44" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B44" s="3" t="s">
         <v>6</v>
       </c>
       <c r="C44" s="5">
-        <v>-22.13</v>
+        <v>-31.9</v>
       </c>
       <c r="D44" s="5">
-        <v>-21.55</v>
+        <v>-33</v>
       </c>
       <c r="E44" s="7">
-        <v>0.58</v>
+        <v>-1.1</v>
       </c>
     </row>
     <row r="45" spans="1:5">
       <c r="A45" s="3" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B45" s="3" t="s">
         <v>6</v>
       </c>
       <c r="C45" s="5">
-        <v>-30.67</v>
+        <v>-16.06</v>
       </c>
       <c r="D45" s="5">
-        <v>-31.9</v>
-      </c>
-      <c r="E45" s="6">
-        <v>-1.23</v>
+        <v>-17.94</v>
+      </c>
+      <c r="E45" s="7">
+        <v>-1.88</v>
       </c>
     </row>
     <row r="46" spans="1:5">
       <c r="A46" s="3" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="C46" s="5">
-        <v>-17.03</v>
+        <v>380.6</v>
       </c>
       <c r="D46" s="5">
-        <v>-16.06</v>
+        <v>375.05</v>
       </c>
       <c r="E46" s="7">
-        <v>0.97</v>
+        <v>-5.55</v>
       </c>
     </row>
     <row r="47" spans="1:5">
       <c r="A47" s="3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B47" s="3" t="s">
         <v>2</v>
       </c>
       <c r="C47" s="5">
-        <v>378</v>
+        <v>46.32</v>
       </c>
       <c r="D47" s="5">
-        <v>380.6</v>
+        <v>44.53</v>
       </c>
       <c r="E47" s="7">
-        <v>2.6</v>
+        <v>-1.79</v>
       </c>
     </row>
     <row r="48" spans="1:5">
       <c r="A48" s="3" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B48" s="3" t="s">
         <v>2</v>
       </c>
       <c r="C48" s="5">
-        <v>46.24</v>
+        <v>3061.9</v>
       </c>
       <c r="D48" s="5">
-        <v>46.32</v>
+        <v>2962</v>
       </c>
       <c r="E48" s="7">
-        <v>0.08</v>
+        <v>-99.90000000000001</v>
       </c>
     </row>
     <row r="49" spans="1:5">
       <c r="A49" s="3" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B49" s="3" t="s">
         <v>2</v>
       </c>
       <c r="C49" s="5">
-        <v>3100</v>
+        <v>941.8</v>
       </c>
       <c r="D49" s="5">
-        <v>3061.9</v>
+        <v>941.85</v>
       </c>
       <c r="E49" s="6">
-        <v>-38.1</v>
+        <v>0.05</v>
       </c>
     </row>
     <row r="50" spans="1:5">
       <c r="A50" s="3" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B50" s="3" t="s">
         <v>2</v>
       </c>
       <c r="C50" s="5">
-        <v>955.2</v>
+        <v>12.95</v>
       </c>
       <c r="D50" s="5">
-        <v>941.8</v>
-      </c>
-      <c r="E50" s="6">
-        <v>-13.4</v>
+        <v>12.64</v>
+      </c>
+      <c r="E50" s="7">
+        <v>-0.31</v>
       </c>
     </row>
     <row r="51" spans="1:5">
       <c r="A51" s="3" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B51" s="3" t="s">
         <v>2</v>
       </c>
       <c r="C51" s="5">
-        <v>13.56</v>
+        <v>10.92</v>
       </c>
       <c r="D51" s="5">
-        <v>12.95</v>
-      </c>
-      <c r="E51" s="6">
-        <v>-0.61</v>
+        <v>10.73</v>
+      </c>
+      <c r="E51" s="7">
+        <v>-0.19</v>
       </c>
     </row>
     <row r="52" spans="1:5">
       <c r="A52" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B52" s="3" t="s">
         <v>2</v>
       </c>
       <c r="C52" s="5">
-        <v>10.84</v>
+        <v>3956.5</v>
       </c>
       <c r="D52" s="5">
-        <v>10.92</v>
+        <v>3892.3</v>
       </c>
       <c r="E52" s="7">
-        <v>0.08</v>
+        <v>-64.2</v>
       </c>
     </row>
     <row r="53" spans="1:5">
       <c r="A53" s="3" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B53" s="3" t="s">
         <v>2</v>
       </c>
       <c r="C53" s="5">
-        <v>4027.7</v>
+        <v>10956</v>
       </c>
       <c r="D53" s="5">
-        <v>3956.5</v>
-      </c>
-      <c r="E53" s="6">
-        <v>-71.2</v>
+        <v>10710</v>
+      </c>
+      <c r="E53" s="7">
+        <v>-246</v>
       </c>
     </row>
     <row r="54" spans="1:5">
       <c r="A54" s="3" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>2</v>
+        <v>24</v>
       </c>
       <c r="C54" s="5">
-        <v>10829</v>
+        <v>40.79</v>
       </c>
       <c r="D54" s="5">
-        <v>10956</v>
+        <v>38.07</v>
       </c>
       <c r="E54" s="7">
-        <v>127</v>
+        <v>-2.72</v>
       </c>
     </row>
     <row r="55" spans="1:5">
       <c r="A55" s="3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="C55" s="5">
-        <v>62</v>
+        <v>28.49</v>
       </c>
       <c r="D55" s="5">
-        <v>74</v>
+        <v>24.23</v>
       </c>
       <c r="E55" s="7">
-        <v>12</v>
+        <v>-4.26</v>
       </c>
     </row>
     <row r="56" spans="1:5">
       <c r="A56" s="3" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="C56" s="5">
-        <v>74</v>
+        <v>34.45</v>
       </c>
       <c r="D56" s="5">
-        <v>62</v>
-      </c>
-      <c r="E56" s="6">
-        <v>-12</v>
+        <v>28.23</v>
+      </c>
+      <c r="E56" s="7">
+        <v>-6.22</v>
       </c>
     </row>
     <row r="57" spans="1:5">
       <c r="A57" s="3" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="B57" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C57" s="5">
-        <v>38.89</v>
+        <v>35.55</v>
       </c>
       <c r="D57" s="5">
-        <v>40.79</v>
-      </c>
-      <c r="E57" s="7">
-        <v>1.9</v>
+        <v>35.57</v>
+      </c>
+      <c r="E57" s="6">
+        <v>0.02</v>
       </c>
     </row>
     <row r="58" spans="1:5">
       <c r="A58" s="3" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="B58" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C58" s="5">
-        <v>27.97</v>
+        <v>35.45</v>
       </c>
       <c r="D58" s="5">
-        <v>28.49</v>
+        <v>32.95</v>
       </c>
       <c r="E58" s="7">
-        <v>0.52</v>
+        <v>-2.5</v>
       </c>
     </row>
     <row r="59" spans="1:5">
       <c r="A59" s="3" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="B59" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C59" s="5">
-        <v>37.36</v>
+        <v>40.18</v>
       </c>
       <c r="D59" s="5">
-        <v>34.45</v>
-      </c>
-      <c r="E59" s="6">
-        <v>-2.91</v>
+        <v>37.8</v>
+      </c>
+      <c r="E59" s="7">
+        <v>-2.38</v>
       </c>
     </row>
     <row r="60" spans="1:5">
       <c r="A60" s="3" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="B60" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C60" s="5">
-        <v>38.46</v>
+        <v>32.47</v>
       </c>
       <c r="D60" s="5">
-        <v>35.55</v>
-      </c>
-      <c r="E60" s="6">
-        <v>-2.91</v>
+        <v>29.02</v>
+      </c>
+      <c r="E60" s="7">
+        <v>-3.45</v>
       </c>
     </row>
     <row r="61" spans="1:5">
       <c r="A61" s="3" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="B61" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C61" s="5">
-        <v>41.18</v>
+        <v>43.59</v>
       </c>
       <c r="D61" s="5">
-        <v>35.45</v>
-      </c>
-      <c r="E61" s="6">
-        <v>-5.73</v>
+        <v>37.63</v>
+      </c>
+      <c r="E61" s="7">
+        <v>-5.96</v>
       </c>
     </row>
     <row r="62" spans="1:5">
       <c r="A62" s="3" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="B62" s="3" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="C62" s="5">
-        <v>38.67</v>
+        <v>26.92</v>
       </c>
       <c r="D62" s="5">
-        <v>40.18</v>
-      </c>
-      <c r="E62" s="7">
-        <v>1.51</v>
+        <v>85</v>
+      </c>
+      <c r="E62" s="6">
+        <v>58.08</v>
       </c>
     </row>
     <row r="63" spans="1:5">
       <c r="A63" s="3" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="B63" s="3" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="C63" s="5">
-        <v>37.01</v>
+        <v>-22.58</v>
       </c>
       <c r="D63" s="5">
-        <v>32.47</v>
+        <v>13.7</v>
       </c>
       <c r="E63" s="6">
-        <v>-4.54</v>
+        <v>36.28</v>
       </c>
     </row>
     <row r="64" spans="1:5">
       <c r="A64" s="3" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="C64" s="5">
-        <v>38.95</v>
+        <v>-49.56</v>
       </c>
       <c r="D64" s="5">
-        <v>43.59</v>
-      </c>
-      <c r="E64" s="7">
-        <v>4.64</v>
+        <v>60.86</v>
+      </c>
+      <c r="E64" s="6">
+        <v>110.42</v>
       </c>
     </row>
     <row r="65" spans="1:5">
       <c r="A65" s="3" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="B65" s="3" t="s">
         <v>31</v>
       </c>
       <c r="C65" s="5">
-        <v>69.65000000000001</v>
+        <v>24.58</v>
       </c>
       <c r="D65" s="5">
-        <v>26.92</v>
+        <v>68.70999999999999</v>
       </c>
       <c r="E65" s="6">
-        <v>-42.73</v>
+        <v>44.13</v>
       </c>
     </row>
     <row r="66" spans="1:5">
       <c r="A66" s="3" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="B66" s="3" t="s">
         <v>31</v>
       </c>
       <c r="C66" s="5">
-        <v>184.13</v>
+        <v>38.55</v>
       </c>
       <c r="D66" s="5">
-        <v>-22.58</v>
-      </c>
-      <c r="E66" s="6">
-        <v>-206.71</v>
+        <v>29.55</v>
+      </c>
+      <c r="E66" s="7">
+        <v>-9</v>
       </c>
     </row>
     <row r="67" spans="1:5">
       <c r="A67" s="3" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="B67" s="3" t="s">
         <v>31</v>
       </c>
       <c r="C67" s="5">
-        <v>33.1</v>
+        <v>24.38</v>
       </c>
       <c r="D67" s="5">
-        <v>-49.56</v>
+        <v>30.84</v>
       </c>
       <c r="E67" s="6">
-        <v>-82.66</v>
+        <v>6.46</v>
       </c>
     </row>
     <row r="68" spans="1:5">
       <c r="A68" s="3" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="B68" s="3" t="s">
         <v>31</v>
       </c>
       <c r="C68" s="5">
-        <v>50.43</v>
+        <v>141.95</v>
       </c>
       <c r="D68" s="5">
-        <v>24.58</v>
-      </c>
-      <c r="E68" s="6">
-        <v>-25.85</v>
+        <v>-7.38</v>
+      </c>
+      <c r="E68" s="7">
+        <v>-149.33</v>
       </c>
     </row>
     <row r="69" spans="1:5">
       <c r="A69" s="3" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="B69" s="3" t="s">
         <v>31</v>
       </c>
       <c r="C69" s="5">
-        <v>170.27</v>
+        <v>-8.699999999999999</v>
       </c>
       <c r="D69" s="5">
-        <v>38.55</v>
+        <v>106.59</v>
       </c>
       <c r="E69" s="6">
-        <v>-131.72</v>
-      </c>
-    </row>
-    <row r="70" spans="1:5">
-      <c r="A70" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="B70" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C70" s="5">
-        <v>146.62</v>
-      </c>
-      <c r="D70" s="5">
-        <v>24.38</v>
-      </c>
-      <c r="E70" s="6">
-        <v>-122.24</v>
-      </c>
-    </row>
-    <row r="71" spans="1:5">
-      <c r="A71" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="B71" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C71" s="5">
-        <v>4.84</v>
-      </c>
-      <c r="D71" s="5">
-        <v>141.95</v>
-      </c>
-      <c r="E71" s="7">
-        <v>137.11</v>
-      </c>
-    </row>
-    <row r="72" spans="1:5">
-      <c r="A72" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="B72" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C72" s="5">
-        <v>91.52</v>
-      </c>
-      <c r="D72" s="5">
-        <v>-8.699999999999999</v>
-      </c>
-      <c r="E72" s="6">
-        <v>-100.22</v>
+        <v>115.29</v>
       </c>
     </row>
   </sheetData>
@@ -3160,22 +3109,22 @@
         <v>45</v>
       </c>
       <c r="B2" s="10">
-        <v>52.44</v>
+        <v>40.44</v>
       </c>
       <c r="C2" s="11">
         <v>8</v>
       </c>
       <c r="D2" s="10">
-        <v>36.4</v>
+        <v>32.9</v>
       </c>
       <c r="E2" s="10">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="F2" s="10">
-        <v>-7.4</v>
+        <v>-8.199999999999999</v>
       </c>
       <c r="G2" s="10">
-        <v>-7.4</v>
+        <v>-9.699999999999999</v>
       </c>
       <c r="H2" s="10">
         <v>56.1</v>
@@ -3309,28 +3258,28 @@
     </row>
     <row r="2" spans="1:8">
       <c r="A2" s="13">
-        <v>0.2755</v>
+        <v>0.2736</v>
       </c>
       <c r="B2" s="13">
-        <v>0.1635</v>
+        <v>0.1587</v>
       </c>
       <c r="C2" s="13">
-        <v>0.1471</v>
+        <v>0.1488</v>
       </c>
       <c r="D2" s="13">
-        <v>0.1342</v>
+        <v>0.1257</v>
       </c>
       <c r="E2" s="13">
-        <v>0.0867</v>
+        <v>0.07919999999999999</v>
       </c>
       <c r="F2" s="13">
-        <v>0.0171</v>
+        <v>0.0209</v>
       </c>
       <c r="G2" s="13">
-        <v>-0.2841</v>
+        <v>-0.2886</v>
       </c>
       <c r="H2" s="13">
-        <v>-0.2965</v>
+        <v>-0.2984</v>
       </c>
     </row>
   </sheetData>

--- a/BIRLA_GROUP_Technical_Metrics.xlsx
+++ b/BIRLA_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="274" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="287" uniqueCount="74">
   <si>
     <t>Symbol</t>
   </si>
@@ -175,7 +175,34 @@
     <t>▶  SIGNAL EVENTS (vs Previous Run)</t>
   </si>
   <si>
-    <t>No signal events detected since last run.</t>
+    <t>Signal</t>
+  </si>
+  <si>
+    <t>Change</t>
+  </si>
+  <si>
+    <t>Direction</t>
+  </si>
+  <si>
+    <t>Prev Value</t>
+  </si>
+  <si>
+    <t>Curr Value</t>
+  </si>
+  <si>
+    <t>RSI Oversold Recovery</t>
+  </si>
+  <si>
+    <t>29.0 → 39.1</t>
+  </si>
+  <si>
+    <t>🟢 BULLISH</t>
+  </si>
+  <si>
+    <t>29.0</t>
+  </si>
+  <si>
+    <t>39.1</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -377,17 +404,18 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -758,15 +786,15 @@
     <col min="13" max="13" width="10.7109375" customWidth="1"/>
     <col min="14" max="14" width="11.7109375" customWidth="1"/>
     <col min="15" max="15" width="10.7109375" customWidth="1"/>
-    <col min="16" max="16" width="9.7109375" customWidth="1"/>
-    <col min="17" max="19" width="10.7109375" customWidth="1"/>
+    <col min="16" max="17" width="9.7109375" customWidth="1"/>
+    <col min="18" max="19" width="10.7109375" customWidth="1"/>
     <col min="20" max="20" width="22.7109375" customWidth="1"/>
     <col min="21" max="21" width="9.7109375" customWidth="1"/>
     <col min="22" max="22" width="10.7109375" customWidth="1"/>
     <col min="23" max="23" width="16.7109375" customWidth="1"/>
     <col min="24" max="24" width="13.7109375" customWidth="1"/>
     <col min="25" max="25" width="7.7109375" customWidth="1"/>
-    <col min="26" max="26" width="8.7109375" customWidth="1"/>
+    <col min="26" max="26" width="9.7109375" customWidth="1"/>
     <col min="27" max="27" width="13.7109375" customWidth="1"/>
     <col min="28" max="28" width="11.7109375" customWidth="1"/>
     <col min="29" max="30" width="13.7109375" customWidth="1"/>
@@ -899,58 +927,58 @@
         <v>45</v>
       </c>
       <c r="C2">
-        <v>375.05</v>
+        <v>377.4</v>
       </c>
       <c r="D2">
-        <v>-1.46</v>
+        <v>0.63</v>
       </c>
       <c r="E2">
         <v>424.7</v>
       </c>
       <c r="F2">
-        <v>289.85</v>
+        <v>292.25</v>
       </c>
       <c r="G2">
-        <v>-11.69</v>
+        <v>-11.14</v>
       </c>
       <c r="H2">
-        <v>29.39</v>
+        <v>29.14</v>
       </c>
       <c r="I2">
-        <v>-3.86</v>
+        <v>-3.23</v>
       </c>
       <c r="J2">
-        <v>-4.92</v>
+        <v>-4.95</v>
       </c>
       <c r="K2">
-        <v>-6.53</v>
+        <v>-7.9</v>
       </c>
       <c r="L2">
-        <v>34.47</v>
+        <v>30.21</v>
       </c>
       <c r="M2">
-        <v>27.36</v>
+        <v>27.76</v>
       </c>
       <c r="N2">
         <v>74</v>
       </c>
       <c r="O2">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="P2">
-        <v>381.27</v>
+        <v>378.75</v>
       </c>
       <c r="Q2">
-        <v>393.08</v>
+        <v>391.85</v>
       </c>
       <c r="R2">
-        <v>400.75</v>
+        <v>400.45</v>
       </c>
       <c r="S2">
-        <v>364.55</v>
+        <v>364.68</v>
       </c>
       <c r="T2">
-        <v>2.88</v>
+        <v>3.49</v>
       </c>
       <c r="U2" t="s">
         <v>46</v>
@@ -965,34 +993,34 @@
         <v>2</v>
       </c>
       <c r="Y2">
-        <v>38.07</v>
+        <v>39.9</v>
       </c>
       <c r="Z2">
-        <v>-5.68</v>
+        <v>-6.07</v>
       </c>
       <c r="AA2">
-        <v>-3.65</v>
+        <v>-4.13</v>
       </c>
       <c r="AB2">
-        <v>-2.04</v>
+        <v>-1.94</v>
       </c>
       <c r="AC2">
-        <v>24.11</v>
+        <v>25.6</v>
       </c>
       <c r="AD2">
-        <v>29.08</v>
+        <v>26.11</v>
       </c>
       <c r="AE2">
-        <v>9.56</v>
+        <v>9.41</v>
       </c>
       <c r="AF2">
-        <v>85</v>
+        <v>-42.92</v>
       </c>
       <c r="AG2">
-        <v>414.21</v>
+        <v>413.65</v>
       </c>
       <c r="AH2">
-        <v>371.94</v>
+        <v>370.05</v>
       </c>
       <c r="AI2">
         <v>372.91</v>
@@ -1001,7 +1029,7 @@
         <v>48</v>
       </c>
       <c r="AK2">
-        <v>30.49</v>
+        <v>32.21</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1012,37 +1040,37 @@
         <v>45</v>
       </c>
       <c r="C3">
-        <v>44.53</v>
+        <v>44.34</v>
       </c>
       <c r="D3">
-        <v>-3.86</v>
+        <v>-0.43</v>
       </c>
       <c r="E3">
         <v>87.98999999999999</v>
       </c>
       <c r="F3">
-        <v>44.53</v>
+        <v>44.34</v>
       </c>
       <c r="G3">
-        <v>-49.39</v>
+        <v>-49.61</v>
       </c>
       <c r="H3">
         <v>0</v>
       </c>
       <c r="I3">
-        <v>-7.34</v>
+        <v>-9.77</v>
       </c>
       <c r="J3">
-        <v>-12.86</v>
+        <v>-12.15</v>
       </c>
       <c r="K3">
-        <v>-28.72</v>
+        <v>-28.98</v>
       </c>
       <c r="L3">
-        <v>-47.55</v>
+        <v>-47.84</v>
       </c>
       <c r="M3">
-        <v>-28.86</v>
+        <v>-29.56</v>
       </c>
       <c r="N3">
         <v>13</v>
@@ -1051,19 +1079,19 @@
         <v>4</v>
       </c>
       <c r="P3">
-        <v>46.76</v>
+        <v>45.8</v>
       </c>
       <c r="Q3">
-        <v>49.55</v>
+        <v>49.24</v>
       </c>
       <c r="R3">
-        <v>53.86</v>
+        <v>53.63</v>
       </c>
       <c r="S3">
-        <v>62.27</v>
+        <v>62.11</v>
       </c>
       <c r="T3">
-        <v>-28.48</v>
+        <v>-28.61</v>
       </c>
       <c r="U3" t="s">
         <v>46</v>
@@ -1078,43 +1106,43 @@
         <v>0</v>
       </c>
       <c r="Y3">
-        <v>24.23</v>
+        <v>23.83</v>
       </c>
       <c r="Z3">
-        <v>-2.15</v>
+        <v>-2.28</v>
       </c>
       <c r="AA3">
-        <v>-1.88</v>
+        <v>-1.96</v>
       </c>
       <c r="AB3">
-        <v>-0.27</v>
+        <v>-0.32</v>
       </c>
       <c r="AC3">
         <v>1.85</v>
       </c>
       <c r="AD3">
-        <v>14.28</v>
+        <v>5.07</v>
       </c>
       <c r="AE3">
-        <v>1.58</v>
+        <v>1.55</v>
       </c>
       <c r="AF3">
-        <v>13.7</v>
+        <v>-24.55</v>
       </c>
       <c r="AG3">
-        <v>53.98</v>
+        <v>54.23</v>
       </c>
       <c r="AH3">
-        <v>45.11</v>
+        <v>44.26</v>
       </c>
       <c r="AI3">
-        <v>50.02</v>
+        <v>49.46</v>
       </c>
       <c r="AJ3" t="s">
         <v>49</v>
       </c>
       <c r="AK3">
-        <v>51.58</v>
+        <v>55.19</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1125,10 +1153,10 @@
         <v>45</v>
       </c>
       <c r="C4">
-        <v>2962</v>
+        <v>2972</v>
       </c>
       <c r="D4">
-        <v>-3.26</v>
+        <v>0.34</v>
       </c>
       <c r="E4">
         <v>3380.5</v>
@@ -1137,25 +1165,25 @@
         <v>2531.1</v>
       </c>
       <c r="G4">
-        <v>-12.38</v>
+        <v>-12.08</v>
       </c>
       <c r="H4">
-        <v>17.02</v>
+        <v>17.42</v>
       </c>
       <c r="I4">
-        <v>-6.46</v>
+        <v>-6.86</v>
       </c>
       <c r="J4">
-        <v>-10.38</v>
+        <v>-9.800000000000001</v>
       </c>
       <c r="K4">
-        <v>-6.88</v>
+        <v>-7.5</v>
       </c>
       <c r="L4">
-        <v>7.83</v>
+        <v>8.19</v>
       </c>
       <c r="M4">
-        <v>12.57</v>
+        <v>13.33</v>
       </c>
       <c r="N4">
         <v>50</v>
@@ -1164,19 +1192,19 @@
         <v>60</v>
       </c>
       <c r="P4">
-        <v>3092.98</v>
+        <v>3049.18</v>
       </c>
       <c r="Q4">
-        <v>3199.82</v>
+        <v>3182.92</v>
       </c>
       <c r="R4">
-        <v>3224.62</v>
+        <v>3221.8</v>
       </c>
       <c r="S4">
-        <v>2976.83</v>
+        <v>2977.59</v>
       </c>
       <c r="T4">
-        <v>-0.5</v>
+        <v>-0.19</v>
       </c>
       <c r="U4" t="s">
         <v>46</v>
@@ -1191,43 +1219,43 @@
         <v>1</v>
       </c>
       <c r="Y4">
-        <v>28.23</v>
+        <v>29.6</v>
       </c>
       <c r="Z4">
-        <v>-52.55</v>
+        <v>-61.38</v>
       </c>
       <c r="AA4">
-        <v>-28.82</v>
+        <v>-35.33</v>
       </c>
       <c r="AB4">
-        <v>-23.73</v>
+        <v>-26.04</v>
       </c>
       <c r="AC4">
-        <v>1.01</v>
+        <v>2.62</v>
       </c>
       <c r="AD4">
-        <v>11.8</v>
+        <v>4.37</v>
       </c>
       <c r="AE4">
-        <v>63.6</v>
+        <v>63.52</v>
       </c>
       <c r="AF4">
-        <v>60.86</v>
+        <v>-70.31999999999999</v>
       </c>
       <c r="AG4">
-        <v>3393.09</v>
+        <v>3393.93</v>
       </c>
       <c r="AH4">
-        <v>3006.56</v>
+        <v>2971.92</v>
       </c>
       <c r="AI4">
-        <v>3185.49</v>
+        <v>3183.3</v>
       </c>
       <c r="AJ4" t="s">
         <v>49</v>
       </c>
       <c r="AK4">
-        <v>47.57</v>
+        <v>51.84</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1238,58 +1266,58 @@
         <v>45</v>
       </c>
       <c r="C5">
-        <v>941.85</v>
+        <v>938.4</v>
       </c>
       <c r="D5">
-        <v>0.01</v>
+        <v>-0.37</v>
       </c>
       <c r="E5">
         <v>1149.7</v>
       </c>
       <c r="F5">
-        <v>753.8</v>
+        <v>760.1</v>
       </c>
       <c r="G5">
-        <v>-18.08</v>
+        <v>-18.38</v>
       </c>
       <c r="H5">
-        <v>24.95</v>
+        <v>23.46</v>
       </c>
       <c r="I5">
-        <v>-4.09</v>
+        <v>-3.95</v>
       </c>
       <c r="J5">
-        <v>-7.15</v>
+        <v>-7.06</v>
       </c>
       <c r="K5">
-        <v>-1.19</v>
+        <v>-4.28</v>
       </c>
       <c r="L5">
-        <v>26.62</v>
+        <v>24.49</v>
       </c>
       <c r="M5">
-        <v>14.88</v>
+        <v>14.29</v>
       </c>
       <c r="N5">
         <v>62</v>
       </c>
       <c r="O5">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="P5">
-        <v>954.35</v>
+        <v>946.63</v>
       </c>
       <c r="Q5">
-        <v>983.4299999999999</v>
+        <v>979.85</v>
       </c>
       <c r="R5">
-        <v>1004.25</v>
+        <v>1003.91</v>
       </c>
       <c r="S5">
-        <v>981.16</v>
+        <v>981.61</v>
       </c>
       <c r="T5">
-        <v>-4.01</v>
+        <v>-4.4</v>
       </c>
       <c r="U5" t="s">
         <v>46</v>
@@ -1304,34 +1332,34 @@
         <v>1</v>
       </c>
       <c r="Y5">
-        <v>35.57</v>
+        <v>34.79</v>
       </c>
       <c r="Z5">
-        <v>-16.74</v>
+        <v>-17.9</v>
       </c>
       <c r="AA5">
-        <v>-12.25</v>
+        <v>-13.38</v>
       </c>
       <c r="AB5">
-        <v>-4.49</v>
+        <v>-4.53</v>
       </c>
       <c r="AC5">
-        <v>13.19</v>
+        <v>6.64</v>
       </c>
       <c r="AD5">
-        <v>21.35</v>
+        <v>12.75</v>
       </c>
       <c r="AE5">
-        <v>21.83</v>
+        <v>21.91</v>
       </c>
       <c r="AF5">
-        <v>68.70999999999999</v>
+        <v>21.15</v>
       </c>
       <c r="AG5">
-        <v>1033.25</v>
+        <v>1031.87</v>
       </c>
       <c r="AH5">
-        <v>933.61</v>
+        <v>927.8200000000001</v>
       </c>
       <c r="AI5">
         <v>1000.57</v>
@@ -1340,7 +1368,7 @@
         <v>49</v>
       </c>
       <c r="AK5">
-        <v>29.78</v>
+        <v>31.26</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1351,10 +1379,10 @@
         <v>45</v>
       </c>
       <c r="C6">
-        <v>12.64</v>
+        <v>12.74</v>
       </c>
       <c r="D6">
-        <v>-2.39</v>
+        <v>0.79</v>
       </c>
       <c r="E6">
         <v>15.6</v>
@@ -1363,25 +1391,25 @@
         <v>8.130000000000001</v>
       </c>
       <c r="G6">
-        <v>-18.97</v>
+        <v>-18.33</v>
       </c>
       <c r="H6">
-        <v>55.47</v>
+        <v>56.7</v>
       </c>
       <c r="I6">
-        <v>-10.48</v>
+        <v>-10.66</v>
       </c>
       <c r="J6">
-        <v>-10.1</v>
+        <v>-12.32</v>
       </c>
       <c r="K6">
-        <v>-11.3</v>
+        <v>-9.58</v>
       </c>
       <c r="L6">
-        <v>57.61</v>
+        <v>54.61</v>
       </c>
       <c r="M6">
-        <v>2.09</v>
+        <v>1.98</v>
       </c>
       <c r="N6">
         <v>87</v>
@@ -1390,19 +1418,19 @@
         <v>81</v>
       </c>
       <c r="P6">
-        <v>13.38</v>
+        <v>13.07</v>
       </c>
       <c r="Q6">
-        <v>14.32</v>
+        <v>14.23</v>
       </c>
       <c r="R6">
-        <v>13.91</v>
+        <v>13.9</v>
       </c>
       <c r="S6">
-        <v>12.24</v>
+        <v>12.25</v>
       </c>
       <c r="T6">
-        <v>3.24</v>
+        <v>4</v>
       </c>
       <c r="U6" t="s">
         <v>47</v>
@@ -1417,43 +1445,43 @@
         <v>3</v>
       </c>
       <c r="Y6">
-        <v>32.95</v>
+        <v>34.56</v>
       </c>
       <c r="Z6">
-        <v>-0.28</v>
+        <v>-0.34</v>
       </c>
       <c r="AA6">
-        <v>-0.06</v>
+        <v>-0.12</v>
       </c>
       <c r="AB6">
         <v>-0.22</v>
       </c>
       <c r="AC6">
-        <v>1.69</v>
+        <v>2.78</v>
       </c>
       <c r="AD6">
-        <v>4.49</v>
+        <v>2.05</v>
       </c>
       <c r="AE6">
-        <v>0.52</v>
+        <v>0.51</v>
       </c>
       <c r="AF6">
-        <v>29.55</v>
+        <v>-5.45</v>
       </c>
       <c r="AG6">
-        <v>15.91</v>
+        <v>15.97</v>
       </c>
       <c r="AH6">
-        <v>12.73</v>
+        <v>12.49</v>
       </c>
       <c r="AI6">
-        <v>14.37</v>
+        <v>14.25</v>
       </c>
       <c r="AJ6" t="s">
         <v>49</v>
       </c>
       <c r="AK6">
-        <v>37.74</v>
+        <v>41.8</v>
       </c>
     </row>
     <row r="7" spans="1:37">
@@ -1464,10 +1492,10 @@
         <v>45</v>
       </c>
       <c r="C7">
-        <v>10.73</v>
+        <v>10.25</v>
       </c>
       <c r="D7">
-        <v>-1.74</v>
+        <v>-4.47</v>
       </c>
       <c r="E7">
         <v>13.92</v>
@@ -1476,46 +1504,46 @@
         <v>4.69</v>
       </c>
       <c r="G7">
-        <v>-22.92</v>
+        <v>-26.36</v>
       </c>
       <c r="H7">
-        <v>128.78</v>
+        <v>118.55</v>
       </c>
       <c r="I7">
-        <v>-5.79</v>
+        <v>-11.41</v>
       </c>
       <c r="J7">
-        <v>-3.33</v>
+        <v>-9.050000000000001</v>
       </c>
       <c r="K7">
-        <v>-2.45</v>
+        <v>-4.92</v>
       </c>
       <c r="L7">
-        <v>86.28</v>
+        <v>87.39</v>
       </c>
       <c r="M7">
-        <v>-29.84</v>
+        <v>-31.66</v>
       </c>
       <c r="N7">
         <v>99</v>
       </c>
       <c r="O7">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="P7">
-        <v>11.02</v>
+        <v>10.75</v>
       </c>
       <c r="Q7">
-        <v>11.5</v>
+        <v>11.46</v>
       </c>
       <c r="R7">
-        <v>11.73</v>
+        <v>11.7</v>
       </c>
       <c r="S7">
-        <v>10.81</v>
+        <v>10.82</v>
       </c>
       <c r="T7">
-        <v>-0.78</v>
+        <v>-5.29</v>
       </c>
       <c r="U7" t="s">
         <v>46</v>
@@ -1530,43 +1558,43 @@
         <v>1</v>
       </c>
       <c r="Y7">
-        <v>37.8</v>
+        <v>32.56</v>
       </c>
       <c r="Z7">
-        <v>-0.18</v>
+        <v>-0.25</v>
       </c>
       <c r="AA7">
-        <v>-0.07000000000000001</v>
+        <v>-0.1</v>
       </c>
       <c r="AB7">
-        <v>-0.11</v>
+        <v>-0.14</v>
       </c>
       <c r="AC7">
         <v>1.78</v>
       </c>
       <c r="AD7">
-        <v>3.95</v>
+        <v>1.78</v>
       </c>
       <c r="AE7">
-        <v>0.49</v>
+        <v>0.51</v>
       </c>
       <c r="AF7">
-        <v>30.84</v>
+        <v>117.53</v>
       </c>
       <c r="AG7">
-        <v>12.59</v>
+        <v>12.67</v>
       </c>
       <c r="AH7">
-        <v>10.42</v>
+        <v>10.25</v>
       </c>
       <c r="AI7">
-        <v>12.13</v>
+        <v>12.12</v>
       </c>
       <c r="AJ7" t="s">
         <v>49</v>
       </c>
       <c r="AK7">
-        <v>34.13</v>
+        <v>37.1</v>
       </c>
     </row>
     <row r="8" spans="1:37">
@@ -1577,10 +1605,10 @@
         <v>45</v>
       </c>
       <c r="C8">
-        <v>3892.3</v>
+        <v>3984.7</v>
       </c>
       <c r="D8">
-        <v>-1.62</v>
+        <v>2.37</v>
       </c>
       <c r="E8">
         <v>5809.5</v>
@@ -1589,46 +1617,46 @@
         <v>3892.3</v>
       </c>
       <c r="G8">
-        <v>-33</v>
+        <v>-31.41</v>
       </c>
       <c r="H8">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="I8">
-        <v>-2.86</v>
+        <v>-0.75</v>
       </c>
       <c r="J8">
-        <v>-10.59</v>
+        <v>-7.87</v>
       </c>
       <c r="K8">
-        <v>-11.85</v>
+        <v>-9.43</v>
       </c>
       <c r="L8">
-        <v>-26.15</v>
+        <v>-24.89</v>
       </c>
       <c r="M8">
-        <v>15.87</v>
+        <v>15.61</v>
       </c>
       <c r="N8">
         <v>26</v>
       </c>
       <c r="O8">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="P8">
-        <v>3977.8</v>
+        <v>3971.74</v>
       </c>
       <c r="Q8">
-        <v>4101.62</v>
+        <v>4083.13</v>
       </c>
       <c r="R8">
-        <v>4258.68</v>
+        <v>4252.31</v>
       </c>
       <c r="S8">
-        <v>4529.8</v>
+        <v>4524.12</v>
       </c>
       <c r="T8">
-        <v>-14.07</v>
+        <v>-11.92</v>
       </c>
       <c r="U8" t="s">
         <v>46</v>
@@ -1643,34 +1671,34 @@
         <v>0</v>
       </c>
       <c r="Y8">
-        <v>29.02</v>
+        <v>39.06</v>
       </c>
       <c r="Z8">
-        <v>-97.02</v>
+        <v>-93.06999999999999</v>
       </c>
       <c r="AA8">
-        <v>-86.58</v>
+        <v>-87.88</v>
       </c>
       <c r="AB8">
-        <v>-10.45</v>
+        <v>-5.19</v>
       </c>
       <c r="AC8">
-        <v>19.71</v>
+        <v>35.15</v>
       </c>
       <c r="AD8">
-        <v>27.96</v>
+        <v>27.53</v>
       </c>
       <c r="AE8">
-        <v>109.36</v>
+        <v>111.6</v>
       </c>
       <c r="AF8">
-        <v>-7.38</v>
+        <v>16.82</v>
       </c>
       <c r="AG8">
-        <v>4362.72</v>
+        <v>4320.08</v>
       </c>
       <c r="AH8">
-        <v>3840.52</v>
+        <v>3846.18</v>
       </c>
       <c r="AI8">
         <v>4247.59</v>
@@ -1679,7 +1707,7 @@
         <v>49</v>
       </c>
       <c r="AK8">
-        <v>57.53</v>
+        <v>52.96</v>
       </c>
     </row>
     <row r="9" spans="1:37">
@@ -1690,10 +1718,10 @@
         <v>45</v>
       </c>
       <c r="C9">
-        <v>10710</v>
+        <v>10850</v>
       </c>
       <c r="D9">
-        <v>-2.25</v>
+        <v>1.31</v>
       </c>
       <c r="E9">
         <v>13052</v>
@@ -1702,46 +1730,46 @@
         <v>10362</v>
       </c>
       <c r="G9">
-        <v>-17.94</v>
+        <v>-16.87</v>
       </c>
       <c r="H9">
-        <v>3.36</v>
+        <v>4.71</v>
       </c>
       <c r="I9">
-        <v>-3.13</v>
+        <v>-2.73</v>
       </c>
       <c r="J9">
-        <v>-6.05</v>
+        <v>-4.77</v>
       </c>
       <c r="K9">
-        <v>-8.640000000000001</v>
+        <v>-6.95</v>
       </c>
       <c r="L9">
-        <v>-11.27</v>
+        <v>-9.890000000000001</v>
       </c>
       <c r="M9">
-        <v>7.92</v>
+        <v>8.26</v>
       </c>
       <c r="N9">
         <v>38</v>
       </c>
       <c r="O9">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="P9">
-        <v>10935</v>
+        <v>10874</v>
       </c>
       <c r="Q9">
-        <v>10995.35</v>
+        <v>10974.1</v>
       </c>
       <c r="R9">
-        <v>11455.54</v>
+        <v>11434.38</v>
       </c>
       <c r="S9">
-        <v>11708.14</v>
+        <v>11703.76</v>
       </c>
       <c r="T9">
-        <v>-8.529999999999999</v>
+        <v>-7.29</v>
       </c>
       <c r="U9" t="s">
         <v>46</v>
@@ -1756,34 +1784,34 @@
         <v>0</v>
       </c>
       <c r="Y9">
-        <v>37.63</v>
+        <v>42.45</v>
       </c>
       <c r="Z9">
-        <v>-146.8</v>
+        <v>-145.23</v>
       </c>
       <c r="AA9">
-        <v>-152.5</v>
+        <v>-151.05</v>
       </c>
       <c r="AB9">
-        <v>5.7</v>
+        <v>5.82</v>
       </c>
       <c r="AC9">
-        <v>61.33</v>
+        <v>66.93000000000001</v>
       </c>
       <c r="AD9">
-        <v>70.7</v>
+        <v>66.68000000000001</v>
       </c>
       <c r="AE9">
-        <v>201.02</v>
+        <v>203.09</v>
       </c>
       <c r="AF9">
-        <v>106.59</v>
+        <v>6.48</v>
       </c>
       <c r="AG9">
-        <v>11378.58</v>
+        <v>11338.71</v>
       </c>
       <c r="AH9">
-        <v>10612.12</v>
+        <v>10609.49</v>
       </c>
       <c r="AI9">
         <v>11348.57</v>
@@ -1792,7 +1820,7 @@
         <v>49</v>
       </c>
       <c r="AK9">
-        <v>29.54</v>
+        <v>30.81</v>
       </c>
     </row>
   </sheetData>
@@ -1933,7 +1961,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F69"/>
+  <dimension ref="A1:F70"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -1953,12 +1981,47 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="3" t="s">
         <v>51</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>60</v>
       </c>
     </row>
     <row r="5" spans="1:6">
       <c r="A5" s="2" t="s">
-        <v>52</v>
+        <v>61</v>
       </c>
       <c r="B5" s="2"/>
       <c r="C5" s="2"/>
@@ -1966,1091 +2029,1108 @@
       <c r="E5" s="2"/>
     </row>
     <row r="6" spans="1:6">
-      <c r="A6" s="4" t="s">
+      <c r="A6" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B6" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="D6" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="E6" s="4" t="s">
-        <v>56</v>
+      <c r="B6" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>65</v>
       </c>
     </row>
     <row r="7" spans="1:6">
-      <c r="A7" s="3" t="s">
+      <c r="A7" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B7" s="3" t="s">
+      <c r="B7" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C7" s="5">
-        <v>-7.03</v>
-      </c>
-      <c r="D7" s="5">
+      <c r="C7" s="6">
         <v>-4.92</v>
       </c>
-      <c r="E7" s="6">
+      <c r="D7" s="6">
+        <v>-4.95</v>
+      </c>
+      <c r="E7" s="7">
+        <v>-0.03</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C8" s="6">
+        <v>-12.86</v>
+      </c>
+      <c r="D8" s="6">
+        <v>-12.15</v>
+      </c>
+      <c r="E8" s="8">
+        <v>0.71</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C9" s="6">
+        <v>-10.38</v>
+      </c>
+      <c r="D9" s="6">
+        <v>-9.800000000000001</v>
+      </c>
+      <c r="E9" s="8">
+        <v>0.58</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C10" s="6">
+        <v>-7.15</v>
+      </c>
+      <c r="D10" s="6">
+        <v>-7.06</v>
+      </c>
+      <c r="E10" s="8">
+        <v>0.09</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B11" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C11" s="6">
+        <v>-10.1</v>
+      </c>
+      <c r="D11" s="6">
+        <v>-12.32</v>
+      </c>
+      <c r="E11" s="7">
+        <v>-2.22</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B12" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C12" s="6">
+        <v>-3.33</v>
+      </c>
+      <c r="D12" s="6">
+        <v>-9.050000000000001</v>
+      </c>
+      <c r="E12" s="7">
+        <v>-5.72</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="A13" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B13" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C13" s="6">
+        <v>-10.59</v>
+      </c>
+      <c r="D13" s="6">
+        <v>-7.87</v>
+      </c>
+      <c r="E13" s="8">
+        <v>2.72</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="B14" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C14" s="6">
+        <v>-6.05</v>
+      </c>
+      <c r="D14" s="6">
+        <v>-4.77</v>
+      </c>
+      <c r="E14" s="8">
+        <v>1.28</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="A15" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B15" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C15" s="6">
+        <v>-3.86</v>
+      </c>
+      <c r="D15" s="6">
+        <v>-3.23</v>
+      </c>
+      <c r="E15" s="8">
+        <v>0.63</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="A16" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B16" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C16" s="6">
+        <v>-7.34</v>
+      </c>
+      <c r="D16" s="6">
+        <v>-9.77</v>
+      </c>
+      <c r="E16" s="7">
+        <v>-2.43</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B17" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C17" s="6">
+        <v>-6.46</v>
+      </c>
+      <c r="D17" s="6">
+        <v>-6.86</v>
+      </c>
+      <c r="E17" s="7">
+        <v>-0.4</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B18" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C18" s="6">
+        <v>-4.09</v>
+      </c>
+      <c r="D18" s="6">
+        <v>-3.95</v>
+      </c>
+      <c r="E18" s="8">
+        <v>0.14</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B19" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C19" s="6">
+        <v>-10.48</v>
+      </c>
+      <c r="D19" s="6">
+        <v>-10.66</v>
+      </c>
+      <c r="E19" s="7">
+        <v>-0.18</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B20" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C20" s="6">
+        <v>-5.79</v>
+      </c>
+      <c r="D20" s="6">
+        <v>-11.41</v>
+      </c>
+      <c r="E20" s="7">
+        <v>-5.62</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B21" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C21" s="6">
+        <v>-2.86</v>
+      </c>
+      <c r="D21" s="6">
+        <v>-0.75</v>
+      </c>
+      <c r="E21" s="8">
         <v>2.11</v>
       </c>
     </row>
-    <row r="8" spans="1:6">
-      <c r="A8" s="3" t="s">
+    <row r="22" spans="1:5">
+      <c r="A22" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="B22" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C22" s="6">
+        <v>-3.13</v>
+      </c>
+      <c r="D22" s="6">
+        <v>-2.73</v>
+      </c>
+      <c r="E22" s="8">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B23" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C23" s="6">
+        <v>34.47</v>
+      </c>
+      <c r="D23" s="6">
+        <v>30.21</v>
+      </c>
+      <c r="E23" s="7">
+        <v>-4.26</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B8" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C8" s="5">
-        <v>-11.09</v>
-      </c>
-      <c r="D8" s="5">
-        <v>-12.86</v>
-      </c>
-      <c r="E8" s="7">
-        <v>-1.77</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9" s="3" t="s">
+      <c r="B24" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C24" s="6">
+        <v>-47.55</v>
+      </c>
+      <c r="D24" s="6">
+        <v>-47.84</v>
+      </c>
+      <c r="E24" s="7">
+        <v>-0.29</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B9" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C9" s="5">
-        <v>-9.17</v>
-      </c>
-      <c r="D9" s="5">
-        <v>-10.38</v>
-      </c>
-      <c r="E9" s="7">
-        <v>-1.21</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10" s="3" t="s">
+      <c r="B25" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C25" s="6">
+        <v>7.83</v>
+      </c>
+      <c r="D25" s="6">
+        <v>8.19</v>
+      </c>
+      <c r="E25" s="8">
+        <v>0.36</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B10" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C10" s="5">
-        <v>-7.25</v>
-      </c>
-      <c r="D10" s="5">
-        <v>-7.15</v>
-      </c>
-      <c r="E10" s="6">
+      <c r="B26" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C26" s="6">
+        <v>26.62</v>
+      </c>
+      <c r="D26" s="6">
+        <v>24.49</v>
+      </c>
+      <c r="E26" s="7">
+        <v>-2.13</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B27" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C27" s="6">
+        <v>57.61</v>
+      </c>
+      <c r="D27" s="6">
+        <v>54.61</v>
+      </c>
+      <c r="E27" s="7">
+        <v>-3</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B28" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C28" s="6">
+        <v>86.28</v>
+      </c>
+      <c r="D28" s="6">
+        <v>87.39</v>
+      </c>
+      <c r="E28" s="8">
+        <v>1.11</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B29" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C29" s="6">
+        <v>-26.15</v>
+      </c>
+      <c r="D29" s="6">
+        <v>-24.89</v>
+      </c>
+      <c r="E29" s="8">
+        <v>1.26</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="B30" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C30" s="6">
+        <v>-11.27</v>
+      </c>
+      <c r="D30" s="6">
+        <v>-9.890000000000001</v>
+      </c>
+      <c r="E30" s="8">
+        <v>1.38</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5">
+      <c r="A31" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B31" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C31" s="6">
+        <v>-6.53</v>
+      </c>
+      <c r="D31" s="6">
+        <v>-7.9</v>
+      </c>
+      <c r="E31" s="7">
+        <v>-1.37</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5">
+      <c r="A32" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B32" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C32" s="6">
+        <v>-28.72</v>
+      </c>
+      <c r="D32" s="6">
+        <v>-28.98</v>
+      </c>
+      <c r="E32" s="7">
+        <v>-0.26</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5">
+      <c r="A33" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B33" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C33" s="6">
+        <v>-6.88</v>
+      </c>
+      <c r="D33" s="6">
+        <v>-7.5</v>
+      </c>
+      <c r="E33" s="7">
+        <v>-0.62</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5">
+      <c r="A34" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B34" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C34" s="6">
+        <v>-1.19</v>
+      </c>
+      <c r="D34" s="6">
+        <v>-4.28</v>
+      </c>
+      <c r="E34" s="7">
+        <v>-3.09</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5">
+      <c r="A35" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B35" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C35" s="6">
+        <v>-11.3</v>
+      </c>
+      <c r="D35" s="6">
+        <v>-9.58</v>
+      </c>
+      <c r="E35" s="8">
+        <v>1.72</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5">
+      <c r="A36" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B36" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C36" s="6">
+        <v>-2.45</v>
+      </c>
+      <c r="D36" s="6">
+        <v>-4.92</v>
+      </c>
+      <c r="E36" s="7">
+        <v>-2.47</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5">
+      <c r="A37" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B37" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C37" s="6">
+        <v>-11.85</v>
+      </c>
+      <c r="D37" s="6">
+        <v>-9.43</v>
+      </c>
+      <c r="E37" s="8">
+        <v>2.42</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5">
+      <c r="A38" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="B38" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C38" s="6">
+        <v>-8.640000000000001</v>
+      </c>
+      <c r="D38" s="6">
+        <v>-6.95</v>
+      </c>
+      <c r="E38" s="8">
+        <v>1.69</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5">
+      <c r="A39" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B39" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C39" s="6">
+        <v>-11.69</v>
+      </c>
+      <c r="D39" s="6">
+        <v>-11.14</v>
+      </c>
+      <c r="E39" s="8">
+        <v>0.55</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5">
+      <c r="A40" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B40" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C40" s="6">
+        <v>-49.39</v>
+      </c>
+      <c r="D40" s="6">
+        <v>-49.61</v>
+      </c>
+      <c r="E40" s="7">
+        <v>-0.22</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5">
+      <c r="A41" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B41" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C41" s="6">
+        <v>-12.38</v>
+      </c>
+      <c r="D41" s="6">
+        <v>-12.08</v>
+      </c>
+      <c r="E41" s="8">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5">
+      <c r="A42" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B42" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C42" s="6">
+        <v>-18.08</v>
+      </c>
+      <c r="D42" s="6">
+        <v>-18.38</v>
+      </c>
+      <c r="E42" s="7">
+        <v>-0.3</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5">
+      <c r="A43" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B43" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C43" s="6">
+        <v>-18.97</v>
+      </c>
+      <c r="D43" s="6">
+        <v>-18.33</v>
+      </c>
+      <c r="E43" s="8">
+        <v>0.64</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5">
+      <c r="A44" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B44" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C44" s="6">
+        <v>-22.92</v>
+      </c>
+      <c r="D44" s="6">
+        <v>-26.36</v>
+      </c>
+      <c r="E44" s="7">
+        <v>-3.44</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5">
+      <c r="A45" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B45" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C45" s="6">
+        <v>-33</v>
+      </c>
+      <c r="D45" s="6">
+        <v>-31.41</v>
+      </c>
+      <c r="E45" s="8">
+        <v>1.59</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5">
+      <c r="A46" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="B46" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C46" s="6">
+        <v>-17.94</v>
+      </c>
+      <c r="D46" s="6">
+        <v>-16.87</v>
+      </c>
+      <c r="E46" s="8">
+        <v>1.07</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5">
+      <c r="A47" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B47" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C47" s="6">
+        <v>375.05</v>
+      </c>
+      <c r="D47" s="6">
+        <v>377.4</v>
+      </c>
+      <c r="E47" s="8">
+        <v>2.35</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5">
+      <c r="A48" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B48" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C48" s="6">
+        <v>44.53</v>
+      </c>
+      <c r="D48" s="6">
+        <v>44.34</v>
+      </c>
+      <c r="E48" s="7">
+        <v>-0.19</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5">
+      <c r="A49" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B49" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C49" s="6">
+        <v>2962</v>
+      </c>
+      <c r="D49" s="6">
+        <v>2972</v>
+      </c>
+      <c r="E49" s="8">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5">
+      <c r="A50" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B50" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C50" s="6">
+        <v>941.85</v>
+      </c>
+      <c r="D50" s="6">
+        <v>938.4</v>
+      </c>
+      <c r="E50" s="7">
+        <v>-3.45</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5">
+      <c r="A51" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B51" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C51" s="6">
+        <v>12.64</v>
+      </c>
+      <c r="D51" s="6">
+        <v>12.74</v>
+      </c>
+      <c r="E51" s="8">
         <v>0.1</v>
       </c>
     </row>
-    <row r="11" spans="1:6">
-      <c r="A11" s="3" t="s">
+    <row r="52" spans="1:5">
+      <c r="A52" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B52" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C52" s="6">
+        <v>10.73</v>
+      </c>
+      <c r="D52" s="6">
+        <v>10.25</v>
+      </c>
+      <c r="E52" s="7">
+        <v>-0.48</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5">
+      <c r="A53" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B53" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C53" s="6">
+        <v>3892.3</v>
+      </c>
+      <c r="D53" s="6">
+        <v>3984.7</v>
+      </c>
+      <c r="E53" s="8">
+        <v>92.40000000000001</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5">
+      <c r="A54" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="B54" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C54" s="6">
+        <v>10710</v>
+      </c>
+      <c r="D54" s="6">
+        <v>10850</v>
+      </c>
+      <c r="E54" s="8">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5">
+      <c r="A55" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B55" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C55" s="6">
+        <v>38.07</v>
+      </c>
+      <c r="D55" s="6">
+        <v>39.9</v>
+      </c>
+      <c r="E55" s="8">
+        <v>1.83</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5">
+      <c r="A56" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B56" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C56" s="6">
+        <v>24.23</v>
+      </c>
+      <c r="D56" s="6">
+        <v>23.83</v>
+      </c>
+      <c r="E56" s="7">
+        <v>-0.4</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5">
+      <c r="A57" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B57" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C57" s="6">
+        <v>28.23</v>
+      </c>
+      <c r="D57" s="6">
+        <v>29.6</v>
+      </c>
+      <c r="E57" s="8">
+        <v>1.37</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5">
+      <c r="A58" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B58" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C58" s="6">
+        <v>35.57</v>
+      </c>
+      <c r="D58" s="6">
+        <v>34.79</v>
+      </c>
+      <c r="E58" s="7">
+        <v>-0.78</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5">
+      <c r="A59" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B11" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C11" s="5">
-        <v>-9.630000000000001</v>
-      </c>
-      <c r="D11" s="5">
-        <v>-10.1</v>
-      </c>
-      <c r="E11" s="7">
-        <v>-0.47</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12" s="3" t="s">
+      <c r="B59" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C59" s="6">
+        <v>32.95</v>
+      </c>
+      <c r="D59" s="6">
+        <v>34.56</v>
+      </c>
+      <c r="E59" s="8">
+        <v>1.61</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5">
+      <c r="A60" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="B12" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C12" s="5">
-        <v>-1.62</v>
-      </c>
-      <c r="D12" s="5">
-        <v>-3.33</v>
-      </c>
-      <c r="E12" s="7">
-        <v>-1.71</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13" s="3" t="s">
+      <c r="B60" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C60" s="6">
+        <v>37.8</v>
+      </c>
+      <c r="D60" s="6">
+        <v>32.56</v>
+      </c>
+      <c r="E60" s="7">
+        <v>-5.24</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5">
+      <c r="A61" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="B13" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C13" s="5">
-        <v>-9.119999999999999</v>
-      </c>
-      <c r="D13" s="5">
-        <v>-10.59</v>
-      </c>
-      <c r="E13" s="7">
-        <v>-1.47</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14" s="3" t="s">
+      <c r="B61" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C61" s="6">
+        <v>29.02</v>
+      </c>
+      <c r="D61" s="6">
+        <v>39.06</v>
+      </c>
+      <c r="E61" s="8">
+        <v>10.04</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5">
+      <c r="A62" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="B14" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C14" s="5">
-        <v>-4.31</v>
-      </c>
-      <c r="D14" s="5">
-        <v>-6.05</v>
-      </c>
-      <c r="E14" s="7">
-        <v>-1.74</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15" s="3" t="s">
+      <c r="B62" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C62" s="6">
+        <v>37.63</v>
+      </c>
+      <c r="D62" s="6">
+        <v>42.45</v>
+      </c>
+      <c r="E62" s="8">
+        <v>4.82</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5">
+      <c r="A63" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B15" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C15" s="5">
-        <v>-5.43</v>
-      </c>
-      <c r="D15" s="5">
-        <v>-3.86</v>
-      </c>
-      <c r="E15" s="6">
-        <v>1.57</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16" s="3" t="s">
+      <c r="B63" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C63" s="6">
+        <v>85</v>
+      </c>
+      <c r="D63" s="6">
+        <v>-42.92</v>
+      </c>
+      <c r="E63" s="7">
+        <v>-127.92</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5">
+      <c r="A64" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B16" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C16" s="5">
-        <v>-5.64</v>
-      </c>
-      <c r="D16" s="5">
-        <v>-7.34</v>
-      </c>
-      <c r="E16" s="7">
-        <v>-1.7</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5">
-      <c r="A17" s="3" t="s">
+      <c r="B64" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C64" s="6">
+        <v>13.7</v>
+      </c>
+      <c r="D64" s="6">
+        <v>-24.55</v>
+      </c>
+      <c r="E64" s="7">
+        <v>-38.25</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5">
+      <c r="A65" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B17" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C17" s="5">
-        <v>-3.97</v>
-      </c>
-      <c r="D17" s="5">
-        <v>-6.46</v>
-      </c>
-      <c r="E17" s="7">
-        <v>-2.49</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5">
-      <c r="A18" s="3" t="s">
+      <c r="B65" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C65" s="6">
+        <v>60.86</v>
+      </c>
+      <c r="D65" s="6">
+        <v>-70.31999999999999</v>
+      </c>
+      <c r="E65" s="7">
+        <v>-131.18</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5">
+      <c r="A66" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B18" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C18" s="5">
-        <v>-6.18</v>
-      </c>
-      <c r="D18" s="5">
-        <v>-4.09</v>
-      </c>
-      <c r="E18" s="6">
-        <v>2.09</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5">
-      <c r="A19" s="3" t="s">
+      <c r="B66" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C66" s="6">
+        <v>68.70999999999999</v>
+      </c>
+      <c r="D66" s="6">
+        <v>21.15</v>
+      </c>
+      <c r="E66" s="7">
+        <v>-47.56</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5">
+      <c r="A67" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B19" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C19" s="5">
-        <v>-10.81</v>
-      </c>
-      <c r="D19" s="5">
-        <v>-10.48</v>
-      </c>
-      <c r="E19" s="6">
-        <v>0.33</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5">
-      <c r="A20" s="3" t="s">
+      <c r="B67" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C67" s="6">
+        <v>29.55</v>
+      </c>
+      <c r="D67" s="6">
+        <v>-5.45</v>
+      </c>
+      <c r="E67" s="7">
+        <v>-35</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5">
+      <c r="A68" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="B20" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C20" s="5">
-        <v>-5.62</v>
-      </c>
-      <c r="D20" s="5">
-        <v>-5.79</v>
-      </c>
-      <c r="E20" s="7">
-        <v>-0.17</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5">
-      <c r="A21" s="3" t="s">
+      <c r="B68" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C68" s="6">
+        <v>30.84</v>
+      </c>
+      <c r="D68" s="6">
+        <v>117.53</v>
+      </c>
+      <c r="E68" s="8">
+        <v>86.69</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5">
+      <c r="A69" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="B21" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C21" s="5">
-        <v>-2.11</v>
-      </c>
-      <c r="D21" s="5">
-        <v>-2.86</v>
-      </c>
-      <c r="E21" s="7">
-        <v>-0.75</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5">
-      <c r="A22" s="3" t="s">
+      <c r="B69" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C69" s="6">
+        <v>-7.38</v>
+      </c>
+      <c r="D69" s="6">
+        <v>16.82</v>
+      </c>
+      <c r="E69" s="8">
+        <v>24.2</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5">
+      <c r="A70" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="B22" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C22" s="5">
-        <v>-1.78</v>
-      </c>
-      <c r="D22" s="5">
-        <v>-3.13</v>
-      </c>
-      <c r="E22" s="7">
-        <v>-1.35</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5">
-      <c r="A23" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B23" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C23" s="5">
-        <v>32.84</v>
-      </c>
-      <c r="D23" s="5">
-        <v>34.47</v>
-      </c>
-      <c r="E23" s="6">
-        <v>1.63</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5">
-      <c r="A24" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B24" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C24" s="5">
-        <v>-46.95</v>
-      </c>
-      <c r="D24" s="5">
-        <v>-47.55</v>
-      </c>
-      <c r="E24" s="7">
-        <v>-0.6</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5">
-      <c r="A25" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B25" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C25" s="5">
-        <v>10.2</v>
-      </c>
-      <c r="D25" s="5">
-        <v>7.83</v>
-      </c>
-      <c r="E25" s="7">
-        <v>-2.37</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5">
-      <c r="A26" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="B26" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C26" s="5">
-        <v>26.31</v>
-      </c>
-      <c r="D26" s="5">
-        <v>26.62</v>
-      </c>
-      <c r="E26" s="6">
-        <v>0.31</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5">
-      <c r="A27" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="B27" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C27" s="5">
-        <v>49.19</v>
-      </c>
-      <c r="D27" s="5">
-        <v>57.61</v>
-      </c>
-      <c r="E27" s="6">
-        <v>8.42</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5">
-      <c r="A28" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="B28" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C28" s="5">
-        <v>82.91</v>
-      </c>
-      <c r="D28" s="5">
-        <v>86.28</v>
-      </c>
-      <c r="E28" s="6">
-        <v>3.37</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5">
-      <c r="A29" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="B29" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C29" s="5">
-        <v>-26.25</v>
-      </c>
-      <c r="D29" s="5">
-        <v>-26.15</v>
-      </c>
-      <c r="E29" s="6">
-        <v>0.1</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5">
-      <c r="A30" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="B30" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C30" s="5">
-        <v>-9.76</v>
-      </c>
-      <c r="D30" s="5">
-        <v>-11.27</v>
-      </c>
-      <c r="E30" s="7">
-        <v>-1.51</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5">
-      <c r="A31" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B31" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C31" s="5">
-        <v>-3.14</v>
-      </c>
-      <c r="D31" s="5">
-        <v>-6.53</v>
-      </c>
-      <c r="E31" s="7">
-        <v>-3.39</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5">
-      <c r="A32" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B32" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C32" s="5">
-        <v>-25.15</v>
-      </c>
-      <c r="D32" s="5">
-        <v>-28.72</v>
-      </c>
-      <c r="E32" s="7">
-        <v>-3.57</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5">
-      <c r="A33" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B33" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C33" s="5">
-        <v>-3.39</v>
-      </c>
-      <c r="D33" s="5">
-        <v>-6.88</v>
-      </c>
-      <c r="E33" s="7">
-        <v>-3.49</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5">
-      <c r="A34" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="B34" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C34" s="5">
-        <v>-0.78</v>
-      </c>
-      <c r="D34" s="5">
-        <v>-1.19</v>
-      </c>
-      <c r="E34" s="7">
-        <v>-0.41</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5">
-      <c r="A35" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="B35" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C35" s="5">
-        <v>-10.57</v>
-      </c>
-      <c r="D35" s="5">
-        <v>-11.3</v>
-      </c>
-      <c r="E35" s="7">
-        <v>-0.73</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5">
-      <c r="A36" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="B36" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C36" s="5">
-        <v>-0.27</v>
-      </c>
-      <c r="D36" s="5">
-        <v>-2.45</v>
-      </c>
-      <c r="E36" s="7">
-        <v>-2.18</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5">
-      <c r="A37" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="B37" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C37" s="5">
-        <v>-10.83</v>
-      </c>
-      <c r="D37" s="5">
-        <v>-11.85</v>
-      </c>
-      <c r="E37" s="7">
-        <v>-1.02</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5">
-      <c r="A38" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="B38" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C38" s="5">
-        <v>-5.03</v>
-      </c>
-      <c r="D38" s="5">
-        <v>-8.640000000000001</v>
-      </c>
-      <c r="E38" s="7">
-        <v>-3.61</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5">
-      <c r="A39" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B39" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C39" s="5">
-        <v>-10.38</v>
-      </c>
-      <c r="D39" s="5">
-        <v>-11.69</v>
-      </c>
-      <c r="E39" s="7">
-        <v>-1.31</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5">
-      <c r="A40" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B40" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C40" s="5">
-        <v>-47.36</v>
-      </c>
-      <c r="D40" s="5">
-        <v>-49.39</v>
-      </c>
-      <c r="E40" s="7">
-        <v>-2.03</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5">
-      <c r="A41" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B41" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C41" s="5">
-        <v>-9.42</v>
-      </c>
-      <c r="D41" s="5">
-        <v>-12.38</v>
-      </c>
-      <c r="E41" s="7">
-        <v>-2.96</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5">
-      <c r="A42" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="B42" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C42" s="5">
-        <v>-16.99</v>
-      </c>
-      <c r="D42" s="5">
-        <v>-18.97</v>
-      </c>
-      <c r="E42" s="7">
-        <v>-1.98</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5">
-      <c r="A43" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="B43" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C43" s="5">
-        <v>-21.55</v>
-      </c>
-      <c r="D43" s="5">
-        <v>-22.92</v>
-      </c>
-      <c r="E43" s="7">
-        <v>-1.37</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5">
-      <c r="A44" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="B44" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C44" s="5">
-        <v>-31.9</v>
-      </c>
-      <c r="D44" s="5">
-        <v>-33</v>
-      </c>
-      <c r="E44" s="7">
-        <v>-1.1</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5">
-      <c r="A45" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="B45" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C45" s="5">
-        <v>-16.06</v>
-      </c>
-      <c r="D45" s="5">
-        <v>-17.94</v>
-      </c>
-      <c r="E45" s="7">
-        <v>-1.88</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5">
-      <c r="A46" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B46" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C46" s="5">
-        <v>380.6</v>
-      </c>
-      <c r="D46" s="5">
-        <v>375.05</v>
-      </c>
-      <c r="E46" s="7">
-        <v>-5.55</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5">
-      <c r="A47" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B47" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C47" s="5">
-        <v>46.32</v>
-      </c>
-      <c r="D47" s="5">
-        <v>44.53</v>
-      </c>
-      <c r="E47" s="7">
-        <v>-1.79</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5">
-      <c r="A48" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B48" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C48" s="5">
-        <v>3061.9</v>
-      </c>
-      <c r="D48" s="5">
-        <v>2962</v>
-      </c>
-      <c r="E48" s="7">
-        <v>-99.90000000000001</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5">
-      <c r="A49" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="B49" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C49" s="5">
-        <v>941.8</v>
-      </c>
-      <c r="D49" s="5">
-        <v>941.85</v>
-      </c>
-      <c r="E49" s="6">
-        <v>0.05</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5">
-      <c r="A50" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="B50" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C50" s="5">
-        <v>12.95</v>
-      </c>
-      <c r="D50" s="5">
-        <v>12.64</v>
-      </c>
-      <c r="E50" s="7">
-        <v>-0.31</v>
-      </c>
-    </row>
-    <row r="51" spans="1:5">
-      <c r="A51" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="B51" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C51" s="5">
-        <v>10.92</v>
-      </c>
-      <c r="D51" s="5">
-        <v>10.73</v>
-      </c>
-      <c r="E51" s="7">
-        <v>-0.19</v>
-      </c>
-    </row>
-    <row r="52" spans="1:5">
-      <c r="A52" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="B52" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C52" s="5">
-        <v>3956.5</v>
-      </c>
-      <c r="D52" s="5">
-        <v>3892.3</v>
-      </c>
-      <c r="E52" s="7">
-        <v>-64.2</v>
-      </c>
-    </row>
-    <row r="53" spans="1:5">
-      <c r="A53" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="B53" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C53" s="5">
-        <v>10956</v>
-      </c>
-      <c r="D53" s="5">
-        <v>10710</v>
-      </c>
-      <c r="E53" s="7">
-        <v>-246</v>
-      </c>
-    </row>
-    <row r="54" spans="1:5">
-      <c r="A54" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B54" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C54" s="5">
-        <v>40.79</v>
-      </c>
-      <c r="D54" s="5">
-        <v>38.07</v>
-      </c>
-      <c r="E54" s="7">
-        <v>-2.72</v>
-      </c>
-    </row>
-    <row r="55" spans="1:5">
-      <c r="A55" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B55" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C55" s="5">
-        <v>28.49</v>
-      </c>
-      <c r="D55" s="5">
-        <v>24.23</v>
-      </c>
-      <c r="E55" s="7">
-        <v>-4.26</v>
-      </c>
-    </row>
-    <row r="56" spans="1:5">
-      <c r="A56" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B56" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C56" s="5">
-        <v>34.45</v>
-      </c>
-      <c r="D56" s="5">
-        <v>28.23</v>
-      </c>
-      <c r="E56" s="7">
-        <v>-6.22</v>
-      </c>
-    </row>
-    <row r="57" spans="1:5">
-      <c r="A57" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="B57" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C57" s="5">
-        <v>35.55</v>
-      </c>
-      <c r="D57" s="5">
-        <v>35.57</v>
-      </c>
-      <c r="E57" s="6">
-        <v>0.02</v>
-      </c>
-    </row>
-    <row r="58" spans="1:5">
-      <c r="A58" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="B58" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C58" s="5">
-        <v>35.45</v>
-      </c>
-      <c r="D58" s="5">
-        <v>32.95</v>
-      </c>
-      <c r="E58" s="7">
-        <v>-2.5</v>
-      </c>
-    </row>
-    <row r="59" spans="1:5">
-      <c r="A59" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="B59" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C59" s="5">
-        <v>40.18</v>
-      </c>
-      <c r="D59" s="5">
-        <v>37.8</v>
-      </c>
-      <c r="E59" s="7">
-        <v>-2.38</v>
-      </c>
-    </row>
-    <row r="60" spans="1:5">
-      <c r="A60" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="B60" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C60" s="5">
-        <v>32.47</v>
-      </c>
-      <c r="D60" s="5">
-        <v>29.02</v>
-      </c>
-      <c r="E60" s="7">
-        <v>-3.45</v>
-      </c>
-    </row>
-    <row r="61" spans="1:5">
-      <c r="A61" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="B61" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C61" s="5">
-        <v>43.59</v>
-      </c>
-      <c r="D61" s="5">
-        <v>37.63</v>
-      </c>
-      <c r="E61" s="7">
-        <v>-5.96</v>
-      </c>
-    </row>
-    <row r="62" spans="1:5">
-      <c r="A62" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B62" s="3" t="s">
+      <c r="B70" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="C62" s="5">
-        <v>26.92</v>
-      </c>
-      <c r="D62" s="5">
-        <v>85</v>
-      </c>
-      <c r="E62" s="6">
-        <v>58.08</v>
-      </c>
-    </row>
-    <row r="63" spans="1:5">
-      <c r="A63" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B63" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C63" s="5">
-        <v>-22.58</v>
-      </c>
-      <c r="D63" s="5">
-        <v>13.7</v>
-      </c>
-      <c r="E63" s="6">
-        <v>36.28</v>
-      </c>
-    </row>
-    <row r="64" spans="1:5">
-      <c r="A64" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B64" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C64" s="5">
-        <v>-49.56</v>
-      </c>
-      <c r="D64" s="5">
-        <v>60.86</v>
-      </c>
-      <c r="E64" s="6">
-        <v>110.42</v>
-      </c>
-    </row>
-    <row r="65" spans="1:5">
-      <c r="A65" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="B65" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C65" s="5">
-        <v>24.58</v>
-      </c>
-      <c r="D65" s="5">
-        <v>68.70999999999999</v>
-      </c>
-      <c r="E65" s="6">
-        <v>44.13</v>
-      </c>
-    </row>
-    <row r="66" spans="1:5">
-      <c r="A66" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="B66" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C66" s="5">
-        <v>38.55</v>
-      </c>
-      <c r="D66" s="5">
-        <v>29.55</v>
-      </c>
-      <c r="E66" s="7">
-        <v>-9</v>
-      </c>
-    </row>
-    <row r="67" spans="1:5">
-      <c r="A67" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="B67" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C67" s="5">
-        <v>24.38</v>
-      </c>
-      <c r="D67" s="5">
-        <v>30.84</v>
-      </c>
-      <c r="E67" s="6">
-        <v>6.46</v>
-      </c>
-    </row>
-    <row r="68" spans="1:5">
-      <c r="A68" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="B68" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C68" s="5">
-        <v>141.95</v>
-      </c>
-      <c r="D68" s="5">
-        <v>-7.38</v>
-      </c>
-      <c r="E68" s="7">
-        <v>-149.33</v>
-      </c>
-    </row>
-    <row r="69" spans="1:5">
-      <c r="A69" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="B69" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C69" s="5">
-        <v>-8.699999999999999</v>
-      </c>
-      <c r="D69" s="5">
+      <c r="C70" s="6">
         <v>106.59</v>
       </c>
-      <c r="E69" s="6">
-        <v>115.29</v>
+      <c r="D70" s="6">
+        <v>6.48</v>
+      </c>
+      <c r="E70" s="7">
+        <v>-100.11</v>
       </c>
     </row>
   </sheetData>
@@ -3076,60 +3156,60 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="28" customHeight="1">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="8" t="s">
-        <v>57</v>
-      </c>
-      <c r="C1" s="8" t="s">
-        <v>58</v>
-      </c>
-      <c r="D1" s="8" t="s">
-        <v>59</v>
-      </c>
-      <c r="E1" s="8" t="s">
-        <v>60</v>
-      </c>
-      <c r="F1" s="8" t="s">
-        <v>61</v>
-      </c>
-      <c r="G1" s="8" t="s">
-        <v>62</v>
-      </c>
-      <c r="H1" s="8" t="s">
-        <v>63</v>
-      </c>
-      <c r="I1" s="8" t="s">
-        <v>64</v>
+      <c r="B1" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="C1" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="D1" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="E1" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="F1" s="9" t="s">
+        <v>70</v>
+      </c>
+      <c r="G1" s="9" t="s">
+        <v>71</v>
+      </c>
+      <c r="H1" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="I1" s="9" t="s">
+        <v>73</v>
       </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="9" t="s">
+      <c r="A2" s="10" t="s">
         <v>45</v>
       </c>
-      <c r="B2" s="10">
+      <c r="B2" s="11">
         <v>40.44</v>
       </c>
-      <c r="C2" s="11">
+      <c r="C2" s="12">
         <v>8</v>
       </c>
-      <c r="D2" s="10">
-        <v>32.9</v>
-      </c>
-      <c r="E2" s="10">
+      <c r="D2" s="11">
+        <v>34.6</v>
+      </c>
+      <c r="E2" s="11">
         <v>20</v>
       </c>
-      <c r="F2" s="10">
-        <v>-8.199999999999999</v>
-      </c>
-      <c r="G2" s="10">
-        <v>-9.699999999999999</v>
-      </c>
-      <c r="H2" s="10">
+      <c r="F2" s="11">
+        <v>-8.5</v>
+      </c>
+      <c r="G2" s="11">
+        <v>-9.9</v>
+      </c>
+      <c r="H2" s="11">
         <v>56.1</v>
       </c>
-      <c r="I2" s="10">
+      <c r="I2" s="11">
         <v>10</v>
       </c>
     </row>
@@ -3231,55 +3311,55 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8">
-      <c r="A1" s="12" t="s">
+      <c r="A1" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="B1" s="12" t="s">
+      <c r="B1" s="13" t="s">
         <v>43</v>
       </c>
-      <c r="C1" s="12" t="s">
+      <c r="C1" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="D1" s="12" t="s">
+      <c r="D1" s="13" t="s">
         <v>39</v>
       </c>
-      <c r="E1" s="12" t="s">
+      <c r="E1" s="13" t="s">
         <v>44</v>
       </c>
-      <c r="F1" s="12" t="s">
+      <c r="F1" s="13" t="s">
         <v>41</v>
       </c>
-      <c r="G1" s="12" t="s">
+      <c r="G1" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="H1" s="12" t="s">
+      <c r="H1" s="13" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="2" spans="1:8">
-      <c r="A2" s="13">
-        <v>0.2736</v>
-      </c>
-      <c r="B2" s="13">
-        <v>0.1587</v>
-      </c>
-      <c r="C2" s="13">
-        <v>0.1488</v>
-      </c>
-      <c r="D2" s="13">
-        <v>0.1257</v>
-      </c>
-      <c r="E2" s="13">
-        <v>0.07919999999999999</v>
-      </c>
-      <c r="F2" s="13">
-        <v>0.0209</v>
-      </c>
-      <c r="G2" s="13">
-        <v>-0.2886</v>
-      </c>
-      <c r="H2" s="13">
-        <v>-0.2984</v>
+      <c r="A2" s="14">
+        <v>0.2776</v>
+      </c>
+      <c r="B2" s="14">
+        <v>0.1561</v>
+      </c>
+      <c r="C2" s="14">
+        <v>0.1429</v>
+      </c>
+      <c r="D2" s="14">
+        <v>0.1333</v>
+      </c>
+      <c r="E2" s="14">
+        <v>0.08259999999999999</v>
+      </c>
+      <c r="F2" s="14">
+        <v>0.0198</v>
+      </c>
+      <c r="G2" s="14">
+        <v>-0.2956</v>
+      </c>
+      <c r="H2" s="14">
+        <v>-0.3166</v>
       </c>
     </row>
   </sheetData>

--- a/BIRLA_GROUP_Technical_Metrics.xlsx
+++ b/BIRLA_GROUP_Technical_Metrics.xlsx
@@ -193,16 +193,16 @@
     <t>RSI Oversold Recovery</t>
   </si>
   <si>
-    <t>29.0 → 39.1</t>
+    <t>23.8 → 32.5</t>
   </si>
   <si>
     <t>🟢 BULLISH</t>
   </si>
   <si>
-    <t>29.0</t>
-  </si>
-  <si>
-    <t>39.1</t>
+    <t>23.8</t>
+  </si>
+  <si>
+    <t>32.5</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -927,10 +927,10 @@
         <v>45</v>
       </c>
       <c r="C2">
-        <v>377.4</v>
+        <v>378.9</v>
       </c>
       <c r="D2">
-        <v>0.63</v>
+        <v>0.4</v>
       </c>
       <c r="E2">
         <v>424.7</v>
@@ -939,25 +939,25 @@
         <v>292.25</v>
       </c>
       <c r="G2">
-        <v>-11.14</v>
+        <v>-10.78</v>
       </c>
       <c r="H2">
-        <v>29.14</v>
+        <v>29.65</v>
       </c>
       <c r="I2">
-        <v>-3.23</v>
+        <v>-0.99</v>
       </c>
       <c r="J2">
-        <v>-4.95</v>
+        <v>-5.75</v>
       </c>
       <c r="K2">
-        <v>-7.9</v>
+        <v>-6.54</v>
       </c>
       <c r="L2">
-        <v>30.21</v>
+        <v>29.6</v>
       </c>
       <c r="M2">
-        <v>27.76</v>
+        <v>28.01</v>
       </c>
       <c r="N2">
         <v>74</v>
@@ -966,19 +966,19 @@
         <v>73</v>
       </c>
       <c r="P2">
-        <v>378.75</v>
+        <v>377.99</v>
       </c>
       <c r="Q2">
-        <v>391.85</v>
+        <v>390.55</v>
       </c>
       <c r="R2">
-        <v>400.45</v>
+        <v>400.15</v>
       </c>
       <c r="S2">
-        <v>364.68</v>
+        <v>364.84</v>
       </c>
       <c r="T2">
-        <v>3.49</v>
+        <v>3.86</v>
       </c>
       <c r="U2" t="s">
         <v>46</v>
@@ -993,34 +993,34 @@
         <v>2</v>
       </c>
       <c r="Y2">
-        <v>39.9</v>
+        <v>41.09</v>
       </c>
       <c r="Z2">
-        <v>-6.07</v>
+        <v>-6.19</v>
       </c>
       <c r="AA2">
-        <v>-4.13</v>
+        <v>-4.54</v>
       </c>
       <c r="AB2">
-        <v>-1.94</v>
+        <v>-1.65</v>
       </c>
       <c r="AC2">
-        <v>25.6</v>
+        <v>23.43</v>
       </c>
       <c r="AD2">
-        <v>26.11</v>
+        <v>24.38</v>
       </c>
       <c r="AE2">
-        <v>9.41</v>
+        <v>9.210000000000001</v>
       </c>
       <c r="AF2">
-        <v>-42.92</v>
+        <v>82.95</v>
       </c>
       <c r="AG2">
-        <v>413.65</v>
+        <v>412.17</v>
       </c>
       <c r="AH2">
-        <v>370.05</v>
+        <v>368.93</v>
       </c>
       <c r="AI2">
         <v>372.91</v>
@@ -1029,7 +1029,7 @@
         <v>48</v>
       </c>
       <c r="AK2">
-        <v>32.21</v>
+        <v>34.07</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1040,10 +1040,10 @@
         <v>45</v>
       </c>
       <c r="C3">
-        <v>44.34</v>
+        <v>45.68</v>
       </c>
       <c r="D3">
-        <v>-0.43</v>
+        <v>3.02</v>
       </c>
       <c r="E3">
         <v>87.98999999999999</v>
@@ -1052,46 +1052,46 @@
         <v>44.34</v>
       </c>
       <c r="G3">
-        <v>-49.61</v>
+        <v>-48.09</v>
       </c>
       <c r="H3">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="I3">
-        <v>-9.77</v>
+        <v>-4.01</v>
       </c>
       <c r="J3">
-        <v>-12.15</v>
+        <v>-9.380000000000001</v>
       </c>
       <c r="K3">
-        <v>-28.98</v>
+        <v>-23.39</v>
       </c>
       <c r="L3">
-        <v>-47.84</v>
+        <v>-45.93</v>
       </c>
       <c r="M3">
-        <v>-29.56</v>
+        <v>-28.28</v>
       </c>
       <c r="N3">
         <v>13</v>
       </c>
       <c r="O3">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="P3">
-        <v>45.8</v>
+        <v>45.42</v>
       </c>
       <c r="Q3">
-        <v>49.24</v>
+        <v>48.88</v>
       </c>
       <c r="R3">
-        <v>53.63</v>
+        <v>53.42</v>
       </c>
       <c r="S3">
-        <v>62.11</v>
+        <v>61.97</v>
       </c>
       <c r="T3">
-        <v>-28.61</v>
+        <v>-26.29</v>
       </c>
       <c r="U3" t="s">
         <v>46</v>
@@ -1106,34 +1106,34 @@
         <v>0</v>
       </c>
       <c r="Y3">
-        <v>23.83</v>
+        <v>32.45</v>
       </c>
       <c r="Z3">
-        <v>-2.28</v>
+        <v>-2.25</v>
       </c>
       <c r="AA3">
-        <v>-1.96</v>
+        <v>-2.02</v>
       </c>
       <c r="AB3">
-        <v>-0.32</v>
+        <v>-0.23</v>
       </c>
       <c r="AC3">
-        <v>1.85</v>
+        <v>21.15</v>
       </c>
       <c r="AD3">
-        <v>5.07</v>
+        <v>8.289999999999999</v>
       </c>
       <c r="AE3">
-        <v>1.55</v>
+        <v>1.66</v>
       </c>
       <c r="AF3">
-        <v>-24.55</v>
+        <v>113.19</v>
       </c>
       <c r="AG3">
-        <v>54.23</v>
+        <v>53.78</v>
       </c>
       <c r="AH3">
-        <v>44.26</v>
+        <v>43.97</v>
       </c>
       <c r="AI3">
         <v>49.46</v>
@@ -1142,7 +1142,7 @@
         <v>49</v>
       </c>
       <c r="AK3">
-        <v>55.19</v>
+        <v>50.43</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1153,10 +1153,10 @@
         <v>45</v>
       </c>
       <c r="C4">
-        <v>2972</v>
+        <v>2969</v>
       </c>
       <c r="D4">
-        <v>0.34</v>
+        <v>-0.1</v>
       </c>
       <c r="E4">
         <v>3380.5</v>
@@ -1165,46 +1165,46 @@
         <v>2531.1</v>
       </c>
       <c r="G4">
-        <v>-12.08</v>
+        <v>-12.17</v>
       </c>
       <c r="H4">
-        <v>17.42</v>
+        <v>17.3</v>
       </c>
       <c r="I4">
-        <v>-6.86</v>
+        <v>-5.75</v>
       </c>
       <c r="J4">
-        <v>-9.800000000000001</v>
+        <v>-10.3</v>
       </c>
       <c r="K4">
-        <v>-7.5</v>
+        <v>-6.95</v>
       </c>
       <c r="L4">
-        <v>8.19</v>
+        <v>7.69</v>
       </c>
       <c r="M4">
-        <v>13.33</v>
+        <v>13.7</v>
       </c>
       <c r="N4">
         <v>50</v>
       </c>
       <c r="O4">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="P4">
-        <v>3049.18</v>
+        <v>3012.98</v>
       </c>
       <c r="Q4">
-        <v>3182.92</v>
+        <v>3165.27</v>
       </c>
       <c r="R4">
-        <v>3221.8</v>
+        <v>3219.39</v>
       </c>
       <c r="S4">
-        <v>2977.59</v>
+        <v>2978.44</v>
       </c>
       <c r="T4">
-        <v>-0.19</v>
+        <v>-0.32</v>
       </c>
       <c r="U4" t="s">
         <v>46</v>
@@ -1219,43 +1219,43 @@
         <v>1</v>
       </c>
       <c r="Y4">
-        <v>29.6</v>
+        <v>29.42</v>
       </c>
       <c r="Z4">
-        <v>-61.38</v>
+        <v>-67.83</v>
       </c>
       <c r="AA4">
-        <v>-35.33</v>
+        <v>-41.83</v>
       </c>
       <c r="AB4">
-        <v>-26.04</v>
+        <v>-26</v>
       </c>
       <c r="AC4">
-        <v>2.62</v>
+        <v>4.89</v>
       </c>
       <c r="AD4">
-        <v>4.37</v>
+        <v>2.84</v>
       </c>
       <c r="AE4">
-        <v>63.52</v>
+        <v>62.77</v>
       </c>
       <c r="AF4">
-        <v>-70.31999999999999</v>
+        <v>-57.64</v>
       </c>
       <c r="AG4">
-        <v>3393.93</v>
+        <v>3386.12</v>
       </c>
       <c r="AH4">
-        <v>2971.92</v>
+        <v>2944.43</v>
       </c>
       <c r="AI4">
-        <v>3183.3</v>
+        <v>3150.47</v>
       </c>
       <c r="AJ4" t="s">
         <v>49</v>
       </c>
       <c r="AK4">
-        <v>51.84</v>
+        <v>55.85</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1266,10 +1266,10 @@
         <v>45</v>
       </c>
       <c r="C5">
-        <v>938.4</v>
+        <v>940.5</v>
       </c>
       <c r="D5">
-        <v>-0.37</v>
+        <v>0.22</v>
       </c>
       <c r="E5">
         <v>1149.7</v>
@@ -1278,46 +1278,46 @@
         <v>760.1</v>
       </c>
       <c r="G5">
-        <v>-18.38</v>
+        <v>-18.2</v>
       </c>
       <c r="H5">
-        <v>23.46</v>
+        <v>23.73</v>
       </c>
       <c r="I5">
-        <v>-3.95</v>
+        <v>-1.61</v>
       </c>
       <c r="J5">
-        <v>-7.06</v>
+        <v>-6.88</v>
       </c>
       <c r="K5">
-        <v>-4.28</v>
+        <v>-2.99</v>
       </c>
       <c r="L5">
-        <v>24.49</v>
+        <v>23.43</v>
       </c>
       <c r="M5">
-        <v>14.29</v>
+        <v>15.26</v>
       </c>
       <c r="N5">
         <v>62</v>
       </c>
       <c r="O5">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="P5">
-        <v>946.63</v>
+        <v>943.55</v>
       </c>
       <c r="Q5">
-        <v>979.85</v>
+        <v>976.3200000000001</v>
       </c>
       <c r="R5">
-        <v>1003.91</v>
+        <v>1003.86</v>
       </c>
       <c r="S5">
-        <v>981.61</v>
+        <v>982.13</v>
       </c>
       <c r="T5">
-        <v>-4.4</v>
+        <v>-4.24</v>
       </c>
       <c r="U5" t="s">
         <v>46</v>
@@ -1332,34 +1332,34 @@
         <v>1</v>
       </c>
       <c r="Y5">
-        <v>34.79</v>
+        <v>35.72</v>
       </c>
       <c r="Z5">
-        <v>-17.9</v>
+        <v>-18.45</v>
       </c>
       <c r="AA5">
-        <v>-13.38</v>
+        <v>-14.39</v>
       </c>
       <c r="AB5">
-        <v>-4.53</v>
+        <v>-4.05</v>
       </c>
       <c r="AC5">
-        <v>6.64</v>
+        <v>5.89</v>
       </c>
       <c r="AD5">
-        <v>12.75</v>
+        <v>8.58</v>
       </c>
       <c r="AE5">
-        <v>21.91</v>
+        <v>21.44</v>
       </c>
       <c r="AF5">
-        <v>21.15</v>
+        <v>-20.24</v>
       </c>
       <c r="AG5">
-        <v>1031.87</v>
+        <v>1029.01</v>
       </c>
       <c r="AH5">
-        <v>927.8200000000001</v>
+        <v>923.64</v>
       </c>
       <c r="AI5">
         <v>1000.57</v>
@@ -1368,7 +1368,7 @@
         <v>49</v>
       </c>
       <c r="AK5">
-        <v>31.26</v>
+        <v>32.54</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1379,58 +1379,58 @@
         <v>45</v>
       </c>
       <c r="C6">
-        <v>12.74</v>
+        <v>13.21</v>
       </c>
       <c r="D6">
-        <v>0.79</v>
+        <v>3.69</v>
       </c>
       <c r="E6">
         <v>15.6</v>
       </c>
       <c r="F6">
-        <v>8.130000000000001</v>
+        <v>8.359999999999999</v>
       </c>
       <c r="G6">
-        <v>-18.33</v>
+        <v>-15.32</v>
       </c>
       <c r="H6">
-        <v>56.7</v>
+        <v>58.01</v>
       </c>
       <c r="I6">
-        <v>-10.66</v>
+        <v>-1.93</v>
       </c>
       <c r="J6">
-        <v>-12.32</v>
+        <v>-8.77</v>
       </c>
       <c r="K6">
-        <v>-9.58</v>
+        <v>-4.62</v>
       </c>
       <c r="L6">
-        <v>54.61</v>
+        <v>62.48</v>
       </c>
       <c r="M6">
-        <v>1.98</v>
+        <v>2.9</v>
       </c>
       <c r="N6">
         <v>87</v>
       </c>
       <c r="O6">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="P6">
-        <v>13.07</v>
+        <v>13.02</v>
       </c>
       <c r="Q6">
-        <v>14.23</v>
+        <v>14.14</v>
       </c>
       <c r="R6">
         <v>13.9</v>
       </c>
       <c r="S6">
-        <v>12.25</v>
+        <v>12.26</v>
       </c>
       <c r="T6">
-        <v>4</v>
+        <v>7.75</v>
       </c>
       <c r="U6" t="s">
         <v>47</v>
@@ -1445,34 +1445,34 @@
         <v>3</v>
       </c>
       <c r="Y6">
-        <v>34.56</v>
+        <v>41.63</v>
       </c>
       <c r="Z6">
-        <v>-0.34</v>
+        <v>-0.35</v>
       </c>
       <c r="AA6">
-        <v>-0.12</v>
+        <v>-0.16</v>
       </c>
       <c r="AB6">
-        <v>-0.22</v>
+        <v>-0.18</v>
       </c>
       <c r="AC6">
-        <v>2.78</v>
+        <v>17.8</v>
       </c>
       <c r="AD6">
-        <v>2.05</v>
+        <v>7.42</v>
       </c>
       <c r="AE6">
-        <v>0.51</v>
+        <v>0.5</v>
       </c>
       <c r="AF6">
-        <v>-5.45</v>
+        <v>-30.3</v>
       </c>
       <c r="AG6">
-        <v>15.97</v>
+        <v>15.9</v>
       </c>
       <c r="AH6">
-        <v>12.49</v>
+        <v>12.39</v>
       </c>
       <c r="AI6">
         <v>14.25</v>
@@ -1481,7 +1481,7 @@
         <v>49</v>
       </c>
       <c r="AK6">
-        <v>41.8</v>
+        <v>41.33</v>
       </c>
     </row>
     <row r="7" spans="1:37">
@@ -1492,10 +1492,10 @@
         <v>45</v>
       </c>
       <c r="C7">
-        <v>10.25</v>
+        <v>10.76</v>
       </c>
       <c r="D7">
-        <v>-4.47</v>
+        <v>4.98</v>
       </c>
       <c r="E7">
         <v>13.92</v>
@@ -1504,46 +1504,46 @@
         <v>4.69</v>
       </c>
       <c r="G7">
-        <v>-26.36</v>
+        <v>-22.7</v>
       </c>
       <c r="H7">
-        <v>118.55</v>
+        <v>129.42</v>
       </c>
       <c r="I7">
-        <v>-11.41</v>
+        <v>-2.36</v>
       </c>
       <c r="J7">
-        <v>-9.050000000000001</v>
+        <v>-2.62</v>
       </c>
       <c r="K7">
-        <v>-4.92</v>
+        <v>1.8</v>
       </c>
       <c r="L7">
-        <v>87.39</v>
+        <v>97.79000000000001</v>
       </c>
       <c r="M7">
-        <v>-31.66</v>
+        <v>-30.73</v>
       </c>
       <c r="N7">
         <v>99</v>
       </c>
       <c r="O7">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="P7">
-        <v>10.75</v>
+        <v>10.7</v>
       </c>
       <c r="Q7">
-        <v>11.46</v>
+        <v>11.45</v>
       </c>
       <c r="R7">
-        <v>11.7</v>
+        <v>11.68</v>
       </c>
       <c r="S7">
-        <v>10.82</v>
+        <v>10.83</v>
       </c>
       <c r="T7">
-        <v>-5.29</v>
+        <v>-0.66</v>
       </c>
       <c r="U7" t="s">
         <v>46</v>
@@ -1558,43 +1558,43 @@
         <v>1</v>
       </c>
       <c r="Y7">
-        <v>32.56</v>
+        <v>41.8</v>
       </c>
       <c r="Z7">
-        <v>-0.25</v>
+        <v>-0.26</v>
       </c>
       <c r="AA7">
-        <v>-0.1</v>
+        <v>-0.13</v>
       </c>
       <c r="AB7">
-        <v>-0.14</v>
+        <v>-0.12</v>
       </c>
       <c r="AC7">
-        <v>1.78</v>
+        <v>10.5</v>
       </c>
       <c r="AD7">
-        <v>1.78</v>
+        <v>4.69</v>
       </c>
       <c r="AE7">
         <v>0.51</v>
       </c>
       <c r="AF7">
-        <v>117.53</v>
+        <v>13.54</v>
       </c>
       <c r="AG7">
-        <v>12.67</v>
+        <v>12.68</v>
       </c>
       <c r="AH7">
-        <v>10.25</v>
+        <v>10.23</v>
       </c>
       <c r="AI7">
-        <v>12.12</v>
+        <v>12.04</v>
       </c>
       <c r="AJ7" t="s">
         <v>49</v>
       </c>
       <c r="AK7">
-        <v>37.1</v>
+        <v>39.67</v>
       </c>
     </row>
     <row r="8" spans="1:37">
@@ -1605,10 +1605,10 @@
         <v>45</v>
       </c>
       <c r="C8">
-        <v>3984.7</v>
+        <v>4067.1</v>
       </c>
       <c r="D8">
-        <v>2.37</v>
+        <v>2.07</v>
       </c>
       <c r="E8">
         <v>5809.5</v>
@@ -1617,46 +1617,46 @@
         <v>3892.3</v>
       </c>
       <c r="G8">
-        <v>-31.41</v>
+        <v>-29.99</v>
       </c>
       <c r="H8">
-        <v>2.37</v>
+        <v>4.49</v>
       </c>
       <c r="I8">
-        <v>-0.75</v>
+        <v>1.74</v>
       </c>
       <c r="J8">
-        <v>-7.87</v>
+        <v>-6.6</v>
       </c>
       <c r="K8">
-        <v>-9.43</v>
+        <v>-7.26</v>
       </c>
       <c r="L8">
-        <v>-24.89</v>
+        <v>-24.05</v>
       </c>
       <c r="M8">
-        <v>15.61</v>
+        <v>16.34</v>
       </c>
       <c r="N8">
         <v>26</v>
       </c>
       <c r="O8">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="P8">
-        <v>3971.74</v>
+        <v>3985.66</v>
       </c>
       <c r="Q8">
-        <v>4083.13</v>
+        <v>4070.3</v>
       </c>
       <c r="R8">
-        <v>4252.31</v>
+        <v>4247.42</v>
       </c>
       <c r="S8">
-        <v>4524.12</v>
+        <v>4518.55</v>
       </c>
       <c r="T8">
-        <v>-11.92</v>
+        <v>-9.99</v>
       </c>
       <c r="U8" t="s">
         <v>46</v>
@@ -1671,34 +1671,34 @@
         <v>0</v>
       </c>
       <c r="Y8">
-        <v>39.06</v>
+        <v>46.35</v>
       </c>
       <c r="Z8">
-        <v>-93.06999999999999</v>
+        <v>-82.34</v>
       </c>
       <c r="AA8">
-        <v>-87.88</v>
+        <v>-86.77</v>
       </c>
       <c r="AB8">
-        <v>-5.19</v>
+        <v>4.43</v>
       </c>
       <c r="AC8">
-        <v>35.15</v>
+        <v>66.67</v>
       </c>
       <c r="AD8">
-        <v>27.53</v>
+        <v>40.51</v>
       </c>
       <c r="AE8">
-        <v>111.6</v>
+        <v>110.44</v>
       </c>
       <c r="AF8">
-        <v>16.82</v>
+        <v>-45.15</v>
       </c>
       <c r="AG8">
-        <v>4320.08</v>
+        <v>4278.41</v>
       </c>
       <c r="AH8">
-        <v>3846.18</v>
+        <v>3862.18</v>
       </c>
       <c r="AI8">
         <v>4247.59</v>
@@ -1707,7 +1707,7 @@
         <v>49</v>
       </c>
       <c r="AK8">
-        <v>52.96</v>
+        <v>46.64</v>
       </c>
     </row>
     <row r="9" spans="1:37">
@@ -1718,10 +1718,10 @@
         <v>45</v>
       </c>
       <c r="C9">
-        <v>10850</v>
+        <v>10750</v>
       </c>
       <c r="D9">
-        <v>1.31</v>
+        <v>-0.92</v>
       </c>
       <c r="E9">
         <v>13052</v>
@@ -1730,46 +1730,46 @@
         <v>10362</v>
       </c>
       <c r="G9">
-        <v>-16.87</v>
+        <v>-17.64</v>
       </c>
       <c r="H9">
-        <v>4.71</v>
+        <v>3.74</v>
       </c>
       <c r="I9">
-        <v>-2.73</v>
+        <v>-2.49</v>
       </c>
       <c r="J9">
-        <v>-4.77</v>
+        <v>-4.66</v>
       </c>
       <c r="K9">
-        <v>-6.95</v>
+        <v>-7.72</v>
       </c>
       <c r="L9">
-        <v>-9.890000000000001</v>
+        <v>-12.04</v>
       </c>
       <c r="M9">
-        <v>8.26</v>
+        <v>8.35</v>
       </c>
       <c r="N9">
         <v>38</v>
       </c>
       <c r="O9">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="P9">
-        <v>10874</v>
+        <v>10819</v>
       </c>
       <c r="Q9">
-        <v>10974.1</v>
+        <v>10941.2</v>
       </c>
       <c r="R9">
-        <v>11434.38</v>
+        <v>11412.46</v>
       </c>
       <c r="S9">
-        <v>11703.76</v>
+        <v>11699.86</v>
       </c>
       <c r="T9">
-        <v>-7.29</v>
+        <v>-8.119999999999999</v>
       </c>
       <c r="U9" t="s">
         <v>46</v>
@@ -1784,34 +1784,34 @@
         <v>0</v>
       </c>
       <c r="Y9">
-        <v>42.45</v>
+        <v>40.07</v>
       </c>
       <c r="Z9">
-        <v>-145.23</v>
+        <v>-150.32</v>
       </c>
       <c r="AA9">
-        <v>-151.05</v>
+        <v>-150.9</v>
       </c>
       <c r="AB9">
-        <v>5.82</v>
+        <v>0.58</v>
       </c>
       <c r="AC9">
-        <v>66.93000000000001</v>
+        <v>61.2</v>
       </c>
       <c r="AD9">
-        <v>66.68000000000001</v>
+        <v>63.15</v>
       </c>
       <c r="AE9">
-        <v>203.09</v>
+        <v>203.44</v>
       </c>
       <c r="AF9">
-        <v>6.48</v>
+        <v>-9.77</v>
       </c>
       <c r="AG9">
-        <v>11338.71</v>
+        <v>11256.36</v>
       </c>
       <c r="AH9">
-        <v>10609.49</v>
+        <v>10626.04</v>
       </c>
       <c r="AI9">
         <v>11348.57</v>
@@ -1820,7 +1820,7 @@
         <v>49</v>
       </c>
       <c r="AK9">
-        <v>30.81</v>
+        <v>32.41</v>
       </c>
     </row>
   </sheetData>
@@ -2001,7 +2001,7 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="4" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="B3" s="4" t="s">
         <v>56</v>
@@ -2053,13 +2053,13 @@
         <v>9</v>
       </c>
       <c r="C7" s="6">
-        <v>-4.92</v>
+        <v>-4.95</v>
       </c>
       <c r="D7" s="6">
-        <v>-4.95</v>
+        <v>-5.75</v>
       </c>
       <c r="E7" s="7">
-        <v>-0.03</v>
+        <v>-0.8</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -2070,13 +2070,13 @@
         <v>9</v>
       </c>
       <c r="C8" s="6">
-        <v>-12.86</v>
+        <v>-12.15</v>
       </c>
       <c r="D8" s="6">
-        <v>-12.15</v>
+        <v>-9.380000000000001</v>
       </c>
       <c r="E8" s="8">
-        <v>0.71</v>
+        <v>2.77</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -2087,13 +2087,13 @@
         <v>9</v>
       </c>
       <c r="C9" s="6">
-        <v>-10.38</v>
+        <v>-9.800000000000001</v>
       </c>
       <c r="D9" s="6">
-        <v>-9.800000000000001</v>
-      </c>
-      <c r="E9" s="8">
-        <v>0.58</v>
+        <v>-10.3</v>
+      </c>
+      <c r="E9" s="7">
+        <v>-0.5</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -2104,13 +2104,13 @@
         <v>9</v>
       </c>
       <c r="C10" s="6">
-        <v>-7.15</v>
+        <v>-7.06</v>
       </c>
       <c r="D10" s="6">
-        <v>-7.06</v>
+        <v>-6.88</v>
       </c>
       <c r="E10" s="8">
-        <v>0.09</v>
+        <v>0.18</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -2121,13 +2121,13 @@
         <v>9</v>
       </c>
       <c r="C11" s="6">
-        <v>-10.1</v>
+        <v>-12.32</v>
       </c>
       <c r="D11" s="6">
-        <v>-12.32</v>
-      </c>
-      <c r="E11" s="7">
-        <v>-2.22</v>
+        <v>-8.77</v>
+      </c>
+      <c r="E11" s="8">
+        <v>3.55</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -2138,13 +2138,13 @@
         <v>9</v>
       </c>
       <c r="C12" s="6">
-        <v>-3.33</v>
+        <v>-9.050000000000001</v>
       </c>
       <c r="D12" s="6">
-        <v>-9.050000000000001</v>
-      </c>
-      <c r="E12" s="7">
-        <v>-5.72</v>
+        <v>-2.62</v>
+      </c>
+      <c r="E12" s="8">
+        <v>6.43</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -2155,13 +2155,13 @@
         <v>9</v>
       </c>
       <c r="C13" s="6">
-        <v>-10.59</v>
+        <v>-7.87</v>
       </c>
       <c r="D13" s="6">
-        <v>-7.87</v>
+        <v>-6.6</v>
       </c>
       <c r="E13" s="8">
-        <v>2.72</v>
+        <v>1.27</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -2172,13 +2172,13 @@
         <v>9</v>
       </c>
       <c r="C14" s="6">
-        <v>-6.05</v>
+        <v>-4.77</v>
       </c>
       <c r="D14" s="6">
-        <v>-4.77</v>
+        <v>-4.66</v>
       </c>
       <c r="E14" s="8">
-        <v>1.28</v>
+        <v>0.11</v>
       </c>
     </row>
     <row r="15" spans="1:6">
@@ -2189,13 +2189,13 @@
         <v>8</v>
       </c>
       <c r="C15" s="6">
-        <v>-3.86</v>
+        <v>-3.23</v>
       </c>
       <c r="D15" s="6">
-        <v>-3.23</v>
+        <v>-0.99</v>
       </c>
       <c r="E15" s="8">
-        <v>0.63</v>
+        <v>2.24</v>
       </c>
     </row>
     <row r="16" spans="1:6">
@@ -2206,13 +2206,13 @@
         <v>8</v>
       </c>
       <c r="C16" s="6">
-        <v>-7.34</v>
+        <v>-9.77</v>
       </c>
       <c r="D16" s="6">
-        <v>-9.77</v>
-      </c>
-      <c r="E16" s="7">
-        <v>-2.43</v>
+        <v>-4.01</v>
+      </c>
+      <c r="E16" s="8">
+        <v>5.76</v>
       </c>
     </row>
     <row r="17" spans="1:5">
@@ -2223,13 +2223,13 @@
         <v>8</v>
       </c>
       <c r="C17" s="6">
-        <v>-6.46</v>
+        <v>-6.86</v>
       </c>
       <c r="D17" s="6">
-        <v>-6.86</v>
-      </c>
-      <c r="E17" s="7">
-        <v>-0.4</v>
+        <v>-5.75</v>
+      </c>
+      <c r="E17" s="8">
+        <v>1.11</v>
       </c>
     </row>
     <row r="18" spans="1:5">
@@ -2240,13 +2240,13 @@
         <v>8</v>
       </c>
       <c r="C18" s="6">
-        <v>-4.09</v>
+        <v>-3.95</v>
       </c>
       <c r="D18" s="6">
-        <v>-3.95</v>
+        <v>-1.61</v>
       </c>
       <c r="E18" s="8">
-        <v>0.14</v>
+        <v>2.34</v>
       </c>
     </row>
     <row r="19" spans="1:5">
@@ -2257,13 +2257,13 @@
         <v>8</v>
       </c>
       <c r="C19" s="6">
-        <v>-10.48</v>
+        <v>-10.66</v>
       </c>
       <c r="D19" s="6">
-        <v>-10.66</v>
-      </c>
-      <c r="E19" s="7">
-        <v>-0.18</v>
+        <v>-1.93</v>
+      </c>
+      <c r="E19" s="8">
+        <v>8.73</v>
       </c>
     </row>
     <row r="20" spans="1:5">
@@ -2274,13 +2274,13 @@
         <v>8</v>
       </c>
       <c r="C20" s="6">
-        <v>-5.79</v>
+        <v>-11.41</v>
       </c>
       <c r="D20" s="6">
-        <v>-11.41</v>
-      </c>
-      <c r="E20" s="7">
-        <v>-5.62</v>
+        <v>-2.36</v>
+      </c>
+      <c r="E20" s="8">
+        <v>9.050000000000001</v>
       </c>
     </row>
     <row r="21" spans="1:5">
@@ -2291,13 +2291,13 @@
         <v>8</v>
       </c>
       <c r="C21" s="6">
-        <v>-2.86</v>
+        <v>-0.75</v>
       </c>
       <c r="D21" s="6">
-        <v>-0.75</v>
+        <v>1.74</v>
       </c>
       <c r="E21" s="8">
-        <v>2.11</v>
+        <v>2.49</v>
       </c>
     </row>
     <row r="22" spans="1:5">
@@ -2308,13 +2308,13 @@
         <v>8</v>
       </c>
       <c r="C22" s="6">
-        <v>-3.13</v>
+        <v>-2.73</v>
       </c>
       <c r="D22" s="6">
-        <v>-2.73</v>
+        <v>-2.49</v>
       </c>
       <c r="E22" s="8">
-        <v>0.4</v>
+        <v>0.24</v>
       </c>
     </row>
     <row r="23" spans="1:5">
@@ -2325,13 +2325,13 @@
         <v>11</v>
       </c>
       <c r="C23" s="6">
-        <v>34.47</v>
+        <v>30.21</v>
       </c>
       <c r="D23" s="6">
-        <v>30.21</v>
+        <v>29.6</v>
       </c>
       <c r="E23" s="7">
-        <v>-4.26</v>
+        <v>-0.61</v>
       </c>
     </row>
     <row r="24" spans="1:5">
@@ -2342,13 +2342,13 @@
         <v>11</v>
       </c>
       <c r="C24" s="6">
-        <v>-47.55</v>
+        <v>-47.84</v>
       </c>
       <c r="D24" s="6">
-        <v>-47.84</v>
-      </c>
-      <c r="E24" s="7">
-        <v>-0.29</v>
+        <v>-45.93</v>
+      </c>
+      <c r="E24" s="8">
+        <v>1.91</v>
       </c>
     </row>
     <row r="25" spans="1:5">
@@ -2359,13 +2359,13 @@
         <v>11</v>
       </c>
       <c r="C25" s="6">
-        <v>7.83</v>
+        <v>8.19</v>
       </c>
       <c r="D25" s="6">
-        <v>8.19</v>
-      </c>
-      <c r="E25" s="8">
-        <v>0.36</v>
+        <v>7.69</v>
+      </c>
+      <c r="E25" s="7">
+        <v>-0.5</v>
       </c>
     </row>
     <row r="26" spans="1:5">
@@ -2376,13 +2376,13 @@
         <v>11</v>
       </c>
       <c r="C26" s="6">
-        <v>26.62</v>
+        <v>24.49</v>
       </c>
       <c r="D26" s="6">
-        <v>24.49</v>
+        <v>23.43</v>
       </c>
       <c r="E26" s="7">
-        <v>-2.13</v>
+        <v>-1.06</v>
       </c>
     </row>
     <row r="27" spans="1:5">
@@ -2393,13 +2393,13 @@
         <v>11</v>
       </c>
       <c r="C27" s="6">
-        <v>57.61</v>
+        <v>54.61</v>
       </c>
       <c r="D27" s="6">
-        <v>54.61</v>
-      </c>
-      <c r="E27" s="7">
-        <v>-3</v>
+        <v>62.48</v>
+      </c>
+      <c r="E27" s="8">
+        <v>7.87</v>
       </c>
     </row>
     <row r="28" spans="1:5">
@@ -2410,13 +2410,13 @@
         <v>11</v>
       </c>
       <c r="C28" s="6">
-        <v>86.28</v>
+        <v>87.39</v>
       </c>
       <c r="D28" s="6">
-        <v>87.39</v>
+        <v>97.79000000000001</v>
       </c>
       <c r="E28" s="8">
-        <v>1.11</v>
+        <v>10.4</v>
       </c>
     </row>
     <row r="29" spans="1:5">
@@ -2427,13 +2427,13 @@
         <v>11</v>
       </c>
       <c r="C29" s="6">
-        <v>-26.15</v>
+        <v>-24.89</v>
       </c>
       <c r="D29" s="6">
-        <v>-24.89</v>
+        <v>-24.05</v>
       </c>
       <c r="E29" s="8">
-        <v>1.26</v>
+        <v>0.84</v>
       </c>
     </row>
     <row r="30" spans="1:5">
@@ -2444,13 +2444,13 @@
         <v>11</v>
       </c>
       <c r="C30" s="6">
-        <v>-11.27</v>
+        <v>-9.890000000000001</v>
       </c>
       <c r="D30" s="6">
-        <v>-9.890000000000001</v>
-      </c>
-      <c r="E30" s="8">
-        <v>1.38</v>
+        <v>-12.04</v>
+      </c>
+      <c r="E30" s="7">
+        <v>-2.15</v>
       </c>
     </row>
     <row r="31" spans="1:5">
@@ -2461,13 +2461,13 @@
         <v>10</v>
       </c>
       <c r="C31" s="6">
-        <v>-6.53</v>
+        <v>-7.9</v>
       </c>
       <c r="D31" s="6">
-        <v>-7.9</v>
-      </c>
-      <c r="E31" s="7">
-        <v>-1.37</v>
+        <v>-6.54</v>
+      </c>
+      <c r="E31" s="8">
+        <v>1.36</v>
       </c>
     </row>
     <row r="32" spans="1:5">
@@ -2478,13 +2478,13 @@
         <v>10</v>
       </c>
       <c r="C32" s="6">
-        <v>-28.72</v>
+        <v>-28.98</v>
       </c>
       <c r="D32" s="6">
-        <v>-28.98</v>
-      </c>
-      <c r="E32" s="7">
-        <v>-0.26</v>
+        <v>-23.39</v>
+      </c>
+      <c r="E32" s="8">
+        <v>5.59</v>
       </c>
     </row>
     <row r="33" spans="1:5">
@@ -2495,13 +2495,13 @@
         <v>10</v>
       </c>
       <c r="C33" s="6">
-        <v>-6.88</v>
+        <v>-7.5</v>
       </c>
       <c r="D33" s="6">
-        <v>-7.5</v>
-      </c>
-      <c r="E33" s="7">
-        <v>-0.62</v>
+        <v>-6.95</v>
+      </c>
+      <c r="E33" s="8">
+        <v>0.55</v>
       </c>
     </row>
     <row r="34" spans="1:5">
@@ -2512,13 +2512,13 @@
         <v>10</v>
       </c>
       <c r="C34" s="6">
-        <v>-1.19</v>
+        <v>-4.28</v>
       </c>
       <c r="D34" s="6">
-        <v>-4.28</v>
-      </c>
-      <c r="E34" s="7">
-        <v>-3.09</v>
+        <v>-2.99</v>
+      </c>
+      <c r="E34" s="8">
+        <v>1.29</v>
       </c>
     </row>
     <row r="35" spans="1:5">
@@ -2529,13 +2529,13 @@
         <v>10</v>
       </c>
       <c r="C35" s="6">
-        <v>-11.3</v>
+        <v>-9.58</v>
       </c>
       <c r="D35" s="6">
-        <v>-9.58</v>
+        <v>-4.62</v>
       </c>
       <c r="E35" s="8">
-        <v>1.72</v>
+        <v>4.96</v>
       </c>
     </row>
     <row r="36" spans="1:5">
@@ -2546,13 +2546,13 @@
         <v>10</v>
       </c>
       <c r="C36" s="6">
-        <v>-2.45</v>
+        <v>-4.92</v>
       </c>
       <c r="D36" s="6">
-        <v>-4.92</v>
-      </c>
-      <c r="E36" s="7">
-        <v>-2.47</v>
+        <v>1.8</v>
+      </c>
+      <c r="E36" s="8">
+        <v>6.72</v>
       </c>
     </row>
     <row r="37" spans="1:5">
@@ -2563,13 +2563,13 @@
         <v>10</v>
       </c>
       <c r="C37" s="6">
-        <v>-11.85</v>
+        <v>-9.43</v>
       </c>
       <c r="D37" s="6">
-        <v>-9.43</v>
+        <v>-7.26</v>
       </c>
       <c r="E37" s="8">
-        <v>2.42</v>
+        <v>2.17</v>
       </c>
     </row>
     <row r="38" spans="1:5">
@@ -2580,13 +2580,13 @@
         <v>10</v>
       </c>
       <c r="C38" s="6">
-        <v>-8.640000000000001</v>
+        <v>-6.95</v>
       </c>
       <c r="D38" s="6">
-        <v>-6.95</v>
-      </c>
-      <c r="E38" s="8">
-        <v>1.69</v>
+        <v>-7.72</v>
+      </c>
+      <c r="E38" s="7">
+        <v>-0.77</v>
       </c>
     </row>
     <row r="39" spans="1:5">
@@ -2597,13 +2597,13 @@
         <v>6</v>
       </c>
       <c r="C39" s="6">
-        <v>-11.69</v>
+        <v>-11.14</v>
       </c>
       <c r="D39" s="6">
-        <v>-11.14</v>
+        <v>-10.78</v>
       </c>
       <c r="E39" s="8">
-        <v>0.55</v>
+        <v>0.36</v>
       </c>
     </row>
     <row r="40" spans="1:5">
@@ -2614,13 +2614,13 @@
         <v>6</v>
       </c>
       <c r="C40" s="6">
-        <v>-49.39</v>
+        <v>-49.61</v>
       </c>
       <c r="D40" s="6">
-        <v>-49.61</v>
-      </c>
-      <c r="E40" s="7">
-        <v>-0.22</v>
+        <v>-48.09</v>
+      </c>
+      <c r="E40" s="8">
+        <v>1.52</v>
       </c>
     </row>
     <row r="41" spans="1:5">
@@ -2631,13 +2631,13 @@
         <v>6</v>
       </c>
       <c r="C41" s="6">
-        <v>-12.38</v>
+        <v>-12.08</v>
       </c>
       <c r="D41" s="6">
-        <v>-12.08</v>
-      </c>
-      <c r="E41" s="8">
-        <v>0.3</v>
+        <v>-12.17</v>
+      </c>
+      <c r="E41" s="7">
+        <v>-0.09</v>
       </c>
     </row>
     <row r="42" spans="1:5">
@@ -2648,13 +2648,13 @@
         <v>6</v>
       </c>
       <c r="C42" s="6">
-        <v>-18.08</v>
+        <v>-18.38</v>
       </c>
       <c r="D42" s="6">
-        <v>-18.38</v>
-      </c>
-      <c r="E42" s="7">
-        <v>-0.3</v>
+        <v>-18.2</v>
+      </c>
+      <c r="E42" s="8">
+        <v>0.18</v>
       </c>
     </row>
     <row r="43" spans="1:5">
@@ -2665,13 +2665,13 @@
         <v>6</v>
       </c>
       <c r="C43" s="6">
-        <v>-18.97</v>
+        <v>-18.33</v>
       </c>
       <c r="D43" s="6">
-        <v>-18.33</v>
+        <v>-15.32</v>
       </c>
       <c r="E43" s="8">
-        <v>0.64</v>
+        <v>3.01</v>
       </c>
     </row>
     <row r="44" spans="1:5">
@@ -2682,13 +2682,13 @@
         <v>6</v>
       </c>
       <c r="C44" s="6">
-        <v>-22.92</v>
+        <v>-26.36</v>
       </c>
       <c r="D44" s="6">
-        <v>-26.36</v>
-      </c>
-      <c r="E44" s="7">
-        <v>-3.44</v>
+        <v>-22.7</v>
+      </c>
+      <c r="E44" s="8">
+        <v>3.66</v>
       </c>
     </row>
     <row r="45" spans="1:5">
@@ -2699,13 +2699,13 @@
         <v>6</v>
       </c>
       <c r="C45" s="6">
-        <v>-33</v>
+        <v>-31.41</v>
       </c>
       <c r="D45" s="6">
-        <v>-31.41</v>
+        <v>-29.99</v>
       </c>
       <c r="E45" s="8">
-        <v>1.59</v>
+        <v>1.42</v>
       </c>
     </row>
     <row r="46" spans="1:5">
@@ -2716,13 +2716,13 @@
         <v>6</v>
       </c>
       <c r="C46" s="6">
-        <v>-17.94</v>
+        <v>-16.87</v>
       </c>
       <c r="D46" s="6">
-        <v>-16.87</v>
-      </c>
-      <c r="E46" s="8">
-        <v>1.07</v>
+        <v>-17.64</v>
+      </c>
+      <c r="E46" s="7">
+        <v>-0.77</v>
       </c>
     </row>
     <row r="47" spans="1:5">
@@ -2733,13 +2733,13 @@
         <v>2</v>
       </c>
       <c r="C47" s="6">
-        <v>375.05</v>
+        <v>377.4</v>
       </c>
       <c r="D47" s="6">
-        <v>377.4</v>
+        <v>378.9</v>
       </c>
       <c r="E47" s="8">
-        <v>2.35</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="48" spans="1:5">
@@ -2750,13 +2750,13 @@
         <v>2</v>
       </c>
       <c r="C48" s="6">
-        <v>44.53</v>
+        <v>44.34</v>
       </c>
       <c r="D48" s="6">
-        <v>44.34</v>
-      </c>
-      <c r="E48" s="7">
-        <v>-0.19</v>
+        <v>45.68</v>
+      </c>
+      <c r="E48" s="8">
+        <v>1.34</v>
       </c>
     </row>
     <row r="49" spans="1:5">
@@ -2767,13 +2767,13 @@
         <v>2</v>
       </c>
       <c r="C49" s="6">
-        <v>2962</v>
+        <v>2972</v>
       </c>
       <c r="D49" s="6">
-        <v>2972</v>
-      </c>
-      <c r="E49" s="8">
-        <v>10</v>
+        <v>2969</v>
+      </c>
+      <c r="E49" s="7">
+        <v>-3</v>
       </c>
     </row>
     <row r="50" spans="1:5">
@@ -2784,13 +2784,13 @@
         <v>2</v>
       </c>
       <c r="C50" s="6">
-        <v>941.85</v>
+        <v>938.4</v>
       </c>
       <c r="D50" s="6">
-        <v>938.4</v>
-      </c>
-      <c r="E50" s="7">
-        <v>-3.45</v>
+        <v>940.5</v>
+      </c>
+      <c r="E50" s="8">
+        <v>2.1</v>
       </c>
     </row>
     <row r="51" spans="1:5">
@@ -2801,13 +2801,13 @@
         <v>2</v>
       </c>
       <c r="C51" s="6">
-        <v>12.64</v>
+        <v>12.74</v>
       </c>
       <c r="D51" s="6">
-        <v>12.74</v>
+        <v>13.21</v>
       </c>
       <c r="E51" s="8">
-        <v>0.1</v>
+        <v>0.47</v>
       </c>
     </row>
     <row r="52" spans="1:5">
@@ -2818,13 +2818,13 @@
         <v>2</v>
       </c>
       <c r="C52" s="6">
-        <v>10.73</v>
+        <v>10.25</v>
       </c>
       <c r="D52" s="6">
-        <v>10.25</v>
-      </c>
-      <c r="E52" s="7">
-        <v>-0.48</v>
+        <v>10.76</v>
+      </c>
+      <c r="E52" s="8">
+        <v>0.51</v>
       </c>
     </row>
     <row r="53" spans="1:5">
@@ -2835,13 +2835,13 @@
         <v>2</v>
       </c>
       <c r="C53" s="6">
-        <v>3892.3</v>
+        <v>3984.7</v>
       </c>
       <c r="D53" s="6">
-        <v>3984.7</v>
+        <v>4067.1</v>
       </c>
       <c r="E53" s="8">
-        <v>92.40000000000001</v>
+        <v>82.40000000000001</v>
       </c>
     </row>
     <row r="54" spans="1:5">
@@ -2852,13 +2852,13 @@
         <v>2</v>
       </c>
       <c r="C54" s="6">
-        <v>10710</v>
+        <v>10850</v>
       </c>
       <c r="D54" s="6">
-        <v>10850</v>
-      </c>
-      <c r="E54" s="8">
-        <v>140</v>
+        <v>10750</v>
+      </c>
+      <c r="E54" s="7">
+        <v>-100</v>
       </c>
     </row>
     <row r="55" spans="1:5">
@@ -2869,13 +2869,13 @@
         <v>24</v>
       </c>
       <c r="C55" s="6">
-        <v>38.07</v>
+        <v>39.9</v>
       </c>
       <c r="D55" s="6">
-        <v>39.9</v>
+        <v>41.09</v>
       </c>
       <c r="E55" s="8">
-        <v>1.83</v>
+        <v>1.19</v>
       </c>
     </row>
     <row r="56" spans="1:5">
@@ -2886,13 +2886,13 @@
         <v>24</v>
       </c>
       <c r="C56" s="6">
-        <v>24.23</v>
+        <v>23.83</v>
       </c>
       <c r="D56" s="6">
-        <v>23.83</v>
-      </c>
-      <c r="E56" s="7">
-        <v>-0.4</v>
+        <v>32.45</v>
+      </c>
+      <c r="E56" s="8">
+        <v>8.619999999999999</v>
       </c>
     </row>
     <row r="57" spans="1:5">
@@ -2903,13 +2903,13 @@
         <v>24</v>
       </c>
       <c r="C57" s="6">
-        <v>28.23</v>
+        <v>29.6</v>
       </c>
       <c r="D57" s="6">
-        <v>29.6</v>
-      </c>
-      <c r="E57" s="8">
-        <v>1.37</v>
+        <v>29.42</v>
+      </c>
+      <c r="E57" s="7">
+        <v>-0.18</v>
       </c>
     </row>
     <row r="58" spans="1:5">
@@ -2920,13 +2920,13 @@
         <v>24</v>
       </c>
       <c r="C58" s="6">
-        <v>35.57</v>
+        <v>34.79</v>
       </c>
       <c r="D58" s="6">
-        <v>34.79</v>
-      </c>
-      <c r="E58" s="7">
-        <v>-0.78</v>
+        <v>35.72</v>
+      </c>
+      <c r="E58" s="8">
+        <v>0.93</v>
       </c>
     </row>
     <row r="59" spans="1:5">
@@ -2937,13 +2937,13 @@
         <v>24</v>
       </c>
       <c r="C59" s="6">
-        <v>32.95</v>
+        <v>34.56</v>
       </c>
       <c r="D59" s="6">
-        <v>34.56</v>
+        <v>41.63</v>
       </c>
       <c r="E59" s="8">
-        <v>1.61</v>
+        <v>7.07</v>
       </c>
     </row>
     <row r="60" spans="1:5">
@@ -2954,13 +2954,13 @@
         <v>24</v>
       </c>
       <c r="C60" s="6">
-        <v>37.8</v>
+        <v>32.56</v>
       </c>
       <c r="D60" s="6">
-        <v>32.56</v>
-      </c>
-      <c r="E60" s="7">
-        <v>-5.24</v>
+        <v>41.8</v>
+      </c>
+      <c r="E60" s="8">
+        <v>9.24</v>
       </c>
     </row>
     <row r="61" spans="1:5">
@@ -2971,13 +2971,13 @@
         <v>24</v>
       </c>
       <c r="C61" s="6">
-        <v>29.02</v>
+        <v>39.06</v>
       </c>
       <c r="D61" s="6">
-        <v>39.06</v>
+        <v>46.35</v>
       </c>
       <c r="E61" s="8">
-        <v>10.04</v>
+        <v>7.29</v>
       </c>
     </row>
     <row r="62" spans="1:5">
@@ -2988,13 +2988,13 @@
         <v>24</v>
       </c>
       <c r="C62" s="6">
-        <v>37.63</v>
+        <v>42.45</v>
       </c>
       <c r="D62" s="6">
-        <v>42.45</v>
-      </c>
-      <c r="E62" s="8">
-        <v>4.82</v>
+        <v>40.07</v>
+      </c>
+      <c r="E62" s="7">
+        <v>-2.38</v>
       </c>
     </row>
     <row r="63" spans="1:5">
@@ -3005,13 +3005,13 @@
         <v>31</v>
       </c>
       <c r="C63" s="6">
-        <v>85</v>
+        <v>-42.92</v>
       </c>
       <c r="D63" s="6">
-        <v>-42.92</v>
-      </c>
-      <c r="E63" s="7">
-        <v>-127.92</v>
+        <v>82.95</v>
+      </c>
+      <c r="E63" s="8">
+        <v>125.87</v>
       </c>
     </row>
     <row r="64" spans="1:5">
@@ -3022,13 +3022,13 @@
         <v>31</v>
       </c>
       <c r="C64" s="6">
-        <v>13.7</v>
+        <v>-24.55</v>
       </c>
       <c r="D64" s="6">
-        <v>-24.55</v>
-      </c>
-      <c r="E64" s="7">
-        <v>-38.25</v>
+        <v>113.19</v>
+      </c>
+      <c r="E64" s="8">
+        <v>137.74</v>
       </c>
     </row>
     <row r="65" spans="1:5">
@@ -3039,13 +3039,13 @@
         <v>31</v>
       </c>
       <c r="C65" s="6">
-        <v>60.86</v>
+        <v>-70.31999999999999</v>
       </c>
       <c r="D65" s="6">
-        <v>-70.31999999999999</v>
-      </c>
-      <c r="E65" s="7">
-        <v>-131.18</v>
+        <v>-57.64</v>
+      </c>
+      <c r="E65" s="8">
+        <v>12.68</v>
       </c>
     </row>
     <row r="66" spans="1:5">
@@ -3056,13 +3056,13 @@
         <v>31</v>
       </c>
       <c r="C66" s="6">
-        <v>68.70999999999999</v>
+        <v>21.15</v>
       </c>
       <c r="D66" s="6">
-        <v>21.15</v>
+        <v>-20.24</v>
       </c>
       <c r="E66" s="7">
-        <v>-47.56</v>
+        <v>-41.39</v>
       </c>
     </row>
     <row r="67" spans="1:5">
@@ -3073,13 +3073,13 @@
         <v>31</v>
       </c>
       <c r="C67" s="6">
-        <v>29.55</v>
+        <v>-5.45</v>
       </c>
       <c r="D67" s="6">
-        <v>-5.45</v>
+        <v>-30.3</v>
       </c>
       <c r="E67" s="7">
-        <v>-35</v>
+        <v>-24.85</v>
       </c>
     </row>
     <row r="68" spans="1:5">
@@ -3090,13 +3090,13 @@
         <v>31</v>
       </c>
       <c r="C68" s="6">
-        <v>30.84</v>
+        <v>117.53</v>
       </c>
       <c r="D68" s="6">
-        <v>117.53</v>
-      </c>
-      <c r="E68" s="8">
-        <v>86.69</v>
+        <v>13.54</v>
+      </c>
+      <c r="E68" s="7">
+        <v>-103.99</v>
       </c>
     </row>
     <row r="69" spans="1:5">
@@ -3107,13 +3107,13 @@
         <v>31</v>
       </c>
       <c r="C69" s="6">
-        <v>-7.38</v>
+        <v>16.82</v>
       </c>
       <c r="D69" s="6">
-        <v>16.82</v>
-      </c>
-      <c r="E69" s="8">
-        <v>24.2</v>
+        <v>-45.15</v>
+      </c>
+      <c r="E69" s="7">
+        <v>-61.97</v>
       </c>
     </row>
     <row r="70" spans="1:5">
@@ -3124,13 +3124,13 @@
         <v>31</v>
       </c>
       <c r="C70" s="6">
-        <v>106.59</v>
+        <v>6.48</v>
       </c>
       <c r="D70" s="6">
-        <v>6.48</v>
+        <v>-9.77</v>
       </c>
       <c r="E70" s="7">
-        <v>-100.11</v>
+        <v>-16.25</v>
       </c>
     </row>
   </sheetData>
@@ -3195,16 +3195,16 @@
         <v>8</v>
       </c>
       <c r="D2" s="11">
-        <v>34.6</v>
+        <v>38.6</v>
       </c>
       <c r="E2" s="11">
         <v>20</v>
       </c>
       <c r="F2" s="11">
-        <v>-8.5</v>
+        <v>-6.9</v>
       </c>
       <c r="G2" s="11">
-        <v>-9.9</v>
+        <v>-7.2</v>
       </c>
       <c r="H2" s="11">
         <v>56.1</v>
@@ -3338,28 +3338,28 @@
     </row>
     <row r="2" spans="1:8">
       <c r="A2" s="14">
-        <v>0.2776</v>
+        <v>0.2801</v>
       </c>
       <c r="B2" s="14">
-        <v>0.1561</v>
+        <v>0.1634</v>
       </c>
       <c r="C2" s="14">
-        <v>0.1429</v>
+        <v>0.1526</v>
       </c>
       <c r="D2" s="14">
-        <v>0.1333</v>
+        <v>0.137</v>
       </c>
       <c r="E2" s="14">
-        <v>0.08259999999999999</v>
+        <v>0.08349999999999999</v>
       </c>
       <c r="F2" s="14">
-        <v>0.0198</v>
+        <v>0.029</v>
       </c>
       <c r="G2" s="14">
-        <v>-0.2956</v>
+        <v>-0.2828</v>
       </c>
       <c r="H2" s="14">
-        <v>-0.3166</v>
+        <v>-0.3073</v>
       </c>
     </row>
   </sheetData>

--- a/BIRLA_GROUP_Technical_Metrics.xlsx
+++ b/BIRLA_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="287" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="276" uniqueCount="64">
   <si>
     <t>Symbol</t>
   </si>
@@ -166,43 +166,13 @@
     <t>Yes</t>
   </si>
   <si>
-    <t>UP</t>
-  </si>
-  <si>
     <t>DOWN</t>
   </si>
   <si>
     <t>▶  SIGNAL EVENTS (vs Previous Run)</t>
   </si>
   <si>
-    <t>Signal</t>
-  </si>
-  <si>
-    <t>Change</t>
-  </si>
-  <si>
-    <t>Direction</t>
-  </si>
-  <si>
-    <t>Prev Value</t>
-  </si>
-  <si>
-    <t>Curr Value</t>
-  </si>
-  <si>
-    <t>RSI Oversold Recovery</t>
-  </si>
-  <si>
-    <t>23.8 → 32.5</t>
-  </si>
-  <si>
-    <t>🟢 BULLISH</t>
-  </si>
-  <si>
-    <t>23.8</t>
-  </si>
-  <si>
-    <t>32.5</t>
+    <t>No signal events detected since last run.</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -288,14 +258,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF9C0006"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF006100"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -328,13 +298,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -404,18 +374,17 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -786,8 +755,10 @@
     <col min="13" max="13" width="10.7109375" customWidth="1"/>
     <col min="14" max="14" width="11.7109375" customWidth="1"/>
     <col min="15" max="15" width="10.7109375" customWidth="1"/>
-    <col min="16" max="17" width="9.7109375" customWidth="1"/>
-    <col min="18" max="19" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="9.7109375" customWidth="1"/>
+    <col min="17" max="17" width="10.7109375" customWidth="1"/>
+    <col min="18" max="18" width="9.7109375" customWidth="1"/>
+    <col min="19" max="19" width="10.7109375" customWidth="1"/>
     <col min="20" max="20" width="22.7109375" customWidth="1"/>
     <col min="21" max="21" width="9.7109375" customWidth="1"/>
     <col min="22" max="22" width="10.7109375" customWidth="1"/>
@@ -927,10 +898,10 @@
         <v>45</v>
       </c>
       <c r="C2">
-        <v>378.9</v>
+        <v>372.1</v>
       </c>
       <c r="D2">
-        <v>0.4</v>
+        <v>-1.79</v>
       </c>
       <c r="E2">
         <v>424.7</v>
@@ -939,46 +910,46 @@
         <v>292.25</v>
       </c>
       <c r="G2">
-        <v>-10.78</v>
+        <v>-12.39</v>
       </c>
       <c r="H2">
-        <v>29.65</v>
+        <v>27.32</v>
       </c>
       <c r="I2">
-        <v>-0.99</v>
+        <v>-1.56</v>
       </c>
       <c r="J2">
-        <v>-5.75</v>
+        <v>-8.1</v>
       </c>
       <c r="K2">
-        <v>-6.54</v>
+        <v>-3.54</v>
       </c>
       <c r="L2">
-        <v>29.6</v>
+        <v>24.1</v>
       </c>
       <c r="M2">
-        <v>28.01</v>
+        <v>27.58</v>
       </c>
       <c r="N2">
         <v>74</v>
       </c>
       <c r="O2">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="P2">
-        <v>377.99</v>
+        <v>376.81</v>
       </c>
       <c r="Q2">
-        <v>390.55</v>
+        <v>388.99</v>
       </c>
       <c r="R2">
-        <v>400.15</v>
+        <v>399.59</v>
       </c>
       <c r="S2">
-        <v>364.84</v>
+        <v>364.96</v>
       </c>
       <c r="T2">
-        <v>3.86</v>
+        <v>1.96</v>
       </c>
       <c r="U2" t="s">
         <v>46</v>
@@ -993,43 +964,43 @@
         <v>2</v>
       </c>
       <c r="Y2">
-        <v>41.09</v>
+        <v>37.46</v>
       </c>
       <c r="Z2">
-        <v>-6.19</v>
+        <v>-6.75</v>
       </c>
       <c r="AA2">
-        <v>-4.54</v>
+        <v>-4.99</v>
       </c>
       <c r="AB2">
-        <v>-1.65</v>
+        <v>-1.77</v>
       </c>
       <c r="AC2">
-        <v>23.43</v>
+        <v>17.15</v>
       </c>
       <c r="AD2">
-        <v>24.38</v>
+        <v>22.06</v>
       </c>
       <c r="AE2">
-        <v>9.210000000000001</v>
+        <v>9.279999999999999</v>
       </c>
       <c r="AF2">
-        <v>82.95</v>
+        <v>56.67</v>
       </c>
       <c r="AG2">
-        <v>412.17</v>
+        <v>411.24</v>
       </c>
       <c r="AH2">
-        <v>368.93</v>
+        <v>366.74</v>
       </c>
       <c r="AI2">
-        <v>372.91</v>
+        <v>402.96</v>
       </c>
       <c r="AJ2" t="s">
         <v>48</v>
       </c>
       <c r="AK2">
-        <v>34.07</v>
+        <v>36.2</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1040,10 +1011,10 @@
         <v>45</v>
       </c>
       <c r="C3">
-        <v>45.68</v>
+        <v>44.62</v>
       </c>
       <c r="D3">
-        <v>3.02</v>
+        <v>-2.32</v>
       </c>
       <c r="E3">
         <v>87.98999999999999</v>
@@ -1052,46 +1023,46 @@
         <v>44.34</v>
       </c>
       <c r="G3">
-        <v>-48.09</v>
+        <v>-49.29</v>
       </c>
       <c r="H3">
-        <v>3.02</v>
+        <v>0.63</v>
       </c>
       <c r="I3">
-        <v>-4.01</v>
+        <v>-3.5</v>
       </c>
       <c r="J3">
-        <v>-9.380000000000001</v>
+        <v>-15.76</v>
       </c>
       <c r="K3">
-        <v>-23.39</v>
+        <v>-23.48</v>
       </c>
       <c r="L3">
-        <v>-45.93</v>
+        <v>-48.35</v>
       </c>
       <c r="M3">
-        <v>-28.28</v>
+        <v>-29.65</v>
       </c>
       <c r="N3">
         <v>13</v>
       </c>
       <c r="O3">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="P3">
-        <v>45.42</v>
+        <v>45.1</v>
       </c>
       <c r="Q3">
-        <v>48.88</v>
+        <v>48.45</v>
       </c>
       <c r="R3">
-        <v>53.42</v>
+        <v>53.17</v>
       </c>
       <c r="S3">
-        <v>61.97</v>
+        <v>61.81</v>
       </c>
       <c r="T3">
-        <v>-26.29</v>
+        <v>-27.81</v>
       </c>
       <c r="U3" t="s">
         <v>46</v>
@@ -1106,43 +1077,43 @@
         <v>0</v>
       </c>
       <c r="Y3">
-        <v>32.45</v>
+        <v>29.59</v>
       </c>
       <c r="Z3">
-        <v>-2.25</v>
+        <v>-2.28</v>
       </c>
       <c r="AA3">
-        <v>-2.02</v>
+        <v>-2.07</v>
       </c>
       <c r="AB3">
-        <v>-0.23</v>
+        <v>-0.21</v>
       </c>
       <c r="AC3">
-        <v>21.15</v>
+        <v>35.3</v>
       </c>
       <c r="AD3">
-        <v>8.289999999999999</v>
+        <v>19.44</v>
       </c>
       <c r="AE3">
-        <v>1.66</v>
+        <v>1.62</v>
       </c>
       <c r="AF3">
-        <v>113.19</v>
+        <v>-22.38</v>
       </c>
       <c r="AG3">
-        <v>53.78</v>
+        <v>53.26</v>
       </c>
       <c r="AH3">
-        <v>43.97</v>
+        <v>43.64</v>
       </c>
       <c r="AI3">
         <v>49.46</v>
       </c>
       <c r="AJ3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="AK3">
-        <v>50.43</v>
+        <v>46.3</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1153,10 +1124,10 @@
         <v>45</v>
       </c>
       <c r="C4">
-        <v>2969</v>
+        <v>2921.1</v>
       </c>
       <c r="D4">
-        <v>-0.1</v>
+        <v>-1.61</v>
       </c>
       <c r="E4">
         <v>3380.5</v>
@@ -1165,46 +1136,46 @@
         <v>2531.1</v>
       </c>
       <c r="G4">
-        <v>-12.17</v>
+        <v>-13.59</v>
       </c>
       <c r="H4">
-        <v>17.3</v>
+        <v>15.41</v>
       </c>
       <c r="I4">
-        <v>-5.75</v>
+        <v>-5.77</v>
       </c>
       <c r="J4">
-        <v>-10.3</v>
+        <v>-12.07</v>
       </c>
       <c r="K4">
-        <v>-6.95</v>
+        <v>-6.82</v>
       </c>
       <c r="L4">
-        <v>7.69</v>
+        <v>4.71</v>
       </c>
       <c r="M4">
-        <v>13.7</v>
+        <v>13.43</v>
       </c>
       <c r="N4">
         <v>50</v>
       </c>
       <c r="O4">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="P4">
-        <v>3012.98</v>
+        <v>2977.2</v>
       </c>
       <c r="Q4">
-        <v>3165.27</v>
+        <v>3146.21</v>
       </c>
       <c r="R4">
-        <v>3219.39</v>
+        <v>3215.56</v>
       </c>
       <c r="S4">
-        <v>2978.44</v>
+        <v>2979.01</v>
       </c>
       <c r="T4">
-        <v>-0.32</v>
+        <v>-1.94</v>
       </c>
       <c r="U4" t="s">
         <v>46</v>
@@ -1219,43 +1190,43 @@
         <v>1</v>
       </c>
       <c r="Y4">
-        <v>29.42</v>
+        <v>26.61</v>
       </c>
       <c r="Z4">
-        <v>-67.83</v>
+        <v>-75.94</v>
       </c>
       <c r="AA4">
-        <v>-41.83</v>
+        <v>-48.65</v>
       </c>
       <c r="AB4">
-        <v>-26</v>
+        <v>-27.28</v>
       </c>
       <c r="AC4">
         <v>4.89</v>
       </c>
       <c r="AD4">
-        <v>2.84</v>
+        <v>4.14</v>
       </c>
       <c r="AE4">
-        <v>62.77</v>
+        <v>63.1</v>
       </c>
       <c r="AF4">
-        <v>-57.64</v>
+        <v>-68.81999999999999</v>
       </c>
       <c r="AG4">
-        <v>3386.12</v>
+        <v>3382.51</v>
       </c>
       <c r="AH4">
-        <v>2944.43</v>
+        <v>2909.91</v>
       </c>
       <c r="AI4">
-        <v>3150.47</v>
+        <v>3118.71</v>
       </c>
       <c r="AJ4" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="AK4">
-        <v>55.85</v>
+        <v>59.68</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1266,10 +1237,10 @@
         <v>45</v>
       </c>
       <c r="C5">
-        <v>940.5</v>
+        <v>910.85</v>
       </c>
       <c r="D5">
-        <v>0.22</v>
+        <v>-3.15</v>
       </c>
       <c r="E5">
         <v>1149.7</v>
@@ -1278,46 +1249,46 @@
         <v>760.1</v>
       </c>
       <c r="G5">
-        <v>-18.2</v>
+        <v>-20.77</v>
       </c>
       <c r="H5">
-        <v>23.73</v>
+        <v>19.83</v>
       </c>
       <c r="I5">
-        <v>-1.61</v>
+        <v>-4.64</v>
       </c>
       <c r="J5">
-        <v>-6.88</v>
+        <v>-9.91</v>
       </c>
       <c r="K5">
-        <v>-2.99</v>
+        <v>-6.26</v>
       </c>
       <c r="L5">
-        <v>23.43</v>
+        <v>18.92</v>
       </c>
       <c r="M5">
-        <v>15.26</v>
+        <v>14.44</v>
       </c>
       <c r="N5">
         <v>62</v>
       </c>
       <c r="O5">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="P5">
-        <v>943.55</v>
+        <v>934.6799999999999</v>
       </c>
       <c r="Q5">
-        <v>976.3200000000001</v>
+        <v>971.5700000000001</v>
       </c>
       <c r="R5">
-        <v>1003.86</v>
+        <v>1003.17</v>
       </c>
       <c r="S5">
-        <v>982.13</v>
+        <v>982.4400000000001</v>
       </c>
       <c r="T5">
-        <v>-4.24</v>
+        <v>-7.29</v>
       </c>
       <c r="U5" t="s">
         <v>46</v>
@@ -1332,43 +1303,43 @@
         <v>1</v>
       </c>
       <c r="Y5">
-        <v>35.72</v>
+        <v>29.36</v>
       </c>
       <c r="Z5">
-        <v>-18.45</v>
+        <v>-21.02</v>
       </c>
       <c r="AA5">
-        <v>-14.39</v>
+        <v>-15.72</v>
       </c>
       <c r="AB5">
-        <v>-4.05</v>
+        <v>-5.31</v>
       </c>
       <c r="AC5">
-        <v>5.89</v>
+        <v>3.13</v>
       </c>
       <c r="AD5">
-        <v>8.58</v>
+        <v>5.22</v>
       </c>
       <c r="AE5">
-        <v>21.44</v>
+        <v>22.03</v>
       </c>
       <c r="AF5">
-        <v>-20.24</v>
+        <v>-0.9</v>
       </c>
       <c r="AG5">
-        <v>1029.01</v>
+        <v>1029.85</v>
       </c>
       <c r="AH5">
-        <v>923.64</v>
+        <v>913.28</v>
       </c>
       <c r="AI5">
-        <v>1000.57</v>
+        <v>990.4299999999999</v>
       </c>
       <c r="AJ5" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="AK5">
-        <v>32.54</v>
+        <v>36.07</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1379,10 +1350,10 @@
         <v>45</v>
       </c>
       <c r="C6">
-        <v>13.21</v>
+        <v>13.18</v>
       </c>
       <c r="D6">
-        <v>3.69</v>
+        <v>-0.23</v>
       </c>
       <c r="E6">
         <v>15.6</v>
@@ -1391,46 +1362,46 @@
         <v>8.359999999999999</v>
       </c>
       <c r="G6">
-        <v>-15.32</v>
+        <v>-15.51</v>
       </c>
       <c r="H6">
-        <v>58.01</v>
+        <v>57.66</v>
       </c>
       <c r="I6">
-        <v>-1.93</v>
+        <v>-2.8</v>
       </c>
       <c r="J6">
-        <v>-8.77</v>
+        <v>-12.25</v>
       </c>
       <c r="K6">
-        <v>-4.62</v>
+        <v>-5.38</v>
       </c>
       <c r="L6">
-        <v>62.48</v>
+        <v>54.69</v>
       </c>
       <c r="M6">
-        <v>2.9</v>
+        <v>3.04</v>
       </c>
       <c r="N6">
         <v>87</v>
       </c>
       <c r="O6">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="P6">
-        <v>13.02</v>
+        <v>12.94</v>
       </c>
       <c r="Q6">
-        <v>14.14</v>
+        <v>14.02</v>
       </c>
       <c r="R6">
         <v>13.9</v>
       </c>
       <c r="S6">
-        <v>12.26</v>
+        <v>12.27</v>
       </c>
       <c r="T6">
-        <v>7.75</v>
+        <v>7.42</v>
       </c>
       <c r="U6" t="s">
         <v>47</v>
@@ -1445,43 +1416,43 @@
         <v>3</v>
       </c>
       <c r="Y6">
-        <v>41.63</v>
+        <v>41.33</v>
       </c>
       <c r="Z6">
         <v>-0.35</v>
       </c>
       <c r="AA6">
-        <v>-0.16</v>
+        <v>-0.2</v>
       </c>
       <c r="AB6">
-        <v>-0.18</v>
+        <v>-0.15</v>
       </c>
       <c r="AC6">
-        <v>17.8</v>
+        <v>32.29</v>
       </c>
       <c r="AD6">
-        <v>7.42</v>
+        <v>17.62</v>
       </c>
       <c r="AE6">
-        <v>0.5</v>
+        <v>0.49</v>
       </c>
       <c r="AF6">
-        <v>-30.3</v>
+        <v>-22.62</v>
       </c>
       <c r="AG6">
-        <v>15.9</v>
+        <v>15.69</v>
       </c>
       <c r="AH6">
-        <v>12.39</v>
+        <v>12.36</v>
       </c>
       <c r="AI6">
         <v>14.25</v>
       </c>
       <c r="AJ6" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="AK6">
-        <v>41.33</v>
+        <v>39.01</v>
       </c>
     </row>
     <row r="7" spans="1:37">
@@ -1492,10 +1463,10 @@
         <v>45</v>
       </c>
       <c r="C7">
-        <v>10.76</v>
+        <v>10.81</v>
       </c>
       <c r="D7">
-        <v>4.98</v>
+        <v>0.46</v>
       </c>
       <c r="E7">
         <v>13.92</v>
@@ -1504,46 +1475,46 @@
         <v>4.69</v>
       </c>
       <c r="G7">
-        <v>-22.7</v>
+        <v>-22.34</v>
       </c>
       <c r="H7">
-        <v>129.42</v>
+        <v>130.49</v>
       </c>
       <c r="I7">
-        <v>-2.36</v>
+        <v>-0.28</v>
       </c>
       <c r="J7">
-        <v>-2.62</v>
+        <v>-0.83</v>
       </c>
       <c r="K7">
-        <v>1.8</v>
+        <v>4.34</v>
       </c>
       <c r="L7">
-        <v>97.79000000000001</v>
+        <v>94.42</v>
       </c>
       <c r="M7">
-        <v>-30.73</v>
+        <v>-30.9</v>
       </c>
       <c r="N7">
         <v>99</v>
       </c>
       <c r="O7">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="P7">
-        <v>10.7</v>
+        <v>10.69</v>
       </c>
       <c r="Q7">
-        <v>11.45</v>
+        <v>11.44</v>
       </c>
       <c r="R7">
-        <v>11.68</v>
+        <v>11.66</v>
       </c>
       <c r="S7">
-        <v>10.83</v>
+        <v>10.84</v>
       </c>
       <c r="T7">
-        <v>-0.66</v>
+        <v>-0.26</v>
       </c>
       <c r="U7" t="s">
         <v>46</v>
@@ -1558,43 +1529,43 @@
         <v>1</v>
       </c>
       <c r="Y7">
-        <v>41.8</v>
+        <v>42.63</v>
       </c>
       <c r="Z7">
         <v>-0.26</v>
       </c>
       <c r="AA7">
-        <v>-0.13</v>
+        <v>-0.16</v>
       </c>
       <c r="AB7">
-        <v>-0.12</v>
+        <v>-0.1</v>
       </c>
       <c r="AC7">
-        <v>10.5</v>
+        <v>22.11</v>
       </c>
       <c r="AD7">
-        <v>4.69</v>
+        <v>11.46</v>
       </c>
       <c r="AE7">
-        <v>0.51</v>
+        <v>0.5</v>
       </c>
       <c r="AF7">
-        <v>13.54</v>
+        <v>-18.11</v>
       </c>
       <c r="AG7">
-        <v>12.68</v>
+        <v>12.69</v>
       </c>
       <c r="AH7">
-        <v>10.23</v>
+        <v>10.19</v>
       </c>
       <c r="AI7">
         <v>12.04</v>
       </c>
       <c r="AJ7" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="AK7">
-        <v>39.67</v>
+        <v>36.63</v>
       </c>
     </row>
     <row r="8" spans="1:37">
@@ -1605,10 +1576,10 @@
         <v>45</v>
       </c>
       <c r="C8">
-        <v>4067.1</v>
+        <v>4076.3</v>
       </c>
       <c r="D8">
-        <v>2.07</v>
+        <v>0.23</v>
       </c>
       <c r="E8">
         <v>5809.5</v>
@@ -1617,25 +1588,25 @@
         <v>3892.3</v>
       </c>
       <c r="G8">
-        <v>-29.99</v>
+        <v>-29.83</v>
       </c>
       <c r="H8">
-        <v>4.49</v>
+        <v>4.73</v>
       </c>
       <c r="I8">
-        <v>1.74</v>
+        <v>1.21</v>
       </c>
       <c r="J8">
-        <v>-6.6</v>
+        <v>-5.72</v>
       </c>
       <c r="K8">
-        <v>-7.26</v>
+        <v>-5.37</v>
       </c>
       <c r="L8">
-        <v>-24.05</v>
+        <v>-24.58</v>
       </c>
       <c r="M8">
-        <v>16.34</v>
+        <v>15.95</v>
       </c>
       <c r="N8">
         <v>26</v>
@@ -1644,19 +1615,19 @@
         <v>32</v>
       </c>
       <c r="P8">
-        <v>3985.66</v>
+        <v>3995.38</v>
       </c>
       <c r="Q8">
-        <v>4070.3</v>
+        <v>4059.18</v>
       </c>
       <c r="R8">
-        <v>4247.42</v>
+        <v>4242.05</v>
       </c>
       <c r="S8">
-        <v>4518.55</v>
+        <v>4512.4</v>
       </c>
       <c r="T8">
-        <v>-9.99</v>
+        <v>-9.66</v>
       </c>
       <c r="U8" t="s">
         <v>46</v>
@@ -1671,43 +1642,43 @@
         <v>0</v>
       </c>
       <c r="Y8">
-        <v>46.35</v>
+        <v>47.11</v>
       </c>
       <c r="Z8">
-        <v>-82.34</v>
+        <v>-72.26000000000001</v>
       </c>
       <c r="AA8">
-        <v>-86.77</v>
+        <v>-83.87</v>
       </c>
       <c r="AB8">
-        <v>4.43</v>
+        <v>11.61</v>
       </c>
       <c r="AC8">
-        <v>66.67</v>
+        <v>100</v>
       </c>
       <c r="AD8">
-        <v>40.51</v>
+        <v>67.27</v>
       </c>
       <c r="AE8">
-        <v>110.44</v>
+        <v>105.55</v>
       </c>
       <c r="AF8">
-        <v>-45.15</v>
+        <v>-48.04</v>
       </c>
       <c r="AG8">
-        <v>4278.41</v>
+        <v>4237.55</v>
       </c>
       <c r="AH8">
-        <v>3862.18</v>
+        <v>3880.8</v>
       </c>
       <c r="AI8">
         <v>4247.59</v>
       </c>
       <c r="AJ8" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="AK8">
-        <v>46.64</v>
+        <v>40.44</v>
       </c>
     </row>
     <row r="9" spans="1:37">
@@ -1718,10 +1689,10 @@
         <v>45</v>
       </c>
       <c r="C9">
-        <v>10750</v>
+        <v>10658</v>
       </c>
       <c r="D9">
-        <v>-0.92</v>
+        <v>-0.86</v>
       </c>
       <c r="E9">
         <v>13052</v>
@@ -1730,46 +1701,46 @@
         <v>10362</v>
       </c>
       <c r="G9">
-        <v>-17.64</v>
+        <v>-18.34</v>
       </c>
       <c r="H9">
-        <v>3.74</v>
+        <v>2.86</v>
       </c>
       <c r="I9">
-        <v>-2.49</v>
+        <v>-1.58</v>
       </c>
       <c r="J9">
-        <v>-4.66</v>
+        <v>-6.57</v>
       </c>
       <c r="K9">
-        <v>-7.72</v>
+        <v>-6.12</v>
       </c>
       <c r="L9">
-        <v>-12.04</v>
+        <v>-11.88</v>
       </c>
       <c r="M9">
-        <v>8.35</v>
+        <v>8.19</v>
       </c>
       <c r="N9">
         <v>38</v>
       </c>
       <c r="O9">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="P9">
-        <v>10819</v>
+        <v>10784.8</v>
       </c>
       <c r="Q9">
-        <v>10941.2</v>
+        <v>10915.35</v>
       </c>
       <c r="R9">
-        <v>11412.46</v>
+        <v>11388</v>
       </c>
       <c r="S9">
-        <v>11699.86</v>
+        <v>11695.46</v>
       </c>
       <c r="T9">
-        <v>-8.119999999999999</v>
+        <v>-8.869999999999999</v>
       </c>
       <c r="U9" t="s">
         <v>46</v>
@@ -1784,43 +1755,43 @@
         <v>0</v>
       </c>
       <c r="Y9">
-        <v>40.07</v>
+        <v>37.96</v>
       </c>
       <c r="Z9">
-        <v>-150.32</v>
+        <v>-159.93</v>
       </c>
       <c r="AA9">
-        <v>-150.9</v>
+        <v>-152.71</v>
       </c>
       <c r="AB9">
-        <v>0.58</v>
+        <v>-7.22</v>
       </c>
       <c r="AC9">
-        <v>61.2</v>
+        <v>58.57</v>
       </c>
       <c r="AD9">
-        <v>63.15</v>
+        <v>62.23</v>
       </c>
       <c r="AE9">
-        <v>203.44</v>
+        <v>204.41</v>
       </c>
       <c r="AF9">
-        <v>-9.77</v>
+        <v>-4.24</v>
       </c>
       <c r="AG9">
-        <v>11256.36</v>
+        <v>11234.55</v>
       </c>
       <c r="AH9">
-        <v>10626.04</v>
+        <v>10596.15</v>
       </c>
       <c r="AI9">
-        <v>11348.57</v>
+        <v>11316.74</v>
       </c>
       <c r="AJ9" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="AK9">
-        <v>32.41</v>
+        <v>35.14</v>
       </c>
     </row>
   </sheetData>
@@ -1971,7 +1942,7 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -1981,47 +1952,12 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="D2" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="F2" s="3" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6">
-      <c r="A3" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="B3" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="C3" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="D3" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="E3" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="F3" s="4" t="s">
-        <v>60</v>
+        <v>50</v>
       </c>
     </row>
     <row r="5" spans="1:6">
       <c r="A5" s="2" t="s">
-        <v>61</v>
+        <v>51</v>
       </c>
       <c r="B5" s="2"/>
       <c r="C5" s="2"/>
@@ -2029,1108 +1965,1108 @@
       <c r="E5" s="2"/>
     </row>
     <row r="6" spans="1:6">
-      <c r="A6" s="3" t="s">
+      <c r="A6" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B6" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>65</v>
+      <c r="B6" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>55</v>
       </c>
     </row>
     <row r="7" spans="1:6">
-      <c r="A7" s="5" t="s">
+      <c r="A7" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B7" s="5" t="s">
+      <c r="B7" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C7" s="6">
-        <v>-4.95</v>
-      </c>
-      <c r="D7" s="6">
+      <c r="C7" s="5">
         <v>-5.75</v>
       </c>
-      <c r="E7" s="7">
-        <v>-0.8</v>
+      <c r="D7" s="5">
+        <v>-8.1</v>
+      </c>
+      <c r="E7" s="6">
+        <v>-2.35</v>
       </c>
     </row>
     <row r="8" spans="1:6">
-      <c r="A8" s="5" t="s">
+      <c r="A8" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B8" s="5" t="s">
+      <c r="B8" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C8" s="6">
-        <v>-12.15</v>
-      </c>
-      <c r="D8" s="6">
+      <c r="C8" s="5">
         <v>-9.380000000000001</v>
       </c>
-      <c r="E8" s="8">
-        <v>2.77</v>
+      <c r="D8" s="5">
+        <v>-15.76</v>
+      </c>
+      <c r="E8" s="6">
+        <v>-6.38</v>
       </c>
     </row>
     <row r="9" spans="1:6">
-      <c r="A9" s="5" t="s">
+      <c r="A9" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B9" s="5" t="s">
+      <c r="B9" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C9" s="6">
-        <v>-9.800000000000001</v>
-      </c>
-      <c r="D9" s="6">
+      <c r="C9" s="5">
         <v>-10.3</v>
       </c>
-      <c r="E9" s="7">
-        <v>-0.5</v>
+      <c r="D9" s="5">
+        <v>-12.07</v>
+      </c>
+      <c r="E9" s="6">
+        <v>-1.77</v>
       </c>
     </row>
     <row r="10" spans="1:6">
-      <c r="A10" s="5" t="s">
+      <c r="A10" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="B10" s="5" t="s">
+      <c r="B10" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C10" s="6">
-        <v>-7.06</v>
-      </c>
-      <c r="D10" s="6">
+      <c r="C10" s="5">
         <v>-6.88</v>
       </c>
-      <c r="E10" s="8">
-        <v>0.18</v>
+      <c r="D10" s="5">
+        <v>-9.91</v>
+      </c>
+      <c r="E10" s="6">
+        <v>-3.03</v>
       </c>
     </row>
     <row r="11" spans="1:6">
-      <c r="A11" s="5" t="s">
+      <c r="A11" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="B11" s="5" t="s">
+      <c r="B11" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C11" s="6">
-        <v>-12.32</v>
-      </c>
-      <c r="D11" s="6">
+      <c r="C11" s="5">
         <v>-8.77</v>
       </c>
-      <c r="E11" s="8">
-        <v>3.55</v>
+      <c r="D11" s="5">
+        <v>-12.25</v>
+      </c>
+      <c r="E11" s="6">
+        <v>-3.48</v>
       </c>
     </row>
     <row r="12" spans="1:6">
-      <c r="A12" s="5" t="s">
+      <c r="A12" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="B12" s="5" t="s">
+      <c r="B12" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C12" s="6">
-        <v>-9.050000000000001</v>
-      </c>
-      <c r="D12" s="6">
+      <c r="C12" s="5">
         <v>-2.62</v>
       </c>
-      <c r="E12" s="8">
-        <v>6.43</v>
+      <c r="D12" s="5">
+        <v>-0.83</v>
+      </c>
+      <c r="E12" s="7">
+        <v>1.79</v>
       </c>
     </row>
     <row r="13" spans="1:6">
-      <c r="A13" s="5" t="s">
+      <c r="A13" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="B13" s="5" t="s">
+      <c r="B13" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C13" s="6">
-        <v>-7.87</v>
-      </c>
-      <c r="D13" s="6">
+      <c r="C13" s="5">
         <v>-6.6</v>
       </c>
-      <c r="E13" s="8">
-        <v>1.27</v>
+      <c r="D13" s="5">
+        <v>-5.72</v>
+      </c>
+      <c r="E13" s="7">
+        <v>0.88</v>
       </c>
     </row>
     <row r="14" spans="1:6">
-      <c r="A14" s="5" t="s">
+      <c r="A14" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="B14" s="5" t="s">
+      <c r="B14" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C14" s="6">
-        <v>-4.77</v>
-      </c>
-      <c r="D14" s="6">
+      <c r="C14" s="5">
         <v>-4.66</v>
       </c>
-      <c r="E14" s="8">
-        <v>0.11</v>
+      <c r="D14" s="5">
+        <v>-6.57</v>
+      </c>
+      <c r="E14" s="6">
+        <v>-1.91</v>
       </c>
     </row>
     <row r="15" spans="1:6">
-      <c r="A15" s="5" t="s">
+      <c r="A15" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B15" s="5" t="s">
+      <c r="B15" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C15" s="6">
-        <v>-3.23</v>
-      </c>
-      <c r="D15" s="6">
+      <c r="C15" s="5">
         <v>-0.99</v>
       </c>
-      <c r="E15" s="8">
-        <v>2.24</v>
+      <c r="D15" s="5">
+        <v>-1.56</v>
+      </c>
+      <c r="E15" s="6">
+        <v>-0.57</v>
       </c>
     </row>
     <row r="16" spans="1:6">
-      <c r="A16" s="5" t="s">
+      <c r="A16" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B16" s="5" t="s">
+      <c r="B16" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C16" s="6">
+      <c r="C16" s="5">
+        <v>-4.01</v>
+      </c>
+      <c r="D16" s="5">
+        <v>-3.5</v>
+      </c>
+      <c r="E16" s="7">
+        <v>0.51</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C17" s="5">
+        <v>-5.75</v>
+      </c>
+      <c r="D17" s="5">
+        <v>-5.77</v>
+      </c>
+      <c r="E17" s="6">
+        <v>-0.02</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C18" s="5">
+        <v>-1.61</v>
+      </c>
+      <c r="D18" s="5">
+        <v>-4.64</v>
+      </c>
+      <c r="E18" s="6">
+        <v>-3.03</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C19" s="5">
+        <v>-1.93</v>
+      </c>
+      <c r="D19" s="5">
+        <v>-2.8</v>
+      </c>
+      <c r="E19" s="6">
+        <v>-0.87</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C20" s="5">
+        <v>-2.36</v>
+      </c>
+      <c r="D20" s="5">
+        <v>-0.28</v>
+      </c>
+      <c r="E20" s="7">
+        <v>2.08</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C21" s="5">
+        <v>1.74</v>
+      </c>
+      <c r="D21" s="5">
+        <v>1.21</v>
+      </c>
+      <c r="E21" s="6">
+        <v>-0.53</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C22" s="5">
+        <v>-2.49</v>
+      </c>
+      <c r="D22" s="5">
+        <v>-1.58</v>
+      </c>
+      <c r="E22" s="7">
+        <v>0.91</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C23" s="5">
+        <v>29.6</v>
+      </c>
+      <c r="D23" s="5">
+        <v>24.1</v>
+      </c>
+      <c r="E23" s="6">
+        <v>-5.5</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C24" s="5">
+        <v>-45.93</v>
+      </c>
+      <c r="D24" s="5">
+        <v>-48.35</v>
+      </c>
+      <c r="E24" s="6">
+        <v>-2.42</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B25" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C25" s="5">
+        <v>7.69</v>
+      </c>
+      <c r="D25" s="5">
+        <v>4.71</v>
+      </c>
+      <c r="E25" s="6">
+        <v>-2.98</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C26" s="5">
+        <v>23.43</v>
+      </c>
+      <c r="D26" s="5">
+        <v>18.92</v>
+      </c>
+      <c r="E26" s="6">
+        <v>-4.51</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B27" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C27" s="5">
+        <v>62.48</v>
+      </c>
+      <c r="D27" s="5">
+        <v>54.69</v>
+      </c>
+      <c r="E27" s="6">
+        <v>-7.79</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B28" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C28" s="5">
+        <v>97.79000000000001</v>
+      </c>
+      <c r="D28" s="5">
+        <v>94.42</v>
+      </c>
+      <c r="E28" s="6">
+        <v>-3.37</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="B29" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C29" s="5">
+        <v>-24.05</v>
+      </c>
+      <c r="D29" s="5">
+        <v>-24.58</v>
+      </c>
+      <c r="E29" s="6">
+        <v>-0.53</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="B30" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C30" s="5">
+        <v>-12.04</v>
+      </c>
+      <c r="D30" s="5">
+        <v>-11.88</v>
+      </c>
+      <c r="E30" s="7">
+        <v>0.16</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5">
+      <c r="A31" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B31" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C31" s="5">
+        <v>-6.54</v>
+      </c>
+      <c r="D31" s="5">
+        <v>-3.54</v>
+      </c>
+      <c r="E31" s="7">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5">
+      <c r="A32" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B32" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C32" s="5">
+        <v>-23.39</v>
+      </c>
+      <c r="D32" s="5">
+        <v>-23.48</v>
+      </c>
+      <c r="E32" s="6">
+        <v>-0.09</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5">
+      <c r="A33" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B33" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C33" s="5">
+        <v>-6.95</v>
+      </c>
+      <c r="D33" s="5">
+        <v>-6.82</v>
+      </c>
+      <c r="E33" s="7">
+        <v>0.13</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5">
+      <c r="A34" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B34" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C34" s="5">
+        <v>-2.99</v>
+      </c>
+      <c r="D34" s="5">
+        <v>-6.26</v>
+      </c>
+      <c r="E34" s="6">
+        <v>-3.27</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5">
+      <c r="A35" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B35" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C35" s="5">
+        <v>-4.62</v>
+      </c>
+      <c r="D35" s="5">
+        <v>-5.38</v>
+      </c>
+      <c r="E35" s="6">
+        <v>-0.76</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5">
+      <c r="A36" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B36" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C36" s="5">
+        <v>1.8</v>
+      </c>
+      <c r="D36" s="5">
+        <v>4.34</v>
+      </c>
+      <c r="E36" s="7">
+        <v>2.54</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5">
+      <c r="A37" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="B37" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C37" s="5">
+        <v>-7.26</v>
+      </c>
+      <c r="D37" s="5">
+        <v>-5.37</v>
+      </c>
+      <c r="E37" s="7">
+        <v>1.89</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5">
+      <c r="A38" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="B38" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C38" s="5">
+        <v>-7.72</v>
+      </c>
+      <c r="D38" s="5">
+        <v>-6.12</v>
+      </c>
+      <c r="E38" s="7">
+        <v>1.6</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5">
+      <c r="A39" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B39" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C39" s="5">
+        <v>-10.78</v>
+      </c>
+      <c r="D39" s="5">
+        <v>-12.39</v>
+      </c>
+      <c r="E39" s="6">
+        <v>-1.61</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5">
+      <c r="A40" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B40" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C40" s="5">
+        <v>-48.09</v>
+      </c>
+      <c r="D40" s="5">
+        <v>-49.29</v>
+      </c>
+      <c r="E40" s="6">
+        <v>-1.2</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5">
+      <c r="A41" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B41" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C41" s="5">
+        <v>-12.17</v>
+      </c>
+      <c r="D41" s="5">
+        <v>-13.59</v>
+      </c>
+      <c r="E41" s="6">
+        <v>-1.42</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5">
+      <c r="A42" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B42" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C42" s="5">
+        <v>-18.2</v>
+      </c>
+      <c r="D42" s="5">
+        <v>-20.77</v>
+      </c>
+      <c r="E42" s="6">
+        <v>-2.57</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5">
+      <c r="A43" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B43" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C43" s="5">
+        <v>-15.32</v>
+      </c>
+      <c r="D43" s="5">
+        <v>-15.51</v>
+      </c>
+      <c r="E43" s="6">
+        <v>-0.19</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5">
+      <c r="A44" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B44" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C44" s="5">
+        <v>-22.7</v>
+      </c>
+      <c r="D44" s="5">
+        <v>-22.34</v>
+      </c>
+      <c r="E44" s="7">
+        <v>0.36</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5">
+      <c r="A45" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="B45" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C45" s="5">
+        <v>-29.99</v>
+      </c>
+      <c r="D45" s="5">
+        <v>-29.83</v>
+      </c>
+      <c r="E45" s="7">
+        <v>0.16</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5">
+      <c r="A46" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="B46" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C46" s="5">
+        <v>-17.64</v>
+      </c>
+      <c r="D46" s="5">
+        <v>-18.34</v>
+      </c>
+      <c r="E46" s="6">
+        <v>-0.7</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5">
+      <c r="A47" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B47" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C47" s="5">
+        <v>378.9</v>
+      </c>
+      <c r="D47" s="5">
+        <v>372.1</v>
+      </c>
+      <c r="E47" s="6">
+        <v>-6.8</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5">
+      <c r="A48" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B48" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C48" s="5">
+        <v>45.68</v>
+      </c>
+      <c r="D48" s="5">
+        <v>44.62</v>
+      </c>
+      <c r="E48" s="6">
+        <v>-1.06</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5">
+      <c r="A49" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B49" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C49" s="5">
+        <v>2969</v>
+      </c>
+      <c r="D49" s="5">
+        <v>2921.1</v>
+      </c>
+      <c r="E49" s="6">
+        <v>-47.9</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5">
+      <c r="A50" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B50" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C50" s="5">
+        <v>940.5</v>
+      </c>
+      <c r="D50" s="5">
+        <v>910.85</v>
+      </c>
+      <c r="E50" s="6">
+        <v>-29.65</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5">
+      <c r="A51" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B51" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C51" s="5">
+        <v>13.21</v>
+      </c>
+      <c r="D51" s="5">
+        <v>13.18</v>
+      </c>
+      <c r="E51" s="6">
+        <v>-0.03</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5">
+      <c r="A52" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B52" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C52" s="5">
+        <v>10.76</v>
+      </c>
+      <c r="D52" s="5">
+        <v>10.81</v>
+      </c>
+      <c r="E52" s="7">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5">
+      <c r="A53" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="B53" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C53" s="5">
+        <v>4067.1</v>
+      </c>
+      <c r="D53" s="5">
+        <v>4076.3</v>
+      </c>
+      <c r="E53" s="7">
+        <v>9.199999999999999</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5">
+      <c r="A54" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="B54" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C54" s="5">
+        <v>10750</v>
+      </c>
+      <c r="D54" s="5">
+        <v>10658</v>
+      </c>
+      <c r="E54" s="6">
+        <v>-92</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5">
+      <c r="A55" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B55" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C55" s="5">
+        <v>41.09</v>
+      </c>
+      <c r="D55" s="5">
+        <v>37.46</v>
+      </c>
+      <c r="E55" s="6">
+        <v>-3.63</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5">
+      <c r="A56" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B56" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C56" s="5">
+        <v>32.45</v>
+      </c>
+      <c r="D56" s="5">
+        <v>29.59</v>
+      </c>
+      <c r="E56" s="6">
+        <v>-2.86</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5">
+      <c r="A57" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B57" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C57" s="5">
+        <v>29.42</v>
+      </c>
+      <c r="D57" s="5">
+        <v>26.61</v>
+      </c>
+      <c r="E57" s="6">
+        <v>-2.81</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5">
+      <c r="A58" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B58" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C58" s="5">
+        <v>35.72</v>
+      </c>
+      <c r="D58" s="5">
+        <v>29.36</v>
+      </c>
+      <c r="E58" s="6">
+        <v>-6.36</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5">
+      <c r="A59" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B59" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C59" s="5">
+        <v>41.63</v>
+      </c>
+      <c r="D59" s="5">
+        <v>41.33</v>
+      </c>
+      <c r="E59" s="6">
+        <v>-0.3</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5">
+      <c r="A60" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B60" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C60" s="5">
+        <v>41.8</v>
+      </c>
+      <c r="D60" s="5">
+        <v>42.63</v>
+      </c>
+      <c r="E60" s="7">
+        <v>0.83</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5">
+      <c r="A61" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="B61" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C61" s="5">
+        <v>46.35</v>
+      </c>
+      <c r="D61" s="5">
+        <v>47.11</v>
+      </c>
+      <c r="E61" s="7">
+        <v>0.76</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5">
+      <c r="A62" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="B62" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C62" s="5">
+        <v>40.07</v>
+      </c>
+      <c r="D62" s="5">
+        <v>37.96</v>
+      </c>
+      <c r="E62" s="6">
+        <v>-2.11</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5">
+      <c r="A63" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B63" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C63" s="5">
+        <v>82.95</v>
+      </c>
+      <c r="D63" s="5">
+        <v>56.67</v>
+      </c>
+      <c r="E63" s="6">
+        <v>-26.28</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5">
+      <c r="A64" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B64" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C64" s="5">
+        <v>113.19</v>
+      </c>
+      <c r="D64" s="5">
+        <v>-22.38</v>
+      </c>
+      <c r="E64" s="6">
+        <v>-135.57</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5">
+      <c r="A65" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B65" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C65" s="5">
+        <v>-57.64</v>
+      </c>
+      <c r="D65" s="5">
+        <v>-68.81999999999999</v>
+      </c>
+      <c r="E65" s="6">
+        <v>-11.18</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5">
+      <c r="A66" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B66" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C66" s="5">
+        <v>-20.24</v>
+      </c>
+      <c r="D66" s="5">
+        <v>-0.9</v>
+      </c>
+      <c r="E66" s="7">
+        <v>19.34</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5">
+      <c r="A67" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B67" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C67" s="5">
+        <v>-30.3</v>
+      </c>
+      <c r="D67" s="5">
+        <v>-22.62</v>
+      </c>
+      <c r="E67" s="7">
+        <v>7.68</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5">
+      <c r="A68" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B68" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C68" s="5">
+        <v>13.54</v>
+      </c>
+      <c r="D68" s="5">
+        <v>-18.11</v>
+      </c>
+      <c r="E68" s="6">
+        <v>-31.65</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5">
+      <c r="A69" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="B69" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C69" s="5">
+        <v>-45.15</v>
+      </c>
+      <c r="D69" s="5">
+        <v>-48.04</v>
+      </c>
+      <c r="E69" s="6">
+        <v>-2.89</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5">
+      <c r="A70" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="B70" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C70" s="5">
         <v>-9.77</v>
       </c>
-      <c r="D16" s="6">
-        <v>-4.01</v>
-      </c>
-      <c r="E16" s="8">
-        <v>5.76</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5">
-      <c r="A17" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B17" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C17" s="6">
-        <v>-6.86</v>
-      </c>
-      <c r="D17" s="6">
-        <v>-5.75</v>
-      </c>
-      <c r="E17" s="8">
-        <v>1.11</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5">
-      <c r="A18" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B18" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C18" s="6">
-        <v>-3.95</v>
-      </c>
-      <c r="D18" s="6">
-        <v>-1.61</v>
-      </c>
-      <c r="E18" s="8">
-        <v>2.34</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5">
-      <c r="A19" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B19" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C19" s="6">
-        <v>-10.66</v>
-      </c>
-      <c r="D19" s="6">
-        <v>-1.93</v>
-      </c>
-      <c r="E19" s="8">
-        <v>8.73</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5">
-      <c r="A20" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B20" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C20" s="6">
-        <v>-11.41</v>
-      </c>
-      <c r="D20" s="6">
-        <v>-2.36</v>
-      </c>
-      <c r="E20" s="8">
-        <v>9.050000000000001</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5">
-      <c r="A21" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B21" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C21" s="6">
-        <v>-0.75</v>
-      </c>
-      <c r="D21" s="6">
-        <v>1.74</v>
-      </c>
-      <c r="E21" s="8">
-        <v>2.49</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5">
-      <c r="A22" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="B22" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C22" s="6">
-        <v>-2.73</v>
-      </c>
-      <c r="D22" s="6">
-        <v>-2.49</v>
-      </c>
-      <c r="E22" s="8">
-        <v>0.24</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5">
-      <c r="A23" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B23" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C23" s="6">
-        <v>30.21</v>
-      </c>
-      <c r="D23" s="6">
-        <v>29.6</v>
-      </c>
-      <c r="E23" s="7">
-        <v>-0.61</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5">
-      <c r="A24" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B24" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C24" s="6">
-        <v>-47.84</v>
-      </c>
-      <c r="D24" s="6">
-        <v>-45.93</v>
-      </c>
-      <c r="E24" s="8">
-        <v>1.91</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5">
-      <c r="A25" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B25" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C25" s="6">
-        <v>8.19</v>
-      </c>
-      <c r="D25" s="6">
-        <v>7.69</v>
-      </c>
-      <c r="E25" s="7">
-        <v>-0.5</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5">
-      <c r="A26" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B26" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C26" s="6">
-        <v>24.49</v>
-      </c>
-      <c r="D26" s="6">
-        <v>23.43</v>
-      </c>
-      <c r="E26" s="7">
-        <v>-1.06</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5">
-      <c r="A27" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B27" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C27" s="6">
-        <v>54.61</v>
-      </c>
-      <c r="D27" s="6">
-        <v>62.48</v>
-      </c>
-      <c r="E27" s="8">
-        <v>7.87</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5">
-      <c r="A28" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B28" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C28" s="6">
-        <v>87.39</v>
-      </c>
-      <c r="D28" s="6">
-        <v>97.79000000000001</v>
-      </c>
-      <c r="E28" s="8">
-        <v>10.4</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5">
-      <c r="A29" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B29" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C29" s="6">
-        <v>-24.89</v>
-      </c>
-      <c r="D29" s="6">
-        <v>-24.05</v>
-      </c>
-      <c r="E29" s="8">
-        <v>0.84</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5">
-      <c r="A30" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="B30" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C30" s="6">
-        <v>-9.890000000000001</v>
-      </c>
-      <c r="D30" s="6">
-        <v>-12.04</v>
-      </c>
-      <c r="E30" s="7">
-        <v>-2.15</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5">
-      <c r="A31" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B31" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C31" s="6">
-        <v>-7.9</v>
-      </c>
-      <c r="D31" s="6">
-        <v>-6.54</v>
-      </c>
-      <c r="E31" s="8">
-        <v>1.36</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5">
-      <c r="A32" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B32" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C32" s="6">
-        <v>-28.98</v>
-      </c>
-      <c r="D32" s="6">
-        <v>-23.39</v>
-      </c>
-      <c r="E32" s="8">
-        <v>5.59</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5">
-      <c r="A33" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B33" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C33" s="6">
-        <v>-7.5</v>
-      </c>
-      <c r="D33" s="6">
-        <v>-6.95</v>
-      </c>
-      <c r="E33" s="8">
-        <v>0.55</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5">
-      <c r="A34" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B34" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C34" s="6">
-        <v>-4.28</v>
-      </c>
-      <c r="D34" s="6">
-        <v>-2.99</v>
-      </c>
-      <c r="E34" s="8">
-        <v>1.29</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5">
-      <c r="A35" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B35" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C35" s="6">
-        <v>-9.58</v>
-      </c>
-      <c r="D35" s="6">
-        <v>-4.62</v>
-      </c>
-      <c r="E35" s="8">
-        <v>4.96</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5">
-      <c r="A36" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B36" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C36" s="6">
-        <v>-4.92</v>
-      </c>
-      <c r="D36" s="6">
-        <v>1.8</v>
-      </c>
-      <c r="E36" s="8">
-        <v>6.72</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5">
-      <c r="A37" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B37" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C37" s="6">
-        <v>-9.43</v>
-      </c>
-      <c r="D37" s="6">
-        <v>-7.26</v>
-      </c>
-      <c r="E37" s="8">
-        <v>2.17</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5">
-      <c r="A38" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="B38" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C38" s="6">
-        <v>-6.95</v>
-      </c>
-      <c r="D38" s="6">
-        <v>-7.72</v>
-      </c>
-      <c r="E38" s="7">
-        <v>-0.77</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5">
-      <c r="A39" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B39" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C39" s="6">
-        <v>-11.14</v>
-      </c>
-      <c r="D39" s="6">
-        <v>-10.78</v>
-      </c>
-      <c r="E39" s="8">
-        <v>0.36</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5">
-      <c r="A40" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B40" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C40" s="6">
-        <v>-49.61</v>
-      </c>
-      <c r="D40" s="6">
-        <v>-48.09</v>
-      </c>
-      <c r="E40" s="8">
-        <v>1.52</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5">
-      <c r="A41" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B41" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C41" s="6">
-        <v>-12.08</v>
-      </c>
-      <c r="D41" s="6">
-        <v>-12.17</v>
-      </c>
-      <c r="E41" s="7">
-        <v>-0.09</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5">
-      <c r="A42" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B42" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C42" s="6">
-        <v>-18.38</v>
-      </c>
-      <c r="D42" s="6">
-        <v>-18.2</v>
-      </c>
-      <c r="E42" s="8">
-        <v>0.18</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5">
-      <c r="A43" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B43" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C43" s="6">
-        <v>-18.33</v>
-      </c>
-      <c r="D43" s="6">
-        <v>-15.32</v>
-      </c>
-      <c r="E43" s="8">
-        <v>3.01</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5">
-      <c r="A44" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B44" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C44" s="6">
-        <v>-26.36</v>
-      </c>
-      <c r="D44" s="6">
-        <v>-22.7</v>
-      </c>
-      <c r="E44" s="8">
-        <v>3.66</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5">
-      <c r="A45" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B45" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C45" s="6">
-        <v>-31.41</v>
-      </c>
-      <c r="D45" s="6">
-        <v>-29.99</v>
-      </c>
-      <c r="E45" s="8">
-        <v>1.42</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5">
-      <c r="A46" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="B46" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C46" s="6">
-        <v>-16.87</v>
-      </c>
-      <c r="D46" s="6">
-        <v>-17.64</v>
-      </c>
-      <c r="E46" s="7">
-        <v>-0.77</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5">
-      <c r="A47" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B47" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C47" s="6">
-        <v>377.4</v>
-      </c>
-      <c r="D47" s="6">
-        <v>378.9</v>
-      </c>
-      <c r="E47" s="8">
-        <v>1.5</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5">
-      <c r="A48" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B48" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C48" s="6">
-        <v>44.34</v>
-      </c>
-      <c r="D48" s="6">
-        <v>45.68</v>
-      </c>
-      <c r="E48" s="8">
-        <v>1.34</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5">
-      <c r="A49" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B49" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C49" s="6">
-        <v>2972</v>
-      </c>
-      <c r="D49" s="6">
-        <v>2969</v>
-      </c>
-      <c r="E49" s="7">
-        <v>-3</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5">
-      <c r="A50" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B50" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C50" s="6">
-        <v>938.4</v>
-      </c>
-      <c r="D50" s="6">
-        <v>940.5</v>
-      </c>
-      <c r="E50" s="8">
-        <v>2.1</v>
-      </c>
-    </row>
-    <row r="51" spans="1:5">
-      <c r="A51" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B51" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C51" s="6">
-        <v>12.74</v>
-      </c>
-      <c r="D51" s="6">
-        <v>13.21</v>
-      </c>
-      <c r="E51" s="8">
-        <v>0.47</v>
-      </c>
-    </row>
-    <row r="52" spans="1:5">
-      <c r="A52" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B52" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C52" s="6">
-        <v>10.25</v>
-      </c>
-      <c r="D52" s="6">
-        <v>10.76</v>
-      </c>
-      <c r="E52" s="8">
-        <v>0.51</v>
-      </c>
-    </row>
-    <row r="53" spans="1:5">
-      <c r="A53" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B53" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C53" s="6">
-        <v>3984.7</v>
-      </c>
-      <c r="D53" s="6">
-        <v>4067.1</v>
-      </c>
-      <c r="E53" s="8">
-        <v>82.40000000000001</v>
-      </c>
-    </row>
-    <row r="54" spans="1:5">
-      <c r="A54" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="B54" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C54" s="6">
-        <v>10850</v>
-      </c>
-      <c r="D54" s="6">
-        <v>10750</v>
-      </c>
-      <c r="E54" s="7">
-        <v>-100</v>
-      </c>
-    </row>
-    <row r="55" spans="1:5">
-      <c r="A55" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B55" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C55" s="6">
-        <v>39.9</v>
-      </c>
-      <c r="D55" s="6">
-        <v>41.09</v>
-      </c>
-      <c r="E55" s="8">
-        <v>1.19</v>
-      </c>
-    </row>
-    <row r="56" spans="1:5">
-      <c r="A56" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B56" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C56" s="6">
-        <v>23.83</v>
-      </c>
-      <c r="D56" s="6">
-        <v>32.45</v>
-      </c>
-      <c r="E56" s="8">
-        <v>8.619999999999999</v>
-      </c>
-    </row>
-    <row r="57" spans="1:5">
-      <c r="A57" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B57" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C57" s="6">
-        <v>29.6</v>
-      </c>
-      <c r="D57" s="6">
-        <v>29.42</v>
-      </c>
-      <c r="E57" s="7">
-        <v>-0.18</v>
-      </c>
-    </row>
-    <row r="58" spans="1:5">
-      <c r="A58" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B58" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C58" s="6">
-        <v>34.79</v>
-      </c>
-      <c r="D58" s="6">
-        <v>35.72</v>
-      </c>
-      <c r="E58" s="8">
-        <v>0.93</v>
-      </c>
-    </row>
-    <row r="59" spans="1:5">
-      <c r="A59" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B59" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C59" s="6">
-        <v>34.56</v>
-      </c>
-      <c r="D59" s="6">
-        <v>41.63</v>
-      </c>
-      <c r="E59" s="8">
-        <v>7.07</v>
-      </c>
-    </row>
-    <row r="60" spans="1:5">
-      <c r="A60" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B60" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C60" s="6">
-        <v>32.56</v>
-      </c>
-      <c r="D60" s="6">
-        <v>41.8</v>
-      </c>
-      <c r="E60" s="8">
-        <v>9.24</v>
-      </c>
-    </row>
-    <row r="61" spans="1:5">
-      <c r="A61" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B61" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C61" s="6">
-        <v>39.06</v>
-      </c>
-      <c r="D61" s="6">
-        <v>46.35</v>
-      </c>
-      <c r="E61" s="8">
-        <v>7.29</v>
-      </c>
-    </row>
-    <row r="62" spans="1:5">
-      <c r="A62" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="B62" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C62" s="6">
-        <v>42.45</v>
-      </c>
-      <c r="D62" s="6">
-        <v>40.07</v>
-      </c>
-      <c r="E62" s="7">
-        <v>-2.38</v>
-      </c>
-    </row>
-    <row r="63" spans="1:5">
-      <c r="A63" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B63" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C63" s="6">
-        <v>-42.92</v>
-      </c>
-      <c r="D63" s="6">
-        <v>82.95</v>
-      </c>
-      <c r="E63" s="8">
-        <v>125.87</v>
-      </c>
-    </row>
-    <row r="64" spans="1:5">
-      <c r="A64" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B64" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C64" s="6">
-        <v>-24.55</v>
-      </c>
-      <c r="D64" s="6">
-        <v>113.19</v>
-      </c>
-      <c r="E64" s="8">
-        <v>137.74</v>
-      </c>
-    </row>
-    <row r="65" spans="1:5">
-      <c r="A65" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B65" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C65" s="6">
-        <v>-70.31999999999999</v>
-      </c>
-      <c r="D65" s="6">
-        <v>-57.64</v>
-      </c>
-      <c r="E65" s="8">
-        <v>12.68</v>
-      </c>
-    </row>
-    <row r="66" spans="1:5">
-      <c r="A66" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B66" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C66" s="6">
-        <v>21.15</v>
-      </c>
-      <c r="D66" s="6">
-        <v>-20.24</v>
-      </c>
-      <c r="E66" s="7">
-        <v>-41.39</v>
-      </c>
-    </row>
-    <row r="67" spans="1:5">
-      <c r="A67" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B67" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C67" s="6">
-        <v>-5.45</v>
-      </c>
-      <c r="D67" s="6">
-        <v>-30.3</v>
-      </c>
-      <c r="E67" s="7">
-        <v>-24.85</v>
-      </c>
-    </row>
-    <row r="68" spans="1:5">
-      <c r="A68" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B68" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C68" s="6">
-        <v>117.53</v>
-      </c>
-      <c r="D68" s="6">
-        <v>13.54</v>
-      </c>
-      <c r="E68" s="7">
-        <v>-103.99</v>
-      </c>
-    </row>
-    <row r="69" spans="1:5">
-      <c r="A69" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B69" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C69" s="6">
-        <v>16.82</v>
-      </c>
-      <c r="D69" s="6">
-        <v>-45.15</v>
-      </c>
-      <c r="E69" s="7">
-        <v>-61.97</v>
-      </c>
-    </row>
-    <row r="70" spans="1:5">
-      <c r="A70" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="B70" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C70" s="6">
-        <v>6.48</v>
-      </c>
-      <c r="D70" s="6">
-        <v>-9.77</v>
+      <c r="D70" s="5">
+        <v>-4.24</v>
       </c>
       <c r="E70" s="7">
-        <v>-16.25</v>
+        <v>5.53</v>
       </c>
     </row>
   </sheetData>
@@ -3156,60 +3092,60 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="28" customHeight="1">
-      <c r="A1" s="9" t="s">
+      <c r="A1" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="C1" s="9" t="s">
-        <v>67</v>
-      </c>
-      <c r="D1" s="9" t="s">
-        <v>68</v>
-      </c>
-      <c r="E1" s="9" t="s">
-        <v>69</v>
-      </c>
-      <c r="F1" s="9" t="s">
-        <v>70</v>
-      </c>
-      <c r="G1" s="9" t="s">
-        <v>71</v>
-      </c>
-      <c r="H1" s="9" t="s">
-        <v>72</v>
-      </c>
-      <c r="I1" s="9" t="s">
-        <v>73</v>
+      <c r="B1" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="C1" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="D1" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="E1" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="F1" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="G1" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="H1" s="8" t="s">
+        <v>62</v>
+      </c>
+      <c r="I1" s="8" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="10" t="s">
+      <c r="A2" s="9" t="s">
         <v>45</v>
       </c>
-      <c r="B2" s="11">
+      <c r="B2" s="10">
         <v>40.44</v>
       </c>
-      <c r="C2" s="12">
+      <c r="C2" s="11">
         <v>8</v>
       </c>
-      <c r="D2" s="11">
-        <v>38.6</v>
-      </c>
-      <c r="E2" s="11">
+      <c r="D2" s="10">
+        <v>36.5</v>
+      </c>
+      <c r="E2" s="10">
         <v>20</v>
       </c>
-      <c r="F2" s="11">
-        <v>-6.9</v>
-      </c>
-      <c r="G2" s="11">
-        <v>-7.2</v>
-      </c>
-      <c r="H2" s="11">
+      <c r="F2" s="10">
+        <v>-8.9</v>
+      </c>
+      <c r="G2" s="10">
+        <v>-6.6</v>
+      </c>
+      <c r="H2" s="10">
         <v>56.1</v>
       </c>
-      <c r="I2" s="11">
+      <c r="I2" s="10">
         <v>10</v>
       </c>
     </row>
@@ -3311,55 +3247,55 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8">
-      <c r="A1" s="13" t="s">
+      <c r="A1" s="12" t="s">
         <v>37</v>
       </c>
-      <c r="B1" s="13" t="s">
+      <c r="B1" s="12" t="s">
         <v>43</v>
       </c>
-      <c r="C1" s="13" t="s">
+      <c r="C1" s="12" t="s">
         <v>40</v>
       </c>
-      <c r="D1" s="13" t="s">
+      <c r="D1" s="12" t="s">
         <v>39</v>
       </c>
-      <c r="E1" s="13" t="s">
+      <c r="E1" s="12" t="s">
         <v>44</v>
       </c>
-      <c r="F1" s="13" t="s">
+      <c r="F1" s="12" t="s">
         <v>41</v>
       </c>
-      <c r="G1" s="13" t="s">
+      <c r="G1" s="12" t="s">
         <v>38</v>
       </c>
-      <c r="H1" s="13" t="s">
+      <c r="H1" s="12" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="2" spans="1:8">
-      <c r="A2" s="14">
-        <v>0.2801</v>
-      </c>
-      <c r="B2" s="14">
-        <v>0.1634</v>
-      </c>
-      <c r="C2" s="14">
-        <v>0.1526</v>
-      </c>
-      <c r="D2" s="14">
-        <v>0.137</v>
-      </c>
-      <c r="E2" s="14">
-        <v>0.08349999999999999</v>
-      </c>
-      <c r="F2" s="14">
-        <v>0.029</v>
-      </c>
-      <c r="G2" s="14">
-        <v>-0.2828</v>
-      </c>
-      <c r="H2" s="14">
-        <v>-0.3073</v>
+      <c r="A2" s="13">
+        <v>0.2758</v>
+      </c>
+      <c r="B2" s="13">
+        <v>0.1595</v>
+      </c>
+      <c r="C2" s="13">
+        <v>0.1444</v>
+      </c>
+      <c r="D2" s="13">
+        <v>0.1343</v>
+      </c>
+      <c r="E2" s="13">
+        <v>0.0819</v>
+      </c>
+      <c r="F2" s="13">
+        <v>0.0304</v>
+      </c>
+      <c r="G2" s="13">
+        <v>-0.2965</v>
+      </c>
+      <c r="H2" s="13">
+        <v>-0.309</v>
       </c>
     </row>
   </sheetData>

--- a/BIRLA_GROUP_Technical_Metrics.xlsx
+++ b/BIRLA_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="276" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="293" uniqueCount="71">
   <si>
     <t>Symbol</t>
   </si>
@@ -172,7 +172,28 @@
     <t>▶  SIGNAL EVENTS (vs Previous Run)</t>
   </si>
   <si>
-    <t>No signal events detected since last run.</t>
+    <t>Signal</t>
+  </si>
+  <si>
+    <t>Change</t>
+  </si>
+  <si>
+    <t>Direction</t>
+  </si>
+  <si>
+    <t>Prev Value</t>
+  </si>
+  <si>
+    <t>Curr Value</t>
+  </si>
+  <si>
+    <t>Yes → No</t>
+  </si>
+  <si>
+    <t>🔴 BEARISH</t>
+  </si>
+  <si>
+    <t>20 DMA &gt; 50 DMA</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -374,14 +395,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -755,9 +777,7 @@
     <col min="13" max="13" width="10.7109375" customWidth="1"/>
     <col min="14" max="14" width="11.7109375" customWidth="1"/>
     <col min="15" max="15" width="10.7109375" customWidth="1"/>
-    <col min="16" max="16" width="9.7109375" customWidth="1"/>
-    <col min="17" max="17" width="10.7109375" customWidth="1"/>
-    <col min="18" max="18" width="9.7109375" customWidth="1"/>
+    <col min="16" max="18" width="9.7109375" customWidth="1"/>
     <col min="19" max="19" width="10.7109375" customWidth="1"/>
     <col min="20" max="20" width="22.7109375" customWidth="1"/>
     <col min="21" max="21" width="9.7109375" customWidth="1"/>
@@ -898,10 +918,10 @@
         <v>45</v>
       </c>
       <c r="C2">
-        <v>372.1</v>
+        <v>368.65</v>
       </c>
       <c r="D2">
-        <v>-1.79</v>
+        <v>-0.93</v>
       </c>
       <c r="E2">
         <v>424.7</v>
@@ -910,46 +930,46 @@
         <v>292.25</v>
       </c>
       <c r="G2">
-        <v>-12.39</v>
+        <v>-13.2</v>
       </c>
       <c r="H2">
-        <v>27.32</v>
+        <v>26.14</v>
       </c>
       <c r="I2">
-        <v>-1.56</v>
+        <v>-3.14</v>
       </c>
       <c r="J2">
-        <v>-8.1</v>
+        <v>-8.58</v>
       </c>
       <c r="K2">
-        <v>-3.54</v>
+        <v>-7.22</v>
       </c>
       <c r="L2">
-        <v>24.1</v>
+        <v>21.29</v>
       </c>
       <c r="M2">
-        <v>27.58</v>
+        <v>27.03</v>
       </c>
       <c r="N2">
         <v>74</v>
       </c>
       <c r="O2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="P2">
-        <v>376.81</v>
+        <v>374.42</v>
       </c>
       <c r="Q2">
-        <v>388.99</v>
+        <v>387.57</v>
       </c>
       <c r="R2">
-        <v>399.59</v>
+        <v>399.13</v>
       </c>
       <c r="S2">
-        <v>364.96</v>
+        <v>365.08</v>
       </c>
       <c r="T2">
-        <v>1.96</v>
+        <v>0.98</v>
       </c>
       <c r="U2" t="s">
         <v>46</v>
@@ -964,43 +984,43 @@
         <v>2</v>
       </c>
       <c r="Y2">
-        <v>37.46</v>
+        <v>35.73</v>
       </c>
       <c r="Z2">
-        <v>-6.75</v>
+        <v>-7.39</v>
       </c>
       <c r="AA2">
-        <v>-4.99</v>
+        <v>-5.47</v>
       </c>
       <c r="AB2">
-        <v>-1.77</v>
+        <v>-1.93</v>
       </c>
       <c r="AC2">
-        <v>17.15</v>
+        <v>8.15</v>
       </c>
       <c r="AD2">
-        <v>22.06</v>
+        <v>16.24</v>
       </c>
       <c r="AE2">
-        <v>9.279999999999999</v>
+        <v>9.109999999999999</v>
       </c>
       <c r="AF2">
-        <v>56.67</v>
+        <v>58.33</v>
       </c>
       <c r="AG2">
-        <v>411.24</v>
+        <v>411.25</v>
       </c>
       <c r="AH2">
-        <v>366.74</v>
+        <v>363.9</v>
       </c>
       <c r="AI2">
-        <v>402.96</v>
+        <v>398.61</v>
       </c>
       <c r="AJ2" t="s">
         <v>48</v>
       </c>
       <c r="AK2">
-        <v>36.2</v>
+        <v>38.57</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1011,37 +1031,37 @@
         <v>45</v>
       </c>
       <c r="C3">
-        <v>44.62</v>
+        <v>43.18</v>
       </c>
       <c r="D3">
-        <v>-2.32</v>
+        <v>-3.23</v>
       </c>
       <c r="E3">
-        <v>87.98999999999999</v>
+        <v>86.23999999999999</v>
       </c>
       <c r="F3">
-        <v>44.34</v>
+        <v>43.18</v>
       </c>
       <c r="G3">
-        <v>-49.29</v>
+        <v>-49.93</v>
       </c>
       <c r="H3">
-        <v>0.63</v>
+        <v>0</v>
       </c>
       <c r="I3">
-        <v>-3.5</v>
+        <v>-6.78</v>
       </c>
       <c r="J3">
-        <v>-15.76</v>
+        <v>-18.85</v>
       </c>
       <c r="K3">
-        <v>-23.48</v>
+        <v>-26.25</v>
       </c>
       <c r="L3">
-        <v>-48.35</v>
+        <v>-50.93</v>
       </c>
       <c r="M3">
-        <v>-29.65</v>
+        <v>-29.99</v>
       </c>
       <c r="N3">
         <v>13</v>
@@ -1050,19 +1070,19 @@
         <v>4</v>
       </c>
       <c r="P3">
-        <v>45.1</v>
+        <v>44.47</v>
       </c>
       <c r="Q3">
-        <v>48.45</v>
+        <v>47.99</v>
       </c>
       <c r="R3">
-        <v>53.17</v>
+        <v>52.9</v>
       </c>
       <c r="S3">
-        <v>61.81</v>
+        <v>61.65</v>
       </c>
       <c r="T3">
-        <v>-27.81</v>
+        <v>-29.96</v>
       </c>
       <c r="U3" t="s">
         <v>46</v>
@@ -1077,43 +1097,43 @@
         <v>0</v>
       </c>
       <c r="Y3">
-        <v>29.59</v>
+        <v>26.22</v>
       </c>
       <c r="Z3">
-        <v>-2.28</v>
+        <v>-2.4</v>
       </c>
       <c r="AA3">
-        <v>-2.07</v>
+        <v>-2.14</v>
       </c>
       <c r="AB3">
-        <v>-0.21</v>
+        <v>-0.26</v>
       </c>
       <c r="AC3">
-        <v>35.3</v>
+        <v>41.5</v>
       </c>
       <c r="AD3">
-        <v>19.44</v>
+        <v>32.65</v>
       </c>
       <c r="AE3">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="AF3">
-        <v>-22.38</v>
+        <v>-21.21</v>
       </c>
       <c r="AG3">
-        <v>53.26</v>
+        <v>53</v>
       </c>
       <c r="AH3">
-        <v>43.64</v>
+        <v>42.99</v>
       </c>
       <c r="AI3">
-        <v>49.46</v>
+        <v>49.03</v>
       </c>
       <c r="AJ3" t="s">
         <v>48</v>
       </c>
       <c r="AK3">
-        <v>46.3</v>
+        <v>45.28</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1124,10 +1144,10 @@
         <v>45</v>
       </c>
       <c r="C4">
-        <v>2921.1</v>
+        <v>2856.8</v>
       </c>
       <c r="D4">
-        <v>-1.61</v>
+        <v>-2.2</v>
       </c>
       <c r="E4">
         <v>3380.5</v>
@@ -1136,25 +1156,25 @@
         <v>2531.1</v>
       </c>
       <c r="G4">
-        <v>-13.59</v>
+        <v>-15.49</v>
       </c>
       <c r="H4">
-        <v>15.41</v>
+        <v>12.87</v>
       </c>
       <c r="I4">
-        <v>-5.77</v>
+        <v>-6.7</v>
       </c>
       <c r="J4">
-        <v>-12.07</v>
+        <v>-13.49</v>
       </c>
       <c r="K4">
-        <v>-6.82</v>
+        <v>-10.5</v>
       </c>
       <c r="L4">
-        <v>4.71</v>
+        <v>2.34</v>
       </c>
       <c r="M4">
-        <v>13.43</v>
+        <v>12.83</v>
       </c>
       <c r="N4">
         <v>50</v>
@@ -1163,19 +1183,19 @@
         <v>55</v>
       </c>
       <c r="P4">
-        <v>2977.2</v>
+        <v>2936.18</v>
       </c>
       <c r="Q4">
-        <v>3146.21</v>
+        <v>3123.71</v>
       </c>
       <c r="R4">
-        <v>3215.56</v>
+        <v>3210.38</v>
       </c>
       <c r="S4">
-        <v>2979.01</v>
+        <v>2979.26</v>
       </c>
       <c r="T4">
-        <v>-1.94</v>
+        <v>-4.11</v>
       </c>
       <c r="U4" t="s">
         <v>46</v>
@@ -1190,43 +1210,43 @@
         <v>1</v>
       </c>
       <c r="Y4">
-        <v>26.61</v>
+        <v>23.39</v>
       </c>
       <c r="Z4">
-        <v>-75.94</v>
+        <v>-86.55</v>
       </c>
       <c r="AA4">
-        <v>-48.65</v>
+        <v>-56.23</v>
       </c>
       <c r="AB4">
-        <v>-27.28</v>
+        <v>-30.32</v>
       </c>
       <c r="AC4">
-        <v>4.89</v>
+        <v>2.27</v>
       </c>
       <c r="AD4">
-        <v>4.14</v>
+        <v>4.02</v>
       </c>
       <c r="AE4">
-        <v>63.1</v>
+        <v>63.42</v>
       </c>
       <c r="AF4">
-        <v>-68.81999999999999</v>
+        <v>-31.99</v>
       </c>
       <c r="AG4">
-        <v>3382.51</v>
+        <v>3380.44</v>
       </c>
       <c r="AH4">
-        <v>2909.91</v>
+        <v>2866.98</v>
       </c>
       <c r="AI4">
-        <v>3118.71</v>
+        <v>3076.97</v>
       </c>
       <c r="AJ4" t="s">
         <v>48</v>
       </c>
       <c r="AK4">
-        <v>59.68</v>
+        <v>63.41</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1237,10 +1257,10 @@
         <v>45</v>
       </c>
       <c r="C5">
-        <v>910.85</v>
+        <v>890.15</v>
       </c>
       <c r="D5">
-        <v>-3.15</v>
+        <v>-2.27</v>
       </c>
       <c r="E5">
         <v>1149.7</v>
@@ -1249,46 +1269,46 @@
         <v>760.1</v>
       </c>
       <c r="G5">
-        <v>-20.77</v>
+        <v>-22.58</v>
       </c>
       <c r="H5">
-        <v>19.83</v>
+        <v>17.11</v>
       </c>
       <c r="I5">
-        <v>-4.64</v>
+        <v>-5.48</v>
       </c>
       <c r="J5">
-        <v>-9.91</v>
+        <v>-11.52</v>
       </c>
       <c r="K5">
-        <v>-6.26</v>
+        <v>-7.61</v>
       </c>
       <c r="L5">
-        <v>18.92</v>
+        <v>14.07</v>
       </c>
       <c r="M5">
-        <v>14.44</v>
+        <v>14.1</v>
       </c>
       <c r="N5">
         <v>62</v>
       </c>
       <c r="O5">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="P5">
-        <v>934.6799999999999</v>
+        <v>924.35</v>
       </c>
       <c r="Q5">
-        <v>971.5700000000001</v>
+        <v>965.62</v>
       </c>
       <c r="R5">
-        <v>1003.17</v>
+        <v>1002.25</v>
       </c>
       <c r="S5">
-        <v>982.4400000000001</v>
+        <v>982.6</v>
       </c>
       <c r="T5">
-        <v>-7.29</v>
+        <v>-9.41</v>
       </c>
       <c r="U5" t="s">
         <v>46</v>
@@ -1303,43 +1323,43 @@
         <v>1</v>
       </c>
       <c r="Y5">
-        <v>29.36</v>
+        <v>25.9</v>
       </c>
       <c r="Z5">
-        <v>-21.02</v>
+        <v>-24.46</v>
       </c>
       <c r="AA5">
-        <v>-15.72</v>
+        <v>-17.47</v>
       </c>
       <c r="AB5">
-        <v>-5.31</v>
+        <v>-6.99</v>
       </c>
       <c r="AC5">
-        <v>3.13</v>
+        <v>1.97</v>
       </c>
       <c r="AD5">
-        <v>5.22</v>
+        <v>3.67</v>
       </c>
       <c r="AE5">
-        <v>22.03</v>
+        <v>22.19</v>
       </c>
       <c r="AF5">
-        <v>-0.9</v>
+        <v>-0.58</v>
       </c>
       <c r="AG5">
-        <v>1029.85</v>
+        <v>1031.57</v>
       </c>
       <c r="AH5">
-        <v>913.28</v>
+        <v>899.67</v>
       </c>
       <c r="AI5">
-        <v>990.4299999999999</v>
+        <v>965.25</v>
       </c>
       <c r="AJ5" t="s">
         <v>48</v>
       </c>
       <c r="AK5">
-        <v>36.07</v>
+        <v>40.56</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1350,10 +1370,10 @@
         <v>45</v>
       </c>
       <c r="C6">
-        <v>13.18</v>
+        <v>12.8</v>
       </c>
       <c r="D6">
-        <v>-0.23</v>
+        <v>-2.88</v>
       </c>
       <c r="E6">
         <v>15.6</v>
@@ -1362,88 +1382,88 @@
         <v>8.359999999999999</v>
       </c>
       <c r="G6">
-        <v>-15.51</v>
+        <v>-17.95</v>
       </c>
       <c r="H6">
-        <v>57.66</v>
+        <v>53.11</v>
       </c>
       <c r="I6">
-        <v>-2.8</v>
+        <v>-1.16</v>
       </c>
       <c r="J6">
-        <v>-12.25</v>
+        <v>-17.95</v>
       </c>
       <c r="K6">
-        <v>-5.38</v>
+        <v>-8.83</v>
       </c>
       <c r="L6">
-        <v>54.69</v>
+        <v>45.12</v>
       </c>
       <c r="M6">
-        <v>3.04</v>
+        <v>2.43</v>
       </c>
       <c r="N6">
         <v>87</v>
       </c>
       <c r="O6">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="P6">
-        <v>12.94</v>
+        <v>12.91</v>
       </c>
       <c r="Q6">
-        <v>14.02</v>
+        <v>13.89</v>
       </c>
       <c r="R6">
         <v>13.9</v>
       </c>
       <c r="S6">
-        <v>12.27</v>
+        <v>12.28</v>
       </c>
       <c r="T6">
-        <v>7.42</v>
+        <v>4.26</v>
       </c>
       <c r="U6" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="V6" t="s">
         <v>47</v>
       </c>
       <c r="W6" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="X6">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Y6">
-        <v>41.33</v>
+        <v>37.55</v>
       </c>
       <c r="Z6">
-        <v>-0.35</v>
+        <v>-0.38</v>
       </c>
       <c r="AA6">
-        <v>-0.2</v>
+        <v>-0.24</v>
       </c>
       <c r="AB6">
-        <v>-0.15</v>
+        <v>-0.14</v>
       </c>
       <c r="AC6">
-        <v>32.29</v>
+        <v>37.47</v>
       </c>
       <c r="AD6">
-        <v>17.62</v>
+        <v>29.19</v>
       </c>
       <c r="AE6">
         <v>0.49</v>
       </c>
       <c r="AF6">
-        <v>-22.62</v>
+        <v>-38.29</v>
       </c>
       <c r="AG6">
-        <v>15.69</v>
+        <v>15.5</v>
       </c>
       <c r="AH6">
-        <v>12.36</v>
+        <v>12.28</v>
       </c>
       <c r="AI6">
         <v>14.25</v>
@@ -1452,7 +1472,7 @@
         <v>48</v>
       </c>
       <c r="AK6">
-        <v>39.01</v>
+        <v>38.63</v>
       </c>
     </row>
     <row r="7" spans="1:37">
@@ -1463,10 +1483,10 @@
         <v>45</v>
       </c>
       <c r="C7">
-        <v>10.81</v>
+        <v>10.56</v>
       </c>
       <c r="D7">
-        <v>0.46</v>
+        <v>-2.31</v>
       </c>
       <c r="E7">
         <v>13.92</v>
@@ -1475,46 +1495,46 @@
         <v>4.69</v>
       </c>
       <c r="G7">
-        <v>-22.34</v>
+        <v>-24.14</v>
       </c>
       <c r="H7">
-        <v>130.49</v>
+        <v>125.16</v>
       </c>
       <c r="I7">
-        <v>-0.28</v>
+        <v>-3.3</v>
       </c>
       <c r="J7">
-        <v>-0.83</v>
+        <v>-4.95</v>
       </c>
       <c r="K7">
-        <v>4.34</v>
+        <v>3.83</v>
       </c>
       <c r="L7">
-        <v>94.42</v>
+        <v>87.23</v>
       </c>
       <c r="M7">
-        <v>-30.9</v>
+        <v>-31.4</v>
       </c>
       <c r="N7">
         <v>99</v>
       </c>
       <c r="O7">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="P7">
-        <v>10.69</v>
+        <v>10.62</v>
       </c>
       <c r="Q7">
-        <v>11.44</v>
+        <v>11.4</v>
       </c>
       <c r="R7">
-        <v>11.66</v>
+        <v>11.65</v>
       </c>
       <c r="S7">
         <v>10.84</v>
       </c>
       <c r="T7">
-        <v>-0.26</v>
+        <v>-2.59</v>
       </c>
       <c r="U7" t="s">
         <v>46</v>
@@ -1529,34 +1549,34 @@
         <v>1</v>
       </c>
       <c r="Y7">
-        <v>42.63</v>
+        <v>39.59</v>
       </c>
       <c r="Z7">
-        <v>-0.26</v>
+        <v>-0.28</v>
       </c>
       <c r="AA7">
-        <v>-0.16</v>
+        <v>-0.18</v>
       </c>
       <c r="AB7">
-        <v>-0.1</v>
+        <v>-0.09</v>
       </c>
       <c r="AC7">
-        <v>22.11</v>
+        <v>33.23</v>
       </c>
       <c r="AD7">
-        <v>11.46</v>
+        <v>21.95</v>
       </c>
       <c r="AE7">
-        <v>0.5</v>
+        <v>0.52</v>
       </c>
       <c r="AF7">
-        <v>-18.11</v>
+        <v>-33.77</v>
       </c>
       <c r="AG7">
-        <v>12.69</v>
+        <v>12.71</v>
       </c>
       <c r="AH7">
-        <v>10.19</v>
+        <v>10.09</v>
       </c>
       <c r="AI7">
         <v>12.04</v>
@@ -1565,7 +1585,7 @@
         <v>48</v>
       </c>
       <c r="AK7">
-        <v>36.63</v>
+        <v>36.24</v>
       </c>
     </row>
     <row r="8" spans="1:37">
@@ -1576,10 +1596,10 @@
         <v>45</v>
       </c>
       <c r="C8">
-        <v>4076.3</v>
+        <v>3948.5</v>
       </c>
       <c r="D8">
-        <v>0.23</v>
+        <v>-3.14</v>
       </c>
       <c r="E8">
         <v>5809.5</v>
@@ -1588,46 +1608,46 @@
         <v>3892.3</v>
       </c>
       <c r="G8">
-        <v>-29.83</v>
+        <v>-32.03</v>
       </c>
       <c r="H8">
-        <v>4.73</v>
+        <v>1.44</v>
       </c>
       <c r="I8">
-        <v>1.21</v>
+        <v>-0.2</v>
       </c>
       <c r="J8">
-        <v>-5.72</v>
+        <v>-8.15</v>
       </c>
       <c r="K8">
-        <v>-5.37</v>
+        <v>-9.93</v>
       </c>
       <c r="L8">
-        <v>-24.58</v>
+        <v>-29.58</v>
       </c>
       <c r="M8">
-        <v>15.95</v>
+        <v>15.38</v>
       </c>
       <c r="N8">
         <v>26</v>
       </c>
       <c r="O8">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="P8">
-        <v>3995.38</v>
+        <v>3993.78</v>
       </c>
       <c r="Q8">
-        <v>4059.18</v>
+        <v>4043.52</v>
       </c>
       <c r="R8">
-        <v>4242.05</v>
+        <v>4236.22</v>
       </c>
       <c r="S8">
-        <v>4512.4</v>
+        <v>4506.36</v>
       </c>
       <c r="T8">
-        <v>-9.66</v>
+        <v>-12.38</v>
       </c>
       <c r="U8" t="s">
         <v>46</v>
@@ -1642,34 +1662,34 @@
         <v>0</v>
       </c>
       <c r="Y8">
-        <v>47.11</v>
+        <v>38.87</v>
       </c>
       <c r="Z8">
-        <v>-72.26000000000001</v>
+        <v>-73.73</v>
       </c>
       <c r="AA8">
-        <v>-83.87</v>
+        <v>-81.84</v>
       </c>
       <c r="AB8">
-        <v>11.61</v>
+        <v>8.109999999999999</v>
       </c>
       <c r="AC8">
-        <v>100</v>
+        <v>84.81</v>
       </c>
       <c r="AD8">
-        <v>67.27</v>
+        <v>83.83</v>
       </c>
       <c r="AE8">
-        <v>105.55</v>
+        <v>113.65</v>
       </c>
       <c r="AF8">
-        <v>-48.04</v>
+        <v>-22.65</v>
       </c>
       <c r="AG8">
-        <v>4237.55</v>
+        <v>4200.77</v>
       </c>
       <c r="AH8">
-        <v>3880.8</v>
+        <v>3886.26</v>
       </c>
       <c r="AI8">
         <v>4247.59</v>
@@ -1678,7 +1698,7 @@
         <v>48</v>
       </c>
       <c r="AK8">
-        <v>40.44</v>
+        <v>39.61</v>
       </c>
     </row>
     <row r="9" spans="1:37">
@@ -1689,10 +1709,10 @@
         <v>45</v>
       </c>
       <c r="C9">
-        <v>10658</v>
+        <v>10426</v>
       </c>
       <c r="D9">
-        <v>-0.86</v>
+        <v>-2.18</v>
       </c>
       <c r="E9">
         <v>13052</v>
@@ -1701,46 +1721,46 @@
         <v>10362</v>
       </c>
       <c r="G9">
-        <v>-18.34</v>
+        <v>-20.12</v>
       </c>
       <c r="H9">
-        <v>2.86</v>
+        <v>0.62</v>
       </c>
       <c r="I9">
-        <v>-1.58</v>
+        <v>-4.84</v>
       </c>
       <c r="J9">
-        <v>-6.57</v>
+        <v>-6.7</v>
       </c>
       <c r="K9">
-        <v>-6.12</v>
+        <v>-9.529999999999999</v>
       </c>
       <c r="L9">
-        <v>-11.88</v>
+        <v>-13.25</v>
       </c>
       <c r="M9">
-        <v>8.19</v>
+        <v>7.77</v>
       </c>
       <c r="N9">
         <v>38</v>
       </c>
       <c r="O9">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="P9">
-        <v>10784.8</v>
+        <v>10678.8</v>
       </c>
       <c r="Q9">
-        <v>10915.35</v>
+        <v>10886.2</v>
       </c>
       <c r="R9">
-        <v>11388</v>
+        <v>11357.4</v>
       </c>
       <c r="S9">
-        <v>11695.46</v>
+        <v>11690.28</v>
       </c>
       <c r="T9">
-        <v>-8.869999999999999</v>
+        <v>-10.81</v>
       </c>
       <c r="U9" t="s">
         <v>46</v>
@@ -1755,43 +1775,43 @@
         <v>0</v>
       </c>
       <c r="Y9">
-        <v>37.96</v>
+        <v>33.2</v>
       </c>
       <c r="Z9">
-        <v>-159.93</v>
+        <v>-184.15</v>
       </c>
       <c r="AA9">
-        <v>-152.71</v>
+        <v>-158.99</v>
       </c>
       <c r="AB9">
-        <v>-7.22</v>
+        <v>-25.15</v>
       </c>
       <c r="AC9">
-        <v>58.57</v>
+        <v>34.3</v>
       </c>
       <c r="AD9">
-        <v>62.23</v>
+        <v>51.36</v>
       </c>
       <c r="AE9">
-        <v>204.41</v>
+        <v>207.24</v>
       </c>
       <c r="AF9">
-        <v>-4.24</v>
+        <v>-24.5</v>
       </c>
       <c r="AG9">
-        <v>11234.55</v>
+        <v>11269.44</v>
       </c>
       <c r="AH9">
-        <v>10596.15</v>
+        <v>10502.96</v>
       </c>
       <c r="AI9">
-        <v>11316.74</v>
+        <v>11169.72</v>
       </c>
       <c r="AJ9" t="s">
         <v>48</v>
       </c>
       <c r="AK9">
-        <v>35.14</v>
+        <v>39.09</v>
       </c>
     </row>
   </sheetData>
@@ -1932,7 +1952,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F70"/>
+  <dimension ref="A1:F71"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -1952,1127 +1972,1182 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="3" t="s">
         <v>50</v>
       </c>
-    </row>
-    <row r="5" spans="1:6">
-      <c r="A5" s="2" t="s">
+      <c r="C2" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="B5" s="2"/>
-      <c r="C5" s="2"/>
-      <c r="D5" s="2"/>
-      <c r="E5" s="2"/>
+      <c r="D2" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
+      <c r="A4" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>46</v>
+      </c>
     </row>
     <row r="6" spans="1:6">
-      <c r="A6" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="D6" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="E6" s="4" t="s">
-        <v>55</v>
-      </c>
+      <c r="A6" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="B6" s="2"/>
+      <c r="C6" s="2"/>
+      <c r="D6" s="2"/>
+      <c r="E6" s="2"/>
     </row>
     <row r="7" spans="1:6">
       <c r="A7" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B7" s="3" t="s">
+      <c r="B8" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C7" s="5">
-        <v>-5.75</v>
-      </c>
-      <c r="D7" s="5">
+      <c r="C8" s="6">
         <v>-8.1</v>
       </c>
-      <c r="E7" s="6">
-        <v>-2.35</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
-      <c r="A8" s="3" t="s">
+      <c r="D8" s="6">
+        <v>-8.58</v>
+      </c>
+      <c r="E8" s="7">
+        <v>-0.48</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B8" s="3" t="s">
+      <c r="B9" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C8" s="5">
-        <v>-9.380000000000001</v>
-      </c>
-      <c r="D8" s="5">
+      <c r="C9" s="6">
         <v>-15.76</v>
       </c>
-      <c r="E8" s="6">
-        <v>-6.38</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9" s="3" t="s">
+      <c r="D9" s="6">
+        <v>-18.85</v>
+      </c>
+      <c r="E9" s="7">
+        <v>-3.09</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B9" s="3" t="s">
+      <c r="B10" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C9" s="5">
-        <v>-10.3</v>
-      </c>
-      <c r="D9" s="5">
+      <c r="C10" s="6">
         <v>-12.07</v>
       </c>
-      <c r="E9" s="6">
-        <v>-1.77</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10" s="3" t="s">
+      <c r="D10" s="6">
+        <v>-13.49</v>
+      </c>
+      <c r="E10" s="7">
+        <v>-1.42</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B10" s="3" t="s">
+      <c r="B11" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C10" s="5">
-        <v>-6.88</v>
-      </c>
-      <c r="D10" s="5">
+      <c r="C11" s="6">
         <v>-9.91</v>
       </c>
-      <c r="E10" s="6">
-        <v>-3.03</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11" s="3" t="s">
+      <c r="D11" s="6">
+        <v>-11.52</v>
+      </c>
+      <c r="E11" s="7">
+        <v>-1.61</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B11" s="3" t="s">
+      <c r="B12" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C11" s="5">
-        <v>-8.77</v>
-      </c>
-      <c r="D11" s="5">
+      <c r="C12" s="6">
         <v>-12.25</v>
       </c>
-      <c r="E11" s="6">
-        <v>-3.48</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12" s="3" t="s">
+      <c r="D12" s="6">
+        <v>-17.95</v>
+      </c>
+      <c r="E12" s="7">
+        <v>-5.7</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="A13" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="B12" s="3" t="s">
+      <c r="B13" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C12" s="5">
-        <v>-2.62</v>
-      </c>
-      <c r="D12" s="5">
+      <c r="C13" s="6">
         <v>-0.83</v>
       </c>
-      <c r="E12" s="7">
-        <v>1.79</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13" s="3" t="s">
+      <c r="D13" s="6">
+        <v>-4.95</v>
+      </c>
+      <c r="E13" s="7">
+        <v>-4.12</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="B13" s="3" t="s">
+      <c r="B14" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C13" s="5">
-        <v>-6.6</v>
-      </c>
-      <c r="D13" s="5">
+      <c r="C14" s="6">
         <v>-5.72</v>
       </c>
-      <c r="E13" s="7">
-        <v>0.88</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14" s="3" t="s">
+      <c r="D14" s="6">
+        <v>-8.15</v>
+      </c>
+      <c r="E14" s="7">
+        <v>-2.43</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="A15" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="B14" s="3" t="s">
+      <c r="B15" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C14" s="5">
-        <v>-4.66</v>
-      </c>
-      <c r="D14" s="5">
+      <c r="C15" s="6">
         <v>-6.57</v>
       </c>
-      <c r="E14" s="6">
-        <v>-1.91</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15" s="3" t="s">
+      <c r="D15" s="6">
+        <v>-6.7</v>
+      </c>
+      <c r="E15" s="7">
+        <v>-0.13</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="A16" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B15" s="3" t="s">
+      <c r="B16" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="C15" s="5">
-        <v>-0.99</v>
-      </c>
-      <c r="D15" s="5">
+      <c r="C16" s="6">
         <v>-1.56</v>
       </c>
-      <c r="E15" s="6">
-        <v>-0.57</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16" s="3" t="s">
+      <c r="D16" s="6">
+        <v>-3.14</v>
+      </c>
+      <c r="E16" s="7">
+        <v>-1.58</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B16" s="3" t="s">
+      <c r="B17" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="C16" s="5">
-        <v>-4.01</v>
-      </c>
-      <c r="D16" s="5">
+      <c r="C17" s="6">
         <v>-3.5</v>
       </c>
-      <c r="E16" s="7">
-        <v>0.51</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5">
-      <c r="A17" s="3" t="s">
+      <c r="D17" s="6">
+        <v>-6.78</v>
+      </c>
+      <c r="E17" s="7">
+        <v>-3.28</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B17" s="3" t="s">
+      <c r="B18" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="C17" s="5">
-        <v>-5.75</v>
-      </c>
-      <c r="D17" s="5">
+      <c r="C18" s="6">
         <v>-5.77</v>
       </c>
-      <c r="E17" s="6">
-        <v>-0.02</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5">
-      <c r="A18" s="3" t="s">
+      <c r="D18" s="6">
+        <v>-6.7</v>
+      </c>
+      <c r="E18" s="7">
+        <v>-0.93</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B18" s="3" t="s">
+      <c r="B19" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="C18" s="5">
-        <v>-1.61</v>
-      </c>
-      <c r="D18" s="5">
+      <c r="C19" s="6">
         <v>-4.64</v>
       </c>
-      <c r="E18" s="6">
-        <v>-3.03</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5">
-      <c r="A19" s="3" t="s">
+      <c r="D19" s="6">
+        <v>-5.48</v>
+      </c>
+      <c r="E19" s="7">
+        <v>-0.84</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B19" s="3" t="s">
+      <c r="B20" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="C19" s="5">
-        <v>-1.93</v>
-      </c>
-      <c r="D19" s="5">
+      <c r="C20" s="6">
         <v>-2.8</v>
       </c>
-      <c r="E19" s="6">
-        <v>-0.87</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5">
-      <c r="A20" s="3" t="s">
+      <c r="D20" s="6">
+        <v>-1.16</v>
+      </c>
+      <c r="E20" s="8">
+        <v>1.64</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="B20" s="3" t="s">
+      <c r="B21" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="C20" s="5">
-        <v>-2.36</v>
-      </c>
-      <c r="D20" s="5">
+      <c r="C21" s="6">
         <v>-0.28</v>
       </c>
-      <c r="E20" s="7">
-        <v>2.08</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5">
-      <c r="A21" s="3" t="s">
+      <c r="D21" s="6">
+        <v>-3.3</v>
+      </c>
+      <c r="E21" s="7">
+        <v>-3.02</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="B21" s="3" t="s">
+      <c r="B22" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="C21" s="5">
-        <v>1.74</v>
-      </c>
-      <c r="D21" s="5">
+      <c r="C22" s="6">
         <v>1.21</v>
       </c>
-      <c r="E21" s="6">
-        <v>-0.53</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5">
-      <c r="A22" s="3" t="s">
+      <c r="D22" s="6">
+        <v>-0.2</v>
+      </c>
+      <c r="E22" s="7">
+        <v>-1.41</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="B22" s="3" t="s">
+      <c r="B23" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="C22" s="5">
-        <v>-2.49</v>
-      </c>
-      <c r="D22" s="5">
+      <c r="C23" s="6">
         <v>-1.58</v>
       </c>
-      <c r="E22" s="7">
-        <v>0.91</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5">
-      <c r="A23" s="3" t="s">
+      <c r="D23" s="6">
+        <v>-4.84</v>
+      </c>
+      <c r="E23" s="7">
+        <v>-3.26</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B23" s="3" t="s">
+      <c r="B24" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="C23" s="5">
-        <v>29.6</v>
-      </c>
-      <c r="D23" s="5">
+      <c r="C24" s="6">
         <v>24.1</v>
       </c>
-      <c r="E23" s="6">
-        <v>-5.5</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5">
-      <c r="A24" s="3" t="s">
+      <c r="D24" s="6">
+        <v>21.29</v>
+      </c>
+      <c r="E24" s="7">
+        <v>-2.81</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B24" s="3" t="s">
+      <c r="B25" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="C24" s="5">
-        <v>-45.93</v>
-      </c>
-      <c r="D24" s="5">
+      <c r="C25" s="6">
         <v>-48.35</v>
       </c>
-      <c r="E24" s="6">
-        <v>-2.42</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5">
-      <c r="A25" s="3" t="s">
+      <c r="D25" s="6">
+        <v>-50.93</v>
+      </c>
+      <c r="E25" s="7">
+        <v>-2.58</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B25" s="3" t="s">
+      <c r="B26" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="C25" s="5">
-        <v>7.69</v>
-      </c>
-      <c r="D25" s="5">
+      <c r="C26" s="6">
         <v>4.71</v>
       </c>
-      <c r="E25" s="6">
-        <v>-2.98</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5">
-      <c r="A26" s="3" t="s">
+      <c r="D26" s="6">
+        <v>2.34</v>
+      </c>
+      <c r="E26" s="7">
+        <v>-2.37</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B26" s="3" t="s">
+      <c r="B27" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="C26" s="5">
-        <v>23.43</v>
-      </c>
-      <c r="D26" s="5">
+      <c r="C27" s="6">
         <v>18.92</v>
       </c>
-      <c r="E26" s="6">
-        <v>-4.51</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5">
-      <c r="A27" s="3" t="s">
+      <c r="D27" s="6">
+        <v>14.07</v>
+      </c>
+      <c r="E27" s="7">
+        <v>-4.85</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B27" s="3" t="s">
+      <c r="B28" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="C27" s="5">
-        <v>62.48</v>
-      </c>
-      <c r="D27" s="5">
+      <c r="C28" s="6">
         <v>54.69</v>
       </c>
-      <c r="E27" s="6">
-        <v>-7.79</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5">
-      <c r="A28" s="3" t="s">
+      <c r="D28" s="6">
+        <v>45.12</v>
+      </c>
+      <c r="E28" s="7">
+        <v>-9.57</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="B28" s="3" t="s">
+      <c r="B29" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="C28" s="5">
-        <v>97.79000000000001</v>
-      </c>
-      <c r="D28" s="5">
+      <c r="C29" s="6">
         <v>94.42</v>
       </c>
-      <c r="E28" s="6">
+      <c r="D29" s="6">
+        <v>87.23</v>
+      </c>
+      <c r="E29" s="7">
+        <v>-7.19</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B30" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C30" s="6">
+        <v>-24.58</v>
+      </c>
+      <c r="D30" s="6">
+        <v>-29.58</v>
+      </c>
+      <c r="E30" s="7">
+        <v>-5</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5">
+      <c r="A31" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="B31" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C31" s="6">
+        <v>-11.88</v>
+      </c>
+      <c r="D31" s="6">
+        <v>-13.25</v>
+      </c>
+      <c r="E31" s="7">
+        <v>-1.37</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5">
+      <c r="A32" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B32" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C32" s="6">
+        <v>-3.54</v>
+      </c>
+      <c r="D32" s="6">
+        <v>-7.22</v>
+      </c>
+      <c r="E32" s="7">
+        <v>-3.68</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5">
+      <c r="A33" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B33" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C33" s="6">
+        <v>-23.48</v>
+      </c>
+      <c r="D33" s="6">
+        <v>-26.25</v>
+      </c>
+      <c r="E33" s="7">
+        <v>-2.77</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5">
+      <c r="A34" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B34" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C34" s="6">
+        <v>-6.82</v>
+      </c>
+      <c r="D34" s="6">
+        <v>-10.5</v>
+      </c>
+      <c r="E34" s="7">
+        <v>-3.68</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5">
+      <c r="A35" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B35" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C35" s="6">
+        <v>-6.26</v>
+      </c>
+      <c r="D35" s="6">
+        <v>-7.61</v>
+      </c>
+      <c r="E35" s="7">
+        <v>-1.35</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5">
+      <c r="A36" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B36" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C36" s="6">
+        <v>-5.38</v>
+      </c>
+      <c r="D36" s="6">
+        <v>-8.83</v>
+      </c>
+      <c r="E36" s="7">
+        <v>-3.45</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5">
+      <c r="A37" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B37" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C37" s="6">
+        <v>4.34</v>
+      </c>
+      <c r="D37" s="6">
+        <v>3.83</v>
+      </c>
+      <c r="E37" s="7">
+        <v>-0.51</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5">
+      <c r="A38" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B38" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C38" s="6">
+        <v>-5.37</v>
+      </c>
+      <c r="D38" s="6">
+        <v>-9.93</v>
+      </c>
+      <c r="E38" s="7">
+        <v>-4.56</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5">
+      <c r="A39" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="B39" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C39" s="6">
+        <v>-6.12</v>
+      </c>
+      <c r="D39" s="6">
+        <v>-9.529999999999999</v>
+      </c>
+      <c r="E39" s="7">
+        <v>-3.41</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5">
+      <c r="A40" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B40" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C40" s="6">
+        <v>-12.39</v>
+      </c>
+      <c r="D40" s="6">
+        <v>-13.2</v>
+      </c>
+      <c r="E40" s="7">
+        <v>-0.8100000000000001</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5">
+      <c r="A41" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B41" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C41" s="6">
+        <v>-49.29</v>
+      </c>
+      <c r="D41" s="6">
+        <v>-49.93</v>
+      </c>
+      <c r="E41" s="7">
+        <v>-0.64</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5">
+      <c r="A42" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B42" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C42" s="6">
+        <v>-13.59</v>
+      </c>
+      <c r="D42" s="6">
+        <v>-15.49</v>
+      </c>
+      <c r="E42" s="7">
+        <v>-1.9</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5">
+      <c r="A43" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B43" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C43" s="6">
+        <v>-20.77</v>
+      </c>
+      <c r="D43" s="6">
+        <v>-22.58</v>
+      </c>
+      <c r="E43" s="7">
+        <v>-1.81</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5">
+      <c r="A44" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B44" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C44" s="6">
+        <v>-15.51</v>
+      </c>
+      <c r="D44" s="6">
+        <v>-17.95</v>
+      </c>
+      <c r="E44" s="7">
+        <v>-2.44</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5">
+      <c r="A45" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B45" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C45" s="6">
+        <v>-22.34</v>
+      </c>
+      <c r="D45" s="6">
+        <v>-24.14</v>
+      </c>
+      <c r="E45" s="7">
+        <v>-1.8</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5">
+      <c r="A46" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B46" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C46" s="6">
+        <v>-29.83</v>
+      </c>
+      <c r="D46" s="6">
+        <v>-32.03</v>
+      </c>
+      <c r="E46" s="7">
+        <v>-2.2</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5">
+      <c r="A47" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="B47" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C47" s="6">
+        <v>-18.34</v>
+      </c>
+      <c r="D47" s="6">
+        <v>-20.12</v>
+      </c>
+      <c r="E47" s="7">
+        <v>-1.78</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5">
+      <c r="A48" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B48" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C48" s="6">
+        <v>372.1</v>
+      </c>
+      <c r="D48" s="6">
+        <v>368.65</v>
+      </c>
+      <c r="E48" s="7">
+        <v>-3.45</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5">
+      <c r="A49" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B49" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C49" s="6">
+        <v>44.62</v>
+      </c>
+      <c r="D49" s="6">
+        <v>43.18</v>
+      </c>
+      <c r="E49" s="7">
+        <v>-1.44</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5">
+      <c r="A50" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B50" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C50" s="6">
+        <v>2921.1</v>
+      </c>
+      <c r="D50" s="6">
+        <v>2856.8</v>
+      </c>
+      <c r="E50" s="7">
+        <v>-64.3</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5">
+      <c r="A51" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B51" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C51" s="6">
+        <v>910.85</v>
+      </c>
+      <c r="D51" s="6">
+        <v>890.15</v>
+      </c>
+      <c r="E51" s="7">
+        <v>-20.7</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5">
+      <c r="A52" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B52" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C52" s="6">
+        <v>13.18</v>
+      </c>
+      <c r="D52" s="6">
+        <v>12.8</v>
+      </c>
+      <c r="E52" s="7">
+        <v>-0.38</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5">
+      <c r="A53" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B53" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C53" s="6">
+        <v>10.81</v>
+      </c>
+      <c r="D53" s="6">
+        <v>10.56</v>
+      </c>
+      <c r="E53" s="7">
+        <v>-0.25</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5">
+      <c r="A54" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B54" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C54" s="6">
+        <v>4076.3</v>
+      </c>
+      <c r="D54" s="6">
+        <v>3948.5</v>
+      </c>
+      <c r="E54" s="7">
+        <v>-127.8</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5">
+      <c r="A55" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="B55" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C55" s="6">
+        <v>10658</v>
+      </c>
+      <c r="D55" s="6">
+        <v>10426</v>
+      </c>
+      <c r="E55" s="7">
+        <v>-232</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5">
+      <c r="A56" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B56" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C56" s="6">
+        <v>37.46</v>
+      </c>
+      <c r="D56" s="6">
+        <v>35.73</v>
+      </c>
+      <c r="E56" s="7">
+        <v>-1.73</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5">
+      <c r="A57" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B57" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C57" s="6">
+        <v>29.59</v>
+      </c>
+      <c r="D57" s="6">
+        <v>26.22</v>
+      </c>
+      <c r="E57" s="7">
         <v>-3.37</v>
       </c>
     </row>
-    <row r="29" spans="1:5">
-      <c r="A29" s="3" t="s">
+    <row r="58" spans="1:5">
+      <c r="A58" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B58" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C58" s="6">
+        <v>26.61</v>
+      </c>
+      <c r="D58" s="6">
+        <v>23.39</v>
+      </c>
+      <c r="E58" s="7">
+        <v>-3.22</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5">
+      <c r="A59" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B59" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C59" s="6">
+        <v>29.36</v>
+      </c>
+      <c r="D59" s="6">
+        <v>25.9</v>
+      </c>
+      <c r="E59" s="7">
+        <v>-3.46</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5">
+      <c r="A60" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B60" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C60" s="6">
+        <v>41.33</v>
+      </c>
+      <c r="D60" s="6">
+        <v>37.55</v>
+      </c>
+      <c r="E60" s="7">
+        <v>-3.78</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5">
+      <c r="A61" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B61" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C61" s="6">
+        <v>42.63</v>
+      </c>
+      <c r="D61" s="6">
+        <v>39.59</v>
+      </c>
+      <c r="E61" s="7">
+        <v>-3.04</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5">
+      <c r="A62" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="B29" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C29" s="5">
-        <v>-24.05</v>
-      </c>
-      <c r="D29" s="5">
-        <v>-24.58</v>
-      </c>
-      <c r="E29" s="6">
-        <v>-0.53</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5">
-      <c r="A30" s="3" t="s">
+      <c r="B62" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C62" s="6">
+        <v>47.11</v>
+      </c>
+      <c r="D62" s="6">
+        <v>38.87</v>
+      </c>
+      <c r="E62" s="7">
+        <v>-8.24</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5">
+      <c r="A63" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="B30" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C30" s="5">
-        <v>-12.04</v>
-      </c>
-      <c r="D30" s="5">
-        <v>-11.88</v>
-      </c>
-      <c r="E30" s="7">
-        <v>0.16</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5">
-      <c r="A31" s="3" t="s">
+      <c r="B63" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C63" s="6">
+        <v>37.96</v>
+      </c>
+      <c r="D63" s="6">
+        <v>33.2</v>
+      </c>
+      <c r="E63" s="7">
+        <v>-4.76</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5">
+      <c r="A64" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B31" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C31" s="5">
-        <v>-6.54</v>
-      </c>
-      <c r="D31" s="5">
-        <v>-3.54</v>
-      </c>
-      <c r="E31" s="7">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5">
-      <c r="A32" s="3" t="s">
+      <c r="B64" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C64" s="6">
+        <v>56.67</v>
+      </c>
+      <c r="D64" s="6">
+        <v>58.33</v>
+      </c>
+      <c r="E64" s="8">
+        <v>1.66</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5">
+      <c r="A65" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B32" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C32" s="5">
-        <v>-23.39</v>
-      </c>
-      <c r="D32" s="5">
-        <v>-23.48</v>
-      </c>
-      <c r="E32" s="6">
-        <v>-0.09</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5">
-      <c r="A33" s="3" t="s">
+      <c r="B65" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C65" s="6">
+        <v>-22.38</v>
+      </c>
+      <c r="D65" s="6">
+        <v>-21.21</v>
+      </c>
+      <c r="E65" s="8">
+        <v>1.17</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5">
+      <c r="A66" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B33" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C33" s="5">
-        <v>-6.95</v>
-      </c>
-      <c r="D33" s="5">
-        <v>-6.82</v>
-      </c>
-      <c r="E33" s="7">
-        <v>0.13</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5">
-      <c r="A34" s="3" t="s">
+      <c r="B66" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C66" s="6">
+        <v>-68.81999999999999</v>
+      </c>
+      <c r="D66" s="6">
+        <v>-31.99</v>
+      </c>
+      <c r="E66" s="8">
+        <v>36.83</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5">
+      <c r="A67" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B34" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C34" s="5">
-        <v>-2.99</v>
-      </c>
-      <c r="D34" s="5">
-        <v>-6.26</v>
-      </c>
-      <c r="E34" s="6">
-        <v>-3.27</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5">
-      <c r="A35" s="3" t="s">
+      <c r="B67" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C67" s="6">
+        <v>-0.9</v>
+      </c>
+      <c r="D67" s="6">
+        <v>-0.58</v>
+      </c>
+      <c r="E67" s="8">
+        <v>0.32</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5">
+      <c r="A68" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B35" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C35" s="5">
-        <v>-4.62</v>
-      </c>
-      <c r="D35" s="5">
-        <v>-5.38</v>
-      </c>
-      <c r="E35" s="6">
-        <v>-0.76</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5">
-      <c r="A36" s="3" t="s">
+      <c r="B68" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C68" s="6">
+        <v>-22.62</v>
+      </c>
+      <c r="D68" s="6">
+        <v>-38.29</v>
+      </c>
+      <c r="E68" s="7">
+        <v>-15.67</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5">
+      <c r="A69" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="B36" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C36" s="5">
-        <v>1.8</v>
-      </c>
-      <c r="D36" s="5">
-        <v>4.34</v>
-      </c>
-      <c r="E36" s="7">
-        <v>2.54</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5">
-      <c r="A37" s="3" t="s">
+      <c r="B69" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C69" s="6">
+        <v>-18.11</v>
+      </c>
+      <c r="D69" s="6">
+        <v>-33.77</v>
+      </c>
+      <c r="E69" s="7">
+        <v>-15.66</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5">
+      <c r="A70" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="B37" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C37" s="5">
-        <v>-7.26</v>
-      </c>
-      <c r="D37" s="5">
-        <v>-5.37</v>
-      </c>
-      <c r="E37" s="7">
-        <v>1.89</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5">
-      <c r="A38" s="3" t="s">
+      <c r="B70" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C70" s="6">
+        <v>-48.04</v>
+      </c>
+      <c r="D70" s="6">
+        <v>-22.65</v>
+      </c>
+      <c r="E70" s="8">
+        <v>25.39</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5">
+      <c r="A71" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="B38" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C38" s="5">
-        <v>-7.72</v>
-      </c>
-      <c r="D38" s="5">
-        <v>-6.12</v>
-      </c>
-      <c r="E38" s="7">
-        <v>1.6</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5">
-      <c r="A39" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B39" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C39" s="5">
-        <v>-10.78</v>
-      </c>
-      <c r="D39" s="5">
-        <v>-12.39</v>
-      </c>
-      <c r="E39" s="6">
-        <v>-1.61</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5">
-      <c r="A40" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B40" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C40" s="5">
-        <v>-48.09</v>
-      </c>
-      <c r="D40" s="5">
-        <v>-49.29</v>
-      </c>
-      <c r="E40" s="6">
-        <v>-1.2</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5">
-      <c r="A41" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B41" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C41" s="5">
-        <v>-12.17</v>
-      </c>
-      <c r="D41" s="5">
-        <v>-13.59</v>
-      </c>
-      <c r="E41" s="6">
-        <v>-1.42</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5">
-      <c r="A42" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="B42" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C42" s="5">
-        <v>-18.2</v>
-      </c>
-      <c r="D42" s="5">
-        <v>-20.77</v>
-      </c>
-      <c r="E42" s="6">
-        <v>-2.57</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5">
-      <c r="A43" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="B43" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C43" s="5">
-        <v>-15.32</v>
-      </c>
-      <c r="D43" s="5">
-        <v>-15.51</v>
-      </c>
-      <c r="E43" s="6">
-        <v>-0.19</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5">
-      <c r="A44" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="B44" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C44" s="5">
-        <v>-22.7</v>
-      </c>
-      <c r="D44" s="5">
-        <v>-22.34</v>
-      </c>
-      <c r="E44" s="7">
-        <v>0.36</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5">
-      <c r="A45" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="B45" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C45" s="5">
-        <v>-29.99</v>
-      </c>
-      <c r="D45" s="5">
-        <v>-29.83</v>
-      </c>
-      <c r="E45" s="7">
-        <v>0.16</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5">
-      <c r="A46" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="B46" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C46" s="5">
-        <v>-17.64</v>
-      </c>
-      <c r="D46" s="5">
-        <v>-18.34</v>
-      </c>
-      <c r="E46" s="6">
-        <v>-0.7</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5">
-      <c r="A47" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B47" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C47" s="5">
-        <v>378.9</v>
-      </c>
-      <c r="D47" s="5">
-        <v>372.1</v>
-      </c>
-      <c r="E47" s="6">
-        <v>-6.8</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5">
-      <c r="A48" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B48" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C48" s="5">
-        <v>45.68</v>
-      </c>
-      <c r="D48" s="5">
-        <v>44.62</v>
-      </c>
-      <c r="E48" s="6">
-        <v>-1.06</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5">
-      <c r="A49" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B49" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C49" s="5">
-        <v>2969</v>
-      </c>
-      <c r="D49" s="5">
-        <v>2921.1</v>
-      </c>
-      <c r="E49" s="6">
-        <v>-47.9</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5">
-      <c r="A50" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="B50" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C50" s="5">
-        <v>940.5</v>
-      </c>
-      <c r="D50" s="5">
-        <v>910.85</v>
-      </c>
-      <c r="E50" s="6">
-        <v>-29.65</v>
-      </c>
-    </row>
-    <row r="51" spans="1:5">
-      <c r="A51" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="B51" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C51" s="5">
-        <v>13.21</v>
-      </c>
-      <c r="D51" s="5">
-        <v>13.18</v>
-      </c>
-      <c r="E51" s="6">
-        <v>-0.03</v>
-      </c>
-    </row>
-    <row r="52" spans="1:5">
-      <c r="A52" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="B52" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C52" s="5">
-        <v>10.76</v>
-      </c>
-      <c r="D52" s="5">
-        <v>10.81</v>
-      </c>
-      <c r="E52" s="7">
-        <v>0.05</v>
-      </c>
-    </row>
-    <row r="53" spans="1:5">
-      <c r="A53" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="B53" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C53" s="5">
-        <v>4067.1</v>
-      </c>
-      <c r="D53" s="5">
-        <v>4076.3</v>
-      </c>
-      <c r="E53" s="7">
-        <v>9.199999999999999</v>
-      </c>
-    </row>
-    <row r="54" spans="1:5">
-      <c r="A54" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="B54" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C54" s="5">
-        <v>10750</v>
-      </c>
-      <c r="D54" s="5">
-        <v>10658</v>
-      </c>
-      <c r="E54" s="6">
-        <v>-92</v>
-      </c>
-    </row>
-    <row r="55" spans="1:5">
-      <c r="A55" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B55" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C55" s="5">
-        <v>41.09</v>
-      </c>
-      <c r="D55" s="5">
-        <v>37.46</v>
-      </c>
-      <c r="E55" s="6">
-        <v>-3.63</v>
-      </c>
-    </row>
-    <row r="56" spans="1:5">
-      <c r="A56" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B56" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C56" s="5">
-        <v>32.45</v>
-      </c>
-      <c r="D56" s="5">
-        <v>29.59</v>
-      </c>
-      <c r="E56" s="6">
-        <v>-2.86</v>
-      </c>
-    </row>
-    <row r="57" spans="1:5">
-      <c r="A57" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B57" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C57" s="5">
-        <v>29.42</v>
-      </c>
-      <c r="D57" s="5">
-        <v>26.61</v>
-      </c>
-      <c r="E57" s="6">
-        <v>-2.81</v>
-      </c>
-    </row>
-    <row r="58" spans="1:5">
-      <c r="A58" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="B58" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C58" s="5">
-        <v>35.72</v>
-      </c>
-      <c r="D58" s="5">
-        <v>29.36</v>
-      </c>
-      <c r="E58" s="6">
-        <v>-6.36</v>
-      </c>
-    </row>
-    <row r="59" spans="1:5">
-      <c r="A59" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="B59" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C59" s="5">
-        <v>41.63</v>
-      </c>
-      <c r="D59" s="5">
-        <v>41.33</v>
-      </c>
-      <c r="E59" s="6">
-        <v>-0.3</v>
-      </c>
-    </row>
-    <row r="60" spans="1:5">
-      <c r="A60" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="B60" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C60" s="5">
-        <v>41.8</v>
-      </c>
-      <c r="D60" s="5">
-        <v>42.63</v>
-      </c>
-      <c r="E60" s="7">
-        <v>0.83</v>
-      </c>
-    </row>
-    <row r="61" spans="1:5">
-      <c r="A61" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="B61" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C61" s="5">
-        <v>46.35</v>
-      </c>
-      <c r="D61" s="5">
-        <v>47.11</v>
-      </c>
-      <c r="E61" s="7">
-        <v>0.76</v>
-      </c>
-    </row>
-    <row r="62" spans="1:5">
-      <c r="A62" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="B62" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C62" s="5">
-        <v>40.07</v>
-      </c>
-      <c r="D62" s="5">
-        <v>37.96</v>
-      </c>
-      <c r="E62" s="6">
-        <v>-2.11</v>
-      </c>
-    </row>
-    <row r="63" spans="1:5">
-      <c r="A63" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B63" s="3" t="s">
+      <c r="B71" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="C63" s="5">
-        <v>82.95</v>
-      </c>
-      <c r="D63" s="5">
-        <v>56.67</v>
-      </c>
-      <c r="E63" s="6">
-        <v>-26.28</v>
-      </c>
-    </row>
-    <row r="64" spans="1:5">
-      <c r="A64" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B64" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C64" s="5">
-        <v>113.19</v>
-      </c>
-      <c r="D64" s="5">
-        <v>-22.38</v>
-      </c>
-      <c r="E64" s="6">
-        <v>-135.57</v>
-      </c>
-    </row>
-    <row r="65" spans="1:5">
-      <c r="A65" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B65" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C65" s="5">
-        <v>-57.64</v>
-      </c>
-      <c r="D65" s="5">
-        <v>-68.81999999999999</v>
-      </c>
-      <c r="E65" s="6">
-        <v>-11.18</v>
-      </c>
-    </row>
-    <row r="66" spans="1:5">
-      <c r="A66" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="B66" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C66" s="5">
-        <v>-20.24</v>
-      </c>
-      <c r="D66" s="5">
-        <v>-0.9</v>
-      </c>
-      <c r="E66" s="7">
-        <v>19.34</v>
-      </c>
-    </row>
-    <row r="67" spans="1:5">
-      <c r="A67" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="B67" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C67" s="5">
-        <v>-30.3</v>
-      </c>
-      <c r="D67" s="5">
-        <v>-22.62</v>
-      </c>
-      <c r="E67" s="7">
-        <v>7.68</v>
-      </c>
-    </row>
-    <row r="68" spans="1:5">
-      <c r="A68" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="B68" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C68" s="5">
-        <v>13.54</v>
-      </c>
-      <c r="D68" s="5">
-        <v>-18.11</v>
-      </c>
-      <c r="E68" s="6">
-        <v>-31.65</v>
-      </c>
-    </row>
-    <row r="69" spans="1:5">
-      <c r="A69" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="B69" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C69" s="5">
-        <v>-45.15</v>
-      </c>
-      <c r="D69" s="5">
-        <v>-48.04</v>
-      </c>
-      <c r="E69" s="6">
-        <v>-2.89</v>
-      </c>
-    </row>
-    <row r="70" spans="1:5">
-      <c r="A70" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="B70" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C70" s="5">
-        <v>-9.77</v>
-      </c>
-      <c r="D70" s="5">
+      <c r="C71" s="6">
         <v>-4.24</v>
       </c>
-      <c r="E70" s="7">
-        <v>5.53</v>
+      <c r="D71" s="6">
+        <v>-24.5</v>
+      </c>
+      <c r="E71" s="7">
+        <v>-20.26</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A5:E5"/>
+    <mergeCell ref="A6:E6"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3092,61 +3167,61 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="28" customHeight="1">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="8" t="s">
-        <v>56</v>
-      </c>
-      <c r="C1" s="8" t="s">
-        <v>57</v>
-      </c>
-      <c r="D1" s="8" t="s">
-        <v>58</v>
-      </c>
-      <c r="E1" s="8" t="s">
-        <v>59</v>
-      </c>
-      <c r="F1" s="8" t="s">
-        <v>60</v>
-      </c>
-      <c r="G1" s="8" t="s">
-        <v>61</v>
-      </c>
-      <c r="H1" s="8" t="s">
-        <v>62</v>
-      </c>
-      <c r="I1" s="8" t="s">
+      <c r="B1" s="9" t="s">
         <v>63</v>
       </c>
+      <c r="C1" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="D1" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="E1" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="F1" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="G1" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="H1" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="I1" s="9" t="s">
+        <v>70</v>
+      </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="9" t="s">
+      <c r="A2" s="10" t="s">
         <v>45</v>
       </c>
-      <c r="B2" s="10">
+      <c r="B2" s="11">
         <v>40.44</v>
       </c>
-      <c r="C2" s="11">
+      <c r="C2" s="12">
         <v>8</v>
       </c>
-      <c r="D2" s="10">
-        <v>36.5</v>
-      </c>
-      <c r="E2" s="10">
+      <c r="D2" s="11">
+        <v>32.6</v>
+      </c>
+      <c r="E2" s="11">
         <v>20</v>
       </c>
-      <c r="F2" s="10">
-        <v>-8.9</v>
-      </c>
-      <c r="G2" s="10">
-        <v>-6.6</v>
-      </c>
-      <c r="H2" s="10">
+      <c r="F2" s="11">
+        <v>-11.3</v>
+      </c>
+      <c r="G2" s="11">
+        <v>-9.5</v>
+      </c>
+      <c r="H2" s="11">
         <v>56.1</v>
       </c>
-      <c r="I2" s="10">
-        <v>10</v>
+      <c r="I2" s="11">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -3247,55 +3322,55 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8">
-      <c r="A1" s="12" t="s">
+      <c r="A1" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="B1" s="12" t="s">
+      <c r="B1" s="13" t="s">
         <v>43</v>
       </c>
-      <c r="C1" s="12" t="s">
+      <c r="C1" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="D1" s="12" t="s">
+      <c r="D1" s="13" t="s">
         <v>39</v>
       </c>
-      <c r="E1" s="12" t="s">
+      <c r="E1" s="13" t="s">
         <v>44</v>
       </c>
-      <c r="F1" s="12" t="s">
+      <c r="F1" s="13" t="s">
         <v>41</v>
       </c>
-      <c r="G1" s="12" t="s">
+      <c r="G1" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="H1" s="12" t="s">
+      <c r="H1" s="13" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="2" spans="1:8">
-      <c r="A2" s="13">
-        <v>0.2758</v>
-      </c>
-      <c r="B2" s="13">
-        <v>0.1595</v>
-      </c>
-      <c r="C2" s="13">
-        <v>0.1444</v>
-      </c>
-      <c r="D2" s="13">
-        <v>0.1343</v>
-      </c>
-      <c r="E2" s="13">
-        <v>0.0819</v>
-      </c>
-      <c r="F2" s="13">
-        <v>0.0304</v>
-      </c>
-      <c r="G2" s="13">
-        <v>-0.2965</v>
-      </c>
-      <c r="H2" s="13">
-        <v>-0.309</v>
+      <c r="A2" s="14">
+        <v>0.2703</v>
+      </c>
+      <c r="B2" s="14">
+        <v>0.1538</v>
+      </c>
+      <c r="C2" s="14">
+        <v>0.141</v>
+      </c>
+      <c r="D2" s="14">
+        <v>0.1283</v>
+      </c>
+      <c r="E2" s="14">
+        <v>0.07769999999999999</v>
+      </c>
+      <c r="F2" s="14">
+        <v>0.0243</v>
+      </c>
+      <c r="G2" s="14">
+        <v>-0.2999</v>
+      </c>
+      <c r="H2" s="14">
+        <v>-0.314</v>
       </c>
     </row>
   </sheetData>

--- a/BIRLA_GROUP_Technical_Metrics.xlsx
+++ b/BIRLA_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="293" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="61">
   <si>
     <t>Symbol</t>
   </si>
@@ -172,43 +172,13 @@
     <t>▶  SIGNAL EVENTS (vs Previous Run)</t>
   </si>
   <si>
-    <t>Signal</t>
-  </si>
-  <si>
-    <t>Change</t>
-  </si>
-  <si>
-    <t>Direction</t>
-  </si>
-  <si>
-    <t>Prev Value</t>
-  </si>
-  <si>
-    <t>Curr Value</t>
-  </si>
-  <si>
-    <t>Yes → No</t>
-  </si>
-  <si>
-    <t>🔴 BEARISH</t>
-  </si>
-  <si>
-    <t>20 DMA &gt; 50 DMA</t>
+    <t>No signal events detected since last run.</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
   </si>
   <si>
-    <t>Metric</t>
-  </si>
-  <si>
-    <t>Previous</t>
-  </si>
-  <si>
-    <t>Current</t>
-  </si>
-  <si>
-    <t>Delta</t>
+    <t>No numeric changes detected since last run.</t>
   </si>
   <si>
     <t>Rank</t>
@@ -239,13 +209,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="4">
-    <numFmt numFmtId="164" formatCode="0.00"/>
-    <numFmt numFmtId="165" formatCode="+0.00;-0.00"/>
-    <numFmt numFmtId="166" formatCode="0.0"/>
-    <numFmt numFmtId="167" formatCode="0.00%"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="0.0"/>
+    <numFmt numFmtId="165" formatCode="0.00%"/>
   </numFmts>
-  <fonts count="6">
+  <fonts count="4">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -277,22 +245,8 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
-  <fills count="9">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -308,24 +262,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF2E4057"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF4A6FA5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -395,34 +331,27 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
@@ -1952,7 +1881,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F71"/>
+  <dimension ref="A1:F6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -1972,1182 +1901,27 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="C2" s="3" t="s">
+    </row>
+    <row r="5" spans="1:6">
+      <c r="A5" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="D2" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="F2" s="3" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6">
-      <c r="A3" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="B3" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="C3" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="D3" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="E3" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="F3" s="4" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6">
-      <c r="A4" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="B4" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="C4" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="D4" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="E4" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="F4" s="4" t="s">
-        <v>46</v>
-      </c>
+      <c r="B5" s="2"/>
+      <c r="C5" s="2"/>
+      <c r="D5" s="2"/>
+      <c r="E5" s="2"/>
     </row>
     <row r="6" spans="1:6">
-      <c r="A6" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="B6" s="2"/>
-      <c r="C6" s="2"/>
-      <c r="D6" s="2"/>
-      <c r="E6" s="2"/>
-    </row>
-    <row r="7" spans="1:6">
-      <c r="A7" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="E7" s="3" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
-      <c r="A8" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B8" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C8" s="6">
-        <v>-8.1</v>
-      </c>
-      <c r="D8" s="6">
-        <v>-8.58</v>
-      </c>
-      <c r="E8" s="7">
-        <v>-0.48</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B9" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C9" s="6">
-        <v>-15.76</v>
-      </c>
-      <c r="D9" s="6">
-        <v>-18.85</v>
-      </c>
-      <c r="E9" s="7">
-        <v>-3.09</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B10" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C10" s="6">
-        <v>-12.07</v>
-      </c>
-      <c r="D10" s="6">
-        <v>-13.49</v>
-      </c>
-      <c r="E10" s="7">
-        <v>-1.42</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B11" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C11" s="6">
-        <v>-9.91</v>
-      </c>
-      <c r="D11" s="6">
-        <v>-11.52</v>
-      </c>
-      <c r="E11" s="7">
-        <v>-1.61</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B12" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C12" s="6">
-        <v>-12.25</v>
-      </c>
-      <c r="D12" s="6">
-        <v>-17.95</v>
-      </c>
-      <c r="E12" s="7">
-        <v>-5.7</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B13" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C13" s="6">
-        <v>-0.83</v>
-      </c>
-      <c r="D13" s="6">
-        <v>-4.95</v>
-      </c>
-      <c r="E13" s="7">
-        <v>-4.12</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B14" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C14" s="6">
-        <v>-5.72</v>
-      </c>
-      <c r="D14" s="6">
-        <v>-8.15</v>
-      </c>
-      <c r="E14" s="7">
-        <v>-2.43</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="B15" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C15" s="6">
-        <v>-6.57</v>
-      </c>
-      <c r="D15" s="6">
-        <v>-6.7</v>
-      </c>
-      <c r="E15" s="7">
-        <v>-0.13</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B16" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C16" s="6">
-        <v>-1.56</v>
-      </c>
-      <c r="D16" s="6">
-        <v>-3.14</v>
-      </c>
-      <c r="E16" s="7">
-        <v>-1.58</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5">
-      <c r="A17" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B17" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C17" s="6">
-        <v>-3.5</v>
-      </c>
-      <c r="D17" s="6">
-        <v>-6.78</v>
-      </c>
-      <c r="E17" s="7">
-        <v>-3.28</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5">
-      <c r="A18" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B18" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C18" s="6">
-        <v>-5.77</v>
-      </c>
-      <c r="D18" s="6">
-        <v>-6.7</v>
-      </c>
-      <c r="E18" s="7">
-        <v>-0.93</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5">
-      <c r="A19" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B19" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C19" s="6">
-        <v>-4.64</v>
-      </c>
-      <c r="D19" s="6">
-        <v>-5.48</v>
-      </c>
-      <c r="E19" s="7">
-        <v>-0.84</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5">
-      <c r="A20" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B20" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C20" s="6">
-        <v>-2.8</v>
-      </c>
-      <c r="D20" s="6">
-        <v>-1.16</v>
-      </c>
-      <c r="E20" s="8">
-        <v>1.64</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5">
-      <c r="A21" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B21" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C21" s="6">
-        <v>-0.28</v>
-      </c>
-      <c r="D21" s="6">
-        <v>-3.3</v>
-      </c>
-      <c r="E21" s="7">
-        <v>-3.02</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5">
-      <c r="A22" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B22" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C22" s="6">
-        <v>1.21</v>
-      </c>
-      <c r="D22" s="6">
-        <v>-0.2</v>
-      </c>
-      <c r="E22" s="7">
-        <v>-1.41</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5">
-      <c r="A23" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="B23" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C23" s="6">
-        <v>-1.58</v>
-      </c>
-      <c r="D23" s="6">
-        <v>-4.84</v>
-      </c>
-      <c r="E23" s="7">
-        <v>-3.26</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5">
-      <c r="A24" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B24" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C24" s="6">
-        <v>24.1</v>
-      </c>
-      <c r="D24" s="6">
-        <v>21.29</v>
-      </c>
-      <c r="E24" s="7">
-        <v>-2.81</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5">
-      <c r="A25" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B25" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C25" s="6">
-        <v>-48.35</v>
-      </c>
-      <c r="D25" s="6">
-        <v>-50.93</v>
-      </c>
-      <c r="E25" s="7">
-        <v>-2.58</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5">
-      <c r="A26" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B26" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C26" s="6">
-        <v>4.71</v>
-      </c>
-      <c r="D26" s="6">
-        <v>2.34</v>
-      </c>
-      <c r="E26" s="7">
-        <v>-2.37</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5">
-      <c r="A27" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B27" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C27" s="6">
-        <v>18.92</v>
-      </c>
-      <c r="D27" s="6">
-        <v>14.07</v>
-      </c>
-      <c r="E27" s="7">
-        <v>-4.85</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5">
-      <c r="A28" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B28" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C28" s="6">
-        <v>54.69</v>
-      </c>
-      <c r="D28" s="6">
-        <v>45.12</v>
-      </c>
-      <c r="E28" s="7">
-        <v>-9.57</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5">
-      <c r="A29" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B29" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C29" s="6">
-        <v>94.42</v>
-      </c>
-      <c r="D29" s="6">
-        <v>87.23</v>
-      </c>
-      <c r="E29" s="7">
-        <v>-7.19</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5">
-      <c r="A30" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B30" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C30" s="6">
-        <v>-24.58</v>
-      </c>
-      <c r="D30" s="6">
-        <v>-29.58</v>
-      </c>
-      <c r="E30" s="7">
-        <v>-5</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5">
-      <c r="A31" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="B31" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C31" s="6">
-        <v>-11.88</v>
-      </c>
-      <c r="D31" s="6">
-        <v>-13.25</v>
-      </c>
-      <c r="E31" s="7">
-        <v>-1.37</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5">
-      <c r="A32" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B32" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C32" s="6">
-        <v>-3.54</v>
-      </c>
-      <c r="D32" s="6">
-        <v>-7.22</v>
-      </c>
-      <c r="E32" s="7">
-        <v>-3.68</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5">
-      <c r="A33" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B33" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C33" s="6">
-        <v>-23.48</v>
-      </c>
-      <c r="D33" s="6">
-        <v>-26.25</v>
-      </c>
-      <c r="E33" s="7">
-        <v>-2.77</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5">
-      <c r="A34" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B34" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C34" s="6">
-        <v>-6.82</v>
-      </c>
-      <c r="D34" s="6">
-        <v>-10.5</v>
-      </c>
-      <c r="E34" s="7">
-        <v>-3.68</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5">
-      <c r="A35" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B35" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C35" s="6">
-        <v>-6.26</v>
-      </c>
-      <c r="D35" s="6">
-        <v>-7.61</v>
-      </c>
-      <c r="E35" s="7">
-        <v>-1.35</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5">
-      <c r="A36" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B36" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C36" s="6">
-        <v>-5.38</v>
-      </c>
-      <c r="D36" s="6">
-        <v>-8.83</v>
-      </c>
-      <c r="E36" s="7">
-        <v>-3.45</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5">
-      <c r="A37" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B37" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C37" s="6">
-        <v>4.34</v>
-      </c>
-      <c r="D37" s="6">
-        <v>3.83</v>
-      </c>
-      <c r="E37" s="7">
-        <v>-0.51</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5">
-      <c r="A38" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B38" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C38" s="6">
-        <v>-5.37</v>
-      </c>
-      <c r="D38" s="6">
-        <v>-9.93</v>
-      </c>
-      <c r="E38" s="7">
-        <v>-4.56</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5">
-      <c r="A39" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="B39" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C39" s="6">
-        <v>-6.12</v>
-      </c>
-      <c r="D39" s="6">
-        <v>-9.529999999999999</v>
-      </c>
-      <c r="E39" s="7">
-        <v>-3.41</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5">
-      <c r="A40" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B40" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C40" s="6">
-        <v>-12.39</v>
-      </c>
-      <c r="D40" s="6">
-        <v>-13.2</v>
-      </c>
-      <c r="E40" s="7">
-        <v>-0.8100000000000001</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5">
-      <c r="A41" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B41" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C41" s="6">
-        <v>-49.29</v>
-      </c>
-      <c r="D41" s="6">
-        <v>-49.93</v>
-      </c>
-      <c r="E41" s="7">
-        <v>-0.64</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5">
-      <c r="A42" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B42" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C42" s="6">
-        <v>-13.59</v>
-      </c>
-      <c r="D42" s="6">
-        <v>-15.49</v>
-      </c>
-      <c r="E42" s="7">
-        <v>-1.9</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5">
-      <c r="A43" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B43" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C43" s="6">
-        <v>-20.77</v>
-      </c>
-      <c r="D43" s="6">
-        <v>-22.58</v>
-      </c>
-      <c r="E43" s="7">
-        <v>-1.81</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5">
-      <c r="A44" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B44" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C44" s="6">
-        <v>-15.51</v>
-      </c>
-      <c r="D44" s="6">
-        <v>-17.95</v>
-      </c>
-      <c r="E44" s="7">
-        <v>-2.44</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5">
-      <c r="A45" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B45" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C45" s="6">
-        <v>-22.34</v>
-      </c>
-      <c r="D45" s="6">
-        <v>-24.14</v>
-      </c>
-      <c r="E45" s="7">
-        <v>-1.8</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5">
-      <c r="A46" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B46" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C46" s="6">
-        <v>-29.83</v>
-      </c>
-      <c r="D46" s="6">
-        <v>-32.03</v>
-      </c>
-      <c r="E46" s="7">
-        <v>-2.2</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5">
-      <c r="A47" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="B47" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C47" s="6">
-        <v>-18.34</v>
-      </c>
-      <c r="D47" s="6">
-        <v>-20.12</v>
-      </c>
-      <c r="E47" s="7">
-        <v>-1.78</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5">
-      <c r="A48" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B48" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C48" s="6">
-        <v>372.1</v>
-      </c>
-      <c r="D48" s="6">
-        <v>368.65</v>
-      </c>
-      <c r="E48" s="7">
-        <v>-3.45</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5">
-      <c r="A49" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B49" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C49" s="6">
-        <v>44.62</v>
-      </c>
-      <c r="D49" s="6">
-        <v>43.18</v>
-      </c>
-      <c r="E49" s="7">
-        <v>-1.44</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5">
-      <c r="A50" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B50" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C50" s="6">
-        <v>2921.1</v>
-      </c>
-      <c r="D50" s="6">
-        <v>2856.8</v>
-      </c>
-      <c r="E50" s="7">
-        <v>-64.3</v>
-      </c>
-    </row>
-    <row r="51" spans="1:5">
-      <c r="A51" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B51" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C51" s="6">
-        <v>910.85</v>
-      </c>
-      <c r="D51" s="6">
-        <v>890.15</v>
-      </c>
-      <c r="E51" s="7">
-        <v>-20.7</v>
-      </c>
-    </row>
-    <row r="52" spans="1:5">
-      <c r="A52" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B52" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C52" s="6">
-        <v>13.18</v>
-      </c>
-      <c r="D52" s="6">
-        <v>12.8</v>
-      </c>
-      <c r="E52" s="7">
-        <v>-0.38</v>
-      </c>
-    </row>
-    <row r="53" spans="1:5">
-      <c r="A53" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B53" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C53" s="6">
-        <v>10.81</v>
-      </c>
-      <c r="D53" s="6">
-        <v>10.56</v>
-      </c>
-      <c r="E53" s="7">
-        <v>-0.25</v>
-      </c>
-    </row>
-    <row r="54" spans="1:5">
-      <c r="A54" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B54" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C54" s="6">
-        <v>4076.3</v>
-      </c>
-      <c r="D54" s="6">
-        <v>3948.5</v>
-      </c>
-      <c r="E54" s="7">
-        <v>-127.8</v>
-      </c>
-    </row>
-    <row r="55" spans="1:5">
-      <c r="A55" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="B55" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C55" s="6">
-        <v>10658</v>
-      </c>
-      <c r="D55" s="6">
-        <v>10426</v>
-      </c>
-      <c r="E55" s="7">
-        <v>-232</v>
-      </c>
-    </row>
-    <row r="56" spans="1:5">
-      <c r="A56" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B56" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C56" s="6">
-        <v>37.46</v>
-      </c>
-      <c r="D56" s="6">
-        <v>35.73</v>
-      </c>
-      <c r="E56" s="7">
-        <v>-1.73</v>
-      </c>
-    </row>
-    <row r="57" spans="1:5">
-      <c r="A57" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B57" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C57" s="6">
-        <v>29.59</v>
-      </c>
-      <c r="D57" s="6">
-        <v>26.22</v>
-      </c>
-      <c r="E57" s="7">
-        <v>-3.37</v>
-      </c>
-    </row>
-    <row r="58" spans="1:5">
-      <c r="A58" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B58" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C58" s="6">
-        <v>26.61</v>
-      </c>
-      <c r="D58" s="6">
-        <v>23.39</v>
-      </c>
-      <c r="E58" s="7">
-        <v>-3.22</v>
-      </c>
-    </row>
-    <row r="59" spans="1:5">
-      <c r="A59" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B59" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C59" s="6">
-        <v>29.36</v>
-      </c>
-      <c r="D59" s="6">
-        <v>25.9</v>
-      </c>
-      <c r="E59" s="7">
-        <v>-3.46</v>
-      </c>
-    </row>
-    <row r="60" spans="1:5">
-      <c r="A60" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B60" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C60" s="6">
-        <v>41.33</v>
-      </c>
-      <c r="D60" s="6">
-        <v>37.55</v>
-      </c>
-      <c r="E60" s="7">
-        <v>-3.78</v>
-      </c>
-    </row>
-    <row r="61" spans="1:5">
-      <c r="A61" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B61" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C61" s="6">
-        <v>42.63</v>
-      </c>
-      <c r="D61" s="6">
-        <v>39.59</v>
-      </c>
-      <c r="E61" s="7">
-        <v>-3.04</v>
-      </c>
-    </row>
-    <row r="62" spans="1:5">
-      <c r="A62" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B62" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C62" s="6">
-        <v>47.11</v>
-      </c>
-      <c r="D62" s="6">
-        <v>38.87</v>
-      </c>
-      <c r="E62" s="7">
-        <v>-8.24</v>
-      </c>
-    </row>
-    <row r="63" spans="1:5">
-      <c r="A63" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="B63" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C63" s="6">
-        <v>37.96</v>
-      </c>
-      <c r="D63" s="6">
-        <v>33.2</v>
-      </c>
-      <c r="E63" s="7">
-        <v>-4.76</v>
-      </c>
-    </row>
-    <row r="64" spans="1:5">
-      <c r="A64" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B64" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C64" s="6">
-        <v>56.67</v>
-      </c>
-      <c r="D64" s="6">
-        <v>58.33</v>
-      </c>
-      <c r="E64" s="8">
-        <v>1.66</v>
-      </c>
-    </row>
-    <row r="65" spans="1:5">
-      <c r="A65" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B65" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C65" s="6">
-        <v>-22.38</v>
-      </c>
-      <c r="D65" s="6">
-        <v>-21.21</v>
-      </c>
-      <c r="E65" s="8">
-        <v>1.17</v>
-      </c>
-    </row>
-    <row r="66" spans="1:5">
-      <c r="A66" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B66" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C66" s="6">
-        <v>-68.81999999999999</v>
-      </c>
-      <c r="D66" s="6">
-        <v>-31.99</v>
-      </c>
-      <c r="E66" s="8">
-        <v>36.83</v>
-      </c>
-    </row>
-    <row r="67" spans="1:5">
-      <c r="A67" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B67" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C67" s="6">
-        <v>-0.9</v>
-      </c>
-      <c r="D67" s="6">
-        <v>-0.58</v>
-      </c>
-      <c r="E67" s="8">
-        <v>0.32</v>
-      </c>
-    </row>
-    <row r="68" spans="1:5">
-      <c r="A68" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B68" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C68" s="6">
-        <v>-22.62</v>
-      </c>
-      <c r="D68" s="6">
-        <v>-38.29</v>
-      </c>
-      <c r="E68" s="7">
-        <v>-15.67</v>
-      </c>
-    </row>
-    <row r="69" spans="1:5">
-      <c r="A69" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B69" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C69" s="6">
-        <v>-18.11</v>
-      </c>
-      <c r="D69" s="6">
-        <v>-33.77</v>
-      </c>
-      <c r="E69" s="7">
-        <v>-15.66</v>
-      </c>
-    </row>
-    <row r="70" spans="1:5">
-      <c r="A70" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B70" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C70" s="6">
-        <v>-48.04</v>
-      </c>
-      <c r="D70" s="6">
-        <v>-22.65</v>
-      </c>
-      <c r="E70" s="8">
-        <v>25.39</v>
-      </c>
-    </row>
-    <row r="71" spans="1:5">
-      <c r="A71" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="B71" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C71" s="6">
-        <v>-4.24</v>
-      </c>
-      <c r="D71" s="6">
-        <v>-24.5</v>
-      </c>
-      <c r="E71" s="7">
-        <v>-20.26</v>
+      <c r="A6" s="3" t="s">
+        <v>52</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A6:E6"/>
+    <mergeCell ref="A5:E5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3167,60 +1941,60 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="28" customHeight="1">
-      <c r="A1" s="9" t="s">
+      <c r="A1" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="9" t="s">
-        <v>63</v>
-      </c>
-      <c r="C1" s="9" t="s">
-        <v>64</v>
-      </c>
-      <c r="D1" s="9" t="s">
-        <v>65</v>
-      </c>
-      <c r="E1" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="F1" s="9" t="s">
-        <v>67</v>
-      </c>
-      <c r="G1" s="9" t="s">
-        <v>68</v>
-      </c>
-      <c r="H1" s="9" t="s">
-        <v>69</v>
-      </c>
-      <c r="I1" s="9" t="s">
-        <v>70</v>
+      <c r="B1" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="F1" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="G1" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="H1" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="I1" s="4" t="s">
+        <v>60</v>
       </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="10" t="s">
+      <c r="A2" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="B2" s="11">
+      <c r="B2" s="6">
         <v>40.44</v>
       </c>
-      <c r="C2" s="12">
+      <c r="C2" s="7">
         <v>8</v>
       </c>
-      <c r="D2" s="11">
+      <c r="D2" s="6">
         <v>32.6</v>
       </c>
-      <c r="E2" s="11">
+      <c r="E2" s="6">
         <v>20</v>
       </c>
-      <c r="F2" s="11">
+      <c r="F2" s="6">
         <v>-11.3</v>
       </c>
-      <c r="G2" s="11">
+      <c r="G2" s="6">
         <v>-9.5</v>
       </c>
-      <c r="H2" s="11">
+      <c r="H2" s="6">
         <v>56.1</v>
       </c>
-      <c r="I2" s="11">
+      <c r="I2" s="6">
         <v>0</v>
       </c>
     </row>
@@ -3322,54 +2096,54 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8">
-      <c r="A1" s="13" t="s">
+      <c r="A1" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="B1" s="13" t="s">
+      <c r="B1" s="8" t="s">
         <v>43</v>
       </c>
-      <c r="C1" s="13" t="s">
+      <c r="C1" s="8" t="s">
         <v>40</v>
       </c>
-      <c r="D1" s="13" t="s">
+      <c r="D1" s="8" t="s">
         <v>39</v>
       </c>
-      <c r="E1" s="13" t="s">
+      <c r="E1" s="8" t="s">
         <v>44</v>
       </c>
-      <c r="F1" s="13" t="s">
+      <c r="F1" s="8" t="s">
         <v>41</v>
       </c>
-      <c r="G1" s="13" t="s">
+      <c r="G1" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="H1" s="13" t="s">
+      <c r="H1" s="8" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="2" spans="1:8">
-      <c r="A2" s="14">
+      <c r="A2" s="9">
         <v>0.2703</v>
       </c>
-      <c r="B2" s="14">
+      <c r="B2" s="9">
         <v>0.1538</v>
       </c>
-      <c r="C2" s="14">
+      <c r="C2" s="9">
         <v>0.141</v>
       </c>
-      <c r="D2" s="14">
+      <c r="D2" s="9">
         <v>0.1283</v>
       </c>
-      <c r="E2" s="14">
+      <c r="E2" s="9">
         <v>0.07769999999999999</v>
       </c>
-      <c r="F2" s="14">
+      <c r="F2" s="9">
         <v>0.0243</v>
       </c>
-      <c r="G2" s="14">
+      <c r="G2" s="9">
         <v>-0.2999</v>
       </c>
-      <c r="H2" s="14">
+      <c r="H2" s="9">
         <v>-0.314</v>
       </c>
     </row>

--- a/BIRLA_GROUP_Technical_Metrics.xlsx
+++ b/BIRLA_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="287" uniqueCount="73">
   <si>
     <t>Symbol</t>
   </si>
@@ -172,13 +172,49 @@
     <t>▶  SIGNAL EVENTS (vs Previous Run)</t>
   </si>
   <si>
-    <t>No signal events detected since last run.</t>
+    <t>Signal</t>
+  </si>
+  <si>
+    <t>Change</t>
+  </si>
+  <si>
+    <t>Direction</t>
+  </si>
+  <si>
+    <t>Prev Value</t>
+  </si>
+  <si>
+    <t>Curr Value</t>
+  </si>
+  <si>
+    <t>RSI Oversold Recovery</t>
+  </si>
+  <si>
+    <t>25.9 → 30.3</t>
+  </si>
+  <si>
+    <t>🟢 BULLISH</t>
+  </si>
+  <si>
+    <t>25.9</t>
+  </si>
+  <si>
+    <t>30.3</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
   </si>
   <si>
-    <t>No numeric changes detected since last run.</t>
+    <t>Metric</t>
+  </si>
+  <si>
+    <t>Previous</t>
+  </si>
+  <si>
+    <t>Current</t>
+  </si>
+  <si>
+    <t>Delta</t>
   </si>
   <si>
     <t>Rank</t>
@@ -209,11 +245,13 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="0.0"/>
-    <numFmt numFmtId="165" formatCode="0.00%"/>
+  <numFmts count="4">
+    <numFmt numFmtId="164" formatCode="0.00"/>
+    <numFmt numFmtId="165" formatCode="+0.00;-0.00"/>
+    <numFmt numFmtId="166" formatCode="0.0"/>
+    <numFmt numFmtId="167" formatCode="0.00%"/>
   </numFmts>
-  <fonts count="4">
+  <fonts count="6">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -245,8 +283,22 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="6">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -262,6 +314,24 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF2E4057"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4A6FA5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -331,27 +401,34 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
@@ -706,8 +783,8 @@
     <col min="13" max="13" width="10.7109375" customWidth="1"/>
     <col min="14" max="14" width="11.7109375" customWidth="1"/>
     <col min="15" max="15" width="10.7109375" customWidth="1"/>
-    <col min="16" max="18" width="9.7109375" customWidth="1"/>
-    <col min="19" max="19" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="9.7109375" customWidth="1"/>
+    <col min="17" max="19" width="10.7109375" customWidth="1"/>
     <col min="20" max="20" width="22.7109375" customWidth="1"/>
     <col min="21" max="21" width="9.7109375" customWidth="1"/>
     <col min="22" max="22" width="10.7109375" customWidth="1"/>
@@ -847,10 +924,10 @@
         <v>45</v>
       </c>
       <c r="C2">
-        <v>368.65</v>
+        <v>380.7</v>
       </c>
       <c r="D2">
-        <v>-0.93</v>
+        <v>3.27</v>
       </c>
       <c r="E2">
         <v>424.7</v>
@@ -859,25 +936,25 @@
         <v>292.25</v>
       </c>
       <c r="G2">
-        <v>-13.2</v>
+        <v>-10.36</v>
       </c>
       <c r="H2">
-        <v>26.14</v>
+        <v>30.27</v>
       </c>
       <c r="I2">
-        <v>-3.14</v>
+        <v>1.51</v>
       </c>
       <c r="J2">
-        <v>-8.58</v>
+        <v>-4.09</v>
       </c>
       <c r="K2">
-        <v>-7.22</v>
+        <v>-6.76</v>
       </c>
       <c r="L2">
-        <v>21.29</v>
+        <v>25.21</v>
       </c>
       <c r="M2">
-        <v>27.03</v>
+        <v>28.44</v>
       </c>
       <c r="N2">
         <v>74</v>
@@ -886,19 +963,19 @@
         <v>72</v>
       </c>
       <c r="P2">
-        <v>374.42</v>
+        <v>375.55</v>
       </c>
       <c r="Q2">
-        <v>387.57</v>
+        <v>386.61</v>
       </c>
       <c r="R2">
-        <v>399.13</v>
+        <v>398.79</v>
       </c>
       <c r="S2">
-        <v>365.08</v>
+        <v>365.24</v>
       </c>
       <c r="T2">
-        <v>0.98</v>
+        <v>4.23</v>
       </c>
       <c r="U2" t="s">
         <v>46</v>
@@ -913,34 +990,34 @@
         <v>2</v>
       </c>
       <c r="Y2">
-        <v>35.73</v>
+        <v>45.23</v>
       </c>
       <c r="Z2">
-        <v>-7.39</v>
+        <v>-6.85</v>
       </c>
       <c r="AA2">
-        <v>-5.47</v>
+        <v>-5.74</v>
       </c>
       <c r="AB2">
-        <v>-1.93</v>
+        <v>-1.11</v>
       </c>
       <c r="AC2">
-        <v>8.15</v>
+        <v>19.32</v>
       </c>
       <c r="AD2">
-        <v>16.24</v>
+        <v>14.87</v>
       </c>
       <c r="AE2">
-        <v>9.109999999999999</v>
+        <v>9.66</v>
       </c>
       <c r="AF2">
-        <v>58.33</v>
+        <v>116.37</v>
       </c>
       <c r="AG2">
-        <v>411.25</v>
+        <v>409.71</v>
       </c>
       <c r="AH2">
-        <v>363.9</v>
+        <v>363.51</v>
       </c>
       <c r="AI2">
         <v>398.61</v>
@@ -949,7 +1026,7 @@
         <v>48</v>
       </c>
       <c r="AK2">
-        <v>38.57</v>
+        <v>34.45</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -960,37 +1037,37 @@
         <v>45</v>
       </c>
       <c r="C3">
-        <v>43.18</v>
+        <v>43.65</v>
       </c>
       <c r="D3">
-        <v>-3.23</v>
+        <v>1.09</v>
       </c>
       <c r="E3">
-        <v>86.23999999999999</v>
+        <v>85.7</v>
       </c>
       <c r="F3">
         <v>43.18</v>
       </c>
       <c r="G3">
-        <v>-49.93</v>
+        <v>-49.07</v>
       </c>
       <c r="H3">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="I3">
-        <v>-6.78</v>
+        <v>-1.98</v>
       </c>
       <c r="J3">
-        <v>-18.85</v>
+        <v>-16.44</v>
       </c>
       <c r="K3">
-        <v>-26.25</v>
+        <v>-27.27</v>
       </c>
       <c r="L3">
-        <v>-50.93</v>
+        <v>-49.39</v>
       </c>
       <c r="M3">
-        <v>-29.99</v>
+        <v>-30.19</v>
       </c>
       <c r="N3">
         <v>13</v>
@@ -999,19 +1076,19 @@
         <v>4</v>
       </c>
       <c r="P3">
-        <v>44.47</v>
+        <v>44.29</v>
       </c>
       <c r="Q3">
-        <v>47.99</v>
+        <v>47.61</v>
       </c>
       <c r="R3">
-        <v>52.9</v>
+        <v>52.61</v>
       </c>
       <c r="S3">
-        <v>61.65</v>
+        <v>61.48</v>
       </c>
       <c r="T3">
-        <v>-29.96</v>
+        <v>-29</v>
       </c>
       <c r="U3" t="s">
         <v>46</v>
@@ -1026,43 +1103,43 @@
         <v>0</v>
       </c>
       <c r="Y3">
-        <v>26.22</v>
+        <v>29.06</v>
       </c>
       <c r="Z3">
-        <v>-2.4</v>
+        <v>-2.43</v>
       </c>
       <c r="AA3">
-        <v>-2.14</v>
+        <v>-2.2</v>
       </c>
       <c r="AB3">
-        <v>-0.26</v>
+        <v>-0.23</v>
       </c>
       <c r="AC3">
-        <v>41.5</v>
+        <v>33.91</v>
       </c>
       <c r="AD3">
-        <v>32.65</v>
+        <v>36.91</v>
       </c>
       <c r="AE3">
-        <v>1.65</v>
+        <v>1.6</v>
       </c>
       <c r="AF3">
-        <v>-21.21</v>
+        <v>-42.98</v>
       </c>
       <c r="AG3">
-        <v>53</v>
+        <v>52.72</v>
       </c>
       <c r="AH3">
-        <v>42.99</v>
+        <v>42.5</v>
       </c>
       <c r="AI3">
-        <v>49.03</v>
+        <v>48.29</v>
       </c>
       <c r="AJ3" t="s">
         <v>48</v>
       </c>
       <c r="AK3">
-        <v>45.28</v>
+        <v>44.4</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1073,10 +1150,10 @@
         <v>45</v>
       </c>
       <c r="C4">
-        <v>2856.8</v>
+        <v>2890</v>
       </c>
       <c r="D4">
-        <v>-2.2</v>
+        <v>1.16</v>
       </c>
       <c r="E4">
         <v>3380.5</v>
@@ -1085,25 +1162,25 @@
         <v>2531.1</v>
       </c>
       <c r="G4">
-        <v>-15.49</v>
+        <v>-14.51</v>
       </c>
       <c r="H4">
-        <v>12.87</v>
+        <v>14.18</v>
       </c>
       <c r="I4">
-        <v>-6.7</v>
+        <v>-2.43</v>
       </c>
       <c r="J4">
-        <v>-13.49</v>
+        <v>-12.6</v>
       </c>
       <c r="K4">
-        <v>-10.5</v>
+        <v>-10.07</v>
       </c>
       <c r="L4">
-        <v>2.34</v>
+        <v>2.94</v>
       </c>
       <c r="M4">
-        <v>12.83</v>
+        <v>12.37</v>
       </c>
       <c r="N4">
         <v>50</v>
@@ -1112,19 +1189,19 @@
         <v>55</v>
       </c>
       <c r="P4">
-        <v>2936.18</v>
+        <v>2921.78</v>
       </c>
       <c r="Q4">
-        <v>3123.71</v>
+        <v>3103.21</v>
       </c>
       <c r="R4">
-        <v>3210.38</v>
+        <v>3205.92</v>
       </c>
       <c r="S4">
-        <v>2979.26</v>
+        <v>2979.64</v>
       </c>
       <c r="T4">
-        <v>-4.11</v>
+        <v>-3.01</v>
       </c>
       <c r="U4" t="s">
         <v>46</v>
@@ -1139,43 +1216,43 @@
         <v>1</v>
       </c>
       <c r="Y4">
-        <v>23.39</v>
+        <v>28.22</v>
       </c>
       <c r="Z4">
-        <v>-86.55</v>
+        <v>-91.23</v>
       </c>
       <c r="AA4">
-        <v>-56.23</v>
+        <v>-63.23</v>
       </c>
       <c r="AB4">
-        <v>-30.32</v>
+        <v>-28</v>
       </c>
       <c r="AC4">
-        <v>2.27</v>
+        <v>7.24</v>
       </c>
       <c r="AD4">
-        <v>4.02</v>
+        <v>4.8</v>
       </c>
       <c r="AE4">
-        <v>63.42</v>
+        <v>61.62</v>
       </c>
       <c r="AF4">
-        <v>-31.99</v>
+        <v>-67.83</v>
       </c>
       <c r="AG4">
-        <v>3380.44</v>
+        <v>3366.07</v>
       </c>
       <c r="AH4">
-        <v>2866.98</v>
+        <v>2840.35</v>
       </c>
       <c r="AI4">
-        <v>3076.97</v>
+        <v>3061.2</v>
       </c>
       <c r="AJ4" t="s">
         <v>48</v>
       </c>
       <c r="AK4">
-        <v>63.41</v>
+        <v>66.63</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1186,10 +1263,10 @@
         <v>45</v>
       </c>
       <c r="C5">
-        <v>890.15</v>
+        <v>900.35</v>
       </c>
       <c r="D5">
-        <v>-2.27</v>
+        <v>1.15</v>
       </c>
       <c r="E5">
         <v>1149.7</v>
@@ -1198,25 +1275,25 @@
         <v>760.1</v>
       </c>
       <c r="G5">
-        <v>-22.58</v>
+        <v>-21.69</v>
       </c>
       <c r="H5">
-        <v>17.11</v>
+        <v>18.45</v>
       </c>
       <c r="I5">
-        <v>-5.48</v>
+        <v>-4.41</v>
       </c>
       <c r="J5">
-        <v>-11.52</v>
+        <v>-10.77</v>
       </c>
       <c r="K5">
-        <v>-7.61</v>
+        <v>-6.94</v>
       </c>
       <c r="L5">
-        <v>14.07</v>
+        <v>15.92</v>
       </c>
       <c r="M5">
-        <v>14.1</v>
+        <v>13.72</v>
       </c>
       <c r="N5">
         <v>62</v>
@@ -1225,19 +1302,19 @@
         <v>67</v>
       </c>
       <c r="P5">
-        <v>924.35</v>
+        <v>916.05</v>
       </c>
       <c r="Q5">
-        <v>965.62</v>
+        <v>959.3</v>
       </c>
       <c r="R5">
-        <v>1002.25</v>
+        <v>1001.01</v>
       </c>
       <c r="S5">
-        <v>982.6</v>
+        <v>982.84</v>
       </c>
       <c r="T5">
-        <v>-9.41</v>
+        <v>-8.390000000000001</v>
       </c>
       <c r="U5" t="s">
         <v>46</v>
@@ -1252,43 +1329,43 @@
         <v>1</v>
       </c>
       <c r="Y5">
-        <v>25.9</v>
+        <v>30.26</v>
       </c>
       <c r="Z5">
-        <v>-24.46</v>
+        <v>-26.05</v>
       </c>
       <c r="AA5">
-        <v>-17.47</v>
+        <v>-19.18</v>
       </c>
       <c r="AB5">
-        <v>-6.99</v>
+        <v>-6.87</v>
       </c>
       <c r="AC5">
-        <v>1.97</v>
+        <v>5.93</v>
       </c>
       <c r="AD5">
-        <v>3.67</v>
+        <v>3.68</v>
       </c>
       <c r="AE5">
-        <v>22.19</v>
+        <v>21.59</v>
       </c>
       <c r="AF5">
-        <v>-0.58</v>
+        <v>-10.78</v>
       </c>
       <c r="AG5">
-        <v>1031.57</v>
+        <v>1024.77</v>
       </c>
       <c r="AH5">
-        <v>899.67</v>
+        <v>893.8200000000001</v>
       </c>
       <c r="AI5">
-        <v>965.25</v>
+        <v>958.48</v>
       </c>
       <c r="AJ5" t="s">
         <v>48</v>
       </c>
       <c r="AK5">
-        <v>40.56</v>
+        <v>44.45</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1299,10 +1376,10 @@
         <v>45</v>
       </c>
       <c r="C6">
-        <v>12.8</v>
+        <v>13</v>
       </c>
       <c r="D6">
-        <v>-2.88</v>
+        <v>1.56</v>
       </c>
       <c r="E6">
         <v>15.6</v>
@@ -1311,25 +1388,25 @@
         <v>8.359999999999999</v>
       </c>
       <c r="G6">
-        <v>-17.95</v>
+        <v>-16.67</v>
       </c>
       <c r="H6">
-        <v>53.11</v>
+        <v>55.5</v>
       </c>
       <c r="I6">
-        <v>-1.16</v>
+        <v>2.85</v>
       </c>
       <c r="J6">
-        <v>-17.95</v>
+        <v>-15.69</v>
       </c>
       <c r="K6">
-        <v>-8.83</v>
+        <v>-8.390000000000001</v>
       </c>
       <c r="L6">
-        <v>45.12</v>
+        <v>53.48</v>
       </c>
       <c r="M6">
-        <v>2.43</v>
+        <v>3.69</v>
       </c>
       <c r="N6">
         <v>87</v>
@@ -1338,10 +1415,10 @@
         <v>79</v>
       </c>
       <c r="P6">
-        <v>12.91</v>
+        <v>12.99</v>
       </c>
       <c r="Q6">
-        <v>13.89</v>
+        <v>13.76</v>
       </c>
       <c r="R6">
         <v>13.9</v>
@@ -1350,7 +1427,7 @@
         <v>12.28</v>
       </c>
       <c r="T6">
-        <v>4.26</v>
+        <v>5.84</v>
       </c>
       <c r="U6" t="s">
         <v>46</v>
@@ -1365,34 +1442,34 @@
         <v>2</v>
       </c>
       <c r="Y6">
-        <v>37.55</v>
+        <v>40.63</v>
       </c>
       <c r="Z6">
         <v>-0.38</v>
       </c>
       <c r="AA6">
-        <v>-0.24</v>
+        <v>-0.26</v>
       </c>
       <c r="AB6">
-        <v>-0.14</v>
+        <v>-0.11</v>
       </c>
       <c r="AC6">
-        <v>37.47</v>
+        <v>35.72</v>
       </c>
       <c r="AD6">
-        <v>29.19</v>
+        <v>35.16</v>
       </c>
       <c r="AE6">
-        <v>0.49</v>
+        <v>0.48</v>
       </c>
       <c r="AF6">
-        <v>-38.29</v>
+        <v>-45.14</v>
       </c>
       <c r="AG6">
-        <v>15.5</v>
+        <v>15.23</v>
       </c>
       <c r="AH6">
-        <v>12.28</v>
+        <v>12.3</v>
       </c>
       <c r="AI6">
         <v>14.25</v>
@@ -1401,7 +1478,7 @@
         <v>48</v>
       </c>
       <c r="AK6">
-        <v>38.63</v>
+        <v>38.31</v>
       </c>
     </row>
     <row r="7" spans="1:37">
@@ -1412,10 +1489,10 @@
         <v>45</v>
       </c>
       <c r="C7">
-        <v>10.56</v>
+        <v>11.06</v>
       </c>
       <c r="D7">
-        <v>-2.31</v>
+        <v>4.73</v>
       </c>
       <c r="E7">
         <v>13.92</v>
@@ -1424,25 +1501,25 @@
         <v>4.69</v>
       </c>
       <c r="G7">
-        <v>-24.14</v>
+        <v>-20.55</v>
       </c>
       <c r="H7">
-        <v>125.16</v>
+        <v>135.82</v>
       </c>
       <c r="I7">
-        <v>-3.3</v>
+        <v>3.08</v>
       </c>
       <c r="J7">
-        <v>-4.95</v>
+        <v>-2.38</v>
       </c>
       <c r="K7">
-        <v>3.83</v>
+        <v>6.65</v>
       </c>
       <c r="L7">
-        <v>87.23</v>
+        <v>101.46</v>
       </c>
       <c r="M7">
-        <v>-31.4</v>
+        <v>-30.78</v>
       </c>
       <c r="N7">
         <v>99</v>
@@ -1451,10 +1528,10 @@
         <v>92</v>
       </c>
       <c r="P7">
-        <v>10.62</v>
+        <v>10.69</v>
       </c>
       <c r="Q7">
-        <v>11.4</v>
+        <v>11.38</v>
       </c>
       <c r="R7">
         <v>11.65</v>
@@ -1463,7 +1540,7 @@
         <v>10.84</v>
       </c>
       <c r="T7">
-        <v>-2.59</v>
+        <v>1.99</v>
       </c>
       <c r="U7" t="s">
         <v>46</v>
@@ -1475,37 +1552,37 @@
         <v>46</v>
       </c>
       <c r="X7">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y7">
-        <v>39.59</v>
+        <v>47.63</v>
       </c>
       <c r="Z7">
-        <v>-0.28</v>
+        <v>-0.25</v>
       </c>
       <c r="AA7">
-        <v>-0.18</v>
+        <v>-0.2</v>
       </c>
       <c r="AB7">
-        <v>-0.09</v>
+        <v>-0.05</v>
       </c>
       <c r="AC7">
-        <v>33.23</v>
+        <v>53.42</v>
       </c>
       <c r="AD7">
-        <v>21.95</v>
+        <v>36.25</v>
       </c>
       <c r="AE7">
-        <v>0.52</v>
+        <v>0.57</v>
       </c>
       <c r="AF7">
-        <v>-33.77</v>
+        <v>128.97</v>
       </c>
       <c r="AG7">
-        <v>12.71</v>
+        <v>12.69</v>
       </c>
       <c r="AH7">
-        <v>10.09</v>
+        <v>10.06</v>
       </c>
       <c r="AI7">
         <v>12.04</v>
@@ -1514,7 +1591,7 @@
         <v>48</v>
       </c>
       <c r="AK7">
-        <v>36.24</v>
+        <v>32.21</v>
       </c>
     </row>
     <row r="8" spans="1:37">
@@ -1525,10 +1602,10 @@
         <v>45</v>
       </c>
       <c r="C8">
-        <v>3948.5</v>
+        <v>3937.7</v>
       </c>
       <c r="D8">
-        <v>-3.14</v>
+        <v>-0.27</v>
       </c>
       <c r="E8">
         <v>5809.5</v>
@@ -1537,25 +1614,25 @@
         <v>3892.3</v>
       </c>
       <c r="G8">
-        <v>-32.03</v>
+        <v>-32.22</v>
       </c>
       <c r="H8">
-        <v>1.44</v>
+        <v>1.17</v>
       </c>
       <c r="I8">
-        <v>-0.2</v>
+        <v>1.17</v>
       </c>
       <c r="J8">
-        <v>-8.15</v>
+        <v>-7.6</v>
       </c>
       <c r="K8">
-        <v>-9.93</v>
+        <v>-11.2</v>
       </c>
       <c r="L8">
-        <v>-29.58</v>
+        <v>-28.42</v>
       </c>
       <c r="M8">
-        <v>15.38</v>
+        <v>14.78</v>
       </c>
       <c r="N8">
         <v>26</v>
@@ -1564,19 +1641,19 @@
         <v>31</v>
       </c>
       <c r="P8">
-        <v>3993.78</v>
+        <v>4002.86</v>
       </c>
       <c r="Q8">
-        <v>4043.52</v>
+        <v>4034.91</v>
       </c>
       <c r="R8">
-        <v>4236.22</v>
+        <v>4228.78</v>
       </c>
       <c r="S8">
-        <v>4506.36</v>
+        <v>4500.25</v>
       </c>
       <c r="T8">
-        <v>-12.38</v>
+        <v>-12.5</v>
       </c>
       <c r="U8" t="s">
         <v>46</v>
@@ -1591,34 +1668,34 @@
         <v>0</v>
       </c>
       <c r="Y8">
-        <v>38.87</v>
+        <v>38.26</v>
       </c>
       <c r="Z8">
-        <v>-73.73</v>
+        <v>-74.91</v>
       </c>
       <c r="AA8">
-        <v>-81.84</v>
+        <v>-80.45</v>
       </c>
       <c r="AB8">
-        <v>8.109999999999999</v>
+        <v>5.55</v>
       </c>
       <c r="AC8">
-        <v>84.81</v>
+        <v>68.5</v>
       </c>
       <c r="AD8">
-        <v>83.83</v>
+        <v>84.44</v>
       </c>
       <c r="AE8">
-        <v>113.65</v>
+        <v>111.39</v>
       </c>
       <c r="AF8">
-        <v>-22.65</v>
+        <v>-60.28</v>
       </c>
       <c r="AG8">
-        <v>4200.77</v>
+        <v>4195.69</v>
       </c>
       <c r="AH8">
-        <v>3886.26</v>
+        <v>3874.13</v>
       </c>
       <c r="AI8">
         <v>4247.59</v>
@@ -1627,7 +1704,7 @@
         <v>48</v>
       </c>
       <c r="AK8">
-        <v>39.61</v>
+        <v>38.98</v>
       </c>
     </row>
     <row r="9" spans="1:37">
@@ -1638,10 +1715,10 @@
         <v>45</v>
       </c>
       <c r="C9">
-        <v>10426</v>
+        <v>10675</v>
       </c>
       <c r="D9">
-        <v>-2.18</v>
+        <v>2.39</v>
       </c>
       <c r="E9">
         <v>13052</v>
@@ -1650,25 +1727,25 @@
         <v>10362</v>
       </c>
       <c r="G9">
-        <v>-20.12</v>
+        <v>-18.21</v>
       </c>
       <c r="H9">
-        <v>0.62</v>
+        <v>3.02</v>
       </c>
       <c r="I9">
-        <v>-4.84</v>
+        <v>-0.33</v>
       </c>
       <c r="J9">
-        <v>-6.7</v>
+        <v>-3.03</v>
       </c>
       <c r="K9">
-        <v>-9.529999999999999</v>
+        <v>-8.85</v>
       </c>
       <c r="L9">
-        <v>-13.25</v>
+        <v>-11.45</v>
       </c>
       <c r="M9">
-        <v>7.77</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="N9">
         <v>38</v>
@@ -1677,19 +1754,19 @@
         <v>47</v>
       </c>
       <c r="P9">
-        <v>10678.8</v>
+        <v>10671.8</v>
       </c>
       <c r="Q9">
-        <v>10886.2</v>
+        <v>10874.95</v>
       </c>
       <c r="R9">
-        <v>11357.4</v>
+        <v>11330.94</v>
       </c>
       <c r="S9">
-        <v>11690.28</v>
+        <v>11686.18</v>
       </c>
       <c r="T9">
-        <v>-10.81</v>
+        <v>-8.65</v>
       </c>
       <c r="U9" t="s">
         <v>46</v>
@@ -1704,34 +1781,34 @@
         <v>0</v>
       </c>
       <c r="Y9">
-        <v>33.2</v>
+        <v>41.65</v>
       </c>
       <c r="Z9">
-        <v>-184.15</v>
+        <v>-181.16</v>
       </c>
       <c r="AA9">
-        <v>-158.99</v>
+        <v>-163.43</v>
       </c>
       <c r="AB9">
-        <v>-25.15</v>
+        <v>-17.73</v>
       </c>
       <c r="AC9">
-        <v>34.3</v>
+        <v>32.81</v>
       </c>
       <c r="AD9">
-        <v>51.36</v>
+        <v>41.89</v>
       </c>
       <c r="AE9">
-        <v>207.24</v>
+        <v>210.87</v>
       </c>
       <c r="AF9">
-        <v>-24.5</v>
+        <v>-47.81</v>
       </c>
       <c r="AG9">
-        <v>11269.44</v>
+        <v>11269.53</v>
       </c>
       <c r="AH9">
-        <v>10502.96</v>
+        <v>10480.37</v>
       </c>
       <c r="AI9">
         <v>11169.72</v>
@@ -1740,7 +1817,7 @@
         <v>48</v>
       </c>
       <c r="AK9">
-        <v>39.09</v>
+        <v>42</v>
       </c>
     </row>
   </sheetData>
@@ -1881,7 +1958,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:F70"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -1901,12 +1978,47 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="3" t="s">
         <v>50</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>59</v>
       </c>
     </row>
     <row r="5" spans="1:6">
       <c r="A5" s="2" t="s">
-        <v>51</v>
+        <v>60</v>
       </c>
       <c r="B5" s="2"/>
       <c r="C5" s="2"/>
@@ -1915,7 +2027,1107 @@
     </row>
     <row r="6" spans="1:6">
       <c r="A6" s="3" t="s">
-        <v>52</v>
+        <v>0</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6">
+      <c r="A7" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C7" s="6">
+        <v>-8.58</v>
+      </c>
+      <c r="D7" s="6">
+        <v>-4.09</v>
+      </c>
+      <c r="E7" s="7">
+        <v>4.49</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C8" s="6">
+        <v>-18.85</v>
+      </c>
+      <c r="D8" s="6">
+        <v>-16.44</v>
+      </c>
+      <c r="E8" s="7">
+        <v>2.41</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C9" s="6">
+        <v>-13.49</v>
+      </c>
+      <c r="D9" s="6">
+        <v>-12.6</v>
+      </c>
+      <c r="E9" s="7">
+        <v>0.89</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C10" s="6">
+        <v>-11.52</v>
+      </c>
+      <c r="D10" s="6">
+        <v>-10.77</v>
+      </c>
+      <c r="E10" s="7">
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B11" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C11" s="6">
+        <v>-17.95</v>
+      </c>
+      <c r="D11" s="6">
+        <v>-15.69</v>
+      </c>
+      <c r="E11" s="7">
+        <v>2.26</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B12" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C12" s="6">
+        <v>-4.95</v>
+      </c>
+      <c r="D12" s="6">
+        <v>-2.38</v>
+      </c>
+      <c r="E12" s="7">
+        <v>2.57</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="A13" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B13" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C13" s="6">
+        <v>-8.15</v>
+      </c>
+      <c r="D13" s="6">
+        <v>-7.6</v>
+      </c>
+      <c r="E13" s="7">
+        <v>0.55</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="B14" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C14" s="6">
+        <v>-6.7</v>
+      </c>
+      <c r="D14" s="6">
+        <v>-3.03</v>
+      </c>
+      <c r="E14" s="7">
+        <v>3.67</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="A15" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B15" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C15" s="6">
+        <v>-3.14</v>
+      </c>
+      <c r="D15" s="6">
+        <v>1.51</v>
+      </c>
+      <c r="E15" s="7">
+        <v>4.65</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="A16" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B16" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C16" s="6">
+        <v>-6.78</v>
+      </c>
+      <c r="D16" s="6">
+        <v>-1.98</v>
+      </c>
+      <c r="E16" s="7">
+        <v>4.8</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B17" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C17" s="6">
+        <v>-6.7</v>
+      </c>
+      <c r="D17" s="6">
+        <v>-2.43</v>
+      </c>
+      <c r="E17" s="7">
+        <v>4.27</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B18" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C18" s="6">
+        <v>-5.48</v>
+      </c>
+      <c r="D18" s="6">
+        <v>-4.41</v>
+      </c>
+      <c r="E18" s="7">
+        <v>1.07</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B19" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C19" s="6">
+        <v>-1.16</v>
+      </c>
+      <c r="D19" s="6">
+        <v>2.85</v>
+      </c>
+      <c r="E19" s="7">
+        <v>4.01</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B20" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C20" s="6">
+        <v>-3.3</v>
+      </c>
+      <c r="D20" s="6">
+        <v>3.08</v>
+      </c>
+      <c r="E20" s="7">
+        <v>6.38</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B21" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C21" s="6">
+        <v>-0.2</v>
+      </c>
+      <c r="D21" s="6">
+        <v>1.17</v>
+      </c>
+      <c r="E21" s="7">
+        <v>1.37</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="B22" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C22" s="6">
+        <v>-4.84</v>
+      </c>
+      <c r="D22" s="6">
+        <v>-0.33</v>
+      </c>
+      <c r="E22" s="7">
+        <v>4.51</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B23" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C23" s="6">
+        <v>21.29</v>
+      </c>
+      <c r="D23" s="6">
+        <v>25.21</v>
+      </c>
+      <c r="E23" s="7">
+        <v>3.92</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B24" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C24" s="6">
+        <v>-50.93</v>
+      </c>
+      <c r="D24" s="6">
+        <v>-49.39</v>
+      </c>
+      <c r="E24" s="7">
+        <v>1.54</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B25" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C25" s="6">
+        <v>2.34</v>
+      </c>
+      <c r="D25" s="6">
+        <v>2.94</v>
+      </c>
+      <c r="E25" s="7">
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B26" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C26" s="6">
+        <v>14.07</v>
+      </c>
+      <c r="D26" s="6">
+        <v>15.92</v>
+      </c>
+      <c r="E26" s="7">
+        <v>1.85</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B27" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C27" s="6">
+        <v>45.12</v>
+      </c>
+      <c r="D27" s="6">
+        <v>53.48</v>
+      </c>
+      <c r="E27" s="7">
+        <v>8.359999999999999</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B28" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C28" s="6">
+        <v>87.23</v>
+      </c>
+      <c r="D28" s="6">
+        <v>101.46</v>
+      </c>
+      <c r="E28" s="7">
+        <v>14.23</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B29" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C29" s="6">
+        <v>-29.58</v>
+      </c>
+      <c r="D29" s="6">
+        <v>-28.42</v>
+      </c>
+      <c r="E29" s="7">
+        <v>1.16</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="B30" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C30" s="6">
+        <v>-13.25</v>
+      </c>
+      <c r="D30" s="6">
+        <v>-11.45</v>
+      </c>
+      <c r="E30" s="7">
+        <v>1.8</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5">
+      <c r="A31" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B31" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C31" s="6">
+        <v>-7.22</v>
+      </c>
+      <c r="D31" s="6">
+        <v>-6.76</v>
+      </c>
+      <c r="E31" s="7">
+        <v>0.46</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5">
+      <c r="A32" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B32" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C32" s="6">
+        <v>-26.25</v>
+      </c>
+      <c r="D32" s="6">
+        <v>-27.27</v>
+      </c>
+      <c r="E32" s="8">
+        <v>-1.02</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5">
+      <c r="A33" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B33" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C33" s="6">
+        <v>-10.5</v>
+      </c>
+      <c r="D33" s="6">
+        <v>-10.07</v>
+      </c>
+      <c r="E33" s="7">
+        <v>0.43</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5">
+      <c r="A34" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B34" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C34" s="6">
+        <v>-7.61</v>
+      </c>
+      <c r="D34" s="6">
+        <v>-6.94</v>
+      </c>
+      <c r="E34" s="7">
+        <v>0.67</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5">
+      <c r="A35" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B35" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C35" s="6">
+        <v>-8.83</v>
+      </c>
+      <c r="D35" s="6">
+        <v>-8.390000000000001</v>
+      </c>
+      <c r="E35" s="7">
+        <v>0.44</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5">
+      <c r="A36" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B36" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C36" s="6">
+        <v>3.83</v>
+      </c>
+      <c r="D36" s="6">
+        <v>6.65</v>
+      </c>
+      <c r="E36" s="7">
+        <v>2.82</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5">
+      <c r="A37" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B37" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C37" s="6">
+        <v>-9.93</v>
+      </c>
+      <c r="D37" s="6">
+        <v>-11.2</v>
+      </c>
+      <c r="E37" s="8">
+        <v>-1.27</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5">
+      <c r="A38" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="B38" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C38" s="6">
+        <v>-9.529999999999999</v>
+      </c>
+      <c r="D38" s="6">
+        <v>-8.85</v>
+      </c>
+      <c r="E38" s="7">
+        <v>0.68</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5">
+      <c r="A39" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B39" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C39" s="6">
+        <v>-13.2</v>
+      </c>
+      <c r="D39" s="6">
+        <v>-10.36</v>
+      </c>
+      <c r="E39" s="7">
+        <v>2.84</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5">
+      <c r="A40" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B40" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C40" s="6">
+        <v>-49.93</v>
+      </c>
+      <c r="D40" s="6">
+        <v>-49.07</v>
+      </c>
+      <c r="E40" s="7">
+        <v>0.86</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5">
+      <c r="A41" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B41" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C41" s="6">
+        <v>-15.49</v>
+      </c>
+      <c r="D41" s="6">
+        <v>-14.51</v>
+      </c>
+      <c r="E41" s="7">
+        <v>0.98</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5">
+      <c r="A42" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B42" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C42" s="6">
+        <v>-22.58</v>
+      </c>
+      <c r="D42" s="6">
+        <v>-21.69</v>
+      </c>
+      <c r="E42" s="7">
+        <v>0.89</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5">
+      <c r="A43" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B43" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C43" s="6">
+        <v>-17.95</v>
+      </c>
+      <c r="D43" s="6">
+        <v>-16.67</v>
+      </c>
+      <c r="E43" s="7">
+        <v>1.28</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5">
+      <c r="A44" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B44" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C44" s="6">
+        <v>-24.14</v>
+      </c>
+      <c r="D44" s="6">
+        <v>-20.55</v>
+      </c>
+      <c r="E44" s="7">
+        <v>3.59</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5">
+      <c r="A45" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B45" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C45" s="6">
+        <v>-32.03</v>
+      </c>
+      <c r="D45" s="6">
+        <v>-32.22</v>
+      </c>
+      <c r="E45" s="8">
+        <v>-0.19</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5">
+      <c r="A46" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="B46" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C46" s="6">
+        <v>-20.12</v>
+      </c>
+      <c r="D46" s="6">
+        <v>-18.21</v>
+      </c>
+      <c r="E46" s="7">
+        <v>1.91</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5">
+      <c r="A47" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B47" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C47" s="6">
+        <v>368.65</v>
+      </c>
+      <c r="D47" s="6">
+        <v>380.7</v>
+      </c>
+      <c r="E47" s="7">
+        <v>12.05</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5">
+      <c r="A48" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B48" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C48" s="6">
+        <v>43.18</v>
+      </c>
+      <c r="D48" s="6">
+        <v>43.65</v>
+      </c>
+      <c r="E48" s="7">
+        <v>0.47</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5">
+      <c r="A49" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B49" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C49" s="6">
+        <v>2856.8</v>
+      </c>
+      <c r="D49" s="6">
+        <v>2890</v>
+      </c>
+      <c r="E49" s="7">
+        <v>33.2</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5">
+      <c r="A50" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B50" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C50" s="6">
+        <v>890.15</v>
+      </c>
+      <c r="D50" s="6">
+        <v>900.35</v>
+      </c>
+      <c r="E50" s="7">
+        <v>10.2</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5">
+      <c r="A51" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B51" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C51" s="6">
+        <v>12.8</v>
+      </c>
+      <c r="D51" s="6">
+        <v>13</v>
+      </c>
+      <c r="E51" s="7">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5">
+      <c r="A52" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B52" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C52" s="6">
+        <v>10.56</v>
+      </c>
+      <c r="D52" s="6">
+        <v>11.06</v>
+      </c>
+      <c r="E52" s="7">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5">
+      <c r="A53" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B53" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C53" s="6">
+        <v>3948.5</v>
+      </c>
+      <c r="D53" s="6">
+        <v>3937.7</v>
+      </c>
+      <c r="E53" s="8">
+        <v>-10.8</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5">
+      <c r="A54" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="B54" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C54" s="6">
+        <v>10426</v>
+      </c>
+      <c r="D54" s="6">
+        <v>10675</v>
+      </c>
+      <c r="E54" s="7">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5">
+      <c r="A55" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B55" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C55" s="6">
+        <v>35.73</v>
+      </c>
+      <c r="D55" s="6">
+        <v>45.23</v>
+      </c>
+      <c r="E55" s="7">
+        <v>9.5</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5">
+      <c r="A56" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B56" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C56" s="6">
+        <v>26.22</v>
+      </c>
+      <c r="D56" s="6">
+        <v>29.06</v>
+      </c>
+      <c r="E56" s="7">
+        <v>2.84</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5">
+      <c r="A57" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B57" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C57" s="6">
+        <v>23.39</v>
+      </c>
+      <c r="D57" s="6">
+        <v>28.22</v>
+      </c>
+      <c r="E57" s="7">
+        <v>4.83</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5">
+      <c r="A58" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B58" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C58" s="6">
+        <v>25.9</v>
+      </c>
+      <c r="D58" s="6">
+        <v>30.26</v>
+      </c>
+      <c r="E58" s="7">
+        <v>4.36</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5">
+      <c r="A59" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B59" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C59" s="6">
+        <v>37.55</v>
+      </c>
+      <c r="D59" s="6">
+        <v>40.63</v>
+      </c>
+      <c r="E59" s="7">
+        <v>3.08</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5">
+      <c r="A60" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B60" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C60" s="6">
+        <v>39.59</v>
+      </c>
+      <c r="D60" s="6">
+        <v>47.63</v>
+      </c>
+      <c r="E60" s="7">
+        <v>8.039999999999999</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5">
+      <c r="A61" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B61" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C61" s="6">
+        <v>38.87</v>
+      </c>
+      <c r="D61" s="6">
+        <v>38.26</v>
+      </c>
+      <c r="E61" s="8">
+        <v>-0.61</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5">
+      <c r="A62" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="B62" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C62" s="6">
+        <v>33.2</v>
+      </c>
+      <c r="D62" s="6">
+        <v>41.65</v>
+      </c>
+      <c r="E62" s="7">
+        <v>8.449999999999999</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5">
+      <c r="A63" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B63" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C63" s="6">
+        <v>58.33</v>
+      </c>
+      <c r="D63" s="6">
+        <v>116.37</v>
+      </c>
+      <c r="E63" s="7">
+        <v>58.04</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5">
+      <c r="A64" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B64" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C64" s="6">
+        <v>-21.21</v>
+      </c>
+      <c r="D64" s="6">
+        <v>-42.98</v>
+      </c>
+      <c r="E64" s="8">
+        <v>-21.77</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5">
+      <c r="A65" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B65" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C65" s="6">
+        <v>-31.99</v>
+      </c>
+      <c r="D65" s="6">
+        <v>-67.83</v>
+      </c>
+      <c r="E65" s="8">
+        <v>-35.84</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5">
+      <c r="A66" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B66" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C66" s="6">
+        <v>-0.58</v>
+      </c>
+      <c r="D66" s="6">
+        <v>-10.78</v>
+      </c>
+      <c r="E66" s="8">
+        <v>-10.2</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5">
+      <c r="A67" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B67" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C67" s="6">
+        <v>-38.29</v>
+      </c>
+      <c r="D67" s="6">
+        <v>-45.14</v>
+      </c>
+      <c r="E67" s="8">
+        <v>-6.85</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5">
+      <c r="A68" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B68" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C68" s="6">
+        <v>-33.77</v>
+      </c>
+      <c r="D68" s="6">
+        <v>128.97</v>
+      </c>
+      <c r="E68" s="7">
+        <v>162.74</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5">
+      <c r="A69" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B69" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C69" s="6">
+        <v>-22.65</v>
+      </c>
+      <c r="D69" s="6">
+        <v>-60.28</v>
+      </c>
+      <c r="E69" s="8">
+        <v>-37.63</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5">
+      <c r="A70" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="B70" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C70" s="6">
+        <v>-24.5</v>
+      </c>
+      <c r="D70" s="6">
+        <v>-47.81</v>
+      </c>
+      <c r="E70" s="8">
+        <v>-23.31</v>
       </c>
     </row>
   </sheetData>
@@ -1941,60 +3153,60 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="28" customHeight="1">
-      <c r="A1" s="4" t="s">
+      <c r="A1" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="C1" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="D1" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="E1" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="F1" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="G1" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="H1" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="I1" s="4" t="s">
-        <v>60</v>
+      <c r="B1" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="C1" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="D1" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="E1" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="F1" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="G1" s="9" t="s">
+        <v>70</v>
+      </c>
+      <c r="H1" s="9" t="s">
+        <v>71</v>
+      </c>
+      <c r="I1" s="9" t="s">
+        <v>72</v>
       </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="5" t="s">
+      <c r="A2" s="10" t="s">
         <v>45</v>
       </c>
-      <c r="B2" s="6">
-        <v>40.44</v>
-      </c>
-      <c r="C2" s="7">
+      <c r="B2" s="11">
+        <v>48.44</v>
+      </c>
+      <c r="C2" s="12">
         <v>8</v>
       </c>
-      <c r="D2" s="6">
-        <v>32.6</v>
-      </c>
-      <c r="E2" s="6">
-        <v>20</v>
-      </c>
-      <c r="F2" s="6">
-        <v>-11.3</v>
-      </c>
-      <c r="G2" s="6">
-        <v>-9.5</v>
-      </c>
-      <c r="H2" s="6">
+      <c r="D2" s="11">
+        <v>37.6</v>
+      </c>
+      <c r="E2" s="11">
+        <v>40</v>
+      </c>
+      <c r="F2" s="11">
+        <v>-9.1</v>
+      </c>
+      <c r="G2" s="11">
+        <v>-9.1</v>
+      </c>
+      <c r="H2" s="11">
         <v>56.1</v>
       </c>
-      <c r="I2" s="6">
+      <c r="I2" s="11">
         <v>0</v>
       </c>
     </row>
@@ -2096,55 +3308,55 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="B1" s="8" t="s">
+      <c r="B1" s="13" t="s">
         <v>43</v>
       </c>
-      <c r="C1" s="8" t="s">
+      <c r="C1" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="D1" s="8" t="s">
+      <c r="D1" s="13" t="s">
         <v>39</v>
       </c>
-      <c r="E1" s="8" t="s">
+      <c r="E1" s="13" t="s">
         <v>44</v>
       </c>
-      <c r="F1" s="8" t="s">
+      <c r="F1" s="13" t="s">
         <v>41</v>
       </c>
-      <c r="G1" s="8" t="s">
+      <c r="G1" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="H1" s="8" t="s">
+      <c r="H1" s="13" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="2" spans="1:8">
-      <c r="A2" s="9">
-        <v>0.2703</v>
-      </c>
-      <c r="B2" s="9">
-        <v>0.1538</v>
-      </c>
-      <c r="C2" s="9">
-        <v>0.141</v>
-      </c>
-      <c r="D2" s="9">
-        <v>0.1283</v>
-      </c>
-      <c r="E2" s="9">
-        <v>0.07769999999999999</v>
-      </c>
-      <c r="F2" s="9">
-        <v>0.0243</v>
-      </c>
-      <c r="G2" s="9">
-        <v>-0.2999</v>
-      </c>
-      <c r="H2" s="9">
-        <v>-0.314</v>
+      <c r="A2" s="14">
+        <v>0.2844</v>
+      </c>
+      <c r="B2" s="14">
+        <v>0.1478</v>
+      </c>
+      <c r="C2" s="14">
+        <v>0.1372</v>
+      </c>
+      <c r="D2" s="14">
+        <v>0.1237</v>
+      </c>
+      <c r="E2" s="14">
+        <v>0.083</v>
+      </c>
+      <c r="F2" s="14">
+        <v>0.0369</v>
+      </c>
+      <c r="G2" s="14">
+        <v>-0.3019</v>
+      </c>
+      <c r="H2" s="14">
+        <v>-0.3078</v>
       </c>
     </row>
   </sheetData>

--- a/BIRLA_GROUP_Technical_Metrics.xlsx
+++ b/BIRLA_GROUP_Technical_Metrics.xlsx
@@ -960,7 +960,7 @@
         <v>74</v>
       </c>
       <c r="O2">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="P2">
         <v>375.55</v>
@@ -1186,7 +1186,7 @@
         <v>50</v>
       </c>
       <c r="O4">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="P4">
         <v>2921.78</v>
@@ -1299,7 +1299,7 @@
         <v>62</v>
       </c>
       <c r="O5">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="P5">
         <v>916.05</v>
@@ -1412,7 +1412,7 @@
         <v>87</v>
       </c>
       <c r="O6">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="P6">
         <v>12.99</v>
@@ -1525,7 +1525,7 @@
         <v>99</v>
       </c>
       <c r="O7">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="P7">
         <v>10.69</v>
@@ -1638,7 +1638,7 @@
         <v>26</v>
       </c>
       <c r="O8">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="P8">
         <v>4002.86</v>
@@ -1751,7 +1751,7 @@
         <v>38</v>
       </c>
       <c r="O9">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="P9">
         <v>10671.8</v>

--- a/BIRLA_GROUP_Technical_Metrics.xlsx
+++ b/BIRLA_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="287" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="276" uniqueCount="64">
   <si>
     <t>Symbol</t>
   </si>
@@ -172,34 +172,7 @@
     <t>▶  SIGNAL EVENTS (vs Previous Run)</t>
   </si>
   <si>
-    <t>Signal</t>
-  </si>
-  <si>
-    <t>Change</t>
-  </si>
-  <si>
-    <t>Direction</t>
-  </si>
-  <si>
-    <t>Prev Value</t>
-  </si>
-  <si>
-    <t>Curr Value</t>
-  </si>
-  <si>
-    <t>RSI Oversold Recovery</t>
-  </si>
-  <si>
-    <t>25.9 → 30.3</t>
-  </si>
-  <si>
-    <t>🟢 BULLISH</t>
-  </si>
-  <si>
-    <t>25.9</t>
-  </si>
-  <si>
-    <t>30.3</t>
+    <t>No signal events detected since last run.</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -285,14 +258,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF9C0006"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF006100"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -325,13 +298,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -401,15 +374,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -783,8 +755,8 @@
     <col min="13" max="13" width="10.7109375" customWidth="1"/>
     <col min="14" max="14" width="11.7109375" customWidth="1"/>
     <col min="15" max="15" width="10.7109375" customWidth="1"/>
-    <col min="16" max="16" width="9.7109375" customWidth="1"/>
-    <col min="17" max="19" width="10.7109375" customWidth="1"/>
+    <col min="16" max="18" width="9.7109375" customWidth="1"/>
+    <col min="19" max="19" width="10.7109375" customWidth="1"/>
     <col min="20" max="20" width="22.7109375" customWidth="1"/>
     <col min="21" max="21" width="9.7109375" customWidth="1"/>
     <col min="22" max="22" width="10.7109375" customWidth="1"/>
@@ -924,10 +896,10 @@
         <v>45</v>
       </c>
       <c r="C2">
-        <v>380.7</v>
+        <v>380.25</v>
       </c>
       <c r="D2">
-        <v>3.27</v>
+        <v>-0.12</v>
       </c>
       <c r="E2">
         <v>424.7</v>
@@ -936,46 +908,46 @@
         <v>292.25</v>
       </c>
       <c r="G2">
-        <v>-10.36</v>
+        <v>-10.47</v>
       </c>
       <c r="H2">
-        <v>30.27</v>
+        <v>30.11</v>
       </c>
       <c r="I2">
-        <v>1.51</v>
+        <v>0.76</v>
       </c>
       <c r="J2">
-        <v>-4.09</v>
+        <v>-4.94</v>
       </c>
       <c r="K2">
-        <v>-6.76</v>
+        <v>-6.68</v>
       </c>
       <c r="L2">
-        <v>25.21</v>
+        <v>25.29</v>
       </c>
       <c r="M2">
-        <v>28.44</v>
+        <v>28.5</v>
       </c>
       <c r="N2">
         <v>74</v>
       </c>
       <c r="O2">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="P2">
-        <v>375.55</v>
+        <v>376.12</v>
       </c>
       <c r="Q2">
-        <v>386.61</v>
+        <v>385.62</v>
       </c>
       <c r="R2">
-        <v>398.79</v>
+        <v>398.52</v>
       </c>
       <c r="S2">
-        <v>365.24</v>
+        <v>365.41</v>
       </c>
       <c r="T2">
-        <v>4.23</v>
+        <v>4.06</v>
       </c>
       <c r="U2" t="s">
         <v>46</v>
@@ -990,34 +962,34 @@
         <v>2</v>
       </c>
       <c r="Y2">
-        <v>45.23</v>
+        <v>44.97</v>
       </c>
       <c r="Z2">
-        <v>-6.85</v>
+        <v>-6.38</v>
       </c>
       <c r="AA2">
-        <v>-5.74</v>
+        <v>-5.87</v>
       </c>
       <c r="AB2">
-        <v>-1.11</v>
+        <v>-0.51</v>
       </c>
       <c r="AC2">
-        <v>19.32</v>
+        <v>38.74</v>
       </c>
       <c r="AD2">
-        <v>14.87</v>
+        <v>22.07</v>
       </c>
       <c r="AE2">
-        <v>9.66</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="AF2">
-        <v>116.37</v>
+        <v>12.95</v>
       </c>
       <c r="AG2">
-        <v>409.71</v>
+        <v>407.99</v>
       </c>
       <c r="AH2">
-        <v>363.51</v>
+        <v>363.25</v>
       </c>
       <c r="AI2">
         <v>398.61</v>
@@ -1026,7 +998,7 @@
         <v>48</v>
       </c>
       <c r="AK2">
-        <v>34.45</v>
+        <v>30.15</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1037,37 +1009,37 @@
         <v>45</v>
       </c>
       <c r="C3">
-        <v>43.65</v>
+        <v>43.53</v>
       </c>
       <c r="D3">
-        <v>1.09</v>
+        <v>-0.27</v>
       </c>
       <c r="E3">
-        <v>85.7</v>
+        <v>85.38</v>
       </c>
       <c r="F3">
         <v>43.18</v>
       </c>
       <c r="G3">
-        <v>-49.07</v>
+        <v>-49.02</v>
       </c>
       <c r="H3">
-        <v>1.09</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="I3">
-        <v>-1.98</v>
+        <v>-1.83</v>
       </c>
       <c r="J3">
-        <v>-16.44</v>
+        <v>-15.2</v>
       </c>
       <c r="K3">
-        <v>-27.27</v>
+        <v>-28.06</v>
       </c>
       <c r="L3">
-        <v>-49.39</v>
+        <v>-49.21</v>
       </c>
       <c r="M3">
-        <v>-30.19</v>
+        <v>-30.68</v>
       </c>
       <c r="N3">
         <v>13</v>
@@ -1076,16 +1048,16 @@
         <v>4</v>
       </c>
       <c r="P3">
-        <v>44.29</v>
+        <v>44.13</v>
       </c>
       <c r="Q3">
-        <v>47.61</v>
+        <v>47.24</v>
       </c>
       <c r="R3">
-        <v>52.61</v>
+        <v>52.3</v>
       </c>
       <c r="S3">
-        <v>61.48</v>
+        <v>61.31</v>
       </c>
       <c r="T3">
         <v>-29</v>
@@ -1103,34 +1075,34 @@
         <v>0</v>
       </c>
       <c r="Y3">
-        <v>29.06</v>
+        <v>28.76</v>
       </c>
       <c r="Z3">
         <v>-2.43</v>
       </c>
       <c r="AA3">
-        <v>-2.2</v>
+        <v>-2.24</v>
       </c>
       <c r="AB3">
-        <v>-0.23</v>
+        <v>-0.19</v>
       </c>
       <c r="AC3">
-        <v>33.91</v>
+        <v>32.53</v>
       </c>
       <c r="AD3">
-        <v>36.91</v>
+        <v>35.98</v>
       </c>
       <c r="AE3">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="AF3">
-        <v>-42.98</v>
+        <v>-65.11</v>
       </c>
       <c r="AG3">
-        <v>52.72</v>
+        <v>52.41</v>
       </c>
       <c r="AH3">
-        <v>42.5</v>
+        <v>42.07</v>
       </c>
       <c r="AI3">
         <v>48.29</v>
@@ -1139,7 +1111,7 @@
         <v>48</v>
       </c>
       <c r="AK3">
-        <v>44.4</v>
+        <v>42.02</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1150,10 +1122,10 @@
         <v>45</v>
       </c>
       <c r="C4">
-        <v>2890</v>
+        <v>2858</v>
       </c>
       <c r="D4">
-        <v>1.16</v>
+        <v>-1.11</v>
       </c>
       <c r="E4">
         <v>3380.5</v>
@@ -1162,46 +1134,46 @@
         <v>2531.1</v>
       </c>
       <c r="G4">
-        <v>-14.51</v>
+        <v>-15.46</v>
       </c>
       <c r="H4">
-        <v>14.18</v>
+        <v>12.92</v>
       </c>
       <c r="I4">
-        <v>-2.43</v>
+        <v>-3.84</v>
       </c>
       <c r="J4">
-        <v>-12.6</v>
+        <v>-13.39</v>
       </c>
       <c r="K4">
-        <v>-10.07</v>
+        <v>-9.109999999999999</v>
       </c>
       <c r="L4">
-        <v>2.94</v>
+        <v>1.78</v>
       </c>
       <c r="M4">
-        <v>12.37</v>
+        <v>12.3</v>
       </c>
       <c r="N4">
         <v>50</v>
       </c>
       <c r="O4">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="P4">
-        <v>2921.78</v>
+        <v>2898.98</v>
       </c>
       <c r="Q4">
-        <v>3103.21</v>
+        <v>3080.16</v>
       </c>
       <c r="R4">
-        <v>3205.92</v>
+        <v>3200.98</v>
       </c>
       <c r="S4">
-        <v>2979.64</v>
+        <v>2979.89</v>
       </c>
       <c r="T4">
-        <v>-3.01</v>
+        <v>-4.09</v>
       </c>
       <c r="U4" t="s">
         <v>46</v>
@@ -1216,34 +1188,34 @@
         <v>1</v>
       </c>
       <c r="Y4">
-        <v>28.22</v>
+        <v>26.49</v>
       </c>
       <c r="Z4">
-        <v>-91.23</v>
+        <v>-96.41</v>
       </c>
       <c r="AA4">
-        <v>-63.23</v>
+        <v>-69.87</v>
       </c>
       <c r="AB4">
-        <v>-28</v>
+        <v>-26.54</v>
       </c>
       <c r="AC4">
-        <v>7.24</v>
+        <v>11.88</v>
       </c>
       <c r="AD4">
-        <v>4.8</v>
+        <v>7.13</v>
       </c>
       <c r="AE4">
-        <v>61.62</v>
+        <v>61.84</v>
       </c>
       <c r="AF4">
-        <v>-67.83</v>
+        <v>-82.25</v>
       </c>
       <c r="AG4">
-        <v>3366.07</v>
+        <v>3344.19</v>
       </c>
       <c r="AH4">
-        <v>2840.35</v>
+        <v>2816.13</v>
       </c>
       <c r="AI4">
         <v>3061.2</v>
@@ -1252,7 +1224,7 @@
         <v>48</v>
       </c>
       <c r="AK4">
-        <v>66.63</v>
+        <v>66.5</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1263,10 +1235,10 @@
         <v>45</v>
       </c>
       <c r="C5">
-        <v>900.35</v>
+        <v>882.5</v>
       </c>
       <c r="D5">
-        <v>1.15</v>
+        <v>-1.98</v>
       </c>
       <c r="E5">
         <v>1149.7</v>
@@ -1275,46 +1247,46 @@
         <v>760.1</v>
       </c>
       <c r="G5">
-        <v>-21.69</v>
+        <v>-23.24</v>
       </c>
       <c r="H5">
-        <v>18.45</v>
+        <v>16.1</v>
       </c>
       <c r="I5">
-        <v>-4.41</v>
+        <v>-5.96</v>
       </c>
       <c r="J5">
-        <v>-10.77</v>
+        <v>-14.06</v>
       </c>
       <c r="K5">
-        <v>-6.94</v>
+        <v>-8.720000000000001</v>
       </c>
       <c r="L5">
-        <v>15.92</v>
+        <v>14.94</v>
       </c>
       <c r="M5">
-        <v>13.72</v>
+        <v>12.74</v>
       </c>
       <c r="N5">
         <v>62</v>
       </c>
       <c r="O5">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="P5">
-        <v>916.05</v>
+        <v>904.87</v>
       </c>
       <c r="Q5">
-        <v>959.3</v>
+        <v>952.72</v>
       </c>
       <c r="R5">
-        <v>1001.01</v>
+        <v>999.25</v>
       </c>
       <c r="S5">
-        <v>982.84</v>
+        <v>982.9299999999999</v>
       </c>
       <c r="T5">
-        <v>-8.390000000000001</v>
+        <v>-10.22</v>
       </c>
       <c r="U5" t="s">
         <v>46</v>
@@ -1329,34 +1301,34 @@
         <v>1</v>
       </c>
       <c r="Y5">
-        <v>30.26</v>
+        <v>27.24</v>
       </c>
       <c r="Z5">
-        <v>-26.05</v>
+        <v>-28.43</v>
       </c>
       <c r="AA5">
-        <v>-19.18</v>
+        <v>-21.03</v>
       </c>
       <c r="AB5">
-        <v>-6.87</v>
+        <v>-7.4</v>
       </c>
       <c r="AC5">
-        <v>5.93</v>
+        <v>7.75</v>
       </c>
       <c r="AD5">
-        <v>3.68</v>
+        <v>5.22</v>
       </c>
       <c r="AE5">
-        <v>21.59</v>
+        <v>21.93</v>
       </c>
       <c r="AF5">
-        <v>-10.78</v>
+        <v>-33.95</v>
       </c>
       <c r="AG5">
-        <v>1024.77</v>
+        <v>1021.4</v>
       </c>
       <c r="AH5">
-        <v>893.8200000000001</v>
+        <v>884.04</v>
       </c>
       <c r="AI5">
         <v>958.48</v>
@@ -1365,7 +1337,7 @@
         <v>48</v>
       </c>
       <c r="AK5">
-        <v>44.45</v>
+        <v>45.43</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1376,10 +1348,10 @@
         <v>45</v>
       </c>
       <c r="C6">
-        <v>13</v>
+        <v>12.67</v>
       </c>
       <c r="D6">
-        <v>1.56</v>
+        <v>-2.54</v>
       </c>
       <c r="E6">
         <v>15.6</v>
@@ -1388,46 +1360,46 @@
         <v>8.359999999999999</v>
       </c>
       <c r="G6">
-        <v>-16.67</v>
+        <v>-18.78</v>
       </c>
       <c r="H6">
-        <v>55.5</v>
+        <v>51.56</v>
       </c>
       <c r="I6">
-        <v>2.85</v>
+        <v>-0.55</v>
       </c>
       <c r="J6">
-        <v>-15.69</v>
+        <v>-18.36</v>
       </c>
       <c r="K6">
-        <v>-8.390000000000001</v>
+        <v>-9.24</v>
       </c>
       <c r="L6">
-        <v>53.48</v>
+        <v>38.02</v>
       </c>
       <c r="M6">
-        <v>3.69</v>
+        <v>3.54</v>
       </c>
       <c r="N6">
         <v>87</v>
       </c>
       <c r="O6">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="P6">
-        <v>12.99</v>
+        <v>12.97</v>
       </c>
       <c r="Q6">
-        <v>13.76</v>
+        <v>13.65</v>
       </c>
       <c r="R6">
-        <v>13.9</v>
+        <v>13.89</v>
       </c>
       <c r="S6">
-        <v>12.28</v>
+        <v>12.29</v>
       </c>
       <c r="T6">
-        <v>5.84</v>
+        <v>3.12</v>
       </c>
       <c r="U6" t="s">
         <v>46</v>
@@ -1442,34 +1414,34 @@
         <v>2</v>
       </c>
       <c r="Y6">
-        <v>40.63</v>
+        <v>37.35</v>
       </c>
       <c r="Z6">
-        <v>-0.38</v>
+        <v>-0.4</v>
       </c>
       <c r="AA6">
-        <v>-0.26</v>
+        <v>-0.29</v>
       </c>
       <c r="AB6">
         <v>-0.11</v>
       </c>
       <c r="AC6">
-        <v>35.72</v>
+        <v>28.85</v>
       </c>
       <c r="AD6">
-        <v>35.16</v>
+        <v>34.01</v>
       </c>
       <c r="AE6">
-        <v>0.48</v>
+        <v>0.47</v>
       </c>
       <c r="AF6">
-        <v>-45.14</v>
+        <v>-28.2</v>
       </c>
       <c r="AG6">
-        <v>15.23</v>
+        <v>15.09</v>
       </c>
       <c r="AH6">
-        <v>12.3</v>
+        <v>12.21</v>
       </c>
       <c r="AI6">
         <v>14.25</v>
@@ -1478,7 +1450,7 @@
         <v>48</v>
       </c>
       <c r="AK6">
-        <v>38.31</v>
+        <v>39.13</v>
       </c>
     </row>
     <row r="7" spans="1:37">
@@ -1489,10 +1461,10 @@
         <v>45</v>
       </c>
       <c r="C7">
-        <v>11.06</v>
+        <v>10.88</v>
       </c>
       <c r="D7">
-        <v>4.73</v>
+        <v>-1.63</v>
       </c>
       <c r="E7">
         <v>13.92</v>
@@ -1501,46 +1473,46 @@
         <v>4.69</v>
       </c>
       <c r="G7">
-        <v>-20.55</v>
+        <v>-21.84</v>
       </c>
       <c r="H7">
-        <v>135.82</v>
+        <v>131.98</v>
       </c>
       <c r="I7">
-        <v>3.08</v>
+        <v>6.15</v>
       </c>
       <c r="J7">
-        <v>-2.38</v>
+        <v>-5.8</v>
       </c>
       <c r="K7">
-        <v>6.65</v>
+        <v>3.03</v>
       </c>
       <c r="L7">
-        <v>101.46</v>
+        <v>100</v>
       </c>
       <c r="M7">
-        <v>-30.78</v>
+        <v>-30.95</v>
       </c>
       <c r="N7">
         <v>99</v>
       </c>
       <c r="O7">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="P7">
-        <v>10.69</v>
+        <v>10.81</v>
       </c>
       <c r="Q7">
-        <v>11.38</v>
+        <v>11.33</v>
       </c>
       <c r="R7">
-        <v>11.65</v>
+        <v>11.63</v>
       </c>
       <c r="S7">
         <v>10.84</v>
       </c>
       <c r="T7">
-        <v>1.99</v>
+        <v>0.33</v>
       </c>
       <c r="U7" t="s">
         <v>46</v>
@@ -1555,34 +1527,34 @@
         <v>2</v>
       </c>
       <c r="Y7">
-        <v>47.63</v>
+        <v>45.29</v>
       </c>
       <c r="Z7">
-        <v>-0.25</v>
+        <v>-0.24</v>
       </c>
       <c r="AA7">
         <v>-0.2</v>
       </c>
       <c r="AB7">
-        <v>-0.05</v>
+        <v>-0.03</v>
       </c>
       <c r="AC7">
-        <v>53.42</v>
+        <v>68.47</v>
       </c>
       <c r="AD7">
-        <v>36.25</v>
+        <v>51.71</v>
       </c>
       <c r="AE7">
-        <v>0.57</v>
+        <v>0.58</v>
       </c>
       <c r="AF7">
-        <v>128.97</v>
+        <v>14.21</v>
       </c>
       <c r="AG7">
-        <v>12.69</v>
+        <v>12.65</v>
       </c>
       <c r="AH7">
-        <v>10.06</v>
+        <v>10.01</v>
       </c>
       <c r="AI7">
         <v>12.04</v>
@@ -1591,7 +1563,7 @@
         <v>48</v>
       </c>
       <c r="AK7">
-        <v>32.21</v>
+        <v>28.72</v>
       </c>
     </row>
     <row r="8" spans="1:37">
@@ -1602,10 +1574,10 @@
         <v>45</v>
       </c>
       <c r="C8">
-        <v>3937.7</v>
+        <v>3934.9</v>
       </c>
       <c r="D8">
-        <v>-0.27</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="E8">
         <v>5809.5</v>
@@ -1614,46 +1586,46 @@
         <v>3892.3</v>
       </c>
       <c r="G8">
-        <v>-32.22</v>
+        <v>-32.27</v>
       </c>
       <c r="H8">
-        <v>1.17</v>
+        <v>1.09</v>
       </c>
       <c r="I8">
-        <v>1.17</v>
+        <v>-1.25</v>
       </c>
       <c r="J8">
-        <v>-7.6</v>
+        <v>-4.26</v>
       </c>
       <c r="K8">
-        <v>-11.2</v>
+        <v>-11.76</v>
       </c>
       <c r="L8">
-        <v>-28.42</v>
+        <v>-27.04</v>
       </c>
       <c r="M8">
-        <v>14.78</v>
+        <v>14.96</v>
       </c>
       <c r="N8">
         <v>26</v>
       </c>
       <c r="O8">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="P8">
-        <v>4002.86</v>
+        <v>3992.9</v>
       </c>
       <c r="Q8">
-        <v>4034.91</v>
+        <v>4019.87</v>
       </c>
       <c r="R8">
-        <v>4228.78</v>
+        <v>4221.13</v>
       </c>
       <c r="S8">
-        <v>4500.25</v>
+        <v>4493.89</v>
       </c>
       <c r="T8">
-        <v>-12.5</v>
+        <v>-12.44</v>
       </c>
       <c r="U8" t="s">
         <v>46</v>
@@ -1668,34 +1640,34 @@
         <v>0</v>
       </c>
       <c r="Y8">
-        <v>38.26</v>
+        <v>38.09</v>
       </c>
       <c r="Z8">
-        <v>-74.91</v>
+        <v>-75.2</v>
       </c>
       <c r="AA8">
-        <v>-80.45</v>
+        <v>-79.40000000000001</v>
       </c>
       <c r="AB8">
-        <v>5.55</v>
+        <v>4.2</v>
       </c>
       <c r="AC8">
-        <v>68.5</v>
+        <v>51.88</v>
       </c>
       <c r="AD8">
-        <v>84.44</v>
+        <v>68.39</v>
       </c>
       <c r="AE8">
-        <v>111.39</v>
+        <v>106.33</v>
       </c>
       <c r="AF8">
-        <v>-60.28</v>
+        <v>-78.52</v>
       </c>
       <c r="AG8">
-        <v>4195.69</v>
+        <v>4155.9</v>
       </c>
       <c r="AH8">
-        <v>3874.13</v>
+        <v>3883.83</v>
       </c>
       <c r="AI8">
         <v>4247.59</v>
@@ -1704,7 +1676,7 @@
         <v>48</v>
       </c>
       <c r="AK8">
-        <v>38.98</v>
+        <v>38.44</v>
       </c>
     </row>
     <row r="9" spans="1:37">
@@ -1715,10 +1687,10 @@
         <v>45</v>
       </c>
       <c r="C9">
-        <v>10675</v>
+        <v>10520</v>
       </c>
       <c r="D9">
-        <v>2.39</v>
+        <v>-1.45</v>
       </c>
       <c r="E9">
         <v>13052</v>
@@ -1727,46 +1699,46 @@
         <v>10362</v>
       </c>
       <c r="G9">
-        <v>-18.21</v>
+        <v>-19.4</v>
       </c>
       <c r="H9">
-        <v>3.02</v>
+        <v>1.52</v>
       </c>
       <c r="I9">
-        <v>-0.33</v>
+        <v>-3.04</v>
       </c>
       <c r="J9">
-        <v>-3.03</v>
+        <v>-3.49</v>
       </c>
       <c r="K9">
-        <v>-8.85</v>
+        <v>-9.08</v>
       </c>
       <c r="L9">
-        <v>-11.45</v>
+        <v>-13.66</v>
       </c>
       <c r="M9">
-        <v>8.300000000000001</v>
+        <v>8.220000000000001</v>
       </c>
       <c r="N9">
         <v>38</v>
       </c>
       <c r="O9">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="P9">
-        <v>10671.8</v>
+        <v>10605.8</v>
       </c>
       <c r="Q9">
-        <v>10874.95</v>
+        <v>10852</v>
       </c>
       <c r="R9">
-        <v>11330.94</v>
+        <v>11304.4</v>
       </c>
       <c r="S9">
-        <v>11686.18</v>
+        <v>11681.12</v>
       </c>
       <c r="T9">
-        <v>-8.65</v>
+        <v>-9.94</v>
       </c>
       <c r="U9" t="s">
         <v>46</v>
@@ -1781,34 +1753,34 @@
         <v>0</v>
       </c>
       <c r="Y9">
-        <v>41.65</v>
+        <v>38.4</v>
       </c>
       <c r="Z9">
-        <v>-181.16</v>
+        <v>-189.12</v>
       </c>
       <c r="AA9">
-        <v>-163.43</v>
+        <v>-168.57</v>
       </c>
       <c r="AB9">
-        <v>-17.73</v>
+        <v>-20.55</v>
       </c>
       <c r="AC9">
-        <v>32.81</v>
+        <v>30.48</v>
       </c>
       <c r="AD9">
-        <v>41.89</v>
+        <v>32.53</v>
       </c>
       <c r="AE9">
-        <v>210.87</v>
+        <v>219.59</v>
       </c>
       <c r="AF9">
-        <v>-47.81</v>
+        <v>-24.75</v>
       </c>
       <c r="AG9">
-        <v>11269.53</v>
+        <v>11273.57</v>
       </c>
       <c r="AH9">
-        <v>10480.37</v>
+        <v>10430.43</v>
       </c>
       <c r="AI9">
         <v>11169.72</v>
@@ -1817,7 +1789,7 @@
         <v>48</v>
       </c>
       <c r="AK9">
-        <v>42</v>
+        <v>41.79</v>
       </c>
     </row>
   </sheetData>
@@ -1978,47 +1950,12 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="3" t="s">
         <v>50</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="D2" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="F2" s="3" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6">
-      <c r="A3" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="B3" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="C3" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="D3" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="E3" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="F3" s="4" t="s">
-        <v>59</v>
       </c>
     </row>
     <row r="5" spans="1:6">
       <c r="A5" s="2" t="s">
-        <v>60</v>
+        <v>51</v>
       </c>
       <c r="B5" s="2"/>
       <c r="C5" s="2"/>
@@ -2026,1108 +1963,1108 @@
       <c r="E5" s="2"/>
     </row>
     <row r="6" spans="1:6">
-      <c r="A6" s="3" t="s">
+      <c r="A6" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B6" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>64</v>
+      <c r="B6" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>55</v>
       </c>
     </row>
     <row r="7" spans="1:6">
-      <c r="A7" s="5" t="s">
+      <c r="A7" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B7" s="5" t="s">
+      <c r="B7" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C7" s="6">
-        <v>-8.58</v>
-      </c>
-      <c r="D7" s="6">
+      <c r="C7" s="5">
         <v>-4.09</v>
       </c>
-      <c r="E7" s="7">
-        <v>4.49</v>
+      <c r="D7" s="5">
+        <v>-4.94</v>
+      </c>
+      <c r="E7" s="6">
+        <v>-0.85</v>
       </c>
     </row>
     <row r="8" spans="1:6">
-      <c r="A8" s="5" t="s">
+      <c r="A8" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B8" s="5" t="s">
+      <c r="B8" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C8" s="6">
-        <v>-18.85</v>
-      </c>
-      <c r="D8" s="6">
+      <c r="C8" s="5">
         <v>-16.44</v>
       </c>
+      <c r="D8" s="5">
+        <v>-15.2</v>
+      </c>
       <c r="E8" s="7">
-        <v>2.41</v>
+        <v>1.24</v>
       </c>
     </row>
     <row r="9" spans="1:6">
-      <c r="A9" s="5" t="s">
+      <c r="A9" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B9" s="5" t="s">
+      <c r="B9" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C9" s="6">
-        <v>-13.49</v>
-      </c>
-      <c r="D9" s="6">
+      <c r="C9" s="5">
         <v>-12.6</v>
       </c>
-      <c r="E9" s="7">
-        <v>0.89</v>
+      <c r="D9" s="5">
+        <v>-13.39</v>
+      </c>
+      <c r="E9" s="6">
+        <v>-0.79</v>
       </c>
     </row>
     <row r="10" spans="1:6">
-      <c r="A10" s="5" t="s">
+      <c r="A10" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="B10" s="5" t="s">
+      <c r="B10" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C10" s="6">
-        <v>-11.52</v>
-      </c>
-      <c r="D10" s="6">
+      <c r="C10" s="5">
         <v>-10.77</v>
       </c>
-      <c r="E10" s="7">
-        <v>0.75</v>
+      <c r="D10" s="5">
+        <v>-14.06</v>
+      </c>
+      <c r="E10" s="6">
+        <v>-3.29</v>
       </c>
     </row>
     <row r="11" spans="1:6">
-      <c r="A11" s="5" t="s">
+      <c r="A11" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="B11" s="5" t="s">
+      <c r="B11" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C11" s="6">
-        <v>-17.95</v>
-      </c>
-      <c r="D11" s="6">
+      <c r="C11" s="5">
         <v>-15.69</v>
       </c>
-      <c r="E11" s="7">
-        <v>2.26</v>
+      <c r="D11" s="5">
+        <v>-18.36</v>
+      </c>
+      <c r="E11" s="6">
+        <v>-2.67</v>
       </c>
     </row>
     <row r="12" spans="1:6">
-      <c r="A12" s="5" t="s">
+      <c r="A12" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="B12" s="5" t="s">
+      <c r="B12" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C12" s="6">
-        <v>-4.95</v>
-      </c>
-      <c r="D12" s="6">
+      <c r="C12" s="5">
         <v>-2.38</v>
       </c>
-      <c r="E12" s="7">
-        <v>2.57</v>
+      <c r="D12" s="5">
+        <v>-5.8</v>
+      </c>
+      <c r="E12" s="6">
+        <v>-3.42</v>
       </c>
     </row>
     <row r="13" spans="1:6">
-      <c r="A13" s="5" t="s">
+      <c r="A13" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="B13" s="5" t="s">
+      <c r="B13" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C13" s="6">
-        <v>-8.15</v>
-      </c>
-      <c r="D13" s="6">
+      <c r="C13" s="5">
         <v>-7.6</v>
       </c>
+      <c r="D13" s="5">
+        <v>-4.26</v>
+      </c>
       <c r="E13" s="7">
-        <v>0.55</v>
+        <v>3.34</v>
       </c>
     </row>
     <row r="14" spans="1:6">
-      <c r="A14" s="5" t="s">
+      <c r="A14" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="B14" s="5" t="s">
+      <c r="B14" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C14" s="6">
-        <v>-6.7</v>
-      </c>
-      <c r="D14" s="6">
+      <c r="C14" s="5">
         <v>-3.03</v>
       </c>
-      <c r="E14" s="7">
-        <v>3.67</v>
+      <c r="D14" s="5">
+        <v>-3.49</v>
+      </c>
+      <c r="E14" s="6">
+        <v>-0.46</v>
       </c>
     </row>
     <row r="15" spans="1:6">
-      <c r="A15" s="5" t="s">
+      <c r="A15" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B15" s="5" t="s">
+      <c r="B15" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C15" s="6">
-        <v>-3.14</v>
-      </c>
-      <c r="D15" s="6">
+      <c r="C15" s="5">
         <v>1.51</v>
       </c>
-      <c r="E15" s="7">
-        <v>4.65</v>
+      <c r="D15" s="5">
+        <v>0.76</v>
+      </c>
+      <c r="E15" s="6">
+        <v>-0.75</v>
       </c>
     </row>
     <row r="16" spans="1:6">
-      <c r="A16" s="5" t="s">
+      <c r="A16" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B16" s="5" t="s">
+      <c r="B16" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C16" s="6">
-        <v>-6.78</v>
-      </c>
-      <c r="D16" s="6">
+      <c r="C16" s="5">
         <v>-1.98</v>
       </c>
+      <c r="D16" s="5">
+        <v>-1.83</v>
+      </c>
       <c r="E16" s="7">
-        <v>4.8</v>
+        <v>0.15</v>
       </c>
     </row>
     <row r="17" spans="1:5">
-      <c r="A17" s="5" t="s">
+      <c r="A17" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B17" s="5" t="s">
+      <c r="B17" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C17" s="6">
-        <v>-6.7</v>
-      </c>
-      <c r="D17" s="6">
+      <c r="C17" s="5">
         <v>-2.43</v>
       </c>
-      <c r="E17" s="7">
-        <v>4.27</v>
+      <c r="D17" s="5">
+        <v>-3.84</v>
+      </c>
+      <c r="E17" s="6">
+        <v>-1.41</v>
       </c>
     </row>
     <row r="18" spans="1:5">
-      <c r="A18" s="5" t="s">
+      <c r="A18" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="B18" s="5" t="s">
+      <c r="B18" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C18" s="6">
-        <v>-5.48</v>
-      </c>
-      <c r="D18" s="6">
+      <c r="C18" s="5">
         <v>-4.41</v>
       </c>
-      <c r="E18" s="7">
-        <v>1.07</v>
+      <c r="D18" s="5">
+        <v>-5.96</v>
+      </c>
+      <c r="E18" s="6">
+        <v>-1.55</v>
       </c>
     </row>
     <row r="19" spans="1:5">
-      <c r="A19" s="5" t="s">
+      <c r="A19" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="B19" s="5" t="s">
+      <c r="B19" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C19" s="6">
+      <c r="C19" s="5">
+        <v>2.85</v>
+      </c>
+      <c r="D19" s="5">
+        <v>-0.55</v>
+      </c>
+      <c r="E19" s="6">
+        <v>-3.4</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C20" s="5">
+        <v>3.08</v>
+      </c>
+      <c r="D20" s="5">
+        <v>6.15</v>
+      </c>
+      <c r="E20" s="7">
+        <v>3.07</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C21" s="5">
+        <v>1.17</v>
+      </c>
+      <c r="D21" s="5">
+        <v>-1.25</v>
+      </c>
+      <c r="E21" s="6">
+        <v>-2.42</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C22" s="5">
+        <v>-0.33</v>
+      </c>
+      <c r="D22" s="5">
+        <v>-3.04</v>
+      </c>
+      <c r="E22" s="6">
+        <v>-2.71</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C23" s="5">
+        <v>25.21</v>
+      </c>
+      <c r="D23" s="5">
+        <v>25.29</v>
+      </c>
+      <c r="E23" s="7">
+        <v>0.08</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C24" s="5">
+        <v>-49.39</v>
+      </c>
+      <c r="D24" s="5">
+        <v>-49.21</v>
+      </c>
+      <c r="E24" s="7">
+        <v>0.18</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B25" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C25" s="5">
+        <v>2.94</v>
+      </c>
+      <c r="D25" s="5">
+        <v>1.78</v>
+      </c>
+      <c r="E25" s="6">
         <v>-1.16</v>
       </c>
-      <c r="D19" s="6">
-        <v>2.85</v>
-      </c>
-      <c r="E19" s="7">
-        <v>4.01</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5">
-      <c r="A20" s="5" t="s">
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C26" s="5">
+        <v>15.92</v>
+      </c>
+      <c r="D26" s="5">
+        <v>14.94</v>
+      </c>
+      <c r="E26" s="6">
+        <v>-0.98</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B27" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C27" s="5">
+        <v>53.48</v>
+      </c>
+      <c r="D27" s="5">
+        <v>38.02</v>
+      </c>
+      <c r="E27" s="6">
+        <v>-15.46</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="B20" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C20" s="6">
-        <v>-3.3</v>
-      </c>
-      <c r="D20" s="6">
-        <v>3.08</v>
-      </c>
-      <c r="E20" s="7">
-        <v>6.38</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5">
-      <c r="A21" s="5" t="s">
+      <c r="B28" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C28" s="5">
+        <v>101.46</v>
+      </c>
+      <c r="D28" s="5">
+        <v>100</v>
+      </c>
+      <c r="E28" s="6">
+        <v>-1.46</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="B21" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C21" s="6">
-        <v>-0.2</v>
-      </c>
-      <c r="D21" s="6">
-        <v>1.17</v>
-      </c>
-      <c r="E21" s="7">
-        <v>1.37</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5">
-      <c r="A22" s="5" t="s">
+      <c r="B29" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C29" s="5">
+        <v>-28.42</v>
+      </c>
+      <c r="D29" s="5">
+        <v>-27.04</v>
+      </c>
+      <c r="E29" s="7">
+        <v>1.38</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="B22" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C22" s="6">
-        <v>-4.84</v>
-      </c>
-      <c r="D22" s="6">
+      <c r="B30" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C30" s="5">
+        <v>-11.45</v>
+      </c>
+      <c r="D30" s="5">
+        <v>-13.66</v>
+      </c>
+      <c r="E30" s="6">
+        <v>-2.21</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5">
+      <c r="A31" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B31" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C31" s="5">
+        <v>-6.76</v>
+      </c>
+      <c r="D31" s="5">
+        <v>-6.68</v>
+      </c>
+      <c r="E31" s="7">
+        <v>0.08</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5">
+      <c r="A32" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B32" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C32" s="5">
+        <v>-27.27</v>
+      </c>
+      <c r="D32" s="5">
+        <v>-28.06</v>
+      </c>
+      <c r="E32" s="6">
+        <v>-0.79</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5">
+      <c r="A33" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B33" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C33" s="5">
+        <v>-10.07</v>
+      </c>
+      <c r="D33" s="5">
+        <v>-9.109999999999999</v>
+      </c>
+      <c r="E33" s="7">
+        <v>0.96</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5">
+      <c r="A34" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B34" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C34" s="5">
+        <v>-6.94</v>
+      </c>
+      <c r="D34" s="5">
+        <v>-8.720000000000001</v>
+      </c>
+      <c r="E34" s="6">
+        <v>-1.78</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5">
+      <c r="A35" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B35" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C35" s="5">
+        <v>-8.390000000000001</v>
+      </c>
+      <c r="D35" s="5">
+        <v>-9.24</v>
+      </c>
+      <c r="E35" s="6">
+        <v>-0.85</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5">
+      <c r="A36" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B36" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C36" s="5">
+        <v>6.65</v>
+      </c>
+      <c r="D36" s="5">
+        <v>3.03</v>
+      </c>
+      <c r="E36" s="6">
+        <v>-3.62</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5">
+      <c r="A37" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="B37" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C37" s="5">
+        <v>-11.2</v>
+      </c>
+      <c r="D37" s="5">
+        <v>-11.76</v>
+      </c>
+      <c r="E37" s="6">
+        <v>-0.5600000000000001</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5">
+      <c r="A38" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="B38" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C38" s="5">
+        <v>-8.85</v>
+      </c>
+      <c r="D38" s="5">
+        <v>-9.08</v>
+      </c>
+      <c r="E38" s="6">
+        <v>-0.23</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5">
+      <c r="A39" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B39" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C39" s="5">
+        <v>-10.36</v>
+      </c>
+      <c r="D39" s="5">
+        <v>-10.47</v>
+      </c>
+      <c r="E39" s="6">
+        <v>-0.11</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5">
+      <c r="A40" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B40" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C40" s="5">
+        <v>-49.07</v>
+      </c>
+      <c r="D40" s="5">
+        <v>-49.02</v>
+      </c>
+      <c r="E40" s="7">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5">
+      <c r="A41" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B41" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C41" s="5">
+        <v>-14.51</v>
+      </c>
+      <c r="D41" s="5">
+        <v>-15.46</v>
+      </c>
+      <c r="E41" s="6">
+        <v>-0.95</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5">
+      <c r="A42" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B42" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C42" s="5">
+        <v>-21.69</v>
+      </c>
+      <c r="D42" s="5">
+        <v>-23.24</v>
+      </c>
+      <c r="E42" s="6">
+        <v>-1.55</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5">
+      <c r="A43" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B43" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C43" s="5">
+        <v>-16.67</v>
+      </c>
+      <c r="D43" s="5">
+        <v>-18.78</v>
+      </c>
+      <c r="E43" s="6">
+        <v>-2.11</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5">
+      <c r="A44" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B44" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C44" s="5">
+        <v>-20.55</v>
+      </c>
+      <c r="D44" s="5">
+        <v>-21.84</v>
+      </c>
+      <c r="E44" s="6">
+        <v>-1.29</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5">
+      <c r="A45" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="B45" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C45" s="5">
+        <v>-32.22</v>
+      </c>
+      <c r="D45" s="5">
+        <v>-32.27</v>
+      </c>
+      <c r="E45" s="6">
+        <v>-0.05</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5">
+      <c r="A46" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="B46" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C46" s="5">
+        <v>-18.21</v>
+      </c>
+      <c r="D46" s="5">
+        <v>-19.4</v>
+      </c>
+      <c r="E46" s="6">
+        <v>-1.19</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5">
+      <c r="A47" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B47" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C47" s="5">
+        <v>380.7</v>
+      </c>
+      <c r="D47" s="5">
+        <v>380.25</v>
+      </c>
+      <c r="E47" s="6">
+        <v>-0.45</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5">
+      <c r="A48" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B48" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C48" s="5">
+        <v>43.65</v>
+      </c>
+      <c r="D48" s="5">
+        <v>43.53</v>
+      </c>
+      <c r="E48" s="6">
+        <v>-0.12</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5">
+      <c r="A49" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B49" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C49" s="5">
+        <v>2890</v>
+      </c>
+      <c r="D49" s="5">
+        <v>2858</v>
+      </c>
+      <c r="E49" s="6">
+        <v>-32</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5">
+      <c r="A50" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B50" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C50" s="5">
+        <v>900.35</v>
+      </c>
+      <c r="D50" s="5">
+        <v>882.5</v>
+      </c>
+      <c r="E50" s="6">
+        <v>-17.85</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5">
+      <c r="A51" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B51" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C51" s="5">
+        <v>13</v>
+      </c>
+      <c r="D51" s="5">
+        <v>12.67</v>
+      </c>
+      <c r="E51" s="6">
         <v>-0.33</v>
       </c>
-      <c r="E22" s="7">
-        <v>4.51</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5">
-      <c r="A23" s="5" t="s">
+    </row>
+    <row r="52" spans="1:5">
+      <c r="A52" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B52" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C52" s="5">
+        <v>11.06</v>
+      </c>
+      <c r="D52" s="5">
+        <v>10.88</v>
+      </c>
+      <c r="E52" s="6">
+        <v>-0.18</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5">
+      <c r="A53" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="B53" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C53" s="5">
+        <v>3937.7</v>
+      </c>
+      <c r="D53" s="5">
+        <v>3934.9</v>
+      </c>
+      <c r="E53" s="6">
+        <v>-2.8</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5">
+      <c r="A54" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="B54" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C54" s="5">
+        <v>10675</v>
+      </c>
+      <c r="D54" s="5">
+        <v>10520</v>
+      </c>
+      <c r="E54" s="6">
+        <v>-155</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5">
+      <c r="A55" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B23" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C23" s="6">
-        <v>21.29</v>
-      </c>
-      <c r="D23" s="6">
-        <v>25.21</v>
-      </c>
-      <c r="E23" s="7">
-        <v>3.92</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5">
-      <c r="A24" s="5" t="s">
+      <c r="B55" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C55" s="5">
+        <v>45.23</v>
+      </c>
+      <c r="D55" s="5">
+        <v>44.97</v>
+      </c>
+      <c r="E55" s="6">
+        <v>-0.26</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5">
+      <c r="A56" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B24" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C24" s="6">
-        <v>-50.93</v>
-      </c>
-      <c r="D24" s="6">
-        <v>-49.39</v>
-      </c>
-      <c r="E24" s="7">
-        <v>1.54</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5">
-      <c r="A25" s="5" t="s">
+      <c r="B56" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C56" s="5">
+        <v>29.06</v>
+      </c>
+      <c r="D56" s="5">
+        <v>28.76</v>
+      </c>
+      <c r="E56" s="6">
+        <v>-0.3</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5">
+      <c r="A57" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B25" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C25" s="6">
-        <v>2.34</v>
-      </c>
-      <c r="D25" s="6">
-        <v>2.94</v>
-      </c>
-      <c r="E25" s="7">
-        <v>0.6</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5">
-      <c r="A26" s="5" t="s">
+      <c r="B57" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C57" s="5">
+        <v>28.22</v>
+      </c>
+      <c r="D57" s="5">
+        <v>26.49</v>
+      </c>
+      <c r="E57" s="6">
+        <v>-1.73</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5">
+      <c r="A58" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="B26" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C26" s="6">
-        <v>14.07</v>
-      </c>
-      <c r="D26" s="6">
-        <v>15.92</v>
-      </c>
-      <c r="E26" s="7">
-        <v>1.85</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5">
-      <c r="A27" s="5" t="s">
+      <c r="B58" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C58" s="5">
+        <v>30.26</v>
+      </c>
+      <c r="D58" s="5">
+        <v>27.24</v>
+      </c>
+      <c r="E58" s="6">
+        <v>-3.02</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5">
+      <c r="A59" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="B27" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C27" s="6">
-        <v>45.12</v>
-      </c>
-      <c r="D27" s="6">
-        <v>53.48</v>
-      </c>
-      <c r="E27" s="7">
-        <v>8.359999999999999</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5">
-      <c r="A28" s="5" t="s">
+      <c r="B59" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C59" s="5">
+        <v>40.63</v>
+      </c>
+      <c r="D59" s="5">
+        <v>37.35</v>
+      </c>
+      <c r="E59" s="6">
+        <v>-3.28</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5">
+      <c r="A60" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="B28" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C28" s="6">
-        <v>87.23</v>
-      </c>
-      <c r="D28" s="6">
-        <v>101.46</v>
-      </c>
-      <c r="E28" s="7">
-        <v>14.23</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5">
-      <c r="A29" s="5" t="s">
+      <c r="B60" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C60" s="5">
+        <v>47.63</v>
+      </c>
+      <c r="D60" s="5">
+        <v>45.29</v>
+      </c>
+      <c r="E60" s="6">
+        <v>-2.34</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5">
+      <c r="A61" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="B29" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C29" s="6">
-        <v>-29.58</v>
-      </c>
-      <c r="D29" s="6">
-        <v>-28.42</v>
-      </c>
-      <c r="E29" s="7">
-        <v>1.16</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5">
-      <c r="A30" s="5" t="s">
+      <c r="B61" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C61" s="5">
+        <v>38.26</v>
+      </c>
+      <c r="D61" s="5">
+        <v>38.09</v>
+      </c>
+      <c r="E61" s="6">
+        <v>-0.17</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5">
+      <c r="A62" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="B30" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C30" s="6">
-        <v>-13.25</v>
-      </c>
-      <c r="D30" s="6">
-        <v>-11.45</v>
-      </c>
-      <c r="E30" s="7">
-        <v>1.8</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5">
-      <c r="A31" s="5" t="s">
+      <c r="B62" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C62" s="5">
+        <v>41.65</v>
+      </c>
+      <c r="D62" s="5">
+        <v>38.4</v>
+      </c>
+      <c r="E62" s="6">
+        <v>-3.25</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5">
+      <c r="A63" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B31" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C31" s="6">
-        <v>-7.22</v>
-      </c>
-      <c r="D31" s="6">
-        <v>-6.76</v>
-      </c>
-      <c r="E31" s="7">
-        <v>0.46</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5">
-      <c r="A32" s="5" t="s">
+      <c r="B63" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C63" s="5">
+        <v>116.37</v>
+      </c>
+      <c r="D63" s="5">
+        <v>12.95</v>
+      </c>
+      <c r="E63" s="6">
+        <v>-103.42</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5">
+      <c r="A64" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B32" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C32" s="6">
-        <v>-26.25</v>
-      </c>
-      <c r="D32" s="6">
-        <v>-27.27</v>
-      </c>
-      <c r="E32" s="8">
-        <v>-1.02</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5">
-      <c r="A33" s="5" t="s">
+      <c r="B64" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C64" s="5">
+        <v>-42.98</v>
+      </c>
+      <c r="D64" s="5">
+        <v>-65.11</v>
+      </c>
+      <c r="E64" s="6">
+        <v>-22.13</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5">
+      <c r="A65" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B33" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C33" s="6">
-        <v>-10.5</v>
-      </c>
-      <c r="D33" s="6">
-        <v>-10.07</v>
-      </c>
-      <c r="E33" s="7">
-        <v>0.43</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5">
-      <c r="A34" s="5" t="s">
+      <c r="B65" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C65" s="5">
+        <v>-67.83</v>
+      </c>
+      <c r="D65" s="5">
+        <v>-82.25</v>
+      </c>
+      <c r="E65" s="6">
+        <v>-14.42</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5">
+      <c r="A66" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="B34" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C34" s="6">
-        <v>-7.61</v>
-      </c>
-      <c r="D34" s="6">
-        <v>-6.94</v>
-      </c>
-      <c r="E34" s="7">
-        <v>0.67</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5">
-      <c r="A35" s="5" t="s">
+      <c r="B66" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C66" s="5">
+        <v>-10.78</v>
+      </c>
+      <c r="D66" s="5">
+        <v>-33.95</v>
+      </c>
+      <c r="E66" s="6">
+        <v>-23.17</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5">
+      <c r="A67" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="B35" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C35" s="6">
-        <v>-8.83</v>
-      </c>
-      <c r="D35" s="6">
-        <v>-8.390000000000001</v>
-      </c>
-      <c r="E35" s="7">
-        <v>0.44</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5">
-      <c r="A36" s="5" t="s">
+      <c r="B67" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C67" s="5">
+        <v>-45.14</v>
+      </c>
+      <c r="D67" s="5">
+        <v>-28.2</v>
+      </c>
+      <c r="E67" s="7">
+        <v>16.94</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5">
+      <c r="A68" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="B36" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C36" s="6">
-        <v>3.83</v>
-      </c>
-      <c r="D36" s="6">
-        <v>6.65</v>
-      </c>
-      <c r="E36" s="7">
-        <v>2.82</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5">
-      <c r="A37" s="5" t="s">
+      <c r="B68" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C68" s="5">
+        <v>128.97</v>
+      </c>
+      <c r="D68" s="5">
+        <v>14.21</v>
+      </c>
+      <c r="E68" s="6">
+        <v>-114.76</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5">
+      <c r="A69" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="B37" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C37" s="6">
-        <v>-9.93</v>
-      </c>
-      <c r="D37" s="6">
-        <v>-11.2</v>
-      </c>
-      <c r="E37" s="8">
-        <v>-1.27</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5">
-      <c r="A38" s="5" t="s">
+      <c r="B69" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C69" s="5">
+        <v>-60.28</v>
+      </c>
+      <c r="D69" s="5">
+        <v>-78.52</v>
+      </c>
+      <c r="E69" s="6">
+        <v>-18.24</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5">
+      <c r="A70" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="B38" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C38" s="6">
-        <v>-9.529999999999999</v>
-      </c>
-      <c r="D38" s="6">
-        <v>-8.85</v>
-      </c>
-      <c r="E38" s="7">
-        <v>0.68</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5">
-      <c r="A39" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B39" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C39" s="6">
-        <v>-13.2</v>
-      </c>
-      <c r="D39" s="6">
-        <v>-10.36</v>
-      </c>
-      <c r="E39" s="7">
-        <v>2.84</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5">
-      <c r="A40" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B40" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C40" s="6">
-        <v>-49.93</v>
-      </c>
-      <c r="D40" s="6">
-        <v>-49.07</v>
-      </c>
-      <c r="E40" s="7">
-        <v>0.86</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5">
-      <c r="A41" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B41" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C41" s="6">
-        <v>-15.49</v>
-      </c>
-      <c r="D41" s="6">
-        <v>-14.51</v>
-      </c>
-      <c r="E41" s="7">
-        <v>0.98</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5">
-      <c r="A42" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B42" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C42" s="6">
-        <v>-22.58</v>
-      </c>
-      <c r="D42" s="6">
-        <v>-21.69</v>
-      </c>
-      <c r="E42" s="7">
-        <v>0.89</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5">
-      <c r="A43" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B43" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C43" s="6">
-        <v>-17.95</v>
-      </c>
-      <c r="D43" s="6">
-        <v>-16.67</v>
-      </c>
-      <c r="E43" s="7">
-        <v>1.28</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5">
-      <c r="A44" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B44" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C44" s="6">
-        <v>-24.14</v>
-      </c>
-      <c r="D44" s="6">
-        <v>-20.55</v>
-      </c>
-      <c r="E44" s="7">
-        <v>3.59</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5">
-      <c r="A45" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B45" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C45" s="6">
-        <v>-32.03</v>
-      </c>
-      <c r="D45" s="6">
-        <v>-32.22</v>
-      </c>
-      <c r="E45" s="8">
-        <v>-0.19</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5">
-      <c r="A46" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="B46" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C46" s="6">
-        <v>-20.12</v>
-      </c>
-      <c r="D46" s="6">
-        <v>-18.21</v>
-      </c>
-      <c r="E46" s="7">
-        <v>1.91</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5">
-      <c r="A47" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B47" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C47" s="6">
-        <v>368.65</v>
-      </c>
-      <c r="D47" s="6">
-        <v>380.7</v>
-      </c>
-      <c r="E47" s="7">
-        <v>12.05</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5">
-      <c r="A48" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B48" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C48" s="6">
-        <v>43.18</v>
-      </c>
-      <c r="D48" s="6">
-        <v>43.65</v>
-      </c>
-      <c r="E48" s="7">
-        <v>0.47</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5">
-      <c r="A49" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B49" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C49" s="6">
-        <v>2856.8</v>
-      </c>
-      <c r="D49" s="6">
-        <v>2890</v>
-      </c>
-      <c r="E49" s="7">
-        <v>33.2</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5">
-      <c r="A50" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B50" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C50" s="6">
-        <v>890.15</v>
-      </c>
-      <c r="D50" s="6">
-        <v>900.35</v>
-      </c>
-      <c r="E50" s="7">
-        <v>10.2</v>
-      </c>
-    </row>
-    <row r="51" spans="1:5">
-      <c r="A51" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B51" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C51" s="6">
-        <v>12.8</v>
-      </c>
-      <c r="D51" s="6">
-        <v>13</v>
-      </c>
-      <c r="E51" s="7">
-        <v>0.2</v>
-      </c>
-    </row>
-    <row r="52" spans="1:5">
-      <c r="A52" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B52" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C52" s="6">
-        <v>10.56</v>
-      </c>
-      <c r="D52" s="6">
-        <v>11.06</v>
-      </c>
-      <c r="E52" s="7">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="53" spans="1:5">
-      <c r="A53" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B53" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C53" s="6">
-        <v>3948.5</v>
-      </c>
-      <c r="D53" s="6">
-        <v>3937.7</v>
-      </c>
-      <c r="E53" s="8">
-        <v>-10.8</v>
-      </c>
-    </row>
-    <row r="54" spans="1:5">
-      <c r="A54" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="B54" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C54" s="6">
-        <v>10426</v>
-      </c>
-      <c r="D54" s="6">
-        <v>10675</v>
-      </c>
-      <c r="E54" s="7">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="55" spans="1:5">
-      <c r="A55" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B55" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C55" s="6">
-        <v>35.73</v>
-      </c>
-      <c r="D55" s="6">
-        <v>45.23</v>
-      </c>
-      <c r="E55" s="7">
-        <v>9.5</v>
-      </c>
-    </row>
-    <row r="56" spans="1:5">
-      <c r="A56" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B56" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C56" s="6">
-        <v>26.22</v>
-      </c>
-      <c r="D56" s="6">
-        <v>29.06</v>
-      </c>
-      <c r="E56" s="7">
-        <v>2.84</v>
-      </c>
-    </row>
-    <row r="57" spans="1:5">
-      <c r="A57" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B57" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C57" s="6">
-        <v>23.39</v>
-      </c>
-      <c r="D57" s="6">
-        <v>28.22</v>
-      </c>
-      <c r="E57" s="7">
-        <v>4.83</v>
-      </c>
-    </row>
-    <row r="58" spans="1:5">
-      <c r="A58" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B58" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C58" s="6">
-        <v>25.9</v>
-      </c>
-      <c r="D58" s="6">
-        <v>30.26</v>
-      </c>
-      <c r="E58" s="7">
-        <v>4.36</v>
-      </c>
-    </row>
-    <row r="59" spans="1:5">
-      <c r="A59" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B59" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C59" s="6">
-        <v>37.55</v>
-      </c>
-      <c r="D59" s="6">
-        <v>40.63</v>
-      </c>
-      <c r="E59" s="7">
-        <v>3.08</v>
-      </c>
-    </row>
-    <row r="60" spans="1:5">
-      <c r="A60" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B60" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C60" s="6">
-        <v>39.59</v>
-      </c>
-      <c r="D60" s="6">
-        <v>47.63</v>
-      </c>
-      <c r="E60" s="7">
-        <v>8.039999999999999</v>
-      </c>
-    </row>
-    <row r="61" spans="1:5">
-      <c r="A61" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B61" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C61" s="6">
-        <v>38.87</v>
-      </c>
-      <c r="D61" s="6">
-        <v>38.26</v>
-      </c>
-      <c r="E61" s="8">
-        <v>-0.61</v>
-      </c>
-    </row>
-    <row r="62" spans="1:5">
-      <c r="A62" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="B62" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C62" s="6">
-        <v>33.2</v>
-      </c>
-      <c r="D62" s="6">
-        <v>41.65</v>
-      </c>
-      <c r="E62" s="7">
-        <v>8.449999999999999</v>
-      </c>
-    </row>
-    <row r="63" spans="1:5">
-      <c r="A63" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B63" s="5" t="s">
+      <c r="B70" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="C63" s="6">
-        <v>58.33</v>
-      </c>
-      <c r="D63" s="6">
-        <v>116.37</v>
-      </c>
-      <c r="E63" s="7">
-        <v>58.04</v>
-      </c>
-    </row>
-    <row r="64" spans="1:5">
-      <c r="A64" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B64" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C64" s="6">
-        <v>-21.21</v>
-      </c>
-      <c r="D64" s="6">
-        <v>-42.98</v>
-      </c>
-      <c r="E64" s="8">
-        <v>-21.77</v>
-      </c>
-    </row>
-    <row r="65" spans="1:5">
-      <c r="A65" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B65" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C65" s="6">
-        <v>-31.99</v>
-      </c>
-      <c r="D65" s="6">
-        <v>-67.83</v>
-      </c>
-      <c r="E65" s="8">
-        <v>-35.84</v>
-      </c>
-    </row>
-    <row r="66" spans="1:5">
-      <c r="A66" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B66" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C66" s="6">
-        <v>-0.58</v>
-      </c>
-      <c r="D66" s="6">
-        <v>-10.78</v>
-      </c>
-      <c r="E66" s="8">
-        <v>-10.2</v>
-      </c>
-    </row>
-    <row r="67" spans="1:5">
-      <c r="A67" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B67" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C67" s="6">
-        <v>-38.29</v>
-      </c>
-      <c r="D67" s="6">
-        <v>-45.14</v>
-      </c>
-      <c r="E67" s="8">
-        <v>-6.85</v>
-      </c>
-    </row>
-    <row r="68" spans="1:5">
-      <c r="A68" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B68" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C68" s="6">
-        <v>-33.77</v>
-      </c>
-      <c r="D68" s="6">
-        <v>128.97</v>
-      </c>
-      <c r="E68" s="7">
-        <v>162.74</v>
-      </c>
-    </row>
-    <row r="69" spans="1:5">
-      <c r="A69" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B69" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C69" s="6">
-        <v>-22.65</v>
-      </c>
-      <c r="D69" s="6">
-        <v>-60.28</v>
-      </c>
-      <c r="E69" s="8">
-        <v>-37.63</v>
-      </c>
-    </row>
-    <row r="70" spans="1:5">
-      <c r="A70" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="B70" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C70" s="6">
-        <v>-24.5</v>
-      </c>
-      <c r="D70" s="6">
+      <c r="C70" s="5">
         <v>-47.81</v>
       </c>
-      <c r="E70" s="8">
-        <v>-23.31</v>
+      <c r="D70" s="5">
+        <v>-24.75</v>
+      </c>
+      <c r="E70" s="7">
+        <v>23.06</v>
       </c>
     </row>
   </sheetData>
@@ -3153,60 +3090,60 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="28" customHeight="1">
-      <c r="A1" s="9" t="s">
+      <c r="A1" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="9" t="s">
-        <v>65</v>
-      </c>
-      <c r="C1" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="D1" s="9" t="s">
-        <v>67</v>
-      </c>
-      <c r="E1" s="9" t="s">
-        <v>68</v>
-      </c>
-      <c r="F1" s="9" t="s">
-        <v>69</v>
-      </c>
-      <c r="G1" s="9" t="s">
-        <v>70</v>
-      </c>
-      <c r="H1" s="9" t="s">
-        <v>71</v>
-      </c>
-      <c r="I1" s="9" t="s">
-        <v>72</v>
+      <c r="B1" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="C1" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="D1" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="E1" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="F1" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="G1" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="H1" s="8" t="s">
+        <v>62</v>
+      </c>
+      <c r="I1" s="8" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="10" t="s">
+      <c r="A2" s="9" t="s">
         <v>45</v>
       </c>
-      <c r="B2" s="11">
+      <c r="B2" s="10">
         <v>48.44</v>
       </c>
-      <c r="C2" s="12">
+      <c r="C2" s="11">
         <v>8</v>
       </c>
-      <c r="D2" s="11">
-        <v>37.6</v>
-      </c>
-      <c r="E2" s="11">
+      <c r="D2" s="10">
+        <v>35.8</v>
+      </c>
+      <c r="E2" s="10">
         <v>40</v>
       </c>
-      <c r="F2" s="11">
-        <v>-9.1</v>
-      </c>
-      <c r="G2" s="11">
-        <v>-9.1</v>
-      </c>
-      <c r="H2" s="11">
+      <c r="F2" s="10">
+        <v>-9.9</v>
+      </c>
+      <c r="G2" s="10">
+        <v>-10</v>
+      </c>
+      <c r="H2" s="10">
         <v>56.1</v>
       </c>
-      <c r="I2" s="11">
+      <c r="I2" s="10">
         <v>0</v>
       </c>
     </row>
@@ -3308,55 +3245,55 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8">
-      <c r="A1" s="13" t="s">
+      <c r="A1" s="12" t="s">
         <v>37</v>
       </c>
-      <c r="B1" s="13" t="s">
+      <c r="B1" s="12" t="s">
         <v>43</v>
       </c>
-      <c r="C1" s="13" t="s">
+      <c r="C1" s="12" t="s">
         <v>40</v>
       </c>
-      <c r="D1" s="13" t="s">
+      <c r="D1" s="12" t="s">
         <v>39</v>
       </c>
-      <c r="E1" s="13" t="s">
+      <c r="E1" s="12" t="s">
         <v>44</v>
       </c>
-      <c r="F1" s="13" t="s">
+      <c r="F1" s="12" t="s">
         <v>41</v>
       </c>
-      <c r="G1" s="13" t="s">
+      <c r="G1" s="12" t="s">
         <v>38</v>
       </c>
-      <c r="H1" s="13" t="s">
+      <c r="H1" s="12" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="2" spans="1:8">
-      <c r="A2" s="14">
-        <v>0.2844</v>
-      </c>
-      <c r="B2" s="14">
-        <v>0.1478</v>
-      </c>
-      <c r="C2" s="14">
-        <v>0.1372</v>
-      </c>
-      <c r="D2" s="14">
-        <v>0.1237</v>
-      </c>
-      <c r="E2" s="14">
-        <v>0.083</v>
-      </c>
-      <c r="F2" s="14">
-        <v>0.0369</v>
-      </c>
-      <c r="G2" s="14">
-        <v>-0.3019</v>
-      </c>
-      <c r="H2" s="14">
-        <v>-0.3078</v>
+      <c r="A2" s="13">
+        <v>0.285</v>
+      </c>
+      <c r="B2" s="13">
+        <v>0.1496</v>
+      </c>
+      <c r="C2" s="13">
+        <v>0.1274</v>
+      </c>
+      <c r="D2" s="13">
+        <v>0.123</v>
+      </c>
+      <c r="E2" s="13">
+        <v>0.08220000000000001</v>
+      </c>
+      <c r="F2" s="13">
+        <v>0.0354</v>
+      </c>
+      <c r="G2" s="13">
+        <v>-0.3068</v>
+      </c>
+      <c r="H2" s="13">
+        <v>-0.3095</v>
       </c>
     </row>
   </sheetData>

--- a/BIRLA_GROUP_Technical_Metrics.xlsx
+++ b/BIRLA_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="276" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="305" uniqueCount="83">
   <si>
     <t>Symbol</t>
   </si>
@@ -172,7 +172,64 @@
     <t>▶  SIGNAL EVENTS (vs Previous Run)</t>
   </si>
   <si>
-    <t>No signal events detected since last run.</t>
+    <t>Signal</t>
+  </si>
+  <si>
+    <t>Change</t>
+  </si>
+  <si>
+    <t>Direction</t>
+  </si>
+  <si>
+    <t>Prev Value</t>
+  </si>
+  <si>
+    <t>Curr Value</t>
+  </si>
+  <si>
+    <t>RSI Oversold Recovery</t>
+  </si>
+  <si>
+    <t>28.8 → 36.2</t>
+  </si>
+  <si>
+    <t>🟢 BULLISH</t>
+  </si>
+  <si>
+    <t>28.8</t>
+  </si>
+  <si>
+    <t>36.2</t>
+  </si>
+  <si>
+    <t>26.5 → 33.9</t>
+  </si>
+  <si>
+    <t>26.5</t>
+  </si>
+  <si>
+    <t>33.9</t>
+  </si>
+  <si>
+    <t>27.2 → 35.0</t>
+  </si>
+  <si>
+    <t>27.2</t>
+  </si>
+  <si>
+    <t>35.0</t>
+  </si>
+  <si>
+    <t>RSI Momentum</t>
+  </si>
+  <si>
+    <t>45.3 → 53.0</t>
+  </si>
+  <si>
+    <t>45.3</t>
+  </si>
+  <si>
+    <t>53.0</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -258,14 +315,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF006100"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF9C0006"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -298,13 +355,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -374,14 +431,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -755,8 +813,8 @@
     <col min="13" max="13" width="10.7109375" customWidth="1"/>
     <col min="14" max="14" width="11.7109375" customWidth="1"/>
     <col min="15" max="15" width="10.7109375" customWidth="1"/>
-    <col min="16" max="18" width="9.7109375" customWidth="1"/>
-    <col min="19" max="19" width="10.7109375" customWidth="1"/>
+    <col min="16" max="17" width="9.7109375" customWidth="1"/>
+    <col min="18" max="19" width="10.7109375" customWidth="1"/>
     <col min="20" max="20" width="22.7109375" customWidth="1"/>
     <col min="21" max="21" width="9.7109375" customWidth="1"/>
     <col min="22" max="22" width="10.7109375" customWidth="1"/>
@@ -896,10 +954,10 @@
         <v>45</v>
       </c>
       <c r="C2">
-        <v>380.25</v>
+        <v>384.65</v>
       </c>
       <c r="D2">
-        <v>-0.12</v>
+        <v>1.16</v>
       </c>
       <c r="E2">
         <v>424.7</v>
@@ -908,46 +966,46 @@
         <v>292.25</v>
       </c>
       <c r="G2">
-        <v>-10.47</v>
+        <v>-9.43</v>
       </c>
       <c r="H2">
-        <v>30.11</v>
+        <v>31.62</v>
       </c>
       <c r="I2">
-        <v>0.76</v>
+        <v>1.52</v>
       </c>
       <c r="J2">
-        <v>-4.94</v>
+        <v>-3.84</v>
       </c>
       <c r="K2">
-        <v>-6.68</v>
+        <v>-3.66</v>
       </c>
       <c r="L2">
-        <v>25.29</v>
+        <v>30.28</v>
       </c>
       <c r="M2">
-        <v>28.5</v>
+        <v>28.99</v>
       </c>
       <c r="N2">
         <v>74</v>
       </c>
       <c r="O2">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="P2">
-        <v>376.12</v>
+        <v>377.27</v>
       </c>
       <c r="Q2">
-        <v>385.62</v>
+        <v>385.1</v>
       </c>
       <c r="R2">
-        <v>398.52</v>
+        <v>398.12</v>
       </c>
       <c r="S2">
-        <v>365.41</v>
+        <v>365.6</v>
       </c>
       <c r="T2">
-        <v>4.06</v>
+        <v>5.21</v>
       </c>
       <c r="U2" t="s">
         <v>46</v>
@@ -962,34 +1020,34 @@
         <v>2</v>
       </c>
       <c r="Y2">
-        <v>44.97</v>
+        <v>48.19</v>
       </c>
       <c r="Z2">
-        <v>-6.38</v>
+        <v>-5.59</v>
       </c>
       <c r="AA2">
-        <v>-5.87</v>
+        <v>-5.81</v>
       </c>
       <c r="AB2">
-        <v>-0.51</v>
+        <v>0.23</v>
       </c>
       <c r="AC2">
-        <v>38.74</v>
+        <v>64.95</v>
       </c>
       <c r="AD2">
-        <v>22.07</v>
+        <v>41</v>
       </c>
       <c r="AE2">
-        <v>9.699999999999999</v>
+        <v>9.57</v>
       </c>
       <c r="AF2">
-        <v>12.95</v>
+        <v>29.47</v>
       </c>
       <c r="AG2">
-        <v>407.99</v>
+        <v>407.04</v>
       </c>
       <c r="AH2">
-        <v>363.25</v>
+        <v>363.17</v>
       </c>
       <c r="AI2">
         <v>398.61</v>
@@ -998,7 +1056,7 @@
         <v>48</v>
       </c>
       <c r="AK2">
-        <v>30.15</v>
+        <v>26.43</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1009,10 +1067,10 @@
         <v>45</v>
       </c>
       <c r="C3">
-        <v>43.53</v>
+        <v>44.78</v>
       </c>
       <c r="D3">
-        <v>-0.27</v>
+        <v>2.87</v>
       </c>
       <c r="E3">
         <v>85.38</v>
@@ -1021,46 +1079,46 @@
         <v>43.18</v>
       </c>
       <c r="G3">
-        <v>-49.02</v>
+        <v>-47.55</v>
       </c>
       <c r="H3">
-        <v>0.8100000000000001</v>
+        <v>3.71</v>
       </c>
       <c r="I3">
-        <v>-1.83</v>
+        <v>-1.97</v>
       </c>
       <c r="J3">
-        <v>-15.2</v>
+        <v>-12.01</v>
       </c>
       <c r="K3">
-        <v>-28.06</v>
+        <v>-24.01</v>
       </c>
       <c r="L3">
-        <v>-49.21</v>
+        <v>-47.2</v>
       </c>
       <c r="M3">
-        <v>-30.68</v>
+        <v>-30.19</v>
       </c>
       <c r="N3">
         <v>13</v>
       </c>
       <c r="O3">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="P3">
-        <v>44.13</v>
+        <v>43.95</v>
       </c>
       <c r="Q3">
-        <v>47.24</v>
+        <v>46.96</v>
       </c>
       <c r="R3">
-        <v>52.3</v>
+        <v>51.99</v>
       </c>
       <c r="S3">
-        <v>61.31</v>
+        <v>61.14</v>
       </c>
       <c r="T3">
-        <v>-29</v>
+        <v>-26.76</v>
       </c>
       <c r="U3" t="s">
         <v>46</v>
@@ -1075,34 +1133,34 @@
         <v>0</v>
       </c>
       <c r="Y3">
-        <v>28.76</v>
+        <v>36.25</v>
       </c>
       <c r="Z3">
-        <v>-2.43</v>
+        <v>-2.3</v>
       </c>
       <c r="AA3">
-        <v>-2.24</v>
+        <v>-2.25</v>
       </c>
       <c r="AB3">
-        <v>-0.19</v>
+        <v>-0.05</v>
       </c>
       <c r="AC3">
-        <v>32.53</v>
+        <v>58.5</v>
       </c>
       <c r="AD3">
-        <v>35.98</v>
+        <v>41.65</v>
       </c>
       <c r="AE3">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="AF3">
-        <v>-65.11</v>
+        <v>-44.73</v>
       </c>
       <c r="AG3">
-        <v>52.41</v>
+        <v>52.01</v>
       </c>
       <c r="AH3">
-        <v>42.07</v>
+        <v>41.91</v>
       </c>
       <c r="AI3">
         <v>48.29</v>
@@ -1111,7 +1169,7 @@
         <v>48</v>
       </c>
       <c r="AK3">
-        <v>42.02</v>
+        <v>37.92</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1122,10 +1180,10 @@
         <v>45</v>
       </c>
       <c r="C4">
-        <v>2858</v>
+        <v>2912</v>
       </c>
       <c r="D4">
-        <v>-1.11</v>
+        <v>1.89</v>
       </c>
       <c r="E4">
         <v>3380.5</v>
@@ -1134,46 +1192,46 @@
         <v>2531.1</v>
       </c>
       <c r="G4">
-        <v>-15.46</v>
+        <v>-13.86</v>
       </c>
       <c r="H4">
-        <v>12.92</v>
+        <v>15.05</v>
       </c>
       <c r="I4">
-        <v>-3.84</v>
+        <v>-1.92</v>
       </c>
       <c r="J4">
-        <v>-13.39</v>
+        <v>-12.26</v>
       </c>
       <c r="K4">
-        <v>-9.109999999999999</v>
+        <v>-6.47</v>
       </c>
       <c r="L4">
-        <v>1.78</v>
+        <v>4.82</v>
       </c>
       <c r="M4">
-        <v>12.3</v>
+        <v>12.19</v>
       </c>
       <c r="N4">
         <v>50</v>
       </c>
       <c r="O4">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="P4">
-        <v>2898.98</v>
+        <v>2887.58</v>
       </c>
       <c r="Q4">
-        <v>3080.16</v>
+        <v>3061.67</v>
       </c>
       <c r="R4">
-        <v>3200.98</v>
+        <v>3197.2</v>
       </c>
       <c r="S4">
-        <v>2979.89</v>
+        <v>2980.3</v>
       </c>
       <c r="T4">
-        <v>-4.09</v>
+        <v>-2.29</v>
       </c>
       <c r="U4" t="s">
         <v>46</v>
@@ -1188,34 +1246,34 @@
         <v>1</v>
       </c>
       <c r="Y4">
-        <v>26.49</v>
+        <v>33.88</v>
       </c>
       <c r="Z4">
-        <v>-96.41</v>
+        <v>-95.06</v>
       </c>
       <c r="AA4">
-        <v>-69.87</v>
+        <v>-74.91</v>
       </c>
       <c r="AB4">
-        <v>-26.54</v>
+        <v>-20.16</v>
       </c>
       <c r="AC4">
-        <v>11.88</v>
+        <v>27.58</v>
       </c>
       <c r="AD4">
-        <v>7.13</v>
+        <v>15.56</v>
       </c>
       <c r="AE4">
-        <v>61.84</v>
+        <v>62.13</v>
       </c>
       <c r="AF4">
-        <v>-82.25</v>
+        <v>-47.74</v>
       </c>
       <c r="AG4">
-        <v>3344.19</v>
+        <v>3317.9</v>
       </c>
       <c r="AH4">
-        <v>2816.13</v>
+        <v>2805.43</v>
       </c>
       <c r="AI4">
         <v>3061.2</v>
@@ -1224,7 +1282,7 @@
         <v>48</v>
       </c>
       <c r="AK4">
-        <v>66.5</v>
+        <v>66.40000000000001</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1235,10 +1293,10 @@
         <v>45</v>
       </c>
       <c r="C5">
-        <v>882.5</v>
+        <v>902.25</v>
       </c>
       <c r="D5">
-        <v>-1.98</v>
+        <v>2.24</v>
       </c>
       <c r="E5">
         <v>1149.7</v>
@@ -1247,46 +1305,46 @@
         <v>760.1</v>
       </c>
       <c r="G5">
-        <v>-23.24</v>
+        <v>-21.52</v>
       </c>
       <c r="H5">
-        <v>16.1</v>
+        <v>18.7</v>
       </c>
       <c r="I5">
-        <v>-5.96</v>
+        <v>-4.07</v>
       </c>
       <c r="J5">
-        <v>-14.06</v>
+        <v>-11.02</v>
       </c>
       <c r="K5">
-        <v>-8.720000000000001</v>
+        <v>-7.4</v>
       </c>
       <c r="L5">
-        <v>14.94</v>
+        <v>17.45</v>
       </c>
       <c r="M5">
-        <v>12.74</v>
+        <v>12.82</v>
       </c>
       <c r="N5">
         <v>62</v>
       </c>
       <c r="O5">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="P5">
-        <v>904.87</v>
+        <v>897.22</v>
       </c>
       <c r="Q5">
-        <v>952.72</v>
+        <v>948.76</v>
       </c>
       <c r="R5">
-        <v>999.25</v>
+        <v>997.8099999999999</v>
       </c>
       <c r="S5">
-        <v>982.9299999999999</v>
+        <v>983.13</v>
       </c>
       <c r="T5">
-        <v>-10.22</v>
+        <v>-8.23</v>
       </c>
       <c r="U5" t="s">
         <v>46</v>
@@ -1301,43 +1359,43 @@
         <v>1</v>
       </c>
       <c r="Y5">
-        <v>27.24</v>
+        <v>34.98</v>
       </c>
       <c r="Z5">
-        <v>-28.43</v>
+        <v>-28.4</v>
       </c>
       <c r="AA5">
-        <v>-21.03</v>
+        <v>-22.51</v>
       </c>
       <c r="AB5">
-        <v>-7.4</v>
+        <v>-5.89</v>
       </c>
       <c r="AC5">
-        <v>7.75</v>
+        <v>20.07</v>
       </c>
       <c r="AD5">
-        <v>5.22</v>
+        <v>11.25</v>
       </c>
       <c r="AE5">
-        <v>21.93</v>
+        <v>21.78</v>
       </c>
       <c r="AF5">
-        <v>-33.95</v>
+        <v>33.07</v>
       </c>
       <c r="AG5">
-        <v>1021.4</v>
+        <v>1019.56</v>
       </c>
       <c r="AH5">
-        <v>884.04</v>
+        <v>877.96</v>
       </c>
       <c r="AI5">
-        <v>958.48</v>
+        <v>957.78</v>
       </c>
       <c r="AJ5" t="s">
         <v>48</v>
       </c>
       <c r="AK5">
-        <v>45.43</v>
+        <v>46.28</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1348,10 +1406,10 @@
         <v>45</v>
       </c>
       <c r="C6">
-        <v>12.67</v>
+        <v>12.8</v>
       </c>
       <c r="D6">
-        <v>-2.54</v>
+        <v>1.03</v>
       </c>
       <c r="E6">
         <v>15.6</v>
@@ -1360,37 +1418,37 @@
         <v>8.359999999999999</v>
       </c>
       <c r="G6">
-        <v>-18.78</v>
+        <v>-17.95</v>
       </c>
       <c r="H6">
-        <v>51.56</v>
+        <v>53.11</v>
       </c>
       <c r="I6">
-        <v>-0.55</v>
+        <v>-3.1</v>
       </c>
       <c r="J6">
-        <v>-18.36</v>
+        <v>-14.09</v>
       </c>
       <c r="K6">
-        <v>-9.24</v>
+        <v>-7.45</v>
       </c>
       <c r="L6">
-        <v>38.02</v>
+        <v>41.59</v>
       </c>
       <c r="M6">
-        <v>3.54</v>
+        <v>3.65</v>
       </c>
       <c r="N6">
         <v>87</v>
       </c>
       <c r="O6">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="P6">
-        <v>12.97</v>
+        <v>12.89</v>
       </c>
       <c r="Q6">
-        <v>13.65</v>
+        <v>13.54</v>
       </c>
       <c r="R6">
         <v>13.89</v>
@@ -1399,7 +1457,7 @@
         <v>12.29</v>
       </c>
       <c r="T6">
-        <v>3.12</v>
+        <v>4.14</v>
       </c>
       <c r="U6" t="s">
         <v>46</v>
@@ -1414,43 +1472,43 @@
         <v>2</v>
       </c>
       <c r="Y6">
-        <v>37.35</v>
+        <v>39.42</v>
       </c>
       <c r="Z6">
-        <v>-0.4</v>
+        <v>-0.41</v>
       </c>
       <c r="AA6">
-        <v>-0.29</v>
+        <v>-0.31</v>
       </c>
       <c r="AB6">
-        <v>-0.11</v>
+        <v>-0.09</v>
       </c>
       <c r="AC6">
-        <v>28.85</v>
+        <v>32.09</v>
       </c>
       <c r="AD6">
-        <v>34.01</v>
+        <v>32.22</v>
       </c>
       <c r="AE6">
-        <v>0.47</v>
+        <v>0.46</v>
       </c>
       <c r="AF6">
-        <v>-28.2</v>
+        <v>-45.87</v>
       </c>
       <c r="AG6">
-        <v>15.09</v>
+        <v>14.89</v>
       </c>
       <c r="AH6">
-        <v>12.21</v>
+        <v>12.2</v>
       </c>
       <c r="AI6">
-        <v>14.25</v>
+        <v>14.1</v>
       </c>
       <c r="AJ6" t="s">
         <v>48</v>
       </c>
       <c r="AK6">
-        <v>39.13</v>
+        <v>40.26</v>
       </c>
     </row>
     <row r="7" spans="1:37">
@@ -1461,10 +1519,10 @@
         <v>45</v>
       </c>
       <c r="C7">
-        <v>10.88</v>
+        <v>11.44</v>
       </c>
       <c r="D7">
-        <v>-1.63</v>
+        <v>5.15</v>
       </c>
       <c r="E7">
         <v>13.92</v>
@@ -1473,46 +1531,46 @@
         <v>4.69</v>
       </c>
       <c r="G7">
-        <v>-21.84</v>
+        <v>-17.82</v>
       </c>
       <c r="H7">
-        <v>131.98</v>
+        <v>143.92</v>
       </c>
       <c r="I7">
-        <v>6.15</v>
+        <v>6.32</v>
       </c>
       <c r="J7">
-        <v>-5.8</v>
+        <v>-2.89</v>
       </c>
       <c r="K7">
-        <v>3.03</v>
+        <v>6.22</v>
       </c>
       <c r="L7">
-        <v>100</v>
+        <v>108.38</v>
       </c>
       <c r="M7">
-        <v>-30.95</v>
+        <v>-30.53</v>
       </c>
       <c r="N7">
         <v>99</v>
       </c>
       <c r="O7">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="P7">
-        <v>10.81</v>
+        <v>10.95</v>
       </c>
       <c r="Q7">
-        <v>11.33</v>
+        <v>11.3</v>
       </c>
       <c r="R7">
-        <v>11.63</v>
+        <v>11.61</v>
       </c>
       <c r="S7">
         <v>10.84</v>
       </c>
       <c r="T7">
-        <v>0.33</v>
+        <v>5.5</v>
       </c>
       <c r="U7" t="s">
         <v>46</v>
@@ -1527,34 +1585,34 @@
         <v>2</v>
       </c>
       <c r="Y7">
-        <v>45.29</v>
+        <v>53.02</v>
       </c>
       <c r="Z7">
-        <v>-0.24</v>
+        <v>-0.18</v>
       </c>
       <c r="AA7">
         <v>-0.2</v>
       </c>
       <c r="AB7">
-        <v>-0.03</v>
+        <v>0.02</v>
       </c>
       <c r="AC7">
-        <v>68.47</v>
+        <v>90.69</v>
       </c>
       <c r="AD7">
-        <v>51.71</v>
+        <v>70.86</v>
       </c>
       <c r="AE7">
-        <v>0.58</v>
+        <v>0.62</v>
       </c>
       <c r="AF7">
-        <v>14.21</v>
+        <v>48.21</v>
       </c>
       <c r="AG7">
-        <v>12.65</v>
+        <v>12.58</v>
       </c>
       <c r="AH7">
-        <v>10.01</v>
+        <v>10.02</v>
       </c>
       <c r="AI7">
         <v>12.04</v>
@@ -1563,7 +1621,7 @@
         <v>48</v>
       </c>
       <c r="AK7">
-        <v>28.72</v>
+        <v>28.22</v>
       </c>
     </row>
     <row r="8" spans="1:37">
@@ -1574,10 +1632,10 @@
         <v>45</v>
       </c>
       <c r="C8">
-        <v>3934.9</v>
+        <v>3949.6</v>
       </c>
       <c r="D8">
-        <v>-0.07000000000000001</v>
+        <v>0.37</v>
       </c>
       <c r="E8">
         <v>5809.5</v>
@@ -1586,25 +1644,25 @@
         <v>3892.3</v>
       </c>
       <c r="G8">
-        <v>-32.27</v>
+        <v>-32.01</v>
       </c>
       <c r="H8">
-        <v>1.09</v>
+        <v>1.47</v>
       </c>
       <c r="I8">
-        <v>-1.25</v>
+        <v>-2.89</v>
       </c>
       <c r="J8">
-        <v>-4.26</v>
+        <v>-6.76</v>
       </c>
       <c r="K8">
-        <v>-11.76</v>
+        <v>-9.460000000000001</v>
       </c>
       <c r="L8">
-        <v>-27.04</v>
+        <v>-26.25</v>
       </c>
       <c r="M8">
-        <v>14.96</v>
+        <v>15.11</v>
       </c>
       <c r="N8">
         <v>26</v>
@@ -1613,19 +1671,19 @@
         <v>31</v>
       </c>
       <c r="P8">
-        <v>3992.9</v>
+        <v>3969.4</v>
       </c>
       <c r="Q8">
-        <v>4019.87</v>
+        <v>4007.77</v>
       </c>
       <c r="R8">
-        <v>4221.13</v>
+        <v>4214.06</v>
       </c>
       <c r="S8">
-        <v>4493.89</v>
+        <v>4487.81</v>
       </c>
       <c r="T8">
-        <v>-12.44</v>
+        <v>-11.99</v>
       </c>
       <c r="U8" t="s">
         <v>46</v>
@@ -1640,43 +1698,43 @@
         <v>0</v>
       </c>
       <c r="Y8">
-        <v>38.09</v>
+        <v>39.58</v>
       </c>
       <c r="Z8">
-        <v>-75.2</v>
+        <v>-73.40000000000001</v>
       </c>
       <c r="AA8">
-        <v>-79.40000000000001</v>
+        <v>-78.2</v>
       </c>
       <c r="AB8">
-        <v>4.2</v>
+        <v>4.8</v>
       </c>
       <c r="AC8">
-        <v>51.88</v>
+        <v>53.19</v>
       </c>
       <c r="AD8">
-        <v>68.39</v>
+        <v>57.86</v>
       </c>
       <c r="AE8">
-        <v>106.33</v>
+        <v>103.49</v>
       </c>
       <c r="AF8">
-        <v>-78.52</v>
+        <v>-68.20999999999999</v>
       </c>
       <c r="AG8">
-        <v>4155.9</v>
+        <v>4120.55</v>
       </c>
       <c r="AH8">
-        <v>3883.83</v>
+        <v>3894.98</v>
       </c>
       <c r="AI8">
-        <v>4247.59</v>
+        <v>4246.97</v>
       </c>
       <c r="AJ8" t="s">
         <v>48</v>
       </c>
       <c r="AK8">
-        <v>38.44</v>
+        <v>38.53</v>
       </c>
     </row>
     <row r="9" spans="1:37">
@@ -1687,10 +1745,10 @@
         <v>45</v>
       </c>
       <c r="C9">
-        <v>10520</v>
+        <v>10750</v>
       </c>
       <c r="D9">
-        <v>-1.45</v>
+        <v>2.19</v>
       </c>
       <c r="E9">
         <v>13052</v>
@@ -1699,46 +1757,46 @@
         <v>10362</v>
       </c>
       <c r="G9">
-        <v>-19.4</v>
+        <v>-17.64</v>
       </c>
       <c r="H9">
-        <v>1.52</v>
+        <v>3.74</v>
       </c>
       <c r="I9">
-        <v>-3.04</v>
+        <v>0</v>
       </c>
       <c r="J9">
-        <v>-3.49</v>
+        <v>-2.09</v>
       </c>
       <c r="K9">
-        <v>-9.08</v>
+        <v>-6.49</v>
       </c>
       <c r="L9">
-        <v>-13.66</v>
+        <v>-10.35</v>
       </c>
       <c r="M9">
-        <v>8.220000000000001</v>
+        <v>8.390000000000001</v>
       </c>
       <c r="N9">
         <v>38</v>
       </c>
       <c r="O9">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="P9">
         <v>10605.8</v>
       </c>
       <c r="Q9">
-        <v>10852</v>
+        <v>10839.5</v>
       </c>
       <c r="R9">
-        <v>11304.4</v>
+        <v>11281.34</v>
       </c>
       <c r="S9">
-        <v>11681.12</v>
+        <v>11676.48</v>
       </c>
       <c r="T9">
-        <v>-9.94</v>
+        <v>-7.93</v>
       </c>
       <c r="U9" t="s">
         <v>46</v>
@@ -1753,34 +1811,34 @@
         <v>0</v>
       </c>
       <c r="Y9">
-        <v>38.4</v>
+        <v>45.23</v>
       </c>
       <c r="Z9">
-        <v>-189.12</v>
+        <v>-174.85</v>
       </c>
       <c r="AA9">
-        <v>-168.57</v>
+        <v>-169.82</v>
       </c>
       <c r="AB9">
-        <v>-20.55</v>
+        <v>-5.03</v>
       </c>
       <c r="AC9">
-        <v>30.48</v>
+        <v>57.37</v>
       </c>
       <c r="AD9">
-        <v>32.53</v>
+        <v>40.22</v>
       </c>
       <c r="AE9">
-        <v>219.59</v>
+        <v>224.19</v>
       </c>
       <c r="AF9">
-        <v>-24.75</v>
+        <v>-32.54</v>
       </c>
       <c r="AG9">
-        <v>11273.57</v>
+        <v>11257.4</v>
       </c>
       <c r="AH9">
-        <v>10430.43</v>
+        <v>10421.6</v>
       </c>
       <c r="AI9">
         <v>11169.72</v>
@@ -1789,7 +1847,7 @@
         <v>48</v>
       </c>
       <c r="AK9">
-        <v>41.79</v>
+        <v>41.61</v>
       </c>
     </row>
   </sheetData>
@@ -1930,7 +1988,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F70"/>
+  <dimension ref="A1:F73"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -1950,1127 +2008,1222 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="3" t="s">
         <v>50</v>
       </c>
+      <c r="C2" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
+      <c r="A4" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>62</v>
+      </c>
     </row>
     <row r="5" spans="1:6">
-      <c r="A5" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="B5" s="2"/>
-      <c r="C5" s="2"/>
-      <c r="D5" s="2"/>
-      <c r="E5" s="2"/>
+      <c r="A5" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="E5" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="F5" s="4" t="s">
+        <v>65</v>
+      </c>
     </row>
     <row r="6" spans="1:6">
       <c r="A6" s="4" t="s">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>52</v>
+        <v>66</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>53</v>
+        <v>67</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6">
-      <c r="A7" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C7" s="5">
-        <v>-4.09</v>
-      </c>
-      <c r="D7" s="5">
-        <v>-4.94</v>
-      </c>
-      <c r="E7" s="6">
-        <v>-0.85</v>
+        <v>68</v>
+      </c>
+      <c r="F6" s="4" t="s">
+        <v>69</v>
       </c>
     </row>
     <row r="8" spans="1:6">
-      <c r="A8" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B8" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C8" s="5">
-        <v>-16.44</v>
-      </c>
-      <c r="D8" s="5">
-        <v>-15.2</v>
-      </c>
-      <c r="E8" s="7">
-        <v>1.24</v>
-      </c>
+      <c r="A8" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="B8" s="2"/>
+      <c r="C8" s="2"/>
+      <c r="D8" s="2"/>
+      <c r="E8" s="2"/>
     </row>
     <row r="9" spans="1:6">
       <c r="A9" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C10" s="6">
+        <v>-4.94</v>
+      </c>
+      <c r="D10" s="6">
+        <v>-3.84</v>
+      </c>
+      <c r="E10" s="7">
+        <v>1.1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B11" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C11" s="6">
+        <v>-15.2</v>
+      </c>
+      <c r="D11" s="6">
+        <v>-12.01</v>
+      </c>
+      <c r="E11" s="7">
+        <v>3.19</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B9" s="3" t="s">
+      <c r="B12" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C9" s="5">
-        <v>-12.6</v>
-      </c>
-      <c r="D9" s="5">
+      <c r="C12" s="6">
         <v>-13.39</v>
       </c>
-      <c r="E9" s="6">
-        <v>-0.79</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10" s="3" t="s">
+      <c r="D12" s="6">
+        <v>-12.26</v>
+      </c>
+      <c r="E12" s="7">
+        <v>1.13</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="A13" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B10" s="3" t="s">
+      <c r="B13" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C10" s="5">
-        <v>-10.77</v>
-      </c>
-      <c r="D10" s="5">
+      <c r="C13" s="6">
         <v>-14.06</v>
       </c>
-      <c r="E10" s="6">
-        <v>-3.29</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11" s="3" t="s">
+      <c r="D13" s="6">
+        <v>-11.02</v>
+      </c>
+      <c r="E13" s="7">
+        <v>3.04</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B11" s="3" t="s">
+      <c r="B14" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C11" s="5">
-        <v>-15.69</v>
-      </c>
-      <c r="D11" s="5">
+      <c r="C14" s="6">
         <v>-18.36</v>
       </c>
-      <c r="E11" s="6">
-        <v>-2.67</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12" s="3" t="s">
+      <c r="D14" s="6">
+        <v>-14.09</v>
+      </c>
+      <c r="E14" s="7">
+        <v>4.27</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="A15" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="B12" s="3" t="s">
+      <c r="B15" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C12" s="5">
-        <v>-2.38</v>
-      </c>
-      <c r="D12" s="5">
+      <c r="C15" s="6">
         <v>-5.8</v>
       </c>
-      <c r="E12" s="6">
-        <v>-3.42</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13" s="3" t="s">
+      <c r="D15" s="6">
+        <v>-2.89</v>
+      </c>
+      <c r="E15" s="7">
+        <v>2.91</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="A16" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="B13" s="3" t="s">
+      <c r="B16" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C13" s="5">
-        <v>-7.6</v>
-      </c>
-      <c r="D13" s="5">
+      <c r="C16" s="6">
         <v>-4.26</v>
       </c>
-      <c r="E13" s="7">
-        <v>3.34</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14" s="3" t="s">
+      <c r="D16" s="6">
+        <v>-6.76</v>
+      </c>
+      <c r="E16" s="8">
+        <v>-2.5</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="B14" s="3" t="s">
+      <c r="B17" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C14" s="5">
-        <v>-3.03</v>
-      </c>
-      <c r="D14" s="5">
+      <c r="C17" s="6">
         <v>-3.49</v>
       </c>
-      <c r="E14" s="6">
-        <v>-0.46</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15" s="3" t="s">
+      <c r="D17" s="6">
+        <v>-2.09</v>
+      </c>
+      <c r="E17" s="7">
+        <v>1.4</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B15" s="3" t="s">
+      <c r="B18" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="C15" s="5">
-        <v>1.51</v>
-      </c>
-      <c r="D15" s="5">
+      <c r="C18" s="6">
         <v>0.76</v>
       </c>
-      <c r="E15" s="6">
-        <v>-0.75</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16" s="3" t="s">
+      <c r="D18" s="6">
+        <v>1.52</v>
+      </c>
+      <c r="E18" s="7">
+        <v>0.76</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B16" s="3" t="s">
+      <c r="B19" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="C16" s="5">
-        <v>-1.98</v>
-      </c>
-      <c r="D16" s="5">
+      <c r="C19" s="6">
         <v>-1.83</v>
       </c>
-      <c r="E16" s="7">
-        <v>0.15</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5">
-      <c r="A17" s="3" t="s">
+      <c r="D19" s="6">
+        <v>-1.97</v>
+      </c>
+      <c r="E19" s="8">
+        <v>-0.14</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B17" s="3" t="s">
+      <c r="B20" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="C17" s="5">
-        <v>-2.43</v>
-      </c>
-      <c r="D17" s="5">
+      <c r="C20" s="6">
         <v>-3.84</v>
       </c>
-      <c r="E17" s="6">
-        <v>-1.41</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5">
-      <c r="A18" s="3" t="s">
+      <c r="D20" s="6">
+        <v>-1.92</v>
+      </c>
+      <c r="E20" s="7">
+        <v>1.92</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B18" s="3" t="s">
+      <c r="B21" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="C18" s="5">
-        <v>-4.41</v>
-      </c>
-      <c r="D18" s="5">
+      <c r="C21" s="6">
         <v>-5.96</v>
       </c>
-      <c r="E18" s="6">
-        <v>-1.55</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5">
-      <c r="A19" s="3" t="s">
+      <c r="D21" s="6">
+        <v>-4.07</v>
+      </c>
+      <c r="E21" s="7">
+        <v>1.89</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B19" s="3" t="s">
+      <c r="B22" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="C19" s="5">
-        <v>2.85</v>
-      </c>
-      <c r="D19" s="5">
+      <c r="C22" s="6">
         <v>-0.55</v>
       </c>
-      <c r="E19" s="6">
-        <v>-3.4</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5">
-      <c r="A20" s="3" t="s">
+      <c r="D22" s="6">
+        <v>-3.1</v>
+      </c>
+      <c r="E22" s="8">
+        <v>-2.55</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="B20" s="3" t="s">
+      <c r="B23" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="C20" s="5">
-        <v>3.08</v>
-      </c>
-      <c r="D20" s="5">
+      <c r="C23" s="6">
         <v>6.15</v>
       </c>
-      <c r="E20" s="7">
-        <v>3.07</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5">
-      <c r="A21" s="3" t="s">
+      <c r="D23" s="6">
+        <v>6.32</v>
+      </c>
+      <c r="E23" s="7">
+        <v>0.17</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="B21" s="3" t="s">
+      <c r="B24" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="C21" s="5">
-        <v>1.17</v>
-      </c>
-      <c r="D21" s="5">
+      <c r="C24" s="6">
         <v>-1.25</v>
       </c>
-      <c r="E21" s="6">
-        <v>-2.42</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5">
-      <c r="A22" s="3" t="s">
+      <c r="D24" s="6">
+        <v>-2.89</v>
+      </c>
+      <c r="E24" s="8">
+        <v>-1.64</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="B22" s="3" t="s">
+      <c r="B25" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="C22" s="5">
-        <v>-0.33</v>
-      </c>
-      <c r="D22" s="5">
+      <c r="C25" s="6">
         <v>-3.04</v>
       </c>
-      <c r="E22" s="6">
-        <v>-2.71</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5">
-      <c r="A23" s="3" t="s">
+      <c r="D25" s="6">
+        <v>0</v>
+      </c>
+      <c r="E25" s="7">
+        <v>3.04</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B23" s="3" t="s">
+      <c r="B26" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="C23" s="5">
-        <v>25.21</v>
-      </c>
-      <c r="D23" s="5">
+      <c r="C26" s="6">
         <v>25.29</v>
       </c>
-      <c r="E23" s="7">
-        <v>0.08</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5">
-      <c r="A24" s="3" t="s">
+      <c r="D26" s="6">
+        <v>30.28</v>
+      </c>
+      <c r="E26" s="7">
+        <v>4.99</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B24" s="3" t="s">
+      <c r="B27" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="C24" s="5">
-        <v>-49.39</v>
-      </c>
-      <c r="D24" s="5">
+      <c r="C27" s="6">
         <v>-49.21</v>
       </c>
-      <c r="E24" s="7">
-        <v>0.18</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5">
-      <c r="A25" s="3" t="s">
+      <c r="D27" s="6">
+        <v>-47.2</v>
+      </c>
+      <c r="E27" s="7">
+        <v>2.01</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B25" s="3" t="s">
+      <c r="B28" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="C25" s="5">
-        <v>2.94</v>
-      </c>
-      <c r="D25" s="5">
+      <c r="C28" s="6">
         <v>1.78</v>
       </c>
-      <c r="E25" s="6">
-        <v>-1.16</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5">
-      <c r="A26" s="3" t="s">
+      <c r="D28" s="6">
+        <v>4.82</v>
+      </c>
+      <c r="E28" s="7">
+        <v>3.04</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B26" s="3" t="s">
+      <c r="B29" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="C26" s="5">
-        <v>15.92</v>
-      </c>
-      <c r="D26" s="5">
+      <c r="C29" s="6">
         <v>14.94</v>
       </c>
-      <c r="E26" s="6">
-        <v>-0.98</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5">
-      <c r="A27" s="3" t="s">
+      <c r="D29" s="6">
+        <v>17.45</v>
+      </c>
+      <c r="E29" s="7">
+        <v>2.51</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B27" s="3" t="s">
+      <c r="B30" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="C27" s="5">
-        <v>53.48</v>
-      </c>
-      <c r="D27" s="5">
+      <c r="C30" s="6">
         <v>38.02</v>
       </c>
-      <c r="E27" s="6">
+      <c r="D30" s="6">
+        <v>41.59</v>
+      </c>
+      <c r="E30" s="7">
+        <v>3.57</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5">
+      <c r="A31" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B31" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C31" s="6">
+        <v>100</v>
+      </c>
+      <c r="D31" s="6">
+        <v>108.38</v>
+      </c>
+      <c r="E31" s="7">
+        <v>8.380000000000001</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5">
+      <c r="A32" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B32" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C32" s="6">
+        <v>-27.04</v>
+      </c>
+      <c r="D32" s="6">
+        <v>-26.25</v>
+      </c>
+      <c r="E32" s="7">
+        <v>0.79</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5">
+      <c r="A33" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="B33" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C33" s="6">
+        <v>-13.66</v>
+      </c>
+      <c r="D33" s="6">
+        <v>-10.35</v>
+      </c>
+      <c r="E33" s="7">
+        <v>3.31</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5">
+      <c r="A34" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B34" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C34" s="6">
+        <v>-6.68</v>
+      </c>
+      <c r="D34" s="6">
+        <v>-3.66</v>
+      </c>
+      <c r="E34" s="7">
+        <v>3.02</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5">
+      <c r="A35" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B35" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C35" s="6">
+        <v>-28.06</v>
+      </c>
+      <c r="D35" s="6">
+        <v>-24.01</v>
+      </c>
+      <c r="E35" s="7">
+        <v>4.05</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5">
+      <c r="A36" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B36" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C36" s="6">
+        <v>-9.109999999999999</v>
+      </c>
+      <c r="D36" s="6">
+        <v>-6.47</v>
+      </c>
+      <c r="E36" s="7">
+        <v>2.64</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5">
+      <c r="A37" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B37" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C37" s="6">
+        <v>-8.720000000000001</v>
+      </c>
+      <c r="D37" s="6">
+        <v>-7.4</v>
+      </c>
+      <c r="E37" s="7">
+        <v>1.32</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5">
+      <c r="A38" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B38" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C38" s="6">
+        <v>-9.24</v>
+      </c>
+      <c r="D38" s="6">
+        <v>-7.45</v>
+      </c>
+      <c r="E38" s="7">
+        <v>1.79</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5">
+      <c r="A39" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B39" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C39" s="6">
+        <v>3.03</v>
+      </c>
+      <c r="D39" s="6">
+        <v>6.22</v>
+      </c>
+      <c r="E39" s="7">
+        <v>3.19</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5">
+      <c r="A40" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B40" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C40" s="6">
+        <v>-11.76</v>
+      </c>
+      <c r="D40" s="6">
+        <v>-9.460000000000001</v>
+      </c>
+      <c r="E40" s="7">
+        <v>2.3</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5">
+      <c r="A41" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="B41" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C41" s="6">
+        <v>-9.08</v>
+      </c>
+      <c r="D41" s="6">
+        <v>-6.49</v>
+      </c>
+      <c r="E41" s="7">
+        <v>2.59</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5">
+      <c r="A42" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B42" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C42" s="6">
+        <v>-10.47</v>
+      </c>
+      <c r="D42" s="6">
+        <v>-9.43</v>
+      </c>
+      <c r="E42" s="7">
+        <v>1.04</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5">
+      <c r="A43" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B43" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C43" s="6">
+        <v>-49.02</v>
+      </c>
+      <c r="D43" s="6">
+        <v>-47.55</v>
+      </c>
+      <c r="E43" s="7">
+        <v>1.47</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5">
+      <c r="A44" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B44" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C44" s="6">
         <v>-15.46</v>
       </c>
-    </row>
-    <row r="28" spans="1:5">
-      <c r="A28" s="3" t="s">
+      <c r="D44" s="6">
+        <v>-13.86</v>
+      </c>
+      <c r="E44" s="7">
+        <v>1.6</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5">
+      <c r="A45" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B45" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C45" s="6">
+        <v>-23.24</v>
+      </c>
+      <c r="D45" s="6">
+        <v>-21.52</v>
+      </c>
+      <c r="E45" s="7">
+        <v>1.72</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5">
+      <c r="A46" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B46" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C46" s="6">
+        <v>-18.78</v>
+      </c>
+      <c r="D46" s="6">
+        <v>-17.95</v>
+      </c>
+      <c r="E46" s="7">
+        <v>0.83</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5">
+      <c r="A47" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="B28" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C28" s="5">
-        <v>101.46</v>
-      </c>
-      <c r="D28" s="5">
-        <v>100</v>
-      </c>
-      <c r="E28" s="6">
-        <v>-1.46</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5">
-      <c r="A29" s="3" t="s">
+      <c r="B47" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C47" s="6">
+        <v>-21.84</v>
+      </c>
+      <c r="D47" s="6">
+        <v>-17.82</v>
+      </c>
+      <c r="E47" s="7">
+        <v>4.02</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5">
+      <c r="A48" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="B29" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C29" s="5">
-        <v>-28.42</v>
-      </c>
-      <c r="D29" s="5">
-        <v>-27.04</v>
-      </c>
-      <c r="E29" s="7">
-        <v>1.38</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5">
-      <c r="A30" s="3" t="s">
+      <c r="B48" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C48" s="6">
+        <v>-32.27</v>
+      </c>
+      <c r="D48" s="6">
+        <v>-32.01</v>
+      </c>
+      <c r="E48" s="7">
+        <v>0.26</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5">
+      <c r="A49" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="B30" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C30" s="5">
-        <v>-11.45</v>
-      </c>
-      <c r="D30" s="5">
-        <v>-13.66</v>
-      </c>
-      <c r="E30" s="6">
-        <v>-2.21</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5">
-      <c r="A31" s="3" t="s">
+      <c r="B49" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C49" s="6">
+        <v>-19.4</v>
+      </c>
+      <c r="D49" s="6">
+        <v>-17.64</v>
+      </c>
+      <c r="E49" s="7">
+        <v>1.76</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5">
+      <c r="A50" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B31" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C31" s="5">
-        <v>-6.76</v>
-      </c>
-      <c r="D31" s="5">
-        <v>-6.68</v>
-      </c>
-      <c r="E31" s="7">
-        <v>0.08</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5">
-      <c r="A32" s="3" t="s">
+      <c r="B50" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C50" s="6">
+        <v>380.25</v>
+      </c>
+      <c r="D50" s="6">
+        <v>384.65</v>
+      </c>
+      <c r="E50" s="7">
+        <v>4.4</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5">
+      <c r="A51" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B32" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C32" s="5">
-        <v>-27.27</v>
-      </c>
-      <c r="D32" s="5">
-        <v>-28.06</v>
-      </c>
-      <c r="E32" s="6">
-        <v>-0.79</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5">
-      <c r="A33" s="3" t="s">
+      <c r="B51" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C51" s="6">
+        <v>43.53</v>
+      </c>
+      <c r="D51" s="6">
+        <v>44.78</v>
+      </c>
+      <c r="E51" s="7">
+        <v>1.25</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5">
+      <c r="A52" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B33" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C33" s="5">
-        <v>-10.07</v>
-      </c>
-      <c r="D33" s="5">
-        <v>-9.109999999999999</v>
-      </c>
-      <c r="E33" s="7">
-        <v>0.96</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5">
-      <c r="A34" s="3" t="s">
+      <c r="B52" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C52" s="6">
+        <v>2858</v>
+      </c>
+      <c r="D52" s="6">
+        <v>2912</v>
+      </c>
+      <c r="E52" s="7">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5">
+      <c r="A53" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B34" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C34" s="5">
-        <v>-6.94</v>
-      </c>
-      <c r="D34" s="5">
-        <v>-8.720000000000001</v>
-      </c>
-      <c r="E34" s="6">
-        <v>-1.78</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5">
-      <c r="A35" s="3" t="s">
+      <c r="B53" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C53" s="6">
+        <v>882.5</v>
+      </c>
+      <c r="D53" s="6">
+        <v>902.25</v>
+      </c>
+      <c r="E53" s="7">
+        <v>19.75</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5">
+      <c r="A54" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B35" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C35" s="5">
-        <v>-8.390000000000001</v>
-      </c>
-      <c r="D35" s="5">
-        <v>-9.24</v>
-      </c>
-      <c r="E35" s="6">
-        <v>-0.85</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5">
-      <c r="A36" s="3" t="s">
+      <c r="B54" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C54" s="6">
+        <v>12.67</v>
+      </c>
+      <c r="D54" s="6">
+        <v>12.8</v>
+      </c>
+      <c r="E54" s="7">
+        <v>0.13</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5">
+      <c r="A55" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="B36" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C36" s="5">
-        <v>6.65</v>
-      </c>
-      <c r="D36" s="5">
-        <v>3.03</v>
-      </c>
-      <c r="E36" s="6">
-        <v>-3.62</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5">
-      <c r="A37" s="3" t="s">
+      <c r="B55" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C55" s="6">
+        <v>10.88</v>
+      </c>
+      <c r="D55" s="6">
+        <v>11.44</v>
+      </c>
+      <c r="E55" s="7">
+        <v>0.5600000000000001</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5">
+      <c r="A56" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="B37" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C37" s="5">
-        <v>-11.2</v>
-      </c>
-      <c r="D37" s="5">
-        <v>-11.76</v>
-      </c>
-      <c r="E37" s="6">
-        <v>-0.5600000000000001</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5">
-      <c r="A38" s="3" t="s">
+      <c r="B56" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C56" s="6">
+        <v>3934.9</v>
+      </c>
+      <c r="D56" s="6">
+        <v>3949.6</v>
+      </c>
+      <c r="E56" s="7">
+        <v>14.7</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5">
+      <c r="A57" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="B38" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C38" s="5">
-        <v>-8.85</v>
-      </c>
-      <c r="D38" s="5">
-        <v>-9.08</v>
-      </c>
-      <c r="E38" s="6">
-        <v>-0.23</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5">
-      <c r="A39" s="3" t="s">
+      <c r="B57" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C57" s="6">
+        <v>10520</v>
+      </c>
+      <c r="D57" s="6">
+        <v>10750</v>
+      </c>
+      <c r="E57" s="7">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5">
+      <c r="A58" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B39" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C39" s="5">
-        <v>-10.36</v>
-      </c>
-      <c r="D39" s="5">
-        <v>-10.47</v>
-      </c>
-      <c r="E39" s="6">
-        <v>-0.11</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5">
-      <c r="A40" s="3" t="s">
+      <c r="B58" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C58" s="6">
+        <v>44.97</v>
+      </c>
+      <c r="D58" s="6">
+        <v>48.19</v>
+      </c>
+      <c r="E58" s="7">
+        <v>3.22</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5">
+      <c r="A59" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B40" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C40" s="5">
-        <v>-49.07</v>
-      </c>
-      <c r="D40" s="5">
-        <v>-49.02</v>
-      </c>
-      <c r="E40" s="7">
-        <v>0.05</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5">
-      <c r="A41" s="3" t="s">
+      <c r="B59" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C59" s="6">
+        <v>28.76</v>
+      </c>
+      <c r="D59" s="6">
+        <v>36.25</v>
+      </c>
+      <c r="E59" s="7">
+        <v>7.49</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5">
+      <c r="A60" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B41" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C41" s="5">
-        <v>-14.51</v>
-      </c>
-      <c r="D41" s="5">
-        <v>-15.46</v>
-      </c>
-      <c r="E41" s="6">
-        <v>-0.95</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5">
-      <c r="A42" s="3" t="s">
+      <c r="B60" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C60" s="6">
+        <v>26.49</v>
+      </c>
+      <c r="D60" s="6">
+        <v>33.88</v>
+      </c>
+      <c r="E60" s="7">
+        <v>7.39</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5">
+      <c r="A61" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B42" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C42" s="5">
-        <v>-21.69</v>
-      </c>
-      <c r="D42" s="5">
-        <v>-23.24</v>
-      </c>
-      <c r="E42" s="6">
-        <v>-1.55</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5">
-      <c r="A43" s="3" t="s">
+      <c r="B61" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C61" s="6">
+        <v>27.24</v>
+      </c>
+      <c r="D61" s="6">
+        <v>34.98</v>
+      </c>
+      <c r="E61" s="7">
+        <v>7.74</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5">
+      <c r="A62" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B43" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C43" s="5">
-        <v>-16.67</v>
-      </c>
-      <c r="D43" s="5">
-        <v>-18.78</v>
-      </c>
-      <c r="E43" s="6">
-        <v>-2.11</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5">
-      <c r="A44" s="3" t="s">
+      <c r="B62" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C62" s="6">
+        <v>37.35</v>
+      </c>
+      <c r="D62" s="6">
+        <v>39.42</v>
+      </c>
+      <c r="E62" s="7">
+        <v>2.07</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5">
+      <c r="A63" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="B44" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C44" s="5">
-        <v>-20.55</v>
-      </c>
-      <c r="D44" s="5">
-        <v>-21.84</v>
-      </c>
-      <c r="E44" s="6">
-        <v>-1.29</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5">
-      <c r="A45" s="3" t="s">
+      <c r="B63" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C63" s="6">
+        <v>45.29</v>
+      </c>
+      <c r="D63" s="6">
+        <v>53.02</v>
+      </c>
+      <c r="E63" s="7">
+        <v>7.73</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5">
+      <c r="A64" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="B45" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C45" s="5">
-        <v>-32.22</v>
-      </c>
-      <c r="D45" s="5">
-        <v>-32.27</v>
-      </c>
-      <c r="E45" s="6">
-        <v>-0.05</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5">
-      <c r="A46" s="3" t="s">
+      <c r="B64" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C64" s="6">
+        <v>38.09</v>
+      </c>
+      <c r="D64" s="6">
+        <v>39.58</v>
+      </c>
+      <c r="E64" s="7">
+        <v>1.49</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5">
+      <c r="A65" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="B46" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C46" s="5">
-        <v>-18.21</v>
-      </c>
-      <c r="D46" s="5">
-        <v>-19.4</v>
-      </c>
-      <c r="E46" s="6">
-        <v>-1.19</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5">
-      <c r="A47" s="3" t="s">
+      <c r="B65" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C65" s="6">
+        <v>38.4</v>
+      </c>
+      <c r="D65" s="6">
+        <v>45.23</v>
+      </c>
+      <c r="E65" s="7">
+        <v>6.83</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5">
+      <c r="A66" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B47" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C47" s="5">
-        <v>380.7</v>
-      </c>
-      <c r="D47" s="5">
-        <v>380.25</v>
-      </c>
-      <c r="E47" s="6">
-        <v>-0.45</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5">
-      <c r="A48" s="3" t="s">
+      <c r="B66" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C66" s="6">
+        <v>12.95</v>
+      </c>
+      <c r="D66" s="6">
+        <v>29.47</v>
+      </c>
+      <c r="E66" s="7">
+        <v>16.52</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5">
+      <c r="A67" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B48" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C48" s="5">
-        <v>43.65</v>
-      </c>
-      <c r="D48" s="5">
-        <v>43.53</v>
-      </c>
-      <c r="E48" s="6">
-        <v>-0.12</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5">
-      <c r="A49" s="3" t="s">
+      <c r="B67" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C67" s="6">
+        <v>-65.11</v>
+      </c>
+      <c r="D67" s="6">
+        <v>-44.73</v>
+      </c>
+      <c r="E67" s="7">
+        <v>20.38</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5">
+      <c r="A68" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B49" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C49" s="5">
-        <v>2890</v>
-      </c>
-      <c r="D49" s="5">
-        <v>2858</v>
-      </c>
-      <c r="E49" s="6">
-        <v>-32</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5">
-      <c r="A50" s="3" t="s">
+      <c r="B68" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C68" s="6">
+        <v>-82.25</v>
+      </c>
+      <c r="D68" s="6">
+        <v>-47.74</v>
+      </c>
+      <c r="E68" s="7">
+        <v>34.51</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5">
+      <c r="A69" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B50" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C50" s="5">
-        <v>900.35</v>
-      </c>
-      <c r="D50" s="5">
-        <v>882.5</v>
-      </c>
-      <c r="E50" s="6">
-        <v>-17.85</v>
-      </c>
-    </row>
-    <row r="51" spans="1:5">
-      <c r="A51" s="3" t="s">
+      <c r="B69" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C69" s="6">
+        <v>-33.95</v>
+      </c>
+      <c r="D69" s="6">
+        <v>33.07</v>
+      </c>
+      <c r="E69" s="7">
+        <v>67.02</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5">
+      <c r="A70" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B51" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C51" s="5">
-        <v>13</v>
-      </c>
-      <c r="D51" s="5">
-        <v>12.67</v>
-      </c>
-      <c r="E51" s="6">
-        <v>-0.33</v>
-      </c>
-    </row>
-    <row r="52" spans="1:5">
-      <c r="A52" s="3" t="s">
+      <c r="B70" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C70" s="6">
+        <v>-28.2</v>
+      </c>
+      <c r="D70" s="6">
+        <v>-45.87</v>
+      </c>
+      <c r="E70" s="8">
+        <v>-17.67</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5">
+      <c r="A71" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="B52" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C52" s="5">
-        <v>11.06</v>
-      </c>
-      <c r="D52" s="5">
-        <v>10.88</v>
-      </c>
-      <c r="E52" s="6">
-        <v>-0.18</v>
-      </c>
-    </row>
-    <row r="53" spans="1:5">
-      <c r="A53" s="3" t="s">
+      <c r="B71" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C71" s="6">
+        <v>14.21</v>
+      </c>
+      <c r="D71" s="6">
+        <v>48.21</v>
+      </c>
+      <c r="E71" s="7">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="72" spans="1:5">
+      <c r="A72" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="B53" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C53" s="5">
-        <v>3937.7</v>
-      </c>
-      <c r="D53" s="5">
-        <v>3934.9</v>
-      </c>
-      <c r="E53" s="6">
-        <v>-2.8</v>
-      </c>
-    </row>
-    <row r="54" spans="1:5">
-      <c r="A54" s="3" t="s">
+      <c r="B72" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C72" s="6">
+        <v>-78.52</v>
+      </c>
+      <c r="D72" s="6">
+        <v>-68.20999999999999</v>
+      </c>
+      <c r="E72" s="7">
+        <v>10.31</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5">
+      <c r="A73" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="B54" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C54" s="5">
-        <v>10675</v>
-      </c>
-      <c r="D54" s="5">
-        <v>10520</v>
-      </c>
-      <c r="E54" s="6">
-        <v>-155</v>
-      </c>
-    </row>
-    <row r="55" spans="1:5">
-      <c r="A55" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B55" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C55" s="5">
-        <v>45.23</v>
-      </c>
-      <c r="D55" s="5">
-        <v>44.97</v>
-      </c>
-      <c r="E55" s="6">
-        <v>-0.26</v>
-      </c>
-    </row>
-    <row r="56" spans="1:5">
-      <c r="A56" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B56" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C56" s="5">
-        <v>29.06</v>
-      </c>
-      <c r="D56" s="5">
-        <v>28.76</v>
-      </c>
-      <c r="E56" s="6">
-        <v>-0.3</v>
-      </c>
-    </row>
-    <row r="57" spans="1:5">
-      <c r="A57" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B57" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C57" s="5">
-        <v>28.22</v>
-      </c>
-      <c r="D57" s="5">
-        <v>26.49</v>
-      </c>
-      <c r="E57" s="6">
-        <v>-1.73</v>
-      </c>
-    </row>
-    <row r="58" spans="1:5">
-      <c r="A58" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="B58" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C58" s="5">
-        <v>30.26</v>
-      </c>
-      <c r="D58" s="5">
-        <v>27.24</v>
-      </c>
-      <c r="E58" s="6">
-        <v>-3.02</v>
-      </c>
-    </row>
-    <row r="59" spans="1:5">
-      <c r="A59" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="B59" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C59" s="5">
-        <v>40.63</v>
-      </c>
-      <c r="D59" s="5">
-        <v>37.35</v>
-      </c>
-      <c r="E59" s="6">
-        <v>-3.28</v>
-      </c>
-    </row>
-    <row r="60" spans="1:5">
-      <c r="A60" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="B60" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C60" s="5">
-        <v>47.63</v>
-      </c>
-      <c r="D60" s="5">
-        <v>45.29</v>
-      </c>
-      <c r="E60" s="6">
-        <v>-2.34</v>
-      </c>
-    </row>
-    <row r="61" spans="1:5">
-      <c r="A61" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="B61" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C61" s="5">
-        <v>38.26</v>
-      </c>
-      <c r="D61" s="5">
-        <v>38.09</v>
-      </c>
-      <c r="E61" s="6">
-        <v>-0.17</v>
-      </c>
-    </row>
-    <row r="62" spans="1:5">
-      <c r="A62" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="B62" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C62" s="5">
-        <v>41.65</v>
-      </c>
-      <c r="D62" s="5">
-        <v>38.4</v>
-      </c>
-      <c r="E62" s="6">
-        <v>-3.25</v>
-      </c>
-    </row>
-    <row r="63" spans="1:5">
-      <c r="A63" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B63" s="3" t="s">
+      <c r="B73" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="C63" s="5">
-        <v>116.37</v>
-      </c>
-      <c r="D63" s="5">
-        <v>12.95</v>
-      </c>
-      <c r="E63" s="6">
-        <v>-103.42</v>
-      </c>
-    </row>
-    <row r="64" spans="1:5">
-      <c r="A64" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B64" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C64" s="5">
-        <v>-42.98</v>
-      </c>
-      <c r="D64" s="5">
-        <v>-65.11</v>
-      </c>
-      <c r="E64" s="6">
-        <v>-22.13</v>
-      </c>
-    </row>
-    <row r="65" spans="1:5">
-      <c r="A65" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B65" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C65" s="5">
-        <v>-67.83</v>
-      </c>
-      <c r="D65" s="5">
-        <v>-82.25</v>
-      </c>
-      <c r="E65" s="6">
-        <v>-14.42</v>
-      </c>
-    </row>
-    <row r="66" spans="1:5">
-      <c r="A66" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="B66" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C66" s="5">
-        <v>-10.78</v>
-      </c>
-      <c r="D66" s="5">
-        <v>-33.95</v>
-      </c>
-      <c r="E66" s="6">
-        <v>-23.17</v>
-      </c>
-    </row>
-    <row r="67" spans="1:5">
-      <c r="A67" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="B67" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C67" s="5">
-        <v>-45.14</v>
-      </c>
-      <c r="D67" s="5">
-        <v>-28.2</v>
-      </c>
-      <c r="E67" s="7">
-        <v>16.94</v>
-      </c>
-    </row>
-    <row r="68" spans="1:5">
-      <c r="A68" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="B68" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C68" s="5">
-        <v>128.97</v>
-      </c>
-      <c r="D68" s="5">
-        <v>14.21</v>
-      </c>
-      <c r="E68" s="6">
-        <v>-114.76</v>
-      </c>
-    </row>
-    <row r="69" spans="1:5">
-      <c r="A69" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="B69" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C69" s="5">
-        <v>-60.28</v>
-      </c>
-      <c r="D69" s="5">
-        <v>-78.52</v>
-      </c>
-      <c r="E69" s="6">
-        <v>-18.24</v>
-      </c>
-    </row>
-    <row r="70" spans="1:5">
-      <c r="A70" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="B70" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C70" s="5">
-        <v>-47.81</v>
-      </c>
-      <c r="D70" s="5">
+      <c r="C73" s="6">
         <v>-24.75</v>
       </c>
-      <c r="E70" s="7">
-        <v>23.06</v>
+      <c r="D73" s="6">
+        <v>-32.54</v>
+      </c>
+      <c r="E73" s="8">
+        <v>-7.79</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A5:E5"/>
+    <mergeCell ref="A8:E8"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3090,60 +3243,60 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="28" customHeight="1">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="8" t="s">
-        <v>56</v>
-      </c>
-      <c r="C1" s="8" t="s">
-        <v>57</v>
-      </c>
-      <c r="D1" s="8" t="s">
-        <v>58</v>
-      </c>
-      <c r="E1" s="8" t="s">
-        <v>59</v>
-      </c>
-      <c r="F1" s="8" t="s">
-        <v>60</v>
-      </c>
-      <c r="G1" s="8" t="s">
-        <v>61</v>
-      </c>
-      <c r="H1" s="8" t="s">
-        <v>62</v>
-      </c>
-      <c r="I1" s="8" t="s">
-        <v>63</v>
+      <c r="B1" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="C1" s="9" t="s">
+        <v>76</v>
+      </c>
+      <c r="D1" s="9" t="s">
+        <v>77</v>
+      </c>
+      <c r="E1" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="F1" s="9" t="s">
+        <v>79</v>
+      </c>
+      <c r="G1" s="9" t="s">
+        <v>80</v>
+      </c>
+      <c r="H1" s="9" t="s">
+        <v>81</v>
+      </c>
+      <c r="I1" s="9" t="s">
+        <v>82</v>
       </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="9" t="s">
+      <c r="A2" s="10" t="s">
         <v>45</v>
       </c>
-      <c r="B2" s="10">
+      <c r="B2" s="11">
         <v>48.44</v>
       </c>
-      <c r="C2" s="11">
+      <c r="C2" s="12">
         <v>8</v>
       </c>
-      <c r="D2" s="10">
-        <v>35.8</v>
-      </c>
-      <c r="E2" s="10">
+      <c r="D2" s="11">
+        <v>41.3</v>
+      </c>
+      <c r="E2" s="11">
         <v>40</v>
       </c>
-      <c r="F2" s="10">
-        <v>-9.9</v>
-      </c>
-      <c r="G2" s="10">
-        <v>-10</v>
-      </c>
-      <c r="H2" s="10">
+      <c r="F2" s="11">
+        <v>-8.1</v>
+      </c>
+      <c r="G2" s="11">
+        <v>-7.3</v>
+      </c>
+      <c r="H2" s="11">
         <v>56.1</v>
       </c>
-      <c r="I2" s="10">
+      <c r="I2" s="11">
         <v>0</v>
       </c>
     </row>
@@ -3245,55 +3398,55 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8">
-      <c r="A1" s="12" t="s">
+      <c r="A1" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="B1" s="12" t="s">
+      <c r="B1" s="13" t="s">
         <v>43</v>
       </c>
-      <c r="C1" s="12" t="s">
+      <c r="C1" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="D1" s="12" t="s">
+      <c r="D1" s="13" t="s">
         <v>39</v>
       </c>
-      <c r="E1" s="12" t="s">
+      <c r="E1" s="13" t="s">
         <v>44</v>
       </c>
-      <c r="F1" s="12" t="s">
+      <c r="F1" s="13" t="s">
         <v>41</v>
       </c>
-      <c r="G1" s="12" t="s">
+      <c r="G1" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="H1" s="12" t="s">
+      <c r="H1" s="13" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="2" spans="1:8">
-      <c r="A2" s="13">
-        <v>0.285</v>
-      </c>
-      <c r="B2" s="13">
-        <v>0.1496</v>
-      </c>
-      <c r="C2" s="13">
-        <v>0.1274</v>
-      </c>
-      <c r="D2" s="13">
-        <v>0.123</v>
-      </c>
-      <c r="E2" s="13">
-        <v>0.08220000000000001</v>
-      </c>
-      <c r="F2" s="13">
-        <v>0.0354</v>
-      </c>
-      <c r="G2" s="13">
-        <v>-0.3068</v>
-      </c>
-      <c r="H2" s="13">
-        <v>-0.3095</v>
+      <c r="A2" s="14">
+        <v>0.2899</v>
+      </c>
+      <c r="B2" s="14">
+        <v>0.1511</v>
+      </c>
+      <c r="C2" s="14">
+        <v>0.1282</v>
+      </c>
+      <c r="D2" s="14">
+        <v>0.1219</v>
+      </c>
+      <c r="E2" s="14">
+        <v>0.0839</v>
+      </c>
+      <c r="F2" s="14">
+        <v>0.0365</v>
+      </c>
+      <c r="G2" s="14">
+        <v>-0.3019</v>
+      </c>
+      <c r="H2" s="14">
+        <v>-0.3053</v>
       </c>
     </row>
   </sheetData>

--- a/BIRLA_GROUP_Technical_Metrics.xlsx
+++ b/BIRLA_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="305" uniqueCount="83">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="276" uniqueCount="64">
   <si>
     <t>Symbol</t>
   </si>
@@ -172,64 +172,7 @@
     <t>▶  SIGNAL EVENTS (vs Previous Run)</t>
   </si>
   <si>
-    <t>Signal</t>
-  </si>
-  <si>
-    <t>Change</t>
-  </si>
-  <si>
-    <t>Direction</t>
-  </si>
-  <si>
-    <t>Prev Value</t>
-  </si>
-  <si>
-    <t>Curr Value</t>
-  </si>
-  <si>
-    <t>RSI Oversold Recovery</t>
-  </si>
-  <si>
-    <t>28.8 → 36.2</t>
-  </si>
-  <si>
-    <t>🟢 BULLISH</t>
-  </si>
-  <si>
-    <t>28.8</t>
-  </si>
-  <si>
-    <t>36.2</t>
-  </si>
-  <si>
-    <t>26.5 → 33.9</t>
-  </si>
-  <si>
-    <t>26.5</t>
-  </si>
-  <si>
-    <t>33.9</t>
-  </si>
-  <si>
-    <t>27.2 → 35.0</t>
-  </si>
-  <si>
-    <t>27.2</t>
-  </si>
-  <si>
-    <t>35.0</t>
-  </si>
-  <si>
-    <t>RSI Momentum</t>
-  </si>
-  <si>
-    <t>45.3 → 53.0</t>
-  </si>
-  <si>
-    <t>45.3</t>
-  </si>
-  <si>
-    <t>53.0</t>
+    <t>No signal events detected since last run.</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -315,14 +258,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF9C0006"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF006100"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -355,13 +298,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -431,15 +374,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -954,10 +896,10 @@
         <v>45</v>
       </c>
       <c r="C2">
-        <v>384.65</v>
+        <v>378.9</v>
       </c>
       <c r="D2">
-        <v>1.16</v>
+        <v>-1.49</v>
       </c>
       <c r="E2">
         <v>424.7</v>
@@ -966,46 +908,46 @@
         <v>292.25</v>
       </c>
       <c r="G2">
-        <v>-9.43</v>
+        <v>-10.78</v>
       </c>
       <c r="H2">
-        <v>31.62</v>
+        <v>29.65</v>
       </c>
       <c r="I2">
-        <v>1.52</v>
+        <v>1.83</v>
       </c>
       <c r="J2">
-        <v>-3.84</v>
+        <v>-4.08</v>
       </c>
       <c r="K2">
-        <v>-3.66</v>
+        <v>-6.28</v>
       </c>
       <c r="L2">
-        <v>30.28</v>
+        <v>27.17</v>
       </c>
       <c r="M2">
-        <v>28.99</v>
+        <v>28.63</v>
       </c>
       <c r="N2">
         <v>74</v>
       </c>
       <c r="O2">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="P2">
-        <v>377.27</v>
+        <v>378.63</v>
       </c>
       <c r="Q2">
-        <v>385.1</v>
+        <v>385.11</v>
       </c>
       <c r="R2">
-        <v>398.12</v>
+        <v>397.22</v>
       </c>
       <c r="S2">
-        <v>365.6</v>
+        <v>365.76</v>
       </c>
       <c r="T2">
-        <v>5.21</v>
+        <v>3.59</v>
       </c>
       <c r="U2" t="s">
         <v>46</v>
@@ -1020,34 +962,34 @@
         <v>2</v>
       </c>
       <c r="Y2">
-        <v>48.19</v>
+        <v>44.52</v>
       </c>
       <c r="Z2">
-        <v>-5.59</v>
+        <v>-5.36</v>
       </c>
       <c r="AA2">
-        <v>-5.81</v>
+        <v>-5.72</v>
       </c>
       <c r="AB2">
-        <v>0.23</v>
+        <v>0.36</v>
       </c>
       <c r="AC2">
-        <v>64.95</v>
+        <v>69.15000000000001</v>
       </c>
       <c r="AD2">
-        <v>41</v>
+        <v>57.62</v>
       </c>
       <c r="AE2">
         <v>9.57</v>
       </c>
       <c r="AF2">
-        <v>29.47</v>
+        <v>-59.1</v>
       </c>
       <c r="AG2">
         <v>407.04</v>
       </c>
       <c r="AH2">
-        <v>363.17</v>
+        <v>363.18</v>
       </c>
       <c r="AI2">
         <v>398.61</v>
@@ -1056,7 +998,7 @@
         <v>48</v>
       </c>
       <c r="AK2">
-        <v>26.43</v>
+        <v>23.44</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1067,10 +1009,10 @@
         <v>45</v>
       </c>
       <c r="C3">
-        <v>44.78</v>
+        <v>45.28</v>
       </c>
       <c r="D3">
-        <v>2.87</v>
+        <v>1.12</v>
       </c>
       <c r="E3">
         <v>85.38</v>
@@ -1079,46 +1021,46 @@
         <v>43.18</v>
       </c>
       <c r="G3">
-        <v>-47.55</v>
+        <v>-46.97</v>
       </c>
       <c r="H3">
-        <v>3.71</v>
+        <v>4.86</v>
       </c>
       <c r="I3">
-        <v>-1.97</v>
+        <v>1.48</v>
       </c>
       <c r="J3">
-        <v>-12.01</v>
+        <v>-10.23</v>
       </c>
       <c r="K3">
-        <v>-24.01</v>
+        <v>-23.59</v>
       </c>
       <c r="L3">
-        <v>-47.2</v>
+        <v>-46.46</v>
       </c>
       <c r="M3">
-        <v>-30.19</v>
+        <v>-29.73</v>
       </c>
       <c r="N3">
         <v>13</v>
       </c>
       <c r="O3">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="P3">
-        <v>43.95</v>
+        <v>44.08</v>
       </c>
       <c r="Q3">
-        <v>46.96</v>
+        <v>46.77</v>
       </c>
       <c r="R3">
-        <v>51.99</v>
+        <v>51.65</v>
       </c>
       <c r="S3">
-        <v>61.14</v>
+        <v>60.98</v>
       </c>
       <c r="T3">
-        <v>-26.76</v>
+        <v>-25.75</v>
       </c>
       <c r="U3" t="s">
         <v>46</v>
@@ -1133,34 +1075,34 @@
         <v>0</v>
       </c>
       <c r="Y3">
-        <v>36.25</v>
+        <v>39.02</v>
       </c>
       <c r="Z3">
-        <v>-2.3</v>
+        <v>-2.14</v>
       </c>
       <c r="AA3">
-        <v>-2.25</v>
+        <v>-2.23</v>
       </c>
       <c r="AB3">
-        <v>-0.05</v>
+        <v>0.09</v>
       </c>
       <c r="AC3">
-        <v>58.5</v>
+        <v>78.28</v>
       </c>
       <c r="AD3">
-        <v>41.65</v>
+        <v>56.43</v>
       </c>
       <c r="AE3">
-        <v>1.54</v>
+        <v>1.57</v>
       </c>
       <c r="AF3">
-        <v>-44.73</v>
+        <v>-40.32</v>
       </c>
       <c r="AG3">
-        <v>52.01</v>
+        <v>51.78</v>
       </c>
       <c r="AH3">
-        <v>41.91</v>
+        <v>41.76</v>
       </c>
       <c r="AI3">
         <v>48.29</v>
@@ -1169,7 +1111,7 @@
         <v>48</v>
       </c>
       <c r="AK3">
-        <v>37.92</v>
+        <v>34.54</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1180,10 +1122,10 @@
         <v>45</v>
       </c>
       <c r="C4">
-        <v>2912</v>
+        <v>2873</v>
       </c>
       <c r="D4">
-        <v>1.89</v>
+        <v>-1.34</v>
       </c>
       <c r="E4">
         <v>3380.5</v>
@@ -1192,46 +1134,46 @@
         <v>2531.1</v>
       </c>
       <c r="G4">
-        <v>-13.86</v>
+        <v>-15.01</v>
       </c>
       <c r="H4">
-        <v>15.05</v>
+        <v>13.51</v>
       </c>
       <c r="I4">
-        <v>-1.92</v>
+        <v>-1.65</v>
       </c>
       <c r="J4">
-        <v>-12.26</v>
+        <v>-12.46</v>
       </c>
       <c r="K4">
-        <v>-6.47</v>
+        <v>-6.91</v>
       </c>
       <c r="L4">
-        <v>4.82</v>
+        <v>2.22</v>
       </c>
       <c r="M4">
-        <v>12.19</v>
+        <v>10.91</v>
       </c>
       <c r="N4">
         <v>50</v>
       </c>
       <c r="O4">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="P4">
-        <v>2887.58</v>
+        <v>2877.96</v>
       </c>
       <c r="Q4">
-        <v>3061.67</v>
+        <v>3046.77</v>
       </c>
       <c r="R4">
-        <v>3197.2</v>
+        <v>3189.46</v>
       </c>
       <c r="S4">
-        <v>2980.3</v>
+        <v>2980.53</v>
       </c>
       <c r="T4">
-        <v>-2.29</v>
+        <v>-3.61</v>
       </c>
       <c r="U4" t="s">
         <v>46</v>
@@ -1246,34 +1188,34 @@
         <v>1</v>
       </c>
       <c r="Y4">
-        <v>33.88</v>
+        <v>31.42</v>
       </c>
       <c r="Z4">
-        <v>-95.06</v>
+        <v>-96.04000000000001</v>
       </c>
       <c r="AA4">
-        <v>-74.91</v>
+        <v>-79.13</v>
       </c>
       <c r="AB4">
-        <v>-20.16</v>
+        <v>-16.9</v>
       </c>
       <c r="AC4">
-        <v>27.58</v>
+        <v>32.36</v>
       </c>
       <c r="AD4">
-        <v>15.56</v>
+        <v>23.94</v>
       </c>
       <c r="AE4">
-        <v>62.13</v>
+        <v>61.65</v>
       </c>
       <c r="AF4">
-        <v>-47.74</v>
+        <v>-44.37</v>
       </c>
       <c r="AG4">
-        <v>3317.9</v>
+        <v>3310.77</v>
       </c>
       <c r="AH4">
-        <v>2805.43</v>
+        <v>2782.76</v>
       </c>
       <c r="AI4">
         <v>3061.2</v>
@@ -1282,7 +1224,7 @@
         <v>48</v>
       </c>
       <c r="AK4">
-        <v>66.40000000000001</v>
+        <v>66.08</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1293,10 +1235,10 @@
         <v>45</v>
       </c>
       <c r="C5">
-        <v>902.25</v>
+        <v>882.5</v>
       </c>
       <c r="D5">
-        <v>2.24</v>
+        <v>-2.19</v>
       </c>
       <c r="E5">
         <v>1149.7</v>
@@ -1305,46 +1247,46 @@
         <v>760.1</v>
       </c>
       <c r="G5">
-        <v>-21.52</v>
+        <v>-23.24</v>
       </c>
       <c r="H5">
-        <v>18.7</v>
+        <v>16.1</v>
       </c>
       <c r="I5">
-        <v>-4.07</v>
+        <v>-3.11</v>
       </c>
       <c r="J5">
-        <v>-11.02</v>
+        <v>-10.09</v>
       </c>
       <c r="K5">
-        <v>-7.4</v>
+        <v>-7.67</v>
       </c>
       <c r="L5">
-        <v>17.45</v>
+        <v>14</v>
       </c>
       <c r="M5">
-        <v>12.82</v>
+        <v>11.97</v>
       </c>
       <c r="N5">
         <v>62</v>
       </c>
       <c r="O5">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="P5">
-        <v>897.22</v>
+        <v>891.55</v>
       </c>
       <c r="Q5">
-        <v>948.76</v>
+        <v>944.95</v>
       </c>
       <c r="R5">
-        <v>997.8099999999999</v>
+        <v>995.5599999999999</v>
       </c>
       <c r="S5">
-        <v>983.13</v>
+        <v>983.22</v>
       </c>
       <c r="T5">
-        <v>-8.23</v>
+        <v>-10.24</v>
       </c>
       <c r="U5" t="s">
         <v>46</v>
@@ -1359,43 +1301,43 @@
         <v>1</v>
       </c>
       <c r="Y5">
-        <v>34.98</v>
+        <v>31.39</v>
       </c>
       <c r="Z5">
-        <v>-28.4</v>
+        <v>-29.62</v>
       </c>
       <c r="AA5">
-        <v>-22.51</v>
+        <v>-23.93</v>
       </c>
       <c r="AB5">
-        <v>-5.89</v>
+        <v>-5.69</v>
       </c>
       <c r="AC5">
-        <v>20.07</v>
+        <v>23.89</v>
       </c>
       <c r="AD5">
-        <v>11.25</v>
+        <v>17.24</v>
       </c>
       <c r="AE5">
-        <v>21.78</v>
+        <v>21.63</v>
       </c>
       <c r="AF5">
-        <v>33.07</v>
+        <v>-23.9</v>
       </c>
       <c r="AG5">
-        <v>1019.56</v>
+        <v>1021.46</v>
       </c>
       <c r="AH5">
-        <v>877.96</v>
+        <v>868.4299999999999</v>
       </c>
       <c r="AI5">
-        <v>957.78</v>
+        <v>956.1</v>
       </c>
       <c r="AJ5" t="s">
         <v>48</v>
       </c>
       <c r="AK5">
-        <v>46.28</v>
+        <v>47.03</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1406,10 +1348,10 @@
         <v>45</v>
       </c>
       <c r="C6">
-        <v>12.8</v>
+        <v>12.67</v>
       </c>
       <c r="D6">
-        <v>1.03</v>
+        <v>-1.02</v>
       </c>
       <c r="E6">
         <v>15.6</v>
@@ -1418,46 +1360,46 @@
         <v>8.359999999999999</v>
       </c>
       <c r="G6">
-        <v>-17.95</v>
+        <v>-18.78</v>
       </c>
       <c r="H6">
-        <v>53.11</v>
+        <v>51.56</v>
       </c>
       <c r="I6">
-        <v>-3.1</v>
+        <v>-3.87</v>
       </c>
       <c r="J6">
-        <v>-14.09</v>
+        <v>-15.36</v>
       </c>
       <c r="K6">
-        <v>-7.45</v>
+        <v>-7.32</v>
       </c>
       <c r="L6">
-        <v>41.59</v>
+        <v>40.31</v>
       </c>
       <c r="M6">
-        <v>3.65</v>
+        <v>3.34</v>
       </c>
       <c r="N6">
         <v>87</v>
       </c>
       <c r="O6">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="P6">
-        <v>12.89</v>
+        <v>12.79</v>
       </c>
       <c r="Q6">
-        <v>13.54</v>
+        <v>13.46</v>
       </c>
       <c r="R6">
-        <v>13.89</v>
+        <v>13.88</v>
       </c>
       <c r="S6">
         <v>12.29</v>
       </c>
       <c r="T6">
-        <v>4.14</v>
+        <v>3.06</v>
       </c>
       <c r="U6" t="s">
         <v>46</v>
@@ -1472,43 +1414,43 @@
         <v>2</v>
       </c>
       <c r="Y6">
-        <v>39.42</v>
+        <v>38.07</v>
       </c>
       <c r="Z6">
         <v>-0.41</v>
       </c>
       <c r="AA6">
-        <v>-0.31</v>
+        <v>-0.33</v>
       </c>
       <c r="AB6">
-        <v>-0.09</v>
+        <v>-0.08</v>
       </c>
       <c r="AC6">
-        <v>32.09</v>
+        <v>29.55</v>
       </c>
       <c r="AD6">
-        <v>32.22</v>
+        <v>30.17</v>
       </c>
       <c r="AE6">
-        <v>0.46</v>
+        <v>0.44</v>
       </c>
       <c r="AF6">
-        <v>-45.87</v>
+        <v>-52.17</v>
       </c>
       <c r="AG6">
-        <v>14.89</v>
+        <v>14.78</v>
       </c>
       <c r="AH6">
-        <v>12.2</v>
+        <v>12.13</v>
       </c>
       <c r="AI6">
-        <v>14.1</v>
+        <v>14.06</v>
       </c>
       <c r="AJ6" t="s">
         <v>48</v>
       </c>
       <c r="AK6">
-        <v>40.26</v>
+        <v>41.23</v>
       </c>
     </row>
     <row r="7" spans="1:37">
@@ -1519,10 +1461,10 @@
         <v>45</v>
       </c>
       <c r="C7">
-        <v>11.44</v>
+        <v>11.61</v>
       </c>
       <c r="D7">
-        <v>5.15</v>
+        <v>1.49</v>
       </c>
       <c r="E7">
         <v>13.92</v>
@@ -1531,25 +1473,25 @@
         <v>4.69</v>
       </c>
       <c r="G7">
-        <v>-17.82</v>
+        <v>-16.59</v>
       </c>
       <c r="H7">
-        <v>143.92</v>
+        <v>147.55</v>
       </c>
       <c r="I7">
-        <v>6.32</v>
+        <v>7.4</v>
       </c>
       <c r="J7">
-        <v>-2.89</v>
+        <v>-3.33</v>
       </c>
       <c r="K7">
-        <v>6.22</v>
+        <v>5.74</v>
       </c>
       <c r="L7">
-        <v>108.38</v>
+        <v>121.14</v>
       </c>
       <c r="M7">
-        <v>-30.53</v>
+        <v>-30.36</v>
       </c>
       <c r="N7">
         <v>99</v>
@@ -1558,19 +1500,19 @@
         <v>94</v>
       </c>
       <c r="P7">
-        <v>10.95</v>
+        <v>11.11</v>
       </c>
       <c r="Q7">
-        <v>11.3</v>
+        <v>11.25</v>
       </c>
       <c r="R7">
-        <v>11.61</v>
+        <v>11.58</v>
       </c>
       <c r="S7">
         <v>10.84</v>
       </c>
       <c r="T7">
-        <v>5.5</v>
+        <v>7.09</v>
       </c>
       <c r="U7" t="s">
         <v>46</v>
@@ -1585,34 +1527,34 @@
         <v>2</v>
       </c>
       <c r="Y7">
-        <v>53.02</v>
+        <v>55.09</v>
       </c>
       <c r="Z7">
+        <v>-0.12</v>
+      </c>
+      <c r="AA7">
         <v>-0.18</v>
       </c>
-      <c r="AA7">
-        <v>-0.2</v>
-      </c>
       <c r="AB7">
-        <v>0.02</v>
+        <v>0.06</v>
       </c>
       <c r="AC7">
-        <v>90.69</v>
+        <v>93.34</v>
       </c>
       <c r="AD7">
-        <v>70.86</v>
+        <v>84.17</v>
       </c>
       <c r="AE7">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="AF7">
-        <v>48.21</v>
+        <v>-23.68</v>
       </c>
       <c r="AG7">
-        <v>12.58</v>
+        <v>12.39</v>
       </c>
       <c r="AH7">
-        <v>10.02</v>
+        <v>10.12</v>
       </c>
       <c r="AI7">
         <v>12.04</v>
@@ -1621,7 +1563,7 @@
         <v>48</v>
       </c>
       <c r="AK7">
-        <v>28.22</v>
+        <v>27.8</v>
       </c>
     </row>
     <row r="8" spans="1:37">
@@ -1632,10 +1574,10 @@
         <v>45</v>
       </c>
       <c r="C8">
-        <v>3949.6</v>
+        <v>3989.7</v>
       </c>
       <c r="D8">
-        <v>0.37</v>
+        <v>1.02</v>
       </c>
       <c r="E8">
         <v>5809.5</v>
@@ -1644,46 +1586,46 @@
         <v>3892.3</v>
       </c>
       <c r="G8">
-        <v>-32.01</v>
+        <v>-31.32</v>
       </c>
       <c r="H8">
-        <v>1.47</v>
+        <v>2.5</v>
       </c>
       <c r="I8">
-        <v>-2.89</v>
+        <v>-2.12</v>
       </c>
       <c r="J8">
-        <v>-6.76</v>
+        <v>-4.82</v>
       </c>
       <c r="K8">
-        <v>-9.460000000000001</v>
+        <v>-8.52</v>
       </c>
       <c r="L8">
-        <v>-26.25</v>
+        <v>-24.68</v>
       </c>
       <c r="M8">
-        <v>15.11</v>
+        <v>15.18</v>
       </c>
       <c r="N8">
         <v>26</v>
       </c>
       <c r="O8">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="P8">
-        <v>3969.4</v>
+        <v>3952.08</v>
       </c>
       <c r="Q8">
-        <v>4007.77</v>
+        <v>4003.16</v>
       </c>
       <c r="R8">
-        <v>4214.06</v>
+        <v>4206.92</v>
       </c>
       <c r="S8">
-        <v>4487.81</v>
+        <v>4482</v>
       </c>
       <c r="T8">
-        <v>-11.99</v>
+        <v>-10.98</v>
       </c>
       <c r="U8" t="s">
         <v>46</v>
@@ -1698,34 +1640,34 @@
         <v>0</v>
       </c>
       <c r="Y8">
-        <v>39.58</v>
+        <v>43.57</v>
       </c>
       <c r="Z8">
-        <v>-73.40000000000001</v>
+        <v>-67.95</v>
       </c>
       <c r="AA8">
-        <v>-78.2</v>
+        <v>-76.15000000000001</v>
       </c>
       <c r="AB8">
-        <v>4.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AC8">
-        <v>53.19</v>
+        <v>62.97</v>
       </c>
       <c r="AD8">
-        <v>57.86</v>
+        <v>56.01</v>
       </c>
       <c r="AE8">
-        <v>103.49</v>
+        <v>103.2</v>
       </c>
       <c r="AF8">
-        <v>-68.20999999999999</v>
+        <v>-60.61</v>
       </c>
       <c r="AG8">
-        <v>4120.55</v>
+        <v>4110.61</v>
       </c>
       <c r="AH8">
-        <v>3894.98</v>
+        <v>3895.71</v>
       </c>
       <c r="AI8">
         <v>4246.97</v>
@@ -1734,7 +1676,7 @@
         <v>48</v>
       </c>
       <c r="AK8">
-        <v>38.53</v>
+        <v>33.99</v>
       </c>
     </row>
     <row r="9" spans="1:37">
@@ -1745,10 +1687,10 @@
         <v>45</v>
       </c>
       <c r="C9">
-        <v>10750</v>
+        <v>10795</v>
       </c>
       <c r="D9">
-        <v>2.19</v>
+        <v>0.42</v>
       </c>
       <c r="E9">
         <v>13052</v>
@@ -1757,46 +1699,46 @@
         <v>10362</v>
       </c>
       <c r="G9">
-        <v>-17.64</v>
+        <v>-17.29</v>
       </c>
       <c r="H9">
-        <v>3.74</v>
+        <v>4.18</v>
       </c>
       <c r="I9">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="J9">
-        <v>-2.09</v>
+        <v>-1.86</v>
       </c>
       <c r="K9">
-        <v>-6.49</v>
+        <v>-8.609999999999999</v>
       </c>
       <c r="L9">
-        <v>-10.35</v>
+        <v>-11.46</v>
       </c>
       <c r="M9">
-        <v>8.390000000000001</v>
+        <v>8.35</v>
       </c>
       <c r="N9">
         <v>38</v>
       </c>
       <c r="O9">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="P9">
-        <v>10605.8</v>
+        <v>10633.2</v>
       </c>
       <c r="Q9">
-        <v>10839.5</v>
+        <v>10844.4</v>
       </c>
       <c r="R9">
-        <v>11281.34</v>
+        <v>11256.16</v>
       </c>
       <c r="S9">
-        <v>11676.48</v>
+        <v>11671.63</v>
       </c>
       <c r="T9">
-        <v>-7.93</v>
+        <v>-7.51</v>
       </c>
       <c r="U9" t="s">
         <v>46</v>
@@ -1811,34 +1753,34 @@
         <v>0</v>
       </c>
       <c r="Y9">
-        <v>45.23</v>
+        <v>46.49</v>
       </c>
       <c r="Z9">
-        <v>-174.85</v>
+        <v>-158.09</v>
       </c>
       <c r="AA9">
-        <v>-169.82</v>
+        <v>-167.48</v>
       </c>
       <c r="AB9">
-        <v>-5.03</v>
+        <v>9.390000000000001</v>
       </c>
       <c r="AC9">
-        <v>57.37</v>
+        <v>68.18000000000001</v>
       </c>
       <c r="AD9">
-        <v>40.22</v>
+        <v>52.01</v>
       </c>
       <c r="AE9">
-        <v>224.19</v>
+        <v>222.82</v>
       </c>
       <c r="AF9">
-        <v>-32.54</v>
+        <v>5.83</v>
       </c>
       <c r="AG9">
-        <v>11257.4</v>
+        <v>11257.54</v>
       </c>
       <c r="AH9">
-        <v>10421.6</v>
+        <v>10431.26</v>
       </c>
       <c r="AI9">
         <v>11169.72</v>
@@ -1847,7 +1789,7 @@
         <v>48</v>
       </c>
       <c r="AK9">
-        <v>41.61</v>
+        <v>37.88</v>
       </c>
     </row>
   </sheetData>
@@ -1988,7 +1930,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F73"/>
+  <dimension ref="A1:F70"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -2008,1222 +1950,1127 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="C2" s="3" t="s">
+    </row>
+    <row r="5" spans="1:6">
+      <c r="A5" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="D2" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="F2" s="3" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6">
-      <c r="A3" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="B3" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="C3" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="D3" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="E3" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="F3" s="4" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6">
-      <c r="A4" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="B4" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="C4" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="D4" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="E4" s="4" t="s">
-        <v>61</v>
-      </c>
-      <c r="F4" s="4" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6">
-      <c r="A5" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="B5" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="C5" s="4" t="s">
-        <v>63</v>
-      </c>
-      <c r="D5" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="E5" s="4" t="s">
-        <v>64</v>
-      </c>
-      <c r="F5" s="4" t="s">
-        <v>65</v>
-      </c>
+      <c r="B5" s="2"/>
+      <c r="C5" s="2"/>
+      <c r="D5" s="2"/>
+      <c r="E5" s="2"/>
     </row>
     <row r="6" spans="1:6">
       <c r="A6" s="4" t="s">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>66</v>
+        <v>52</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>67</v>
+        <v>53</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>68</v>
-      </c>
-      <c r="F6" s="4" t="s">
-        <v>69</v>
+        <v>55</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6">
+      <c r="A7" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C7" s="5">
+        <v>-3.84</v>
+      </c>
+      <c r="D7" s="5">
+        <v>-4.08</v>
+      </c>
+      <c r="E7" s="6">
+        <v>-0.24</v>
       </c>
     </row>
     <row r="8" spans="1:6">
-      <c r="A8" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="B8" s="2"/>
-      <c r="C8" s="2"/>
-      <c r="D8" s="2"/>
-      <c r="E8" s="2"/>
+      <c r="A8" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C8" s="5">
+        <v>-12.01</v>
+      </c>
+      <c r="D8" s="5">
+        <v>-10.23</v>
+      </c>
+      <c r="E8" s="7">
+        <v>1.78</v>
+      </c>
     </row>
     <row r="9" spans="1:6">
       <c r="A9" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C9" s="5">
+        <v>-12.26</v>
+      </c>
+      <c r="D9" s="5">
+        <v>-12.46</v>
+      </c>
+      <c r="E9" s="6">
+        <v>-0.2</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C10" s="5">
+        <v>-11.02</v>
+      </c>
+      <c r="D10" s="5">
+        <v>-10.09</v>
+      </c>
+      <c r="E10" s="7">
+        <v>0.93</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C11" s="5">
+        <v>-14.09</v>
+      </c>
+      <c r="D11" s="5">
+        <v>-15.36</v>
+      </c>
+      <c r="E11" s="6">
+        <v>-1.27</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C12" s="5">
+        <v>-2.89</v>
+      </c>
+      <c r="D12" s="5">
+        <v>-3.33</v>
+      </c>
+      <c r="E12" s="6">
+        <v>-0.44</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="A13" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C13" s="5">
+        <v>-6.76</v>
+      </c>
+      <c r="D13" s="5">
+        <v>-4.82</v>
+      </c>
+      <c r="E13" s="7">
+        <v>1.94</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C14" s="5">
+        <v>-2.09</v>
+      </c>
+      <c r="D14" s="5">
+        <v>-1.86</v>
+      </c>
+      <c r="E14" s="7">
+        <v>0.23</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="A15" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C15" s="5">
+        <v>1.52</v>
+      </c>
+      <c r="D15" s="5">
+        <v>1.83</v>
+      </c>
+      <c r="E15" s="7">
+        <v>0.31</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="A16" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C16" s="5">
+        <v>-1.97</v>
+      </c>
+      <c r="D16" s="5">
+        <v>1.48</v>
+      </c>
+      <c r="E16" s="7">
+        <v>3.45</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C17" s="5">
+        <v>-1.92</v>
+      </c>
+      <c r="D17" s="5">
+        <v>-1.65</v>
+      </c>
+      <c r="E17" s="7">
+        <v>0.27</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C18" s="5">
+        <v>-4.07</v>
+      </c>
+      <c r="D18" s="5">
+        <v>-3.11</v>
+      </c>
+      <c r="E18" s="7">
+        <v>0.96</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C19" s="5">
+        <v>-3.1</v>
+      </c>
+      <c r="D19" s="5">
+        <v>-3.87</v>
+      </c>
+      <c r="E19" s="6">
+        <v>-0.77</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C20" s="5">
+        <v>6.32</v>
+      </c>
+      <c r="D20" s="5">
+        <v>7.4</v>
+      </c>
+      <c r="E20" s="7">
+        <v>1.08</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C21" s="5">
+        <v>-2.89</v>
+      </c>
+      <c r="D21" s="5">
+        <v>-2.12</v>
+      </c>
+      <c r="E21" s="7">
+        <v>0.77</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C22" s="5">
         <v>0</v>
       </c>
-      <c r="B9" s="3" t="s">
-        <v>71</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="D9" s="3" t="s">
-        <v>73</v>
-      </c>
-      <c r="E9" s="3" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10" s="5" t="s">
+      <c r="D22" s="5">
+        <v>1.29</v>
+      </c>
+      <c r="E22" s="7">
+        <v>1.29</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B10" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C10" s="6">
-        <v>-4.94</v>
-      </c>
-      <c r="D10" s="6">
-        <v>-3.84</v>
-      </c>
-      <c r="E10" s="7">
-        <v>1.1</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11" s="5" t="s">
+      <c r="B23" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C23" s="5">
+        <v>30.28</v>
+      </c>
+      <c r="D23" s="5">
+        <v>27.17</v>
+      </c>
+      <c r="E23" s="6">
+        <v>-3.11</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B11" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C11" s="6">
-        <v>-15.2</v>
-      </c>
-      <c r="D11" s="6">
-        <v>-12.01</v>
-      </c>
-      <c r="E11" s="7">
-        <v>3.19</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12" s="5" t="s">
+      <c r="B24" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C24" s="5">
+        <v>-47.2</v>
+      </c>
+      <c r="D24" s="5">
+        <v>-46.46</v>
+      </c>
+      <c r="E24" s="7">
+        <v>0.74</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B12" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C12" s="6">
-        <v>-13.39</v>
-      </c>
-      <c r="D12" s="6">
-        <v>-12.26</v>
-      </c>
-      <c r="E12" s="7">
-        <v>1.13</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13" s="5" t="s">
+      <c r="B25" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C25" s="5">
+        <v>4.82</v>
+      </c>
+      <c r="D25" s="5">
+        <v>2.22</v>
+      </c>
+      <c r="E25" s="6">
+        <v>-2.6</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="B13" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C13" s="6">
-        <v>-14.06</v>
-      </c>
-      <c r="D13" s="6">
-        <v>-11.02</v>
-      </c>
-      <c r="E13" s="7">
-        <v>3.04</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14" s="5" t="s">
+      <c r="B26" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C26" s="5">
+        <v>17.45</v>
+      </c>
+      <c r="D26" s="5">
+        <v>14</v>
+      </c>
+      <c r="E26" s="6">
+        <v>-3.45</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="B14" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C14" s="6">
-        <v>-18.36</v>
-      </c>
-      <c r="D14" s="6">
-        <v>-14.09</v>
-      </c>
-      <c r="E14" s="7">
-        <v>4.27</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15" s="5" t="s">
+      <c r="B27" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C27" s="5">
+        <v>41.59</v>
+      </c>
+      <c r="D27" s="5">
+        <v>40.31</v>
+      </c>
+      <c r="E27" s="6">
+        <v>-1.28</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="B15" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C15" s="6">
-        <v>-5.8</v>
-      </c>
-      <c r="D15" s="6">
-        <v>-2.89</v>
-      </c>
-      <c r="E15" s="7">
-        <v>2.91</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16" s="5" t="s">
+      <c r="B28" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C28" s="5">
+        <v>108.38</v>
+      </c>
+      <c r="D28" s="5">
+        <v>121.14</v>
+      </c>
+      <c r="E28" s="7">
+        <v>12.76</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="B16" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C16" s="6">
-        <v>-4.26</v>
-      </c>
-      <c r="D16" s="6">
-        <v>-6.76</v>
-      </c>
-      <c r="E16" s="8">
-        <v>-2.5</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5">
-      <c r="A17" s="5" t="s">
+      <c r="B29" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C29" s="5">
+        <v>-26.25</v>
+      </c>
+      <c r="D29" s="5">
+        <v>-24.68</v>
+      </c>
+      <c r="E29" s="7">
+        <v>1.57</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="B17" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C17" s="6">
-        <v>-3.49</v>
-      </c>
-      <c r="D17" s="6">
-        <v>-2.09</v>
-      </c>
-      <c r="E17" s="7">
-        <v>1.4</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5">
-      <c r="A18" s="5" t="s">
+      <c r="B30" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C30" s="5">
+        <v>-10.35</v>
+      </c>
+      <c r="D30" s="5">
+        <v>-11.46</v>
+      </c>
+      <c r="E30" s="6">
+        <v>-1.11</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5">
+      <c r="A31" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B18" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C18" s="6">
-        <v>0.76</v>
-      </c>
-      <c r="D18" s="6">
-        <v>1.52</v>
-      </c>
-      <c r="E18" s="7">
-        <v>0.76</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5">
-      <c r="A19" s="5" t="s">
+      <c r="B31" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C31" s="5">
+        <v>-3.66</v>
+      </c>
+      <c r="D31" s="5">
+        <v>-6.28</v>
+      </c>
+      <c r="E31" s="6">
+        <v>-2.62</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5">
+      <c r="A32" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B19" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C19" s="6">
-        <v>-1.83</v>
-      </c>
-      <c r="D19" s="6">
-        <v>-1.97</v>
-      </c>
-      <c r="E19" s="8">
-        <v>-0.14</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5">
-      <c r="A20" s="5" t="s">
+      <c r="B32" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C32" s="5">
+        <v>-24.01</v>
+      </c>
+      <c r="D32" s="5">
+        <v>-23.59</v>
+      </c>
+      <c r="E32" s="7">
+        <v>0.42</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5">
+      <c r="A33" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B20" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C20" s="6">
-        <v>-3.84</v>
-      </c>
-      <c r="D20" s="6">
-        <v>-1.92</v>
-      </c>
-      <c r="E20" s="7">
-        <v>1.92</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5">
-      <c r="A21" s="5" t="s">
+      <c r="B33" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C33" s="5">
+        <v>-6.47</v>
+      </c>
+      <c r="D33" s="5">
+        <v>-6.91</v>
+      </c>
+      <c r="E33" s="6">
+        <v>-0.44</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5">
+      <c r="A34" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="B21" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C21" s="6">
-        <v>-5.96</v>
-      </c>
-      <c r="D21" s="6">
-        <v>-4.07</v>
-      </c>
-      <c r="E21" s="7">
-        <v>1.89</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5">
-      <c r="A22" s="5" t="s">
+      <c r="B34" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C34" s="5">
+        <v>-7.4</v>
+      </c>
+      <c r="D34" s="5">
+        <v>-7.67</v>
+      </c>
+      <c r="E34" s="6">
+        <v>-0.27</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5">
+      <c r="A35" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="B22" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C22" s="6">
-        <v>-0.55</v>
-      </c>
-      <c r="D22" s="6">
-        <v>-3.1</v>
-      </c>
-      <c r="E22" s="8">
-        <v>-2.55</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5">
-      <c r="A23" s="5" t="s">
+      <c r="B35" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C35" s="5">
+        <v>-7.45</v>
+      </c>
+      <c r="D35" s="5">
+        <v>-7.32</v>
+      </c>
+      <c r="E35" s="7">
+        <v>0.13</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5">
+      <c r="A36" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="B23" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C23" s="6">
-        <v>6.15</v>
-      </c>
-      <c r="D23" s="6">
-        <v>6.32</v>
-      </c>
-      <c r="E23" s="7">
+      <c r="B36" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C36" s="5">
+        <v>6.22</v>
+      </c>
+      <c r="D36" s="5">
+        <v>5.74</v>
+      </c>
+      <c r="E36" s="6">
+        <v>-0.48</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5">
+      <c r="A37" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="B37" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C37" s="5">
+        <v>-9.460000000000001</v>
+      </c>
+      <c r="D37" s="5">
+        <v>-8.52</v>
+      </c>
+      <c r="E37" s="7">
+        <v>0.9399999999999999</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5">
+      <c r="A38" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="B38" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C38" s="5">
+        <v>-6.49</v>
+      </c>
+      <c r="D38" s="5">
+        <v>-8.609999999999999</v>
+      </c>
+      <c r="E38" s="6">
+        <v>-2.12</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5">
+      <c r="A39" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B39" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C39" s="5">
+        <v>-9.43</v>
+      </c>
+      <c r="D39" s="5">
+        <v>-10.78</v>
+      </c>
+      <c r="E39" s="6">
+        <v>-1.35</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5">
+      <c r="A40" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B40" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C40" s="5">
+        <v>-47.55</v>
+      </c>
+      <c r="D40" s="5">
+        <v>-46.97</v>
+      </c>
+      <c r="E40" s="7">
+        <v>0.58</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5">
+      <c r="A41" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B41" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C41" s="5">
+        <v>-13.86</v>
+      </c>
+      <c r="D41" s="5">
+        <v>-15.01</v>
+      </c>
+      <c r="E41" s="6">
+        <v>-1.15</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5">
+      <c r="A42" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B42" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C42" s="5">
+        <v>-21.52</v>
+      </c>
+      <c r="D42" s="5">
+        <v>-23.24</v>
+      </c>
+      <c r="E42" s="6">
+        <v>-1.72</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5">
+      <c r="A43" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B43" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C43" s="5">
+        <v>-17.95</v>
+      </c>
+      <c r="D43" s="5">
+        <v>-18.78</v>
+      </c>
+      <c r="E43" s="6">
+        <v>-0.83</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5">
+      <c r="A44" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B44" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C44" s="5">
+        <v>-17.82</v>
+      </c>
+      <c r="D44" s="5">
+        <v>-16.59</v>
+      </c>
+      <c r="E44" s="7">
+        <v>1.23</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5">
+      <c r="A45" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="B45" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C45" s="5">
+        <v>-32.01</v>
+      </c>
+      <c r="D45" s="5">
+        <v>-31.32</v>
+      </c>
+      <c r="E45" s="7">
+        <v>0.6899999999999999</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5">
+      <c r="A46" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="B46" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C46" s="5">
+        <v>-17.64</v>
+      </c>
+      <c r="D46" s="5">
+        <v>-17.29</v>
+      </c>
+      <c r="E46" s="7">
+        <v>0.35</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5">
+      <c r="A47" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B47" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C47" s="5">
+        <v>384.65</v>
+      </c>
+      <c r="D47" s="5">
+        <v>378.9</v>
+      </c>
+      <c r="E47" s="6">
+        <v>-5.75</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5">
+      <c r="A48" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B48" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C48" s="5">
+        <v>44.78</v>
+      </c>
+      <c r="D48" s="5">
+        <v>45.28</v>
+      </c>
+      <c r="E48" s="7">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5">
+      <c r="A49" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B49" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C49" s="5">
+        <v>2912</v>
+      </c>
+      <c r="D49" s="5">
+        <v>2873</v>
+      </c>
+      <c r="E49" s="6">
+        <v>-39</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5">
+      <c r="A50" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B50" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C50" s="5">
+        <v>902.25</v>
+      </c>
+      <c r="D50" s="5">
+        <v>882.5</v>
+      </c>
+      <c r="E50" s="6">
+        <v>-19.75</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5">
+      <c r="A51" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B51" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C51" s="5">
+        <v>12.8</v>
+      </c>
+      <c r="D51" s="5">
+        <v>12.67</v>
+      </c>
+      <c r="E51" s="6">
+        <v>-0.13</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5">
+      <c r="A52" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B52" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C52" s="5">
+        <v>11.44</v>
+      </c>
+      <c r="D52" s="5">
+        <v>11.61</v>
+      </c>
+      <c r="E52" s="7">
         <v>0.17</v>
       </c>
     </row>
-    <row r="24" spans="1:5">
-      <c r="A24" s="5" t="s">
+    <row r="53" spans="1:5">
+      <c r="A53" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="B24" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C24" s="6">
-        <v>-1.25</v>
-      </c>
-      <c r="D24" s="6">
-        <v>-2.89</v>
-      </c>
-      <c r="E24" s="8">
-        <v>-1.64</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5">
-      <c r="A25" s="5" t="s">
+      <c r="B53" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C53" s="5">
+        <v>3949.6</v>
+      </c>
+      <c r="D53" s="5">
+        <v>3989.7</v>
+      </c>
+      <c r="E53" s="7">
+        <v>40.1</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5">
+      <c r="A54" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="B25" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C25" s="6">
-        <v>-3.04</v>
-      </c>
-      <c r="D25" s="6">
-        <v>0</v>
-      </c>
-      <c r="E25" s="7">
-        <v>3.04</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5">
-      <c r="A26" s="5" t="s">
+      <c r="B54" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C54" s="5">
+        <v>10750</v>
+      </c>
+      <c r="D54" s="5">
+        <v>10795</v>
+      </c>
+      <c r="E54" s="7">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5">
+      <c r="A55" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B26" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C26" s="6">
-        <v>25.29</v>
-      </c>
-      <c r="D26" s="6">
-        <v>30.28</v>
-      </c>
-      <c r="E26" s="7">
-        <v>4.99</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5">
-      <c r="A27" s="5" t="s">
+      <c r="B55" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C55" s="5">
+        <v>48.19</v>
+      </c>
+      <c r="D55" s="5">
+        <v>44.52</v>
+      </c>
+      <c r="E55" s="6">
+        <v>-3.67</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5">
+      <c r="A56" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B27" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C27" s="6">
-        <v>-49.21</v>
-      </c>
-      <c r="D27" s="6">
-        <v>-47.2</v>
-      </c>
-      <c r="E27" s="7">
-        <v>2.01</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5">
-      <c r="A28" s="5" t="s">
+      <c r="B56" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C56" s="5">
+        <v>36.25</v>
+      </c>
+      <c r="D56" s="5">
+        <v>39.02</v>
+      </c>
+      <c r="E56" s="7">
+        <v>2.77</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5">
+      <c r="A57" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B28" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C28" s="6">
-        <v>1.78</v>
-      </c>
-      <c r="D28" s="6">
-        <v>4.82</v>
-      </c>
-      <c r="E28" s="7">
-        <v>3.04</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5">
-      <c r="A29" s="5" t="s">
+      <c r="B57" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C57" s="5">
+        <v>33.88</v>
+      </c>
+      <c r="D57" s="5">
+        <v>31.42</v>
+      </c>
+      <c r="E57" s="6">
+        <v>-2.46</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5">
+      <c r="A58" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="B29" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C29" s="6">
-        <v>14.94</v>
-      </c>
-      <c r="D29" s="6">
-        <v>17.45</v>
-      </c>
-      <c r="E29" s="7">
-        <v>2.51</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5">
-      <c r="A30" s="5" t="s">
+      <c r="B58" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C58" s="5">
+        <v>34.98</v>
+      </c>
+      <c r="D58" s="5">
+        <v>31.39</v>
+      </c>
+      <c r="E58" s="6">
+        <v>-3.59</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5">
+      <c r="A59" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="B30" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C30" s="6">
-        <v>38.02</v>
-      </c>
-      <c r="D30" s="6">
-        <v>41.59</v>
-      </c>
-      <c r="E30" s="7">
-        <v>3.57</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5">
-      <c r="A31" s="5" t="s">
+      <c r="B59" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C59" s="5">
+        <v>39.42</v>
+      </c>
+      <c r="D59" s="5">
+        <v>38.07</v>
+      </c>
+      <c r="E59" s="6">
+        <v>-1.35</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5">
+      <c r="A60" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="B31" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C31" s="6">
-        <v>100</v>
-      </c>
-      <c r="D31" s="6">
-        <v>108.38</v>
-      </c>
-      <c r="E31" s="7">
-        <v>8.380000000000001</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5">
-      <c r="A32" s="5" t="s">
+      <c r="B60" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C60" s="5">
+        <v>53.02</v>
+      </c>
+      <c r="D60" s="5">
+        <v>55.09</v>
+      </c>
+      <c r="E60" s="7">
+        <v>2.07</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5">
+      <c r="A61" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="B32" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C32" s="6">
-        <v>-27.04</v>
-      </c>
-      <c r="D32" s="6">
-        <v>-26.25</v>
-      </c>
-      <c r="E32" s="7">
-        <v>0.79</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5">
-      <c r="A33" s="5" t="s">
+      <c r="B61" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C61" s="5">
+        <v>39.58</v>
+      </c>
+      <c r="D61" s="5">
+        <v>43.57</v>
+      </c>
+      <c r="E61" s="7">
+        <v>3.99</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5">
+      <c r="A62" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="B33" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C33" s="6">
-        <v>-13.66</v>
-      </c>
-      <c r="D33" s="6">
-        <v>-10.35</v>
-      </c>
-      <c r="E33" s="7">
-        <v>3.31</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5">
-      <c r="A34" s="5" t="s">
+      <c r="B62" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C62" s="5">
+        <v>45.23</v>
+      </c>
+      <c r="D62" s="5">
+        <v>46.49</v>
+      </c>
+      <c r="E62" s="7">
+        <v>1.26</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5">
+      <c r="A63" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B34" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C34" s="6">
-        <v>-6.68</v>
-      </c>
-      <c r="D34" s="6">
-        <v>-3.66</v>
-      </c>
-      <c r="E34" s="7">
-        <v>3.02</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5">
-      <c r="A35" s="5" t="s">
+      <c r="B63" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C63" s="5">
+        <v>29.47</v>
+      </c>
+      <c r="D63" s="5">
+        <v>-59.1</v>
+      </c>
+      <c r="E63" s="6">
+        <v>-88.56999999999999</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5">
+      <c r="A64" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B35" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C35" s="6">
-        <v>-28.06</v>
-      </c>
-      <c r="D35" s="6">
-        <v>-24.01</v>
-      </c>
-      <c r="E35" s="7">
-        <v>4.05</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5">
-      <c r="A36" s="5" t="s">
+      <c r="B64" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C64" s="5">
+        <v>-44.73</v>
+      </c>
+      <c r="D64" s="5">
+        <v>-40.32</v>
+      </c>
+      <c r="E64" s="7">
+        <v>4.41</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5">
+      <c r="A65" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B36" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C36" s="6">
-        <v>-9.109999999999999</v>
-      </c>
-      <c r="D36" s="6">
-        <v>-6.47</v>
-      </c>
-      <c r="E36" s="7">
-        <v>2.64</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5">
-      <c r="A37" s="5" t="s">
+      <c r="B65" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C65" s="5">
+        <v>-47.74</v>
+      </c>
+      <c r="D65" s="5">
+        <v>-44.37</v>
+      </c>
+      <c r="E65" s="7">
+        <v>3.37</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5">
+      <c r="A66" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="B37" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C37" s="6">
-        <v>-8.720000000000001</v>
-      </c>
-      <c r="D37" s="6">
-        <v>-7.4</v>
-      </c>
-      <c r="E37" s="7">
-        <v>1.32</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5">
-      <c r="A38" s="5" t="s">
+      <c r="B66" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C66" s="5">
+        <v>33.07</v>
+      </c>
+      <c r="D66" s="5">
+        <v>-23.9</v>
+      </c>
+      <c r="E66" s="6">
+        <v>-56.97</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5">
+      <c r="A67" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="B38" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C38" s="6">
-        <v>-9.24</v>
-      </c>
-      <c r="D38" s="6">
-        <v>-7.45</v>
-      </c>
-      <c r="E38" s="7">
-        <v>1.79</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5">
-      <c r="A39" s="5" t="s">
+      <c r="B67" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C67" s="5">
+        <v>-45.87</v>
+      </c>
+      <c r="D67" s="5">
+        <v>-52.17</v>
+      </c>
+      <c r="E67" s="6">
+        <v>-6.3</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5">
+      <c r="A68" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="B39" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C39" s="6">
-        <v>3.03</v>
-      </c>
-      <c r="D39" s="6">
-        <v>6.22</v>
-      </c>
-      <c r="E39" s="7">
-        <v>3.19</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5">
-      <c r="A40" s="5" t="s">
+      <c r="B68" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C68" s="5">
+        <v>48.21</v>
+      </c>
+      <c r="D68" s="5">
+        <v>-23.68</v>
+      </c>
+      <c r="E68" s="6">
+        <v>-71.89</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5">
+      <c r="A69" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="B40" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C40" s="6">
-        <v>-11.76</v>
-      </c>
-      <c r="D40" s="6">
-        <v>-9.460000000000001</v>
-      </c>
-      <c r="E40" s="7">
-        <v>2.3</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5">
-      <c r="A41" s="5" t="s">
+      <c r="B69" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C69" s="5">
+        <v>-68.20999999999999</v>
+      </c>
+      <c r="D69" s="5">
+        <v>-60.61</v>
+      </c>
+      <c r="E69" s="7">
+        <v>7.6</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5">
+      <c r="A70" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="B41" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C41" s="6">
-        <v>-9.08</v>
-      </c>
-      <c r="D41" s="6">
-        <v>-6.49</v>
-      </c>
-      <c r="E41" s="7">
-        <v>2.59</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5">
-      <c r="A42" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B42" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C42" s="6">
-        <v>-10.47</v>
-      </c>
-      <c r="D42" s="6">
-        <v>-9.43</v>
-      </c>
-      <c r="E42" s="7">
-        <v>1.04</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5">
-      <c r="A43" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B43" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C43" s="6">
-        <v>-49.02</v>
-      </c>
-      <c r="D43" s="6">
-        <v>-47.55</v>
-      </c>
-      <c r="E43" s="7">
-        <v>1.47</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5">
-      <c r="A44" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B44" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C44" s="6">
-        <v>-15.46</v>
-      </c>
-      <c r="D44" s="6">
-        <v>-13.86</v>
-      </c>
-      <c r="E44" s="7">
-        <v>1.6</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5">
-      <c r="A45" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B45" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C45" s="6">
-        <v>-23.24</v>
-      </c>
-      <c r="D45" s="6">
-        <v>-21.52</v>
-      </c>
-      <c r="E45" s="7">
-        <v>1.72</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5">
-      <c r="A46" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B46" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C46" s="6">
-        <v>-18.78</v>
-      </c>
-      <c r="D46" s="6">
-        <v>-17.95</v>
-      </c>
-      <c r="E46" s="7">
-        <v>0.83</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5">
-      <c r="A47" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B47" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C47" s="6">
-        <v>-21.84</v>
-      </c>
-      <c r="D47" s="6">
-        <v>-17.82</v>
-      </c>
-      <c r="E47" s="7">
-        <v>4.02</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5">
-      <c r="A48" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B48" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C48" s="6">
-        <v>-32.27</v>
-      </c>
-      <c r="D48" s="6">
-        <v>-32.01</v>
-      </c>
-      <c r="E48" s="7">
-        <v>0.26</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5">
-      <c r="A49" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="B49" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C49" s="6">
-        <v>-19.4</v>
-      </c>
-      <c r="D49" s="6">
-        <v>-17.64</v>
-      </c>
-      <c r="E49" s="7">
-        <v>1.76</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5">
-      <c r="A50" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B50" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C50" s="6">
-        <v>380.25</v>
-      </c>
-      <c r="D50" s="6">
-        <v>384.65</v>
-      </c>
-      <c r="E50" s="7">
-        <v>4.4</v>
-      </c>
-    </row>
-    <row r="51" spans="1:5">
-      <c r="A51" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B51" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C51" s="6">
-        <v>43.53</v>
-      </c>
-      <c r="D51" s="6">
-        <v>44.78</v>
-      </c>
-      <c r="E51" s="7">
-        <v>1.25</v>
-      </c>
-    </row>
-    <row r="52" spans="1:5">
-      <c r="A52" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B52" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C52" s="6">
-        <v>2858</v>
-      </c>
-      <c r="D52" s="6">
-        <v>2912</v>
-      </c>
-      <c r="E52" s="7">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="53" spans="1:5">
-      <c r="A53" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B53" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C53" s="6">
-        <v>882.5</v>
-      </c>
-      <c r="D53" s="6">
-        <v>902.25</v>
-      </c>
-      <c r="E53" s="7">
-        <v>19.75</v>
-      </c>
-    </row>
-    <row r="54" spans="1:5">
-      <c r="A54" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B54" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C54" s="6">
-        <v>12.67</v>
-      </c>
-      <c r="D54" s="6">
-        <v>12.8</v>
-      </c>
-      <c r="E54" s="7">
-        <v>0.13</v>
-      </c>
-    </row>
-    <row r="55" spans="1:5">
-      <c r="A55" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B55" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C55" s="6">
-        <v>10.88</v>
-      </c>
-      <c r="D55" s="6">
-        <v>11.44</v>
-      </c>
-      <c r="E55" s="7">
-        <v>0.5600000000000001</v>
-      </c>
-    </row>
-    <row r="56" spans="1:5">
-      <c r="A56" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B56" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C56" s="6">
-        <v>3934.9</v>
-      </c>
-      <c r="D56" s="6">
-        <v>3949.6</v>
-      </c>
-      <c r="E56" s="7">
-        <v>14.7</v>
-      </c>
-    </row>
-    <row r="57" spans="1:5">
-      <c r="A57" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="B57" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C57" s="6">
-        <v>10520</v>
-      </c>
-      <c r="D57" s="6">
-        <v>10750</v>
-      </c>
-      <c r="E57" s="7">
-        <v>230</v>
-      </c>
-    </row>
-    <row r="58" spans="1:5">
-      <c r="A58" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B58" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C58" s="6">
-        <v>44.97</v>
-      </c>
-      <c r="D58" s="6">
-        <v>48.19</v>
-      </c>
-      <c r="E58" s="7">
-        <v>3.22</v>
-      </c>
-    </row>
-    <row r="59" spans="1:5">
-      <c r="A59" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B59" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C59" s="6">
-        <v>28.76</v>
-      </c>
-      <c r="D59" s="6">
-        <v>36.25</v>
-      </c>
-      <c r="E59" s="7">
-        <v>7.49</v>
-      </c>
-    </row>
-    <row r="60" spans="1:5">
-      <c r="A60" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B60" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C60" s="6">
-        <v>26.49</v>
-      </c>
-      <c r="D60" s="6">
-        <v>33.88</v>
-      </c>
-      <c r="E60" s="7">
-        <v>7.39</v>
-      </c>
-    </row>
-    <row r="61" spans="1:5">
-      <c r="A61" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B61" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C61" s="6">
-        <v>27.24</v>
-      </c>
-      <c r="D61" s="6">
-        <v>34.98</v>
-      </c>
-      <c r="E61" s="7">
-        <v>7.74</v>
-      </c>
-    </row>
-    <row r="62" spans="1:5">
-      <c r="A62" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B62" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C62" s="6">
-        <v>37.35</v>
-      </c>
-      <c r="D62" s="6">
-        <v>39.42</v>
-      </c>
-      <c r="E62" s="7">
-        <v>2.07</v>
-      </c>
-    </row>
-    <row r="63" spans="1:5">
-      <c r="A63" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B63" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C63" s="6">
-        <v>45.29</v>
-      </c>
-      <c r="D63" s="6">
-        <v>53.02</v>
-      </c>
-      <c r="E63" s="7">
-        <v>7.73</v>
-      </c>
-    </row>
-    <row r="64" spans="1:5">
-      <c r="A64" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B64" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C64" s="6">
-        <v>38.09</v>
-      </c>
-      <c r="D64" s="6">
-        <v>39.58</v>
-      </c>
-      <c r="E64" s="7">
-        <v>1.49</v>
-      </c>
-    </row>
-    <row r="65" spans="1:5">
-      <c r="A65" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="B65" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C65" s="6">
-        <v>38.4</v>
-      </c>
-      <c r="D65" s="6">
-        <v>45.23</v>
-      </c>
-      <c r="E65" s="7">
-        <v>6.83</v>
-      </c>
-    </row>
-    <row r="66" spans="1:5">
-      <c r="A66" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B66" s="5" t="s">
+      <c r="B70" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="C66" s="6">
-        <v>12.95</v>
-      </c>
-      <c r="D66" s="6">
-        <v>29.47</v>
-      </c>
-      <c r="E66" s="7">
-        <v>16.52</v>
-      </c>
-    </row>
-    <row r="67" spans="1:5">
-      <c r="A67" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B67" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C67" s="6">
-        <v>-65.11</v>
-      </c>
-      <c r="D67" s="6">
-        <v>-44.73</v>
-      </c>
-      <c r="E67" s="7">
-        <v>20.38</v>
-      </c>
-    </row>
-    <row r="68" spans="1:5">
-      <c r="A68" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B68" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C68" s="6">
-        <v>-82.25</v>
-      </c>
-      <c r="D68" s="6">
-        <v>-47.74</v>
-      </c>
-      <c r="E68" s="7">
-        <v>34.51</v>
-      </c>
-    </row>
-    <row r="69" spans="1:5">
-      <c r="A69" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B69" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C69" s="6">
-        <v>-33.95</v>
-      </c>
-      <c r="D69" s="6">
-        <v>33.07</v>
-      </c>
-      <c r="E69" s="7">
-        <v>67.02</v>
-      </c>
-    </row>
-    <row r="70" spans="1:5">
-      <c r="A70" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B70" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C70" s="6">
-        <v>-28.2</v>
-      </c>
-      <c r="D70" s="6">
-        <v>-45.87</v>
-      </c>
-      <c r="E70" s="8">
-        <v>-17.67</v>
-      </c>
-    </row>
-    <row r="71" spans="1:5">
-      <c r="A71" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B71" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C71" s="6">
-        <v>14.21</v>
-      </c>
-      <c r="D71" s="6">
-        <v>48.21</v>
-      </c>
-      <c r="E71" s="7">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="72" spans="1:5">
-      <c r="A72" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B72" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C72" s="6">
-        <v>-78.52</v>
-      </c>
-      <c r="D72" s="6">
-        <v>-68.20999999999999</v>
-      </c>
-      <c r="E72" s="7">
-        <v>10.31</v>
-      </c>
-    </row>
-    <row r="73" spans="1:5">
-      <c r="A73" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="B73" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C73" s="6">
-        <v>-24.75</v>
-      </c>
-      <c r="D73" s="6">
+      <c r="C70" s="5">
         <v>-32.54</v>
       </c>
-      <c r="E73" s="8">
-        <v>-7.79</v>
+      <c r="D70" s="5">
+        <v>5.83</v>
+      </c>
+      <c r="E70" s="7">
+        <v>38.37</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A8:E8"/>
+    <mergeCell ref="A5:E5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3243,60 +3090,60 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="28" customHeight="1">
-      <c r="A1" s="9" t="s">
+      <c r="A1" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="9" t="s">
-        <v>75</v>
-      </c>
-      <c r="C1" s="9" t="s">
-        <v>76</v>
-      </c>
-      <c r="D1" s="9" t="s">
-        <v>77</v>
-      </c>
-      <c r="E1" s="9" t="s">
-        <v>78</v>
-      </c>
-      <c r="F1" s="9" t="s">
-        <v>79</v>
-      </c>
-      <c r="G1" s="9" t="s">
-        <v>80</v>
-      </c>
-      <c r="H1" s="9" t="s">
-        <v>81</v>
-      </c>
-      <c r="I1" s="9" t="s">
-        <v>82</v>
+      <c r="B1" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="C1" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="D1" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="E1" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="F1" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="G1" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="H1" s="8" t="s">
+        <v>62</v>
+      </c>
+      <c r="I1" s="8" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="10" t="s">
+      <c r="A2" s="9" t="s">
         <v>45</v>
       </c>
-      <c r="B2" s="11">
+      <c r="B2" s="10">
         <v>48.44</v>
       </c>
-      <c r="C2" s="12">
+      <c r="C2" s="11">
         <v>8</v>
       </c>
-      <c r="D2" s="11">
-        <v>41.3</v>
-      </c>
-      <c r="E2" s="11">
+      <c r="D2" s="10">
+        <v>41.2</v>
+      </c>
+      <c r="E2" s="10">
         <v>40</v>
       </c>
-      <c r="F2" s="11">
-        <v>-8.1</v>
-      </c>
-      <c r="G2" s="11">
-        <v>-7.3</v>
-      </c>
-      <c r="H2" s="11">
+      <c r="F2" s="10">
+        <v>-7.8</v>
+      </c>
+      <c r="G2" s="10">
+        <v>-7.9</v>
+      </c>
+      <c r="H2" s="10">
         <v>56.1</v>
       </c>
-      <c r="I2" s="11">
+      <c r="I2" s="10">
         <v>0</v>
       </c>
     </row>
@@ -3398,55 +3245,55 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8">
-      <c r="A1" s="13" t="s">
+      <c r="A1" s="12" t="s">
         <v>37</v>
       </c>
-      <c r="B1" s="13" t="s">
+      <c r="B1" s="12" t="s">
         <v>43</v>
       </c>
-      <c r="C1" s="13" t="s">
+      <c r="C1" s="12" t="s">
         <v>40</v>
       </c>
-      <c r="D1" s="13" t="s">
+      <c r="D1" s="12" t="s">
         <v>39</v>
       </c>
-      <c r="E1" s="13" t="s">
+      <c r="E1" s="12" t="s">
         <v>44</v>
       </c>
-      <c r="F1" s="13" t="s">
+      <c r="F1" s="12" t="s">
         <v>41</v>
       </c>
-      <c r="G1" s="13" t="s">
+      <c r="G1" s="12" t="s">
         <v>38</v>
       </c>
-      <c r="H1" s="13" t="s">
+      <c r="H1" s="12" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="2" spans="1:8">
-      <c r="A2" s="14">
-        <v>0.2899</v>
-      </c>
-      <c r="B2" s="14">
-        <v>0.1511</v>
-      </c>
-      <c r="C2" s="14">
-        <v>0.1282</v>
-      </c>
-      <c r="D2" s="14">
-        <v>0.1219</v>
-      </c>
-      <c r="E2" s="14">
-        <v>0.0839</v>
-      </c>
-      <c r="F2" s="14">
-        <v>0.0365</v>
-      </c>
-      <c r="G2" s="14">
-        <v>-0.3019</v>
-      </c>
-      <c r="H2" s="14">
-        <v>-0.3053</v>
+      <c r="A2" s="13">
+        <v>0.2863</v>
+      </c>
+      <c r="B2" s="13">
+        <v>0.1518</v>
+      </c>
+      <c r="C2" s="13">
+        <v>0.1197</v>
+      </c>
+      <c r="D2" s="13">
+        <v>0.1091</v>
+      </c>
+      <c r="E2" s="13">
+        <v>0.08349999999999999</v>
+      </c>
+      <c r="F2" s="13">
+        <v>0.0334</v>
+      </c>
+      <c r="G2" s="13">
+        <v>-0.2973</v>
+      </c>
+      <c r="H2" s="13">
+        <v>-0.3036</v>
       </c>
     </row>
   </sheetData>

--- a/BIRLA_GROUP_Technical_Metrics.xlsx
+++ b/BIRLA_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="276" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="280" uniqueCount="64">
   <si>
     <t>Symbol</t>
   </si>
@@ -258,14 +258,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF006100"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF9C0006"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -298,13 +298,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -755,8 +755,8 @@
     <col min="13" max="13" width="10.7109375" customWidth="1"/>
     <col min="14" max="14" width="11.7109375" customWidth="1"/>
     <col min="15" max="15" width="10.7109375" customWidth="1"/>
-    <col min="16" max="17" width="9.7109375" customWidth="1"/>
-    <col min="18" max="19" width="10.7109375" customWidth="1"/>
+    <col min="16" max="18" width="9.7109375" customWidth="1"/>
+    <col min="19" max="19" width="10.7109375" customWidth="1"/>
     <col min="20" max="20" width="22.7109375" customWidth="1"/>
     <col min="21" max="21" width="9.7109375" customWidth="1"/>
     <col min="22" max="22" width="10.7109375" customWidth="1"/>
@@ -896,10 +896,10 @@
         <v>45</v>
       </c>
       <c r="C2">
-        <v>378.9</v>
+        <v>382.25</v>
       </c>
       <c r="D2">
-        <v>-1.49</v>
+        <v>0.88</v>
       </c>
       <c r="E2">
         <v>424.7</v>
@@ -908,46 +908,46 @@
         <v>292.25</v>
       </c>
       <c r="G2">
-        <v>-10.78</v>
+        <v>-10</v>
       </c>
       <c r="H2">
-        <v>29.65</v>
+        <v>30.8</v>
       </c>
       <c r="I2">
-        <v>1.83</v>
+        <v>3.69</v>
       </c>
       <c r="J2">
-        <v>-4.08</v>
+        <v>0.91</v>
       </c>
       <c r="K2">
-        <v>-6.28</v>
+        <v>-4.37</v>
       </c>
       <c r="L2">
-        <v>27.17</v>
+        <v>30.31</v>
       </c>
       <c r="M2">
-        <v>28.63</v>
+        <v>29</v>
       </c>
       <c r="N2">
-        <v>74</v>
+        <v>87</v>
       </c>
       <c r="O2">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="P2">
-        <v>378.63</v>
+        <v>381.35</v>
       </c>
       <c r="Q2">
-        <v>385.11</v>
+        <v>385.16</v>
       </c>
       <c r="R2">
-        <v>397.22</v>
+        <v>396.46</v>
       </c>
       <c r="S2">
-        <v>365.76</v>
+        <v>365.93</v>
       </c>
       <c r="T2">
-        <v>3.59</v>
+        <v>4.46</v>
       </c>
       <c r="U2" t="s">
         <v>46</v>
@@ -962,34 +962,34 @@
         <v>2</v>
       </c>
       <c r="Y2">
-        <v>44.52</v>
+        <v>47.05</v>
       </c>
       <c r="Z2">
-        <v>-5.36</v>
+        <v>-4.86</v>
       </c>
       <c r="AA2">
-        <v>-5.72</v>
+        <v>-5.55</v>
       </c>
       <c r="AB2">
-        <v>0.36</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AC2">
-        <v>69.15000000000001</v>
+        <v>80.01000000000001</v>
       </c>
       <c r="AD2">
-        <v>57.62</v>
+        <v>71.37</v>
       </c>
       <c r="AE2">
-        <v>9.57</v>
+        <v>9.52</v>
       </c>
       <c r="AF2">
-        <v>-59.1</v>
+        <v>-55.42</v>
       </c>
       <c r="AG2">
-        <v>407.04</v>
+        <v>407.05</v>
       </c>
       <c r="AH2">
-        <v>363.18</v>
+        <v>363.26</v>
       </c>
       <c r="AI2">
         <v>398.61</v>
@@ -998,7 +998,7 @@
         <v>48</v>
       </c>
       <c r="AK2">
-        <v>23.44</v>
+        <v>20.35</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1009,10 +1009,10 @@
         <v>45</v>
       </c>
       <c r="C3">
-        <v>45.28</v>
+        <v>44.86</v>
       </c>
       <c r="D3">
-        <v>1.12</v>
+        <v>-0.93</v>
       </c>
       <c r="E3">
         <v>85.38</v>
@@ -1021,46 +1021,46 @@
         <v>43.18</v>
       </c>
       <c r="G3">
-        <v>-46.97</v>
+        <v>-47.46</v>
       </c>
       <c r="H3">
-        <v>4.86</v>
+        <v>3.89</v>
       </c>
       <c r="I3">
-        <v>1.48</v>
+        <v>3.89</v>
       </c>
       <c r="J3">
-        <v>-10.23</v>
+        <v>-8.49</v>
       </c>
       <c r="K3">
-        <v>-23.59</v>
+        <v>-23.55</v>
       </c>
       <c r="L3">
-        <v>-46.46</v>
+        <v>-46.08</v>
       </c>
       <c r="M3">
-        <v>-29.73</v>
+        <v>-30.04</v>
       </c>
       <c r="N3">
         <v>13</v>
       </c>
       <c r="O3">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="P3">
-        <v>44.08</v>
+        <v>44.42</v>
       </c>
       <c r="Q3">
-        <v>46.77</v>
+        <v>46.53</v>
       </c>
       <c r="R3">
-        <v>51.65</v>
+        <v>51.33</v>
       </c>
       <c r="S3">
-        <v>60.98</v>
+        <v>60.82</v>
       </c>
       <c r="T3">
-        <v>-25.75</v>
+        <v>-26.24</v>
       </c>
       <c r="U3" t="s">
         <v>46</v>
@@ -1075,34 +1075,34 @@
         <v>0</v>
       </c>
       <c r="Y3">
-        <v>39.02</v>
+        <v>37.55</v>
       </c>
       <c r="Z3">
-        <v>-2.14</v>
+        <v>-2.02</v>
       </c>
       <c r="AA3">
-        <v>-2.23</v>
+        <v>-2.19</v>
       </c>
       <c r="AB3">
-        <v>0.09</v>
+        <v>0.17</v>
       </c>
       <c r="AC3">
-        <v>78.28</v>
+        <v>95.61</v>
       </c>
       <c r="AD3">
-        <v>56.43</v>
+        <v>77.45999999999999</v>
       </c>
       <c r="AE3">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AF3">
-        <v>-40.32</v>
+        <v>-65.7</v>
       </c>
       <c r="AG3">
-        <v>51.78</v>
+        <v>51.4</v>
       </c>
       <c r="AH3">
-        <v>41.76</v>
+        <v>41.65</v>
       </c>
       <c r="AI3">
         <v>48.29</v>
@@ -1111,7 +1111,7 @@
         <v>48</v>
       </c>
       <c r="AK3">
-        <v>34.54</v>
+        <v>31.6</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1122,10 +1122,10 @@
         <v>45</v>
       </c>
       <c r="C4">
-        <v>2873</v>
+        <v>2885.9</v>
       </c>
       <c r="D4">
-        <v>-1.34</v>
+        <v>0.45</v>
       </c>
       <c r="E4">
         <v>3380.5</v>
@@ -1134,25 +1134,25 @@
         <v>2531.1</v>
       </c>
       <c r="G4">
-        <v>-15.01</v>
+        <v>-14.63</v>
       </c>
       <c r="H4">
-        <v>13.51</v>
+        <v>14.02</v>
       </c>
       <c r="I4">
-        <v>-1.65</v>
+        <v>1.02</v>
       </c>
       <c r="J4">
-        <v>-12.46</v>
+        <v>-8.99</v>
       </c>
       <c r="K4">
-        <v>-6.91</v>
+        <v>-6.09</v>
       </c>
       <c r="L4">
-        <v>2.22</v>
+        <v>2.66</v>
       </c>
       <c r="M4">
-        <v>10.91</v>
+        <v>11.01</v>
       </c>
       <c r="N4">
         <v>50</v>
@@ -1161,19 +1161,19 @@
         <v>58</v>
       </c>
       <c r="P4">
-        <v>2877.96</v>
+        <v>2883.78</v>
       </c>
       <c r="Q4">
-        <v>3046.77</v>
+        <v>3031.71</v>
       </c>
       <c r="R4">
-        <v>3189.46</v>
+        <v>3184.42</v>
       </c>
       <c r="S4">
-        <v>2980.53</v>
+        <v>2980.87</v>
       </c>
       <c r="T4">
-        <v>-3.61</v>
+        <v>-3.19</v>
       </c>
       <c r="U4" t="s">
         <v>46</v>
@@ -1188,34 +1188,34 @@
         <v>1</v>
       </c>
       <c r="Y4">
-        <v>31.42</v>
+        <v>33.15</v>
       </c>
       <c r="Z4">
-        <v>-96.04000000000001</v>
+        <v>-94.67</v>
       </c>
       <c r="AA4">
-        <v>-79.13</v>
+        <v>-82.23999999999999</v>
       </c>
       <c r="AB4">
-        <v>-16.9</v>
+        <v>-12.43</v>
       </c>
       <c r="AC4">
-        <v>32.36</v>
+        <v>42.33</v>
       </c>
       <c r="AD4">
-        <v>23.94</v>
+        <v>34.09</v>
       </c>
       <c r="AE4">
-        <v>61.65</v>
+        <v>60.34</v>
       </c>
       <c r="AF4">
-        <v>-44.37</v>
+        <v>-43.7</v>
       </c>
       <c r="AG4">
-        <v>3310.77</v>
+        <v>3296.39</v>
       </c>
       <c r="AH4">
-        <v>2782.76</v>
+        <v>2767.03</v>
       </c>
       <c r="AI4">
         <v>3061.2</v>
@@ -1224,7 +1224,7 @@
         <v>48</v>
       </c>
       <c r="AK4">
-        <v>66.08</v>
+        <v>65.84</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1235,10 +1235,10 @@
         <v>45</v>
       </c>
       <c r="C5">
-        <v>882.5</v>
+        <v>893.85</v>
       </c>
       <c r="D5">
-        <v>-2.19</v>
+        <v>1.29</v>
       </c>
       <c r="E5">
         <v>1149.7</v>
@@ -1247,46 +1247,46 @@
         <v>760.1</v>
       </c>
       <c r="G5">
-        <v>-23.24</v>
+        <v>-22.25</v>
       </c>
       <c r="H5">
-        <v>16.1</v>
+        <v>17.6</v>
       </c>
       <c r="I5">
-        <v>-3.11</v>
+        <v>0.42</v>
       </c>
       <c r="J5">
-        <v>-10.09</v>
+        <v>-6.76</v>
       </c>
       <c r="K5">
-        <v>-7.67</v>
+        <v>-6.82</v>
       </c>
       <c r="L5">
-        <v>14</v>
+        <v>15.49</v>
       </c>
       <c r="M5">
-        <v>11.97</v>
+        <v>11.15</v>
       </c>
       <c r="N5">
         <v>62</v>
       </c>
       <c r="O5">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="P5">
-        <v>891.55</v>
+        <v>892.29</v>
       </c>
       <c r="Q5">
-        <v>944.95</v>
+        <v>941</v>
       </c>
       <c r="R5">
-        <v>995.5599999999999</v>
+        <v>993.03</v>
       </c>
       <c r="S5">
-        <v>983.22</v>
+        <v>983.3200000000001</v>
       </c>
       <c r="T5">
-        <v>-10.24</v>
+        <v>-9.1</v>
       </c>
       <c r="U5" t="s">
         <v>46</v>
@@ -1301,43 +1301,43 @@
         <v>1</v>
       </c>
       <c r="Y5">
-        <v>31.39</v>
+        <v>35.49</v>
       </c>
       <c r="Z5">
-        <v>-29.62</v>
+        <v>-29.34</v>
       </c>
       <c r="AA5">
-        <v>-23.93</v>
+        <v>-25.01</v>
       </c>
       <c r="AB5">
-        <v>-5.69</v>
+        <v>-4.33</v>
       </c>
       <c r="AC5">
-        <v>23.89</v>
+        <v>40.3</v>
       </c>
       <c r="AD5">
-        <v>17.24</v>
+        <v>28.09</v>
       </c>
       <c r="AE5">
-        <v>21.63</v>
+        <v>22.99</v>
       </c>
       <c r="AF5">
-        <v>-23.9</v>
+        <v>43.67</v>
       </c>
       <c r="AG5">
-        <v>1021.46</v>
+        <v>1019.6</v>
       </c>
       <c r="AH5">
-        <v>868.4299999999999</v>
+        <v>862.41</v>
       </c>
       <c r="AI5">
-        <v>956.1</v>
+        <v>946.48</v>
       </c>
       <c r="AJ5" t="s">
         <v>48</v>
       </c>
       <c r="AK5">
-        <v>47.03</v>
+        <v>49.81</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1348,10 +1348,10 @@
         <v>45</v>
       </c>
       <c r="C6">
-        <v>12.67</v>
+        <v>12.52</v>
       </c>
       <c r="D6">
-        <v>-1.02</v>
+        <v>-1.18</v>
       </c>
       <c r="E6">
         <v>15.6</v>
@@ -1360,46 +1360,46 @@
         <v>8.359999999999999</v>
       </c>
       <c r="G6">
-        <v>-18.78</v>
+        <v>-19.74</v>
       </c>
       <c r="H6">
-        <v>51.56</v>
+        <v>49.76</v>
       </c>
       <c r="I6">
-        <v>-3.87</v>
+        <v>-2.19</v>
       </c>
       <c r="J6">
-        <v>-15.36</v>
+        <v>-13.36</v>
       </c>
       <c r="K6">
-        <v>-7.32</v>
+        <v>-9.859999999999999</v>
       </c>
       <c r="L6">
-        <v>40.31</v>
+        <v>38.5</v>
       </c>
       <c r="M6">
-        <v>3.34</v>
+        <v>3.39</v>
       </c>
       <c r="N6">
-        <v>87</v>
+        <v>74</v>
       </c>
       <c r="O6">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="P6">
-        <v>12.79</v>
+        <v>12.73</v>
       </c>
       <c r="Q6">
-        <v>13.46</v>
+        <v>13.37</v>
       </c>
       <c r="R6">
         <v>13.88</v>
       </c>
       <c r="S6">
-        <v>12.29</v>
+        <v>12.3</v>
       </c>
       <c r="T6">
-        <v>3.06</v>
+        <v>1.81</v>
       </c>
       <c r="U6" t="s">
         <v>46</v>
@@ -1414,43 +1414,43 @@
         <v>2</v>
       </c>
       <c r="Y6">
-        <v>38.07</v>
+        <v>36.51</v>
       </c>
       <c r="Z6">
-        <v>-0.41</v>
+        <v>-0.43</v>
       </c>
       <c r="AA6">
-        <v>-0.33</v>
+        <v>-0.35</v>
       </c>
       <c r="AB6">
-        <v>-0.08</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="AC6">
-        <v>29.55</v>
+        <v>29.4</v>
       </c>
       <c r="AD6">
-        <v>30.17</v>
+        <v>30.35</v>
       </c>
       <c r="AE6">
         <v>0.44</v>
       </c>
       <c r="AF6">
-        <v>-52.17</v>
+        <v>-26.32</v>
       </c>
       <c r="AG6">
-        <v>14.78</v>
+        <v>14.7</v>
       </c>
       <c r="AH6">
-        <v>12.13</v>
+        <v>12.04</v>
       </c>
       <c r="AI6">
-        <v>14.06</v>
+        <v>14.02</v>
       </c>
       <c r="AJ6" t="s">
         <v>48</v>
       </c>
       <c r="AK6">
-        <v>41.23</v>
+        <v>42.78</v>
       </c>
     </row>
     <row r="7" spans="1:37">
@@ -1461,10 +1461,10 @@
         <v>45</v>
       </c>
       <c r="C7">
-        <v>11.61</v>
+        <v>11.35</v>
       </c>
       <c r="D7">
-        <v>1.49</v>
+        <v>-2.24</v>
       </c>
       <c r="E7">
         <v>13.92</v>
@@ -1473,25 +1473,25 @@
         <v>4.69</v>
       </c>
       <c r="G7">
-        <v>-16.59</v>
+        <v>-18.46</v>
       </c>
       <c r="H7">
-        <v>147.55</v>
+        <v>142</v>
       </c>
       <c r="I7">
-        <v>7.4</v>
+        <v>7.48</v>
       </c>
       <c r="J7">
-        <v>-3.33</v>
+        <v>-9.92</v>
       </c>
       <c r="K7">
-        <v>5.74</v>
+        <v>1.43</v>
       </c>
       <c r="L7">
-        <v>121.14</v>
+        <v>118.69</v>
       </c>
       <c r="M7">
-        <v>-30.36</v>
+        <v>-30.35</v>
       </c>
       <c r="N7">
         <v>99</v>
@@ -1500,19 +1500,19 @@
         <v>94</v>
       </c>
       <c r="P7">
-        <v>11.11</v>
+        <v>11.27</v>
       </c>
       <c r="Q7">
-        <v>11.25</v>
+        <v>11.2</v>
       </c>
       <c r="R7">
-        <v>11.58</v>
+        <v>11.53</v>
       </c>
       <c r="S7">
         <v>10.84</v>
       </c>
       <c r="T7">
-        <v>7.09</v>
+        <v>4.75</v>
       </c>
       <c r="U7" t="s">
         <v>46</v>
@@ -1527,34 +1527,34 @@
         <v>2</v>
       </c>
       <c r="Y7">
-        <v>55.09</v>
+        <v>51.36</v>
       </c>
       <c r="Z7">
-        <v>-0.12</v>
+        <v>-0.09</v>
       </c>
       <c r="AA7">
-        <v>-0.18</v>
+        <v>-0.16</v>
       </c>
       <c r="AB7">
-        <v>0.06</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="AC7">
-        <v>93.34</v>
+        <v>94.48</v>
       </c>
       <c r="AD7">
-        <v>84.17</v>
+        <v>92.83</v>
       </c>
       <c r="AE7">
-        <v>0.63</v>
+        <v>0.62</v>
       </c>
       <c r="AF7">
-        <v>-23.68</v>
+        <v>-42.64</v>
       </c>
       <c r="AG7">
-        <v>12.39</v>
+        <v>12.22</v>
       </c>
       <c r="AH7">
-        <v>10.12</v>
+        <v>10.19</v>
       </c>
       <c r="AI7">
         <v>12.04</v>
@@ -1563,7 +1563,7 @@
         <v>48</v>
       </c>
       <c r="AK7">
-        <v>27.8</v>
+        <v>27.43</v>
       </c>
     </row>
     <row r="8" spans="1:37">
@@ -1574,10 +1574,10 @@
         <v>45</v>
       </c>
       <c r="C8">
-        <v>3989.7</v>
+        <v>3969.3</v>
       </c>
       <c r="D8">
-        <v>1.02</v>
+        <v>-0.51</v>
       </c>
       <c r="E8">
         <v>5809.5</v>
@@ -1586,46 +1586,46 @@
         <v>3892.3</v>
       </c>
       <c r="G8">
-        <v>-31.32</v>
+        <v>-31.68</v>
       </c>
       <c r="H8">
-        <v>2.5</v>
+        <v>1.98</v>
       </c>
       <c r="I8">
-        <v>-2.12</v>
+        <v>0.53</v>
       </c>
       <c r="J8">
-        <v>-4.82</v>
+        <v>-2.76</v>
       </c>
       <c r="K8">
-        <v>-8.52</v>
+        <v>-10.02</v>
       </c>
       <c r="L8">
-        <v>-24.68</v>
+        <v>-25.06</v>
       </c>
       <c r="M8">
-        <v>15.18</v>
+        <v>15.35</v>
       </c>
       <c r="N8">
         <v>26</v>
       </c>
       <c r="O8">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="P8">
-        <v>3952.08</v>
+        <v>3956.24</v>
       </c>
       <c r="Q8">
-        <v>4003.16</v>
+        <v>3999.02</v>
       </c>
       <c r="R8">
-        <v>4206.92</v>
+        <v>4199.42</v>
       </c>
       <c r="S8">
-        <v>4482</v>
+        <v>4475.03</v>
       </c>
       <c r="T8">
-        <v>-10.98</v>
+        <v>-11.3</v>
       </c>
       <c r="U8" t="s">
         <v>46</v>
@@ -1640,34 +1640,34 @@
         <v>0</v>
       </c>
       <c r="Y8">
-        <v>43.57</v>
+        <v>42.05</v>
       </c>
       <c r="Z8">
-        <v>-67.95</v>
+        <v>-64.53</v>
       </c>
       <c r="AA8">
-        <v>-76.15000000000001</v>
+        <v>-73.83</v>
       </c>
       <c r="AB8">
-        <v>8.199999999999999</v>
+        <v>9.289999999999999</v>
       </c>
       <c r="AC8">
-        <v>62.97</v>
+        <v>70.26000000000001</v>
       </c>
       <c r="AD8">
-        <v>56.01</v>
+        <v>62.14</v>
       </c>
       <c r="AE8">
-        <v>103.2</v>
+        <v>99.33</v>
       </c>
       <c r="AF8">
-        <v>-60.61</v>
+        <v>-62.15</v>
       </c>
       <c r="AG8">
-        <v>4110.61</v>
+        <v>4104.88</v>
       </c>
       <c r="AH8">
-        <v>3895.71</v>
+        <v>3893.15</v>
       </c>
       <c r="AI8">
         <v>4246.97</v>
@@ -1676,7 +1676,7 @@
         <v>48</v>
       </c>
       <c r="AK8">
-        <v>33.99</v>
+        <v>30.45</v>
       </c>
     </row>
     <row r="9" spans="1:37">
@@ -1687,10 +1687,10 @@
         <v>45</v>
       </c>
       <c r="C9">
-        <v>10795</v>
+        <v>10862</v>
       </c>
       <c r="D9">
-        <v>0.42</v>
+        <v>0.62</v>
       </c>
       <c r="E9">
         <v>13052</v>
@@ -1699,46 +1699,46 @@
         <v>10362</v>
       </c>
       <c r="G9">
-        <v>-17.29</v>
+        <v>-16.78</v>
       </c>
       <c r="H9">
+        <v>4.83</v>
+      </c>
+      <c r="I9">
         <v>4.18</v>
       </c>
-      <c r="I9">
-        <v>1.29</v>
-      </c>
       <c r="J9">
-        <v>-1.86</v>
+        <v>1.54</v>
       </c>
       <c r="K9">
-        <v>-8.609999999999999</v>
+        <v>-7.72</v>
       </c>
       <c r="L9">
-        <v>-11.46</v>
+        <v>-11.55</v>
       </c>
       <c r="M9">
-        <v>8.35</v>
+        <v>8.48</v>
       </c>
       <c r="N9">
         <v>38</v>
       </c>
       <c r="O9">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="P9">
-        <v>10633.2</v>
+        <v>10720.4</v>
       </c>
       <c r="Q9">
-        <v>10844.4</v>
+        <v>10852.5</v>
       </c>
       <c r="R9">
-        <v>11256.16</v>
+        <v>11232.4</v>
       </c>
       <c r="S9">
-        <v>11671.63</v>
+        <v>11666.97</v>
       </c>
       <c r="T9">
-        <v>-7.51</v>
+        <v>-6.9</v>
       </c>
       <c r="U9" t="s">
         <v>46</v>
@@ -1753,34 +1753,34 @@
         <v>0</v>
       </c>
       <c r="Y9">
-        <v>46.49</v>
+        <v>48.38</v>
       </c>
       <c r="Z9">
-        <v>-158.09</v>
+        <v>-137.81</v>
       </c>
       <c r="AA9">
-        <v>-167.48</v>
+        <v>-161.54</v>
       </c>
       <c r="AB9">
-        <v>9.390000000000001</v>
+        <v>23.73</v>
       </c>
       <c r="AC9">
-        <v>68.18000000000001</v>
+        <v>89.91</v>
       </c>
       <c r="AD9">
-        <v>52.01</v>
+        <v>71.81999999999999</v>
       </c>
       <c r="AE9">
-        <v>222.82</v>
+        <v>220.55</v>
       </c>
       <c r="AF9">
-        <v>5.83</v>
+        <v>21.41</v>
       </c>
       <c r="AG9">
-        <v>11257.54</v>
+        <v>11260.03</v>
       </c>
       <c r="AH9">
-        <v>10431.26</v>
+        <v>10444.97</v>
       </c>
       <c r="AI9">
         <v>11169.72</v>
@@ -1789,7 +1789,7 @@
         <v>48</v>
       </c>
       <c r="AK9">
-        <v>37.88</v>
+        <v>33.17</v>
       </c>
     </row>
   </sheetData>
@@ -1930,7 +1930,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F70"/>
+  <dimension ref="A1:F72"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -1987,13 +1987,13 @@
         <v>9</v>
       </c>
       <c r="C7" s="5">
-        <v>-3.84</v>
+        <v>-4.08</v>
       </c>
       <c r="D7" s="5">
-        <v>-4.08</v>
+        <v>0.91</v>
       </c>
       <c r="E7" s="6">
-        <v>-0.24</v>
+        <v>4.99</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -2004,13 +2004,13 @@
         <v>9</v>
       </c>
       <c r="C8" s="5">
-        <v>-12.01</v>
+        <v>-10.23</v>
       </c>
       <c r="D8" s="5">
-        <v>-10.23</v>
-      </c>
-      <c r="E8" s="7">
-        <v>1.78</v>
+        <v>-8.49</v>
+      </c>
+      <c r="E8" s="6">
+        <v>1.74</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -2021,13 +2021,13 @@
         <v>9</v>
       </c>
       <c r="C9" s="5">
-        <v>-12.26</v>
+        <v>-12.46</v>
       </c>
       <c r="D9" s="5">
-        <v>-12.46</v>
+        <v>-8.99</v>
       </c>
       <c r="E9" s="6">
-        <v>-0.2</v>
+        <v>3.47</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -2038,13 +2038,13 @@
         <v>9</v>
       </c>
       <c r="C10" s="5">
-        <v>-11.02</v>
+        <v>-10.09</v>
       </c>
       <c r="D10" s="5">
-        <v>-10.09</v>
-      </c>
-      <c r="E10" s="7">
-        <v>0.93</v>
+        <v>-6.76</v>
+      </c>
+      <c r="E10" s="6">
+        <v>3.33</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -2055,13 +2055,13 @@
         <v>9</v>
       </c>
       <c r="C11" s="5">
-        <v>-14.09</v>
+        <v>-15.36</v>
       </c>
       <c r="D11" s="5">
-        <v>-15.36</v>
+        <v>-13.36</v>
       </c>
       <c r="E11" s="6">
-        <v>-1.27</v>
+        <v>2</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -2072,13 +2072,13 @@
         <v>9</v>
       </c>
       <c r="C12" s="5">
-        <v>-2.89</v>
+        <v>-3.33</v>
       </c>
       <c r="D12" s="5">
-        <v>-3.33</v>
-      </c>
-      <c r="E12" s="6">
-        <v>-0.44</v>
+        <v>-9.92</v>
+      </c>
+      <c r="E12" s="7">
+        <v>-6.59</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -2089,13 +2089,13 @@
         <v>9</v>
       </c>
       <c r="C13" s="5">
-        <v>-6.76</v>
+        <v>-4.82</v>
       </c>
       <c r="D13" s="5">
-        <v>-4.82</v>
-      </c>
-      <c r="E13" s="7">
-        <v>1.94</v>
+        <v>-2.76</v>
+      </c>
+      <c r="E13" s="6">
+        <v>2.06</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -2106,13 +2106,13 @@
         <v>9</v>
       </c>
       <c r="C14" s="5">
-        <v>-2.09</v>
+        <v>-1.86</v>
       </c>
       <c r="D14" s="5">
-        <v>-1.86</v>
-      </c>
-      <c r="E14" s="7">
-        <v>0.23</v>
+        <v>1.54</v>
+      </c>
+      <c r="E14" s="6">
+        <v>3.4</v>
       </c>
     </row>
     <row r="15" spans="1:6">
@@ -2123,13 +2123,13 @@
         <v>8</v>
       </c>
       <c r="C15" s="5">
-        <v>1.52</v>
+        <v>1.83</v>
       </c>
       <c r="D15" s="5">
-        <v>1.83</v>
-      </c>
-      <c r="E15" s="7">
-        <v>0.31</v>
+        <v>3.69</v>
+      </c>
+      <c r="E15" s="6">
+        <v>1.86</v>
       </c>
     </row>
     <row r="16" spans="1:6">
@@ -2140,13 +2140,13 @@
         <v>8</v>
       </c>
       <c r="C16" s="5">
-        <v>-1.97</v>
+        <v>1.48</v>
       </c>
       <c r="D16" s="5">
-        <v>1.48</v>
-      </c>
-      <c r="E16" s="7">
-        <v>3.45</v>
+        <v>3.89</v>
+      </c>
+      <c r="E16" s="6">
+        <v>2.41</v>
       </c>
     </row>
     <row r="17" spans="1:5">
@@ -2157,13 +2157,13 @@
         <v>8</v>
       </c>
       <c r="C17" s="5">
-        <v>-1.92</v>
+        <v>-1.65</v>
       </c>
       <c r="D17" s="5">
-        <v>-1.65</v>
-      </c>
-      <c r="E17" s="7">
-        <v>0.27</v>
+        <v>1.02</v>
+      </c>
+      <c r="E17" s="6">
+        <v>2.67</v>
       </c>
     </row>
     <row r="18" spans="1:5">
@@ -2174,13 +2174,13 @@
         <v>8</v>
       </c>
       <c r="C18" s="5">
-        <v>-4.07</v>
+        <v>-3.11</v>
       </c>
       <c r="D18" s="5">
-        <v>-3.11</v>
-      </c>
-      <c r="E18" s="7">
-        <v>0.96</v>
+        <v>0.42</v>
+      </c>
+      <c r="E18" s="6">
+        <v>3.53</v>
       </c>
     </row>
     <row r="19" spans="1:5">
@@ -2191,13 +2191,13 @@
         <v>8</v>
       </c>
       <c r="C19" s="5">
-        <v>-3.1</v>
+        <v>-3.87</v>
       </c>
       <c r="D19" s="5">
-        <v>-3.87</v>
+        <v>-2.19</v>
       </c>
       <c r="E19" s="6">
-        <v>-0.77</v>
+        <v>1.68</v>
       </c>
     </row>
     <row r="20" spans="1:5">
@@ -2208,13 +2208,13 @@
         <v>8</v>
       </c>
       <c r="C20" s="5">
-        <v>6.32</v>
+        <v>7.4</v>
       </c>
       <c r="D20" s="5">
-        <v>7.4</v>
-      </c>
-      <c r="E20" s="7">
-        <v>1.08</v>
+        <v>7.48</v>
+      </c>
+      <c r="E20" s="6">
+        <v>0.08</v>
       </c>
     </row>
     <row r="21" spans="1:5">
@@ -2225,13 +2225,13 @@
         <v>8</v>
       </c>
       <c r="C21" s="5">
-        <v>-2.89</v>
+        <v>-2.12</v>
       </c>
       <c r="D21" s="5">
-        <v>-2.12</v>
-      </c>
-      <c r="E21" s="7">
-        <v>0.77</v>
+        <v>0.53</v>
+      </c>
+      <c r="E21" s="6">
+        <v>2.65</v>
       </c>
     </row>
     <row r="22" spans="1:5">
@@ -2242,13 +2242,13 @@
         <v>8</v>
       </c>
       <c r="C22" s="5">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="D22" s="5">
-        <v>1.29</v>
-      </c>
-      <c r="E22" s="7">
-        <v>1.29</v>
+        <v>4.18</v>
+      </c>
+      <c r="E22" s="6">
+        <v>2.89</v>
       </c>
     </row>
     <row r="23" spans="1:5">
@@ -2259,13 +2259,13 @@
         <v>11</v>
       </c>
       <c r="C23" s="5">
-        <v>30.28</v>
+        <v>27.17</v>
       </c>
       <c r="D23" s="5">
-        <v>27.17</v>
+        <v>30.31</v>
       </c>
       <c r="E23" s="6">
-        <v>-3.11</v>
+        <v>3.14</v>
       </c>
     </row>
     <row r="24" spans="1:5">
@@ -2276,13 +2276,13 @@
         <v>11</v>
       </c>
       <c r="C24" s="5">
-        <v>-47.2</v>
+        <v>-46.46</v>
       </c>
       <c r="D24" s="5">
-        <v>-46.46</v>
-      </c>
-      <c r="E24" s="7">
-        <v>0.74</v>
+        <v>-46.08</v>
+      </c>
+      <c r="E24" s="6">
+        <v>0.38</v>
       </c>
     </row>
     <row r="25" spans="1:5">
@@ -2293,13 +2293,13 @@
         <v>11</v>
       </c>
       <c r="C25" s="5">
-        <v>4.82</v>
+        <v>2.22</v>
       </c>
       <c r="D25" s="5">
-        <v>2.22</v>
+        <v>2.66</v>
       </c>
       <c r="E25" s="6">
-        <v>-2.6</v>
+        <v>0.44</v>
       </c>
     </row>
     <row r="26" spans="1:5">
@@ -2310,13 +2310,13 @@
         <v>11</v>
       </c>
       <c r="C26" s="5">
-        <v>17.45</v>
+        <v>14</v>
       </c>
       <c r="D26" s="5">
-        <v>14</v>
+        <v>15.49</v>
       </c>
       <c r="E26" s="6">
-        <v>-3.45</v>
+        <v>1.49</v>
       </c>
     </row>
     <row r="27" spans="1:5">
@@ -2327,13 +2327,13 @@
         <v>11</v>
       </c>
       <c r="C27" s="5">
-        <v>41.59</v>
+        <v>40.31</v>
       </c>
       <c r="D27" s="5">
-        <v>40.31</v>
-      </c>
-      <c r="E27" s="6">
-        <v>-1.28</v>
+        <v>38.5</v>
+      </c>
+      <c r="E27" s="7">
+        <v>-1.81</v>
       </c>
     </row>
     <row r="28" spans="1:5">
@@ -2344,13 +2344,13 @@
         <v>11</v>
       </c>
       <c r="C28" s="5">
-        <v>108.38</v>
+        <v>121.14</v>
       </c>
       <c r="D28" s="5">
-        <v>121.14</v>
+        <v>118.69</v>
       </c>
       <c r="E28" s="7">
-        <v>12.76</v>
+        <v>-2.45</v>
       </c>
     </row>
     <row r="29" spans="1:5">
@@ -2361,13 +2361,13 @@
         <v>11</v>
       </c>
       <c r="C29" s="5">
-        <v>-26.25</v>
+        <v>-24.68</v>
       </c>
       <c r="D29" s="5">
-        <v>-24.68</v>
+        <v>-25.06</v>
       </c>
       <c r="E29" s="7">
-        <v>1.57</v>
+        <v>-0.38</v>
       </c>
     </row>
     <row r="30" spans="1:5">
@@ -2378,13 +2378,13 @@
         <v>11</v>
       </c>
       <c r="C30" s="5">
-        <v>-10.35</v>
+        <v>-11.46</v>
       </c>
       <c r="D30" s="5">
-        <v>-11.46</v>
-      </c>
-      <c r="E30" s="6">
-        <v>-1.11</v>
+        <v>-11.55</v>
+      </c>
+      <c r="E30" s="7">
+        <v>-0.09</v>
       </c>
     </row>
     <row r="31" spans="1:5">
@@ -2395,13 +2395,13 @@
         <v>10</v>
       </c>
       <c r="C31" s="5">
-        <v>-3.66</v>
+        <v>-6.28</v>
       </c>
       <c r="D31" s="5">
-        <v>-6.28</v>
+        <v>-4.37</v>
       </c>
       <c r="E31" s="6">
-        <v>-2.62</v>
+        <v>1.91</v>
       </c>
     </row>
     <row r="32" spans="1:5">
@@ -2412,13 +2412,13 @@
         <v>10</v>
       </c>
       <c r="C32" s="5">
-        <v>-24.01</v>
+        <v>-23.59</v>
       </c>
       <c r="D32" s="5">
-        <v>-23.59</v>
-      </c>
-      <c r="E32" s="7">
-        <v>0.42</v>
+        <v>-23.55</v>
+      </c>
+      <c r="E32" s="6">
+        <v>0.04</v>
       </c>
     </row>
     <row r="33" spans="1:5">
@@ -2429,13 +2429,13 @@
         <v>10</v>
       </c>
       <c r="C33" s="5">
-        <v>-6.47</v>
+        <v>-6.91</v>
       </c>
       <c r="D33" s="5">
-        <v>-6.91</v>
+        <v>-6.09</v>
       </c>
       <c r="E33" s="6">
-        <v>-0.44</v>
+        <v>0.82</v>
       </c>
     </row>
     <row r="34" spans="1:5">
@@ -2446,13 +2446,13 @@
         <v>10</v>
       </c>
       <c r="C34" s="5">
-        <v>-7.4</v>
+        <v>-7.67</v>
       </c>
       <c r="D34" s="5">
-        <v>-7.67</v>
+        <v>-6.82</v>
       </c>
       <c r="E34" s="6">
-        <v>-0.27</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="35" spans="1:5">
@@ -2463,13 +2463,13 @@
         <v>10</v>
       </c>
       <c r="C35" s="5">
-        <v>-7.45</v>
+        <v>-7.32</v>
       </c>
       <c r="D35" s="5">
-        <v>-7.32</v>
+        <v>-9.859999999999999</v>
       </c>
       <c r="E35" s="7">
-        <v>0.13</v>
+        <v>-2.54</v>
       </c>
     </row>
     <row r="36" spans="1:5">
@@ -2480,13 +2480,13 @@
         <v>10</v>
       </c>
       <c r="C36" s="5">
-        <v>6.22</v>
+        <v>5.74</v>
       </c>
       <c r="D36" s="5">
-        <v>5.74</v>
-      </c>
-      <c r="E36" s="6">
-        <v>-0.48</v>
+        <v>1.43</v>
+      </c>
+      <c r="E36" s="7">
+        <v>-4.31</v>
       </c>
     </row>
     <row r="37" spans="1:5">
@@ -2497,13 +2497,13 @@
         <v>10</v>
       </c>
       <c r="C37" s="5">
-        <v>-9.460000000000001</v>
+        <v>-8.52</v>
       </c>
       <c r="D37" s="5">
-        <v>-8.52</v>
+        <v>-10.02</v>
       </c>
       <c r="E37" s="7">
-        <v>0.9399999999999999</v>
+        <v>-1.5</v>
       </c>
     </row>
     <row r="38" spans="1:5">
@@ -2514,13 +2514,13 @@
         <v>10</v>
       </c>
       <c r="C38" s="5">
-        <v>-6.49</v>
+        <v>-8.609999999999999</v>
       </c>
       <c r="D38" s="5">
-        <v>-8.609999999999999</v>
+        <v>-7.72</v>
       </c>
       <c r="E38" s="6">
-        <v>-2.12</v>
+        <v>0.89</v>
       </c>
     </row>
     <row r="39" spans="1:5">
@@ -2531,13 +2531,13 @@
         <v>6</v>
       </c>
       <c r="C39" s="5">
-        <v>-9.43</v>
+        <v>-10.78</v>
       </c>
       <c r="D39" s="5">
-        <v>-10.78</v>
+        <v>-10</v>
       </c>
       <c r="E39" s="6">
-        <v>-1.35</v>
+        <v>0.78</v>
       </c>
     </row>
     <row r="40" spans="1:5">
@@ -2548,13 +2548,13 @@
         <v>6</v>
       </c>
       <c r="C40" s="5">
-        <v>-47.55</v>
+        <v>-46.97</v>
       </c>
       <c r="D40" s="5">
-        <v>-46.97</v>
+        <v>-47.46</v>
       </c>
       <c r="E40" s="7">
-        <v>0.58</v>
+        <v>-0.49</v>
       </c>
     </row>
     <row r="41" spans="1:5">
@@ -2565,13 +2565,13 @@
         <v>6</v>
       </c>
       <c r="C41" s="5">
-        <v>-13.86</v>
+        <v>-15.01</v>
       </c>
       <c r="D41" s="5">
-        <v>-15.01</v>
+        <v>-14.63</v>
       </c>
       <c r="E41" s="6">
-        <v>-1.15</v>
+        <v>0.38</v>
       </c>
     </row>
     <row r="42" spans="1:5">
@@ -2582,13 +2582,13 @@
         <v>6</v>
       </c>
       <c r="C42" s="5">
-        <v>-21.52</v>
+        <v>-23.24</v>
       </c>
       <c r="D42" s="5">
-        <v>-23.24</v>
+        <v>-22.25</v>
       </c>
       <c r="E42" s="6">
-        <v>-1.72</v>
+        <v>0.99</v>
       </c>
     </row>
     <row r="43" spans="1:5">
@@ -2599,13 +2599,13 @@
         <v>6</v>
       </c>
       <c r="C43" s="5">
-        <v>-17.95</v>
+        <v>-18.78</v>
       </c>
       <c r="D43" s="5">
-        <v>-18.78</v>
-      </c>
-      <c r="E43" s="6">
-        <v>-0.83</v>
+        <v>-19.74</v>
+      </c>
+      <c r="E43" s="7">
+        <v>-0.96</v>
       </c>
     </row>
     <row r="44" spans="1:5">
@@ -2616,13 +2616,13 @@
         <v>6</v>
       </c>
       <c r="C44" s="5">
-        <v>-17.82</v>
+        <v>-16.59</v>
       </c>
       <c r="D44" s="5">
-        <v>-16.59</v>
+        <v>-18.46</v>
       </c>
       <c r="E44" s="7">
-        <v>1.23</v>
+        <v>-1.87</v>
       </c>
     </row>
     <row r="45" spans="1:5">
@@ -2633,13 +2633,13 @@
         <v>6</v>
       </c>
       <c r="C45" s="5">
-        <v>-32.01</v>
+        <v>-31.32</v>
       </c>
       <c r="D45" s="5">
-        <v>-31.32</v>
+        <v>-31.68</v>
       </c>
       <c r="E45" s="7">
-        <v>0.6899999999999999</v>
+        <v>-0.36</v>
       </c>
     </row>
     <row r="46" spans="1:5">
@@ -2650,13 +2650,13 @@
         <v>6</v>
       </c>
       <c r="C46" s="5">
-        <v>-17.64</v>
+        <v>-17.29</v>
       </c>
       <c r="D46" s="5">
-        <v>-17.29</v>
-      </c>
-      <c r="E46" s="7">
-        <v>0.35</v>
+        <v>-16.78</v>
+      </c>
+      <c r="E46" s="6">
+        <v>0.51</v>
       </c>
     </row>
     <row r="47" spans="1:5">
@@ -2667,13 +2667,13 @@
         <v>2</v>
       </c>
       <c r="C47" s="5">
-        <v>384.65</v>
+        <v>378.9</v>
       </c>
       <c r="D47" s="5">
-        <v>378.9</v>
+        <v>382.25</v>
       </c>
       <c r="E47" s="6">
-        <v>-5.75</v>
+        <v>3.35</v>
       </c>
     </row>
     <row r="48" spans="1:5">
@@ -2684,13 +2684,13 @@
         <v>2</v>
       </c>
       <c r="C48" s="5">
-        <v>44.78</v>
+        <v>45.28</v>
       </c>
       <c r="D48" s="5">
-        <v>45.28</v>
+        <v>44.86</v>
       </c>
       <c r="E48" s="7">
-        <v>0.5</v>
+        <v>-0.42</v>
       </c>
     </row>
     <row r="49" spans="1:5">
@@ -2701,13 +2701,13 @@
         <v>2</v>
       </c>
       <c r="C49" s="5">
-        <v>2912</v>
+        <v>2873</v>
       </c>
       <c r="D49" s="5">
-        <v>2873</v>
+        <v>2885.9</v>
       </c>
       <c r="E49" s="6">
-        <v>-39</v>
+        <v>12.9</v>
       </c>
     </row>
     <row r="50" spans="1:5">
@@ -2718,13 +2718,13 @@
         <v>2</v>
       </c>
       <c r="C50" s="5">
-        <v>902.25</v>
+        <v>882.5</v>
       </c>
       <c r="D50" s="5">
-        <v>882.5</v>
+        <v>893.85</v>
       </c>
       <c r="E50" s="6">
-        <v>-19.75</v>
+        <v>11.35</v>
       </c>
     </row>
     <row r="51" spans="1:5">
@@ -2735,13 +2735,13 @@
         <v>2</v>
       </c>
       <c r="C51" s="5">
-        <v>12.8</v>
+        <v>12.67</v>
       </c>
       <c r="D51" s="5">
-        <v>12.67</v>
-      </c>
-      <c r="E51" s="6">
-        <v>-0.13</v>
+        <v>12.52</v>
+      </c>
+      <c r="E51" s="7">
+        <v>-0.15</v>
       </c>
     </row>
     <row r="52" spans="1:5">
@@ -2752,13 +2752,13 @@
         <v>2</v>
       </c>
       <c r="C52" s="5">
-        <v>11.44</v>
+        <v>11.61</v>
       </c>
       <c r="D52" s="5">
-        <v>11.61</v>
+        <v>11.35</v>
       </c>
       <c r="E52" s="7">
-        <v>0.17</v>
+        <v>-0.26</v>
       </c>
     </row>
     <row r="53" spans="1:5">
@@ -2769,13 +2769,13 @@
         <v>2</v>
       </c>
       <c r="C53" s="5">
-        <v>3949.6</v>
+        <v>3989.7</v>
       </c>
       <c r="D53" s="5">
-        <v>3989.7</v>
+        <v>3969.3</v>
       </c>
       <c r="E53" s="7">
-        <v>40.1</v>
+        <v>-20.4</v>
       </c>
     </row>
     <row r="54" spans="1:5">
@@ -2786,13 +2786,13 @@
         <v>2</v>
       </c>
       <c r="C54" s="5">
-        <v>10750</v>
+        <v>10795</v>
       </c>
       <c r="D54" s="5">
-        <v>10795</v>
-      </c>
-      <c r="E54" s="7">
-        <v>45</v>
+        <v>10862</v>
+      </c>
+      <c r="E54" s="6">
+        <v>67</v>
       </c>
     </row>
     <row r="55" spans="1:5">
@@ -2800,271 +2800,305 @@
         <v>37</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="C55" s="5">
-        <v>48.19</v>
+        <v>74</v>
       </c>
       <c r="D55" s="5">
-        <v>44.52</v>
+        <v>87</v>
       </c>
       <c r="E55" s="6">
-        <v>-3.67</v>
+        <v>13</v>
       </c>
     </row>
     <row r="56" spans="1:5">
       <c r="A56" s="3" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="C56" s="5">
-        <v>36.25</v>
+        <v>87</v>
       </c>
       <c r="D56" s="5">
-        <v>39.02</v>
+        <v>74</v>
       </c>
       <c r="E56" s="7">
-        <v>2.77</v>
+        <v>-13</v>
       </c>
     </row>
     <row r="57" spans="1:5">
       <c r="A57" s="3" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B57" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C57" s="5">
-        <v>33.88</v>
+        <v>44.52</v>
       </c>
       <c r="D57" s="5">
-        <v>31.42</v>
+        <v>47.05</v>
       </c>
       <c r="E57" s="6">
-        <v>-2.46</v>
+        <v>2.53</v>
       </c>
     </row>
     <row r="58" spans="1:5">
       <c r="A58" s="3" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B58" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C58" s="5">
-        <v>34.98</v>
+        <v>39.02</v>
       </c>
       <c r="D58" s="5">
-        <v>31.39</v>
-      </c>
-      <c r="E58" s="6">
-        <v>-3.59</v>
+        <v>37.55</v>
+      </c>
+      <c r="E58" s="7">
+        <v>-1.47</v>
       </c>
     </row>
     <row r="59" spans="1:5">
       <c r="A59" s="3" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B59" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C59" s="5">
-        <v>39.42</v>
+        <v>31.42</v>
       </c>
       <c r="D59" s="5">
-        <v>38.07</v>
+        <v>33.15</v>
       </c>
       <c r="E59" s="6">
-        <v>-1.35</v>
+        <v>1.73</v>
       </c>
     </row>
     <row r="60" spans="1:5">
       <c r="A60" s="3" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B60" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C60" s="5">
-        <v>53.02</v>
+        <v>31.39</v>
       </c>
       <c r="D60" s="5">
-        <v>55.09</v>
-      </c>
-      <c r="E60" s="7">
-        <v>2.07</v>
+        <v>35.49</v>
+      </c>
+      <c r="E60" s="6">
+        <v>4.1</v>
       </c>
     </row>
     <row r="61" spans="1:5">
       <c r="A61" s="3" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B61" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C61" s="5">
-        <v>39.58</v>
+        <v>38.07</v>
       </c>
       <c r="D61" s="5">
-        <v>43.57</v>
+        <v>36.51</v>
       </c>
       <c r="E61" s="7">
-        <v>3.99</v>
+        <v>-1.56</v>
       </c>
     </row>
     <row r="62" spans="1:5">
       <c r="A62" s="3" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B62" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C62" s="5">
-        <v>45.23</v>
+        <v>55.09</v>
       </c>
       <c r="D62" s="5">
-        <v>46.49</v>
+        <v>51.36</v>
       </c>
       <c r="E62" s="7">
-        <v>1.26</v>
+        <v>-3.73</v>
       </c>
     </row>
     <row r="63" spans="1:5">
       <c r="A63" s="3" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="B63" s="3" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="C63" s="5">
-        <v>29.47</v>
+        <v>43.57</v>
       </c>
       <c r="D63" s="5">
-        <v>-59.1</v>
-      </c>
-      <c r="E63" s="6">
-        <v>-88.56999999999999</v>
+        <v>42.05</v>
+      </c>
+      <c r="E63" s="7">
+        <v>-1.52</v>
       </c>
     </row>
     <row r="64" spans="1:5">
       <c r="A64" s="3" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="C64" s="5">
-        <v>-44.73</v>
+        <v>46.49</v>
       </c>
       <c r="D64" s="5">
-        <v>-40.32</v>
-      </c>
-      <c r="E64" s="7">
-        <v>4.41</v>
+        <v>48.38</v>
+      </c>
+      <c r="E64" s="6">
+        <v>1.89</v>
       </c>
     </row>
     <row r="65" spans="1:5">
       <c r="A65" s="3" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B65" s="3" t="s">
         <v>31</v>
       </c>
       <c r="C65" s="5">
-        <v>-47.74</v>
+        <v>-59.1</v>
       </c>
       <c r="D65" s="5">
-        <v>-44.37</v>
-      </c>
-      <c r="E65" s="7">
-        <v>3.37</v>
+        <v>-55.42</v>
+      </c>
+      <c r="E65" s="6">
+        <v>3.68</v>
       </c>
     </row>
     <row r="66" spans="1:5">
       <c r="A66" s="3" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B66" s="3" t="s">
         <v>31</v>
       </c>
       <c r="C66" s="5">
-        <v>33.07</v>
+        <v>-40.32</v>
       </c>
       <c r="D66" s="5">
-        <v>-23.9</v>
-      </c>
-      <c r="E66" s="6">
-        <v>-56.97</v>
+        <v>-65.7</v>
+      </c>
+      <c r="E66" s="7">
+        <v>-25.38</v>
       </c>
     </row>
     <row r="67" spans="1:5">
       <c r="A67" s="3" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B67" s="3" t="s">
         <v>31</v>
       </c>
       <c r="C67" s="5">
-        <v>-45.87</v>
+        <v>-44.37</v>
       </c>
       <c r="D67" s="5">
-        <v>-52.17</v>
+        <v>-43.7</v>
       </c>
       <c r="E67" s="6">
-        <v>-6.3</v>
+        <v>0.67</v>
       </c>
     </row>
     <row r="68" spans="1:5">
       <c r="A68" s="3" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B68" s="3" t="s">
         <v>31</v>
       </c>
       <c r="C68" s="5">
-        <v>48.21</v>
+        <v>-23.9</v>
       </c>
       <c r="D68" s="5">
-        <v>-23.68</v>
+        <v>43.67</v>
       </c>
       <c r="E68" s="6">
-        <v>-71.89</v>
+        <v>67.56999999999999</v>
       </c>
     </row>
     <row r="69" spans="1:5">
       <c r="A69" s="3" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B69" s="3" t="s">
         <v>31</v>
       </c>
       <c r="C69" s="5">
-        <v>-68.20999999999999</v>
+        <v>-52.17</v>
       </c>
       <c r="D69" s="5">
-        <v>-60.61</v>
-      </c>
-      <c r="E69" s="7">
-        <v>7.6</v>
+        <v>-26.32</v>
+      </c>
+      <c r="E69" s="6">
+        <v>25.85</v>
       </c>
     </row>
     <row r="70" spans="1:5">
       <c r="A70" s="3" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B70" s="3" t="s">
         <v>31</v>
       </c>
       <c r="C70" s="5">
-        <v>-32.54</v>
+        <v>-23.68</v>
       </c>
       <c r="D70" s="5">
+        <v>-42.64</v>
+      </c>
+      <c r="E70" s="7">
+        <v>-18.96</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5">
+      <c r="A71" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="B71" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C71" s="5">
+        <v>-60.61</v>
+      </c>
+      <c r="D71" s="5">
+        <v>-62.15</v>
+      </c>
+      <c r="E71" s="7">
+        <v>-1.54</v>
+      </c>
+    </row>
+    <row r="72" spans="1:5">
+      <c r="A72" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="B72" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C72" s="5">
         <v>5.83</v>
       </c>
-      <c r="E70" s="7">
-        <v>38.37</v>
+      <c r="D72" s="5">
+        <v>21.41</v>
+      </c>
+      <c r="E72" s="6">
+        <v>15.58</v>
       </c>
     </row>
   </sheetData>
@@ -3129,16 +3163,16 @@
         <v>8</v>
       </c>
       <c r="D2" s="10">
-        <v>41.2</v>
+        <v>41.4</v>
       </c>
       <c r="E2" s="10">
         <v>40</v>
       </c>
       <c r="F2" s="10">
-        <v>-7.8</v>
+        <v>-6</v>
       </c>
       <c r="G2" s="10">
-        <v>-7.9</v>
+        <v>-8.4</v>
       </c>
       <c r="H2" s="10">
         <v>56.1</v>
@@ -3272,28 +3306,28 @@
     </row>
     <row r="2" spans="1:8">
       <c r="A2" s="13">
-        <v>0.2863</v>
+        <v>0.29</v>
       </c>
       <c r="B2" s="13">
-        <v>0.1518</v>
+        <v>0.1535</v>
       </c>
       <c r="C2" s="13">
-        <v>0.1197</v>
+        <v>0.1115</v>
       </c>
       <c r="D2" s="13">
-        <v>0.1091</v>
+        <v>0.1101</v>
       </c>
       <c r="E2" s="13">
-        <v>0.08349999999999999</v>
+        <v>0.0848</v>
       </c>
       <c r="F2" s="13">
-        <v>0.0334</v>
+        <v>0.0339</v>
       </c>
       <c r="G2" s="13">
-        <v>-0.2973</v>
+        <v>-0.3004</v>
       </c>
       <c r="H2" s="13">
-        <v>-0.3036</v>
+        <v>-0.3035</v>
       </c>
     </row>
   </sheetData>

--- a/BIRLA_GROUP_Technical_Metrics.xlsx
+++ b/BIRLA_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="280" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="280" uniqueCount="65">
   <si>
     <t>Symbol</t>
   </si>
@@ -167,6 +167,9 @@
   </si>
   <si>
     <t>DOWN</t>
+  </si>
+  <si>
+    <t>UP</t>
   </si>
   <si>
     <t>▶  SIGNAL EVENTS (vs Previous Run)</t>
@@ -258,14 +261,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF9C0006"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF006100"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -298,13 +301,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -755,8 +758,8 @@
     <col min="13" max="13" width="10.7109375" customWidth="1"/>
     <col min="14" max="14" width="11.7109375" customWidth="1"/>
     <col min="15" max="15" width="10.7109375" customWidth="1"/>
-    <col min="16" max="18" width="9.7109375" customWidth="1"/>
-    <col min="19" max="19" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="9.7109375" customWidth="1"/>
+    <col min="17" max="19" width="10.7109375" customWidth="1"/>
     <col min="20" max="20" width="22.7109375" customWidth="1"/>
     <col min="21" max="21" width="9.7109375" customWidth="1"/>
     <col min="22" max="22" width="10.7109375" customWidth="1"/>
@@ -896,10 +899,10 @@
         <v>45</v>
       </c>
       <c r="C2">
-        <v>382.25</v>
+        <v>379.4</v>
       </c>
       <c r="D2">
-        <v>0.88</v>
+        <v>-0.75</v>
       </c>
       <c r="E2">
         <v>424.7</v>
@@ -908,46 +911,46 @@
         <v>292.25</v>
       </c>
       <c r="G2">
-        <v>-10</v>
+        <v>-10.67</v>
       </c>
       <c r="H2">
-        <v>30.8</v>
+        <v>29.82</v>
       </c>
       <c r="I2">
-        <v>3.69</v>
+        <v>-0.34</v>
       </c>
       <c r="J2">
-        <v>0.91</v>
+        <v>-0.5</v>
       </c>
       <c r="K2">
-        <v>-4.37</v>
+        <v>-5.52</v>
       </c>
       <c r="L2">
-        <v>30.31</v>
+        <v>26.87</v>
       </c>
       <c r="M2">
-        <v>29</v>
+        <v>28.79</v>
       </c>
       <c r="N2">
-        <v>87</v>
+        <v>74</v>
       </c>
       <c r="O2">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="P2">
-        <v>381.35</v>
+        <v>381.09</v>
       </c>
       <c r="Q2">
-        <v>385.16</v>
+        <v>384.63</v>
       </c>
       <c r="R2">
-        <v>396.46</v>
+        <v>395.55</v>
       </c>
       <c r="S2">
-        <v>365.93</v>
+        <v>366.1</v>
       </c>
       <c r="T2">
-        <v>4.46</v>
+        <v>3.63</v>
       </c>
       <c r="U2" t="s">
         <v>46</v>
@@ -962,34 +965,34 @@
         <v>2</v>
       </c>
       <c r="Y2">
-        <v>47.05</v>
+        <v>45.16</v>
       </c>
       <c r="Z2">
-        <v>-4.86</v>
+        <v>-4.64</v>
       </c>
       <c r="AA2">
-        <v>-5.55</v>
+        <v>-5.37</v>
       </c>
       <c r="AB2">
-        <v>0.6899999999999999</v>
+        <v>0.73</v>
       </c>
       <c r="AC2">
-        <v>80.01000000000001</v>
+        <v>79.03</v>
       </c>
       <c r="AD2">
-        <v>71.37</v>
+        <v>76.06</v>
       </c>
       <c r="AE2">
-        <v>9.52</v>
+        <v>9.41</v>
       </c>
       <c r="AF2">
-        <v>-55.42</v>
+        <v>-29.02</v>
       </c>
       <c r="AG2">
-        <v>407.05</v>
+        <v>406.54</v>
       </c>
       <c r="AH2">
-        <v>363.26</v>
+        <v>362.71</v>
       </c>
       <c r="AI2">
         <v>398.61</v>
@@ -998,7 +1001,7 @@
         <v>48</v>
       </c>
       <c r="AK2">
-        <v>20.35</v>
+        <v>18.05</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1009,10 +1012,10 @@
         <v>45</v>
       </c>
       <c r="C3">
-        <v>44.86</v>
+        <v>44.83</v>
       </c>
       <c r="D3">
-        <v>-0.93</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="E3">
         <v>85.38</v>
@@ -1021,25 +1024,25 @@
         <v>43.18</v>
       </c>
       <c r="G3">
-        <v>-47.46</v>
+        <v>-47.49</v>
       </c>
       <c r="H3">
-        <v>3.89</v>
+        <v>3.82</v>
       </c>
       <c r="I3">
-        <v>3.89</v>
+        <v>2.7</v>
       </c>
       <c r="J3">
-        <v>-8.49</v>
+        <v>-9.869999999999999</v>
       </c>
       <c r="K3">
-        <v>-23.55</v>
+        <v>-22.51</v>
       </c>
       <c r="L3">
-        <v>-46.08</v>
+        <v>-45.31</v>
       </c>
       <c r="M3">
-        <v>-30.04</v>
+        <v>-30.03</v>
       </c>
       <c r="N3">
         <v>13</v>
@@ -1048,19 +1051,19 @@
         <v>6</v>
       </c>
       <c r="P3">
-        <v>44.42</v>
+        <v>44.66</v>
       </c>
       <c r="Q3">
-        <v>46.53</v>
+        <v>46.25</v>
       </c>
       <c r="R3">
-        <v>51.33</v>
+        <v>50.98</v>
       </c>
       <c r="S3">
-        <v>60.82</v>
+        <v>60.66</v>
       </c>
       <c r="T3">
-        <v>-26.24</v>
+        <v>-26.1</v>
       </c>
       <c r="U3" t="s">
         <v>46</v>
@@ -1075,34 +1078,34 @@
         <v>0</v>
       </c>
       <c r="Y3">
-        <v>37.55</v>
+        <v>37.44</v>
       </c>
       <c r="Z3">
-        <v>-2.02</v>
+        <v>-1.91</v>
       </c>
       <c r="AA3">
-        <v>-2.19</v>
+        <v>-2.13</v>
       </c>
       <c r="AB3">
-        <v>0.17</v>
+        <v>0.23</v>
       </c>
       <c r="AC3">
-        <v>95.61</v>
+        <v>93.3</v>
       </c>
       <c r="AD3">
-        <v>77.45999999999999</v>
+        <v>89.06</v>
       </c>
       <c r="AE3">
-        <v>1.53</v>
+        <v>1.49</v>
       </c>
       <c r="AF3">
-        <v>-65.7</v>
+        <v>-64.12</v>
       </c>
       <c r="AG3">
-        <v>51.4</v>
+        <v>50.81</v>
       </c>
       <c r="AH3">
-        <v>41.65</v>
+        <v>41.69</v>
       </c>
       <c r="AI3">
         <v>48.29</v>
@@ -1111,7 +1114,7 @@
         <v>48</v>
       </c>
       <c r="AK3">
-        <v>31.6</v>
+        <v>28.28</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1122,10 +1125,10 @@
         <v>45</v>
       </c>
       <c r="C4">
-        <v>2885.9</v>
+        <v>2920</v>
       </c>
       <c r="D4">
-        <v>0.45</v>
+        <v>1.18</v>
       </c>
       <c r="E4">
         <v>3380.5</v>
@@ -1134,46 +1137,46 @@
         <v>2531.1</v>
       </c>
       <c r="G4">
-        <v>-14.63</v>
+        <v>-13.62</v>
       </c>
       <c r="H4">
-        <v>14.02</v>
+        <v>15.36</v>
       </c>
       <c r="I4">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="J4">
-        <v>-8.99</v>
+        <v>-8.380000000000001</v>
       </c>
       <c r="K4">
-        <v>-6.09</v>
+        <v>-6.1</v>
       </c>
       <c r="L4">
-        <v>2.66</v>
+        <v>4.36</v>
       </c>
       <c r="M4">
-        <v>11.01</v>
+        <v>11.26</v>
       </c>
       <c r="N4">
         <v>50</v>
       </c>
       <c r="O4">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="P4">
-        <v>2883.78</v>
+        <v>2889.78</v>
       </c>
       <c r="Q4">
-        <v>3031.71</v>
+        <v>3019.05</v>
       </c>
       <c r="R4">
-        <v>3184.42</v>
+        <v>3178.34</v>
       </c>
       <c r="S4">
-        <v>2980.87</v>
+        <v>2981.26</v>
       </c>
       <c r="T4">
-        <v>-3.19</v>
+        <v>-2.05</v>
       </c>
       <c r="U4" t="s">
         <v>46</v>
@@ -1188,34 +1191,34 @@
         <v>1</v>
       </c>
       <c r="Y4">
-        <v>33.15</v>
+        <v>37.62</v>
       </c>
       <c r="Z4">
-        <v>-94.67</v>
+        <v>-89.81</v>
       </c>
       <c r="AA4">
-        <v>-82.23999999999999</v>
+        <v>-83.75</v>
       </c>
       <c r="AB4">
-        <v>-12.43</v>
+        <v>-6.05</v>
       </c>
       <c r="AC4">
-        <v>42.33</v>
+        <v>52.59</v>
       </c>
       <c r="AD4">
-        <v>34.09</v>
+        <v>42.43</v>
       </c>
       <c r="AE4">
-        <v>60.34</v>
+        <v>61.83</v>
       </c>
       <c r="AF4">
-        <v>-43.7</v>
+        <v>-2</v>
       </c>
       <c r="AG4">
-        <v>3296.39</v>
+        <v>3279.43</v>
       </c>
       <c r="AH4">
-        <v>2767.03</v>
+        <v>2758.68</v>
       </c>
       <c r="AI4">
         <v>3061.2</v>
@@ -1224,7 +1227,7 @@
         <v>48</v>
       </c>
       <c r="AK4">
-        <v>65.84</v>
+        <v>66.36</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1235,10 +1238,10 @@
         <v>45</v>
       </c>
       <c r="C5">
-        <v>893.85</v>
+        <v>908</v>
       </c>
       <c r="D5">
-        <v>1.29</v>
+        <v>1.58</v>
       </c>
       <c r="E5">
         <v>1149.7</v>
@@ -1247,46 +1250,46 @@
         <v>760.1</v>
       </c>
       <c r="G5">
-        <v>-22.25</v>
+        <v>-21.02</v>
       </c>
       <c r="H5">
-        <v>17.6</v>
+        <v>19.46</v>
       </c>
       <c r="I5">
-        <v>0.42</v>
+        <v>0.85</v>
       </c>
       <c r="J5">
-        <v>-6.76</v>
+        <v>-6.65</v>
       </c>
       <c r="K5">
-        <v>-6.82</v>
+        <v>-3.83</v>
       </c>
       <c r="L5">
-        <v>15.49</v>
+        <v>17.89</v>
       </c>
       <c r="M5">
-        <v>11.15</v>
+        <v>11.49</v>
       </c>
       <c r="N5">
         <v>62</v>
       </c>
       <c r="O5">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="P5">
-        <v>892.29</v>
+        <v>893.8200000000001</v>
       </c>
       <c r="Q5">
-        <v>941</v>
+        <v>937.38</v>
       </c>
       <c r="R5">
-        <v>993.03</v>
+        <v>990.39</v>
       </c>
       <c r="S5">
-        <v>983.3200000000001</v>
+        <v>983.54</v>
       </c>
       <c r="T5">
-        <v>-9.1</v>
+        <v>-7.68</v>
       </c>
       <c r="U5" t="s">
         <v>46</v>
@@ -1301,34 +1304,34 @@
         <v>1</v>
       </c>
       <c r="Y5">
-        <v>35.49</v>
+        <v>40.29</v>
       </c>
       <c r="Z5">
-        <v>-29.34</v>
+        <v>-27.65</v>
       </c>
       <c r="AA5">
-        <v>-25.01</v>
+        <v>-25.54</v>
       </c>
       <c r="AB5">
-        <v>-4.33</v>
+        <v>-2.11</v>
       </c>
       <c r="AC5">
-        <v>40.3</v>
+        <v>61.3</v>
       </c>
       <c r="AD5">
-        <v>28.09</v>
+        <v>41.83</v>
       </c>
       <c r="AE5">
-        <v>22.99</v>
+        <v>22.75</v>
       </c>
       <c r="AF5">
-        <v>43.67</v>
+        <v>-17.83</v>
       </c>
       <c r="AG5">
-        <v>1019.6</v>
+        <v>1014.98</v>
       </c>
       <c r="AH5">
-        <v>862.41</v>
+        <v>859.78</v>
       </c>
       <c r="AI5">
         <v>946.48</v>
@@ -1337,7 +1340,7 @@
         <v>48</v>
       </c>
       <c r="AK5">
-        <v>49.81</v>
+        <v>48.31</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1348,10 +1351,10 @@
         <v>45</v>
       </c>
       <c r="C6">
-        <v>12.52</v>
+        <v>12.59</v>
       </c>
       <c r="D6">
-        <v>-1.18</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="E6">
         <v>15.6</v>
@@ -1360,46 +1363,46 @@
         <v>8.359999999999999</v>
       </c>
       <c r="G6">
-        <v>-19.74</v>
+        <v>-19.29</v>
       </c>
       <c r="H6">
-        <v>49.76</v>
+        <v>50.6</v>
       </c>
       <c r="I6">
-        <v>-2.19</v>
+        <v>-3.15</v>
       </c>
       <c r="J6">
-        <v>-13.36</v>
+        <v>-11.71</v>
       </c>
       <c r="K6">
-        <v>-9.859999999999999</v>
+        <v>-8.369999999999999</v>
       </c>
       <c r="L6">
-        <v>38.5</v>
+        <v>44.22</v>
       </c>
       <c r="M6">
-        <v>3.39</v>
+        <v>3.51</v>
       </c>
       <c r="N6">
-        <v>74</v>
+        <v>87</v>
       </c>
       <c r="O6">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="P6">
-        <v>12.73</v>
+        <v>12.65</v>
       </c>
       <c r="Q6">
-        <v>13.37</v>
+        <v>13.29</v>
       </c>
       <c r="R6">
-        <v>13.88</v>
+        <v>13.87</v>
       </c>
       <c r="S6">
         <v>12.3</v>
       </c>
       <c r="T6">
-        <v>1.81</v>
+        <v>2.36</v>
       </c>
       <c r="U6" t="s">
         <v>46</v>
@@ -1414,43 +1417,43 @@
         <v>2</v>
       </c>
       <c r="Y6">
-        <v>36.51</v>
+        <v>37.79</v>
       </c>
       <c r="Z6">
         <v>-0.43</v>
       </c>
       <c r="AA6">
-        <v>-0.35</v>
+        <v>-0.37</v>
       </c>
       <c r="AB6">
-        <v>-0.07000000000000001</v>
+        <v>-0.06</v>
       </c>
       <c r="AC6">
-        <v>29.4</v>
+        <v>36.78</v>
       </c>
       <c r="AD6">
-        <v>30.35</v>
+        <v>31.91</v>
       </c>
       <c r="AE6">
-        <v>0.44</v>
+        <v>0.42</v>
       </c>
       <c r="AF6">
-        <v>-26.32</v>
+        <v>-29.65</v>
       </c>
       <c r="AG6">
-        <v>14.7</v>
+        <v>14.6</v>
       </c>
       <c r="AH6">
-        <v>12.04</v>
+        <v>11.97</v>
       </c>
       <c r="AI6">
-        <v>14.02</v>
+        <v>13.83</v>
       </c>
       <c r="AJ6" t="s">
         <v>48</v>
       </c>
       <c r="AK6">
-        <v>42.78</v>
+        <v>44.53</v>
       </c>
     </row>
     <row r="7" spans="1:37">
@@ -1461,10 +1464,10 @@
         <v>45</v>
       </c>
       <c r="C7">
-        <v>11.35</v>
+        <v>12.4</v>
       </c>
       <c r="D7">
-        <v>-2.24</v>
+        <v>9.25</v>
       </c>
       <c r="E7">
         <v>13.92</v>
@@ -1473,46 +1476,46 @@
         <v>4.69</v>
       </c>
       <c r="G7">
-        <v>-18.46</v>
+        <v>-10.92</v>
       </c>
       <c r="H7">
-        <v>142</v>
+        <v>164.39</v>
       </c>
       <c r="I7">
-        <v>7.48</v>
+        <v>12.12</v>
       </c>
       <c r="J7">
-        <v>-9.92</v>
+        <v>0.32</v>
       </c>
       <c r="K7">
-        <v>1.43</v>
+        <v>8.68</v>
       </c>
       <c r="L7">
-        <v>118.69</v>
+        <v>143.61</v>
       </c>
       <c r="M7">
-        <v>-30.35</v>
+        <v>-29.09</v>
       </c>
       <c r="N7">
         <v>99</v>
       </c>
       <c r="O7">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="P7">
-        <v>11.27</v>
+        <v>11.54</v>
       </c>
       <c r="Q7">
-        <v>11.2</v>
+        <v>11.21</v>
       </c>
       <c r="R7">
-        <v>11.53</v>
+        <v>11.51</v>
       </c>
       <c r="S7">
-        <v>10.84</v>
+        <v>10.83</v>
       </c>
       <c r="T7">
-        <v>4.75</v>
+        <v>14.49</v>
       </c>
       <c r="U7" t="s">
         <v>46</v>
@@ -1527,43 +1530,43 @@
         <v>2</v>
       </c>
       <c r="Y7">
-        <v>51.36</v>
+        <v>62.43</v>
       </c>
       <c r="Z7">
-        <v>-0.09</v>
+        <v>0.01</v>
       </c>
       <c r="AA7">
-        <v>-0.16</v>
+        <v>-0.13</v>
       </c>
       <c r="AB7">
-        <v>0.07000000000000001</v>
+        <v>0.14</v>
       </c>
       <c r="AC7">
         <v>94.48</v>
       </c>
       <c r="AD7">
-        <v>92.83</v>
+        <v>94.09999999999999</v>
       </c>
       <c r="AE7">
-        <v>0.62</v>
+        <v>0.67</v>
       </c>
       <c r="AF7">
-        <v>-42.64</v>
+        <v>731.73</v>
       </c>
       <c r="AG7">
-        <v>12.22</v>
+        <v>12.23</v>
       </c>
       <c r="AH7">
-        <v>10.19</v>
+        <v>10.18</v>
       </c>
       <c r="AI7">
-        <v>12.04</v>
+        <v>9.83</v>
       </c>
       <c r="AJ7" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="AK7">
-        <v>27.43</v>
+        <v>30.29</v>
       </c>
     </row>
     <row r="8" spans="1:37">
@@ -1574,10 +1577,10 @@
         <v>45</v>
       </c>
       <c r="C8">
-        <v>3969.3</v>
+        <v>3984.2</v>
       </c>
       <c r="D8">
-        <v>-0.51</v>
+        <v>0.38</v>
       </c>
       <c r="E8">
         <v>5809.5</v>
@@ -1586,46 +1589,46 @@
         <v>3892.3</v>
       </c>
       <c r="G8">
-        <v>-31.68</v>
+        <v>-31.42</v>
       </c>
       <c r="H8">
-        <v>1.98</v>
+        <v>2.36</v>
       </c>
       <c r="I8">
-        <v>0.53</v>
+        <v>1.18</v>
       </c>
       <c r="J8">
-        <v>-2.76</v>
+        <v>-1.68</v>
       </c>
       <c r="K8">
-        <v>-10.02</v>
+        <v>-9.15</v>
       </c>
       <c r="L8">
-        <v>-25.06</v>
+        <v>-24.59</v>
       </c>
       <c r="M8">
-        <v>15.35</v>
+        <v>15.42</v>
       </c>
       <c r="N8">
         <v>26</v>
       </c>
       <c r="O8">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="P8">
-        <v>3956.24</v>
+        <v>3965.54</v>
       </c>
       <c r="Q8">
-        <v>3999.02</v>
+        <v>3994.12</v>
       </c>
       <c r="R8">
-        <v>4199.42</v>
+        <v>4192.33</v>
       </c>
       <c r="S8">
-        <v>4475.03</v>
+        <v>4469.03</v>
       </c>
       <c r="T8">
-        <v>-11.3</v>
+        <v>-10.85</v>
       </c>
       <c r="U8" t="s">
         <v>46</v>
@@ -1640,34 +1643,34 @@
         <v>0</v>
       </c>
       <c r="Y8">
-        <v>42.05</v>
+        <v>43.59</v>
       </c>
       <c r="Z8">
-        <v>-64.53</v>
+        <v>-59.94</v>
       </c>
       <c r="AA8">
-        <v>-73.83</v>
+        <v>-71.05</v>
       </c>
       <c r="AB8">
-        <v>9.289999999999999</v>
+        <v>11.11</v>
       </c>
       <c r="AC8">
-        <v>70.26000000000001</v>
+        <v>77.65000000000001</v>
       </c>
       <c r="AD8">
-        <v>62.14</v>
+        <v>70.29000000000001</v>
       </c>
       <c r="AE8">
-        <v>99.33</v>
+        <v>96.64</v>
       </c>
       <c r="AF8">
-        <v>-62.15</v>
+        <v>-46.43</v>
       </c>
       <c r="AG8">
-        <v>4104.88</v>
+        <v>4092.58</v>
       </c>
       <c r="AH8">
-        <v>3893.15</v>
+        <v>3895.65</v>
       </c>
       <c r="AI8">
         <v>4246.97</v>
@@ -1676,7 +1679,7 @@
         <v>48</v>
       </c>
       <c r="AK8">
-        <v>30.45</v>
+        <v>26.9</v>
       </c>
     </row>
     <row r="9" spans="1:37">
@@ -1687,10 +1690,10 @@
         <v>45</v>
       </c>
       <c r="C9">
-        <v>10862</v>
+        <v>10907</v>
       </c>
       <c r="D9">
-        <v>0.62</v>
+        <v>0.41</v>
       </c>
       <c r="E9">
         <v>13052</v>
@@ -1699,46 +1702,46 @@
         <v>10362</v>
       </c>
       <c r="G9">
-        <v>-16.78</v>
+        <v>-16.43</v>
       </c>
       <c r="H9">
-        <v>4.83</v>
+        <v>5.26</v>
       </c>
       <c r="I9">
-        <v>4.18</v>
+        <v>2.17</v>
       </c>
       <c r="J9">
-        <v>1.54</v>
+        <v>1.93</v>
       </c>
       <c r="K9">
-        <v>-7.72</v>
+        <v>-6.99</v>
       </c>
       <c r="L9">
-        <v>-11.55</v>
+        <v>-10.39</v>
       </c>
       <c r="M9">
-        <v>8.48</v>
+        <v>8.57</v>
       </c>
       <c r="N9">
         <v>38</v>
       </c>
       <c r="O9">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="P9">
-        <v>10720.4</v>
+        <v>10766.8</v>
       </c>
       <c r="Q9">
-        <v>10852.5</v>
+        <v>10859.65</v>
       </c>
       <c r="R9">
-        <v>11232.4</v>
+        <v>11206.74</v>
       </c>
       <c r="S9">
-        <v>11666.97</v>
+        <v>11662.51</v>
       </c>
       <c r="T9">
-        <v>-6.9</v>
+        <v>-6.48</v>
       </c>
       <c r="U9" t="s">
         <v>46</v>
@@ -1753,34 +1756,34 @@
         <v>0</v>
       </c>
       <c r="Y9">
-        <v>48.38</v>
+        <v>49.66</v>
       </c>
       <c r="Z9">
-        <v>-137.81</v>
+        <v>-116.76</v>
       </c>
       <c r="AA9">
-        <v>-161.54</v>
+        <v>-152.59</v>
       </c>
       <c r="AB9">
-        <v>23.73</v>
+        <v>35.82</v>
       </c>
       <c r="AC9">
-        <v>89.91</v>
+        <v>96.34999999999999</v>
       </c>
       <c r="AD9">
-        <v>71.81999999999999</v>
+        <v>84.81</v>
       </c>
       <c r="AE9">
-        <v>220.55</v>
+        <v>219.86</v>
       </c>
       <c r="AF9">
-        <v>21.41</v>
+        <v>-36.91</v>
       </c>
       <c r="AG9">
-        <v>11260.03</v>
+        <v>11265.66</v>
       </c>
       <c r="AH9">
-        <v>10444.97</v>
+        <v>10453.64</v>
       </c>
       <c r="AI9">
         <v>11169.72</v>
@@ -1789,7 +1792,7 @@
         <v>48</v>
       </c>
       <c r="AK9">
-        <v>33.17</v>
+        <v>30.42</v>
       </c>
     </row>
   </sheetData>
@@ -1940,7 +1943,7 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -1950,12 +1953,12 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="3" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="5" spans="1:6">
       <c r="A5" s="2" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B5" s="2"/>
       <c r="C5" s="2"/>
@@ -1967,16 +1970,16 @@
         <v>0</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -1987,13 +1990,13 @@
         <v>9</v>
       </c>
       <c r="C7" s="5">
-        <v>-4.08</v>
+        <v>0.91</v>
       </c>
       <c r="D7" s="5">
-        <v>0.91</v>
+        <v>-0.5</v>
       </c>
       <c r="E7" s="6">
-        <v>4.99</v>
+        <v>-1.41</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -2004,13 +2007,13 @@
         <v>9</v>
       </c>
       <c r="C8" s="5">
-        <v>-10.23</v>
+        <v>-8.49</v>
       </c>
       <c r="D8" s="5">
-        <v>-8.49</v>
+        <v>-9.869999999999999</v>
       </c>
       <c r="E8" s="6">
-        <v>1.74</v>
+        <v>-1.38</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -2021,13 +2024,13 @@
         <v>9</v>
       </c>
       <c r="C9" s="5">
-        <v>-12.46</v>
+        <v>-8.99</v>
       </c>
       <c r="D9" s="5">
-        <v>-8.99</v>
-      </c>
-      <c r="E9" s="6">
-        <v>3.47</v>
+        <v>-8.380000000000001</v>
+      </c>
+      <c r="E9" s="7">
+        <v>0.61</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -2038,13 +2041,13 @@
         <v>9</v>
       </c>
       <c r="C10" s="5">
-        <v>-10.09</v>
+        <v>-6.76</v>
       </c>
       <c r="D10" s="5">
-        <v>-6.76</v>
-      </c>
-      <c r="E10" s="6">
-        <v>3.33</v>
+        <v>-6.65</v>
+      </c>
+      <c r="E10" s="7">
+        <v>0.11</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -2055,13 +2058,13 @@
         <v>9</v>
       </c>
       <c r="C11" s="5">
-        <v>-15.36</v>
+        <v>-13.36</v>
       </c>
       <c r="D11" s="5">
-        <v>-13.36</v>
-      </c>
-      <c r="E11" s="6">
-        <v>2</v>
+        <v>-11.71</v>
+      </c>
+      <c r="E11" s="7">
+        <v>1.65</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -2072,13 +2075,13 @@
         <v>9</v>
       </c>
       <c r="C12" s="5">
-        <v>-3.33</v>
+        <v>-9.92</v>
       </c>
       <c r="D12" s="5">
-        <v>-9.92</v>
+        <v>0.32</v>
       </c>
       <c r="E12" s="7">
-        <v>-6.59</v>
+        <v>10.24</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -2089,13 +2092,13 @@
         <v>9</v>
       </c>
       <c r="C13" s="5">
-        <v>-4.82</v>
+        <v>-2.76</v>
       </c>
       <c r="D13" s="5">
-        <v>-2.76</v>
-      </c>
-      <c r="E13" s="6">
-        <v>2.06</v>
+        <v>-1.68</v>
+      </c>
+      <c r="E13" s="7">
+        <v>1.08</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -2106,13 +2109,13 @@
         <v>9</v>
       </c>
       <c r="C14" s="5">
-        <v>-1.86</v>
+        <v>1.54</v>
       </c>
       <c r="D14" s="5">
-        <v>1.54</v>
-      </c>
-      <c r="E14" s="6">
-        <v>3.4</v>
+        <v>1.93</v>
+      </c>
+      <c r="E14" s="7">
+        <v>0.39</v>
       </c>
     </row>
     <row r="15" spans="1:6">
@@ -2123,13 +2126,13 @@
         <v>8</v>
       </c>
       <c r="C15" s="5">
-        <v>1.83</v>
+        <v>3.69</v>
       </c>
       <c r="D15" s="5">
-        <v>3.69</v>
+        <v>-0.34</v>
       </c>
       <c r="E15" s="6">
-        <v>1.86</v>
+        <v>-4.03</v>
       </c>
     </row>
     <row r="16" spans="1:6">
@@ -2140,13 +2143,13 @@
         <v>8</v>
       </c>
       <c r="C16" s="5">
-        <v>1.48</v>
+        <v>3.89</v>
       </c>
       <c r="D16" s="5">
-        <v>3.89</v>
+        <v>2.7</v>
       </c>
       <c r="E16" s="6">
-        <v>2.41</v>
+        <v>-1.19</v>
       </c>
     </row>
     <row r="17" spans="1:5">
@@ -2157,13 +2160,13 @@
         <v>8</v>
       </c>
       <c r="C17" s="5">
-        <v>-1.65</v>
+        <v>1.02</v>
       </c>
       <c r="D17" s="5">
-        <v>1.02</v>
-      </c>
-      <c r="E17" s="6">
-        <v>2.67</v>
+        <v>1.04</v>
+      </c>
+      <c r="E17" s="7">
+        <v>0.02</v>
       </c>
     </row>
     <row r="18" spans="1:5">
@@ -2174,13 +2177,13 @@
         <v>8</v>
       </c>
       <c r="C18" s="5">
-        <v>-3.11</v>
+        <v>0.42</v>
       </c>
       <c r="D18" s="5">
-        <v>0.42</v>
-      </c>
-      <c r="E18" s="6">
-        <v>3.53</v>
+        <v>0.85</v>
+      </c>
+      <c r="E18" s="7">
+        <v>0.43</v>
       </c>
     </row>
     <row r="19" spans="1:5">
@@ -2191,13 +2194,13 @@
         <v>8</v>
       </c>
       <c r="C19" s="5">
-        <v>-3.87</v>
+        <v>-2.19</v>
       </c>
       <c r="D19" s="5">
-        <v>-2.19</v>
+        <v>-3.15</v>
       </c>
       <c r="E19" s="6">
-        <v>1.68</v>
+        <v>-0.96</v>
       </c>
     </row>
     <row r="20" spans="1:5">
@@ -2208,13 +2211,13 @@
         <v>8</v>
       </c>
       <c r="C20" s="5">
-        <v>7.4</v>
+        <v>7.48</v>
       </c>
       <c r="D20" s="5">
-        <v>7.48</v>
-      </c>
-      <c r="E20" s="6">
-        <v>0.08</v>
+        <v>12.12</v>
+      </c>
+      <c r="E20" s="7">
+        <v>4.64</v>
       </c>
     </row>
     <row r="21" spans="1:5">
@@ -2225,13 +2228,13 @@
         <v>8</v>
       </c>
       <c r="C21" s="5">
-        <v>-2.12</v>
+        <v>0.53</v>
       </c>
       <c r="D21" s="5">
-        <v>0.53</v>
-      </c>
-      <c r="E21" s="6">
-        <v>2.65</v>
+        <v>1.18</v>
+      </c>
+      <c r="E21" s="7">
+        <v>0.65</v>
       </c>
     </row>
     <row r="22" spans="1:5">
@@ -2242,13 +2245,13 @@
         <v>8</v>
       </c>
       <c r="C22" s="5">
-        <v>1.29</v>
+        <v>4.18</v>
       </c>
       <c r="D22" s="5">
-        <v>4.18</v>
+        <v>2.17</v>
       </c>
       <c r="E22" s="6">
-        <v>2.89</v>
+        <v>-2.01</v>
       </c>
     </row>
     <row r="23" spans="1:5">
@@ -2259,13 +2262,13 @@
         <v>11</v>
       </c>
       <c r="C23" s="5">
-        <v>27.17</v>
+        <v>30.31</v>
       </c>
       <c r="D23" s="5">
-        <v>30.31</v>
+        <v>26.87</v>
       </c>
       <c r="E23" s="6">
-        <v>3.14</v>
+        <v>-3.44</v>
       </c>
     </row>
     <row r="24" spans="1:5">
@@ -2276,13 +2279,13 @@
         <v>11</v>
       </c>
       <c r="C24" s="5">
-        <v>-46.46</v>
+        <v>-46.08</v>
       </c>
       <c r="D24" s="5">
-        <v>-46.08</v>
-      </c>
-      <c r="E24" s="6">
-        <v>0.38</v>
+        <v>-45.31</v>
+      </c>
+      <c r="E24" s="7">
+        <v>0.77</v>
       </c>
     </row>
     <row r="25" spans="1:5">
@@ -2293,13 +2296,13 @@
         <v>11</v>
       </c>
       <c r="C25" s="5">
-        <v>2.22</v>
+        <v>2.66</v>
       </c>
       <c r="D25" s="5">
-        <v>2.66</v>
-      </c>
-      <c r="E25" s="6">
-        <v>0.44</v>
+        <v>4.36</v>
+      </c>
+      <c r="E25" s="7">
+        <v>1.7</v>
       </c>
     </row>
     <row r="26" spans="1:5">
@@ -2310,13 +2313,13 @@
         <v>11</v>
       </c>
       <c r="C26" s="5">
-        <v>14</v>
+        <v>15.49</v>
       </c>
       <c r="D26" s="5">
-        <v>15.49</v>
-      </c>
-      <c r="E26" s="6">
-        <v>1.49</v>
+        <v>17.89</v>
+      </c>
+      <c r="E26" s="7">
+        <v>2.4</v>
       </c>
     </row>
     <row r="27" spans="1:5">
@@ -2327,13 +2330,13 @@
         <v>11</v>
       </c>
       <c r="C27" s="5">
-        <v>40.31</v>
+        <v>38.5</v>
       </c>
       <c r="D27" s="5">
-        <v>38.5</v>
+        <v>44.22</v>
       </c>
       <c r="E27" s="7">
-        <v>-1.81</v>
+        <v>5.72</v>
       </c>
     </row>
     <row r="28" spans="1:5">
@@ -2344,13 +2347,13 @@
         <v>11</v>
       </c>
       <c r="C28" s="5">
-        <v>121.14</v>
+        <v>118.69</v>
       </c>
       <c r="D28" s="5">
-        <v>118.69</v>
+        <v>143.61</v>
       </c>
       <c r="E28" s="7">
-        <v>-2.45</v>
+        <v>24.92</v>
       </c>
     </row>
     <row r="29" spans="1:5">
@@ -2361,13 +2364,13 @@
         <v>11</v>
       </c>
       <c r="C29" s="5">
-        <v>-24.68</v>
+        <v>-25.06</v>
       </c>
       <c r="D29" s="5">
-        <v>-25.06</v>
+        <v>-24.59</v>
       </c>
       <c r="E29" s="7">
-        <v>-0.38</v>
+        <v>0.47</v>
       </c>
     </row>
     <row r="30" spans="1:5">
@@ -2378,13 +2381,13 @@
         <v>11</v>
       </c>
       <c r="C30" s="5">
-        <v>-11.46</v>
+        <v>-11.55</v>
       </c>
       <c r="D30" s="5">
-        <v>-11.55</v>
+        <v>-10.39</v>
       </c>
       <c r="E30" s="7">
-        <v>-0.09</v>
+        <v>1.16</v>
       </c>
     </row>
     <row r="31" spans="1:5">
@@ -2395,13 +2398,13 @@
         <v>10</v>
       </c>
       <c r="C31" s="5">
-        <v>-6.28</v>
+        <v>-4.37</v>
       </c>
       <c r="D31" s="5">
-        <v>-4.37</v>
+        <v>-5.52</v>
       </c>
       <c r="E31" s="6">
-        <v>1.91</v>
+        <v>-1.15</v>
       </c>
     </row>
     <row r="32" spans="1:5">
@@ -2412,13 +2415,13 @@
         <v>10</v>
       </c>
       <c r="C32" s="5">
-        <v>-23.59</v>
+        <v>-23.55</v>
       </c>
       <c r="D32" s="5">
-        <v>-23.55</v>
-      </c>
-      <c r="E32" s="6">
-        <v>0.04</v>
+        <v>-22.51</v>
+      </c>
+      <c r="E32" s="7">
+        <v>1.04</v>
       </c>
     </row>
     <row r="33" spans="1:5">
@@ -2429,13 +2432,13 @@
         <v>10</v>
       </c>
       <c r="C33" s="5">
-        <v>-6.91</v>
+        <v>-6.09</v>
       </c>
       <c r="D33" s="5">
-        <v>-6.09</v>
+        <v>-6.1</v>
       </c>
       <c r="E33" s="6">
-        <v>0.82</v>
+        <v>-0.01</v>
       </c>
     </row>
     <row r="34" spans="1:5">
@@ -2446,13 +2449,13 @@
         <v>10</v>
       </c>
       <c r="C34" s="5">
-        <v>-7.67</v>
+        <v>-6.82</v>
       </c>
       <c r="D34" s="5">
-        <v>-6.82</v>
-      </c>
-      <c r="E34" s="6">
-        <v>0.85</v>
+        <v>-3.83</v>
+      </c>
+      <c r="E34" s="7">
+        <v>2.99</v>
       </c>
     </row>
     <row r="35" spans="1:5">
@@ -2463,13 +2466,13 @@
         <v>10</v>
       </c>
       <c r="C35" s="5">
-        <v>-7.32</v>
+        <v>-9.859999999999999</v>
       </c>
       <c r="D35" s="5">
-        <v>-9.859999999999999</v>
+        <v>-8.369999999999999</v>
       </c>
       <c r="E35" s="7">
-        <v>-2.54</v>
+        <v>1.49</v>
       </c>
     </row>
     <row r="36" spans="1:5">
@@ -2480,13 +2483,13 @@
         <v>10</v>
       </c>
       <c r="C36" s="5">
-        <v>5.74</v>
+        <v>1.43</v>
       </c>
       <c r="D36" s="5">
-        <v>1.43</v>
+        <v>8.68</v>
       </c>
       <c r="E36" s="7">
-        <v>-4.31</v>
+        <v>7.25</v>
       </c>
     </row>
     <row r="37" spans="1:5">
@@ -2497,13 +2500,13 @@
         <v>10</v>
       </c>
       <c r="C37" s="5">
-        <v>-8.52</v>
+        <v>-10.02</v>
       </c>
       <c r="D37" s="5">
-        <v>-10.02</v>
+        <v>-9.15</v>
       </c>
       <c r="E37" s="7">
-        <v>-1.5</v>
+        <v>0.87</v>
       </c>
     </row>
     <row r="38" spans="1:5">
@@ -2514,13 +2517,13 @@
         <v>10</v>
       </c>
       <c r="C38" s="5">
-        <v>-8.609999999999999</v>
+        <v>-7.72</v>
       </c>
       <c r="D38" s="5">
-        <v>-7.72</v>
-      </c>
-      <c r="E38" s="6">
-        <v>0.89</v>
+        <v>-6.99</v>
+      </c>
+      <c r="E38" s="7">
+        <v>0.73</v>
       </c>
     </row>
     <row r="39" spans="1:5">
@@ -2531,13 +2534,13 @@
         <v>6</v>
       </c>
       <c r="C39" s="5">
-        <v>-10.78</v>
+        <v>-10</v>
       </c>
       <c r="D39" s="5">
-        <v>-10</v>
+        <v>-10.67</v>
       </c>
       <c r="E39" s="6">
-        <v>0.78</v>
+        <v>-0.67</v>
       </c>
     </row>
     <row r="40" spans="1:5">
@@ -2548,13 +2551,13 @@
         <v>6</v>
       </c>
       <c r="C40" s="5">
-        <v>-46.97</v>
+        <v>-47.46</v>
       </c>
       <c r="D40" s="5">
-        <v>-47.46</v>
-      </c>
-      <c r="E40" s="7">
-        <v>-0.49</v>
+        <v>-47.49</v>
+      </c>
+      <c r="E40" s="6">
+        <v>-0.03</v>
       </c>
     </row>
     <row r="41" spans="1:5">
@@ -2565,13 +2568,13 @@
         <v>6</v>
       </c>
       <c r="C41" s="5">
-        <v>-15.01</v>
+        <v>-14.63</v>
       </c>
       <c r="D41" s="5">
-        <v>-14.63</v>
-      </c>
-      <c r="E41" s="6">
-        <v>0.38</v>
+        <v>-13.62</v>
+      </c>
+      <c r="E41" s="7">
+        <v>1.01</v>
       </c>
     </row>
     <row r="42" spans="1:5">
@@ -2582,13 +2585,13 @@
         <v>6</v>
       </c>
       <c r="C42" s="5">
-        <v>-23.24</v>
+        <v>-22.25</v>
       </c>
       <c r="D42" s="5">
-        <v>-22.25</v>
-      </c>
-      <c r="E42" s="6">
-        <v>0.99</v>
+        <v>-21.02</v>
+      </c>
+      <c r="E42" s="7">
+        <v>1.23</v>
       </c>
     </row>
     <row r="43" spans="1:5">
@@ -2599,13 +2602,13 @@
         <v>6</v>
       </c>
       <c r="C43" s="5">
-        <v>-18.78</v>
+        <v>-19.74</v>
       </c>
       <c r="D43" s="5">
-        <v>-19.74</v>
+        <v>-19.29</v>
       </c>
       <c r="E43" s="7">
-        <v>-0.96</v>
+        <v>0.45</v>
       </c>
     </row>
     <row r="44" spans="1:5">
@@ -2616,13 +2619,13 @@
         <v>6</v>
       </c>
       <c r="C44" s="5">
-        <v>-16.59</v>
+        <v>-18.46</v>
       </c>
       <c r="D44" s="5">
-        <v>-18.46</v>
+        <v>-10.92</v>
       </c>
       <c r="E44" s="7">
-        <v>-1.87</v>
+        <v>7.54</v>
       </c>
     </row>
     <row r="45" spans="1:5">
@@ -2633,13 +2636,13 @@
         <v>6</v>
       </c>
       <c r="C45" s="5">
-        <v>-31.32</v>
+        <v>-31.68</v>
       </c>
       <c r="D45" s="5">
-        <v>-31.68</v>
+        <v>-31.42</v>
       </c>
       <c r="E45" s="7">
-        <v>-0.36</v>
+        <v>0.26</v>
       </c>
     </row>
     <row r="46" spans="1:5">
@@ -2650,13 +2653,13 @@
         <v>6</v>
       </c>
       <c r="C46" s="5">
-        <v>-17.29</v>
+        <v>-16.78</v>
       </c>
       <c r="D46" s="5">
-        <v>-16.78</v>
-      </c>
-      <c r="E46" s="6">
-        <v>0.51</v>
+        <v>-16.43</v>
+      </c>
+      <c r="E46" s="7">
+        <v>0.35</v>
       </c>
     </row>
     <row r="47" spans="1:5">
@@ -2667,13 +2670,13 @@
         <v>2</v>
       </c>
       <c r="C47" s="5">
-        <v>378.9</v>
+        <v>382.25</v>
       </c>
       <c r="D47" s="5">
-        <v>382.25</v>
+        <v>379.4</v>
       </c>
       <c r="E47" s="6">
-        <v>3.35</v>
+        <v>-2.85</v>
       </c>
     </row>
     <row r="48" spans="1:5">
@@ -2684,13 +2687,13 @@
         <v>2</v>
       </c>
       <c r="C48" s="5">
-        <v>45.28</v>
+        <v>44.86</v>
       </c>
       <c r="D48" s="5">
-        <v>44.86</v>
-      </c>
-      <c r="E48" s="7">
-        <v>-0.42</v>
+        <v>44.83</v>
+      </c>
+      <c r="E48" s="6">
+        <v>-0.03</v>
       </c>
     </row>
     <row r="49" spans="1:5">
@@ -2701,13 +2704,13 @@
         <v>2</v>
       </c>
       <c r="C49" s="5">
-        <v>2873</v>
+        <v>2885.9</v>
       </c>
       <c r="D49" s="5">
-        <v>2885.9</v>
-      </c>
-      <c r="E49" s="6">
-        <v>12.9</v>
+        <v>2920</v>
+      </c>
+      <c r="E49" s="7">
+        <v>34.1</v>
       </c>
     </row>
     <row r="50" spans="1:5">
@@ -2718,13 +2721,13 @@
         <v>2</v>
       </c>
       <c r="C50" s="5">
-        <v>882.5</v>
+        <v>893.85</v>
       </c>
       <c r="D50" s="5">
-        <v>893.85</v>
-      </c>
-      <c r="E50" s="6">
-        <v>11.35</v>
+        <v>908</v>
+      </c>
+      <c r="E50" s="7">
+        <v>14.15</v>
       </c>
     </row>
     <row r="51" spans="1:5">
@@ -2735,13 +2738,13 @@
         <v>2</v>
       </c>
       <c r="C51" s="5">
-        <v>12.67</v>
+        <v>12.52</v>
       </c>
       <c r="D51" s="5">
-        <v>12.52</v>
+        <v>12.59</v>
       </c>
       <c r="E51" s="7">
-        <v>-0.15</v>
+        <v>0.07000000000000001</v>
       </c>
     </row>
     <row r="52" spans="1:5">
@@ -2752,13 +2755,13 @@
         <v>2</v>
       </c>
       <c r="C52" s="5">
-        <v>11.61</v>
+        <v>11.35</v>
       </c>
       <c r="D52" s="5">
-        <v>11.35</v>
+        <v>12.4</v>
       </c>
       <c r="E52" s="7">
-        <v>-0.26</v>
+        <v>1.05</v>
       </c>
     </row>
     <row r="53" spans="1:5">
@@ -2769,13 +2772,13 @@
         <v>2</v>
       </c>
       <c r="C53" s="5">
-        <v>3989.7</v>
+        <v>3969.3</v>
       </c>
       <c r="D53" s="5">
-        <v>3969.3</v>
+        <v>3984.2</v>
       </c>
       <c r="E53" s="7">
-        <v>-20.4</v>
+        <v>14.9</v>
       </c>
     </row>
     <row r="54" spans="1:5">
@@ -2786,13 +2789,13 @@
         <v>2</v>
       </c>
       <c r="C54" s="5">
-        <v>10795</v>
+        <v>10862</v>
       </c>
       <c r="D54" s="5">
-        <v>10862</v>
-      </c>
-      <c r="E54" s="6">
-        <v>67</v>
+        <v>10907</v>
+      </c>
+      <c r="E54" s="7">
+        <v>45</v>
       </c>
     </row>
     <row r="55" spans="1:5">
@@ -2803,13 +2806,13 @@
         <v>13</v>
       </c>
       <c r="C55" s="5">
+        <v>87</v>
+      </c>
+      <c r="D55" s="5">
         <v>74</v>
       </c>
-      <c r="D55" s="5">
-        <v>87</v>
-      </c>
       <c r="E55" s="6">
-        <v>13</v>
+        <v>-13</v>
       </c>
     </row>
     <row r="56" spans="1:5">
@@ -2820,13 +2823,13 @@
         <v>13</v>
       </c>
       <c r="C56" s="5">
+        <v>74</v>
+      </c>
+      <c r="D56" s="5">
         <v>87</v>
       </c>
-      <c r="D56" s="5">
-        <v>74</v>
-      </c>
       <c r="E56" s="7">
-        <v>-13</v>
+        <v>13</v>
       </c>
     </row>
     <row r="57" spans="1:5">
@@ -2837,13 +2840,13 @@
         <v>24</v>
       </c>
       <c r="C57" s="5">
-        <v>44.52</v>
+        <v>47.05</v>
       </c>
       <c r="D57" s="5">
-        <v>47.05</v>
+        <v>45.16</v>
       </c>
       <c r="E57" s="6">
-        <v>2.53</v>
+        <v>-1.89</v>
       </c>
     </row>
     <row r="58" spans="1:5">
@@ -2854,13 +2857,13 @@
         <v>24</v>
       </c>
       <c r="C58" s="5">
-        <v>39.02</v>
+        <v>37.55</v>
       </c>
       <c r="D58" s="5">
-        <v>37.55</v>
-      </c>
-      <c r="E58" s="7">
-        <v>-1.47</v>
+        <v>37.44</v>
+      </c>
+      <c r="E58" s="6">
+        <v>-0.11</v>
       </c>
     </row>
     <row r="59" spans="1:5">
@@ -2871,13 +2874,13 @@
         <v>24</v>
       </c>
       <c r="C59" s="5">
-        <v>31.42</v>
+        <v>33.15</v>
       </c>
       <c r="D59" s="5">
-        <v>33.15</v>
-      </c>
-      <c r="E59" s="6">
-        <v>1.73</v>
+        <v>37.62</v>
+      </c>
+      <c r="E59" s="7">
+        <v>4.47</v>
       </c>
     </row>
     <row r="60" spans="1:5">
@@ -2888,13 +2891,13 @@
         <v>24</v>
       </c>
       <c r="C60" s="5">
-        <v>31.39</v>
+        <v>35.49</v>
       </c>
       <c r="D60" s="5">
-        <v>35.49</v>
-      </c>
-      <c r="E60" s="6">
-        <v>4.1</v>
+        <v>40.29</v>
+      </c>
+      <c r="E60" s="7">
+        <v>4.8</v>
       </c>
     </row>
     <row r="61" spans="1:5">
@@ -2905,13 +2908,13 @@
         <v>24</v>
       </c>
       <c r="C61" s="5">
-        <v>38.07</v>
+        <v>36.51</v>
       </c>
       <c r="D61" s="5">
-        <v>36.51</v>
+        <v>37.79</v>
       </c>
       <c r="E61" s="7">
-        <v>-1.56</v>
+        <v>1.28</v>
       </c>
     </row>
     <row r="62" spans="1:5">
@@ -2922,13 +2925,13 @@
         <v>24</v>
       </c>
       <c r="C62" s="5">
-        <v>55.09</v>
+        <v>51.36</v>
       </c>
       <c r="D62" s="5">
-        <v>51.36</v>
+        <v>62.43</v>
       </c>
       <c r="E62" s="7">
-        <v>-3.73</v>
+        <v>11.07</v>
       </c>
     </row>
     <row r="63" spans="1:5">
@@ -2939,13 +2942,13 @@
         <v>24</v>
       </c>
       <c r="C63" s="5">
-        <v>43.57</v>
+        <v>42.05</v>
       </c>
       <c r="D63" s="5">
-        <v>42.05</v>
+        <v>43.59</v>
       </c>
       <c r="E63" s="7">
-        <v>-1.52</v>
+        <v>1.54</v>
       </c>
     </row>
     <row r="64" spans="1:5">
@@ -2956,13 +2959,13 @@
         <v>24</v>
       </c>
       <c r="C64" s="5">
-        <v>46.49</v>
+        <v>48.38</v>
       </c>
       <c r="D64" s="5">
-        <v>48.38</v>
-      </c>
-      <c r="E64" s="6">
-        <v>1.89</v>
+        <v>49.66</v>
+      </c>
+      <c r="E64" s="7">
+        <v>1.28</v>
       </c>
     </row>
     <row r="65" spans="1:5">
@@ -2973,13 +2976,13 @@
         <v>31</v>
       </c>
       <c r="C65" s="5">
-        <v>-59.1</v>
+        <v>-55.42</v>
       </c>
       <c r="D65" s="5">
-        <v>-55.42</v>
-      </c>
-      <c r="E65" s="6">
-        <v>3.68</v>
+        <v>-29.02</v>
+      </c>
+      <c r="E65" s="7">
+        <v>26.4</v>
       </c>
     </row>
     <row r="66" spans="1:5">
@@ -2990,13 +2993,13 @@
         <v>31</v>
       </c>
       <c r="C66" s="5">
-        <v>-40.32</v>
+        <v>-65.7</v>
       </c>
       <c r="D66" s="5">
-        <v>-65.7</v>
+        <v>-64.12</v>
       </c>
       <c r="E66" s="7">
-        <v>-25.38</v>
+        <v>1.58</v>
       </c>
     </row>
     <row r="67" spans="1:5">
@@ -3007,13 +3010,13 @@
         <v>31</v>
       </c>
       <c r="C67" s="5">
-        <v>-44.37</v>
+        <v>-43.7</v>
       </c>
       <c r="D67" s="5">
-        <v>-43.7</v>
-      </c>
-      <c r="E67" s="6">
-        <v>0.67</v>
+        <v>-2</v>
+      </c>
+      <c r="E67" s="7">
+        <v>41.7</v>
       </c>
     </row>
     <row r="68" spans="1:5">
@@ -3024,13 +3027,13 @@
         <v>31</v>
       </c>
       <c r="C68" s="5">
-        <v>-23.9</v>
+        <v>43.67</v>
       </c>
       <c r="D68" s="5">
-        <v>43.67</v>
+        <v>-17.83</v>
       </c>
       <c r="E68" s="6">
-        <v>67.56999999999999</v>
+        <v>-61.5</v>
       </c>
     </row>
     <row r="69" spans="1:5">
@@ -3041,13 +3044,13 @@
         <v>31</v>
       </c>
       <c r="C69" s="5">
-        <v>-52.17</v>
+        <v>-26.32</v>
       </c>
       <c r="D69" s="5">
-        <v>-26.32</v>
+        <v>-29.65</v>
       </c>
       <c r="E69" s="6">
-        <v>25.85</v>
+        <v>-3.33</v>
       </c>
     </row>
     <row r="70" spans="1:5">
@@ -3058,13 +3061,13 @@
         <v>31</v>
       </c>
       <c r="C70" s="5">
-        <v>-23.68</v>
+        <v>-42.64</v>
       </c>
       <c r="D70" s="5">
-        <v>-42.64</v>
+        <v>731.73</v>
       </c>
       <c r="E70" s="7">
-        <v>-18.96</v>
+        <v>774.37</v>
       </c>
     </row>
     <row r="71" spans="1:5">
@@ -3075,13 +3078,13 @@
         <v>31</v>
       </c>
       <c r="C71" s="5">
-        <v>-60.61</v>
+        <v>-62.15</v>
       </c>
       <c r="D71" s="5">
-        <v>-62.15</v>
+        <v>-46.43</v>
       </c>
       <c r="E71" s="7">
-        <v>-1.54</v>
+        <v>15.72</v>
       </c>
     </row>
     <row r="72" spans="1:5">
@@ -3092,13 +3095,13 @@
         <v>31</v>
       </c>
       <c r="C72" s="5">
-        <v>5.83</v>
+        <v>21.41</v>
       </c>
       <c r="D72" s="5">
-        <v>21.41</v>
+        <v>-36.91</v>
       </c>
       <c r="E72" s="6">
-        <v>15.58</v>
+        <v>-58.32</v>
       </c>
     </row>
   </sheetData>
@@ -3128,28 +3131,28 @@
         <v>1</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F1" s="8" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="G1" s="8" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="H1" s="8" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="I1" s="8" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -3163,16 +3166,16 @@
         <v>8</v>
       </c>
       <c r="D2" s="10">
-        <v>41.4</v>
+        <v>44.2</v>
       </c>
       <c r="E2" s="10">
         <v>40</v>
       </c>
       <c r="F2" s="10">
-        <v>-6</v>
+        <v>-4.6</v>
       </c>
       <c r="G2" s="10">
-        <v>-8.4</v>
+        <v>-6.7</v>
       </c>
       <c r="H2" s="10">
         <v>56.1</v>
@@ -3298,36 +3301,36 @@
         <v>41</v>
       </c>
       <c r="G1" s="12" t="s">
+        <v>42</v>
+      </c>
+      <c r="H1" s="12" t="s">
         <v>38</v>
-      </c>
-      <c r="H1" s="12" t="s">
-        <v>42</v>
       </c>
     </row>
     <row r="2" spans="1:8">
       <c r="A2" s="13">
-        <v>0.29</v>
+        <v>0.2879</v>
       </c>
       <c r="B2" s="13">
-        <v>0.1535</v>
+        <v>0.1542</v>
       </c>
       <c r="C2" s="13">
-        <v>0.1115</v>
+        <v>0.1149</v>
       </c>
       <c r="D2" s="13">
-        <v>0.1101</v>
+        <v>0.1126</v>
       </c>
       <c r="E2" s="13">
-        <v>0.0848</v>
+        <v>0.0857</v>
       </c>
       <c r="F2" s="13">
-        <v>0.0339</v>
+        <v>0.0351</v>
       </c>
       <c r="G2" s="13">
-        <v>-0.3004</v>
+        <v>-0.2909</v>
       </c>
       <c r="H2" s="13">
-        <v>-0.3035</v>
+        <v>-0.3003</v>
       </c>
     </row>
   </sheetData>

--- a/BIRLA_GROUP_Technical_Metrics.xlsx
+++ b/BIRLA_GROUP_Technical_Metrics.xlsx
@@ -899,10 +899,10 @@
         <v>45</v>
       </c>
       <c r="C2">
-        <v>379.4</v>
+        <v>373.05</v>
       </c>
       <c r="D2">
-        <v>-0.75</v>
+        <v>-1.67</v>
       </c>
       <c r="E2">
         <v>424.7</v>
@@ -911,46 +911,46 @@
         <v>292.25</v>
       </c>
       <c r="G2">
-        <v>-10.67</v>
+        <v>-12.16</v>
       </c>
       <c r="H2">
-        <v>29.82</v>
+        <v>27.65</v>
       </c>
       <c r="I2">
-        <v>-0.34</v>
+        <v>-1.89</v>
       </c>
       <c r="J2">
-        <v>-0.5</v>
+        <v>-4.35</v>
       </c>
       <c r="K2">
-        <v>-5.52</v>
+        <v>-7</v>
       </c>
       <c r="L2">
-        <v>26.87</v>
+        <v>25.18</v>
       </c>
       <c r="M2">
-        <v>28.79</v>
+        <v>28.55</v>
       </c>
       <c r="N2">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="O2">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="P2">
-        <v>381.09</v>
+        <v>379.65</v>
       </c>
       <c r="Q2">
-        <v>384.63</v>
+        <v>382.78</v>
       </c>
       <c r="R2">
-        <v>395.55</v>
+        <v>394.59</v>
       </c>
       <c r="S2">
-        <v>366.1</v>
+        <v>366.21</v>
       </c>
       <c r="T2">
-        <v>3.63</v>
+        <v>1.87</v>
       </c>
       <c r="U2" t="s">
         <v>46</v>
@@ -965,34 +965,34 @@
         <v>2</v>
       </c>
       <c r="Y2">
-        <v>45.16</v>
+        <v>41.2</v>
       </c>
       <c r="Z2">
-        <v>-4.64</v>
+        <v>-4.92</v>
       </c>
       <c r="AA2">
-        <v>-5.37</v>
+        <v>-5.28</v>
       </c>
       <c r="AB2">
-        <v>0.73</v>
+        <v>0.36</v>
       </c>
       <c r="AC2">
-        <v>79.03</v>
+        <v>70.14</v>
       </c>
       <c r="AD2">
-        <v>76.06</v>
+        <v>76.39</v>
       </c>
       <c r="AE2">
-        <v>9.41</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="AF2">
-        <v>-29.02</v>
+        <v>-59.52</v>
       </c>
       <c r="AG2">
-        <v>406.54</v>
+        <v>401.7</v>
       </c>
       <c r="AH2">
-        <v>362.71</v>
+        <v>363.86</v>
       </c>
       <c r="AI2">
         <v>398.61</v>
@@ -1001,7 +1001,7 @@
         <v>48</v>
       </c>
       <c r="AK2">
-        <v>18.05</v>
+        <v>17.47</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1012,58 +1012,58 @@
         <v>45</v>
       </c>
       <c r="C3">
-        <v>44.83</v>
+        <v>43.15</v>
       </c>
       <c r="D3">
-        <v>-0.07000000000000001</v>
+        <v>-3.75</v>
       </c>
       <c r="E3">
         <v>85.38</v>
       </c>
       <c r="F3">
-        <v>43.18</v>
+        <v>43.15</v>
       </c>
       <c r="G3">
-        <v>-47.49</v>
+        <v>-49.46</v>
       </c>
       <c r="H3">
-        <v>3.82</v>
+        <v>0</v>
       </c>
       <c r="I3">
-        <v>2.7</v>
+        <v>-0.87</v>
       </c>
       <c r="J3">
-        <v>-9.869999999999999</v>
+        <v>-14.47</v>
       </c>
       <c r="K3">
-        <v>-22.51</v>
+        <v>-24.67</v>
       </c>
       <c r="L3">
-        <v>-45.31</v>
+        <v>-46.16</v>
       </c>
       <c r="M3">
-        <v>-30.03</v>
+        <v>-29.89</v>
       </c>
       <c r="N3">
         <v>13</v>
       </c>
       <c r="O3">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="P3">
-        <v>44.66</v>
+        <v>44.58</v>
       </c>
       <c r="Q3">
-        <v>46.25</v>
+        <v>45.9</v>
       </c>
       <c r="R3">
-        <v>50.98</v>
+        <v>50.58</v>
       </c>
       <c r="S3">
-        <v>60.66</v>
+        <v>60.5</v>
       </c>
       <c r="T3">
-        <v>-26.1</v>
+        <v>-28.67</v>
       </c>
       <c r="U3" t="s">
         <v>46</v>
@@ -1078,34 +1078,34 @@
         <v>0</v>
       </c>
       <c r="Y3">
-        <v>37.44</v>
+        <v>31.87</v>
       </c>
       <c r="Z3">
-        <v>-1.91</v>
+        <v>-1.93</v>
       </c>
       <c r="AA3">
-        <v>-2.13</v>
+        <v>-2.09</v>
       </c>
       <c r="AB3">
-        <v>0.23</v>
+        <v>0.16</v>
       </c>
       <c r="AC3">
-        <v>93.3</v>
+        <v>77.62</v>
       </c>
       <c r="AD3">
-        <v>89.06</v>
+        <v>88.84</v>
       </c>
       <c r="AE3">
-        <v>1.49</v>
+        <v>1.52</v>
       </c>
       <c r="AF3">
-        <v>-64.12</v>
+        <v>-49.79</v>
       </c>
       <c r="AG3">
-        <v>50.81</v>
+        <v>50.26</v>
       </c>
       <c r="AH3">
-        <v>41.69</v>
+        <v>41.53</v>
       </c>
       <c r="AI3">
         <v>48.29</v>
@@ -1114,7 +1114,7 @@
         <v>48</v>
       </c>
       <c r="AK3">
-        <v>28.28</v>
+        <v>27.79</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1125,10 +1125,10 @@
         <v>45</v>
       </c>
       <c r="C4">
-        <v>2920</v>
+        <v>2879</v>
       </c>
       <c r="D4">
-        <v>1.18</v>
+        <v>-1.4</v>
       </c>
       <c r="E4">
         <v>3380.5</v>
@@ -1137,46 +1137,46 @@
         <v>2531.1</v>
       </c>
       <c r="G4">
-        <v>-13.62</v>
+        <v>-14.84</v>
       </c>
       <c r="H4">
-        <v>15.36</v>
+        <v>13.75</v>
       </c>
       <c r="I4">
-        <v>1.04</v>
+        <v>0.73</v>
       </c>
       <c r="J4">
-        <v>-8.380000000000001</v>
+        <v>-9.27</v>
       </c>
       <c r="K4">
-        <v>-6.1</v>
+        <v>-8.42</v>
       </c>
       <c r="L4">
-        <v>4.36</v>
+        <v>3.72</v>
       </c>
       <c r="M4">
-        <v>11.26</v>
+        <v>11.39</v>
       </c>
       <c r="N4">
         <v>50</v>
       </c>
       <c r="O4">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="P4">
-        <v>2889.78</v>
+        <v>2893.98</v>
       </c>
       <c r="Q4">
-        <v>3019.05</v>
+        <v>3002.54</v>
       </c>
       <c r="R4">
-        <v>3178.34</v>
+        <v>3171.52</v>
       </c>
       <c r="S4">
-        <v>2981.26</v>
+        <v>2981.44</v>
       </c>
       <c r="T4">
-        <v>-2.05</v>
+        <v>-3.44</v>
       </c>
       <c r="U4" t="s">
         <v>46</v>
@@ -1191,34 +1191,34 @@
         <v>1</v>
       </c>
       <c r="Y4">
-        <v>37.62</v>
+        <v>34.62</v>
       </c>
       <c r="Z4">
-        <v>-89.81</v>
+        <v>-88.23999999999999</v>
       </c>
       <c r="AA4">
-        <v>-83.75</v>
+        <v>-84.65000000000001</v>
       </c>
       <c r="AB4">
-        <v>-6.05</v>
+        <v>-3.59</v>
       </c>
       <c r="AC4">
-        <v>52.59</v>
+        <v>66.88</v>
       </c>
       <c r="AD4">
-        <v>42.43</v>
+        <v>53.93</v>
       </c>
       <c r="AE4">
-        <v>61.83</v>
+        <v>63.72</v>
       </c>
       <c r="AF4">
-        <v>-2</v>
+        <v>-40.46</v>
       </c>
       <c r="AG4">
-        <v>3279.43</v>
+        <v>3253.88</v>
       </c>
       <c r="AH4">
-        <v>2758.68</v>
+        <v>2751.21</v>
       </c>
       <c r="AI4">
         <v>3061.2</v>
@@ -1227,7 +1227,7 @@
         <v>48</v>
       </c>
       <c r="AK4">
-        <v>66.36</v>
+        <v>62.36</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1238,58 +1238,58 @@
         <v>45</v>
       </c>
       <c r="C5">
-        <v>908</v>
+        <v>900.45</v>
       </c>
       <c r="D5">
-        <v>1.58</v>
+        <v>-0.83</v>
       </c>
       <c r="E5">
         <v>1149.7</v>
       </c>
       <c r="F5">
-        <v>760.1</v>
+        <v>764.25</v>
       </c>
       <c r="G5">
-        <v>-21.02</v>
+        <v>-21.68</v>
       </c>
       <c r="H5">
-        <v>19.46</v>
+        <v>17.82</v>
       </c>
       <c r="I5">
-        <v>0.85</v>
+        <v>2.03</v>
       </c>
       <c r="J5">
-        <v>-6.65</v>
+        <v>-8.16</v>
       </c>
       <c r="K5">
-        <v>-3.83</v>
+        <v>-5</v>
       </c>
       <c r="L5">
-        <v>17.89</v>
+        <v>18.46</v>
       </c>
       <c r="M5">
-        <v>11.49</v>
+        <v>11.67</v>
       </c>
       <c r="N5">
         <v>62</v>
       </c>
       <c r="O5">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="P5">
-        <v>893.8200000000001</v>
+        <v>897.41</v>
       </c>
       <c r="Q5">
-        <v>937.38</v>
+        <v>933.08</v>
       </c>
       <c r="R5">
-        <v>990.39</v>
+        <v>987.86</v>
       </c>
       <c r="S5">
-        <v>983.54</v>
+        <v>983.62</v>
       </c>
       <c r="T5">
-        <v>-7.68</v>
+        <v>-8.460000000000001</v>
       </c>
       <c r="U5" t="s">
         <v>46</v>
@@ -1304,34 +1304,34 @@
         <v>1</v>
       </c>
       <c r="Y5">
-        <v>40.29</v>
+        <v>38.64</v>
       </c>
       <c r="Z5">
-        <v>-27.65</v>
+        <v>-26.62</v>
       </c>
       <c r="AA5">
-        <v>-25.54</v>
+        <v>-25.75</v>
       </c>
       <c r="AB5">
-        <v>-2.11</v>
+        <v>-0.86</v>
       </c>
       <c r="AC5">
-        <v>61.3</v>
+        <v>81.06999999999999</v>
       </c>
       <c r="AD5">
-        <v>41.83</v>
+        <v>60.89</v>
       </c>
       <c r="AE5">
-        <v>22.75</v>
+        <v>22.34</v>
       </c>
       <c r="AF5">
-        <v>-17.83</v>
+        <v>-51.51</v>
       </c>
       <c r="AG5">
-        <v>1014.98</v>
+        <v>1008.73</v>
       </c>
       <c r="AH5">
-        <v>859.78</v>
+        <v>857.42</v>
       </c>
       <c r="AI5">
         <v>946.48</v>
@@ -1340,7 +1340,7 @@
         <v>48</v>
       </c>
       <c r="AK5">
-        <v>48.31</v>
+        <v>45.8</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1351,49 +1351,49 @@
         <v>45</v>
       </c>
       <c r="C6">
-        <v>12.59</v>
+        <v>12.28</v>
       </c>
       <c r="D6">
-        <v>0.5600000000000001</v>
+        <v>-2.46</v>
       </c>
       <c r="E6">
         <v>15.6</v>
       </c>
       <c r="F6">
-        <v>8.359999999999999</v>
+        <v>8.529999999999999</v>
       </c>
       <c r="G6">
-        <v>-19.29</v>
+        <v>-21.28</v>
       </c>
       <c r="H6">
-        <v>50.6</v>
+        <v>43.96</v>
       </c>
       <c r="I6">
-        <v>-3.15</v>
+        <v>-3.08</v>
       </c>
       <c r="J6">
-        <v>-11.71</v>
+        <v>-13.64</v>
       </c>
       <c r="K6">
-        <v>-8.369999999999999</v>
+        <v>-9.1</v>
       </c>
       <c r="L6">
-        <v>44.22</v>
+        <v>46.89</v>
       </c>
       <c r="M6">
-        <v>3.51</v>
+        <v>4.19</v>
       </c>
       <c r="N6">
         <v>87</v>
       </c>
       <c r="O6">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="P6">
-        <v>12.65</v>
+        <v>12.57</v>
       </c>
       <c r="Q6">
-        <v>13.29</v>
+        <v>13.2</v>
       </c>
       <c r="R6">
         <v>13.87</v>
@@ -1402,7 +1402,7 @@
         <v>12.3</v>
       </c>
       <c r="T6">
-        <v>2.36</v>
+        <v>-0.17</v>
       </c>
       <c r="U6" t="s">
         <v>46</v>
@@ -1414,46 +1414,46 @@
         <v>46</v>
       </c>
       <c r="X6">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y6">
-        <v>37.79</v>
+        <v>34.48</v>
       </c>
       <c r="Z6">
-        <v>-0.43</v>
+        <v>-0.45</v>
       </c>
       <c r="AA6">
-        <v>-0.37</v>
+        <v>-0.38</v>
       </c>
       <c r="AB6">
         <v>-0.06</v>
       </c>
       <c r="AC6">
-        <v>36.78</v>
+        <v>31.91</v>
       </c>
       <c r="AD6">
-        <v>31.91</v>
+        <v>32.7</v>
       </c>
       <c r="AE6">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="AF6">
-        <v>-29.65</v>
+        <v>-17.97</v>
       </c>
       <c r="AG6">
-        <v>14.6</v>
+        <v>14.55</v>
       </c>
       <c r="AH6">
-        <v>11.97</v>
+        <v>11.85</v>
       </c>
       <c r="AI6">
-        <v>13.83</v>
+        <v>13.73</v>
       </c>
       <c r="AJ6" t="s">
         <v>48</v>
       </c>
       <c r="AK6">
-        <v>44.53</v>
+        <v>47.19</v>
       </c>
     </row>
     <row r="7" spans="1:37">
@@ -1464,10 +1464,10 @@
         <v>45</v>
       </c>
       <c r="C7">
-        <v>12.4</v>
+        <v>12.74</v>
       </c>
       <c r="D7">
-        <v>9.25</v>
+        <v>2.74</v>
       </c>
       <c r="E7">
         <v>13.92</v>
@@ -1476,46 +1476,46 @@
         <v>4.69</v>
       </c>
       <c r="G7">
-        <v>-10.92</v>
+        <v>-8.48</v>
       </c>
       <c r="H7">
-        <v>164.39</v>
+        <v>171.64</v>
       </c>
       <c r="I7">
-        <v>12.12</v>
+        <v>17.1</v>
       </c>
       <c r="J7">
-        <v>0.32</v>
+        <v>3.24</v>
       </c>
       <c r="K7">
-        <v>8.68</v>
+        <v>9.539999999999999</v>
       </c>
       <c r="L7">
-        <v>143.61</v>
+        <v>153.28</v>
       </c>
       <c r="M7">
-        <v>-29.09</v>
+        <v>-28.24</v>
       </c>
       <c r="N7">
         <v>99</v>
       </c>
       <c r="O7">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="P7">
-        <v>11.54</v>
+        <v>11.91</v>
       </c>
       <c r="Q7">
-        <v>11.21</v>
+        <v>11.25</v>
       </c>
       <c r="R7">
         <v>11.51</v>
       </c>
       <c r="S7">
-        <v>10.83</v>
+        <v>10.82</v>
       </c>
       <c r="T7">
-        <v>14.49</v>
+        <v>17.69</v>
       </c>
       <c r="U7" t="s">
         <v>46</v>
@@ -1530,43 +1530,43 @@
         <v>2</v>
       </c>
       <c r="Y7">
-        <v>62.43</v>
+        <v>65.19</v>
       </c>
       <c r="Z7">
-        <v>0.01</v>
+        <v>0.12</v>
       </c>
       <c r="AA7">
-        <v>-0.13</v>
+        <v>-0.08</v>
       </c>
       <c r="AB7">
-        <v>0.14</v>
+        <v>0.2</v>
       </c>
       <c r="AC7">
         <v>94.48</v>
       </c>
       <c r="AD7">
-        <v>94.09999999999999</v>
+        <v>94.48</v>
       </c>
       <c r="AE7">
-        <v>0.67</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AF7">
-        <v>731.73</v>
+        <v>183.03</v>
       </c>
       <c r="AG7">
-        <v>12.23</v>
+        <v>12.44</v>
       </c>
       <c r="AH7">
-        <v>10.18</v>
+        <v>10.05</v>
       </c>
       <c r="AI7">
-        <v>9.83</v>
+        <v>10.86</v>
       </c>
       <c r="AJ7" t="s">
         <v>49</v>
       </c>
       <c r="AK7">
-        <v>30.29</v>
+        <v>35.15</v>
       </c>
     </row>
     <row r="8" spans="1:37">
@@ -1577,10 +1577,10 @@
         <v>45</v>
       </c>
       <c r="C8">
-        <v>3984.2</v>
+        <v>3951.5</v>
       </c>
       <c r="D8">
-        <v>0.38</v>
+        <v>-0.82</v>
       </c>
       <c r="E8">
         <v>5809.5</v>
@@ -1589,46 +1589,46 @@
         <v>3892.3</v>
       </c>
       <c r="G8">
-        <v>-31.42</v>
+        <v>-31.98</v>
       </c>
       <c r="H8">
-        <v>2.36</v>
+        <v>1.52</v>
       </c>
       <c r="I8">
-        <v>1.18</v>
+        <v>0.42</v>
       </c>
       <c r="J8">
-        <v>-1.68</v>
+        <v>-3.2</v>
       </c>
       <c r="K8">
-        <v>-9.15</v>
+        <v>-9.550000000000001</v>
       </c>
       <c r="L8">
-        <v>-24.59</v>
+        <v>-24.81</v>
       </c>
       <c r="M8">
-        <v>15.42</v>
+        <v>15.61</v>
       </c>
       <c r="N8">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="O8">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="P8">
-        <v>3965.54</v>
+        <v>3968.86</v>
       </c>
       <c r="Q8">
-        <v>3994.12</v>
+        <v>3988.34</v>
       </c>
       <c r="R8">
-        <v>4192.33</v>
+        <v>4185.06</v>
       </c>
       <c r="S8">
-        <v>4469.03</v>
+        <v>4462.85</v>
       </c>
       <c r="T8">
-        <v>-10.85</v>
+        <v>-11.46</v>
       </c>
       <c r="U8" t="s">
         <v>46</v>
@@ -1643,34 +1643,34 @@
         <v>0</v>
       </c>
       <c r="Y8">
-        <v>43.59</v>
+        <v>41.01</v>
       </c>
       <c r="Z8">
-        <v>-59.94</v>
+        <v>-58.26</v>
       </c>
       <c r="AA8">
-        <v>-71.05</v>
+        <v>-68.48999999999999</v>
       </c>
       <c r="AB8">
-        <v>11.11</v>
+        <v>10.23</v>
       </c>
       <c r="AC8">
-        <v>77.65000000000001</v>
+        <v>72.94</v>
       </c>
       <c r="AD8">
-        <v>70.29000000000001</v>
+        <v>73.62</v>
       </c>
       <c r="AE8">
-        <v>96.64</v>
+        <v>96.31</v>
       </c>
       <c r="AF8">
-        <v>-46.43</v>
+        <v>-77.20999999999999</v>
       </c>
       <c r="AG8">
-        <v>4092.58</v>
+        <v>4082.25</v>
       </c>
       <c r="AH8">
-        <v>3895.65</v>
+        <v>3894.43</v>
       </c>
       <c r="AI8">
         <v>4246.97</v>
@@ -1679,7 +1679,7 @@
         <v>48</v>
       </c>
       <c r="AK8">
-        <v>26.9</v>
+        <v>24.84</v>
       </c>
     </row>
     <row r="9" spans="1:37">
@@ -1690,10 +1690,10 @@
         <v>45</v>
       </c>
       <c r="C9">
-        <v>10907</v>
+        <v>10650</v>
       </c>
       <c r="D9">
-        <v>0.41</v>
+        <v>-2.36</v>
       </c>
       <c r="E9">
         <v>13052</v>
@@ -1702,46 +1702,46 @@
         <v>10362</v>
       </c>
       <c r="G9">
-        <v>-16.43</v>
+        <v>-18.4</v>
       </c>
       <c r="H9">
-        <v>5.26</v>
+        <v>2.78</v>
       </c>
       <c r="I9">
-        <v>2.17</v>
+        <v>1.24</v>
       </c>
       <c r="J9">
-        <v>1.93</v>
+        <v>-1.06</v>
       </c>
       <c r="K9">
-        <v>-6.99</v>
+        <v>-10.53</v>
       </c>
       <c r="L9">
-        <v>-10.39</v>
+        <v>-11.76</v>
       </c>
       <c r="M9">
-        <v>8.57</v>
+        <v>8.720000000000001</v>
       </c>
       <c r="N9">
         <v>38</v>
       </c>
       <c r="O9">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="P9">
-        <v>10766.8</v>
+        <v>10792.8</v>
       </c>
       <c r="Q9">
-        <v>10859.65</v>
+        <v>10841.45</v>
       </c>
       <c r="R9">
-        <v>11206.74</v>
+        <v>11178.24</v>
       </c>
       <c r="S9">
-        <v>11662.51</v>
+        <v>11657.24</v>
       </c>
       <c r="T9">
-        <v>-6.48</v>
+        <v>-8.640000000000001</v>
       </c>
       <c r="U9" t="s">
         <v>46</v>
@@ -1756,34 +1756,34 @@
         <v>0</v>
       </c>
       <c r="Y9">
-        <v>49.66</v>
+        <v>43.06</v>
       </c>
       <c r="Z9">
-        <v>-116.76</v>
+        <v>-119.44</v>
       </c>
       <c r="AA9">
-        <v>-152.59</v>
+        <v>-145.96</v>
       </c>
       <c r="AB9">
-        <v>35.82</v>
+        <v>26.51</v>
       </c>
       <c r="AC9">
-        <v>96.34999999999999</v>
+        <v>86.63</v>
       </c>
       <c r="AD9">
-        <v>84.81</v>
+        <v>90.95999999999999</v>
       </c>
       <c r="AE9">
-        <v>219.86</v>
+        <v>251.87</v>
       </c>
       <c r="AF9">
-        <v>-36.91</v>
+        <v>113.02</v>
       </c>
       <c r="AG9">
-        <v>11265.66</v>
+        <v>11250.94</v>
       </c>
       <c r="AH9">
-        <v>10453.64</v>
+        <v>10431.96</v>
       </c>
       <c r="AI9">
         <v>11169.72</v>
@@ -1792,12 +1792,72 @@
         <v>48</v>
       </c>
       <c r="AK9">
-        <v>30.42</v>
+        <v>31.95</v>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AK9"/>
   <conditionalFormatting sqref="AF2:AF9">
+    <cfRule type="colorScale" priority="13">
+      <colorScale>
+        <cfvo type="min" val="0"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max" val="0"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFFFFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D2:D9">
+    <cfRule type="colorScale" priority="7">
+      <colorScale>
+        <cfvo type="min" val="0"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max" val="0"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFFFFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I2:I9">
+    <cfRule type="colorScale" priority="8">
+      <colorScale>
+        <cfvo type="min" val="0"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max" val="0"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFFFFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J2:J9">
+    <cfRule type="colorScale" priority="9">
+      <colorScale>
+        <cfvo type="min" val="0"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max" val="0"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFFFFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K2:K9">
+    <cfRule type="colorScale" priority="10">
+      <colorScale>
+        <cfvo type="min" val="0"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max" val="0"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFFFFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="L2:L9">
     <cfRule type="colorScale" priority="11">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -1809,8 +1869,14 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2:D9">
-    <cfRule type="colorScale" priority="5">
+  <conditionalFormatting sqref="N2:N9">
+    <cfRule type="cellIs" dxfId="2" priority="5" operator="greaterThanOrEqual">
+      <formula>80</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="3" priority="6" operator="lessThanOrEqual">
+      <formula>20</formula>
+    </cfRule>
+    <cfRule type="colorScale" priority="12">
       <colorScale>
         <cfvo type="min" val="0"/>
         <cfvo type="percentile" val="50"/>
@@ -1819,72 +1885,6 @@
         <color rgb="FFFFFFFF"/>
         <color rgb="FF63BE7B"/>
       </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I2:I9">
-    <cfRule type="colorScale" priority="6">
-      <colorScale>
-        <cfvo type="min" val="0"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max" val="0"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFFFFFF"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="J2:J9">
-    <cfRule type="colorScale" priority="7">
-      <colorScale>
-        <cfvo type="min" val="0"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max" val="0"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFFFFFF"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K2:K9">
-    <cfRule type="colorScale" priority="8">
-      <colorScale>
-        <cfvo type="min" val="0"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max" val="0"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFFFFFF"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="L2:L9">
-    <cfRule type="colorScale" priority="9">
-      <colorScale>
-        <cfvo type="min" val="0"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max" val="0"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFFFFFF"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="N2:N9">
-    <cfRule type="colorScale" priority="10">
-      <colorScale>
-        <cfvo type="min" val="0"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max" val="0"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFFFFFF"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="2" priority="18" operator="greaterThanOrEqual">
-      <formula>80</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="3" priority="19" operator="lessThanOrEqual">
-      <formula>20</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="T2:T9">
@@ -1896,26 +1896,26 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="U2:U9">
-    <cfRule type="containsText" dxfId="1" priority="12" operator="containsText" text="Yes">
+    <cfRule type="containsText" dxfId="1" priority="14" operator="containsText" text="Yes">
       <formula>NOT(ISERROR(SEARCH("Yes",U2)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="0" priority="13" operator="containsText" text="No">
+    <cfRule type="containsText" dxfId="0" priority="15" operator="containsText" text="No">
       <formula>NOT(ISERROR(SEARCH("No",U2)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V2:V9">
-    <cfRule type="containsText" dxfId="1" priority="14" operator="containsText" text="Yes">
+    <cfRule type="containsText" dxfId="1" priority="16" operator="containsText" text="Yes">
       <formula>NOT(ISERROR(SEARCH("Yes",V2)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="0" priority="15" operator="containsText" text="No">
+    <cfRule type="containsText" dxfId="0" priority="17" operator="containsText" text="No">
       <formula>NOT(ISERROR(SEARCH("No",V2)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="W2:W9">
-    <cfRule type="containsText" dxfId="1" priority="16" operator="containsText" text="Yes">
+    <cfRule type="containsText" dxfId="1" priority="18" operator="containsText" text="Yes">
       <formula>NOT(ISERROR(SEARCH("Yes",W2)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="0" priority="17" operator="containsText" text="No">
+    <cfRule type="containsText" dxfId="0" priority="19" operator="containsText" text="No">
       <formula>NOT(ISERROR(SEARCH("No",W2)))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -1990,13 +1990,13 @@
         <v>9</v>
       </c>
       <c r="C7" s="5">
-        <v>0.91</v>
+        <v>-0.5</v>
       </c>
       <c r="D7" s="5">
-        <v>-0.5</v>
+        <v>-4.35</v>
       </c>
       <c r="E7" s="6">
-        <v>-1.41</v>
+        <v>-3.85</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -2007,13 +2007,13 @@
         <v>9</v>
       </c>
       <c r="C8" s="5">
-        <v>-8.49</v>
+        <v>-9.869999999999999</v>
       </c>
       <c r="D8" s="5">
-        <v>-9.869999999999999</v>
+        <v>-14.47</v>
       </c>
       <c r="E8" s="6">
-        <v>-1.38</v>
+        <v>-4.6</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -2024,13 +2024,13 @@
         <v>9</v>
       </c>
       <c r="C9" s="5">
-        <v>-8.99</v>
+        <v>-8.380000000000001</v>
       </c>
       <c r="D9" s="5">
-        <v>-8.380000000000001</v>
-      </c>
-      <c r="E9" s="7">
-        <v>0.61</v>
+        <v>-9.27</v>
+      </c>
+      <c r="E9" s="6">
+        <v>-0.89</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -2041,13 +2041,13 @@
         <v>9</v>
       </c>
       <c r="C10" s="5">
-        <v>-6.76</v>
+        <v>-6.65</v>
       </c>
       <c r="D10" s="5">
-        <v>-6.65</v>
-      </c>
-      <c r="E10" s="7">
-        <v>0.11</v>
+        <v>-8.16</v>
+      </c>
+      <c r="E10" s="6">
+        <v>-1.51</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -2058,13 +2058,13 @@
         <v>9</v>
       </c>
       <c r="C11" s="5">
-        <v>-13.36</v>
+        <v>-11.71</v>
       </c>
       <c r="D11" s="5">
-        <v>-11.71</v>
-      </c>
-      <c r="E11" s="7">
-        <v>1.65</v>
+        <v>-13.64</v>
+      </c>
+      <c r="E11" s="6">
+        <v>-1.93</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -2075,13 +2075,13 @@
         <v>9</v>
       </c>
       <c r="C12" s="5">
-        <v>-9.92</v>
+        <v>0.32</v>
       </c>
       <c r="D12" s="5">
-        <v>0.32</v>
+        <v>3.24</v>
       </c>
       <c r="E12" s="7">
-        <v>10.24</v>
+        <v>2.92</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -2092,13 +2092,13 @@
         <v>9</v>
       </c>
       <c r="C13" s="5">
-        <v>-2.76</v>
+        <v>-1.68</v>
       </c>
       <c r="D13" s="5">
-        <v>-1.68</v>
-      </c>
-      <c r="E13" s="7">
-        <v>1.08</v>
+        <v>-3.2</v>
+      </c>
+      <c r="E13" s="6">
+        <v>-1.52</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -2109,13 +2109,13 @@
         <v>9</v>
       </c>
       <c r="C14" s="5">
-        <v>1.54</v>
+        <v>1.93</v>
       </c>
       <c r="D14" s="5">
-        <v>1.93</v>
-      </c>
-      <c r="E14" s="7">
-        <v>0.39</v>
+        <v>-1.06</v>
+      </c>
+      <c r="E14" s="6">
+        <v>-2.99</v>
       </c>
     </row>
     <row r="15" spans="1:6">
@@ -2126,13 +2126,13 @@
         <v>8</v>
       </c>
       <c r="C15" s="5">
-        <v>3.69</v>
+        <v>-0.34</v>
       </c>
       <c r="D15" s="5">
-        <v>-0.34</v>
+        <v>-1.89</v>
       </c>
       <c r="E15" s="6">
-        <v>-4.03</v>
+        <v>-1.55</v>
       </c>
     </row>
     <row r="16" spans="1:6">
@@ -2143,13 +2143,13 @@
         <v>8</v>
       </c>
       <c r="C16" s="5">
-        <v>3.89</v>
+        <v>2.7</v>
       </c>
       <c r="D16" s="5">
-        <v>2.7</v>
+        <v>-0.87</v>
       </c>
       <c r="E16" s="6">
-        <v>-1.19</v>
+        <v>-3.57</v>
       </c>
     </row>
     <row r="17" spans="1:5">
@@ -2160,13 +2160,13 @@
         <v>8</v>
       </c>
       <c r="C17" s="5">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="D17" s="5">
-        <v>1.04</v>
-      </c>
-      <c r="E17" s="7">
-        <v>0.02</v>
+        <v>0.73</v>
+      </c>
+      <c r="E17" s="6">
+        <v>-0.31</v>
       </c>
     </row>
     <row r="18" spans="1:5">
@@ -2177,13 +2177,13 @@
         <v>8</v>
       </c>
       <c r="C18" s="5">
-        <v>0.42</v>
+        <v>0.85</v>
       </c>
       <c r="D18" s="5">
-        <v>0.85</v>
+        <v>2.03</v>
       </c>
       <c r="E18" s="7">
-        <v>0.43</v>
+        <v>1.18</v>
       </c>
     </row>
     <row r="19" spans="1:5">
@@ -2194,13 +2194,13 @@
         <v>8</v>
       </c>
       <c r="C19" s="5">
-        <v>-2.19</v>
+        <v>-3.15</v>
       </c>
       <c r="D19" s="5">
-        <v>-3.15</v>
-      </c>
-      <c r="E19" s="6">
-        <v>-0.96</v>
+        <v>-3.08</v>
+      </c>
+      <c r="E19" s="7">
+        <v>0.07000000000000001</v>
       </c>
     </row>
     <row r="20" spans="1:5">
@@ -2211,13 +2211,13 @@
         <v>8</v>
       </c>
       <c r="C20" s="5">
-        <v>7.48</v>
+        <v>12.12</v>
       </c>
       <c r="D20" s="5">
-        <v>12.12</v>
+        <v>17.1</v>
       </c>
       <c r="E20" s="7">
-        <v>4.64</v>
+        <v>4.98</v>
       </c>
     </row>
     <row r="21" spans="1:5">
@@ -2228,13 +2228,13 @@
         <v>8</v>
       </c>
       <c r="C21" s="5">
-        <v>0.53</v>
+        <v>1.18</v>
       </c>
       <c r="D21" s="5">
-        <v>1.18</v>
-      </c>
-      <c r="E21" s="7">
-        <v>0.65</v>
+        <v>0.42</v>
+      </c>
+      <c r="E21" s="6">
+        <v>-0.76</v>
       </c>
     </row>
     <row r="22" spans="1:5">
@@ -2245,13 +2245,13 @@
         <v>8</v>
       </c>
       <c r="C22" s="5">
-        <v>4.18</v>
+        <v>2.17</v>
       </c>
       <c r="D22" s="5">
-        <v>2.17</v>
+        <v>1.24</v>
       </c>
       <c r="E22" s="6">
-        <v>-2.01</v>
+        <v>-0.93</v>
       </c>
     </row>
     <row r="23" spans="1:5">
@@ -2262,13 +2262,13 @@
         <v>11</v>
       </c>
       <c r="C23" s="5">
-        <v>30.31</v>
+        <v>26.87</v>
       </c>
       <c r="D23" s="5">
-        <v>26.87</v>
+        <v>25.18</v>
       </c>
       <c r="E23" s="6">
-        <v>-3.44</v>
+        <v>-1.69</v>
       </c>
     </row>
     <row r="24" spans="1:5">
@@ -2279,13 +2279,13 @@
         <v>11</v>
       </c>
       <c r="C24" s="5">
-        <v>-46.08</v>
+        <v>-45.31</v>
       </c>
       <c r="D24" s="5">
-        <v>-45.31</v>
-      </c>
-      <c r="E24" s="7">
-        <v>0.77</v>
+        <v>-46.16</v>
+      </c>
+      <c r="E24" s="6">
+        <v>-0.85</v>
       </c>
     </row>
     <row r="25" spans="1:5">
@@ -2296,13 +2296,13 @@
         <v>11</v>
       </c>
       <c r="C25" s="5">
-        <v>2.66</v>
+        <v>4.36</v>
       </c>
       <c r="D25" s="5">
-        <v>4.36</v>
-      </c>
-      <c r="E25" s="7">
-        <v>1.7</v>
+        <v>3.72</v>
+      </c>
+      <c r="E25" s="6">
+        <v>-0.64</v>
       </c>
     </row>
     <row r="26" spans="1:5">
@@ -2313,13 +2313,13 @@
         <v>11</v>
       </c>
       <c r="C26" s="5">
-        <v>15.49</v>
+        <v>17.89</v>
       </c>
       <c r="D26" s="5">
-        <v>17.89</v>
+        <v>18.46</v>
       </c>
       <c r="E26" s="7">
-        <v>2.4</v>
+        <v>0.57</v>
       </c>
     </row>
     <row r="27" spans="1:5">
@@ -2330,13 +2330,13 @@
         <v>11</v>
       </c>
       <c r="C27" s="5">
-        <v>38.5</v>
+        <v>44.22</v>
       </c>
       <c r="D27" s="5">
-        <v>44.22</v>
+        <v>46.89</v>
       </c>
       <c r="E27" s="7">
-        <v>5.72</v>
+        <v>2.67</v>
       </c>
     </row>
     <row r="28" spans="1:5">
@@ -2347,13 +2347,13 @@
         <v>11</v>
       </c>
       <c r="C28" s="5">
-        <v>118.69</v>
+        <v>143.61</v>
       </c>
       <c r="D28" s="5">
-        <v>143.61</v>
+        <v>153.28</v>
       </c>
       <c r="E28" s="7">
-        <v>24.92</v>
+        <v>9.67</v>
       </c>
     </row>
     <row r="29" spans="1:5">
@@ -2364,13 +2364,13 @@
         <v>11</v>
       </c>
       <c r="C29" s="5">
-        <v>-25.06</v>
+        <v>-24.59</v>
       </c>
       <c r="D29" s="5">
-        <v>-24.59</v>
-      </c>
-      <c r="E29" s="7">
-        <v>0.47</v>
+        <v>-24.81</v>
+      </c>
+      <c r="E29" s="6">
+        <v>-0.22</v>
       </c>
     </row>
     <row r="30" spans="1:5">
@@ -2381,13 +2381,13 @@
         <v>11</v>
       </c>
       <c r="C30" s="5">
-        <v>-11.55</v>
+        <v>-10.39</v>
       </c>
       <c r="D30" s="5">
-        <v>-10.39</v>
-      </c>
-      <c r="E30" s="7">
-        <v>1.16</v>
+        <v>-11.76</v>
+      </c>
+      <c r="E30" s="6">
+        <v>-1.37</v>
       </c>
     </row>
     <row r="31" spans="1:5">
@@ -2398,13 +2398,13 @@
         <v>10</v>
       </c>
       <c r="C31" s="5">
-        <v>-4.37</v>
+        <v>-5.52</v>
       </c>
       <c r="D31" s="5">
-        <v>-5.52</v>
+        <v>-7</v>
       </c>
       <c r="E31" s="6">
-        <v>-1.15</v>
+        <v>-1.48</v>
       </c>
     </row>
     <row r="32" spans="1:5">
@@ -2415,13 +2415,13 @@
         <v>10</v>
       </c>
       <c r="C32" s="5">
-        <v>-23.55</v>
+        <v>-22.51</v>
       </c>
       <c r="D32" s="5">
-        <v>-22.51</v>
-      </c>
-      <c r="E32" s="7">
-        <v>1.04</v>
+        <v>-24.67</v>
+      </c>
+      <c r="E32" s="6">
+        <v>-2.16</v>
       </c>
     </row>
     <row r="33" spans="1:5">
@@ -2432,13 +2432,13 @@
         <v>10</v>
       </c>
       <c r="C33" s="5">
-        <v>-6.09</v>
+        <v>-6.1</v>
       </c>
       <c r="D33" s="5">
-        <v>-6.1</v>
+        <v>-8.42</v>
       </c>
       <c r="E33" s="6">
-        <v>-0.01</v>
+        <v>-2.32</v>
       </c>
     </row>
     <row r="34" spans="1:5">
@@ -2449,13 +2449,13 @@
         <v>10</v>
       </c>
       <c r="C34" s="5">
-        <v>-6.82</v>
+        <v>-3.83</v>
       </c>
       <c r="D34" s="5">
-        <v>-3.83</v>
-      </c>
-      <c r="E34" s="7">
-        <v>2.99</v>
+        <v>-5</v>
+      </c>
+      <c r="E34" s="6">
+        <v>-1.17</v>
       </c>
     </row>
     <row r="35" spans="1:5">
@@ -2466,13 +2466,13 @@
         <v>10</v>
       </c>
       <c r="C35" s="5">
-        <v>-9.859999999999999</v>
+        <v>-8.369999999999999</v>
       </c>
       <c r="D35" s="5">
-        <v>-8.369999999999999</v>
-      </c>
-      <c r="E35" s="7">
-        <v>1.49</v>
+        <v>-9.1</v>
+      </c>
+      <c r="E35" s="6">
+        <v>-0.73</v>
       </c>
     </row>
     <row r="36" spans="1:5">
@@ -2483,13 +2483,13 @@
         <v>10</v>
       </c>
       <c r="C36" s="5">
-        <v>1.43</v>
+        <v>8.68</v>
       </c>
       <c r="D36" s="5">
-        <v>8.68</v>
+        <v>9.539999999999999</v>
       </c>
       <c r="E36" s="7">
-        <v>7.25</v>
+        <v>0.86</v>
       </c>
     </row>
     <row r="37" spans="1:5">
@@ -2500,13 +2500,13 @@
         <v>10</v>
       </c>
       <c r="C37" s="5">
-        <v>-10.02</v>
+        <v>-9.15</v>
       </c>
       <c r="D37" s="5">
-        <v>-9.15</v>
-      </c>
-      <c r="E37" s="7">
-        <v>0.87</v>
+        <v>-9.550000000000001</v>
+      </c>
+      <c r="E37" s="6">
+        <v>-0.4</v>
       </c>
     </row>
     <row r="38" spans="1:5">
@@ -2517,13 +2517,13 @@
         <v>10</v>
       </c>
       <c r="C38" s="5">
-        <v>-7.72</v>
+        <v>-6.99</v>
       </c>
       <c r="D38" s="5">
-        <v>-6.99</v>
-      </c>
-      <c r="E38" s="7">
-        <v>0.73</v>
+        <v>-10.53</v>
+      </c>
+      <c r="E38" s="6">
+        <v>-3.54</v>
       </c>
     </row>
     <row r="39" spans="1:5">
@@ -2534,13 +2534,13 @@
         <v>6</v>
       </c>
       <c r="C39" s="5">
-        <v>-10</v>
+        <v>-10.67</v>
       </c>
       <c r="D39" s="5">
-        <v>-10.67</v>
+        <v>-12.16</v>
       </c>
       <c r="E39" s="6">
-        <v>-0.67</v>
+        <v>-1.49</v>
       </c>
     </row>
     <row r="40" spans="1:5">
@@ -2551,13 +2551,13 @@
         <v>6</v>
       </c>
       <c r="C40" s="5">
-        <v>-47.46</v>
+        <v>-47.49</v>
       </c>
       <c r="D40" s="5">
-        <v>-47.49</v>
+        <v>-49.46</v>
       </c>
       <c r="E40" s="6">
-        <v>-0.03</v>
+        <v>-1.97</v>
       </c>
     </row>
     <row r="41" spans="1:5">
@@ -2568,13 +2568,13 @@
         <v>6</v>
       </c>
       <c r="C41" s="5">
-        <v>-14.63</v>
+        <v>-13.62</v>
       </c>
       <c r="D41" s="5">
-        <v>-13.62</v>
-      </c>
-      <c r="E41" s="7">
-        <v>1.01</v>
+        <v>-14.84</v>
+      </c>
+      <c r="E41" s="6">
+        <v>-1.22</v>
       </c>
     </row>
     <row r="42" spans="1:5">
@@ -2585,13 +2585,13 @@
         <v>6</v>
       </c>
       <c r="C42" s="5">
-        <v>-22.25</v>
+        <v>-21.02</v>
       </c>
       <c r="D42" s="5">
-        <v>-21.02</v>
-      </c>
-      <c r="E42" s="7">
-        <v>1.23</v>
+        <v>-21.68</v>
+      </c>
+      <c r="E42" s="6">
+        <v>-0.66</v>
       </c>
     </row>
     <row r="43" spans="1:5">
@@ -2602,13 +2602,13 @@
         <v>6</v>
       </c>
       <c r="C43" s="5">
-        <v>-19.74</v>
+        <v>-19.29</v>
       </c>
       <c r="D43" s="5">
-        <v>-19.29</v>
-      </c>
-      <c r="E43" s="7">
-        <v>0.45</v>
+        <v>-21.28</v>
+      </c>
+      <c r="E43" s="6">
+        <v>-1.99</v>
       </c>
     </row>
     <row r="44" spans="1:5">
@@ -2619,13 +2619,13 @@
         <v>6</v>
       </c>
       <c r="C44" s="5">
-        <v>-18.46</v>
+        <v>-10.92</v>
       </c>
       <c r="D44" s="5">
-        <v>-10.92</v>
+        <v>-8.48</v>
       </c>
       <c r="E44" s="7">
-        <v>7.54</v>
+        <v>2.44</v>
       </c>
     </row>
     <row r="45" spans="1:5">
@@ -2636,13 +2636,13 @@
         <v>6</v>
       </c>
       <c r="C45" s="5">
-        <v>-31.68</v>
+        <v>-31.42</v>
       </c>
       <c r="D45" s="5">
-        <v>-31.42</v>
-      </c>
-      <c r="E45" s="7">
-        <v>0.26</v>
+        <v>-31.98</v>
+      </c>
+      <c r="E45" s="6">
+        <v>-0.5600000000000001</v>
       </c>
     </row>
     <row r="46" spans="1:5">
@@ -2653,13 +2653,13 @@
         <v>6</v>
       </c>
       <c r="C46" s="5">
-        <v>-16.78</v>
+        <v>-16.43</v>
       </c>
       <c r="D46" s="5">
-        <v>-16.43</v>
-      </c>
-      <c r="E46" s="7">
-        <v>0.35</v>
+        <v>-18.4</v>
+      </c>
+      <c r="E46" s="6">
+        <v>-1.97</v>
       </c>
     </row>
     <row r="47" spans="1:5">
@@ -2670,13 +2670,13 @@
         <v>2</v>
       </c>
       <c r="C47" s="5">
-        <v>382.25</v>
+        <v>379.4</v>
       </c>
       <c r="D47" s="5">
-        <v>379.4</v>
+        <v>373.05</v>
       </c>
       <c r="E47" s="6">
-        <v>-2.85</v>
+        <v>-6.35</v>
       </c>
     </row>
     <row r="48" spans="1:5">
@@ -2687,13 +2687,13 @@
         <v>2</v>
       </c>
       <c r="C48" s="5">
-        <v>44.86</v>
+        <v>44.83</v>
       </c>
       <c r="D48" s="5">
-        <v>44.83</v>
+        <v>43.15</v>
       </c>
       <c r="E48" s="6">
-        <v>-0.03</v>
+        <v>-1.68</v>
       </c>
     </row>
     <row r="49" spans="1:5">
@@ -2704,13 +2704,13 @@
         <v>2</v>
       </c>
       <c r="C49" s="5">
-        <v>2885.9</v>
+        <v>2920</v>
       </c>
       <c r="D49" s="5">
-        <v>2920</v>
-      </c>
-      <c r="E49" s="7">
-        <v>34.1</v>
+        <v>2879</v>
+      </c>
+      <c r="E49" s="6">
+        <v>-41</v>
       </c>
     </row>
     <row r="50" spans="1:5">
@@ -2721,13 +2721,13 @@
         <v>2</v>
       </c>
       <c r="C50" s="5">
-        <v>893.85</v>
+        <v>908</v>
       </c>
       <c r="D50" s="5">
-        <v>908</v>
-      </c>
-      <c r="E50" s="7">
-        <v>14.15</v>
+        <v>900.45</v>
+      </c>
+      <c r="E50" s="6">
+        <v>-7.55</v>
       </c>
     </row>
     <row r="51" spans="1:5">
@@ -2738,13 +2738,13 @@
         <v>2</v>
       </c>
       <c r="C51" s="5">
-        <v>12.52</v>
+        <v>12.59</v>
       </c>
       <c r="D51" s="5">
-        <v>12.59</v>
-      </c>
-      <c r="E51" s="7">
-        <v>0.07000000000000001</v>
+        <v>12.28</v>
+      </c>
+      <c r="E51" s="6">
+        <v>-0.31</v>
       </c>
     </row>
     <row r="52" spans="1:5">
@@ -2755,13 +2755,13 @@
         <v>2</v>
       </c>
       <c r="C52" s="5">
-        <v>11.35</v>
+        <v>12.4</v>
       </c>
       <c r="D52" s="5">
-        <v>12.4</v>
+        <v>12.74</v>
       </c>
       <c r="E52" s="7">
-        <v>1.05</v>
+        <v>0.34</v>
       </c>
     </row>
     <row r="53" spans="1:5">
@@ -2772,13 +2772,13 @@
         <v>2</v>
       </c>
       <c r="C53" s="5">
-        <v>3969.3</v>
+        <v>3984.2</v>
       </c>
       <c r="D53" s="5">
-        <v>3984.2</v>
-      </c>
-      <c r="E53" s="7">
-        <v>14.9</v>
+        <v>3951.5</v>
+      </c>
+      <c r="E53" s="6">
+        <v>-32.7</v>
       </c>
     </row>
     <row r="54" spans="1:5">
@@ -2789,13 +2789,13 @@
         <v>2</v>
       </c>
       <c r="C54" s="5">
-        <v>10862</v>
+        <v>10907</v>
       </c>
       <c r="D54" s="5">
-        <v>10907</v>
-      </c>
-      <c r="E54" s="7">
-        <v>45</v>
+        <v>10650</v>
+      </c>
+      <c r="E54" s="6">
+        <v>-257</v>
       </c>
     </row>
     <row r="55" spans="1:5">
@@ -2806,30 +2806,30 @@
         <v>13</v>
       </c>
       <c r="C55" s="5">
-        <v>87</v>
+        <v>74</v>
       </c>
       <c r="D55" s="5">
-        <v>74</v>
-      </c>
-      <c r="E55" s="6">
-        <v>-13</v>
+        <v>75</v>
+      </c>
+      <c r="E55" s="7">
+        <v>1</v>
       </c>
     </row>
     <row r="56" spans="1:5">
       <c r="A56" s="3" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="B56" s="3" t="s">
         <v>13</v>
       </c>
       <c r="C56" s="5">
-        <v>74</v>
+        <v>26</v>
       </c>
       <c r="D56" s="5">
-        <v>87</v>
-      </c>
-      <c r="E56" s="7">
-        <v>13</v>
+        <v>25</v>
+      </c>
+      <c r="E56" s="6">
+        <v>-1</v>
       </c>
     </row>
     <row r="57" spans="1:5">
@@ -2840,13 +2840,13 @@
         <v>24</v>
       </c>
       <c r="C57" s="5">
-        <v>47.05</v>
+        <v>45.16</v>
       </c>
       <c r="D57" s="5">
-        <v>45.16</v>
+        <v>41.2</v>
       </c>
       <c r="E57" s="6">
-        <v>-1.89</v>
+        <v>-3.96</v>
       </c>
     </row>
     <row r="58" spans="1:5">
@@ -2857,13 +2857,13 @@
         <v>24</v>
       </c>
       <c r="C58" s="5">
-        <v>37.55</v>
+        <v>37.44</v>
       </c>
       <c r="D58" s="5">
-        <v>37.44</v>
+        <v>31.87</v>
       </c>
       <c r="E58" s="6">
-        <v>-0.11</v>
+        <v>-5.57</v>
       </c>
     </row>
     <row r="59" spans="1:5">
@@ -2874,13 +2874,13 @@
         <v>24</v>
       </c>
       <c r="C59" s="5">
-        <v>33.15</v>
+        <v>37.62</v>
       </c>
       <c r="D59" s="5">
-        <v>37.62</v>
-      </c>
-      <c r="E59" s="7">
-        <v>4.47</v>
+        <v>34.62</v>
+      </c>
+      <c r="E59" s="6">
+        <v>-3</v>
       </c>
     </row>
     <row r="60" spans="1:5">
@@ -2891,13 +2891,13 @@
         <v>24</v>
       </c>
       <c r="C60" s="5">
-        <v>35.49</v>
+        <v>40.29</v>
       </c>
       <c r="D60" s="5">
-        <v>40.29</v>
-      </c>
-      <c r="E60" s="7">
-        <v>4.8</v>
+        <v>38.64</v>
+      </c>
+      <c r="E60" s="6">
+        <v>-1.65</v>
       </c>
     </row>
     <row r="61" spans="1:5">
@@ -2908,13 +2908,13 @@
         <v>24</v>
       </c>
       <c r="C61" s="5">
-        <v>36.51</v>
+        <v>37.79</v>
       </c>
       <c r="D61" s="5">
-        <v>37.79</v>
-      </c>
-      <c r="E61" s="7">
-        <v>1.28</v>
+        <v>34.48</v>
+      </c>
+      <c r="E61" s="6">
+        <v>-3.31</v>
       </c>
     </row>
     <row r="62" spans="1:5">
@@ -2925,13 +2925,13 @@
         <v>24</v>
       </c>
       <c r="C62" s="5">
-        <v>51.36</v>
+        <v>62.43</v>
       </c>
       <c r="D62" s="5">
-        <v>62.43</v>
+        <v>65.19</v>
       </c>
       <c r="E62" s="7">
-        <v>11.07</v>
+        <v>2.76</v>
       </c>
     </row>
     <row r="63" spans="1:5">
@@ -2942,13 +2942,13 @@
         <v>24</v>
       </c>
       <c r="C63" s="5">
-        <v>42.05</v>
+        <v>43.59</v>
       </c>
       <c r="D63" s="5">
-        <v>43.59</v>
-      </c>
-      <c r="E63" s="7">
-        <v>1.54</v>
+        <v>41.01</v>
+      </c>
+      <c r="E63" s="6">
+        <v>-2.58</v>
       </c>
     </row>
     <row r="64" spans="1:5">
@@ -2959,13 +2959,13 @@
         <v>24</v>
       </c>
       <c r="C64" s="5">
-        <v>48.38</v>
+        <v>49.66</v>
       </c>
       <c r="D64" s="5">
-        <v>49.66</v>
-      </c>
-      <c r="E64" s="7">
-        <v>1.28</v>
+        <v>43.06</v>
+      </c>
+      <c r="E64" s="6">
+        <v>-6.6</v>
       </c>
     </row>
     <row r="65" spans="1:5">
@@ -2976,13 +2976,13 @@
         <v>31</v>
       </c>
       <c r="C65" s="5">
-        <v>-55.42</v>
+        <v>-29.02</v>
       </c>
       <c r="D65" s="5">
-        <v>-29.02</v>
-      </c>
-      <c r="E65" s="7">
-        <v>26.4</v>
+        <v>-59.52</v>
+      </c>
+      <c r="E65" s="6">
+        <v>-30.5</v>
       </c>
     </row>
     <row r="66" spans="1:5">
@@ -2993,13 +2993,13 @@
         <v>31</v>
       </c>
       <c r="C66" s="5">
-        <v>-65.7</v>
+        <v>-64.12</v>
       </c>
       <c r="D66" s="5">
-        <v>-64.12</v>
+        <v>-49.79</v>
       </c>
       <c r="E66" s="7">
-        <v>1.58</v>
+        <v>14.33</v>
       </c>
     </row>
     <row r="67" spans="1:5">
@@ -3010,13 +3010,13 @@
         <v>31</v>
       </c>
       <c r="C67" s="5">
-        <v>-43.7</v>
+        <v>-2</v>
       </c>
       <c r="D67" s="5">
-        <v>-2</v>
-      </c>
-      <c r="E67" s="7">
-        <v>41.7</v>
+        <v>-40.46</v>
+      </c>
+      <c r="E67" s="6">
+        <v>-38.46</v>
       </c>
     </row>
     <row r="68" spans="1:5">
@@ -3027,13 +3027,13 @@
         <v>31</v>
       </c>
       <c r="C68" s="5">
-        <v>43.67</v>
+        <v>-17.83</v>
       </c>
       <c r="D68" s="5">
-        <v>-17.83</v>
+        <v>-51.51</v>
       </c>
       <c r="E68" s="6">
-        <v>-61.5</v>
+        <v>-33.68</v>
       </c>
     </row>
     <row r="69" spans="1:5">
@@ -3044,13 +3044,13 @@
         <v>31</v>
       </c>
       <c r="C69" s="5">
-        <v>-26.32</v>
+        <v>-29.65</v>
       </c>
       <c r="D69" s="5">
-        <v>-29.65</v>
-      </c>
-      <c r="E69" s="6">
-        <v>-3.33</v>
+        <v>-17.97</v>
+      </c>
+      <c r="E69" s="7">
+        <v>11.68</v>
       </c>
     </row>
     <row r="70" spans="1:5">
@@ -3061,13 +3061,13 @@
         <v>31</v>
       </c>
       <c r="C70" s="5">
-        <v>-42.64</v>
+        <v>731.73</v>
       </c>
       <c r="D70" s="5">
-        <v>731.73</v>
-      </c>
-      <c r="E70" s="7">
-        <v>774.37</v>
+        <v>183.03</v>
+      </c>
+      <c r="E70" s="6">
+        <v>-548.7</v>
       </c>
     </row>
     <row r="71" spans="1:5">
@@ -3078,13 +3078,13 @@
         <v>31</v>
       </c>
       <c r="C71" s="5">
-        <v>-62.15</v>
+        <v>-46.43</v>
       </c>
       <c r="D71" s="5">
-        <v>-46.43</v>
-      </c>
-      <c r="E71" s="7">
-        <v>15.72</v>
+        <v>-77.20999999999999</v>
+      </c>
+      <c r="E71" s="6">
+        <v>-30.78</v>
       </c>
     </row>
     <row r="72" spans="1:5">
@@ -3095,13 +3095,13 @@
         <v>31</v>
       </c>
       <c r="C72" s="5">
-        <v>21.41</v>
+        <v>-36.91</v>
       </c>
       <c r="D72" s="5">
-        <v>-36.91</v>
-      </c>
-      <c r="E72" s="6">
-        <v>-58.32</v>
+        <v>113.02</v>
+      </c>
+      <c r="E72" s="7">
+        <v>149.93</v>
       </c>
     </row>
   </sheetData>
@@ -3160,22 +3160,22 @@
         <v>45</v>
       </c>
       <c r="B2" s="10">
-        <v>48.44</v>
+        <v>42.44</v>
       </c>
       <c r="C2" s="11">
         <v>8</v>
       </c>
       <c r="D2" s="10">
-        <v>44.2</v>
+        <v>41.3</v>
       </c>
       <c r="E2" s="10">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="F2" s="10">
-        <v>-4.6</v>
+        <v>-6.4</v>
       </c>
       <c r="G2" s="10">
-        <v>-6.7</v>
+        <v>-8.1</v>
       </c>
       <c r="H2" s="10">
         <v>56.1</v>
@@ -3309,28 +3309,28 @@
     </row>
     <row r="2" spans="1:8">
       <c r="A2" s="13">
-        <v>0.2879</v>
+        <v>0.2855</v>
       </c>
       <c r="B2" s="13">
-        <v>0.1542</v>
+        <v>0.1561</v>
       </c>
       <c r="C2" s="13">
-        <v>0.1149</v>
+        <v>0.1167</v>
       </c>
       <c r="D2" s="13">
-        <v>0.1126</v>
+        <v>0.1139</v>
       </c>
       <c r="E2" s="13">
-        <v>0.0857</v>
+        <v>0.0872</v>
       </c>
       <c r="F2" s="13">
-        <v>0.0351</v>
+        <v>0.04190000000000001</v>
       </c>
       <c r="G2" s="13">
-        <v>-0.2909</v>
+        <v>-0.2824</v>
       </c>
       <c r="H2" s="13">
-        <v>-0.3003</v>
+        <v>-0.2989</v>
       </c>
     </row>
   </sheetData>

--- a/BIRLA_GROUP_Technical_Metrics.xlsx
+++ b/BIRLA_GROUP_Technical_Metrics.xlsx
@@ -758,8 +758,8 @@
     <col min="13" max="13" width="10.7109375" customWidth="1"/>
     <col min="14" max="14" width="11.7109375" customWidth="1"/>
     <col min="15" max="15" width="10.7109375" customWidth="1"/>
-    <col min="16" max="16" width="9.7109375" customWidth="1"/>
-    <col min="17" max="19" width="10.7109375" customWidth="1"/>
+    <col min="16" max="17" width="9.7109375" customWidth="1"/>
+    <col min="18" max="19" width="10.7109375" customWidth="1"/>
     <col min="20" max="20" width="22.7109375" customWidth="1"/>
     <col min="21" max="21" width="9.7109375" customWidth="1"/>
     <col min="22" max="22" width="10.7109375" customWidth="1"/>
@@ -899,10 +899,10 @@
         <v>45</v>
       </c>
       <c r="C2">
-        <v>373.05</v>
+        <v>367</v>
       </c>
       <c r="D2">
-        <v>-1.67</v>
+        <v>-1.62</v>
       </c>
       <c r="E2">
         <v>424.7</v>
@@ -911,46 +911,46 @@
         <v>292.25</v>
       </c>
       <c r="G2">
-        <v>-12.16</v>
+        <v>-13.59</v>
       </c>
       <c r="H2">
-        <v>27.65</v>
+        <v>25.58</v>
       </c>
       <c r="I2">
-        <v>-1.89</v>
+        <v>-4.59</v>
       </c>
       <c r="J2">
-        <v>-4.35</v>
+        <v>-10.5</v>
       </c>
       <c r="K2">
-        <v>-7</v>
+        <v>-10.28</v>
       </c>
       <c r="L2">
-        <v>25.18</v>
+        <v>20.92</v>
       </c>
       <c r="M2">
-        <v>28.55</v>
+        <v>29.11</v>
       </c>
       <c r="N2">
-        <v>75</v>
+        <v>62</v>
       </c>
       <c r="O2">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="P2">
-        <v>379.65</v>
+        <v>376.12</v>
       </c>
       <c r="Q2">
-        <v>382.78</v>
+        <v>380.96</v>
       </c>
       <c r="R2">
-        <v>394.59</v>
+        <v>393.76</v>
       </c>
       <c r="S2">
-        <v>366.21</v>
+        <v>366.26</v>
       </c>
       <c r="T2">
-        <v>1.87</v>
+        <v>0.2</v>
       </c>
       <c r="U2" t="s">
         <v>46</v>
@@ -965,43 +965,43 @@
         <v>2</v>
       </c>
       <c r="Y2">
-        <v>41.2</v>
+        <v>37.79</v>
       </c>
       <c r="Z2">
-        <v>-4.92</v>
+        <v>-5.56</v>
       </c>
       <c r="AA2">
-        <v>-5.28</v>
+        <v>-5.33</v>
       </c>
       <c r="AB2">
-        <v>0.36</v>
+        <v>-0.23</v>
       </c>
       <c r="AC2">
-        <v>70.14</v>
+        <v>45.38</v>
       </c>
       <c r="AD2">
-        <v>76.39</v>
+        <v>64.84999999999999</v>
       </c>
       <c r="AE2">
-        <v>9.300000000000001</v>
+        <v>9.359999999999999</v>
       </c>
       <c r="AF2">
-        <v>-59.52</v>
+        <v>-6.47</v>
       </c>
       <c r="AG2">
-        <v>401.7</v>
+        <v>398.48</v>
       </c>
       <c r="AH2">
-        <v>363.86</v>
+        <v>363.44</v>
       </c>
       <c r="AI2">
-        <v>398.61</v>
+        <v>397.11</v>
       </c>
       <c r="AJ2" t="s">
         <v>48</v>
       </c>
       <c r="AK2">
-        <v>17.47</v>
+        <v>20.87</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1012,37 +1012,37 @@
         <v>45</v>
       </c>
       <c r="C3">
-        <v>43.15</v>
+        <v>43.01</v>
       </c>
       <c r="D3">
-        <v>-3.75</v>
+        <v>-0.32</v>
       </c>
       <c r="E3">
         <v>85.38</v>
       </c>
       <c r="F3">
-        <v>43.15</v>
+        <v>43.01</v>
       </c>
       <c r="G3">
-        <v>-49.46</v>
+        <v>-49.63</v>
       </c>
       <c r="H3">
         <v>0</v>
       </c>
       <c r="I3">
-        <v>-0.87</v>
+        <v>-3.95</v>
       </c>
       <c r="J3">
-        <v>-14.47</v>
+        <v>-14.25</v>
       </c>
       <c r="K3">
-        <v>-24.67</v>
+        <v>-25.08</v>
       </c>
       <c r="L3">
-        <v>-46.16</v>
+        <v>-48.46</v>
       </c>
       <c r="M3">
-        <v>-29.89</v>
+        <v>-29.68</v>
       </c>
       <c r="N3">
         <v>13</v>
@@ -1051,19 +1051,19 @@
         <v>5</v>
       </c>
       <c r="P3">
-        <v>44.58</v>
+        <v>44.23</v>
       </c>
       <c r="Q3">
-        <v>45.9</v>
+        <v>45.56</v>
       </c>
       <c r="R3">
-        <v>50.58</v>
+        <v>50.17</v>
       </c>
       <c r="S3">
-        <v>60.5</v>
+        <v>60.33</v>
       </c>
       <c r="T3">
-        <v>-28.67</v>
+        <v>-28.71</v>
       </c>
       <c r="U3" t="s">
         <v>46</v>
@@ -1078,34 +1078,34 @@
         <v>0</v>
       </c>
       <c r="Y3">
-        <v>31.87</v>
+        <v>31.45</v>
       </c>
       <c r="Z3">
-        <v>-1.93</v>
+        <v>-1.94</v>
       </c>
       <c r="AA3">
-        <v>-2.09</v>
+        <v>-2.06</v>
       </c>
       <c r="AB3">
-        <v>0.16</v>
+        <v>0.13</v>
       </c>
       <c r="AC3">
-        <v>77.62</v>
+        <v>64.25</v>
       </c>
       <c r="AD3">
-        <v>88.84</v>
+        <v>78.39</v>
       </c>
       <c r="AE3">
-        <v>1.52</v>
+        <v>1.68</v>
       </c>
       <c r="AF3">
-        <v>-49.79</v>
+        <v>186</v>
       </c>
       <c r="AG3">
-        <v>50.26</v>
+        <v>49.68</v>
       </c>
       <c r="AH3">
-        <v>41.53</v>
+        <v>41.43</v>
       </c>
       <c r="AI3">
         <v>48.29</v>
@@ -1114,7 +1114,7 @@
         <v>48</v>
       </c>
       <c r="AK3">
-        <v>27.79</v>
+        <v>29.22</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1125,10 +1125,10 @@
         <v>45</v>
       </c>
       <c r="C4">
-        <v>2879</v>
+        <v>2889.1</v>
       </c>
       <c r="D4">
-        <v>-1.4</v>
+        <v>0.35</v>
       </c>
       <c r="E4">
         <v>3380.5</v>
@@ -1137,46 +1137,46 @@
         <v>2531.1</v>
       </c>
       <c r="G4">
-        <v>-14.84</v>
+        <v>-14.54</v>
       </c>
       <c r="H4">
-        <v>13.75</v>
+        <v>14.14</v>
       </c>
       <c r="I4">
-        <v>0.73</v>
+        <v>-0.79</v>
       </c>
       <c r="J4">
-        <v>-9.27</v>
+        <v>-9.970000000000001</v>
       </c>
       <c r="K4">
-        <v>-8.42</v>
+        <v>-9.140000000000001</v>
       </c>
       <c r="L4">
-        <v>3.72</v>
+        <v>2.57</v>
       </c>
       <c r="M4">
-        <v>11.39</v>
+        <v>11.11</v>
       </c>
       <c r="N4">
         <v>50</v>
       </c>
       <c r="O4">
-        <v>54</v>
+        <v>61</v>
       </c>
       <c r="P4">
-        <v>2893.98</v>
+        <v>2889.4</v>
       </c>
       <c r="Q4">
-        <v>3002.54</v>
+        <v>2988.7</v>
       </c>
       <c r="R4">
-        <v>3171.52</v>
+        <v>3162.84</v>
       </c>
       <c r="S4">
-        <v>2981.44</v>
+        <v>2981.74</v>
       </c>
       <c r="T4">
-        <v>-3.44</v>
+        <v>-3.11</v>
       </c>
       <c r="U4" t="s">
         <v>46</v>
@@ -1191,34 +1191,34 @@
         <v>1</v>
       </c>
       <c r="Y4">
-        <v>34.62</v>
+        <v>35.97</v>
       </c>
       <c r="Z4">
-        <v>-88.23999999999999</v>
+        <v>-85.2</v>
       </c>
       <c r="AA4">
-        <v>-84.65000000000001</v>
+        <v>-84.76000000000001</v>
       </c>
       <c r="AB4">
-        <v>-3.59</v>
+        <v>-0.44</v>
       </c>
       <c r="AC4">
-        <v>66.88</v>
+        <v>81.75</v>
       </c>
       <c r="AD4">
-        <v>53.93</v>
+        <v>67.06999999999999</v>
       </c>
       <c r="AE4">
-        <v>63.72</v>
+        <v>62.94</v>
       </c>
       <c r="AF4">
-        <v>-40.46</v>
+        <v>-38.67</v>
       </c>
       <c r="AG4">
-        <v>3253.88</v>
+        <v>3232.51</v>
       </c>
       <c r="AH4">
-        <v>2751.21</v>
+        <v>2744.89</v>
       </c>
       <c r="AI4">
         <v>3061.2</v>
@@ -1227,7 +1227,7 @@
         <v>48</v>
       </c>
       <c r="AK4">
-        <v>62.36</v>
+        <v>59.23</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1238,58 +1238,58 @@
         <v>45</v>
       </c>
       <c r="C5">
-        <v>900.45</v>
+        <v>892.85</v>
       </c>
       <c r="D5">
-        <v>-0.83</v>
+        <v>-0.84</v>
       </c>
       <c r="E5">
         <v>1149.7</v>
       </c>
       <c r="F5">
-        <v>764.25</v>
+        <v>772.8</v>
       </c>
       <c r="G5">
-        <v>-21.68</v>
+        <v>-22.34</v>
       </c>
       <c r="H5">
-        <v>17.82</v>
+        <v>15.53</v>
       </c>
       <c r="I5">
-        <v>2.03</v>
+        <v>-1.04</v>
       </c>
       <c r="J5">
-        <v>-8.16</v>
+        <v>-9.49</v>
       </c>
       <c r="K5">
-        <v>-5</v>
+        <v>-6.15</v>
       </c>
       <c r="L5">
-        <v>18.46</v>
+        <v>16.83</v>
       </c>
       <c r="M5">
-        <v>11.67</v>
+        <v>13.23</v>
       </c>
       <c r="N5">
-        <v>62</v>
+        <v>75</v>
       </c>
       <c r="O5">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="P5">
-        <v>897.41</v>
+        <v>895.53</v>
       </c>
       <c r="Q5">
-        <v>933.08</v>
+        <v>928.66</v>
       </c>
       <c r="R5">
-        <v>987.86</v>
+        <v>984.53</v>
       </c>
       <c r="S5">
-        <v>983.62</v>
+        <v>983.65</v>
       </c>
       <c r="T5">
-        <v>-8.460000000000001</v>
+        <v>-9.23</v>
       </c>
       <c r="U5" t="s">
         <v>46</v>
@@ -1304,34 +1304,34 @@
         <v>1</v>
       </c>
       <c r="Y5">
-        <v>38.64</v>
+        <v>36.99</v>
       </c>
       <c r="Z5">
-        <v>-26.62</v>
+        <v>-26.11</v>
       </c>
       <c r="AA5">
-        <v>-25.75</v>
+        <v>-25.83</v>
       </c>
       <c r="AB5">
-        <v>-0.86</v>
+        <v>-0.28</v>
       </c>
       <c r="AC5">
-        <v>81.06999999999999</v>
+        <v>88.55</v>
       </c>
       <c r="AD5">
-        <v>60.89</v>
+        <v>76.97</v>
       </c>
       <c r="AE5">
-        <v>22.34</v>
+        <v>22.68</v>
       </c>
       <c r="AF5">
-        <v>-51.51</v>
+        <v>-20.59</v>
       </c>
       <c r="AG5">
-        <v>1008.73</v>
+        <v>1002.79</v>
       </c>
       <c r="AH5">
-        <v>857.42</v>
+        <v>854.53</v>
       </c>
       <c r="AI5">
         <v>946.48</v>
@@ -1340,7 +1340,7 @@
         <v>48</v>
       </c>
       <c r="AK5">
-        <v>45.8</v>
+        <v>45.37</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1351,10 +1351,10 @@
         <v>45</v>
       </c>
       <c r="C6">
-        <v>12.28</v>
+        <v>11.64</v>
       </c>
       <c r="D6">
-        <v>-2.46</v>
+        <v>-5.21</v>
       </c>
       <c r="E6">
         <v>15.6</v>
@@ -1363,46 +1363,46 @@
         <v>8.529999999999999</v>
       </c>
       <c r="G6">
-        <v>-21.28</v>
+        <v>-25.38</v>
       </c>
       <c r="H6">
-        <v>43.96</v>
+        <v>36.46</v>
       </c>
       <c r="I6">
-        <v>-3.08</v>
+        <v>-9.06</v>
       </c>
       <c r="J6">
-        <v>-13.64</v>
+        <v>-16.38</v>
       </c>
       <c r="K6">
-        <v>-9.1</v>
+        <v>-13.71</v>
       </c>
       <c r="L6">
-        <v>46.89</v>
+        <v>33.03</v>
       </c>
       <c r="M6">
-        <v>4.19</v>
+        <v>2.48</v>
       </c>
       <c r="N6">
         <v>87</v>
       </c>
       <c r="O6">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="P6">
-        <v>12.57</v>
+        <v>12.34</v>
       </c>
       <c r="Q6">
-        <v>13.2</v>
+        <v>13.09</v>
       </c>
       <c r="R6">
-        <v>13.87</v>
+        <v>13.84</v>
       </c>
       <c r="S6">
-        <v>12.3</v>
+        <v>12.31</v>
       </c>
       <c r="T6">
-        <v>-0.17</v>
+        <v>-5.41</v>
       </c>
       <c r="U6" t="s">
         <v>46</v>
@@ -1417,43 +1417,43 @@
         <v>1</v>
       </c>
       <c r="Y6">
-        <v>34.48</v>
+        <v>28.85</v>
       </c>
       <c r="Z6">
-        <v>-0.45</v>
+        <v>-0.51</v>
       </c>
       <c r="AA6">
-        <v>-0.38</v>
+        <v>-0.41</v>
       </c>
       <c r="AB6">
-        <v>-0.06</v>
+        <v>-0.1</v>
       </c>
       <c r="AC6">
-        <v>31.91</v>
+        <v>24.44</v>
       </c>
       <c r="AD6">
-        <v>32.7</v>
+        <v>31.04</v>
       </c>
       <c r="AE6">
-        <v>0.43</v>
+        <v>0.45</v>
       </c>
       <c r="AF6">
-        <v>-17.97</v>
+        <v>31.24</v>
       </c>
       <c r="AG6">
-        <v>14.55</v>
+        <v>14.58</v>
       </c>
       <c r="AH6">
-        <v>11.85</v>
+        <v>11.61</v>
       </c>
       <c r="AI6">
-        <v>13.73</v>
+        <v>13.35</v>
       </c>
       <c r="AJ6" t="s">
         <v>48</v>
       </c>
       <c r="AK6">
-        <v>47.19</v>
+        <v>51.24</v>
       </c>
     </row>
     <row r="7" spans="1:37">
@@ -1464,10 +1464,10 @@
         <v>45</v>
       </c>
       <c r="C7">
-        <v>12.74</v>
+        <v>11.67</v>
       </c>
       <c r="D7">
-        <v>2.74</v>
+        <v>-8.4</v>
       </c>
       <c r="E7">
         <v>13.92</v>
@@ -1476,46 +1476,46 @@
         <v>4.69</v>
       </c>
       <c r="G7">
-        <v>-8.48</v>
+        <v>-16.16</v>
       </c>
       <c r="H7">
-        <v>171.64</v>
+        <v>148.83</v>
       </c>
       <c r="I7">
-        <v>17.1</v>
+        <v>2.01</v>
       </c>
       <c r="J7">
-        <v>3.24</v>
+        <v>-2.26</v>
       </c>
       <c r="K7">
-        <v>9.539999999999999</v>
+        <v>-1.6</v>
       </c>
       <c r="L7">
-        <v>153.28</v>
+        <v>123.56</v>
       </c>
       <c r="M7">
-        <v>-28.24</v>
+        <v>-29.51</v>
       </c>
       <c r="N7">
         <v>99</v>
       </c>
       <c r="O7">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="P7">
-        <v>11.91</v>
+        <v>11.95</v>
       </c>
       <c r="Q7">
         <v>11.25</v>
       </c>
       <c r="R7">
-        <v>11.51</v>
+        <v>11.49</v>
       </c>
       <c r="S7">
         <v>10.82</v>
       </c>
       <c r="T7">
-        <v>17.69</v>
+        <v>7.89</v>
       </c>
       <c r="U7" t="s">
         <v>46</v>
@@ -1530,28 +1530,28 @@
         <v>2</v>
       </c>
       <c r="Y7">
-        <v>65.19</v>
+        <v>52.19</v>
       </c>
       <c r="Z7">
         <v>0.12</v>
       </c>
       <c r="AA7">
-        <v>-0.08</v>
+        <v>-0.04</v>
       </c>
       <c r="AB7">
-        <v>0.2</v>
+        <v>0.16</v>
       </c>
       <c r="AC7">
-        <v>94.48</v>
+        <v>86.72</v>
       </c>
       <c r="AD7">
-        <v>94.48</v>
+        <v>91.89</v>
       </c>
       <c r="AE7">
-        <v>0.6899999999999999</v>
+        <v>0.74</v>
       </c>
       <c r="AF7">
-        <v>183.03</v>
+        <v>18.7</v>
       </c>
       <c r="AG7">
         <v>12.44</v>
@@ -1566,7 +1566,7 @@
         <v>49</v>
       </c>
       <c r="AK7">
-        <v>35.15</v>
+        <v>32.55</v>
       </c>
     </row>
     <row r="8" spans="1:37">
@@ -1577,10 +1577,10 @@
         <v>45</v>
       </c>
       <c r="C8">
-        <v>3951.5</v>
+        <v>3907.2</v>
       </c>
       <c r="D8">
-        <v>-0.82</v>
+        <v>-1.12</v>
       </c>
       <c r="E8">
         <v>5809.5</v>
@@ -1589,46 +1589,46 @@
         <v>3892.3</v>
       </c>
       <c r="G8">
-        <v>-31.98</v>
+        <v>-32.74</v>
       </c>
       <c r="H8">
-        <v>1.52</v>
+        <v>0.38</v>
       </c>
       <c r="I8">
-        <v>0.42</v>
+        <v>-1.07</v>
       </c>
       <c r="J8">
-        <v>-3.2</v>
+        <v>-3.93</v>
       </c>
       <c r="K8">
-        <v>-9.550000000000001</v>
+        <v>-11.95</v>
       </c>
       <c r="L8">
-        <v>-24.81</v>
+        <v>-25.9</v>
       </c>
       <c r="M8">
-        <v>15.61</v>
+        <v>16.09</v>
       </c>
       <c r="N8">
         <v>25</v>
       </c>
       <c r="O8">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="P8">
-        <v>3968.86</v>
+        <v>3960.38</v>
       </c>
       <c r="Q8">
-        <v>3988.34</v>
+        <v>3982.35</v>
       </c>
       <c r="R8">
-        <v>4185.06</v>
+        <v>4175.79</v>
       </c>
       <c r="S8">
-        <v>4462.85</v>
+        <v>4456.27</v>
       </c>
       <c r="T8">
-        <v>-11.46</v>
+        <v>-12.32</v>
       </c>
       <c r="U8" t="s">
         <v>46</v>
@@ -1643,43 +1643,43 @@
         <v>0</v>
       </c>
       <c r="Y8">
-        <v>41.01</v>
+        <v>37.74</v>
       </c>
       <c r="Z8">
-        <v>-58.26</v>
+        <v>-59.81</v>
       </c>
       <c r="AA8">
-        <v>-68.48999999999999</v>
+        <v>-66.76000000000001</v>
       </c>
       <c r="AB8">
-        <v>10.23</v>
+        <v>6.94</v>
       </c>
       <c r="AC8">
-        <v>72.94</v>
+        <v>65</v>
       </c>
       <c r="AD8">
-        <v>73.62</v>
+        <v>71.86</v>
       </c>
       <c r="AE8">
-        <v>96.31</v>
+        <v>94.70999999999999</v>
       </c>
       <c r="AF8">
-        <v>-77.20999999999999</v>
+        <v>80.8</v>
       </c>
       <c r="AG8">
-        <v>4082.25</v>
+        <v>4081.03</v>
       </c>
       <c r="AH8">
-        <v>3894.43</v>
+        <v>3883.66</v>
       </c>
       <c r="AI8">
-        <v>4246.97</v>
+        <v>4221.07</v>
       </c>
       <c r="AJ8" t="s">
         <v>48</v>
       </c>
       <c r="AK8">
-        <v>24.84</v>
+        <v>24.2</v>
       </c>
     </row>
     <row r="9" spans="1:37">
@@ -1690,10 +1690,10 @@
         <v>45</v>
       </c>
       <c r="C9">
-        <v>10650</v>
+        <v>10849</v>
       </c>
       <c r="D9">
-        <v>-2.36</v>
+        <v>1.87</v>
       </c>
       <c r="E9">
         <v>13052</v>
@@ -1702,46 +1702,46 @@
         <v>10362</v>
       </c>
       <c r="G9">
-        <v>-18.4</v>
+        <v>-16.88</v>
       </c>
       <c r="H9">
-        <v>2.78</v>
+        <v>4.7</v>
       </c>
       <c r="I9">
-        <v>1.24</v>
+        <v>0.92</v>
       </c>
       <c r="J9">
-        <v>-1.06</v>
+        <v>-1.5</v>
       </c>
       <c r="K9">
-        <v>-10.53</v>
+        <v>-10.29</v>
       </c>
       <c r="L9">
-        <v>-11.76</v>
+        <v>-11.88</v>
       </c>
       <c r="M9">
-        <v>8.720000000000001</v>
+        <v>9.25</v>
       </c>
       <c r="N9">
         <v>38</v>
       </c>
       <c r="O9">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="P9">
-        <v>10792.8</v>
+        <v>10812.6</v>
       </c>
       <c r="Q9">
-        <v>10841.45</v>
+        <v>10828.9</v>
       </c>
       <c r="R9">
-        <v>11178.24</v>
+        <v>11153.12</v>
       </c>
       <c r="S9">
-        <v>11657.24</v>
+        <v>11652.56</v>
       </c>
       <c r="T9">
-        <v>-8.640000000000001</v>
+        <v>-6.9</v>
       </c>
       <c r="U9" t="s">
         <v>46</v>
@@ -1756,34 +1756,34 @@
         <v>0</v>
       </c>
       <c r="Y9">
-        <v>43.06</v>
+        <v>48.74</v>
       </c>
       <c r="Z9">
-        <v>-119.44</v>
+        <v>-104.31</v>
       </c>
       <c r="AA9">
-        <v>-145.96</v>
+        <v>-137.63</v>
       </c>
       <c r="AB9">
-        <v>26.51</v>
+        <v>33.32</v>
       </c>
       <c r="AC9">
-        <v>86.63</v>
+        <v>84.76000000000001</v>
       </c>
       <c r="AD9">
-        <v>90.95999999999999</v>
+        <v>89.25</v>
       </c>
       <c r="AE9">
-        <v>251.87</v>
+        <v>255.95</v>
       </c>
       <c r="AF9">
-        <v>113.02</v>
+        <v>29.23</v>
       </c>
       <c r="AG9">
-        <v>11250.94</v>
+        <v>11220</v>
       </c>
       <c r="AH9">
-        <v>10431.96</v>
+        <v>10437.8</v>
       </c>
       <c r="AI9">
         <v>11169.72</v>
@@ -1792,7 +1792,7 @@
         <v>48</v>
       </c>
       <c r="AK9">
-        <v>31.95</v>
+        <v>33.27</v>
       </c>
     </row>
   </sheetData>
@@ -1990,13 +1990,13 @@
         <v>9</v>
       </c>
       <c r="C7" s="5">
-        <v>-0.5</v>
+        <v>-4.35</v>
       </c>
       <c r="D7" s="5">
-        <v>-4.35</v>
+        <v>-10.5</v>
       </c>
       <c r="E7" s="6">
-        <v>-3.85</v>
+        <v>-6.15</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -2007,13 +2007,13 @@
         <v>9</v>
       </c>
       <c r="C8" s="5">
-        <v>-9.869999999999999</v>
+        <v>-14.47</v>
       </c>
       <c r="D8" s="5">
-        <v>-14.47</v>
-      </c>
-      <c r="E8" s="6">
-        <v>-4.6</v>
+        <v>-14.25</v>
+      </c>
+      <c r="E8" s="7">
+        <v>0.22</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -2024,13 +2024,13 @@
         <v>9</v>
       </c>
       <c r="C9" s="5">
-        <v>-8.380000000000001</v>
+        <v>-9.27</v>
       </c>
       <c r="D9" s="5">
-        <v>-9.27</v>
+        <v>-9.970000000000001</v>
       </c>
       <c r="E9" s="6">
-        <v>-0.89</v>
+        <v>-0.7</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -2041,13 +2041,13 @@
         <v>9</v>
       </c>
       <c r="C10" s="5">
-        <v>-6.65</v>
+        <v>-8.16</v>
       </c>
       <c r="D10" s="5">
-        <v>-8.16</v>
+        <v>-9.49</v>
       </c>
       <c r="E10" s="6">
-        <v>-1.51</v>
+        <v>-1.33</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -2058,13 +2058,13 @@
         <v>9</v>
       </c>
       <c r="C11" s="5">
-        <v>-11.71</v>
+        <v>-13.64</v>
       </c>
       <c r="D11" s="5">
-        <v>-13.64</v>
+        <v>-16.38</v>
       </c>
       <c r="E11" s="6">
-        <v>-1.93</v>
+        <v>-2.74</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -2075,13 +2075,13 @@
         <v>9</v>
       </c>
       <c r="C12" s="5">
-        <v>0.32</v>
+        <v>3.24</v>
       </c>
       <c r="D12" s="5">
-        <v>3.24</v>
-      </c>
-      <c r="E12" s="7">
-        <v>2.92</v>
+        <v>-2.26</v>
+      </c>
+      <c r="E12" s="6">
+        <v>-5.5</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -2092,13 +2092,13 @@
         <v>9</v>
       </c>
       <c r="C13" s="5">
-        <v>-1.68</v>
+        <v>-3.2</v>
       </c>
       <c r="D13" s="5">
-        <v>-3.2</v>
+        <v>-3.93</v>
       </c>
       <c r="E13" s="6">
-        <v>-1.52</v>
+        <v>-0.73</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -2109,13 +2109,13 @@
         <v>9</v>
       </c>
       <c r="C14" s="5">
-        <v>1.93</v>
+        <v>-1.06</v>
       </c>
       <c r="D14" s="5">
-        <v>-1.06</v>
+        <v>-1.5</v>
       </c>
       <c r="E14" s="6">
-        <v>-2.99</v>
+        <v>-0.44</v>
       </c>
     </row>
     <row r="15" spans="1:6">
@@ -2126,13 +2126,13 @@
         <v>8</v>
       </c>
       <c r="C15" s="5">
-        <v>-0.34</v>
+        <v>-1.89</v>
       </c>
       <c r="D15" s="5">
-        <v>-1.89</v>
+        <v>-4.59</v>
       </c>
       <c r="E15" s="6">
-        <v>-1.55</v>
+        <v>-2.7</v>
       </c>
     </row>
     <row r="16" spans="1:6">
@@ -2143,13 +2143,13 @@
         <v>8</v>
       </c>
       <c r="C16" s="5">
-        <v>2.7</v>
+        <v>-0.87</v>
       </c>
       <c r="D16" s="5">
-        <v>-0.87</v>
+        <v>-3.95</v>
       </c>
       <c r="E16" s="6">
-        <v>-3.57</v>
+        <v>-3.08</v>
       </c>
     </row>
     <row r="17" spans="1:5">
@@ -2160,13 +2160,13 @@
         <v>8</v>
       </c>
       <c r="C17" s="5">
-        <v>1.04</v>
+        <v>0.73</v>
       </c>
       <c r="D17" s="5">
-        <v>0.73</v>
+        <v>-0.79</v>
       </c>
       <c r="E17" s="6">
-        <v>-0.31</v>
+        <v>-1.52</v>
       </c>
     </row>
     <row r="18" spans="1:5">
@@ -2177,13 +2177,13 @@
         <v>8</v>
       </c>
       <c r="C18" s="5">
-        <v>0.85</v>
+        <v>2.03</v>
       </c>
       <c r="D18" s="5">
-        <v>2.03</v>
-      </c>
-      <c r="E18" s="7">
-        <v>1.18</v>
+        <v>-1.04</v>
+      </c>
+      <c r="E18" s="6">
+        <v>-3.07</v>
       </c>
     </row>
     <row r="19" spans="1:5">
@@ -2194,13 +2194,13 @@
         <v>8</v>
       </c>
       <c r="C19" s="5">
-        <v>-3.15</v>
+        <v>-3.08</v>
       </c>
       <c r="D19" s="5">
-        <v>-3.08</v>
-      </c>
-      <c r="E19" s="7">
-        <v>0.07000000000000001</v>
+        <v>-9.06</v>
+      </c>
+      <c r="E19" s="6">
+        <v>-5.98</v>
       </c>
     </row>
     <row r="20" spans="1:5">
@@ -2211,13 +2211,13 @@
         <v>8</v>
       </c>
       <c r="C20" s="5">
-        <v>12.12</v>
+        <v>17.1</v>
       </c>
       <c r="D20" s="5">
-        <v>17.1</v>
-      </c>
-      <c r="E20" s="7">
-        <v>4.98</v>
+        <v>2.01</v>
+      </c>
+      <c r="E20" s="6">
+        <v>-15.09</v>
       </c>
     </row>
     <row r="21" spans="1:5">
@@ -2228,13 +2228,13 @@
         <v>8</v>
       </c>
       <c r="C21" s="5">
-        <v>1.18</v>
+        <v>0.42</v>
       </c>
       <c r="D21" s="5">
-        <v>0.42</v>
+        <v>-1.07</v>
       </c>
       <c r="E21" s="6">
-        <v>-0.76</v>
+        <v>-1.49</v>
       </c>
     </row>
     <row r="22" spans="1:5">
@@ -2245,13 +2245,13 @@
         <v>8</v>
       </c>
       <c r="C22" s="5">
-        <v>2.17</v>
+        <v>1.24</v>
       </c>
       <c r="D22" s="5">
-        <v>1.24</v>
+        <v>0.92</v>
       </c>
       <c r="E22" s="6">
-        <v>-0.93</v>
+        <v>-0.32</v>
       </c>
     </row>
     <row r="23" spans="1:5">
@@ -2262,13 +2262,13 @@
         <v>11</v>
       </c>
       <c r="C23" s="5">
-        <v>26.87</v>
+        <v>25.18</v>
       </c>
       <c r="D23" s="5">
-        <v>25.18</v>
+        <v>20.92</v>
       </c>
       <c r="E23" s="6">
-        <v>-1.69</v>
+        <v>-4.26</v>
       </c>
     </row>
     <row r="24" spans="1:5">
@@ -2279,13 +2279,13 @@
         <v>11</v>
       </c>
       <c r="C24" s="5">
-        <v>-45.31</v>
+        <v>-46.16</v>
       </c>
       <c r="D24" s="5">
-        <v>-46.16</v>
+        <v>-48.46</v>
       </c>
       <c r="E24" s="6">
-        <v>-0.85</v>
+        <v>-2.3</v>
       </c>
     </row>
     <row r="25" spans="1:5">
@@ -2296,13 +2296,13 @@
         <v>11</v>
       </c>
       <c r="C25" s="5">
-        <v>4.36</v>
+        <v>3.72</v>
       </c>
       <c r="D25" s="5">
-        <v>3.72</v>
+        <v>2.57</v>
       </c>
       <c r="E25" s="6">
-        <v>-0.64</v>
+        <v>-1.15</v>
       </c>
     </row>
     <row r="26" spans="1:5">
@@ -2313,13 +2313,13 @@
         <v>11</v>
       </c>
       <c r="C26" s="5">
-        <v>17.89</v>
+        <v>18.46</v>
       </c>
       <c r="D26" s="5">
-        <v>18.46</v>
-      </c>
-      <c r="E26" s="7">
-        <v>0.57</v>
+        <v>16.83</v>
+      </c>
+      <c r="E26" s="6">
+        <v>-1.63</v>
       </c>
     </row>
     <row r="27" spans="1:5">
@@ -2330,13 +2330,13 @@
         <v>11</v>
       </c>
       <c r="C27" s="5">
-        <v>44.22</v>
+        <v>46.89</v>
       </c>
       <c r="D27" s="5">
-        <v>46.89</v>
-      </c>
-      <c r="E27" s="7">
-        <v>2.67</v>
+        <v>33.03</v>
+      </c>
+      <c r="E27" s="6">
+        <v>-13.86</v>
       </c>
     </row>
     <row r="28" spans="1:5">
@@ -2347,13 +2347,13 @@
         <v>11</v>
       </c>
       <c r="C28" s="5">
-        <v>143.61</v>
+        <v>153.28</v>
       </c>
       <c r="D28" s="5">
-        <v>153.28</v>
-      </c>
-      <c r="E28" s="7">
-        <v>9.67</v>
+        <v>123.56</v>
+      </c>
+      <c r="E28" s="6">
+        <v>-29.72</v>
       </c>
     </row>
     <row r="29" spans="1:5">
@@ -2364,13 +2364,13 @@
         <v>11</v>
       </c>
       <c r="C29" s="5">
-        <v>-24.59</v>
+        <v>-24.81</v>
       </c>
       <c r="D29" s="5">
-        <v>-24.81</v>
+        <v>-25.9</v>
       </c>
       <c r="E29" s="6">
-        <v>-0.22</v>
+        <v>-1.09</v>
       </c>
     </row>
     <row r="30" spans="1:5">
@@ -2381,13 +2381,13 @@
         <v>11</v>
       </c>
       <c r="C30" s="5">
-        <v>-10.39</v>
+        <v>-11.76</v>
       </c>
       <c r="D30" s="5">
-        <v>-11.76</v>
+        <v>-11.88</v>
       </c>
       <c r="E30" s="6">
-        <v>-1.37</v>
+        <v>-0.12</v>
       </c>
     </row>
     <row r="31" spans="1:5">
@@ -2398,13 +2398,13 @@
         <v>10</v>
       </c>
       <c r="C31" s="5">
-        <v>-5.52</v>
+        <v>-7</v>
       </c>
       <c r="D31" s="5">
-        <v>-7</v>
+        <v>-10.28</v>
       </c>
       <c r="E31" s="6">
-        <v>-1.48</v>
+        <v>-3.28</v>
       </c>
     </row>
     <row r="32" spans="1:5">
@@ -2415,13 +2415,13 @@
         <v>10</v>
       </c>
       <c r="C32" s="5">
-        <v>-22.51</v>
+        <v>-24.67</v>
       </c>
       <c r="D32" s="5">
-        <v>-24.67</v>
+        <v>-25.08</v>
       </c>
       <c r="E32" s="6">
-        <v>-2.16</v>
+        <v>-0.41</v>
       </c>
     </row>
     <row r="33" spans="1:5">
@@ -2432,13 +2432,13 @@
         <v>10</v>
       </c>
       <c r="C33" s="5">
-        <v>-6.1</v>
+        <v>-8.42</v>
       </c>
       <c r="D33" s="5">
-        <v>-8.42</v>
+        <v>-9.140000000000001</v>
       </c>
       <c r="E33" s="6">
-        <v>-2.32</v>
+        <v>-0.72</v>
       </c>
     </row>
     <row r="34" spans="1:5">
@@ -2449,13 +2449,13 @@
         <v>10</v>
       </c>
       <c r="C34" s="5">
-        <v>-3.83</v>
+        <v>-5</v>
       </c>
       <c r="D34" s="5">
-        <v>-5</v>
+        <v>-6.15</v>
       </c>
       <c r="E34" s="6">
-        <v>-1.17</v>
+        <v>-1.15</v>
       </c>
     </row>
     <row r="35" spans="1:5">
@@ -2466,13 +2466,13 @@
         <v>10</v>
       </c>
       <c r="C35" s="5">
-        <v>-8.369999999999999</v>
+        <v>-9.1</v>
       </c>
       <c r="D35" s="5">
-        <v>-9.1</v>
+        <v>-13.71</v>
       </c>
       <c r="E35" s="6">
-        <v>-0.73</v>
+        <v>-4.61</v>
       </c>
     </row>
     <row r="36" spans="1:5">
@@ -2483,13 +2483,13 @@
         <v>10</v>
       </c>
       <c r="C36" s="5">
-        <v>8.68</v>
+        <v>9.539999999999999</v>
       </c>
       <c r="D36" s="5">
-        <v>9.539999999999999</v>
-      </c>
-      <c r="E36" s="7">
-        <v>0.86</v>
+        <v>-1.6</v>
+      </c>
+      <c r="E36" s="6">
+        <v>-11.14</v>
       </c>
     </row>
     <row r="37" spans="1:5">
@@ -2500,13 +2500,13 @@
         <v>10</v>
       </c>
       <c r="C37" s="5">
-        <v>-9.15</v>
+        <v>-9.550000000000001</v>
       </c>
       <c r="D37" s="5">
-        <v>-9.550000000000001</v>
+        <v>-11.95</v>
       </c>
       <c r="E37" s="6">
-        <v>-0.4</v>
+        <v>-2.4</v>
       </c>
     </row>
     <row r="38" spans="1:5">
@@ -2517,13 +2517,13 @@
         <v>10</v>
       </c>
       <c r="C38" s="5">
-        <v>-6.99</v>
+        <v>-10.53</v>
       </c>
       <c r="D38" s="5">
-        <v>-10.53</v>
-      </c>
-      <c r="E38" s="6">
-        <v>-3.54</v>
+        <v>-10.29</v>
+      </c>
+      <c r="E38" s="7">
+        <v>0.24</v>
       </c>
     </row>
     <row r="39" spans="1:5">
@@ -2534,13 +2534,13 @@
         <v>6</v>
       </c>
       <c r="C39" s="5">
-        <v>-10.67</v>
+        <v>-12.16</v>
       </c>
       <c r="D39" s="5">
-        <v>-12.16</v>
+        <v>-13.59</v>
       </c>
       <c r="E39" s="6">
-        <v>-1.49</v>
+        <v>-1.43</v>
       </c>
     </row>
     <row r="40" spans="1:5">
@@ -2551,13 +2551,13 @@
         <v>6</v>
       </c>
       <c r="C40" s="5">
-        <v>-47.49</v>
+        <v>-49.46</v>
       </c>
       <c r="D40" s="5">
-        <v>-49.46</v>
+        <v>-49.63</v>
       </c>
       <c r="E40" s="6">
-        <v>-1.97</v>
+        <v>-0.17</v>
       </c>
     </row>
     <row r="41" spans="1:5">
@@ -2568,13 +2568,13 @@
         <v>6</v>
       </c>
       <c r="C41" s="5">
-        <v>-13.62</v>
+        <v>-14.84</v>
       </c>
       <c r="D41" s="5">
-        <v>-14.84</v>
-      </c>
-      <c r="E41" s="6">
-        <v>-1.22</v>
+        <v>-14.54</v>
+      </c>
+      <c r="E41" s="7">
+        <v>0.3</v>
       </c>
     </row>
     <row r="42" spans="1:5">
@@ -2585,10 +2585,10 @@
         <v>6</v>
       </c>
       <c r="C42" s="5">
-        <v>-21.02</v>
+        <v>-21.68</v>
       </c>
       <c r="D42" s="5">
-        <v>-21.68</v>
+        <v>-22.34</v>
       </c>
       <c r="E42" s="6">
         <v>-0.66</v>
@@ -2602,13 +2602,13 @@
         <v>6</v>
       </c>
       <c r="C43" s="5">
-        <v>-19.29</v>
+        <v>-21.28</v>
       </c>
       <c r="D43" s="5">
-        <v>-21.28</v>
+        <v>-25.38</v>
       </c>
       <c r="E43" s="6">
-        <v>-1.99</v>
+        <v>-4.1</v>
       </c>
     </row>
     <row r="44" spans="1:5">
@@ -2619,13 +2619,13 @@
         <v>6</v>
       </c>
       <c r="C44" s="5">
-        <v>-10.92</v>
+        <v>-8.48</v>
       </c>
       <c r="D44" s="5">
-        <v>-8.48</v>
-      </c>
-      <c r="E44" s="7">
-        <v>2.44</v>
+        <v>-16.16</v>
+      </c>
+      <c r="E44" s="6">
+        <v>-7.68</v>
       </c>
     </row>
     <row r="45" spans="1:5">
@@ -2636,13 +2636,13 @@
         <v>6</v>
       </c>
       <c r="C45" s="5">
-        <v>-31.42</v>
+        <v>-31.98</v>
       </c>
       <c r="D45" s="5">
-        <v>-31.98</v>
+        <v>-32.74</v>
       </c>
       <c r="E45" s="6">
-        <v>-0.5600000000000001</v>
+        <v>-0.76</v>
       </c>
     </row>
     <row r="46" spans="1:5">
@@ -2653,13 +2653,13 @@
         <v>6</v>
       </c>
       <c r="C46" s="5">
-        <v>-16.43</v>
+        <v>-18.4</v>
       </c>
       <c r="D46" s="5">
-        <v>-18.4</v>
-      </c>
-      <c r="E46" s="6">
-        <v>-1.97</v>
+        <v>-16.88</v>
+      </c>
+      <c r="E46" s="7">
+        <v>1.52</v>
       </c>
     </row>
     <row r="47" spans="1:5">
@@ -2670,13 +2670,13 @@
         <v>2</v>
       </c>
       <c r="C47" s="5">
-        <v>379.4</v>
+        <v>373.05</v>
       </c>
       <c r="D47" s="5">
-        <v>373.05</v>
+        <v>367</v>
       </c>
       <c r="E47" s="6">
-        <v>-6.35</v>
+        <v>-6.05</v>
       </c>
     </row>
     <row r="48" spans="1:5">
@@ -2687,13 +2687,13 @@
         <v>2</v>
       </c>
       <c r="C48" s="5">
-        <v>44.83</v>
+        <v>43.15</v>
       </c>
       <c r="D48" s="5">
-        <v>43.15</v>
+        <v>43.01</v>
       </c>
       <c r="E48" s="6">
-        <v>-1.68</v>
+        <v>-0.14</v>
       </c>
     </row>
     <row r="49" spans="1:5">
@@ -2704,13 +2704,13 @@
         <v>2</v>
       </c>
       <c r="C49" s="5">
-        <v>2920</v>
+        <v>2879</v>
       </c>
       <c r="D49" s="5">
-        <v>2879</v>
-      </c>
-      <c r="E49" s="6">
-        <v>-41</v>
+        <v>2889.1</v>
+      </c>
+      <c r="E49" s="7">
+        <v>10.1</v>
       </c>
     </row>
     <row r="50" spans="1:5">
@@ -2721,13 +2721,13 @@
         <v>2</v>
       </c>
       <c r="C50" s="5">
-        <v>908</v>
+        <v>900.45</v>
       </c>
       <c r="D50" s="5">
-        <v>900.45</v>
+        <v>892.85</v>
       </c>
       <c r="E50" s="6">
-        <v>-7.55</v>
+        <v>-7.6</v>
       </c>
     </row>
     <row r="51" spans="1:5">
@@ -2738,13 +2738,13 @@
         <v>2</v>
       </c>
       <c r="C51" s="5">
-        <v>12.59</v>
+        <v>12.28</v>
       </c>
       <c r="D51" s="5">
-        <v>12.28</v>
+        <v>11.64</v>
       </c>
       <c r="E51" s="6">
-        <v>-0.31</v>
+        <v>-0.64</v>
       </c>
     </row>
     <row r="52" spans="1:5">
@@ -2755,13 +2755,13 @@
         <v>2</v>
       </c>
       <c r="C52" s="5">
-        <v>12.4</v>
+        <v>12.74</v>
       </c>
       <c r="D52" s="5">
-        <v>12.74</v>
-      </c>
-      <c r="E52" s="7">
-        <v>0.34</v>
+        <v>11.67</v>
+      </c>
+      <c r="E52" s="6">
+        <v>-1.07</v>
       </c>
     </row>
     <row r="53" spans="1:5">
@@ -2772,13 +2772,13 @@
         <v>2</v>
       </c>
       <c r="C53" s="5">
-        <v>3984.2</v>
+        <v>3951.5</v>
       </c>
       <c r="D53" s="5">
-        <v>3951.5</v>
+        <v>3907.2</v>
       </c>
       <c r="E53" s="6">
-        <v>-32.7</v>
+        <v>-44.3</v>
       </c>
     </row>
     <row r="54" spans="1:5">
@@ -2789,13 +2789,13 @@
         <v>2</v>
       </c>
       <c r="C54" s="5">
-        <v>10907</v>
+        <v>10650</v>
       </c>
       <c r="D54" s="5">
-        <v>10650</v>
-      </c>
-      <c r="E54" s="6">
-        <v>-257</v>
+        <v>10849</v>
+      </c>
+      <c r="E54" s="7">
+        <v>199</v>
       </c>
     </row>
     <row r="55" spans="1:5">
@@ -2806,30 +2806,30 @@
         <v>13</v>
       </c>
       <c r="C55" s="5">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D55" s="5">
-        <v>75</v>
-      </c>
-      <c r="E55" s="7">
-        <v>1</v>
+        <v>62</v>
+      </c>
+      <c r="E55" s="6">
+        <v>-13</v>
       </c>
     </row>
     <row r="56" spans="1:5">
       <c r="A56" s="3" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="B56" s="3" t="s">
         <v>13</v>
       </c>
       <c r="C56" s="5">
-        <v>26</v>
+        <v>62</v>
       </c>
       <c r="D56" s="5">
-        <v>25</v>
-      </c>
-      <c r="E56" s="6">
-        <v>-1</v>
+        <v>75</v>
+      </c>
+      <c r="E56" s="7">
+        <v>13</v>
       </c>
     </row>
     <row r="57" spans="1:5">
@@ -2840,13 +2840,13 @@
         <v>24</v>
       </c>
       <c r="C57" s="5">
-        <v>45.16</v>
+        <v>41.2</v>
       </c>
       <c r="D57" s="5">
-        <v>41.2</v>
+        <v>37.79</v>
       </c>
       <c r="E57" s="6">
-        <v>-3.96</v>
+        <v>-3.41</v>
       </c>
     </row>
     <row r="58" spans="1:5">
@@ -2857,13 +2857,13 @@
         <v>24</v>
       </c>
       <c r="C58" s="5">
-        <v>37.44</v>
+        <v>31.87</v>
       </c>
       <c r="D58" s="5">
-        <v>31.87</v>
+        <v>31.45</v>
       </c>
       <c r="E58" s="6">
-        <v>-5.57</v>
+        <v>-0.42</v>
       </c>
     </row>
     <row r="59" spans="1:5">
@@ -2874,13 +2874,13 @@
         <v>24</v>
       </c>
       <c r="C59" s="5">
-        <v>37.62</v>
+        <v>34.62</v>
       </c>
       <c r="D59" s="5">
-        <v>34.62</v>
-      </c>
-      <c r="E59" s="6">
-        <v>-3</v>
+        <v>35.97</v>
+      </c>
+      <c r="E59" s="7">
+        <v>1.35</v>
       </c>
     </row>
     <row r="60" spans="1:5">
@@ -2891,10 +2891,10 @@
         <v>24</v>
       </c>
       <c r="C60" s="5">
-        <v>40.29</v>
+        <v>38.64</v>
       </c>
       <c r="D60" s="5">
-        <v>38.64</v>
+        <v>36.99</v>
       </c>
       <c r="E60" s="6">
         <v>-1.65</v>
@@ -2908,13 +2908,13 @@
         <v>24</v>
       </c>
       <c r="C61" s="5">
-        <v>37.79</v>
+        <v>34.48</v>
       </c>
       <c r="D61" s="5">
-        <v>34.48</v>
+        <v>28.85</v>
       </c>
       <c r="E61" s="6">
-        <v>-3.31</v>
+        <v>-5.63</v>
       </c>
     </row>
     <row r="62" spans="1:5">
@@ -2925,13 +2925,13 @@
         <v>24</v>
       </c>
       <c r="C62" s="5">
-        <v>62.43</v>
+        <v>65.19</v>
       </c>
       <c r="D62" s="5">
-        <v>65.19</v>
-      </c>
-      <c r="E62" s="7">
-        <v>2.76</v>
+        <v>52.19</v>
+      </c>
+      <c r="E62" s="6">
+        <v>-13</v>
       </c>
     </row>
     <row r="63" spans="1:5">
@@ -2942,13 +2942,13 @@
         <v>24</v>
       </c>
       <c r="C63" s="5">
-        <v>43.59</v>
+        <v>41.01</v>
       </c>
       <c r="D63" s="5">
-        <v>41.01</v>
+        <v>37.74</v>
       </c>
       <c r="E63" s="6">
-        <v>-2.58</v>
+        <v>-3.27</v>
       </c>
     </row>
     <row r="64" spans="1:5">
@@ -2959,13 +2959,13 @@
         <v>24</v>
       </c>
       <c r="C64" s="5">
-        <v>49.66</v>
+        <v>43.06</v>
       </c>
       <c r="D64" s="5">
-        <v>43.06</v>
-      </c>
-      <c r="E64" s="6">
-        <v>-6.6</v>
+        <v>48.74</v>
+      </c>
+      <c r="E64" s="7">
+        <v>5.68</v>
       </c>
     </row>
     <row r="65" spans="1:5">
@@ -2976,13 +2976,13 @@
         <v>31</v>
       </c>
       <c r="C65" s="5">
-        <v>-29.02</v>
+        <v>-59.52</v>
       </c>
       <c r="D65" s="5">
-        <v>-59.52</v>
-      </c>
-      <c r="E65" s="6">
-        <v>-30.5</v>
+        <v>-6.47</v>
+      </c>
+      <c r="E65" s="7">
+        <v>53.05</v>
       </c>
     </row>
     <row r="66" spans="1:5">
@@ -2993,13 +2993,13 @@
         <v>31</v>
       </c>
       <c r="C66" s="5">
-        <v>-64.12</v>
+        <v>-49.79</v>
       </c>
       <c r="D66" s="5">
-        <v>-49.79</v>
+        <v>186</v>
       </c>
       <c r="E66" s="7">
-        <v>14.33</v>
+        <v>235.79</v>
       </c>
     </row>
     <row r="67" spans="1:5">
@@ -3010,13 +3010,13 @@
         <v>31</v>
       </c>
       <c r="C67" s="5">
-        <v>-2</v>
+        <v>-40.46</v>
       </c>
       <c r="D67" s="5">
-        <v>-40.46</v>
-      </c>
-      <c r="E67" s="6">
-        <v>-38.46</v>
+        <v>-38.67</v>
+      </c>
+      <c r="E67" s="7">
+        <v>1.79</v>
       </c>
     </row>
     <row r="68" spans="1:5">
@@ -3027,13 +3027,13 @@
         <v>31</v>
       </c>
       <c r="C68" s="5">
-        <v>-17.83</v>
+        <v>-51.51</v>
       </c>
       <c r="D68" s="5">
-        <v>-51.51</v>
-      </c>
-      <c r="E68" s="6">
-        <v>-33.68</v>
+        <v>-20.59</v>
+      </c>
+      <c r="E68" s="7">
+        <v>30.92</v>
       </c>
     </row>
     <row r="69" spans="1:5">
@@ -3044,13 +3044,13 @@
         <v>31</v>
       </c>
       <c r="C69" s="5">
-        <v>-29.65</v>
+        <v>-17.97</v>
       </c>
       <c r="D69" s="5">
-        <v>-17.97</v>
+        <v>31.24</v>
       </c>
       <c r="E69" s="7">
-        <v>11.68</v>
+        <v>49.21</v>
       </c>
     </row>
     <row r="70" spans="1:5">
@@ -3061,13 +3061,13 @@
         <v>31</v>
       </c>
       <c r="C70" s="5">
-        <v>731.73</v>
+        <v>183.03</v>
       </c>
       <c r="D70" s="5">
-        <v>183.03</v>
+        <v>18.7</v>
       </c>
       <c r="E70" s="6">
-        <v>-548.7</v>
+        <v>-164.33</v>
       </c>
     </row>
     <row r="71" spans="1:5">
@@ -3078,13 +3078,13 @@
         <v>31</v>
       </c>
       <c r="C71" s="5">
-        <v>-46.43</v>
+        <v>-77.20999999999999</v>
       </c>
       <c r="D71" s="5">
-        <v>-77.20999999999999</v>
-      </c>
-      <c r="E71" s="6">
-        <v>-30.78</v>
+        <v>80.8</v>
+      </c>
+      <c r="E71" s="7">
+        <v>158.01</v>
       </c>
     </row>
     <row r="72" spans="1:5">
@@ -3095,13 +3095,13 @@
         <v>31</v>
       </c>
       <c r="C72" s="5">
-        <v>-36.91</v>
+        <v>113.02</v>
       </c>
       <c r="D72" s="5">
-        <v>113.02</v>
-      </c>
-      <c r="E72" s="7">
-        <v>149.93</v>
+        <v>29.23</v>
+      </c>
+      <c r="E72" s="6">
+        <v>-83.79000000000001</v>
       </c>
     </row>
   </sheetData>
@@ -3166,16 +3166,16 @@
         <v>8</v>
       </c>
       <c r="D2" s="10">
-        <v>41.3</v>
+        <v>38.7</v>
       </c>
       <c r="E2" s="10">
         <v>25</v>
       </c>
       <c r="F2" s="10">
-        <v>-6.4</v>
+        <v>-8.5</v>
       </c>
       <c r="G2" s="10">
-        <v>-8.1</v>
+        <v>-11</v>
       </c>
       <c r="H2" s="10">
         <v>56.1</v>
@@ -3309,28 +3309,28 @@
     </row>
     <row r="2" spans="1:8">
       <c r="A2" s="13">
-        <v>0.2855</v>
+        <v>0.2911</v>
       </c>
       <c r="B2" s="13">
-        <v>0.1561</v>
+        <v>0.1609</v>
       </c>
       <c r="C2" s="13">
-        <v>0.1167</v>
+        <v>0.1323</v>
       </c>
       <c r="D2" s="13">
-        <v>0.1139</v>
+        <v>0.1111</v>
       </c>
       <c r="E2" s="13">
-        <v>0.0872</v>
+        <v>0.0925</v>
       </c>
       <c r="F2" s="13">
-        <v>0.04190000000000001</v>
+        <v>0.0248</v>
       </c>
       <c r="G2" s="13">
-        <v>-0.2824</v>
+        <v>-0.2951</v>
       </c>
       <c r="H2" s="13">
-        <v>-0.2989</v>
+        <v>-0.2968</v>
       </c>
     </row>
   </sheetData>

--- a/BIRLA_GROUP_Technical_Metrics.xlsx
+++ b/BIRLA_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="280" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="303" uniqueCount="81">
   <si>
     <t>Symbol</t>
   </si>
@@ -175,7 +175,55 @@
     <t>▶  SIGNAL EVENTS (vs Previous Run)</t>
   </si>
   <si>
-    <t>No signal events detected since last run.</t>
+    <t>Signal</t>
+  </si>
+  <si>
+    <t>Change</t>
+  </si>
+  <si>
+    <t>Direction</t>
+  </si>
+  <si>
+    <t>Prev Value</t>
+  </si>
+  <si>
+    <t>Curr Value</t>
+  </si>
+  <si>
+    <t>RSI Momentum</t>
+  </si>
+  <si>
+    <t>48.7 → 51.6</t>
+  </si>
+  <si>
+    <t>🟢 BULLISH</t>
+  </si>
+  <si>
+    <t>48.7</t>
+  </si>
+  <si>
+    <t>51.6</t>
+  </si>
+  <si>
+    <t>52.2 → 49.5</t>
+  </si>
+  <si>
+    <t>🔴 BEARISH</t>
+  </si>
+  <si>
+    <t>52.2</t>
+  </si>
+  <si>
+    <t>49.5</t>
+  </si>
+  <si>
+    <t>50 DMA &gt; 200 DMA</t>
+  </si>
+  <si>
+    <t>Yes → No</t>
+  </si>
+  <si>
+    <t>🔴 DEATH CROSS</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -261,14 +309,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF006100"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF9C0006"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -301,13 +349,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -377,17 +425,19 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -766,7 +816,7 @@
     <col min="23" max="23" width="16.7109375" customWidth="1"/>
     <col min="24" max="24" width="13.7109375" customWidth="1"/>
     <col min="25" max="25" width="7.7109375" customWidth="1"/>
-    <col min="26" max="26" width="9.7109375" customWidth="1"/>
+    <col min="26" max="26" width="8.7109375" customWidth="1"/>
     <col min="27" max="27" width="13.7109375" customWidth="1"/>
     <col min="28" max="28" width="11.7109375" customWidth="1"/>
     <col min="29" max="30" width="13.7109375" customWidth="1"/>
@@ -899,10 +949,10 @@
         <v>45</v>
       </c>
       <c r="C2">
-        <v>367</v>
+        <v>357.2</v>
       </c>
       <c r="D2">
-        <v>-1.62</v>
+        <v>-2.67</v>
       </c>
       <c r="E2">
         <v>424.7</v>
@@ -911,46 +961,46 @@
         <v>292.25</v>
       </c>
       <c r="G2">
-        <v>-13.59</v>
+        <v>-15.89</v>
       </c>
       <c r="H2">
-        <v>25.58</v>
+        <v>22.22</v>
       </c>
       <c r="I2">
-        <v>-4.59</v>
+        <v>-5.73</v>
       </c>
       <c r="J2">
-        <v>-10.5</v>
+        <v>-11.45</v>
       </c>
       <c r="K2">
-        <v>-10.28</v>
+        <v>-10.83</v>
       </c>
       <c r="L2">
-        <v>20.92</v>
+        <v>19.07</v>
       </c>
       <c r="M2">
-        <v>29.11</v>
+        <v>28.84</v>
       </c>
       <c r="N2">
-        <v>62</v>
+        <v>75</v>
       </c>
       <c r="O2">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="P2">
-        <v>376.12</v>
+        <v>371.78</v>
       </c>
       <c r="Q2">
-        <v>380.96</v>
+        <v>378.97</v>
       </c>
       <c r="R2">
-        <v>393.76</v>
+        <v>392.75</v>
       </c>
       <c r="S2">
-        <v>366.26</v>
+        <v>366.24</v>
       </c>
       <c r="T2">
-        <v>0.2</v>
+        <v>-2.47</v>
       </c>
       <c r="U2" t="s">
         <v>46</v>
@@ -962,46 +1012,46 @@
         <v>46</v>
       </c>
       <c r="X2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y2">
-        <v>37.79</v>
+        <v>33.03</v>
       </c>
       <c r="Z2">
-        <v>-5.56</v>
+        <v>-6.78</v>
       </c>
       <c r="AA2">
-        <v>-5.33</v>
+        <v>-5.62</v>
       </c>
       <c r="AB2">
-        <v>-0.23</v>
+        <v>-1.16</v>
       </c>
       <c r="AC2">
-        <v>45.38</v>
+        <v>20.14</v>
       </c>
       <c r="AD2">
-        <v>64.84999999999999</v>
+        <v>45.22</v>
       </c>
       <c r="AE2">
-        <v>9.359999999999999</v>
+        <v>9.52</v>
       </c>
       <c r="AF2">
-        <v>-6.47</v>
+        <v>-2.77</v>
       </c>
       <c r="AG2">
-        <v>398.48</v>
+        <v>397.81</v>
       </c>
       <c r="AH2">
-        <v>363.44</v>
+        <v>360.13</v>
       </c>
       <c r="AI2">
-        <v>397.11</v>
+        <v>389.27</v>
       </c>
       <c r="AJ2" t="s">
         <v>48</v>
       </c>
       <c r="AK2">
-        <v>20.87</v>
+        <v>25.85</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1012,58 +1062,58 @@
         <v>45</v>
       </c>
       <c r="C3">
-        <v>43.01</v>
+        <v>41.34</v>
       </c>
       <c r="D3">
-        <v>-0.32</v>
+        <v>-3.88</v>
       </c>
       <c r="E3">
         <v>85.38</v>
       </c>
       <c r="F3">
-        <v>43.01</v>
+        <v>41.34</v>
       </c>
       <c r="G3">
-        <v>-49.63</v>
+        <v>-51.58</v>
       </c>
       <c r="H3">
         <v>0</v>
       </c>
       <c r="I3">
-        <v>-3.95</v>
+        <v>-8.699999999999999</v>
       </c>
       <c r="J3">
-        <v>-14.25</v>
+        <v>-17.07</v>
       </c>
       <c r="K3">
-        <v>-25.08</v>
+        <v>-27.54</v>
       </c>
       <c r="L3">
-        <v>-48.46</v>
+        <v>-50.6</v>
       </c>
       <c r="M3">
-        <v>-29.68</v>
+        <v>-30.38</v>
       </c>
       <c r="N3">
         <v>13</v>
       </c>
       <c r="O3">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="P3">
-        <v>44.23</v>
+        <v>43.44</v>
       </c>
       <c r="Q3">
-        <v>45.56</v>
+        <v>45.16</v>
       </c>
       <c r="R3">
-        <v>50.17</v>
+        <v>49.78</v>
       </c>
       <c r="S3">
-        <v>60.33</v>
+        <v>60.15</v>
       </c>
       <c r="T3">
-        <v>-28.71</v>
+        <v>-31.28</v>
       </c>
       <c r="U3" t="s">
         <v>46</v>
@@ -1078,43 +1128,43 @@
         <v>0</v>
       </c>
       <c r="Y3">
-        <v>31.45</v>
+        <v>26.9</v>
       </c>
       <c r="Z3">
-        <v>-1.94</v>
+        <v>-2.05</v>
       </c>
       <c r="AA3">
         <v>-2.06</v>
       </c>
       <c r="AB3">
-        <v>0.13</v>
+        <v>0.01</v>
       </c>
       <c r="AC3">
-        <v>64.25</v>
+        <v>41.14</v>
       </c>
       <c r="AD3">
-        <v>78.39</v>
+        <v>61</v>
       </c>
       <c r="AE3">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="AF3">
-        <v>186</v>
+        <v>0.25</v>
       </c>
       <c r="AG3">
-        <v>49.68</v>
+        <v>49.32</v>
       </c>
       <c r="AH3">
-        <v>41.43</v>
+        <v>41</v>
       </c>
       <c r="AI3">
-        <v>48.29</v>
+        <v>47.15</v>
       </c>
       <c r="AJ3" t="s">
         <v>48</v>
       </c>
       <c r="AK3">
-        <v>29.22</v>
+        <v>31.65</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1125,10 +1175,10 @@
         <v>45</v>
       </c>
       <c r="C4">
-        <v>2889.1</v>
+        <v>2894.4</v>
       </c>
       <c r="D4">
-        <v>0.35</v>
+        <v>0.18</v>
       </c>
       <c r="E4">
         <v>3380.5</v>
@@ -1137,46 +1187,46 @@
         <v>2531.1</v>
       </c>
       <c r="G4">
-        <v>-14.54</v>
+        <v>-14.38</v>
       </c>
       <c r="H4">
-        <v>14.14</v>
+        <v>14.35</v>
       </c>
       <c r="I4">
-        <v>-0.79</v>
+        <v>0.74</v>
       </c>
       <c r="J4">
-        <v>-9.970000000000001</v>
+        <v>-8.58</v>
       </c>
       <c r="K4">
-        <v>-9.140000000000001</v>
+        <v>-8.59</v>
       </c>
       <c r="L4">
-        <v>2.57</v>
+        <v>1.21</v>
       </c>
       <c r="M4">
-        <v>11.11</v>
+        <v>11.57</v>
       </c>
       <c r="N4">
         <v>50</v>
       </c>
       <c r="O4">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="P4">
-        <v>2889.4</v>
+        <v>2893.68</v>
       </c>
       <c r="Q4">
-        <v>2988.7</v>
+        <v>2977.01</v>
       </c>
       <c r="R4">
-        <v>3162.84</v>
+        <v>3153.12</v>
       </c>
       <c r="S4">
-        <v>2981.74</v>
+        <v>2981.96</v>
       </c>
       <c r="T4">
-        <v>-3.11</v>
+        <v>-2.94</v>
       </c>
       <c r="U4" t="s">
         <v>46</v>
@@ -1191,43 +1241,43 @@
         <v>1</v>
       </c>
       <c r="Y4">
-        <v>35.97</v>
+        <v>36.71</v>
       </c>
       <c r="Z4">
-        <v>-85.2</v>
+        <v>-81.43000000000001</v>
       </c>
       <c r="AA4">
-        <v>-84.76000000000001</v>
+        <v>-84.09999999999999</v>
       </c>
       <c r="AB4">
-        <v>-0.44</v>
+        <v>2.67</v>
       </c>
       <c r="AC4">
-        <v>81.75</v>
+        <v>87.01000000000001</v>
       </c>
       <c r="AD4">
-        <v>67.06999999999999</v>
+        <v>78.55</v>
       </c>
       <c r="AE4">
-        <v>62.94</v>
+        <v>63.18</v>
       </c>
       <c r="AF4">
-        <v>-38.67</v>
+        <v>-55.32</v>
       </c>
       <c r="AG4">
-        <v>3232.51</v>
+        <v>3215.01</v>
       </c>
       <c r="AH4">
-        <v>2744.89</v>
+        <v>2739.01</v>
       </c>
       <c r="AI4">
-        <v>3061.2</v>
+        <v>3050.83</v>
       </c>
       <c r="AJ4" t="s">
         <v>48</v>
       </c>
       <c r="AK4">
-        <v>59.23</v>
+        <v>58.27</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1238,10 +1288,10 @@
         <v>45</v>
       </c>
       <c r="C5">
-        <v>892.85</v>
+        <v>885.6</v>
       </c>
       <c r="D5">
-        <v>-0.84</v>
+        <v>-0.8100000000000001</v>
       </c>
       <c r="E5">
         <v>1149.7</v>
@@ -1250,88 +1300,88 @@
         <v>772.8</v>
       </c>
       <c r="G5">
-        <v>-22.34</v>
+        <v>-22.97</v>
       </c>
       <c r="H5">
-        <v>15.53</v>
+        <v>14.6</v>
       </c>
       <c r="I5">
-        <v>-1.04</v>
+        <v>0.35</v>
       </c>
       <c r="J5">
-        <v>-9.49</v>
+        <v>-9.74</v>
       </c>
       <c r="K5">
-        <v>-6.15</v>
+        <v>-6.78</v>
       </c>
       <c r="L5">
-        <v>16.83</v>
+        <v>13.52</v>
       </c>
       <c r="M5">
-        <v>13.23</v>
+        <v>14.14</v>
       </c>
       <c r="N5">
-        <v>75</v>
+        <v>62</v>
       </c>
       <c r="O5">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="P5">
-        <v>895.53</v>
+        <v>896.15</v>
       </c>
       <c r="Q5">
-        <v>928.66</v>
+        <v>924.29</v>
       </c>
       <c r="R5">
-        <v>984.53</v>
+        <v>981.16</v>
       </c>
       <c r="S5">
-        <v>983.65</v>
+        <v>983.6</v>
       </c>
       <c r="T5">
-        <v>-9.23</v>
+        <v>-9.960000000000001</v>
       </c>
       <c r="U5" t="s">
         <v>46</v>
       </c>
       <c r="V5" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="W5" t="s">
         <v>46</v>
       </c>
       <c r="X5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y5">
-        <v>36.99</v>
+        <v>35.44</v>
       </c>
       <c r="Z5">
-        <v>-26.11</v>
+        <v>-25.99</v>
       </c>
       <c r="AA5">
-        <v>-25.83</v>
+        <v>-25.86</v>
       </c>
       <c r="AB5">
-        <v>-0.28</v>
+        <v>-0.13</v>
       </c>
       <c r="AC5">
-        <v>88.55</v>
+        <v>77.33</v>
       </c>
       <c r="AD5">
-        <v>76.97</v>
+        <v>82.31</v>
       </c>
       <c r="AE5">
-        <v>22.68</v>
+        <v>22.69</v>
       </c>
       <c r="AF5">
-        <v>-20.59</v>
+        <v>-6.44</v>
       </c>
       <c r="AG5">
-        <v>1002.79</v>
+        <v>997.71</v>
       </c>
       <c r="AH5">
-        <v>854.53</v>
+        <v>850.87</v>
       </c>
       <c r="AI5">
         <v>946.48</v>
@@ -1340,7 +1390,7 @@
         <v>48</v>
       </c>
       <c r="AK5">
-        <v>45.37</v>
+        <v>46.38</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1351,10 +1401,10 @@
         <v>45</v>
       </c>
       <c r="C6">
-        <v>11.64</v>
+        <v>11.53</v>
       </c>
       <c r="D6">
-        <v>-5.21</v>
+        <v>-0.95</v>
       </c>
       <c r="E6">
         <v>15.6</v>
@@ -1363,46 +1413,46 @@
         <v>8.529999999999999</v>
       </c>
       <c r="G6">
-        <v>-25.38</v>
+        <v>-26.09</v>
       </c>
       <c r="H6">
-        <v>36.46</v>
+        <v>35.17</v>
       </c>
       <c r="I6">
-        <v>-9.06</v>
+        <v>-9</v>
       </c>
       <c r="J6">
-        <v>-16.38</v>
+        <v>-16.69</v>
       </c>
       <c r="K6">
-        <v>-13.71</v>
+        <v>-14.84</v>
       </c>
       <c r="L6">
-        <v>33.03</v>
+        <v>30.28</v>
       </c>
       <c r="M6">
-        <v>2.48</v>
+        <v>2.38</v>
       </c>
       <c r="N6">
         <v>87</v>
       </c>
       <c r="O6">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="P6">
-        <v>12.34</v>
+        <v>12.11</v>
       </c>
       <c r="Q6">
-        <v>13.09</v>
+        <v>12.96</v>
       </c>
       <c r="R6">
-        <v>13.84</v>
+        <v>13.82</v>
       </c>
       <c r="S6">
         <v>12.31</v>
       </c>
       <c r="T6">
-        <v>-5.41</v>
+        <v>-6.3</v>
       </c>
       <c r="U6" t="s">
         <v>46</v>
@@ -1417,43 +1467,43 @@
         <v>1</v>
       </c>
       <c r="Y6">
-        <v>28.85</v>
+        <v>28</v>
       </c>
       <c r="Z6">
-        <v>-0.51</v>
+        <v>-0.5600000000000001</v>
       </c>
       <c r="AA6">
-        <v>-0.41</v>
+        <v>-0.44</v>
       </c>
       <c r="AB6">
-        <v>-0.1</v>
+        <v>-0.12</v>
       </c>
       <c r="AC6">
-        <v>24.44</v>
+        <v>5.86</v>
       </c>
       <c r="AD6">
-        <v>31.04</v>
+        <v>20.73</v>
       </c>
       <c r="AE6">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="AF6">
-        <v>31.24</v>
+        <v>22.94</v>
       </c>
       <c r="AG6">
-        <v>14.58</v>
+        <v>14.49</v>
       </c>
       <c r="AH6">
-        <v>11.61</v>
+        <v>11.43</v>
       </c>
       <c r="AI6">
-        <v>13.35</v>
+        <v>12.88</v>
       </c>
       <c r="AJ6" t="s">
         <v>48</v>
       </c>
       <c r="AK6">
-        <v>51.24</v>
+        <v>55.4</v>
       </c>
     </row>
     <row r="7" spans="1:37">
@@ -1464,10 +1514,10 @@
         <v>45</v>
       </c>
       <c r="C7">
-        <v>11.67</v>
+        <v>11.4</v>
       </c>
       <c r="D7">
-        <v>-8.4</v>
+        <v>-2.31</v>
       </c>
       <c r="E7">
         <v>13.92</v>
@@ -1476,25 +1526,25 @@
         <v>4.69</v>
       </c>
       <c r="G7">
-        <v>-16.16</v>
+        <v>-18.1</v>
       </c>
       <c r="H7">
-        <v>148.83</v>
+        <v>143.07</v>
       </c>
       <c r="I7">
-        <v>2.01</v>
+        <v>-1.81</v>
       </c>
       <c r="J7">
-        <v>-2.26</v>
+        <v>-2.23</v>
       </c>
       <c r="K7">
-        <v>-1.6</v>
+        <v>-5.71</v>
       </c>
       <c r="L7">
-        <v>123.56</v>
+        <v>118.39</v>
       </c>
       <c r="M7">
-        <v>-29.51</v>
+        <v>-29.81</v>
       </c>
       <c r="N7">
         <v>99</v>
@@ -1503,19 +1553,19 @@
         <v>96</v>
       </c>
       <c r="P7">
-        <v>11.95</v>
+        <v>11.91</v>
       </c>
       <c r="Q7">
         <v>11.25</v>
       </c>
       <c r="R7">
-        <v>11.49</v>
+        <v>11.46</v>
       </c>
       <c r="S7">
-        <v>10.82</v>
+        <v>10.81</v>
       </c>
       <c r="T7">
-        <v>7.89</v>
+        <v>5.45</v>
       </c>
       <c r="U7" t="s">
         <v>46</v>
@@ -1530,31 +1580,31 @@
         <v>2</v>
       </c>
       <c r="Y7">
-        <v>52.19</v>
+        <v>49.5</v>
       </c>
       <c r="Z7">
-        <v>0.12</v>
+        <v>0.1</v>
       </c>
       <c r="AA7">
-        <v>-0.04</v>
+        <v>-0.01</v>
       </c>
       <c r="AB7">
-        <v>0.16</v>
+        <v>0.11</v>
       </c>
       <c r="AC7">
-        <v>86.72</v>
+        <v>70.69</v>
       </c>
       <c r="AD7">
-        <v>91.89</v>
+        <v>83.95999999999999</v>
       </c>
       <c r="AE7">
-        <v>0.74</v>
+        <v>0.8</v>
       </c>
       <c r="AF7">
-        <v>18.7</v>
+        <v>26.19</v>
       </c>
       <c r="AG7">
-        <v>12.44</v>
+        <v>12.45</v>
       </c>
       <c r="AH7">
         <v>10.05</v>
@@ -1566,7 +1616,7 @@
         <v>49</v>
       </c>
       <c r="AK7">
-        <v>32.55</v>
+        <v>29.49</v>
       </c>
     </row>
     <row r="8" spans="1:37">
@@ -1577,37 +1627,37 @@
         <v>45</v>
       </c>
       <c r="C8">
-        <v>3907.2</v>
+        <v>3885.7</v>
       </c>
       <c r="D8">
-        <v>-1.12</v>
+        <v>-0.55</v>
       </c>
       <c r="E8">
         <v>5809.5</v>
       </c>
       <c r="F8">
-        <v>3892.3</v>
+        <v>3885.7</v>
       </c>
       <c r="G8">
-        <v>-32.74</v>
+        <v>-33.11</v>
       </c>
       <c r="H8">
-        <v>0.38</v>
+        <v>0</v>
       </c>
       <c r="I8">
-        <v>-1.07</v>
+        <v>-2.61</v>
       </c>
       <c r="J8">
-        <v>-3.93</v>
+        <v>-3.51</v>
       </c>
       <c r="K8">
-        <v>-11.95</v>
+        <v>-10.72</v>
       </c>
       <c r="L8">
-        <v>-25.9</v>
+        <v>-27.55</v>
       </c>
       <c r="M8">
-        <v>16.09</v>
+        <v>16.33</v>
       </c>
       <c r="N8">
         <v>25</v>
@@ -1616,19 +1666,19 @@
         <v>31</v>
       </c>
       <c r="P8">
-        <v>3960.38</v>
+        <v>3939.58</v>
       </c>
       <c r="Q8">
-        <v>3982.35</v>
+        <v>3976.22</v>
       </c>
       <c r="R8">
-        <v>4175.79</v>
+        <v>4166.22</v>
       </c>
       <c r="S8">
-        <v>4456.27</v>
+        <v>4449.8</v>
       </c>
       <c r="T8">
-        <v>-12.32</v>
+        <v>-12.68</v>
       </c>
       <c r="U8" t="s">
         <v>46</v>
@@ -1643,43 +1693,43 @@
         <v>0</v>
       </c>
       <c r="Y8">
-        <v>37.74</v>
+        <v>36.23</v>
       </c>
       <c r="Z8">
-        <v>-59.81</v>
+        <v>-62.07</v>
       </c>
       <c r="AA8">
-        <v>-66.76000000000001</v>
+        <v>-65.81999999999999</v>
       </c>
       <c r="AB8">
-        <v>6.94</v>
+        <v>3.75</v>
       </c>
       <c r="AC8">
-        <v>65</v>
+        <v>51.42</v>
       </c>
       <c r="AD8">
-        <v>71.86</v>
+        <v>63.12</v>
       </c>
       <c r="AE8">
-        <v>94.70999999999999</v>
+        <v>93.86</v>
       </c>
       <c r="AF8">
-        <v>80.8</v>
+        <v>-3.75</v>
       </c>
       <c r="AG8">
-        <v>4081.03</v>
+        <v>4083.01</v>
       </c>
       <c r="AH8">
-        <v>3883.66</v>
+        <v>3869.42</v>
       </c>
       <c r="AI8">
-        <v>4221.07</v>
+        <v>4152.97</v>
       </c>
       <c r="AJ8" t="s">
         <v>48</v>
       </c>
       <c r="AK8">
-        <v>24.2</v>
+        <v>26.11</v>
       </c>
     </row>
     <row r="9" spans="1:37">
@@ -1690,10 +1740,10 @@
         <v>45</v>
       </c>
       <c r="C9">
-        <v>10849</v>
+        <v>10958</v>
       </c>
       <c r="D9">
-        <v>1.87</v>
+        <v>1</v>
       </c>
       <c r="E9">
         <v>13052</v>
@@ -1702,46 +1752,46 @@
         <v>10362</v>
       </c>
       <c r="G9">
-        <v>-16.88</v>
+        <v>-16.04</v>
       </c>
       <c r="H9">
-        <v>4.7</v>
+        <v>5.75</v>
       </c>
       <c r="I9">
-        <v>0.92</v>
+        <v>1.51</v>
       </c>
       <c r="J9">
-        <v>-1.5</v>
+        <v>-1.28</v>
       </c>
       <c r="K9">
-        <v>-10.29</v>
+        <v>-7.86</v>
       </c>
       <c r="L9">
-        <v>-11.88</v>
+        <v>-11.33</v>
       </c>
       <c r="M9">
-        <v>9.25</v>
+        <v>9.41</v>
       </c>
       <c r="N9">
         <v>38</v>
       </c>
       <c r="O9">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="P9">
-        <v>10812.6</v>
+        <v>10845.2</v>
       </c>
       <c r="Q9">
-        <v>10828.9</v>
+        <v>10826.8</v>
       </c>
       <c r="R9">
-        <v>11153.12</v>
+        <v>11131.52</v>
       </c>
       <c r="S9">
-        <v>11652.56</v>
+        <v>11647.84</v>
       </c>
       <c r="T9">
-        <v>-6.9</v>
+        <v>-5.92</v>
       </c>
       <c r="U9" t="s">
         <v>46</v>
@@ -1756,34 +1806,34 @@
         <v>0</v>
       </c>
       <c r="Y9">
-        <v>48.74</v>
+        <v>51.59</v>
       </c>
       <c r="Z9">
-        <v>-104.31</v>
+        <v>-82.56999999999999</v>
       </c>
       <c r="AA9">
-        <v>-137.63</v>
+        <v>-126.62</v>
       </c>
       <c r="AB9">
-        <v>33.32</v>
+        <v>44.05</v>
       </c>
       <c r="AC9">
         <v>84.76000000000001</v>
       </c>
       <c r="AD9">
-        <v>89.25</v>
+        <v>85.39</v>
       </c>
       <c r="AE9">
-        <v>255.95</v>
+        <v>260.89</v>
       </c>
       <c r="AF9">
-        <v>29.23</v>
+        <v>-43.23</v>
       </c>
       <c r="AG9">
-        <v>11220</v>
+        <v>11214.47</v>
       </c>
       <c r="AH9">
-        <v>10437.8</v>
+        <v>10439.13</v>
       </c>
       <c r="AI9">
         <v>11169.72</v>
@@ -1792,7 +1842,7 @@
         <v>48</v>
       </c>
       <c r="AK9">
-        <v>33.27</v>
+        <v>32.3</v>
       </c>
     </row>
   </sheetData>
@@ -1933,7 +1983,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F72"/>
+  <dimension ref="A1:F74"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -1953,1161 +2003,1236 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="3" t="s">
         <v>51</v>
       </c>
+      <c r="C2" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
+      <c r="A4" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="C4" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="D4" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="E4" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="F4" s="5" t="s">
+        <v>64</v>
+      </c>
     </row>
     <row r="5" spans="1:6">
-      <c r="A5" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="B5" s="2"/>
-      <c r="C5" s="2"/>
-      <c r="D5" s="2"/>
-      <c r="E5" s="2"/>
-    </row>
-    <row r="6" spans="1:6">
-      <c r="A6" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="D6" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="E6" s="4" t="s">
-        <v>56</v>
+      <c r="A5" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="E5" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="F5" s="5" t="s">
+        <v>46</v>
       </c>
     </row>
     <row r="7" spans="1:6">
-      <c r="A7" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C7" s="5">
-        <v>-4.35</v>
-      </c>
-      <c r="D7" s="5">
-        <v>-10.5</v>
-      </c>
-      <c r="E7" s="6">
-        <v>-6.15</v>
-      </c>
+      <c r="A7" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="B7" s="2"/>
+      <c r="C7" s="2"/>
+      <c r="D7" s="2"/>
+      <c r="E7" s="2"/>
     </row>
     <row r="8" spans="1:6">
       <c r="A8" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="B9" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C9" s="7">
+        <v>-10.5</v>
+      </c>
+      <c r="D9" s="7">
+        <v>-11.45</v>
+      </c>
+      <c r="E9" s="8">
+        <v>-0.95</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="B8" s="3" t="s">
+      <c r="B10" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="C8" s="5">
-        <v>-14.47</v>
-      </c>
-      <c r="D8" s="5">
+      <c r="C10" s="7">
         <v>-14.25</v>
       </c>
-      <c r="E8" s="7">
+      <c r="D10" s="7">
+        <v>-17.07</v>
+      </c>
+      <c r="E10" s="8">
+        <v>-2.82</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="B11" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C11" s="7">
+        <v>-9.970000000000001</v>
+      </c>
+      <c r="D11" s="7">
+        <v>-8.58</v>
+      </c>
+      <c r="E11" s="9">
+        <v>1.39</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="B12" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C12" s="7">
+        <v>-9.49</v>
+      </c>
+      <c r="D12" s="7">
+        <v>-9.74</v>
+      </c>
+      <c r="E12" s="8">
+        <v>-0.25</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="A13" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="B13" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C13" s="7">
+        <v>-16.38</v>
+      </c>
+      <c r="D13" s="7">
+        <v>-16.69</v>
+      </c>
+      <c r="E13" s="8">
+        <v>-0.31</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="B14" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C14" s="7">
+        <v>-2.26</v>
+      </c>
+      <c r="D14" s="7">
+        <v>-2.23</v>
+      </c>
+      <c r="E14" s="9">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="A15" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="B15" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C15" s="7">
+        <v>-3.93</v>
+      </c>
+      <c r="D15" s="7">
+        <v>-3.51</v>
+      </c>
+      <c r="E15" s="9">
+        <v>0.42</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="A16" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="B16" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C16" s="7">
+        <v>-1.5</v>
+      </c>
+      <c r="D16" s="7">
+        <v>-1.28</v>
+      </c>
+      <c r="E16" s="9">
         <v>0.22</v>
       </c>
     </row>
-    <row r="9" spans="1:6">
-      <c r="A9" s="3" t="s">
+    <row r="17" spans="1:5">
+      <c r="A17" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="B17" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C17" s="7">
+        <v>-4.59</v>
+      </c>
+      <c r="D17" s="7">
+        <v>-5.73</v>
+      </c>
+      <c r="E17" s="8">
+        <v>-1.14</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="B18" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C18" s="7">
+        <v>-3.95</v>
+      </c>
+      <c r="D18" s="7">
+        <v>-8.699999999999999</v>
+      </c>
+      <c r="E18" s="8">
+        <v>-4.75</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="B9" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C9" s="5">
-        <v>-9.27</v>
-      </c>
-      <c r="D9" s="5">
-        <v>-9.970000000000001</v>
-      </c>
-      <c r="E9" s="6">
-        <v>-0.7</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10" s="3" t="s">
+      <c r="B19" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C19" s="7">
+        <v>-0.79</v>
+      </c>
+      <c r="D19" s="7">
+        <v>0.74</v>
+      </c>
+      <c r="E19" s="9">
+        <v>1.53</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="B10" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C10" s="5">
-        <v>-8.16</v>
-      </c>
-      <c r="D10" s="5">
-        <v>-9.49</v>
-      </c>
-      <c r="E10" s="6">
-        <v>-1.33</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11" s="3" t="s">
+      <c r="B20" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C20" s="7">
+        <v>-1.04</v>
+      </c>
+      <c r="D20" s="7">
+        <v>0.35</v>
+      </c>
+      <c r="E20" s="9">
+        <v>1.39</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="B11" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C11" s="5">
-        <v>-13.64</v>
-      </c>
-      <c r="D11" s="5">
-        <v>-16.38</v>
-      </c>
-      <c r="E11" s="6">
-        <v>-2.74</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12" s="3" t="s">
+      <c r="B21" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C21" s="7">
+        <v>-9.06</v>
+      </c>
+      <c r="D21" s="7">
+        <v>-9</v>
+      </c>
+      <c r="E21" s="9">
+        <v>0.06</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="B12" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C12" s="5">
-        <v>3.24</v>
-      </c>
-      <c r="D12" s="5">
-        <v>-2.26</v>
-      </c>
-      <c r="E12" s="6">
-        <v>-5.5</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13" s="3" t="s">
+      <c r="B22" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C22" s="7">
+        <v>2.01</v>
+      </c>
+      <c r="D22" s="7">
+        <v>-1.81</v>
+      </c>
+      <c r="E22" s="8">
+        <v>-3.82</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="B13" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C13" s="5">
-        <v>-3.2</v>
-      </c>
-      <c r="D13" s="5">
-        <v>-3.93</v>
-      </c>
-      <c r="E13" s="6">
-        <v>-0.73</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14" s="3" t="s">
+      <c r="B23" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C23" s="7">
+        <v>-1.07</v>
+      </c>
+      <c r="D23" s="7">
+        <v>-2.61</v>
+      </c>
+      <c r="E23" s="8">
+        <v>-1.54</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="B14" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C14" s="5">
-        <v>-1.06</v>
-      </c>
-      <c r="D14" s="5">
-        <v>-1.5</v>
-      </c>
-      <c r="E14" s="6">
-        <v>-0.44</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15" s="3" t="s">
+      <c r="B24" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C24" s="7">
+        <v>0.92</v>
+      </c>
+      <c r="D24" s="7">
+        <v>1.51</v>
+      </c>
+      <c r="E24" s="9">
+        <v>0.59</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="B15" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C15" s="5">
-        <v>-1.89</v>
-      </c>
-      <c r="D15" s="5">
-        <v>-4.59</v>
-      </c>
-      <c r="E15" s="6">
-        <v>-2.7</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16" s="3" t="s">
+      <c r="B25" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C25" s="7">
+        <v>20.92</v>
+      </c>
+      <c r="D25" s="7">
+        <v>19.07</v>
+      </c>
+      <c r="E25" s="8">
+        <v>-1.85</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="B16" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C16" s="5">
-        <v>-0.87</v>
-      </c>
-      <c r="D16" s="5">
-        <v>-3.95</v>
-      </c>
-      <c r="E16" s="6">
-        <v>-3.08</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5">
-      <c r="A17" s="3" t="s">
+      <c r="B26" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C26" s="7">
+        <v>-48.46</v>
+      </c>
+      <c r="D26" s="7">
+        <v>-50.6</v>
+      </c>
+      <c r="E26" s="8">
+        <v>-2.14</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="B17" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C17" s="5">
-        <v>0.73</v>
-      </c>
-      <c r="D17" s="5">
-        <v>-0.79</v>
-      </c>
-      <c r="E17" s="6">
-        <v>-1.52</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5">
-      <c r="A18" s="3" t="s">
+      <c r="B27" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C27" s="7">
+        <v>2.57</v>
+      </c>
+      <c r="D27" s="7">
+        <v>1.21</v>
+      </c>
+      <c r="E27" s="8">
+        <v>-1.36</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="B18" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C18" s="5">
-        <v>2.03</v>
-      </c>
-      <c r="D18" s="5">
-        <v>-1.04</v>
-      </c>
-      <c r="E18" s="6">
-        <v>-3.07</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5">
-      <c r="A19" s="3" t="s">
+      <c r="B28" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C28" s="7">
+        <v>16.83</v>
+      </c>
+      <c r="D28" s="7">
+        <v>13.52</v>
+      </c>
+      <c r="E28" s="8">
+        <v>-3.31</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="B19" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C19" s="5">
-        <v>-3.08</v>
-      </c>
-      <c r="D19" s="5">
-        <v>-9.06</v>
-      </c>
-      <c r="E19" s="6">
-        <v>-5.98</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5">
-      <c r="A20" s="3" t="s">
+      <c r="B29" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C29" s="7">
+        <v>33.03</v>
+      </c>
+      <c r="D29" s="7">
+        <v>30.28</v>
+      </c>
+      <c r="E29" s="8">
+        <v>-2.75</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="B20" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C20" s="5">
-        <v>17.1</v>
-      </c>
-      <c r="D20" s="5">
-        <v>2.01</v>
-      </c>
-      <c r="E20" s="6">
-        <v>-15.09</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5">
-      <c r="A21" s="3" t="s">
+      <c r="B30" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C30" s="7">
+        <v>123.56</v>
+      </c>
+      <c r="D30" s="7">
+        <v>118.39</v>
+      </c>
+      <c r="E30" s="8">
+        <v>-5.17</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5">
+      <c r="A31" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="B21" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C21" s="5">
-        <v>0.42</v>
-      </c>
-      <c r="D21" s="5">
-        <v>-1.07</v>
-      </c>
-      <c r="E21" s="6">
-        <v>-1.49</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5">
-      <c r="A22" s="3" t="s">
+      <c r="B31" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C31" s="7">
+        <v>-25.9</v>
+      </c>
+      <c r="D31" s="7">
+        <v>-27.55</v>
+      </c>
+      <c r="E31" s="8">
+        <v>-1.65</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5">
+      <c r="A32" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="B22" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C22" s="5">
-        <v>1.24</v>
-      </c>
-      <c r="D22" s="5">
-        <v>0.92</v>
-      </c>
-      <c r="E22" s="6">
-        <v>-0.32</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5">
-      <c r="A23" s="3" t="s">
+      <c r="B32" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C32" s="7">
+        <v>-11.88</v>
+      </c>
+      <c r="D32" s="7">
+        <v>-11.33</v>
+      </c>
+      <c r="E32" s="9">
+        <v>0.55</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5">
+      <c r="A33" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="B23" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C23" s="5">
-        <v>25.18</v>
-      </c>
-      <c r="D23" s="5">
-        <v>20.92</v>
-      </c>
-      <c r="E23" s="6">
-        <v>-4.26</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5">
-      <c r="A24" s="3" t="s">
+      <c r="B33" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C33" s="7">
+        <v>-10.28</v>
+      </c>
+      <c r="D33" s="7">
+        <v>-10.83</v>
+      </c>
+      <c r="E33" s="8">
+        <v>-0.55</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5">
+      <c r="A34" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="B24" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C24" s="5">
-        <v>-46.16</v>
-      </c>
-      <c r="D24" s="5">
-        <v>-48.46</v>
-      </c>
-      <c r="E24" s="6">
+      <c r="B34" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C34" s="7">
+        <v>-25.08</v>
+      </c>
+      <c r="D34" s="7">
+        <v>-27.54</v>
+      </c>
+      <c r="E34" s="8">
+        <v>-2.46</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5">
+      <c r="A35" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="B35" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C35" s="7">
+        <v>-9.140000000000001</v>
+      </c>
+      <c r="D35" s="7">
+        <v>-8.59</v>
+      </c>
+      <c r="E35" s="9">
+        <v>0.55</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5">
+      <c r="A36" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="B36" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C36" s="7">
+        <v>-6.15</v>
+      </c>
+      <c r="D36" s="7">
+        <v>-6.78</v>
+      </c>
+      <c r="E36" s="8">
+        <v>-0.63</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5">
+      <c r="A37" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="B37" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C37" s="7">
+        <v>-13.71</v>
+      </c>
+      <c r="D37" s="7">
+        <v>-14.84</v>
+      </c>
+      <c r="E37" s="8">
+        <v>-1.13</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5">
+      <c r="A38" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="B38" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C38" s="7">
+        <v>-1.6</v>
+      </c>
+      <c r="D38" s="7">
+        <v>-5.71</v>
+      </c>
+      <c r="E38" s="8">
+        <v>-4.11</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5">
+      <c r="A39" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="B39" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C39" s="7">
+        <v>-11.95</v>
+      </c>
+      <c r="D39" s="7">
+        <v>-10.72</v>
+      </c>
+      <c r="E39" s="9">
+        <v>1.23</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5">
+      <c r="A40" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="B40" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C40" s="7">
+        <v>-10.29</v>
+      </c>
+      <c r="D40" s="7">
+        <v>-7.86</v>
+      </c>
+      <c r="E40" s="9">
+        <v>2.43</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5">
+      <c r="A41" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="B41" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C41" s="7">
+        <v>-13.59</v>
+      </c>
+      <c r="D41" s="7">
+        <v>-15.89</v>
+      </c>
+      <c r="E41" s="8">
         <v>-2.3</v>
       </c>
     </row>
-    <row r="25" spans="1:5">
-      <c r="A25" s="3" t="s">
+    <row r="42" spans="1:5">
+      <c r="A42" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="B42" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C42" s="7">
+        <v>-49.63</v>
+      </c>
+      <c r="D42" s="7">
+        <v>-51.58</v>
+      </c>
+      <c r="E42" s="8">
+        <v>-1.95</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5">
+      <c r="A43" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="B25" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C25" s="5">
-        <v>3.72</v>
-      </c>
-      <c r="D25" s="5">
-        <v>2.57</v>
-      </c>
-      <c r="E25" s="6">
-        <v>-1.15</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5">
-      <c r="A26" s="3" t="s">
+      <c r="B43" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C43" s="7">
+        <v>-14.54</v>
+      </c>
+      <c r="D43" s="7">
+        <v>-14.38</v>
+      </c>
+      <c r="E43" s="9">
+        <v>0.16</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5">
+      <c r="A44" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="B26" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C26" s="5">
-        <v>18.46</v>
-      </c>
-      <c r="D26" s="5">
-        <v>16.83</v>
-      </c>
-      <c r="E26" s="6">
-        <v>-1.63</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5">
-      <c r="A27" s="3" t="s">
+      <c r="B44" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C44" s="7">
+        <v>-22.34</v>
+      </c>
+      <c r="D44" s="7">
+        <v>-22.97</v>
+      </c>
+      <c r="E44" s="8">
+        <v>-0.63</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5">
+      <c r="A45" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="B27" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C27" s="5">
-        <v>46.89</v>
-      </c>
-      <c r="D27" s="5">
+      <c r="B45" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C45" s="7">
+        <v>-25.38</v>
+      </c>
+      <c r="D45" s="7">
+        <v>-26.09</v>
+      </c>
+      <c r="E45" s="8">
+        <v>-0.71</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5">
+      <c r="A46" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="B46" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C46" s="7">
+        <v>-16.16</v>
+      </c>
+      <c r="D46" s="7">
+        <v>-18.1</v>
+      </c>
+      <c r="E46" s="8">
+        <v>-1.94</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5">
+      <c r="A47" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="B47" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C47" s="7">
+        <v>-32.74</v>
+      </c>
+      <c r="D47" s="7">
+        <v>-33.11</v>
+      </c>
+      <c r="E47" s="8">
+        <v>-0.37</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5">
+      <c r="A48" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="B48" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C48" s="7">
+        <v>-16.88</v>
+      </c>
+      <c r="D48" s="7">
+        <v>-16.04</v>
+      </c>
+      <c r="E48" s="9">
+        <v>0.84</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5">
+      <c r="A49" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="B49" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C49" s="7">
+        <v>367</v>
+      </c>
+      <c r="D49" s="7">
+        <v>357.2</v>
+      </c>
+      <c r="E49" s="8">
+        <v>-9.800000000000001</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5">
+      <c r="A50" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="B50" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C50" s="7">
+        <v>43.01</v>
+      </c>
+      <c r="D50" s="7">
+        <v>41.34</v>
+      </c>
+      <c r="E50" s="8">
+        <v>-1.67</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5">
+      <c r="A51" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="B51" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C51" s="7">
+        <v>2889.1</v>
+      </c>
+      <c r="D51" s="7">
+        <v>2894.4</v>
+      </c>
+      <c r="E51" s="9">
+        <v>5.3</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5">
+      <c r="A52" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="B52" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C52" s="7">
+        <v>892.85</v>
+      </c>
+      <c r="D52" s="7">
+        <v>885.6</v>
+      </c>
+      <c r="E52" s="8">
+        <v>-7.25</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5">
+      <c r="A53" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="B53" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C53" s="7">
+        <v>11.64</v>
+      </c>
+      <c r="D53" s="7">
+        <v>11.53</v>
+      </c>
+      <c r="E53" s="8">
+        <v>-0.11</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5">
+      <c r="A54" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="B54" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C54" s="7">
+        <v>11.67</v>
+      </c>
+      <c r="D54" s="7">
+        <v>11.4</v>
+      </c>
+      <c r="E54" s="8">
+        <v>-0.27</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5">
+      <c r="A55" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="B55" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C55" s="7">
+        <v>3907.2</v>
+      </c>
+      <c r="D55" s="7">
+        <v>3885.7</v>
+      </c>
+      <c r="E55" s="8">
+        <v>-21.5</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5">
+      <c r="A56" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="B56" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C56" s="7">
+        <v>10849</v>
+      </c>
+      <c r="D56" s="7">
+        <v>10958</v>
+      </c>
+      <c r="E56" s="9">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5">
+      <c r="A57" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="B57" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="C57" s="7">
+        <v>62</v>
+      </c>
+      <c r="D57" s="7">
+        <v>75</v>
+      </c>
+      <c r="E57" s="9">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5">
+      <c r="A58" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="B58" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="C58" s="7">
+        <v>75</v>
+      </c>
+      <c r="D58" s="7">
+        <v>62</v>
+      </c>
+      <c r="E58" s="8">
+        <v>-13</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5">
+      <c r="A59" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="B59" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C59" s="7">
+        <v>37.79</v>
+      </c>
+      <c r="D59" s="7">
         <v>33.03</v>
       </c>
-      <c r="E27" s="6">
-        <v>-13.86</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5">
-      <c r="A28" s="3" t="s">
+      <c r="E59" s="8">
+        <v>-4.76</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5">
+      <c r="A60" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="B60" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C60" s="7">
+        <v>31.45</v>
+      </c>
+      <c r="D60" s="7">
+        <v>26.9</v>
+      </c>
+      <c r="E60" s="8">
+        <v>-4.55</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5">
+      <c r="A61" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="B61" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C61" s="7">
+        <v>35.97</v>
+      </c>
+      <c r="D61" s="7">
+        <v>36.71</v>
+      </c>
+      <c r="E61" s="9">
+        <v>0.74</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5">
+      <c r="A62" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="B62" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C62" s="7">
+        <v>36.99</v>
+      </c>
+      <c r="D62" s="7">
+        <v>35.44</v>
+      </c>
+      <c r="E62" s="8">
+        <v>-1.55</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5">
+      <c r="A63" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="B63" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C63" s="7">
+        <v>28.85</v>
+      </c>
+      <c r="D63" s="7">
+        <v>28</v>
+      </c>
+      <c r="E63" s="8">
+        <v>-0.85</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5">
+      <c r="A64" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="B28" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C28" s="5">
-        <v>153.28</v>
-      </c>
-      <c r="D28" s="5">
-        <v>123.56</v>
-      </c>
-      <c r="E28" s="6">
-        <v>-29.72</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5">
-      <c r="A29" s="3" t="s">
+      <c r="B64" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C64" s="7">
+        <v>52.19</v>
+      </c>
+      <c r="D64" s="7">
+        <v>49.5</v>
+      </c>
+      <c r="E64" s="8">
+        <v>-2.69</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5">
+      <c r="A65" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="B29" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C29" s="5">
-        <v>-24.81</v>
-      </c>
-      <c r="D29" s="5">
-        <v>-25.9</v>
-      </c>
-      <c r="E29" s="6">
-        <v>-1.09</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5">
-      <c r="A30" s="3" t="s">
+      <c r="B65" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C65" s="7">
+        <v>37.74</v>
+      </c>
+      <c r="D65" s="7">
+        <v>36.23</v>
+      </c>
+      <c r="E65" s="8">
+        <v>-1.51</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5">
+      <c r="A66" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="B30" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C30" s="5">
-        <v>-11.76</v>
-      </c>
-      <c r="D30" s="5">
-        <v>-11.88</v>
-      </c>
-      <c r="E30" s="6">
-        <v>-0.12</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5">
-      <c r="A31" s="3" t="s">
+      <c r="B66" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C66" s="7">
+        <v>48.74</v>
+      </c>
+      <c r="D66" s="7">
+        <v>51.59</v>
+      </c>
+      <c r="E66" s="9">
+        <v>2.85</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5">
+      <c r="A67" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="B31" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C31" s="5">
-        <v>-7</v>
-      </c>
-      <c r="D31" s="5">
-        <v>-10.28</v>
-      </c>
-      <c r="E31" s="6">
-        <v>-3.28</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5">
-      <c r="A32" s="3" t="s">
+      <c r="B67" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C67" s="7">
+        <v>-6.47</v>
+      </c>
+      <c r="D67" s="7">
+        <v>-2.77</v>
+      </c>
+      <c r="E67" s="9">
+        <v>3.7</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5">
+      <c r="A68" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="B32" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C32" s="5">
-        <v>-24.67</v>
-      </c>
-      <c r="D32" s="5">
-        <v>-25.08</v>
-      </c>
-      <c r="E32" s="6">
-        <v>-0.41</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5">
-      <c r="A33" s="3" t="s">
+      <c r="B68" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C68" s="7">
+        <v>186</v>
+      </c>
+      <c r="D68" s="7">
+        <v>0.25</v>
+      </c>
+      <c r="E68" s="8">
+        <v>-185.75</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5">
+      <c r="A69" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="B33" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C33" s="5">
-        <v>-8.42</v>
-      </c>
-      <c r="D33" s="5">
-        <v>-9.140000000000001</v>
-      </c>
-      <c r="E33" s="6">
-        <v>-0.72</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5">
-      <c r="A34" s="3" t="s">
+      <c r="B69" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C69" s="7">
+        <v>-38.67</v>
+      </c>
+      <c r="D69" s="7">
+        <v>-55.32</v>
+      </c>
+      <c r="E69" s="8">
+        <v>-16.65</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5">
+      <c r="A70" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="B34" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C34" s="5">
-        <v>-5</v>
-      </c>
-      <c r="D34" s="5">
-        <v>-6.15</v>
-      </c>
-      <c r="E34" s="6">
-        <v>-1.15</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5">
-      <c r="A35" s="3" t="s">
+      <c r="B70" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C70" s="7">
+        <v>-20.59</v>
+      </c>
+      <c r="D70" s="7">
+        <v>-6.44</v>
+      </c>
+      <c r="E70" s="9">
+        <v>14.15</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5">
+      <c r="A71" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="B35" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C35" s="5">
-        <v>-9.1</v>
-      </c>
-      <c r="D35" s="5">
-        <v>-13.71</v>
-      </c>
-      <c r="E35" s="6">
-        <v>-4.61</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5">
-      <c r="A36" s="3" t="s">
+      <c r="B71" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C71" s="7">
+        <v>31.24</v>
+      </c>
+      <c r="D71" s="7">
+        <v>22.94</v>
+      </c>
+      <c r="E71" s="8">
+        <v>-8.300000000000001</v>
+      </c>
+    </row>
+    <row r="72" spans="1:5">
+      <c r="A72" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="B36" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C36" s="5">
-        <v>9.539999999999999</v>
-      </c>
-      <c r="D36" s="5">
-        <v>-1.6</v>
-      </c>
-      <c r="E36" s="6">
-        <v>-11.14</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5">
-      <c r="A37" s="3" t="s">
+      <c r="B72" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C72" s="7">
+        <v>18.7</v>
+      </c>
+      <c r="D72" s="7">
+        <v>26.19</v>
+      </c>
+      <c r="E72" s="9">
+        <v>7.49</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5">
+      <c r="A73" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="B37" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C37" s="5">
-        <v>-9.550000000000001</v>
-      </c>
-      <c r="D37" s="5">
-        <v>-11.95</v>
-      </c>
-      <c r="E37" s="6">
-        <v>-2.4</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5">
-      <c r="A38" s="3" t="s">
+      <c r="B73" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C73" s="7">
+        <v>80.8</v>
+      </c>
+      <c r="D73" s="7">
+        <v>-3.75</v>
+      </c>
+      <c r="E73" s="8">
+        <v>-84.55</v>
+      </c>
+    </row>
+    <row r="74" spans="1:5">
+      <c r="A74" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="B38" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C38" s="5">
-        <v>-10.53</v>
-      </c>
-      <c r="D38" s="5">
-        <v>-10.29</v>
-      </c>
-      <c r="E38" s="7">
-        <v>0.24</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5">
-      <c r="A39" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B39" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C39" s="5">
-        <v>-12.16</v>
-      </c>
-      <c r="D39" s="5">
-        <v>-13.59</v>
-      </c>
-      <c r="E39" s="6">
-        <v>-1.43</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5">
-      <c r="A40" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B40" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C40" s="5">
-        <v>-49.46</v>
-      </c>
-      <c r="D40" s="5">
-        <v>-49.63</v>
-      </c>
-      <c r="E40" s="6">
-        <v>-0.17</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5">
-      <c r="A41" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B41" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C41" s="5">
-        <v>-14.84</v>
-      </c>
-      <c r="D41" s="5">
-        <v>-14.54</v>
-      </c>
-      <c r="E41" s="7">
-        <v>0.3</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5">
-      <c r="A42" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="B42" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C42" s="5">
-        <v>-21.68</v>
-      </c>
-      <c r="D42" s="5">
-        <v>-22.34</v>
-      </c>
-      <c r="E42" s="6">
-        <v>-0.66</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5">
-      <c r="A43" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="B43" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C43" s="5">
-        <v>-21.28</v>
-      </c>
-      <c r="D43" s="5">
-        <v>-25.38</v>
-      </c>
-      <c r="E43" s="6">
-        <v>-4.1</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5">
-      <c r="A44" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="B44" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C44" s="5">
-        <v>-8.48</v>
-      </c>
-      <c r="D44" s="5">
-        <v>-16.16</v>
-      </c>
-      <c r="E44" s="6">
-        <v>-7.68</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5">
-      <c r="A45" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="B45" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C45" s="5">
-        <v>-31.98</v>
-      </c>
-      <c r="D45" s="5">
-        <v>-32.74</v>
-      </c>
-      <c r="E45" s="6">
-        <v>-0.76</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5">
-      <c r="A46" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="B46" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C46" s="5">
-        <v>-18.4</v>
-      </c>
-      <c r="D46" s="5">
-        <v>-16.88</v>
-      </c>
-      <c r="E46" s="7">
-        <v>1.52</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5">
-      <c r="A47" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B47" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C47" s="5">
-        <v>373.05</v>
-      </c>
-      <c r="D47" s="5">
-        <v>367</v>
-      </c>
-      <c r="E47" s="6">
-        <v>-6.05</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5">
-      <c r="A48" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B48" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C48" s="5">
-        <v>43.15</v>
-      </c>
-      <c r="D48" s="5">
-        <v>43.01</v>
-      </c>
-      <c r="E48" s="6">
-        <v>-0.14</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5">
-      <c r="A49" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B49" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C49" s="5">
-        <v>2879</v>
-      </c>
-      <c r="D49" s="5">
-        <v>2889.1</v>
-      </c>
-      <c r="E49" s="7">
-        <v>10.1</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5">
-      <c r="A50" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="B50" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C50" s="5">
-        <v>900.45</v>
-      </c>
-      <c r="D50" s="5">
-        <v>892.85</v>
-      </c>
-      <c r="E50" s="6">
-        <v>-7.6</v>
-      </c>
-    </row>
-    <row r="51" spans="1:5">
-      <c r="A51" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="B51" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C51" s="5">
-        <v>12.28</v>
-      </c>
-      <c r="D51" s="5">
-        <v>11.64</v>
-      </c>
-      <c r="E51" s="6">
-        <v>-0.64</v>
-      </c>
-    </row>
-    <row r="52" spans="1:5">
-      <c r="A52" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="B52" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C52" s="5">
-        <v>12.74</v>
-      </c>
-      <c r="D52" s="5">
-        <v>11.67</v>
-      </c>
-      <c r="E52" s="6">
-        <v>-1.07</v>
-      </c>
-    </row>
-    <row r="53" spans="1:5">
-      <c r="A53" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="B53" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C53" s="5">
-        <v>3951.5</v>
-      </c>
-      <c r="D53" s="5">
-        <v>3907.2</v>
-      </c>
-      <c r="E53" s="6">
-        <v>-44.3</v>
-      </c>
-    </row>
-    <row r="54" spans="1:5">
-      <c r="A54" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="B54" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C54" s="5">
-        <v>10650</v>
-      </c>
-      <c r="D54" s="5">
-        <v>10849</v>
-      </c>
-      <c r="E54" s="7">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="55" spans="1:5">
-      <c r="A55" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B55" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="C55" s="5">
-        <v>75</v>
-      </c>
-      <c r="D55" s="5">
-        <v>62</v>
-      </c>
-      <c r="E55" s="6">
-        <v>-13</v>
-      </c>
-    </row>
-    <row r="56" spans="1:5">
-      <c r="A56" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="B56" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="C56" s="5">
-        <v>62</v>
-      </c>
-      <c r="D56" s="5">
-        <v>75</v>
-      </c>
-      <c r="E56" s="7">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="57" spans="1:5">
-      <c r="A57" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B57" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C57" s="5">
-        <v>41.2</v>
-      </c>
-      <c r="D57" s="5">
-        <v>37.79</v>
-      </c>
-      <c r="E57" s="6">
-        <v>-3.41</v>
-      </c>
-    </row>
-    <row r="58" spans="1:5">
-      <c r="A58" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B58" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C58" s="5">
-        <v>31.87</v>
-      </c>
-      <c r="D58" s="5">
-        <v>31.45</v>
-      </c>
-      <c r="E58" s="6">
-        <v>-0.42</v>
-      </c>
-    </row>
-    <row r="59" spans="1:5">
-      <c r="A59" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B59" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C59" s="5">
-        <v>34.62</v>
-      </c>
-      <c r="D59" s="5">
-        <v>35.97</v>
-      </c>
-      <c r="E59" s="7">
-        <v>1.35</v>
-      </c>
-    </row>
-    <row r="60" spans="1:5">
-      <c r="A60" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="B60" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C60" s="5">
-        <v>38.64</v>
-      </c>
-      <c r="D60" s="5">
-        <v>36.99</v>
-      </c>
-      <c r="E60" s="6">
-        <v>-1.65</v>
-      </c>
-    </row>
-    <row r="61" spans="1:5">
-      <c r="A61" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="B61" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C61" s="5">
-        <v>34.48</v>
-      </c>
-      <c r="D61" s="5">
-        <v>28.85</v>
-      </c>
-      <c r="E61" s="6">
-        <v>-5.63</v>
-      </c>
-    </row>
-    <row r="62" spans="1:5">
-      <c r="A62" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="B62" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C62" s="5">
-        <v>65.19</v>
-      </c>
-      <c r="D62" s="5">
-        <v>52.19</v>
-      </c>
-      <c r="E62" s="6">
-        <v>-13</v>
-      </c>
-    </row>
-    <row r="63" spans="1:5">
-      <c r="A63" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="B63" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C63" s="5">
-        <v>41.01</v>
-      </c>
-      <c r="D63" s="5">
-        <v>37.74</v>
-      </c>
-      <c r="E63" s="6">
-        <v>-3.27</v>
-      </c>
-    </row>
-    <row r="64" spans="1:5">
-      <c r="A64" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="B64" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C64" s="5">
-        <v>43.06</v>
-      </c>
-      <c r="D64" s="5">
-        <v>48.74</v>
-      </c>
-      <c r="E64" s="7">
-        <v>5.68</v>
-      </c>
-    </row>
-    <row r="65" spans="1:5">
-      <c r="A65" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B65" s="3" t="s">
+      <c r="B74" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="C65" s="5">
-        <v>-59.52</v>
-      </c>
-      <c r="D65" s="5">
-        <v>-6.47</v>
-      </c>
-      <c r="E65" s="7">
-        <v>53.05</v>
-      </c>
-    </row>
-    <row r="66" spans="1:5">
-      <c r="A66" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B66" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C66" s="5">
-        <v>-49.79</v>
-      </c>
-      <c r="D66" s="5">
-        <v>186</v>
-      </c>
-      <c r="E66" s="7">
-        <v>235.79</v>
-      </c>
-    </row>
-    <row r="67" spans="1:5">
-      <c r="A67" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B67" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C67" s="5">
-        <v>-40.46</v>
-      </c>
-      <c r="D67" s="5">
-        <v>-38.67</v>
-      </c>
-      <c r="E67" s="7">
-        <v>1.79</v>
-      </c>
-    </row>
-    <row r="68" spans="1:5">
-      <c r="A68" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="B68" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C68" s="5">
-        <v>-51.51</v>
-      </c>
-      <c r="D68" s="5">
-        <v>-20.59</v>
-      </c>
-      <c r="E68" s="7">
-        <v>30.92</v>
-      </c>
-    </row>
-    <row r="69" spans="1:5">
-      <c r="A69" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="B69" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C69" s="5">
-        <v>-17.97</v>
-      </c>
-      <c r="D69" s="5">
-        <v>31.24</v>
-      </c>
-      <c r="E69" s="7">
-        <v>49.21</v>
-      </c>
-    </row>
-    <row r="70" spans="1:5">
-      <c r="A70" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="B70" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C70" s="5">
-        <v>183.03</v>
-      </c>
-      <c r="D70" s="5">
-        <v>18.7</v>
-      </c>
-      <c r="E70" s="6">
-        <v>-164.33</v>
-      </c>
-    </row>
-    <row r="71" spans="1:5">
-      <c r="A71" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="B71" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C71" s="5">
-        <v>-77.20999999999999</v>
-      </c>
-      <c r="D71" s="5">
-        <v>80.8</v>
-      </c>
-      <c r="E71" s="7">
-        <v>158.01</v>
-      </c>
-    </row>
-    <row r="72" spans="1:5">
-      <c r="A72" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="B72" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C72" s="5">
-        <v>113.02</v>
-      </c>
-      <c r="D72" s="5">
+      <c r="C74" s="7">
         <v>29.23</v>
       </c>
-      <c r="E72" s="6">
-        <v>-83.79000000000001</v>
+      <c r="D74" s="7">
+        <v>-43.23</v>
+      </c>
+      <c r="E74" s="8">
+        <v>-72.45999999999999</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A5:E5"/>
+    <mergeCell ref="A7:E7"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3127,60 +3252,60 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="28" customHeight="1">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="8" t="s">
-        <v>57</v>
-      </c>
-      <c r="C1" s="8" t="s">
-        <v>58</v>
-      </c>
-      <c r="D1" s="8" t="s">
-        <v>59</v>
-      </c>
-      <c r="E1" s="8" t="s">
-        <v>60</v>
-      </c>
-      <c r="F1" s="8" t="s">
-        <v>61</v>
-      </c>
-      <c r="G1" s="8" t="s">
-        <v>62</v>
-      </c>
-      <c r="H1" s="8" t="s">
-        <v>63</v>
-      </c>
-      <c r="I1" s="8" t="s">
-        <v>64</v>
+      <c r="B1" s="10" t="s">
+        <v>73</v>
+      </c>
+      <c r="C1" s="10" t="s">
+        <v>74</v>
+      </c>
+      <c r="D1" s="10" t="s">
+        <v>75</v>
+      </c>
+      <c r="E1" s="10" t="s">
+        <v>76</v>
+      </c>
+      <c r="F1" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="G1" s="10" t="s">
+        <v>78</v>
+      </c>
+      <c r="H1" s="10" t="s">
+        <v>79</v>
+      </c>
+      <c r="I1" s="10" t="s">
+        <v>80</v>
       </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="9" t="s">
+      <c r="A2" s="11" t="s">
         <v>45</v>
       </c>
-      <c r="B2" s="10">
-        <v>42.44</v>
-      </c>
-      <c r="C2" s="11">
+      <c r="B2" s="12">
+        <v>37.44</v>
+      </c>
+      <c r="C2" s="13">
         <v>8</v>
       </c>
-      <c r="D2" s="10">
-        <v>38.7</v>
-      </c>
-      <c r="E2" s="10">
-        <v>25</v>
-      </c>
-      <c r="F2" s="10">
-        <v>-8.5</v>
-      </c>
-      <c r="G2" s="10">
-        <v>-11</v>
-      </c>
-      <c r="H2" s="10">
+      <c r="D2" s="12">
+        <v>37.2</v>
+      </c>
+      <c r="E2" s="12">
+        <v>12.5</v>
+      </c>
+      <c r="F2" s="12">
+        <v>-8.800000000000001</v>
+      </c>
+      <c r="G2" s="12">
+        <v>-11.6</v>
+      </c>
+      <c r="H2" s="12">
         <v>56.1</v>
       </c>
-      <c r="I2" s="10">
+      <c r="I2" s="12">
         <v>0</v>
       </c>
     </row>
@@ -3282,55 +3407,55 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8">
-      <c r="A1" s="12" t="s">
+      <c r="A1" s="14" t="s">
         <v>37</v>
       </c>
-      <c r="B1" s="12" t="s">
+      <c r="B1" s="14" t="s">
         <v>43</v>
       </c>
-      <c r="C1" s="12" t="s">
+      <c r="C1" s="14" t="s">
         <v>40</v>
       </c>
-      <c r="D1" s="12" t="s">
+      <c r="D1" s="14" t="s">
         <v>39</v>
       </c>
-      <c r="E1" s="12" t="s">
+      <c r="E1" s="14" t="s">
         <v>44</v>
       </c>
-      <c r="F1" s="12" t="s">
+      <c r="F1" s="14" t="s">
         <v>41</v>
       </c>
-      <c r="G1" s="12" t="s">
+      <c r="G1" s="14" t="s">
         <v>42</v>
       </c>
-      <c r="H1" s="12" t="s">
+      <c r="H1" s="14" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="2" spans="1:8">
-      <c r="A2" s="13">
-        <v>0.2911</v>
-      </c>
-      <c r="B2" s="13">
-        <v>0.1609</v>
-      </c>
-      <c r="C2" s="13">
-        <v>0.1323</v>
-      </c>
-      <c r="D2" s="13">
-        <v>0.1111</v>
-      </c>
-      <c r="E2" s="13">
-        <v>0.0925</v>
-      </c>
-      <c r="F2" s="13">
-        <v>0.0248</v>
-      </c>
-      <c r="G2" s="13">
-        <v>-0.2951</v>
-      </c>
-      <c r="H2" s="13">
-        <v>-0.2968</v>
+      <c r="A2" s="15">
+        <v>0.2884</v>
+      </c>
+      <c r="B2" s="15">
+        <v>0.1633</v>
+      </c>
+      <c r="C2" s="15">
+        <v>0.1414</v>
+      </c>
+      <c r="D2" s="15">
+        <v>0.1157</v>
+      </c>
+      <c r="E2" s="15">
+        <v>0.0941</v>
+      </c>
+      <c r="F2" s="15">
+        <v>0.0238</v>
+      </c>
+      <c r="G2" s="15">
+        <v>-0.2981</v>
+      </c>
+      <c r="H2" s="15">
+        <v>-0.3038</v>
       </c>
     </row>
   </sheetData>

--- a/BIRLA_GROUP_Technical_Metrics.xlsx
+++ b/BIRLA_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="303" uniqueCount="81">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="276" uniqueCount="65">
   <si>
     <t>Symbol</t>
   </si>
@@ -175,55 +175,7 @@
     <t>▶  SIGNAL EVENTS (vs Previous Run)</t>
   </si>
   <si>
-    <t>Signal</t>
-  </si>
-  <si>
-    <t>Change</t>
-  </si>
-  <si>
-    <t>Direction</t>
-  </si>
-  <si>
-    <t>Prev Value</t>
-  </si>
-  <si>
-    <t>Curr Value</t>
-  </si>
-  <si>
-    <t>RSI Momentum</t>
-  </si>
-  <si>
-    <t>48.7 → 51.6</t>
-  </si>
-  <si>
-    <t>🟢 BULLISH</t>
-  </si>
-  <si>
-    <t>48.7</t>
-  </si>
-  <si>
-    <t>51.6</t>
-  </si>
-  <si>
-    <t>52.2 → 49.5</t>
-  </si>
-  <si>
-    <t>🔴 BEARISH</t>
-  </si>
-  <si>
-    <t>52.2</t>
-  </si>
-  <si>
-    <t>49.5</t>
-  </si>
-  <si>
-    <t>50 DMA &gt; 200 DMA</t>
-  </si>
-  <si>
-    <t>Yes → No</t>
-  </si>
-  <si>
-    <t>🔴 DEATH CROSS</t>
+    <t>No signal events detected since last run.</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -309,14 +261,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF9C0006"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF006100"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -349,13 +301,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -425,19 +377,17 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -808,8 +758,9 @@
     <col min="13" max="13" width="10.7109375" customWidth="1"/>
     <col min="14" max="14" width="11.7109375" customWidth="1"/>
     <col min="15" max="15" width="10.7109375" customWidth="1"/>
-    <col min="16" max="17" width="9.7109375" customWidth="1"/>
-    <col min="18" max="19" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="9.7109375" customWidth="1"/>
+    <col min="17" max="18" width="10.7109375" customWidth="1"/>
+    <col min="19" max="19" width="9.7109375" customWidth="1"/>
     <col min="20" max="20" width="22.7109375" customWidth="1"/>
     <col min="21" max="21" width="9.7109375" customWidth="1"/>
     <col min="22" max="22" width="10.7109375" customWidth="1"/>
@@ -949,10 +900,10 @@
         <v>45</v>
       </c>
       <c r="C2">
-        <v>357.2</v>
+        <v>347.25</v>
       </c>
       <c r="D2">
-        <v>-2.67</v>
+        <v>-2.79</v>
       </c>
       <c r="E2">
         <v>424.7</v>
@@ -961,46 +912,46 @@
         <v>292.25</v>
       </c>
       <c r="G2">
-        <v>-15.89</v>
+        <v>-18.24</v>
       </c>
       <c r="H2">
-        <v>22.22</v>
+        <v>18.82</v>
       </c>
       <c r="I2">
-        <v>-5.73</v>
+        <v>-9.16</v>
       </c>
       <c r="J2">
-        <v>-11.45</v>
+        <v>-12.53</v>
       </c>
       <c r="K2">
-        <v>-10.83</v>
+        <v>-11.47</v>
       </c>
       <c r="L2">
-        <v>19.07</v>
+        <v>16.02</v>
       </c>
       <c r="M2">
-        <v>28.84</v>
+        <v>28.98</v>
       </c>
       <c r="N2">
         <v>75</v>
       </c>
       <c r="O2">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="P2">
-        <v>371.78</v>
+        <v>364.78</v>
       </c>
       <c r="Q2">
-        <v>378.97</v>
+        <v>376.21</v>
       </c>
       <c r="R2">
-        <v>392.75</v>
+        <v>391.56</v>
       </c>
       <c r="S2">
-        <v>366.24</v>
+        <v>366.17</v>
       </c>
       <c r="T2">
-        <v>-2.47</v>
+        <v>-5.17</v>
       </c>
       <c r="U2" t="s">
         <v>46</v>
@@ -1015,43 +966,43 @@
         <v>1</v>
       </c>
       <c r="Y2">
-        <v>33.03</v>
+        <v>29.03</v>
       </c>
       <c r="Z2">
-        <v>-6.78</v>
+        <v>-8.460000000000001</v>
       </c>
       <c r="AA2">
-        <v>-5.62</v>
+        <v>-6.19</v>
       </c>
       <c r="AB2">
-        <v>-1.16</v>
+        <v>-2.27</v>
       </c>
       <c r="AC2">
-        <v>20.14</v>
+        <v>5.52</v>
       </c>
       <c r="AD2">
-        <v>45.22</v>
+        <v>23.68</v>
       </c>
       <c r="AE2">
-        <v>9.52</v>
+        <v>9.9</v>
       </c>
       <c r="AF2">
-        <v>-2.77</v>
+        <v>-36.1</v>
       </c>
       <c r="AG2">
-        <v>397.81</v>
+        <v>396.67</v>
       </c>
       <c r="AH2">
-        <v>360.13</v>
+        <v>355.75</v>
       </c>
       <c r="AI2">
-        <v>389.27</v>
+        <v>379.33</v>
       </c>
       <c r="AJ2" t="s">
         <v>48</v>
       </c>
       <c r="AK2">
-        <v>25.85</v>
+        <v>31.96</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1062,58 +1013,58 @@
         <v>45</v>
       </c>
       <c r="C3">
-        <v>41.34</v>
+        <v>39.77</v>
       </c>
       <c r="D3">
-        <v>-3.88</v>
+        <v>-3.8</v>
       </c>
       <c r="E3">
         <v>85.38</v>
       </c>
       <c r="F3">
-        <v>41.34</v>
+        <v>39.77</v>
       </c>
       <c r="G3">
-        <v>-51.58</v>
+        <v>-53.42</v>
       </c>
       <c r="H3">
         <v>0</v>
       </c>
       <c r="I3">
-        <v>-8.699999999999999</v>
+        <v>-11.35</v>
       </c>
       <c r="J3">
-        <v>-17.07</v>
+        <v>-19.2</v>
       </c>
       <c r="K3">
-        <v>-27.54</v>
+        <v>-29.02</v>
       </c>
       <c r="L3">
-        <v>-50.6</v>
+        <v>-51.67</v>
       </c>
       <c r="M3">
-        <v>-30.38</v>
+        <v>-30.71</v>
       </c>
       <c r="N3">
         <v>13</v>
       </c>
       <c r="O3">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="P3">
-        <v>43.44</v>
+        <v>42.42</v>
       </c>
       <c r="Q3">
-        <v>45.16</v>
+        <v>44.7</v>
       </c>
       <c r="R3">
-        <v>49.78</v>
+        <v>49.4</v>
       </c>
       <c r="S3">
-        <v>60.15</v>
+        <v>59.96</v>
       </c>
       <c r="T3">
-        <v>-31.28</v>
+        <v>-33.67</v>
       </c>
       <c r="U3" t="s">
         <v>46</v>
@@ -1128,43 +1079,43 @@
         <v>0</v>
       </c>
       <c r="Y3">
-        <v>26.9</v>
+        <v>23.47</v>
       </c>
       <c r="Z3">
-        <v>-2.05</v>
+        <v>-2.25</v>
       </c>
       <c r="AA3">
-        <v>-2.06</v>
+        <v>-2.1</v>
       </c>
       <c r="AB3">
-        <v>0.01</v>
+        <v>-0.15</v>
       </c>
       <c r="AC3">
-        <v>41.14</v>
+        <v>23.49</v>
       </c>
       <c r="AD3">
-        <v>61</v>
+        <v>42.96</v>
       </c>
       <c r="AE3">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="AF3">
-        <v>0.25</v>
+        <v>28.73</v>
       </c>
       <c r="AG3">
-        <v>49.32</v>
+        <v>49.08</v>
       </c>
       <c r="AH3">
-        <v>41</v>
+        <v>40.31</v>
       </c>
       <c r="AI3">
-        <v>47.15</v>
+        <v>45.56</v>
       </c>
       <c r="AJ3" t="s">
         <v>48</v>
       </c>
       <c r="AK3">
-        <v>31.65</v>
+        <v>35.67</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1175,10 +1126,10 @@
         <v>45</v>
       </c>
       <c r="C4">
-        <v>2894.4</v>
+        <v>2894</v>
       </c>
       <c r="D4">
-        <v>0.18</v>
+        <v>-0.01</v>
       </c>
       <c r="E4">
         <v>3380.5</v>
@@ -1187,46 +1138,46 @@
         <v>2531.1</v>
       </c>
       <c r="G4">
-        <v>-14.38</v>
+        <v>-14.39</v>
       </c>
       <c r="H4">
-        <v>14.35</v>
+        <v>14.34</v>
       </c>
       <c r="I4">
-        <v>0.74</v>
+        <v>0.28</v>
       </c>
       <c r="J4">
-        <v>-8.58</v>
+        <v>-7.49</v>
       </c>
       <c r="K4">
-        <v>-8.59</v>
+        <v>-7.04</v>
       </c>
       <c r="L4">
-        <v>1.21</v>
+        <v>2.04</v>
       </c>
       <c r="M4">
-        <v>11.57</v>
+        <v>11.62</v>
       </c>
       <c r="N4">
         <v>50</v>
       </c>
       <c r="O4">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="P4">
-        <v>2893.68</v>
+        <v>2895.3</v>
       </c>
       <c r="Q4">
-        <v>2977.01</v>
+        <v>2962.28</v>
       </c>
       <c r="R4">
-        <v>3153.12</v>
+        <v>3144.56</v>
       </c>
       <c r="S4">
-        <v>2981.96</v>
+        <v>2982.15</v>
       </c>
       <c r="T4">
-        <v>-2.94</v>
+        <v>-2.96</v>
       </c>
       <c r="U4" t="s">
         <v>46</v>
@@ -1241,34 +1192,34 @@
         <v>1</v>
       </c>
       <c r="Y4">
-        <v>36.71</v>
+        <v>36.68</v>
       </c>
       <c r="Z4">
-        <v>-81.43000000000001</v>
+        <v>-77.58</v>
       </c>
       <c r="AA4">
-        <v>-84.09999999999999</v>
+        <v>-82.79000000000001</v>
       </c>
       <c r="AB4">
-        <v>2.67</v>
+        <v>5.21</v>
       </c>
       <c r="AC4">
-        <v>87.01000000000001</v>
+        <v>91.83</v>
       </c>
       <c r="AD4">
-        <v>78.55</v>
+        <v>86.86</v>
       </c>
       <c r="AE4">
-        <v>63.18</v>
+        <v>61.77</v>
       </c>
       <c r="AF4">
-        <v>-55.32</v>
+        <v>-34.77</v>
       </c>
       <c r="AG4">
-        <v>3215.01</v>
+        <v>3180.84</v>
       </c>
       <c r="AH4">
-        <v>2739.01</v>
+        <v>2743.73</v>
       </c>
       <c r="AI4">
         <v>3050.83</v>
@@ -1277,7 +1228,7 @@
         <v>48</v>
       </c>
       <c r="AK4">
-        <v>58.27</v>
+        <v>56.43</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1288,58 +1239,58 @@
         <v>45</v>
       </c>
       <c r="C5">
-        <v>885.6</v>
+        <v>869.85</v>
       </c>
       <c r="D5">
-        <v>-0.8100000000000001</v>
+        <v>-1.78</v>
       </c>
       <c r="E5">
         <v>1149.7</v>
       </c>
       <c r="F5">
-        <v>772.8</v>
+        <v>774.65</v>
       </c>
       <c r="G5">
-        <v>-22.97</v>
+        <v>-24.34</v>
       </c>
       <c r="H5">
-        <v>14.6</v>
+        <v>12.29</v>
       </c>
       <c r="I5">
-        <v>0.35</v>
+        <v>-2.69</v>
       </c>
       <c r="J5">
-        <v>-9.74</v>
+        <v>-10.6</v>
       </c>
       <c r="K5">
-        <v>-6.78</v>
+        <v>-8.98</v>
       </c>
       <c r="L5">
-        <v>13.52</v>
+        <v>12.56</v>
       </c>
       <c r="M5">
-        <v>14.14</v>
+        <v>13.61</v>
       </c>
       <c r="N5">
         <v>62</v>
       </c>
       <c r="O5">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="P5">
-        <v>896.15</v>
+        <v>891.35</v>
       </c>
       <c r="Q5">
-        <v>924.29</v>
+        <v>917.59</v>
       </c>
       <c r="R5">
-        <v>981.16</v>
+        <v>977.5700000000001</v>
       </c>
       <c r="S5">
-        <v>983.6</v>
+        <v>983.3200000000001</v>
       </c>
       <c r="T5">
-        <v>-9.960000000000001</v>
+        <v>-11.54</v>
       </c>
       <c r="U5" t="s">
         <v>46</v>
@@ -1354,43 +1305,43 @@
         <v>0</v>
       </c>
       <c r="Y5">
-        <v>35.44</v>
+        <v>32.28</v>
       </c>
       <c r="Z5">
-        <v>-25.99</v>
+        <v>-26.86</v>
       </c>
       <c r="AA5">
-        <v>-25.86</v>
+        <v>-26.06</v>
       </c>
       <c r="AB5">
-        <v>-0.13</v>
+        <v>-0.8</v>
       </c>
       <c r="AC5">
-        <v>77.33</v>
+        <v>62.61</v>
       </c>
       <c r="AD5">
-        <v>82.31</v>
+        <v>76.16</v>
       </c>
       <c r="AE5">
-        <v>22.69</v>
+        <v>23.47</v>
       </c>
       <c r="AF5">
-        <v>-6.44</v>
+        <v>97.94</v>
       </c>
       <c r="AG5">
-        <v>997.71</v>
+        <v>984.64</v>
       </c>
       <c r="AH5">
-        <v>850.87</v>
+        <v>850.55</v>
       </c>
       <c r="AI5">
-        <v>946.48</v>
+        <v>933.28</v>
       </c>
       <c r="AJ5" t="s">
         <v>48</v>
       </c>
       <c r="AK5">
-        <v>46.38</v>
+        <v>48.5</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1401,10 +1352,10 @@
         <v>45</v>
       </c>
       <c r="C6">
-        <v>11.53</v>
+        <v>11.36</v>
       </c>
       <c r="D6">
-        <v>-0.95</v>
+        <v>-1.47</v>
       </c>
       <c r="E6">
         <v>15.6</v>
@@ -1413,46 +1364,46 @@
         <v>8.529999999999999</v>
       </c>
       <c r="G6">
-        <v>-26.09</v>
+        <v>-27.18</v>
       </c>
       <c r="H6">
-        <v>35.17</v>
+        <v>33.18</v>
       </c>
       <c r="I6">
-        <v>-9</v>
+        <v>-9.27</v>
       </c>
       <c r="J6">
-        <v>-16.69</v>
+        <v>-20.39</v>
       </c>
       <c r="K6">
-        <v>-14.84</v>
+        <v>-13.94</v>
       </c>
       <c r="L6">
-        <v>30.28</v>
+        <v>30.57</v>
       </c>
       <c r="M6">
-        <v>2.38</v>
+        <v>1.78</v>
       </c>
       <c r="N6">
         <v>87</v>
       </c>
       <c r="O6">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="P6">
-        <v>12.11</v>
+        <v>11.88</v>
       </c>
       <c r="Q6">
-        <v>12.96</v>
+        <v>12.8</v>
       </c>
       <c r="R6">
-        <v>13.82</v>
+        <v>13.79</v>
       </c>
       <c r="S6">
-        <v>12.31</v>
+        <v>12.3</v>
       </c>
       <c r="T6">
-        <v>-6.3</v>
+        <v>-7.67</v>
       </c>
       <c r="U6" t="s">
         <v>46</v>
@@ -1467,43 +1418,43 @@
         <v>1</v>
       </c>
       <c r="Y6">
-        <v>28</v>
+        <v>26.7</v>
       </c>
       <c r="Z6">
-        <v>-0.5600000000000001</v>
+        <v>-0.61</v>
       </c>
       <c r="AA6">
-        <v>-0.44</v>
+        <v>-0.47</v>
       </c>
       <c r="AB6">
-        <v>-0.12</v>
+        <v>-0.14</v>
       </c>
       <c r="AC6">
-        <v>5.86</v>
+        <v>0</v>
       </c>
       <c r="AD6">
-        <v>20.73</v>
+        <v>10.1</v>
       </c>
       <c r="AE6">
         <v>0.46</v>
       </c>
       <c r="AF6">
-        <v>22.94</v>
+        <v>22.48</v>
       </c>
       <c r="AG6">
-        <v>14.49</v>
+        <v>14.3</v>
       </c>
       <c r="AH6">
-        <v>11.43</v>
+        <v>11.29</v>
       </c>
       <c r="AI6">
-        <v>12.88</v>
+        <v>12.7</v>
       </c>
       <c r="AJ6" t="s">
         <v>48</v>
       </c>
       <c r="AK6">
-        <v>55.4</v>
+        <v>59.27</v>
       </c>
     </row>
     <row r="7" spans="1:37">
@@ -1514,10 +1465,10 @@
         <v>45</v>
       </c>
       <c r="C7">
-        <v>11.4</v>
+        <v>11.12</v>
       </c>
       <c r="D7">
-        <v>-2.31</v>
+        <v>-2.46</v>
       </c>
       <c r="E7">
         <v>13.92</v>
@@ -1526,25 +1477,25 @@
         <v>4.69</v>
       </c>
       <c r="G7">
-        <v>-18.1</v>
+        <v>-20.11</v>
       </c>
       <c r="H7">
-        <v>143.07</v>
+        <v>137.1</v>
       </c>
       <c r="I7">
-        <v>-1.81</v>
+        <v>-2.03</v>
       </c>
       <c r="J7">
-        <v>-2.23</v>
+        <v>-2.03</v>
       </c>
       <c r="K7">
-        <v>-5.71</v>
+        <v>-6.95</v>
       </c>
       <c r="L7">
-        <v>118.39</v>
+        <v>111.01</v>
       </c>
       <c r="M7">
-        <v>-29.81</v>
+        <v>-29.83</v>
       </c>
       <c r="N7">
         <v>99</v>
@@ -1553,19 +1504,19 @@
         <v>96</v>
       </c>
       <c r="P7">
-        <v>11.91</v>
+        <v>11.87</v>
       </c>
       <c r="Q7">
-        <v>11.25</v>
+        <v>11.23</v>
       </c>
       <c r="R7">
-        <v>11.46</v>
+        <v>11.44</v>
       </c>
       <c r="S7">
         <v>10.81</v>
       </c>
       <c r="T7">
-        <v>5.45</v>
+        <v>2.9</v>
       </c>
       <c r="U7" t="s">
         <v>46</v>
@@ -1580,34 +1531,34 @@
         <v>2</v>
       </c>
       <c r="Y7">
-        <v>49.5</v>
+        <v>46.81</v>
       </c>
       <c r="Z7">
-        <v>0.1</v>
+        <v>0.06</v>
       </c>
       <c r="AA7">
-        <v>-0.01</v>
+        <v>0</v>
       </c>
       <c r="AB7">
-        <v>0.11</v>
+        <v>0.06</v>
       </c>
       <c r="AC7">
-        <v>70.69</v>
+        <v>51.92</v>
       </c>
       <c r="AD7">
-        <v>83.95999999999999</v>
+        <v>69.78</v>
       </c>
       <c r="AE7">
-        <v>0.8</v>
+        <v>0.82</v>
       </c>
       <c r="AF7">
-        <v>26.19</v>
+        <v>6.56</v>
       </c>
       <c r="AG7">
-        <v>12.45</v>
+        <v>12.42</v>
       </c>
       <c r="AH7">
-        <v>10.05</v>
+        <v>10.04</v>
       </c>
       <c r="AI7">
         <v>10.86</v>
@@ -1616,7 +1567,7 @@
         <v>49</v>
       </c>
       <c r="AK7">
-        <v>29.49</v>
+        <v>26.84</v>
       </c>
     </row>
     <row r="8" spans="1:37">
@@ -1627,37 +1578,37 @@
         <v>45</v>
       </c>
       <c r="C8">
-        <v>3885.7</v>
+        <v>3789.3</v>
       </c>
       <c r="D8">
-        <v>-0.55</v>
+        <v>-2.48</v>
       </c>
       <c r="E8">
         <v>5809.5</v>
       </c>
       <c r="F8">
-        <v>3885.7</v>
+        <v>3789.3</v>
       </c>
       <c r="G8">
-        <v>-33.11</v>
+        <v>-34.77</v>
       </c>
       <c r="H8">
         <v>0</v>
       </c>
       <c r="I8">
-        <v>-2.61</v>
+        <v>-4.53</v>
       </c>
       <c r="J8">
-        <v>-3.51</v>
+        <v>-5.46</v>
       </c>
       <c r="K8">
-        <v>-10.72</v>
+        <v>-11.94</v>
       </c>
       <c r="L8">
-        <v>-27.55</v>
+        <v>-32.69</v>
       </c>
       <c r="M8">
-        <v>16.33</v>
+        <v>15.95</v>
       </c>
       <c r="N8">
         <v>25</v>
@@ -1666,19 +1617,19 @@
         <v>31</v>
       </c>
       <c r="P8">
-        <v>3939.58</v>
+        <v>3903.58</v>
       </c>
       <c r="Q8">
-        <v>3976.22</v>
+        <v>3963.59</v>
       </c>
       <c r="R8">
-        <v>4166.22</v>
+        <v>4154.2</v>
       </c>
       <c r="S8">
-        <v>4449.8</v>
+        <v>4442.9</v>
       </c>
       <c r="T8">
-        <v>-12.68</v>
+        <v>-14.71</v>
       </c>
       <c r="U8" t="s">
         <v>46</v>
@@ -1693,43 +1644,43 @@
         <v>0</v>
       </c>
       <c r="Y8">
-        <v>36.23</v>
+        <v>30.36</v>
       </c>
       <c r="Z8">
-        <v>-62.07</v>
+        <v>-70.81</v>
       </c>
       <c r="AA8">
-        <v>-65.81999999999999</v>
+        <v>-66.81999999999999</v>
       </c>
       <c r="AB8">
-        <v>3.75</v>
+        <v>-4</v>
       </c>
       <c r="AC8">
-        <v>51.42</v>
+        <v>29.34</v>
       </c>
       <c r="AD8">
-        <v>63.12</v>
+        <v>48.59</v>
       </c>
       <c r="AE8">
-        <v>93.86</v>
+        <v>96.94</v>
       </c>
       <c r="AF8">
-        <v>-3.75</v>
+        <v>-13.67</v>
       </c>
       <c r="AG8">
-        <v>4083.01</v>
+        <v>4094.67</v>
       </c>
       <c r="AH8">
-        <v>3869.42</v>
+        <v>3832.51</v>
       </c>
       <c r="AI8">
-        <v>4152.97</v>
+        <v>4109.12</v>
       </c>
       <c r="AJ8" t="s">
         <v>48</v>
       </c>
       <c r="AK8">
-        <v>26.11</v>
+        <v>29.69</v>
       </c>
     </row>
     <row r="9" spans="1:37">
@@ -1740,10 +1691,10 @@
         <v>45</v>
       </c>
       <c r="C9">
-        <v>10958</v>
+        <v>11050</v>
       </c>
       <c r="D9">
-        <v>1</v>
+        <v>0.84</v>
       </c>
       <c r="E9">
         <v>13052</v>
@@ -1752,46 +1703,46 @@
         <v>10362</v>
       </c>
       <c r="G9">
-        <v>-16.04</v>
+        <v>-15.34</v>
       </c>
       <c r="H9">
-        <v>5.75</v>
+        <v>6.64</v>
       </c>
       <c r="I9">
-        <v>1.51</v>
+        <v>1.73</v>
       </c>
       <c r="J9">
-        <v>-1.28</v>
+        <v>0.45</v>
       </c>
       <c r="K9">
-        <v>-7.86</v>
+        <v>-7.21</v>
       </c>
       <c r="L9">
-        <v>-11.33</v>
+        <v>-10.67</v>
       </c>
       <c r="M9">
-        <v>9.41</v>
+        <v>9.6</v>
       </c>
       <c r="N9">
         <v>38</v>
       </c>
       <c r="O9">
-        <v>55</v>
+        <v>61</v>
       </c>
       <c r="P9">
-        <v>10845.2</v>
+        <v>10882.8</v>
       </c>
       <c r="Q9">
-        <v>10826.8</v>
+        <v>10821.55</v>
       </c>
       <c r="R9">
-        <v>11131.52</v>
+        <v>11116.92</v>
       </c>
       <c r="S9">
-        <v>11647.84</v>
+        <v>11643.6</v>
       </c>
       <c r="T9">
-        <v>-5.92</v>
+        <v>-5.1</v>
       </c>
       <c r="U9" t="s">
         <v>46</v>
@@ -1806,34 +1757,34 @@
         <v>0</v>
       </c>
       <c r="Y9">
-        <v>51.59</v>
+        <v>53.92</v>
       </c>
       <c r="Z9">
-        <v>-82.56999999999999</v>
+        <v>-57.25</v>
       </c>
       <c r="AA9">
-        <v>-126.62</v>
+        <v>-112.74</v>
       </c>
       <c r="AB9">
-        <v>44.05</v>
+        <v>55.49</v>
       </c>
       <c r="AC9">
-        <v>84.76000000000001</v>
+        <v>98.14</v>
       </c>
       <c r="AD9">
-        <v>85.39</v>
+        <v>89.22</v>
       </c>
       <c r="AE9">
-        <v>260.89</v>
+        <v>259.97</v>
       </c>
       <c r="AF9">
-        <v>-43.23</v>
+        <v>-0.3</v>
       </c>
       <c r="AG9">
-        <v>11214.47</v>
+        <v>11193.01</v>
       </c>
       <c r="AH9">
-        <v>10439.13</v>
+        <v>10450.09</v>
       </c>
       <c r="AI9">
         <v>11169.72</v>
@@ -1842,7 +1793,7 @@
         <v>48</v>
       </c>
       <c r="AK9">
-        <v>32.3</v>
+        <v>32.71</v>
       </c>
     </row>
   </sheetData>
@@ -1983,7 +1934,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F74"/>
+  <dimension ref="A1:F70"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -2003,1236 +1954,1127 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="3" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6">
+      <c r="A5" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="B5" s="2"/>
+      <c r="C5" s="2"/>
+      <c r="D5" s="2"/>
+      <c r="E5" s="2"/>
+    </row>
+    <row r="6" spans="1:6">
+      <c r="A6" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="D2" s="3" t="s">
+      <c r="B6" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="E2" s="3" t="s">
+      <c r="C6" s="4" t="s">
         <v>54</v>
       </c>
-      <c r="F2" s="3" t="s">
+      <c r="D6" s="4" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="3" spans="1:6">
-      <c r="A3" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="B3" s="4" t="s">
+      <c r="E6" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="C3" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="D3" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="E3" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="F3" s="4" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6">
-      <c r="A4" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B4" s="5" t="s">
-        <v>56</v>
-      </c>
-      <c r="C4" s="5" t="s">
-        <v>61</v>
-      </c>
-      <c r="D4" s="5" t="s">
-        <v>62</v>
-      </c>
-      <c r="E4" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="F4" s="5" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6">
-      <c r="A5" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B5" s="5" t="s">
-        <v>65</v>
-      </c>
-      <c r="C5" s="5" t="s">
-        <v>66</v>
-      </c>
-      <c r="D5" s="5" t="s">
-        <v>67</v>
-      </c>
-      <c r="E5" s="5" t="s">
-        <v>47</v>
-      </c>
-      <c r="F5" s="5" t="s">
-        <v>46</v>
-      </c>
     </row>
     <row r="7" spans="1:6">
-      <c r="A7" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="B7" s="2"/>
-      <c r="C7" s="2"/>
-      <c r="D7" s="2"/>
-      <c r="E7" s="2"/>
+      <c r="A7" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C7" s="5">
+        <v>-11.45</v>
+      </c>
+      <c r="D7" s="5">
+        <v>-12.53</v>
+      </c>
+      <c r="E7" s="6">
+        <v>-1.08</v>
+      </c>
     </row>
     <row r="8" spans="1:6">
       <c r="A8" s="3" t="s">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="D8" s="3" t="s">
-        <v>71</v>
-      </c>
-      <c r="E8" s="3" t="s">
-        <v>72</v>
+        <v>9</v>
+      </c>
+      <c r="C8" s="5">
+        <v>-17.07</v>
+      </c>
+      <c r="D8" s="5">
+        <v>-19.2</v>
+      </c>
+      <c r="E8" s="6">
+        <v>-2.13</v>
       </c>
     </row>
     <row r="9" spans="1:6">
-      <c r="A9" s="6" t="s">
+      <c r="A9" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C9" s="5">
+        <v>-8.58</v>
+      </c>
+      <c r="D9" s="5">
+        <v>-7.49</v>
+      </c>
+      <c r="E9" s="7">
+        <v>1.09</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C10" s="5">
+        <v>-9.74</v>
+      </c>
+      <c r="D10" s="5">
+        <v>-10.6</v>
+      </c>
+      <c r="E10" s="6">
+        <v>-0.86</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C11" s="5">
+        <v>-16.69</v>
+      </c>
+      <c r="D11" s="5">
+        <v>-20.39</v>
+      </c>
+      <c r="E11" s="6">
+        <v>-3.7</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C12" s="5">
+        <v>-2.23</v>
+      </c>
+      <c r="D12" s="5">
+        <v>-2.03</v>
+      </c>
+      <c r="E12" s="7">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="A13" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C13" s="5">
+        <v>-3.51</v>
+      </c>
+      <c r="D13" s="5">
+        <v>-5.46</v>
+      </c>
+      <c r="E13" s="6">
+        <v>-1.95</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C14" s="5">
+        <v>-1.28</v>
+      </c>
+      <c r="D14" s="5">
+        <v>0.45</v>
+      </c>
+      <c r="E14" s="7">
+        <v>1.73</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="A15" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B9" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C9" s="7">
-        <v>-10.5</v>
-      </c>
-      <c r="D9" s="7">
-        <v>-11.45</v>
-      </c>
-      <c r="E9" s="8">
-        <v>-0.95</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10" s="6" t="s">
+      <c r="B15" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C15" s="5">
+        <v>-5.73</v>
+      </c>
+      <c r="D15" s="5">
+        <v>-9.16</v>
+      </c>
+      <c r="E15" s="6">
+        <v>-3.43</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="A16" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B10" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C10" s="7">
-        <v>-14.25</v>
-      </c>
-      <c r="D10" s="7">
-        <v>-17.07</v>
-      </c>
-      <c r="E10" s="8">
-        <v>-2.82</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11" s="6" t="s">
+      <c r="B16" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C16" s="5">
+        <v>-8.699999999999999</v>
+      </c>
+      <c r="D16" s="5">
+        <v>-11.35</v>
+      </c>
+      <c r="E16" s="6">
+        <v>-2.65</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B11" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C11" s="7">
-        <v>-9.970000000000001</v>
-      </c>
-      <c r="D11" s="7">
-        <v>-8.58</v>
-      </c>
-      <c r="E11" s="9">
-        <v>1.39</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12" s="6" t="s">
+      <c r="B17" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C17" s="5">
+        <v>0.74</v>
+      </c>
+      <c r="D17" s="5">
+        <v>0.28</v>
+      </c>
+      <c r="E17" s="6">
+        <v>-0.46</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="B12" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C12" s="7">
-        <v>-9.49</v>
-      </c>
-      <c r="D12" s="7">
-        <v>-9.74</v>
-      </c>
-      <c r="E12" s="8">
-        <v>-0.25</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13" s="6" t="s">
+      <c r="B18" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C18" s="5">
+        <v>0.35</v>
+      </c>
+      <c r="D18" s="5">
+        <v>-2.69</v>
+      </c>
+      <c r="E18" s="6">
+        <v>-3.04</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="B13" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C13" s="7">
-        <v>-16.38</v>
-      </c>
-      <c r="D13" s="7">
-        <v>-16.69</v>
-      </c>
-      <c r="E13" s="8">
-        <v>-0.31</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14" s="6" t="s">
+      <c r="B19" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C19" s="5">
+        <v>-9</v>
+      </c>
+      <c r="D19" s="5">
+        <v>-9.27</v>
+      </c>
+      <c r="E19" s="6">
+        <v>-0.27</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="B14" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C14" s="7">
-        <v>-2.26</v>
-      </c>
-      <c r="D14" s="7">
-        <v>-2.23</v>
-      </c>
-      <c r="E14" s="9">
-        <v>0.03</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15" s="6" t="s">
+      <c r="B20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C20" s="5">
+        <v>-1.81</v>
+      </c>
+      <c r="D20" s="5">
+        <v>-2.03</v>
+      </c>
+      <c r="E20" s="6">
+        <v>-0.22</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="B15" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C15" s="7">
-        <v>-3.93</v>
-      </c>
-      <c r="D15" s="7">
-        <v>-3.51</v>
-      </c>
-      <c r="E15" s="9">
-        <v>0.42</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16" s="6" t="s">
+      <c r="B21" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C21" s="5">
+        <v>-2.61</v>
+      </c>
+      <c r="D21" s="5">
+        <v>-4.53</v>
+      </c>
+      <c r="E21" s="6">
+        <v>-1.92</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="B16" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C16" s="7">
-        <v>-1.5</v>
-      </c>
-      <c r="D16" s="7">
-        <v>-1.28</v>
-      </c>
-      <c r="E16" s="9">
+      <c r="B22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C22" s="5">
+        <v>1.51</v>
+      </c>
+      <c r="D22" s="5">
+        <v>1.73</v>
+      </c>
+      <c r="E22" s="7">
         <v>0.22</v>
       </c>
     </row>
-    <row r="17" spans="1:5">
-      <c r="A17" s="6" t="s">
+    <row r="23" spans="1:5">
+      <c r="A23" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B17" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C17" s="7">
-        <v>-4.59</v>
-      </c>
-      <c r="D17" s="7">
-        <v>-5.73</v>
-      </c>
-      <c r="E17" s="8">
-        <v>-1.14</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5">
-      <c r="A18" s="6" t="s">
+      <c r="B23" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C23" s="5">
+        <v>19.07</v>
+      </c>
+      <c r="D23" s="5">
+        <v>16.02</v>
+      </c>
+      <c r="E23" s="6">
+        <v>-3.05</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B18" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C18" s="7">
-        <v>-3.95</v>
-      </c>
-      <c r="D18" s="7">
-        <v>-8.699999999999999</v>
-      </c>
-      <c r="E18" s="8">
-        <v>-4.75</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5">
-      <c r="A19" s="6" t="s">
+      <c r="B24" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C24" s="5">
+        <v>-50.6</v>
+      </c>
+      <c r="D24" s="5">
+        <v>-51.67</v>
+      </c>
+      <c r="E24" s="6">
+        <v>-1.07</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B19" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C19" s="7">
-        <v>-0.79</v>
-      </c>
-      <c r="D19" s="7">
-        <v>0.74</v>
-      </c>
-      <c r="E19" s="9">
-        <v>1.53</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5">
-      <c r="A20" s="6" t="s">
+      <c r="B25" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C25" s="5">
+        <v>1.21</v>
+      </c>
+      <c r="D25" s="5">
+        <v>2.04</v>
+      </c>
+      <c r="E25" s="7">
+        <v>0.83</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="B20" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C20" s="7">
-        <v>-1.04</v>
-      </c>
-      <c r="D20" s="7">
-        <v>0.35</v>
-      </c>
-      <c r="E20" s="9">
-        <v>1.39</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5">
-      <c r="A21" s="6" t="s">
+      <c r="B26" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C26" s="5">
+        <v>13.52</v>
+      </c>
+      <c r="D26" s="5">
+        <v>12.56</v>
+      </c>
+      <c r="E26" s="6">
+        <v>-0.96</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="B21" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C21" s="7">
-        <v>-9.06</v>
-      </c>
-      <c r="D21" s="7">
-        <v>-9</v>
-      </c>
-      <c r="E21" s="9">
-        <v>0.06</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5">
-      <c r="A22" s="6" t="s">
+      <c r="B27" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C27" s="5">
+        <v>30.28</v>
+      </c>
+      <c r="D27" s="5">
+        <v>30.57</v>
+      </c>
+      <c r="E27" s="7">
+        <v>0.29</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="B22" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C22" s="7">
-        <v>2.01</v>
-      </c>
-      <c r="D22" s="7">
-        <v>-1.81</v>
-      </c>
-      <c r="E22" s="8">
-        <v>-3.82</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5">
-      <c r="A23" s="6" t="s">
+      <c r="B28" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C28" s="5">
+        <v>118.39</v>
+      </c>
+      <c r="D28" s="5">
+        <v>111.01</v>
+      </c>
+      <c r="E28" s="6">
+        <v>-7.38</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="B23" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C23" s="7">
-        <v>-1.07</v>
-      </c>
-      <c r="D23" s="7">
-        <v>-2.61</v>
-      </c>
-      <c r="E23" s="8">
-        <v>-1.54</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5">
-      <c r="A24" s="6" t="s">
+      <c r="B29" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C29" s="5">
+        <v>-27.55</v>
+      </c>
+      <c r="D29" s="5">
+        <v>-32.69</v>
+      </c>
+      <c r="E29" s="6">
+        <v>-5.14</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="B24" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C24" s="7">
-        <v>0.92</v>
-      </c>
-      <c r="D24" s="7">
-        <v>1.51</v>
-      </c>
-      <c r="E24" s="9">
-        <v>0.59</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5">
-      <c r="A25" s="6" t="s">
+      <c r="B30" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C30" s="5">
+        <v>-11.33</v>
+      </c>
+      <c r="D30" s="5">
+        <v>-10.67</v>
+      </c>
+      <c r="E30" s="7">
+        <v>0.66</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5">
+      <c r="A31" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B25" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C25" s="7">
-        <v>20.92</v>
-      </c>
-      <c r="D25" s="7">
-        <v>19.07</v>
-      </c>
-      <c r="E25" s="8">
-        <v>-1.85</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5">
-      <c r="A26" s="6" t="s">
+      <c r="B31" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C31" s="5">
+        <v>-10.83</v>
+      </c>
+      <c r="D31" s="5">
+        <v>-11.47</v>
+      </c>
+      <c r="E31" s="6">
+        <v>-0.64</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5">
+      <c r="A32" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B26" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C26" s="7">
-        <v>-48.46</v>
-      </c>
-      <c r="D26" s="7">
-        <v>-50.6</v>
-      </c>
-      <c r="E26" s="8">
-        <v>-2.14</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5">
-      <c r="A27" s="6" t="s">
+      <c r="B32" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C32" s="5">
+        <v>-27.54</v>
+      </c>
+      <c r="D32" s="5">
+        <v>-29.02</v>
+      </c>
+      <c r="E32" s="6">
+        <v>-1.48</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5">
+      <c r="A33" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B27" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C27" s="7">
-        <v>2.57</v>
-      </c>
-      <c r="D27" s="7">
-        <v>1.21</v>
-      </c>
-      <c r="E27" s="8">
-        <v>-1.36</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5">
-      <c r="A28" s="6" t="s">
+      <c r="B33" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C33" s="5">
+        <v>-8.59</v>
+      </c>
+      <c r="D33" s="5">
+        <v>-7.04</v>
+      </c>
+      <c r="E33" s="7">
+        <v>1.55</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5">
+      <c r="A34" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="B28" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C28" s="7">
-        <v>16.83</v>
-      </c>
-      <c r="D28" s="7">
-        <v>13.52</v>
-      </c>
-      <c r="E28" s="8">
-        <v>-3.31</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5">
-      <c r="A29" s="6" t="s">
+      <c r="B34" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C34" s="5">
+        <v>-6.78</v>
+      </c>
+      <c r="D34" s="5">
+        <v>-8.98</v>
+      </c>
+      <c r="E34" s="6">
+        <v>-2.2</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5">
+      <c r="A35" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="B29" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C29" s="7">
+      <c r="B35" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C35" s="5">
+        <v>-14.84</v>
+      </c>
+      <c r="D35" s="5">
+        <v>-13.94</v>
+      </c>
+      <c r="E35" s="7">
+        <v>0.9</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5">
+      <c r="A36" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B36" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C36" s="5">
+        <v>-5.71</v>
+      </c>
+      <c r="D36" s="5">
+        <v>-6.95</v>
+      </c>
+      <c r="E36" s="6">
+        <v>-1.24</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5">
+      <c r="A37" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="B37" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C37" s="5">
+        <v>-10.72</v>
+      </c>
+      <c r="D37" s="5">
+        <v>-11.94</v>
+      </c>
+      <c r="E37" s="6">
+        <v>-1.22</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5">
+      <c r="A38" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="B38" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C38" s="5">
+        <v>-7.86</v>
+      </c>
+      <c r="D38" s="5">
+        <v>-7.21</v>
+      </c>
+      <c r="E38" s="7">
+        <v>0.65</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5">
+      <c r="A39" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B39" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C39" s="5">
+        <v>-15.89</v>
+      </c>
+      <c r="D39" s="5">
+        <v>-18.24</v>
+      </c>
+      <c r="E39" s="6">
+        <v>-2.35</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5">
+      <c r="A40" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B40" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C40" s="5">
+        <v>-51.58</v>
+      </c>
+      <c r="D40" s="5">
+        <v>-53.42</v>
+      </c>
+      <c r="E40" s="6">
+        <v>-1.84</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5">
+      <c r="A41" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B41" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C41" s="5">
+        <v>-14.38</v>
+      </c>
+      <c r="D41" s="5">
+        <v>-14.39</v>
+      </c>
+      <c r="E41" s="6">
+        <v>-0.01</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5">
+      <c r="A42" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B42" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C42" s="5">
+        <v>-22.97</v>
+      </c>
+      <c r="D42" s="5">
+        <v>-24.34</v>
+      </c>
+      <c r="E42" s="6">
+        <v>-1.37</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5">
+      <c r="A43" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B43" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C43" s="5">
+        <v>-26.09</v>
+      </c>
+      <c r="D43" s="5">
+        <v>-27.18</v>
+      </c>
+      <c r="E43" s="6">
+        <v>-1.09</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5">
+      <c r="A44" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B44" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C44" s="5">
+        <v>-18.1</v>
+      </c>
+      <c r="D44" s="5">
+        <v>-20.11</v>
+      </c>
+      <c r="E44" s="6">
+        <v>-2.01</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5">
+      <c r="A45" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="B45" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C45" s="5">
+        <v>-33.11</v>
+      </c>
+      <c r="D45" s="5">
+        <v>-34.77</v>
+      </c>
+      <c r="E45" s="6">
+        <v>-1.66</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5">
+      <c r="A46" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="B46" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C46" s="5">
+        <v>-16.04</v>
+      </c>
+      <c r="D46" s="5">
+        <v>-15.34</v>
+      </c>
+      <c r="E46" s="7">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5">
+      <c r="A47" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B47" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C47" s="5">
+        <v>357.2</v>
+      </c>
+      <c r="D47" s="5">
+        <v>347.25</v>
+      </c>
+      <c r="E47" s="6">
+        <v>-9.949999999999999</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5">
+      <c r="A48" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B48" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C48" s="5">
+        <v>41.34</v>
+      </c>
+      <c r="D48" s="5">
+        <v>39.77</v>
+      </c>
+      <c r="E48" s="6">
+        <v>-1.57</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5">
+      <c r="A49" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B49" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C49" s="5">
+        <v>2894.4</v>
+      </c>
+      <c r="D49" s="5">
+        <v>2894</v>
+      </c>
+      <c r="E49" s="6">
+        <v>-0.4</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5">
+      <c r="A50" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B50" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C50" s="5">
+        <v>885.6</v>
+      </c>
+      <c r="D50" s="5">
+        <v>869.85</v>
+      </c>
+      <c r="E50" s="6">
+        <v>-15.75</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5">
+      <c r="A51" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B51" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C51" s="5">
+        <v>11.53</v>
+      </c>
+      <c r="D51" s="5">
+        <v>11.36</v>
+      </c>
+      <c r="E51" s="6">
+        <v>-0.17</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5">
+      <c r="A52" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B52" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C52" s="5">
+        <v>11.4</v>
+      </c>
+      <c r="D52" s="5">
+        <v>11.12</v>
+      </c>
+      <c r="E52" s="6">
+        <v>-0.28</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5">
+      <c r="A53" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="B53" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C53" s="5">
+        <v>3885.7</v>
+      </c>
+      <c r="D53" s="5">
+        <v>3789.3</v>
+      </c>
+      <c r="E53" s="6">
+        <v>-96.40000000000001</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5">
+      <c r="A54" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="B54" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C54" s="5">
+        <v>10958</v>
+      </c>
+      <c r="D54" s="5">
+        <v>11050</v>
+      </c>
+      <c r="E54" s="7">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5">
+      <c r="A55" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B55" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C55" s="5">
         <v>33.03</v>
       </c>
-      <c r="D29" s="7">
-        <v>30.28</v>
-      </c>
-      <c r="E29" s="8">
-        <v>-2.75</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5">
-      <c r="A30" s="6" t="s">
+      <c r="D55" s="5">
+        <v>29.03</v>
+      </c>
+      <c r="E55" s="6">
+        <v>-4</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5">
+      <c r="A56" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B56" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C56" s="5">
+        <v>26.9</v>
+      </c>
+      <c r="D56" s="5">
+        <v>23.47</v>
+      </c>
+      <c r="E56" s="6">
+        <v>-3.43</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5">
+      <c r="A57" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B57" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C57" s="5">
+        <v>36.71</v>
+      </c>
+      <c r="D57" s="5">
+        <v>36.68</v>
+      </c>
+      <c r="E57" s="6">
+        <v>-0.03</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5">
+      <c r="A58" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B58" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C58" s="5">
+        <v>35.44</v>
+      </c>
+      <c r="D58" s="5">
+        <v>32.28</v>
+      </c>
+      <c r="E58" s="6">
+        <v>-3.16</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5">
+      <c r="A59" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B59" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C59" s="5">
+        <v>28</v>
+      </c>
+      <c r="D59" s="5">
+        <v>26.7</v>
+      </c>
+      <c r="E59" s="6">
+        <v>-1.3</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5">
+      <c r="A60" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="B30" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C30" s="7">
-        <v>123.56</v>
-      </c>
-      <c r="D30" s="7">
-        <v>118.39</v>
-      </c>
-      <c r="E30" s="8">
-        <v>-5.17</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5">
-      <c r="A31" s="6" t="s">
+      <c r="B60" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C60" s="5">
+        <v>49.5</v>
+      </c>
+      <c r="D60" s="5">
+        <v>46.81</v>
+      </c>
+      <c r="E60" s="6">
+        <v>-2.69</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5">
+      <c r="A61" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="B31" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C31" s="7">
-        <v>-25.9</v>
-      </c>
-      <c r="D31" s="7">
-        <v>-27.55</v>
-      </c>
-      <c r="E31" s="8">
-        <v>-1.65</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5">
-      <c r="A32" s="6" t="s">
+      <c r="B61" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C61" s="5">
+        <v>36.23</v>
+      </c>
+      <c r="D61" s="5">
+        <v>30.36</v>
+      </c>
+      <c r="E61" s="6">
+        <v>-5.87</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5">
+      <c r="A62" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="B32" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C32" s="7">
-        <v>-11.88</v>
-      </c>
-      <c r="D32" s="7">
-        <v>-11.33</v>
-      </c>
-      <c r="E32" s="9">
-        <v>0.55</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5">
-      <c r="A33" s="6" t="s">
+      <c r="B62" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C62" s="5">
+        <v>51.59</v>
+      </c>
+      <c r="D62" s="5">
+        <v>53.92</v>
+      </c>
+      <c r="E62" s="7">
+        <v>2.33</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5">
+      <c r="A63" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B33" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C33" s="7">
-        <v>-10.28</v>
-      </c>
-      <c r="D33" s="7">
-        <v>-10.83</v>
-      </c>
-      <c r="E33" s="8">
-        <v>-0.55</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5">
-      <c r="A34" s="6" t="s">
+      <c r="B63" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C63" s="5">
+        <v>-2.77</v>
+      </c>
+      <c r="D63" s="5">
+        <v>-36.1</v>
+      </c>
+      <c r="E63" s="6">
+        <v>-33.33</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5">
+      <c r="A64" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B34" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C34" s="7">
-        <v>-25.08</v>
-      </c>
-      <c r="D34" s="7">
-        <v>-27.54</v>
-      </c>
-      <c r="E34" s="8">
-        <v>-2.46</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5">
-      <c r="A35" s="6" t="s">
+      <c r="B64" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C64" s="5">
+        <v>0.25</v>
+      </c>
+      <c r="D64" s="5">
+        <v>28.73</v>
+      </c>
+      <c r="E64" s="7">
+        <v>28.48</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5">
+      <c r="A65" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B35" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C35" s="7">
-        <v>-9.140000000000001</v>
-      </c>
-      <c r="D35" s="7">
-        <v>-8.59</v>
-      </c>
-      <c r="E35" s="9">
-        <v>0.55</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5">
-      <c r="A36" s="6" t="s">
+      <c r="B65" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C65" s="5">
+        <v>-55.32</v>
+      </c>
+      <c r="D65" s="5">
+        <v>-34.77</v>
+      </c>
+      <c r="E65" s="7">
+        <v>20.55</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5">
+      <c r="A66" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="B36" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C36" s="7">
-        <v>-6.15</v>
-      </c>
-      <c r="D36" s="7">
-        <v>-6.78</v>
-      </c>
-      <c r="E36" s="8">
-        <v>-0.63</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5">
-      <c r="A37" s="6" t="s">
+      <c r="B66" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C66" s="5">
+        <v>-6.44</v>
+      </c>
+      <c r="D66" s="5">
+        <v>97.94</v>
+      </c>
+      <c r="E66" s="7">
+        <v>104.38</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5">
+      <c r="A67" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="B37" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C37" s="7">
-        <v>-13.71</v>
-      </c>
-      <c r="D37" s="7">
-        <v>-14.84</v>
-      </c>
-      <c r="E37" s="8">
-        <v>-1.13</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5">
-      <c r="A38" s="6" t="s">
+      <c r="B67" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C67" s="5">
+        <v>22.94</v>
+      </c>
+      <c r="D67" s="5">
+        <v>22.48</v>
+      </c>
+      <c r="E67" s="6">
+        <v>-0.46</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5">
+      <c r="A68" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="B38" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C38" s="7">
-        <v>-1.6</v>
-      </c>
-      <c r="D38" s="7">
-        <v>-5.71</v>
-      </c>
-      <c r="E38" s="8">
-        <v>-4.11</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5">
-      <c r="A39" s="6" t="s">
+      <c r="B68" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C68" s="5">
+        <v>26.19</v>
+      </c>
+      <c r="D68" s="5">
+        <v>6.56</v>
+      </c>
+      <c r="E68" s="6">
+        <v>-19.63</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5">
+      <c r="A69" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="B39" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C39" s="7">
-        <v>-11.95</v>
-      </c>
-      <c r="D39" s="7">
-        <v>-10.72</v>
-      </c>
-      <c r="E39" s="9">
-        <v>1.23</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5">
-      <c r="A40" s="6" t="s">
+      <c r="B69" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C69" s="5">
+        <v>-3.75</v>
+      </c>
+      <c r="D69" s="5">
+        <v>-13.67</v>
+      </c>
+      <c r="E69" s="6">
+        <v>-9.92</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5">
+      <c r="A70" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="B40" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C40" s="7">
-        <v>-10.29</v>
-      </c>
-      <c r="D40" s="7">
-        <v>-7.86</v>
-      </c>
-      <c r="E40" s="9">
-        <v>2.43</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5">
-      <c r="A41" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="B41" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C41" s="7">
-        <v>-13.59</v>
-      </c>
-      <c r="D41" s="7">
-        <v>-15.89</v>
-      </c>
-      <c r="E41" s="8">
-        <v>-2.3</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5">
-      <c r="A42" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="B42" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C42" s="7">
-        <v>-49.63</v>
-      </c>
-      <c r="D42" s="7">
-        <v>-51.58</v>
-      </c>
-      <c r="E42" s="8">
-        <v>-1.95</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5">
-      <c r="A43" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="B43" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C43" s="7">
-        <v>-14.54</v>
-      </c>
-      <c r="D43" s="7">
-        <v>-14.38</v>
-      </c>
-      <c r="E43" s="9">
-        <v>0.16</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5">
-      <c r="A44" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="B44" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C44" s="7">
-        <v>-22.34</v>
-      </c>
-      <c r="D44" s="7">
-        <v>-22.97</v>
-      </c>
-      <c r="E44" s="8">
-        <v>-0.63</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5">
-      <c r="A45" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="B45" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C45" s="7">
-        <v>-25.38</v>
-      </c>
-      <c r="D45" s="7">
-        <v>-26.09</v>
-      </c>
-      <c r="E45" s="8">
-        <v>-0.71</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5">
-      <c r="A46" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="B46" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C46" s="7">
-        <v>-16.16</v>
-      </c>
-      <c r="D46" s="7">
-        <v>-18.1</v>
-      </c>
-      <c r="E46" s="8">
-        <v>-1.94</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5">
-      <c r="A47" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="B47" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C47" s="7">
-        <v>-32.74</v>
-      </c>
-      <c r="D47" s="7">
-        <v>-33.11</v>
-      </c>
-      <c r="E47" s="8">
-        <v>-0.37</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5">
-      <c r="A48" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="B48" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C48" s="7">
-        <v>-16.88</v>
-      </c>
-      <c r="D48" s="7">
-        <v>-16.04</v>
-      </c>
-      <c r="E48" s="9">
-        <v>0.84</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5">
-      <c r="A49" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="B49" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C49" s="7">
-        <v>367</v>
-      </c>
-      <c r="D49" s="7">
-        <v>357.2</v>
-      </c>
-      <c r="E49" s="8">
-        <v>-9.800000000000001</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5">
-      <c r="A50" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="B50" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C50" s="7">
-        <v>43.01</v>
-      </c>
-      <c r="D50" s="7">
-        <v>41.34</v>
-      </c>
-      <c r="E50" s="8">
-        <v>-1.67</v>
-      </c>
-    </row>
-    <row r="51" spans="1:5">
-      <c r="A51" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="B51" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C51" s="7">
-        <v>2889.1</v>
-      </c>
-      <c r="D51" s="7">
-        <v>2894.4</v>
-      </c>
-      <c r="E51" s="9">
-        <v>5.3</v>
-      </c>
-    </row>
-    <row r="52" spans="1:5">
-      <c r="A52" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="B52" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C52" s="7">
-        <v>892.85</v>
-      </c>
-      <c r="D52" s="7">
-        <v>885.6</v>
-      </c>
-      <c r="E52" s="8">
-        <v>-7.25</v>
-      </c>
-    </row>
-    <row r="53" spans="1:5">
-      <c r="A53" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="B53" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C53" s="7">
-        <v>11.64</v>
-      </c>
-      <c r="D53" s="7">
-        <v>11.53</v>
-      </c>
-      <c r="E53" s="8">
-        <v>-0.11</v>
-      </c>
-    </row>
-    <row r="54" spans="1:5">
-      <c r="A54" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="B54" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C54" s="7">
-        <v>11.67</v>
-      </c>
-      <c r="D54" s="7">
-        <v>11.4</v>
-      </c>
-      <c r="E54" s="8">
-        <v>-0.27</v>
-      </c>
-    </row>
-    <row r="55" spans="1:5">
-      <c r="A55" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="B55" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C55" s="7">
-        <v>3907.2</v>
-      </c>
-      <c r="D55" s="7">
-        <v>3885.7</v>
-      </c>
-      <c r="E55" s="8">
-        <v>-21.5</v>
-      </c>
-    </row>
-    <row r="56" spans="1:5">
-      <c r="A56" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="B56" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C56" s="7">
-        <v>10849</v>
-      </c>
-      <c r="D56" s="7">
-        <v>10958</v>
-      </c>
-      <c r="E56" s="9">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="57" spans="1:5">
-      <c r="A57" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="B57" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="C57" s="7">
-        <v>62</v>
-      </c>
-      <c r="D57" s="7">
-        <v>75</v>
-      </c>
-      <c r="E57" s="9">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="58" spans="1:5">
-      <c r="A58" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="B58" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="C58" s="7">
-        <v>75</v>
-      </c>
-      <c r="D58" s="7">
-        <v>62</v>
-      </c>
-      <c r="E58" s="8">
-        <v>-13</v>
-      </c>
-    </row>
-    <row r="59" spans="1:5">
-      <c r="A59" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="B59" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C59" s="7">
-        <v>37.79</v>
-      </c>
-      <c r="D59" s="7">
-        <v>33.03</v>
-      </c>
-      <c r="E59" s="8">
-        <v>-4.76</v>
-      </c>
-    </row>
-    <row r="60" spans="1:5">
-      <c r="A60" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="B60" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C60" s="7">
-        <v>31.45</v>
-      </c>
-      <c r="D60" s="7">
-        <v>26.9</v>
-      </c>
-      <c r="E60" s="8">
-        <v>-4.55</v>
-      </c>
-    </row>
-    <row r="61" spans="1:5">
-      <c r="A61" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="B61" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C61" s="7">
-        <v>35.97</v>
-      </c>
-      <c r="D61" s="7">
-        <v>36.71</v>
-      </c>
-      <c r="E61" s="9">
-        <v>0.74</v>
-      </c>
-    </row>
-    <row r="62" spans="1:5">
-      <c r="A62" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="B62" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C62" s="7">
-        <v>36.99</v>
-      </c>
-      <c r="D62" s="7">
-        <v>35.44</v>
-      </c>
-      <c r="E62" s="8">
-        <v>-1.55</v>
-      </c>
-    </row>
-    <row r="63" spans="1:5">
-      <c r="A63" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="B63" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C63" s="7">
-        <v>28.85</v>
-      </c>
-      <c r="D63" s="7">
-        <v>28</v>
-      </c>
-      <c r="E63" s="8">
-        <v>-0.85</v>
-      </c>
-    </row>
-    <row r="64" spans="1:5">
-      <c r="A64" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="B64" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C64" s="7">
-        <v>52.19</v>
-      </c>
-      <c r="D64" s="7">
-        <v>49.5</v>
-      </c>
-      <c r="E64" s="8">
-        <v>-2.69</v>
-      </c>
-    </row>
-    <row r="65" spans="1:5">
-      <c r="A65" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="B65" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C65" s="7">
-        <v>37.74</v>
-      </c>
-      <c r="D65" s="7">
-        <v>36.23</v>
-      </c>
-      <c r="E65" s="8">
-        <v>-1.51</v>
-      </c>
-    </row>
-    <row r="66" spans="1:5">
-      <c r="A66" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="B66" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C66" s="7">
-        <v>48.74</v>
-      </c>
-      <c r="D66" s="7">
-        <v>51.59</v>
-      </c>
-      <c r="E66" s="9">
-        <v>2.85</v>
-      </c>
-    </row>
-    <row r="67" spans="1:5">
-      <c r="A67" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="B67" s="6" t="s">
+      <c r="B70" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="C67" s="7">
-        <v>-6.47</v>
-      </c>
-      <c r="D67" s="7">
-        <v>-2.77</v>
-      </c>
-      <c r="E67" s="9">
-        <v>3.7</v>
-      </c>
-    </row>
-    <row r="68" spans="1:5">
-      <c r="A68" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="B68" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C68" s="7">
-        <v>186</v>
-      </c>
-      <c r="D68" s="7">
-        <v>0.25</v>
-      </c>
-      <c r="E68" s="8">
-        <v>-185.75</v>
-      </c>
-    </row>
-    <row r="69" spans="1:5">
-      <c r="A69" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="B69" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C69" s="7">
-        <v>-38.67</v>
-      </c>
-      <c r="D69" s="7">
-        <v>-55.32</v>
-      </c>
-      <c r="E69" s="8">
-        <v>-16.65</v>
-      </c>
-    </row>
-    <row r="70" spans="1:5">
-      <c r="A70" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="B70" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C70" s="7">
-        <v>-20.59</v>
-      </c>
-      <c r="D70" s="7">
-        <v>-6.44</v>
-      </c>
-      <c r="E70" s="9">
-        <v>14.15</v>
-      </c>
-    </row>
-    <row r="71" spans="1:5">
-      <c r="A71" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="B71" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C71" s="7">
-        <v>31.24</v>
-      </c>
-      <c r="D71" s="7">
-        <v>22.94</v>
-      </c>
-      <c r="E71" s="8">
-        <v>-8.300000000000001</v>
-      </c>
-    </row>
-    <row r="72" spans="1:5">
-      <c r="A72" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="B72" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C72" s="7">
-        <v>18.7</v>
-      </c>
-      <c r="D72" s="7">
-        <v>26.19</v>
-      </c>
-      <c r="E72" s="9">
-        <v>7.49</v>
-      </c>
-    </row>
-    <row r="73" spans="1:5">
-      <c r="A73" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="B73" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C73" s="7">
-        <v>80.8</v>
-      </c>
-      <c r="D73" s="7">
-        <v>-3.75</v>
-      </c>
-      <c r="E73" s="8">
-        <v>-84.55</v>
-      </c>
-    </row>
-    <row r="74" spans="1:5">
-      <c r="A74" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="B74" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C74" s="7">
-        <v>29.23</v>
-      </c>
-      <c r="D74" s="7">
+      <c r="C70" s="5">
         <v>-43.23</v>
       </c>
-      <c r="E74" s="8">
-        <v>-72.45999999999999</v>
+      <c r="D70" s="5">
+        <v>-0.3</v>
+      </c>
+      <c r="E70" s="7">
+        <v>42.93</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A7:E7"/>
+    <mergeCell ref="A5:E5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3252,60 +3094,60 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="28" customHeight="1">
-      <c r="A1" s="10" t="s">
+      <c r="A1" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="10" t="s">
-        <v>73</v>
-      </c>
-      <c r="C1" s="10" t="s">
-        <v>74</v>
-      </c>
-      <c r="D1" s="10" t="s">
-        <v>75</v>
-      </c>
-      <c r="E1" s="10" t="s">
-        <v>76</v>
-      </c>
-      <c r="F1" s="10" t="s">
-        <v>77</v>
-      </c>
-      <c r="G1" s="10" t="s">
-        <v>78</v>
-      </c>
-      <c r="H1" s="10" t="s">
-        <v>79</v>
-      </c>
-      <c r="I1" s="10" t="s">
-        <v>80</v>
+      <c r="B1" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="C1" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="D1" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="E1" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="F1" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="G1" s="8" t="s">
+        <v>62</v>
+      </c>
+      <c r="H1" s="8" t="s">
+        <v>63</v>
+      </c>
+      <c r="I1" s="8" t="s">
+        <v>64</v>
       </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="11" t="s">
+      <c r="A2" s="9" t="s">
         <v>45</v>
       </c>
-      <c r="B2" s="12">
+      <c r="B2" s="10">
         <v>37.44</v>
       </c>
-      <c r="C2" s="13">
+      <c r="C2" s="11">
         <v>8</v>
       </c>
-      <c r="D2" s="12">
-        <v>37.2</v>
-      </c>
-      <c r="E2" s="12">
+      <c r="D2" s="10">
+        <v>34.9</v>
+      </c>
+      <c r="E2" s="10">
         <v>12.5</v>
       </c>
-      <c r="F2" s="12">
-        <v>-8.800000000000001</v>
-      </c>
-      <c r="G2" s="12">
-        <v>-11.6</v>
-      </c>
-      <c r="H2" s="12">
+      <c r="F2" s="10">
+        <v>-9.699999999999999</v>
+      </c>
+      <c r="G2" s="10">
+        <v>-12.1</v>
+      </c>
+      <c r="H2" s="10">
         <v>56.1</v>
       </c>
-      <c r="I2" s="12">
+      <c r="I2" s="10">
         <v>0</v>
       </c>
     </row>
@@ -3407,55 +3249,55 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8">
-      <c r="A1" s="14" t="s">
+      <c r="A1" s="12" t="s">
         <v>37</v>
       </c>
-      <c r="B1" s="14" t="s">
+      <c r="B1" s="12" t="s">
         <v>43</v>
       </c>
-      <c r="C1" s="14" t="s">
+      <c r="C1" s="12" t="s">
         <v>40</v>
       </c>
-      <c r="D1" s="14" t="s">
+      <c r="D1" s="12" t="s">
         <v>39</v>
       </c>
-      <c r="E1" s="14" t="s">
+      <c r="E1" s="12" t="s">
         <v>44</v>
       </c>
-      <c r="F1" s="14" t="s">
+      <c r="F1" s="12" t="s">
         <v>41</v>
       </c>
-      <c r="G1" s="14" t="s">
+      <c r="G1" s="12" t="s">
         <v>42</v>
       </c>
-      <c r="H1" s="14" t="s">
+      <c r="H1" s="12" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="2" spans="1:8">
-      <c r="A2" s="15">
-        <v>0.2884</v>
-      </c>
-      <c r="B2" s="15">
-        <v>0.1633</v>
-      </c>
-      <c r="C2" s="15">
-        <v>0.1414</v>
-      </c>
-      <c r="D2" s="15">
-        <v>0.1157</v>
-      </c>
-      <c r="E2" s="15">
-        <v>0.0941</v>
-      </c>
-      <c r="F2" s="15">
-        <v>0.0238</v>
-      </c>
-      <c r="G2" s="15">
-        <v>-0.2981</v>
-      </c>
-      <c r="H2" s="15">
-        <v>-0.3038</v>
+      <c r="A2" s="13">
+        <v>0.2898</v>
+      </c>
+      <c r="B2" s="13">
+        <v>0.1595</v>
+      </c>
+      <c r="C2" s="13">
+        <v>0.1361</v>
+      </c>
+      <c r="D2" s="13">
+        <v>0.1162</v>
+      </c>
+      <c r="E2" s="13">
+        <v>0.096</v>
+      </c>
+      <c r="F2" s="13">
+        <v>0.0178</v>
+      </c>
+      <c r="G2" s="13">
+        <v>-0.2983</v>
+      </c>
+      <c r="H2" s="13">
+        <v>-0.3071</v>
       </c>
     </row>
   </sheetData>

--- a/BIRLA_GROUP_Technical_Metrics.xlsx
+++ b/BIRLA_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="276" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="303" uniqueCount="81">
   <si>
     <t>Symbol</t>
   </si>
@@ -175,7 +175,55 @@
     <t>▶  SIGNAL EVENTS (vs Previous Run)</t>
   </si>
   <si>
-    <t>No signal events detected since last run.</t>
+    <t>Signal</t>
+  </si>
+  <si>
+    <t>Change</t>
+  </si>
+  <si>
+    <t>Direction</t>
+  </si>
+  <si>
+    <t>Prev Value</t>
+  </si>
+  <si>
+    <t>Curr Value</t>
+  </si>
+  <si>
+    <t>RSI Oversold Recovery</t>
+  </si>
+  <si>
+    <t>29.0 → 34.0</t>
+  </si>
+  <si>
+    <t>🟢 BULLISH</t>
+  </si>
+  <si>
+    <t>29.0</t>
+  </si>
+  <si>
+    <t>34.0</t>
+  </si>
+  <si>
+    <t>26.7 → 37.6</t>
+  </si>
+  <si>
+    <t>26.7</t>
+  </si>
+  <si>
+    <t>37.6</t>
+  </si>
+  <si>
+    <t>RSI Momentum</t>
+  </si>
+  <si>
+    <t>46.8 → 56.8</t>
+  </si>
+  <si>
+    <t>46.8</t>
+  </si>
+  <si>
+    <t>56.8</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -261,14 +309,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF006100"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF9C0006"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -301,13 +349,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -377,14 +425,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -759,8 +808,9 @@
     <col min="14" max="14" width="11.7109375" customWidth="1"/>
     <col min="15" max="15" width="10.7109375" customWidth="1"/>
     <col min="16" max="16" width="9.7109375" customWidth="1"/>
-    <col min="17" max="18" width="10.7109375" customWidth="1"/>
-    <col min="19" max="19" width="9.7109375" customWidth="1"/>
+    <col min="17" max="17" width="10.7109375" customWidth="1"/>
+    <col min="18" max="18" width="9.7109375" customWidth="1"/>
+    <col min="19" max="19" width="10.7109375" customWidth="1"/>
     <col min="20" max="20" width="22.7109375" customWidth="1"/>
     <col min="21" max="21" width="9.7109375" customWidth="1"/>
     <col min="22" max="22" width="10.7109375" customWidth="1"/>
@@ -900,10 +950,10 @@
         <v>45</v>
       </c>
       <c r="C2">
-        <v>347.25</v>
+        <v>353.05</v>
       </c>
       <c r="D2">
-        <v>-2.79</v>
+        <v>1.67</v>
       </c>
       <c r="E2">
         <v>424.7</v>
@@ -912,46 +962,46 @@
         <v>292.25</v>
       </c>
       <c r="G2">
-        <v>-18.24</v>
+        <v>-16.87</v>
       </c>
       <c r="H2">
-        <v>18.82</v>
+        <v>20.8</v>
       </c>
       <c r="I2">
-        <v>-9.16</v>
+        <v>-6.95</v>
       </c>
       <c r="J2">
-        <v>-12.53</v>
+        <v>-12.27</v>
       </c>
       <c r="K2">
-        <v>-11.47</v>
+        <v>-10.36</v>
       </c>
       <c r="L2">
-        <v>16.02</v>
+        <v>15.62</v>
       </c>
       <c r="M2">
-        <v>28.98</v>
+        <v>28.62</v>
       </c>
       <c r="N2">
-        <v>75</v>
+        <v>62</v>
       </c>
       <c r="O2">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="P2">
-        <v>364.78</v>
+        <v>359.51</v>
       </c>
       <c r="Q2">
-        <v>376.21</v>
+        <v>374.35</v>
       </c>
       <c r="R2">
-        <v>391.56</v>
+        <v>390.4</v>
       </c>
       <c r="S2">
-        <v>366.17</v>
+        <v>366.12</v>
       </c>
       <c r="T2">
-        <v>-5.17</v>
+        <v>-3.57</v>
       </c>
       <c r="U2" t="s">
         <v>46</v>
@@ -966,43 +1016,43 @@
         <v>1</v>
       </c>
       <c r="Y2">
-        <v>29.03</v>
+        <v>34.04</v>
       </c>
       <c r="Z2">
-        <v>-8.460000000000001</v>
+        <v>-9.210000000000001</v>
       </c>
       <c r="AA2">
-        <v>-6.19</v>
+        <v>-6.8</v>
       </c>
       <c r="AB2">
-        <v>-2.27</v>
+        <v>-2.42</v>
       </c>
       <c r="AC2">
-        <v>5.52</v>
+        <v>8.720000000000001</v>
       </c>
       <c r="AD2">
-        <v>23.68</v>
+        <v>11.46</v>
       </c>
       <c r="AE2">
-        <v>9.9</v>
+        <v>10.52</v>
       </c>
       <c r="AF2">
-        <v>-36.1</v>
+        <v>-36.77</v>
       </c>
       <c r="AG2">
-        <v>396.67</v>
+        <v>396.18</v>
       </c>
       <c r="AH2">
-        <v>355.75</v>
+        <v>352.53</v>
       </c>
       <c r="AI2">
-        <v>379.33</v>
+        <v>375.32</v>
       </c>
       <c r="AJ2" t="s">
         <v>48</v>
       </c>
       <c r="AK2">
-        <v>31.96</v>
+        <v>37.95</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1013,58 +1063,58 @@
         <v>45</v>
       </c>
       <c r="C3">
-        <v>39.77</v>
+        <v>39.58</v>
       </c>
       <c r="D3">
-        <v>-3.8</v>
+        <v>-0.48</v>
       </c>
       <c r="E3">
         <v>85.38</v>
       </c>
       <c r="F3">
-        <v>39.77</v>
+        <v>39.58</v>
       </c>
       <c r="G3">
-        <v>-53.42</v>
+        <v>-53.64</v>
       </c>
       <c r="H3">
         <v>0</v>
       </c>
       <c r="I3">
-        <v>-11.35</v>
+        <v>-11.71</v>
       </c>
       <c r="J3">
-        <v>-19.2</v>
+        <v>-19.37</v>
       </c>
       <c r="K3">
-        <v>-29.02</v>
+        <v>-29.64</v>
       </c>
       <c r="L3">
-        <v>-51.67</v>
+        <v>-52.33</v>
       </c>
       <c r="M3">
-        <v>-30.71</v>
+        <v>-31.39</v>
       </c>
       <c r="N3">
         <v>13</v>
       </c>
       <c r="O3">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="P3">
-        <v>42.42</v>
+        <v>41.37</v>
       </c>
       <c r="Q3">
-        <v>44.7</v>
+        <v>44.27</v>
       </c>
       <c r="R3">
-        <v>49.4</v>
+        <v>49.05</v>
       </c>
       <c r="S3">
-        <v>59.96</v>
+        <v>59.77</v>
       </c>
       <c r="T3">
-        <v>-33.67</v>
+        <v>-33.78</v>
       </c>
       <c r="U3" t="s">
         <v>46</v>
@@ -1079,43 +1129,43 @@
         <v>0</v>
       </c>
       <c r="Y3">
-        <v>23.47</v>
+        <v>23.08</v>
       </c>
       <c r="Z3">
-        <v>-2.25</v>
+        <v>-2.39</v>
       </c>
       <c r="AA3">
-        <v>-2.1</v>
+        <v>-2.15</v>
       </c>
       <c r="AB3">
-        <v>-0.15</v>
+        <v>-0.23</v>
       </c>
       <c r="AC3">
-        <v>23.49</v>
+        <v>6.75</v>
       </c>
       <c r="AD3">
-        <v>42.96</v>
+        <v>23.79</v>
       </c>
       <c r="AE3">
-        <v>1.73</v>
+        <v>1.71</v>
       </c>
       <c r="AF3">
-        <v>28.73</v>
+        <v>-43.77</v>
       </c>
       <c r="AG3">
-        <v>49.08</v>
+        <v>48.92</v>
       </c>
       <c r="AH3">
-        <v>40.31</v>
+        <v>39.62</v>
       </c>
       <c r="AI3">
-        <v>45.56</v>
+        <v>44.98</v>
       </c>
       <c r="AJ3" t="s">
         <v>48</v>
       </c>
       <c r="AK3">
-        <v>35.67</v>
+        <v>39.28</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1126,10 +1176,10 @@
         <v>45</v>
       </c>
       <c r="C4">
-        <v>2894</v>
+        <v>2950</v>
       </c>
       <c r="D4">
-        <v>-0.01</v>
+        <v>1.94</v>
       </c>
       <c r="E4">
         <v>3380.5</v>
@@ -1138,46 +1188,46 @@
         <v>2531.1</v>
       </c>
       <c r="G4">
-        <v>-14.39</v>
+        <v>-12.73</v>
       </c>
       <c r="H4">
-        <v>14.34</v>
+        <v>16.55</v>
       </c>
       <c r="I4">
-        <v>0.28</v>
+        <v>1.03</v>
       </c>
       <c r="J4">
-        <v>-7.49</v>
+        <v>-7.48</v>
       </c>
       <c r="K4">
-        <v>-7.04</v>
+        <v>-4.51</v>
       </c>
       <c r="L4">
-        <v>2.04</v>
+        <v>3.36</v>
       </c>
       <c r="M4">
-        <v>11.62</v>
+        <v>11.66</v>
       </c>
       <c r="N4">
         <v>50</v>
       </c>
       <c r="O4">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="P4">
-        <v>2895.3</v>
+        <v>2901.3</v>
       </c>
       <c r="Q4">
-        <v>2962.28</v>
+        <v>2951.46</v>
       </c>
       <c r="R4">
-        <v>3144.56</v>
+        <v>3137.4</v>
       </c>
       <c r="S4">
-        <v>2982.15</v>
+        <v>2982.65</v>
       </c>
       <c r="T4">
-        <v>-2.96</v>
+        <v>-1.09</v>
       </c>
       <c r="U4" t="s">
         <v>46</v>
@@ -1192,34 +1242,34 @@
         <v>1</v>
       </c>
       <c r="Y4">
-        <v>36.68</v>
+        <v>44.53</v>
       </c>
       <c r="Z4">
-        <v>-77.58</v>
+        <v>-69.20999999999999</v>
       </c>
       <c r="AA4">
-        <v>-82.79000000000001</v>
+        <v>-80.08</v>
       </c>
       <c r="AB4">
-        <v>5.21</v>
+        <v>10.87</v>
       </c>
       <c r="AC4">
-        <v>91.83</v>
+        <v>95.68000000000001</v>
       </c>
       <c r="AD4">
-        <v>86.86</v>
+        <v>91.51000000000001</v>
       </c>
       <c r="AE4">
-        <v>61.77</v>
+        <v>63.93</v>
       </c>
       <c r="AF4">
-        <v>-34.77</v>
+        <v>-52.8</v>
       </c>
       <c r="AG4">
-        <v>3180.84</v>
+        <v>3147.74</v>
       </c>
       <c r="AH4">
-        <v>2743.73</v>
+        <v>2755.18</v>
       </c>
       <c r="AI4">
         <v>3050.83</v>
@@ -1228,7 +1278,7 @@
         <v>48</v>
       </c>
       <c r="AK4">
-        <v>56.43</v>
+        <v>49.31</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1239,10 +1289,10 @@
         <v>45</v>
       </c>
       <c r="C5">
-        <v>869.85</v>
+        <v>885.65</v>
       </c>
       <c r="D5">
-        <v>-1.78</v>
+        <v>1.82</v>
       </c>
       <c r="E5">
         <v>1149.7</v>
@@ -1251,46 +1301,46 @@
         <v>774.65</v>
       </c>
       <c r="G5">
-        <v>-24.34</v>
+        <v>-22.97</v>
       </c>
       <c r="H5">
-        <v>12.29</v>
+        <v>14.33</v>
       </c>
       <c r="I5">
-        <v>-2.69</v>
+        <v>-2.46</v>
       </c>
       <c r="J5">
-        <v>-10.6</v>
+        <v>-11.77</v>
       </c>
       <c r="K5">
-        <v>-8.98</v>
+        <v>-6.06</v>
       </c>
       <c r="L5">
-        <v>12.56</v>
+        <v>12.63</v>
       </c>
       <c r="M5">
-        <v>13.61</v>
+        <v>13.4</v>
       </c>
       <c r="N5">
-        <v>62</v>
+        <v>75</v>
       </c>
       <c r="O5">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="P5">
-        <v>891.35</v>
+        <v>886.88</v>
       </c>
       <c r="Q5">
-        <v>917.59</v>
+        <v>912.77</v>
       </c>
       <c r="R5">
-        <v>977.5700000000001</v>
+        <v>973.72</v>
       </c>
       <c r="S5">
-        <v>983.3200000000001</v>
+        <v>983.09</v>
       </c>
       <c r="T5">
-        <v>-11.54</v>
+        <v>-9.91</v>
       </c>
       <c r="U5" t="s">
         <v>46</v>
@@ -1305,34 +1355,34 @@
         <v>0</v>
       </c>
       <c r="Y5">
-        <v>32.28</v>
+        <v>38.24</v>
       </c>
       <c r="Z5">
-        <v>-26.86</v>
+        <v>-25.98</v>
       </c>
       <c r="AA5">
-        <v>-26.06</v>
+        <v>-26.04</v>
       </c>
       <c r="AB5">
-        <v>-0.8</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="AC5">
-        <v>62.61</v>
+        <v>65.48999999999999</v>
       </c>
       <c r="AD5">
-        <v>76.16</v>
+        <v>68.48</v>
       </c>
       <c r="AE5">
-        <v>23.47</v>
+        <v>24.69</v>
       </c>
       <c r="AF5">
-        <v>97.94</v>
+        <v>-0.76</v>
       </c>
       <c r="AG5">
-        <v>984.64</v>
+        <v>973.92</v>
       </c>
       <c r="AH5">
-        <v>850.55</v>
+        <v>851.63</v>
       </c>
       <c r="AI5">
         <v>933.28</v>
@@ -1341,7 +1391,7 @@
         <v>48</v>
       </c>
       <c r="AK5">
-        <v>48.5</v>
+        <v>46.31</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1352,10 +1402,10 @@
         <v>45</v>
       </c>
       <c r="C6">
-        <v>11.36</v>
+        <v>11.95</v>
       </c>
       <c r="D6">
-        <v>-1.47</v>
+        <v>5.19</v>
       </c>
       <c r="E6">
         <v>15.6</v>
@@ -1364,46 +1414,46 @@
         <v>8.529999999999999</v>
       </c>
       <c r="G6">
-        <v>-27.18</v>
+        <v>-23.4</v>
       </c>
       <c r="H6">
-        <v>33.18</v>
+        <v>40.09</v>
       </c>
       <c r="I6">
-        <v>-9.27</v>
+        <v>-5.08</v>
       </c>
       <c r="J6">
-        <v>-20.39</v>
+        <v>-17.7</v>
       </c>
       <c r="K6">
-        <v>-13.94</v>
+        <v>-8.99</v>
       </c>
       <c r="L6">
-        <v>30.57</v>
+        <v>33.67</v>
       </c>
       <c r="M6">
-        <v>1.78</v>
+        <v>2.82</v>
       </c>
       <c r="N6">
         <v>87</v>
       </c>
       <c r="O6">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="P6">
-        <v>11.88</v>
+        <v>11.75</v>
       </c>
       <c r="Q6">
-        <v>12.8</v>
+        <v>12.69</v>
       </c>
       <c r="R6">
-        <v>13.79</v>
+        <v>13.75</v>
       </c>
       <c r="S6">
-        <v>12.3</v>
+        <v>12.31</v>
       </c>
       <c r="T6">
-        <v>-7.67</v>
+        <v>-2.89</v>
       </c>
       <c r="U6" t="s">
         <v>46</v>
@@ -1418,34 +1468,34 @@
         <v>1</v>
       </c>
       <c r="Y6">
-        <v>26.7</v>
+        <v>37.56</v>
       </c>
       <c r="Z6">
-        <v>-0.61</v>
+        <v>-0.59</v>
       </c>
       <c r="AA6">
-        <v>-0.47</v>
+        <v>-0.5</v>
       </c>
       <c r="AB6">
-        <v>-0.14</v>
+        <v>-0.09</v>
       </c>
       <c r="AC6">
-        <v>0</v>
+        <v>24.24</v>
       </c>
       <c r="AD6">
-        <v>10.1</v>
+        <v>10.03</v>
       </c>
       <c r="AE6">
-        <v>0.46</v>
+        <v>0.49</v>
       </c>
       <c r="AF6">
-        <v>22.48</v>
+        <v>17.93</v>
       </c>
       <c r="AG6">
-        <v>14.3</v>
+        <v>14.11</v>
       </c>
       <c r="AH6">
-        <v>11.29</v>
+        <v>11.28</v>
       </c>
       <c r="AI6">
         <v>12.7</v>
@@ -1454,7 +1504,7 @@
         <v>48</v>
       </c>
       <c r="AK6">
-        <v>59.27</v>
+        <v>57.31</v>
       </c>
     </row>
     <row r="7" spans="1:37">
@@ -1465,10 +1515,10 @@
         <v>45</v>
       </c>
       <c r="C7">
-        <v>11.12</v>
+        <v>12.23</v>
       </c>
       <c r="D7">
-        <v>-2.46</v>
+        <v>9.98</v>
       </c>
       <c r="E7">
         <v>13.92</v>
@@ -1477,37 +1527,37 @@
         <v>4.69</v>
       </c>
       <c r="G7">
-        <v>-20.11</v>
+        <v>-12.14</v>
       </c>
       <c r="H7">
-        <v>137.1</v>
+        <v>160.77</v>
       </c>
       <c r="I7">
-        <v>-2.03</v>
+        <v>-1.37</v>
       </c>
       <c r="J7">
-        <v>-2.03</v>
+        <v>5.7</v>
       </c>
       <c r="K7">
-        <v>-6.95</v>
+        <v>4.35</v>
       </c>
       <c r="L7">
-        <v>111.01</v>
+        <v>136.56</v>
       </c>
       <c r="M7">
-        <v>-29.83</v>
+        <v>-28.55</v>
       </c>
       <c r="N7">
         <v>99</v>
       </c>
       <c r="O7">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="P7">
-        <v>11.87</v>
+        <v>11.83</v>
       </c>
       <c r="Q7">
-        <v>11.23</v>
+        <v>11.27</v>
       </c>
       <c r="R7">
         <v>11.44</v>
@@ -1516,7 +1566,7 @@
         <v>10.81</v>
       </c>
       <c r="T7">
-        <v>2.9</v>
+        <v>13.12</v>
       </c>
       <c r="U7" t="s">
         <v>46</v>
@@ -1531,34 +1581,34 @@
         <v>2</v>
       </c>
       <c r="Y7">
-        <v>46.81</v>
+        <v>56.82</v>
       </c>
       <c r="Z7">
-        <v>0.06</v>
+        <v>0.11</v>
       </c>
       <c r="AA7">
-        <v>0</v>
+        <v>0.03</v>
       </c>
       <c r="AB7">
-        <v>0.06</v>
+        <v>0.09</v>
       </c>
       <c r="AC7">
-        <v>51.92</v>
+        <v>54.31</v>
       </c>
       <c r="AD7">
-        <v>69.78</v>
+        <v>58.97</v>
       </c>
       <c r="AE7">
-        <v>0.82</v>
+        <v>0.84</v>
       </c>
       <c r="AF7">
-        <v>6.56</v>
+        <v>145.05</v>
       </c>
       <c r="AG7">
-        <v>12.42</v>
+        <v>12.54</v>
       </c>
       <c r="AH7">
-        <v>10.04</v>
+        <v>10</v>
       </c>
       <c r="AI7">
         <v>10.86</v>
@@ -1567,7 +1617,7 @@
         <v>49</v>
       </c>
       <c r="AK7">
-        <v>26.84</v>
+        <v>23.94</v>
       </c>
     </row>
     <row r="8" spans="1:37">
@@ -1578,58 +1628,58 @@
         <v>45</v>
       </c>
       <c r="C8">
-        <v>3789.3</v>
+        <v>3784.3</v>
       </c>
       <c r="D8">
-        <v>-2.48</v>
+        <v>-0.13</v>
       </c>
       <c r="E8">
         <v>5809.5</v>
       </c>
       <c r="F8">
-        <v>3789.3</v>
+        <v>3784.3</v>
       </c>
       <c r="G8">
-        <v>-34.77</v>
+        <v>-34.86</v>
       </c>
       <c r="H8">
         <v>0</v>
       </c>
       <c r="I8">
-        <v>-4.53</v>
+        <v>-5.02</v>
       </c>
       <c r="J8">
-        <v>-5.46</v>
+        <v>-6.37</v>
       </c>
       <c r="K8">
-        <v>-11.94</v>
+        <v>-12.23</v>
       </c>
       <c r="L8">
-        <v>-32.69</v>
+        <v>-34.62</v>
       </c>
       <c r="M8">
-        <v>15.95</v>
+        <v>16.01</v>
       </c>
       <c r="N8">
         <v>25</v>
       </c>
       <c r="O8">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="P8">
-        <v>3903.58</v>
+        <v>3863.6</v>
       </c>
       <c r="Q8">
-        <v>3963.59</v>
+        <v>3952.45</v>
       </c>
       <c r="R8">
-        <v>4154.2</v>
+        <v>4142.59</v>
       </c>
       <c r="S8">
-        <v>4442.9</v>
+        <v>4436.14</v>
       </c>
       <c r="T8">
-        <v>-14.71</v>
+        <v>-14.69</v>
       </c>
       <c r="U8" t="s">
         <v>46</v>
@@ -1644,43 +1694,43 @@
         <v>0</v>
       </c>
       <c r="Y8">
-        <v>30.36</v>
+        <v>30.09</v>
       </c>
       <c r="Z8">
-        <v>-70.81</v>
+        <v>-77.26000000000001</v>
       </c>
       <c r="AA8">
-        <v>-66.81999999999999</v>
+        <v>-68.90000000000001</v>
       </c>
       <c r="AB8">
-        <v>-4</v>
+        <v>-8.35</v>
       </c>
       <c r="AC8">
-        <v>29.34</v>
+        <v>13.28</v>
       </c>
       <c r="AD8">
-        <v>48.59</v>
+        <v>31.35</v>
       </c>
       <c r="AE8">
-        <v>96.94</v>
+        <v>100.18</v>
       </c>
       <c r="AF8">
-        <v>-13.67</v>
+        <v>5.84</v>
       </c>
       <c r="AG8">
-        <v>4094.67</v>
+        <v>4104.2</v>
       </c>
       <c r="AH8">
-        <v>3832.51</v>
+        <v>3800.7</v>
       </c>
       <c r="AI8">
-        <v>4109.12</v>
+        <v>4043.79</v>
       </c>
       <c r="AJ8" t="s">
         <v>48</v>
       </c>
       <c r="AK8">
-        <v>29.69</v>
+        <v>34.09</v>
       </c>
     </row>
     <row r="9" spans="1:37">
@@ -1691,10 +1741,10 @@
         <v>45</v>
       </c>
       <c r="C9">
-        <v>11050</v>
+        <v>11180</v>
       </c>
       <c r="D9">
-        <v>0.84</v>
+        <v>1.18</v>
       </c>
       <c r="E9">
         <v>13052</v>
@@ -1703,46 +1753,46 @@
         <v>10362</v>
       </c>
       <c r="G9">
-        <v>-15.34</v>
+        <v>-14.34</v>
       </c>
       <c r="H9">
-        <v>6.64</v>
+        <v>7.89</v>
       </c>
       <c r="I9">
-        <v>1.73</v>
+        <v>2.5</v>
       </c>
       <c r="J9">
-        <v>0.45</v>
+        <v>0.22</v>
       </c>
       <c r="K9">
-        <v>-7.21</v>
+        <v>-5.62</v>
       </c>
       <c r="L9">
-        <v>-10.67</v>
+        <v>-9.44</v>
       </c>
       <c r="M9">
-        <v>9.6</v>
+        <v>9.48</v>
       </c>
       <c r="N9">
         <v>38</v>
       </c>
       <c r="O9">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="P9">
-        <v>10882.8</v>
+        <v>10937.4</v>
       </c>
       <c r="Q9">
-        <v>10821.55</v>
+        <v>10827.75</v>
       </c>
       <c r="R9">
-        <v>11116.92</v>
+        <v>11102.7</v>
       </c>
       <c r="S9">
-        <v>11643.6</v>
+        <v>11639.06</v>
       </c>
       <c r="T9">
-        <v>-5.1</v>
+        <v>-3.94</v>
       </c>
       <c r="U9" t="s">
         <v>46</v>
@@ -1757,43 +1807,43 @@
         <v>0</v>
       </c>
       <c r="Y9">
-        <v>53.92</v>
+        <v>57.07</v>
       </c>
       <c r="Z9">
-        <v>-57.25</v>
+        <v>-26.4</v>
       </c>
       <c r="AA9">
-        <v>-112.74</v>
+        <v>-95.47</v>
       </c>
       <c r="AB9">
-        <v>55.49</v>
+        <v>69.08</v>
       </c>
       <c r="AC9">
-        <v>98.14</v>
+        <v>100</v>
       </c>
       <c r="AD9">
-        <v>89.22</v>
+        <v>94.3</v>
       </c>
       <c r="AE9">
-        <v>259.97</v>
+        <v>259.4</v>
       </c>
       <c r="AF9">
-        <v>-0.3</v>
+        <v>-9.34</v>
       </c>
       <c r="AG9">
-        <v>11193.01</v>
+        <v>11219.29</v>
       </c>
       <c r="AH9">
-        <v>10450.09</v>
+        <v>10436.21</v>
       </c>
       <c r="AI9">
-        <v>11169.72</v>
+        <v>10275.81</v>
       </c>
       <c r="AJ9" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="AK9">
-        <v>32.71</v>
+        <v>34.82</v>
       </c>
     </row>
   </sheetData>
@@ -1934,7 +1984,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F70"/>
+  <dimension ref="A1:F74"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -1954,1127 +2004,1236 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="3" t="s">
         <v>51</v>
       </c>
+      <c r="C2" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
+      <c r="A4" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="5" spans="1:6">
-      <c r="A5" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="B5" s="2"/>
-      <c r="C5" s="2"/>
-      <c r="D5" s="2"/>
-      <c r="E5" s="2"/>
-    </row>
-    <row r="6" spans="1:6">
-      <c r="A6" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="D6" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="E6" s="4" t="s">
-        <v>56</v>
+      <c r="A5" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="E5" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="F5" s="4" t="s">
+        <v>67</v>
       </c>
     </row>
     <row r="7" spans="1:6">
-      <c r="A7" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C7" s="5">
-        <v>-11.45</v>
-      </c>
-      <c r="D7" s="5">
-        <v>-12.53</v>
-      </c>
-      <c r="E7" s="6">
-        <v>-1.08</v>
-      </c>
+      <c r="A7" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="B7" s="2"/>
+      <c r="C7" s="2"/>
+      <c r="D7" s="2"/>
+      <c r="E7" s="2"/>
     </row>
     <row r="8" spans="1:6">
       <c r="A8" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C9" s="6">
+        <v>-12.53</v>
+      </c>
+      <c r="D9" s="6">
+        <v>-12.27</v>
+      </c>
+      <c r="E9" s="7">
+        <v>0.26</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B8" s="3" t="s">
+      <c r="B10" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C8" s="5">
-        <v>-17.07</v>
-      </c>
-      <c r="D8" s="5">
+      <c r="C10" s="6">
         <v>-19.2</v>
       </c>
-      <c r="E8" s="6">
-        <v>-2.13</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9" s="3" t="s">
+      <c r="D10" s="6">
+        <v>-19.37</v>
+      </c>
+      <c r="E10" s="8">
+        <v>-0.17</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B9" s="3" t="s">
+      <c r="B11" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C9" s="5">
-        <v>-8.58</v>
-      </c>
-      <c r="D9" s="5">
+      <c r="C11" s="6">
         <v>-7.49</v>
       </c>
-      <c r="E9" s="7">
-        <v>1.09</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10" s="3" t="s">
+      <c r="D11" s="6">
+        <v>-7.48</v>
+      </c>
+      <c r="E11" s="7">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B10" s="3" t="s">
+      <c r="B12" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C10" s="5">
-        <v>-9.74</v>
-      </c>
-      <c r="D10" s="5">
+      <c r="C12" s="6">
         <v>-10.6</v>
       </c>
-      <c r="E10" s="6">
-        <v>-0.86</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11" s="3" t="s">
+      <c r="D12" s="6">
+        <v>-11.77</v>
+      </c>
+      <c r="E12" s="8">
+        <v>-1.17</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="A13" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B11" s="3" t="s">
+      <c r="B13" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C11" s="5">
-        <v>-16.69</v>
-      </c>
-      <c r="D11" s="5">
+      <c r="C13" s="6">
         <v>-20.39</v>
       </c>
-      <c r="E11" s="6">
-        <v>-3.7</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12" s="3" t="s">
+      <c r="D13" s="6">
+        <v>-17.7</v>
+      </c>
+      <c r="E13" s="7">
+        <v>2.69</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="B12" s="3" t="s">
+      <c r="B14" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C12" s="5">
-        <v>-2.23</v>
-      </c>
-      <c r="D12" s="5">
+      <c r="C14" s="6">
         <v>-2.03</v>
       </c>
-      <c r="E12" s="7">
-        <v>0.2</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13" s="3" t="s">
+      <c r="D14" s="6">
+        <v>5.7</v>
+      </c>
+      <c r="E14" s="7">
+        <v>7.73</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="A15" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="B13" s="3" t="s">
+      <c r="B15" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C13" s="5">
-        <v>-3.51</v>
-      </c>
-      <c r="D13" s="5">
+      <c r="C15" s="6">
         <v>-5.46</v>
       </c>
-      <c r="E13" s="6">
-        <v>-1.95</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14" s="3" t="s">
+      <c r="D15" s="6">
+        <v>-6.37</v>
+      </c>
+      <c r="E15" s="8">
+        <v>-0.91</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="A16" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="B14" s="3" t="s">
+      <c r="B16" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C14" s="5">
-        <v>-1.28</v>
-      </c>
-      <c r="D14" s="5">
+      <c r="C16" s="6">
         <v>0.45</v>
       </c>
-      <c r="E14" s="7">
+      <c r="D16" s="6">
+        <v>0.22</v>
+      </c>
+      <c r="E16" s="8">
+        <v>-0.23</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B17" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C17" s="6">
+        <v>-9.16</v>
+      </c>
+      <c r="D17" s="6">
+        <v>-6.95</v>
+      </c>
+      <c r="E17" s="7">
+        <v>2.21</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B18" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C18" s="6">
+        <v>-11.35</v>
+      </c>
+      <c r="D18" s="6">
+        <v>-11.71</v>
+      </c>
+      <c r="E18" s="8">
+        <v>-0.36</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B19" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C19" s="6">
+        <v>0.28</v>
+      </c>
+      <c r="D19" s="6">
+        <v>1.03</v>
+      </c>
+      <c r="E19" s="7">
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B20" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C20" s="6">
+        <v>-2.69</v>
+      </c>
+      <c r="D20" s="6">
+        <v>-2.46</v>
+      </c>
+      <c r="E20" s="7">
+        <v>0.23</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B21" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C21" s="6">
+        <v>-9.27</v>
+      </c>
+      <c r="D21" s="6">
+        <v>-5.08</v>
+      </c>
+      <c r="E21" s="7">
+        <v>4.19</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B22" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C22" s="6">
+        <v>-2.03</v>
+      </c>
+      <c r="D22" s="6">
+        <v>-1.37</v>
+      </c>
+      <c r="E22" s="7">
+        <v>0.66</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B23" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C23" s="6">
+        <v>-4.53</v>
+      </c>
+      <c r="D23" s="6">
+        <v>-5.02</v>
+      </c>
+      <c r="E23" s="8">
+        <v>-0.49</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="B24" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C24" s="6">
         <v>1.73</v>
       </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15" s="3" t="s">
+      <c r="D24" s="6">
+        <v>2.5</v>
+      </c>
+      <c r="E24" s="7">
+        <v>0.77</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B15" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C15" s="5">
-        <v>-5.73</v>
-      </c>
-      <c r="D15" s="5">
-        <v>-9.16</v>
-      </c>
-      <c r="E15" s="6">
-        <v>-3.43</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16" s="3" t="s">
+      <c r="B25" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C25" s="6">
+        <v>16.02</v>
+      </c>
+      <c r="D25" s="6">
+        <v>15.62</v>
+      </c>
+      <c r="E25" s="8">
+        <v>-0.4</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B16" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C16" s="5">
-        <v>-8.699999999999999</v>
-      </c>
-      <c r="D16" s="5">
-        <v>-11.35</v>
-      </c>
-      <c r="E16" s="6">
-        <v>-2.65</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5">
-      <c r="A17" s="3" t="s">
+      <c r="B26" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C26" s="6">
+        <v>-51.67</v>
+      </c>
+      <c r="D26" s="6">
+        <v>-52.33</v>
+      </c>
+      <c r="E26" s="8">
+        <v>-0.66</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B17" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C17" s="5">
-        <v>0.74</v>
-      </c>
-      <c r="D17" s="5">
-        <v>0.28</v>
-      </c>
-      <c r="E17" s="6">
-        <v>-0.46</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5">
-      <c r="A18" s="3" t="s">
+      <c r="B27" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C27" s="6">
+        <v>2.04</v>
+      </c>
+      <c r="D27" s="6">
+        <v>3.36</v>
+      </c>
+      <c r="E27" s="7">
+        <v>1.32</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B18" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C18" s="5">
-        <v>0.35</v>
-      </c>
-      <c r="D18" s="5">
-        <v>-2.69</v>
-      </c>
-      <c r="E18" s="6">
-        <v>-3.04</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5">
-      <c r="A19" s="3" t="s">
+      <c r="B28" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C28" s="6">
+        <v>12.56</v>
+      </c>
+      <c r="D28" s="6">
+        <v>12.63</v>
+      </c>
+      <c r="E28" s="7">
+        <v>0.07000000000000001</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B19" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C19" s="5">
-        <v>-9</v>
-      </c>
-      <c r="D19" s="5">
-        <v>-9.27</v>
-      </c>
-      <c r="E19" s="6">
+      <c r="B29" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C29" s="6">
+        <v>30.57</v>
+      </c>
+      <c r="D29" s="6">
+        <v>33.67</v>
+      </c>
+      <c r="E29" s="7">
+        <v>3.1</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B30" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C30" s="6">
+        <v>111.01</v>
+      </c>
+      <c r="D30" s="6">
+        <v>136.56</v>
+      </c>
+      <c r="E30" s="7">
+        <v>25.55</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5">
+      <c r="A31" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B31" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C31" s="6">
+        <v>-32.69</v>
+      </c>
+      <c r="D31" s="6">
+        <v>-34.62</v>
+      </c>
+      <c r="E31" s="8">
+        <v>-1.93</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5">
+      <c r="A32" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="B32" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C32" s="6">
+        <v>-10.67</v>
+      </c>
+      <c r="D32" s="6">
+        <v>-9.44</v>
+      </c>
+      <c r="E32" s="7">
+        <v>1.23</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5">
+      <c r="A33" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B33" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C33" s="6">
+        <v>-11.47</v>
+      </c>
+      <c r="D33" s="6">
+        <v>-10.36</v>
+      </c>
+      <c r="E33" s="7">
+        <v>1.11</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5">
+      <c r="A34" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B34" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C34" s="6">
+        <v>-29.02</v>
+      </c>
+      <c r="D34" s="6">
+        <v>-29.64</v>
+      </c>
+      <c r="E34" s="8">
+        <v>-0.62</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5">
+      <c r="A35" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B35" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C35" s="6">
+        <v>-7.04</v>
+      </c>
+      <c r="D35" s="6">
+        <v>-4.51</v>
+      </c>
+      <c r="E35" s="7">
+        <v>2.53</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5">
+      <c r="A36" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B36" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C36" s="6">
+        <v>-8.98</v>
+      </c>
+      <c r="D36" s="6">
+        <v>-6.06</v>
+      </c>
+      <c r="E36" s="7">
+        <v>2.92</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5">
+      <c r="A37" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B37" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C37" s="6">
+        <v>-13.94</v>
+      </c>
+      <c r="D37" s="6">
+        <v>-8.99</v>
+      </c>
+      <c r="E37" s="7">
+        <v>4.95</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5">
+      <c r="A38" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B38" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C38" s="6">
+        <v>-6.95</v>
+      </c>
+      <c r="D38" s="6">
+        <v>4.35</v>
+      </c>
+      <c r="E38" s="7">
+        <v>11.3</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5">
+      <c r="A39" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B39" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C39" s="6">
+        <v>-11.94</v>
+      </c>
+      <c r="D39" s="6">
+        <v>-12.23</v>
+      </c>
+      <c r="E39" s="8">
+        <v>-0.29</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5">
+      <c r="A40" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="B40" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C40" s="6">
+        <v>-7.21</v>
+      </c>
+      <c r="D40" s="6">
+        <v>-5.62</v>
+      </c>
+      <c r="E40" s="7">
+        <v>1.59</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5">
+      <c r="A41" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B41" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C41" s="6">
+        <v>-18.24</v>
+      </c>
+      <c r="D41" s="6">
+        <v>-16.87</v>
+      </c>
+      <c r="E41" s="7">
+        <v>1.37</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5">
+      <c r="A42" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B42" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C42" s="6">
+        <v>-53.42</v>
+      </c>
+      <c r="D42" s="6">
+        <v>-53.64</v>
+      </c>
+      <c r="E42" s="8">
+        <v>-0.22</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5">
+      <c r="A43" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B43" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C43" s="6">
+        <v>-14.39</v>
+      </c>
+      <c r="D43" s="6">
+        <v>-12.73</v>
+      </c>
+      <c r="E43" s="7">
+        <v>1.66</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5">
+      <c r="A44" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B44" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C44" s="6">
+        <v>-24.34</v>
+      </c>
+      <c r="D44" s="6">
+        <v>-22.97</v>
+      </c>
+      <c r="E44" s="7">
+        <v>1.37</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5">
+      <c r="A45" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B45" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C45" s="6">
+        <v>-27.18</v>
+      </c>
+      <c r="D45" s="6">
+        <v>-23.4</v>
+      </c>
+      <c r="E45" s="7">
+        <v>3.78</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5">
+      <c r="A46" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B46" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C46" s="6">
+        <v>-20.11</v>
+      </c>
+      <c r="D46" s="6">
+        <v>-12.14</v>
+      </c>
+      <c r="E46" s="7">
+        <v>7.97</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5">
+      <c r="A47" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B47" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C47" s="6">
+        <v>-34.77</v>
+      </c>
+      <c r="D47" s="6">
+        <v>-34.86</v>
+      </c>
+      <c r="E47" s="8">
+        <v>-0.09</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5">
+      <c r="A48" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="B48" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C48" s="6">
+        <v>-15.34</v>
+      </c>
+      <c r="D48" s="6">
+        <v>-14.34</v>
+      </c>
+      <c r="E48" s="7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5">
+      <c r="A49" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B49" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C49" s="6">
+        <v>347.25</v>
+      </c>
+      <c r="D49" s="6">
+        <v>353.05</v>
+      </c>
+      <c r="E49" s="7">
+        <v>5.8</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5">
+      <c r="A50" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B50" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C50" s="6">
+        <v>39.77</v>
+      </c>
+      <c r="D50" s="6">
+        <v>39.58</v>
+      </c>
+      <c r="E50" s="8">
+        <v>-0.19</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5">
+      <c r="A51" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B51" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C51" s="6">
+        <v>2894</v>
+      </c>
+      <c r="D51" s="6">
+        <v>2950</v>
+      </c>
+      <c r="E51" s="7">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5">
+      <c r="A52" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B52" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C52" s="6">
+        <v>869.85</v>
+      </c>
+      <c r="D52" s="6">
+        <v>885.65</v>
+      </c>
+      <c r="E52" s="7">
+        <v>15.8</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5">
+      <c r="A53" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B53" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C53" s="6">
+        <v>11.36</v>
+      </c>
+      <c r="D53" s="6">
+        <v>11.95</v>
+      </c>
+      <c r="E53" s="7">
+        <v>0.59</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5">
+      <c r="A54" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B54" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C54" s="6">
+        <v>11.12</v>
+      </c>
+      <c r="D54" s="6">
+        <v>12.23</v>
+      </c>
+      <c r="E54" s="7">
+        <v>1.11</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5">
+      <c r="A55" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B55" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C55" s="6">
+        <v>3789.3</v>
+      </c>
+      <c r="D55" s="6">
+        <v>3784.3</v>
+      </c>
+      <c r="E55" s="8">
+        <v>-5</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5">
+      <c r="A56" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="B56" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C56" s="6">
+        <v>11050</v>
+      </c>
+      <c r="D56" s="6">
+        <v>11180</v>
+      </c>
+      <c r="E56" s="7">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5">
+      <c r="A57" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B57" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C57" s="6">
+        <v>75</v>
+      </c>
+      <c r="D57" s="6">
+        <v>62</v>
+      </c>
+      <c r="E57" s="8">
+        <v>-13</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5">
+      <c r="A58" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B58" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C58" s="6">
+        <v>62</v>
+      </c>
+      <c r="D58" s="6">
+        <v>75</v>
+      </c>
+      <c r="E58" s="7">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5">
+      <c r="A59" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B59" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C59" s="6">
+        <v>29.03</v>
+      </c>
+      <c r="D59" s="6">
+        <v>34.04</v>
+      </c>
+      <c r="E59" s="7">
+        <v>5.01</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5">
+      <c r="A60" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B60" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C60" s="6">
+        <v>23.47</v>
+      </c>
+      <c r="D60" s="6">
+        <v>23.08</v>
+      </c>
+      <c r="E60" s="8">
+        <v>-0.39</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5">
+      <c r="A61" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B61" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C61" s="6">
+        <v>36.68</v>
+      </c>
+      <c r="D61" s="6">
+        <v>44.53</v>
+      </c>
+      <c r="E61" s="7">
+        <v>7.85</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5">
+      <c r="A62" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B62" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C62" s="6">
+        <v>32.28</v>
+      </c>
+      <c r="D62" s="6">
+        <v>38.24</v>
+      </c>
+      <c r="E62" s="7">
+        <v>5.96</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5">
+      <c r="A63" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B63" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C63" s="6">
+        <v>26.7</v>
+      </c>
+      <c r="D63" s="6">
+        <v>37.56</v>
+      </c>
+      <c r="E63" s="7">
+        <v>10.86</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5">
+      <c r="A64" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B64" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C64" s="6">
+        <v>46.81</v>
+      </c>
+      <c r="D64" s="6">
+        <v>56.82</v>
+      </c>
+      <c r="E64" s="7">
+        <v>10.01</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5">
+      <c r="A65" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B65" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C65" s="6">
+        <v>30.36</v>
+      </c>
+      <c r="D65" s="6">
+        <v>30.09</v>
+      </c>
+      <c r="E65" s="8">
         <v>-0.27</v>
       </c>
     </row>
-    <row r="20" spans="1:5">
-      <c r="A20" s="3" t="s">
+    <row r="66" spans="1:5">
+      <c r="A66" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="B66" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C66" s="6">
+        <v>53.92</v>
+      </c>
+      <c r="D66" s="6">
+        <v>57.07</v>
+      </c>
+      <c r="E66" s="7">
+        <v>3.15</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5">
+      <c r="A67" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B67" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C67" s="6">
+        <v>-36.1</v>
+      </c>
+      <c r="D67" s="6">
+        <v>-36.77</v>
+      </c>
+      <c r="E67" s="8">
+        <v>-0.67</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5">
+      <c r="A68" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B68" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C68" s="6">
+        <v>28.73</v>
+      </c>
+      <c r="D68" s="6">
+        <v>-43.77</v>
+      </c>
+      <c r="E68" s="8">
+        <v>-72.5</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5">
+      <c r="A69" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B69" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C69" s="6">
+        <v>-34.77</v>
+      </c>
+      <c r="D69" s="6">
+        <v>-52.8</v>
+      </c>
+      <c r="E69" s="8">
+        <v>-18.03</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5">
+      <c r="A70" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B70" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C70" s="6">
+        <v>97.94</v>
+      </c>
+      <c r="D70" s="6">
+        <v>-0.76</v>
+      </c>
+      <c r="E70" s="8">
+        <v>-98.7</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5">
+      <c r="A71" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B71" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C71" s="6">
+        <v>22.48</v>
+      </c>
+      <c r="D71" s="6">
+        <v>17.93</v>
+      </c>
+      <c r="E71" s="8">
+        <v>-4.55</v>
+      </c>
+    </row>
+    <row r="72" spans="1:5">
+      <c r="A72" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="B20" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C20" s="5">
-        <v>-1.81</v>
-      </c>
-      <c r="D20" s="5">
-        <v>-2.03</v>
-      </c>
-      <c r="E20" s="6">
-        <v>-0.22</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5">
-      <c r="A21" s="3" t="s">
+      <c r="B72" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C72" s="6">
+        <v>6.56</v>
+      </c>
+      <c r="D72" s="6">
+        <v>145.05</v>
+      </c>
+      <c r="E72" s="7">
+        <v>138.49</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5">
+      <c r="A73" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="B21" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C21" s="5">
-        <v>-2.61</v>
-      </c>
-      <c r="D21" s="5">
-        <v>-4.53</v>
-      </c>
-      <c r="E21" s="6">
-        <v>-1.92</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5">
-      <c r="A22" s="3" t="s">
+      <c r="B73" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C73" s="6">
+        <v>-13.67</v>
+      </c>
+      <c r="D73" s="6">
+        <v>5.84</v>
+      </c>
+      <c r="E73" s="7">
+        <v>19.51</v>
+      </c>
+    </row>
+    <row r="74" spans="1:5">
+      <c r="A74" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="B22" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C22" s="5">
-        <v>1.51</v>
-      </c>
-      <c r="D22" s="5">
-        <v>1.73</v>
-      </c>
-      <c r="E22" s="7">
-        <v>0.22</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5">
-      <c r="A23" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B23" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C23" s="5">
-        <v>19.07</v>
-      </c>
-      <c r="D23" s="5">
-        <v>16.02</v>
-      </c>
-      <c r="E23" s="6">
-        <v>-3.05</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5">
-      <c r="A24" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B24" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C24" s="5">
-        <v>-50.6</v>
-      </c>
-      <c r="D24" s="5">
-        <v>-51.67</v>
-      </c>
-      <c r="E24" s="6">
-        <v>-1.07</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5">
-      <c r="A25" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B25" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C25" s="5">
-        <v>1.21</v>
-      </c>
-      <c r="D25" s="5">
-        <v>2.04</v>
-      </c>
-      <c r="E25" s="7">
-        <v>0.83</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5">
-      <c r="A26" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="B26" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C26" s="5">
-        <v>13.52</v>
-      </c>
-      <c r="D26" s="5">
-        <v>12.56</v>
-      </c>
-      <c r="E26" s="6">
-        <v>-0.96</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5">
-      <c r="A27" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="B27" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C27" s="5">
-        <v>30.28</v>
-      </c>
-      <c r="D27" s="5">
-        <v>30.57</v>
-      </c>
-      <c r="E27" s="7">
-        <v>0.29</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5">
-      <c r="A28" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="B28" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C28" s="5">
-        <v>118.39</v>
-      </c>
-      <c r="D28" s="5">
-        <v>111.01</v>
-      </c>
-      <c r="E28" s="6">
-        <v>-7.38</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5">
-      <c r="A29" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="B29" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C29" s="5">
-        <v>-27.55</v>
-      </c>
-      <c r="D29" s="5">
-        <v>-32.69</v>
-      </c>
-      <c r="E29" s="6">
-        <v>-5.14</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5">
-      <c r="A30" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="B30" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C30" s="5">
-        <v>-11.33</v>
-      </c>
-      <c r="D30" s="5">
-        <v>-10.67</v>
-      </c>
-      <c r="E30" s="7">
-        <v>0.66</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5">
-      <c r="A31" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B31" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C31" s="5">
-        <v>-10.83</v>
-      </c>
-      <c r="D31" s="5">
-        <v>-11.47</v>
-      </c>
-      <c r="E31" s="6">
-        <v>-0.64</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5">
-      <c r="A32" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B32" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C32" s="5">
-        <v>-27.54</v>
-      </c>
-      <c r="D32" s="5">
-        <v>-29.02</v>
-      </c>
-      <c r="E32" s="6">
-        <v>-1.48</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5">
-      <c r="A33" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B33" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C33" s="5">
-        <v>-8.59</v>
-      </c>
-      <c r="D33" s="5">
-        <v>-7.04</v>
-      </c>
-      <c r="E33" s="7">
-        <v>1.55</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5">
-      <c r="A34" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="B34" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C34" s="5">
-        <v>-6.78</v>
-      </c>
-      <c r="D34" s="5">
-        <v>-8.98</v>
-      </c>
-      <c r="E34" s="6">
-        <v>-2.2</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5">
-      <c r="A35" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="B35" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C35" s="5">
-        <v>-14.84</v>
-      </c>
-      <c r="D35" s="5">
-        <v>-13.94</v>
-      </c>
-      <c r="E35" s="7">
-        <v>0.9</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5">
-      <c r="A36" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="B36" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C36" s="5">
-        <v>-5.71</v>
-      </c>
-      <c r="D36" s="5">
-        <v>-6.95</v>
-      </c>
-      <c r="E36" s="6">
-        <v>-1.24</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5">
-      <c r="A37" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="B37" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C37" s="5">
-        <v>-10.72</v>
-      </c>
-      <c r="D37" s="5">
-        <v>-11.94</v>
-      </c>
-      <c r="E37" s="6">
-        <v>-1.22</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5">
-      <c r="A38" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="B38" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C38" s="5">
-        <v>-7.86</v>
-      </c>
-      <c r="D38" s="5">
-        <v>-7.21</v>
-      </c>
-      <c r="E38" s="7">
-        <v>0.65</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5">
-      <c r="A39" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B39" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C39" s="5">
-        <v>-15.89</v>
-      </c>
-      <c r="D39" s="5">
-        <v>-18.24</v>
-      </c>
-      <c r="E39" s="6">
-        <v>-2.35</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5">
-      <c r="A40" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B40" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C40" s="5">
-        <v>-51.58</v>
-      </c>
-      <c r="D40" s="5">
-        <v>-53.42</v>
-      </c>
-      <c r="E40" s="6">
-        <v>-1.84</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5">
-      <c r="A41" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B41" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C41" s="5">
-        <v>-14.38</v>
-      </c>
-      <c r="D41" s="5">
-        <v>-14.39</v>
-      </c>
-      <c r="E41" s="6">
-        <v>-0.01</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5">
-      <c r="A42" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="B42" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C42" s="5">
-        <v>-22.97</v>
-      </c>
-      <c r="D42" s="5">
-        <v>-24.34</v>
-      </c>
-      <c r="E42" s="6">
-        <v>-1.37</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5">
-      <c r="A43" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="B43" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C43" s="5">
-        <v>-26.09</v>
-      </c>
-      <c r="D43" s="5">
-        <v>-27.18</v>
-      </c>
-      <c r="E43" s="6">
-        <v>-1.09</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5">
-      <c r="A44" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="B44" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C44" s="5">
-        <v>-18.1</v>
-      </c>
-      <c r="D44" s="5">
-        <v>-20.11</v>
-      </c>
-      <c r="E44" s="6">
-        <v>-2.01</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5">
-      <c r="A45" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="B45" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C45" s="5">
-        <v>-33.11</v>
-      </c>
-      <c r="D45" s="5">
-        <v>-34.77</v>
-      </c>
-      <c r="E45" s="6">
-        <v>-1.66</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5">
-      <c r="A46" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="B46" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C46" s="5">
-        <v>-16.04</v>
-      </c>
-      <c r="D46" s="5">
-        <v>-15.34</v>
-      </c>
-      <c r="E46" s="7">
-        <v>0.7</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5">
-      <c r="A47" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B47" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C47" s="5">
-        <v>357.2</v>
-      </c>
-      <c r="D47" s="5">
-        <v>347.25</v>
-      </c>
-      <c r="E47" s="6">
-        <v>-9.949999999999999</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5">
-      <c r="A48" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B48" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C48" s="5">
-        <v>41.34</v>
-      </c>
-      <c r="D48" s="5">
-        <v>39.77</v>
-      </c>
-      <c r="E48" s="6">
-        <v>-1.57</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5">
-      <c r="A49" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B49" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C49" s="5">
-        <v>2894.4</v>
-      </c>
-      <c r="D49" s="5">
-        <v>2894</v>
-      </c>
-      <c r="E49" s="6">
-        <v>-0.4</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5">
-      <c r="A50" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="B50" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C50" s="5">
-        <v>885.6</v>
-      </c>
-      <c r="D50" s="5">
-        <v>869.85</v>
-      </c>
-      <c r="E50" s="6">
-        <v>-15.75</v>
-      </c>
-    </row>
-    <row r="51" spans="1:5">
-      <c r="A51" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="B51" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C51" s="5">
-        <v>11.53</v>
-      </c>
-      <c r="D51" s="5">
-        <v>11.36</v>
-      </c>
-      <c r="E51" s="6">
-        <v>-0.17</v>
-      </c>
-    </row>
-    <row r="52" spans="1:5">
-      <c r="A52" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="B52" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C52" s="5">
-        <v>11.4</v>
-      </c>
-      <c r="D52" s="5">
-        <v>11.12</v>
-      </c>
-      <c r="E52" s="6">
-        <v>-0.28</v>
-      </c>
-    </row>
-    <row r="53" spans="1:5">
-      <c r="A53" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="B53" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C53" s="5">
-        <v>3885.7</v>
-      </c>
-      <c r="D53" s="5">
-        <v>3789.3</v>
-      </c>
-      <c r="E53" s="6">
-        <v>-96.40000000000001</v>
-      </c>
-    </row>
-    <row r="54" spans="1:5">
-      <c r="A54" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="B54" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C54" s="5">
-        <v>10958</v>
-      </c>
-      <c r="D54" s="5">
-        <v>11050</v>
-      </c>
-      <c r="E54" s="7">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="55" spans="1:5">
-      <c r="A55" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B55" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C55" s="5">
-        <v>33.03</v>
-      </c>
-      <c r="D55" s="5">
-        <v>29.03</v>
-      </c>
-      <c r="E55" s="6">
-        <v>-4</v>
-      </c>
-    </row>
-    <row r="56" spans="1:5">
-      <c r="A56" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B56" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C56" s="5">
-        <v>26.9</v>
-      </c>
-      <c r="D56" s="5">
-        <v>23.47</v>
-      </c>
-      <c r="E56" s="6">
-        <v>-3.43</v>
-      </c>
-    </row>
-    <row r="57" spans="1:5">
-      <c r="A57" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B57" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C57" s="5">
-        <v>36.71</v>
-      </c>
-      <c r="D57" s="5">
-        <v>36.68</v>
-      </c>
-      <c r="E57" s="6">
-        <v>-0.03</v>
-      </c>
-    </row>
-    <row r="58" spans="1:5">
-      <c r="A58" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="B58" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C58" s="5">
-        <v>35.44</v>
-      </c>
-      <c r="D58" s="5">
-        <v>32.28</v>
-      </c>
-      <c r="E58" s="6">
-        <v>-3.16</v>
-      </c>
-    </row>
-    <row r="59" spans="1:5">
-      <c r="A59" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="B59" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C59" s="5">
-        <v>28</v>
-      </c>
-      <c r="D59" s="5">
-        <v>26.7</v>
-      </c>
-      <c r="E59" s="6">
-        <v>-1.3</v>
-      </c>
-    </row>
-    <row r="60" spans="1:5">
-      <c r="A60" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="B60" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C60" s="5">
-        <v>49.5</v>
-      </c>
-      <c r="D60" s="5">
-        <v>46.81</v>
-      </c>
-      <c r="E60" s="6">
-        <v>-2.69</v>
-      </c>
-    </row>
-    <row r="61" spans="1:5">
-      <c r="A61" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="B61" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C61" s="5">
-        <v>36.23</v>
-      </c>
-      <c r="D61" s="5">
-        <v>30.36</v>
-      </c>
-      <c r="E61" s="6">
-        <v>-5.87</v>
-      </c>
-    </row>
-    <row r="62" spans="1:5">
-      <c r="A62" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="B62" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C62" s="5">
-        <v>51.59</v>
-      </c>
-      <c r="D62" s="5">
-        <v>53.92</v>
-      </c>
-      <c r="E62" s="7">
-        <v>2.33</v>
-      </c>
-    </row>
-    <row r="63" spans="1:5">
-      <c r="A63" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B63" s="3" t="s">
+      <c r="B74" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="C63" s="5">
-        <v>-2.77</v>
-      </c>
-      <c r="D63" s="5">
-        <v>-36.1</v>
-      </c>
-      <c r="E63" s="6">
-        <v>-33.33</v>
-      </c>
-    </row>
-    <row r="64" spans="1:5">
-      <c r="A64" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B64" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C64" s="5">
-        <v>0.25</v>
-      </c>
-      <c r="D64" s="5">
-        <v>28.73</v>
-      </c>
-      <c r="E64" s="7">
-        <v>28.48</v>
-      </c>
-    </row>
-    <row r="65" spans="1:5">
-      <c r="A65" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B65" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C65" s="5">
-        <v>-55.32</v>
-      </c>
-      <c r="D65" s="5">
-        <v>-34.77</v>
-      </c>
-      <c r="E65" s="7">
-        <v>20.55</v>
-      </c>
-    </row>
-    <row r="66" spans="1:5">
-      <c r="A66" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="B66" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C66" s="5">
-        <v>-6.44</v>
-      </c>
-      <c r="D66" s="5">
-        <v>97.94</v>
-      </c>
-      <c r="E66" s="7">
-        <v>104.38</v>
-      </c>
-    </row>
-    <row r="67" spans="1:5">
-      <c r="A67" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="B67" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C67" s="5">
-        <v>22.94</v>
-      </c>
-      <c r="D67" s="5">
-        <v>22.48</v>
-      </c>
-      <c r="E67" s="6">
-        <v>-0.46</v>
-      </c>
-    </row>
-    <row r="68" spans="1:5">
-      <c r="A68" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="B68" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C68" s="5">
-        <v>26.19</v>
-      </c>
-      <c r="D68" s="5">
-        <v>6.56</v>
-      </c>
-      <c r="E68" s="6">
-        <v>-19.63</v>
-      </c>
-    </row>
-    <row r="69" spans="1:5">
-      <c r="A69" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="B69" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C69" s="5">
-        <v>-3.75</v>
-      </c>
-      <c r="D69" s="5">
-        <v>-13.67</v>
-      </c>
-      <c r="E69" s="6">
-        <v>-9.92</v>
-      </c>
-    </row>
-    <row r="70" spans="1:5">
-      <c r="A70" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="B70" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C70" s="5">
-        <v>-43.23</v>
-      </c>
-      <c r="D70" s="5">
+      <c r="C74" s="6">
         <v>-0.3</v>
       </c>
-      <c r="E70" s="7">
-        <v>42.93</v>
+      <c r="D74" s="6">
+        <v>-9.34</v>
+      </c>
+      <c r="E74" s="8">
+        <v>-9.039999999999999</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A5:E5"/>
+    <mergeCell ref="A7:E7"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3094,60 +3253,60 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="28" customHeight="1">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="8" t="s">
-        <v>57</v>
-      </c>
-      <c r="C1" s="8" t="s">
-        <v>58</v>
-      </c>
-      <c r="D1" s="8" t="s">
-        <v>59</v>
-      </c>
-      <c r="E1" s="8" t="s">
-        <v>60</v>
-      </c>
-      <c r="F1" s="8" t="s">
-        <v>61</v>
-      </c>
-      <c r="G1" s="8" t="s">
-        <v>62</v>
-      </c>
-      <c r="H1" s="8" t="s">
-        <v>63</v>
-      </c>
-      <c r="I1" s="8" t="s">
-        <v>64</v>
+      <c r="B1" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="C1" s="9" t="s">
+        <v>74</v>
+      </c>
+      <c r="D1" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="E1" s="9" t="s">
+        <v>76</v>
+      </c>
+      <c r="F1" s="9" t="s">
+        <v>77</v>
+      </c>
+      <c r="G1" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="H1" s="9" t="s">
+        <v>79</v>
+      </c>
+      <c r="I1" s="9" t="s">
+        <v>80</v>
       </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="9" t="s">
+      <c r="A2" s="10" t="s">
         <v>45</v>
       </c>
-      <c r="B2" s="10">
+      <c r="B2" s="11">
         <v>37.44</v>
       </c>
-      <c r="C2" s="11">
+      <c r="C2" s="12">
         <v>8</v>
       </c>
-      <c r="D2" s="10">
-        <v>34.9</v>
-      </c>
-      <c r="E2" s="10">
+      <c r="D2" s="11">
+        <v>40.2</v>
+      </c>
+      <c r="E2" s="11">
         <v>12.5</v>
       </c>
-      <c r="F2" s="10">
-        <v>-9.699999999999999</v>
-      </c>
-      <c r="G2" s="10">
-        <v>-12.1</v>
-      </c>
-      <c r="H2" s="10">
+      <c r="F2" s="11">
+        <v>-8.6</v>
+      </c>
+      <c r="G2" s="11">
+        <v>-9.1</v>
+      </c>
+      <c r="H2" s="11">
         <v>56.1</v>
       </c>
-      <c r="I2" s="10">
+      <c r="I2" s="11">
         <v>0</v>
       </c>
     </row>
@@ -3249,55 +3408,55 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8">
-      <c r="A1" s="12" t="s">
+      <c r="A1" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="B1" s="12" t="s">
+      <c r="B1" s="13" t="s">
         <v>43</v>
       </c>
-      <c r="C1" s="12" t="s">
+      <c r="C1" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="D1" s="12" t="s">
+      <c r="D1" s="13" t="s">
         <v>39</v>
       </c>
-      <c r="E1" s="12" t="s">
+      <c r="E1" s="13" t="s">
         <v>44</v>
       </c>
-      <c r="F1" s="12" t="s">
+      <c r="F1" s="13" t="s">
         <v>41</v>
       </c>
-      <c r="G1" s="12" t="s">
+      <c r="G1" s="13" t="s">
         <v>42</v>
       </c>
-      <c r="H1" s="12" t="s">
+      <c r="H1" s="13" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="2" spans="1:8">
-      <c r="A2" s="13">
-        <v>0.2898</v>
-      </c>
-      <c r="B2" s="13">
-        <v>0.1595</v>
-      </c>
-      <c r="C2" s="13">
-        <v>0.1361</v>
-      </c>
-      <c r="D2" s="13">
-        <v>0.1162</v>
-      </c>
-      <c r="E2" s="13">
-        <v>0.096</v>
-      </c>
-      <c r="F2" s="13">
-        <v>0.0178</v>
-      </c>
-      <c r="G2" s="13">
-        <v>-0.2983</v>
-      </c>
-      <c r="H2" s="13">
-        <v>-0.3071</v>
+      <c r="A2" s="14">
+        <v>0.2862</v>
+      </c>
+      <c r="B2" s="14">
+        <v>0.1601</v>
+      </c>
+      <c r="C2" s="14">
+        <v>0.134</v>
+      </c>
+      <c r="D2" s="14">
+        <v>0.1166</v>
+      </c>
+      <c r="E2" s="14">
+        <v>0.09480000000000001</v>
+      </c>
+      <c r="F2" s="14">
+        <v>0.0282</v>
+      </c>
+      <c r="G2" s="14">
+        <v>-0.2855</v>
+      </c>
+      <c r="H2" s="14">
+        <v>-0.3139</v>
       </c>
     </row>
   </sheetData>

--- a/BIRLA_GROUP_Technical_Metrics.xlsx
+++ b/BIRLA_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="303" uniqueCount="81">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="276" uniqueCount="65">
   <si>
     <t>Symbol</t>
   </si>
@@ -175,55 +175,7 @@
     <t>▶  SIGNAL EVENTS (vs Previous Run)</t>
   </si>
   <si>
-    <t>Signal</t>
-  </si>
-  <si>
-    <t>Change</t>
-  </si>
-  <si>
-    <t>Direction</t>
-  </si>
-  <si>
-    <t>Prev Value</t>
-  </si>
-  <si>
-    <t>Curr Value</t>
-  </si>
-  <si>
-    <t>RSI Oversold Recovery</t>
-  </si>
-  <si>
-    <t>29.0 → 34.0</t>
-  </si>
-  <si>
-    <t>🟢 BULLISH</t>
-  </si>
-  <si>
-    <t>29.0</t>
-  </si>
-  <si>
-    <t>34.0</t>
-  </si>
-  <si>
-    <t>26.7 → 37.6</t>
-  </si>
-  <si>
-    <t>26.7</t>
-  </si>
-  <si>
-    <t>37.6</t>
-  </si>
-  <si>
-    <t>RSI Momentum</t>
-  </si>
-  <si>
-    <t>46.8 → 56.8</t>
-  </si>
-  <si>
-    <t>46.8</t>
-  </si>
-  <si>
-    <t>56.8</t>
+    <t>No signal events detected since last run.</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -425,15 +377,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -807,10 +758,9 @@
     <col min="13" max="13" width="10.7109375" customWidth="1"/>
     <col min="14" max="14" width="11.7109375" customWidth="1"/>
     <col min="15" max="15" width="10.7109375" customWidth="1"/>
-    <col min="16" max="16" width="9.7109375" customWidth="1"/>
-    <col min="17" max="17" width="10.7109375" customWidth="1"/>
-    <col min="18" max="18" width="9.7109375" customWidth="1"/>
-    <col min="19" max="19" width="10.7109375" customWidth="1"/>
+    <col min="16" max="17" width="9.7109375" customWidth="1"/>
+    <col min="18" max="18" width="10.7109375" customWidth="1"/>
+    <col min="19" max="19" width="9.7109375" customWidth="1"/>
     <col min="20" max="20" width="22.7109375" customWidth="1"/>
     <col min="21" max="21" width="9.7109375" customWidth="1"/>
     <col min="22" max="22" width="10.7109375" customWidth="1"/>
@@ -950,10 +900,10 @@
         <v>45</v>
       </c>
       <c r="C2">
-        <v>353.05</v>
+        <v>353.55</v>
       </c>
       <c r="D2">
-        <v>1.67</v>
+        <v>0.14</v>
       </c>
       <c r="E2">
         <v>424.7</v>
@@ -962,46 +912,46 @@
         <v>292.25</v>
       </c>
       <c r="G2">
-        <v>-16.87</v>
+        <v>-16.75</v>
       </c>
       <c r="H2">
-        <v>20.8</v>
+        <v>20.98</v>
       </c>
       <c r="I2">
-        <v>-6.95</v>
+        <v>-5.23</v>
       </c>
       <c r="J2">
-        <v>-12.27</v>
+        <v>-9.369999999999999</v>
       </c>
       <c r="K2">
-        <v>-10.36</v>
+        <v>-11.71</v>
       </c>
       <c r="L2">
-        <v>15.62</v>
+        <v>15.98</v>
       </c>
       <c r="M2">
-        <v>28.62</v>
+        <v>29.1</v>
       </c>
       <c r="N2">
         <v>62</v>
       </c>
       <c r="O2">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="P2">
-        <v>359.51</v>
+        <v>355.61</v>
       </c>
       <c r="Q2">
-        <v>374.35</v>
+        <v>372.53</v>
       </c>
       <c r="R2">
-        <v>390.4</v>
+        <v>389.31</v>
       </c>
       <c r="S2">
-        <v>366.12</v>
+        <v>366.08</v>
       </c>
       <c r="T2">
-        <v>-3.57</v>
+        <v>-3.42</v>
       </c>
       <c r="U2" t="s">
         <v>46</v>
@@ -1016,34 +966,34 @@
         <v>1</v>
       </c>
       <c r="Y2">
-        <v>34.04</v>
+        <v>34.47</v>
       </c>
       <c r="Z2">
-        <v>-9.210000000000001</v>
+        <v>-9.66</v>
       </c>
       <c r="AA2">
-        <v>-6.8</v>
+        <v>-7.37</v>
       </c>
       <c r="AB2">
-        <v>-2.42</v>
+        <v>-2.29</v>
       </c>
       <c r="AC2">
-        <v>8.720000000000001</v>
+        <v>18.19</v>
       </c>
       <c r="AD2">
-        <v>11.46</v>
+        <v>10.81</v>
       </c>
       <c r="AE2">
-        <v>10.52</v>
+        <v>10.13</v>
       </c>
       <c r="AF2">
-        <v>-36.77</v>
+        <v>-29.06</v>
       </c>
       <c r="AG2">
-        <v>396.18</v>
+        <v>394.94</v>
       </c>
       <c r="AH2">
-        <v>352.53</v>
+        <v>350.13</v>
       </c>
       <c r="AI2">
         <v>375.32</v>
@@ -1052,7 +1002,7 @@
         <v>48</v>
       </c>
       <c r="AK2">
-        <v>37.95</v>
+        <v>41.69</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1063,10 +1013,10 @@
         <v>45</v>
       </c>
       <c r="C3">
-        <v>39.58</v>
+        <v>39.97</v>
       </c>
       <c r="D3">
-        <v>-0.48</v>
+        <v>0.99</v>
       </c>
       <c r="E3">
         <v>85.38</v>
@@ -1075,25 +1025,25 @@
         <v>39.58</v>
       </c>
       <c r="G3">
-        <v>-53.64</v>
+        <v>-53.19</v>
       </c>
       <c r="H3">
-        <v>0</v>
+        <v>0.99</v>
       </c>
       <c r="I3">
-        <v>-11.71</v>
+        <v>-7.37</v>
       </c>
       <c r="J3">
-        <v>-19.37</v>
+        <v>-16.83</v>
       </c>
       <c r="K3">
-        <v>-29.64</v>
+        <v>-29.94</v>
       </c>
       <c r="L3">
-        <v>-52.33</v>
+        <v>-52.22</v>
       </c>
       <c r="M3">
-        <v>-31.39</v>
+        <v>-30.95</v>
       </c>
       <c r="N3">
         <v>13</v>
@@ -1102,19 +1052,19 @@
         <v>4</v>
       </c>
       <c r="P3">
-        <v>41.37</v>
+        <v>40.73</v>
       </c>
       <c r="Q3">
-        <v>44.27</v>
+        <v>43.81</v>
       </c>
       <c r="R3">
-        <v>49.05</v>
+        <v>48.71</v>
       </c>
       <c r="S3">
-        <v>59.77</v>
+        <v>59.59</v>
       </c>
       <c r="T3">
-        <v>-33.78</v>
+        <v>-32.92</v>
       </c>
       <c r="U3" t="s">
         <v>46</v>
@@ -1129,43 +1079,43 @@
         <v>0</v>
       </c>
       <c r="Y3">
-        <v>23.08</v>
+        <v>25.77</v>
       </c>
       <c r="Z3">
-        <v>-2.39</v>
+        <v>-2.44</v>
       </c>
       <c r="AA3">
-        <v>-2.15</v>
+        <v>-2.21</v>
       </c>
       <c r="AB3">
         <v>-0.23</v>
       </c>
       <c r="AC3">
-        <v>6.75</v>
+        <v>5.62</v>
       </c>
       <c r="AD3">
-        <v>23.79</v>
+        <v>11.95</v>
       </c>
       <c r="AE3">
-        <v>1.71</v>
+        <v>1.67</v>
       </c>
       <c r="AF3">
-        <v>-43.77</v>
+        <v>-46.61</v>
       </c>
       <c r="AG3">
-        <v>48.92</v>
+        <v>48.25</v>
       </c>
       <c r="AH3">
-        <v>39.62</v>
+        <v>39.38</v>
       </c>
       <c r="AI3">
-        <v>44.98</v>
+        <v>44.72</v>
       </c>
       <c r="AJ3" t="s">
         <v>48</v>
       </c>
       <c r="AK3">
-        <v>39.28</v>
+        <v>42.4</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1176,10 +1126,10 @@
         <v>45</v>
       </c>
       <c r="C4">
-        <v>2950</v>
+        <v>2900.8</v>
       </c>
       <c r="D4">
-        <v>1.94</v>
+        <v>-1.67</v>
       </c>
       <c r="E4">
         <v>3380.5</v>
@@ -1188,46 +1138,46 @@
         <v>2531.1</v>
       </c>
       <c r="G4">
-        <v>-12.73</v>
+        <v>-14.19</v>
       </c>
       <c r="H4">
-        <v>16.55</v>
+        <v>14.61</v>
       </c>
       <c r="I4">
-        <v>1.03</v>
+        <v>0.76</v>
       </c>
       <c r="J4">
-        <v>-7.48</v>
+        <v>-8.390000000000001</v>
       </c>
       <c r="K4">
-        <v>-4.51</v>
+        <v>-6.8</v>
       </c>
       <c r="L4">
-        <v>3.36</v>
+        <v>1.05</v>
       </c>
       <c r="M4">
-        <v>11.66</v>
+        <v>11.43</v>
       </c>
       <c r="N4">
         <v>50</v>
       </c>
       <c r="O4">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="P4">
-        <v>2901.3</v>
+        <v>2905.66</v>
       </c>
       <c r="Q4">
-        <v>2951.46</v>
+        <v>2936.95</v>
       </c>
       <c r="R4">
-        <v>3137.4</v>
+        <v>3130.28</v>
       </c>
       <c r="S4">
-        <v>2982.65</v>
+        <v>2982.83</v>
       </c>
       <c r="T4">
-        <v>-1.09</v>
+        <v>-2.75</v>
       </c>
       <c r="U4" t="s">
         <v>46</v>
@@ -1242,34 +1192,34 @@
         <v>1</v>
       </c>
       <c r="Y4">
-        <v>44.53</v>
+        <v>39.86</v>
       </c>
       <c r="Z4">
-        <v>-69.20999999999999</v>
+        <v>-65.79000000000001</v>
       </c>
       <c r="AA4">
-        <v>-80.08</v>
+        <v>-77.22</v>
       </c>
       <c r="AB4">
-        <v>10.87</v>
+        <v>11.43</v>
       </c>
       <c r="AC4">
-        <v>95.68000000000001</v>
+        <v>90.43000000000001</v>
       </c>
       <c r="AD4">
-        <v>91.51000000000001</v>
+        <v>92.65000000000001</v>
       </c>
       <c r="AE4">
-        <v>63.93</v>
+        <v>64.29000000000001</v>
       </c>
       <c r="AF4">
-        <v>-52.8</v>
+        <v>1.57</v>
       </c>
       <c r="AG4">
-        <v>3147.74</v>
+        <v>3098.5</v>
       </c>
       <c r="AH4">
-        <v>2755.18</v>
+        <v>2775.4</v>
       </c>
       <c r="AI4">
         <v>3050.83</v>
@@ -1278,7 +1228,7 @@
         <v>48</v>
       </c>
       <c r="AK4">
-        <v>49.31</v>
+        <v>43.14</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1289,10 +1239,10 @@
         <v>45</v>
       </c>
       <c r="C5">
-        <v>885.65</v>
+        <v>891.2</v>
       </c>
       <c r="D5">
-        <v>1.82</v>
+        <v>0.63</v>
       </c>
       <c r="E5">
         <v>1149.7</v>
@@ -1301,25 +1251,25 @@
         <v>774.65</v>
       </c>
       <c r="G5">
-        <v>-22.97</v>
+        <v>-22.48</v>
       </c>
       <c r="H5">
-        <v>14.33</v>
+        <v>15.05</v>
       </c>
       <c r="I5">
-        <v>-2.46</v>
+        <v>-1.03</v>
       </c>
       <c r="J5">
-        <v>-11.77</v>
+        <v>-9.25</v>
       </c>
       <c r="K5">
-        <v>-6.06</v>
+        <v>-5.72</v>
       </c>
       <c r="L5">
-        <v>12.63</v>
+        <v>13.54</v>
       </c>
       <c r="M5">
-        <v>13.4</v>
+        <v>13.83</v>
       </c>
       <c r="N5">
         <v>75</v>
@@ -1328,19 +1278,19 @@
         <v>74</v>
       </c>
       <c r="P5">
-        <v>886.88</v>
+        <v>885.03</v>
       </c>
       <c r="Q5">
-        <v>912.77</v>
+        <v>908.48</v>
       </c>
       <c r="R5">
-        <v>973.72</v>
+        <v>970.62</v>
       </c>
       <c r="S5">
-        <v>983.09</v>
+        <v>982.84</v>
       </c>
       <c r="T5">
-        <v>-9.91</v>
+        <v>-9.32</v>
       </c>
       <c r="U5" t="s">
         <v>46</v>
@@ -1355,34 +1305,34 @@
         <v>0</v>
       </c>
       <c r="Y5">
-        <v>38.24</v>
+        <v>40.22</v>
       </c>
       <c r="Z5">
-        <v>-25.98</v>
+        <v>-24.54</v>
       </c>
       <c r="AA5">
-        <v>-26.04</v>
+        <v>-25.74</v>
       </c>
       <c r="AB5">
-        <v>0.07000000000000001</v>
+        <v>1.2</v>
       </c>
       <c r="AC5">
-        <v>65.48999999999999</v>
+        <v>76.55</v>
       </c>
       <c r="AD5">
-        <v>68.48</v>
+        <v>68.22</v>
       </c>
       <c r="AE5">
-        <v>24.69</v>
+        <v>23.89</v>
       </c>
       <c r="AF5">
-        <v>-0.76</v>
+        <v>-6.19</v>
       </c>
       <c r="AG5">
-        <v>973.92</v>
+        <v>962.25</v>
       </c>
       <c r="AH5">
-        <v>851.63</v>
+        <v>854.72</v>
       </c>
       <c r="AI5">
         <v>933.28</v>
@@ -1391,7 +1341,7 @@
         <v>48</v>
       </c>
       <c r="AK5">
-        <v>46.31</v>
+        <v>43.83</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1402,10 +1352,10 @@
         <v>45</v>
       </c>
       <c r="C6">
-        <v>11.95</v>
+        <v>12.11</v>
       </c>
       <c r="D6">
-        <v>5.19</v>
+        <v>1.34</v>
       </c>
       <c r="E6">
         <v>15.6</v>
@@ -1414,25 +1364,25 @@
         <v>8.529999999999999</v>
       </c>
       <c r="G6">
-        <v>-23.4</v>
+        <v>-22.37</v>
       </c>
       <c r="H6">
-        <v>40.09</v>
+        <v>41.97</v>
       </c>
       <c r="I6">
-        <v>-5.08</v>
+        <v>-1.38</v>
       </c>
       <c r="J6">
-        <v>-17.7</v>
+        <v>-14.24</v>
       </c>
       <c r="K6">
-        <v>-8.99</v>
+        <v>-7.27</v>
       </c>
       <c r="L6">
-        <v>33.67</v>
+        <v>34.56</v>
       </c>
       <c r="M6">
-        <v>2.82</v>
+        <v>3.39</v>
       </c>
       <c r="N6">
         <v>87</v>
@@ -1441,19 +1391,19 @@
         <v>81</v>
       </c>
       <c r="P6">
-        <v>11.75</v>
+        <v>11.72</v>
       </c>
       <c r="Q6">
-        <v>12.69</v>
+        <v>12.58</v>
       </c>
       <c r="R6">
-        <v>13.75</v>
+        <v>13.73</v>
       </c>
       <c r="S6">
         <v>12.31</v>
       </c>
       <c r="T6">
-        <v>-2.89</v>
+        <v>-1.61</v>
       </c>
       <c r="U6" t="s">
         <v>46</v>
@@ -1468,34 +1418,34 @@
         <v>1</v>
       </c>
       <c r="Y6">
-        <v>37.56</v>
+        <v>40.15</v>
       </c>
       <c r="Z6">
-        <v>-0.59</v>
+        <v>-0.5600000000000001</v>
       </c>
       <c r="AA6">
-        <v>-0.5</v>
+        <v>-0.51</v>
       </c>
       <c r="AB6">
-        <v>-0.09</v>
+        <v>-0.05</v>
       </c>
       <c r="AC6">
-        <v>24.24</v>
+        <v>54.88</v>
       </c>
       <c r="AD6">
-        <v>10.03</v>
+        <v>26.37</v>
       </c>
       <c r="AE6">
-        <v>0.49</v>
+        <v>0.47</v>
       </c>
       <c r="AF6">
-        <v>17.93</v>
+        <v>-13.74</v>
       </c>
       <c r="AG6">
-        <v>14.11</v>
+        <v>13.81</v>
       </c>
       <c r="AH6">
-        <v>11.28</v>
+        <v>11.36</v>
       </c>
       <c r="AI6">
         <v>12.7</v>
@@ -1504,7 +1454,7 @@
         <v>48</v>
       </c>
       <c r="AK6">
-        <v>57.31</v>
+        <v>53.66</v>
       </c>
     </row>
     <row r="7" spans="1:37">
@@ -1515,10 +1465,10 @@
         <v>45</v>
       </c>
       <c r="C7">
-        <v>12.23</v>
+        <v>12.63</v>
       </c>
       <c r="D7">
-        <v>9.98</v>
+        <v>3.27</v>
       </c>
       <c r="E7">
         <v>13.92</v>
@@ -1527,46 +1477,46 @@
         <v>4.69</v>
       </c>
       <c r="G7">
-        <v>-12.14</v>
+        <v>-9.27</v>
       </c>
       <c r="H7">
-        <v>160.77</v>
+        <v>169.3</v>
       </c>
       <c r="I7">
-        <v>-1.37</v>
+        <v>-0.86</v>
       </c>
       <c r="J7">
-        <v>5.7</v>
+        <v>10.89</v>
       </c>
       <c r="K7">
-        <v>4.35</v>
+        <v>10.31</v>
       </c>
       <c r="L7">
-        <v>136.56</v>
+        <v>140.57</v>
       </c>
       <c r="M7">
-        <v>-28.55</v>
+        <v>-28.34</v>
       </c>
       <c r="N7">
         <v>99</v>
       </c>
       <c r="O7">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="P7">
-        <v>11.83</v>
+        <v>11.81</v>
       </c>
       <c r="Q7">
-        <v>11.27</v>
+        <v>11.32</v>
       </c>
       <c r="R7">
-        <v>11.44</v>
+        <v>11.46</v>
       </c>
       <c r="S7">
-        <v>10.81</v>
+        <v>10.82</v>
       </c>
       <c r="T7">
-        <v>13.12</v>
+        <v>16.72</v>
       </c>
       <c r="U7" t="s">
         <v>46</v>
@@ -1581,34 +1531,34 @@
         <v>2</v>
       </c>
       <c r="Y7">
-        <v>56.82</v>
+        <v>59.76</v>
       </c>
       <c r="Z7">
-        <v>0.11</v>
+        <v>0.19</v>
       </c>
       <c r="AA7">
-        <v>0.03</v>
+        <v>0.06</v>
       </c>
       <c r="AB7">
-        <v>0.09</v>
+        <v>0.13</v>
       </c>
       <c r="AC7">
-        <v>54.31</v>
+        <v>63.27</v>
       </c>
       <c r="AD7">
-        <v>58.97</v>
+        <v>56.5</v>
       </c>
       <c r="AE7">
-        <v>0.84</v>
+        <v>0.88</v>
       </c>
       <c r="AF7">
-        <v>145.05</v>
+        <v>253.73</v>
       </c>
       <c r="AG7">
-        <v>12.54</v>
+        <v>12.73</v>
       </c>
       <c r="AH7">
-        <v>10</v>
+        <v>9.92</v>
       </c>
       <c r="AI7">
         <v>10.86</v>
@@ -1617,7 +1567,7 @@
         <v>49</v>
       </c>
       <c r="AK7">
-        <v>23.94</v>
+        <v>25.49</v>
       </c>
     </row>
     <row r="8" spans="1:37">
@@ -1628,58 +1578,58 @@
         <v>45</v>
       </c>
       <c r="C8">
-        <v>3784.3</v>
+        <v>3779.4</v>
       </c>
       <c r="D8">
         <v>-0.13</v>
       </c>
       <c r="E8">
-        <v>5809.5</v>
+        <v>5779</v>
       </c>
       <c r="F8">
-        <v>3784.3</v>
+        <v>3779.4</v>
       </c>
       <c r="G8">
-        <v>-34.86</v>
+        <v>-34.6</v>
       </c>
       <c r="H8">
         <v>0</v>
       </c>
       <c r="I8">
-        <v>-5.02</v>
+        <v>-4.36</v>
       </c>
       <c r="J8">
-        <v>-6.37</v>
+        <v>-5.68</v>
       </c>
       <c r="K8">
-        <v>-12.23</v>
+        <v>-13.02</v>
       </c>
       <c r="L8">
-        <v>-34.62</v>
+        <v>-34.94</v>
       </c>
       <c r="M8">
-        <v>16.01</v>
+        <v>15.56</v>
       </c>
       <c r="N8">
         <v>25</v>
       </c>
       <c r="O8">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="P8">
-        <v>3863.6</v>
+        <v>3829.18</v>
       </c>
       <c r="Q8">
-        <v>3952.45</v>
+        <v>3940.67</v>
       </c>
       <c r="R8">
-        <v>4142.59</v>
+        <v>4127.51</v>
       </c>
       <c r="S8">
-        <v>4436.14</v>
+        <v>4429.61</v>
       </c>
       <c r="T8">
-        <v>-14.69</v>
+        <v>-14.68</v>
       </c>
       <c r="U8" t="s">
         <v>46</v>
@@ -1694,34 +1644,34 @@
         <v>0</v>
       </c>
       <c r="Y8">
-        <v>30.09</v>
+        <v>29.81</v>
       </c>
       <c r="Z8">
-        <v>-77.26000000000001</v>
+        <v>-81.81999999999999</v>
       </c>
       <c r="AA8">
-        <v>-68.90000000000001</v>
+        <v>-71.48999999999999</v>
       </c>
       <c r="AB8">
-        <v>-8.35</v>
+        <v>-10.33</v>
       </c>
       <c r="AC8">
-        <v>13.28</v>
+        <v>0</v>
       </c>
       <c r="AD8">
-        <v>31.35</v>
+        <v>14.21</v>
       </c>
       <c r="AE8">
-        <v>100.18</v>
+        <v>107.71</v>
       </c>
       <c r="AF8">
-        <v>5.84</v>
+        <v>138.8</v>
       </c>
       <c r="AG8">
-        <v>4104.2</v>
+        <v>4107.78</v>
       </c>
       <c r="AH8">
-        <v>3800.7</v>
+        <v>3773.56</v>
       </c>
       <c r="AI8">
         <v>4043.79</v>
@@ -1730,7 +1680,7 @@
         <v>48</v>
       </c>
       <c r="AK8">
-        <v>34.09</v>
+        <v>33.35</v>
       </c>
     </row>
     <row r="9" spans="1:37">
@@ -1741,10 +1691,10 @@
         <v>45</v>
       </c>
       <c r="C9">
-        <v>11180</v>
+        <v>11150</v>
       </c>
       <c r="D9">
-        <v>1.18</v>
+        <v>-0.27</v>
       </c>
       <c r="E9">
         <v>13052</v>
@@ -1753,46 +1703,46 @@
         <v>10362</v>
       </c>
       <c r="G9">
-        <v>-14.34</v>
+        <v>-14.57</v>
       </c>
       <c r="H9">
-        <v>7.89</v>
+        <v>7.6</v>
       </c>
       <c r="I9">
-        <v>2.5</v>
+        <v>4.69</v>
       </c>
       <c r="J9">
-        <v>0.22</v>
+        <v>0.85</v>
       </c>
       <c r="K9">
-        <v>-5.62</v>
+        <v>-6.15</v>
       </c>
       <c r="L9">
-        <v>-9.44</v>
+        <v>-9.66</v>
       </c>
       <c r="M9">
-        <v>9.48</v>
+        <v>9.17</v>
       </c>
       <c r="N9">
         <v>38</v>
       </c>
       <c r="O9">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="P9">
-        <v>10937.4</v>
+        <v>11037.4</v>
       </c>
       <c r="Q9">
-        <v>10827.75</v>
+        <v>10827.5</v>
       </c>
       <c r="R9">
-        <v>11102.7</v>
+        <v>11091.58</v>
       </c>
       <c r="S9">
-        <v>11639.06</v>
+        <v>11633.8</v>
       </c>
       <c r="T9">
-        <v>-3.94</v>
+        <v>-4.16</v>
       </c>
       <c r="U9" t="s">
         <v>46</v>
@@ -1807,43 +1757,43 @@
         <v>0</v>
       </c>
       <c r="Y9">
-        <v>57.07</v>
+        <v>56.11</v>
       </c>
       <c r="Z9">
-        <v>-26.4</v>
+        <v>-4.31</v>
       </c>
       <c r="AA9">
-        <v>-95.47</v>
+        <v>-77.23999999999999</v>
       </c>
       <c r="AB9">
-        <v>69.08</v>
+        <v>72.93000000000001</v>
       </c>
       <c r="AC9">
-        <v>100</v>
+        <v>98.67</v>
       </c>
       <c r="AD9">
-        <v>94.3</v>
+        <v>98.94</v>
       </c>
       <c r="AE9">
-        <v>259.4</v>
+        <v>252.65</v>
       </c>
       <c r="AF9">
-        <v>-9.34</v>
+        <v>-5.73</v>
       </c>
       <c r="AG9">
-        <v>11219.29</v>
+        <v>11218.16</v>
       </c>
       <c r="AH9">
-        <v>10436.21</v>
+        <v>10436.84</v>
       </c>
       <c r="AI9">
-        <v>10275.81</v>
+        <v>10345.54</v>
       </c>
       <c r="AJ9" t="s">
         <v>49</v>
       </c>
       <c r="AK9">
-        <v>34.82</v>
+        <v>36.73</v>
       </c>
     </row>
   </sheetData>
@@ -1984,7 +1934,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F74"/>
+  <dimension ref="A1:F70"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -2004,1236 +1954,1127 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="3" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6">
+      <c r="A5" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="B5" s="2"/>
+      <c r="C5" s="2"/>
+      <c r="D5" s="2"/>
+      <c r="E5" s="2"/>
+    </row>
+    <row r="6" spans="1:6">
+      <c r="A6" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="D2" s="3" t="s">
+      <c r="B6" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="E2" s="3" t="s">
+      <c r="C6" s="4" t="s">
         <v>54</v>
       </c>
-      <c r="F2" s="3" t="s">
+      <c r="D6" s="4" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="3" spans="1:6">
-      <c r="A3" s="4" t="s">
+      <c r="E6" s="4" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6">
+      <c r="A7" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B3" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="C3" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="D3" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="E3" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="F3" s="4" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6">
-      <c r="A4" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="B4" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="C4" s="4" t="s">
-        <v>61</v>
-      </c>
-      <c r="D4" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="E4" s="4" t="s">
-        <v>62</v>
-      </c>
-      <c r="F4" s="4" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6">
-      <c r="A5" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="B5" s="4" t="s">
-        <v>64</v>
-      </c>
-      <c r="C5" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="D5" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="E5" s="4" t="s">
-        <v>66</v>
-      </c>
-      <c r="F5" s="4" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6">
-      <c r="A7" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="B7" s="2"/>
-      <c r="C7" s="2"/>
-      <c r="D7" s="2"/>
-      <c r="E7" s="2"/>
+      <c r="B7" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C7" s="5">
+        <v>-12.27</v>
+      </c>
+      <c r="D7" s="5">
+        <v>-9.369999999999999</v>
+      </c>
+      <c r="E7" s="6">
+        <v>2.9</v>
+      </c>
     </row>
     <row r="8" spans="1:6">
       <c r="A8" s="3" t="s">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="D8" s="3" t="s">
-        <v>71</v>
-      </c>
-      <c r="E8" s="3" t="s">
-        <v>72</v>
+        <v>9</v>
+      </c>
+      <c r="C8" s="5">
+        <v>-19.37</v>
+      </c>
+      <c r="D8" s="5">
+        <v>-16.83</v>
+      </c>
+      <c r="E8" s="6">
+        <v>2.54</v>
       </c>
     </row>
     <row r="9" spans="1:6">
-      <c r="A9" s="5" t="s">
+      <c r="A9" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C9" s="5">
+        <v>-7.48</v>
+      </c>
+      <c r="D9" s="5">
+        <v>-8.390000000000001</v>
+      </c>
+      <c r="E9" s="7">
+        <v>-0.91</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C10" s="5">
+        <v>-11.77</v>
+      </c>
+      <c r="D10" s="5">
+        <v>-9.25</v>
+      </c>
+      <c r="E10" s="6">
+        <v>2.52</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C11" s="5">
+        <v>-17.7</v>
+      </c>
+      <c r="D11" s="5">
+        <v>-14.24</v>
+      </c>
+      <c r="E11" s="6">
+        <v>3.46</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C12" s="5">
+        <v>5.7</v>
+      </c>
+      <c r="D12" s="5">
+        <v>10.89</v>
+      </c>
+      <c r="E12" s="6">
+        <v>5.19</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="A13" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C13" s="5">
+        <v>-6.37</v>
+      </c>
+      <c r="D13" s="5">
+        <v>-5.68</v>
+      </c>
+      <c r="E13" s="6">
+        <v>0.6899999999999999</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C14" s="5">
+        <v>0.22</v>
+      </c>
+      <c r="D14" s="5">
+        <v>0.85</v>
+      </c>
+      <c r="E14" s="6">
+        <v>0.63</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="A15" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B9" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C9" s="6">
-        <v>-12.53</v>
-      </c>
-      <c r="D9" s="6">
-        <v>-12.27</v>
-      </c>
-      <c r="E9" s="7">
+      <c r="B15" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C15" s="5">
+        <v>-6.95</v>
+      </c>
+      <c r="D15" s="5">
+        <v>-5.23</v>
+      </c>
+      <c r="E15" s="6">
+        <v>1.72</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="A16" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C16" s="5">
+        <v>-11.71</v>
+      </c>
+      <c r="D16" s="5">
+        <v>-7.37</v>
+      </c>
+      <c r="E16" s="6">
+        <v>4.34</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C17" s="5">
+        <v>1.03</v>
+      </c>
+      <c r="D17" s="5">
+        <v>0.76</v>
+      </c>
+      <c r="E17" s="7">
+        <v>-0.27</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C18" s="5">
+        <v>-2.46</v>
+      </c>
+      <c r="D18" s="5">
+        <v>-1.03</v>
+      </c>
+      <c r="E18" s="6">
+        <v>1.43</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C19" s="5">
+        <v>-5.08</v>
+      </c>
+      <c r="D19" s="5">
+        <v>-1.38</v>
+      </c>
+      <c r="E19" s="6">
+        <v>3.7</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C20" s="5">
+        <v>-1.37</v>
+      </c>
+      <c r="D20" s="5">
+        <v>-0.86</v>
+      </c>
+      <c r="E20" s="6">
+        <v>0.51</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C21" s="5">
+        <v>-5.02</v>
+      </c>
+      <c r="D21" s="5">
+        <v>-4.36</v>
+      </c>
+      <c r="E21" s="6">
+        <v>0.66</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C22" s="5">
+        <v>2.5</v>
+      </c>
+      <c r="D22" s="5">
+        <v>4.69</v>
+      </c>
+      <c r="E22" s="6">
+        <v>2.19</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C23" s="5">
+        <v>15.62</v>
+      </c>
+      <c r="D23" s="5">
+        <v>15.98</v>
+      </c>
+      <c r="E23" s="6">
+        <v>0.36</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C24" s="5">
+        <v>-52.33</v>
+      </c>
+      <c r="D24" s="5">
+        <v>-52.22</v>
+      </c>
+      <c r="E24" s="6">
+        <v>0.11</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B25" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C25" s="5">
+        <v>3.36</v>
+      </c>
+      <c r="D25" s="5">
+        <v>1.05</v>
+      </c>
+      <c r="E25" s="7">
+        <v>-2.31</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C26" s="5">
+        <v>12.63</v>
+      </c>
+      <c r="D26" s="5">
+        <v>13.54</v>
+      </c>
+      <c r="E26" s="6">
+        <v>0.91</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B27" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C27" s="5">
+        <v>33.67</v>
+      </c>
+      <c r="D27" s="5">
+        <v>34.56</v>
+      </c>
+      <c r="E27" s="6">
+        <v>0.89</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B28" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C28" s="5">
+        <v>136.56</v>
+      </c>
+      <c r="D28" s="5">
+        <v>140.57</v>
+      </c>
+      <c r="E28" s="6">
+        <v>4.01</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="B29" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C29" s="5">
+        <v>-34.62</v>
+      </c>
+      <c r="D29" s="5">
+        <v>-34.94</v>
+      </c>
+      <c r="E29" s="7">
+        <v>-0.32</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="B30" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C30" s="5">
+        <v>-9.44</v>
+      </c>
+      <c r="D30" s="5">
+        <v>-9.66</v>
+      </c>
+      <c r="E30" s="7">
+        <v>-0.22</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5">
+      <c r="A31" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B31" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C31" s="5">
+        <v>-10.36</v>
+      </c>
+      <c r="D31" s="5">
+        <v>-11.71</v>
+      </c>
+      <c r="E31" s="7">
+        <v>-1.35</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5">
+      <c r="A32" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B32" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C32" s="5">
+        <v>-29.64</v>
+      </c>
+      <c r="D32" s="5">
+        <v>-29.94</v>
+      </c>
+      <c r="E32" s="7">
+        <v>-0.3</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5">
+      <c r="A33" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B33" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C33" s="5">
+        <v>-4.51</v>
+      </c>
+      <c r="D33" s="5">
+        <v>-6.8</v>
+      </c>
+      <c r="E33" s="7">
+        <v>-2.29</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5">
+      <c r="A34" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B34" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C34" s="5">
+        <v>-6.06</v>
+      </c>
+      <c r="D34" s="5">
+        <v>-5.72</v>
+      </c>
+      <c r="E34" s="6">
+        <v>0.34</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5">
+      <c r="A35" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B35" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C35" s="5">
+        <v>-8.99</v>
+      </c>
+      <c r="D35" s="5">
+        <v>-7.27</v>
+      </c>
+      <c r="E35" s="6">
+        <v>1.72</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5">
+      <c r="A36" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B36" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C36" s="5">
+        <v>4.35</v>
+      </c>
+      <c r="D36" s="5">
+        <v>10.31</v>
+      </c>
+      <c r="E36" s="6">
+        <v>5.96</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5">
+      <c r="A37" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="B37" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C37" s="5">
+        <v>-12.23</v>
+      </c>
+      <c r="D37" s="5">
+        <v>-13.02</v>
+      </c>
+      <c r="E37" s="7">
+        <v>-0.79</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5">
+      <c r="A38" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="B38" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C38" s="5">
+        <v>-5.62</v>
+      </c>
+      <c r="D38" s="5">
+        <v>-6.15</v>
+      </c>
+      <c r="E38" s="7">
+        <v>-0.53</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5">
+      <c r="A39" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B39" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C39" s="5">
+        <v>-16.87</v>
+      </c>
+      <c r="D39" s="5">
+        <v>-16.75</v>
+      </c>
+      <c r="E39" s="6">
+        <v>0.12</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5">
+      <c r="A40" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B40" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C40" s="5">
+        <v>-53.64</v>
+      </c>
+      <c r="D40" s="5">
+        <v>-53.19</v>
+      </c>
+      <c r="E40" s="6">
+        <v>0.45</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5">
+      <c r="A41" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B41" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C41" s="5">
+        <v>-12.73</v>
+      </c>
+      <c r="D41" s="5">
+        <v>-14.19</v>
+      </c>
+      <c r="E41" s="7">
+        <v>-1.46</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5">
+      <c r="A42" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B42" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C42" s="5">
+        <v>-22.97</v>
+      </c>
+      <c r="D42" s="5">
+        <v>-22.48</v>
+      </c>
+      <c r="E42" s="6">
+        <v>0.49</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5">
+      <c r="A43" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B43" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C43" s="5">
+        <v>-23.4</v>
+      </c>
+      <c r="D43" s="5">
+        <v>-22.37</v>
+      </c>
+      <c r="E43" s="6">
+        <v>1.03</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5">
+      <c r="A44" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B44" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C44" s="5">
+        <v>-12.14</v>
+      </c>
+      <c r="D44" s="5">
+        <v>-9.27</v>
+      </c>
+      <c r="E44" s="6">
+        <v>2.87</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5">
+      <c r="A45" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="B45" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C45" s="5">
+        <v>-34.86</v>
+      </c>
+      <c r="D45" s="5">
+        <v>-34.6</v>
+      </c>
+      <c r="E45" s="6">
         <v>0.26</v>
       </c>
     </row>
-    <row r="10" spans="1:6">
-      <c r="A10" s="5" t="s">
+    <row r="46" spans="1:5">
+      <c r="A46" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="B46" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C46" s="5">
+        <v>-14.34</v>
+      </c>
+      <c r="D46" s="5">
+        <v>-14.57</v>
+      </c>
+      <c r="E46" s="7">
+        <v>-0.23</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5">
+      <c r="A47" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B47" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C47" s="5">
+        <v>353.05</v>
+      </c>
+      <c r="D47" s="5">
+        <v>353.55</v>
+      </c>
+      <c r="E47" s="6">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5">
+      <c r="A48" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B10" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C10" s="6">
-        <v>-19.2</v>
-      </c>
-      <c r="D10" s="6">
-        <v>-19.37</v>
-      </c>
-      <c r="E10" s="8">
-        <v>-0.17</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11" s="5" t="s">
+      <c r="B48" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C48" s="5">
+        <v>39.58</v>
+      </c>
+      <c r="D48" s="5">
+        <v>39.97</v>
+      </c>
+      <c r="E48" s="6">
+        <v>0.39</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5">
+      <c r="A49" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B11" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C11" s="6">
-        <v>-7.49</v>
-      </c>
-      <c r="D11" s="6">
-        <v>-7.48</v>
-      </c>
-      <c r="E11" s="7">
-        <v>0.01</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12" s="5" t="s">
+      <c r="B49" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C49" s="5">
+        <v>2950</v>
+      </c>
+      <c r="D49" s="5">
+        <v>2900.8</v>
+      </c>
+      <c r="E49" s="7">
+        <v>-49.2</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5">
+      <c r="A50" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="B12" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C12" s="6">
-        <v>-10.6</v>
-      </c>
-      <c r="D12" s="6">
-        <v>-11.77</v>
-      </c>
-      <c r="E12" s="8">
-        <v>-1.17</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13" s="5" t="s">
+      <c r="B50" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C50" s="5">
+        <v>885.65</v>
+      </c>
+      <c r="D50" s="5">
+        <v>891.2</v>
+      </c>
+      <c r="E50" s="6">
+        <v>5.55</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5">
+      <c r="A51" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="B13" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C13" s="6">
-        <v>-20.39</v>
-      </c>
-      <c r="D13" s="6">
-        <v>-17.7</v>
-      </c>
-      <c r="E13" s="7">
+      <c r="B51" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C51" s="5">
+        <v>11.95</v>
+      </c>
+      <c r="D51" s="5">
+        <v>12.11</v>
+      </c>
+      <c r="E51" s="6">
+        <v>0.16</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5">
+      <c r="A52" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B52" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C52" s="5">
+        <v>12.23</v>
+      </c>
+      <c r="D52" s="5">
+        <v>12.63</v>
+      </c>
+      <c r="E52" s="6">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5">
+      <c r="A53" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="B53" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C53" s="5">
+        <v>3784.3</v>
+      </c>
+      <c r="D53" s="5">
+        <v>3779.4</v>
+      </c>
+      <c r="E53" s="7">
+        <v>-4.9</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5">
+      <c r="A54" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="B54" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C54" s="5">
+        <v>11180</v>
+      </c>
+      <c r="D54" s="5">
+        <v>11150</v>
+      </c>
+      <c r="E54" s="7">
+        <v>-30</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5">
+      <c r="A55" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B55" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C55" s="5">
+        <v>34.04</v>
+      </c>
+      <c r="D55" s="5">
+        <v>34.47</v>
+      </c>
+      <c r="E55" s="6">
+        <v>0.43</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5">
+      <c r="A56" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B56" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C56" s="5">
+        <v>23.08</v>
+      </c>
+      <c r="D56" s="5">
+        <v>25.77</v>
+      </c>
+      <c r="E56" s="6">
         <v>2.69</v>
       </c>
     </row>
-    <row r="14" spans="1:6">
-      <c r="A14" s="5" t="s">
+    <row r="57" spans="1:5">
+      <c r="A57" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B57" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C57" s="5">
+        <v>44.53</v>
+      </c>
+      <c r="D57" s="5">
+        <v>39.86</v>
+      </c>
+      <c r="E57" s="7">
+        <v>-4.67</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5">
+      <c r="A58" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B58" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C58" s="5">
+        <v>38.24</v>
+      </c>
+      <c r="D58" s="5">
+        <v>40.22</v>
+      </c>
+      <c r="E58" s="6">
+        <v>1.98</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5">
+      <c r="A59" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B59" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C59" s="5">
+        <v>37.56</v>
+      </c>
+      <c r="D59" s="5">
+        <v>40.15</v>
+      </c>
+      <c r="E59" s="6">
+        <v>2.59</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5">
+      <c r="A60" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="B14" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C14" s="6">
-        <v>-2.03</v>
-      </c>
-      <c r="D14" s="6">
-        <v>5.7</v>
-      </c>
-      <c r="E14" s="7">
-        <v>7.73</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15" s="5" t="s">
+      <c r="B60" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C60" s="5">
+        <v>56.82</v>
+      </c>
+      <c r="D60" s="5">
+        <v>59.76</v>
+      </c>
+      <c r="E60" s="6">
+        <v>2.94</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5">
+      <c r="A61" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="B15" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C15" s="6">
-        <v>-5.46</v>
-      </c>
-      <c r="D15" s="6">
-        <v>-6.37</v>
-      </c>
-      <c r="E15" s="8">
-        <v>-0.91</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16" s="5" t="s">
+      <c r="B61" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C61" s="5">
+        <v>30.09</v>
+      </c>
+      <c r="D61" s="5">
+        <v>29.81</v>
+      </c>
+      <c r="E61" s="7">
+        <v>-0.28</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5">
+      <c r="A62" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="B16" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C16" s="6">
-        <v>0.45</v>
-      </c>
-      <c r="D16" s="6">
-        <v>0.22</v>
-      </c>
-      <c r="E16" s="8">
-        <v>-0.23</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5">
-      <c r="A17" s="5" t="s">
+      <c r="B62" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C62" s="5">
+        <v>57.07</v>
+      </c>
+      <c r="D62" s="5">
+        <v>56.11</v>
+      </c>
+      <c r="E62" s="7">
+        <v>-0.96</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5">
+      <c r="A63" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B17" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C17" s="6">
-        <v>-9.16</v>
-      </c>
-      <c r="D17" s="6">
-        <v>-6.95</v>
-      </c>
-      <c r="E17" s="7">
-        <v>2.21</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5">
-      <c r="A18" s="5" t="s">
+      <c r="B63" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C63" s="5">
+        <v>-36.77</v>
+      </c>
+      <c r="D63" s="5">
+        <v>-29.06</v>
+      </c>
+      <c r="E63" s="6">
+        <v>7.71</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5">
+      <c r="A64" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B18" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C18" s="6">
-        <v>-11.35</v>
-      </c>
-      <c r="D18" s="6">
-        <v>-11.71</v>
-      </c>
-      <c r="E18" s="8">
-        <v>-0.36</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5">
-      <c r="A19" s="5" t="s">
+      <c r="B64" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C64" s="5">
+        <v>-43.77</v>
+      </c>
+      <c r="D64" s="5">
+        <v>-46.61</v>
+      </c>
+      <c r="E64" s="7">
+        <v>-2.84</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5">
+      <c r="A65" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B19" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C19" s="6">
-        <v>0.28</v>
-      </c>
-      <c r="D19" s="6">
-        <v>1.03</v>
-      </c>
-      <c r="E19" s="7">
-        <v>0.75</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5">
-      <c r="A20" s="5" t="s">
+      <c r="B65" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C65" s="5">
+        <v>-52.8</v>
+      </c>
+      <c r="D65" s="5">
+        <v>1.57</v>
+      </c>
+      <c r="E65" s="6">
+        <v>54.37</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5">
+      <c r="A66" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="B20" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C20" s="6">
-        <v>-2.69</v>
-      </c>
-      <c r="D20" s="6">
-        <v>-2.46</v>
-      </c>
-      <c r="E20" s="7">
-        <v>0.23</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5">
-      <c r="A21" s="5" t="s">
+      <c r="B66" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C66" s="5">
+        <v>-0.76</v>
+      </c>
+      <c r="D66" s="5">
+        <v>-6.19</v>
+      </c>
+      <c r="E66" s="7">
+        <v>-5.43</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5">
+      <c r="A67" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="B21" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C21" s="6">
-        <v>-9.27</v>
-      </c>
-      <c r="D21" s="6">
-        <v>-5.08</v>
-      </c>
-      <c r="E21" s="7">
-        <v>4.19</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5">
-      <c r="A22" s="5" t="s">
+      <c r="B67" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C67" s="5">
+        <v>17.93</v>
+      </c>
+      <c r="D67" s="5">
+        <v>-13.74</v>
+      </c>
+      <c r="E67" s="7">
+        <v>-31.67</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5">
+      <c r="A68" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="B22" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C22" s="6">
-        <v>-2.03</v>
-      </c>
-      <c r="D22" s="6">
-        <v>-1.37</v>
-      </c>
-      <c r="E22" s="7">
-        <v>0.66</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5">
-      <c r="A23" s="5" t="s">
+      <c r="B68" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C68" s="5">
+        <v>145.05</v>
+      </c>
+      <c r="D68" s="5">
+        <v>253.73</v>
+      </c>
+      <c r="E68" s="6">
+        <v>108.68</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5">
+      <c r="A69" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="B23" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C23" s="6">
-        <v>-4.53</v>
-      </c>
-      <c r="D23" s="6">
-        <v>-5.02</v>
-      </c>
-      <c r="E23" s="8">
-        <v>-0.49</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5">
-      <c r="A24" s="5" t="s">
+      <c r="B69" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C69" s="5">
+        <v>5.84</v>
+      </c>
+      <c r="D69" s="5">
+        <v>138.8</v>
+      </c>
+      <c r="E69" s="6">
+        <v>132.96</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5">
+      <c r="A70" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="B24" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C24" s="6">
-        <v>1.73</v>
-      </c>
-      <c r="D24" s="6">
-        <v>2.5</v>
-      </c>
-      <c r="E24" s="7">
-        <v>0.77</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5">
-      <c r="A25" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B25" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C25" s="6">
-        <v>16.02</v>
-      </c>
-      <c r="D25" s="6">
-        <v>15.62</v>
-      </c>
-      <c r="E25" s="8">
-        <v>-0.4</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5">
-      <c r="A26" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B26" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C26" s="6">
-        <v>-51.67</v>
-      </c>
-      <c r="D26" s="6">
-        <v>-52.33</v>
-      </c>
-      <c r="E26" s="8">
-        <v>-0.66</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5">
-      <c r="A27" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B27" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C27" s="6">
-        <v>2.04</v>
-      </c>
-      <c r="D27" s="6">
-        <v>3.36</v>
-      </c>
-      <c r="E27" s="7">
-        <v>1.32</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5">
-      <c r="A28" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B28" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C28" s="6">
-        <v>12.56</v>
-      </c>
-      <c r="D28" s="6">
-        <v>12.63</v>
-      </c>
-      <c r="E28" s="7">
-        <v>0.07000000000000001</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5">
-      <c r="A29" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B29" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C29" s="6">
-        <v>30.57</v>
-      </c>
-      <c r="D29" s="6">
-        <v>33.67</v>
-      </c>
-      <c r="E29" s="7">
-        <v>3.1</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5">
-      <c r="A30" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B30" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C30" s="6">
-        <v>111.01</v>
-      </c>
-      <c r="D30" s="6">
-        <v>136.56</v>
-      </c>
-      <c r="E30" s="7">
-        <v>25.55</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5">
-      <c r="A31" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B31" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C31" s="6">
-        <v>-32.69</v>
-      </c>
-      <c r="D31" s="6">
-        <v>-34.62</v>
-      </c>
-      <c r="E31" s="8">
-        <v>-1.93</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5">
-      <c r="A32" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="B32" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C32" s="6">
-        <v>-10.67</v>
-      </c>
-      <c r="D32" s="6">
-        <v>-9.44</v>
-      </c>
-      <c r="E32" s="7">
-        <v>1.23</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5">
-      <c r="A33" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B33" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C33" s="6">
-        <v>-11.47</v>
-      </c>
-      <c r="D33" s="6">
-        <v>-10.36</v>
-      </c>
-      <c r="E33" s="7">
-        <v>1.11</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5">
-      <c r="A34" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B34" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C34" s="6">
-        <v>-29.02</v>
-      </c>
-      <c r="D34" s="6">
-        <v>-29.64</v>
-      </c>
-      <c r="E34" s="8">
-        <v>-0.62</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5">
-      <c r="A35" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B35" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C35" s="6">
-        <v>-7.04</v>
-      </c>
-      <c r="D35" s="6">
-        <v>-4.51</v>
-      </c>
-      <c r="E35" s="7">
-        <v>2.53</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5">
-      <c r="A36" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B36" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C36" s="6">
-        <v>-8.98</v>
-      </c>
-      <c r="D36" s="6">
-        <v>-6.06</v>
-      </c>
-      <c r="E36" s="7">
-        <v>2.92</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5">
-      <c r="A37" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B37" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C37" s="6">
-        <v>-13.94</v>
-      </c>
-      <c r="D37" s="6">
-        <v>-8.99</v>
-      </c>
-      <c r="E37" s="7">
-        <v>4.95</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5">
-      <c r="A38" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B38" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C38" s="6">
-        <v>-6.95</v>
-      </c>
-      <c r="D38" s="6">
-        <v>4.35</v>
-      </c>
-      <c r="E38" s="7">
-        <v>11.3</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5">
-      <c r="A39" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B39" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C39" s="6">
-        <v>-11.94</v>
-      </c>
-      <c r="D39" s="6">
-        <v>-12.23</v>
-      </c>
-      <c r="E39" s="8">
-        <v>-0.29</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5">
-      <c r="A40" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="B40" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C40" s="6">
-        <v>-7.21</v>
-      </c>
-      <c r="D40" s="6">
-        <v>-5.62</v>
-      </c>
-      <c r="E40" s="7">
-        <v>1.59</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5">
-      <c r="A41" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B41" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C41" s="6">
-        <v>-18.24</v>
-      </c>
-      <c r="D41" s="6">
-        <v>-16.87</v>
-      </c>
-      <c r="E41" s="7">
-        <v>1.37</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5">
-      <c r="A42" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B42" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C42" s="6">
-        <v>-53.42</v>
-      </c>
-      <c r="D42" s="6">
-        <v>-53.64</v>
-      </c>
-      <c r="E42" s="8">
-        <v>-0.22</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5">
-      <c r="A43" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B43" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C43" s="6">
-        <v>-14.39</v>
-      </c>
-      <c r="D43" s="6">
-        <v>-12.73</v>
-      </c>
-      <c r="E43" s="7">
-        <v>1.66</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5">
-      <c r="A44" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B44" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C44" s="6">
-        <v>-24.34</v>
-      </c>
-      <c r="D44" s="6">
-        <v>-22.97</v>
-      </c>
-      <c r="E44" s="7">
-        <v>1.37</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5">
-      <c r="A45" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B45" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C45" s="6">
-        <v>-27.18</v>
-      </c>
-      <c r="D45" s="6">
-        <v>-23.4</v>
-      </c>
-      <c r="E45" s="7">
-        <v>3.78</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5">
-      <c r="A46" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B46" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C46" s="6">
-        <v>-20.11</v>
-      </c>
-      <c r="D46" s="6">
-        <v>-12.14</v>
-      </c>
-      <c r="E46" s="7">
-        <v>7.97</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5">
-      <c r="A47" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B47" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C47" s="6">
-        <v>-34.77</v>
-      </c>
-      <c r="D47" s="6">
-        <v>-34.86</v>
-      </c>
-      <c r="E47" s="8">
-        <v>-0.09</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5">
-      <c r="A48" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="B48" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C48" s="6">
-        <v>-15.34</v>
-      </c>
-      <c r="D48" s="6">
-        <v>-14.34</v>
-      </c>
-      <c r="E48" s="7">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5">
-      <c r="A49" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B49" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C49" s="6">
-        <v>347.25</v>
-      </c>
-      <c r="D49" s="6">
-        <v>353.05</v>
-      </c>
-      <c r="E49" s="7">
-        <v>5.8</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5">
-      <c r="A50" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B50" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C50" s="6">
-        <v>39.77</v>
-      </c>
-      <c r="D50" s="6">
-        <v>39.58</v>
-      </c>
-      <c r="E50" s="8">
-        <v>-0.19</v>
-      </c>
-    </row>
-    <row r="51" spans="1:5">
-      <c r="A51" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B51" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C51" s="6">
-        <v>2894</v>
-      </c>
-      <c r="D51" s="6">
-        <v>2950</v>
-      </c>
-      <c r="E51" s="7">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="52" spans="1:5">
-      <c r="A52" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B52" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C52" s="6">
-        <v>869.85</v>
-      </c>
-      <c r="D52" s="6">
-        <v>885.65</v>
-      </c>
-      <c r="E52" s="7">
-        <v>15.8</v>
-      </c>
-    </row>
-    <row r="53" spans="1:5">
-      <c r="A53" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B53" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C53" s="6">
-        <v>11.36</v>
-      </c>
-      <c r="D53" s="6">
-        <v>11.95</v>
-      </c>
-      <c r="E53" s="7">
-        <v>0.59</v>
-      </c>
-    </row>
-    <row r="54" spans="1:5">
-      <c r="A54" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B54" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C54" s="6">
-        <v>11.12</v>
-      </c>
-      <c r="D54" s="6">
-        <v>12.23</v>
-      </c>
-      <c r="E54" s="7">
-        <v>1.11</v>
-      </c>
-    </row>
-    <row r="55" spans="1:5">
-      <c r="A55" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B55" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C55" s="6">
-        <v>3789.3</v>
-      </c>
-      <c r="D55" s="6">
-        <v>3784.3</v>
-      </c>
-      <c r="E55" s="8">
-        <v>-5</v>
-      </c>
-    </row>
-    <row r="56" spans="1:5">
-      <c r="A56" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="B56" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C56" s="6">
-        <v>11050</v>
-      </c>
-      <c r="D56" s="6">
-        <v>11180</v>
-      </c>
-      <c r="E56" s="7">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="57" spans="1:5">
-      <c r="A57" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B57" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="C57" s="6">
-        <v>75</v>
-      </c>
-      <c r="D57" s="6">
-        <v>62</v>
-      </c>
-      <c r="E57" s="8">
-        <v>-13</v>
-      </c>
-    </row>
-    <row r="58" spans="1:5">
-      <c r="A58" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B58" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="C58" s="6">
-        <v>62</v>
-      </c>
-      <c r="D58" s="6">
-        <v>75</v>
-      </c>
-      <c r="E58" s="7">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="59" spans="1:5">
-      <c r="A59" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B59" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C59" s="6">
-        <v>29.03</v>
-      </c>
-      <c r="D59" s="6">
-        <v>34.04</v>
-      </c>
-      <c r="E59" s="7">
-        <v>5.01</v>
-      </c>
-    </row>
-    <row r="60" spans="1:5">
-      <c r="A60" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B60" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C60" s="6">
-        <v>23.47</v>
-      </c>
-      <c r="D60" s="6">
-        <v>23.08</v>
-      </c>
-      <c r="E60" s="8">
-        <v>-0.39</v>
-      </c>
-    </row>
-    <row r="61" spans="1:5">
-      <c r="A61" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B61" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C61" s="6">
-        <v>36.68</v>
-      </c>
-      <c r="D61" s="6">
-        <v>44.53</v>
-      </c>
-      <c r="E61" s="7">
-        <v>7.85</v>
-      </c>
-    </row>
-    <row r="62" spans="1:5">
-      <c r="A62" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B62" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C62" s="6">
-        <v>32.28</v>
-      </c>
-      <c r="D62" s="6">
-        <v>38.24</v>
-      </c>
-      <c r="E62" s="7">
-        <v>5.96</v>
-      </c>
-    </row>
-    <row r="63" spans="1:5">
-      <c r="A63" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B63" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C63" s="6">
-        <v>26.7</v>
-      </c>
-      <c r="D63" s="6">
-        <v>37.56</v>
-      </c>
-      <c r="E63" s="7">
-        <v>10.86</v>
-      </c>
-    </row>
-    <row r="64" spans="1:5">
-      <c r="A64" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B64" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C64" s="6">
-        <v>46.81</v>
-      </c>
-      <c r="D64" s="6">
-        <v>56.82</v>
-      </c>
-      <c r="E64" s="7">
-        <v>10.01</v>
-      </c>
-    </row>
-    <row r="65" spans="1:5">
-      <c r="A65" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B65" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C65" s="6">
-        <v>30.36</v>
-      </c>
-      <c r="D65" s="6">
-        <v>30.09</v>
-      </c>
-      <c r="E65" s="8">
-        <v>-0.27</v>
-      </c>
-    </row>
-    <row r="66" spans="1:5">
-      <c r="A66" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="B66" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C66" s="6">
-        <v>53.92</v>
-      </c>
-      <c r="D66" s="6">
-        <v>57.07</v>
-      </c>
-      <c r="E66" s="7">
-        <v>3.15</v>
-      </c>
-    </row>
-    <row r="67" spans="1:5">
-      <c r="A67" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B67" s="5" t="s">
+      <c r="B70" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="C67" s="6">
-        <v>-36.1</v>
-      </c>
-      <c r="D67" s="6">
-        <v>-36.77</v>
-      </c>
-      <c r="E67" s="8">
-        <v>-0.67</v>
-      </c>
-    </row>
-    <row r="68" spans="1:5">
-      <c r="A68" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B68" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C68" s="6">
-        <v>28.73</v>
-      </c>
-      <c r="D68" s="6">
-        <v>-43.77</v>
-      </c>
-      <c r="E68" s="8">
-        <v>-72.5</v>
-      </c>
-    </row>
-    <row r="69" spans="1:5">
-      <c r="A69" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B69" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C69" s="6">
-        <v>-34.77</v>
-      </c>
-      <c r="D69" s="6">
-        <v>-52.8</v>
-      </c>
-      <c r="E69" s="8">
-        <v>-18.03</v>
-      </c>
-    </row>
-    <row r="70" spans="1:5">
-      <c r="A70" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B70" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C70" s="6">
-        <v>97.94</v>
-      </c>
-      <c r="D70" s="6">
-        <v>-0.76</v>
-      </c>
-      <c r="E70" s="8">
-        <v>-98.7</v>
-      </c>
-    </row>
-    <row r="71" spans="1:5">
-      <c r="A71" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B71" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C71" s="6">
-        <v>22.48</v>
-      </c>
-      <c r="D71" s="6">
-        <v>17.93</v>
-      </c>
-      <c r="E71" s="8">
-        <v>-4.55</v>
-      </c>
-    </row>
-    <row r="72" spans="1:5">
-      <c r="A72" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B72" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C72" s="6">
-        <v>6.56</v>
-      </c>
-      <c r="D72" s="6">
-        <v>145.05</v>
-      </c>
-      <c r="E72" s="7">
-        <v>138.49</v>
-      </c>
-    </row>
-    <row r="73" spans="1:5">
-      <c r="A73" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B73" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C73" s="6">
-        <v>-13.67</v>
-      </c>
-      <c r="D73" s="6">
-        <v>5.84</v>
-      </c>
-      <c r="E73" s="7">
-        <v>19.51</v>
-      </c>
-    </row>
-    <row r="74" spans="1:5">
-      <c r="A74" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="B74" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C74" s="6">
-        <v>-0.3</v>
-      </c>
-      <c r="D74" s="6">
+      <c r="C70" s="5">
         <v>-9.34</v>
       </c>
-      <c r="E74" s="8">
-        <v>-9.039999999999999</v>
+      <c r="D70" s="5">
+        <v>-5.73</v>
+      </c>
+      <c r="E70" s="6">
+        <v>3.61</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A7:E7"/>
+    <mergeCell ref="A5:E5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3253,60 +3094,60 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="28" customHeight="1">
-      <c r="A1" s="9" t="s">
+      <c r="A1" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="9" t="s">
-        <v>73</v>
-      </c>
-      <c r="C1" s="9" t="s">
-        <v>74</v>
-      </c>
-      <c r="D1" s="9" t="s">
-        <v>75</v>
-      </c>
-      <c r="E1" s="9" t="s">
-        <v>76</v>
-      </c>
-      <c r="F1" s="9" t="s">
-        <v>77</v>
-      </c>
-      <c r="G1" s="9" t="s">
-        <v>78</v>
-      </c>
-      <c r="H1" s="9" t="s">
-        <v>79</v>
-      </c>
-      <c r="I1" s="9" t="s">
-        <v>80</v>
+      <c r="B1" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="C1" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="D1" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="E1" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="F1" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="G1" s="8" t="s">
+        <v>62</v>
+      </c>
+      <c r="H1" s="8" t="s">
+        <v>63</v>
+      </c>
+      <c r="I1" s="8" t="s">
+        <v>64</v>
       </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="10" t="s">
+      <c r="A2" s="9" t="s">
         <v>45</v>
       </c>
-      <c r="B2" s="11">
+      <c r="B2" s="10">
         <v>37.44</v>
       </c>
-      <c r="C2" s="12">
+      <c r="C2" s="11">
         <v>8</v>
       </c>
-      <c r="D2" s="11">
-        <v>40.2</v>
-      </c>
-      <c r="E2" s="11">
+      <c r="D2" s="10">
+        <v>40.8</v>
+      </c>
+      <c r="E2" s="10">
         <v>12.5</v>
       </c>
-      <c r="F2" s="11">
-        <v>-8.6</v>
-      </c>
-      <c r="G2" s="11">
-        <v>-9.1</v>
-      </c>
-      <c r="H2" s="11">
+      <c r="F2" s="10">
+        <v>-6.5</v>
+      </c>
+      <c r="G2" s="10">
+        <v>-8.800000000000001</v>
+      </c>
+      <c r="H2" s="10">
         <v>56.1</v>
       </c>
-      <c r="I2" s="11">
+      <c r="I2" s="10">
         <v>0</v>
       </c>
     </row>
@@ -3408,55 +3249,55 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8">
-      <c r="A1" s="13" t="s">
+      <c r="A1" s="12" t="s">
         <v>37</v>
       </c>
-      <c r="B1" s="13" t="s">
+      <c r="B1" s="12" t="s">
         <v>43</v>
       </c>
-      <c r="C1" s="13" t="s">
+      <c r="C1" s="12" t="s">
         <v>40</v>
       </c>
-      <c r="D1" s="13" t="s">
+      <c r="D1" s="12" t="s">
         <v>39</v>
       </c>
-      <c r="E1" s="13" t="s">
+      <c r="E1" s="12" t="s">
         <v>44</v>
       </c>
-      <c r="F1" s="13" t="s">
+      <c r="F1" s="12" t="s">
         <v>41</v>
       </c>
-      <c r="G1" s="13" t="s">
+      <c r="G1" s="12" t="s">
         <v>42</v>
       </c>
-      <c r="H1" s="13" t="s">
+      <c r="H1" s="12" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="2" spans="1:8">
-      <c r="A2" s="14">
-        <v>0.2862</v>
-      </c>
-      <c r="B2" s="14">
-        <v>0.1601</v>
-      </c>
-      <c r="C2" s="14">
-        <v>0.134</v>
-      </c>
-      <c r="D2" s="14">
-        <v>0.1166</v>
-      </c>
-      <c r="E2" s="14">
-        <v>0.09480000000000001</v>
-      </c>
-      <c r="F2" s="14">
-        <v>0.0282</v>
-      </c>
-      <c r="G2" s="14">
-        <v>-0.2855</v>
-      </c>
-      <c r="H2" s="14">
-        <v>-0.3139</v>
+      <c r="A2" s="13">
+        <v>0.291</v>
+      </c>
+      <c r="B2" s="13">
+        <v>0.1556</v>
+      </c>
+      <c r="C2" s="13">
+        <v>0.1383</v>
+      </c>
+      <c r="D2" s="13">
+        <v>0.1143</v>
+      </c>
+      <c r="E2" s="13">
+        <v>0.0917</v>
+      </c>
+      <c r="F2" s="13">
+        <v>0.0339</v>
+      </c>
+      <c r="G2" s="13">
+        <v>-0.2834</v>
+      </c>
+      <c r="H2" s="13">
+        <v>-0.3095</v>
       </c>
     </row>
   </sheetData>

--- a/BIRLA_GROUP_Technical_Metrics.xlsx
+++ b/BIRLA_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="276" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="285" uniqueCount="74">
   <si>
     <t>Symbol</t>
   </si>
@@ -175,7 +175,34 @@
     <t>▶  SIGNAL EVENTS (vs Previous Run)</t>
   </si>
   <si>
-    <t>No signal events detected since last run.</t>
+    <t>Signal</t>
+  </si>
+  <si>
+    <t>Change</t>
+  </si>
+  <si>
+    <t>Direction</t>
+  </si>
+  <si>
+    <t>Prev Value</t>
+  </si>
+  <si>
+    <t>Curr Value</t>
+  </si>
+  <si>
+    <t>RSI Oversold Recovery</t>
+  </si>
+  <si>
+    <t>29.8 → 45.2</t>
+  </si>
+  <si>
+    <t>🟢 BULLISH</t>
+  </si>
+  <si>
+    <t>29.8</t>
+  </si>
+  <si>
+    <t>45.2</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -377,14 +404,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -758,8 +786,8 @@
     <col min="13" max="13" width="10.7109375" customWidth="1"/>
     <col min="14" max="14" width="11.7109375" customWidth="1"/>
     <col min="15" max="15" width="10.7109375" customWidth="1"/>
-    <col min="16" max="17" width="9.7109375" customWidth="1"/>
-    <col min="18" max="18" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="9.7109375" customWidth="1"/>
+    <col min="17" max="18" width="10.7109375" customWidth="1"/>
     <col min="19" max="19" width="9.7109375" customWidth="1"/>
     <col min="20" max="20" width="22.7109375" customWidth="1"/>
     <col min="21" max="21" width="9.7109375" customWidth="1"/>
@@ -900,10 +928,10 @@
         <v>45</v>
       </c>
       <c r="C2">
-        <v>353.55</v>
+        <v>356</v>
       </c>
       <c r="D2">
-        <v>0.14</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="E2">
         <v>424.7</v>
@@ -912,46 +940,46 @@
         <v>292.25</v>
       </c>
       <c r="G2">
-        <v>-16.75</v>
+        <v>-16.18</v>
       </c>
       <c r="H2">
-        <v>20.98</v>
+        <v>21.81</v>
       </c>
       <c r="I2">
-        <v>-5.23</v>
+        <v>-3</v>
       </c>
       <c r="J2">
-        <v>-9.369999999999999</v>
+        <v>-8.720000000000001</v>
       </c>
       <c r="K2">
-        <v>-11.71</v>
+        <v>-9.029999999999999</v>
       </c>
       <c r="L2">
-        <v>15.98</v>
+        <v>15.58</v>
       </c>
       <c r="M2">
-        <v>29.1</v>
+        <v>29.24</v>
       </c>
       <c r="N2">
         <v>62</v>
       </c>
       <c r="O2">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="P2">
-        <v>355.61</v>
+        <v>353.41</v>
       </c>
       <c r="Q2">
-        <v>372.53</v>
+        <v>371.2</v>
       </c>
       <c r="R2">
-        <v>389.31</v>
+        <v>388.41</v>
       </c>
       <c r="S2">
-        <v>366.08</v>
+        <v>366.05</v>
       </c>
       <c r="T2">
-        <v>-3.42</v>
+        <v>-2.75</v>
       </c>
       <c r="U2" t="s">
         <v>46</v>
@@ -966,34 +994,34 @@
         <v>1</v>
       </c>
       <c r="Y2">
-        <v>34.47</v>
+        <v>36.65</v>
       </c>
       <c r="Z2">
-        <v>-9.66</v>
+        <v>-9.699999999999999</v>
       </c>
       <c r="AA2">
-        <v>-7.37</v>
+        <v>-7.84</v>
       </c>
       <c r="AB2">
-        <v>-2.29</v>
+        <v>-1.87</v>
       </c>
       <c r="AC2">
-        <v>18.19</v>
+        <v>31.45</v>
       </c>
       <c r="AD2">
-        <v>10.81</v>
+        <v>19.46</v>
       </c>
       <c r="AE2">
-        <v>10.13</v>
+        <v>9.98</v>
       </c>
       <c r="AF2">
-        <v>-29.06</v>
+        <v>-65.40000000000001</v>
       </c>
       <c r="AG2">
-        <v>394.94</v>
+        <v>394.23</v>
       </c>
       <c r="AH2">
-        <v>350.13</v>
+        <v>348.17</v>
       </c>
       <c r="AI2">
         <v>375.32</v>
@@ -1002,7 +1030,7 @@
         <v>48</v>
       </c>
       <c r="AK2">
-        <v>41.69</v>
+        <v>43.54</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1013,10 +1041,10 @@
         <v>45</v>
       </c>
       <c r="C3">
-        <v>39.97</v>
+        <v>39.84</v>
       </c>
       <c r="D3">
-        <v>0.99</v>
+        <v>-0.33</v>
       </c>
       <c r="E3">
         <v>85.38</v>
@@ -1025,25 +1053,25 @@
         <v>39.58</v>
       </c>
       <c r="G3">
-        <v>-53.19</v>
+        <v>-53.34</v>
       </c>
       <c r="H3">
-        <v>0.99</v>
+        <v>0.66</v>
       </c>
       <c r="I3">
         <v>-7.37</v>
       </c>
       <c r="J3">
-        <v>-16.83</v>
+        <v>-18.93</v>
       </c>
       <c r="K3">
-        <v>-29.94</v>
+        <v>-29.74</v>
       </c>
       <c r="L3">
-        <v>-52.22</v>
+        <v>-52.3</v>
       </c>
       <c r="M3">
-        <v>-30.95</v>
+        <v>-31.05</v>
       </c>
       <c r="N3">
         <v>13</v>
@@ -1052,19 +1080,19 @@
         <v>4</v>
       </c>
       <c r="P3">
-        <v>40.73</v>
+        <v>40.1</v>
       </c>
       <c r="Q3">
-        <v>43.81</v>
+        <v>43.43</v>
       </c>
       <c r="R3">
-        <v>48.71</v>
+        <v>48.39</v>
       </c>
       <c r="S3">
-        <v>59.59</v>
+        <v>59.4</v>
       </c>
       <c r="T3">
-        <v>-32.92</v>
+        <v>-32.93</v>
       </c>
       <c r="U3" t="s">
         <v>46</v>
@@ -1079,43 +1107,43 @@
         <v>0</v>
       </c>
       <c r="Y3">
-        <v>25.77</v>
+        <v>25.45</v>
       </c>
       <c r="Z3">
-        <v>-2.44</v>
+        <v>-2.46</v>
       </c>
       <c r="AA3">
-        <v>-2.21</v>
+        <v>-2.26</v>
       </c>
       <c r="AB3">
-        <v>-0.23</v>
+        <v>-0.2</v>
       </c>
       <c r="AC3">
-        <v>5.62</v>
+        <v>10.57</v>
       </c>
       <c r="AD3">
-        <v>11.95</v>
+        <v>7.65</v>
       </c>
       <c r="AE3">
-        <v>1.67</v>
+        <v>1.61</v>
       </c>
       <c r="AF3">
-        <v>-46.61</v>
+        <v>-30.3</v>
       </c>
       <c r="AG3">
-        <v>48.25</v>
+        <v>47.82</v>
       </c>
       <c r="AH3">
-        <v>39.38</v>
+        <v>39.03</v>
       </c>
       <c r="AI3">
-        <v>44.72</v>
+        <v>44.5</v>
       </c>
       <c r="AJ3" t="s">
         <v>48</v>
       </c>
       <c r="AK3">
-        <v>42.4</v>
+        <v>45.11</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1126,10 +1154,10 @@
         <v>45</v>
       </c>
       <c r="C4">
-        <v>2900.8</v>
+        <v>2900</v>
       </c>
       <c r="D4">
-        <v>-1.67</v>
+        <v>-0.03</v>
       </c>
       <c r="E4">
         <v>3380.5</v>
@@ -1138,46 +1166,46 @@
         <v>2531.1</v>
       </c>
       <c r="G4">
-        <v>-14.19</v>
+        <v>-14.21</v>
       </c>
       <c r="H4">
-        <v>14.61</v>
+        <v>14.57</v>
       </c>
       <c r="I4">
-        <v>0.76</v>
+        <v>0.38</v>
       </c>
       <c r="J4">
-        <v>-8.390000000000001</v>
+        <v>-9.119999999999999</v>
       </c>
       <c r="K4">
-        <v>-6.8</v>
+        <v>-6.94</v>
       </c>
       <c r="L4">
-        <v>1.05</v>
+        <v>1.24</v>
       </c>
       <c r="M4">
-        <v>11.43</v>
+        <v>11.76</v>
       </c>
       <c r="N4">
         <v>50</v>
       </c>
       <c r="O4">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="P4">
-        <v>2905.66</v>
+        <v>2907.84</v>
       </c>
       <c r="Q4">
-        <v>2936.95</v>
+        <v>2924.45</v>
       </c>
       <c r="R4">
-        <v>3130.28</v>
+        <v>3123.3</v>
       </c>
       <c r="S4">
-        <v>2982.83</v>
+        <v>2983.14</v>
       </c>
       <c r="T4">
-        <v>-2.75</v>
+        <v>-2.79</v>
       </c>
       <c r="U4" t="s">
         <v>46</v>
@@ -1192,34 +1220,34 @@
         <v>1</v>
       </c>
       <c r="Y4">
-        <v>39.86</v>
+        <v>39.78</v>
       </c>
       <c r="Z4">
-        <v>-65.79000000000001</v>
+        <v>-62.42</v>
       </c>
       <c r="AA4">
-        <v>-77.22</v>
+        <v>-74.26000000000001</v>
       </c>
       <c r="AB4">
-        <v>11.43</v>
+        <v>11.84</v>
       </c>
       <c r="AC4">
-        <v>90.43000000000001</v>
+        <v>85.14</v>
       </c>
       <c r="AD4">
-        <v>92.65000000000001</v>
+        <v>90.42</v>
       </c>
       <c r="AE4">
-        <v>64.29000000000001</v>
+        <v>62.46</v>
       </c>
       <c r="AF4">
-        <v>1.57</v>
+        <v>19.38</v>
       </c>
       <c r="AG4">
-        <v>3098.5</v>
+        <v>3051.62</v>
       </c>
       <c r="AH4">
-        <v>2775.4</v>
+        <v>2797.28</v>
       </c>
       <c r="AI4">
         <v>3050.83</v>
@@ -1228,7 +1256,7 @@
         <v>48</v>
       </c>
       <c r="AK4">
-        <v>43.14</v>
+        <v>38.26</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1239,10 +1267,10 @@
         <v>45</v>
       </c>
       <c r="C5">
-        <v>891.2</v>
+        <v>893.75</v>
       </c>
       <c r="D5">
-        <v>0.63</v>
+        <v>0.29</v>
       </c>
       <c r="E5">
         <v>1149.7</v>
@@ -1251,25 +1279,25 @@
         <v>774.65</v>
       </c>
       <c r="G5">
-        <v>-22.48</v>
+        <v>-22.26</v>
       </c>
       <c r="H5">
-        <v>15.05</v>
+        <v>15.37</v>
       </c>
       <c r="I5">
-        <v>-1.03</v>
+        <v>0.1</v>
       </c>
       <c r="J5">
-        <v>-9.25</v>
+        <v>-8.52</v>
       </c>
       <c r="K5">
-        <v>-5.72</v>
+        <v>-4.55</v>
       </c>
       <c r="L5">
-        <v>13.54</v>
+        <v>12.79</v>
       </c>
       <c r="M5">
-        <v>13.83</v>
+        <v>14.43</v>
       </c>
       <c r="N5">
         <v>75</v>
@@ -1278,19 +1306,19 @@
         <v>74</v>
       </c>
       <c r="P5">
-        <v>885.03</v>
+        <v>885.21</v>
       </c>
       <c r="Q5">
-        <v>908.48</v>
+        <v>905.38</v>
       </c>
       <c r="R5">
-        <v>970.62</v>
+        <v>967.9</v>
       </c>
       <c r="S5">
-        <v>982.84</v>
+        <v>982.61</v>
       </c>
       <c r="T5">
-        <v>-9.32</v>
+        <v>-9.039999999999999</v>
       </c>
       <c r="U5" t="s">
         <v>46</v>
@@ -1305,34 +1333,34 @@
         <v>0</v>
       </c>
       <c r="Y5">
-        <v>40.22</v>
+        <v>41.16</v>
       </c>
       <c r="Z5">
-        <v>-24.54</v>
+        <v>-22.94</v>
       </c>
       <c r="AA5">
-        <v>-25.74</v>
+        <v>-25.18</v>
       </c>
       <c r="AB5">
-        <v>1.2</v>
+        <v>2.24</v>
       </c>
       <c r="AC5">
-        <v>76.55</v>
+        <v>95.09999999999999</v>
       </c>
       <c r="AD5">
-        <v>68.22</v>
+        <v>79.05</v>
       </c>
       <c r="AE5">
-        <v>23.89</v>
+        <v>22.94</v>
       </c>
       <c r="AF5">
-        <v>-6.19</v>
+        <v>-25.33</v>
       </c>
       <c r="AG5">
-        <v>962.25</v>
+        <v>954.6</v>
       </c>
       <c r="AH5">
-        <v>854.72</v>
+        <v>856.16</v>
       </c>
       <c r="AI5">
         <v>933.28</v>
@@ -1341,7 +1369,7 @@
         <v>48</v>
       </c>
       <c r="AK5">
-        <v>43.83</v>
+        <v>40.32</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1352,10 +1380,10 @@
         <v>45</v>
       </c>
       <c r="C6">
-        <v>12.11</v>
+        <v>11.86</v>
       </c>
       <c r="D6">
-        <v>1.34</v>
+        <v>-2.06</v>
       </c>
       <c r="E6">
         <v>15.6</v>
@@ -1364,46 +1392,46 @@
         <v>8.529999999999999</v>
       </c>
       <c r="G6">
-        <v>-22.37</v>
+        <v>-23.97</v>
       </c>
       <c r="H6">
-        <v>41.97</v>
+        <v>39.04</v>
       </c>
       <c r="I6">
-        <v>-1.38</v>
+        <v>1.89</v>
       </c>
       <c r="J6">
-        <v>-14.24</v>
+        <v>-16.83</v>
       </c>
       <c r="K6">
-        <v>-7.27</v>
+        <v>-8.42</v>
       </c>
       <c r="L6">
-        <v>34.56</v>
+        <v>24.58</v>
       </c>
       <c r="M6">
-        <v>3.39</v>
+        <v>4.1</v>
       </c>
       <c r="N6">
         <v>87</v>
       </c>
       <c r="O6">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="P6">
-        <v>11.72</v>
+        <v>11.76</v>
       </c>
       <c r="Q6">
-        <v>12.58</v>
+        <v>12.5</v>
       </c>
       <c r="R6">
-        <v>13.73</v>
+        <v>13.68</v>
       </c>
       <c r="S6">
         <v>12.31</v>
       </c>
       <c r="T6">
-        <v>-1.61</v>
+        <v>-3.66</v>
       </c>
       <c r="U6" t="s">
         <v>46</v>
@@ -1418,34 +1446,34 @@
         <v>1</v>
       </c>
       <c r="Y6">
-        <v>40.15</v>
+        <v>37.53</v>
       </c>
       <c r="Z6">
-        <v>-0.5600000000000001</v>
+        <v>-0.55</v>
       </c>
       <c r="AA6">
-        <v>-0.51</v>
+        <v>-0.52</v>
       </c>
       <c r="AB6">
-        <v>-0.05</v>
+        <v>-0.03</v>
       </c>
       <c r="AC6">
-        <v>54.88</v>
+        <v>80.81</v>
       </c>
       <c r="AD6">
-        <v>26.37</v>
+        <v>53.31</v>
       </c>
       <c r="AE6">
         <v>0.47</v>
       </c>
       <c r="AF6">
-        <v>-13.74</v>
+        <v>-31.83</v>
       </c>
       <c r="AG6">
-        <v>13.81</v>
+        <v>13.7</v>
       </c>
       <c r="AH6">
-        <v>11.36</v>
+        <v>11.31</v>
       </c>
       <c r="AI6">
         <v>12.7</v>
@@ -1454,7 +1482,7 @@
         <v>48</v>
       </c>
       <c r="AK6">
-        <v>53.66</v>
+        <v>50.99</v>
       </c>
     </row>
     <row r="7" spans="1:37">
@@ -1465,10 +1493,10 @@
         <v>45</v>
       </c>
       <c r="C7">
-        <v>12.63</v>
+        <v>12.77</v>
       </c>
       <c r="D7">
-        <v>3.27</v>
+        <v>1.11</v>
       </c>
       <c r="E7">
         <v>13.92</v>
@@ -1477,25 +1505,25 @@
         <v>4.69</v>
       </c>
       <c r="G7">
-        <v>-9.27</v>
+        <v>-8.26</v>
       </c>
       <c r="H7">
-        <v>169.3</v>
+        <v>172.28</v>
       </c>
       <c r="I7">
-        <v>-0.86</v>
+        <v>9.43</v>
       </c>
       <c r="J7">
-        <v>10.89</v>
+        <v>10.37</v>
       </c>
       <c r="K7">
-        <v>10.31</v>
+        <v>15.88</v>
       </c>
       <c r="L7">
-        <v>140.57</v>
+        <v>145.58</v>
       </c>
       <c r="M7">
-        <v>-28.34</v>
+        <v>-27.63</v>
       </c>
       <c r="N7">
         <v>99</v>
@@ -1504,19 +1532,19 @@
         <v>98</v>
       </c>
       <c r="P7">
-        <v>11.81</v>
+        <v>12.03</v>
       </c>
       <c r="Q7">
-        <v>11.32</v>
+        <v>11.41</v>
       </c>
       <c r="R7">
-        <v>11.46</v>
+        <v>11.48</v>
       </c>
       <c r="S7">
-        <v>10.82</v>
+        <v>10.83</v>
       </c>
       <c r="T7">
-        <v>16.72</v>
+        <v>17.94</v>
       </c>
       <c r="U7" t="s">
         <v>46</v>
@@ -1531,34 +1559,34 @@
         <v>2</v>
       </c>
       <c r="Y7">
-        <v>59.76</v>
+        <v>60.77</v>
       </c>
       <c r="Z7">
-        <v>0.19</v>
+        <v>0.25</v>
       </c>
       <c r="AA7">
-        <v>0.06</v>
+        <v>0.1</v>
       </c>
       <c r="AB7">
-        <v>0.13</v>
+        <v>0.16</v>
       </c>
       <c r="AC7">
-        <v>63.27</v>
+        <v>76.29000000000001</v>
       </c>
       <c r="AD7">
-        <v>56.5</v>
+        <v>64.62</v>
       </c>
       <c r="AE7">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="AF7">
-        <v>253.73</v>
+        <v>1.04</v>
       </c>
       <c r="AG7">
-        <v>12.73</v>
+        <v>12.95</v>
       </c>
       <c r="AH7">
-        <v>9.92</v>
+        <v>9.869999999999999</v>
       </c>
       <c r="AI7">
         <v>10.86</v>
@@ -1567,7 +1595,7 @@
         <v>49</v>
       </c>
       <c r="AK7">
-        <v>25.49</v>
+        <v>26.83</v>
       </c>
     </row>
     <row r="8" spans="1:37">
@@ -1578,58 +1606,58 @@
         <v>45</v>
       </c>
       <c r="C8">
-        <v>3779.4</v>
+        <v>3916</v>
       </c>
       <c r="D8">
-        <v>-0.13</v>
+        <v>3.61</v>
       </c>
       <c r="E8">
-        <v>5779</v>
+        <v>5724</v>
       </c>
       <c r="F8">
         <v>3779.4</v>
       </c>
       <c r="G8">
-        <v>-34.6</v>
+        <v>-31.59</v>
       </c>
       <c r="H8">
-        <v>0</v>
+        <v>3.61</v>
       </c>
       <c r="I8">
-        <v>-4.36</v>
+        <v>0.23</v>
       </c>
       <c r="J8">
-        <v>-5.68</v>
+        <v>-2.47</v>
       </c>
       <c r="K8">
-        <v>-13.02</v>
+        <v>-7.64</v>
       </c>
       <c r="L8">
-        <v>-34.94</v>
+        <v>-32.24</v>
       </c>
       <c r="M8">
-        <v>15.56</v>
+        <v>16.66</v>
       </c>
       <c r="N8">
         <v>25</v>
       </c>
       <c r="O8">
-        <v>27</v>
+        <v>38</v>
       </c>
       <c r="P8">
-        <v>3829.18</v>
+        <v>3830.94</v>
       </c>
       <c r="Q8">
-        <v>3940.67</v>
+        <v>3936.59</v>
       </c>
       <c r="R8">
-        <v>4127.51</v>
+        <v>4114.89</v>
       </c>
       <c r="S8">
-        <v>4429.61</v>
+        <v>4423.72</v>
       </c>
       <c r="T8">
-        <v>-14.68</v>
+        <v>-11.48</v>
       </c>
       <c r="U8" t="s">
         <v>46</v>
@@ -1644,34 +1672,34 @@
         <v>0</v>
       </c>
       <c r="Y8">
-        <v>29.81</v>
+        <v>45.22</v>
       </c>
       <c r="Z8">
-        <v>-81.81999999999999</v>
+        <v>-73.56</v>
       </c>
       <c r="AA8">
-        <v>-71.48999999999999</v>
+        <v>-71.90000000000001</v>
       </c>
       <c r="AB8">
-        <v>-10.33</v>
+        <v>-1.66</v>
       </c>
       <c r="AC8">
-        <v>0</v>
+        <v>33.33</v>
       </c>
       <c r="AD8">
-        <v>14.21</v>
+        <v>15.54</v>
       </c>
       <c r="AE8">
-        <v>107.71</v>
+        <v>112.13</v>
       </c>
       <c r="AF8">
-        <v>138.8</v>
+        <v>-14.48</v>
       </c>
       <c r="AG8">
-        <v>4107.78</v>
+        <v>4101.83</v>
       </c>
       <c r="AH8">
-        <v>3773.56</v>
+        <v>3771.36</v>
       </c>
       <c r="AI8">
         <v>4043.79</v>
@@ -1680,7 +1708,7 @@
         <v>48</v>
       </c>
       <c r="AK8">
-        <v>33.35</v>
+        <v>30.66</v>
       </c>
     </row>
     <row r="9" spans="1:37">
@@ -1691,10 +1719,10 @@
         <v>45</v>
       </c>
       <c r="C9">
-        <v>11150</v>
+        <v>11104</v>
       </c>
       <c r="D9">
-        <v>-0.27</v>
+        <v>-0.41</v>
       </c>
       <c r="E9">
         <v>13052</v>
@@ -1703,46 +1731,46 @@
         <v>10362</v>
       </c>
       <c r="G9">
-        <v>-14.57</v>
+        <v>-14.92</v>
       </c>
       <c r="H9">
-        <v>7.6</v>
+        <v>7.16</v>
       </c>
       <c r="I9">
-        <v>4.69</v>
+        <v>2.35</v>
       </c>
       <c r="J9">
-        <v>0.85</v>
+        <v>-0.46</v>
       </c>
       <c r="K9">
-        <v>-6.15</v>
+        <v>-7.13</v>
       </c>
       <c r="L9">
-        <v>-9.66</v>
+        <v>-8.57</v>
       </c>
       <c r="M9">
-        <v>9.17</v>
+        <v>8.81</v>
       </c>
       <c r="N9">
         <v>38</v>
       </c>
       <c r="O9">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="P9">
-        <v>11037.4</v>
+        <v>11088.4</v>
       </c>
       <c r="Q9">
-        <v>10827.5</v>
+        <v>10831.45</v>
       </c>
       <c r="R9">
-        <v>11091.58</v>
+        <v>11081.28</v>
       </c>
       <c r="S9">
-        <v>11633.8</v>
+        <v>11628.4</v>
       </c>
       <c r="T9">
-        <v>-4.16</v>
+        <v>-4.51</v>
       </c>
       <c r="U9" t="s">
         <v>46</v>
@@ -1757,43 +1785,43 @@
         <v>0</v>
       </c>
       <c r="Y9">
-        <v>56.11</v>
+        <v>54.61</v>
       </c>
       <c r="Z9">
-        <v>-4.31</v>
+        <v>9.369999999999999</v>
       </c>
       <c r="AA9">
-        <v>-77.23999999999999</v>
+        <v>-59.92</v>
       </c>
       <c r="AB9">
-        <v>72.93000000000001</v>
+        <v>69.29000000000001</v>
       </c>
       <c r="AC9">
-        <v>98.67</v>
+        <v>95.23999999999999</v>
       </c>
       <c r="AD9">
-        <v>98.94</v>
+        <v>97.97</v>
       </c>
       <c r="AE9">
-        <v>252.65</v>
+        <v>248.04</v>
       </c>
       <c r="AF9">
-        <v>-5.73</v>
+        <v>-30.04</v>
       </c>
       <c r="AG9">
-        <v>11218.16</v>
+        <v>11231.99</v>
       </c>
       <c r="AH9">
-        <v>10436.84</v>
+        <v>10430.91</v>
       </c>
       <c r="AI9">
-        <v>10345.54</v>
+        <v>10372.89</v>
       </c>
       <c r="AJ9" t="s">
         <v>49</v>
       </c>
       <c r="AK9">
-        <v>36.73</v>
+        <v>38.71</v>
       </c>
     </row>
   </sheetData>
@@ -1934,7 +1962,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F70"/>
+  <dimension ref="A1:F69"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -1954,12 +1982,47 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="3" t="s">
         <v>51</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>60</v>
       </c>
     </row>
     <row r="5" spans="1:6">
       <c r="A5" s="2" t="s">
-        <v>52</v>
+        <v>61</v>
       </c>
       <c r="B5" s="2"/>
       <c r="C5" s="2"/>
@@ -1967,1108 +2030,1091 @@
       <c r="E5" s="2"/>
     </row>
     <row r="6" spans="1:6">
-      <c r="A6" s="4" t="s">
+      <c r="A6" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B6" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="D6" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="E6" s="4" t="s">
-        <v>56</v>
+      <c r="B6" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>65</v>
       </c>
     </row>
     <row r="7" spans="1:6">
-      <c r="A7" s="3" t="s">
+      <c r="A7" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B7" s="3" t="s">
+      <c r="B7" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C7" s="5">
-        <v>-12.27</v>
-      </c>
-      <c r="D7" s="5">
+      <c r="C7" s="6">
         <v>-9.369999999999999</v>
       </c>
-      <c r="E7" s="6">
-        <v>2.9</v>
+      <c r="D7" s="6">
+        <v>-8.720000000000001</v>
+      </c>
+      <c r="E7" s="7">
+        <v>0.65</v>
       </c>
     </row>
     <row r="8" spans="1:6">
-      <c r="A8" s="3" t="s">
+      <c r="A8" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B8" s="3" t="s">
+      <c r="B8" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C8" s="5">
-        <v>-19.37</v>
-      </c>
-      <c r="D8" s="5">
+      <c r="C8" s="6">
         <v>-16.83</v>
       </c>
-      <c r="E8" s="6">
-        <v>2.54</v>
+      <c r="D8" s="6">
+        <v>-18.93</v>
+      </c>
+      <c r="E8" s="8">
+        <v>-2.1</v>
       </c>
     </row>
     <row r="9" spans="1:6">
-      <c r="A9" s="3" t="s">
+      <c r="A9" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B9" s="3" t="s">
+      <c r="B9" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C9" s="5">
-        <v>-7.48</v>
-      </c>
-      <c r="D9" s="5">
+      <c r="C9" s="6">
         <v>-8.390000000000001</v>
       </c>
-      <c r="E9" s="7">
-        <v>-0.91</v>
+      <c r="D9" s="6">
+        <v>-9.119999999999999</v>
+      </c>
+      <c r="E9" s="8">
+        <v>-0.73</v>
       </c>
     </row>
     <row r="10" spans="1:6">
-      <c r="A10" s="3" t="s">
+      <c r="A10" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B10" s="3" t="s">
+      <c r="B10" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C10" s="5">
-        <v>-11.77</v>
-      </c>
-      <c r="D10" s="5">
+      <c r="C10" s="6">
         <v>-9.25</v>
       </c>
-      <c r="E10" s="6">
-        <v>2.52</v>
+      <c r="D10" s="6">
+        <v>-8.52</v>
+      </c>
+      <c r="E10" s="7">
+        <v>0.73</v>
       </c>
     </row>
     <row r="11" spans="1:6">
-      <c r="A11" s="3" t="s">
+      <c r="A11" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B11" s="3" t="s">
+      <c r="B11" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C11" s="5">
-        <v>-17.7</v>
-      </c>
-      <c r="D11" s="5">
+      <c r="C11" s="6">
         <v>-14.24</v>
       </c>
-      <c r="E11" s="6">
-        <v>3.46</v>
+      <c r="D11" s="6">
+        <v>-16.83</v>
+      </c>
+      <c r="E11" s="8">
+        <v>-2.59</v>
       </c>
     </row>
     <row r="12" spans="1:6">
-      <c r="A12" s="3" t="s">
+      <c r="A12" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="B12" s="3" t="s">
+      <c r="B12" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C12" s="5">
-        <v>5.7</v>
-      </c>
-      <c r="D12" s="5">
+      <c r="C12" s="6">
         <v>10.89</v>
       </c>
-      <c r="E12" s="6">
-        <v>5.19</v>
+      <c r="D12" s="6">
+        <v>10.37</v>
+      </c>
+      <c r="E12" s="8">
+        <v>-0.52</v>
       </c>
     </row>
     <row r="13" spans="1:6">
-      <c r="A13" s="3" t="s">
+      <c r="A13" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="B13" s="3" t="s">
+      <c r="B13" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C13" s="5">
-        <v>-6.37</v>
-      </c>
-      <c r="D13" s="5">
+      <c r="C13" s="6">
         <v>-5.68</v>
       </c>
-      <c r="E13" s="6">
-        <v>0.6899999999999999</v>
+      <c r="D13" s="6">
+        <v>-2.47</v>
+      </c>
+      <c r="E13" s="7">
+        <v>3.21</v>
       </c>
     </row>
     <row r="14" spans="1:6">
-      <c r="A14" s="3" t="s">
+      <c r="A14" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="B14" s="3" t="s">
+      <c r="B14" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C14" s="5">
+      <c r="C14" s="6">
+        <v>0.85</v>
+      </c>
+      <c r="D14" s="6">
+        <v>-0.46</v>
+      </c>
+      <c r="E14" s="8">
+        <v>-1.31</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="A15" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B15" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C15" s="6">
+        <v>-5.23</v>
+      </c>
+      <c r="D15" s="6">
+        <v>-3</v>
+      </c>
+      <c r="E15" s="7">
+        <v>2.23</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="A16" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B16" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C16" s="6">
+        <v>0.76</v>
+      </c>
+      <c r="D16" s="6">
+        <v>0.38</v>
+      </c>
+      <c r="E16" s="8">
+        <v>-0.38</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B17" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C17" s="6">
+        <v>-1.03</v>
+      </c>
+      <c r="D17" s="6">
+        <v>0.1</v>
+      </c>
+      <c r="E17" s="7">
+        <v>1.13</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B18" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C18" s="6">
+        <v>-1.38</v>
+      </c>
+      <c r="D18" s="6">
+        <v>1.89</v>
+      </c>
+      <c r="E18" s="7">
+        <v>3.27</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B19" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C19" s="6">
+        <v>-0.86</v>
+      </c>
+      <c r="D19" s="6">
+        <v>9.43</v>
+      </c>
+      <c r="E19" s="7">
+        <v>10.29</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B20" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C20" s="6">
+        <v>-4.36</v>
+      </c>
+      <c r="D20" s="6">
+        <v>0.23</v>
+      </c>
+      <c r="E20" s="7">
+        <v>4.59</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="B21" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C21" s="6">
+        <v>4.69</v>
+      </c>
+      <c r="D21" s="6">
+        <v>2.35</v>
+      </c>
+      <c r="E21" s="8">
+        <v>-2.34</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B22" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C22" s="6">
+        <v>15.98</v>
+      </c>
+      <c r="D22" s="6">
+        <v>15.58</v>
+      </c>
+      <c r="E22" s="8">
+        <v>-0.4</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B23" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C23" s="6">
+        <v>-52.22</v>
+      </c>
+      <c r="D23" s="6">
+        <v>-52.3</v>
+      </c>
+      <c r="E23" s="8">
+        <v>-0.08</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B24" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C24" s="6">
+        <v>1.05</v>
+      </c>
+      <c r="D24" s="6">
+        <v>1.24</v>
+      </c>
+      <c r="E24" s="7">
+        <v>0.19</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B25" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C25" s="6">
+        <v>13.54</v>
+      </c>
+      <c r="D25" s="6">
+        <v>12.79</v>
+      </c>
+      <c r="E25" s="8">
+        <v>-0.75</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B26" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C26" s="6">
+        <v>34.56</v>
+      </c>
+      <c r="D26" s="6">
+        <v>24.58</v>
+      </c>
+      <c r="E26" s="8">
+        <v>-9.98</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B27" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C27" s="6">
+        <v>140.57</v>
+      </c>
+      <c r="D27" s="6">
+        <v>145.58</v>
+      </c>
+      <c r="E27" s="7">
+        <v>5.01</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B28" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C28" s="6">
+        <v>-34.94</v>
+      </c>
+      <c r="D28" s="6">
+        <v>-32.24</v>
+      </c>
+      <c r="E28" s="7">
+        <v>2.7</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="B29" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C29" s="6">
+        <v>-9.66</v>
+      </c>
+      <c r="D29" s="6">
+        <v>-8.57</v>
+      </c>
+      <c r="E29" s="7">
+        <v>1.09</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B30" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C30" s="6">
+        <v>-11.71</v>
+      </c>
+      <c r="D30" s="6">
+        <v>-9.029999999999999</v>
+      </c>
+      <c r="E30" s="7">
+        <v>2.68</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5">
+      <c r="A31" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B31" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C31" s="6">
+        <v>-29.94</v>
+      </c>
+      <c r="D31" s="6">
+        <v>-29.74</v>
+      </c>
+      <c r="E31" s="7">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5">
+      <c r="A32" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B32" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C32" s="6">
+        <v>-6.8</v>
+      </c>
+      <c r="D32" s="6">
+        <v>-6.94</v>
+      </c>
+      <c r="E32" s="8">
+        <v>-0.14</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5">
+      <c r="A33" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B33" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C33" s="6">
+        <v>-5.72</v>
+      </c>
+      <c r="D33" s="6">
+        <v>-4.55</v>
+      </c>
+      <c r="E33" s="7">
+        <v>1.17</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5">
+      <c r="A34" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B34" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C34" s="6">
+        <v>-7.27</v>
+      </c>
+      <c r="D34" s="6">
+        <v>-8.42</v>
+      </c>
+      <c r="E34" s="8">
+        <v>-1.15</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5">
+      <c r="A35" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B35" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C35" s="6">
+        <v>10.31</v>
+      </c>
+      <c r="D35" s="6">
+        <v>15.88</v>
+      </c>
+      <c r="E35" s="7">
+        <v>5.57</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5">
+      <c r="A36" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B36" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C36" s="6">
+        <v>-13.02</v>
+      </c>
+      <c r="D36" s="6">
+        <v>-7.64</v>
+      </c>
+      <c r="E36" s="7">
+        <v>5.38</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5">
+      <c r="A37" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="B37" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C37" s="6">
+        <v>-6.15</v>
+      </c>
+      <c r="D37" s="6">
+        <v>-7.13</v>
+      </c>
+      <c r="E37" s="8">
+        <v>-0.98</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5">
+      <c r="A38" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B38" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C38" s="6">
+        <v>-16.75</v>
+      </c>
+      <c r="D38" s="6">
+        <v>-16.18</v>
+      </c>
+      <c r="E38" s="7">
+        <v>0.57</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5">
+      <c r="A39" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B39" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C39" s="6">
+        <v>-53.19</v>
+      </c>
+      <c r="D39" s="6">
+        <v>-53.34</v>
+      </c>
+      <c r="E39" s="8">
+        <v>-0.15</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5">
+      <c r="A40" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B40" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C40" s="6">
+        <v>-14.19</v>
+      </c>
+      <c r="D40" s="6">
+        <v>-14.21</v>
+      </c>
+      <c r="E40" s="8">
+        <v>-0.02</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5">
+      <c r="A41" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B41" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C41" s="6">
+        <v>-22.48</v>
+      </c>
+      <c r="D41" s="6">
+        <v>-22.26</v>
+      </c>
+      <c r="E41" s="7">
         <v>0.22</v>
       </c>
-      <c r="D14" s="5">
-        <v>0.85</v>
-      </c>
-      <c r="E14" s="6">
-        <v>0.63</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15" s="3" t="s">
+    </row>
+    <row r="42" spans="1:5">
+      <c r="A42" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B42" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C42" s="6">
+        <v>-22.37</v>
+      </c>
+      <c r="D42" s="6">
+        <v>-23.97</v>
+      </c>
+      <c r="E42" s="8">
+        <v>-1.6</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5">
+      <c r="A43" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B43" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C43" s="6">
+        <v>-9.27</v>
+      </c>
+      <c r="D43" s="6">
+        <v>-8.26</v>
+      </c>
+      <c r="E43" s="7">
+        <v>1.01</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5">
+      <c r="A44" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B44" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C44" s="6">
+        <v>-34.6</v>
+      </c>
+      <c r="D44" s="6">
+        <v>-31.59</v>
+      </c>
+      <c r="E44" s="7">
+        <v>3.01</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5">
+      <c r="A45" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="B45" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C45" s="6">
+        <v>-14.57</v>
+      </c>
+      <c r="D45" s="6">
+        <v>-14.92</v>
+      </c>
+      <c r="E45" s="8">
+        <v>-0.35</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5">
+      <c r="A46" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B15" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C15" s="5">
-        <v>-6.95</v>
-      </c>
-      <c r="D15" s="5">
-        <v>-5.23</v>
-      </c>
-      <c r="E15" s="6">
-        <v>1.72</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16" s="3" t="s">
+      <c r="B46" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C46" s="6">
+        <v>353.55</v>
+      </c>
+      <c r="D46" s="6">
+        <v>356</v>
+      </c>
+      <c r="E46" s="7">
+        <v>2.45</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5">
+      <c r="A47" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B16" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C16" s="5">
-        <v>-11.71</v>
-      </c>
-      <c r="D16" s="5">
-        <v>-7.37</v>
-      </c>
-      <c r="E16" s="6">
-        <v>4.34</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5">
-      <c r="A17" s="3" t="s">
+      <c r="B47" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C47" s="6">
+        <v>39.97</v>
+      </c>
+      <c r="D47" s="6">
+        <v>39.84</v>
+      </c>
+      <c r="E47" s="8">
+        <v>-0.13</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5">
+      <c r="A48" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B17" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C17" s="5">
-        <v>1.03</v>
-      </c>
-      <c r="D17" s="5">
-        <v>0.76</v>
-      </c>
-      <c r="E17" s="7">
-        <v>-0.27</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5">
-      <c r="A18" s="3" t="s">
+      <c r="B48" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C48" s="6">
+        <v>2900.8</v>
+      </c>
+      <c r="D48" s="6">
+        <v>2900</v>
+      </c>
+      <c r="E48" s="8">
+        <v>-0.8</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5">
+      <c r="A49" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B18" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C18" s="5">
-        <v>-2.46</v>
-      </c>
-      <c r="D18" s="5">
-        <v>-1.03</v>
-      </c>
-      <c r="E18" s="6">
-        <v>1.43</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5">
-      <c r="A19" s="3" t="s">
+      <c r="B49" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C49" s="6">
+        <v>891.2</v>
+      </c>
+      <c r="D49" s="6">
+        <v>893.75</v>
+      </c>
+      <c r="E49" s="7">
+        <v>2.55</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5">
+      <c r="A50" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B19" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C19" s="5">
-        <v>-5.08</v>
-      </c>
-      <c r="D19" s="5">
-        <v>-1.38</v>
-      </c>
-      <c r="E19" s="6">
-        <v>3.7</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5">
-      <c r="A20" s="3" t="s">
+      <c r="B50" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C50" s="6">
+        <v>12.11</v>
+      </c>
+      <c r="D50" s="6">
+        <v>11.86</v>
+      </c>
+      <c r="E50" s="8">
+        <v>-0.25</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5">
+      <c r="A51" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="B20" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C20" s="5">
-        <v>-1.37</v>
-      </c>
-      <c r="D20" s="5">
-        <v>-0.86</v>
-      </c>
-      <c r="E20" s="6">
-        <v>0.51</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5">
-      <c r="A21" s="3" t="s">
+      <c r="B51" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C51" s="6">
+        <v>12.63</v>
+      </c>
+      <c r="D51" s="6">
+        <v>12.77</v>
+      </c>
+      <c r="E51" s="7">
+        <v>0.14</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5">
+      <c r="A52" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="B21" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C21" s="5">
-        <v>-5.02</v>
-      </c>
-      <c r="D21" s="5">
-        <v>-4.36</v>
-      </c>
-      <c r="E21" s="6">
-        <v>0.66</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5">
-      <c r="A22" s="3" t="s">
+      <c r="B52" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C52" s="6">
+        <v>3779.4</v>
+      </c>
+      <c r="D52" s="6">
+        <v>3916</v>
+      </c>
+      <c r="E52" s="7">
+        <v>136.6</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5">
+      <c r="A53" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="B22" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C22" s="5">
-        <v>2.5</v>
-      </c>
-      <c r="D22" s="5">
-        <v>4.69</v>
-      </c>
-      <c r="E22" s="6">
-        <v>2.19</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5">
-      <c r="A23" s="3" t="s">
+      <c r="B53" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C53" s="6">
+        <v>11150</v>
+      </c>
+      <c r="D53" s="6">
+        <v>11104</v>
+      </c>
+      <c r="E53" s="8">
+        <v>-46</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5">
+      <c r="A54" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B23" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C23" s="5">
-        <v>15.62</v>
-      </c>
-      <c r="D23" s="5">
-        <v>15.98</v>
-      </c>
-      <c r="E23" s="6">
-        <v>0.36</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5">
-      <c r="A24" s="3" t="s">
+      <c r="B54" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C54" s="6">
+        <v>34.47</v>
+      </c>
+      <c r="D54" s="6">
+        <v>36.65</v>
+      </c>
+      <c r="E54" s="7">
+        <v>2.18</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5">
+      <c r="A55" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B24" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C24" s="5">
-        <v>-52.33</v>
-      </c>
-      <c r="D24" s="5">
-        <v>-52.22</v>
-      </c>
-      <c r="E24" s="6">
-        <v>0.11</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5">
-      <c r="A25" s="3" t="s">
+      <c r="B55" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C55" s="6">
+        <v>25.77</v>
+      </c>
+      <c r="D55" s="6">
+        <v>25.45</v>
+      </c>
+      <c r="E55" s="8">
+        <v>-0.32</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5">
+      <c r="A56" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B25" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C25" s="5">
-        <v>3.36</v>
-      </c>
-      <c r="D25" s="5">
-        <v>1.05</v>
-      </c>
-      <c r="E25" s="7">
-        <v>-2.31</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5">
-      <c r="A26" s="3" t="s">
+      <c r="B56" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C56" s="6">
+        <v>39.86</v>
+      </c>
+      <c r="D56" s="6">
+        <v>39.78</v>
+      </c>
+      <c r="E56" s="8">
+        <v>-0.08</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5">
+      <c r="A57" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B26" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C26" s="5">
-        <v>12.63</v>
-      </c>
-      <c r="D26" s="5">
-        <v>13.54</v>
-      </c>
-      <c r="E26" s="6">
-        <v>0.91</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5">
-      <c r="A27" s="3" t="s">
+      <c r="B57" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C57" s="6">
+        <v>40.22</v>
+      </c>
+      <c r="D57" s="6">
+        <v>41.16</v>
+      </c>
+      <c r="E57" s="7">
+        <v>0.9399999999999999</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5">
+      <c r="A58" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B27" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C27" s="5">
-        <v>33.67</v>
-      </c>
-      <c r="D27" s="5">
-        <v>34.56</v>
-      </c>
-      <c r="E27" s="6">
-        <v>0.89</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5">
-      <c r="A28" s="3" t="s">
+      <c r="B58" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C58" s="6">
+        <v>40.15</v>
+      </c>
+      <c r="D58" s="6">
+        <v>37.53</v>
+      </c>
+      <c r="E58" s="8">
+        <v>-2.62</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5">
+      <c r="A59" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="B28" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C28" s="5">
-        <v>136.56</v>
-      </c>
-      <c r="D28" s="5">
-        <v>140.57</v>
-      </c>
-      <c r="E28" s="6">
-        <v>4.01</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5">
-      <c r="A29" s="3" t="s">
+      <c r="B59" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C59" s="6">
+        <v>59.76</v>
+      </c>
+      <c r="D59" s="6">
+        <v>60.77</v>
+      </c>
+      <c r="E59" s="7">
+        <v>1.01</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5">
+      <c r="A60" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="B29" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C29" s="5">
-        <v>-34.62</v>
-      </c>
-      <c r="D29" s="5">
-        <v>-34.94</v>
-      </c>
-      <c r="E29" s="7">
-        <v>-0.32</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5">
-      <c r="A30" s="3" t="s">
+      <c r="B60" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C60" s="6">
+        <v>29.81</v>
+      </c>
+      <c r="D60" s="6">
+        <v>45.22</v>
+      </c>
+      <c r="E60" s="7">
+        <v>15.41</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5">
+      <c r="A61" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="B30" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C30" s="5">
-        <v>-9.44</v>
-      </c>
-      <c r="D30" s="5">
-        <v>-9.66</v>
-      </c>
-      <c r="E30" s="7">
-        <v>-0.22</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5">
-      <c r="A31" s="3" t="s">
+      <c r="B61" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C61" s="6">
+        <v>56.11</v>
+      </c>
+      <c r="D61" s="6">
+        <v>54.61</v>
+      </c>
+      <c r="E61" s="8">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5">
+      <c r="A62" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B31" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C31" s="5">
-        <v>-10.36</v>
-      </c>
-      <c r="D31" s="5">
-        <v>-11.71</v>
-      </c>
-      <c r="E31" s="7">
-        <v>-1.35</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5">
-      <c r="A32" s="3" t="s">
+      <c r="B62" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C62" s="6">
+        <v>-29.06</v>
+      </c>
+      <c r="D62" s="6">
+        <v>-65.40000000000001</v>
+      </c>
+      <c r="E62" s="8">
+        <v>-36.34</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5">
+      <c r="A63" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B32" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C32" s="5">
-        <v>-29.64</v>
-      </c>
-      <c r="D32" s="5">
-        <v>-29.94</v>
-      </c>
-      <c r="E32" s="7">
-        <v>-0.3</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5">
-      <c r="A33" s="3" t="s">
+      <c r="B63" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C63" s="6">
+        <v>-46.61</v>
+      </c>
+      <c r="D63" s="6">
+        <v>-30.3</v>
+      </c>
+      <c r="E63" s="7">
+        <v>16.31</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5">
+      <c r="A64" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B33" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C33" s="5">
-        <v>-4.51</v>
-      </c>
-      <c r="D33" s="5">
-        <v>-6.8</v>
-      </c>
-      <c r="E33" s="7">
-        <v>-2.29</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5">
-      <c r="A34" s="3" t="s">
+      <c r="B64" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C64" s="6">
+        <v>1.57</v>
+      </c>
+      <c r="D64" s="6">
+        <v>19.38</v>
+      </c>
+      <c r="E64" s="7">
+        <v>17.81</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5">
+      <c r="A65" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B34" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C34" s="5">
-        <v>-6.06</v>
-      </c>
-      <c r="D34" s="5">
-        <v>-5.72</v>
-      </c>
-      <c r="E34" s="6">
-        <v>0.34</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5">
-      <c r="A35" s="3" t="s">
+      <c r="B65" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C65" s="6">
+        <v>-6.19</v>
+      </c>
+      <c r="D65" s="6">
+        <v>-25.33</v>
+      </c>
+      <c r="E65" s="8">
+        <v>-19.14</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5">
+      <c r="A66" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B35" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C35" s="5">
-        <v>-8.99</v>
-      </c>
-      <c r="D35" s="5">
-        <v>-7.27</v>
-      </c>
-      <c r="E35" s="6">
-        <v>1.72</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5">
-      <c r="A36" s="3" t="s">
+      <c r="B66" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C66" s="6">
+        <v>-13.74</v>
+      </c>
+      <c r="D66" s="6">
+        <v>-31.83</v>
+      </c>
+      <c r="E66" s="8">
+        <v>-18.09</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5">
+      <c r="A67" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="B36" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C36" s="5">
-        <v>4.35</v>
-      </c>
-      <c r="D36" s="5">
-        <v>10.31</v>
-      </c>
-      <c r="E36" s="6">
-        <v>5.96</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5">
-      <c r="A37" s="3" t="s">
+      <c r="B67" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C67" s="6">
+        <v>253.73</v>
+      </c>
+      <c r="D67" s="6">
+        <v>1.04</v>
+      </c>
+      <c r="E67" s="8">
+        <v>-252.69</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5">
+      <c r="A68" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="B37" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C37" s="5">
-        <v>-12.23</v>
-      </c>
-      <c r="D37" s="5">
-        <v>-13.02</v>
-      </c>
-      <c r="E37" s="7">
-        <v>-0.79</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5">
-      <c r="A38" s="3" t="s">
+      <c r="B68" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C68" s="6">
+        <v>138.8</v>
+      </c>
+      <c r="D68" s="6">
+        <v>-14.48</v>
+      </c>
+      <c r="E68" s="8">
+        <v>-153.28</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5">
+      <c r="A69" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="B38" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C38" s="5">
-        <v>-5.62</v>
-      </c>
-      <c r="D38" s="5">
-        <v>-6.15</v>
-      </c>
-      <c r="E38" s="7">
-        <v>-0.53</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5">
-      <c r="A39" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B39" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C39" s="5">
-        <v>-16.87</v>
-      </c>
-      <c r="D39" s="5">
-        <v>-16.75</v>
-      </c>
-      <c r="E39" s="6">
-        <v>0.12</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5">
-      <c r="A40" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B40" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C40" s="5">
-        <v>-53.64</v>
-      </c>
-      <c r="D40" s="5">
-        <v>-53.19</v>
-      </c>
-      <c r="E40" s="6">
-        <v>0.45</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5">
-      <c r="A41" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B41" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C41" s="5">
-        <v>-12.73</v>
-      </c>
-      <c r="D41" s="5">
-        <v>-14.19</v>
-      </c>
-      <c r="E41" s="7">
-        <v>-1.46</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5">
-      <c r="A42" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="B42" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C42" s="5">
-        <v>-22.97</v>
-      </c>
-      <c r="D42" s="5">
-        <v>-22.48</v>
-      </c>
-      <c r="E42" s="6">
-        <v>0.49</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5">
-      <c r="A43" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="B43" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C43" s="5">
-        <v>-23.4</v>
-      </c>
-      <c r="D43" s="5">
-        <v>-22.37</v>
-      </c>
-      <c r="E43" s="6">
-        <v>1.03</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5">
-      <c r="A44" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="B44" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C44" s="5">
-        <v>-12.14</v>
-      </c>
-      <c r="D44" s="5">
-        <v>-9.27</v>
-      </c>
-      <c r="E44" s="6">
-        <v>2.87</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5">
-      <c r="A45" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="B45" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C45" s="5">
-        <v>-34.86</v>
-      </c>
-      <c r="D45" s="5">
-        <v>-34.6</v>
-      </c>
-      <c r="E45" s="6">
-        <v>0.26</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5">
-      <c r="A46" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="B46" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C46" s="5">
-        <v>-14.34</v>
-      </c>
-      <c r="D46" s="5">
-        <v>-14.57</v>
-      </c>
-      <c r="E46" s="7">
-        <v>-0.23</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5">
-      <c r="A47" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B47" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C47" s="5">
-        <v>353.05</v>
-      </c>
-      <c r="D47" s="5">
-        <v>353.55</v>
-      </c>
-      <c r="E47" s="6">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5">
-      <c r="A48" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B48" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C48" s="5">
-        <v>39.58</v>
-      </c>
-      <c r="D48" s="5">
-        <v>39.97</v>
-      </c>
-      <c r="E48" s="6">
-        <v>0.39</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5">
-      <c r="A49" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B49" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C49" s="5">
-        <v>2950</v>
-      </c>
-      <c r="D49" s="5">
-        <v>2900.8</v>
-      </c>
-      <c r="E49" s="7">
-        <v>-49.2</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5">
-      <c r="A50" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="B50" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C50" s="5">
-        <v>885.65</v>
-      </c>
-      <c r="D50" s="5">
-        <v>891.2</v>
-      </c>
-      <c r="E50" s="6">
-        <v>5.55</v>
-      </c>
-    </row>
-    <row r="51" spans="1:5">
-      <c r="A51" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="B51" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C51" s="5">
-        <v>11.95</v>
-      </c>
-      <c r="D51" s="5">
-        <v>12.11</v>
-      </c>
-      <c r="E51" s="6">
-        <v>0.16</v>
-      </c>
-    </row>
-    <row r="52" spans="1:5">
-      <c r="A52" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="B52" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C52" s="5">
-        <v>12.23</v>
-      </c>
-      <c r="D52" s="5">
-        <v>12.63</v>
-      </c>
-      <c r="E52" s="6">
-        <v>0.4</v>
-      </c>
-    </row>
-    <row r="53" spans="1:5">
-      <c r="A53" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="B53" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C53" s="5">
-        <v>3784.3</v>
-      </c>
-      <c r="D53" s="5">
-        <v>3779.4</v>
-      </c>
-      <c r="E53" s="7">
-        <v>-4.9</v>
-      </c>
-    </row>
-    <row r="54" spans="1:5">
-      <c r="A54" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="B54" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C54" s="5">
-        <v>11180</v>
-      </c>
-      <c r="D54" s="5">
-        <v>11150</v>
-      </c>
-      <c r="E54" s="7">
-        <v>-30</v>
-      </c>
-    </row>
-    <row r="55" spans="1:5">
-      <c r="A55" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B55" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C55" s="5">
-        <v>34.04</v>
-      </c>
-      <c r="D55" s="5">
-        <v>34.47</v>
-      </c>
-      <c r="E55" s="6">
-        <v>0.43</v>
-      </c>
-    </row>
-    <row r="56" spans="1:5">
-      <c r="A56" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B56" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C56" s="5">
-        <v>23.08</v>
-      </c>
-      <c r="D56" s="5">
-        <v>25.77</v>
-      </c>
-      <c r="E56" s="6">
-        <v>2.69</v>
-      </c>
-    </row>
-    <row r="57" spans="1:5">
-      <c r="A57" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B57" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C57" s="5">
-        <v>44.53</v>
-      </c>
-      <c r="D57" s="5">
-        <v>39.86</v>
-      </c>
-      <c r="E57" s="7">
-        <v>-4.67</v>
-      </c>
-    </row>
-    <row r="58" spans="1:5">
-      <c r="A58" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="B58" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C58" s="5">
-        <v>38.24</v>
-      </c>
-      <c r="D58" s="5">
-        <v>40.22</v>
-      </c>
-      <c r="E58" s="6">
-        <v>1.98</v>
-      </c>
-    </row>
-    <row r="59" spans="1:5">
-      <c r="A59" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="B59" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C59" s="5">
-        <v>37.56</v>
-      </c>
-      <c r="D59" s="5">
-        <v>40.15</v>
-      </c>
-      <c r="E59" s="6">
-        <v>2.59</v>
-      </c>
-    </row>
-    <row r="60" spans="1:5">
-      <c r="A60" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="B60" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C60" s="5">
-        <v>56.82</v>
-      </c>
-      <c r="D60" s="5">
-        <v>59.76</v>
-      </c>
-      <c r="E60" s="6">
-        <v>2.94</v>
-      </c>
-    </row>
-    <row r="61" spans="1:5">
-      <c r="A61" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="B61" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C61" s="5">
-        <v>30.09</v>
-      </c>
-      <c r="D61" s="5">
-        <v>29.81</v>
-      </c>
-      <c r="E61" s="7">
-        <v>-0.28</v>
-      </c>
-    </row>
-    <row r="62" spans="1:5">
-      <c r="A62" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="B62" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C62" s="5">
-        <v>57.07</v>
-      </c>
-      <c r="D62" s="5">
-        <v>56.11</v>
-      </c>
-      <c r="E62" s="7">
-        <v>-0.96</v>
-      </c>
-    </row>
-    <row r="63" spans="1:5">
-      <c r="A63" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B63" s="3" t="s">
+      <c r="B69" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="C63" s="5">
-        <v>-36.77</v>
-      </c>
-      <c r="D63" s="5">
-        <v>-29.06</v>
-      </c>
-      <c r="E63" s="6">
-        <v>7.71</v>
-      </c>
-    </row>
-    <row r="64" spans="1:5">
-      <c r="A64" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B64" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C64" s="5">
-        <v>-43.77</v>
-      </c>
-      <c r="D64" s="5">
-        <v>-46.61</v>
-      </c>
-      <c r="E64" s="7">
-        <v>-2.84</v>
-      </c>
-    </row>
-    <row r="65" spans="1:5">
-      <c r="A65" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B65" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C65" s="5">
-        <v>-52.8</v>
-      </c>
-      <c r="D65" s="5">
-        <v>1.57</v>
-      </c>
-      <c r="E65" s="6">
-        <v>54.37</v>
-      </c>
-    </row>
-    <row r="66" spans="1:5">
-      <c r="A66" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="B66" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C66" s="5">
-        <v>-0.76</v>
-      </c>
-      <c r="D66" s="5">
-        <v>-6.19</v>
-      </c>
-      <c r="E66" s="7">
-        <v>-5.43</v>
-      </c>
-    </row>
-    <row r="67" spans="1:5">
-      <c r="A67" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="B67" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C67" s="5">
-        <v>17.93</v>
-      </c>
-      <c r="D67" s="5">
-        <v>-13.74</v>
-      </c>
-      <c r="E67" s="7">
-        <v>-31.67</v>
-      </c>
-    </row>
-    <row r="68" spans="1:5">
-      <c r="A68" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="B68" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C68" s="5">
-        <v>145.05</v>
-      </c>
-      <c r="D68" s="5">
-        <v>253.73</v>
-      </c>
-      <c r="E68" s="6">
-        <v>108.68</v>
-      </c>
-    </row>
-    <row r="69" spans="1:5">
-      <c r="A69" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="B69" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C69" s="5">
-        <v>5.84</v>
-      </c>
-      <c r="D69" s="5">
-        <v>138.8</v>
-      </c>
-      <c r="E69" s="6">
-        <v>132.96</v>
-      </c>
-    </row>
-    <row r="70" spans="1:5">
-      <c r="A70" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="B70" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C70" s="5">
-        <v>-9.34</v>
-      </c>
-      <c r="D70" s="5">
+      <c r="C69" s="6">
         <v>-5.73</v>
       </c>
-      <c r="E70" s="6">
-        <v>3.61</v>
+      <c r="D69" s="6">
+        <v>-30.04</v>
+      </c>
+      <c r="E69" s="8">
+        <v>-24.31</v>
       </c>
     </row>
   </sheetData>
@@ -3094,60 +3140,60 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="28" customHeight="1">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="8" t="s">
-        <v>57</v>
-      </c>
-      <c r="C1" s="8" t="s">
-        <v>58</v>
-      </c>
-      <c r="D1" s="8" t="s">
-        <v>59</v>
-      </c>
-      <c r="E1" s="8" t="s">
-        <v>60</v>
-      </c>
-      <c r="F1" s="8" t="s">
-        <v>61</v>
-      </c>
-      <c r="G1" s="8" t="s">
-        <v>62</v>
-      </c>
-      <c r="H1" s="8" t="s">
-        <v>63</v>
-      </c>
-      <c r="I1" s="8" t="s">
-        <v>64</v>
+      <c r="B1" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="C1" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="D1" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="E1" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="F1" s="9" t="s">
+        <v>70</v>
+      </c>
+      <c r="G1" s="9" t="s">
+        <v>71</v>
+      </c>
+      <c r="H1" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="I1" s="9" t="s">
+        <v>73</v>
       </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="9" t="s">
+      <c r="A2" s="10" t="s">
         <v>45</v>
       </c>
-      <c r="B2" s="10">
+      <c r="B2" s="11">
         <v>37.44</v>
       </c>
-      <c r="C2" s="11">
+      <c r="C2" s="12">
         <v>8</v>
       </c>
-      <c r="D2" s="10">
-        <v>40.8</v>
-      </c>
-      <c r="E2" s="10">
+      <c r="D2" s="11">
+        <v>42.6</v>
+      </c>
+      <c r="E2" s="11">
         <v>12.5</v>
       </c>
-      <c r="F2" s="10">
-        <v>-6.5</v>
-      </c>
-      <c r="G2" s="10">
-        <v>-8.800000000000001</v>
-      </c>
-      <c r="H2" s="10">
+      <c r="F2" s="11">
+        <v>-6.8</v>
+      </c>
+      <c r="G2" s="11">
+        <v>-7.2</v>
+      </c>
+      <c r="H2" s="11">
         <v>56.1</v>
       </c>
-      <c r="I2" s="10">
+      <c r="I2" s="11">
         <v>0</v>
       </c>
     </row>
@@ -3249,55 +3295,55 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8">
-      <c r="A1" s="12" t="s">
+      <c r="A1" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="B1" s="12" t="s">
+      <c r="B1" s="13" t="s">
         <v>43</v>
       </c>
-      <c r="C1" s="12" t="s">
+      <c r="C1" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="D1" s="12" t="s">
+      <c r="D1" s="13" t="s">
         <v>39</v>
       </c>
-      <c r="E1" s="12" t="s">
+      <c r="E1" s="13" t="s">
         <v>44</v>
       </c>
-      <c r="F1" s="12" t="s">
+      <c r="F1" s="13" t="s">
         <v>41</v>
       </c>
-      <c r="G1" s="12" t="s">
+      <c r="G1" s="13" t="s">
         <v>42</v>
       </c>
-      <c r="H1" s="12" t="s">
+      <c r="H1" s="13" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="2" spans="1:8">
-      <c r="A2" s="13">
-        <v>0.291</v>
-      </c>
-      <c r="B2" s="13">
-        <v>0.1556</v>
-      </c>
-      <c r="C2" s="13">
-        <v>0.1383</v>
-      </c>
-      <c r="D2" s="13">
-        <v>0.1143</v>
-      </c>
-      <c r="E2" s="13">
-        <v>0.0917</v>
-      </c>
-      <c r="F2" s="13">
-        <v>0.0339</v>
-      </c>
-      <c r="G2" s="13">
-        <v>-0.2834</v>
-      </c>
-      <c r="H2" s="13">
-        <v>-0.3095</v>
+      <c r="A2" s="14">
+        <v>0.2924</v>
+      </c>
+      <c r="B2" s="14">
+        <v>0.1666</v>
+      </c>
+      <c r="C2" s="14">
+        <v>0.1443</v>
+      </c>
+      <c r="D2" s="14">
+        <v>0.1176</v>
+      </c>
+      <c r="E2" s="14">
+        <v>0.08810000000000001</v>
+      </c>
+      <c r="F2" s="14">
+        <v>0.04099999999999999</v>
+      </c>
+      <c r="G2" s="14">
+        <v>-0.2763</v>
+      </c>
+      <c r="H2" s="14">
+        <v>-0.3105</v>
       </c>
     </row>
   </sheetData>

--- a/BIRLA_GROUP_Technical_Metrics.xlsx
+++ b/BIRLA_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="285" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="280" uniqueCount="65">
   <si>
     <t>Symbol</t>
   </si>
@@ -175,34 +175,7 @@
     <t>▶  SIGNAL EVENTS (vs Previous Run)</t>
   </si>
   <si>
-    <t>Signal</t>
-  </si>
-  <si>
-    <t>Change</t>
-  </si>
-  <si>
-    <t>Direction</t>
-  </si>
-  <si>
-    <t>Prev Value</t>
-  </si>
-  <si>
-    <t>Curr Value</t>
-  </si>
-  <si>
-    <t>RSI Oversold Recovery</t>
-  </si>
-  <si>
-    <t>29.8 → 45.2</t>
-  </si>
-  <si>
-    <t>🟢 BULLISH</t>
-  </si>
-  <si>
-    <t>29.8</t>
-  </si>
-  <si>
-    <t>45.2</t>
+    <t>No signal events detected since last run.</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -404,15 +377,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -787,8 +759,9 @@
     <col min="14" max="14" width="11.7109375" customWidth="1"/>
     <col min="15" max="15" width="10.7109375" customWidth="1"/>
     <col min="16" max="16" width="9.7109375" customWidth="1"/>
-    <col min="17" max="18" width="10.7109375" customWidth="1"/>
-    <col min="19" max="19" width="9.7109375" customWidth="1"/>
+    <col min="17" max="17" width="10.7109375" customWidth="1"/>
+    <col min="18" max="18" width="9.7109375" customWidth="1"/>
+    <col min="19" max="19" width="10.7109375" customWidth="1"/>
     <col min="20" max="20" width="22.7109375" customWidth="1"/>
     <col min="21" max="21" width="9.7109375" customWidth="1"/>
     <col min="22" max="22" width="10.7109375" customWidth="1"/>
@@ -928,10 +901,10 @@
         <v>45</v>
       </c>
       <c r="C2">
-        <v>356</v>
+        <v>358.35</v>
       </c>
       <c r="D2">
-        <v>0.6899999999999999</v>
+        <v>0.66</v>
       </c>
       <c r="E2">
         <v>424.7</v>
@@ -940,46 +913,46 @@
         <v>292.25</v>
       </c>
       <c r="G2">
-        <v>-16.18</v>
+        <v>-15.62</v>
       </c>
       <c r="H2">
-        <v>21.81</v>
+        <v>22.62</v>
       </c>
       <c r="I2">
-        <v>-3</v>
+        <v>0.32</v>
       </c>
       <c r="J2">
-        <v>-8.720000000000001</v>
+        <v>-6.36</v>
       </c>
       <c r="K2">
-        <v>-9.029999999999999</v>
+        <v>-9.869999999999999</v>
       </c>
       <c r="L2">
-        <v>15.58</v>
+        <v>17.05</v>
       </c>
       <c r="M2">
-        <v>29.24</v>
+        <v>29.95</v>
       </c>
       <c r="N2">
-        <v>62</v>
+        <v>75</v>
       </c>
       <c r="O2">
         <v>73</v>
       </c>
       <c r="P2">
-        <v>353.41</v>
+        <v>353.64</v>
       </c>
       <c r="Q2">
-        <v>371.2</v>
+        <v>370.21</v>
       </c>
       <c r="R2">
-        <v>388.41</v>
+        <v>387.61</v>
       </c>
       <c r="S2">
         <v>366.05</v>
       </c>
       <c r="T2">
-        <v>-2.75</v>
+        <v>-2.1</v>
       </c>
       <c r="U2" t="s">
         <v>46</v>
@@ -994,34 +967,34 @@
         <v>1</v>
       </c>
       <c r="Y2">
-        <v>36.65</v>
+        <v>38.75</v>
       </c>
       <c r="Z2">
-        <v>-9.699999999999999</v>
+        <v>-9.44</v>
       </c>
       <c r="AA2">
-        <v>-7.84</v>
+        <v>-8.16</v>
       </c>
       <c r="AB2">
-        <v>-1.87</v>
+        <v>-1.28</v>
       </c>
       <c r="AC2">
-        <v>31.45</v>
+        <v>39.65</v>
       </c>
       <c r="AD2">
-        <v>19.46</v>
+        <v>29.76</v>
       </c>
       <c r="AE2">
-        <v>9.98</v>
+        <v>10.01</v>
       </c>
       <c r="AF2">
-        <v>-65.40000000000001</v>
+        <v>-5.36</v>
       </c>
       <c r="AG2">
-        <v>394.23</v>
+        <v>393.69</v>
       </c>
       <c r="AH2">
-        <v>348.17</v>
+        <v>346.74</v>
       </c>
       <c r="AI2">
         <v>375.32</v>
@@ -1030,7 +1003,7 @@
         <v>48</v>
       </c>
       <c r="AK2">
-        <v>43.54</v>
+        <v>40.74</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1041,10 +1014,10 @@
         <v>45</v>
       </c>
       <c r="C3">
-        <v>39.84</v>
+        <v>40.14</v>
       </c>
       <c r="D3">
-        <v>-0.33</v>
+        <v>0.75</v>
       </c>
       <c r="E3">
         <v>85.38</v>
@@ -1053,25 +1026,25 @@
         <v>39.58</v>
       </c>
       <c r="G3">
-        <v>-53.34</v>
+        <v>-52.99</v>
       </c>
       <c r="H3">
-        <v>0.66</v>
+        <v>1.41</v>
       </c>
       <c r="I3">
-        <v>-7.37</v>
+        <v>-2.9</v>
       </c>
       <c r="J3">
-        <v>-18.93</v>
+        <v>-15.65</v>
       </c>
       <c r="K3">
-        <v>-29.74</v>
+        <v>-30.86</v>
       </c>
       <c r="L3">
-        <v>-52.3</v>
+        <v>-51.01</v>
       </c>
       <c r="M3">
-        <v>-31.05</v>
+        <v>-31.34</v>
       </c>
       <c r="N3">
         <v>13</v>
@@ -1080,19 +1053,19 @@
         <v>4</v>
       </c>
       <c r="P3">
-        <v>40.1</v>
+        <v>39.86</v>
       </c>
       <c r="Q3">
-        <v>43.43</v>
+        <v>43.12</v>
       </c>
       <c r="R3">
-        <v>48.39</v>
+        <v>48.07</v>
       </c>
       <c r="S3">
-        <v>59.4</v>
+        <v>59.22</v>
       </c>
       <c r="T3">
-        <v>-32.93</v>
+        <v>-32.22</v>
       </c>
       <c r="U3" t="s">
         <v>46</v>
@@ -1107,34 +1080,34 @@
         <v>0</v>
       </c>
       <c r="Y3">
-        <v>25.45</v>
+        <v>27.68</v>
       </c>
       <c r="Z3">
-        <v>-2.46</v>
+        <v>-2.43</v>
       </c>
       <c r="AA3">
-        <v>-2.26</v>
+        <v>-2.29</v>
       </c>
       <c r="AB3">
-        <v>-0.2</v>
+        <v>-0.13</v>
       </c>
       <c r="AC3">
-        <v>10.57</v>
+        <v>20.18</v>
       </c>
       <c r="AD3">
-        <v>7.65</v>
+        <v>12.13</v>
       </c>
       <c r="AE3">
-        <v>1.61</v>
+        <v>1.57</v>
       </c>
       <c r="AF3">
-        <v>-30.3</v>
+        <v>-40.26</v>
       </c>
       <c r="AG3">
-        <v>47.82</v>
+        <v>47.54</v>
       </c>
       <c r="AH3">
-        <v>39.03</v>
+        <v>38.7</v>
       </c>
       <c r="AI3">
         <v>44.5</v>
@@ -1143,7 +1116,7 @@
         <v>48</v>
       </c>
       <c r="AK3">
-        <v>45.11</v>
+        <v>45.57</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1154,10 +1127,10 @@
         <v>45</v>
       </c>
       <c r="C4">
-        <v>2900</v>
+        <v>2932.8</v>
       </c>
       <c r="D4">
-        <v>-0.03</v>
+        <v>1.13</v>
       </c>
       <c r="E4">
         <v>3380.5</v>
@@ -1166,46 +1139,46 @@
         <v>2531.1</v>
       </c>
       <c r="G4">
-        <v>-14.21</v>
+        <v>-13.24</v>
       </c>
       <c r="H4">
-        <v>14.57</v>
+        <v>15.87</v>
       </c>
       <c r="I4">
-        <v>0.38</v>
+        <v>1.33</v>
       </c>
       <c r="J4">
-        <v>-9.119999999999999</v>
+        <v>-6.9</v>
       </c>
       <c r="K4">
-        <v>-6.94</v>
+        <v>-5.79</v>
       </c>
       <c r="L4">
-        <v>1.24</v>
+        <v>3.22</v>
       </c>
       <c r="M4">
-        <v>11.76</v>
+        <v>11.77</v>
       </c>
       <c r="N4">
         <v>50</v>
       </c>
       <c r="O4">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="P4">
-        <v>2907.84</v>
+        <v>2915.52</v>
       </c>
       <c r="Q4">
-        <v>2924.45</v>
+        <v>2916.09</v>
       </c>
       <c r="R4">
-        <v>3123.3</v>
+        <v>3116.95</v>
       </c>
       <c r="S4">
-        <v>2983.14</v>
+        <v>2983.85</v>
       </c>
       <c r="T4">
-        <v>-2.79</v>
+        <v>-1.71</v>
       </c>
       <c r="U4" t="s">
         <v>46</v>
@@ -1220,34 +1193,34 @@
         <v>1</v>
       </c>
       <c r="Y4">
-        <v>39.78</v>
+        <v>44.3</v>
       </c>
       <c r="Z4">
-        <v>-62.42</v>
+        <v>-56.45</v>
       </c>
       <c r="AA4">
-        <v>-74.26000000000001</v>
+        <v>-70.7</v>
       </c>
       <c r="AB4">
-        <v>11.84</v>
+        <v>14.24</v>
       </c>
       <c r="AC4">
-        <v>85.14</v>
+        <v>84.7</v>
       </c>
       <c r="AD4">
-        <v>90.42</v>
+        <v>86.76000000000001</v>
       </c>
       <c r="AE4">
-        <v>62.46</v>
+        <v>62.29</v>
       </c>
       <c r="AF4">
-        <v>19.38</v>
+        <v>-45.44</v>
       </c>
       <c r="AG4">
-        <v>3051.62</v>
+        <v>3013.07</v>
       </c>
       <c r="AH4">
-        <v>2797.28</v>
+        <v>2819.11</v>
       </c>
       <c r="AI4">
         <v>3050.83</v>
@@ -1256,7 +1229,7 @@
         <v>48</v>
       </c>
       <c r="AK4">
-        <v>38.26</v>
+        <v>35.09</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1267,10 +1240,10 @@
         <v>45</v>
       </c>
       <c r="C5">
-        <v>893.75</v>
+        <v>886.3</v>
       </c>
       <c r="D5">
-        <v>0.29</v>
+        <v>-0.83</v>
       </c>
       <c r="E5">
         <v>1149.7</v>
@@ -1279,46 +1252,46 @@
         <v>774.65</v>
       </c>
       <c r="G5">
-        <v>-22.26</v>
+        <v>-22.91</v>
       </c>
       <c r="H5">
-        <v>15.37</v>
+        <v>14.41</v>
       </c>
       <c r="I5">
-        <v>0.1</v>
+        <v>0.08</v>
       </c>
       <c r="J5">
-        <v>-8.52</v>
+        <v>-7.28</v>
       </c>
       <c r="K5">
-        <v>-4.55</v>
+        <v>-7.91</v>
       </c>
       <c r="L5">
-        <v>12.79</v>
+        <v>7.5</v>
       </c>
       <c r="M5">
-        <v>14.43</v>
+        <v>14.68</v>
       </c>
       <c r="N5">
-        <v>75</v>
+        <v>62</v>
       </c>
       <c r="O5">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="P5">
-        <v>885.21</v>
+        <v>885.35</v>
       </c>
       <c r="Q5">
-        <v>905.38</v>
+        <v>901.9299999999999</v>
       </c>
       <c r="R5">
-        <v>967.9</v>
+        <v>964.63</v>
       </c>
       <c r="S5">
-        <v>982.61</v>
+        <v>982.53</v>
       </c>
       <c r="T5">
-        <v>-9.039999999999999</v>
+        <v>-9.789999999999999</v>
       </c>
       <c r="U5" t="s">
         <v>46</v>
@@ -1333,34 +1306,34 @@
         <v>0</v>
       </c>
       <c r="Y5">
-        <v>41.16</v>
+        <v>39.23</v>
       </c>
       <c r="Z5">
-        <v>-22.94</v>
+        <v>-22.01</v>
       </c>
       <c r="AA5">
-        <v>-25.18</v>
+        <v>-24.55</v>
       </c>
       <c r="AB5">
-        <v>2.24</v>
+        <v>2.54</v>
       </c>
       <c r="AC5">
-        <v>95.09999999999999</v>
+        <v>95.22</v>
       </c>
       <c r="AD5">
-        <v>79.05</v>
+        <v>88.95999999999999</v>
       </c>
       <c r="AE5">
-        <v>22.94</v>
+        <v>22.28</v>
       </c>
       <c r="AF5">
-        <v>-25.33</v>
+        <v>24.14</v>
       </c>
       <c r="AG5">
-        <v>954.6</v>
+        <v>945.8200000000001</v>
       </c>
       <c r="AH5">
-        <v>856.16</v>
+        <v>858.04</v>
       </c>
       <c r="AI5">
         <v>933.28</v>
@@ -1369,7 +1342,7 @@
         <v>48</v>
       </c>
       <c r="AK5">
-        <v>40.32</v>
+        <v>38.7</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1380,10 +1353,10 @@
         <v>45</v>
       </c>
       <c r="C6">
-        <v>11.86</v>
+        <v>12.12</v>
       </c>
       <c r="D6">
-        <v>-2.06</v>
+        <v>2.19</v>
       </c>
       <c r="E6">
         <v>15.6</v>
@@ -1392,46 +1365,46 @@
         <v>8.529999999999999</v>
       </c>
       <c r="G6">
-        <v>-23.97</v>
+        <v>-22.31</v>
       </c>
       <c r="H6">
-        <v>39.04</v>
+        <v>42.09</v>
       </c>
       <c r="I6">
-        <v>1.89</v>
+        <v>5.12</v>
       </c>
       <c r="J6">
-        <v>-16.83</v>
+        <v>-10.02</v>
       </c>
       <c r="K6">
-        <v>-8.42</v>
+        <v>-7.13</v>
       </c>
       <c r="L6">
-        <v>24.58</v>
+        <v>25.99</v>
       </c>
       <c r="M6">
-        <v>4.1</v>
+        <v>4.88</v>
       </c>
       <c r="N6">
         <v>87</v>
       </c>
       <c r="O6">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="P6">
-        <v>11.76</v>
+        <v>11.88</v>
       </c>
       <c r="Q6">
-        <v>12.5</v>
+        <v>12.43</v>
       </c>
       <c r="R6">
-        <v>13.68</v>
+        <v>13.65</v>
       </c>
       <c r="S6">
         <v>12.31</v>
       </c>
       <c r="T6">
-        <v>-3.66</v>
+        <v>-1.57</v>
       </c>
       <c r="U6" t="s">
         <v>46</v>
@@ -1446,34 +1419,34 @@
         <v>1</v>
       </c>
       <c r="Y6">
-        <v>37.53</v>
+        <v>41.78</v>
       </c>
       <c r="Z6">
-        <v>-0.55</v>
+        <v>-0.51</v>
       </c>
       <c r="AA6">
         <v>-0.52</v>
       </c>
       <c r="AB6">
-        <v>-0.03</v>
+        <v>0.01</v>
       </c>
       <c r="AC6">
-        <v>80.81</v>
+        <v>89.90000000000001</v>
       </c>
       <c r="AD6">
-        <v>53.31</v>
+        <v>75.2</v>
       </c>
       <c r="AE6">
-        <v>0.47</v>
+        <v>0.46</v>
       </c>
       <c r="AF6">
-        <v>-31.83</v>
+        <v>-43.95</v>
       </c>
       <c r="AG6">
-        <v>13.7</v>
+        <v>13.52</v>
       </c>
       <c r="AH6">
-        <v>11.31</v>
+        <v>11.34</v>
       </c>
       <c r="AI6">
         <v>12.7</v>
@@ -1482,7 +1455,7 @@
         <v>48</v>
       </c>
       <c r="AK6">
-        <v>50.99</v>
+        <v>48.91</v>
       </c>
     </row>
     <row r="7" spans="1:37">
@@ -1493,10 +1466,10 @@
         <v>45</v>
       </c>
       <c r="C7">
-        <v>12.77</v>
+        <v>12.54</v>
       </c>
       <c r="D7">
-        <v>1.11</v>
+        <v>-1.8</v>
       </c>
       <c r="E7">
         <v>13.92</v>
@@ -1505,46 +1478,46 @@
         <v>4.69</v>
       </c>
       <c r="G7">
-        <v>-8.26</v>
+        <v>-9.91</v>
       </c>
       <c r="H7">
-        <v>172.28</v>
+        <v>167.38</v>
       </c>
       <c r="I7">
-        <v>9.43</v>
+        <v>10</v>
       </c>
       <c r="J7">
-        <v>10.37</v>
+        <v>13.79</v>
       </c>
       <c r="K7">
-        <v>15.88</v>
+        <v>10.29</v>
       </c>
       <c r="L7">
-        <v>145.58</v>
+        <v>142.55</v>
       </c>
       <c r="M7">
-        <v>-27.63</v>
+        <v>-27.7</v>
       </c>
       <c r="N7">
         <v>99</v>
       </c>
       <c r="O7">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="P7">
-        <v>12.03</v>
+        <v>12.26</v>
       </c>
       <c r="Q7">
-        <v>11.41</v>
+        <v>11.49</v>
       </c>
       <c r="R7">
-        <v>11.48</v>
+        <v>11.5</v>
       </c>
       <c r="S7">
-        <v>10.83</v>
+        <v>10.84</v>
       </c>
       <c r="T7">
-        <v>17.94</v>
+        <v>15.72</v>
       </c>
       <c r="U7" t="s">
         <v>46</v>
@@ -1559,34 +1532,34 @@
         <v>2</v>
       </c>
       <c r="Y7">
-        <v>60.77</v>
+        <v>58.19</v>
       </c>
       <c r="Z7">
-        <v>0.25</v>
+        <v>0.29</v>
       </c>
       <c r="AA7">
-        <v>0.1</v>
+        <v>0.14</v>
       </c>
       <c r="AB7">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="AC7">
-        <v>76.29000000000001</v>
+        <v>75.45999999999999</v>
       </c>
       <c r="AD7">
-        <v>64.62</v>
+        <v>71.67</v>
       </c>
       <c r="AE7">
-        <v>0.89</v>
+        <v>0.88</v>
       </c>
       <c r="AF7">
-        <v>1.04</v>
+        <v>-23.64</v>
       </c>
       <c r="AG7">
-        <v>12.95</v>
+        <v>13.09</v>
       </c>
       <c r="AH7">
-        <v>9.869999999999999</v>
+        <v>9.9</v>
       </c>
       <c r="AI7">
         <v>10.86</v>
@@ -1595,7 +1568,7 @@
         <v>49</v>
       </c>
       <c r="AK7">
-        <v>26.83</v>
+        <v>28</v>
       </c>
     </row>
     <row r="8" spans="1:37">
@@ -1606,10 +1579,10 @@
         <v>45</v>
       </c>
       <c r="C8">
-        <v>3916</v>
+        <v>3872.2</v>
       </c>
       <c r="D8">
-        <v>3.61</v>
+        <v>-1.12</v>
       </c>
       <c r="E8">
         <v>5724</v>
@@ -1618,46 +1591,46 @@
         <v>3779.4</v>
       </c>
       <c r="G8">
-        <v>-31.59</v>
+        <v>-32.35</v>
       </c>
       <c r="H8">
-        <v>3.61</v>
+        <v>2.46</v>
       </c>
       <c r="I8">
-        <v>0.23</v>
+        <v>-0.35</v>
       </c>
       <c r="J8">
-        <v>-2.47</v>
+        <v>-3.13</v>
       </c>
       <c r="K8">
-        <v>-7.64</v>
+        <v>-10.15</v>
       </c>
       <c r="L8">
-        <v>-32.24</v>
+        <v>-31.2</v>
       </c>
       <c r="M8">
-        <v>16.66</v>
+        <v>16.24</v>
       </c>
       <c r="N8">
         <v>25</v>
       </c>
       <c r="O8">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="P8">
-        <v>3830.94</v>
+        <v>3828.24</v>
       </c>
       <c r="Q8">
-        <v>3936.59</v>
+        <v>3928.82</v>
       </c>
       <c r="R8">
-        <v>4114.89</v>
+        <v>4101.39</v>
       </c>
       <c r="S8">
-        <v>4423.72</v>
+        <v>4418.04</v>
       </c>
       <c r="T8">
-        <v>-11.48</v>
+        <v>-12.35</v>
       </c>
       <c r="U8" t="s">
         <v>46</v>
@@ -1672,34 +1645,34 @@
         <v>0</v>
       </c>
       <c r="Y8">
-        <v>45.22</v>
+        <v>42.03</v>
       </c>
       <c r="Z8">
-        <v>-73.56</v>
+        <v>-69.75</v>
       </c>
       <c r="AA8">
-        <v>-71.90000000000001</v>
+        <v>-71.47</v>
       </c>
       <c r="AB8">
-        <v>-1.66</v>
+        <v>1.72</v>
       </c>
       <c r="AC8">
-        <v>33.33</v>
+        <v>59.77</v>
       </c>
       <c r="AD8">
-        <v>15.54</v>
+        <v>31.04</v>
       </c>
       <c r="AE8">
-        <v>112.13</v>
+        <v>109.84</v>
       </c>
       <c r="AF8">
-        <v>-14.48</v>
+        <v>-63.44</v>
       </c>
       <c r="AG8">
-        <v>4101.83</v>
+        <v>4090.61</v>
       </c>
       <c r="AH8">
-        <v>3771.36</v>
+        <v>3767.03</v>
       </c>
       <c r="AI8">
         <v>4043.79</v>
@@ -1708,7 +1681,7 @@
         <v>48</v>
       </c>
       <c r="AK8">
-        <v>30.66</v>
+        <v>28.28</v>
       </c>
     </row>
     <row r="9" spans="1:37">
@@ -1719,10 +1692,10 @@
         <v>45</v>
       </c>
       <c r="C9">
-        <v>11104</v>
+        <v>11175</v>
       </c>
       <c r="D9">
-        <v>-0.41</v>
+        <v>0.64</v>
       </c>
       <c r="E9">
         <v>13052</v>
@@ -1731,46 +1704,46 @@
         <v>10362</v>
       </c>
       <c r="G9">
-        <v>-14.92</v>
+        <v>-14.38</v>
       </c>
       <c r="H9">
-        <v>7.16</v>
+        <v>7.85</v>
       </c>
       <c r="I9">
-        <v>2.35</v>
+        <v>1.98</v>
       </c>
       <c r="J9">
-        <v>-0.46</v>
+        <v>1.36</v>
       </c>
       <c r="K9">
-        <v>-7.13</v>
+        <v>-6.86</v>
       </c>
       <c r="L9">
-        <v>-8.57</v>
+        <v>-6.23</v>
       </c>
       <c r="M9">
-        <v>8.81</v>
+        <v>8.4</v>
       </c>
       <c r="N9">
         <v>38</v>
       </c>
       <c r="O9">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="P9">
-        <v>11088.4</v>
+        <v>11131.8</v>
       </c>
       <c r="Q9">
-        <v>10831.45</v>
+        <v>10848.75</v>
       </c>
       <c r="R9">
-        <v>11081.28</v>
+        <v>11072.4</v>
       </c>
       <c r="S9">
-        <v>11628.4</v>
+        <v>11623.95</v>
       </c>
       <c r="T9">
-        <v>-4.51</v>
+        <v>-3.86</v>
       </c>
       <c r="U9" t="s">
         <v>46</v>
@@ -1785,34 +1758,34 @@
         <v>0</v>
       </c>
       <c r="Y9">
-        <v>54.61</v>
+        <v>56.55</v>
       </c>
       <c r="Z9">
-        <v>9.369999999999999</v>
+        <v>25.64</v>
       </c>
       <c r="AA9">
-        <v>-59.92</v>
+        <v>-42.81</v>
       </c>
       <c r="AB9">
-        <v>69.29000000000001</v>
+        <v>68.45</v>
       </c>
       <c r="AC9">
-        <v>95.23999999999999</v>
+        <v>94.31</v>
       </c>
       <c r="AD9">
-        <v>97.97</v>
+        <v>96.08</v>
       </c>
       <c r="AE9">
-        <v>248.04</v>
+        <v>247.32</v>
       </c>
       <c r="AF9">
-        <v>-30.04</v>
+        <v>-54.62</v>
       </c>
       <c r="AG9">
-        <v>11231.99</v>
+        <v>11277.73</v>
       </c>
       <c r="AH9">
-        <v>10430.91</v>
+        <v>10419.77</v>
       </c>
       <c r="AI9">
         <v>10372.89</v>
@@ -1821,7 +1794,7 @@
         <v>49</v>
       </c>
       <c r="AK9">
-        <v>38.71</v>
+        <v>38.15</v>
       </c>
     </row>
   </sheetData>
@@ -1962,7 +1935,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F69"/>
+  <dimension ref="A1:F72"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -1982,47 +1955,12 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="3" t="s">
         <v>51</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="D2" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="F2" s="3" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6">
-      <c r="A3" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="B3" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="C3" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="D3" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="E3" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="F3" s="4" t="s">
-        <v>60</v>
       </c>
     </row>
     <row r="5" spans="1:6">
       <c r="A5" s="2" t="s">
-        <v>61</v>
+        <v>52</v>
       </c>
       <c r="B5" s="2"/>
       <c r="C5" s="2"/>
@@ -2030,1091 +1968,1142 @@
       <c r="E5" s="2"/>
     </row>
     <row r="6" spans="1:6">
-      <c r="A6" s="3" t="s">
+      <c r="A6" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B6" s="3" t="s">
+      <c r="B6" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6">
+      <c r="A7" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C7" s="5">
+        <v>-8.720000000000001</v>
+      </c>
+      <c r="D7" s="5">
+        <v>-6.36</v>
+      </c>
+      <c r="E7" s="6">
+        <v>2.36</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C8" s="5">
+        <v>-18.93</v>
+      </c>
+      <c r="D8" s="5">
+        <v>-15.65</v>
+      </c>
+      <c r="E8" s="6">
+        <v>3.28</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C9" s="5">
+        <v>-9.119999999999999</v>
+      </c>
+      <c r="D9" s="5">
+        <v>-6.9</v>
+      </c>
+      <c r="E9" s="6">
+        <v>2.22</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C10" s="5">
+        <v>-8.52</v>
+      </c>
+      <c r="D10" s="5">
+        <v>-7.28</v>
+      </c>
+      <c r="E10" s="6">
+        <v>1.24</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C11" s="5">
+        <v>-16.83</v>
+      </c>
+      <c r="D11" s="5">
+        <v>-10.02</v>
+      </c>
+      <c r="E11" s="6">
+        <v>6.81</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C12" s="5">
+        <v>10.37</v>
+      </c>
+      <c r="D12" s="5">
+        <v>13.79</v>
+      </c>
+      <c r="E12" s="6">
+        <v>3.42</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="A13" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C13" s="5">
+        <v>-2.47</v>
+      </c>
+      <c r="D13" s="5">
+        <v>-3.13</v>
+      </c>
+      <c r="E13" s="7">
+        <v>-0.66</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C14" s="5">
+        <v>-0.46</v>
+      </c>
+      <c r="D14" s="5">
+        <v>1.36</v>
+      </c>
+      <c r="E14" s="6">
+        <v>1.82</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="A15" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C15" s="5">
+        <v>-3</v>
+      </c>
+      <c r="D15" s="5">
+        <v>0.32</v>
+      </c>
+      <c r="E15" s="6">
+        <v>3.32</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="A16" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C16" s="5">
+        <v>-7.37</v>
+      </c>
+      <c r="D16" s="5">
+        <v>-2.9</v>
+      </c>
+      <c r="E16" s="6">
+        <v>4.47</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C17" s="5">
+        <v>0.38</v>
+      </c>
+      <c r="D17" s="5">
+        <v>1.33</v>
+      </c>
+      <c r="E17" s="6">
+        <v>0.95</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C18" s="5">
+        <v>0.1</v>
+      </c>
+      <c r="D18" s="5">
+        <v>0.08</v>
+      </c>
+      <c r="E18" s="7">
+        <v>-0.02</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C19" s="5">
+        <v>1.89</v>
+      </c>
+      <c r="D19" s="5">
+        <v>5.12</v>
+      </c>
+      <c r="E19" s="6">
+        <v>3.23</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C20" s="5">
+        <v>9.43</v>
+      </c>
+      <c r="D20" s="5">
+        <v>10</v>
+      </c>
+      <c r="E20" s="6">
+        <v>0.57</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C21" s="5">
+        <v>0.23</v>
+      </c>
+      <c r="D21" s="5">
+        <v>-0.35</v>
+      </c>
+      <c r="E21" s="7">
+        <v>-0.58</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C22" s="5">
+        <v>2.35</v>
+      </c>
+      <c r="D22" s="5">
+        <v>1.98</v>
+      </c>
+      <c r="E22" s="7">
+        <v>-0.37</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C23" s="5">
+        <v>15.58</v>
+      </c>
+      <c r="D23" s="5">
+        <v>17.05</v>
+      </c>
+      <c r="E23" s="6">
+        <v>1.47</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C24" s="5">
+        <v>-52.3</v>
+      </c>
+      <c r="D24" s="5">
+        <v>-51.01</v>
+      </c>
+      <c r="E24" s="6">
+        <v>1.29</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B25" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C25" s="5">
+        <v>1.24</v>
+      </c>
+      <c r="D25" s="5">
+        <v>3.22</v>
+      </c>
+      <c r="E25" s="6">
+        <v>1.98</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C26" s="5">
+        <v>12.79</v>
+      </c>
+      <c r="D26" s="5">
+        <v>7.5</v>
+      </c>
+      <c r="E26" s="7">
+        <v>-5.29</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B27" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C27" s="5">
+        <v>24.58</v>
+      </c>
+      <c r="D27" s="5">
+        <v>25.99</v>
+      </c>
+      <c r="E27" s="6">
+        <v>1.41</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B28" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C28" s="5">
+        <v>145.58</v>
+      </c>
+      <c r="D28" s="5">
+        <v>142.55</v>
+      </c>
+      <c r="E28" s="7">
+        <v>-3.03</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="B29" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C29" s="5">
+        <v>-32.24</v>
+      </c>
+      <c r="D29" s="5">
+        <v>-31.2</v>
+      </c>
+      <c r="E29" s="6">
+        <v>1.04</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="B30" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C30" s="5">
+        <v>-8.57</v>
+      </c>
+      <c r="D30" s="5">
+        <v>-6.23</v>
+      </c>
+      <c r="E30" s="6">
+        <v>2.34</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5">
+      <c r="A31" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B31" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C31" s="5">
+        <v>-9.029999999999999</v>
+      </c>
+      <c r="D31" s="5">
+        <v>-9.869999999999999</v>
+      </c>
+      <c r="E31" s="7">
+        <v>-0.84</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5">
+      <c r="A32" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B32" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C32" s="5">
+        <v>-29.74</v>
+      </c>
+      <c r="D32" s="5">
+        <v>-30.86</v>
+      </c>
+      <c r="E32" s="7">
+        <v>-1.12</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5">
+      <c r="A33" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B33" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C33" s="5">
+        <v>-6.94</v>
+      </c>
+      <c r="D33" s="5">
+        <v>-5.79</v>
+      </c>
+      <c r="E33" s="6">
+        <v>1.15</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5">
+      <c r="A34" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B34" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C34" s="5">
+        <v>-4.55</v>
+      </c>
+      <c r="D34" s="5">
+        <v>-7.91</v>
+      </c>
+      <c r="E34" s="7">
+        <v>-3.36</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5">
+      <c r="A35" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B35" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C35" s="5">
+        <v>-8.42</v>
+      </c>
+      <c r="D35" s="5">
+        <v>-7.13</v>
+      </c>
+      <c r="E35" s="6">
+        <v>1.29</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5">
+      <c r="A36" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B36" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C36" s="5">
+        <v>15.88</v>
+      </c>
+      <c r="D36" s="5">
+        <v>10.29</v>
+      </c>
+      <c r="E36" s="7">
+        <v>-5.59</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5">
+      <c r="A37" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="B37" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C37" s="5">
+        <v>-7.64</v>
+      </c>
+      <c r="D37" s="5">
+        <v>-10.15</v>
+      </c>
+      <c r="E37" s="7">
+        <v>-2.51</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5">
+      <c r="A38" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="B38" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C38" s="5">
+        <v>-7.13</v>
+      </c>
+      <c r="D38" s="5">
+        <v>-6.86</v>
+      </c>
+      <c r="E38" s="6">
+        <v>0.27</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5">
+      <c r="A39" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B39" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C39" s="5">
+        <v>-16.18</v>
+      </c>
+      <c r="D39" s="5">
+        <v>-15.62</v>
+      </c>
+      <c r="E39" s="6">
+        <v>0.5600000000000001</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5">
+      <c r="A40" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B40" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C40" s="5">
+        <v>-53.34</v>
+      </c>
+      <c r="D40" s="5">
+        <v>-52.99</v>
+      </c>
+      <c r="E40" s="6">
+        <v>0.35</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5">
+      <c r="A41" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B41" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C41" s="5">
+        <v>-14.21</v>
+      </c>
+      <c r="D41" s="5">
+        <v>-13.24</v>
+      </c>
+      <c r="E41" s="6">
+        <v>0.97</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5">
+      <c r="A42" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B42" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C42" s="5">
+        <v>-22.26</v>
+      </c>
+      <c r="D42" s="5">
+        <v>-22.91</v>
+      </c>
+      <c r="E42" s="7">
+        <v>-0.65</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5">
+      <c r="A43" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B43" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C43" s="5">
+        <v>-23.97</v>
+      </c>
+      <c r="D43" s="5">
+        <v>-22.31</v>
+      </c>
+      <c r="E43" s="6">
+        <v>1.66</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5">
+      <c r="A44" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B44" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C44" s="5">
+        <v>-8.26</v>
+      </c>
+      <c r="D44" s="5">
+        <v>-9.91</v>
+      </c>
+      <c r="E44" s="7">
+        <v>-1.65</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5">
+      <c r="A45" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="B45" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C45" s="5">
+        <v>-31.59</v>
+      </c>
+      <c r="D45" s="5">
+        <v>-32.35</v>
+      </c>
+      <c r="E45" s="7">
+        <v>-0.76</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5">
+      <c r="A46" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="B46" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C46" s="5">
+        <v>-14.92</v>
+      </c>
+      <c r="D46" s="5">
+        <v>-14.38</v>
+      </c>
+      <c r="E46" s="6">
+        <v>0.54</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5">
+      <c r="A47" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B47" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C47" s="5">
+        <v>356</v>
+      </c>
+      <c r="D47" s="5">
+        <v>358.35</v>
+      </c>
+      <c r="E47" s="6">
+        <v>2.35</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5">
+      <c r="A48" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B48" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C48" s="5">
+        <v>39.84</v>
+      </c>
+      <c r="D48" s="5">
+        <v>40.14</v>
+      </c>
+      <c r="E48" s="6">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5">
+      <c r="A49" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B49" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C49" s="5">
+        <v>2900</v>
+      </c>
+      <c r="D49" s="5">
+        <v>2932.8</v>
+      </c>
+      <c r="E49" s="6">
+        <v>32.8</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5">
+      <c r="A50" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B50" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C50" s="5">
+        <v>893.75</v>
+      </c>
+      <c r="D50" s="5">
+        <v>886.3</v>
+      </c>
+      <c r="E50" s="7">
+        <v>-7.45</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5">
+      <c r="A51" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B51" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C51" s="5">
+        <v>11.86</v>
+      </c>
+      <c r="D51" s="5">
+        <v>12.12</v>
+      </c>
+      <c r="E51" s="6">
+        <v>0.26</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5">
+      <c r="A52" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B52" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C52" s="5">
+        <v>12.77</v>
+      </c>
+      <c r="D52" s="5">
+        <v>12.54</v>
+      </c>
+      <c r="E52" s="7">
+        <v>-0.23</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5">
+      <c r="A53" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="B53" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C53" s="5">
+        <v>3916</v>
+      </c>
+      <c r="D53" s="5">
+        <v>3872.2</v>
+      </c>
+      <c r="E53" s="7">
+        <v>-43.8</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5">
+      <c r="A54" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="B54" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C54" s="5">
+        <v>11104</v>
+      </c>
+      <c r="D54" s="5">
+        <v>11175</v>
+      </c>
+      <c r="E54" s="6">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5">
+      <c r="A55" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B55" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C55" s="5">
         <v>62</v>
       </c>
-      <c r="C6" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6">
-      <c r="A7" s="5" t="s">
+      <c r="D55" s="5">
+        <v>75</v>
+      </c>
+      <c r="E55" s="6">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5">
+      <c r="A56" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B56" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C56" s="5">
+        <v>75</v>
+      </c>
+      <c r="D56" s="5">
+        <v>62</v>
+      </c>
+      <c r="E56" s="7">
+        <v>-13</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5">
+      <c r="A57" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B7" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C7" s="6">
-        <v>-9.369999999999999</v>
-      </c>
-      <c r="D7" s="6">
-        <v>-8.720000000000001</v>
-      </c>
-      <c r="E7" s="7">
-        <v>0.65</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
-      <c r="A8" s="5" t="s">
+      <c r="B57" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C57" s="5">
+        <v>36.65</v>
+      </c>
+      <c r="D57" s="5">
+        <v>38.75</v>
+      </c>
+      <c r="E57" s="6">
+        <v>2.1</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5">
+      <c r="A58" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B8" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C8" s="6">
-        <v>-16.83</v>
-      </c>
-      <c r="D8" s="6">
-        <v>-18.93</v>
-      </c>
-      <c r="E8" s="8">
-        <v>-2.1</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9" s="5" t="s">
+      <c r="B58" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C58" s="5">
+        <v>25.45</v>
+      </c>
+      <c r="D58" s="5">
+        <v>27.68</v>
+      </c>
+      <c r="E58" s="6">
+        <v>2.23</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5">
+      <c r="A59" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B9" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C9" s="6">
-        <v>-8.390000000000001</v>
-      </c>
-      <c r="D9" s="6">
-        <v>-9.119999999999999</v>
-      </c>
-      <c r="E9" s="8">
-        <v>-0.73</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10" s="5" t="s">
+      <c r="B59" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C59" s="5">
+        <v>39.78</v>
+      </c>
+      <c r="D59" s="5">
+        <v>44.3</v>
+      </c>
+      <c r="E59" s="6">
+        <v>4.52</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5">
+      <c r="A60" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="B10" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C10" s="6">
-        <v>-9.25</v>
-      </c>
-      <c r="D10" s="6">
-        <v>-8.52</v>
-      </c>
-      <c r="E10" s="7">
-        <v>0.73</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11" s="5" t="s">
+      <c r="B60" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C60" s="5">
+        <v>41.16</v>
+      </c>
+      <c r="D60" s="5">
+        <v>39.23</v>
+      </c>
+      <c r="E60" s="7">
+        <v>-1.93</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5">
+      <c r="A61" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="B11" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C11" s="6">
-        <v>-14.24</v>
-      </c>
-      <c r="D11" s="6">
-        <v>-16.83</v>
-      </c>
-      <c r="E11" s="8">
-        <v>-2.59</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12" s="5" t="s">
+      <c r="B61" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C61" s="5">
+        <v>37.53</v>
+      </c>
+      <c r="D61" s="5">
+        <v>41.78</v>
+      </c>
+      <c r="E61" s="6">
+        <v>4.25</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5">
+      <c r="A62" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="B12" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C12" s="6">
-        <v>10.89</v>
-      </c>
-      <c r="D12" s="6">
-        <v>10.37</v>
-      </c>
-      <c r="E12" s="8">
-        <v>-0.52</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13" s="5" t="s">
+      <c r="B62" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C62" s="5">
+        <v>60.77</v>
+      </c>
+      <c r="D62" s="5">
+        <v>58.19</v>
+      </c>
+      <c r="E62" s="7">
+        <v>-2.58</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5">
+      <c r="A63" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="B13" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C13" s="6">
-        <v>-5.68</v>
-      </c>
-      <c r="D13" s="6">
-        <v>-2.47</v>
-      </c>
-      <c r="E13" s="7">
-        <v>3.21</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14" s="5" t="s">
+      <c r="B63" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C63" s="5">
+        <v>45.22</v>
+      </c>
+      <c r="D63" s="5">
+        <v>42.03</v>
+      </c>
+      <c r="E63" s="7">
+        <v>-3.19</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5">
+      <c r="A64" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="B14" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C14" s="6">
-        <v>0.85</v>
-      </c>
-      <c r="D14" s="6">
-        <v>-0.46</v>
-      </c>
-      <c r="E14" s="8">
-        <v>-1.31</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15" s="5" t="s">
+      <c r="B64" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C64" s="5">
+        <v>54.61</v>
+      </c>
+      <c r="D64" s="5">
+        <v>56.55</v>
+      </c>
+      <c r="E64" s="6">
+        <v>1.94</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5">
+      <c r="A65" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B15" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C15" s="6">
-        <v>-5.23</v>
-      </c>
-      <c r="D15" s="6">
-        <v>-3</v>
-      </c>
-      <c r="E15" s="7">
-        <v>2.23</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16" s="5" t="s">
+      <c r="B65" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C65" s="5">
+        <v>-65.40000000000001</v>
+      </c>
+      <c r="D65" s="5">
+        <v>-5.36</v>
+      </c>
+      <c r="E65" s="6">
+        <v>60.04</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5">
+      <c r="A66" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B66" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C66" s="5">
+        <v>-30.3</v>
+      </c>
+      <c r="D66" s="5">
+        <v>-40.26</v>
+      </c>
+      <c r="E66" s="7">
+        <v>-9.960000000000001</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5">
+      <c r="A67" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B16" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C16" s="6">
-        <v>0.76</v>
-      </c>
-      <c r="D16" s="6">
-        <v>0.38</v>
-      </c>
-      <c r="E16" s="8">
-        <v>-0.38</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5">
-      <c r="A17" s="5" t="s">
+      <c r="B67" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C67" s="5">
+        <v>19.38</v>
+      </c>
+      <c r="D67" s="5">
+        <v>-45.44</v>
+      </c>
+      <c r="E67" s="7">
+        <v>-64.81999999999999</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5">
+      <c r="A68" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="B17" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C17" s="6">
-        <v>-1.03</v>
-      </c>
-      <c r="D17" s="6">
-        <v>0.1</v>
-      </c>
-      <c r="E17" s="7">
-        <v>1.13</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5">
-      <c r="A18" s="5" t="s">
+      <c r="B68" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C68" s="5">
+        <v>-25.33</v>
+      </c>
+      <c r="D68" s="5">
+        <v>24.14</v>
+      </c>
+      <c r="E68" s="6">
+        <v>49.47</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5">
+      <c r="A69" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="B18" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C18" s="6">
-        <v>-1.38</v>
-      </c>
-      <c r="D18" s="6">
-        <v>1.89</v>
-      </c>
-      <c r="E18" s="7">
-        <v>3.27</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5">
-      <c r="A19" s="5" t="s">
+      <c r="B69" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C69" s="5">
+        <v>-31.83</v>
+      </c>
+      <c r="D69" s="5">
+        <v>-43.95</v>
+      </c>
+      <c r="E69" s="7">
+        <v>-12.12</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5">
+      <c r="A70" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="B19" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C19" s="6">
-        <v>-0.86</v>
-      </c>
-      <c r="D19" s="6">
-        <v>9.43</v>
-      </c>
-      <c r="E19" s="7">
-        <v>10.29</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5">
-      <c r="A20" s="5" t="s">
+      <c r="B70" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C70" s="5">
+        <v>1.04</v>
+      </c>
+      <c r="D70" s="5">
+        <v>-23.64</v>
+      </c>
+      <c r="E70" s="7">
+        <v>-24.68</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5">
+      <c r="A71" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="B20" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C20" s="6">
-        <v>-4.36</v>
-      </c>
-      <c r="D20" s="6">
-        <v>0.23</v>
-      </c>
-      <c r="E20" s="7">
-        <v>4.59</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5">
-      <c r="A21" s="5" t="s">
+      <c r="B71" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C71" s="5">
+        <v>-14.48</v>
+      </c>
+      <c r="D71" s="5">
+        <v>-63.44</v>
+      </c>
+      <c r="E71" s="7">
+        <v>-48.96</v>
+      </c>
+    </row>
+    <row r="72" spans="1:5">
+      <c r="A72" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="B21" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C21" s="6">
-        <v>4.69</v>
-      </c>
-      <c r="D21" s="6">
-        <v>2.35</v>
-      </c>
-      <c r="E21" s="8">
-        <v>-2.34</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5">
-      <c r="A22" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B22" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C22" s="6">
-        <v>15.98</v>
-      </c>
-      <c r="D22" s="6">
-        <v>15.58</v>
-      </c>
-      <c r="E22" s="8">
-        <v>-0.4</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5">
-      <c r="A23" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B23" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C23" s="6">
-        <v>-52.22</v>
-      </c>
-      <c r="D23" s="6">
-        <v>-52.3</v>
-      </c>
-      <c r="E23" s="8">
-        <v>-0.08</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5">
-      <c r="A24" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B24" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C24" s="6">
-        <v>1.05</v>
-      </c>
-      <c r="D24" s="6">
-        <v>1.24</v>
-      </c>
-      <c r="E24" s="7">
-        <v>0.19</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5">
-      <c r="A25" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B25" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C25" s="6">
-        <v>13.54</v>
-      </c>
-      <c r="D25" s="6">
-        <v>12.79</v>
-      </c>
-      <c r="E25" s="8">
-        <v>-0.75</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5">
-      <c r="A26" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B26" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C26" s="6">
-        <v>34.56</v>
-      </c>
-      <c r="D26" s="6">
-        <v>24.58</v>
-      </c>
-      <c r="E26" s="8">
-        <v>-9.98</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5">
-      <c r="A27" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B27" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C27" s="6">
-        <v>140.57</v>
-      </c>
-      <c r="D27" s="6">
-        <v>145.58</v>
-      </c>
-      <c r="E27" s="7">
-        <v>5.01</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5">
-      <c r="A28" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B28" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C28" s="6">
-        <v>-34.94</v>
-      </c>
-      <c r="D28" s="6">
-        <v>-32.24</v>
-      </c>
-      <c r="E28" s="7">
-        <v>2.7</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5">
-      <c r="A29" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="B29" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C29" s="6">
-        <v>-9.66</v>
-      </c>
-      <c r="D29" s="6">
-        <v>-8.57</v>
-      </c>
-      <c r="E29" s="7">
-        <v>1.09</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5">
-      <c r="A30" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B30" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C30" s="6">
-        <v>-11.71</v>
-      </c>
-      <c r="D30" s="6">
-        <v>-9.029999999999999</v>
-      </c>
-      <c r="E30" s="7">
-        <v>2.68</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5">
-      <c r="A31" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B31" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C31" s="6">
-        <v>-29.94</v>
-      </c>
-      <c r="D31" s="6">
-        <v>-29.74</v>
-      </c>
-      <c r="E31" s="7">
-        <v>0.2</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5">
-      <c r="A32" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B32" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C32" s="6">
-        <v>-6.8</v>
-      </c>
-      <c r="D32" s="6">
-        <v>-6.94</v>
-      </c>
-      <c r="E32" s="8">
-        <v>-0.14</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5">
-      <c r="A33" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B33" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C33" s="6">
-        <v>-5.72</v>
-      </c>
-      <c r="D33" s="6">
-        <v>-4.55</v>
-      </c>
-      <c r="E33" s="7">
-        <v>1.17</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5">
-      <c r="A34" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B34" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C34" s="6">
-        <v>-7.27</v>
-      </c>
-      <c r="D34" s="6">
-        <v>-8.42</v>
-      </c>
-      <c r="E34" s="8">
-        <v>-1.15</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5">
-      <c r="A35" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B35" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C35" s="6">
-        <v>10.31</v>
-      </c>
-      <c r="D35" s="6">
-        <v>15.88</v>
-      </c>
-      <c r="E35" s="7">
-        <v>5.57</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5">
-      <c r="A36" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B36" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C36" s="6">
-        <v>-13.02</v>
-      </c>
-      <c r="D36" s="6">
-        <v>-7.64</v>
-      </c>
-      <c r="E36" s="7">
-        <v>5.38</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5">
-      <c r="A37" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="B37" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C37" s="6">
-        <v>-6.15</v>
-      </c>
-      <c r="D37" s="6">
-        <v>-7.13</v>
-      </c>
-      <c r="E37" s="8">
-        <v>-0.98</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5">
-      <c r="A38" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B38" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C38" s="6">
-        <v>-16.75</v>
-      </c>
-      <c r="D38" s="6">
-        <v>-16.18</v>
-      </c>
-      <c r="E38" s="7">
-        <v>0.57</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5">
-      <c r="A39" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B39" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C39" s="6">
-        <v>-53.19</v>
-      </c>
-      <c r="D39" s="6">
-        <v>-53.34</v>
-      </c>
-      <c r="E39" s="8">
-        <v>-0.15</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5">
-      <c r="A40" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B40" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C40" s="6">
-        <v>-14.19</v>
-      </c>
-      <c r="D40" s="6">
-        <v>-14.21</v>
-      </c>
-      <c r="E40" s="8">
-        <v>-0.02</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5">
-      <c r="A41" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B41" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C41" s="6">
-        <v>-22.48</v>
-      </c>
-      <c r="D41" s="6">
-        <v>-22.26</v>
-      </c>
-      <c r="E41" s="7">
-        <v>0.22</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5">
-      <c r="A42" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B42" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C42" s="6">
-        <v>-22.37</v>
-      </c>
-      <c r="D42" s="6">
-        <v>-23.97</v>
-      </c>
-      <c r="E42" s="8">
-        <v>-1.6</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5">
-      <c r="A43" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B43" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C43" s="6">
-        <v>-9.27</v>
-      </c>
-      <c r="D43" s="6">
-        <v>-8.26</v>
-      </c>
-      <c r="E43" s="7">
-        <v>1.01</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5">
-      <c r="A44" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B44" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C44" s="6">
-        <v>-34.6</v>
-      </c>
-      <c r="D44" s="6">
-        <v>-31.59</v>
-      </c>
-      <c r="E44" s="7">
-        <v>3.01</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5">
-      <c r="A45" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="B45" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C45" s="6">
-        <v>-14.57</v>
-      </c>
-      <c r="D45" s="6">
-        <v>-14.92</v>
-      </c>
-      <c r="E45" s="8">
-        <v>-0.35</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5">
-      <c r="A46" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B46" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C46" s="6">
-        <v>353.55</v>
-      </c>
-      <c r="D46" s="6">
-        <v>356</v>
-      </c>
-      <c r="E46" s="7">
-        <v>2.45</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5">
-      <c r="A47" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B47" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C47" s="6">
-        <v>39.97</v>
-      </c>
-      <c r="D47" s="6">
-        <v>39.84</v>
-      </c>
-      <c r="E47" s="8">
-        <v>-0.13</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5">
-      <c r="A48" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B48" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C48" s="6">
-        <v>2900.8</v>
-      </c>
-      <c r="D48" s="6">
-        <v>2900</v>
-      </c>
-      <c r="E48" s="8">
-        <v>-0.8</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5">
-      <c r="A49" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B49" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C49" s="6">
-        <v>891.2</v>
-      </c>
-      <c r="D49" s="6">
-        <v>893.75</v>
-      </c>
-      <c r="E49" s="7">
-        <v>2.55</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5">
-      <c r="A50" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B50" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C50" s="6">
-        <v>12.11</v>
-      </c>
-      <c r="D50" s="6">
-        <v>11.86</v>
-      </c>
-      <c r="E50" s="8">
-        <v>-0.25</v>
-      </c>
-    </row>
-    <row r="51" spans="1:5">
-      <c r="A51" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B51" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C51" s="6">
-        <v>12.63</v>
-      </c>
-      <c r="D51" s="6">
-        <v>12.77</v>
-      </c>
-      <c r="E51" s="7">
-        <v>0.14</v>
-      </c>
-    </row>
-    <row r="52" spans="1:5">
-      <c r="A52" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B52" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C52" s="6">
-        <v>3779.4</v>
-      </c>
-      <c r="D52" s="6">
-        <v>3916</v>
-      </c>
-      <c r="E52" s="7">
-        <v>136.6</v>
-      </c>
-    </row>
-    <row r="53" spans="1:5">
-      <c r="A53" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="B53" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C53" s="6">
-        <v>11150</v>
-      </c>
-      <c r="D53" s="6">
-        <v>11104</v>
-      </c>
-      <c r="E53" s="8">
-        <v>-46</v>
-      </c>
-    </row>
-    <row r="54" spans="1:5">
-      <c r="A54" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B54" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C54" s="6">
-        <v>34.47</v>
-      </c>
-      <c r="D54" s="6">
-        <v>36.65</v>
-      </c>
-      <c r="E54" s="7">
-        <v>2.18</v>
-      </c>
-    </row>
-    <row r="55" spans="1:5">
-      <c r="A55" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B55" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C55" s="6">
-        <v>25.77</v>
-      </c>
-      <c r="D55" s="6">
-        <v>25.45</v>
-      </c>
-      <c r="E55" s="8">
-        <v>-0.32</v>
-      </c>
-    </row>
-    <row r="56" spans="1:5">
-      <c r="A56" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B56" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C56" s="6">
-        <v>39.86</v>
-      </c>
-      <c r="D56" s="6">
-        <v>39.78</v>
-      </c>
-      <c r="E56" s="8">
-        <v>-0.08</v>
-      </c>
-    </row>
-    <row r="57" spans="1:5">
-      <c r="A57" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B57" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C57" s="6">
-        <v>40.22</v>
-      </c>
-      <c r="D57" s="6">
-        <v>41.16</v>
-      </c>
-      <c r="E57" s="7">
-        <v>0.9399999999999999</v>
-      </c>
-    </row>
-    <row r="58" spans="1:5">
-      <c r="A58" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B58" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C58" s="6">
-        <v>40.15</v>
-      </c>
-      <c r="D58" s="6">
-        <v>37.53</v>
-      </c>
-      <c r="E58" s="8">
-        <v>-2.62</v>
-      </c>
-    </row>
-    <row r="59" spans="1:5">
-      <c r="A59" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B59" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C59" s="6">
-        <v>59.76</v>
-      </c>
-      <c r="D59" s="6">
-        <v>60.77</v>
-      </c>
-      <c r="E59" s="7">
-        <v>1.01</v>
-      </c>
-    </row>
-    <row r="60" spans="1:5">
-      <c r="A60" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B60" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C60" s="6">
-        <v>29.81</v>
-      </c>
-      <c r="D60" s="6">
-        <v>45.22</v>
-      </c>
-      <c r="E60" s="7">
-        <v>15.41</v>
-      </c>
-    </row>
-    <row r="61" spans="1:5">
-      <c r="A61" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="B61" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C61" s="6">
-        <v>56.11</v>
-      </c>
-      <c r="D61" s="6">
-        <v>54.61</v>
-      </c>
-      <c r="E61" s="8">
-        <v>-1.5</v>
-      </c>
-    </row>
-    <row r="62" spans="1:5">
-      <c r="A62" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B62" s="5" t="s">
+      <c r="B72" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="C62" s="6">
-        <v>-29.06</v>
-      </c>
-      <c r="D62" s="6">
-        <v>-65.40000000000001</v>
-      </c>
-      <c r="E62" s="8">
-        <v>-36.34</v>
-      </c>
-    </row>
-    <row r="63" spans="1:5">
-      <c r="A63" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B63" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C63" s="6">
-        <v>-46.61</v>
-      </c>
-      <c r="D63" s="6">
-        <v>-30.3</v>
-      </c>
-      <c r="E63" s="7">
-        <v>16.31</v>
-      </c>
-    </row>
-    <row r="64" spans="1:5">
-      <c r="A64" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B64" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C64" s="6">
-        <v>1.57</v>
-      </c>
-      <c r="D64" s="6">
-        <v>19.38</v>
-      </c>
-      <c r="E64" s="7">
-        <v>17.81</v>
-      </c>
-    </row>
-    <row r="65" spans="1:5">
-      <c r="A65" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B65" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C65" s="6">
-        <v>-6.19</v>
-      </c>
-      <c r="D65" s="6">
-        <v>-25.33</v>
-      </c>
-      <c r="E65" s="8">
-        <v>-19.14</v>
-      </c>
-    </row>
-    <row r="66" spans="1:5">
-      <c r="A66" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B66" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C66" s="6">
-        <v>-13.74</v>
-      </c>
-      <c r="D66" s="6">
-        <v>-31.83</v>
-      </c>
-      <c r="E66" s="8">
-        <v>-18.09</v>
-      </c>
-    </row>
-    <row r="67" spans="1:5">
-      <c r="A67" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B67" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C67" s="6">
-        <v>253.73</v>
-      </c>
-      <c r="D67" s="6">
-        <v>1.04</v>
-      </c>
-      <c r="E67" s="8">
-        <v>-252.69</v>
-      </c>
-    </row>
-    <row r="68" spans="1:5">
-      <c r="A68" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B68" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C68" s="6">
-        <v>138.8</v>
-      </c>
-      <c r="D68" s="6">
-        <v>-14.48</v>
-      </c>
-      <c r="E68" s="8">
-        <v>-153.28</v>
-      </c>
-    </row>
-    <row r="69" spans="1:5">
-      <c r="A69" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="B69" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C69" s="6">
-        <v>-5.73</v>
-      </c>
-      <c r="D69" s="6">
+      <c r="C72" s="5">
         <v>-30.04</v>
       </c>
-      <c r="E69" s="8">
-        <v>-24.31</v>
+      <c r="D72" s="5">
+        <v>-54.62</v>
+      </c>
+      <c r="E72" s="7">
+        <v>-24.58</v>
       </c>
     </row>
   </sheetData>
@@ -3140,60 +3129,60 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="28" customHeight="1">
-      <c r="A1" s="9" t="s">
+      <c r="A1" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="C1" s="9" t="s">
-        <v>67</v>
-      </c>
-      <c r="D1" s="9" t="s">
-        <v>68</v>
-      </c>
-      <c r="E1" s="9" t="s">
-        <v>69</v>
-      </c>
-      <c r="F1" s="9" t="s">
-        <v>70</v>
-      </c>
-      <c r="G1" s="9" t="s">
-        <v>71</v>
-      </c>
-      <c r="H1" s="9" t="s">
-        <v>72</v>
-      </c>
-      <c r="I1" s="9" t="s">
-        <v>73</v>
+      <c r="B1" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="C1" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="D1" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="E1" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="F1" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="G1" s="8" t="s">
+        <v>62</v>
+      </c>
+      <c r="H1" s="8" t="s">
+        <v>63</v>
+      </c>
+      <c r="I1" s="8" t="s">
+        <v>64</v>
       </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="10" t="s">
+      <c r="A2" s="9" t="s">
         <v>45</v>
       </c>
-      <c r="B2" s="11">
+      <c r="B2" s="10">
         <v>37.44</v>
       </c>
-      <c r="C2" s="12">
+      <c r="C2" s="11">
         <v>8</v>
       </c>
-      <c r="D2" s="11">
-        <v>42.6</v>
-      </c>
-      <c r="E2" s="11">
+      <c r="D2" s="10">
+        <v>43.6</v>
+      </c>
+      <c r="E2" s="10">
         <v>12.5</v>
       </c>
-      <c r="F2" s="11">
-        <v>-6.8</v>
-      </c>
-      <c r="G2" s="11">
-        <v>-7.2</v>
-      </c>
-      <c r="H2" s="11">
+      <c r="F2" s="10">
+        <v>-4.3</v>
+      </c>
+      <c r="G2" s="10">
+        <v>-8.5</v>
+      </c>
+      <c r="H2" s="10">
         <v>56.1</v>
       </c>
-      <c r="I2" s="11">
+      <c r="I2" s="10">
         <v>0</v>
       </c>
     </row>
@@ -3295,55 +3284,55 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8">
-      <c r="A1" s="13" t="s">
+      <c r="A1" s="12" t="s">
         <v>37</v>
       </c>
-      <c r="B1" s="13" t="s">
+      <c r="B1" s="12" t="s">
         <v>43</v>
       </c>
-      <c r="C1" s="13" t="s">
+      <c r="C1" s="12" t="s">
         <v>40</v>
       </c>
-      <c r="D1" s="13" t="s">
+      <c r="D1" s="12" t="s">
         <v>39</v>
       </c>
-      <c r="E1" s="13" t="s">
+      <c r="E1" s="12" t="s">
         <v>44</v>
       </c>
-      <c r="F1" s="13" t="s">
+      <c r="F1" s="12" t="s">
         <v>41</v>
       </c>
-      <c r="G1" s="13" t="s">
+      <c r="G1" s="12" t="s">
         <v>42</v>
       </c>
-      <c r="H1" s="13" t="s">
+      <c r="H1" s="12" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="2" spans="1:8">
-      <c r="A2" s="14">
-        <v>0.2924</v>
-      </c>
-      <c r="B2" s="14">
-        <v>0.1666</v>
-      </c>
-      <c r="C2" s="14">
-        <v>0.1443</v>
-      </c>
-      <c r="D2" s="14">
-        <v>0.1176</v>
-      </c>
-      <c r="E2" s="14">
-        <v>0.08810000000000001</v>
-      </c>
-      <c r="F2" s="14">
-        <v>0.04099999999999999</v>
-      </c>
-      <c r="G2" s="14">
-        <v>-0.2763</v>
-      </c>
-      <c r="H2" s="14">
-        <v>-0.3105</v>
+      <c r="A2" s="13">
+        <v>0.2995</v>
+      </c>
+      <c r="B2" s="13">
+        <v>0.1624</v>
+      </c>
+      <c r="C2" s="13">
+        <v>0.1468</v>
+      </c>
+      <c r="D2" s="13">
+        <v>0.1177</v>
+      </c>
+      <c r="E2" s="13">
+        <v>0.08400000000000001</v>
+      </c>
+      <c r="F2" s="13">
+        <v>0.0488</v>
+      </c>
+      <c r="G2" s="13">
+        <v>-0.277</v>
+      </c>
+      <c r="H2" s="13">
+        <v>-0.3134</v>
       </c>
     </row>
   </sheetData>

--- a/BIRLA_GROUP_Technical_Metrics.xlsx
+++ b/BIRLA_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="280" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="301" uniqueCount="76">
   <si>
     <t>Symbol</t>
   </si>
@@ -175,7 +175,40 @@
     <t>▶  SIGNAL EVENTS (vs Previous Run)</t>
   </si>
   <si>
-    <t>No signal events detected since last run.</t>
+    <t>Signal</t>
+  </si>
+  <si>
+    <t>Change</t>
+  </si>
+  <si>
+    <t>Direction</t>
+  </si>
+  <si>
+    <t>Prev Value</t>
+  </si>
+  <si>
+    <t>Curr Value</t>
+  </si>
+  <si>
+    <t>RSI Momentum</t>
+  </si>
+  <si>
+    <t>44.3 → 50.2</t>
+  </si>
+  <si>
+    <t>🟢 BULLISH</t>
+  </si>
+  <si>
+    <t>44.3</t>
+  </si>
+  <si>
+    <t>50.2</t>
+  </si>
+  <si>
+    <t>No → Yes</t>
+  </si>
+  <si>
+    <t>20 DMA &gt; 50 DMA</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -377,14 +410,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -758,10 +792,8 @@
     <col min="13" max="13" width="10.7109375" customWidth="1"/>
     <col min="14" max="14" width="11.7109375" customWidth="1"/>
     <col min="15" max="15" width="10.7109375" customWidth="1"/>
-    <col min="16" max="16" width="9.7109375" customWidth="1"/>
-    <col min="17" max="17" width="10.7109375" customWidth="1"/>
-    <col min="18" max="18" width="9.7109375" customWidth="1"/>
-    <col min="19" max="19" width="10.7109375" customWidth="1"/>
+    <col min="16" max="17" width="9.7109375" customWidth="1"/>
+    <col min="18" max="19" width="10.7109375" customWidth="1"/>
     <col min="20" max="20" width="22.7109375" customWidth="1"/>
     <col min="21" max="21" width="9.7109375" customWidth="1"/>
     <col min="22" max="22" width="10.7109375" customWidth="1"/>
@@ -901,10 +933,10 @@
         <v>45</v>
       </c>
       <c r="C2">
-        <v>358.35</v>
+        <v>369.45</v>
       </c>
       <c r="D2">
-        <v>0.66</v>
+        <v>3.1</v>
       </c>
       <c r="E2">
         <v>424.7</v>
@@ -913,46 +945,46 @@
         <v>292.25</v>
       </c>
       <c r="G2">
-        <v>-15.62</v>
+        <v>-13.01</v>
       </c>
       <c r="H2">
-        <v>22.62</v>
+        <v>26.42</v>
       </c>
       <c r="I2">
-        <v>0.32</v>
+        <v>6.39</v>
       </c>
       <c r="J2">
-        <v>-6.36</v>
+        <v>-2.26</v>
       </c>
       <c r="K2">
-        <v>-9.869999999999999</v>
+        <v>-6.24</v>
       </c>
       <c r="L2">
-        <v>17.05</v>
+        <v>18.89</v>
       </c>
       <c r="M2">
-        <v>29.95</v>
+        <v>30.04</v>
       </c>
       <c r="N2">
-        <v>75</v>
+        <v>87</v>
       </c>
       <c r="O2">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="P2">
-        <v>353.64</v>
+        <v>358.08</v>
       </c>
       <c r="Q2">
-        <v>370.21</v>
+        <v>369.66</v>
       </c>
       <c r="R2">
-        <v>387.61</v>
+        <v>386.96</v>
       </c>
       <c r="S2">
-        <v>366.05</v>
+        <v>366.13</v>
       </c>
       <c r="T2">
-        <v>-2.1</v>
+        <v>0.91</v>
       </c>
       <c r="U2" t="s">
         <v>46</v>
@@ -964,37 +996,37 @@
         <v>46</v>
       </c>
       <c r="X2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y2">
-        <v>38.75</v>
+        <v>47.6</v>
       </c>
       <c r="Z2">
-        <v>-9.44</v>
+        <v>-8.24</v>
       </c>
       <c r="AA2">
-        <v>-8.16</v>
+        <v>-8.17</v>
       </c>
       <c r="AB2">
-        <v>-1.28</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="AC2">
-        <v>39.65</v>
+        <v>62.49</v>
       </c>
       <c r="AD2">
-        <v>29.76</v>
+        <v>44.53</v>
       </c>
       <c r="AE2">
-        <v>10.01</v>
+        <v>11.15</v>
       </c>
       <c r="AF2">
-        <v>-5.36</v>
+        <v>181.18</v>
       </c>
       <c r="AG2">
-        <v>393.69</v>
+        <v>392.62</v>
       </c>
       <c r="AH2">
-        <v>346.74</v>
+        <v>346.69</v>
       </c>
       <c r="AI2">
         <v>375.32</v>
@@ -1003,7 +1035,7 @@
         <v>48</v>
       </c>
       <c r="AK2">
-        <v>40.74</v>
+        <v>36.74</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1014,37 +1046,37 @@
         <v>45</v>
       </c>
       <c r="C3">
-        <v>40.14</v>
+        <v>38.78</v>
       </c>
       <c r="D3">
-        <v>0.75</v>
+        <v>-3.39</v>
       </c>
       <c r="E3">
         <v>85.38</v>
       </c>
       <c r="F3">
-        <v>39.58</v>
+        <v>38.78</v>
       </c>
       <c r="G3">
-        <v>-52.99</v>
+        <v>-54.58</v>
       </c>
       <c r="H3">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="I3">
-        <v>-2.9</v>
+        <v>-2.49</v>
       </c>
       <c r="J3">
-        <v>-15.65</v>
+        <v>-16.13</v>
       </c>
       <c r="K3">
-        <v>-30.86</v>
+        <v>-34.2</v>
       </c>
       <c r="L3">
-        <v>-51.01</v>
+        <v>-52.57</v>
       </c>
       <c r="M3">
-        <v>-31.34</v>
+        <v>-32.26</v>
       </c>
       <c r="N3">
         <v>13</v>
@@ -1053,19 +1085,19 @@
         <v>4</v>
       </c>
       <c r="P3">
-        <v>39.86</v>
+        <v>39.66</v>
       </c>
       <c r="Q3">
-        <v>43.12</v>
+        <v>42.74</v>
       </c>
       <c r="R3">
-        <v>48.07</v>
+        <v>47.75</v>
       </c>
       <c r="S3">
-        <v>59.22</v>
+        <v>59.05</v>
       </c>
       <c r="T3">
-        <v>-32.22</v>
+        <v>-34.32</v>
       </c>
       <c r="U3" t="s">
         <v>46</v>
@@ -1080,43 +1112,43 @@
         <v>0</v>
       </c>
       <c r="Y3">
-        <v>27.68</v>
+        <v>24.16</v>
       </c>
       <c r="Z3">
-        <v>-2.43</v>
+        <v>-2.48</v>
       </c>
       <c r="AA3">
-        <v>-2.29</v>
+        <v>-2.33</v>
       </c>
       <c r="AB3">
-        <v>-0.13</v>
+        <v>-0.15</v>
       </c>
       <c r="AC3">
-        <v>20.18</v>
+        <v>16.81</v>
       </c>
       <c r="AD3">
-        <v>12.13</v>
+        <v>15.85</v>
       </c>
       <c r="AE3">
-        <v>1.57</v>
+        <v>1.59</v>
       </c>
       <c r="AF3">
-        <v>-40.26</v>
+        <v>-8.619999999999999</v>
       </c>
       <c r="AG3">
-        <v>47.54</v>
+        <v>47.3</v>
       </c>
       <c r="AH3">
-        <v>38.7</v>
+        <v>38.19</v>
       </c>
       <c r="AI3">
-        <v>44.5</v>
+        <v>43.91</v>
       </c>
       <c r="AJ3" t="s">
         <v>48</v>
       </c>
       <c r="AK3">
-        <v>45.57</v>
+        <v>47.51</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1127,10 +1159,10 @@
         <v>45</v>
       </c>
       <c r="C4">
-        <v>2932.8</v>
+        <v>2981.4</v>
       </c>
       <c r="D4">
-        <v>1.13</v>
+        <v>1.66</v>
       </c>
       <c r="E4">
         <v>3380.5</v>
@@ -1139,46 +1171,46 @@
         <v>2531.1</v>
       </c>
       <c r="G4">
-        <v>-13.24</v>
+        <v>-11.81</v>
       </c>
       <c r="H4">
-        <v>15.87</v>
+        <v>17.79</v>
       </c>
       <c r="I4">
-        <v>1.33</v>
+        <v>3.02</v>
       </c>
       <c r="J4">
-        <v>-6.9</v>
+        <v>-3.83</v>
       </c>
       <c r="K4">
-        <v>-5.79</v>
+        <v>-3.97</v>
       </c>
       <c r="L4">
-        <v>3.22</v>
+        <v>1.97</v>
       </c>
       <c r="M4">
-        <v>11.77</v>
+        <v>11.28</v>
       </c>
       <c r="N4">
-        <v>50</v>
+        <v>62</v>
       </c>
       <c r="O4">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="P4">
-        <v>2915.52</v>
+        <v>2933</v>
       </c>
       <c r="Q4">
-        <v>2916.09</v>
+        <v>2912.07</v>
       </c>
       <c r="R4">
-        <v>3116.95</v>
+        <v>3111</v>
       </c>
       <c r="S4">
-        <v>2983.85</v>
+        <v>2984.87</v>
       </c>
       <c r="T4">
-        <v>-1.71</v>
+        <v>-0.12</v>
       </c>
       <c r="U4" t="s">
         <v>46</v>
@@ -1193,34 +1225,34 @@
         <v>1</v>
       </c>
       <c r="Y4">
-        <v>44.3</v>
+        <v>50.25</v>
       </c>
       <c r="Z4">
-        <v>-56.45</v>
+        <v>-47.26</v>
       </c>
       <c r="AA4">
-        <v>-70.7</v>
+        <v>-66.01000000000001</v>
       </c>
       <c r="AB4">
-        <v>14.24</v>
+        <v>18.75</v>
       </c>
       <c r="AC4">
-        <v>84.7</v>
+        <v>92.08</v>
       </c>
       <c r="AD4">
-        <v>86.76000000000001</v>
+        <v>87.31</v>
       </c>
       <c r="AE4">
-        <v>62.29</v>
+        <v>63.65</v>
       </c>
       <c r="AF4">
-        <v>-45.44</v>
+        <v>25.28</v>
       </c>
       <c r="AG4">
-        <v>3013.07</v>
+        <v>2987.95</v>
       </c>
       <c r="AH4">
-        <v>2819.11</v>
+        <v>2836.18</v>
       </c>
       <c r="AI4">
         <v>3050.83</v>
@@ -1229,7 +1261,7 @@
         <v>48</v>
       </c>
       <c r="AK4">
-        <v>35.09</v>
+        <v>35.04</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1240,10 +1272,10 @@
         <v>45</v>
       </c>
       <c r="C5">
-        <v>886.3</v>
+        <v>884.7</v>
       </c>
       <c r="D5">
-        <v>-0.83</v>
+        <v>-0.18</v>
       </c>
       <c r="E5">
         <v>1149.7</v>
@@ -1252,46 +1284,46 @@
         <v>774.65</v>
       </c>
       <c r="G5">
-        <v>-22.91</v>
+        <v>-23.05</v>
       </c>
       <c r="H5">
-        <v>14.41</v>
+        <v>14.21</v>
       </c>
       <c r="I5">
-        <v>0.08</v>
+        <v>1.71</v>
       </c>
       <c r="J5">
-        <v>-7.28</v>
+        <v>-7.38</v>
       </c>
       <c r="K5">
-        <v>-7.91</v>
+        <v>-8.83</v>
       </c>
       <c r="L5">
-        <v>7.5</v>
+        <v>5.21</v>
       </c>
       <c r="M5">
-        <v>14.68</v>
+        <v>13.76</v>
       </c>
       <c r="N5">
-        <v>62</v>
+        <v>50</v>
       </c>
       <c r="O5">
         <v>68</v>
       </c>
       <c r="P5">
-        <v>885.35</v>
+        <v>888.3200000000001</v>
       </c>
       <c r="Q5">
-        <v>901.9299999999999</v>
+        <v>899.08</v>
       </c>
       <c r="R5">
-        <v>964.63</v>
+        <v>961.49</v>
       </c>
       <c r="S5">
-        <v>982.53</v>
+        <v>982.4400000000001</v>
       </c>
       <c r="T5">
-        <v>-9.789999999999999</v>
+        <v>-9.949999999999999</v>
       </c>
       <c r="U5" t="s">
         <v>46</v>
@@ -1306,34 +1338,34 @@
         <v>0</v>
       </c>
       <c r="Y5">
-        <v>39.23</v>
+        <v>38.8</v>
       </c>
       <c r="Z5">
-        <v>-22.01</v>
+        <v>-21.17</v>
       </c>
       <c r="AA5">
-        <v>-24.55</v>
+        <v>-23.87</v>
       </c>
       <c r="AB5">
-        <v>2.54</v>
+        <v>2.71</v>
       </c>
       <c r="AC5">
-        <v>95.22</v>
+        <v>89.73</v>
       </c>
       <c r="AD5">
-        <v>88.95999999999999</v>
+        <v>93.34999999999999</v>
       </c>
       <c r="AE5">
-        <v>22.28</v>
+        <v>21.86</v>
       </c>
       <c r="AF5">
-        <v>24.14</v>
+        <v>-32.65</v>
       </c>
       <c r="AG5">
-        <v>945.8200000000001</v>
+        <v>939.33</v>
       </c>
       <c r="AH5">
-        <v>858.04</v>
+        <v>858.83</v>
       </c>
       <c r="AI5">
         <v>933.28</v>
@@ -1342,7 +1374,7 @@
         <v>48</v>
       </c>
       <c r="AK5">
-        <v>38.7</v>
+        <v>37.8</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1353,10 +1385,10 @@
         <v>45</v>
       </c>
       <c r="C6">
-        <v>12.12</v>
+        <v>11.83</v>
       </c>
       <c r="D6">
-        <v>2.19</v>
+        <v>-2.39</v>
       </c>
       <c r="E6">
         <v>15.6</v>
@@ -1365,46 +1397,46 @@
         <v>8.529999999999999</v>
       </c>
       <c r="G6">
-        <v>-22.31</v>
+        <v>-24.17</v>
       </c>
       <c r="H6">
-        <v>42.09</v>
+        <v>38.69</v>
       </c>
       <c r="I6">
-        <v>5.12</v>
+        <v>4.14</v>
       </c>
       <c r="J6">
-        <v>-10.02</v>
+        <v>-12.76</v>
       </c>
       <c r="K6">
-        <v>-7.13</v>
+        <v>-8.08</v>
       </c>
       <c r="L6">
-        <v>25.99</v>
+        <v>18.66</v>
       </c>
       <c r="M6">
-        <v>4.88</v>
+        <v>3.22</v>
       </c>
       <c r="N6">
-        <v>87</v>
+        <v>75</v>
       </c>
       <c r="O6">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="P6">
-        <v>11.88</v>
+        <v>11.97</v>
       </c>
       <c r="Q6">
-        <v>12.43</v>
+        <v>12.38</v>
       </c>
       <c r="R6">
-        <v>13.65</v>
+        <v>13.6</v>
       </c>
       <c r="S6">
-        <v>12.31</v>
+        <v>12.32</v>
       </c>
       <c r="T6">
-        <v>-1.57</v>
+        <v>-3.95</v>
       </c>
       <c r="U6" t="s">
         <v>46</v>
@@ -1419,34 +1451,34 @@
         <v>1</v>
       </c>
       <c r="Y6">
-        <v>41.78</v>
+        <v>38.62</v>
       </c>
       <c r="Z6">
+        <v>-0.5</v>
+      </c>
+      <c r="AA6">
         <v>-0.51</v>
-      </c>
-      <c r="AA6">
-        <v>-0.52</v>
       </c>
       <c r="AB6">
         <v>0.01</v>
       </c>
       <c r="AC6">
-        <v>89.90000000000001</v>
+        <v>85.61</v>
       </c>
       <c r="AD6">
-        <v>75.2</v>
+        <v>85.44</v>
       </c>
       <c r="AE6">
-        <v>0.46</v>
+        <v>0.45</v>
       </c>
       <c r="AF6">
-        <v>-43.95</v>
+        <v>-47.18</v>
       </c>
       <c r="AG6">
-        <v>13.52</v>
+        <v>13.47</v>
       </c>
       <c r="AH6">
-        <v>11.34</v>
+        <v>11.28</v>
       </c>
       <c r="AI6">
         <v>12.7</v>
@@ -1455,7 +1487,7 @@
         <v>48</v>
       </c>
       <c r="AK6">
-        <v>48.91</v>
+        <v>47.41</v>
       </c>
     </row>
     <row r="7" spans="1:37">
@@ -1466,10 +1498,10 @@
         <v>45</v>
       </c>
       <c r="C7">
-        <v>12.54</v>
+        <v>12.03</v>
       </c>
       <c r="D7">
-        <v>-1.8</v>
+        <v>-4.07</v>
       </c>
       <c r="E7">
         <v>13.92</v>
@@ -1478,25 +1510,25 @@
         <v>4.69</v>
       </c>
       <c r="G7">
-        <v>-9.91</v>
+        <v>-13.58</v>
       </c>
       <c r="H7">
-        <v>167.38</v>
+        <v>156.5</v>
       </c>
       <c r="I7">
-        <v>10</v>
+        <v>8.18</v>
       </c>
       <c r="J7">
-        <v>13.79</v>
+        <v>10.98</v>
       </c>
       <c r="K7">
-        <v>10.29</v>
+        <v>0.84</v>
       </c>
       <c r="L7">
-        <v>142.55</v>
+        <v>131.35</v>
       </c>
       <c r="M7">
-        <v>-27.7</v>
+        <v>-28.42</v>
       </c>
       <c r="N7">
         <v>99</v>
@@ -1505,61 +1537,61 @@
         <v>97</v>
       </c>
       <c r="P7">
-        <v>12.26</v>
+        <v>12.44</v>
       </c>
       <c r="Q7">
-        <v>11.49</v>
+        <v>11.55</v>
       </c>
       <c r="R7">
         <v>11.5</v>
       </c>
       <c r="S7">
-        <v>10.84</v>
+        <v>10.85</v>
       </c>
       <c r="T7">
-        <v>15.72</v>
+        <v>10.92</v>
       </c>
       <c r="U7" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="V7" t="s">
         <v>47</v>
       </c>
       <c r="W7" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="X7">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Y7">
-        <v>58.19</v>
+        <v>52.85</v>
       </c>
       <c r="Z7">
-        <v>0.29</v>
+        <v>0.27</v>
       </c>
       <c r="AA7">
-        <v>0.14</v>
+        <v>0.16</v>
       </c>
       <c r="AB7">
-        <v>0.15</v>
+        <v>0.11</v>
       </c>
       <c r="AC7">
-        <v>75.45999999999999</v>
+        <v>61.85</v>
       </c>
       <c r="AD7">
-        <v>71.67</v>
+        <v>71.2</v>
       </c>
       <c r="AE7">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="AF7">
-        <v>-23.64</v>
+        <v>-48.93</v>
       </c>
       <c r="AG7">
-        <v>13.09</v>
+        <v>13.13</v>
       </c>
       <c r="AH7">
-        <v>9.9</v>
+        <v>9.960000000000001</v>
       </c>
       <c r="AI7">
         <v>10.86</v>
@@ -1568,7 +1600,7 @@
         <v>49</v>
       </c>
       <c r="AK7">
-        <v>28</v>
+        <v>26.17</v>
       </c>
     </row>
     <row r="8" spans="1:37">
@@ -1582,7 +1614,7 @@
         <v>3872.2</v>
       </c>
       <c r="D8">
-        <v>-1.12</v>
+        <v>0</v>
       </c>
       <c r="E8">
         <v>5724</v>
@@ -1597,40 +1629,40 @@
         <v>2.46</v>
       </c>
       <c r="I8">
-        <v>-0.35</v>
+        <v>2.19</v>
       </c>
       <c r="J8">
-        <v>-3.13</v>
+        <v>-3.86</v>
       </c>
       <c r="K8">
-        <v>-10.15</v>
+        <v>-10.32</v>
       </c>
       <c r="L8">
-        <v>-31.2</v>
+        <v>-31.71</v>
       </c>
       <c r="M8">
-        <v>16.24</v>
+        <v>15.88</v>
       </c>
       <c r="N8">
         <v>25</v>
       </c>
       <c r="O8">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="P8">
-        <v>3828.24</v>
+        <v>3844.82</v>
       </c>
       <c r="Q8">
-        <v>3928.82</v>
+        <v>3924.6</v>
       </c>
       <c r="R8">
-        <v>4101.39</v>
+        <v>4091.12</v>
       </c>
       <c r="S8">
-        <v>4418.04</v>
+        <v>4412.72</v>
       </c>
       <c r="T8">
-        <v>-12.35</v>
+        <v>-12.25</v>
       </c>
       <c r="U8" t="s">
         <v>46</v>
@@ -1648,31 +1680,31 @@
         <v>42.03</v>
       </c>
       <c r="Z8">
-        <v>-69.75</v>
+        <v>-65.97</v>
       </c>
       <c r="AA8">
-        <v>-71.47</v>
+        <v>-70.37</v>
       </c>
       <c r="AB8">
-        <v>1.72</v>
+        <v>4.4</v>
       </c>
       <c r="AC8">
+        <v>86.20999999999999</v>
+      </c>
+      <c r="AD8">
         <v>59.77</v>
       </c>
-      <c r="AD8">
-        <v>31.04</v>
-      </c>
       <c r="AE8">
-        <v>109.84</v>
+        <v>107.7</v>
       </c>
       <c r="AF8">
-        <v>-63.44</v>
+        <v>-62.73</v>
       </c>
       <c r="AG8">
-        <v>4090.61</v>
+        <v>4087.74</v>
       </c>
       <c r="AH8">
-        <v>3767.03</v>
+        <v>3761.47</v>
       </c>
       <c r="AI8">
         <v>4043.79</v>
@@ -1681,7 +1713,7 @@
         <v>48</v>
       </c>
       <c r="AK8">
-        <v>28.28</v>
+        <v>26.23</v>
       </c>
     </row>
     <row r="9" spans="1:37">
@@ -1692,10 +1724,10 @@
         <v>45</v>
       </c>
       <c r="C9">
-        <v>11175</v>
+        <v>11045</v>
       </c>
       <c r="D9">
-        <v>0.64</v>
+        <v>-1.16</v>
       </c>
       <c r="E9">
         <v>13052</v>
@@ -1704,46 +1736,46 @@
         <v>10362</v>
       </c>
       <c r="G9">
-        <v>-14.38</v>
+        <v>-15.38</v>
       </c>
       <c r="H9">
-        <v>7.85</v>
+        <v>6.59</v>
       </c>
       <c r="I9">
-        <v>1.98</v>
+        <v>-0.05</v>
       </c>
       <c r="J9">
-        <v>1.36</v>
+        <v>1.99</v>
       </c>
       <c r="K9">
-        <v>-6.86</v>
+        <v>-6.77</v>
       </c>
       <c r="L9">
-        <v>-6.23</v>
+        <v>-8.07</v>
       </c>
       <c r="M9">
-        <v>8.4</v>
+        <v>7.77</v>
       </c>
       <c r="N9">
         <v>38</v>
       </c>
       <c r="O9">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="P9">
-        <v>11131.8</v>
+        <v>11130.8</v>
       </c>
       <c r="Q9">
-        <v>10848.75</v>
+        <v>10853.2</v>
       </c>
       <c r="R9">
-        <v>11072.4</v>
+        <v>11063.32</v>
       </c>
       <c r="S9">
-        <v>11623.95</v>
+        <v>11619.49</v>
       </c>
       <c r="T9">
-        <v>-3.86</v>
+        <v>-4.94</v>
       </c>
       <c r="U9" t="s">
         <v>46</v>
@@ -1758,34 +1790,34 @@
         <v>0</v>
       </c>
       <c r="Y9">
-        <v>56.55</v>
+        <v>52.16</v>
       </c>
       <c r="Z9">
-        <v>25.64</v>
+        <v>27.73</v>
       </c>
       <c r="AA9">
-        <v>-42.81</v>
+        <v>-28.7</v>
       </c>
       <c r="AB9">
-        <v>68.45</v>
+        <v>56.43</v>
       </c>
       <c r="AC9">
-        <v>94.31</v>
+        <v>86.89</v>
       </c>
       <c r="AD9">
-        <v>96.08</v>
+        <v>92.15000000000001</v>
       </c>
       <c r="AE9">
-        <v>247.32</v>
+        <v>241.87</v>
       </c>
       <c r="AF9">
-        <v>-54.62</v>
+        <v>-32.89</v>
       </c>
       <c r="AG9">
-        <v>11277.73</v>
+        <v>11288.66</v>
       </c>
       <c r="AH9">
-        <v>10419.77</v>
+        <v>10417.74</v>
       </c>
       <c r="AI9">
         <v>10372.89</v>
@@ -1794,7 +1826,7 @@
         <v>49</v>
       </c>
       <c r="AK9">
-        <v>38.15</v>
+        <v>37.67</v>
       </c>
     </row>
   </sheetData>
@@ -1898,27 +1930,27 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="U2:U9">
-    <cfRule type="containsText" dxfId="1" priority="14" operator="containsText" text="Yes">
-      <formula>NOT(ISERROR(SEARCH("Yes",U2)))</formula>
+    <cfRule type="cellIs" dxfId="1" priority="16" operator="equal">
+      <formula>"Yes"</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="0" priority="15" operator="containsText" text="No">
-      <formula>NOT(ISERROR(SEARCH("No",U2)))</formula>
+    <cfRule type="cellIs" dxfId="0" priority="17" operator="equal">
+      <formula>"No"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V2:V9">
-    <cfRule type="containsText" dxfId="1" priority="16" operator="containsText" text="Yes">
-      <formula>NOT(ISERROR(SEARCH("Yes",V2)))</formula>
+    <cfRule type="cellIs" dxfId="1" priority="18" operator="equal">
+      <formula>"Yes"</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="0" priority="17" operator="containsText" text="No">
-      <formula>NOT(ISERROR(SEARCH("No",V2)))</formula>
+    <cfRule type="cellIs" dxfId="0" priority="19" operator="equal">
+      <formula>"No"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="W2:W9">
-    <cfRule type="containsText" dxfId="1" priority="18" operator="containsText" text="Yes">
-      <formula>NOT(ISERROR(SEARCH("Yes",W2)))</formula>
+    <cfRule type="cellIs" dxfId="1" priority="14" operator="equal">
+      <formula>"Yes"</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="0" priority="19" operator="containsText" text="No">
-      <formula>NOT(ISERROR(SEARCH("No",W2)))</formula>
+    <cfRule type="cellIs" dxfId="0" priority="15" operator="equal">
+      <formula>"No"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Y2:Y9">
@@ -1935,7 +1967,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F72"/>
+  <dimension ref="A1:F73"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -1955,1161 +1987,1219 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="3" t="s">
         <v>51</v>
       </c>
+      <c r="C2" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
+      <c r="A4" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>47</v>
+      </c>
     </row>
     <row r="5" spans="1:6">
-      <c r="A5" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="B5" s="2"/>
-      <c r="C5" s="2"/>
-      <c r="D5" s="2"/>
-      <c r="E5" s="2"/>
-    </row>
-    <row r="6" spans="1:6">
-      <c r="A6" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="D6" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="E6" s="4" t="s">
-        <v>56</v>
+      <c r="A5" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="E5" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="F5" s="4" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="7" spans="1:6">
-      <c r="A7" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C7" s="5">
-        <v>-8.720000000000001</v>
-      </c>
-      <c r="D7" s="5">
-        <v>-6.36</v>
-      </c>
-      <c r="E7" s="6">
-        <v>2.36</v>
-      </c>
+      <c r="A7" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="B7" s="2"/>
+      <c r="C7" s="2"/>
+      <c r="D7" s="2"/>
+      <c r="E7" s="2"/>
     </row>
     <row r="8" spans="1:6">
       <c r="A8" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C9" s="6">
+        <v>-6.36</v>
+      </c>
+      <c r="D9" s="6">
+        <v>-2.26</v>
+      </c>
+      <c r="E9" s="7">
+        <v>4.1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B8" s="3" t="s">
+      <c r="B10" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C8" s="5">
-        <v>-18.93</v>
-      </c>
-      <c r="D8" s="5">
+      <c r="C10" s="6">
         <v>-15.65</v>
       </c>
-      <c r="E8" s="6">
-        <v>3.28</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9" s="3" t="s">
+      <c r="D10" s="6">
+        <v>-16.13</v>
+      </c>
+      <c r="E10" s="8">
+        <v>-0.48</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B9" s="3" t="s">
+      <c r="B11" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C9" s="5">
-        <v>-9.119999999999999</v>
-      </c>
-      <c r="D9" s="5">
+      <c r="C11" s="6">
         <v>-6.9</v>
       </c>
-      <c r="E9" s="6">
-        <v>2.22</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10" s="3" t="s">
+      <c r="D11" s="6">
+        <v>-3.83</v>
+      </c>
+      <c r="E11" s="7">
+        <v>3.07</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B10" s="3" t="s">
+      <c r="B12" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C10" s="5">
-        <v>-8.52</v>
-      </c>
-      <c r="D10" s="5">
+      <c r="C12" s="6">
         <v>-7.28</v>
       </c>
-      <c r="E10" s="6">
-        <v>1.24</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11" s="3" t="s">
+      <c r="D12" s="6">
+        <v>-7.38</v>
+      </c>
+      <c r="E12" s="8">
+        <v>-0.1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="A13" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B11" s="3" t="s">
+      <c r="B13" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C11" s="5">
-        <v>-16.83</v>
-      </c>
-      <c r="D11" s="5">
+      <c r="C13" s="6">
         <v>-10.02</v>
       </c>
-      <c r="E11" s="6">
-        <v>6.81</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12" s="3" t="s">
+      <c r="D13" s="6">
+        <v>-12.76</v>
+      </c>
+      <c r="E13" s="8">
+        <v>-2.74</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="B12" s="3" t="s">
+      <c r="B14" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C12" s="5">
-        <v>10.37</v>
-      </c>
-      <c r="D12" s="5">
+      <c r="C14" s="6">
         <v>13.79</v>
       </c>
-      <c r="E12" s="6">
-        <v>3.42</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13" s="3" t="s">
+      <c r="D14" s="6">
+        <v>10.98</v>
+      </c>
+      <c r="E14" s="8">
+        <v>-2.81</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="A15" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="B13" s="3" t="s">
+      <c r="B15" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C13" s="5">
-        <v>-2.47</v>
-      </c>
-      <c r="D13" s="5">
+      <c r="C15" s="6">
         <v>-3.13</v>
       </c>
-      <c r="E13" s="7">
-        <v>-0.66</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14" s="3" t="s">
+      <c r="D15" s="6">
+        <v>-3.86</v>
+      </c>
+      <c r="E15" s="8">
+        <v>-0.73</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="A16" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="B14" s="3" t="s">
+      <c r="B16" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C14" s="5">
-        <v>-0.46</v>
-      </c>
-      <c r="D14" s="5">
+      <c r="C16" s="6">
         <v>1.36</v>
       </c>
-      <c r="E14" s="6">
+      <c r="D16" s="6">
+        <v>1.99</v>
+      </c>
+      <c r="E16" s="7">
+        <v>0.63</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B17" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C17" s="6">
+        <v>0.32</v>
+      </c>
+      <c r="D17" s="6">
+        <v>6.39</v>
+      </c>
+      <c r="E17" s="7">
+        <v>6.07</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B18" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C18" s="6">
+        <v>-2.9</v>
+      </c>
+      <c r="D18" s="6">
+        <v>-2.49</v>
+      </c>
+      <c r="E18" s="7">
+        <v>0.41</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B19" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C19" s="6">
+        <v>1.33</v>
+      </c>
+      <c r="D19" s="6">
+        <v>3.02</v>
+      </c>
+      <c r="E19" s="7">
+        <v>1.69</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B20" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C20" s="6">
+        <v>0.08</v>
+      </c>
+      <c r="D20" s="6">
+        <v>1.71</v>
+      </c>
+      <c r="E20" s="7">
+        <v>1.63</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B21" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C21" s="6">
+        <v>5.12</v>
+      </c>
+      <c r="D21" s="6">
+        <v>4.14</v>
+      </c>
+      <c r="E21" s="8">
+        <v>-0.98</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B22" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C22" s="6">
+        <v>10</v>
+      </c>
+      <c r="D22" s="6">
+        <v>8.18</v>
+      </c>
+      <c r="E22" s="8">
+        <v>-1.82</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B23" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C23" s="6">
+        <v>-0.35</v>
+      </c>
+      <c r="D23" s="6">
+        <v>2.19</v>
+      </c>
+      <c r="E23" s="7">
+        <v>2.54</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="B24" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C24" s="6">
+        <v>1.98</v>
+      </c>
+      <c r="D24" s="6">
+        <v>-0.05</v>
+      </c>
+      <c r="E24" s="8">
+        <v>-2.03</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B25" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C25" s="6">
+        <v>17.05</v>
+      </c>
+      <c r="D25" s="6">
+        <v>18.89</v>
+      </c>
+      <c r="E25" s="7">
+        <v>1.84</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B26" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C26" s="6">
+        <v>-51.01</v>
+      </c>
+      <c r="D26" s="6">
+        <v>-52.57</v>
+      </c>
+      <c r="E26" s="8">
+        <v>-1.56</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B27" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C27" s="6">
+        <v>3.22</v>
+      </c>
+      <c r="D27" s="6">
+        <v>1.97</v>
+      </c>
+      <c r="E27" s="8">
+        <v>-1.25</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B28" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C28" s="6">
+        <v>7.5</v>
+      </c>
+      <c r="D28" s="6">
+        <v>5.21</v>
+      </c>
+      <c r="E28" s="8">
+        <v>-2.29</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B29" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C29" s="6">
+        <v>25.99</v>
+      </c>
+      <c r="D29" s="6">
+        <v>18.66</v>
+      </c>
+      <c r="E29" s="8">
+        <v>-7.33</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B30" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C30" s="6">
+        <v>142.55</v>
+      </c>
+      <c r="D30" s="6">
+        <v>131.35</v>
+      </c>
+      <c r="E30" s="8">
+        <v>-11.2</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5">
+      <c r="A31" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B31" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C31" s="6">
+        <v>-31.2</v>
+      </c>
+      <c r="D31" s="6">
+        <v>-31.71</v>
+      </c>
+      <c r="E31" s="8">
+        <v>-0.51</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5">
+      <c r="A32" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="B32" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C32" s="6">
+        <v>-6.23</v>
+      </c>
+      <c r="D32" s="6">
+        <v>-8.07</v>
+      </c>
+      <c r="E32" s="8">
+        <v>-1.84</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5">
+      <c r="A33" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B33" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C33" s="6">
+        <v>-9.869999999999999</v>
+      </c>
+      <c r="D33" s="6">
+        <v>-6.24</v>
+      </c>
+      <c r="E33" s="7">
+        <v>3.63</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5">
+      <c r="A34" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B34" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C34" s="6">
+        <v>-30.86</v>
+      </c>
+      <c r="D34" s="6">
+        <v>-34.2</v>
+      </c>
+      <c r="E34" s="8">
+        <v>-3.34</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5">
+      <c r="A35" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B35" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C35" s="6">
+        <v>-5.79</v>
+      </c>
+      <c r="D35" s="6">
+        <v>-3.97</v>
+      </c>
+      <c r="E35" s="7">
         <v>1.82</v>
       </c>
     </row>
-    <row r="15" spans="1:6">
-      <c r="A15" s="3" t="s">
+    <row r="36" spans="1:5">
+      <c r="A36" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B36" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C36" s="6">
+        <v>-7.91</v>
+      </c>
+      <c r="D36" s="6">
+        <v>-8.83</v>
+      </c>
+      <c r="E36" s="8">
+        <v>-0.92</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5">
+      <c r="A37" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B37" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C37" s="6">
+        <v>-7.13</v>
+      </c>
+      <c r="D37" s="6">
+        <v>-8.08</v>
+      </c>
+      <c r="E37" s="8">
+        <v>-0.95</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5">
+      <c r="A38" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B38" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C38" s="6">
+        <v>10.29</v>
+      </c>
+      <c r="D38" s="6">
+        <v>0.84</v>
+      </c>
+      <c r="E38" s="8">
+        <v>-9.449999999999999</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5">
+      <c r="A39" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B39" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C39" s="6">
+        <v>-10.15</v>
+      </c>
+      <c r="D39" s="6">
+        <v>-10.32</v>
+      </c>
+      <c r="E39" s="8">
+        <v>-0.17</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5">
+      <c r="A40" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="B40" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C40" s="6">
+        <v>-6.86</v>
+      </c>
+      <c r="D40" s="6">
+        <v>-6.77</v>
+      </c>
+      <c r="E40" s="7">
+        <v>0.09</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5">
+      <c r="A41" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B15" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C15" s="5">
-        <v>-3</v>
-      </c>
-      <c r="D15" s="5">
-        <v>0.32</v>
-      </c>
-      <c r="E15" s="6">
-        <v>3.32</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16" s="3" t="s">
+      <c r="B41" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C41" s="6">
+        <v>-15.62</v>
+      </c>
+      <c r="D41" s="6">
+        <v>-13.01</v>
+      </c>
+      <c r="E41" s="7">
+        <v>2.61</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5">
+      <c r="A42" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B16" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C16" s="5">
-        <v>-7.37</v>
-      </c>
-      <c r="D16" s="5">
-        <v>-2.9</v>
-      </c>
-      <c r="E16" s="6">
-        <v>4.47</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5">
-      <c r="A17" s="3" t="s">
+      <c r="B42" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C42" s="6">
+        <v>-52.99</v>
+      </c>
+      <c r="D42" s="6">
+        <v>-54.58</v>
+      </c>
+      <c r="E42" s="8">
+        <v>-1.59</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5">
+      <c r="A43" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B17" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C17" s="5">
-        <v>0.38</v>
-      </c>
-      <c r="D17" s="5">
-        <v>1.33</v>
-      </c>
-      <c r="E17" s="6">
-        <v>0.95</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5">
-      <c r="A18" s="3" t="s">
+      <c r="B43" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C43" s="6">
+        <v>-13.24</v>
+      </c>
+      <c r="D43" s="6">
+        <v>-11.81</v>
+      </c>
+      <c r="E43" s="7">
+        <v>1.43</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5">
+      <c r="A44" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B18" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C18" s="5">
-        <v>0.1</v>
-      </c>
-      <c r="D18" s="5">
-        <v>0.08</v>
-      </c>
-      <c r="E18" s="7">
-        <v>-0.02</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5">
-      <c r="A19" s="3" t="s">
+      <c r="B44" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C44" s="6">
+        <v>-22.91</v>
+      </c>
+      <c r="D44" s="6">
+        <v>-23.05</v>
+      </c>
+      <c r="E44" s="8">
+        <v>-0.14</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5">
+      <c r="A45" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B19" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C19" s="5">
-        <v>1.89</v>
-      </c>
-      <c r="D19" s="5">
-        <v>5.12</v>
-      </c>
-      <c r="E19" s="6">
-        <v>3.23</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5">
-      <c r="A20" s="3" t="s">
+      <c r="B45" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C45" s="6">
+        <v>-22.31</v>
+      </c>
+      <c r="D45" s="6">
+        <v>-24.17</v>
+      </c>
+      <c r="E45" s="8">
+        <v>-1.86</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5">
+      <c r="A46" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="B20" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C20" s="5">
-        <v>9.43</v>
-      </c>
-      <c r="D20" s="5">
-        <v>10</v>
-      </c>
-      <c r="E20" s="6">
-        <v>0.57</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5">
-      <c r="A21" s="3" t="s">
+      <c r="B46" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C46" s="6">
+        <v>-9.91</v>
+      </c>
+      <c r="D46" s="6">
+        <v>-13.58</v>
+      </c>
+      <c r="E46" s="8">
+        <v>-3.67</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5">
+      <c r="A47" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="B47" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C47" s="6">
+        <v>-14.38</v>
+      </c>
+      <c r="D47" s="6">
+        <v>-15.38</v>
+      </c>
+      <c r="E47" s="8">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5">
+      <c r="A48" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B48" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C48" s="6">
+        <v>358.35</v>
+      </c>
+      <c r="D48" s="6">
+        <v>369.45</v>
+      </c>
+      <c r="E48" s="7">
+        <v>11.1</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5">
+      <c r="A49" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B49" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C49" s="6">
+        <v>40.14</v>
+      </c>
+      <c r="D49" s="6">
+        <v>38.78</v>
+      </c>
+      <c r="E49" s="8">
+        <v>-1.36</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5">
+      <c r="A50" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B50" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C50" s="6">
+        <v>2932.8</v>
+      </c>
+      <c r="D50" s="6">
+        <v>2981.4</v>
+      </c>
+      <c r="E50" s="7">
+        <v>48.6</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5">
+      <c r="A51" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B51" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C51" s="6">
+        <v>886.3</v>
+      </c>
+      <c r="D51" s="6">
+        <v>884.7</v>
+      </c>
+      <c r="E51" s="8">
+        <v>-1.6</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5">
+      <c r="A52" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B52" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C52" s="6">
+        <v>12.12</v>
+      </c>
+      <c r="D52" s="6">
+        <v>11.83</v>
+      </c>
+      <c r="E52" s="8">
+        <v>-0.29</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5">
+      <c r="A53" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B53" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C53" s="6">
+        <v>12.54</v>
+      </c>
+      <c r="D53" s="6">
+        <v>12.03</v>
+      </c>
+      <c r="E53" s="8">
+        <v>-0.51</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5">
+      <c r="A54" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="B54" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C54" s="6">
+        <v>11175</v>
+      </c>
+      <c r="D54" s="6">
+        <v>11045</v>
+      </c>
+      <c r="E54" s="8">
+        <v>-130</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5">
+      <c r="A55" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B55" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C55" s="6">
+        <v>75</v>
+      </c>
+      <c r="D55" s="6">
+        <v>87</v>
+      </c>
+      <c r="E55" s="7">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5">
+      <c r="A56" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B56" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C56" s="6">
+        <v>50</v>
+      </c>
+      <c r="D56" s="6">
+        <v>62</v>
+      </c>
+      <c r="E56" s="7">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5">
+      <c r="A57" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B57" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C57" s="6">
+        <v>62</v>
+      </c>
+      <c r="D57" s="6">
+        <v>50</v>
+      </c>
+      <c r="E57" s="8">
+        <v>-12</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5">
+      <c r="A58" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B58" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C58" s="6">
+        <v>87</v>
+      </c>
+      <c r="D58" s="6">
+        <v>75</v>
+      </c>
+      <c r="E58" s="8">
+        <v>-12</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5">
+      <c r="A59" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B59" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C59" s="6">
+        <v>38.75</v>
+      </c>
+      <c r="D59" s="6">
+        <v>47.6</v>
+      </c>
+      <c r="E59" s="7">
+        <v>8.85</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5">
+      <c r="A60" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B60" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C60" s="6">
+        <v>27.68</v>
+      </c>
+      <c r="D60" s="6">
+        <v>24.16</v>
+      </c>
+      <c r="E60" s="8">
+        <v>-3.52</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5">
+      <c r="A61" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B61" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C61" s="6">
+        <v>44.3</v>
+      </c>
+      <c r="D61" s="6">
+        <v>50.25</v>
+      </c>
+      <c r="E61" s="7">
+        <v>5.95</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5">
+      <c r="A62" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B62" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C62" s="6">
+        <v>39.23</v>
+      </c>
+      <c r="D62" s="6">
+        <v>38.8</v>
+      </c>
+      <c r="E62" s="8">
+        <v>-0.43</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5">
+      <c r="A63" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B63" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C63" s="6">
+        <v>41.78</v>
+      </c>
+      <c r="D63" s="6">
+        <v>38.62</v>
+      </c>
+      <c r="E63" s="8">
+        <v>-3.16</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5">
+      <c r="A64" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B64" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C64" s="6">
+        <v>58.19</v>
+      </c>
+      <c r="D64" s="6">
+        <v>52.85</v>
+      </c>
+      <c r="E64" s="8">
+        <v>-5.34</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5">
+      <c r="A65" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="B65" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C65" s="6">
+        <v>56.55</v>
+      </c>
+      <c r="D65" s="6">
+        <v>52.16</v>
+      </c>
+      <c r="E65" s="8">
+        <v>-4.39</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5">
+      <c r="A66" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B66" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C66" s="6">
+        <v>-5.36</v>
+      </c>
+      <c r="D66" s="6">
+        <v>181.18</v>
+      </c>
+      <c r="E66" s="7">
+        <v>186.54</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5">
+      <c r="A67" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B67" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C67" s="6">
+        <v>-40.26</v>
+      </c>
+      <c r="D67" s="6">
+        <v>-8.619999999999999</v>
+      </c>
+      <c r="E67" s="7">
+        <v>31.64</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5">
+      <c r="A68" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B68" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C68" s="6">
+        <v>-45.44</v>
+      </c>
+      <c r="D68" s="6">
+        <v>25.28</v>
+      </c>
+      <c r="E68" s="7">
+        <v>70.72</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5">
+      <c r="A69" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B69" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C69" s="6">
+        <v>24.14</v>
+      </c>
+      <c r="D69" s="6">
+        <v>-32.65</v>
+      </c>
+      <c r="E69" s="8">
+        <v>-56.79</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5">
+      <c r="A70" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B70" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C70" s="6">
+        <v>-43.95</v>
+      </c>
+      <c r="D70" s="6">
+        <v>-47.18</v>
+      </c>
+      <c r="E70" s="8">
+        <v>-3.23</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5">
+      <c r="A71" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B71" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C71" s="6">
+        <v>-23.64</v>
+      </c>
+      <c r="D71" s="6">
+        <v>-48.93</v>
+      </c>
+      <c r="E71" s="8">
+        <v>-25.29</v>
+      </c>
+    </row>
+    <row r="72" spans="1:5">
+      <c r="A72" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="B21" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C21" s="5">
-        <v>0.23</v>
-      </c>
-      <c r="D21" s="5">
-        <v>-0.35</v>
-      </c>
-      <c r="E21" s="7">
-        <v>-0.58</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5">
-      <c r="A22" s="3" t="s">
+      <c r="B72" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C72" s="6">
+        <v>-63.44</v>
+      </c>
+      <c r="D72" s="6">
+        <v>-62.73</v>
+      </c>
+      <c r="E72" s="7">
+        <v>0.71</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5">
+      <c r="A73" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="B22" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C22" s="5">
-        <v>2.35</v>
-      </c>
-      <c r="D22" s="5">
-        <v>1.98</v>
-      </c>
-      <c r="E22" s="7">
-        <v>-0.37</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5">
-      <c r="A23" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B23" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C23" s="5">
-        <v>15.58</v>
-      </c>
-      <c r="D23" s="5">
-        <v>17.05</v>
-      </c>
-      <c r="E23" s="6">
-        <v>1.47</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5">
-      <c r="A24" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B24" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C24" s="5">
-        <v>-52.3</v>
-      </c>
-      <c r="D24" s="5">
-        <v>-51.01</v>
-      </c>
-      <c r="E24" s="6">
-        <v>1.29</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5">
-      <c r="A25" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B25" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C25" s="5">
-        <v>1.24</v>
-      </c>
-      <c r="D25" s="5">
-        <v>3.22</v>
-      </c>
-      <c r="E25" s="6">
-        <v>1.98</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5">
-      <c r="A26" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="B26" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C26" s="5">
-        <v>12.79</v>
-      </c>
-      <c r="D26" s="5">
-        <v>7.5</v>
-      </c>
-      <c r="E26" s="7">
-        <v>-5.29</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5">
-      <c r="A27" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="B27" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C27" s="5">
-        <v>24.58</v>
-      </c>
-      <c r="D27" s="5">
-        <v>25.99</v>
-      </c>
-      <c r="E27" s="6">
-        <v>1.41</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5">
-      <c r="A28" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="B28" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C28" s="5">
-        <v>145.58</v>
-      </c>
-      <c r="D28" s="5">
-        <v>142.55</v>
-      </c>
-      <c r="E28" s="7">
-        <v>-3.03</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5">
-      <c r="A29" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="B29" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C29" s="5">
-        <v>-32.24</v>
-      </c>
-      <c r="D29" s="5">
-        <v>-31.2</v>
-      </c>
-      <c r="E29" s="6">
-        <v>1.04</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5">
-      <c r="A30" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="B30" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C30" s="5">
-        <v>-8.57</v>
-      </c>
-      <c r="D30" s="5">
-        <v>-6.23</v>
-      </c>
-      <c r="E30" s="6">
-        <v>2.34</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5">
-      <c r="A31" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B31" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C31" s="5">
-        <v>-9.029999999999999</v>
-      </c>
-      <c r="D31" s="5">
-        <v>-9.869999999999999</v>
-      </c>
-      <c r="E31" s="7">
-        <v>-0.84</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5">
-      <c r="A32" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B32" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C32" s="5">
-        <v>-29.74</v>
-      </c>
-      <c r="D32" s="5">
-        <v>-30.86</v>
-      </c>
-      <c r="E32" s="7">
-        <v>-1.12</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5">
-      <c r="A33" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B33" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C33" s="5">
-        <v>-6.94</v>
-      </c>
-      <c r="D33" s="5">
-        <v>-5.79</v>
-      </c>
-      <c r="E33" s="6">
-        <v>1.15</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5">
-      <c r="A34" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="B34" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C34" s="5">
-        <v>-4.55</v>
-      </c>
-      <c r="D34" s="5">
-        <v>-7.91</v>
-      </c>
-      <c r="E34" s="7">
-        <v>-3.36</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5">
-      <c r="A35" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="B35" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C35" s="5">
-        <v>-8.42</v>
-      </c>
-      <c r="D35" s="5">
-        <v>-7.13</v>
-      </c>
-      <c r="E35" s="6">
-        <v>1.29</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5">
-      <c r="A36" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="B36" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C36" s="5">
-        <v>15.88</v>
-      </c>
-      <c r="D36" s="5">
-        <v>10.29</v>
-      </c>
-      <c r="E36" s="7">
-        <v>-5.59</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5">
-      <c r="A37" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="B37" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C37" s="5">
-        <v>-7.64</v>
-      </c>
-      <c r="D37" s="5">
-        <v>-10.15</v>
-      </c>
-      <c r="E37" s="7">
-        <v>-2.51</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5">
-      <c r="A38" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="B38" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C38" s="5">
-        <v>-7.13</v>
-      </c>
-      <c r="D38" s="5">
-        <v>-6.86</v>
-      </c>
-      <c r="E38" s="6">
-        <v>0.27</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5">
-      <c r="A39" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B39" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C39" s="5">
-        <v>-16.18</v>
-      </c>
-      <c r="D39" s="5">
-        <v>-15.62</v>
-      </c>
-      <c r="E39" s="6">
-        <v>0.5600000000000001</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5">
-      <c r="A40" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B40" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C40" s="5">
-        <v>-53.34</v>
-      </c>
-      <c r="D40" s="5">
-        <v>-52.99</v>
-      </c>
-      <c r="E40" s="6">
-        <v>0.35</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5">
-      <c r="A41" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B41" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C41" s="5">
-        <v>-14.21</v>
-      </c>
-      <c r="D41" s="5">
-        <v>-13.24</v>
-      </c>
-      <c r="E41" s="6">
-        <v>0.97</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5">
-      <c r="A42" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="B42" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C42" s="5">
-        <v>-22.26</v>
-      </c>
-      <c r="D42" s="5">
-        <v>-22.91</v>
-      </c>
-      <c r="E42" s="7">
-        <v>-0.65</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5">
-      <c r="A43" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="B43" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C43" s="5">
-        <v>-23.97</v>
-      </c>
-      <c r="D43" s="5">
-        <v>-22.31</v>
-      </c>
-      <c r="E43" s="6">
-        <v>1.66</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5">
-      <c r="A44" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="B44" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C44" s="5">
-        <v>-8.26</v>
-      </c>
-      <c r="D44" s="5">
-        <v>-9.91</v>
-      </c>
-      <c r="E44" s="7">
-        <v>-1.65</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5">
-      <c r="A45" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="B45" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C45" s="5">
-        <v>-31.59</v>
-      </c>
-      <c r="D45" s="5">
-        <v>-32.35</v>
-      </c>
-      <c r="E45" s="7">
-        <v>-0.76</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5">
-      <c r="A46" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="B46" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C46" s="5">
-        <v>-14.92</v>
-      </c>
-      <c r="D46" s="5">
-        <v>-14.38</v>
-      </c>
-      <c r="E46" s="6">
-        <v>0.54</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5">
-      <c r="A47" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B47" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C47" s="5">
-        <v>356</v>
-      </c>
-      <c r="D47" s="5">
-        <v>358.35</v>
-      </c>
-      <c r="E47" s="6">
-        <v>2.35</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5">
-      <c r="A48" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B48" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C48" s="5">
-        <v>39.84</v>
-      </c>
-      <c r="D48" s="5">
-        <v>40.14</v>
-      </c>
-      <c r="E48" s="6">
-        <v>0.3</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5">
-      <c r="A49" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B49" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C49" s="5">
-        <v>2900</v>
-      </c>
-      <c r="D49" s="5">
-        <v>2932.8</v>
-      </c>
-      <c r="E49" s="6">
-        <v>32.8</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5">
-      <c r="A50" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="B50" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C50" s="5">
-        <v>893.75</v>
-      </c>
-      <c r="D50" s="5">
-        <v>886.3</v>
-      </c>
-      <c r="E50" s="7">
-        <v>-7.45</v>
-      </c>
-    </row>
-    <row r="51" spans="1:5">
-      <c r="A51" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="B51" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C51" s="5">
-        <v>11.86</v>
-      </c>
-      <c r="D51" s="5">
-        <v>12.12</v>
-      </c>
-      <c r="E51" s="6">
-        <v>0.26</v>
-      </c>
-    </row>
-    <row r="52" spans="1:5">
-      <c r="A52" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="B52" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C52" s="5">
-        <v>12.77</v>
-      </c>
-      <c r="D52" s="5">
-        <v>12.54</v>
-      </c>
-      <c r="E52" s="7">
-        <v>-0.23</v>
-      </c>
-    </row>
-    <row r="53" spans="1:5">
-      <c r="A53" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="B53" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C53" s="5">
-        <v>3916</v>
-      </c>
-      <c r="D53" s="5">
-        <v>3872.2</v>
-      </c>
-      <c r="E53" s="7">
-        <v>-43.8</v>
-      </c>
-    </row>
-    <row r="54" spans="1:5">
-      <c r="A54" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="B54" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C54" s="5">
-        <v>11104</v>
-      </c>
-      <c r="D54" s="5">
-        <v>11175</v>
-      </c>
-      <c r="E54" s="6">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="55" spans="1:5">
-      <c r="A55" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B55" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="C55" s="5">
-        <v>62</v>
-      </c>
-      <c r="D55" s="5">
-        <v>75</v>
-      </c>
-      <c r="E55" s="6">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="56" spans="1:5">
-      <c r="A56" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="B56" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="C56" s="5">
-        <v>75</v>
-      </c>
-      <c r="D56" s="5">
-        <v>62</v>
-      </c>
-      <c r="E56" s="7">
-        <v>-13</v>
-      </c>
-    </row>
-    <row r="57" spans="1:5">
-      <c r="A57" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B57" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C57" s="5">
-        <v>36.65</v>
-      </c>
-      <c r="D57" s="5">
-        <v>38.75</v>
-      </c>
-      <c r="E57" s="6">
-        <v>2.1</v>
-      </c>
-    </row>
-    <row r="58" spans="1:5">
-      <c r="A58" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B58" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C58" s="5">
-        <v>25.45</v>
-      </c>
-      <c r="D58" s="5">
-        <v>27.68</v>
-      </c>
-      <c r="E58" s="6">
-        <v>2.23</v>
-      </c>
-    </row>
-    <row r="59" spans="1:5">
-      <c r="A59" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B59" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C59" s="5">
-        <v>39.78</v>
-      </c>
-      <c r="D59" s="5">
-        <v>44.3</v>
-      </c>
-      <c r="E59" s="6">
-        <v>4.52</v>
-      </c>
-    </row>
-    <row r="60" spans="1:5">
-      <c r="A60" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="B60" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C60" s="5">
-        <v>41.16</v>
-      </c>
-      <c r="D60" s="5">
-        <v>39.23</v>
-      </c>
-      <c r="E60" s="7">
-        <v>-1.93</v>
-      </c>
-    </row>
-    <row r="61" spans="1:5">
-      <c r="A61" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="B61" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C61" s="5">
-        <v>37.53</v>
-      </c>
-      <c r="D61" s="5">
-        <v>41.78</v>
-      </c>
-      <c r="E61" s="6">
-        <v>4.25</v>
-      </c>
-    </row>
-    <row r="62" spans="1:5">
-      <c r="A62" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="B62" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C62" s="5">
-        <v>60.77</v>
-      </c>
-      <c r="D62" s="5">
-        <v>58.19</v>
-      </c>
-      <c r="E62" s="7">
-        <v>-2.58</v>
-      </c>
-    </row>
-    <row r="63" spans="1:5">
-      <c r="A63" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="B63" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C63" s="5">
-        <v>45.22</v>
-      </c>
-      <c r="D63" s="5">
-        <v>42.03</v>
-      </c>
-      <c r="E63" s="7">
-        <v>-3.19</v>
-      </c>
-    </row>
-    <row r="64" spans="1:5">
-      <c r="A64" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="B64" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C64" s="5">
-        <v>54.61</v>
-      </c>
-      <c r="D64" s="5">
-        <v>56.55</v>
-      </c>
-      <c r="E64" s="6">
-        <v>1.94</v>
-      </c>
-    </row>
-    <row r="65" spans="1:5">
-      <c r="A65" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B65" s="3" t="s">
+      <c r="B73" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="C65" s="5">
-        <v>-65.40000000000001</v>
-      </c>
-      <c r="D65" s="5">
-        <v>-5.36</v>
-      </c>
-      <c r="E65" s="6">
-        <v>60.04</v>
-      </c>
-    </row>
-    <row r="66" spans="1:5">
-      <c r="A66" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B66" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C66" s="5">
-        <v>-30.3</v>
-      </c>
-      <c r="D66" s="5">
-        <v>-40.26</v>
-      </c>
-      <c r="E66" s="7">
-        <v>-9.960000000000001</v>
-      </c>
-    </row>
-    <row r="67" spans="1:5">
-      <c r="A67" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B67" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C67" s="5">
-        <v>19.38</v>
-      </c>
-      <c r="D67" s="5">
-        <v>-45.44</v>
-      </c>
-      <c r="E67" s="7">
-        <v>-64.81999999999999</v>
-      </c>
-    </row>
-    <row r="68" spans="1:5">
-      <c r="A68" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="B68" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C68" s="5">
-        <v>-25.33</v>
-      </c>
-      <c r="D68" s="5">
-        <v>24.14</v>
-      </c>
-      <c r="E68" s="6">
-        <v>49.47</v>
-      </c>
-    </row>
-    <row r="69" spans="1:5">
-      <c r="A69" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="B69" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C69" s="5">
-        <v>-31.83</v>
-      </c>
-      <c r="D69" s="5">
-        <v>-43.95</v>
-      </c>
-      <c r="E69" s="7">
-        <v>-12.12</v>
-      </c>
-    </row>
-    <row r="70" spans="1:5">
-      <c r="A70" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="B70" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C70" s="5">
-        <v>1.04</v>
-      </c>
-      <c r="D70" s="5">
-        <v>-23.64</v>
-      </c>
-      <c r="E70" s="7">
-        <v>-24.68</v>
-      </c>
-    </row>
-    <row r="71" spans="1:5">
-      <c r="A71" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="B71" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C71" s="5">
-        <v>-14.48</v>
-      </c>
-      <c r="D71" s="5">
-        <v>-63.44</v>
-      </c>
-      <c r="E71" s="7">
-        <v>-48.96</v>
-      </c>
-    </row>
-    <row r="72" spans="1:5">
-      <c r="A72" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="B72" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C72" s="5">
-        <v>-30.04</v>
-      </c>
-      <c r="D72" s="5">
+      <c r="C73" s="6">
         <v>-54.62</v>
       </c>
-      <c r="E72" s="7">
-        <v>-24.58</v>
+      <c r="D73" s="6">
+        <v>-32.89</v>
+      </c>
+      <c r="E73" s="7">
+        <v>21.73</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A5:E5"/>
+    <mergeCell ref="A7:E7"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3129,61 +3219,61 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="28" customHeight="1">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="8" t="s">
-        <v>57</v>
-      </c>
-      <c r="C1" s="8" t="s">
-        <v>58</v>
-      </c>
-      <c r="D1" s="8" t="s">
-        <v>59</v>
-      </c>
-      <c r="E1" s="8" t="s">
-        <v>60</v>
-      </c>
-      <c r="F1" s="8" t="s">
-        <v>61</v>
-      </c>
-      <c r="G1" s="8" t="s">
-        <v>62</v>
-      </c>
-      <c r="H1" s="8" t="s">
-        <v>63</v>
-      </c>
-      <c r="I1" s="8" t="s">
-        <v>64</v>
+      <c r="B1" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="C1" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="D1" s="9" t="s">
+        <v>70</v>
+      </c>
+      <c r="E1" s="9" t="s">
+        <v>71</v>
+      </c>
+      <c r="F1" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="G1" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="H1" s="9" t="s">
+        <v>74</v>
+      </c>
+      <c r="I1" s="9" t="s">
+        <v>75</v>
       </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="9" t="s">
+      <c r="A2" s="10" t="s">
         <v>45</v>
       </c>
-      <c r="B2" s="10">
-        <v>37.44</v>
-      </c>
-      <c r="C2" s="11">
+      <c r="B2" s="11">
+        <v>42.4</v>
+      </c>
+      <c r="C2" s="12">
         <v>8</v>
       </c>
-      <c r="D2" s="10">
-        <v>43.6</v>
-      </c>
-      <c r="E2" s="10">
+      <c r="D2" s="11">
+        <v>43.3</v>
+      </c>
+      <c r="E2" s="11">
+        <v>25</v>
+      </c>
+      <c r="F2" s="11">
+        <v>-4.2</v>
+      </c>
+      <c r="G2" s="11">
+        <v>-9.699999999999999</v>
+      </c>
+      <c r="H2" s="11">
+        <v>56.1</v>
+      </c>
+      <c r="I2" s="11">
         <v>12.5</v>
-      </c>
-      <c r="F2" s="10">
-        <v>-4.3</v>
-      </c>
-      <c r="G2" s="10">
-        <v>-8.5</v>
-      </c>
-      <c r="H2" s="10">
-        <v>56.1</v>
-      </c>
-      <c r="I2" s="10">
-        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -3284,55 +3374,55 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8">
-      <c r="A1" s="12" t="s">
+      <c r="A1" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="B1" s="12" t="s">
+      <c r="B1" s="13" t="s">
         <v>43</v>
       </c>
-      <c r="C1" s="12" t="s">
+      <c r="C1" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="D1" s="12" t="s">
+      <c r="D1" s="13" t="s">
         <v>39</v>
       </c>
-      <c r="E1" s="12" t="s">
+      <c r="E1" s="13" t="s">
         <v>44</v>
       </c>
-      <c r="F1" s="12" t="s">
+      <c r="F1" s="13" t="s">
         <v>41</v>
       </c>
-      <c r="G1" s="12" t="s">
+      <c r="G1" s="13" t="s">
         <v>42</v>
       </c>
-      <c r="H1" s="12" t="s">
+      <c r="H1" s="13" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="2" spans="1:8">
-      <c r="A2" s="13">
-        <v>0.2995</v>
-      </c>
-      <c r="B2" s="13">
-        <v>0.1624</v>
-      </c>
-      <c r="C2" s="13">
-        <v>0.1468</v>
-      </c>
-      <c r="D2" s="13">
-        <v>0.1177</v>
-      </c>
-      <c r="E2" s="13">
-        <v>0.08400000000000001</v>
-      </c>
-      <c r="F2" s="13">
-        <v>0.0488</v>
-      </c>
-      <c r="G2" s="13">
-        <v>-0.277</v>
-      </c>
-      <c r="H2" s="13">
-        <v>-0.3134</v>
+      <c r="A2" s="14">
+        <v>0.3004</v>
+      </c>
+      <c r="B2" s="14">
+        <v>0.1588</v>
+      </c>
+      <c r="C2" s="14">
+        <v>0.1376</v>
+      </c>
+      <c r="D2" s="14">
+        <v>0.1128</v>
+      </c>
+      <c r="E2" s="14">
+        <v>0.07769999999999999</v>
+      </c>
+      <c r="F2" s="14">
+        <v>0.0322</v>
+      </c>
+      <c r="G2" s="14">
+        <v>-0.2842</v>
+      </c>
+      <c r="H2" s="14">
+        <v>-0.3226</v>
       </c>
     </row>
   </sheetData>
